--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F18F31-00D8-A94B-BF4D-DAA0F7A5D341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889439BF-21A5-5645-9B87-9323EE455D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9020" yWindow="780" windowWidth="25180" windowHeight="20000" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="9020" yWindow="780" windowWidth="25180" windowHeight="20000" activeTab="3" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -27882,17 +27882,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2508B5-8FE0-E24B-BF36-9D8165A8259C}">
   <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
@@ -27943,10 +27932,10 @@
         <v>0.38145000000000001</v>
       </c>
       <c r="F2">
-        <v>0.26274999999999998</v>
+        <v>0.2611</v>
       </c>
       <c r="G2">
-        <v>0.15840000000000001</v>
+        <v>0.15759999999999999</v>
       </c>
       <c r="H2" t="s">
         <v>384</v>
@@ -27978,7 +27967,7 @@
         <v>0.26255000000000001</v>
       </c>
       <c r="G3">
-        <v>0.15679999999999999</v>
+        <v>0.15645000000000001</v>
       </c>
       <c r="H3" t="s">
         <v>382</v>
@@ -28010,7 +27999,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1207</v>
+        <v>0.12035</v>
       </c>
       <c r="H4" t="s">
         <v>383</v>
@@ -28024,386 +28013,386 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>0.93464999999999998</v>
+        <v>0.98494999999999999</v>
       </c>
       <c r="C5">
-        <v>0.65325</v>
+        <v>0.75409999999999999</v>
       </c>
       <c r="D5">
-        <v>0.39510000000000001</v>
+        <v>0.52639999999999998</v>
       </c>
       <c r="E5">
-        <v>0.2009</v>
+        <v>0.26924999999999999</v>
       </c>
       <c r="F5">
-        <v>0.12745000000000001</v>
+        <v>0.13420000000000001</v>
       </c>
       <c r="G5">
-        <v>6.6199999999999995E-2</v>
+        <v>6.5500000000000003E-2</v>
       </c>
       <c r="H5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>22.732528951568561</v>
+        <v>21.027489150518061</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.98494999999999999</v>
+        <v>0.93464999999999998</v>
       </c>
       <c r="C6">
-        <v>0.75409999999999999</v>
+        <v>0.65325</v>
       </c>
       <c r="D6">
-        <v>0.52639999999999998</v>
+        <v>0.39510000000000001</v>
       </c>
       <c r="E6">
-        <v>0.26924999999999999</v>
+        <v>0.2009</v>
       </c>
       <c r="F6">
-        <v>0.13420000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="G6">
-        <v>6.6049999999999998E-2</v>
+        <v>6.5449999999999994E-2</v>
       </c>
       <c r="H6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6">
-        <v>21.027489150518061</v>
+        <v>22.732528951568561</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>0.99285000000000001</v>
+        <v>0.86114999999999997</v>
       </c>
       <c r="C7">
-        <v>0.86214999999999997</v>
+        <v>0.64124999999999999</v>
       </c>
       <c r="D7">
-        <v>0.55249999999999999</v>
+        <v>0.38114999999999999</v>
       </c>
       <c r="E7">
-        <v>0.29235</v>
+        <v>0.20635000000000001</v>
       </c>
       <c r="F7">
-        <v>0.13125000000000001</v>
+        <v>9.1399999999999995E-2</v>
       </c>
       <c r="G7">
-        <v>5.74E-2</v>
+        <v>4.1250000000000002E-2</v>
       </c>
       <c r="H7" t="s">
         <v>385</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>19.44163014249413</v>
+        <v>20.113161202374119</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>0.99285000000000001</v>
+        <v>0.96855000000000002</v>
       </c>
       <c r="C8">
-        <v>0.86214999999999997</v>
+        <v>0.66234999999999999</v>
       </c>
       <c r="D8">
-        <v>0.55249999999999999</v>
+        <v>0.40134999999999998</v>
       </c>
       <c r="E8">
-        <v>0.29235</v>
+        <v>0.17574999999999999</v>
       </c>
       <c r="F8">
-        <v>0.13125000000000001</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="G8">
-        <v>5.74E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="H8" t="s">
         <v>383</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>19.44163014249413</v>
+        <v>20.483780607843489</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>0.86114999999999997</v>
+        <v>0.90459999999999996</v>
       </c>
       <c r="C9">
-        <v>0.64124999999999999</v>
+        <v>0.52975000000000005</v>
       </c>
       <c r="D9">
-        <v>0.38114999999999999</v>
+        <v>0.25004999999999999</v>
       </c>
       <c r="E9">
-        <v>0.21045</v>
+        <v>0.1477</v>
       </c>
       <c r="F9">
-        <v>9.2999999999999999E-2</v>
+        <v>7.8950000000000006E-2</v>
       </c>
       <c r="G9">
-        <v>4.1549999999999997E-2</v>
+        <v>3.9949999999999999E-2</v>
       </c>
       <c r="H9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9">
-        <v>20.113161202374119</v>
+        <v>21.422678976942951</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>0.96855000000000002</v>
+        <v>0.92774999999999996</v>
       </c>
       <c r="C10">
-        <v>0.66234999999999999</v>
+        <v>0.66569999999999996</v>
       </c>
       <c r="D10">
-        <v>0.40134999999999998</v>
+        <v>0.37040000000000001</v>
       </c>
       <c r="E10">
-        <v>0.17574999999999999</v>
+        <v>0.20930000000000001</v>
       </c>
       <c r="F10">
-        <v>8.6400000000000005E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
       <c r="G10">
-        <v>4.1250000000000002E-2</v>
+        <v>3.9350000000000003E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>20.483780607843489</v>
+        <v>20.15253517001112</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>0.90459999999999996</v>
+        <v>0.90869999999999995</v>
       </c>
       <c r="C11">
-        <v>0.52975000000000005</v>
+        <v>0.5585</v>
       </c>
       <c r="D11">
-        <v>0.25004999999999999</v>
+        <v>0.28265000000000001</v>
       </c>
       <c r="E11">
-        <v>0.1477</v>
+        <v>0.12684999999999999</v>
       </c>
       <c r="F11">
-        <v>7.8950000000000006E-2</v>
+        <v>7.0300000000000001E-2</v>
       </c>
       <c r="G11">
-        <v>4.0149999999999998E-2</v>
+        <v>3.3550000000000003E-2</v>
       </c>
       <c r="H11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>21.422678976942951</v>
+        <v>20.818800425665561</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>0.90869999999999995</v>
+        <v>0.90969999999999995</v>
       </c>
       <c r="C12">
-        <v>0.5585</v>
+        <v>0.54154999999999998</v>
       </c>
       <c r="D12">
-        <v>0.28265000000000001</v>
+        <v>0.30375000000000002</v>
       </c>
       <c r="E12">
-        <v>0.12684999999999999</v>
+        <v>0.16885</v>
       </c>
       <c r="F12">
-        <v>7.1150000000000005E-2</v>
+        <v>7.2900000000000006E-2</v>
       </c>
       <c r="G12">
-        <v>3.3950000000000001E-2</v>
+        <v>3.1600000000000003E-2</v>
       </c>
       <c r="H12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>20.818800425665561</v>
+        <v>19.614167714334961</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13">
-        <v>0.90969999999999995</v>
+        <v>0.82965</v>
       </c>
       <c r="C13">
-        <v>0.54154999999999998</v>
+        <v>0.54759999999999998</v>
       </c>
       <c r="D13">
-        <v>0.31419999999999998</v>
+        <v>0.22889999999999999</v>
       </c>
       <c r="E13">
-        <v>0.17485000000000001</v>
+        <v>0.11395</v>
       </c>
       <c r="F13">
-        <v>7.535E-2</v>
+        <v>6.4750000000000002E-2</v>
       </c>
       <c r="G13">
-        <v>3.2649999999999998E-2</v>
+        <v>3.0949999999999998E-2</v>
       </c>
       <c r="H13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>19.614167714334961</v>
+        <v>20.61748149962505</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>386</v>
       </c>
       <c r="B14">
-        <v>0.82965</v>
+        <v>0.9708</v>
       </c>
       <c r="C14">
-        <v>0.54759999999999998</v>
+        <v>0.60335000000000005</v>
       </c>
       <c r="D14">
-        <v>0.22889999999999999</v>
+        <v>0.32505000000000001</v>
       </c>
       <c r="E14">
-        <v>0.11395</v>
+        <v>0.16785</v>
       </c>
       <c r="F14">
-        <v>6.54E-2</v>
+        <v>6.59E-2</v>
       </c>
       <c r="G14">
-        <v>3.1199999999999999E-2</v>
+        <v>2.7949999999999999E-2</v>
       </c>
       <c r="H14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>20.61748149962505</v>
+        <v>18.846137419885739</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>386</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>0.9708</v>
+        <v>0.87144999999999995</v>
       </c>
       <c r="C15">
-        <v>0.60335000000000005</v>
+        <v>0.44005</v>
       </c>
       <c r="D15">
-        <v>0.32505000000000001</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="E15">
-        <v>0.17165</v>
+        <v>0.11055</v>
       </c>
       <c r="F15">
-        <v>6.7000000000000004E-2</v>
+        <v>5.5500000000000001E-2</v>
       </c>
       <c r="G15">
-        <v>2.835E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="H15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>18.846137419885739</v>
+        <v>20.47719721517084</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>0.87144999999999995</v>
+        <v>0.89305000000000001</v>
       </c>
       <c r="C16">
-        <v>0.44005</v>
+        <v>0.60740000000000005</v>
       </c>
       <c r="D16">
-        <v>0.19600000000000001</v>
+        <v>0.31559999999999999</v>
       </c>
       <c r="E16">
-        <v>0.11055</v>
+        <v>0.12984999999999999</v>
       </c>
       <c r="F16">
-        <v>5.5500000000000001E-2</v>
+        <v>5.935E-2</v>
       </c>
       <c r="G16">
-        <v>2.615E-2</v>
+        <v>2.53E-2</v>
       </c>
       <c r="H16" t="s">
         <v>383</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>20.47719721517084</v>
+        <v>19.44163014249413</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -28417,16 +28406,16 @@
         <v>0.3458</v>
       </c>
       <c r="D17">
-        <v>0.18575</v>
+        <v>0.17885000000000001</v>
       </c>
       <c r="E17">
-        <v>9.4600000000000004E-2</v>
+        <v>9.1149999999999995E-2</v>
       </c>
       <c r="F17">
-        <v>3.6600000000000001E-2</v>
+        <v>3.5349999999999999E-2</v>
       </c>
       <c r="G17">
-        <v>1.4449999999999999E-2</v>
+        <v>1.3849999999999999E-2</v>
       </c>
       <c r="H17" t="s">
         <v>385</v>
@@ -28455,10 +28444,10 @@
         <v>6.0150000000000002E-2</v>
       </c>
       <c r="F18">
-        <v>3.1099999999999999E-2</v>
+        <v>3.065E-2</v>
       </c>
       <c r="G18">
-        <v>1.3849999999999999E-2</v>
+        <v>1.35E-2</v>
       </c>
       <c r="H18" t="s">
         <v>384</v>
@@ -28519,7 +28508,7 @@
         <v>4.4350000000000001E-2</v>
       </c>
       <c r="F20">
-        <v>2.2100000000000002E-2</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="G20">
         <v>7.9000000000000008E-3</v>
@@ -28586,7 +28575,7 @@
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="G22">
-        <v>4.6499999999999996E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="H22" t="s">
         <v>382</v>
@@ -28618,7 +28607,7 @@
         <v>1.255E-2</v>
       </c>
       <c r="G23">
-        <v>4.5999999999999999E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="H23" t="s">
         <v>383</v>
@@ -28650,7 +28639,7 @@
         <v>1.3350000000000001E-2</v>
       </c>
       <c r="G24">
-        <v>4.3E-3</v>
+        <v>4.2500000000000003E-3</v>
       </c>
       <c r="H24" t="s">
         <v>383</v>
@@ -28740,10 +28729,10 @@
         <v>8.9499999999999996E-2</v>
       </c>
       <c r="E27">
-        <v>3.6499999999999998E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="F27">
-        <v>1.095E-2</v>
+        <v>1.0749999999999999E-2</v>
       </c>
       <c r="G27">
         <v>3.15E-3</v>
@@ -28772,10 +28761,10 @@
         <v>8.5150000000000003E-2</v>
       </c>
       <c r="E28">
-        <v>3.3599999999999998E-2</v>
+        <v>3.3399999999999999E-2</v>
       </c>
       <c r="F28">
-        <v>1.1050000000000001E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="G28">
         <v>3.0999999999999999E-3</v>
@@ -28804,10 +28793,10 @@
         <v>9.8900000000000002E-2</v>
       </c>
       <c r="E29">
-        <v>3.5799999999999998E-2</v>
+        <v>3.4849999999999999E-2</v>
       </c>
       <c r="F29">
-        <v>9.4999999999999998E-3</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="G29">
         <v>2.65E-3</v>
@@ -28906,7 +28895,7 @@
         <v>8.8000000000000005E-3</v>
       </c>
       <c r="G32">
-        <v>2.0500000000000002E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="H32" t="s">
         <v>382</v>
@@ -28952,66 +28941,66 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B34">
-        <v>0.54164999999999996</v>
+        <v>0.52205000000000001</v>
       </c>
       <c r="C34">
-        <v>0.20455000000000001</v>
+        <v>0.1507</v>
       </c>
       <c r="D34">
-        <v>7.5200000000000003E-2</v>
+        <v>7.0349999999999996E-2</v>
       </c>
       <c r="E34">
-        <v>2.9049999999999999E-2</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="F34">
-        <v>6.7999999999999996E-3</v>
+        <v>5.3499999999999997E-3</v>
       </c>
       <c r="G34">
-        <v>1.6999999999999999E-3</v>
+        <v>1.65E-3</v>
       </c>
       <c r="H34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>14.298125666815221</v>
+        <v>13.72126897474508</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B35">
-        <v>0.52205000000000001</v>
+        <v>0.54164999999999996</v>
       </c>
       <c r="C35">
-        <v>0.1507</v>
+        <v>0.1925</v>
       </c>
       <c r="D35">
-        <v>7.0349999999999996E-2</v>
+        <v>7.0849999999999996E-2</v>
       </c>
       <c r="E35">
-        <v>2.2200000000000001E-2</v>
+        <v>2.7449999999999999E-2</v>
       </c>
       <c r="F35">
-        <v>5.3499999999999997E-3</v>
+        <v>6.1500000000000001E-3</v>
       </c>
       <c r="G35">
-        <v>1.65E-3</v>
+        <v>1.5499999999999999E-3</v>
       </c>
       <c r="H35" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J35">
-        <v>13.72126897474508</v>
+        <v>14.298125666815221</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -29048,98 +29037,98 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37">
-        <v>0.33989999999999998</v>
+        <v>0.60355000000000003</v>
       </c>
       <c r="C37">
-        <v>8.5750000000000007E-2</v>
+        <v>0.10555</v>
       </c>
       <c r="D37">
-        <v>2.75E-2</v>
+        <v>3.3399999999999999E-2</v>
       </c>
       <c r="E37">
-        <v>5.5500000000000002E-3</v>
+        <v>9.5499999999999995E-3</v>
       </c>
       <c r="F37">
-        <v>1.9E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G37">
-        <v>6.9999999999999999E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="H37" t="s">
         <v>384</v>
       </c>
       <c r="I37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>13.101532229438829</v>
+        <v>12.580793120111631</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B38">
-        <v>0.31109999999999999</v>
+        <v>0.33989999999999998</v>
       </c>
       <c r="C38">
-        <v>9.98E-2</v>
+        <v>8.5750000000000007E-2</v>
       </c>
       <c r="D38">
-        <v>3.5299999999999998E-2</v>
+        <v>2.75E-2</v>
       </c>
       <c r="E38">
-        <v>1.1599999999999999E-2</v>
+        <v>5.5500000000000002E-3</v>
       </c>
       <c r="F38">
-        <v>3.15E-3</v>
+        <v>1.8500000000000001E-3</v>
       </c>
       <c r="G38">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="H38" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I38">
         <v>10</v>
       </c>
       <c r="J38">
-        <v>12.18385037778865</v>
+        <v>13.101532229438829</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39">
-        <v>0.60355000000000003</v>
+        <v>0.31109999999999999</v>
       </c>
       <c r="C39">
-        <v>0.10555</v>
+        <v>9.98E-2</v>
       </c>
       <c r="D39">
-        <v>3.3399999999999999E-2</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="E39">
-        <v>9.5499999999999995E-3</v>
+        <v>1.09E-2</v>
       </c>
       <c r="F39">
-        <v>3.0500000000000002E-3</v>
+        <v>2.9499999999999999E-3</v>
       </c>
       <c r="G39">
-        <v>5.9999999999999995E-4</v>
+        <v>5.5000000000000003E-4</v>
       </c>
       <c r="H39" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>12.580793120111631</v>
+        <v>12.18385037778865</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -29214,16 +29203,16 @@
         <v>0.45834999999999998</v>
       </c>
       <c r="C42">
-        <v>0.13850000000000001</v>
+        <v>0.1295</v>
       </c>
       <c r="D42">
-        <v>4.2000000000000003E-2</v>
+        <v>3.9600000000000003E-2</v>
       </c>
       <c r="E42">
-        <v>1.18E-2</v>
+        <v>1.12E-2</v>
       </c>
       <c r="F42">
-        <v>2.4499999999999999E-3</v>
+        <v>2.3500000000000001E-3</v>
       </c>
       <c r="G42">
         <v>4.0000000000000002E-4</v>
@@ -29290,7 +29279,7 @@
         <v>1.8E-3</v>
       </c>
       <c r="G44">
-        <v>3.5E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="H44" t="s">
         <v>383</v>
@@ -29412,7 +29401,7 @@
         <v>1.095E-2</v>
       </c>
       <c r="E48">
-        <v>1.3500000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="F48">
         <v>1E-4</v>
@@ -29447,7 +29436,7 @@
         <v>6.4999999999999997E-4</v>
       </c>
       <c r="F49">
-        <v>1.4999999999999999E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="G49">
         <v>5.0000000000000002E-5</v>
@@ -29508,7 +29497,7 @@
         <v>9.2499999999999995E-3</v>
       </c>
       <c r="E51">
-        <v>1.15E-3</v>
+        <v>1.0499999999999999E-3</v>
       </c>
       <c r="F51">
         <v>1.4999999999999999E-4</v>
@@ -29595,13 +29584,13 @@
         <v>174</v>
       </c>
       <c r="B54">
-        <v>7.7899999999999997E-2</v>
+        <v>7.2249999999999995E-2</v>
       </c>
       <c r="C54">
-        <v>1.29E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="D54">
-        <v>1.3500000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="E54">
         <v>2.0000000000000001E-4</v>
@@ -29697,7 +29686,7 @@
         <v>1.285E-2</v>
       </c>
       <c r="D57">
-        <v>1.6999999999999999E-3</v>
+        <v>1.5499999999999999E-3</v>
       </c>
       <c r="E57">
         <v>1.4999999999999999E-4</v>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1D09FF-DA2C-7440-B590-CA1A7A1961E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CD2440-6142-A342-AB7C-1D86FB4870B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17260" yWindow="780" windowWidth="16660" windowHeight="20000" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="426">
   <si>
     <t>Team</t>
   </si>
@@ -1299,14 +1299,40 @@
   </si>
   <si>
     <t>2025-26</t>
+  </si>
+  <si>
+    <t>05/02/2025</t>
+  </si>
+  <si>
+    <t>04/25/2025</t>
+  </si>
+  <si>
+    <t>Closing Odds</t>
+  </si>
+  <si>
+    <t>Closing Line</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Position Line</t>
+  </si>
+  <si>
+    <t>Position Odds</t>
+  </si>
+  <si>
+    <t>03/08/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="[$-1009]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1381,7 +1407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1419,8 +1445,13 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -25687,7 +25718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49754F4-77C8-5D43-B0D7-0D09062FB370}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1"/>
@@ -25695,9 +25726,14 @@
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>388</v>
       </c>
@@ -25718,13 +25754,31 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C2" s="5" t="e">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <f>COUNTIF($C$6:$C$150,"W")</f>
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <f>COUNTIF($C$6:$C$150,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="5">
         <f>SUM(E6:E13)/SUM(D6:D13)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-1</v>
+      </c>
+      <c r="D2" s="15">
+        <f>AVERAGE(G6:G150)</f>
+        <v>-1.9985536081552357E-2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -25749,40 +25803,93 @@
       <c r="H5" s="1" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E6" s="1" t="e">
-        <f>IF(AB14="N",0,IF(AB14="L",-Z14,IF(I14&lt;0,Z14*(100/-I14),Z14*(I14/100)))/$D$2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F6" t="e">
+      <c r="I5" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="E6" s="1">
+        <f>IF(C6="P",0,IF(C6="L",-D6,IF(I6&lt;0,D6*(100/-I6),D6*(I6/100)))/1)</f>
+        <v>-0.94499999999999995</v>
+      </c>
+      <c r="F6" s="1">
         <f>E6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6">
+        <v>-0.94499999999999995</v>
+      </c>
+      <c r="G6" s="12">
+        <f>((K6-N6)*3.55%)+(M6-J6)</f>
+        <v>-1.9985536081552357E-2</v>
+      </c>
+      <c r="H6" s="12">
         <f>G6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F7" t="e">
+        <v>-1.9985536081552357E-2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-112</v>
+      </c>
+      <c r="J6" s="14">
+        <f>IF(I6&lt;0,I6/(I6-100),100/(I6+100))</f>
+        <v>0.52830188679245282</v>
+      </c>
+      <c r="K6" s="1">
+        <v>-14.5</v>
+      </c>
+      <c r="L6" s="1">
+        <v>-111</v>
+      </c>
+      <c r="M6" s="14">
+        <f>IF(L6&lt;0,L6/(L6-100),100/(L6+100))</f>
+        <v>0.52606635071090047</v>
+      </c>
+      <c r="N6" s="1">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F7" s="1">
         <f>E7+F6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H7" t="e">
+        <v>-0.94499999999999995</v>
+      </c>
+      <c r="H7" s="12">
         <f>AVERAGE($G$6:G7)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F8" t="e">
+        <v>-1.9985536081552357E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F8" s="1">
         <f>E8+F7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H8" t="e">
+        <v>-0.94499999999999995</v>
+      </c>
+      <c r="H8" s="12">
         <f>AVERAGE($G$6:G8)</f>
-        <v>#DIV/0!</v>
+        <v>-1.9985536081552357E-2</v>
       </c>
     </row>
   </sheetData>
@@ -25857,8 +25964,8 @@
       <c r="G2" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H2" s="14">
-        <v>46144</v>
+      <c r="H2" s="13" t="s">
+        <v>418</v>
       </c>
       <c r="K2" s="1">
         <f>IF(J2="W",(D2/100)*E2,IF(J2="",0,-E2))</f>
@@ -25887,8 +25994,8 @@
       <c r="G3" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H3" s="14">
-        <v>46137</v>
+      <c r="H3" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" ref="K3:K5" si="0">IF(J3="W",(D3/100)*E3,IF(J3="",0,-E3))</f>
@@ -25917,8 +26024,8 @@
       <c r="G4" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H4" s="14">
-        <v>46137</v>
+      <c r="H4" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="0"/>
@@ -25947,8 +26054,8 @@
       <c r="G5" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H5" s="14">
-        <v>46137</v>
+      <c r="H5" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="0"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A85F46-9474-7A4C-AA15-36B9104B1C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDEE71C-B12D-4340-9115-015D826B7F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="800" windowWidth="19480" windowHeight="20020" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -1256,9 +1256,6 @@
     <t>Stake</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Team Position</t>
   </si>
   <si>
@@ -1326,16 +1323,20 @@
   </si>
   <si>
     <t>East Tennessee Staet</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="[$-1009]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1424,9 +1425,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1455,6 +1453,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1491,28 +1492,28 @@
             <v>1</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Monmouth</v>
+            <v>Arizona State</v>
           </cell>
           <cell r="D2" t="str">
-            <v>Campbell</v>
+            <v>Baylor</v>
           </cell>
           <cell r="E2">
-            <v>2.0432430675448949</v>
+            <v>-1.948400156476102</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.51354256226679329</v>
+            <v>0.53862687213287508</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>-1.9600562945212782E-2</v>
+            <v>2.8287664980943369E-2</v>
           </cell>
           <cell r="J2">
-            <v>9.800400958915767E-2</v>
+            <v>2.9983757887917021E-2</v>
           </cell>
           <cell r="K2">
             <v>0</v>
@@ -1523,28 +1524,28 @@
             <v>2</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Wright State</v>
+            <v>Cincinnati</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Northern Kentucky</v>
+            <v>Utah</v>
           </cell>
           <cell r="E3">
-            <v>2.002938145514376</v>
+            <v>12.460122496131939</v>
           </cell>
           <cell r="F3" t="b">
             <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.58664912712271777</v>
+            <v>0.54796377476621294</v>
           </cell>
           <cell r="H3">
             <v>0</v>
           </cell>
           <cell r="I3">
-            <v>0.1199665154160976</v>
+            <v>4.611266091731564E-2</v>
           </cell>
           <cell r="J3">
-            <v>0.27159306156854079</v>
+            <v>0.49904533824960001</v>
           </cell>
           <cell r="K3">
             <v>0</v>
@@ -1555,28 +1556,28 @@
             <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Robert Morris</v>
+            <v>BYU</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Detroit</v>
+            <v>Kansas State</v>
           </cell>
           <cell r="E4">
-            <v>7.4135811496377304</v>
+            <v>12.183694358971669</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.55995251369068677</v>
+            <v>0.54171011788734458</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>6.9000253409493006E-2</v>
+            <v>3.4173861421294249E-2</v>
           </cell>
           <cell r="J4">
-            <v>0.37670483889389772</v>
+            <v>0.47803427310386359</v>
           </cell>
           <cell r="K4">
             <v>0</v>
@@ -1587,28 +1588,28 @@
             <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Montana</v>
+            <v>Colorado</v>
           </cell>
           <cell r="D5" t="str">
-            <v>Northern Colorado</v>
+            <v>Oklahoma State</v>
           </cell>
           <cell r="E5">
-            <v>-1.818746888235788</v>
+            <v>3.2558665647533802</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.56654248573940258</v>
+            <v>0.51883968777267175</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>8.158110913885952E-2</v>
+            <v>-9.4878687976265863E-3</v>
           </cell>
           <cell r="J5">
-            <v>0.1014855196192842</v>
+            <v>0.14946377226080959</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1619,28 +1620,28 @@
             <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Eastern Washington</v>
+            <v>Stanford</v>
           </cell>
           <cell r="D6" t="str">
-            <v>Weber State</v>
+            <v>Pittsburgh</v>
           </cell>
           <cell r="E6">
-            <v>3.6178287776241209</v>
+            <v>8.4596682351243899</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.5154010489200318</v>
+            <v>0.58559547842153947</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>-1.6052542970848349E-2</v>
+            <v>0.11795500425930271</v>
           </cell>
           <cell r="J6">
-            <v>0.15283797055300019</v>
+            <v>0.4662316790861335</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1651,28 +1652,28 @@
             <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Alabama State</v>
+            <v>SMU</v>
           </cell>
           <cell r="D7" t="str">
-            <v>Alcorn State</v>
+            <v>Syracuse</v>
           </cell>
           <cell r="E7">
-            <v>9.042313354498468</v>
+            <v>8.3198683321756555</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.56312403634473363</v>
+            <v>0.59377581101083676</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>7.5054978476309708E-2</v>
+            <v>0.1335720028388703</v>
           </cell>
           <cell r="J7">
-            <v>0.43309663535377269</v>
+            <v>0.48081905285959958</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1683,28 +1684,28 @@
             <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Grambling</v>
+            <v>Virginia Tech</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Mississippi Valley State</v>
+            <v>Wake Forest</v>
           </cell>
           <cell r="E8">
-            <v>17.223799225115261</v>
+            <v>1.9546377737059979</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.6000335330277925</v>
+            <v>0.5135953705772307</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0.14551856305305841</v>
+            <v>-1.949974707983226E-2</v>
           </cell>
           <cell r="J8">
-            <v>0.70847310826383803</v>
+            <v>3.0262618484464428E-2</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1715,31 +1716,31 @@
             <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Texas A&amp;M-CC</v>
+            <v>Oregon</v>
           </cell>
           <cell r="D9" t="str">
-            <v>New Orleans</v>
+            <v>Maryland</v>
           </cell>
           <cell r="E9">
-            <v>7.3868951200287372</v>
+            <v>6.9551514513020471</v>
           </cell>
           <cell r="F9" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.62741830170284763</v>
+            <v>0.58548545632970861</v>
           </cell>
           <cell r="H9">
-            <v>5.7031373430392038E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I9">
-            <v>0.19779857597816369</v>
+            <v>0.1177449620839892</v>
           </cell>
           <cell r="J9">
-            <v>0.53202678492272726</v>
+            <v>0.42137975310016901</v>
           </cell>
           <cell r="K9">
-            <v>1.1132524093612526</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="10">
@@ -1747,31 +1748,31 @@
             <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Campbell</v>
+            <v>Northwestern</v>
           </cell>
           <cell r="D10" t="str">
-            <v>Monmouth</v>
+            <v>Penn State</v>
           </cell>
           <cell r="E10">
-            <v>3.3775609745382869</v>
+            <v>9.683526089681564</v>
           </cell>
           <cell r="F10" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.61975887194670809</v>
+            <v>0.58903913608620428</v>
           </cell>
           <cell r="H10">
-            <v>5.0597452435234738E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I10">
-            <v>0.1831760282618973</v>
+            <v>0.1245292598009355</v>
           </cell>
           <cell r="J10">
-            <v>0.39314315209501782</v>
+            <v>0.51006700691313822</v>
           </cell>
           <cell r="K10">
-            <v>0.98766227153578212</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="11">
@@ -1779,28 +1780,28 @@
             <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Northern Kentucky</v>
+            <v>Florida International</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Wright State</v>
+            <v>Missouri State</v>
           </cell>
           <cell r="E11">
-            <v>2.1555175358168048</v>
+            <v>4.2303699993993691</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.51634003245744553</v>
+            <v>0.58000181602224798</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>-1.4259938035785791E-2</v>
+            <v>0.1072761942242917</v>
           </cell>
           <cell r="J11">
-            <v>0.1082859437067244</v>
+            <v>0.32538020573530968</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1811,28 +1812,28 @@
             <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Detroit</v>
+            <v>Jacksonville State</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Robert Morris</v>
+            <v>New Mexico State</v>
           </cell>
           <cell r="E12">
-            <v>-2.5930097206063221</v>
+            <v>0.83786939361755797</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.55979003176379438</v>
+            <v>0.54572466438895106</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>6.8690060639971184E-2</v>
+            <v>4.1837995651633868E-2</v>
           </cell>
           <cell r="J12">
-            <v>6.0302765106299838E-2</v>
+            <v>0.13640142191527169</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1843,28 +1844,28 @@
             <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Northern Colorado</v>
+            <v>Merrimack</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Montana</v>
+            <v>Siena</v>
           </cell>
           <cell r="E13">
-            <v>6.3687545752816437</v>
+            <v>6.2628557313104043</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.54648960320793782</v>
+            <v>0.56854792118969855</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>4.3298333396972262E-2</v>
+            <v>8.5409667725788174E-2</v>
           </cell>
           <cell r="J13">
-            <v>0.31324381532624579</v>
+            <v>0.36133006647441002</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1875,31 +1876,31 @@
             <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Weber State</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Eastern Washington</v>
+            <v>Alcorn State</v>
           </cell>
           <cell r="E14">
-            <v>1.647409309030833</v>
+            <v>10.491972175727399</v>
           </cell>
           <cell r="F14" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.6142690048404108</v>
+            <v>0.60468002780131946</v>
           </cell>
           <cell r="H14">
-            <v>4.5985964065945087E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I14">
-            <v>0.17269537287714801</v>
+            <v>0.1543891439843372</v>
           </cell>
           <cell r="J14">
-            <v>0.32689113933500502</v>
+            <v>0.56686463363651218</v>
           </cell>
           <cell r="K14">
-            <v>0.89764601856724813</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="15">
@@ -1907,28 +1908,28 @@
             <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Alcorn State</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="D15" t="str">
-            <v>Alabama State</v>
+            <v>Mercyhurst</v>
           </cell>
           <cell r="E15">
-            <v>-4.4739352717455549</v>
+            <v>8.5844158439926268</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.55038299650398148</v>
+            <v>0.55182596241363058</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>5.0731175143964642E-2</v>
+            <v>5.348592824420384E-2</v>
           </cell>
           <cell r="J15">
-            <v>2.2854359884752599E-2</v>
+            <v>0.39373745179787079</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -1939,28 +1940,28 @@
             <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Mississippi Valley State</v>
+            <v>UMBC</v>
           </cell>
           <cell r="D16" t="str">
-            <v>Grambling</v>
+            <v>UMass Lowell</v>
           </cell>
           <cell r="E16">
-            <v>-11.5565125315274</v>
+            <v>8.0265437577454151</v>
           </cell>
           <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.52351118874843883</v>
+            <v>0.51312641610171039</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>-5.6954875298037555E-4</v>
+            <v>-2.0395023805825589E-2</v>
           </cell>
           <cell r="J16">
-            <v>0.31215439863861622</v>
+            <v>0.28716124389816622</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -1971,28 +1972,28 @@
             <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>New Orleans</v>
+            <v>Vermont</v>
           </cell>
           <cell r="D17" t="str">
-            <v>Texas A&amp;M-CC</v>
+            <v>NJIT</v>
           </cell>
           <cell r="E17">
-            <v>-1.5734941648667511</v>
+            <v>11.8146673754801</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.51063319135944385</v>
+            <v>0.50462096040657378</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>-2.5154816495607139E-2</v>
+            <v>-3.6632711951086361E-2</v>
           </cell>
           <cell r="J17">
-            <v>2.5108865743573849E-2</v>
+            <v>0.36368121692904481</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2002,23 +2003,29 @@
           <cell r="B18">
             <v>17</v>
           </cell>
+          <cell r="C18" t="str">
+            <v>Baylor</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>Arizona State</v>
+          </cell>
           <cell r="E18">
-            <v>0</v>
-          </cell>
-          <cell r="F18">
+            <v>5.8529881441836533</v>
+          </cell>
+          <cell r="F18" t="b">
             <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0</v>
+            <v>0.55845836323863085</v>
           </cell>
           <cell r="H18">
             <v>0</v>
           </cell>
           <cell r="I18">
-            <v>0</v>
+            <v>6.6147784364658957E-2</v>
           </cell>
           <cell r="J18">
-            <v>0</v>
+            <v>0.32516894849077371</v>
           </cell>
           <cell r="K18">
             <v>0</v>
@@ -2028,23 +2035,29 @@
           <cell r="B19">
             <v>18</v>
           </cell>
+          <cell r="C19" t="str">
+            <v>Utah</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>Cincinnati</v>
+          </cell>
           <cell r="E19">
-            <v>0</v>
-          </cell>
-          <cell r="F19">
+            <v>-6.1747428483275488</v>
+          </cell>
+          <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0</v>
+            <v>0.60654625696172393</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>0</v>
+            <v>0.1579519451087458</v>
           </cell>
           <cell r="J19">
-            <v>0</v>
+            <v>5.968509949904921E-2</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2054,23 +2067,29 @@
           <cell r="B20">
             <v>19</v>
           </cell>
+          <cell r="C20" t="str">
+            <v>Kansas State</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>BYU</v>
+          </cell>
           <cell r="E20">
-            <v>0</v>
-          </cell>
-          <cell r="F20">
+            <v>-7.5050081796346424</v>
+          </cell>
+          <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0</v>
+            <v>0.57424298700519538</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>0</v>
+            <v>9.6282066100827568E-2</v>
           </cell>
           <cell r="J20">
-            <v>0</v>
+            <v>6.2414236764861568E-2</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2080,23 +2099,29 @@
           <cell r="B21">
             <v>20</v>
           </cell>
+          <cell r="C21" t="str">
+            <v>Oklahoma State</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>Colorado</v>
+          </cell>
           <cell r="E21">
-            <v>0</v>
-          </cell>
-          <cell r="F21">
+            <v>0.24750251499965439</v>
+          </cell>
+          <cell r="F21" t="b">
             <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0</v>
+            <v>0.56817073958757003</v>
           </cell>
           <cell r="H21">
             <v>0</v>
           </cell>
           <cell r="I21">
-            <v>0</v>
+            <v>8.4689593758088266E-2</v>
           </cell>
           <cell r="J21">
-            <v>0</v>
+            <v>0.17150422950300201</v>
           </cell>
           <cell r="K21">
             <v>0</v>
@@ -2106,23 +2131,29 @@
           <cell r="B22">
             <v>21</v>
           </cell>
+          <cell r="C22" t="str">
+            <v>Pittsburgh</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>Stanford</v>
+          </cell>
           <cell r="E22">
-            <v>0</v>
-          </cell>
-          <cell r="F22">
+            <v>-2.369386519382958</v>
+          </cell>
+          <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0</v>
+            <v>0.56529711966207874</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>0</v>
+            <v>7.9203592082150331E-2</v>
           </cell>
           <cell r="J22">
-            <v>0</v>
+            <v>8.0810015817737613E-2</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2132,23 +2163,29 @@
           <cell r="B23">
             <v>22</v>
           </cell>
+          <cell r="C23" t="str">
+            <v>Syracuse</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>SMU</v>
+          </cell>
           <cell r="E23">
-            <v>0</v>
-          </cell>
-          <cell r="F23">
+            <v>-3.1474854922138928</v>
+          </cell>
+          <cell r="F23" t="b">
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0</v>
+            <v>0.53368333152480207</v>
           </cell>
           <cell r="H23">
             <v>0</v>
           </cell>
           <cell r="I23">
-            <v>0</v>
+            <v>1.8849996547349479E-2</v>
           </cell>
           <cell r="J23">
-            <v>0</v>
+            <v>2.042621106830644E-2</v>
           </cell>
           <cell r="K23">
             <v>0</v>
@@ -2158,49 +2195,61 @@
           <cell r="B24">
             <v>23</v>
           </cell>
+          <cell r="C24" t="str">
+            <v>Wake Forest</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>Virginia Tech</v>
+          </cell>
           <cell r="E24">
-            <v>0</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
+            <v>2.3151298429323668</v>
+          </cell>
+          <cell r="F24" t="b">
+            <v>1</v>
           </cell>
           <cell r="G24">
-            <v>0</v>
+            <v>0.61827201709420276</v>
           </cell>
           <cell r="H24">
-            <v>0</v>
+            <v>4.9348494359130413E-2</v>
           </cell>
           <cell r="I24">
-            <v>0</v>
+            <v>0.18033748717984169</v>
           </cell>
           <cell r="J24">
-            <v>0</v>
+            <v>0.35714032797427958</v>
           </cell>
           <cell r="K24">
-            <v>0</v>
+            <v>0.96328260989022563</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
             <v>24</v>
           </cell>
+          <cell r="C25" t="str">
+            <v>Maryland</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>Oregon</v>
+          </cell>
           <cell r="E25">
-            <v>0</v>
-          </cell>
-          <cell r="F25">
+            <v>-0.95128866771280784</v>
+          </cell>
+          <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0</v>
+            <v>0.56328155666280744</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>0</v>
+            <v>7.5355699083541561E-2</v>
           </cell>
           <cell r="J25">
-            <v>0</v>
+            <v>0.1213909929186644</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2210,23 +2259,29 @@
           <cell r="B26">
             <v>25</v>
           </cell>
+          <cell r="C26" t="str">
+            <v>Penn State</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>Northwestern</v>
+          </cell>
           <cell r="E26">
-            <v>0</v>
-          </cell>
-          <cell r="F26">
+            <v>-2.9603916891163822</v>
+          </cell>
+          <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0</v>
+            <v>0.57533584307907415</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>0</v>
+            <v>9.8368427696414296E-2</v>
           </cell>
           <cell r="J26">
-            <v>0</v>
+            <v>8.6217555694112991E-2</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2236,23 +2291,29 @@
           <cell r="B27">
             <v>26</v>
           </cell>
+          <cell r="C27" t="str">
+            <v>Missouri State</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>Florida International</v>
+          </cell>
           <cell r="E27">
-            <v>0</v>
-          </cell>
-          <cell r="F27">
+            <v>1.614328123845522</v>
+          </cell>
+          <cell r="F27" t="b">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0</v>
+            <v>0.56489648017119498</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>0</v>
+            <v>7.8438734872281368E-2</v>
           </cell>
           <cell r="J27">
-            <v>0</v>
+            <v>0.20713966370299841</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2262,23 +2323,29 @@
           <cell r="B28">
             <v>27</v>
           </cell>
+          <cell r="C28" t="str">
+            <v>New Mexico State</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>Jacksonville State</v>
+          </cell>
           <cell r="E28">
-            <v>0</v>
-          </cell>
-          <cell r="F28">
+            <v>4.7906254510700297</v>
+          </cell>
+          <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0</v>
+            <v>0.59363828082218861</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>0</v>
+            <v>0.1333094452059965</v>
           </cell>
           <cell r="J28">
-            <v>0</v>
+            <v>0.37470112295373909</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2288,23 +2355,29 @@
           <cell r="B29">
             <v>28</v>
           </cell>
+          <cell r="C29" t="str">
+            <v>Siena</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>Merrimack</v>
+          </cell>
           <cell r="E29">
-            <v>0</v>
-          </cell>
-          <cell r="F29">
+            <v>-0.32934654469103197</v>
+          </cell>
+          <cell r="F29" t="b">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0</v>
+            <v>0.57854234377963076</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>0</v>
+            <v>0.10448992903384061</v>
           </cell>
           <cell r="J29">
-            <v>0</v>
+            <v>0.1781676262894791</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2314,23 +2387,29 @@
           <cell r="B30">
             <v>29</v>
           </cell>
+          <cell r="C30" t="str">
+            <v>Alcorn State</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>Prairie View A&amp;M</v>
+          </cell>
           <cell r="E30">
-            <v>0</v>
-          </cell>
-          <cell r="F30">
+            <v>-5.0617994389838499</v>
+          </cell>
+          <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0</v>
+            <v>0.52337959327652317</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>0</v>
+            <v>-8.2077647209211069E-4</v>
           </cell>
           <cell r="J30">
-            <v>0</v>
+            <v>0.1065721497848801</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2340,23 +2419,29 @@
           <cell r="B31">
             <v>30</v>
           </cell>
+          <cell r="C31" t="str">
+            <v>Mercyhurst</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>Long Island University</v>
+          </cell>
           <cell r="E31">
-            <v>0</v>
-          </cell>
-          <cell r="F31">
+            <v>-3.3314425511176271</v>
+          </cell>
+          <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0</v>
+            <v>0.57849109765578277</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>0</v>
+            <v>0.1043920955246762</v>
           </cell>
           <cell r="J31">
-            <v>0</v>
+            <v>8.1996576802844834E-2</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2366,23 +2451,29 @@
           <cell r="B32">
             <v>31</v>
           </cell>
+          <cell r="C32" t="str">
+            <v>UMass Lowell</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>UMBC</v>
+          </cell>
           <cell r="E32">
-            <v>0</v>
-          </cell>
-          <cell r="F32">
+            <v>-2.693936053267902</v>
+          </cell>
+          <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0</v>
+            <v>0.61805595868083574</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>0</v>
+            <v>0.17992501202705011</v>
           </cell>
           <cell r="J32">
-            <v>0</v>
+            <v>0.1995792506513199</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2392,23 +2483,29 @@
           <cell r="B33">
             <v>32</v>
           </cell>
+          <cell r="C33" t="str">
+            <v>NJIT</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>Vermont</v>
+          </cell>
           <cell r="E33">
-            <v>0</v>
-          </cell>
-          <cell r="F33">
+            <v>-6.7230657392074322</v>
+          </cell>
+          <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0</v>
+            <v>0.6292276267557454</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>0</v>
+            <v>0.20125274198824131</v>
           </cell>
           <cell r="J33">
-            <v>0</v>
+            <v>9.8800127547925554E-2</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -8578,73 +8675,73 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>Monmouth</v>
+            <v>Arizona State</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Campbell</v>
+            <v>Baylor</v>
           </cell>
           <cell r="D2">
-            <v>-2.7998693866967312</v>
+            <v>11.676210374037039</v>
           </cell>
           <cell r="E2">
-            <v>99.327473229982417</v>
+            <v>97.795147404122091</v>
           </cell>
           <cell r="F2">
-            <v>101.71037425999569</v>
+            <v>95.965512535699588</v>
           </cell>
           <cell r="G2">
-            <v>0.49972632731253419</v>
+            <v>0.50599315068493156</v>
           </cell>
           <cell r="H2">
-            <v>67.424516129032256</v>
+            <v>69.834666666666664</v>
           </cell>
           <cell r="I2">
-            <v>58.935483870967744</v>
+            <v>58.4</v>
           </cell>
           <cell r="J2">
-            <v>19</v>
+            <v>23.033333333333335</v>
           </cell>
           <cell r="K2">
-            <v>11.35483870967742</v>
+            <v>10.366666666666667</v>
           </cell>
           <cell r="L2">
-            <v>11.483870967741936</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="M2">
-            <v>3.1</v>
+            <v>0</v>
           </cell>
           <cell r="N2">
-            <v>1.1551322574216147</v>
+            <v>13.997941784567479</v>
           </cell>
           <cell r="O2">
-            <v>99.959130560508953</v>
+            <v>101.13544029968871</v>
           </cell>
           <cell r="P2">
-            <v>102.06367103779606</v>
+            <v>105.02424567854018</v>
           </cell>
           <cell r="Q2">
-            <v>0.51521511017838406</v>
+            <v>0.5503812636165577</v>
           </cell>
           <cell r="R2">
-            <v>70.135000000000005</v>
+            <v>69.473333333333329</v>
           </cell>
           <cell r="S2">
-            <v>59.5625</v>
+            <v>61.2</v>
           </cell>
           <cell r="T2">
-            <v>25.09375</v>
+            <v>21.833333333333332</v>
           </cell>
           <cell r="U2">
-            <v>12.625</v>
+            <v>12.633333333333333</v>
           </cell>
           <cell r="V2">
-            <v>12.15625</v>
+            <v>11.3</v>
           </cell>
           <cell r="W2">
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-1.5</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="3">
@@ -8652,73 +8749,73 @@
             <v>2</v>
           </cell>
           <cell r="B3" t="str">
-            <v>Wright State</v>
+            <v>Cincinnati</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Northern Kentucky</v>
+            <v>Utah</v>
           </cell>
           <cell r="D3">
-            <v>2.6723435907353315</v>
+            <v>13.013886487974281</v>
           </cell>
           <cell r="E3">
-            <v>99.481742279448753</v>
+            <v>98.819278377666578</v>
           </cell>
           <cell r="F3">
-            <v>101.22113929223009</v>
+            <v>97.225851270115911</v>
           </cell>
           <cell r="G3">
-            <v>0.54976051091005851</v>
+            <v>0.50693703308431159</v>
           </cell>
           <cell r="H3">
-            <v>68.23</v>
+            <v>68.820645161290329</v>
           </cell>
           <cell r="I3">
-            <v>58.71875</v>
+            <v>60.451612903225808</v>
           </cell>
           <cell r="J3">
-            <v>21.6875</v>
+            <v>17.774193548387096</v>
           </cell>
           <cell r="K3">
-            <v>11.375</v>
+            <v>11.161290322580646</v>
           </cell>
           <cell r="L3">
-            <v>11.34375</v>
+            <v>11.709677419354838</v>
           </cell>
           <cell r="M3">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="N3">
-            <v>1.38975763828766</v>
+            <v>6.9075926290659249</v>
           </cell>
           <cell r="O3">
-            <v>99.14590747330962</v>
+            <v>97.474667091092371</v>
           </cell>
           <cell r="P3">
-            <v>98.998456911194168</v>
+            <v>100.13185770788762</v>
           </cell>
           <cell r="Q3">
-            <v>0.54238578680203042</v>
+            <v>0.52409972299168972</v>
           </cell>
           <cell r="R3">
-            <v>71.575000000000003</v>
+            <v>67.935483870967744</v>
           </cell>
           <cell r="S3">
-            <v>61.5625</v>
+            <v>58.225806451612904</v>
           </cell>
           <cell r="T3">
-            <v>22.1875</v>
+            <v>18.548387096774192</v>
           </cell>
           <cell r="U3">
-            <v>11.71875</v>
+            <v>10</v>
           </cell>
           <cell r="V3">
-            <v>11.96875</v>
+            <v>11.548387096774194</v>
           </cell>
           <cell r="W3">
             <v>0</v>
           </cell>
           <cell r="X3">
-            <v>1.5</v>
+            <v>-10.5</v>
           </cell>
         </row>
         <row r="4">
@@ -8726,73 +8823,73 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>Robert Morris</v>
+            <v>BYU</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Detroit</v>
+            <v>Kansas State</v>
           </cell>
           <cell r="D4">
-            <v>0.91783713669028455</v>
+            <v>16.600220651643195</v>
           </cell>
           <cell r="E4">
-            <v>100.1603136571553</v>
+            <v>101.6412542424396</v>
           </cell>
           <cell r="F4">
-            <v>104.21574979976155</v>
+            <v>101.90007741800223</v>
           </cell>
           <cell r="G4">
-            <v>0.54870828848223896</v>
+            <v>0.54686690833764884</v>
           </cell>
           <cell r="H4">
-            <v>66.807741935483861</v>
+            <v>70.129032258064512</v>
           </cell>
           <cell r="I4">
-            <v>59.935483870967744</v>
+            <v>62.29032258064516</v>
           </cell>
           <cell r="J4">
-            <v>16.64516129032258</v>
+            <v>21.774193548387096</v>
           </cell>
           <cell r="K4">
-            <v>13</v>
+            <v>12.32258064516129</v>
           </cell>
           <cell r="L4">
-            <v>12.548387096774194</v>
+            <v>10.580645161290322</v>
           </cell>
           <cell r="M4">
-            <v>2.8</v>
+            <v>0</v>
           </cell>
           <cell r="N4">
-            <v>-1.1374478645185355</v>
+            <v>8.6039512771540601</v>
           </cell>
           <cell r="O4">
-            <v>100.48054895750857</v>
+            <v>96.575607312797402</v>
           </cell>
           <cell r="P4">
-            <v>96.746768196564886</v>
+            <v>98.325303696839384</v>
           </cell>
           <cell r="Q4">
-            <v>0.50298913043478266</v>
+            <v>0.53056546102903723</v>
           </cell>
           <cell r="R4">
-            <v>69.787999999999997</v>
+            <v>73.165161290322573</v>
           </cell>
           <cell r="S4">
-            <v>61.333333333333336</v>
+            <v>63.322580645161288</v>
           </cell>
           <cell r="T4">
-            <v>21.033333333333335</v>
+            <v>16.870967741935484</v>
           </cell>
           <cell r="U4">
-            <v>12.2</v>
+            <v>10.451612903225806</v>
           </cell>
           <cell r="V4">
-            <v>11.4</v>
+            <v>12.870967741935484</v>
           </cell>
           <cell r="W4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-5</v>
+            <v>-10.5</v>
           </cell>
         </row>
         <row r="5">
@@ -8800,73 +8897,73 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>Montana</v>
+            <v>Colorado</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Northern Colorado</v>
+            <v>Oklahoma State</v>
           </cell>
           <cell r="D5">
-            <v>2.5375154961101685</v>
+            <v>9.8189534899998705</v>
           </cell>
           <cell r="E5">
-            <v>91.063188911928393</v>
+            <v>98.962524252016749</v>
           </cell>
           <cell r="F5">
-            <v>94.640063686767107</v>
+            <v>102.28356507324483</v>
           </cell>
           <cell r="G5">
-            <v>0.55520504731861198</v>
+            <v>0.53135135135135136</v>
           </cell>
           <cell r="H5">
-            <v>70.201379310344819</v>
+            <v>69.5741935483871</v>
           </cell>
           <cell r="I5">
-            <v>54.655172413793103</v>
+            <v>59.677419354838712</v>
           </cell>
           <cell r="J5">
-            <v>20.206896551724139</v>
+            <v>21.612903225806452</v>
           </cell>
           <cell r="K5">
-            <v>7.1034482758620694</v>
+            <v>9.9677419354838701</v>
           </cell>
           <cell r="L5">
-            <v>13.758620689655173</v>
+            <v>10.35483870967742</v>
           </cell>
           <cell r="M5">
-            <v>2.9</v>
+            <v>0</v>
           </cell>
           <cell r="N5">
-            <v>3.7888532794728649</v>
+            <v>10.400184605664766</v>
           </cell>
           <cell r="O5">
-            <v>97.300800773902282</v>
+            <v>98.362133308139249</v>
           </cell>
           <cell r="P5">
-            <v>96.601572065948844</v>
+            <v>100.64400740314213</v>
           </cell>
           <cell r="Q5">
-            <v>0.56747967479674799</v>
+            <v>0.52157164869029271</v>
           </cell>
           <cell r="R5">
-            <v>70.438666666666663</v>
+            <v>74.596129032258062</v>
           </cell>
           <cell r="S5">
-            <v>61.5</v>
+            <v>62.806451612903224</v>
           </cell>
           <cell r="T5">
-            <v>16.3</v>
+            <v>24.741935483870968</v>
           </cell>
           <cell r="U5">
-            <v>9.4333333333333336</v>
+            <v>11.32258064516129</v>
           </cell>
           <cell r="V5">
-            <v>11.2</v>
+            <v>12.225806451612904</v>
           </cell>
           <cell r="W5">
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>4.5</v>
+            <v>-2.5</v>
           </cell>
         </row>
         <row r="6">
@@ -8874,73 +8971,73 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>Eastern Washington</v>
+            <v>Stanford</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Weber State</v>
+            <v>Pittsburgh</v>
           </cell>
           <cell r="D6">
-            <v>1.6745596773049956</v>
+            <v>11.634002216606197</v>
           </cell>
           <cell r="E6">
-            <v>96.45410010649627</v>
+            <v>99.979621987875078</v>
           </cell>
           <cell r="F6">
-            <v>94.243332897672701</v>
+            <v>88.78433637984817</v>
           </cell>
           <cell r="G6">
-            <v>0.54709936817920735</v>
+            <v>0.51572494669509594</v>
           </cell>
           <cell r="H6">
-            <v>69.375999999999991</v>
+            <v>67.5</v>
           </cell>
           <cell r="I6">
-            <v>58.033333333333331</v>
+            <v>58.625</v>
           </cell>
           <cell r="J6">
-            <v>20.399999999999999</v>
+            <v>21.09375</v>
           </cell>
           <cell r="K6">
-            <v>10.066666666666666</v>
+            <v>11.21875</v>
           </cell>
           <cell r="L6">
-            <v>12.433333333333334</v>
+            <v>10.8125</v>
           </cell>
           <cell r="M6">
-            <v>2.2999999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="N6">
-            <v>2.6674007845525285</v>
+            <v>5.1655310926871802</v>
           </cell>
           <cell r="O6">
-            <v>99.879254581857381</v>
+            <v>100.13985858248427</v>
           </cell>
           <cell r="P6">
-            <v>96.950453466976299</v>
+            <v>104.42105719874289</v>
           </cell>
           <cell r="Q6">
-            <v>0.52559912854030499</v>
+            <v>0.50756726457399104</v>
           </cell>
           <cell r="R6">
-            <v>71.055999999999983</v>
+            <v>64.803870967741929</v>
           </cell>
           <cell r="S6">
-            <v>61.2</v>
+            <v>57.548387096774192</v>
           </cell>
           <cell r="T6">
-            <v>23.233333333333334</v>
+            <v>17.516129032258064</v>
           </cell>
           <cell r="U6">
-            <v>11.7</v>
+            <v>11.774193548387096</v>
           </cell>
           <cell r="V6">
-            <v>11.333333333333334</v>
+            <v>11.32258064516129</v>
           </cell>
           <cell r="W6">
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>-3</v>
+            <v>-5</v>
           </cell>
         </row>
         <row r="7">
@@ -8948,73 +9045,73 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>Alabama State</v>
+            <v>SMU</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Alcorn State</v>
+            <v>Syracuse</v>
           </cell>
           <cell r="D7">
-            <v>-12.610080468302302</v>
+            <v>13.536513873870378</v>
           </cell>
           <cell r="E7">
-            <v>98.54414125200644</v>
+            <v>100.42773804088671</v>
           </cell>
           <cell r="F7">
-            <v>94.651073379053571</v>
+            <v>99.400324400971755</v>
           </cell>
           <cell r="G7">
-            <v>0.48040254237288138</v>
+            <v>0.55947476828012355</v>
           </cell>
           <cell r="H7">
-            <v>71.069677419354832</v>
+            <v>70.745806451612893</v>
           </cell>
           <cell r="I7">
-            <v>60.903225806451616</v>
+            <v>62.645161290322584</v>
           </cell>
           <cell r="J7">
-            <v>21.419354838709676</v>
+            <v>20.096774193548388</v>
           </cell>
           <cell r="K7">
-            <v>12.451612903225806</v>
+            <v>12.096774193548388</v>
           </cell>
           <cell r="L7">
-            <v>13.193548387096774</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="M7">
-            <v>2.2999999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="N7">
-            <v>-19.948242350647938</v>
+            <v>5.9340551424645511</v>
           </cell>
           <cell r="O7">
-            <v>94.015466724757644</v>
+            <v>98.460835237897356</v>
           </cell>
           <cell r="P7">
-            <v>99.142194717936277</v>
+            <v>105.23886558606168</v>
           </cell>
           <cell r="Q7">
-            <v>0.47871720116618077</v>
+            <v>0.52649006622516559</v>
           </cell>
           <cell r="R7">
-            <v>68.99733333333333</v>
+            <v>68.48</v>
           </cell>
           <cell r="S7">
-            <v>57.166666666666664</v>
+            <v>58.451612903225808</v>
           </cell>
           <cell r="T7">
-            <v>17.266666666666666</v>
+            <v>21.032258064516128</v>
           </cell>
           <cell r="U7">
-            <v>9.6</v>
+            <v>10.258064516129032</v>
           </cell>
           <cell r="V7">
-            <v>13.833333333333334</v>
+            <v>11.03225806451613</v>
           </cell>
           <cell r="W7">
             <v>0</v>
           </cell>
           <cell r="X7">
-            <v>-6.5</v>
+            <v>-4.5</v>
           </cell>
         </row>
         <row r="8">
@@ -9022,73 +9119,73 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>Grambling</v>
+            <v>Virginia Tech</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Mississippi Valley State</v>
+            <v>Wake Forest</v>
           </cell>
           <cell r="D8">
-            <v>-12.244735033381547</v>
+            <v>7.8547628130707166</v>
           </cell>
           <cell r="E8">
-            <v>93.914180629342042</v>
+            <v>99.930485155684281</v>
           </cell>
           <cell r="F8">
-            <v>92.582124972917441</v>
+            <v>111.6058758458976</v>
           </cell>
           <cell r="G8">
-            <v>0.48972401644157371</v>
+            <v>0.52429257875066737</v>
           </cell>
           <cell r="H8">
-            <v>69.169032258064519</v>
+            <v>69.063225806451612</v>
           </cell>
           <cell r="I8">
-            <v>54.935483870967744</v>
+            <v>60.41935483870968</v>
           </cell>
           <cell r="J8">
-            <v>22.451612903225808</v>
+            <v>20.451612903225808</v>
           </cell>
           <cell r="K8">
-            <v>10.32258064516129</v>
+            <v>10.709677419354838</v>
           </cell>
           <cell r="L8">
-            <v>14.67741935483871</v>
+            <v>10.35483870967742</v>
           </cell>
           <cell r="M8">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="N8">
-            <v>-23.27475617406899</v>
+            <v>10.516525865882155</v>
           </cell>
           <cell r="O8">
-            <v>91.587842551071247</v>
+            <v>98.652278422748424</v>
           </cell>
           <cell r="P8">
-            <v>90.431460168876654</v>
+            <v>98.023629781570804</v>
           </cell>
           <cell r="Q8">
-            <v>0.45905776780706675</v>
+            <v>0.52368137782561897</v>
           </cell>
           <cell r="R8">
-            <v>70.215000000000003</v>
+            <v>69.763870967741923</v>
           </cell>
           <cell r="S8">
-            <v>55.71875</v>
+            <v>59.935483870967744</v>
           </cell>
           <cell r="T8">
-            <v>18.8125</v>
+            <v>20.870967741935484</v>
           </cell>
           <cell r="U8">
-            <v>9.0625</v>
+            <v>10.193548387096774</v>
           </cell>
           <cell r="V8">
-            <v>15.28125</v>
+            <v>10.838709677419354</v>
           </cell>
           <cell r="W8">
             <v>0</v>
           </cell>
           <cell r="X8">
-            <v>-12.5</v>
+            <v>-2.5</v>
           </cell>
         </row>
         <row r="9">
@@ -9096,73 +9193,73 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>Texas A&amp;M-CC</v>
+            <v>Oregon</v>
           </cell>
           <cell r="C9" t="str">
-            <v>New Orleans</v>
+            <v>Maryland</v>
           </cell>
           <cell r="D9">
-            <v>2.6773979827270198</v>
+            <v>9.1810811715653209</v>
           </cell>
           <cell r="E9">
-            <v>97.434861434861432</v>
+            <v>98.275204963438952</v>
           </cell>
           <cell r="F9">
-            <v>91.54725372808565</v>
+            <v>98.342033542784705</v>
           </cell>
           <cell r="G9">
-            <v>0.50939100739897558</v>
+            <v>0.50146370023419207</v>
           </cell>
           <cell r="H9">
-            <v>68.090322580645164</v>
+            <v>66.574666666666673</v>
           </cell>
           <cell r="I9">
-            <v>56.677419354838712</v>
+            <v>56.93333333333333</v>
           </cell>
           <cell r="J9">
-            <v>22.419354838709676</v>
+            <v>19.866666666666667</v>
           </cell>
           <cell r="K9">
-            <v>11.419354838709678</v>
+            <v>11.166666666666666</v>
           </cell>
           <cell r="L9">
-            <v>12.96774193548387</v>
+            <v>12.066666666666666</v>
           </cell>
           <cell r="M9">
-            <v>2.7</v>
+            <v>0</v>
           </cell>
           <cell r="N9">
-            <v>-1.1890718220528178</v>
+            <v>5.4012937777418486</v>
           </cell>
           <cell r="O9">
-            <v>96.09802749551703</v>
+            <v>98.853381463000318</v>
           </cell>
           <cell r="P9">
-            <v>94.94556455971933</v>
+            <v>97.751369406938508</v>
           </cell>
           <cell r="Q9">
-            <v>0.49971114962449453</v>
+            <v>0.47940180586907449</v>
           </cell>
           <cell r="R9">
-            <v>69.781935483870953</v>
+            <v>66.838709677419359</v>
           </cell>
           <cell r="S9">
-            <v>55.838709677419352</v>
+            <v>57.161290322580648</v>
           </cell>
           <cell r="T9">
-            <v>25.677419354838708</v>
+            <v>20.967741935483872</v>
           </cell>
           <cell r="U9">
-            <v>11.935483870967742</v>
+            <v>12.32258064516129</v>
           </cell>
           <cell r="V9">
-            <v>14.580645161290322</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="W9">
             <v>0</v>
           </cell>
           <cell r="X9">
-            <v>-2</v>
+            <v>-3.5</v>
           </cell>
         </row>
         <row r="10">
@@ -9170,73 +9267,73 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>Campbell</v>
+            <v>Northwestern</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Monmouth</v>
+            <v>Penn State</v>
           </cell>
           <cell r="D10">
-            <v>1.1551322574216147</v>
+            <v>9.8709972215460926</v>
           </cell>
           <cell r="E10">
-            <v>99.959130560508953</v>
+            <v>100.10597226153411</v>
           </cell>
           <cell r="F10">
-            <v>102.06367103779606</v>
+            <v>99.834711537488872</v>
           </cell>
           <cell r="G10">
-            <v>0.51521511017838406</v>
+            <v>0.51577102803738317</v>
           </cell>
           <cell r="H10">
-            <v>70.135000000000005</v>
+            <v>65.150666666666666</v>
           </cell>
           <cell r="I10">
-            <v>59.5625</v>
+            <v>57.06666666666667</v>
           </cell>
           <cell r="J10">
-            <v>25.09375</v>
+            <v>19.433333333333334</v>
           </cell>
           <cell r="K10">
-            <v>12.625</v>
+            <v>9.1999999999999993</v>
           </cell>
           <cell r="L10">
-            <v>12.15625</v>
+            <v>8.7333333333333325</v>
           </cell>
           <cell r="M10">
             <v>0</v>
           </cell>
           <cell r="N10">
-            <v>-2.7998693866967312</v>
+            <v>3.4310910013046207</v>
           </cell>
           <cell r="O10">
-            <v>99.327473229982417</v>
+            <v>97.000389299816476</v>
           </cell>
           <cell r="P10">
-            <v>101.71037425999569</v>
+            <v>107.49318045680276</v>
           </cell>
           <cell r="Q10">
-            <v>0.49972632731253419</v>
+            <v>0.53161938534278963</v>
           </cell>
           <cell r="R10">
-            <v>67.424516129032256</v>
+            <v>66.641333333333336</v>
           </cell>
           <cell r="S10">
-            <v>58.935483870967744</v>
+            <v>56.4</v>
           </cell>
           <cell r="T10">
-            <v>19</v>
+            <v>19.033333333333335</v>
           </cell>
           <cell r="U10">
-            <v>11.35483870967742</v>
+            <v>8.4666666666666668</v>
           </cell>
           <cell r="V10">
-            <v>11.483870967741936</v>
+            <v>10.333333333333334</v>
           </cell>
           <cell r="W10">
-            <v>3.1</v>
+            <v>0</v>
           </cell>
           <cell r="X10">
-            <v>1.5</v>
+            <v>-6</v>
           </cell>
         </row>
         <row r="11">
@@ -9244,73 +9341,73 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>Northern Kentucky</v>
+            <v>Florida International</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Wright State</v>
+            <v>Missouri State</v>
           </cell>
           <cell r="D11">
-            <v>1.38975763828766</v>
+            <v>4.0785218527380627</v>
           </cell>
           <cell r="E11">
-            <v>99.14590747330962</v>
+            <v>99.498571082586579</v>
           </cell>
           <cell r="F11">
-            <v>98.998456911194168</v>
+            <v>100.06986322243148</v>
           </cell>
           <cell r="G11">
-            <v>0.54238578680203042</v>
+            <v>0.51632970451010884</v>
           </cell>
           <cell r="H11">
-            <v>71.575000000000003</v>
+            <v>72.763870967741923</v>
           </cell>
           <cell r="I11">
-            <v>61.5625</v>
+            <v>62.225806451612904</v>
           </cell>
           <cell r="J11">
-            <v>22.1875</v>
+            <v>24.096774193548388</v>
           </cell>
           <cell r="K11">
-            <v>11.71875</v>
+            <v>12.96774193548387</v>
           </cell>
           <cell r="L11">
-            <v>11.96875</v>
+            <v>12.903225806451612</v>
           </cell>
           <cell r="M11">
             <v>0</v>
           </cell>
           <cell r="N11">
-            <v>2.6723435907353315</v>
+            <v>3.7737649628252234</v>
           </cell>
           <cell r="O11">
-            <v>99.481742279448753</v>
+            <v>99.995875650873856</v>
           </cell>
           <cell r="P11">
-            <v>101.22113929223009</v>
+            <v>97.704588737615268</v>
           </cell>
           <cell r="Q11">
-            <v>0.54976051091005851</v>
+            <v>0.51096121416526141</v>
           </cell>
           <cell r="R11">
-            <v>68.23</v>
+            <v>67.619354838709683</v>
           </cell>
           <cell r="S11">
-            <v>58.71875</v>
+            <v>57.387096774193552</v>
           </cell>
           <cell r="T11">
-            <v>21.6875</v>
+            <v>24.35483870967742</v>
           </cell>
           <cell r="U11">
-            <v>11.375</v>
+            <v>11.806451612903226</v>
           </cell>
           <cell r="V11">
-            <v>11.34375</v>
+            <v>11.32258064516129</v>
           </cell>
           <cell r="W11">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="X11">
-            <v>-1.5</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="12">
@@ -9318,73 +9415,73 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>Detroit</v>
+            <v>Jacksonville State</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Robert Morris</v>
+            <v>New Mexico State</v>
           </cell>
           <cell r="D12">
-            <v>-1.1374478645185355</v>
+            <v>4.6377315934158476</v>
           </cell>
           <cell r="E12">
-            <v>100.48054895750857</v>
+            <v>98.878253568429869</v>
           </cell>
           <cell r="F12">
-            <v>96.746768196564886</v>
+            <v>94.933607449739725</v>
           </cell>
           <cell r="G12">
-            <v>0.50298913043478266</v>
+            <v>0.50898030127462346</v>
           </cell>
           <cell r="H12">
-            <v>69.787999999999997</v>
+            <v>66.510967741935488</v>
           </cell>
           <cell r="I12">
-            <v>61.333333333333336</v>
+            <v>55.677419354838712</v>
           </cell>
           <cell r="J12">
-            <v>21.033333333333335</v>
+            <v>23.741935483870968</v>
           </cell>
           <cell r="K12">
-            <v>12.2</v>
+            <v>11.03225806451613</v>
           </cell>
           <cell r="L12">
-            <v>11.4</v>
+            <v>11.419354838709678</v>
           </cell>
           <cell r="M12">
             <v>0</v>
           </cell>
           <cell r="N12">
-            <v>0.91783713669028455</v>
+            <v>5.3974553997046488</v>
           </cell>
           <cell r="O12">
-            <v>100.1603136571553</v>
+            <v>101.86846355181825</v>
           </cell>
           <cell r="P12">
-            <v>104.21574979976155</v>
+            <v>97.421007658448275</v>
           </cell>
           <cell r="Q12">
-            <v>0.54870828848223896</v>
+            <v>0.49463579898362509</v>
           </cell>
           <cell r="R12">
-            <v>66.807741935483861</v>
+            <v>68.355862068965521</v>
           </cell>
           <cell r="S12">
-            <v>59.935483870967744</v>
+            <v>61.068965517241381</v>
           </cell>
           <cell r="T12">
-            <v>16.64516129032258</v>
+            <v>20.793103448275861</v>
           </cell>
           <cell r="U12">
-            <v>13</v>
+            <v>12.241379310344827</v>
           </cell>
           <cell r="V12">
-            <v>12.548387096774194</v>
+            <v>10.379310344827585</v>
           </cell>
           <cell r="W12">
-            <v>2.8</v>
+            <v>0</v>
           </cell>
           <cell r="X12">
-            <v>5</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
@@ -9392,73 +9489,73 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>Northern Colorado</v>
+            <v>Merrimack</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Montana</v>
+            <v>Siena</v>
           </cell>
           <cell r="D13">
-            <v>3.7888532794728649</v>
+            <v>-10.233301819165744</v>
           </cell>
           <cell r="E13">
-            <v>97.300800773902282</v>
+            <v>97.289776682911139</v>
           </cell>
           <cell r="F13">
-            <v>96.601572065948844</v>
+            <v>110.00568539088987</v>
           </cell>
           <cell r="G13">
-            <v>0.56747967479674799</v>
+            <v>0.49735915492957744</v>
           </cell>
           <cell r="H13">
-            <v>70.438666666666663</v>
+            <v>63.928750000000001</v>
           </cell>
           <cell r="I13">
-            <v>61.5</v>
+            <v>53.25</v>
           </cell>
           <cell r="J13">
-            <v>16.3</v>
+            <v>20.71875</v>
           </cell>
           <cell r="K13">
-            <v>9.4333333333333336</v>
+            <v>8.125</v>
           </cell>
           <cell r="L13">
-            <v>11.2</v>
+            <v>9.6875</v>
           </cell>
           <cell r="M13">
             <v>0</v>
           </cell>
           <cell r="N13">
-            <v>2.5375154961101685</v>
+            <v>-10.548029111159565</v>
           </cell>
           <cell r="O13">
-            <v>91.063188911928393</v>
+            <v>99.221142888153253</v>
           </cell>
           <cell r="P13">
-            <v>94.640063686767107</v>
+            <v>104.56507728604723</v>
           </cell>
           <cell r="Q13">
-            <v>0.55520504731861198</v>
+            <v>0.50704225352112675</v>
           </cell>
           <cell r="R13">
-            <v>70.201379310344819</v>
+            <v>63.864999999999995</v>
           </cell>
           <cell r="S13">
-            <v>54.655172413793103</v>
+            <v>55.46875</v>
           </cell>
           <cell r="T13">
-            <v>20.206896551724139</v>
+            <v>18.65625</v>
           </cell>
           <cell r="U13">
-            <v>7.1034482758620694</v>
+            <v>10.03125</v>
           </cell>
           <cell r="V13">
-            <v>13.758620689655173</v>
+            <v>10.21875</v>
           </cell>
           <cell r="W13">
-            <v>2.9</v>
+            <v>0</v>
           </cell>
           <cell r="X13">
-            <v>-4.5</v>
+            <v>-3.5</v>
           </cell>
         </row>
         <row r="14">
@@ -9466,73 +9563,73 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>Weber State</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Eastern Washington</v>
+            <v>Alcorn State</v>
           </cell>
           <cell r="D14">
-            <v>2.6674007845525285</v>
+            <v>-10.740619332032924</v>
           </cell>
           <cell r="E14">
-            <v>99.879254581857381</v>
+            <v>96.942723004694827</v>
           </cell>
           <cell r="F14">
-            <v>96.950453466976299</v>
+            <v>93.291737667336207</v>
           </cell>
           <cell r="G14">
-            <v>0.52559912854030499</v>
+            <v>0.49388297872340425</v>
           </cell>
           <cell r="H14">
-            <v>71.055999999999983</v>
+            <v>74.380645161290332</v>
           </cell>
           <cell r="I14">
-            <v>61.2</v>
+            <v>60.645161290322584</v>
           </cell>
           <cell r="J14">
-            <v>23.233333333333334</v>
+            <v>26.451612903225808</v>
           </cell>
           <cell r="K14">
-            <v>11.7</v>
+            <v>10.161290322580646</v>
           </cell>
           <cell r="L14">
-            <v>11.333333333333334</v>
+            <v>12.258064516129032</v>
           </cell>
           <cell r="M14">
             <v>0</v>
           </cell>
           <cell r="N14">
-            <v>1.6745596773049956</v>
+            <v>-19.948242350647938</v>
           </cell>
           <cell r="O14">
-            <v>96.45410010649627</v>
+            <v>94.015466724757644</v>
           </cell>
           <cell r="P14">
-            <v>94.243332897672701</v>
+            <v>99.142194717936277</v>
           </cell>
           <cell r="Q14">
-            <v>0.54709936817920735</v>
+            <v>0.47871720116618077</v>
           </cell>
           <cell r="R14">
-            <v>69.375999999999991</v>
+            <v>68.99733333333333</v>
           </cell>
           <cell r="S14">
-            <v>58.033333333333331</v>
+            <v>57.166666666666664</v>
           </cell>
           <cell r="T14">
-            <v>20.399999999999999</v>
+            <v>17.266666666666666</v>
           </cell>
           <cell r="U14">
-            <v>10.066666666666666</v>
+            <v>9.6</v>
           </cell>
           <cell r="V14">
-            <v>12.433333333333334</v>
+            <v>13.833333333333334</v>
           </cell>
           <cell r="W14">
-            <v>2.2999999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="X14">
-            <v>3</v>
+            <v>-6</v>
           </cell>
         </row>
         <row r="15">
@@ -9540,73 +9637,73 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>Alcorn State</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Alabama State</v>
+            <v>Mercyhurst</v>
           </cell>
           <cell r="D15">
-            <v>-19.948242350647938</v>
+            <v>-5.3862870517485577</v>
           </cell>
           <cell r="E15">
-            <v>94.015466724757644</v>
+            <v>97.110724162654932</v>
           </cell>
           <cell r="F15">
-            <v>99.142194717936277</v>
+            <v>96.845289405897276</v>
           </cell>
           <cell r="G15">
-            <v>0.47871720116618077</v>
+            <v>0.53378746594005455</v>
           </cell>
           <cell r="H15">
-            <v>68.99733333333333</v>
+            <v>67.763750000000002</v>
           </cell>
           <cell r="I15">
-            <v>57.166666666666664</v>
+            <v>57.34375</v>
           </cell>
           <cell r="J15">
-            <v>17.266666666666666</v>
+            <v>19.5625</v>
           </cell>
           <cell r="K15">
-            <v>9.6</v>
+            <v>11.46875</v>
           </cell>
           <cell r="L15">
-            <v>13.833333333333334</v>
+            <v>13.28125</v>
           </cell>
           <cell r="M15">
             <v>0</v>
           </cell>
           <cell r="N15">
-            <v>-12.610080468302302</v>
+            <v>-8.9892302193689186</v>
           </cell>
           <cell r="O15">
-            <v>98.54414125200644</v>
+            <v>99.107385837914336</v>
           </cell>
           <cell r="P15">
-            <v>94.651073379053571</v>
+            <v>101.60426992452147</v>
           </cell>
           <cell r="Q15">
-            <v>0.48040254237288138</v>
+            <v>0.50320855614973259</v>
           </cell>
           <cell r="R15">
-            <v>71.069677419354832</v>
+            <v>65.3125</v>
           </cell>
           <cell r="S15">
-            <v>60.903225806451616</v>
+            <v>58.4375</v>
           </cell>
           <cell r="T15">
-            <v>21.419354838709676</v>
+            <v>14.84375</v>
           </cell>
           <cell r="U15">
-            <v>12.451612903225806</v>
+            <v>9.15625</v>
           </cell>
           <cell r="V15">
-            <v>13.193548387096774</v>
+            <v>9.5</v>
           </cell>
           <cell r="W15">
-            <v>2.2999999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="X15">
-            <v>6.5</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="16">
@@ -9614,73 +9711,73 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>Mississippi Valley State</v>
+            <v>UMBC</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Grambling</v>
+            <v>UMass Lowell</v>
           </cell>
           <cell r="D16">
-            <v>-23.27475617406899</v>
+            <v>-9.1795715901906192</v>
           </cell>
           <cell r="E16">
-            <v>91.587842551071247</v>
+            <v>97.210907835692097</v>
           </cell>
           <cell r="F16">
-            <v>90.431460168876654</v>
+            <v>110.54326482948768</v>
           </cell>
           <cell r="G16">
-            <v>0.45905776780706675</v>
+            <v>0.5430982519590114</v>
           </cell>
           <cell r="H16">
-            <v>70.215000000000003</v>
+            <v>66.972413793103442</v>
           </cell>
           <cell r="I16">
-            <v>55.71875</v>
+            <v>57.206896551724135</v>
           </cell>
           <cell r="J16">
-            <v>18.8125</v>
+            <v>18.275862068965516</v>
           </cell>
           <cell r="K16">
-            <v>9.0625</v>
+            <v>8.068965517241379</v>
           </cell>
           <cell r="L16">
-            <v>15.28125</v>
+            <v>9.7931034482758612</v>
           </cell>
           <cell r="M16">
             <v>0</v>
           </cell>
           <cell r="N16">
-            <v>-12.244735033381547</v>
+            <v>-10.78545288970942</v>
           </cell>
           <cell r="O16">
-            <v>93.914180629342042</v>
+            <v>99.396366256626706</v>
           </cell>
           <cell r="P16">
-            <v>92.582124972917441</v>
+            <v>109.60513696431309</v>
           </cell>
           <cell r="Q16">
-            <v>0.48972401644157371</v>
+            <v>0.51174863387978142</v>
           </cell>
           <cell r="R16">
-            <v>69.169032258064519</v>
+            <v>68.758709677419347</v>
           </cell>
           <cell r="S16">
-            <v>54.935483870967744</v>
+            <v>59.032258064516128</v>
           </cell>
           <cell r="T16">
-            <v>22.451612903225808</v>
+            <v>22.032258064516128</v>
           </cell>
           <cell r="U16">
-            <v>10.32258064516129</v>
+            <v>12.225806451612904</v>
           </cell>
           <cell r="V16">
-            <v>14.67741935483871</v>
+            <v>12.258064516129032</v>
           </cell>
           <cell r="W16">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="X16">
-            <v>12.5</v>
+            <v>-7.5</v>
           </cell>
         </row>
         <row r="17">
@@ -9688,4214 +9785,1258 @@
             <v>16</v>
           </cell>
           <cell r="B17" t="str">
-            <v>New Orleans</v>
+            <v>Vermont</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Texas A&amp;M-CC</v>
+            <v>NJIT</v>
           </cell>
           <cell r="D17">
-            <v>-1.1890718220528178</v>
+            <v>-8.3063732632254172</v>
           </cell>
           <cell r="E17">
-            <v>96.09802749551703</v>
+            <v>98.685284640171872</v>
           </cell>
           <cell r="F17">
-            <v>94.94556455971933</v>
+            <v>109.91881615719028</v>
           </cell>
           <cell r="G17">
-            <v>0.49971114962449453</v>
+            <v>0.54303164908384227</v>
           </cell>
           <cell r="H17">
-            <v>69.781935483870953</v>
+            <v>64.849999999999994</v>
           </cell>
           <cell r="I17">
-            <v>55.838709677419352</v>
+            <v>56.28125</v>
           </cell>
           <cell r="J17">
-            <v>25.677419354838708</v>
+            <v>18.125</v>
           </cell>
           <cell r="K17">
-            <v>11.935483870967742</v>
+            <v>8.84375</v>
           </cell>
           <cell r="L17">
-            <v>14.580645161290322</v>
+            <v>9.4375</v>
           </cell>
           <cell r="M17">
             <v>0</v>
           </cell>
           <cell r="N17">
-            <v>2.6773979827270198</v>
+            <v>-12.855933529800252</v>
           </cell>
           <cell r="O17">
-            <v>97.434861434861432</v>
+            <v>97.230326689952733</v>
           </cell>
           <cell r="P17">
-            <v>91.54725372808565</v>
+            <v>98.860244215497659</v>
           </cell>
           <cell r="Q17">
-            <v>0.50939100739897558</v>
+            <v>0.4684095860566449</v>
           </cell>
           <cell r="R17">
-            <v>68.090322580645164</v>
+            <v>67.618750000000006</v>
           </cell>
           <cell r="S17">
-            <v>56.677419354838712</v>
+            <v>57.375</v>
           </cell>
           <cell r="T17">
-            <v>22.419354838709676</v>
+            <v>19.375</v>
           </cell>
           <cell r="U17">
+            <v>9.84375</v>
+          </cell>
+          <cell r="V17">
+            <v>11.5625</v>
+          </cell>
+          <cell r="W17">
+            <v>0</v>
+          </cell>
+          <cell r="X17">
+            <v>-12</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>Baylor</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>Arizona State</v>
+          </cell>
+          <cell r="D18">
+            <v>13.997941784567479</v>
+          </cell>
+          <cell r="E18">
+            <v>101.13544029968871</v>
+          </cell>
+          <cell r="F18">
+            <v>105.02424567854018</v>
+          </cell>
+          <cell r="G18">
+            <v>0.5503812636165577</v>
+          </cell>
+          <cell r="H18">
+            <v>69.473333333333329</v>
+          </cell>
+          <cell r="I18">
+            <v>61.2</v>
+          </cell>
+          <cell r="J18">
+            <v>21.833333333333332</v>
+          </cell>
+          <cell r="K18">
+            <v>12.633333333333333</v>
+          </cell>
+          <cell r="L18">
+            <v>11.3</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>11.676210374037039</v>
+          </cell>
+          <cell r="O18">
+            <v>97.795147404122091</v>
+          </cell>
+          <cell r="P18">
+            <v>95.965512535699588</v>
+          </cell>
+          <cell r="Q18">
+            <v>0.50599315068493156</v>
+          </cell>
+          <cell r="R18">
+            <v>69.834666666666664</v>
+          </cell>
+          <cell r="S18">
+            <v>58.4</v>
+          </cell>
+          <cell r="T18">
+            <v>23.033333333333335</v>
+          </cell>
+          <cell r="U18">
+            <v>10.366666666666667</v>
+          </cell>
+          <cell r="V18">
+            <v>11.666666666666666</v>
+          </cell>
+          <cell r="W18">
+            <v>0</v>
+          </cell>
+          <cell r="X18">
+            <v>-3.5</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>Utah</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>Cincinnati</v>
+          </cell>
+          <cell r="D19">
+            <v>6.9075926290659249</v>
+          </cell>
+          <cell r="E19">
+            <v>97.474667091092371</v>
+          </cell>
+          <cell r="F19">
+            <v>100.13185770788762</v>
+          </cell>
+          <cell r="G19">
+            <v>0.52409972299168972</v>
+          </cell>
+          <cell r="H19">
+            <v>67.935483870967744</v>
+          </cell>
+          <cell r="I19">
+            <v>58.225806451612904</v>
+          </cell>
+          <cell r="J19">
+            <v>18.548387096774192</v>
+          </cell>
+          <cell r="K19">
+            <v>10</v>
+          </cell>
+          <cell r="L19">
+            <v>11.548387096774194</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>13.013886487974281</v>
+          </cell>
+          <cell r="O19">
+            <v>98.819278377666578</v>
+          </cell>
+          <cell r="P19">
+            <v>97.225851270115911</v>
+          </cell>
+          <cell r="Q19">
+            <v>0.50693703308431159</v>
+          </cell>
+          <cell r="R19">
+            <v>68.820645161290329</v>
+          </cell>
+          <cell r="S19">
+            <v>60.451612903225808</v>
+          </cell>
+          <cell r="T19">
+            <v>17.774193548387096</v>
+          </cell>
+          <cell r="U19">
+            <v>11.161290322580646</v>
+          </cell>
+          <cell r="V19">
+            <v>11.709677419354838</v>
+          </cell>
+          <cell r="W19">
+            <v>0</v>
+          </cell>
+          <cell r="X19">
+            <v>10.5</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>Kansas State</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>BYU</v>
+          </cell>
+          <cell r="D20">
+            <v>8.6039512771540601</v>
+          </cell>
+          <cell r="E20">
+            <v>96.575607312797402</v>
+          </cell>
+          <cell r="F20">
+            <v>98.325303696839384</v>
+          </cell>
+          <cell r="G20">
+            <v>0.53056546102903723</v>
+          </cell>
+          <cell r="H20">
+            <v>73.165161290322573</v>
+          </cell>
+          <cell r="I20">
+            <v>63.322580645161288</v>
+          </cell>
+          <cell r="J20">
+            <v>16.870967741935484</v>
+          </cell>
+          <cell r="K20">
+            <v>10.451612903225806</v>
+          </cell>
+          <cell r="L20">
+            <v>12.870967741935484</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>16.600220651643195</v>
+          </cell>
+          <cell r="O20">
+            <v>101.6412542424396</v>
+          </cell>
+          <cell r="P20">
+            <v>101.90007741800223</v>
+          </cell>
+          <cell r="Q20">
+            <v>0.54686690833764884</v>
+          </cell>
+          <cell r="R20">
+            <v>70.129032258064512</v>
+          </cell>
+          <cell r="S20">
+            <v>62.29032258064516</v>
+          </cell>
+          <cell r="T20">
+            <v>21.774193548387096</v>
+          </cell>
+          <cell r="U20">
+            <v>12.32258064516129</v>
+          </cell>
+          <cell r="V20">
+            <v>10.580645161290322</v>
+          </cell>
+          <cell r="W20">
+            <v>0</v>
+          </cell>
+          <cell r="X20">
+            <v>10.5</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>Oklahoma State</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>Colorado</v>
+          </cell>
+          <cell r="D21">
+            <v>10.400184605664766</v>
+          </cell>
+          <cell r="E21">
+            <v>98.362133308139249</v>
+          </cell>
+          <cell r="F21">
+            <v>100.64400740314213</v>
+          </cell>
+          <cell r="G21">
+            <v>0.52157164869029271</v>
+          </cell>
+          <cell r="H21">
+            <v>74.596129032258062</v>
+          </cell>
+          <cell r="I21">
+            <v>62.806451612903224</v>
+          </cell>
+          <cell r="J21">
+            <v>24.741935483870968</v>
+          </cell>
+          <cell r="K21">
+            <v>11.32258064516129</v>
+          </cell>
+          <cell r="L21">
+            <v>12.225806451612904</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>9.8189534899998705</v>
+          </cell>
+          <cell r="O21">
+            <v>98.962524252016749</v>
+          </cell>
+          <cell r="P21">
+            <v>102.28356507324483</v>
+          </cell>
+          <cell r="Q21">
+            <v>0.53135135135135136</v>
+          </cell>
+          <cell r="R21">
+            <v>69.5741935483871</v>
+          </cell>
+          <cell r="S21">
+            <v>59.677419354838712</v>
+          </cell>
+          <cell r="T21">
+            <v>21.612903225806452</v>
+          </cell>
+          <cell r="U21">
+            <v>9.9677419354838701</v>
+          </cell>
+          <cell r="V21">
+            <v>10.35483870967742</v>
+          </cell>
+          <cell r="W21">
+            <v>0</v>
+          </cell>
+          <cell r="X21">
+            <v>2.5</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>Pittsburgh</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>Stanford</v>
+          </cell>
+          <cell r="D22">
+            <v>5.1655310926871802</v>
+          </cell>
+          <cell r="E22">
+            <v>100.13985858248427</v>
+          </cell>
+          <cell r="F22">
+            <v>104.42105719874289</v>
+          </cell>
+          <cell r="G22">
+            <v>0.50756726457399104</v>
+          </cell>
+          <cell r="H22">
+            <v>64.803870967741929</v>
+          </cell>
+          <cell r="I22">
+            <v>57.548387096774192</v>
+          </cell>
+          <cell r="J22">
+            <v>17.516129032258064</v>
+          </cell>
+          <cell r="K22">
+            <v>11.774193548387096</v>
+          </cell>
+          <cell r="L22">
+            <v>11.32258064516129</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>11.634002216606197</v>
+          </cell>
+          <cell r="O22">
+            <v>99.979621987875078</v>
+          </cell>
+          <cell r="P22">
+            <v>88.78433637984817</v>
+          </cell>
+          <cell r="Q22">
+            <v>0.51572494669509594</v>
+          </cell>
+          <cell r="R22">
+            <v>67.5</v>
+          </cell>
+          <cell r="S22">
+            <v>58.625</v>
+          </cell>
+          <cell r="T22">
+            <v>21.09375</v>
+          </cell>
+          <cell r="U22">
+            <v>11.21875</v>
+          </cell>
+          <cell r="V22">
+            <v>10.8125</v>
+          </cell>
+          <cell r="W22">
+            <v>0</v>
+          </cell>
+          <cell r="X22">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>Syracuse</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>SMU</v>
+          </cell>
+          <cell r="D23">
+            <v>5.9340551424645511</v>
+          </cell>
+          <cell r="E23">
+            <v>98.460835237897356</v>
+          </cell>
+          <cell r="F23">
+            <v>105.23886558606168</v>
+          </cell>
+          <cell r="G23">
+            <v>0.52649006622516559</v>
+          </cell>
+          <cell r="H23">
+            <v>68.48</v>
+          </cell>
+          <cell r="I23">
+            <v>58.451612903225808</v>
+          </cell>
+          <cell r="J23">
+            <v>21.032258064516128</v>
+          </cell>
+          <cell r="K23">
+            <v>10.258064516129032</v>
+          </cell>
+          <cell r="L23">
+            <v>11.03225806451613</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>13.536513873870378</v>
+          </cell>
+          <cell r="O23">
+            <v>100.42773804088671</v>
+          </cell>
+          <cell r="P23">
+            <v>99.400324400971755</v>
+          </cell>
+          <cell r="Q23">
+            <v>0.55947476828012355</v>
+          </cell>
+          <cell r="R23">
+            <v>70.745806451612893</v>
+          </cell>
+          <cell r="S23">
+            <v>62.645161290322584</v>
+          </cell>
+          <cell r="T23">
+            <v>20.096774193548388</v>
+          </cell>
+          <cell r="U23">
+            <v>12.096774193548388</v>
+          </cell>
+          <cell r="V23">
+            <v>11.35483870967742</v>
+          </cell>
+          <cell r="W23">
+            <v>0</v>
+          </cell>
+          <cell r="X23">
+            <v>4.5</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Wake Forest</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>Virginia Tech</v>
+          </cell>
+          <cell r="D24">
+            <v>10.516525865882155</v>
+          </cell>
+          <cell r="E24">
+            <v>98.652278422748424</v>
+          </cell>
+          <cell r="F24">
+            <v>98.023629781570804</v>
+          </cell>
+          <cell r="G24">
+            <v>0.52368137782561897</v>
+          </cell>
+          <cell r="H24">
+            <v>69.763870967741923</v>
+          </cell>
+          <cell r="I24">
+            <v>59.935483870967744</v>
+          </cell>
+          <cell r="J24">
+            <v>20.870967741935484</v>
+          </cell>
+          <cell r="K24">
+            <v>10.193548387096774</v>
+          </cell>
+          <cell r="L24">
+            <v>10.838709677419354</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>7.8547628130707166</v>
+          </cell>
+          <cell r="O24">
+            <v>99.930485155684281</v>
+          </cell>
+          <cell r="P24">
+            <v>111.6058758458976</v>
+          </cell>
+          <cell r="Q24">
+            <v>0.52429257875066737</v>
+          </cell>
+          <cell r="R24">
+            <v>69.063225806451612</v>
+          </cell>
+          <cell r="S24">
+            <v>60.41935483870968</v>
+          </cell>
+          <cell r="T24">
+            <v>20.451612903225808</v>
+          </cell>
+          <cell r="U24">
+            <v>10.709677419354838</v>
+          </cell>
+          <cell r="V24">
+            <v>10.35483870967742</v>
+          </cell>
+          <cell r="W24">
+            <v>0</v>
+          </cell>
+          <cell r="X24">
+            <v>2.5</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Maryland</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Oregon</v>
+          </cell>
+          <cell r="D25">
+            <v>5.4012937777418486</v>
+          </cell>
+          <cell r="E25">
+            <v>98.853381463000318</v>
+          </cell>
+          <cell r="F25">
+            <v>97.751369406938508</v>
+          </cell>
+          <cell r="G25">
+            <v>0.47940180586907449</v>
+          </cell>
+          <cell r="H25">
+            <v>66.838709677419359</v>
+          </cell>
+          <cell r="I25">
+            <v>57.161290322580648</v>
+          </cell>
+          <cell r="J25">
+            <v>20.967741935483872</v>
+          </cell>
+          <cell r="K25">
+            <v>12.32258064516129</v>
+          </cell>
+          <cell r="L25">
+            <v>12.774193548387096</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>9.1810811715653209</v>
+          </cell>
+          <cell r="O25">
+            <v>98.275204963438952</v>
+          </cell>
+          <cell r="P25">
+            <v>98.342033542784705</v>
+          </cell>
+          <cell r="Q25">
+            <v>0.50146370023419207</v>
+          </cell>
+          <cell r="R25">
+            <v>66.574666666666673</v>
+          </cell>
+          <cell r="S25">
+            <v>56.93333333333333</v>
+          </cell>
+          <cell r="T25">
+            <v>19.866666666666667</v>
+          </cell>
+          <cell r="U25">
+            <v>11.166666666666666</v>
+          </cell>
+          <cell r="V25">
+            <v>12.066666666666666</v>
+          </cell>
+          <cell r="W25">
+            <v>0</v>
+          </cell>
+          <cell r="X25">
+            <v>3.5</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>Penn State</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>Northwestern</v>
+          </cell>
+          <cell r="D26">
+            <v>3.4310910013046207</v>
+          </cell>
+          <cell r="E26">
+            <v>97.000389299816476</v>
+          </cell>
+          <cell r="F26">
+            <v>107.49318045680276</v>
+          </cell>
+          <cell r="G26">
+            <v>0.53161938534278963</v>
+          </cell>
+          <cell r="H26">
+            <v>66.641333333333336</v>
+          </cell>
+          <cell r="I26">
+            <v>56.4</v>
+          </cell>
+          <cell r="J26">
+            <v>19.033333333333335</v>
+          </cell>
+          <cell r="K26">
+            <v>8.4666666666666668</v>
+          </cell>
+          <cell r="L26">
+            <v>10.333333333333334</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>9.8709972215460926</v>
+          </cell>
+          <cell r="O26">
+            <v>100.10597226153411</v>
+          </cell>
+          <cell r="P26">
+            <v>99.834711537488872</v>
+          </cell>
+          <cell r="Q26">
+            <v>0.51577102803738317</v>
+          </cell>
+          <cell r="R26">
+            <v>65.150666666666666</v>
+          </cell>
+          <cell r="S26">
+            <v>57.06666666666667</v>
+          </cell>
+          <cell r="T26">
+            <v>19.433333333333334</v>
+          </cell>
+          <cell r="U26">
+            <v>9.1999999999999993</v>
+          </cell>
+          <cell r="V26">
+            <v>8.7333333333333325</v>
+          </cell>
+          <cell r="W26">
+            <v>0</v>
+          </cell>
+          <cell r="X26">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Missouri State</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>Florida International</v>
+          </cell>
+          <cell r="D27">
+            <v>3.7737649628252234</v>
+          </cell>
+          <cell r="E27">
+            <v>99.995875650873856</v>
+          </cell>
+          <cell r="F27">
+            <v>97.704588737615268</v>
+          </cell>
+          <cell r="G27">
+            <v>0.51096121416526141</v>
+          </cell>
+          <cell r="H27">
+            <v>67.619354838709683</v>
+          </cell>
+          <cell r="I27">
+            <v>57.387096774193552</v>
+          </cell>
+          <cell r="J27">
+            <v>24.35483870967742</v>
+          </cell>
+          <cell r="K27">
+            <v>11.806451612903226</v>
+          </cell>
+          <cell r="L27">
+            <v>11.32258064516129</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>4.0785218527380627</v>
+          </cell>
+          <cell r="O27">
+            <v>99.498571082586579</v>
+          </cell>
+          <cell r="P27">
+            <v>100.06986322243148</v>
+          </cell>
+          <cell r="Q27">
+            <v>0.51632970451010884</v>
+          </cell>
+          <cell r="R27">
+            <v>72.763870967741923</v>
+          </cell>
+          <cell r="S27">
+            <v>62.225806451612904</v>
+          </cell>
+          <cell r="T27">
+            <v>24.096774193548388</v>
+          </cell>
+          <cell r="U27">
+            <v>12.96774193548387</v>
+          </cell>
+          <cell r="V27">
+            <v>12.903225806451612</v>
+          </cell>
+          <cell r="W27">
+            <v>0</v>
+          </cell>
+          <cell r="X27">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>New Mexico State</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>Jacksonville State</v>
+          </cell>
+          <cell r="D28">
+            <v>5.3974553997046488</v>
+          </cell>
+          <cell r="E28">
+            <v>101.86846355181825</v>
+          </cell>
+          <cell r="F28">
+            <v>97.421007658448275</v>
+          </cell>
+          <cell r="G28">
+            <v>0.49463579898362509</v>
+          </cell>
+          <cell r="H28">
+            <v>68.355862068965521</v>
+          </cell>
+          <cell r="I28">
+            <v>61.068965517241381</v>
+          </cell>
+          <cell r="J28">
+            <v>20.793103448275861</v>
+          </cell>
+          <cell r="K28">
+            <v>12.241379310344827</v>
+          </cell>
+          <cell r="L28">
+            <v>10.379310344827585</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>4.6377315934158476</v>
+          </cell>
+          <cell r="O28">
+            <v>98.878253568429869</v>
+          </cell>
+          <cell r="P28">
+            <v>94.933607449739725</v>
+          </cell>
+          <cell r="Q28">
+            <v>0.50898030127462346</v>
+          </cell>
+          <cell r="R28">
+            <v>66.510967741935488</v>
+          </cell>
+          <cell r="S28">
+            <v>55.677419354838712</v>
+          </cell>
+          <cell r="T28">
+            <v>23.741935483870968</v>
+          </cell>
+          <cell r="U28">
+            <v>11.03225806451613</v>
+          </cell>
+          <cell r="V28">
             <v>11.419354838709678</v>
           </cell>
-          <cell r="V17">
-            <v>12.96774193548387</v>
-          </cell>
-          <cell r="W17">
-            <v>2.7</v>
-          </cell>
-          <cell r="X17">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="D18"/>
-          <cell r="E18"/>
-          <cell r="F18"/>
-          <cell r="G18"/>
-          <cell r="H18"/>
-          <cell r="I18"/>
-          <cell r="J18"/>
-          <cell r="K18"/>
-          <cell r="L18"/>
-          <cell r="M18"/>
-          <cell r="N18"/>
-          <cell r="O18"/>
-          <cell r="P18"/>
-          <cell r="Q18"/>
-          <cell r="R18"/>
-          <cell r="S18"/>
-          <cell r="T18"/>
-          <cell r="U18"/>
-          <cell r="V18"/>
-          <cell r="W18"/>
-          <cell r="X18"/>
-        </row>
-        <row r="19">
-          <cell r="D19"/>
-          <cell r="E19"/>
-          <cell r="F19"/>
-          <cell r="G19"/>
-          <cell r="H19"/>
-          <cell r="I19"/>
-          <cell r="J19"/>
-          <cell r="K19"/>
-          <cell r="L19"/>
-          <cell r="M19"/>
-          <cell r="N19"/>
-          <cell r="O19"/>
-          <cell r="P19"/>
-          <cell r="Q19"/>
-          <cell r="R19"/>
-          <cell r="S19"/>
-          <cell r="T19"/>
-          <cell r="U19"/>
-          <cell r="V19"/>
-          <cell r="W19"/>
-          <cell r="X19"/>
-        </row>
-        <row r="20">
-          <cell r="D20"/>
-          <cell r="E20"/>
-          <cell r="F20"/>
-          <cell r="G20"/>
-          <cell r="H20"/>
-          <cell r="I20"/>
-          <cell r="J20"/>
-          <cell r="K20"/>
-          <cell r="L20"/>
-          <cell r="M20"/>
-          <cell r="N20"/>
-          <cell r="O20"/>
-          <cell r="P20"/>
-          <cell r="Q20"/>
-          <cell r="R20"/>
-          <cell r="S20"/>
-          <cell r="T20"/>
-          <cell r="U20"/>
-          <cell r="V20"/>
-          <cell r="W20"/>
-          <cell r="X20"/>
-        </row>
-        <row r="21">
-          <cell r="D21"/>
-          <cell r="E21"/>
-          <cell r="F21"/>
-          <cell r="G21"/>
-          <cell r="H21"/>
-          <cell r="I21"/>
-          <cell r="J21"/>
-          <cell r="K21"/>
-          <cell r="L21"/>
-          <cell r="M21"/>
-          <cell r="N21"/>
-          <cell r="O21"/>
-          <cell r="P21"/>
-          <cell r="Q21"/>
-          <cell r="R21"/>
-          <cell r="S21"/>
-          <cell r="T21"/>
-          <cell r="U21"/>
-          <cell r="V21"/>
-          <cell r="W21"/>
-          <cell r="X21"/>
-        </row>
-        <row r="22">
-          <cell r="D22"/>
-          <cell r="E22"/>
-          <cell r="F22"/>
-          <cell r="G22"/>
-          <cell r="H22"/>
-          <cell r="I22"/>
-          <cell r="J22"/>
-          <cell r="K22"/>
-          <cell r="L22"/>
-          <cell r="M22"/>
-          <cell r="N22"/>
-          <cell r="O22"/>
-          <cell r="P22"/>
-          <cell r="Q22"/>
-          <cell r="R22"/>
-          <cell r="S22"/>
-          <cell r="T22"/>
-          <cell r="U22"/>
-          <cell r="V22"/>
-          <cell r="W22"/>
-          <cell r="X22"/>
-        </row>
-        <row r="23">
-          <cell r="D23"/>
-          <cell r="E23"/>
-          <cell r="F23"/>
-          <cell r="G23"/>
-          <cell r="H23"/>
-          <cell r="I23"/>
-          <cell r="J23"/>
-          <cell r="K23"/>
-          <cell r="L23"/>
-          <cell r="M23"/>
-          <cell r="N23"/>
-          <cell r="O23"/>
-          <cell r="P23"/>
-          <cell r="Q23"/>
-          <cell r="R23"/>
-          <cell r="S23"/>
-          <cell r="T23"/>
-          <cell r="U23"/>
-          <cell r="V23"/>
-          <cell r="W23"/>
-          <cell r="X23"/>
-        </row>
-        <row r="24">
-          <cell r="D24"/>
-          <cell r="E24"/>
-          <cell r="F24"/>
-          <cell r="G24"/>
-          <cell r="H24"/>
-          <cell r="I24"/>
-          <cell r="J24"/>
-          <cell r="K24"/>
-          <cell r="L24"/>
-          <cell r="M24"/>
-          <cell r="N24"/>
-          <cell r="O24"/>
-          <cell r="P24"/>
-          <cell r="Q24"/>
-          <cell r="R24"/>
-          <cell r="S24"/>
-          <cell r="T24"/>
-          <cell r="U24"/>
-          <cell r="V24"/>
-          <cell r="W24"/>
-          <cell r="X24"/>
-        </row>
-        <row r="25">
-          <cell r="D25"/>
-          <cell r="E25"/>
-          <cell r="F25"/>
-          <cell r="G25"/>
-          <cell r="H25"/>
-          <cell r="I25"/>
-          <cell r="J25"/>
-          <cell r="K25"/>
-          <cell r="L25"/>
-          <cell r="M25"/>
-          <cell r="N25"/>
-          <cell r="O25"/>
-          <cell r="P25"/>
-          <cell r="Q25"/>
-          <cell r="R25"/>
-          <cell r="S25"/>
-          <cell r="T25"/>
-          <cell r="U25"/>
-          <cell r="V25"/>
-          <cell r="W25"/>
-          <cell r="X25"/>
-        </row>
-        <row r="26">
-          <cell r="D26"/>
-          <cell r="E26"/>
-          <cell r="F26"/>
-          <cell r="G26"/>
-          <cell r="H26"/>
-          <cell r="I26"/>
-          <cell r="J26"/>
-          <cell r="K26"/>
-          <cell r="L26"/>
-          <cell r="M26"/>
-          <cell r="N26"/>
-          <cell r="O26"/>
-          <cell r="P26"/>
-          <cell r="Q26"/>
-          <cell r="R26"/>
-          <cell r="S26"/>
-          <cell r="T26"/>
-          <cell r="U26"/>
-          <cell r="V26"/>
-          <cell r="W26"/>
-          <cell r="X26"/>
-        </row>
-        <row r="27">
-          <cell r="D27"/>
-          <cell r="E27"/>
-          <cell r="F27"/>
-          <cell r="G27"/>
-          <cell r="H27"/>
-          <cell r="I27"/>
-          <cell r="J27"/>
-          <cell r="K27"/>
-          <cell r="L27"/>
-          <cell r="M27"/>
-          <cell r="N27"/>
-          <cell r="O27"/>
-          <cell r="P27"/>
-          <cell r="Q27"/>
-          <cell r="R27"/>
-          <cell r="S27"/>
-          <cell r="T27"/>
-          <cell r="U27"/>
-          <cell r="V27"/>
-          <cell r="W27"/>
-          <cell r="X27"/>
-        </row>
-        <row r="28">
-          <cell r="D28"/>
-          <cell r="E28"/>
-          <cell r="F28"/>
-          <cell r="G28"/>
-          <cell r="H28"/>
-          <cell r="I28"/>
-          <cell r="J28"/>
-          <cell r="K28"/>
-          <cell r="L28"/>
-          <cell r="M28"/>
-          <cell r="N28"/>
-          <cell r="O28"/>
-          <cell r="P28"/>
-          <cell r="Q28"/>
-          <cell r="R28"/>
-          <cell r="S28"/>
-          <cell r="T28"/>
-          <cell r="U28"/>
-          <cell r="V28"/>
-          <cell r="W28"/>
-          <cell r="X28"/>
+          <cell r="W28">
+            <v>0</v>
+          </cell>
+          <cell r="X28">
+            <v>-1</v>
+          </cell>
         </row>
         <row r="29">
-          <cell r="D29"/>
-          <cell r="E29"/>
-          <cell r="F29"/>
-          <cell r="G29"/>
-          <cell r="H29"/>
-          <cell r="I29"/>
-          <cell r="J29"/>
-          <cell r="K29"/>
-          <cell r="L29"/>
-          <cell r="M29"/>
-          <cell r="N29"/>
-          <cell r="O29"/>
-          <cell r="P29"/>
-          <cell r="Q29"/>
-          <cell r="R29"/>
-          <cell r="S29"/>
-          <cell r="T29"/>
-          <cell r="U29"/>
-          <cell r="V29"/>
-          <cell r="W29"/>
-          <cell r="X29"/>
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Siena</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>Merrimack</v>
+          </cell>
+          <cell r="D29">
+            <v>-10.548029111159565</v>
+          </cell>
+          <cell r="E29">
+            <v>99.221142888153253</v>
+          </cell>
+          <cell r="F29">
+            <v>104.56507728604723</v>
+          </cell>
+          <cell r="G29">
+            <v>0.50704225352112675</v>
+          </cell>
+          <cell r="H29">
+            <v>63.864999999999995</v>
+          </cell>
+          <cell r="I29">
+            <v>55.46875</v>
+          </cell>
+          <cell r="J29">
+            <v>18.65625</v>
+          </cell>
+          <cell r="K29">
+            <v>10.03125</v>
+          </cell>
+          <cell r="L29">
+            <v>10.21875</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>-10.233301819165744</v>
+          </cell>
+          <cell r="O29">
+            <v>97.289776682911139</v>
+          </cell>
+          <cell r="P29">
+            <v>110.00568539088987</v>
+          </cell>
+          <cell r="Q29">
+            <v>0.49735915492957744</v>
+          </cell>
+          <cell r="R29">
+            <v>63.928750000000001</v>
+          </cell>
+          <cell r="S29">
+            <v>53.25</v>
+          </cell>
+          <cell r="T29">
+            <v>20.71875</v>
+          </cell>
+          <cell r="U29">
+            <v>8.125</v>
+          </cell>
+          <cell r="V29">
+            <v>9.6875</v>
+          </cell>
+          <cell r="W29">
+            <v>0</v>
+          </cell>
+          <cell r="X29">
+            <v>3.5</v>
+          </cell>
         </row>
         <row r="30">
-          <cell r="D30"/>
-          <cell r="E30"/>
-          <cell r="F30"/>
-          <cell r="G30"/>
-          <cell r="H30"/>
-          <cell r="I30"/>
-          <cell r="J30"/>
-          <cell r="K30"/>
-          <cell r="L30"/>
-          <cell r="M30"/>
-          <cell r="N30"/>
-          <cell r="O30"/>
-          <cell r="P30"/>
-          <cell r="Q30"/>
-          <cell r="R30"/>
-          <cell r="S30"/>
-          <cell r="T30"/>
-          <cell r="U30"/>
-          <cell r="V30"/>
-          <cell r="W30"/>
-          <cell r="X30"/>
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Alcorn State</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>Prairie View A&amp;M</v>
+          </cell>
+          <cell r="D30">
+            <v>-19.948242350647938</v>
+          </cell>
+          <cell r="E30">
+            <v>94.015466724757644</v>
+          </cell>
+          <cell r="F30">
+            <v>99.142194717936277</v>
+          </cell>
+          <cell r="G30">
+            <v>0.47871720116618077</v>
+          </cell>
+          <cell r="H30">
+            <v>68.99733333333333</v>
+          </cell>
+          <cell r="I30">
+            <v>57.166666666666664</v>
+          </cell>
+          <cell r="J30">
+            <v>17.266666666666666</v>
+          </cell>
+          <cell r="K30">
+            <v>9.6</v>
+          </cell>
+          <cell r="L30">
+            <v>13.833333333333334</v>
+          </cell>
+          <cell r="M30">
+            <v>0</v>
+          </cell>
+          <cell r="N30">
+            <v>-10.740619332032924</v>
+          </cell>
+          <cell r="O30">
+            <v>96.942723004694827</v>
+          </cell>
+          <cell r="P30">
+            <v>93.291737667336207</v>
+          </cell>
+          <cell r="Q30">
+            <v>0.49388297872340425</v>
+          </cell>
+          <cell r="R30">
+            <v>74.380645161290332</v>
+          </cell>
+          <cell r="S30">
+            <v>60.645161290322584</v>
+          </cell>
+          <cell r="T30">
+            <v>26.451612903225808</v>
+          </cell>
+          <cell r="U30">
+            <v>10.161290322580646</v>
+          </cell>
+          <cell r="V30">
+            <v>12.258064516129032</v>
+          </cell>
+          <cell r="W30">
+            <v>0</v>
+          </cell>
+          <cell r="X30">
+            <v>6</v>
+          </cell>
         </row>
         <row r="31">
-          <cell r="D31"/>
-          <cell r="E31"/>
-          <cell r="F31"/>
-          <cell r="G31"/>
-          <cell r="H31"/>
-          <cell r="I31"/>
-          <cell r="J31"/>
-          <cell r="K31"/>
-          <cell r="L31"/>
-          <cell r="M31"/>
-          <cell r="N31"/>
-          <cell r="O31"/>
-          <cell r="P31"/>
-          <cell r="Q31"/>
-          <cell r="R31"/>
-          <cell r="S31"/>
-          <cell r="T31"/>
-          <cell r="U31"/>
-          <cell r="V31"/>
-          <cell r="W31"/>
-          <cell r="X31"/>
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Mercyhurst</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>Long Island University</v>
+          </cell>
+          <cell r="D31">
+            <v>-8.9892302193689186</v>
+          </cell>
+          <cell r="E31">
+            <v>99.107385837914336</v>
+          </cell>
+          <cell r="F31">
+            <v>101.60426992452147</v>
+          </cell>
+          <cell r="G31">
+            <v>0.50320855614973259</v>
+          </cell>
+          <cell r="H31">
+            <v>65.3125</v>
+          </cell>
+          <cell r="I31">
+            <v>58.4375</v>
+          </cell>
+          <cell r="J31">
+            <v>14.84375</v>
+          </cell>
+          <cell r="K31">
+            <v>9.15625</v>
+          </cell>
+          <cell r="L31">
+            <v>9.5</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+          <cell r="N31">
+            <v>-5.3862870517485577</v>
+          </cell>
+          <cell r="O31">
+            <v>97.110724162654932</v>
+          </cell>
+          <cell r="P31">
+            <v>96.845289405897276</v>
+          </cell>
+          <cell r="Q31">
+            <v>0.53378746594005455</v>
+          </cell>
+          <cell r="R31">
+            <v>67.763750000000002</v>
+          </cell>
+          <cell r="S31">
+            <v>57.34375</v>
+          </cell>
+          <cell r="T31">
+            <v>19.5625</v>
+          </cell>
+          <cell r="U31">
+            <v>11.46875</v>
+          </cell>
+          <cell r="V31">
+            <v>13.28125</v>
+          </cell>
+          <cell r="W31">
+            <v>0</v>
+          </cell>
+          <cell r="X31">
+            <v>6.5</v>
+          </cell>
         </row>
         <row r="32">
-          <cell r="D32"/>
-          <cell r="E32"/>
-          <cell r="F32"/>
-          <cell r="G32"/>
-          <cell r="H32"/>
-          <cell r="I32"/>
-          <cell r="J32"/>
-          <cell r="K32"/>
-          <cell r="L32"/>
-          <cell r="M32"/>
-          <cell r="N32"/>
-          <cell r="O32"/>
-          <cell r="P32"/>
-          <cell r="Q32"/>
-          <cell r="R32"/>
-          <cell r="S32"/>
-          <cell r="T32"/>
-          <cell r="U32"/>
-          <cell r="V32"/>
-          <cell r="W32"/>
-          <cell r="X32"/>
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>UMass Lowell</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>UMBC</v>
+          </cell>
+          <cell r="D32">
+            <v>-10.78545288970942</v>
+          </cell>
+          <cell r="E32">
+            <v>99.396366256626706</v>
+          </cell>
+          <cell r="F32">
+            <v>109.60513696431309</v>
+          </cell>
+          <cell r="G32">
+            <v>0.51174863387978142</v>
+          </cell>
+          <cell r="H32">
+            <v>68.758709677419347</v>
+          </cell>
+          <cell r="I32">
+            <v>59.032258064516128</v>
+          </cell>
+          <cell r="J32">
+            <v>22.032258064516128</v>
+          </cell>
+          <cell r="K32">
+            <v>12.225806451612904</v>
+          </cell>
+          <cell r="L32">
+            <v>12.258064516129032</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+          <cell r="N32">
+            <v>-9.1795715901906192</v>
+          </cell>
+          <cell r="O32">
+            <v>97.210907835692097</v>
+          </cell>
+          <cell r="P32">
+            <v>110.54326482948768</v>
+          </cell>
+          <cell r="Q32">
+            <v>0.5430982519590114</v>
+          </cell>
+          <cell r="R32">
+            <v>66.972413793103442</v>
+          </cell>
+          <cell r="S32">
+            <v>57.206896551724135</v>
+          </cell>
+          <cell r="T32">
+            <v>18.275862068965516</v>
+          </cell>
+          <cell r="U32">
+            <v>8.068965517241379</v>
+          </cell>
+          <cell r="V32">
+            <v>9.7931034482758612</v>
+          </cell>
+          <cell r="W32">
+            <v>0</v>
+          </cell>
+          <cell r="X32">
+            <v>7.5</v>
+          </cell>
         </row>
         <row r="33">
-          <cell r="D33"/>
-          <cell r="E33"/>
-          <cell r="F33"/>
-          <cell r="G33"/>
-          <cell r="H33"/>
-          <cell r="I33"/>
-          <cell r="J33"/>
-          <cell r="K33"/>
-          <cell r="L33"/>
-          <cell r="M33"/>
-          <cell r="N33"/>
-          <cell r="O33"/>
-          <cell r="P33"/>
-          <cell r="Q33"/>
-          <cell r="R33"/>
-          <cell r="S33"/>
-          <cell r="T33"/>
-          <cell r="U33"/>
-          <cell r="V33"/>
-          <cell r="W33"/>
-          <cell r="X33"/>
-        </row>
-        <row r="34">
-          <cell r="D34"/>
-          <cell r="E34"/>
-          <cell r="F34"/>
-          <cell r="G34"/>
-          <cell r="H34"/>
-          <cell r="I34"/>
-          <cell r="J34"/>
-          <cell r="K34"/>
-          <cell r="L34"/>
-          <cell r="M34"/>
-          <cell r="N34"/>
-          <cell r="O34"/>
-          <cell r="P34"/>
-          <cell r="Q34"/>
-          <cell r="R34"/>
-          <cell r="S34"/>
-          <cell r="T34"/>
-          <cell r="U34"/>
-          <cell r="V34"/>
-          <cell r="W34"/>
-          <cell r="X34"/>
-        </row>
-        <row r="35">
-          <cell r="D35"/>
-          <cell r="E35"/>
-          <cell r="F35"/>
-          <cell r="G35"/>
-          <cell r="H35"/>
-          <cell r="I35"/>
-          <cell r="J35"/>
-          <cell r="K35"/>
-          <cell r="L35"/>
-          <cell r="M35"/>
-          <cell r="N35"/>
-          <cell r="O35"/>
-          <cell r="P35"/>
-          <cell r="Q35"/>
-          <cell r="R35"/>
-          <cell r="S35"/>
-          <cell r="T35"/>
-          <cell r="U35"/>
-          <cell r="V35"/>
-          <cell r="W35"/>
-          <cell r="X35"/>
-        </row>
-        <row r="36">
-          <cell r="D36"/>
-          <cell r="E36"/>
-          <cell r="F36"/>
-          <cell r="G36"/>
-          <cell r="H36"/>
-          <cell r="I36"/>
-          <cell r="J36"/>
-          <cell r="K36"/>
-          <cell r="L36"/>
-          <cell r="M36"/>
-          <cell r="N36"/>
-          <cell r="O36"/>
-          <cell r="P36"/>
-          <cell r="Q36"/>
-          <cell r="R36"/>
-          <cell r="S36"/>
-          <cell r="T36"/>
-          <cell r="U36"/>
-          <cell r="V36"/>
-          <cell r="W36"/>
-          <cell r="X36"/>
-        </row>
-        <row r="37">
-          <cell r="D37"/>
-          <cell r="E37"/>
-          <cell r="F37"/>
-          <cell r="G37"/>
-          <cell r="H37"/>
-          <cell r="I37"/>
-          <cell r="J37"/>
-          <cell r="K37"/>
-          <cell r="L37"/>
-          <cell r="M37"/>
-          <cell r="N37"/>
-          <cell r="O37"/>
-          <cell r="P37"/>
-          <cell r="Q37"/>
-          <cell r="R37"/>
-          <cell r="S37"/>
-          <cell r="T37"/>
-          <cell r="U37"/>
-          <cell r="V37"/>
-          <cell r="W37"/>
-          <cell r="X37"/>
-        </row>
-        <row r="38">
-          <cell r="D38"/>
-          <cell r="E38"/>
-          <cell r="F38"/>
-          <cell r="G38"/>
-          <cell r="H38"/>
-          <cell r="I38"/>
-          <cell r="J38"/>
-          <cell r="K38"/>
-          <cell r="L38"/>
-          <cell r="M38"/>
-          <cell r="N38"/>
-          <cell r="O38"/>
-          <cell r="P38"/>
-          <cell r="Q38"/>
-          <cell r="R38"/>
-          <cell r="S38"/>
-          <cell r="T38"/>
-          <cell r="U38"/>
-          <cell r="V38"/>
-          <cell r="W38"/>
-          <cell r="X38"/>
-        </row>
-        <row r="39">
-          <cell r="D39"/>
-          <cell r="E39"/>
-          <cell r="F39"/>
-          <cell r="G39"/>
-          <cell r="H39"/>
-          <cell r="I39"/>
-          <cell r="J39"/>
-          <cell r="K39"/>
-          <cell r="L39"/>
-          <cell r="M39"/>
-          <cell r="N39"/>
-          <cell r="O39"/>
-          <cell r="P39"/>
-          <cell r="Q39"/>
-          <cell r="R39"/>
-          <cell r="S39"/>
-          <cell r="T39"/>
-          <cell r="U39"/>
-          <cell r="V39"/>
-          <cell r="W39"/>
-          <cell r="X39"/>
-        </row>
-        <row r="40">
-          <cell r="D40"/>
-          <cell r="E40"/>
-          <cell r="F40"/>
-          <cell r="G40"/>
-          <cell r="H40"/>
-          <cell r="I40"/>
-          <cell r="J40"/>
-          <cell r="K40"/>
-          <cell r="L40"/>
-          <cell r="M40"/>
-          <cell r="N40"/>
-          <cell r="O40"/>
-          <cell r="P40"/>
-          <cell r="Q40"/>
-          <cell r="R40"/>
-          <cell r="S40"/>
-          <cell r="T40"/>
-          <cell r="U40"/>
-          <cell r="V40"/>
-          <cell r="W40"/>
-          <cell r="X40"/>
-        </row>
-        <row r="41">
-          <cell r="D41"/>
-          <cell r="E41"/>
-          <cell r="F41"/>
-          <cell r="G41"/>
-          <cell r="H41"/>
-          <cell r="I41"/>
-          <cell r="J41"/>
-          <cell r="K41"/>
-          <cell r="L41"/>
-          <cell r="M41"/>
-          <cell r="N41"/>
-          <cell r="O41"/>
-          <cell r="P41"/>
-          <cell r="Q41"/>
-          <cell r="R41"/>
-          <cell r="S41"/>
-          <cell r="T41"/>
-          <cell r="U41"/>
-          <cell r="V41"/>
-          <cell r="W41"/>
-          <cell r="X41"/>
-        </row>
-        <row r="42">
-          <cell r="D42"/>
-          <cell r="E42"/>
-          <cell r="F42"/>
-          <cell r="G42"/>
-          <cell r="H42"/>
-          <cell r="I42"/>
-          <cell r="J42"/>
-          <cell r="K42"/>
-          <cell r="L42"/>
-          <cell r="M42"/>
-          <cell r="N42"/>
-          <cell r="O42"/>
-          <cell r="P42"/>
-          <cell r="Q42"/>
-          <cell r="R42"/>
-          <cell r="S42"/>
-          <cell r="T42"/>
-          <cell r="U42"/>
-          <cell r="V42"/>
-          <cell r="W42"/>
-          <cell r="X42"/>
-        </row>
-        <row r="43">
-          <cell r="D43"/>
-          <cell r="E43"/>
-          <cell r="F43"/>
-          <cell r="G43"/>
-          <cell r="H43"/>
-          <cell r="I43"/>
-          <cell r="J43"/>
-          <cell r="K43"/>
-          <cell r="L43"/>
-          <cell r="M43"/>
-          <cell r="N43"/>
-          <cell r="O43"/>
-          <cell r="P43"/>
-          <cell r="Q43"/>
-          <cell r="R43"/>
-          <cell r="S43"/>
-          <cell r="T43"/>
-          <cell r="U43"/>
-          <cell r="V43"/>
-          <cell r="W43"/>
-          <cell r="X43"/>
-        </row>
-        <row r="44">
-          <cell r="D44"/>
-          <cell r="E44"/>
-          <cell r="F44"/>
-          <cell r="G44"/>
-          <cell r="H44"/>
-          <cell r="I44"/>
-          <cell r="J44"/>
-          <cell r="K44"/>
-          <cell r="L44"/>
-          <cell r="M44"/>
-          <cell r="N44"/>
-          <cell r="O44"/>
-          <cell r="P44"/>
-          <cell r="Q44"/>
-          <cell r="R44"/>
-          <cell r="S44"/>
-          <cell r="T44"/>
-          <cell r="U44"/>
-          <cell r="V44"/>
-          <cell r="W44"/>
-          <cell r="X44"/>
-        </row>
-        <row r="45">
-          <cell r="D45"/>
-          <cell r="E45"/>
-          <cell r="F45"/>
-          <cell r="G45"/>
-          <cell r="H45"/>
-          <cell r="I45"/>
-          <cell r="J45"/>
-          <cell r="K45"/>
-          <cell r="L45"/>
-          <cell r="M45"/>
-          <cell r="N45"/>
-          <cell r="O45"/>
-          <cell r="P45"/>
-          <cell r="Q45"/>
-          <cell r="R45"/>
-          <cell r="S45"/>
-          <cell r="T45"/>
-          <cell r="U45"/>
-          <cell r="V45"/>
-          <cell r="W45"/>
-          <cell r="X45"/>
-        </row>
-        <row r="46">
-          <cell r="D46"/>
-          <cell r="E46"/>
-          <cell r="F46"/>
-          <cell r="G46"/>
-          <cell r="H46"/>
-          <cell r="I46"/>
-          <cell r="J46"/>
-          <cell r="K46"/>
-          <cell r="L46"/>
-          <cell r="M46"/>
-          <cell r="N46"/>
-          <cell r="O46"/>
-          <cell r="P46"/>
-          <cell r="Q46"/>
-          <cell r="R46"/>
-          <cell r="S46"/>
-          <cell r="T46"/>
-          <cell r="U46"/>
-          <cell r="V46"/>
-          <cell r="W46"/>
-          <cell r="X46"/>
-        </row>
-        <row r="47">
-          <cell r="D47"/>
-          <cell r="E47"/>
-          <cell r="F47"/>
-          <cell r="G47"/>
-          <cell r="H47"/>
-          <cell r="I47"/>
-          <cell r="J47"/>
-          <cell r="K47"/>
-          <cell r="L47"/>
-          <cell r="M47"/>
-          <cell r="N47"/>
-          <cell r="O47"/>
-          <cell r="P47"/>
-          <cell r="Q47"/>
-          <cell r="R47"/>
-          <cell r="S47"/>
-          <cell r="T47"/>
-          <cell r="U47"/>
-          <cell r="V47"/>
-          <cell r="W47"/>
-          <cell r="X47"/>
-        </row>
-        <row r="48">
-          <cell r="D48"/>
-          <cell r="E48"/>
-          <cell r="F48"/>
-          <cell r="G48"/>
-          <cell r="H48"/>
-          <cell r="I48"/>
-          <cell r="J48"/>
-          <cell r="K48"/>
-          <cell r="L48"/>
-          <cell r="M48"/>
-          <cell r="N48"/>
-          <cell r="O48"/>
-          <cell r="P48"/>
-          <cell r="Q48"/>
-          <cell r="R48"/>
-          <cell r="S48"/>
-          <cell r="T48"/>
-          <cell r="U48"/>
-          <cell r="V48"/>
-          <cell r="W48"/>
-          <cell r="X48"/>
-        </row>
-        <row r="49">
-          <cell r="D49"/>
-          <cell r="E49"/>
-          <cell r="F49"/>
-          <cell r="G49"/>
-          <cell r="H49"/>
-          <cell r="I49"/>
-          <cell r="J49"/>
-          <cell r="K49"/>
-          <cell r="L49"/>
-          <cell r="M49"/>
-          <cell r="N49"/>
-          <cell r="O49"/>
-          <cell r="P49"/>
-          <cell r="Q49"/>
-          <cell r="R49"/>
-          <cell r="S49"/>
-          <cell r="T49"/>
-          <cell r="U49"/>
-          <cell r="V49"/>
-          <cell r="W49"/>
-          <cell r="X49"/>
-        </row>
-        <row r="50">
-          <cell r="D50"/>
-          <cell r="E50"/>
-          <cell r="F50"/>
-          <cell r="G50"/>
-          <cell r="H50"/>
-          <cell r="I50"/>
-          <cell r="J50"/>
-          <cell r="K50"/>
-          <cell r="L50"/>
-          <cell r="M50"/>
-          <cell r="N50"/>
-          <cell r="O50"/>
-          <cell r="P50"/>
-          <cell r="Q50"/>
-          <cell r="R50"/>
-          <cell r="S50"/>
-          <cell r="T50"/>
-          <cell r="U50"/>
-          <cell r="V50"/>
-          <cell r="W50"/>
-          <cell r="X50"/>
-        </row>
-        <row r="51">
-          <cell r="D51"/>
-          <cell r="E51"/>
-          <cell r="F51"/>
-          <cell r="G51"/>
-          <cell r="H51"/>
-          <cell r="I51"/>
-          <cell r="J51"/>
-          <cell r="K51"/>
-          <cell r="L51"/>
-          <cell r="M51"/>
-          <cell r="N51"/>
-          <cell r="O51"/>
-          <cell r="P51"/>
-          <cell r="Q51"/>
-          <cell r="R51"/>
-          <cell r="S51"/>
-          <cell r="T51"/>
-          <cell r="U51"/>
-          <cell r="V51"/>
-          <cell r="W51"/>
-          <cell r="X51"/>
-        </row>
-        <row r="52">
-          <cell r="D52"/>
-          <cell r="E52"/>
-          <cell r="F52"/>
-          <cell r="G52"/>
-          <cell r="H52"/>
-          <cell r="I52"/>
-          <cell r="J52"/>
-          <cell r="K52"/>
-          <cell r="L52"/>
-          <cell r="M52"/>
-          <cell r="N52"/>
-          <cell r="O52"/>
-          <cell r="P52"/>
-          <cell r="Q52"/>
-          <cell r="R52"/>
-          <cell r="S52"/>
-          <cell r="T52"/>
-          <cell r="U52"/>
-          <cell r="V52"/>
-          <cell r="W52"/>
-          <cell r="X52"/>
-        </row>
-        <row r="53">
-          <cell r="D53"/>
-          <cell r="E53"/>
-          <cell r="F53"/>
-          <cell r="G53"/>
-          <cell r="H53"/>
-          <cell r="I53"/>
-          <cell r="J53"/>
-          <cell r="K53"/>
-          <cell r="L53"/>
-          <cell r="M53"/>
-          <cell r="N53"/>
-          <cell r="O53"/>
-          <cell r="P53"/>
-          <cell r="Q53"/>
-          <cell r="R53"/>
-          <cell r="S53"/>
-          <cell r="T53"/>
-          <cell r="U53"/>
-          <cell r="V53"/>
-          <cell r="W53"/>
-          <cell r="X53"/>
-        </row>
-        <row r="54">
-          <cell r="D54"/>
-          <cell r="E54"/>
-          <cell r="F54"/>
-          <cell r="G54"/>
-          <cell r="H54"/>
-          <cell r="I54"/>
-          <cell r="J54"/>
-          <cell r="K54"/>
-          <cell r="L54"/>
-          <cell r="M54"/>
-          <cell r="N54"/>
-          <cell r="O54"/>
-          <cell r="P54"/>
-          <cell r="Q54"/>
-          <cell r="R54"/>
-          <cell r="S54"/>
-          <cell r="T54"/>
-          <cell r="U54"/>
-          <cell r="V54"/>
-          <cell r="W54"/>
-          <cell r="X54"/>
-        </row>
-        <row r="55">
-          <cell r="D55"/>
-          <cell r="E55"/>
-          <cell r="F55"/>
-          <cell r="G55"/>
-          <cell r="H55"/>
-          <cell r="I55"/>
-          <cell r="J55"/>
-          <cell r="K55"/>
-          <cell r="L55"/>
-          <cell r="M55"/>
-          <cell r="N55"/>
-          <cell r="O55"/>
-          <cell r="P55"/>
-          <cell r="Q55"/>
-          <cell r="R55"/>
-          <cell r="S55"/>
-          <cell r="T55"/>
-          <cell r="U55"/>
-          <cell r="V55"/>
-          <cell r="W55"/>
-          <cell r="X55"/>
-        </row>
-        <row r="56">
-          <cell r="D56"/>
-          <cell r="E56"/>
-          <cell r="F56"/>
-          <cell r="G56"/>
-          <cell r="H56"/>
-          <cell r="I56"/>
-          <cell r="J56"/>
-          <cell r="K56"/>
-          <cell r="L56"/>
-          <cell r="M56"/>
-          <cell r="N56"/>
-          <cell r="O56"/>
-          <cell r="P56"/>
-          <cell r="Q56"/>
-          <cell r="R56"/>
-          <cell r="S56"/>
-          <cell r="T56"/>
-          <cell r="U56"/>
-          <cell r="V56"/>
-          <cell r="W56"/>
-          <cell r="X56"/>
-        </row>
-        <row r="57">
-          <cell r="D57"/>
-          <cell r="E57"/>
-          <cell r="F57"/>
-          <cell r="G57"/>
-          <cell r="H57"/>
-          <cell r="I57"/>
-          <cell r="J57"/>
-          <cell r="K57"/>
-          <cell r="L57"/>
-          <cell r="M57"/>
-          <cell r="N57"/>
-          <cell r="O57"/>
-          <cell r="P57"/>
-          <cell r="Q57"/>
-          <cell r="R57"/>
-          <cell r="S57"/>
-          <cell r="T57"/>
-          <cell r="U57"/>
-          <cell r="V57"/>
-          <cell r="W57"/>
-          <cell r="X57"/>
-        </row>
-        <row r="58">
-          <cell r="D58"/>
-          <cell r="E58"/>
-          <cell r="F58"/>
-          <cell r="G58"/>
-          <cell r="H58"/>
-          <cell r="I58"/>
-          <cell r="J58"/>
-          <cell r="K58"/>
-          <cell r="L58"/>
-          <cell r="M58"/>
-          <cell r="N58"/>
-          <cell r="O58"/>
-          <cell r="P58"/>
-          <cell r="Q58"/>
-          <cell r="R58"/>
-          <cell r="S58"/>
-          <cell r="T58"/>
-          <cell r="U58"/>
-          <cell r="V58"/>
-          <cell r="W58"/>
-          <cell r="X58"/>
-        </row>
-        <row r="59">
-          <cell r="D59"/>
-          <cell r="E59"/>
-          <cell r="F59"/>
-          <cell r="G59"/>
-          <cell r="H59"/>
-          <cell r="I59"/>
-          <cell r="J59"/>
-          <cell r="K59"/>
-          <cell r="L59"/>
-          <cell r="M59"/>
-          <cell r="N59"/>
-          <cell r="O59"/>
-          <cell r="P59"/>
-          <cell r="Q59"/>
-          <cell r="R59"/>
-          <cell r="S59"/>
-          <cell r="T59"/>
-          <cell r="U59"/>
-          <cell r="V59"/>
-          <cell r="W59"/>
-          <cell r="X59"/>
-        </row>
-        <row r="60">
-          <cell r="D60"/>
-          <cell r="E60"/>
-          <cell r="F60"/>
-          <cell r="G60"/>
-          <cell r="H60"/>
-          <cell r="I60"/>
-          <cell r="J60"/>
-          <cell r="K60"/>
-          <cell r="L60"/>
-          <cell r="M60"/>
-          <cell r="N60"/>
-          <cell r="O60"/>
-          <cell r="P60"/>
-          <cell r="Q60"/>
-          <cell r="R60"/>
-          <cell r="S60"/>
-          <cell r="T60"/>
-          <cell r="U60"/>
-          <cell r="V60"/>
-          <cell r="W60"/>
-          <cell r="X60"/>
-        </row>
-        <row r="61">
-          <cell r="D61"/>
-          <cell r="E61"/>
-          <cell r="F61"/>
-          <cell r="G61"/>
-          <cell r="H61"/>
-          <cell r="I61"/>
-          <cell r="J61"/>
-          <cell r="K61"/>
-          <cell r="L61"/>
-          <cell r="M61"/>
-          <cell r="N61"/>
-          <cell r="O61"/>
-          <cell r="P61"/>
-          <cell r="Q61"/>
-          <cell r="R61"/>
-          <cell r="S61"/>
-          <cell r="T61"/>
-          <cell r="U61"/>
-          <cell r="V61"/>
-          <cell r="W61"/>
-          <cell r="X61"/>
-        </row>
-        <row r="62">
-          <cell r="D62"/>
-          <cell r="E62"/>
-          <cell r="F62"/>
-          <cell r="G62"/>
-          <cell r="H62"/>
-          <cell r="I62"/>
-          <cell r="J62"/>
-          <cell r="K62"/>
-          <cell r="L62"/>
-          <cell r="M62"/>
-          <cell r="N62"/>
-          <cell r="O62"/>
-          <cell r="P62"/>
-          <cell r="Q62"/>
-          <cell r="R62"/>
-          <cell r="S62"/>
-          <cell r="T62"/>
-          <cell r="U62"/>
-          <cell r="V62"/>
-          <cell r="W62"/>
-          <cell r="X62"/>
-        </row>
-        <row r="63">
-          <cell r="D63"/>
-          <cell r="E63"/>
-          <cell r="F63"/>
-          <cell r="G63"/>
-          <cell r="H63"/>
-          <cell r="I63"/>
-          <cell r="J63"/>
-          <cell r="K63"/>
-          <cell r="L63"/>
-          <cell r="M63"/>
-          <cell r="N63"/>
-          <cell r="O63"/>
-          <cell r="P63"/>
-          <cell r="Q63"/>
-          <cell r="R63"/>
-          <cell r="S63"/>
-          <cell r="T63"/>
-          <cell r="U63"/>
-          <cell r="V63"/>
-          <cell r="W63"/>
-          <cell r="X63"/>
-        </row>
-        <row r="64">
-          <cell r="D64"/>
-          <cell r="E64"/>
-          <cell r="F64"/>
-          <cell r="G64"/>
-          <cell r="H64"/>
-          <cell r="I64"/>
-          <cell r="J64"/>
-          <cell r="K64"/>
-          <cell r="L64"/>
-          <cell r="M64"/>
-          <cell r="N64"/>
-          <cell r="O64"/>
-          <cell r="P64"/>
-          <cell r="Q64"/>
-          <cell r="R64"/>
-          <cell r="S64"/>
-          <cell r="T64"/>
-          <cell r="U64"/>
-          <cell r="V64"/>
-          <cell r="W64"/>
-          <cell r="X64"/>
-        </row>
-        <row r="65">
-          <cell r="D65"/>
-          <cell r="E65"/>
-          <cell r="F65"/>
-          <cell r="G65"/>
-          <cell r="H65"/>
-          <cell r="I65"/>
-          <cell r="J65"/>
-          <cell r="K65"/>
-          <cell r="L65"/>
-          <cell r="M65"/>
-          <cell r="N65"/>
-          <cell r="O65"/>
-          <cell r="P65"/>
-          <cell r="Q65"/>
-          <cell r="R65"/>
-          <cell r="S65"/>
-          <cell r="T65"/>
-          <cell r="U65"/>
-          <cell r="V65"/>
-          <cell r="W65"/>
-          <cell r="X65"/>
-        </row>
-        <row r="66">
-          <cell r="D66"/>
-          <cell r="E66"/>
-          <cell r="F66"/>
-          <cell r="G66"/>
-          <cell r="H66"/>
-          <cell r="I66"/>
-          <cell r="J66"/>
-          <cell r="K66"/>
-          <cell r="L66"/>
-          <cell r="M66"/>
-          <cell r="N66"/>
-          <cell r="O66"/>
-          <cell r="P66"/>
-          <cell r="Q66"/>
-          <cell r="R66"/>
-          <cell r="S66"/>
-          <cell r="T66"/>
-          <cell r="U66"/>
-          <cell r="V66"/>
-          <cell r="W66"/>
-          <cell r="X66"/>
-        </row>
-        <row r="67">
-          <cell r="D67"/>
-          <cell r="E67"/>
-          <cell r="F67"/>
-          <cell r="G67"/>
-          <cell r="H67"/>
-          <cell r="I67"/>
-          <cell r="J67"/>
-          <cell r="K67"/>
-          <cell r="L67"/>
-          <cell r="M67"/>
-          <cell r="N67"/>
-          <cell r="O67"/>
-          <cell r="P67"/>
-          <cell r="Q67"/>
-          <cell r="R67"/>
-          <cell r="S67"/>
-          <cell r="T67"/>
-          <cell r="U67"/>
-          <cell r="V67"/>
-          <cell r="W67"/>
-          <cell r="X67"/>
-        </row>
-        <row r="68">
-          <cell r="D68"/>
-          <cell r="E68"/>
-          <cell r="F68"/>
-          <cell r="G68"/>
-          <cell r="H68"/>
-          <cell r="I68"/>
-          <cell r="J68"/>
-          <cell r="K68"/>
-          <cell r="L68"/>
-          <cell r="M68"/>
-          <cell r="N68"/>
-          <cell r="O68"/>
-          <cell r="P68"/>
-          <cell r="Q68"/>
-          <cell r="R68"/>
-          <cell r="S68"/>
-          <cell r="T68"/>
-          <cell r="U68"/>
-          <cell r="V68"/>
-          <cell r="W68"/>
-          <cell r="X68"/>
-        </row>
-        <row r="69">
-          <cell r="D69"/>
-          <cell r="E69"/>
-          <cell r="F69"/>
-          <cell r="G69"/>
-          <cell r="H69"/>
-          <cell r="I69"/>
-          <cell r="J69"/>
-          <cell r="K69"/>
-          <cell r="L69"/>
-          <cell r="M69"/>
-          <cell r="N69"/>
-          <cell r="O69"/>
-          <cell r="P69"/>
-          <cell r="Q69"/>
-          <cell r="R69"/>
-          <cell r="S69"/>
-          <cell r="T69"/>
-          <cell r="U69"/>
-          <cell r="V69"/>
-          <cell r="W69"/>
-          <cell r="X69"/>
-        </row>
-        <row r="70">
-          <cell r="D70"/>
-          <cell r="E70"/>
-          <cell r="F70"/>
-          <cell r="G70"/>
-          <cell r="H70"/>
-          <cell r="I70"/>
-          <cell r="J70"/>
-          <cell r="K70"/>
-          <cell r="L70"/>
-          <cell r="M70"/>
-          <cell r="N70"/>
-          <cell r="O70"/>
-          <cell r="P70"/>
-          <cell r="Q70"/>
-          <cell r="R70"/>
-          <cell r="S70"/>
-          <cell r="T70"/>
-          <cell r="U70"/>
-          <cell r="V70"/>
-          <cell r="W70"/>
-          <cell r="X70"/>
-        </row>
-        <row r="71">
-          <cell r="D71"/>
-          <cell r="E71"/>
-          <cell r="F71"/>
-          <cell r="G71"/>
-          <cell r="H71"/>
-          <cell r="I71"/>
-          <cell r="J71"/>
-          <cell r="K71"/>
-          <cell r="L71"/>
-          <cell r="M71"/>
-          <cell r="N71"/>
-          <cell r="O71"/>
-          <cell r="P71"/>
-          <cell r="Q71"/>
-          <cell r="R71"/>
-          <cell r="S71"/>
-          <cell r="T71"/>
-          <cell r="U71"/>
-          <cell r="V71"/>
-          <cell r="W71"/>
-          <cell r="X71"/>
-        </row>
-        <row r="72">
-          <cell r="D72"/>
-          <cell r="E72"/>
-          <cell r="F72"/>
-          <cell r="G72"/>
-          <cell r="H72"/>
-          <cell r="I72"/>
-          <cell r="J72"/>
-          <cell r="K72"/>
-          <cell r="L72"/>
-          <cell r="M72"/>
-          <cell r="N72"/>
-          <cell r="O72"/>
-          <cell r="P72"/>
-          <cell r="Q72"/>
-          <cell r="R72"/>
-          <cell r="S72"/>
-          <cell r="T72"/>
-          <cell r="U72"/>
-          <cell r="V72"/>
-          <cell r="W72"/>
-          <cell r="X72"/>
-        </row>
-        <row r="73">
-          <cell r="D73"/>
-          <cell r="E73"/>
-          <cell r="F73"/>
-          <cell r="G73"/>
-          <cell r="H73"/>
-          <cell r="I73"/>
-          <cell r="J73"/>
-          <cell r="K73"/>
-          <cell r="L73"/>
-          <cell r="M73"/>
-          <cell r="N73"/>
-          <cell r="O73"/>
-          <cell r="P73"/>
-          <cell r="Q73"/>
-          <cell r="R73"/>
-          <cell r="S73"/>
-          <cell r="T73"/>
-          <cell r="U73"/>
-          <cell r="V73"/>
-          <cell r="W73"/>
-          <cell r="X73"/>
-        </row>
-        <row r="74">
-          <cell r="D74"/>
-          <cell r="E74"/>
-          <cell r="F74"/>
-          <cell r="G74"/>
-          <cell r="H74"/>
-          <cell r="I74"/>
-          <cell r="J74"/>
-          <cell r="K74"/>
-          <cell r="L74"/>
-          <cell r="M74"/>
-          <cell r="N74"/>
-          <cell r="O74"/>
-          <cell r="P74"/>
-          <cell r="Q74"/>
-          <cell r="R74"/>
-          <cell r="S74"/>
-          <cell r="T74"/>
-          <cell r="U74"/>
-          <cell r="V74"/>
-          <cell r="W74"/>
-          <cell r="X74"/>
-        </row>
-        <row r="75">
-          <cell r="D75"/>
-          <cell r="E75"/>
-          <cell r="F75"/>
-          <cell r="G75"/>
-          <cell r="H75"/>
-          <cell r="I75"/>
-          <cell r="J75"/>
-          <cell r="K75"/>
-          <cell r="L75"/>
-          <cell r="M75"/>
-          <cell r="N75"/>
-          <cell r="O75"/>
-          <cell r="P75"/>
-          <cell r="Q75"/>
-          <cell r="R75"/>
-          <cell r="S75"/>
-          <cell r="T75"/>
-          <cell r="U75"/>
-          <cell r="V75"/>
-          <cell r="W75"/>
-          <cell r="X75"/>
-        </row>
-        <row r="76">
-          <cell r="D76"/>
-          <cell r="E76"/>
-          <cell r="F76"/>
-          <cell r="G76"/>
-          <cell r="H76"/>
-          <cell r="I76"/>
-          <cell r="J76"/>
-          <cell r="K76"/>
-          <cell r="L76"/>
-          <cell r="M76"/>
-          <cell r="N76"/>
-          <cell r="O76"/>
-          <cell r="P76"/>
-          <cell r="Q76"/>
-          <cell r="R76"/>
-          <cell r="S76"/>
-          <cell r="T76"/>
-          <cell r="U76"/>
-          <cell r="V76"/>
-          <cell r="W76"/>
-          <cell r="X76"/>
-        </row>
-        <row r="77">
-          <cell r="D77"/>
-          <cell r="E77"/>
-          <cell r="F77"/>
-          <cell r="G77"/>
-          <cell r="H77"/>
-          <cell r="I77"/>
-          <cell r="J77"/>
-          <cell r="K77"/>
-          <cell r="L77"/>
-          <cell r="M77"/>
-          <cell r="N77"/>
-          <cell r="O77"/>
-          <cell r="P77"/>
-          <cell r="Q77"/>
-          <cell r="R77"/>
-          <cell r="S77"/>
-          <cell r="T77"/>
-          <cell r="U77"/>
-          <cell r="V77"/>
-          <cell r="W77"/>
-          <cell r="X77"/>
-        </row>
-        <row r="78">
-          <cell r="D78"/>
-          <cell r="E78"/>
-          <cell r="F78"/>
-          <cell r="G78"/>
-          <cell r="H78"/>
-          <cell r="I78"/>
-          <cell r="J78"/>
-          <cell r="K78"/>
-          <cell r="L78"/>
-          <cell r="M78"/>
-          <cell r="N78"/>
-          <cell r="O78"/>
-          <cell r="P78"/>
-          <cell r="Q78"/>
-          <cell r="R78"/>
-          <cell r="S78"/>
-          <cell r="T78"/>
-          <cell r="U78"/>
-          <cell r="V78"/>
-          <cell r="W78"/>
-          <cell r="X78"/>
-        </row>
-        <row r="79">
-          <cell r="D79"/>
-          <cell r="E79"/>
-          <cell r="F79"/>
-          <cell r="G79"/>
-          <cell r="H79"/>
-          <cell r="I79"/>
-          <cell r="J79"/>
-          <cell r="K79"/>
-          <cell r="L79"/>
-          <cell r="M79"/>
-          <cell r="N79"/>
-          <cell r="O79"/>
-          <cell r="P79"/>
-          <cell r="Q79"/>
-          <cell r="R79"/>
-          <cell r="S79"/>
-          <cell r="T79"/>
-          <cell r="U79"/>
-          <cell r="V79"/>
-          <cell r="W79"/>
-          <cell r="X79"/>
-        </row>
-        <row r="80">
-          <cell r="D80"/>
-          <cell r="E80"/>
-          <cell r="F80"/>
-          <cell r="G80"/>
-          <cell r="H80"/>
-          <cell r="I80"/>
-          <cell r="J80"/>
-          <cell r="K80"/>
-          <cell r="L80"/>
-          <cell r="M80"/>
-          <cell r="N80"/>
-          <cell r="O80"/>
-          <cell r="P80"/>
-          <cell r="Q80"/>
-          <cell r="R80"/>
-          <cell r="S80"/>
-          <cell r="T80"/>
-          <cell r="U80"/>
-          <cell r="V80"/>
-          <cell r="W80"/>
-          <cell r="X80"/>
-        </row>
-        <row r="81">
-          <cell r="D81"/>
-          <cell r="E81"/>
-          <cell r="F81"/>
-          <cell r="G81"/>
-          <cell r="H81"/>
-          <cell r="I81"/>
-          <cell r="J81"/>
-          <cell r="K81"/>
-          <cell r="L81"/>
-          <cell r="M81"/>
-          <cell r="N81"/>
-          <cell r="O81"/>
-          <cell r="P81"/>
-          <cell r="Q81"/>
-          <cell r="R81"/>
-          <cell r="S81"/>
-          <cell r="T81"/>
-          <cell r="U81"/>
-          <cell r="V81"/>
-          <cell r="W81"/>
-          <cell r="X81"/>
-        </row>
-        <row r="82">
-          <cell r="D82"/>
-          <cell r="E82"/>
-          <cell r="F82"/>
-          <cell r="G82"/>
-          <cell r="H82"/>
-          <cell r="I82"/>
-          <cell r="J82"/>
-          <cell r="K82"/>
-          <cell r="L82"/>
-          <cell r="M82"/>
-          <cell r="N82"/>
-          <cell r="O82"/>
-          <cell r="P82"/>
-          <cell r="Q82"/>
-          <cell r="R82"/>
-          <cell r="S82"/>
-          <cell r="T82"/>
-          <cell r="U82"/>
-          <cell r="V82"/>
-          <cell r="W82"/>
-          <cell r="X82"/>
-        </row>
-        <row r="83">
-          <cell r="D83"/>
-          <cell r="E83"/>
-          <cell r="F83"/>
-          <cell r="G83"/>
-          <cell r="H83"/>
-          <cell r="I83"/>
-          <cell r="J83"/>
-          <cell r="K83"/>
-          <cell r="L83"/>
-          <cell r="M83"/>
-          <cell r="N83"/>
-          <cell r="O83"/>
-          <cell r="P83"/>
-          <cell r="Q83"/>
-          <cell r="R83"/>
-          <cell r="S83"/>
-          <cell r="T83"/>
-          <cell r="U83"/>
-          <cell r="V83"/>
-          <cell r="W83"/>
-          <cell r="X83"/>
-        </row>
-        <row r="84">
-          <cell r="D84"/>
-          <cell r="E84"/>
-          <cell r="F84"/>
-          <cell r="G84"/>
-          <cell r="H84"/>
-          <cell r="I84"/>
-          <cell r="J84"/>
-          <cell r="K84"/>
-          <cell r="L84"/>
-          <cell r="M84"/>
-          <cell r="N84"/>
-          <cell r="O84"/>
-          <cell r="P84"/>
-          <cell r="Q84"/>
-          <cell r="R84"/>
-          <cell r="S84"/>
-          <cell r="T84"/>
-          <cell r="U84"/>
-          <cell r="V84"/>
-          <cell r="W84"/>
-          <cell r="X84"/>
-        </row>
-        <row r="85">
-          <cell r="D85"/>
-          <cell r="E85"/>
-          <cell r="F85"/>
-          <cell r="G85"/>
-          <cell r="H85"/>
-          <cell r="I85"/>
-          <cell r="J85"/>
-          <cell r="K85"/>
-          <cell r="L85"/>
-          <cell r="M85"/>
-          <cell r="N85"/>
-          <cell r="O85"/>
-          <cell r="P85"/>
-          <cell r="Q85"/>
-          <cell r="R85"/>
-          <cell r="S85"/>
-          <cell r="T85"/>
-          <cell r="U85"/>
-          <cell r="V85"/>
-          <cell r="W85"/>
-          <cell r="X85"/>
-        </row>
-        <row r="86">
-          <cell r="D86"/>
-          <cell r="E86"/>
-          <cell r="F86"/>
-          <cell r="G86"/>
-          <cell r="H86"/>
-          <cell r="I86"/>
-          <cell r="J86"/>
-          <cell r="K86"/>
-          <cell r="L86"/>
-          <cell r="M86"/>
-          <cell r="N86"/>
-          <cell r="O86"/>
-          <cell r="P86"/>
-          <cell r="Q86"/>
-          <cell r="R86"/>
-          <cell r="S86"/>
-          <cell r="T86"/>
-          <cell r="U86"/>
-          <cell r="V86"/>
-          <cell r="W86"/>
-          <cell r="X86"/>
-        </row>
-        <row r="87">
-          <cell r="D87"/>
-          <cell r="E87"/>
-          <cell r="F87"/>
-          <cell r="G87"/>
-          <cell r="H87"/>
-          <cell r="I87"/>
-          <cell r="J87"/>
-          <cell r="K87"/>
-          <cell r="L87"/>
-          <cell r="M87"/>
-          <cell r="N87"/>
-          <cell r="O87"/>
-          <cell r="P87"/>
-          <cell r="Q87"/>
-          <cell r="R87"/>
-          <cell r="S87"/>
-          <cell r="T87"/>
-          <cell r="U87"/>
-          <cell r="V87"/>
-          <cell r="W87"/>
-          <cell r="X87"/>
-        </row>
-        <row r="88">
-          <cell r="D88"/>
-          <cell r="E88"/>
-          <cell r="F88"/>
-          <cell r="G88"/>
-          <cell r="H88"/>
-          <cell r="I88"/>
-          <cell r="J88"/>
-          <cell r="K88"/>
-          <cell r="L88"/>
-          <cell r="M88"/>
-          <cell r="N88"/>
-          <cell r="O88"/>
-          <cell r="P88"/>
-          <cell r="Q88"/>
-          <cell r="R88"/>
-          <cell r="S88"/>
-          <cell r="T88"/>
-          <cell r="U88"/>
-          <cell r="V88"/>
-          <cell r="W88"/>
-          <cell r="X88"/>
-        </row>
-        <row r="89">
-          <cell r="D89"/>
-          <cell r="E89"/>
-          <cell r="F89"/>
-          <cell r="G89"/>
-          <cell r="H89"/>
-          <cell r="I89"/>
-          <cell r="J89"/>
-          <cell r="K89"/>
-          <cell r="L89"/>
-          <cell r="M89"/>
-          <cell r="N89"/>
-          <cell r="O89"/>
-          <cell r="P89"/>
-          <cell r="Q89"/>
-          <cell r="R89"/>
-          <cell r="S89"/>
-          <cell r="T89"/>
-          <cell r="U89"/>
-          <cell r="V89"/>
-          <cell r="W89"/>
-          <cell r="X89"/>
-        </row>
-        <row r="90">
-          <cell r="D90"/>
-          <cell r="E90"/>
-          <cell r="F90"/>
-          <cell r="G90"/>
-          <cell r="H90"/>
-          <cell r="I90"/>
-          <cell r="J90"/>
-          <cell r="K90"/>
-          <cell r="L90"/>
-          <cell r="M90"/>
-          <cell r="N90"/>
-          <cell r="O90"/>
-          <cell r="P90"/>
-          <cell r="Q90"/>
-          <cell r="R90"/>
-          <cell r="S90"/>
-          <cell r="T90"/>
-          <cell r="U90"/>
-          <cell r="V90"/>
-          <cell r="W90"/>
-          <cell r="X90"/>
-        </row>
-        <row r="91">
-          <cell r="D91"/>
-          <cell r="E91"/>
-          <cell r="F91"/>
-          <cell r="G91"/>
-          <cell r="H91"/>
-          <cell r="I91"/>
-          <cell r="J91"/>
-          <cell r="K91"/>
-          <cell r="L91"/>
-          <cell r="M91"/>
-          <cell r="N91"/>
-          <cell r="O91"/>
-          <cell r="P91"/>
-          <cell r="Q91"/>
-          <cell r="R91"/>
-          <cell r="S91"/>
-          <cell r="T91"/>
-          <cell r="U91"/>
-          <cell r="V91"/>
-          <cell r="W91"/>
-          <cell r="X91"/>
-        </row>
-        <row r="92">
-          <cell r="D92"/>
-          <cell r="E92"/>
-          <cell r="F92"/>
-          <cell r="G92"/>
-          <cell r="H92"/>
-          <cell r="I92"/>
-          <cell r="J92"/>
-          <cell r="K92"/>
-          <cell r="L92"/>
-          <cell r="M92"/>
-          <cell r="N92"/>
-          <cell r="O92"/>
-          <cell r="P92"/>
-          <cell r="Q92"/>
-          <cell r="R92"/>
-          <cell r="S92"/>
-          <cell r="T92"/>
-          <cell r="U92"/>
-          <cell r="V92"/>
-          <cell r="W92"/>
-          <cell r="X92"/>
-        </row>
-        <row r="93">
-          <cell r="D93"/>
-          <cell r="E93"/>
-          <cell r="F93"/>
-          <cell r="G93"/>
-          <cell r="H93"/>
-          <cell r="I93"/>
-          <cell r="J93"/>
-          <cell r="K93"/>
-          <cell r="L93"/>
-          <cell r="M93"/>
-          <cell r="N93"/>
-          <cell r="O93"/>
-          <cell r="P93"/>
-          <cell r="Q93"/>
-          <cell r="R93"/>
-          <cell r="S93"/>
-          <cell r="T93"/>
-          <cell r="U93"/>
-          <cell r="V93"/>
-          <cell r="W93"/>
-          <cell r="X93"/>
-        </row>
-        <row r="94">
-          <cell r="D94"/>
-          <cell r="E94"/>
-          <cell r="F94"/>
-          <cell r="G94"/>
-          <cell r="H94"/>
-          <cell r="I94"/>
-          <cell r="J94"/>
-          <cell r="K94"/>
-          <cell r="L94"/>
-          <cell r="M94"/>
-          <cell r="N94"/>
-          <cell r="O94"/>
-          <cell r="P94"/>
-          <cell r="Q94"/>
-          <cell r="R94"/>
-          <cell r="S94"/>
-          <cell r="T94"/>
-          <cell r="U94"/>
-          <cell r="V94"/>
-          <cell r="W94"/>
-          <cell r="X94"/>
-        </row>
-        <row r="95">
-          <cell r="D95"/>
-          <cell r="E95"/>
-          <cell r="F95"/>
-          <cell r="G95"/>
-          <cell r="H95"/>
-          <cell r="I95"/>
-          <cell r="J95"/>
-          <cell r="K95"/>
-          <cell r="L95"/>
-          <cell r="M95"/>
-          <cell r="N95"/>
-          <cell r="O95"/>
-          <cell r="P95"/>
-          <cell r="Q95"/>
-          <cell r="R95"/>
-          <cell r="S95"/>
-          <cell r="T95"/>
-          <cell r="U95"/>
-          <cell r="V95"/>
-          <cell r="W95"/>
-          <cell r="X95"/>
-        </row>
-        <row r="96">
-          <cell r="D96"/>
-          <cell r="E96"/>
-          <cell r="F96"/>
-          <cell r="G96"/>
-          <cell r="H96"/>
-          <cell r="I96"/>
-          <cell r="J96"/>
-          <cell r="K96"/>
-          <cell r="L96"/>
-          <cell r="M96"/>
-          <cell r="N96"/>
-          <cell r="O96"/>
-          <cell r="P96"/>
-          <cell r="Q96"/>
-          <cell r="R96"/>
-          <cell r="S96"/>
-          <cell r="T96"/>
-          <cell r="U96"/>
-          <cell r="V96"/>
-          <cell r="W96"/>
-          <cell r="X96"/>
-        </row>
-        <row r="97">
-          <cell r="D97"/>
-          <cell r="E97"/>
-          <cell r="F97"/>
-          <cell r="G97"/>
-          <cell r="H97"/>
-          <cell r="I97"/>
-          <cell r="J97"/>
-          <cell r="K97"/>
-          <cell r="L97"/>
-          <cell r="M97"/>
-          <cell r="N97"/>
-          <cell r="O97"/>
-          <cell r="P97"/>
-          <cell r="Q97"/>
-          <cell r="R97"/>
-          <cell r="S97"/>
-          <cell r="T97"/>
-          <cell r="U97"/>
-          <cell r="V97"/>
-          <cell r="W97"/>
-          <cell r="X97"/>
-        </row>
-        <row r="98">
-          <cell r="D98"/>
-          <cell r="E98"/>
-          <cell r="F98"/>
-          <cell r="G98"/>
-          <cell r="H98"/>
-          <cell r="I98"/>
-          <cell r="J98"/>
-          <cell r="K98"/>
-          <cell r="L98"/>
-          <cell r="M98"/>
-          <cell r="N98"/>
-          <cell r="O98"/>
-          <cell r="P98"/>
-          <cell r="Q98"/>
-          <cell r="R98"/>
-          <cell r="S98"/>
-          <cell r="T98"/>
-          <cell r="U98"/>
-          <cell r="V98"/>
-          <cell r="W98"/>
-          <cell r="X98"/>
-        </row>
-        <row r="99">
-          <cell r="D99"/>
-          <cell r="E99"/>
-          <cell r="F99"/>
-          <cell r="G99"/>
-          <cell r="H99"/>
-          <cell r="I99"/>
-          <cell r="J99"/>
-          <cell r="K99"/>
-          <cell r="L99"/>
-          <cell r="M99"/>
-          <cell r="N99"/>
-          <cell r="O99"/>
-          <cell r="P99"/>
-          <cell r="Q99"/>
-          <cell r="R99"/>
-          <cell r="S99"/>
-          <cell r="T99"/>
-          <cell r="U99"/>
-          <cell r="V99"/>
-          <cell r="W99"/>
-          <cell r="X99"/>
-        </row>
-        <row r="100">
-          <cell r="D100"/>
-          <cell r="E100"/>
-          <cell r="F100"/>
-          <cell r="G100"/>
-          <cell r="H100"/>
-          <cell r="I100"/>
-          <cell r="J100"/>
-          <cell r="K100"/>
-          <cell r="L100"/>
-          <cell r="M100"/>
-          <cell r="N100"/>
-          <cell r="O100"/>
-          <cell r="P100"/>
-          <cell r="Q100"/>
-          <cell r="R100"/>
-          <cell r="S100"/>
-          <cell r="T100"/>
-          <cell r="U100"/>
-          <cell r="V100"/>
-          <cell r="W100"/>
-          <cell r="X100"/>
-        </row>
-        <row r="101">
-          <cell r="D101"/>
-          <cell r="E101"/>
-          <cell r="F101"/>
-          <cell r="G101"/>
-          <cell r="H101"/>
-          <cell r="I101"/>
-          <cell r="J101"/>
-          <cell r="K101"/>
-          <cell r="L101"/>
-          <cell r="M101"/>
-          <cell r="N101"/>
-          <cell r="O101"/>
-          <cell r="P101"/>
-          <cell r="Q101"/>
-          <cell r="R101"/>
-          <cell r="S101"/>
-          <cell r="T101"/>
-          <cell r="U101"/>
-          <cell r="V101"/>
-          <cell r="W101"/>
-          <cell r="X101"/>
-        </row>
-        <row r="102">
-          <cell r="D102"/>
-          <cell r="E102"/>
-          <cell r="F102"/>
-          <cell r="G102"/>
-          <cell r="H102"/>
-          <cell r="I102"/>
-          <cell r="J102"/>
-          <cell r="K102"/>
-          <cell r="L102"/>
-          <cell r="M102"/>
-          <cell r="N102"/>
-          <cell r="O102"/>
-          <cell r="P102"/>
-          <cell r="Q102"/>
-          <cell r="R102"/>
-          <cell r="S102"/>
-          <cell r="T102"/>
-          <cell r="U102"/>
-          <cell r="V102"/>
-          <cell r="W102"/>
-          <cell r="X102"/>
-        </row>
-        <row r="103">
-          <cell r="D103"/>
-          <cell r="E103"/>
-          <cell r="F103"/>
-          <cell r="G103"/>
-          <cell r="H103"/>
-          <cell r="I103"/>
-          <cell r="J103"/>
-          <cell r="K103"/>
-          <cell r="L103"/>
-          <cell r="M103"/>
-          <cell r="N103"/>
-          <cell r="O103"/>
-          <cell r="P103"/>
-          <cell r="Q103"/>
-          <cell r="R103"/>
-          <cell r="S103"/>
-          <cell r="T103"/>
-          <cell r="U103"/>
-          <cell r="V103"/>
-          <cell r="W103"/>
-          <cell r="X103"/>
-        </row>
-        <row r="104">
-          <cell r="D104"/>
-          <cell r="E104"/>
-          <cell r="F104"/>
-          <cell r="G104"/>
-          <cell r="H104"/>
-          <cell r="I104"/>
-          <cell r="J104"/>
-          <cell r="K104"/>
-          <cell r="L104"/>
-          <cell r="M104"/>
-          <cell r="N104"/>
-          <cell r="O104"/>
-          <cell r="P104"/>
-          <cell r="Q104"/>
-          <cell r="R104"/>
-          <cell r="S104"/>
-          <cell r="T104"/>
-          <cell r="U104"/>
-          <cell r="V104"/>
-          <cell r="W104"/>
-          <cell r="X104"/>
-        </row>
-        <row r="105">
-          <cell r="D105"/>
-          <cell r="E105"/>
-          <cell r="F105"/>
-          <cell r="G105"/>
-          <cell r="H105"/>
-          <cell r="I105"/>
-          <cell r="J105"/>
-          <cell r="K105"/>
-          <cell r="L105"/>
-          <cell r="M105"/>
-          <cell r="N105"/>
-          <cell r="O105"/>
-          <cell r="P105"/>
-          <cell r="Q105"/>
-          <cell r="R105"/>
-          <cell r="S105"/>
-          <cell r="T105"/>
-          <cell r="U105"/>
-          <cell r="V105"/>
-          <cell r="W105"/>
-          <cell r="X105"/>
-        </row>
-        <row r="106">
-          <cell r="D106"/>
-          <cell r="E106"/>
-          <cell r="F106"/>
-          <cell r="G106"/>
-          <cell r="H106"/>
-          <cell r="I106"/>
-          <cell r="J106"/>
-          <cell r="K106"/>
-          <cell r="L106"/>
-          <cell r="M106"/>
-          <cell r="N106"/>
-          <cell r="O106"/>
-          <cell r="P106"/>
-          <cell r="Q106"/>
-          <cell r="R106"/>
-          <cell r="S106"/>
-          <cell r="T106"/>
-          <cell r="U106"/>
-          <cell r="V106"/>
-          <cell r="W106"/>
-          <cell r="X106"/>
-        </row>
-        <row r="107">
-          <cell r="D107"/>
-          <cell r="E107"/>
-          <cell r="F107"/>
-          <cell r="G107"/>
-          <cell r="H107"/>
-          <cell r="I107"/>
-          <cell r="J107"/>
-          <cell r="K107"/>
-          <cell r="L107"/>
-          <cell r="M107"/>
-          <cell r="N107"/>
-          <cell r="O107"/>
-          <cell r="P107"/>
-          <cell r="Q107"/>
-          <cell r="R107"/>
-          <cell r="S107"/>
-          <cell r="T107"/>
-          <cell r="U107"/>
-          <cell r="V107"/>
-          <cell r="W107"/>
-          <cell r="X107"/>
-        </row>
-        <row r="108">
-          <cell r="D108"/>
-          <cell r="E108"/>
-          <cell r="F108"/>
-          <cell r="G108"/>
-          <cell r="H108"/>
-          <cell r="I108"/>
-          <cell r="J108"/>
-          <cell r="K108"/>
-          <cell r="L108"/>
-          <cell r="M108"/>
-          <cell r="N108"/>
-          <cell r="O108"/>
-          <cell r="P108"/>
-          <cell r="Q108"/>
-          <cell r="R108"/>
-          <cell r="S108"/>
-          <cell r="T108"/>
-          <cell r="U108"/>
-          <cell r="V108"/>
-          <cell r="W108"/>
-          <cell r="X108"/>
-        </row>
-        <row r="109">
-          <cell r="D109"/>
-          <cell r="E109"/>
-          <cell r="F109"/>
-          <cell r="G109"/>
-          <cell r="H109"/>
-          <cell r="I109"/>
-          <cell r="J109"/>
-          <cell r="K109"/>
-          <cell r="L109"/>
-          <cell r="M109"/>
-          <cell r="N109"/>
-          <cell r="O109"/>
-          <cell r="P109"/>
-          <cell r="Q109"/>
-          <cell r="R109"/>
-          <cell r="S109"/>
-          <cell r="T109"/>
-          <cell r="U109"/>
-          <cell r="V109"/>
-          <cell r="W109"/>
-          <cell r="X109"/>
-        </row>
-        <row r="110">
-          <cell r="D110"/>
-          <cell r="E110"/>
-          <cell r="F110"/>
-          <cell r="G110"/>
-          <cell r="H110"/>
-          <cell r="I110"/>
-          <cell r="J110"/>
-          <cell r="K110"/>
-          <cell r="L110"/>
-          <cell r="M110"/>
-          <cell r="N110"/>
-          <cell r="O110"/>
-          <cell r="P110"/>
-          <cell r="Q110"/>
-          <cell r="R110"/>
-          <cell r="S110"/>
-          <cell r="T110"/>
-          <cell r="U110"/>
-          <cell r="V110"/>
-          <cell r="W110"/>
-          <cell r="X110"/>
-        </row>
-        <row r="111">
-          <cell r="D111"/>
-          <cell r="E111"/>
-          <cell r="F111"/>
-          <cell r="G111"/>
-          <cell r="H111"/>
-          <cell r="I111"/>
-          <cell r="J111"/>
-          <cell r="K111"/>
-          <cell r="L111"/>
-          <cell r="M111"/>
-          <cell r="N111"/>
-          <cell r="O111"/>
-          <cell r="P111"/>
-          <cell r="Q111"/>
-          <cell r="R111"/>
-          <cell r="S111"/>
-          <cell r="T111"/>
-          <cell r="U111"/>
-          <cell r="V111"/>
-          <cell r="W111"/>
-          <cell r="X111"/>
-        </row>
-        <row r="112">
-          <cell r="D112"/>
-          <cell r="E112"/>
-          <cell r="F112"/>
-          <cell r="G112"/>
-          <cell r="H112"/>
-          <cell r="I112"/>
-          <cell r="J112"/>
-          <cell r="K112"/>
-          <cell r="L112"/>
-          <cell r="M112"/>
-          <cell r="N112"/>
-          <cell r="O112"/>
-          <cell r="P112"/>
-          <cell r="Q112"/>
-          <cell r="R112"/>
-          <cell r="S112"/>
-          <cell r="T112"/>
-          <cell r="U112"/>
-          <cell r="V112"/>
-          <cell r="W112"/>
-          <cell r="X112"/>
-        </row>
-        <row r="113">
-          <cell r="D113"/>
-          <cell r="E113"/>
-          <cell r="F113"/>
-          <cell r="G113"/>
-          <cell r="H113"/>
-          <cell r="I113"/>
-          <cell r="J113"/>
-          <cell r="K113"/>
-          <cell r="L113"/>
-          <cell r="M113"/>
-          <cell r="N113"/>
-          <cell r="O113"/>
-          <cell r="P113"/>
-          <cell r="Q113"/>
-          <cell r="R113"/>
-          <cell r="S113"/>
-          <cell r="T113"/>
-          <cell r="U113"/>
-          <cell r="V113"/>
-          <cell r="W113"/>
-          <cell r="X113"/>
-        </row>
-        <row r="114">
-          <cell r="D114"/>
-          <cell r="E114"/>
-          <cell r="F114"/>
-          <cell r="G114"/>
-          <cell r="H114"/>
-          <cell r="I114"/>
-          <cell r="J114"/>
-          <cell r="K114"/>
-          <cell r="L114"/>
-          <cell r="M114"/>
-          <cell r="N114"/>
-          <cell r="O114"/>
-          <cell r="P114"/>
-          <cell r="Q114"/>
-          <cell r="R114"/>
-          <cell r="S114"/>
-          <cell r="T114"/>
-          <cell r="U114"/>
-          <cell r="V114"/>
-          <cell r="W114"/>
-          <cell r="X114"/>
-        </row>
-        <row r="115">
-          <cell r="D115"/>
-          <cell r="E115"/>
-          <cell r="F115"/>
-          <cell r="G115"/>
-          <cell r="H115"/>
-          <cell r="I115"/>
-          <cell r="J115"/>
-          <cell r="K115"/>
-          <cell r="L115"/>
-          <cell r="M115"/>
-          <cell r="N115"/>
-          <cell r="O115"/>
-          <cell r="P115"/>
-          <cell r="Q115"/>
-          <cell r="R115"/>
-          <cell r="S115"/>
-          <cell r="T115"/>
-          <cell r="U115"/>
-          <cell r="V115"/>
-          <cell r="W115"/>
-          <cell r="X115"/>
-        </row>
-        <row r="116">
-          <cell r="D116"/>
-          <cell r="E116"/>
-          <cell r="F116"/>
-          <cell r="G116"/>
-          <cell r="H116"/>
-          <cell r="I116"/>
-          <cell r="J116"/>
-          <cell r="K116"/>
-          <cell r="L116"/>
-          <cell r="M116"/>
-          <cell r="N116"/>
-          <cell r="O116"/>
-          <cell r="P116"/>
-          <cell r="Q116"/>
-          <cell r="R116"/>
-          <cell r="S116"/>
-          <cell r="T116"/>
-          <cell r="U116"/>
-          <cell r="V116"/>
-          <cell r="W116"/>
-          <cell r="X116"/>
-        </row>
-        <row r="117">
-          <cell r="D117"/>
-          <cell r="E117"/>
-          <cell r="F117"/>
-          <cell r="G117"/>
-          <cell r="H117"/>
-          <cell r="I117"/>
-          <cell r="J117"/>
-          <cell r="K117"/>
-          <cell r="L117"/>
-          <cell r="M117"/>
-          <cell r="N117"/>
-          <cell r="O117"/>
-          <cell r="P117"/>
-          <cell r="Q117"/>
-          <cell r="R117"/>
-          <cell r="S117"/>
-          <cell r="T117"/>
-          <cell r="U117"/>
-          <cell r="V117"/>
-          <cell r="W117"/>
-          <cell r="X117"/>
-        </row>
-        <row r="118">
-          <cell r="D118"/>
-          <cell r="E118"/>
-          <cell r="F118"/>
-          <cell r="G118"/>
-          <cell r="H118"/>
-          <cell r="I118"/>
-          <cell r="J118"/>
-          <cell r="K118"/>
-          <cell r="L118"/>
-          <cell r="M118"/>
-          <cell r="N118"/>
-          <cell r="O118"/>
-          <cell r="P118"/>
-          <cell r="Q118"/>
-          <cell r="R118"/>
-          <cell r="S118"/>
-          <cell r="T118"/>
-          <cell r="U118"/>
-          <cell r="V118"/>
-          <cell r="W118"/>
-          <cell r="X118"/>
-        </row>
-        <row r="119">
-          <cell r="D119"/>
-          <cell r="E119"/>
-          <cell r="F119"/>
-          <cell r="G119"/>
-          <cell r="H119"/>
-          <cell r="I119"/>
-          <cell r="J119"/>
-          <cell r="K119"/>
-          <cell r="L119"/>
-          <cell r="M119"/>
-          <cell r="N119"/>
-          <cell r="O119"/>
-          <cell r="P119"/>
-          <cell r="Q119"/>
-          <cell r="R119"/>
-          <cell r="S119"/>
-          <cell r="T119"/>
-          <cell r="U119"/>
-          <cell r="V119"/>
-          <cell r="W119"/>
-          <cell r="X119"/>
-        </row>
-        <row r="120">
-          <cell r="D120"/>
-          <cell r="E120"/>
-          <cell r="F120"/>
-          <cell r="G120"/>
-          <cell r="H120"/>
-          <cell r="I120"/>
-          <cell r="J120"/>
-          <cell r="K120"/>
-          <cell r="L120"/>
-          <cell r="M120"/>
-          <cell r="N120"/>
-          <cell r="O120"/>
-          <cell r="P120"/>
-          <cell r="Q120"/>
-          <cell r="R120"/>
-          <cell r="S120"/>
-          <cell r="T120"/>
-          <cell r="U120"/>
-          <cell r="V120"/>
-          <cell r="W120"/>
-          <cell r="X120"/>
-        </row>
-        <row r="121">
-          <cell r="D121"/>
-          <cell r="E121"/>
-          <cell r="F121"/>
-          <cell r="G121"/>
-          <cell r="H121"/>
-          <cell r="I121"/>
-          <cell r="J121"/>
-          <cell r="K121"/>
-          <cell r="L121"/>
-          <cell r="M121"/>
-          <cell r="N121"/>
-          <cell r="O121"/>
-          <cell r="P121"/>
-          <cell r="Q121"/>
-          <cell r="R121"/>
-          <cell r="S121"/>
-          <cell r="T121"/>
-          <cell r="U121"/>
-          <cell r="V121"/>
-          <cell r="W121"/>
-          <cell r="X121"/>
-        </row>
-        <row r="122">
-          <cell r="D122"/>
-          <cell r="E122"/>
-          <cell r="F122"/>
-          <cell r="G122"/>
-          <cell r="H122"/>
-          <cell r="I122"/>
-          <cell r="J122"/>
-          <cell r="K122"/>
-          <cell r="L122"/>
-          <cell r="M122"/>
-          <cell r="N122"/>
-          <cell r="O122"/>
-          <cell r="P122"/>
-          <cell r="Q122"/>
-          <cell r="R122"/>
-          <cell r="S122"/>
-          <cell r="T122"/>
-          <cell r="U122"/>
-          <cell r="V122"/>
-          <cell r="W122"/>
-          <cell r="X122"/>
-        </row>
-        <row r="123">
-          <cell r="D123"/>
-          <cell r="E123"/>
-          <cell r="F123"/>
-          <cell r="G123"/>
-          <cell r="H123"/>
-          <cell r="I123"/>
-          <cell r="J123"/>
-          <cell r="K123"/>
-          <cell r="L123"/>
-          <cell r="M123"/>
-          <cell r="N123"/>
-          <cell r="O123"/>
-          <cell r="P123"/>
-          <cell r="Q123"/>
-          <cell r="R123"/>
-          <cell r="S123"/>
-          <cell r="T123"/>
-          <cell r="U123"/>
-          <cell r="V123"/>
-          <cell r="W123"/>
-          <cell r="X123"/>
-        </row>
-        <row r="124">
-          <cell r="D124"/>
-          <cell r="E124"/>
-          <cell r="F124"/>
-          <cell r="G124"/>
-          <cell r="H124"/>
-          <cell r="I124"/>
-          <cell r="J124"/>
-          <cell r="K124"/>
-          <cell r="L124"/>
-          <cell r="M124"/>
-          <cell r="N124"/>
-          <cell r="O124"/>
-          <cell r="P124"/>
-          <cell r="Q124"/>
-          <cell r="R124"/>
-          <cell r="S124"/>
-          <cell r="T124"/>
-          <cell r="U124"/>
-          <cell r="V124"/>
-          <cell r="W124"/>
-          <cell r="X124"/>
-        </row>
-        <row r="125">
-          <cell r="D125"/>
-          <cell r="E125"/>
-          <cell r="F125"/>
-          <cell r="G125"/>
-          <cell r="H125"/>
-          <cell r="I125"/>
-          <cell r="J125"/>
-          <cell r="K125"/>
-          <cell r="L125"/>
-          <cell r="M125"/>
-          <cell r="N125"/>
-          <cell r="O125"/>
-          <cell r="P125"/>
-          <cell r="Q125"/>
-          <cell r="R125"/>
-          <cell r="S125"/>
-          <cell r="T125"/>
-          <cell r="U125"/>
-          <cell r="V125"/>
-          <cell r="W125"/>
-          <cell r="X125"/>
-        </row>
-        <row r="126">
-          <cell r="D126"/>
-          <cell r="E126"/>
-          <cell r="F126"/>
-          <cell r="G126"/>
-          <cell r="H126"/>
-          <cell r="I126"/>
-          <cell r="J126"/>
-          <cell r="K126"/>
-          <cell r="L126"/>
-          <cell r="M126"/>
-          <cell r="N126"/>
-          <cell r="O126"/>
-          <cell r="P126"/>
-          <cell r="Q126"/>
-          <cell r="R126"/>
-          <cell r="S126"/>
-          <cell r="T126"/>
-          <cell r="U126"/>
-          <cell r="V126"/>
-          <cell r="W126"/>
-          <cell r="X126"/>
-        </row>
-        <row r="127">
-          <cell r="D127"/>
-          <cell r="E127"/>
-          <cell r="F127"/>
-          <cell r="G127"/>
-          <cell r="H127"/>
-          <cell r="I127"/>
-          <cell r="J127"/>
-          <cell r="K127"/>
-          <cell r="L127"/>
-          <cell r="M127"/>
-          <cell r="N127"/>
-          <cell r="O127"/>
-          <cell r="P127"/>
-          <cell r="Q127"/>
-          <cell r="R127"/>
-          <cell r="S127"/>
-          <cell r="T127"/>
-          <cell r="U127"/>
-          <cell r="V127"/>
-          <cell r="W127"/>
-          <cell r="X127"/>
-        </row>
-        <row r="128">
-          <cell r="D128"/>
-          <cell r="E128"/>
-          <cell r="F128"/>
-          <cell r="G128"/>
-          <cell r="H128"/>
-          <cell r="I128"/>
-          <cell r="J128"/>
-          <cell r="K128"/>
-          <cell r="L128"/>
-          <cell r="M128"/>
-          <cell r="N128"/>
-          <cell r="O128"/>
-          <cell r="P128"/>
-          <cell r="Q128"/>
-          <cell r="R128"/>
-          <cell r="S128"/>
-          <cell r="T128"/>
-          <cell r="U128"/>
-          <cell r="V128"/>
-          <cell r="W128"/>
-          <cell r="X128"/>
-        </row>
-        <row r="129">
-          <cell r="D129"/>
-          <cell r="E129"/>
-          <cell r="F129"/>
-          <cell r="G129"/>
-          <cell r="H129"/>
-          <cell r="I129"/>
-          <cell r="J129"/>
-          <cell r="K129"/>
-          <cell r="L129"/>
-          <cell r="M129"/>
-          <cell r="N129"/>
-          <cell r="O129"/>
-          <cell r="P129"/>
-          <cell r="Q129"/>
-          <cell r="R129"/>
-          <cell r="S129"/>
-          <cell r="T129"/>
-          <cell r="U129"/>
-          <cell r="V129"/>
-          <cell r="W129"/>
-          <cell r="X129"/>
-        </row>
-        <row r="130">
-          <cell r="D130"/>
-          <cell r="E130"/>
-          <cell r="F130"/>
-          <cell r="G130"/>
-          <cell r="H130"/>
-          <cell r="I130"/>
-          <cell r="J130"/>
-          <cell r="K130"/>
-          <cell r="L130"/>
-          <cell r="M130"/>
-          <cell r="N130"/>
-          <cell r="O130"/>
-          <cell r="P130"/>
-          <cell r="Q130"/>
-          <cell r="R130"/>
-          <cell r="S130"/>
-          <cell r="T130"/>
-          <cell r="U130"/>
-          <cell r="V130"/>
-          <cell r="W130"/>
-          <cell r="X130"/>
-        </row>
-        <row r="131">
-          <cell r="D131"/>
-          <cell r="E131"/>
-          <cell r="F131"/>
-          <cell r="G131"/>
-          <cell r="H131"/>
-          <cell r="I131"/>
-          <cell r="J131"/>
-          <cell r="K131"/>
-          <cell r="L131"/>
-          <cell r="M131"/>
-          <cell r="N131"/>
-          <cell r="O131"/>
-          <cell r="P131"/>
-          <cell r="Q131"/>
-          <cell r="R131"/>
-          <cell r="S131"/>
-          <cell r="T131"/>
-          <cell r="U131"/>
-          <cell r="V131"/>
-          <cell r="W131"/>
-          <cell r="X131"/>
-        </row>
-        <row r="132">
-          <cell r="D132"/>
-          <cell r="E132"/>
-          <cell r="F132"/>
-          <cell r="G132"/>
-          <cell r="H132"/>
-          <cell r="I132"/>
-          <cell r="J132"/>
-          <cell r="K132"/>
-          <cell r="L132"/>
-          <cell r="M132"/>
-          <cell r="N132"/>
-          <cell r="O132"/>
-          <cell r="P132"/>
-          <cell r="Q132"/>
-          <cell r="R132"/>
-          <cell r="S132"/>
-          <cell r="T132"/>
-          <cell r="U132"/>
-          <cell r="V132"/>
-          <cell r="W132"/>
-          <cell r="X132"/>
-        </row>
-        <row r="133">
-          <cell r="D133"/>
-          <cell r="E133"/>
-          <cell r="F133"/>
-          <cell r="G133"/>
-          <cell r="H133"/>
-          <cell r="I133"/>
-          <cell r="J133"/>
-          <cell r="K133"/>
-          <cell r="L133"/>
-          <cell r="M133"/>
-          <cell r="N133"/>
-          <cell r="O133"/>
-          <cell r="P133"/>
-          <cell r="Q133"/>
-          <cell r="R133"/>
-          <cell r="S133"/>
-          <cell r="T133"/>
-          <cell r="U133"/>
-          <cell r="V133"/>
-          <cell r="W133"/>
-          <cell r="X133"/>
-        </row>
-        <row r="134">
-          <cell r="D134"/>
-          <cell r="E134"/>
-          <cell r="F134"/>
-          <cell r="G134"/>
-          <cell r="H134"/>
-          <cell r="I134"/>
-          <cell r="J134"/>
-          <cell r="K134"/>
-          <cell r="L134"/>
-          <cell r="M134"/>
-          <cell r="N134"/>
-          <cell r="O134"/>
-          <cell r="P134"/>
-          <cell r="Q134"/>
-          <cell r="R134"/>
-          <cell r="S134"/>
-          <cell r="T134"/>
-          <cell r="U134"/>
-          <cell r="V134"/>
-          <cell r="W134"/>
-          <cell r="X134"/>
-        </row>
-        <row r="135">
-          <cell r="D135"/>
-          <cell r="E135"/>
-          <cell r="F135"/>
-          <cell r="G135"/>
-          <cell r="H135"/>
-          <cell r="I135"/>
-          <cell r="J135"/>
-          <cell r="K135"/>
-          <cell r="L135"/>
-          <cell r="M135"/>
-          <cell r="N135"/>
-          <cell r="O135"/>
-          <cell r="P135"/>
-          <cell r="Q135"/>
-          <cell r="R135"/>
-          <cell r="S135"/>
-          <cell r="T135"/>
-          <cell r="U135"/>
-          <cell r="V135"/>
-          <cell r="W135"/>
-          <cell r="X135"/>
-        </row>
-        <row r="136">
-          <cell r="D136"/>
-          <cell r="E136"/>
-          <cell r="F136"/>
-          <cell r="G136"/>
-          <cell r="H136"/>
-          <cell r="I136"/>
-          <cell r="J136"/>
-          <cell r="K136"/>
-          <cell r="L136"/>
-          <cell r="M136"/>
-          <cell r="N136"/>
-          <cell r="O136"/>
-          <cell r="P136"/>
-          <cell r="Q136"/>
-          <cell r="R136"/>
-          <cell r="S136"/>
-          <cell r="T136"/>
-          <cell r="U136"/>
-          <cell r="V136"/>
-          <cell r="W136"/>
-          <cell r="X136"/>
-        </row>
-        <row r="137">
-          <cell r="D137"/>
-          <cell r="E137"/>
-          <cell r="F137"/>
-          <cell r="G137"/>
-          <cell r="H137"/>
-          <cell r="I137"/>
-          <cell r="J137"/>
-          <cell r="K137"/>
-          <cell r="L137"/>
-          <cell r="M137"/>
-          <cell r="N137"/>
-          <cell r="O137"/>
-          <cell r="P137"/>
-          <cell r="Q137"/>
-          <cell r="R137"/>
-          <cell r="S137"/>
-          <cell r="T137"/>
-          <cell r="U137"/>
-          <cell r="V137"/>
-          <cell r="W137"/>
-          <cell r="X137"/>
-        </row>
-        <row r="138">
-          <cell r="D138"/>
-          <cell r="E138"/>
-          <cell r="F138"/>
-          <cell r="G138"/>
-          <cell r="H138"/>
-          <cell r="I138"/>
-          <cell r="J138"/>
-          <cell r="K138"/>
-          <cell r="L138"/>
-          <cell r="M138"/>
-          <cell r="N138"/>
-          <cell r="O138"/>
-          <cell r="P138"/>
-          <cell r="Q138"/>
-          <cell r="R138"/>
-          <cell r="S138"/>
-          <cell r="T138"/>
-          <cell r="U138"/>
-          <cell r="V138"/>
-          <cell r="W138"/>
-          <cell r="X138"/>
-        </row>
-        <row r="139">
-          <cell r="D139"/>
-          <cell r="E139"/>
-          <cell r="F139"/>
-          <cell r="G139"/>
-          <cell r="H139"/>
-          <cell r="I139"/>
-          <cell r="J139"/>
-          <cell r="K139"/>
-          <cell r="L139"/>
-          <cell r="M139"/>
-          <cell r="N139"/>
-          <cell r="O139"/>
-          <cell r="P139"/>
-          <cell r="Q139"/>
-          <cell r="R139"/>
-          <cell r="S139"/>
-          <cell r="T139"/>
-          <cell r="U139"/>
-          <cell r="V139"/>
-          <cell r="W139"/>
-          <cell r="X139"/>
-        </row>
-        <row r="140">
-          <cell r="D140"/>
-          <cell r="E140"/>
-          <cell r="F140"/>
-          <cell r="G140"/>
-          <cell r="H140"/>
-          <cell r="I140"/>
-          <cell r="J140"/>
-          <cell r="K140"/>
-          <cell r="L140"/>
-          <cell r="M140"/>
-          <cell r="N140"/>
-          <cell r="O140"/>
-          <cell r="P140"/>
-          <cell r="Q140"/>
-          <cell r="R140"/>
-          <cell r="S140"/>
-          <cell r="T140"/>
-          <cell r="U140"/>
-          <cell r="V140"/>
-          <cell r="W140"/>
-          <cell r="X140"/>
-        </row>
-        <row r="141">
-          <cell r="D141"/>
-          <cell r="E141"/>
-          <cell r="F141"/>
-          <cell r="G141"/>
-          <cell r="H141"/>
-          <cell r="I141"/>
-          <cell r="J141"/>
-          <cell r="K141"/>
-          <cell r="L141"/>
-          <cell r="M141"/>
-          <cell r="N141"/>
-          <cell r="O141"/>
-          <cell r="P141"/>
-          <cell r="Q141"/>
-          <cell r="R141"/>
-          <cell r="S141"/>
-          <cell r="T141"/>
-          <cell r="U141"/>
-          <cell r="V141"/>
-          <cell r="W141"/>
-          <cell r="X141"/>
-        </row>
-        <row r="142">
-          <cell r="D142"/>
-          <cell r="E142"/>
-          <cell r="F142"/>
-          <cell r="G142"/>
-          <cell r="H142"/>
-          <cell r="I142"/>
-          <cell r="J142"/>
-          <cell r="K142"/>
-          <cell r="L142"/>
-          <cell r="M142"/>
-          <cell r="N142"/>
-          <cell r="O142"/>
-          <cell r="P142"/>
-          <cell r="Q142"/>
-          <cell r="R142"/>
-          <cell r="S142"/>
-          <cell r="T142"/>
-          <cell r="U142"/>
-          <cell r="V142"/>
-          <cell r="W142"/>
-          <cell r="X142"/>
-        </row>
-        <row r="143">
-          <cell r="D143"/>
-          <cell r="E143"/>
-          <cell r="F143"/>
-          <cell r="G143"/>
-          <cell r="H143"/>
-          <cell r="I143"/>
-          <cell r="J143"/>
-          <cell r="K143"/>
-          <cell r="L143"/>
-          <cell r="M143"/>
-          <cell r="N143"/>
-          <cell r="O143"/>
-          <cell r="P143"/>
-          <cell r="Q143"/>
-          <cell r="R143"/>
-          <cell r="S143"/>
-          <cell r="T143"/>
-          <cell r="U143"/>
-          <cell r="V143"/>
-          <cell r="W143"/>
-          <cell r="X143"/>
-        </row>
-        <row r="144">
-          <cell r="D144"/>
-          <cell r="E144"/>
-          <cell r="F144"/>
-          <cell r="G144"/>
-          <cell r="H144"/>
-          <cell r="I144"/>
-          <cell r="J144"/>
-          <cell r="K144"/>
-          <cell r="L144"/>
-          <cell r="M144"/>
-          <cell r="N144"/>
-          <cell r="O144"/>
-          <cell r="P144"/>
-          <cell r="Q144"/>
-          <cell r="R144"/>
-          <cell r="S144"/>
-          <cell r="T144"/>
-          <cell r="U144"/>
-          <cell r="V144"/>
-          <cell r="W144"/>
-          <cell r="X144"/>
-        </row>
-        <row r="145">
-          <cell r="D145"/>
-          <cell r="E145"/>
-          <cell r="F145"/>
-          <cell r="G145"/>
-          <cell r="H145"/>
-          <cell r="I145"/>
-          <cell r="J145"/>
-          <cell r="K145"/>
-          <cell r="L145"/>
-          <cell r="M145"/>
-          <cell r="N145"/>
-          <cell r="O145"/>
-          <cell r="P145"/>
-          <cell r="Q145"/>
-          <cell r="R145"/>
-          <cell r="S145"/>
-          <cell r="T145"/>
-          <cell r="U145"/>
-          <cell r="V145"/>
-          <cell r="W145"/>
-          <cell r="X145"/>
-        </row>
-        <row r="146">
-          <cell r="D146"/>
-          <cell r="E146"/>
-          <cell r="F146"/>
-          <cell r="G146"/>
-          <cell r="H146"/>
-          <cell r="I146"/>
-          <cell r="J146"/>
-          <cell r="K146"/>
-          <cell r="L146"/>
-          <cell r="M146"/>
-          <cell r="N146"/>
-          <cell r="O146"/>
-          <cell r="P146"/>
-          <cell r="Q146"/>
-          <cell r="R146"/>
-          <cell r="S146"/>
-          <cell r="T146"/>
-          <cell r="U146"/>
-          <cell r="V146"/>
-          <cell r="W146"/>
-          <cell r="X146"/>
-        </row>
-        <row r="147">
-          <cell r="D147"/>
-          <cell r="E147"/>
-          <cell r="F147"/>
-          <cell r="G147"/>
-          <cell r="H147"/>
-          <cell r="I147"/>
-          <cell r="J147"/>
-          <cell r="K147"/>
-          <cell r="L147"/>
-          <cell r="M147"/>
-          <cell r="N147"/>
-          <cell r="O147"/>
-          <cell r="P147"/>
-          <cell r="Q147"/>
-          <cell r="R147"/>
-          <cell r="S147"/>
-          <cell r="T147"/>
-          <cell r="U147"/>
-          <cell r="V147"/>
-          <cell r="W147"/>
-          <cell r="X147"/>
-        </row>
-        <row r="148">
-          <cell r="D148"/>
-          <cell r="E148"/>
-          <cell r="F148"/>
-          <cell r="G148"/>
-          <cell r="H148"/>
-          <cell r="I148"/>
-          <cell r="J148"/>
-          <cell r="K148"/>
-          <cell r="L148"/>
-          <cell r="M148"/>
-          <cell r="N148"/>
-          <cell r="O148"/>
-          <cell r="P148"/>
-          <cell r="Q148"/>
-          <cell r="R148"/>
-          <cell r="S148"/>
-          <cell r="T148"/>
-          <cell r="U148"/>
-          <cell r="V148"/>
-          <cell r="W148"/>
-          <cell r="X148"/>
-        </row>
-        <row r="149">
-          <cell r="D149"/>
-          <cell r="E149"/>
-          <cell r="F149"/>
-          <cell r="G149"/>
-          <cell r="H149"/>
-          <cell r="I149"/>
-          <cell r="J149"/>
-          <cell r="K149"/>
-          <cell r="L149"/>
-          <cell r="M149"/>
-          <cell r="N149"/>
-          <cell r="O149"/>
-          <cell r="P149"/>
-          <cell r="Q149"/>
-          <cell r="R149"/>
-          <cell r="S149"/>
-          <cell r="T149"/>
-          <cell r="U149"/>
-          <cell r="V149"/>
-          <cell r="W149"/>
-          <cell r="X149"/>
-        </row>
-        <row r="150">
-          <cell r="D150"/>
-          <cell r="E150"/>
-          <cell r="F150"/>
-          <cell r="G150"/>
-          <cell r="H150"/>
-          <cell r="I150"/>
-          <cell r="J150"/>
-          <cell r="K150"/>
-          <cell r="L150"/>
-          <cell r="M150"/>
-          <cell r="N150"/>
-          <cell r="O150"/>
-          <cell r="P150"/>
-          <cell r="Q150"/>
-          <cell r="R150"/>
-          <cell r="S150"/>
-          <cell r="T150"/>
-          <cell r="U150"/>
-          <cell r="V150"/>
-          <cell r="W150"/>
-          <cell r="X150"/>
-        </row>
-        <row r="151">
-          <cell r="D151"/>
-          <cell r="E151"/>
-          <cell r="F151"/>
-          <cell r="G151"/>
-          <cell r="H151"/>
-          <cell r="I151"/>
-          <cell r="J151"/>
-          <cell r="K151"/>
-          <cell r="L151"/>
-          <cell r="M151"/>
-          <cell r="N151"/>
-          <cell r="O151"/>
-          <cell r="P151"/>
-          <cell r="Q151"/>
-          <cell r="R151"/>
-          <cell r="S151"/>
-          <cell r="T151"/>
-          <cell r="U151"/>
-          <cell r="V151"/>
-          <cell r="W151"/>
-          <cell r="X151"/>
-        </row>
-        <row r="152">
-          <cell r="D152"/>
-          <cell r="E152"/>
-          <cell r="F152"/>
-          <cell r="G152"/>
-          <cell r="H152"/>
-          <cell r="I152"/>
-          <cell r="J152"/>
-          <cell r="K152"/>
-          <cell r="L152"/>
-          <cell r="M152"/>
-          <cell r="N152"/>
-          <cell r="O152"/>
-          <cell r="P152"/>
-          <cell r="Q152"/>
-          <cell r="R152"/>
-          <cell r="S152"/>
-          <cell r="T152"/>
-          <cell r="U152"/>
-          <cell r="V152"/>
-          <cell r="W152"/>
-          <cell r="X152"/>
-        </row>
-        <row r="153">
-          <cell r="D153"/>
-          <cell r="E153"/>
-          <cell r="F153"/>
-          <cell r="G153"/>
-          <cell r="H153"/>
-          <cell r="I153"/>
-          <cell r="J153"/>
-          <cell r="K153"/>
-          <cell r="L153"/>
-          <cell r="M153"/>
-          <cell r="N153"/>
-          <cell r="O153"/>
-          <cell r="P153"/>
-          <cell r="Q153"/>
-          <cell r="R153"/>
-          <cell r="S153"/>
-          <cell r="T153"/>
-          <cell r="U153"/>
-          <cell r="V153"/>
-          <cell r="W153"/>
-          <cell r="X153"/>
-        </row>
-        <row r="154">
-          <cell r="D154"/>
-          <cell r="E154"/>
-          <cell r="F154"/>
-          <cell r="G154"/>
-          <cell r="H154"/>
-          <cell r="I154"/>
-          <cell r="J154"/>
-          <cell r="K154"/>
-          <cell r="L154"/>
-          <cell r="M154"/>
-          <cell r="N154"/>
-          <cell r="O154"/>
-          <cell r="P154"/>
-          <cell r="Q154"/>
-          <cell r="R154"/>
-          <cell r="S154"/>
-          <cell r="T154"/>
-          <cell r="U154"/>
-          <cell r="V154"/>
-          <cell r="W154"/>
-          <cell r="X154"/>
-        </row>
-        <row r="155">
-          <cell r="D155"/>
-          <cell r="E155"/>
-          <cell r="F155"/>
-          <cell r="G155"/>
-          <cell r="H155"/>
-          <cell r="I155"/>
-          <cell r="J155"/>
-          <cell r="K155"/>
-          <cell r="L155"/>
-          <cell r="M155"/>
-          <cell r="N155"/>
-          <cell r="O155"/>
-          <cell r="P155"/>
-          <cell r="Q155"/>
-          <cell r="R155"/>
-          <cell r="S155"/>
-          <cell r="T155"/>
-          <cell r="U155"/>
-          <cell r="V155"/>
-          <cell r="W155"/>
-          <cell r="X155"/>
-        </row>
-        <row r="156">
-          <cell r="D156"/>
-          <cell r="E156"/>
-          <cell r="F156"/>
-          <cell r="G156"/>
-          <cell r="H156"/>
-          <cell r="I156"/>
-          <cell r="J156"/>
-          <cell r="K156"/>
-          <cell r="L156"/>
-          <cell r="M156"/>
-          <cell r="N156"/>
-          <cell r="O156"/>
-          <cell r="P156"/>
-          <cell r="Q156"/>
-          <cell r="R156"/>
-          <cell r="S156"/>
-          <cell r="T156"/>
-          <cell r="U156"/>
-          <cell r="V156"/>
-          <cell r="W156"/>
-          <cell r="X156"/>
-        </row>
-        <row r="157">
-          <cell r="D157"/>
-          <cell r="E157"/>
-          <cell r="F157"/>
-          <cell r="G157"/>
-          <cell r="H157"/>
-          <cell r="I157"/>
-          <cell r="J157"/>
-          <cell r="K157"/>
-          <cell r="L157"/>
-          <cell r="M157"/>
-          <cell r="N157"/>
-          <cell r="O157"/>
-          <cell r="P157"/>
-          <cell r="Q157"/>
-          <cell r="R157"/>
-          <cell r="S157"/>
-          <cell r="T157"/>
-          <cell r="U157"/>
-          <cell r="V157"/>
-          <cell r="W157"/>
-          <cell r="X157"/>
-        </row>
-        <row r="158">
-          <cell r="D158"/>
-          <cell r="E158"/>
-          <cell r="F158"/>
-          <cell r="G158"/>
-          <cell r="H158"/>
-          <cell r="I158"/>
-          <cell r="J158"/>
-          <cell r="K158"/>
-          <cell r="L158"/>
-          <cell r="M158"/>
-          <cell r="N158"/>
-          <cell r="O158"/>
-          <cell r="P158"/>
-          <cell r="Q158"/>
-          <cell r="R158"/>
-          <cell r="S158"/>
-          <cell r="T158"/>
-          <cell r="U158"/>
-          <cell r="V158"/>
-          <cell r="W158"/>
-          <cell r="X158"/>
-        </row>
-        <row r="159">
-          <cell r="D159"/>
-          <cell r="E159"/>
-          <cell r="F159"/>
-          <cell r="G159"/>
-          <cell r="H159"/>
-          <cell r="I159"/>
-          <cell r="J159"/>
-          <cell r="K159"/>
-          <cell r="L159"/>
-          <cell r="M159"/>
-          <cell r="N159"/>
-          <cell r="O159"/>
-          <cell r="P159"/>
-          <cell r="Q159"/>
-          <cell r="R159"/>
-          <cell r="S159"/>
-          <cell r="T159"/>
-          <cell r="U159"/>
-          <cell r="V159"/>
-          <cell r="W159"/>
-          <cell r="X159"/>
-        </row>
-        <row r="160">
-          <cell r="D160"/>
-          <cell r="E160"/>
-          <cell r="F160"/>
-          <cell r="G160"/>
-          <cell r="H160"/>
-          <cell r="I160"/>
-          <cell r="J160"/>
-          <cell r="K160"/>
-          <cell r="L160"/>
-          <cell r="M160"/>
-          <cell r="N160"/>
-          <cell r="O160"/>
-          <cell r="P160"/>
-          <cell r="Q160"/>
-          <cell r="R160"/>
-          <cell r="S160"/>
-          <cell r="T160"/>
-          <cell r="U160"/>
-          <cell r="V160"/>
-          <cell r="W160"/>
-          <cell r="X160"/>
-        </row>
-        <row r="161">
-          <cell r="D161"/>
-          <cell r="E161"/>
-          <cell r="F161"/>
-          <cell r="G161"/>
-          <cell r="H161"/>
-          <cell r="I161"/>
-          <cell r="J161"/>
-          <cell r="K161"/>
-          <cell r="L161"/>
-          <cell r="M161"/>
-          <cell r="N161"/>
-          <cell r="O161"/>
-          <cell r="P161"/>
-          <cell r="Q161"/>
-          <cell r="R161"/>
-          <cell r="S161"/>
-          <cell r="T161"/>
-          <cell r="U161"/>
-          <cell r="V161"/>
-          <cell r="W161"/>
-          <cell r="X161"/>
-        </row>
-        <row r="162">
-          <cell r="D162"/>
-          <cell r="E162"/>
-          <cell r="F162"/>
-          <cell r="G162"/>
-          <cell r="H162"/>
-          <cell r="I162"/>
-          <cell r="J162"/>
-          <cell r="K162"/>
-          <cell r="L162"/>
-          <cell r="M162"/>
-          <cell r="N162"/>
-          <cell r="O162"/>
-          <cell r="P162"/>
-          <cell r="Q162"/>
-          <cell r="R162"/>
-          <cell r="S162"/>
-          <cell r="T162"/>
-          <cell r="U162"/>
-          <cell r="V162"/>
-          <cell r="W162"/>
-          <cell r="X162"/>
-        </row>
-        <row r="163">
-          <cell r="D163"/>
-          <cell r="E163"/>
-          <cell r="F163"/>
-          <cell r="G163"/>
-          <cell r="H163"/>
-          <cell r="I163"/>
-          <cell r="J163"/>
-          <cell r="K163"/>
-          <cell r="L163"/>
-          <cell r="M163"/>
-          <cell r="N163"/>
-          <cell r="O163"/>
-          <cell r="P163"/>
-          <cell r="Q163"/>
-          <cell r="R163"/>
-          <cell r="S163"/>
-          <cell r="T163"/>
-          <cell r="U163"/>
-          <cell r="V163"/>
-          <cell r="W163"/>
-          <cell r="X163"/>
-        </row>
-        <row r="164">
-          <cell r="D164"/>
-          <cell r="E164"/>
-          <cell r="F164"/>
-          <cell r="G164"/>
-          <cell r="H164"/>
-          <cell r="I164"/>
-          <cell r="J164"/>
-          <cell r="K164"/>
-          <cell r="L164"/>
-          <cell r="M164"/>
-          <cell r="N164"/>
-          <cell r="O164"/>
-          <cell r="P164"/>
-          <cell r="Q164"/>
-          <cell r="R164"/>
-          <cell r="S164"/>
-          <cell r="T164"/>
-          <cell r="U164"/>
-          <cell r="V164"/>
-          <cell r="W164"/>
-          <cell r="X164"/>
-        </row>
-        <row r="165">
-          <cell r="D165"/>
-          <cell r="E165"/>
-          <cell r="F165"/>
-          <cell r="G165"/>
-          <cell r="H165"/>
-          <cell r="I165"/>
-          <cell r="J165"/>
-          <cell r="K165"/>
-          <cell r="L165"/>
-          <cell r="M165"/>
-          <cell r="N165"/>
-          <cell r="O165"/>
-          <cell r="P165"/>
-          <cell r="Q165"/>
-          <cell r="R165"/>
-          <cell r="S165"/>
-          <cell r="T165"/>
-          <cell r="U165"/>
-          <cell r="V165"/>
-          <cell r="W165"/>
-          <cell r="X165"/>
-        </row>
-        <row r="166">
-          <cell r="D166"/>
-          <cell r="E166"/>
-          <cell r="F166"/>
-          <cell r="G166"/>
-          <cell r="H166"/>
-          <cell r="I166"/>
-          <cell r="J166"/>
-          <cell r="K166"/>
-          <cell r="L166"/>
-          <cell r="M166"/>
-          <cell r="N166"/>
-          <cell r="O166"/>
-          <cell r="P166"/>
-          <cell r="Q166"/>
-          <cell r="R166"/>
-          <cell r="S166"/>
-          <cell r="T166"/>
-          <cell r="U166"/>
-          <cell r="V166"/>
-          <cell r="W166"/>
-          <cell r="X166"/>
-        </row>
-        <row r="167">
-          <cell r="D167"/>
-          <cell r="E167"/>
-          <cell r="F167"/>
-          <cell r="G167"/>
-          <cell r="H167"/>
-          <cell r="I167"/>
-          <cell r="J167"/>
-          <cell r="K167"/>
-          <cell r="L167"/>
-          <cell r="M167"/>
-          <cell r="N167"/>
-          <cell r="O167"/>
-          <cell r="P167"/>
-          <cell r="Q167"/>
-          <cell r="R167"/>
-          <cell r="S167"/>
-          <cell r="T167"/>
-          <cell r="U167"/>
-          <cell r="V167"/>
-          <cell r="W167"/>
-          <cell r="X167"/>
-        </row>
-        <row r="168">
-          <cell r="D168"/>
-          <cell r="E168"/>
-          <cell r="F168"/>
-          <cell r="G168"/>
-          <cell r="H168"/>
-          <cell r="I168"/>
-          <cell r="J168"/>
-          <cell r="K168"/>
-          <cell r="L168"/>
-          <cell r="M168"/>
-          <cell r="N168"/>
-          <cell r="O168"/>
-          <cell r="P168"/>
-          <cell r="Q168"/>
-          <cell r="R168"/>
-          <cell r="S168"/>
-          <cell r="T168"/>
-          <cell r="U168"/>
-          <cell r="V168"/>
-          <cell r="W168"/>
-          <cell r="X168"/>
-        </row>
-        <row r="169">
-          <cell r="D169"/>
-          <cell r="E169"/>
-          <cell r="F169"/>
-          <cell r="G169"/>
-          <cell r="H169"/>
-          <cell r="I169"/>
-          <cell r="J169"/>
-          <cell r="K169"/>
-          <cell r="L169"/>
-          <cell r="M169"/>
-          <cell r="N169"/>
-          <cell r="O169"/>
-          <cell r="P169"/>
-          <cell r="Q169"/>
-          <cell r="R169"/>
-          <cell r="S169"/>
-          <cell r="T169"/>
-          <cell r="U169"/>
-          <cell r="V169"/>
-          <cell r="W169"/>
-          <cell r="X169"/>
-        </row>
-        <row r="170">
-          <cell r="D170"/>
-          <cell r="E170"/>
-          <cell r="F170"/>
-          <cell r="G170"/>
-          <cell r="H170"/>
-          <cell r="I170"/>
-          <cell r="J170"/>
-          <cell r="K170"/>
-          <cell r="L170"/>
-          <cell r="M170"/>
-          <cell r="N170"/>
-          <cell r="O170"/>
-          <cell r="P170"/>
-          <cell r="Q170"/>
-          <cell r="R170"/>
-          <cell r="S170"/>
-          <cell r="T170"/>
-          <cell r="U170"/>
-          <cell r="V170"/>
-          <cell r="W170"/>
-          <cell r="X170"/>
-        </row>
-        <row r="171">
-          <cell r="D171"/>
-          <cell r="E171"/>
-          <cell r="F171"/>
-          <cell r="G171"/>
-          <cell r="H171"/>
-          <cell r="I171"/>
-          <cell r="J171"/>
-          <cell r="K171"/>
-          <cell r="L171"/>
-          <cell r="M171"/>
-          <cell r="N171"/>
-          <cell r="O171"/>
-          <cell r="P171"/>
-          <cell r="Q171"/>
-          <cell r="R171"/>
-          <cell r="S171"/>
-          <cell r="T171"/>
-          <cell r="U171"/>
-          <cell r="V171"/>
-          <cell r="W171"/>
-          <cell r="X171"/>
-        </row>
-        <row r="172">
-          <cell r="D172"/>
-          <cell r="E172"/>
-          <cell r="F172"/>
-          <cell r="G172"/>
-          <cell r="H172"/>
-          <cell r="I172"/>
-          <cell r="J172"/>
-          <cell r="K172"/>
-          <cell r="L172"/>
-          <cell r="M172"/>
-          <cell r="N172"/>
-          <cell r="O172"/>
-          <cell r="P172"/>
-          <cell r="Q172"/>
-          <cell r="R172"/>
-          <cell r="S172"/>
-          <cell r="T172"/>
-          <cell r="U172"/>
-          <cell r="V172"/>
-          <cell r="W172"/>
-          <cell r="X172"/>
-        </row>
-        <row r="173">
-          <cell r="D173"/>
-          <cell r="E173"/>
-          <cell r="F173"/>
-          <cell r="G173"/>
-          <cell r="H173"/>
-          <cell r="I173"/>
-          <cell r="J173"/>
-          <cell r="K173"/>
-          <cell r="L173"/>
-          <cell r="M173"/>
-          <cell r="N173"/>
-          <cell r="O173"/>
-          <cell r="P173"/>
-          <cell r="Q173"/>
-          <cell r="R173"/>
-          <cell r="S173"/>
-          <cell r="T173"/>
-          <cell r="U173"/>
-          <cell r="V173"/>
-          <cell r="W173"/>
-          <cell r="X173"/>
-        </row>
-        <row r="174">
-          <cell r="D174"/>
-          <cell r="E174"/>
-          <cell r="F174"/>
-          <cell r="G174"/>
-          <cell r="H174"/>
-          <cell r="I174"/>
-          <cell r="J174"/>
-          <cell r="K174"/>
-          <cell r="L174"/>
-          <cell r="M174"/>
-          <cell r="N174"/>
-          <cell r="O174"/>
-          <cell r="P174"/>
-          <cell r="Q174"/>
-          <cell r="R174"/>
-          <cell r="S174"/>
-          <cell r="T174"/>
-          <cell r="U174"/>
-          <cell r="V174"/>
-          <cell r="W174"/>
-          <cell r="X174"/>
-        </row>
-        <row r="175">
-          <cell r="D175"/>
-          <cell r="E175"/>
-          <cell r="F175"/>
-          <cell r="G175"/>
-          <cell r="H175"/>
-          <cell r="I175"/>
-          <cell r="J175"/>
-          <cell r="K175"/>
-          <cell r="L175"/>
-          <cell r="M175"/>
-          <cell r="N175"/>
-          <cell r="O175"/>
-          <cell r="P175"/>
-          <cell r="Q175"/>
-          <cell r="R175"/>
-          <cell r="S175"/>
-          <cell r="T175"/>
-          <cell r="U175"/>
-          <cell r="V175"/>
-          <cell r="W175"/>
-          <cell r="X175"/>
-        </row>
-        <row r="176">
-          <cell r="D176"/>
-          <cell r="E176"/>
-          <cell r="F176"/>
-          <cell r="G176"/>
-          <cell r="H176"/>
-          <cell r="I176"/>
-          <cell r="J176"/>
-          <cell r="K176"/>
-          <cell r="L176"/>
-          <cell r="M176"/>
-          <cell r="N176"/>
-          <cell r="O176"/>
-          <cell r="P176"/>
-          <cell r="Q176"/>
-          <cell r="R176"/>
-          <cell r="S176"/>
-          <cell r="T176"/>
-          <cell r="U176"/>
-          <cell r="V176"/>
-          <cell r="W176"/>
-          <cell r="X176"/>
-        </row>
-        <row r="177">
-          <cell r="D177"/>
-          <cell r="E177"/>
-          <cell r="F177"/>
-          <cell r="G177"/>
-          <cell r="H177"/>
-          <cell r="I177"/>
-          <cell r="J177"/>
-          <cell r="K177"/>
-          <cell r="L177"/>
-          <cell r="M177"/>
-          <cell r="N177"/>
-          <cell r="O177"/>
-          <cell r="P177"/>
-          <cell r="Q177"/>
-          <cell r="R177"/>
-          <cell r="S177"/>
-          <cell r="T177"/>
-          <cell r="U177"/>
-          <cell r="V177"/>
-          <cell r="W177"/>
-          <cell r="X177"/>
-        </row>
-        <row r="178">
-          <cell r="D178"/>
-          <cell r="E178"/>
-          <cell r="F178"/>
-          <cell r="G178"/>
-          <cell r="H178"/>
-          <cell r="I178"/>
-          <cell r="J178"/>
-          <cell r="K178"/>
-          <cell r="L178"/>
-          <cell r="M178"/>
-          <cell r="N178"/>
-          <cell r="O178"/>
-          <cell r="P178"/>
-          <cell r="Q178"/>
-          <cell r="R178"/>
-          <cell r="S178"/>
-          <cell r="T178"/>
-          <cell r="U178"/>
-          <cell r="V178"/>
-          <cell r="W178"/>
-          <cell r="X178"/>
-        </row>
-        <row r="179">
-          <cell r="D179"/>
-          <cell r="E179"/>
-          <cell r="F179"/>
-          <cell r="G179"/>
-          <cell r="H179"/>
-          <cell r="I179"/>
-          <cell r="J179"/>
-          <cell r="K179"/>
-          <cell r="L179"/>
-          <cell r="M179"/>
-          <cell r="N179"/>
-          <cell r="O179"/>
-          <cell r="P179"/>
-          <cell r="Q179"/>
-          <cell r="R179"/>
-          <cell r="S179"/>
-          <cell r="T179"/>
-          <cell r="U179"/>
-          <cell r="V179"/>
-          <cell r="W179"/>
-          <cell r="X179"/>
-        </row>
-        <row r="180">
-          <cell r="D180"/>
-          <cell r="E180"/>
-          <cell r="F180"/>
-          <cell r="G180"/>
-          <cell r="H180"/>
-          <cell r="I180"/>
-          <cell r="J180"/>
-          <cell r="K180"/>
-          <cell r="L180"/>
-          <cell r="M180"/>
-          <cell r="N180"/>
-          <cell r="O180"/>
-          <cell r="P180"/>
-          <cell r="Q180"/>
-          <cell r="R180"/>
-          <cell r="S180"/>
-          <cell r="T180"/>
-          <cell r="U180"/>
-          <cell r="V180"/>
-          <cell r="W180"/>
-          <cell r="X180"/>
-        </row>
-        <row r="181">
-          <cell r="D181"/>
-          <cell r="E181"/>
-          <cell r="F181"/>
-          <cell r="G181"/>
-          <cell r="H181"/>
-          <cell r="I181"/>
-          <cell r="J181"/>
-          <cell r="K181"/>
-          <cell r="L181"/>
-          <cell r="M181"/>
-          <cell r="N181"/>
-          <cell r="O181"/>
-          <cell r="P181"/>
-          <cell r="Q181"/>
-          <cell r="R181"/>
-          <cell r="S181"/>
-          <cell r="T181"/>
-          <cell r="U181"/>
-          <cell r="V181"/>
-          <cell r="W181"/>
-          <cell r="X181"/>
-        </row>
-        <row r="182">
-          <cell r="D182"/>
-          <cell r="E182"/>
-          <cell r="F182"/>
-          <cell r="G182"/>
-          <cell r="H182"/>
-          <cell r="I182"/>
-          <cell r="J182"/>
-          <cell r="K182"/>
-          <cell r="L182"/>
-          <cell r="M182"/>
-          <cell r="N182"/>
-          <cell r="O182"/>
-          <cell r="P182"/>
-          <cell r="Q182"/>
-          <cell r="R182"/>
-          <cell r="S182"/>
-          <cell r="T182"/>
-          <cell r="U182"/>
-          <cell r="V182"/>
-          <cell r="W182"/>
-          <cell r="X182"/>
-        </row>
-        <row r="183">
-          <cell r="D183"/>
-          <cell r="E183"/>
-          <cell r="F183"/>
-          <cell r="G183"/>
-          <cell r="H183"/>
-          <cell r="I183"/>
-          <cell r="J183"/>
-          <cell r="K183"/>
-          <cell r="L183"/>
-          <cell r="M183"/>
-          <cell r="N183"/>
-          <cell r="O183"/>
-          <cell r="P183"/>
-          <cell r="Q183"/>
-          <cell r="R183"/>
-          <cell r="S183"/>
-          <cell r="T183"/>
-          <cell r="U183"/>
-          <cell r="V183"/>
-          <cell r="W183"/>
-          <cell r="X183"/>
-        </row>
-        <row r="184">
-          <cell r="D184"/>
-          <cell r="E184"/>
-          <cell r="F184"/>
-          <cell r="G184"/>
-          <cell r="H184"/>
-          <cell r="I184"/>
-          <cell r="J184"/>
-          <cell r="K184"/>
-          <cell r="L184"/>
-          <cell r="M184"/>
-          <cell r="N184"/>
-          <cell r="O184"/>
-          <cell r="P184"/>
-          <cell r="Q184"/>
-          <cell r="R184"/>
-          <cell r="S184"/>
-          <cell r="T184"/>
-          <cell r="U184"/>
-          <cell r="V184"/>
-          <cell r="W184"/>
-          <cell r="X184"/>
-        </row>
-        <row r="185">
-          <cell r="D185"/>
-          <cell r="E185"/>
-          <cell r="F185"/>
-          <cell r="G185"/>
-          <cell r="H185"/>
-          <cell r="I185"/>
-          <cell r="J185"/>
-          <cell r="K185"/>
-          <cell r="L185"/>
-          <cell r="M185"/>
-          <cell r="N185"/>
-          <cell r="O185"/>
-          <cell r="P185"/>
-          <cell r="Q185"/>
-          <cell r="R185"/>
-          <cell r="S185"/>
-          <cell r="T185"/>
-          <cell r="U185"/>
-          <cell r="V185"/>
-          <cell r="W185"/>
-          <cell r="X185"/>
-        </row>
-        <row r="186">
-          <cell r="D186"/>
-          <cell r="E186"/>
-          <cell r="F186"/>
-          <cell r="G186"/>
-          <cell r="H186"/>
-          <cell r="I186"/>
-          <cell r="J186"/>
-          <cell r="K186"/>
-          <cell r="L186"/>
-          <cell r="M186"/>
-          <cell r="N186"/>
-          <cell r="O186"/>
-          <cell r="P186"/>
-          <cell r="Q186"/>
-          <cell r="R186"/>
-          <cell r="S186"/>
-          <cell r="T186"/>
-          <cell r="U186"/>
-          <cell r="V186"/>
-          <cell r="W186"/>
-          <cell r="X186"/>
-        </row>
-        <row r="187">
-          <cell r="D187"/>
-          <cell r="E187"/>
-          <cell r="F187"/>
-          <cell r="G187"/>
-          <cell r="H187"/>
-          <cell r="I187"/>
-          <cell r="J187"/>
-          <cell r="K187"/>
-          <cell r="L187"/>
-          <cell r="M187"/>
-          <cell r="N187"/>
-          <cell r="O187"/>
-          <cell r="P187"/>
-          <cell r="Q187"/>
-          <cell r="R187"/>
-          <cell r="S187"/>
-          <cell r="T187"/>
-          <cell r="U187"/>
-          <cell r="V187"/>
-          <cell r="W187"/>
-          <cell r="X187"/>
-        </row>
-        <row r="188">
-          <cell r="D188"/>
-          <cell r="E188"/>
-          <cell r="F188"/>
-          <cell r="G188"/>
-          <cell r="H188"/>
-          <cell r="I188"/>
-          <cell r="J188"/>
-          <cell r="K188"/>
-          <cell r="L188"/>
-          <cell r="M188"/>
-          <cell r="N188"/>
-          <cell r="O188"/>
-          <cell r="P188"/>
-          <cell r="Q188"/>
-          <cell r="R188"/>
-          <cell r="S188"/>
-          <cell r="T188"/>
-          <cell r="U188"/>
-          <cell r="V188"/>
-          <cell r="W188"/>
-          <cell r="X188"/>
-        </row>
-        <row r="189">
-          <cell r="D189"/>
-          <cell r="E189"/>
-          <cell r="F189"/>
-          <cell r="G189"/>
-          <cell r="H189"/>
-          <cell r="I189"/>
-          <cell r="J189"/>
-          <cell r="K189"/>
-          <cell r="L189"/>
-          <cell r="M189"/>
-          <cell r="N189"/>
-          <cell r="O189"/>
-          <cell r="P189"/>
-          <cell r="Q189"/>
-          <cell r="R189"/>
-          <cell r="S189"/>
-          <cell r="T189"/>
-          <cell r="U189"/>
-          <cell r="V189"/>
-          <cell r="W189"/>
-          <cell r="X189"/>
-        </row>
-        <row r="190">
-          <cell r="D190"/>
-          <cell r="E190"/>
-          <cell r="F190"/>
-          <cell r="G190"/>
-          <cell r="H190"/>
-          <cell r="I190"/>
-          <cell r="J190"/>
-          <cell r="K190"/>
-          <cell r="L190"/>
-          <cell r="M190"/>
-          <cell r="N190"/>
-          <cell r="O190"/>
-          <cell r="P190"/>
-          <cell r="Q190"/>
-          <cell r="R190"/>
-          <cell r="S190"/>
-          <cell r="T190"/>
-          <cell r="U190"/>
-          <cell r="V190"/>
-          <cell r="W190"/>
-          <cell r="X190"/>
-        </row>
-        <row r="191">
-          <cell r="D191"/>
-          <cell r="E191"/>
-          <cell r="F191"/>
-          <cell r="G191"/>
-          <cell r="H191"/>
-          <cell r="I191"/>
-          <cell r="J191"/>
-          <cell r="K191"/>
-          <cell r="L191"/>
-          <cell r="M191"/>
-          <cell r="N191"/>
-          <cell r="O191"/>
-          <cell r="P191"/>
-          <cell r="Q191"/>
-          <cell r="R191"/>
-          <cell r="S191"/>
-          <cell r="T191"/>
-          <cell r="U191"/>
-          <cell r="V191"/>
-          <cell r="W191"/>
-          <cell r="X191"/>
-        </row>
-        <row r="192">
-          <cell r="D192"/>
-          <cell r="E192"/>
-          <cell r="F192"/>
-          <cell r="G192"/>
-          <cell r="H192"/>
-          <cell r="I192"/>
-          <cell r="J192"/>
-          <cell r="K192"/>
-          <cell r="L192"/>
-          <cell r="M192"/>
-          <cell r="N192"/>
-          <cell r="O192"/>
-          <cell r="P192"/>
-          <cell r="Q192"/>
-          <cell r="R192"/>
-          <cell r="S192"/>
-          <cell r="T192"/>
-          <cell r="U192"/>
-          <cell r="V192"/>
-          <cell r="W192"/>
-          <cell r="X192"/>
-        </row>
-        <row r="193">
-          <cell r="D193"/>
-          <cell r="E193"/>
-          <cell r="F193"/>
-          <cell r="G193"/>
-          <cell r="H193"/>
-          <cell r="I193"/>
-          <cell r="J193"/>
-          <cell r="K193"/>
-          <cell r="L193"/>
-          <cell r="M193"/>
-          <cell r="N193"/>
-          <cell r="O193"/>
-          <cell r="P193"/>
-          <cell r="Q193"/>
-          <cell r="R193"/>
-          <cell r="S193"/>
-          <cell r="T193"/>
-          <cell r="U193"/>
-          <cell r="V193"/>
-          <cell r="W193"/>
-          <cell r="X193"/>
-        </row>
-        <row r="194">
-          <cell r="D194"/>
-          <cell r="E194"/>
-          <cell r="F194"/>
-          <cell r="G194"/>
-          <cell r="H194"/>
-          <cell r="I194"/>
-          <cell r="J194"/>
-          <cell r="K194"/>
-          <cell r="L194"/>
-          <cell r="M194"/>
-          <cell r="N194"/>
-          <cell r="O194"/>
-          <cell r="P194"/>
-          <cell r="Q194"/>
-          <cell r="R194"/>
-          <cell r="S194"/>
-          <cell r="T194"/>
-          <cell r="U194"/>
-          <cell r="V194"/>
-          <cell r="W194"/>
-          <cell r="X194"/>
-        </row>
-        <row r="195">
-          <cell r="D195"/>
-          <cell r="E195"/>
-          <cell r="F195"/>
-          <cell r="G195"/>
-          <cell r="H195"/>
-          <cell r="I195"/>
-          <cell r="J195"/>
-          <cell r="K195"/>
-          <cell r="L195"/>
-          <cell r="M195"/>
-          <cell r="N195"/>
-          <cell r="O195"/>
-          <cell r="P195"/>
-          <cell r="Q195"/>
-          <cell r="R195"/>
-          <cell r="S195"/>
-          <cell r="T195"/>
-          <cell r="U195"/>
-          <cell r="V195"/>
-          <cell r="W195"/>
-          <cell r="X195"/>
-        </row>
-        <row r="196">
-          <cell r="D196"/>
-          <cell r="E196"/>
-          <cell r="F196"/>
-          <cell r="G196"/>
-          <cell r="H196"/>
-          <cell r="I196"/>
-          <cell r="J196"/>
-          <cell r="K196"/>
-          <cell r="L196"/>
-          <cell r="M196"/>
-          <cell r="N196"/>
-          <cell r="O196"/>
-          <cell r="P196"/>
-          <cell r="Q196"/>
-          <cell r="R196"/>
-          <cell r="S196"/>
-          <cell r="T196"/>
-          <cell r="U196"/>
-          <cell r="V196"/>
-          <cell r="W196"/>
-          <cell r="X196"/>
-        </row>
-        <row r="197">
-          <cell r="D197"/>
-          <cell r="E197"/>
-          <cell r="F197"/>
-          <cell r="G197"/>
-          <cell r="H197"/>
-          <cell r="I197"/>
-          <cell r="J197"/>
-          <cell r="K197"/>
-          <cell r="L197"/>
-          <cell r="M197"/>
-          <cell r="N197"/>
-          <cell r="O197"/>
-          <cell r="P197"/>
-          <cell r="Q197"/>
-          <cell r="R197"/>
-          <cell r="S197"/>
-          <cell r="T197"/>
-          <cell r="U197"/>
-          <cell r="V197"/>
-          <cell r="W197"/>
-          <cell r="X197"/>
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>NJIT</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>Vermont</v>
+          </cell>
+          <cell r="D33">
+            <v>-12.855933529800252</v>
+          </cell>
+          <cell r="E33">
+            <v>97.230326689952733</v>
+          </cell>
+          <cell r="F33">
+            <v>98.860244215497659</v>
+          </cell>
+          <cell r="G33">
+            <v>0.4684095860566449</v>
+          </cell>
+          <cell r="H33">
+            <v>67.618750000000006</v>
+          </cell>
+          <cell r="I33">
+            <v>57.375</v>
+          </cell>
+          <cell r="J33">
+            <v>19.375</v>
+          </cell>
+          <cell r="K33">
+            <v>9.84375</v>
+          </cell>
+          <cell r="L33">
+            <v>11.5625</v>
+          </cell>
+          <cell r="M33">
+            <v>0</v>
+          </cell>
+          <cell r="N33">
+            <v>-8.3063732632254172</v>
+          </cell>
+          <cell r="O33">
+            <v>98.685284640171872</v>
+          </cell>
+          <cell r="P33">
+            <v>109.91881615719028</v>
+          </cell>
+          <cell r="Q33">
+            <v>0.54303164908384227</v>
+          </cell>
+          <cell r="R33">
+            <v>64.849999999999994</v>
+          </cell>
+          <cell r="S33">
+            <v>56.28125</v>
+          </cell>
+          <cell r="T33">
+            <v>18.125</v>
+          </cell>
+          <cell r="U33">
+            <v>8.84375</v>
+          </cell>
+          <cell r="V33">
+            <v>9.4375</v>
+          </cell>
+          <cell r="W33">
+            <v>0</v>
+          </cell>
+          <cell r="X33">
+            <v>12</v>
+          </cell>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -22671,7 +19812,8 @@
     <col min="2" max="2" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="1"/>
+    <col min="5" max="5" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="10.83203125" style="1"/>
   </cols>
@@ -22687,13 +19829,13 @@
         <v>368</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>369</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>370</v>
@@ -22713,306 +19855,242 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>8</v>
-      </c>
-      <c r="B2" s="7" t="str">
+        <v>23</v>
+      </c>
+      <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Texas A&amp;M-CC</v>
-      </c>
-      <c r="C2" s="7" t="str">
+        <v>Wake Forest</v>
+      </c>
+      <c r="C2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>New Orleans</v>
-      </c>
-      <c r="D2" s="7" t="str">
+        <v>Virginia Tech</v>
+      </c>
+      <c r="D2" s="6" t="str">
         <f>B2</f>
-        <v>Texas A&amp;M-CC</v>
-      </c>
-      <c r="E2" s="6">
+        <v>Wake Forest</v>
+      </c>
+      <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.3868951200287372</v>
-      </c>
-      <c r="F2" s="6">
+        <v>2.3151298429323668</v>
+      </c>
+      <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="G2" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.53202678492272726</v>
-      </c>
-      <c r="H2" s="8">
+        <v>0.35714032797427958</v>
+      </c>
+      <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>5.7031373430392038E-2</v>
-      </c>
-      <c r="I2" s="8">
+        <v>4.9348494359130413E-2</v>
+      </c>
+      <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.9449643994540923E-2</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="K2" s="10">
+        <v>4.5084371794960422E-2</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="K2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
-        <v>0</v>
+        <v>0.74022741538695613</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Campbell</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Monmouth</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <f t="shared" ref="D3" si="0">B3</f>
-        <v>Campbell</v>
-      </c>
-      <c r="E3" s="6">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>3.3775609745382869</v>
-      </c>
-      <c r="F3" s="6">
-        <f>-VLOOKUP(A3,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>-1.5</v>
-      </c>
-      <c r="G3" s="8">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.39314315209501782</v>
-      </c>
-      <c r="H3" s="8">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>5.0597452435234738E-2</v>
-      </c>
-      <c r="I3" s="8">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.5794007065474325E-2</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="K3" s="10">
-        <f t="shared" ref="K3" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
-        <v>0</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>13</v>
-      </c>
-      <c r="B4" s="7" t="str">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Weber State</v>
-      </c>
-      <c r="C4" s="7" t="str">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Eastern Washington</v>
-      </c>
-      <c r="D4" s="7" t="str">
-        <f t="shared" ref="D4" si="2">B4</f>
-        <v>Weber State</v>
-      </c>
-      <c r="E4" s="6">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>1.647409309030833</v>
-      </c>
-      <c r="F4" s="6">
-        <f>-VLOOKUP(A4,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>-3</v>
-      </c>
-      <c r="G4" s="8">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.32689113933500502</v>
-      </c>
-      <c r="H4" s="8">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>4.5985964065945087E-2</v>
-      </c>
-      <c r="I4" s="8">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.3173843219287002E-2</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="K4" s="10">
-        <f t="shared" ref="K4" si="3">IF(J4="Yes",(H4*1500)/100,0)</f>
-        <v>0.68978946098917637</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="11"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="11"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="11"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="11"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="11"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="11"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="11"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="11"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="11"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="11"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="11"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="11"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="10"/>
     </row>
     <row r="17" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="11"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="11"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="10"/>
     </row>
     <row r="19" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="11"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="10"/>
     </row>
     <row r="20" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="11"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="10"/>
     </row>
     <row r="21" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="11"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="10"/>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="11"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="10"/>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="11"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23064,21 +20142,21 @@
       </c>
       <c r="B2" s="1">
         <f>COUNTIF($C$6:$C$150,"L")</f>
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+      <c r="C2" s="13">
         <f>SUM(E6:E13)/SUM(D6:D13)</f>
         <v>-1</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <f>AVERAGE(G6:G150)</f>
-        <v>-1.9985536081552357E-2</v>
+        <v>-7.3041333591230655E-3</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23107,27 +20185,27 @@
         <v>399</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="L5" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -23138,26 +20216,26 @@
       <c r="D6" s="1">
         <v>0.94499999999999995</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="15">
         <f>IF(C6="P",0,IF(C6="L",-D6,IF(I6&lt;0,D6*(100/-I6),D6*(I6/100)))/1)</f>
         <v>-0.94499999999999995</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="15">
         <f>E6</f>
         <v>-0.94499999999999995</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <f>((K6-N6)*3.55%)+(M6-J6)</f>
         <v>-1.9985536081552357E-2</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <f>G6</f>
         <v>-1.9985536081552357E-2</v>
       </c>
       <c r="I6" s="1">
         <v>-112</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <f>IF(I6&lt;0,I6/(I6-100),100/(I6+100))</f>
         <v>0.52830188679245282</v>
       </c>
@@ -23167,7 +20245,7 @@
       <c r="L6" s="1">
         <v>-111</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
         <f>IF(L6&lt;0,L6/(L6-100),100/(L6+100))</f>
         <v>0.52606635071090047</v>
       </c>
@@ -23176,23 +20254,63 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F7" s="1">
+      <c r="A7" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.68979999999999997</v>
+      </c>
+      <c r="E7" s="15">
+        <f>IF(C7="P",0,IF(C7="L",-D7,IF(I7&lt;0,D7*(100/-I7),D7*(I7/100)))/1)</f>
+        <v>-0.68979999999999997</v>
+      </c>
+      <c r="F7" s="15">
         <f>E7+F6</f>
-        <v>-0.94499999999999995</v>
-      </c>
-      <c r="H7" s="12">
+        <v>-1.6347999999999998</v>
+      </c>
+      <c r="G7" s="11">
+        <f>((K7-N7)*3.55%)+(M7-J7)</f>
+        <v>5.3772693633062259E-3</v>
+      </c>
+      <c r="H7" s="11">
         <f>AVERAGE($G$6:G7)</f>
-        <v>-1.9985536081552357E-2</v>
+        <v>-7.3041333591230655E-3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>-103</v>
+      </c>
+      <c r="J7" s="13">
+        <f>IF(I7&lt;0,I7/(I7-100),100/(I7+100))</f>
+        <v>0.5073891625615764</v>
+      </c>
+      <c r="K7" s="1">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1">
+        <v>-113</v>
+      </c>
+      <c r="M7" s="13">
+        <f>IF(L7&lt;0,L7/(L7-100),100/(L7+100))</f>
+        <v>0.53051643192488263</v>
+      </c>
+      <c r="N7" s="1">
+        <v>3.5</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F8" s="1">
+      <c r="F8" s="15">
         <f>E8+F7</f>
-        <v>-0.94499999999999995</v>
-      </c>
-      <c r="H8" s="12">
+        <v>-1.6347999999999998</v>
+      </c>
+      <c r="H8" s="11">
         <f>AVERAGE($G$6:G8)</f>
-        <v>-1.9985536081552357E-2</v>
+        <v>-7.3041333591230655E-3</v>
       </c>
     </row>
   </sheetData>
@@ -23212,45 +20330,45 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>402</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>394</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -23265,10 +20383,10 @@
         <v>475</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>418</v>
+        <v>414</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>417</v>
       </c>
       <c r="K2" s="1">
         <f>IF(J2="W",(D2/100)*E2,IF(J2="",0,-E2))</f>
@@ -23277,10 +20395,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
@@ -23295,10 +20413,10 @@
         <v>6000</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>419</v>
+        <v>414</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>418</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" ref="K3:K5" si="0">IF(J3="W",(D3/100)*E3,IF(J3="",0,-E3))</f>
@@ -23307,10 +20425,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -23325,10 +20443,10 @@
         <v>1800</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>419</v>
+        <v>414</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>418</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="0"/>
@@ -23337,10 +20455,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>48</v>
@@ -23355,10 +20473,10 @@
         <v>50000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>419</v>
+        <v>414</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>418</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="0"/>
@@ -23389,7 +20507,7 @@
         <v>366</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -31164,7 +28282,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B61">
         <v>7.9899999999999999E-2</v>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39349594-DF93-F24B-BEB1-528C92A4251D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3572140-CFF3-B942-9DE1-42EEC952A7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="780" windowWidth="26480" windowHeight="20020" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="26480" windowHeight="20020" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="431">
   <si>
     <t>Team</t>
   </si>
@@ -1335,6 +1335,9 @@
   </si>
   <si>
     <t>03/11/2026</t>
+  </si>
+  <si>
+    <t>03/12/2026</t>
   </si>
 </sst>
 </file>
@@ -1501,28 +1504,28 @@
             <v>1</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Miami (OH)</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D2" t="str">
-            <v>Umass</v>
+            <v>George Washington</v>
           </cell>
           <cell r="E2">
-            <v>9.6440480102351742</v>
+            <v>9.0805766650700406</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.54092049610243209</v>
+            <v>0.56406594172665581</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>3.2666401650097647E-2</v>
+            <v>7.6853161478161125E-2</v>
           </cell>
           <cell r="J2">
-            <v>0.40106307360420351</v>
+            <v>0.43635340476220003</v>
           </cell>
           <cell r="K2">
             <v>0</v>
@@ -1533,28 +1536,28 @@
             <v>2</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Toledo</v>
+            <v>Dayton</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Bowling Green</v>
+            <v>St. Bonaventure</v>
           </cell>
           <cell r="E3">
-            <v>2.466006613885622</v>
+            <v>7.9192002583351826</v>
           </cell>
           <cell r="F3" t="b">
             <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.53650217028484337</v>
+            <v>0.52290663918076241</v>
           </cell>
           <cell r="H3">
             <v>0</v>
           </cell>
           <cell r="I3">
-            <v>2.4231415998337391E-2</v>
+            <v>-1.7236888367262451E-3</v>
           </cell>
           <cell r="J3">
-            <v>0.1663549809744056</v>
+            <v>0.30660460921342519</v>
           </cell>
           <cell r="K3">
             <v>0</v>
@@ -1565,28 +1568,28 @@
             <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Akron</v>
+            <v>VCU</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Buffalo</v>
+            <v>Duquesne</v>
           </cell>
           <cell r="E4">
-            <v>18.293854047872539</v>
+            <v>11.166254009998839</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.59997344698184496</v>
+            <v>0.55369703862163899</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.14540385332897679</v>
+            <v>5.7057982823129023E-2</v>
           </cell>
           <cell r="J4">
-            <v>0.72744949634122513</v>
+            <v>0.47475370428699287</v>
           </cell>
           <cell r="K4">
             <v>0</v>
@@ -1597,28 +1600,28 @@
             <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Kent State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D5" t="str">
-            <v>Ohio</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="E5">
-            <v>7.3494976863221746</v>
+            <v>15.73344652849749</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.59506494660903186</v>
+            <v>0.57281242840487234</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>0.1360330798899699</v>
+            <v>9.3550999682029068E-2</v>
           </cell>
           <cell r="J5">
-            <v>0.45488298441217162</v>
+            <v>0.63043332049671086</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1629,28 +1632,28 @@
             <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Fordham</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D6" t="str">
-            <v>George Washington</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="E6">
-            <v>-3.4268515086737832</v>
+            <v>9.7378847084676998</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.56388311499783716</v>
+            <v>0.53083451979601748</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>7.6504128632234658E-2</v>
+            <v>1.341135597421522E-2</v>
           </cell>
           <cell r="J6">
-            <v>4.3434474836319237E-2</v>
+            <v>0.38100338281320922</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1661,28 +1664,28 @@
             <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>George Mason</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D7" t="str">
-            <v>St. Bonaventure</v>
+            <v>Purdue</v>
           </cell>
           <cell r="E7">
-            <v>5.8092212409012438</v>
+            <v>-1.745415723067971</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.55737860521784821</v>
+            <v>0.55603007828005568</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>6.4086428143164786E-2</v>
+            <v>6.1511967625560882E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.32128490555613298</v>
+            <v>7.8423778572120351E-2</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1693,28 +1696,28 @@
             <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Duquesne</v>
+            <v>Louisiana Tech</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Rhode Island</v>
+            <v>Missouri State</v>
           </cell>
           <cell r="E8">
-            <v>6.0066904778971582</v>
+            <v>3.1501192436748431</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.59886800438278553</v>
+            <v>0.54107107560517276</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0.1432934629125906</v>
+            <v>3.2953871609875278E-2</v>
           </cell>
           <cell r="J8">
-            <v>0.42365189800711361</v>
+            <v>0.19903920029703731</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1725,31 +1728,31 @@
             <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Davidson</v>
+            <v>Florida</v>
           </cell>
           <cell r="D9" t="str">
-            <v>Loyola Chicago</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="E9">
-            <v>14.669605825431679</v>
+            <v>12.721469211896</v>
           </cell>
           <cell r="F9" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.66188969994400637</v>
+            <v>0.55373312139582753</v>
           </cell>
           <cell r="H9">
-            <v>8.5987347952965434E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I9">
-            <v>0.26360760898401231</v>
+            <v>5.7126868119307117E-2</v>
           </cell>
           <cell r="J9">
-            <v>0.76503986048856765</v>
+            <v>0.518332563847963</v>
           </cell>
           <cell r="K9">
-            <v>1.6784730320418852</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="10">
@@ -1757,28 +1760,28 @@
             <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Virginia</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D10" t="str">
-            <v>NC State</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="E10">
-            <v>8.3078502633334779</v>
+            <v>1.550264273249496</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.5696529381454235</v>
+            <v>0.50125328192558738</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>8.7519245550354063E-2</v>
+            <v>-4.3061916323878617E-2</v>
           </cell>
           <cell r="J10">
-            <v>0.4258892115948269</v>
+            <v>5.280490465141674E-2</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1789,28 +1792,28 @@
             <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Miami</v>
+            <v>Toledo</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Louisville</v>
+            <v>Umass</v>
           </cell>
           <cell r="E11">
-            <v>-1.653069067470895</v>
+            <v>5.2638557338713943</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.52110742749402328</v>
+            <v>0.55625895869178854</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>-5.1585475114100388E-3</v>
+            <v>6.1948921138869073E-2</v>
           </cell>
           <cell r="J11">
-            <v>2.5770789969586372E-3</v>
+            <v>0.3016690356213893</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1821,28 +1824,28 @@
             <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>St. John's</v>
+            <v>Akron</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Providence</v>
+            <v>Kent State</v>
           </cell>
           <cell r="E12">
-            <v>11.113965511448241</v>
+            <v>8.5781163171341159</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.51530479399617379</v>
+            <v>0.53928487633708933</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>-1.6236302370940921E-2</v>
+            <v>2.9543854825352382E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.38762291209784461</v>
+            <v>0.36485986617792998</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1853,28 +1856,28 @@
             <v>12</v>
           </cell>
           <cell r="C13" t="str">
+            <v>St. John'S</v>
+          </cell>
+          <cell r="D13" t="str">
             <v>Seton Hall</v>
           </cell>
-          <cell r="D13" t="str">
-            <v>Creighton</v>
-          </cell>
           <cell r="E13">
-            <v>5.175740826606134</v>
+            <v>10.36855199557233</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.55408295679600794</v>
+            <v>0.58141961548989163</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>5.7794735701469757E-2</v>
+            <v>0.10998290229888411</v>
           </cell>
           <cell r="J13">
-            <v>0.29379909124133158</v>
+            <v>0.51264169102342805</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1885,28 +1888,28 @@
             <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Ohio State</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Iowa</v>
+            <v>Miami</v>
           </cell>
           <cell r="E14">
-            <v>2.1498040744598441</v>
+            <v>6.1417083046904253</v>
           </cell>
           <cell r="F14" t="b">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.52864443456849863</v>
+            <v>0.55324208206947656</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>9.230284176224679E-3</v>
+            <v>5.6189429405364422E-2</v>
           </cell>
           <cell r="J14">
-            <v>0.1374921095189576</v>
+            <v>0.32194962549615419</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -1917,28 +1920,28 @@
             <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Wisconsin</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D15" t="str">
-            <v>Washington</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="E15">
-            <v>9.8269801687062213</v>
+            <v>8.1430940958016542</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.57004243243133568</v>
+            <v>0.61129835798834531</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>8.8262825550731838E-2</v>
+            <v>0.1670241379777502</v>
           </cell>
           <cell r="J15">
-            <v>0.47170508060701832</v>
+            <v>0.5162659846229557</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -1949,28 +1952,28 @@
             <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Missouri</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D16" t="str">
-            <v>Kentucky</v>
+            <v>Nevada</v>
           </cell>
           <cell r="E16">
-            <v>-1.146439175535074</v>
+            <v>9.5599619631437314</v>
           </cell>
           <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.54611331823840359</v>
+            <v>0.57556239493808958</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>4.2579971182406917E-2</v>
+            <v>9.8800935790898325E-2</v>
           </cell>
           <cell r="J16">
-            <v>7.3745566648167671E-2</v>
+            <v>0.47620157555302872</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -1981,28 +1984,28 @@
             <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Tennessee</v>
+            <v>Alabama A&amp;M</v>
           </cell>
           <cell r="D17" t="str">
-            <v>Auburn</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="E17">
-            <v>8.4905386620125256</v>
+            <v>0.81106282232327365</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.57413387792013393</v>
+            <v>0.55742404687951042</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>9.6073766938437499E-2</v>
+            <v>6.4173180406338126E-2</v>
           </cell>
           <cell r="J17">
-            <v>0.44144638711713352</v>
+            <v>0.16362477907810821</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2013,28 +2016,28 @@
             <v>17</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Texas Tech</v>
+            <v>Howard</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Iowa State</v>
+            <v>South Carolina State</v>
           </cell>
           <cell r="E18">
-            <v>-2.9845795031237792</v>
+            <v>15.36825580567713</v>
           </cell>
           <cell r="F18" t="b">
             <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0.55011970265521237</v>
+            <v>0.50903861411179752</v>
           </cell>
           <cell r="H18">
             <v>0</v>
           </cell>
           <cell r="I18">
-            <v>5.0228523250860017E-2</v>
+            <v>-2.8199009422931961E-2</v>
           </cell>
           <cell r="J18">
-            <v>2.4367709420224652E-2</v>
+            <v>0.49778117835928459</v>
           </cell>
           <cell r="K18">
             <v>0</v>
@@ -2045,28 +2048,28 @@
             <v>18</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Arizona</v>
+            <v>George Washington</v>
           </cell>
           <cell r="D19" t="str">
-            <v>UCF</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="E19">
-            <v>19.23665813839775</v>
+            <v>-3.3025895141847661</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.54940737614280311</v>
+            <v>0.57919642025240214</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>4.8868627181715092E-2</v>
+            <v>0.1057386204818587</v>
           </cell>
           <cell r="J19">
-            <v>0.66277687393145923</v>
+            <v>8.4641304381282811E-2</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2077,28 +2080,28 @@
             <v>19</v>
           </cell>
           <cell r="C20" t="str">
-            <v>Utah State</v>
+            <v>St. Bonaventure</v>
           </cell>
           <cell r="D20" t="str">
-            <v>UNLV</v>
+            <v>Dayton</v>
           </cell>
           <cell r="E20">
-            <v>9.8836640534565952</v>
+            <v>-3.3804737803700688</v>
           </cell>
           <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0.57126084170358116</v>
+            <v>0.58948499314896396</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>9.0588879615927764E-2</v>
+            <v>0.125380441466204</v>
           </cell>
           <cell r="J20">
-            <v>0.47610121634844738</v>
+            <v>0.10727961854544581</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2109,28 +2112,28 @@
             <v>20</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Louisiana Tech</v>
+            <v>Duquesne</v>
           </cell>
           <cell r="D21" t="str">
-            <v>Middle Tennessee</v>
+            <v>VCU</v>
           </cell>
           <cell r="E21">
-            <v>0.55009423841244076</v>
+            <v>-6.4040274345806596</v>
           </cell>
           <cell r="F21" t="b">
             <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0.55097730454227634</v>
+            <v>0.5644448313537479</v>
           </cell>
           <cell r="H21">
             <v>0</v>
           </cell>
           <cell r="I21">
-            <v>5.1865763217073042E-2</v>
+            <v>7.7576496220791546E-2</v>
           </cell>
           <cell r="J21">
-            <v>0.13980304188158671</v>
+            <v>5.0856318615345342E-2</v>
           </cell>
           <cell r="K21">
             <v>0</v>
@@ -2141,28 +2144,28 @@
             <v>21</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Western Kentucky</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="D22" t="str">
-            <v>Kennesaw State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="E22">
-            <v>3.4024260616289901</v>
+            <v>-10.878489744531951</v>
           </cell>
           <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0.54732335435947865</v>
+            <v>0.54036146066461055</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>4.4890040140822929E-2</v>
+            <v>3.1599152177892893E-2</v>
           </cell>
           <cell r="J22">
-            <v>0.22192745583176249</v>
+            <v>0.25139475433000569</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2173,28 +2176,28 @@
             <v>22</v>
           </cell>
           <cell r="C23" t="str">
-            <v>UT Arlington</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="D23" t="str">
-            <v>Southern Utah</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E23">
-            <v>8.4663485338859594</v>
+            <v>-5.7535302614113499</v>
           </cell>
           <cell r="F23" t="b">
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0.57354108440508789</v>
+            <v>0.56814536519259196</v>
           </cell>
           <cell r="H23">
             <v>0</v>
           </cell>
           <cell r="I23">
-            <v>9.4942070227895137E-2</v>
+            <v>8.4641151731311925E-2</v>
           </cell>
           <cell r="J23">
-            <v>0.43939333422217081</v>
+            <v>2.098113949660585E-2</v>
           </cell>
           <cell r="K23">
             <v>0</v>
@@ -2205,28 +2208,28 @@
             <v>23</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Texas Southern</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D24" t="str">
-            <v>Alabama A&amp;M</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="E24">
-            <v>3.1269648809618138</v>
+            <v>6.682599948396966</v>
           </cell>
           <cell r="F24" t="b">
             <v>0</v>
           </cell>
           <cell r="G24">
-            <v>0.60177158148862575</v>
+            <v>0.5665755991492083</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>0.1488366555691947</v>
+            <v>8.1644325648488669E-2</v>
           </cell>
           <cell r="J24">
-            <v>0.34277357102266748</v>
+            <v>0.36962984797906079</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2237,31 +2240,31 @@
             <v>24</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Southern</v>
+            <v>Missouri State</v>
           </cell>
           <cell r="D25" t="str">
-            <v>Arkansas-Pine Bluff</v>
+            <v>Louisiana Tech</v>
           </cell>
           <cell r="E25">
-            <v>7.6186047152767644</v>
+            <v>3.1421879785812341</v>
           </cell>
           <cell r="F25" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G25">
-            <v>0.56500169596568006</v>
+            <v>0.61414418851700514</v>
           </cell>
           <cell r="H25">
-            <v>0</v>
+            <v>4.5881118354284427E-2</v>
           </cell>
           <cell r="I25">
-            <v>7.8639601389025593E-2</v>
+            <v>0.17245708716882799</v>
           </cell>
           <cell r="J25">
-            <v>0.39453388156286051</v>
+            <v>0.37265385549244079</v>
           </cell>
           <cell r="K25">
-            <v>0</v>
+            <v>0.89559943027563205</v>
           </cell>
         </row>
         <row r="26">
@@ -2269,28 +2272,28 @@
             <v>25</v>
           </cell>
           <cell r="C26" t="str">
-            <v>Norfolk State</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D26" t="str">
-            <v>South Carolina State</v>
+            <v>Florida</v>
           </cell>
           <cell r="E26">
-            <v>9.4891467738595612</v>
+            <v>-7.1810229062204636</v>
           </cell>
           <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0.56181467279022113</v>
+            <v>0.58216534167225553</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>7.2555284417694876E-2</v>
+            <v>0.111406561374306</v>
           </cell>
           <cell r="J26">
-            <v>0.44344796320776858</v>
+            <v>3.2684541054098459E-2</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2301,31 +2304,31 @@
             <v>26</v>
           </cell>
           <cell r="C27" t="str">
-            <v>North Carolina Central</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D27" t="str">
-            <v>Maryland-Eastern Shore</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="E27">
-            <v>6.1257329326571277</v>
+            <v>3.1650827197892308</v>
           </cell>
           <cell r="F27" t="b">
             <v>1</v>
           </cell>
           <cell r="G27">
-            <v>0.61375075206838403</v>
+            <v>0.61469140127671673</v>
           </cell>
           <cell r="H27">
-            <v>4.5550631737442553E-2</v>
+            <v>4.6340777072442073E-2</v>
           </cell>
           <cell r="I27">
-            <v>0.1717059812214605</v>
+            <v>0.17350176607373199</v>
           </cell>
           <cell r="J27">
-            <v>0.46129250554468809</v>
+            <v>0.37465373235659188</v>
           </cell>
           <cell r="K27">
-            <v>0.88914833151487871</v>
+            <v>0.90457196845406929</v>
           </cell>
         </row>
         <row r="28">
@@ -2336,25 +2339,25 @@
             <v>Umass</v>
           </cell>
           <cell r="D28" t="str">
-            <v>Miami (OH)</v>
+            <v>Toledo</v>
           </cell>
           <cell r="E28">
-            <v>-4.7323598506735527</v>
+            <v>-2.3075124067073789</v>
           </cell>
           <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0.58091214248835032</v>
+            <v>0.5172610221683327</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>0.1090140902050325</v>
+            <v>-1.250168495136483E-2</v>
           </cell>
           <cell r="J28">
-            <v>4.2928959963025308E-2</v>
+            <v>3.2821261488724378E-2</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2365,28 +2368,28 @@
             <v>28</v>
           </cell>
           <cell r="C29" t="str">
-            <v>Bowling Green</v>
+            <v>Kent State</v>
           </cell>
           <cell r="D29" t="str">
-            <v>Toledo</v>
+            <v>Akron</v>
           </cell>
           <cell r="E29">
-            <v>2.3609305101229721</v>
+            <v>-3.5228945005294729</v>
           </cell>
           <cell r="F29" t="b">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0.58318885859493508</v>
+            <v>0.58602016099304166</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>0.11336054822669429</v>
+            <v>0.1187657618958069</v>
           </cell>
           <cell r="J29">
-            <v>0.27455551501838382</v>
+            <v>9.4235374230409175E-2</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2397,28 +2400,28 @@
             <v>29</v>
           </cell>
           <cell r="C30" t="str">
-            <v>Buffalo</v>
+            <v>Seton Hall</v>
           </cell>
           <cell r="D30" t="str">
-            <v>Akron</v>
+            <v>St. John'S</v>
           </cell>
           <cell r="E30">
-            <v>-13.243788676914111</v>
+            <v>-5.6305511978857661</v>
           </cell>
           <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0.50638807258443608</v>
+            <v>0.53410404460273708</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>-3.3259134156985608E-2</v>
+            <v>1.9653176059770849E-2</v>
           </cell>
           <cell r="J30">
-            <v>0.40320040946425051</v>
+            <v>9.9131431803276382E-2</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2429,28 +2432,28 @@
             <v>30</v>
           </cell>
           <cell r="C31" t="str">
-            <v>Ohio</v>
+            <v>Miami</v>
           </cell>
           <cell r="D31" t="str">
-            <v>Kent State</v>
+            <v>Virginia</v>
           </cell>
           <cell r="E31">
-            <v>-2.738700766425429</v>
+            <v>-1.0562179673746921</v>
           </cell>
           <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0.5189749931943165</v>
+            <v>0.57298792898271877</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>-9.2295584472139036E-3</v>
+            <v>9.3886046239735843E-2</v>
           </cell>
           <cell r="J31">
-            <v>4.2567429414205223E-2</v>
+            <v>0.14151041668232769</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2461,28 +2464,28 @@
             <v>31</v>
           </cell>
           <cell r="C32" t="str">
-            <v>George Washington</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D32" t="str">
-            <v>Fordham</v>
+            <v>Arizona</v>
           </cell>
           <cell r="E32">
-            <v>8.7090029492375933</v>
+            <v>-1.879890319738613</v>
           </cell>
           <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0.56722465031475355</v>
+            <v>0.54032671759455519</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>8.2883423328165895E-2</v>
+            <v>3.1532824498696321E-2</v>
           </cell>
           <cell r="J32">
-            <v>0.43238860568207088</v>
+            <v>3.6272197522773657E-2</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2493,28 +2496,28 @@
             <v>32</v>
           </cell>
           <cell r="C33" t="str">
-            <v>St. Bonaventure</v>
+            <v>Nevada</v>
           </cell>
           <cell r="D33" t="str">
-            <v>George Mason</v>
+            <v>Utah State</v>
           </cell>
           <cell r="E33">
-            <v>-1.7749892366537861</v>
+            <v>-3.5906886038474162</v>
           </cell>
           <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0.54292805325529159</v>
+            <v>0.57214269981132204</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>3.6499010760102153E-2</v>
+            <v>9.2272426912523908E-2</v>
           </cell>
           <cell r="J33">
-            <v>4.5899620263135647E-2</v>
+            <v>5.8222267933530913E-2</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -2525,28 +2528,28 @@
             <v>33</v>
           </cell>
           <cell r="C34" t="str">
-            <v>Rhode Island</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D34" t="str">
-            <v>Duquesne</v>
+            <v>Alabama A&amp;M</v>
           </cell>
           <cell r="E34">
-            <v>-1.1394727795895241</v>
+            <v>3.6577675938421161</v>
           </cell>
           <cell r="F34" t="b">
             <v>0</v>
           </cell>
           <cell r="G34">
-            <v>0.52144595361541635</v>
+            <v>0.55363890466104715</v>
           </cell>
           <cell r="H34">
             <v>0</v>
           </cell>
           <cell r="I34">
-            <v>-4.5122703705687273E-3</v>
+            <v>5.6946999807453658E-2</v>
           </cell>
           <cell r="J34">
-            <v>1.4738098234328921E-2</v>
+            <v>0.24501522613721469</v>
           </cell>
           <cell r="K34">
             <v>0</v>
@@ -2557,28 +2560,28 @@
             <v>34</v>
           </cell>
           <cell r="C35" t="str">
-            <v>Loyola Chicago</v>
+            <v>South Carolina State</v>
           </cell>
           <cell r="D35" t="str">
-            <v>Davidson</v>
+            <v>Howard</v>
           </cell>
           <cell r="E35">
-            <v>-6.7962509172065619</v>
+            <v>-11.39304466171944</v>
           </cell>
           <cell r="F35" t="b">
             <v>0</v>
           </cell>
           <cell r="G35">
-            <v>0.50738626648811402</v>
+            <v>0.58917944355767848</v>
           </cell>
           <cell r="H35">
             <v>0</v>
           </cell>
           <cell r="I35">
-            <v>-3.1353491249964123E-2</v>
+            <v>0.1247971195192045</v>
           </cell>
           <cell r="J35">
-            <v>0.2349421208471634</v>
+            <v>0.15057558695248269</v>
           </cell>
           <cell r="K35">
             <v>0</v>
@@ -2588,29 +2591,23 @@
           <cell r="B36">
             <v>35</v>
           </cell>
-          <cell r="C36" t="str">
-            <v>NC State</v>
-          </cell>
-          <cell r="D36" t="str">
-            <v>Virginia</v>
-          </cell>
           <cell r="E36">
-            <v>-1.840253399084091</v>
-          </cell>
-          <cell r="F36" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F36">
             <v>0</v>
           </cell>
           <cell r="G36">
-            <v>0.59046222964154416</v>
+            <v>0</v>
           </cell>
           <cell r="H36">
             <v>0</v>
           </cell>
           <cell r="I36">
-            <v>0.12724607477022079</v>
+            <v>0</v>
           </cell>
           <cell r="J36">
-            <v>0.15894431431892711</v>
+            <v>0</v>
           </cell>
           <cell r="K36">
             <v>0</v>
@@ -2620,61 +2617,49 @@
           <cell r="B37">
             <v>36</v>
           </cell>
-          <cell r="C37" t="str">
-            <v>Louisville</v>
-          </cell>
-          <cell r="D37" t="str">
-            <v>Miami</v>
-          </cell>
           <cell r="E37">
-            <v>7.2253929834058637</v>
-          </cell>
-          <cell r="F37" t="b">
-            <v>1</v>
+            <v>0</v>
+          </cell>
+          <cell r="F37">
+            <v>0</v>
           </cell>
           <cell r="G37">
-            <v>0.61446196800199138</v>
+            <v>0</v>
           </cell>
           <cell r="H37">
-            <v>4.6148053121672909E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I37">
-            <v>0.17306375709471089</v>
+            <v>0</v>
           </cell>
           <cell r="J37">
-            <v>0.49643981009159899</v>
+            <v>0</v>
           </cell>
           <cell r="K37">
-            <v>0.90080999693505515</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38">
             <v>37</v>
           </cell>
-          <cell r="C38" t="str">
-            <v>Providence</v>
-          </cell>
-          <cell r="D38" t="str">
-            <v>St. John's</v>
-          </cell>
           <cell r="E38">
-            <v>-6.7179433361797418</v>
-          </cell>
-          <cell r="F38" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F38">
             <v>0</v>
           </cell>
           <cell r="G38">
-            <v>0.59343052707215405</v>
+            <v>0</v>
           </cell>
           <cell r="H38">
             <v>0</v>
           </cell>
           <cell r="I38">
-            <v>0.13291282441047589</v>
+            <v>0</v>
           </cell>
           <cell r="J38">
-            <v>9.8290256539185772E-3</v>
+            <v>0</v>
           </cell>
           <cell r="K38">
             <v>0</v>
@@ -2684,29 +2669,23 @@
           <cell r="B39">
             <v>38</v>
           </cell>
-          <cell r="C39" t="str">
-            <v>Creighton</v>
-          </cell>
-          <cell r="D39" t="str">
-            <v>Seton Hall</v>
-          </cell>
           <cell r="E39">
-            <v>-1.376188566601076</v>
-          </cell>
-          <cell r="F39" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F39">
             <v>0</v>
           </cell>
           <cell r="G39">
-            <v>0.54041854367466291</v>
+            <v>0</v>
           </cell>
           <cell r="H39">
             <v>0</v>
           </cell>
           <cell r="I39">
-            <v>3.1708128833447417E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J39">
-            <v>5.2671602291088027E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K39">
             <v>0</v>
@@ -2716,29 +2695,23 @@
           <cell r="B40">
             <v>39</v>
           </cell>
-          <cell r="C40" t="str">
-            <v>Iowa</v>
-          </cell>
-          <cell r="D40" t="str">
-            <v>Ohio State</v>
-          </cell>
           <cell r="E40">
-            <v>2.001748280687123</v>
-          </cell>
-          <cell r="F40" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F40">
             <v>0</v>
           </cell>
           <cell r="G40">
-            <v>0.57440851959936123</v>
+            <v>0</v>
           </cell>
           <cell r="H40">
             <v>0</v>
           </cell>
           <cell r="I40">
-            <v>9.659808287150784E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J40">
-            <v>0.2422149549565433</v>
+            <v>0</v>
           </cell>
           <cell r="K40">
             <v>0</v>
@@ -2748,29 +2721,23 @@
           <cell r="B41">
             <v>40</v>
           </cell>
-          <cell r="C41" t="str">
-            <v>Washington</v>
-          </cell>
-          <cell r="D41" t="str">
-            <v>Wisconsin</v>
-          </cell>
           <cell r="E41">
-            <v>-4.4627736897012369</v>
-          </cell>
-          <cell r="F41" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F41">
             <v>0</v>
           </cell>
           <cell r="G41">
-            <v>0.56299878449898999</v>
+            <v>0</v>
           </cell>
           <cell r="H41">
             <v>0</v>
           </cell>
           <cell r="I41">
-            <v>7.4815861316253618E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J41">
-            <v>8.0083923561810044E-3</v>
+            <v>0</v>
           </cell>
           <cell r="K41">
             <v>0</v>
@@ -2780,29 +2747,23 @@
           <cell r="B42">
             <v>41</v>
           </cell>
-          <cell r="C42" t="str">
-            <v>Kentucky</v>
-          </cell>
-          <cell r="D42" t="str">
-            <v>Missouri</v>
-          </cell>
           <cell r="E42">
-            <v>7.5741710473550912</v>
-          </cell>
-          <cell r="F42" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F42">
             <v>0</v>
           </cell>
           <cell r="G42">
-            <v>0.61078807181947214</v>
+            <v>0</v>
           </cell>
           <cell r="H42">
             <v>0</v>
           </cell>
           <cell r="I42">
-            <v>0.16604995529171959</v>
+            <v>0</v>
           </cell>
           <cell r="J42">
-            <v>0.49822479248117479</v>
+            <v>0</v>
           </cell>
           <cell r="K42">
             <v>0</v>
@@ -2812,29 +2773,23 @@
           <cell r="B43">
             <v>42</v>
           </cell>
-          <cell r="C43" t="str">
-            <v>Auburn</v>
-          </cell>
-          <cell r="D43" t="str">
-            <v>Tennessee</v>
-          </cell>
           <cell r="E43">
-            <v>-4.5521786042897094</v>
-          </cell>
-          <cell r="F43" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F43">
             <v>0</v>
           </cell>
           <cell r="G43">
-            <v>0.5236190618476203</v>
+            <v>0</v>
           </cell>
           <cell r="H43">
             <v>0</v>
           </cell>
           <cell r="I43">
-            <v>-3.6360919999756097E-4</v>
+            <v>0</v>
           </cell>
           <cell r="J43">
-            <v>8.9660662109924627E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K43">
             <v>0</v>
@@ -2844,29 +2799,23 @@
           <cell r="B44">
             <v>43</v>
           </cell>
-          <cell r="C44" t="str">
-            <v>Iowa State</v>
-          </cell>
-          <cell r="D44" t="str">
-            <v>Texas Tech</v>
-          </cell>
           <cell r="E44">
-            <v>6.2358828476634516</v>
-          </cell>
-          <cell r="F44" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F44">
             <v>0</v>
           </cell>
           <cell r="G44">
-            <v>0.53078475453736063</v>
+            <v>0</v>
           </cell>
           <cell r="H44">
             <v>0</v>
           </cell>
           <cell r="I44">
-            <v>1.331634957132488E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J44">
-            <v>0.27230659313486272</v>
+            <v>0</v>
           </cell>
           <cell r="K44">
             <v>0</v>
@@ -2876,29 +2825,23 @@
           <cell r="B45">
             <v>44</v>
           </cell>
-          <cell r="C45" t="str">
-            <v>UCF</v>
-          </cell>
-          <cell r="D45" t="str">
-            <v>Arizona</v>
-          </cell>
           <cell r="E45">
-            <v>-15.244872435267879</v>
-          </cell>
-          <cell r="F45" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F45">
             <v>0</v>
           </cell>
           <cell r="G45">
-            <v>0.54367455453249747</v>
+            <v>0</v>
           </cell>
           <cell r="H45">
             <v>0</v>
           </cell>
           <cell r="I45">
-            <v>3.7924149562040647E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J45">
-            <v>0.37943377114551913</v>
+            <v>0</v>
           </cell>
           <cell r="K45">
             <v>0</v>
@@ -2908,29 +2851,23 @@
           <cell r="B46">
             <v>45</v>
           </cell>
-          <cell r="C46" t="str">
-            <v>UNLV</v>
-          </cell>
-          <cell r="D46" t="str">
-            <v>Utah State</v>
-          </cell>
           <cell r="E46">
-            <v>-5.7042635217661566</v>
-          </cell>
-          <cell r="F46" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F46">
             <v>0</v>
           </cell>
           <cell r="G46">
-            <v>0.53227247463879057</v>
+            <v>0</v>
           </cell>
           <cell r="H46">
             <v>0</v>
           </cell>
           <cell r="I46">
-            <v>1.6156542492236581E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J46">
-            <v>0.1058821308422614</v>
+            <v>0</v>
           </cell>
           <cell r="K46">
             <v>0</v>
@@ -2940,29 +2877,23 @@
           <cell r="B47">
             <v>46</v>
           </cell>
-          <cell r="C47" t="str">
-            <v>Middle Tennessee</v>
-          </cell>
-          <cell r="D47" t="str">
-            <v>Louisiana Tech</v>
-          </cell>
           <cell r="E47">
-            <v>5.9029261614359108</v>
-          </cell>
-          <cell r="F47" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F47">
             <v>0</v>
           </cell>
           <cell r="G47">
-            <v>0.60841213235939462</v>
+            <v>0</v>
           </cell>
           <cell r="H47">
             <v>0</v>
           </cell>
           <cell r="I47">
-            <v>0.16151407086793521</v>
+            <v>0</v>
           </cell>
           <cell r="J47">
-            <v>0.44249689878412479</v>
+            <v>0</v>
           </cell>
           <cell r="K47">
             <v>0</v>
@@ -2972,29 +2903,23 @@
           <cell r="B48">
             <v>47</v>
           </cell>
-          <cell r="C48" t="str">
-            <v>Kennesaw State</v>
-          </cell>
-          <cell r="D48" t="str">
-            <v>Western Kentucky</v>
-          </cell>
           <cell r="E48">
-            <v>1.766362723865704</v>
-          </cell>
-          <cell r="F48" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F48">
             <v>0</v>
           </cell>
           <cell r="G48">
-            <v>0.58088094840529991</v>
+            <v>0</v>
           </cell>
           <cell r="H48">
             <v>0</v>
           </cell>
           <cell r="I48">
-            <v>0.1089545378646635</v>
+            <v>0</v>
           </cell>
           <cell r="J48">
-            <v>0.25030132435461783</v>
+            <v>0</v>
           </cell>
           <cell r="K48">
             <v>0</v>
@@ -3004,29 +2929,23 @@
           <cell r="B49">
             <v>48</v>
           </cell>
-          <cell r="C49" t="str">
-            <v>Southern Utah</v>
-          </cell>
-          <cell r="D49" t="str">
-            <v>UT Arlington</v>
-          </cell>
           <cell r="E49">
-            <v>-3.72491610209098</v>
-          </cell>
-          <cell r="F49" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F49">
             <v>0</v>
           </cell>
           <cell r="G49">
-            <v>0.54416912485592184</v>
+            <v>0</v>
           </cell>
           <cell r="H49">
             <v>0</v>
           </cell>
           <cell r="I49">
-            <v>3.8868329270396303E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J49">
-            <v>1.376391444724012E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K49">
             <v>0</v>
@@ -3036,29 +2955,23 @@
           <cell r="B50">
             <v>49</v>
           </cell>
-          <cell r="C50" t="str">
-            <v>Alabama A&amp;M</v>
-          </cell>
-          <cell r="D50" t="str">
-            <v>Texas Southern</v>
-          </cell>
           <cell r="E50">
-            <v>3.312445258588065</v>
-          </cell>
-          <cell r="F50" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F50">
             <v>0</v>
           </cell>
           <cell r="G50">
-            <v>0.55745815847845215</v>
+            <v>0</v>
           </cell>
           <cell r="H50">
             <v>0</v>
           </cell>
           <cell r="I50">
-            <v>6.4238302549772364E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J50">
-            <v>0.24318077164230489</v>
+            <v>0</v>
           </cell>
           <cell r="K50">
             <v>0</v>
@@ -3068,29 +2981,23 @@
           <cell r="B51">
             <v>50</v>
           </cell>
-          <cell r="C51" t="str">
-            <v>Arkansas-Pine Bluff</v>
-          </cell>
-          <cell r="D51" t="str">
-            <v>Southern</v>
-          </cell>
           <cell r="E51">
-            <v>-3.0183006630540841</v>
-          </cell>
-          <cell r="F51" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F51">
             <v>0</v>
           </cell>
           <cell r="G51">
-            <v>0.5492854368028609</v>
+            <v>0</v>
           </cell>
           <cell r="H51">
             <v>0</v>
           </cell>
           <cell r="I51">
-            <v>4.8635833896370877E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J51">
-            <v>2.127206920851377E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K51">
             <v>0</v>
@@ -3100,29 +3007,23 @@
           <cell r="B52">
             <v>51</v>
           </cell>
-          <cell r="C52" t="str">
-            <v>South Carolina State</v>
-          </cell>
-          <cell r="D52" t="str">
-            <v>Norfolk State</v>
-          </cell>
           <cell r="E52">
-            <v>-4.8464088506426242</v>
-          </cell>
-          <cell r="F52" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F52">
             <v>0</v>
           </cell>
           <cell r="G52">
-            <v>0.55353571050516193</v>
+            <v>0</v>
           </cell>
           <cell r="H52">
             <v>0</v>
           </cell>
           <cell r="I52">
-            <v>5.674999278258186E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J52">
-            <v>2.7212380511523752E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K52">
             <v>0</v>
@@ -3132,29 +3033,23 @@
           <cell r="B53">
             <v>52</v>
           </cell>
-          <cell r="C53" t="str">
-            <v>Maryland-Eastern Shore</v>
-          </cell>
-          <cell r="D53" t="str">
-            <v>North Carolina Central</v>
-          </cell>
           <cell r="E53">
-            <v>0.43458051285308641</v>
-          </cell>
-          <cell r="F53" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F53">
             <v>0</v>
           </cell>
           <cell r="G53">
-            <v>0.54811934702490117</v>
+            <v>0</v>
           </cell>
           <cell r="H53">
             <v>0</v>
           </cell>
           <cell r="I53">
-            <v>4.6409662502084108E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J53">
-            <v>0.1292446640291556</v>
+            <v>0</v>
           </cell>
           <cell r="K53">
             <v>0</v>
@@ -8804,73 +8699,73 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>Miami (OH)</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Umass</v>
+            <v>George Washington</v>
           </cell>
           <cell r="D2">
-            <v>8.0718958761759509</v>
+            <v>12.924462689730786</v>
           </cell>
           <cell r="E2">
-            <v>96.34903131164954</v>
+            <v>96.65371999791742</v>
           </cell>
           <cell r="F2">
-            <v>97.622654172658116</v>
+            <v>94.854733271656428</v>
           </cell>
           <cell r="G2">
-            <v>0.61308516638465882</v>
+            <v>0.60122699386503065</v>
           </cell>
           <cell r="H2">
-            <v>72.061333333333337</v>
+            <v>71.082666666666668</v>
           </cell>
           <cell r="I2">
-            <v>59.1</v>
+            <v>59.766666666666666</v>
           </cell>
           <cell r="J2">
-            <v>23.7</v>
+            <v>20.566666666666666</v>
           </cell>
           <cell r="K2">
-            <v>7.9666666666666668</v>
+            <v>10.133333333333333</v>
           </cell>
           <cell r="L2">
-            <v>10.5</v>
+            <v>12.4</v>
           </cell>
           <cell r="M2">
             <v>0</v>
           </cell>
           <cell r="N2">
-            <v>1.9653328411701338</v>
+            <v>8.1181174856323501</v>
           </cell>
           <cell r="O2">
-            <v>98.035528511139475</v>
+            <v>99.423073027448609</v>
           </cell>
           <cell r="P2">
-            <v>92.56634666376938</v>
+            <v>102.88385819155521</v>
           </cell>
           <cell r="Q2">
-            <v>0.53268318397469694</v>
+            <v>0.55111228813559321</v>
           </cell>
           <cell r="R2">
-            <v>72.318709677419363</v>
+            <v>70.331612903225803</v>
           </cell>
           <cell r="S2">
-            <v>61.193548387096776</v>
+            <v>60.903225806451616</v>
           </cell>
           <cell r="T2">
-            <v>22.64516129032258</v>
+            <v>21.35483870967742</v>
           </cell>
           <cell r="U2">
-            <v>11.935483870967742</v>
+            <v>12.741935483870968</v>
           </cell>
           <cell r="V2">
-            <v>13.096774193548388</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="W2">
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-8</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="3">
@@ -8878,73 +8773,73 @@
             <v>2</v>
           </cell>
           <cell r="B3" t="str">
-            <v>Toledo</v>
+            <v>Dayton</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Bowling Green</v>
+            <v>St. Bonaventure</v>
           </cell>
           <cell r="D3">
-            <v>4.1368006701786264</v>
+            <v>7.2080821342928445</v>
           </cell>
           <cell r="E3">
-            <v>100.01830473218929</v>
+            <v>95.080309824704429</v>
           </cell>
           <cell r="F3">
-            <v>101.61078845085268</v>
+            <v>92.716319767963711</v>
           </cell>
           <cell r="G3">
-            <v>0.54476439790575915</v>
+            <v>0.52316486161251508</v>
           </cell>
           <cell r="H3">
-            <v>69.429677419354846</v>
+            <v>68.127741935483868</v>
           </cell>
           <cell r="I3">
-            <v>61.612903225806448</v>
+            <v>53.612903225806448</v>
           </cell>
           <cell r="J3">
-            <v>18.64516129032258</v>
+            <v>25.29032258064516</v>
           </cell>
           <cell r="K3">
-            <v>10.516129032258064</v>
+            <v>8.7096774193548381</v>
           </cell>
           <cell r="L3">
-            <v>10.129032258064516</v>
+            <v>12.096774193548388</v>
           </cell>
           <cell r="M3">
             <v>0</v>
           </cell>
           <cell r="N3">
-            <v>5.2719145340748046</v>
+            <v>3.6587011371081828</v>
           </cell>
           <cell r="O3">
-            <v>97.904002363018748</v>
+            <v>100.06821327722717</v>
           </cell>
           <cell r="P3">
-            <v>98.018930609306281</v>
+            <v>98.203101803703447</v>
           </cell>
           <cell r="Q3">
-            <v>0.5335463258785943</v>
+            <v>0.52207505518763797</v>
           </cell>
           <cell r="R3">
-            <v>71.930322580645168</v>
+            <v>67.670666666666662</v>
           </cell>
           <cell r="S3">
-            <v>60.58064516129032</v>
+            <v>60.4</v>
           </cell>
           <cell r="T3">
-            <v>22.93548387096774</v>
+            <v>17.433333333333334</v>
           </cell>
           <cell r="U3">
-            <v>10.258064516129032</v>
+            <v>11.866666666666667</v>
           </cell>
           <cell r="V3">
-            <v>11.516129032258064</v>
+            <v>11.466666666666667</v>
           </cell>
           <cell r="W3">
             <v>0</v>
           </cell>
           <cell r="X3">
-            <v>-1</v>
+            <v>-7</v>
           </cell>
         </row>
         <row r="4">
@@ -8952,73 +8847,73 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>Akron</v>
+            <v>VCU</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Buffalo</v>
+            <v>Duquesne</v>
           </cell>
           <cell r="D4">
-            <v>10.49945141256813</v>
+            <v>10.046934010674722</v>
           </cell>
           <cell r="E4">
-            <v>99.8801284338209</v>
+            <v>100.11649510419282</v>
           </cell>
           <cell r="F4">
-            <v>94.797305672709399</v>
+            <v>100.40585231866712</v>
           </cell>
           <cell r="G4">
-            <v>0.59409687184661952</v>
+            <v>0.54296008869179602</v>
           </cell>
           <cell r="H4">
-            <v>71.441290322580642</v>
+            <v>69.00645161290322</v>
           </cell>
           <cell r="I4">
-            <v>63.935483870967744</v>
+            <v>58.193548387096776</v>
           </cell>
           <cell r="J4">
-            <v>17.64516129032258</v>
+            <v>25.967741935483872</v>
           </cell>
           <cell r="K4">
-            <v>11.35483870967742</v>
+            <v>11.419354838709678</v>
           </cell>
           <cell r="L4">
-            <v>11.096774193548388</v>
+            <v>10.806451612903226</v>
           </cell>
           <cell r="M4">
             <v>0</v>
           </cell>
           <cell r="N4">
-            <v>-1.0571421583922851</v>
+            <v>5.2557397789312335</v>
           </cell>
           <cell r="O4">
-            <v>97.183539617052787</v>
+            <v>96.601451088316239</v>
           </cell>
           <cell r="P4">
-            <v>101.35092831730259</v>
+            <v>91.760435156727468</v>
           </cell>
           <cell r="Q4">
-            <v>0.56027955736750146</v>
+            <v>0.53655854865310615</v>
           </cell>
           <cell r="R4">
-            <v>66.719999999999985</v>
+            <v>70.832258064516139</v>
           </cell>
           <cell r="S4">
-            <v>55.387096774193552</v>
+            <v>58.677419354838712</v>
           </cell>
           <cell r="T4">
-            <v>21.870967741935484</v>
+            <v>22.419354838709676</v>
           </cell>
           <cell r="U4">
-            <v>9.0967741935483879</v>
+            <v>10.548387096774194</v>
           </cell>
           <cell r="V4">
-            <v>10.806451612903226</v>
+            <v>12.838709677419354</v>
           </cell>
           <cell r="W4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-13.5</v>
+            <v>-9</v>
           </cell>
         </row>
         <row r="5">
@@ -9026,73 +8921,73 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>Kent State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Ohio</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="D5">
-            <v>4.4847029976942387</v>
+            <v>23.915638484765847</v>
           </cell>
           <cell r="E5">
-            <v>98.659971577451444</v>
+            <v>98.283491704002756</v>
           </cell>
           <cell r="F5">
-            <v>95.854047743121285</v>
+            <v>95.448163069798071</v>
           </cell>
           <cell r="G5">
-            <v>0.53807773109243695</v>
+            <v>0.5870726495726496</v>
           </cell>
           <cell r="H5">
-            <v>73.642580645161289</v>
+            <v>71.669677419354841</v>
           </cell>
           <cell r="I5">
-            <v>61.41935483870968</v>
+            <v>60.387096774193552</v>
           </cell>
           <cell r="J5">
-            <v>26.387096774193548</v>
+            <v>23.516129032258064</v>
           </cell>
           <cell r="K5">
-            <v>12.96774193548387</v>
+            <v>11.225806451612904</v>
           </cell>
           <cell r="L5">
-            <v>13.580645161290322</v>
+            <v>12.161290322580646</v>
           </cell>
           <cell r="M5">
             <v>0</v>
           </cell>
           <cell r="N5">
-            <v>0.8327745257037279</v>
+            <v>14.643537446231871</v>
           </cell>
           <cell r="O5">
-            <v>98.605036917163957</v>
+            <v>97.86818231500709</v>
           </cell>
           <cell r="P5">
-            <v>97.750721733641825</v>
+            <v>101.49670801900939</v>
           </cell>
           <cell r="Q5">
-            <v>0.52149382052659865</v>
+            <v>0.56910809214412283</v>
           </cell>
           <cell r="R5">
-            <v>70.276129032258069</v>
+            <v>66.990666666666669</v>
           </cell>
           <cell r="S5">
-            <v>60.032258064516128</v>
+            <v>56.43333333333333</v>
           </cell>
           <cell r="T5">
-            <v>21.741935483870968</v>
+            <v>21.266666666666666</v>
           </cell>
           <cell r="U5">
-            <v>10</v>
+            <v>9.1666666666666661</v>
           </cell>
           <cell r="V5">
-            <v>10.67741935483871</v>
+            <v>10.366666666666667</v>
           </cell>
           <cell r="W5">
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>-3.5</v>
+            <v>-12.5</v>
           </cell>
         </row>
         <row r="6">
@@ -9100,73 +8995,73 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>Fordham</v>
+            <v>Illinois</v>
           </cell>
           <cell r="C6" t="str">
-            <v>George Washington</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="D6">
-            <v>0.61640859402863835</v>
+            <v>19.052161675549581</v>
           </cell>
           <cell r="E6">
-            <v>101.22953110154809</v>
+            <v>105.19498868590982</v>
           </cell>
           <cell r="F6">
-            <v>103.32832155844922</v>
+            <v>109.65132721821237</v>
           </cell>
           <cell r="G6">
-            <v>0.49542518837459631</v>
+            <v>0.55067385444743933</v>
           </cell>
           <cell r="H6">
-            <v>65.483870967741936</v>
+            <v>66.549333333333337</v>
           </cell>
           <cell r="I6">
-            <v>59.935483870967744</v>
+            <v>61.833333333333336</v>
           </cell>
           <cell r="J6">
-            <v>15.32258064516129</v>
+            <v>20.566666666666666</v>
           </cell>
           <cell r="K6">
-            <v>12.774193548387096</v>
+            <v>13.4</v>
           </cell>
           <cell r="L6">
-            <v>11.580645161290322</v>
+            <v>9.0666666666666664</v>
           </cell>
           <cell r="M6">
             <v>0</v>
           </cell>
           <cell r="N6">
-            <v>8.1181174856323501</v>
+            <v>15.99115140253407</v>
           </cell>
           <cell r="O6">
-            <v>99.423073027448609</v>
+            <v>101.25838978230519</v>
           </cell>
           <cell r="P6">
-            <v>102.88385819155521</v>
+            <v>98.106398085976267</v>
           </cell>
           <cell r="Q6">
-            <v>0.55111228813559321</v>
+            <v>0.54685863874345553</v>
           </cell>
           <cell r="R6">
-            <v>70.331612903225803</v>
+            <v>69.153548387096777</v>
           </cell>
           <cell r="S6">
-            <v>60.903225806451616</v>
+            <v>61.612903225806448</v>
           </cell>
           <cell r="T6">
-            <v>21.35483870967742</v>
+            <v>20.29032258064516</v>
           </cell>
           <cell r="U6">
-            <v>12.741935483870968</v>
+            <v>10.419354838709678</v>
           </cell>
           <cell r="V6">
-            <v>12.774193548387096</v>
+            <v>9.0322580645161299</v>
           </cell>
           <cell r="W6">
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>6</v>
+            <v>-8.5</v>
           </cell>
         </row>
         <row r="7">
@@ -9174,73 +9069,73 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>George Mason</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="C7" t="str">
-            <v>St. Bonaventure</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D7">
-            <v>4.9372307624760952</v>
+            <v>16.038493727225667</v>
           </cell>
           <cell r="E7">
-            <v>97.993055555555557</v>
+            <v>98.214103191431519</v>
           </cell>
           <cell r="F7">
-            <v>105.96199138286919</v>
+            <v>102.68181819319739</v>
           </cell>
           <cell r="G7">
-            <v>0.53668890236506972</v>
+            <v>0.5566192560175055</v>
           </cell>
           <cell r="H7">
-            <v>64.331612903225803</v>
+            <v>67.107096774193565</v>
           </cell>
           <cell r="I7">
-            <v>53.193548387096776</v>
+            <v>58.967741935483872</v>
           </cell>
           <cell r="J7">
-            <v>22.967741935483872</v>
+            <v>16.225806451612904</v>
           </cell>
           <cell r="K7">
-            <v>9.612903225806452</v>
+            <v>8.741935483870968</v>
           </cell>
           <cell r="L7">
-            <v>10.64516129032258</v>
+            <v>9.741935483870968</v>
           </cell>
           <cell r="M7">
             <v>0</v>
           </cell>
           <cell r="N7">
-            <v>3.6587011371081828</v>
+            <v>20.822747409737431</v>
           </cell>
           <cell r="O7">
-            <v>100.06821327722717</v>
+            <v>102.36430980153686</v>
           </cell>
           <cell r="P7">
-            <v>98.203101803703447</v>
+            <v>102.10099533949814</v>
           </cell>
           <cell r="Q7">
-            <v>0.52207505518763797</v>
+            <v>0.57913090128755362</v>
           </cell>
           <cell r="R7">
-            <v>67.670666666666662</v>
+            <v>65.54451612903226</v>
           </cell>
           <cell r="S7">
-            <v>60.4</v>
+            <v>60.12903225806452</v>
           </cell>
           <cell r="T7">
-            <v>17.433333333333334</v>
+            <v>17</v>
           </cell>
           <cell r="U7">
-            <v>11.866666666666667</v>
+            <v>11.161290322580646</v>
           </cell>
           <cell r="V7">
-            <v>11.466666666666667</v>
+            <v>9.0967741935483879</v>
           </cell>
           <cell r="W7">
             <v>0</v>
           </cell>
           <cell r="X7">
-            <v>-3.5</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="8">
@@ -9248,73 +9143,73 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>Duquesne</v>
+            <v>Louisiana Tech</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Rhode Island</v>
+            <v>Missouri State</v>
           </cell>
           <cell r="D8">
-            <v>5.2557397789312335</v>
+            <v>2.6443345975686983</v>
           </cell>
           <cell r="E8">
-            <v>96.601451088316239</v>
+            <v>99.919161188678217</v>
           </cell>
           <cell r="F8">
-            <v>91.760435156727468</v>
+            <v>98.415627483867411</v>
           </cell>
           <cell r="G8">
-            <v>0.53655854865310615</v>
+            <v>0.49525669642857145</v>
           </cell>
           <cell r="H8">
-            <v>70.832258064516139</v>
+            <v>65.900645161290328</v>
           </cell>
           <cell r="I8">
-            <v>58.677419354838712</v>
+            <v>57.806451612903224</v>
           </cell>
           <cell r="J8">
-            <v>22.419354838709676</v>
+            <v>19.129032258064516</v>
           </cell>
           <cell r="K8">
-            <v>10.548387096774194</v>
+            <v>12.96774193548387</v>
           </cell>
           <cell r="L8">
-            <v>12.838709677419354</v>
+            <v>12.64516129032258</v>
           </cell>
           <cell r="M8">
             <v>0</v>
           </cell>
           <cell r="N8">
-            <v>2.4850838421555053</v>
+            <v>3.7666624431054507</v>
           </cell>
           <cell r="O8">
-            <v>96.572160546541426</v>
+            <v>99.995875650873856</v>
           </cell>
           <cell r="P8">
-            <v>97.687267748233438</v>
+            <v>97.704588737615268</v>
           </cell>
           <cell r="Q8">
-            <v>0.4997048406139315</v>
+            <v>0.51096121416526141</v>
           </cell>
           <cell r="R8">
-            <v>66.230967741935473</v>
+            <v>67.619354838709683</v>
           </cell>
           <cell r="S8">
-            <v>54.645161290322584</v>
+            <v>57.387096774193552</v>
           </cell>
           <cell r="T8">
-            <v>21.419354838709676</v>
+            <v>24.35483870967742</v>
           </cell>
           <cell r="U8">
-            <v>10.580645161290322</v>
+            <v>11.806451612903226</v>
           </cell>
           <cell r="V8">
-            <v>12.741935483870968</v>
+            <v>11.32258064516129</v>
           </cell>
           <cell r="W8">
             <v>0</v>
           </cell>
           <cell r="X8">
-            <v>-2</v>
+            <v>-1.5</v>
           </cell>
         </row>
         <row r="9">
@@ -9322,73 +9217,73 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>Davidson</v>
+            <v>Florida</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Loyola Chicago</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D9">
-            <v>5.7827826511419316</v>
+            <v>22.748625673592354</v>
           </cell>
           <cell r="E9">
-            <v>98.650066696309466</v>
+            <v>104.56180875012235</v>
           </cell>
           <cell r="F9">
-            <v>102.50299343544884</v>
+            <v>99.903229832962509</v>
           </cell>
           <cell r="G9">
-            <v>0.53981534910559725</v>
+            <v>0.54031856645097065</v>
           </cell>
           <cell r="H9">
-            <v>64.578064516129032</v>
+            <v>71.534193548387094</v>
           </cell>
           <cell r="I9">
-            <v>55.903225806451616</v>
+            <v>64.806451612903231</v>
           </cell>
           <cell r="J9">
-            <v>18.322580645161292</v>
+            <v>24.967741935483872</v>
           </cell>
           <cell r="K9">
-            <v>9.806451612903226</v>
+            <v>15.903225806451612</v>
           </cell>
           <cell r="L9">
-            <v>10.419354838709678</v>
+            <v>11.64516129032258</v>
           </cell>
           <cell r="M9">
             <v>0</v>
           </cell>
           <cell r="N9">
-            <v>-4.8270734029954374</v>
+            <v>18.55702494743041</v>
           </cell>
           <cell r="O9">
-            <v>95.812691466083152</v>
+            <v>101.42630906768839</v>
           </cell>
           <cell r="P9">
-            <v>110.4400700823726</v>
+            <v>97.25385817981919</v>
           </cell>
           <cell r="Q9">
-            <v>0.4958579881656805</v>
+            <v>0.53432676955827563</v>
           </cell>
           <cell r="R9">
-            <v>65.51483870967742</v>
+            <v>69.038709677419348</v>
           </cell>
           <cell r="S9">
-            <v>54.516129032258064</v>
+            <v>60.612903225806448</v>
           </cell>
           <cell r="T9">
-            <v>18.838709677419356</v>
+            <v>22.741935483870968</v>
           </cell>
           <cell r="U9">
-            <v>10.35483870967742</v>
+            <v>12.258064516129032</v>
           </cell>
           <cell r="V9">
-            <v>13.064516129032258</v>
+            <v>10.67741935483871</v>
           </cell>
           <cell r="W9">
             <v>0</v>
           </cell>
           <cell r="X9">
-            <v>-6.5</v>
+            <v>-10.5</v>
           </cell>
         </row>
         <row r="10">
@@ -9396,73 +9291,73 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>Virginia</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="C10" t="str">
-            <v>NC State</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D10">
-            <v>13.035509619415494</v>
+            <v>19.188801343657655</v>
           </cell>
           <cell r="E10">
-            <v>102.89121915051371</v>
+            <v>100.6501092787602</v>
           </cell>
           <cell r="F10">
-            <v>105.11224188648033</v>
+            <v>97.808224636267653</v>
           </cell>
           <cell r="G10">
-            <v>0.54407859798194369</v>
+            <v>0.55637126376507606</v>
           </cell>
           <cell r="H10">
-            <v>67.184516129032261</v>
+            <v>70.905806451612904</v>
           </cell>
           <cell r="I10">
-            <v>60.741935483870968</v>
+            <v>61.516129032258064</v>
           </cell>
           <cell r="J10">
-            <v>20.580645161290324</v>
+            <v>23.612903225806452</v>
           </cell>
           <cell r="K10">
-            <v>13.451612903225806</v>
+            <v>10.741935483870968</v>
           </cell>
           <cell r="L10">
-            <v>10.838709677419354</v>
+            <v>9.741935483870968</v>
           </cell>
           <cell r="M10">
             <v>0</v>
           </cell>
           <cell r="N10">
-            <v>12.828546458354715</v>
+            <v>20.649012498581907</v>
           </cell>
           <cell r="O10">
-            <v>100.3633950900832</v>
+            <v>104.63085785458507</v>
           </cell>
           <cell r="P10">
-            <v>106.43023746558204</v>
+            <v>93.935133911329061</v>
           </cell>
           <cell r="Q10">
-            <v>0.55110642781875663</v>
+            <v>0.52050473186119872</v>
           </cell>
           <cell r="R10">
-            <v>69.812903225806451</v>
+            <v>67.552258064516124</v>
           </cell>
           <cell r="S10">
-            <v>61.225806451612904</v>
+            <v>61.354838709677416</v>
           </cell>
           <cell r="T10">
-            <v>21.129032258064516</v>
+            <v>23.322580645161292</v>
           </cell>
           <cell r="U10">
-            <v>10.03225806451613</v>
+            <v>16</v>
           </cell>
           <cell r="V10">
-            <v>9.32258064516129</v>
+            <v>11.935483870967742</v>
           </cell>
           <cell r="W10">
             <v>0</v>
           </cell>
           <cell r="X10">
-            <v>-5.5</v>
+            <v>-1.5</v>
           </cell>
         </row>
         <row r="11">
@@ -9470,73 +9365,73 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>Miami</v>
+            <v>Toledo</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Louisville</v>
+            <v>Umass</v>
           </cell>
           <cell r="D11">
-            <v>11.929329589884304</v>
+            <v>4.1368006701786264</v>
           </cell>
           <cell r="E11">
-            <v>100.61828618286182</v>
+            <v>100.01830473218929</v>
           </cell>
           <cell r="F11">
-            <v>99.00132783057046</v>
+            <v>101.61078845085268</v>
           </cell>
           <cell r="G11">
-            <v>0.56159225389994616</v>
+            <v>0.54476439790575915</v>
           </cell>
           <cell r="H11">
-            <v>68.91096774193548</v>
+            <v>69.429677419354846</v>
           </cell>
           <cell r="I11">
-            <v>59.967741935483872</v>
+            <v>61.612903225806448</v>
           </cell>
           <cell r="J11">
-            <v>22.451612903225808</v>
+            <v>18.64516129032258</v>
           </cell>
           <cell r="K11">
-            <v>12.387096774193548</v>
+            <v>10.516129032258064</v>
           </cell>
           <cell r="L11">
-            <v>11.451612903225806</v>
+            <v>10.129032258064516</v>
           </cell>
           <cell r="M11">
             <v>0</v>
           </cell>
           <cell r="N11">
-            <v>17.621046484960765</v>
+            <v>1.9653328411701338</v>
           </cell>
           <cell r="O11">
-            <v>99.240870005058156</v>
+            <v>98.035528511139475</v>
           </cell>
           <cell r="P11">
-            <v>98.862537345674525</v>
+            <v>92.56634666376938</v>
           </cell>
           <cell r="Q11">
-            <v>0.56843209229155744</v>
+            <v>0.53268318397469694</v>
           </cell>
           <cell r="R11">
-            <v>70.765161290322581</v>
+            <v>72.318709677419363</v>
           </cell>
           <cell r="S11">
-            <v>61.516129032258064</v>
+            <v>61.193548387096776</v>
           </cell>
           <cell r="T11">
-            <v>20.580645161290324</v>
+            <v>22.64516129032258</v>
           </cell>
           <cell r="U11">
-            <v>11.451612903225806</v>
+            <v>11.935483870967742</v>
           </cell>
           <cell r="V11">
-            <v>11.64516129032258</v>
+            <v>13.096774193548388</v>
           </cell>
           <cell r="W11">
             <v>0</v>
           </cell>
           <cell r="X11">
-            <v>2.5</v>
+            <v>-3</v>
           </cell>
         </row>
         <row r="12">
@@ -9544,73 +9439,73 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>St. John's</v>
+            <v>Akron</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Providence</v>
+            <v>Kent State</v>
           </cell>
           <cell r="D12">
-            <v>15.109788733361889</v>
+            <v>10.49945141256813</v>
           </cell>
           <cell r="E12">
-            <v>102.58678864787763</v>
+            <v>99.8801284338209</v>
           </cell>
           <cell r="F12">
-            <v>99.76074998519745</v>
+            <v>94.797305672709399</v>
           </cell>
           <cell r="G12">
-            <v>0.50967573221757323</v>
+            <v>0.59409687184661952</v>
           </cell>
           <cell r="H12">
-            <v>70.571612903225812</v>
+            <v>71.441290322580642</v>
           </cell>
           <cell r="I12">
-            <v>61.677419354838712</v>
+            <v>63.935483870967744</v>
           </cell>
           <cell r="J12">
-            <v>26.225806451612904</v>
+            <v>17.64516129032258</v>
           </cell>
           <cell r="K12">
-            <v>13.193548387096774</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="L12">
-            <v>10.548387096774194</v>
+            <v>11.096774193548388</v>
           </cell>
           <cell r="M12">
             <v>0</v>
           </cell>
           <cell r="N12">
-            <v>7.2230139841859584</v>
+            <v>4.4847029976942387</v>
           </cell>
           <cell r="O12">
-            <v>97.978328173374621</v>
+            <v>98.659971577451444</v>
           </cell>
           <cell r="P12">
-            <v>103.93584445667233</v>
+            <v>95.854047743121285</v>
           </cell>
           <cell r="Q12">
-            <v>0.54862194487779514</v>
+            <v>0.53807773109243695</v>
           </cell>
           <cell r="R12">
-            <v>73.363870967741946</v>
+            <v>73.642580645161289</v>
           </cell>
           <cell r="S12">
-            <v>62.032258064516128</v>
+            <v>61.41935483870968</v>
           </cell>
           <cell r="T12">
-            <v>22.967741935483872</v>
+            <v>26.387096774193548</v>
           </cell>
           <cell r="U12">
-            <v>11.290322580645162</v>
+            <v>12.96774193548387</v>
           </cell>
           <cell r="V12">
-            <v>12.516129032258064</v>
+            <v>13.580645161290322</v>
           </cell>
           <cell r="W12">
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>-10.5</v>
+            <v>-7</v>
           </cell>
         </row>
         <row r="13">
@@ -9618,73 +9513,73 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
+            <v>St. John'S</v>
+          </cell>
+          <cell r="C13" t="str">
             <v>Seton Hall</v>
           </cell>
-          <cell r="C13" t="str">
-            <v>Creighton</v>
-          </cell>
           <cell r="D13">
+            <v>15.109788733361889</v>
+          </cell>
+          <cell r="E13">
+            <v>102.58678864787763</v>
+          </cell>
+          <cell r="F13">
+            <v>99.76074998519745</v>
+          </cell>
+          <cell r="G13">
+            <v>0.50967573221757323</v>
+          </cell>
+          <cell r="H13">
+            <v>70.571612903225812</v>
+          </cell>
+          <cell r="I13">
+            <v>61.677419354838712</v>
+          </cell>
+          <cell r="J13">
+            <v>26.225806451612904</v>
+          </cell>
+          <cell r="K13">
+            <v>13.193548387096774</v>
+          </cell>
+          <cell r="L13">
+            <v>10.548387096774194</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
             <v>9.7071392836284129</v>
           </cell>
-          <cell r="E13">
+          <cell r="O13">
             <v>101.21709106603365</v>
           </cell>
-          <cell r="F13">
+          <cell r="P13">
             <v>89.560914057491601</v>
           </cell>
-          <cell r="G13">
+          <cell r="Q13">
             <v>0.47830923248053392</v>
           </cell>
-          <cell r="H13">
+          <cell r="R13">
             <v>65.761290322580649</v>
           </cell>
-          <cell r="I13">
+          <cell r="S13">
             <v>58</v>
           </cell>
-          <cell r="J13">
+          <cell r="T13">
             <v>20.64516129032258</v>
           </cell>
-          <cell r="K13">
+          <cell r="U13">
             <v>12.516129032258064</v>
           </cell>
-          <cell r="L13">
+          <cell r="V13">
             <v>11.193548387096774</v>
           </cell>
-          <cell r="M13">
-            <v>0</v>
-          </cell>
-          <cell r="N13">
-            <v>7.0331892521354531</v>
-          </cell>
-          <cell r="O13">
-            <v>96.994313914816004</v>
-          </cell>
-          <cell r="P13">
-            <v>106.9382662201575</v>
-          </cell>
-          <cell r="Q13">
-            <v>0.53549972692517744</v>
-          </cell>
-          <cell r="R13">
-            <v>68.12516129032258</v>
-          </cell>
-          <cell r="S13">
-            <v>59.064516129032256</v>
-          </cell>
-          <cell r="T13">
-            <v>16.193548387096776</v>
-          </cell>
-          <cell r="U13">
-            <v>9.4516129032258061</v>
-          </cell>
-          <cell r="V13">
-            <v>11.387096774193548</v>
-          </cell>
           <cell r="W13">
             <v>0</v>
           </cell>
           <cell r="X13">
-            <v>-3</v>
+            <v>-7</v>
           </cell>
         </row>
         <row r="14">
@@ -9692,73 +9587,73 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>Ohio State</v>
+            <v>Virginia</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Iowa</v>
+            <v>Miami</v>
           </cell>
           <cell r="D14">
-            <v>14.643537446231871</v>
+            <v>13.035509619415494</v>
           </cell>
           <cell r="E14">
-            <v>97.86818231500709</v>
+            <v>102.89121915051371</v>
           </cell>
           <cell r="F14">
-            <v>101.49670801900939</v>
+            <v>105.11224188648033</v>
           </cell>
           <cell r="G14">
-            <v>0.56910809214412283</v>
+            <v>0.54407859798194369</v>
           </cell>
           <cell r="H14">
-            <v>66.990666666666669</v>
+            <v>67.184516129032261</v>
           </cell>
           <cell r="I14">
-            <v>56.43333333333333</v>
+            <v>60.741935483870968</v>
           </cell>
           <cell r="J14">
-            <v>21.266666666666666</v>
+            <v>20.580645161290324</v>
           </cell>
           <cell r="K14">
-            <v>9.1666666666666661</v>
+            <v>13.451612903225806</v>
           </cell>
           <cell r="L14">
-            <v>10.366666666666667</v>
+            <v>10.838709677419354</v>
           </cell>
           <cell r="M14">
             <v>0</v>
           </cell>
           <cell r="N14">
-            <v>16.132747635538259</v>
+            <v>11.929329589884304</v>
           </cell>
           <cell r="O14">
-            <v>98.481116025859137</v>
+            <v>100.61828618286182</v>
           </cell>
           <cell r="P14">
-            <v>91.651955607786036</v>
+            <v>99.00132783057046</v>
           </cell>
           <cell r="Q14">
-            <v>0.56339285714285714</v>
+            <v>0.56159225389994616</v>
           </cell>
           <cell r="R14">
-            <v>63.050322580645158</v>
+            <v>68.91096774193548</v>
           </cell>
           <cell r="S14">
-            <v>54.193548387096776</v>
+            <v>59.967741935483872</v>
           </cell>
           <cell r="T14">
-            <v>18.516129032258064</v>
+            <v>22.451612903225808</v>
           </cell>
           <cell r="U14">
-            <v>8.935483870967742</v>
+            <v>12.387096774193548</v>
           </cell>
           <cell r="V14">
-            <v>9.6451612903225801</v>
+            <v>11.451612903225806</v>
           </cell>
           <cell r="W14">
             <v>0</v>
           </cell>
           <cell r="X14">
-            <v>-1</v>
+            <v>-4</v>
           </cell>
         </row>
         <row r="15">
@@ -9766,73 +9661,73 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>Wisconsin</v>
+            <v>Arizona</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Washington</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D15">
-            <v>15.99115140253407</v>
+            <v>23.726370739322146</v>
           </cell>
           <cell r="E15">
-            <v>101.25838978230519</v>
+            <v>101.71571463594017</v>
           </cell>
           <cell r="F15">
-            <v>98.106398085976267</v>
+            <v>98.8245285938752</v>
           </cell>
           <cell r="G15">
-            <v>0.54685863874345553</v>
+            <v>0.54952581664910427</v>
           </cell>
           <cell r="H15">
-            <v>69.153548387096777</v>
+            <v>70.829677419354852</v>
           </cell>
           <cell r="I15">
-            <v>61.612903225806448</v>
+            <v>61.225806451612904</v>
           </cell>
           <cell r="J15">
-            <v>20.29032258064516</v>
+            <v>26.225806451612904</v>
           </cell>
           <cell r="K15">
-            <v>10.419354838709678</v>
+            <v>12.903225806451612</v>
           </cell>
           <cell r="L15">
-            <v>9.0322580645161299</v>
+            <v>10.96774193548387</v>
           </cell>
           <cell r="M15">
             <v>0</v>
           </cell>
           <cell r="N15">
-            <v>11.573237900042043</v>
+            <v>19.724267702693741</v>
           </cell>
           <cell r="O15">
-            <v>100.95814989656817</v>
+            <v>101.38630280766203</v>
           </cell>
           <cell r="P15">
-            <v>98.788425473817696</v>
+            <v>95.516490153604366</v>
           </cell>
           <cell r="Q15">
-            <v>0.51374933897408781</v>
+            <v>0.56290322580645158</v>
           </cell>
           <cell r="R15">
-            <v>68.007741935483864</v>
+            <v>67.727741935483877</v>
           </cell>
           <cell r="S15">
-            <v>61</v>
+            <v>60</v>
           </cell>
           <cell r="T15">
-            <v>18.419354838709676</v>
+            <v>20.93548387096774</v>
           </cell>
           <cell r="U15">
-            <v>11.67741935483871</v>
+            <v>11.806451612903226</v>
           </cell>
           <cell r="V15">
-            <v>10.580645161290322</v>
+            <v>10.32258064516129</v>
           </cell>
           <cell r="W15">
             <v>0</v>
           </cell>
           <cell r="X15">
-            <v>-7</v>
+            <v>-3.5</v>
           </cell>
         </row>
         <row r="16">
@@ -9840,73 +9735,73 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>Missouri</v>
+            <v>Utah State</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Kentucky</v>
+            <v>Nevada</v>
           </cell>
           <cell r="D16">
-            <v>12.160899195127248</v>
+            <v>16.347492910416953</v>
           </cell>
           <cell r="E16">
-            <v>98.568347897184324</v>
+            <v>99.814093598708979</v>
           </cell>
           <cell r="F16">
-            <v>95.041322915195849</v>
+            <v>89.773356716311071</v>
           </cell>
           <cell r="G16">
-            <v>0.55426794799321655</v>
+            <v>0.57657142857142862</v>
           </cell>
           <cell r="H16">
-            <v>68.369032258064522</v>
+            <v>67.801333333333332</v>
           </cell>
           <cell r="I16">
-            <v>57.064516129032256</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="J16">
-            <v>24.225806451612904</v>
+            <v>22.2</v>
           </cell>
           <cell r="K16">
-            <v>11.64516129032258</v>
+            <v>10.766666666666667</v>
           </cell>
           <cell r="L16">
-            <v>12.290322580645162</v>
+            <v>10.466666666666667</v>
           </cell>
           <cell r="M16">
             <v>0</v>
           </cell>
           <cell r="N16">
-            <v>18.55702494743041</v>
+            <v>9.2097769172278117</v>
           </cell>
           <cell r="O16">
-            <v>101.42630906768839</v>
+            <v>101.36929460580913</v>
           </cell>
           <cell r="P16">
-            <v>97.25385817981919</v>
+            <v>93.092548572138085</v>
           </cell>
           <cell r="Q16">
-            <v>0.53432676955827563</v>
+            <v>0.49772598067083568</v>
           </cell>
           <cell r="R16">
-            <v>69.038709677419348</v>
+            <v>66.516129032258064</v>
           </cell>
           <cell r="S16">
-            <v>60.612903225806448</v>
+            <v>56.741935483870968</v>
           </cell>
           <cell r="T16">
-            <v>22.741935483870968</v>
+            <v>25.806451612903224</v>
           </cell>
           <cell r="U16">
-            <v>12.258064516129032</v>
+            <v>11.419354838709678</v>
           </cell>
           <cell r="V16">
-            <v>10.67741935483871</v>
+            <v>9.8387096774193541</v>
           </cell>
           <cell r="W16">
             <v>0</v>
           </cell>
           <cell r="X16">
-            <v>3</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="17">
@@ -9914,73 +9809,73 @@
             <v>16</v>
           </cell>
           <cell r="B17" t="str">
-            <v>Tennessee</v>
+            <v>Alabama A&amp;M</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Auburn</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D17">
-            <v>20.649012498581907</v>
+            <v>-12.778230890104188</v>
           </cell>
           <cell r="E17">
-            <v>104.63085785458507</v>
+            <v>96.92565895642818</v>
           </cell>
           <cell r="F17">
-            <v>93.935133911329061</v>
+            <v>96.855429590956433</v>
           </cell>
           <cell r="G17">
-            <v>0.52050473186119872</v>
+            <v>0.49847094801223241</v>
           </cell>
           <cell r="H17">
-            <v>67.552258064516124</v>
+            <v>66.989333333333335</v>
           </cell>
           <cell r="I17">
-            <v>61.354838709677416</v>
+            <v>54.5</v>
           </cell>
           <cell r="J17">
-            <v>23.322580645161292</v>
+            <v>24.066666666666666</v>
           </cell>
           <cell r="K17">
-            <v>16</v>
+            <v>9.3333333333333339</v>
           </cell>
           <cell r="L17">
-            <v>11.935483870967742</v>
+            <v>11.233333333333333</v>
           </cell>
           <cell r="M17">
             <v>0</v>
           </cell>
           <cell r="N17">
-            <v>17.579382543026234</v>
+            <v>-10.748183340293197</v>
           </cell>
           <cell r="O17">
-            <v>103.12857214353635</v>
+            <v>96.942723004694827</v>
           </cell>
           <cell r="P17">
-            <v>92.623653201414598</v>
+            <v>93.291737667336207</v>
           </cell>
           <cell r="Q17">
-            <v>0.52776280323450131</v>
+            <v>0.49388297872340425</v>
           </cell>
           <cell r="R17">
-            <v>68.739354838709673</v>
+            <v>74.380645161290332</v>
           </cell>
           <cell r="S17">
-            <v>59.838709677419352</v>
+            <v>60.645161290322584</v>
           </cell>
           <cell r="T17">
-            <v>27.193548387096776</v>
+            <v>26.451612903225808</v>
           </cell>
           <cell r="U17">
-            <v>13.35483870967742</v>
+            <v>10.161290322580646</v>
           </cell>
           <cell r="V17">
-            <v>10.290322580645162</v>
+            <v>12.258064516129032</v>
           </cell>
           <cell r="W17">
             <v>0</v>
           </cell>
           <cell r="X17">
-            <v>-5.5</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="18">
@@ -9988,73 +9883,73 @@
             <v>17</v>
           </cell>
           <cell r="B18" t="str">
-            <v>Texas Tech</v>
+            <v>Howard</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Iowa State</v>
+            <v>South Carolina State</v>
           </cell>
           <cell r="D18">
-            <v>17.917409465972611</v>
+            <v>-7.0667288784066029</v>
           </cell>
           <cell r="E18">
-            <v>100.6715030361653</v>
+            <v>97.771296389419689</v>
           </cell>
           <cell r="F18">
-            <v>103.12783146278295</v>
+            <v>101.22012384797286</v>
           </cell>
           <cell r="G18">
-            <v>0.56585879873551104</v>
+            <v>0.52172686230248311</v>
           </cell>
           <cell r="H18">
-            <v>67.753548387096771</v>
+            <v>69.380645161290332</v>
           </cell>
           <cell r="I18">
-            <v>61.225806451612904</v>
+            <v>57.161290322580648</v>
           </cell>
           <cell r="J18">
-            <v>16.741935483870968</v>
+            <v>24.838709677419356</v>
           </cell>
           <cell r="K18">
-            <v>11.67741935483871</v>
+            <v>12.290322580645162</v>
           </cell>
           <cell r="L18">
-            <v>10.838709677419354</v>
+            <v>13.580645161290322</v>
           </cell>
           <cell r="M18">
             <v>0</v>
           </cell>
           <cell r="N18">
-            <v>19.724267702693741</v>
+            <v>-15.059792168727887</v>
           </cell>
           <cell r="O18">
-            <v>101.38630280766203</v>
+            <v>94.89192336191384</v>
           </cell>
           <cell r="P18">
-            <v>95.516490153604366</v>
+            <v>88.02533549738591</v>
           </cell>
           <cell r="Q18">
-            <v>0.56290322580645158</v>
+            <v>0.46562123039806996</v>
           </cell>
           <cell r="R18">
-            <v>67.727741935483877</v>
+            <v>68.835999999999999</v>
           </cell>
           <cell r="S18">
-            <v>60</v>
+            <v>55.266666666666666</v>
           </cell>
           <cell r="T18">
-            <v>20.93548387096774</v>
+            <v>22.733333333333334</v>
           </cell>
           <cell r="U18">
-            <v>11.806451612903226</v>
+            <v>11</v>
           </cell>
           <cell r="V18">
-            <v>10.32258064516129</v>
+            <v>14.566666666666666</v>
           </cell>
           <cell r="W18">
             <v>0</v>
           </cell>
           <cell r="X18">
-            <v>5</v>
+            <v>-15</v>
           </cell>
         </row>
         <row r="19">
@@ -10062,73 +9957,73 @@
             <v>18</v>
           </cell>
           <cell r="B19" t="str">
-            <v>Arizona</v>
+            <v>George Washington</v>
           </cell>
           <cell r="C19" t="str">
-            <v>UCF</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D19">
-            <v>23.726370739322146</v>
+            <v>8.1181174856323501</v>
           </cell>
           <cell r="E19">
-            <v>101.71571463594017</v>
+            <v>99.423073027448609</v>
           </cell>
           <cell r="F19">
-            <v>98.8245285938752</v>
+            <v>102.88385819155521</v>
           </cell>
           <cell r="G19">
-            <v>0.54952581664910427</v>
+            <v>0.55111228813559321</v>
           </cell>
           <cell r="H19">
-            <v>70.829677419354852</v>
+            <v>70.331612903225803</v>
           </cell>
           <cell r="I19">
-            <v>61.225806451612904</v>
+            <v>60.903225806451616</v>
           </cell>
           <cell r="J19">
-            <v>26.225806451612904</v>
+            <v>21.35483870967742</v>
           </cell>
           <cell r="K19">
-            <v>12.903225806451612</v>
+            <v>12.741935483870968</v>
           </cell>
           <cell r="L19">
-            <v>10.96774193548387</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="M19">
             <v>0</v>
           </cell>
           <cell r="N19">
-            <v>12.68819911571482</v>
+            <v>12.924462689730786</v>
           </cell>
           <cell r="O19">
-            <v>100.7354909489852</v>
+            <v>96.65371999791742</v>
           </cell>
           <cell r="P19">
-            <v>98.072123997625383</v>
+            <v>94.854733271656428</v>
           </cell>
           <cell r="Q19">
-            <v>0.53966942148760333</v>
+            <v>0.60122699386503065</v>
           </cell>
           <cell r="R19">
-            <v>70.147586206896563</v>
+            <v>71.082666666666668</v>
           </cell>
           <cell r="S19">
-            <v>62.586206896551722</v>
+            <v>59.766666666666666</v>
           </cell>
           <cell r="T19">
-            <v>19.379310344827587</v>
+            <v>20.566666666666666</v>
           </cell>
           <cell r="U19">
-            <v>12.172413793103448</v>
+            <v>10.133333333333333</v>
           </cell>
           <cell r="V19">
-            <v>11.206896551724139</v>
+            <v>12.4</v>
           </cell>
           <cell r="W19">
             <v>0</v>
           </cell>
           <cell r="X19">
-            <v>-17</v>
+            <v>6.5</v>
           </cell>
         </row>
         <row r="20">
@@ -10136,73 +10031,73 @@
             <v>19</v>
           </cell>
           <cell r="B20" t="str">
-            <v>Utah State</v>
+            <v>St. Bonaventure</v>
           </cell>
           <cell r="C20" t="str">
-            <v>UNLV</v>
+            <v>Dayton</v>
           </cell>
           <cell r="D20">
-            <v>16.347492910416953</v>
+            <v>3.6587011371081828</v>
           </cell>
           <cell r="E20">
-            <v>99.814093598708979</v>
+            <v>100.06821327722717</v>
           </cell>
           <cell r="F20">
-            <v>89.773356716311071</v>
+            <v>98.203101803703447</v>
           </cell>
           <cell r="G20">
-            <v>0.57657142857142862</v>
+            <v>0.52207505518763797</v>
           </cell>
           <cell r="H20">
-            <v>67.801333333333332</v>
+            <v>67.670666666666662</v>
           </cell>
           <cell r="I20">
-            <v>58.333333333333336</v>
+            <v>60.4</v>
           </cell>
           <cell r="J20">
-            <v>22.2</v>
+            <v>17.433333333333334</v>
           </cell>
           <cell r="K20">
-            <v>10.766666666666667</v>
+            <v>11.866666666666667</v>
           </cell>
           <cell r="L20">
-            <v>10.466666666666667</v>
+            <v>11.466666666666667</v>
           </cell>
           <cell r="M20">
             <v>0</v>
           </cell>
           <cell r="N20">
-            <v>8.1833176881236689</v>
+            <v>7.2080821342928445</v>
           </cell>
           <cell r="O20">
-            <v>98.332117488961416</v>
+            <v>95.080309824704429</v>
           </cell>
           <cell r="P20">
-            <v>88.010291760587222</v>
+            <v>92.716319767963711</v>
           </cell>
           <cell r="Q20">
-            <v>0.53103629668595476</v>
+            <v>0.52316486161251508</v>
           </cell>
           <cell r="R20">
-            <v>70.896249999999995</v>
+            <v>68.127741935483868</v>
           </cell>
           <cell r="S20">
-            <v>59.40625</v>
+            <v>53.612903225806448</v>
           </cell>
           <cell r="T20">
-            <v>24.125</v>
+            <v>25.29032258064516</v>
           </cell>
           <cell r="U20">
-            <v>11.03125</v>
+            <v>8.7096774193548381</v>
           </cell>
           <cell r="V20">
-            <v>11.90625</v>
+            <v>12.096774193548388</v>
           </cell>
           <cell r="W20">
             <v>0</v>
           </cell>
           <cell r="X20">
-            <v>-7</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="21">
@@ -10210,73 +10105,73 @@
             <v>20</v>
           </cell>
           <cell r="B21" t="str">
-            <v>Louisiana Tech</v>
+            <v>Duquesne</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Middle Tennessee</v>
+            <v>VCU</v>
           </cell>
           <cell r="D21">
-            <v>2.6443345975686983</v>
+            <v>5.2557397789312335</v>
           </cell>
           <cell r="E21">
-            <v>99.919161188678217</v>
+            <v>96.601451088316239</v>
           </cell>
           <cell r="F21">
-            <v>98.415627483867411</v>
+            <v>91.760435156727468</v>
           </cell>
           <cell r="G21">
-            <v>0.49525669642857145</v>
+            <v>0.53655854865310615</v>
           </cell>
           <cell r="H21">
-            <v>65.900645161290328</v>
+            <v>70.832258064516139</v>
           </cell>
           <cell r="I21">
-            <v>57.806451612903224</v>
+            <v>58.677419354838712</v>
           </cell>
           <cell r="J21">
-            <v>19.129032258064516</v>
+            <v>22.419354838709676</v>
           </cell>
           <cell r="K21">
-            <v>12.96774193548387</v>
+            <v>10.548387096774194</v>
           </cell>
           <cell r="L21">
-            <v>12.64516129032258</v>
+            <v>12.838709677419354</v>
           </cell>
           <cell r="M21">
             <v>0</v>
           </cell>
           <cell r="N21">
-            <v>7.273503348238739</v>
+            <v>10.046934010674722</v>
           </cell>
           <cell r="O21">
-            <v>99.424133027021128</v>
+            <v>100.11649510419282</v>
           </cell>
           <cell r="P21">
-            <v>99.488720427804381</v>
+            <v>100.40585231866712</v>
           </cell>
           <cell r="Q21">
-            <v>0.52200557103064071</v>
+            <v>0.54296008869179602</v>
           </cell>
           <cell r="R21">
-            <v>68.084000000000003</v>
+            <v>69.00645161290322</v>
           </cell>
           <cell r="S21">
-            <v>59.833333333333336</v>
+            <v>58.193548387096776</v>
           </cell>
           <cell r="T21">
-            <v>18.600000000000001</v>
+            <v>25.967741935483872</v>
           </cell>
           <cell r="U21">
-            <v>11.266666666666667</v>
+            <v>11.419354838709678</v>
           </cell>
           <cell r="V21">
-            <v>11.333333333333334</v>
+            <v>10.806451612903226</v>
           </cell>
           <cell r="W21">
             <v>0</v>
           </cell>
           <cell r="X21">
-            <v>1.5</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="22">
@@ -10284,73 +10179,73 @@
             <v>21</v>
           </cell>
           <cell r="B22" t="str">
-            <v>Western Kentucky</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Kennesaw State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D22">
-            <v>5.5553615261544227</v>
+            <v>14.643537446231871</v>
           </cell>
           <cell r="E22">
-            <v>102.21523481083274</v>
+            <v>97.86818231500709</v>
           </cell>
           <cell r="F22">
-            <v>102.35314169399868</v>
+            <v>101.49670801900939</v>
           </cell>
           <cell r="G22">
-            <v>0.48414830736163356</v>
+            <v>0.56910809214412283</v>
           </cell>
           <cell r="H22">
-            <v>70.993333333333339</v>
+            <v>66.990666666666669</v>
           </cell>
           <cell r="I22">
-            <v>62.033333333333331</v>
+            <v>56.43333333333333</v>
           </cell>
           <cell r="J22">
-            <v>25.666666666666668</v>
+            <v>21.266666666666666</v>
           </cell>
           <cell r="K22">
-            <v>12.766666666666667</v>
+            <v>9.1666666666666661</v>
           </cell>
           <cell r="L22">
-            <v>10.433333333333334</v>
+            <v>10.366666666666667</v>
           </cell>
           <cell r="M22">
             <v>0</v>
           </cell>
           <cell r="N22">
-            <v>6.490752715038262</v>
+            <v>23.915638484765847</v>
           </cell>
           <cell r="O22">
-            <v>101.8432322449375</v>
+            <v>98.283491704002756</v>
           </cell>
           <cell r="P22">
-            <v>97.141081053482708</v>
+            <v>95.448163069798071</v>
           </cell>
           <cell r="Q22">
-            <v>0.52519480519480521</v>
+            <v>0.5870726495726496</v>
           </cell>
           <cell r="R22">
-            <v>71.699354838709667</v>
+            <v>71.669677419354841</v>
           </cell>
           <cell r="S22">
-            <v>62.096774193548384</v>
+            <v>60.387096774193552</v>
           </cell>
           <cell r="T22">
-            <v>26.516129032258064</v>
+            <v>23.516129032258064</v>
           </cell>
           <cell r="U22">
-            <v>13.806451612903226</v>
+            <v>11.225806451612904</v>
           </cell>
           <cell r="V22">
-            <v>11.741935483870968</v>
+            <v>12.161290322580646</v>
           </cell>
           <cell r="W22">
             <v>0</v>
           </cell>
           <cell r="X22">
-            <v>-1.5</v>
+            <v>12.5</v>
           </cell>
         </row>
         <row r="23">
@@ -10358,73 +10253,73 @@
             <v>22</v>
           </cell>
           <cell r="B23" t="str">
-            <v>UT Arlington</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="C23" t="str">
-            <v>Southern Utah</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D23">
-            <v>3.3990966185562335</v>
+            <v>15.99115140253407</v>
           </cell>
           <cell r="E23">
-            <v>96.820667384284164</v>
+            <v>101.25838978230519</v>
           </cell>
           <cell r="F23">
-            <v>94.886171282090174</v>
+            <v>98.106398085976267</v>
           </cell>
           <cell r="G23">
-            <v>0.4855159927579964</v>
+            <v>0.54685863874345553</v>
           </cell>
           <cell r="H23">
-            <v>67.382666666666665</v>
+            <v>69.153548387096777</v>
           </cell>
           <cell r="I23">
-            <v>55.233333333333334</v>
+            <v>61.612903225806448</v>
           </cell>
           <cell r="J23">
-            <v>23.066666666666666</v>
+            <v>20.29032258064516</v>
           </cell>
           <cell r="K23">
-            <v>12.1</v>
+            <v>10.419354838709678</v>
           </cell>
           <cell r="L23">
-            <v>14.1</v>
+            <v>9.0322580645161299</v>
           </cell>
           <cell r="M23">
             <v>0</v>
           </cell>
           <cell r="N23">
-            <v>0.10290105788384882</v>
+            <v>19.052161675549581</v>
           </cell>
           <cell r="O23">
-            <v>94.858918582970801</v>
+            <v>105.19498868590982</v>
           </cell>
           <cell r="P23">
-            <v>96.529523762300542</v>
+            <v>109.65132721821237</v>
           </cell>
           <cell r="Q23">
-            <v>0.52679075014100396</v>
+            <v>0.55067385444743933</v>
           </cell>
           <cell r="R23">
-            <v>71.692000000000007</v>
+            <v>66.549333333333337</v>
           </cell>
           <cell r="S23">
-            <v>59.1</v>
+            <v>61.833333333333336</v>
           </cell>
           <cell r="T23">
-            <v>20.133333333333333</v>
+            <v>20.566666666666666</v>
           </cell>
           <cell r="U23">
-            <v>10.433333333333334</v>
+            <v>13.4</v>
           </cell>
           <cell r="V23">
-            <v>14.166666666666666</v>
+            <v>9.0666666666666664</v>
           </cell>
           <cell r="W23">
             <v>0</v>
           </cell>
           <cell r="X23">
-            <v>-5.5</v>
+            <v>8.5</v>
           </cell>
         </row>
         <row r="24">
@@ -10432,73 +10327,73 @@
             <v>23</v>
           </cell>
           <cell r="B24" t="str">
-            <v>Texas Southern</v>
+            <v>Purdue</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Alabama A&amp;M</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D24">
-            <v>-12.77273260985422</v>
+            <v>20.822747409737431</v>
           </cell>
           <cell r="E24">
-            <v>95.293918203009113</v>
+            <v>102.36430980153686</v>
           </cell>
           <cell r="F24">
-            <v>98.078075334634491</v>
+            <v>102.10099533949814</v>
           </cell>
           <cell r="G24">
-            <v>0.5056179775280899</v>
+            <v>0.57913090128755362</v>
           </cell>
           <cell r="H24">
-            <v>71.582068965517237</v>
+            <v>65.54451612903226</v>
           </cell>
           <cell r="I24">
-            <v>58.310344827586206</v>
+            <v>60.12903225806452</v>
           </cell>
           <cell r="J24">
-            <v>22.482758620689655</v>
+            <v>17</v>
           </cell>
           <cell r="K24">
-            <v>10.172413793103448</v>
+            <v>11.161290322580646</v>
           </cell>
           <cell r="L24">
-            <v>13.551724137931034</v>
+            <v>9.0967741935483879</v>
           </cell>
           <cell r="M24">
             <v>0</v>
           </cell>
           <cell r="N24">
-            <v>-12.778230890104188</v>
+            <v>16.038493727225667</v>
           </cell>
           <cell r="O24">
-            <v>96.92565895642818</v>
+            <v>98.214103191431519</v>
           </cell>
           <cell r="P24">
-            <v>96.855429590956433</v>
+            <v>102.68181819319739</v>
           </cell>
           <cell r="Q24">
-            <v>0.49847094801223241</v>
+            <v>0.5566192560175055</v>
           </cell>
           <cell r="R24">
-            <v>66.989333333333335</v>
+            <v>67.107096774193565</v>
           </cell>
           <cell r="S24">
-            <v>54.5</v>
+            <v>58.967741935483872</v>
           </cell>
           <cell r="T24">
-            <v>24.066666666666666</v>
+            <v>16.225806451612904</v>
           </cell>
           <cell r="U24">
-            <v>9.3333333333333339</v>
+            <v>8.741935483870968</v>
           </cell>
           <cell r="V24">
-            <v>11.233333333333333</v>
+            <v>9.741935483870968</v>
           </cell>
           <cell r="W24">
             <v>0</v>
           </cell>
           <cell r="X24">
-            <v>1</v>
+            <v>-4</v>
           </cell>
         </row>
         <row r="25">
@@ -10506,73 +10401,73 @@
             <v>24</v>
           </cell>
           <cell r="B25" t="str">
-            <v>Southern</v>
+            <v>Missouri State</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Arkansas-Pine Bluff</v>
+            <v>Louisiana Tech</v>
           </cell>
           <cell r="D25">
-            <v>-6.7092460643817606</v>
+            <v>3.7666624431054507</v>
           </cell>
           <cell r="E25">
-            <v>99.018646109371232</v>
+            <v>99.995875650873856</v>
           </cell>
           <cell r="F25">
-            <v>93.207129449722274</v>
+            <v>97.704588737615268</v>
           </cell>
           <cell r="G25">
-            <v>0.50943396226415094</v>
+            <v>0.51096121416526141</v>
           </cell>
           <cell r="H25">
-            <v>72.842580645161291</v>
+            <v>67.619354838709683</v>
           </cell>
           <cell r="I25">
-            <v>61.548387096774192</v>
+            <v>57.387096774193552</v>
           </cell>
           <cell r="J25">
-            <v>24.93548387096774</v>
+            <v>24.35483870967742</v>
           </cell>
           <cell r="K25">
-            <v>11.67741935483871</v>
+            <v>11.806451612903226</v>
           </cell>
           <cell r="L25">
-            <v>12</v>
+            <v>11.32258064516129</v>
           </cell>
           <cell r="M25">
             <v>0</v>
           </cell>
           <cell r="N25">
-            <v>-12.958561275000525</v>
+            <v>2.6443345975686983</v>
           </cell>
           <cell r="O25">
-            <v>95.393026941362919</v>
+            <v>99.919161188678217</v>
           </cell>
           <cell r="P25">
-            <v>98.671403378251426</v>
+            <v>98.415627483867411</v>
           </cell>
           <cell r="Q25">
-            <v>0.51358695652173914</v>
+            <v>0.49525669642857145</v>
           </cell>
           <cell r="R25">
-            <v>72.10193548387096</v>
+            <v>65.900645161290328</v>
           </cell>
           <cell r="S25">
-            <v>59.354838709677416</v>
+            <v>57.806451612903224</v>
           </cell>
           <cell r="T25">
-            <v>21.419354838709676</v>
+            <v>19.129032258064516</v>
           </cell>
           <cell r="U25">
-            <v>10.290322580645162</v>
+            <v>12.96774193548387</v>
           </cell>
           <cell r="V25">
-            <v>13.612903225806452</v>
+            <v>12.64516129032258</v>
           </cell>
           <cell r="W25">
             <v>0</v>
           </cell>
           <cell r="X25">
-            <v>-5</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="26">
@@ -10580,73 +10475,73 @@
             <v>25</v>
           </cell>
           <cell r="B26" t="str">
-            <v>Norfolk State</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="C26" t="str">
-            <v>South Carolina State</v>
+            <v>Florida</v>
           </cell>
           <cell r="D26">
-            <v>-8.7139195057519103</v>
+            <v>18.55702494743041</v>
           </cell>
           <cell r="E26">
-            <v>98.578119467907541</v>
+            <v>101.42630906768839</v>
           </cell>
           <cell r="F26">
-            <v>98.49546939189942</v>
+            <v>97.25385817981919</v>
           </cell>
           <cell r="G26">
-            <v>0.51537171604248189</v>
+            <v>0.53432676955827563</v>
           </cell>
           <cell r="H26">
-            <v>69.099354838709672</v>
+            <v>69.038709677419348</v>
           </cell>
           <cell r="I26">
-            <v>57.70967741935484</v>
+            <v>60.612903225806448</v>
           </cell>
           <cell r="J26">
-            <v>24.419354838709676</v>
+            <v>22.741935483870968</v>
           </cell>
           <cell r="K26">
-            <v>11.483870967741936</v>
+            <v>12.258064516129032</v>
           </cell>
           <cell r="L26">
-            <v>12.129032258064516</v>
+            <v>10.67741935483871</v>
           </cell>
           <cell r="M26">
             <v>0</v>
           </cell>
           <cell r="N26">
-            <v>-15.059792168727887</v>
+            <v>22.748625673592354</v>
           </cell>
           <cell r="O26">
-            <v>94.89192336191384</v>
+            <v>104.56180875012235</v>
           </cell>
           <cell r="P26">
-            <v>88.02533549738591</v>
+            <v>99.903229832962509</v>
           </cell>
           <cell r="Q26">
-            <v>0.46562123039806996</v>
+            <v>0.54031856645097065</v>
           </cell>
           <cell r="R26">
-            <v>68.835999999999999</v>
+            <v>71.534193548387094</v>
           </cell>
           <cell r="S26">
-            <v>55.266666666666666</v>
+            <v>64.806451612903231</v>
           </cell>
           <cell r="T26">
-            <v>22.733333333333334</v>
+            <v>24.967741935483872</v>
           </cell>
           <cell r="U26">
-            <v>11</v>
+            <v>15.903225806451612</v>
           </cell>
           <cell r="V26">
-            <v>14.566666666666666</v>
+            <v>11.64516129032258</v>
           </cell>
           <cell r="W26">
             <v>0</v>
           </cell>
           <cell r="X26">
-            <v>-7</v>
+            <v>10.5</v>
           </cell>
         </row>
         <row r="27">
@@ -10654,73 +10549,73 @@
             <v>26</v>
           </cell>
           <cell r="B27" t="str">
-            <v>North Carolina Central</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="C27" t="str">
-            <v>Maryland-Eastern Shore</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D27">
-            <v>-12.049706064548028</v>
+            <v>20.649012498581907</v>
           </cell>
           <cell r="E27">
-            <v>97.391178918169217</v>
+            <v>104.63085785458507</v>
           </cell>
           <cell r="F27">
-            <v>102.17668911130822</v>
+            <v>93.935133911329061</v>
           </cell>
           <cell r="G27">
-            <v>0.49514563106796117</v>
+            <v>0.52050473186119872</v>
           </cell>
           <cell r="H27">
-            <v>68.108965517241387</v>
+            <v>67.552258064516124</v>
           </cell>
           <cell r="I27">
-            <v>56.827586206896555</v>
+            <v>61.354838709677416</v>
           </cell>
           <cell r="J27">
-            <v>22.03448275862069</v>
+            <v>23.322580645161292</v>
           </cell>
           <cell r="K27">
-            <v>10.689655172413794</v>
+            <v>16</v>
           </cell>
           <cell r="L27">
-            <v>12.275862068965518</v>
+            <v>11.935483870967742</v>
           </cell>
           <cell r="M27">
             <v>0</v>
           </cell>
           <cell r="N27">
-            <v>-15.054111575487484</v>
+            <v>19.188801343657655</v>
           </cell>
           <cell r="O27">
-            <v>92.100589740736609</v>
+            <v>100.6501092787602</v>
           </cell>
           <cell r="P27">
-            <v>99.022221353495468</v>
+            <v>97.808224636267653</v>
           </cell>
           <cell r="Q27">
-            <v>0.49519230769230771</v>
+            <v>0.55637126376507606</v>
           </cell>
           <cell r="R27">
-            <v>65.824516129032261</v>
+            <v>70.905806451612904</v>
           </cell>
           <cell r="S27">
-            <v>53.677419354838712</v>
+            <v>61.516129032258064</v>
           </cell>
           <cell r="T27">
-            <v>15.290322580645162</v>
+            <v>23.612903225806452</v>
           </cell>
           <cell r="U27">
-            <v>10.32258064516129</v>
+            <v>10.741935483870968</v>
           </cell>
           <cell r="V27">
-            <v>15.741935483870968</v>
+            <v>9.741935483870968</v>
           </cell>
           <cell r="W27">
             <v>0</v>
           </cell>
           <cell r="X27">
-            <v>-1.5</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="28">
@@ -10731,7 +10626,7 @@
             <v>Umass</v>
           </cell>
           <cell r="C28" t="str">
-            <v>Miami (OH)</v>
+            <v>Toledo</v>
           </cell>
           <cell r="D28">
             <v>1.9653328411701338</v>
@@ -10764,37 +10659,37 @@
             <v>0</v>
           </cell>
           <cell r="N28">
-            <v>8.0718958761759509</v>
+            <v>4.1368006701786264</v>
           </cell>
           <cell r="O28">
-            <v>96.34903131164954</v>
+            <v>100.01830473218929</v>
           </cell>
           <cell r="P28">
-            <v>97.622654172658116</v>
+            <v>101.61078845085268</v>
           </cell>
           <cell r="Q28">
-            <v>0.61308516638465882</v>
+            <v>0.54476439790575915</v>
           </cell>
           <cell r="R28">
-            <v>72.061333333333337</v>
+            <v>69.429677419354846</v>
           </cell>
           <cell r="S28">
-            <v>59.1</v>
+            <v>61.612903225806448</v>
           </cell>
           <cell r="T28">
-            <v>23.7</v>
+            <v>18.64516129032258</v>
           </cell>
           <cell r="U28">
-            <v>7.9666666666666668</v>
+            <v>10.516129032258064</v>
           </cell>
           <cell r="V28">
-            <v>10.5</v>
+            <v>10.129032258064516</v>
           </cell>
           <cell r="W28">
             <v>0</v>
           </cell>
           <cell r="X28">
-            <v>8</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="29">
@@ -10802,73 +10697,73 @@
             <v>28</v>
           </cell>
           <cell r="B29" t="str">
-            <v>Bowling Green</v>
+            <v>Kent State</v>
           </cell>
           <cell r="C29" t="str">
-            <v>Toledo</v>
+            <v>Akron</v>
           </cell>
           <cell r="D29">
-            <v>5.2719145340748046</v>
+            <v>4.4847029976942387</v>
           </cell>
           <cell r="E29">
-            <v>97.904002363018748</v>
+            <v>98.659971577451444</v>
           </cell>
           <cell r="F29">
-            <v>98.018930609306281</v>
+            <v>95.854047743121285</v>
           </cell>
           <cell r="G29">
-            <v>0.5335463258785943</v>
+            <v>0.53807773109243695</v>
           </cell>
           <cell r="H29">
-            <v>71.930322580645168</v>
+            <v>73.642580645161289</v>
           </cell>
           <cell r="I29">
-            <v>60.58064516129032</v>
+            <v>61.41935483870968</v>
           </cell>
           <cell r="J29">
-            <v>22.93548387096774</v>
+            <v>26.387096774193548</v>
           </cell>
           <cell r="K29">
-            <v>10.258064516129032</v>
+            <v>12.96774193548387</v>
           </cell>
           <cell r="L29">
-            <v>11.516129032258064</v>
+            <v>13.580645161290322</v>
           </cell>
           <cell r="M29">
             <v>0</v>
           </cell>
           <cell r="N29">
-            <v>4.1368006701786264</v>
+            <v>10.49945141256813</v>
           </cell>
           <cell r="O29">
-            <v>100.01830473218929</v>
+            <v>99.8801284338209</v>
           </cell>
           <cell r="P29">
-            <v>101.61078845085268</v>
+            <v>94.797305672709399</v>
           </cell>
           <cell r="Q29">
-            <v>0.54476439790575915</v>
+            <v>0.59409687184661952</v>
           </cell>
           <cell r="R29">
-            <v>69.429677419354846</v>
+            <v>71.441290322580642</v>
           </cell>
           <cell r="S29">
-            <v>61.612903225806448</v>
+            <v>63.935483870967744</v>
           </cell>
           <cell r="T29">
-            <v>18.64516129032258</v>
+            <v>17.64516129032258</v>
           </cell>
           <cell r="U29">
-            <v>10.516129032258064</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="V29">
-            <v>10.129032258064516</v>
+            <v>11.096774193548388</v>
           </cell>
           <cell r="W29">
             <v>0</v>
           </cell>
           <cell r="X29">
-            <v>1</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="30">
@@ -10876,73 +10771,73 @@
             <v>29</v>
           </cell>
           <cell r="B30" t="str">
-            <v>Buffalo</v>
+            <v>Seton Hall</v>
           </cell>
           <cell r="C30" t="str">
-            <v>Akron</v>
+            <v>St. John'S</v>
           </cell>
           <cell r="D30">
-            <v>-1.0571421583922851</v>
+            <v>9.7071392836284129</v>
           </cell>
           <cell r="E30">
-            <v>97.183539617052787</v>
+            <v>101.21709106603365</v>
           </cell>
           <cell r="F30">
-            <v>101.35092831730259</v>
+            <v>89.560914057491601</v>
           </cell>
           <cell r="G30">
-            <v>0.56027955736750146</v>
+            <v>0.47830923248053392</v>
           </cell>
           <cell r="H30">
-            <v>66.719999999999985</v>
+            <v>65.761290322580649</v>
           </cell>
           <cell r="I30">
-            <v>55.387096774193552</v>
+            <v>58</v>
           </cell>
           <cell r="J30">
-            <v>21.870967741935484</v>
+            <v>20.64516129032258</v>
           </cell>
           <cell r="K30">
-            <v>9.0967741935483879</v>
+            <v>12.516129032258064</v>
           </cell>
           <cell r="L30">
-            <v>10.806451612903226</v>
+            <v>11.193548387096774</v>
           </cell>
           <cell r="M30">
             <v>0</v>
           </cell>
           <cell r="N30">
-            <v>10.49945141256813</v>
+            <v>15.109788733361889</v>
           </cell>
           <cell r="O30">
-            <v>99.8801284338209</v>
+            <v>102.58678864787763</v>
           </cell>
           <cell r="P30">
-            <v>94.797305672709399</v>
+            <v>99.76074998519745</v>
           </cell>
           <cell r="Q30">
-            <v>0.59409687184661952</v>
+            <v>0.50967573221757323</v>
           </cell>
           <cell r="R30">
-            <v>71.441290322580642</v>
+            <v>70.571612903225812</v>
           </cell>
           <cell r="S30">
-            <v>63.935483870967744</v>
+            <v>61.677419354838712</v>
           </cell>
           <cell r="T30">
-            <v>17.64516129032258</v>
+            <v>26.225806451612904</v>
           </cell>
           <cell r="U30">
-            <v>11.35483870967742</v>
+            <v>13.193548387096774</v>
           </cell>
           <cell r="V30">
-            <v>11.096774193548388</v>
+            <v>10.548387096774194</v>
           </cell>
           <cell r="W30">
             <v>0</v>
           </cell>
           <cell r="X30">
-            <v>13.5</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="31">
@@ -10950,73 +10845,73 @@
             <v>30</v>
           </cell>
           <cell r="B31" t="str">
-            <v>Ohio</v>
+            <v>Miami</v>
           </cell>
           <cell r="C31" t="str">
-            <v>Kent State</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D31">
-            <v>0.8327745257037279</v>
+            <v>11.929329589884304</v>
           </cell>
           <cell r="E31">
-            <v>98.605036917163957</v>
+            <v>100.61828618286182</v>
           </cell>
           <cell r="F31">
-            <v>97.750721733641825</v>
+            <v>99.00132783057046</v>
           </cell>
           <cell r="G31">
-            <v>0.52149382052659865</v>
+            <v>0.56159225389994616</v>
           </cell>
           <cell r="H31">
-            <v>70.276129032258069</v>
+            <v>68.91096774193548</v>
           </cell>
           <cell r="I31">
-            <v>60.032258064516128</v>
+            <v>59.967741935483872</v>
           </cell>
           <cell r="J31">
-            <v>21.741935483870968</v>
+            <v>22.451612903225808</v>
           </cell>
           <cell r="K31">
-            <v>10</v>
+            <v>12.387096774193548</v>
           </cell>
           <cell r="L31">
-            <v>10.67741935483871</v>
+            <v>11.451612903225806</v>
           </cell>
           <cell r="M31">
             <v>0</v>
           </cell>
           <cell r="N31">
-            <v>4.4847029976942387</v>
+            <v>13.035509619415494</v>
           </cell>
           <cell r="O31">
-            <v>98.659971577451444</v>
+            <v>102.89121915051371</v>
           </cell>
           <cell r="P31">
-            <v>95.854047743121285</v>
+            <v>105.11224188648033</v>
           </cell>
           <cell r="Q31">
-            <v>0.53807773109243695</v>
+            <v>0.54407859798194369</v>
           </cell>
           <cell r="R31">
-            <v>73.642580645161289</v>
+            <v>67.184516129032261</v>
           </cell>
           <cell r="S31">
-            <v>61.41935483870968</v>
+            <v>60.741935483870968</v>
           </cell>
           <cell r="T31">
-            <v>26.387096774193548</v>
+            <v>20.580645161290324</v>
           </cell>
           <cell r="U31">
-            <v>12.96774193548387</v>
+            <v>13.451612903225806</v>
           </cell>
           <cell r="V31">
-            <v>13.580645161290322</v>
+            <v>10.838709677419354</v>
           </cell>
           <cell r="W31">
             <v>0</v>
           </cell>
           <cell r="X31">
-            <v>3.5</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="32">
@@ -11024,73 +10919,73 @@
             <v>31</v>
           </cell>
           <cell r="B32" t="str">
-            <v>George Washington</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="C32" t="str">
-            <v>Fordham</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D32">
-            <v>8.1181174856323501</v>
+            <v>19.724267702693741</v>
           </cell>
           <cell r="E32">
-            <v>99.423073027448609</v>
+            <v>101.38630280766203</v>
           </cell>
           <cell r="F32">
-            <v>102.88385819155521</v>
+            <v>95.516490153604366</v>
           </cell>
           <cell r="G32">
-            <v>0.55111228813559321</v>
+            <v>0.56290322580645158</v>
           </cell>
           <cell r="H32">
-            <v>70.331612903225803</v>
+            <v>67.727741935483877</v>
           </cell>
           <cell r="I32">
-            <v>60.903225806451616</v>
+            <v>60</v>
           </cell>
           <cell r="J32">
-            <v>21.35483870967742</v>
+            <v>20.93548387096774</v>
           </cell>
           <cell r="K32">
-            <v>12.741935483870968</v>
+            <v>11.806451612903226</v>
           </cell>
           <cell r="L32">
-            <v>12.774193548387096</v>
+            <v>10.32258064516129</v>
           </cell>
           <cell r="M32">
             <v>0</v>
           </cell>
           <cell r="N32">
-            <v>0.61640859402863835</v>
+            <v>23.726370739322146</v>
           </cell>
           <cell r="O32">
-            <v>101.22953110154809</v>
+            <v>101.71571463594017</v>
           </cell>
           <cell r="P32">
-            <v>103.32832155844922</v>
+            <v>98.8245285938752</v>
           </cell>
           <cell r="Q32">
-            <v>0.49542518837459631</v>
+            <v>0.54952581664910427</v>
           </cell>
           <cell r="R32">
-            <v>65.483870967741936</v>
+            <v>70.829677419354852</v>
           </cell>
           <cell r="S32">
-            <v>59.935483870967744</v>
+            <v>61.225806451612904</v>
           </cell>
           <cell r="T32">
-            <v>15.32258064516129</v>
+            <v>26.225806451612904</v>
           </cell>
           <cell r="U32">
-            <v>12.774193548387096</v>
+            <v>12.903225806451612</v>
           </cell>
           <cell r="V32">
-            <v>11.580645161290322</v>
+            <v>10.96774193548387</v>
           </cell>
           <cell r="W32">
             <v>0</v>
           </cell>
           <cell r="X32">
-            <v>-6</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="33">
@@ -11098,73 +10993,73 @@
             <v>32</v>
           </cell>
           <cell r="B33" t="str">
-            <v>St. Bonaventure</v>
+            <v>Nevada</v>
           </cell>
           <cell r="C33" t="str">
-            <v>George Mason</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D33">
-            <v>3.6587011371081828</v>
+            <v>9.2097769172278117</v>
           </cell>
           <cell r="E33">
-            <v>100.06821327722717</v>
+            <v>101.36929460580913</v>
           </cell>
           <cell r="F33">
-            <v>98.203101803703447</v>
+            <v>93.092548572138085</v>
           </cell>
           <cell r="G33">
-            <v>0.52207505518763797</v>
+            <v>0.49772598067083568</v>
           </cell>
           <cell r="H33">
-            <v>67.670666666666662</v>
+            <v>66.516129032258064</v>
           </cell>
           <cell r="I33">
-            <v>60.4</v>
+            <v>56.741935483870968</v>
           </cell>
           <cell r="J33">
-            <v>17.433333333333334</v>
+            <v>25.806451612903224</v>
           </cell>
           <cell r="K33">
-            <v>11.866666666666667</v>
+            <v>11.419354838709678</v>
           </cell>
           <cell r="L33">
-            <v>11.466666666666667</v>
+            <v>9.8387096774193541</v>
           </cell>
           <cell r="M33">
             <v>0</v>
           </cell>
           <cell r="N33">
-            <v>4.9372307624760952</v>
+            <v>16.347492910416953</v>
           </cell>
           <cell r="O33">
-            <v>97.993055555555557</v>
+            <v>99.814093598708979</v>
           </cell>
           <cell r="P33">
-            <v>105.96199138286919</v>
+            <v>89.773356716311071</v>
           </cell>
           <cell r="Q33">
-            <v>0.53668890236506972</v>
+            <v>0.57657142857142862</v>
           </cell>
           <cell r="R33">
-            <v>64.331612903225803</v>
+            <v>67.801333333333332</v>
           </cell>
           <cell r="S33">
-            <v>53.193548387096776</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="T33">
-            <v>22.967741935483872</v>
+            <v>22.2</v>
           </cell>
           <cell r="U33">
-            <v>9.612903225806452</v>
+            <v>10.766666666666667</v>
           </cell>
           <cell r="V33">
-            <v>10.64516129032258</v>
+            <v>10.466666666666667</v>
           </cell>
           <cell r="W33">
             <v>0</v>
           </cell>
           <cell r="X33">
-            <v>3.5</v>
+            <v>6.5</v>
           </cell>
         </row>
         <row r="34">
@@ -11172,73 +11067,73 @@
             <v>33</v>
           </cell>
           <cell r="B34" t="str">
-            <v>Rhode Island</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="C34" t="str">
-            <v>Duquesne</v>
+            <v>Alabama A&amp;M</v>
           </cell>
           <cell r="D34">
-            <v>2.4850838421555053</v>
+            <v>-10.748183340293197</v>
           </cell>
           <cell r="E34">
-            <v>96.572160546541426</v>
+            <v>96.942723004694827</v>
           </cell>
           <cell r="F34">
-            <v>97.687267748233438</v>
+            <v>93.291737667336207</v>
           </cell>
           <cell r="G34">
-            <v>0.4997048406139315</v>
+            <v>0.49388297872340425</v>
           </cell>
           <cell r="H34">
-            <v>66.230967741935473</v>
+            <v>74.380645161290332</v>
           </cell>
           <cell r="I34">
-            <v>54.645161290322584</v>
+            <v>60.645161290322584</v>
           </cell>
           <cell r="J34">
-            <v>21.419354838709676</v>
+            <v>26.451612903225808</v>
           </cell>
           <cell r="K34">
-            <v>10.580645161290322</v>
+            <v>10.161290322580646</v>
           </cell>
           <cell r="L34">
-            <v>12.741935483870968</v>
+            <v>12.258064516129032</v>
           </cell>
           <cell r="M34">
             <v>0</v>
           </cell>
           <cell r="N34">
-            <v>5.2557397789312335</v>
+            <v>-12.778230890104188</v>
           </cell>
           <cell r="O34">
-            <v>96.601451088316239</v>
+            <v>96.92565895642818</v>
           </cell>
           <cell r="P34">
-            <v>91.760435156727468</v>
+            <v>96.855429590956433</v>
           </cell>
           <cell r="Q34">
-            <v>0.53655854865310615</v>
+            <v>0.49847094801223241</v>
           </cell>
           <cell r="R34">
-            <v>70.832258064516139</v>
+            <v>66.989333333333335</v>
           </cell>
           <cell r="S34">
-            <v>58.677419354838712</v>
+            <v>54.5</v>
           </cell>
           <cell r="T34">
-            <v>22.419354838709676</v>
+            <v>24.066666666666666</v>
           </cell>
           <cell r="U34">
-            <v>10.548387096774194</v>
+            <v>9.3333333333333339</v>
           </cell>
           <cell r="V34">
-            <v>12.838709677419354</v>
+            <v>11.233333333333333</v>
           </cell>
           <cell r="W34">
             <v>0</v>
           </cell>
           <cell r="X34">
-            <v>2</v>
+            <v>-1.5</v>
           </cell>
         </row>
         <row r="35">
@@ -11246,1405 +11141,73 @@
             <v>34</v>
           </cell>
           <cell r="B35" t="str">
-            <v>Loyola Chicago</v>
+            <v>South Carolina State</v>
           </cell>
           <cell r="C35" t="str">
-            <v>Davidson</v>
+            <v>Howard</v>
           </cell>
           <cell r="D35">
-            <v>-4.8270734029954374</v>
+            <v>-15.059792168727887</v>
           </cell>
           <cell r="E35">
-            <v>95.812691466083152</v>
+            <v>94.89192336191384</v>
           </cell>
           <cell r="F35">
-            <v>110.4400700823726</v>
+            <v>88.02533549738591</v>
           </cell>
           <cell r="G35">
-            <v>0.4958579881656805</v>
+            <v>0.46562123039806996</v>
           </cell>
           <cell r="H35">
-            <v>65.51483870967742</v>
+            <v>68.835999999999999</v>
           </cell>
           <cell r="I35">
-            <v>54.516129032258064</v>
+            <v>55.266666666666666</v>
           </cell>
           <cell r="J35">
-            <v>18.838709677419356</v>
+            <v>22.733333333333334</v>
           </cell>
           <cell r="K35">
-            <v>10.35483870967742</v>
+            <v>11</v>
           </cell>
           <cell r="L35">
-            <v>13.064516129032258</v>
+            <v>14.566666666666666</v>
           </cell>
           <cell r="M35">
             <v>0</v>
           </cell>
           <cell r="N35">
-            <v>5.7827826511419316</v>
+            <v>-7.0667288784066029</v>
           </cell>
           <cell r="O35">
-            <v>98.650066696309466</v>
+            <v>97.771296389419689</v>
           </cell>
           <cell r="P35">
-            <v>102.50299343544884</v>
+            <v>101.22012384797286</v>
           </cell>
           <cell r="Q35">
-            <v>0.53981534910559725</v>
+            <v>0.52172686230248311</v>
           </cell>
           <cell r="R35">
-            <v>64.578064516129032</v>
+            <v>69.380645161290332</v>
           </cell>
           <cell r="S35">
-            <v>55.903225806451616</v>
+            <v>57.161290322580648</v>
           </cell>
           <cell r="T35">
-            <v>18.322580645161292</v>
+            <v>24.838709677419356</v>
           </cell>
           <cell r="U35">
-            <v>9.806451612903226</v>
+            <v>12.290322580645162</v>
           </cell>
           <cell r="V35">
-            <v>10.419354838709678</v>
+            <v>13.580645161290322</v>
           </cell>
           <cell r="W35">
             <v>0</v>
           </cell>
           <cell r="X35">
-            <v>6.5</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>35</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>NC State</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>Virginia</v>
-          </cell>
-          <cell r="D36">
-            <v>12.828546458354715</v>
-          </cell>
-          <cell r="E36">
-            <v>100.3633950900832</v>
-          </cell>
-          <cell r="F36">
-            <v>106.43023746558204</v>
-          </cell>
-          <cell r="G36">
-            <v>0.55110642781875663</v>
-          </cell>
-          <cell r="H36">
-            <v>69.812903225806451</v>
-          </cell>
-          <cell r="I36">
-            <v>61.225806451612904</v>
-          </cell>
-          <cell r="J36">
-            <v>21.129032258064516</v>
-          </cell>
-          <cell r="K36">
-            <v>10.03225806451613</v>
-          </cell>
-          <cell r="L36">
-            <v>9.32258064516129</v>
-          </cell>
-          <cell r="M36">
-            <v>0</v>
-          </cell>
-          <cell r="N36">
-            <v>13.035509619415494</v>
-          </cell>
-          <cell r="O36">
-            <v>102.89121915051371</v>
-          </cell>
-          <cell r="P36">
-            <v>105.11224188648033</v>
-          </cell>
-          <cell r="Q36">
-            <v>0.54407859798194369</v>
-          </cell>
-          <cell r="R36">
-            <v>67.184516129032261</v>
-          </cell>
-          <cell r="S36">
-            <v>60.741935483870968</v>
-          </cell>
-          <cell r="T36">
-            <v>20.580645161290324</v>
-          </cell>
-          <cell r="U36">
-            <v>13.451612903225806</v>
-          </cell>
-          <cell r="V36">
-            <v>10.838709677419354</v>
-          </cell>
-          <cell r="W36">
-            <v>0</v>
-          </cell>
-          <cell r="X36">
-            <v>5.5</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>36</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Louisville</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>Miami</v>
-          </cell>
-          <cell r="D37">
-            <v>17.621046484960765</v>
-          </cell>
-          <cell r="E37">
-            <v>99.240870005058156</v>
-          </cell>
-          <cell r="F37">
-            <v>98.862537345674525</v>
-          </cell>
-          <cell r="G37">
-            <v>0.56843209229155744</v>
-          </cell>
-          <cell r="H37">
-            <v>70.765161290322581</v>
-          </cell>
-          <cell r="I37">
-            <v>61.516129032258064</v>
-          </cell>
-          <cell r="J37">
-            <v>20.580645161290324</v>
-          </cell>
-          <cell r="K37">
-            <v>11.451612903225806</v>
-          </cell>
-          <cell r="L37">
-            <v>11.64516129032258</v>
-          </cell>
-          <cell r="M37">
-            <v>0</v>
-          </cell>
-          <cell r="N37">
-            <v>11.929329589884304</v>
-          </cell>
-          <cell r="O37">
-            <v>100.61828618286182</v>
-          </cell>
-          <cell r="P37">
-            <v>99.00132783057046</v>
-          </cell>
-          <cell r="Q37">
-            <v>0.56159225389994616</v>
-          </cell>
-          <cell r="R37">
-            <v>68.91096774193548</v>
-          </cell>
-          <cell r="S37">
-            <v>59.967741935483872</v>
-          </cell>
-          <cell r="T37">
-            <v>22.451612903225808</v>
-          </cell>
-          <cell r="U37">
-            <v>12.387096774193548</v>
-          </cell>
-          <cell r="V37">
-            <v>11.451612903225806</v>
-          </cell>
-          <cell r="W37">
-            <v>0</v>
-          </cell>
-          <cell r="X37">
-            <v>-2.5</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>37</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Providence</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>St. John's</v>
-          </cell>
-          <cell r="D38">
-            <v>7.2230139841859584</v>
-          </cell>
-          <cell r="E38">
-            <v>97.978328173374621</v>
-          </cell>
-          <cell r="F38">
-            <v>103.93584445667233</v>
-          </cell>
-          <cell r="G38">
-            <v>0.54862194487779514</v>
-          </cell>
-          <cell r="H38">
-            <v>73.363870967741946</v>
-          </cell>
-          <cell r="I38">
-            <v>62.032258064516128</v>
-          </cell>
-          <cell r="J38">
-            <v>22.967741935483872</v>
-          </cell>
-          <cell r="K38">
-            <v>11.290322580645162</v>
-          </cell>
-          <cell r="L38">
-            <v>12.516129032258064</v>
-          </cell>
-          <cell r="M38">
-            <v>0</v>
-          </cell>
-          <cell r="N38">
-            <v>15.109788733361889</v>
-          </cell>
-          <cell r="O38">
-            <v>102.58678864787763</v>
-          </cell>
-          <cell r="P38">
-            <v>99.76074998519745</v>
-          </cell>
-          <cell r="Q38">
-            <v>0.50967573221757323</v>
-          </cell>
-          <cell r="R38">
-            <v>70.571612903225812</v>
-          </cell>
-          <cell r="S38">
-            <v>61.677419354838712</v>
-          </cell>
-          <cell r="T38">
-            <v>26.225806451612904</v>
-          </cell>
-          <cell r="U38">
-            <v>13.193548387096774</v>
-          </cell>
-          <cell r="V38">
-            <v>10.548387096774194</v>
-          </cell>
-          <cell r="W38">
-            <v>0</v>
-          </cell>
-          <cell r="X38">
-            <v>10.5</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>38</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>Creighton</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>Seton Hall</v>
-          </cell>
-          <cell r="D39">
-            <v>7.0331892521354531</v>
-          </cell>
-          <cell r="E39">
-            <v>96.994313914816004</v>
-          </cell>
-          <cell r="F39">
-            <v>106.9382662201575</v>
-          </cell>
-          <cell r="G39">
-            <v>0.53549972692517744</v>
-          </cell>
-          <cell r="H39">
-            <v>68.12516129032258</v>
-          </cell>
-          <cell r="I39">
-            <v>59.064516129032256</v>
-          </cell>
-          <cell r="J39">
-            <v>16.193548387096776</v>
-          </cell>
-          <cell r="K39">
-            <v>9.4516129032258061</v>
-          </cell>
-          <cell r="L39">
-            <v>11.387096774193548</v>
-          </cell>
-          <cell r="M39">
-            <v>0</v>
-          </cell>
-          <cell r="N39">
-            <v>9.7071392836284129</v>
-          </cell>
-          <cell r="O39">
-            <v>101.21709106603365</v>
-          </cell>
-          <cell r="P39">
-            <v>89.560914057491601</v>
-          </cell>
-          <cell r="Q39">
-            <v>0.47830923248053392</v>
-          </cell>
-          <cell r="R39">
-            <v>65.761290322580649</v>
-          </cell>
-          <cell r="S39">
-            <v>58</v>
-          </cell>
-          <cell r="T39">
-            <v>20.64516129032258</v>
-          </cell>
-          <cell r="U39">
-            <v>12.516129032258064</v>
-          </cell>
-          <cell r="V39">
-            <v>11.193548387096774</v>
-          </cell>
-          <cell r="W39">
-            <v>0</v>
-          </cell>
-          <cell r="X39">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>39</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Iowa</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>Ohio State</v>
-          </cell>
-          <cell r="D40">
-            <v>16.132747635538259</v>
-          </cell>
-          <cell r="E40">
-            <v>98.481116025859137</v>
-          </cell>
-          <cell r="F40">
-            <v>91.651955607786036</v>
-          </cell>
-          <cell r="G40">
-            <v>0.56339285714285714</v>
-          </cell>
-          <cell r="H40">
-            <v>63.050322580645158</v>
-          </cell>
-          <cell r="I40">
-            <v>54.193548387096776</v>
-          </cell>
-          <cell r="J40">
-            <v>18.516129032258064</v>
-          </cell>
-          <cell r="K40">
-            <v>8.935483870967742</v>
-          </cell>
-          <cell r="L40">
-            <v>9.6451612903225801</v>
-          </cell>
-          <cell r="M40">
-            <v>0</v>
-          </cell>
-          <cell r="N40">
-            <v>14.643537446231871</v>
-          </cell>
-          <cell r="O40">
-            <v>97.86818231500709</v>
-          </cell>
-          <cell r="P40">
-            <v>101.49670801900939</v>
-          </cell>
-          <cell r="Q40">
-            <v>0.56910809214412283</v>
-          </cell>
-          <cell r="R40">
-            <v>66.990666666666669</v>
-          </cell>
-          <cell r="S40">
-            <v>56.43333333333333</v>
-          </cell>
-          <cell r="T40">
-            <v>21.266666666666666</v>
-          </cell>
-          <cell r="U40">
-            <v>9.1666666666666661</v>
-          </cell>
-          <cell r="V40">
-            <v>10.366666666666667</v>
-          </cell>
-          <cell r="W40">
-            <v>0</v>
-          </cell>
-          <cell r="X40">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>40</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Washington</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>Wisconsin</v>
-          </cell>
-          <cell r="D41">
-            <v>11.573237900042043</v>
-          </cell>
-          <cell r="E41">
-            <v>100.95814989656817</v>
-          </cell>
-          <cell r="F41">
-            <v>98.788425473817696</v>
-          </cell>
-          <cell r="G41">
-            <v>0.51374933897408781</v>
-          </cell>
-          <cell r="H41">
-            <v>68.007741935483864</v>
-          </cell>
-          <cell r="I41">
-            <v>61</v>
-          </cell>
-          <cell r="J41">
-            <v>18.419354838709676</v>
-          </cell>
-          <cell r="K41">
-            <v>11.67741935483871</v>
-          </cell>
-          <cell r="L41">
-            <v>10.580645161290322</v>
-          </cell>
-          <cell r="M41">
-            <v>0</v>
-          </cell>
-          <cell r="N41">
-            <v>15.99115140253407</v>
-          </cell>
-          <cell r="O41">
-            <v>101.25838978230519</v>
-          </cell>
-          <cell r="P41">
-            <v>98.106398085976267</v>
-          </cell>
-          <cell r="Q41">
-            <v>0.54685863874345553</v>
-          </cell>
-          <cell r="R41">
-            <v>69.153548387096777</v>
-          </cell>
-          <cell r="S41">
-            <v>61.612903225806448</v>
-          </cell>
-          <cell r="T41">
-            <v>20.29032258064516</v>
-          </cell>
-          <cell r="U41">
-            <v>10.419354838709678</v>
-          </cell>
-          <cell r="V41">
-            <v>9.0322580645161299</v>
-          </cell>
-          <cell r="W41">
-            <v>0</v>
-          </cell>
-          <cell r="X41">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>41</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Kentucky</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>Missouri</v>
-          </cell>
-          <cell r="D42">
-            <v>18.55702494743041</v>
-          </cell>
-          <cell r="E42">
-            <v>101.42630906768839</v>
-          </cell>
-          <cell r="F42">
-            <v>97.25385817981919</v>
-          </cell>
-          <cell r="G42">
-            <v>0.53432676955827563</v>
-          </cell>
-          <cell r="H42">
-            <v>69.038709677419348</v>
-          </cell>
-          <cell r="I42">
-            <v>60.612903225806448</v>
-          </cell>
-          <cell r="J42">
-            <v>22.741935483870968</v>
-          </cell>
-          <cell r="K42">
-            <v>12.258064516129032</v>
-          </cell>
-          <cell r="L42">
-            <v>10.67741935483871</v>
-          </cell>
-          <cell r="M42">
-            <v>0</v>
-          </cell>
-          <cell r="N42">
-            <v>12.160899195127248</v>
-          </cell>
-          <cell r="O42">
-            <v>98.568347897184324</v>
-          </cell>
-          <cell r="P42">
-            <v>95.041322915195849</v>
-          </cell>
-          <cell r="Q42">
-            <v>0.55426794799321655</v>
-          </cell>
-          <cell r="R42">
-            <v>68.369032258064522</v>
-          </cell>
-          <cell r="S42">
-            <v>57.064516129032256</v>
-          </cell>
-          <cell r="T42">
-            <v>24.225806451612904</v>
-          </cell>
-          <cell r="U42">
-            <v>11.64516129032258</v>
-          </cell>
-          <cell r="V42">
-            <v>12.290322580645162</v>
-          </cell>
-          <cell r="W42">
-            <v>0</v>
-          </cell>
-          <cell r="X42">
-            <v>-3</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>42</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Auburn</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>Tennessee</v>
-          </cell>
-          <cell r="D43">
-            <v>17.579382543026234</v>
-          </cell>
-          <cell r="E43">
-            <v>103.12857214353635</v>
-          </cell>
-          <cell r="F43">
-            <v>92.623653201414598</v>
-          </cell>
-          <cell r="G43">
-            <v>0.52776280323450131</v>
-          </cell>
-          <cell r="H43">
-            <v>68.739354838709673</v>
-          </cell>
-          <cell r="I43">
-            <v>59.838709677419352</v>
-          </cell>
-          <cell r="J43">
-            <v>27.193548387096776</v>
-          </cell>
-          <cell r="K43">
-            <v>13.35483870967742</v>
-          </cell>
-          <cell r="L43">
-            <v>10.290322580645162</v>
-          </cell>
-          <cell r="M43">
-            <v>0</v>
-          </cell>
-          <cell r="N43">
-            <v>20.649012498581907</v>
-          </cell>
-          <cell r="O43">
-            <v>104.63085785458507</v>
-          </cell>
-          <cell r="P43">
-            <v>93.935133911329061</v>
-          </cell>
-          <cell r="Q43">
-            <v>0.52050473186119872</v>
-          </cell>
-          <cell r="R43">
-            <v>67.552258064516124</v>
-          </cell>
-          <cell r="S43">
-            <v>61.354838709677416</v>
-          </cell>
-          <cell r="T43">
-            <v>23.322580645161292</v>
-          </cell>
-          <cell r="U43">
-            <v>16</v>
-          </cell>
-          <cell r="V43">
-            <v>11.935483870967742</v>
-          </cell>
-          <cell r="W43">
-            <v>0</v>
-          </cell>
-          <cell r="X43">
-            <v>5.5</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>43</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Iowa State</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>Texas Tech</v>
-          </cell>
-          <cell r="D44">
-            <v>19.724267702693741</v>
-          </cell>
-          <cell r="E44">
-            <v>101.38630280766203</v>
-          </cell>
-          <cell r="F44">
-            <v>95.516490153604366</v>
-          </cell>
-          <cell r="G44">
-            <v>0.56290322580645158</v>
-          </cell>
-          <cell r="H44">
-            <v>67.727741935483877</v>
-          </cell>
-          <cell r="I44">
-            <v>60</v>
-          </cell>
-          <cell r="J44">
-            <v>20.93548387096774</v>
-          </cell>
-          <cell r="K44">
-            <v>11.806451612903226</v>
-          </cell>
-          <cell r="L44">
-            <v>10.32258064516129</v>
-          </cell>
-          <cell r="M44">
-            <v>0</v>
-          </cell>
-          <cell r="N44">
-            <v>17.917409465972611</v>
-          </cell>
-          <cell r="O44">
-            <v>100.6715030361653</v>
-          </cell>
-          <cell r="P44">
-            <v>103.12783146278295</v>
-          </cell>
-          <cell r="Q44">
-            <v>0.56585879873551104</v>
-          </cell>
-          <cell r="R44">
-            <v>67.753548387096771</v>
-          </cell>
-          <cell r="S44">
-            <v>61.225806451612904</v>
-          </cell>
-          <cell r="T44">
-            <v>16.741935483870968</v>
-          </cell>
-          <cell r="U44">
-            <v>11.67741935483871</v>
-          </cell>
-          <cell r="V44">
-            <v>10.838709677419354</v>
-          </cell>
-          <cell r="W44">
-            <v>0</v>
-          </cell>
-          <cell r="X44">
-            <v>-5</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>44</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>UCF</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>Arizona</v>
-          </cell>
-          <cell r="D45">
-            <v>12.68819911571482</v>
-          </cell>
-          <cell r="E45">
-            <v>100.7354909489852</v>
-          </cell>
-          <cell r="F45">
-            <v>98.072123997625383</v>
-          </cell>
-          <cell r="G45">
-            <v>0.53966942148760333</v>
-          </cell>
-          <cell r="H45">
-            <v>70.147586206896563</v>
-          </cell>
-          <cell r="I45">
-            <v>62.586206896551722</v>
-          </cell>
-          <cell r="J45">
-            <v>19.379310344827587</v>
-          </cell>
-          <cell r="K45">
-            <v>12.172413793103448</v>
-          </cell>
-          <cell r="L45">
-            <v>11.206896551724139</v>
-          </cell>
-          <cell r="M45">
-            <v>0</v>
-          </cell>
-          <cell r="N45">
-            <v>23.726370739322146</v>
-          </cell>
-          <cell r="O45">
-            <v>101.71571463594017</v>
-          </cell>
-          <cell r="P45">
-            <v>98.8245285938752</v>
-          </cell>
-          <cell r="Q45">
-            <v>0.54952581664910427</v>
-          </cell>
-          <cell r="R45">
-            <v>70.829677419354852</v>
-          </cell>
-          <cell r="S45">
-            <v>61.225806451612904</v>
-          </cell>
-          <cell r="T45">
-            <v>26.225806451612904</v>
-          </cell>
-          <cell r="U45">
-            <v>12.903225806451612</v>
-          </cell>
-          <cell r="V45">
-            <v>10.96774193548387</v>
-          </cell>
-          <cell r="W45">
-            <v>0</v>
-          </cell>
-          <cell r="X45">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>45</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>UNLV</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>Utah State</v>
-          </cell>
-          <cell r="D46">
-            <v>8.1833176881236689</v>
-          </cell>
-          <cell r="E46">
-            <v>98.332117488961416</v>
-          </cell>
-          <cell r="F46">
-            <v>88.010291760587222</v>
-          </cell>
-          <cell r="G46">
-            <v>0.53103629668595476</v>
-          </cell>
-          <cell r="H46">
-            <v>70.896249999999995</v>
-          </cell>
-          <cell r="I46">
-            <v>59.40625</v>
-          </cell>
-          <cell r="J46">
-            <v>24.125</v>
-          </cell>
-          <cell r="K46">
-            <v>11.03125</v>
-          </cell>
-          <cell r="L46">
-            <v>11.90625</v>
-          </cell>
-          <cell r="M46">
-            <v>0</v>
-          </cell>
-          <cell r="N46">
-            <v>16.347492910416953</v>
-          </cell>
-          <cell r="O46">
-            <v>99.814093598708979</v>
-          </cell>
-          <cell r="P46">
-            <v>89.773356716311071</v>
-          </cell>
-          <cell r="Q46">
-            <v>0.57657142857142862</v>
-          </cell>
-          <cell r="R46">
-            <v>67.801333333333332</v>
-          </cell>
-          <cell r="S46">
-            <v>58.333333333333336</v>
-          </cell>
-          <cell r="T46">
-            <v>22.2</v>
-          </cell>
-          <cell r="U46">
-            <v>10.766666666666667</v>
-          </cell>
-          <cell r="V46">
-            <v>10.466666666666667</v>
-          </cell>
-          <cell r="W46">
-            <v>0</v>
-          </cell>
-          <cell r="X46">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>46</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Middle Tennessee</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>Louisiana Tech</v>
-          </cell>
-          <cell r="D47">
-            <v>7.273503348238739</v>
-          </cell>
-          <cell r="E47">
-            <v>99.424133027021128</v>
-          </cell>
-          <cell r="F47">
-            <v>99.488720427804381</v>
-          </cell>
-          <cell r="G47">
-            <v>0.52200557103064071</v>
-          </cell>
-          <cell r="H47">
-            <v>68.084000000000003</v>
-          </cell>
-          <cell r="I47">
-            <v>59.833333333333336</v>
-          </cell>
-          <cell r="J47">
-            <v>18.600000000000001</v>
-          </cell>
-          <cell r="K47">
-            <v>11.266666666666667</v>
-          </cell>
-          <cell r="L47">
-            <v>11.333333333333334</v>
-          </cell>
-          <cell r="M47">
-            <v>0</v>
-          </cell>
-          <cell r="N47">
-            <v>2.6443345975686983</v>
-          </cell>
-          <cell r="O47">
-            <v>99.919161188678217</v>
-          </cell>
-          <cell r="P47">
-            <v>98.415627483867411</v>
-          </cell>
-          <cell r="Q47">
-            <v>0.49525669642857145</v>
-          </cell>
-          <cell r="R47">
-            <v>65.900645161290328</v>
-          </cell>
-          <cell r="S47">
-            <v>57.806451612903224</v>
-          </cell>
-          <cell r="T47">
-            <v>19.129032258064516</v>
-          </cell>
-          <cell r="U47">
-            <v>12.96774193548387</v>
-          </cell>
-          <cell r="V47">
-            <v>12.64516129032258</v>
-          </cell>
-          <cell r="W47">
-            <v>0</v>
-          </cell>
-          <cell r="X47">
-            <v>-1.5</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>47</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Kennesaw State</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>Western Kentucky</v>
-          </cell>
-          <cell r="D48">
-            <v>6.490752715038262</v>
-          </cell>
-          <cell r="E48">
-            <v>101.8432322449375</v>
-          </cell>
-          <cell r="F48">
-            <v>97.141081053482708</v>
-          </cell>
-          <cell r="G48">
-            <v>0.52519480519480521</v>
-          </cell>
-          <cell r="H48">
-            <v>71.699354838709667</v>
-          </cell>
-          <cell r="I48">
-            <v>62.096774193548384</v>
-          </cell>
-          <cell r="J48">
-            <v>26.516129032258064</v>
-          </cell>
-          <cell r="K48">
-            <v>13.806451612903226</v>
-          </cell>
-          <cell r="L48">
-            <v>11.741935483870968</v>
-          </cell>
-          <cell r="M48">
-            <v>0</v>
-          </cell>
-          <cell r="N48">
-            <v>5.5553615261544227</v>
-          </cell>
-          <cell r="O48">
-            <v>102.21523481083274</v>
-          </cell>
-          <cell r="P48">
-            <v>102.35314169399868</v>
-          </cell>
-          <cell r="Q48">
-            <v>0.48414830736163356</v>
-          </cell>
-          <cell r="R48">
-            <v>70.993333333333339</v>
-          </cell>
-          <cell r="S48">
-            <v>62.033333333333331</v>
-          </cell>
-          <cell r="T48">
-            <v>25.666666666666668</v>
-          </cell>
-          <cell r="U48">
-            <v>12.766666666666667</v>
-          </cell>
-          <cell r="V48">
-            <v>10.433333333333334</v>
-          </cell>
-          <cell r="W48">
-            <v>0</v>
-          </cell>
-          <cell r="X48">
-            <v>1.5</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>48</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>Southern Utah</v>
-          </cell>
-          <cell r="C49" t="str">
-            <v>UT Arlington</v>
-          </cell>
-          <cell r="D49">
-            <v>0.10290105788384882</v>
-          </cell>
-          <cell r="E49">
-            <v>94.858918582970801</v>
-          </cell>
-          <cell r="F49">
-            <v>96.529523762300542</v>
-          </cell>
-          <cell r="G49">
-            <v>0.52679075014100396</v>
-          </cell>
-          <cell r="H49">
-            <v>71.692000000000007</v>
-          </cell>
-          <cell r="I49">
-            <v>59.1</v>
-          </cell>
-          <cell r="J49">
-            <v>20.133333333333333</v>
-          </cell>
-          <cell r="K49">
-            <v>10.433333333333334</v>
-          </cell>
-          <cell r="L49">
-            <v>14.166666666666666</v>
-          </cell>
-          <cell r="M49">
-            <v>0</v>
-          </cell>
-          <cell r="N49">
-            <v>3.3990966185562335</v>
-          </cell>
-          <cell r="O49">
-            <v>96.820667384284164</v>
-          </cell>
-          <cell r="P49">
-            <v>94.886171282090174</v>
-          </cell>
-          <cell r="Q49">
-            <v>0.4855159927579964</v>
-          </cell>
-          <cell r="R49">
-            <v>67.382666666666665</v>
-          </cell>
-          <cell r="S49">
-            <v>55.233333333333334</v>
-          </cell>
-          <cell r="T49">
-            <v>23.066666666666666</v>
-          </cell>
-          <cell r="U49">
-            <v>12.1</v>
-          </cell>
-          <cell r="V49">
-            <v>14.1</v>
-          </cell>
-          <cell r="W49">
-            <v>0</v>
-          </cell>
-          <cell r="X49">
-            <v>5.5</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>49</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>Alabama A&amp;M</v>
-          </cell>
-          <cell r="C50" t="str">
-            <v>Texas Southern</v>
-          </cell>
-          <cell r="D50">
-            <v>-12.778230890104188</v>
-          </cell>
-          <cell r="E50">
-            <v>96.92565895642818</v>
-          </cell>
-          <cell r="F50">
-            <v>96.855429590956433</v>
-          </cell>
-          <cell r="G50">
-            <v>0.49847094801223241</v>
-          </cell>
-          <cell r="H50">
-            <v>66.989333333333335</v>
-          </cell>
-          <cell r="I50">
-            <v>54.5</v>
-          </cell>
-          <cell r="J50">
-            <v>24.066666666666666</v>
-          </cell>
-          <cell r="K50">
-            <v>9.3333333333333339</v>
-          </cell>
-          <cell r="L50">
-            <v>11.233333333333333</v>
-          </cell>
-          <cell r="M50">
-            <v>0</v>
-          </cell>
-          <cell r="N50">
-            <v>-12.77273260985422</v>
-          </cell>
-          <cell r="O50">
-            <v>95.293918203009113</v>
-          </cell>
-          <cell r="P50">
-            <v>98.078075334634491</v>
-          </cell>
-          <cell r="Q50">
-            <v>0.5056179775280899</v>
-          </cell>
-          <cell r="R50">
-            <v>71.582068965517237</v>
-          </cell>
-          <cell r="S50">
-            <v>58.310344827586206</v>
-          </cell>
-          <cell r="T50">
-            <v>22.482758620689655</v>
-          </cell>
-          <cell r="U50">
-            <v>10.172413793103448</v>
-          </cell>
-          <cell r="V50">
-            <v>13.551724137931034</v>
-          </cell>
-          <cell r="W50">
-            <v>0</v>
-          </cell>
-          <cell r="X50">
-            <v>-1</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>50</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>Arkansas-Pine Bluff</v>
-          </cell>
-          <cell r="C51" t="str">
-            <v>Southern</v>
-          </cell>
-          <cell r="D51">
-            <v>-12.958561275000525</v>
-          </cell>
-          <cell r="E51">
-            <v>95.393026941362919</v>
-          </cell>
-          <cell r="F51">
-            <v>98.671403378251426</v>
-          </cell>
-          <cell r="G51">
-            <v>0.51358695652173914</v>
-          </cell>
-          <cell r="H51">
-            <v>72.10193548387096</v>
-          </cell>
-          <cell r="I51">
-            <v>59.354838709677416</v>
-          </cell>
-          <cell r="J51">
-            <v>21.419354838709676</v>
-          </cell>
-          <cell r="K51">
-            <v>10.290322580645162</v>
-          </cell>
-          <cell r="L51">
-            <v>13.612903225806452</v>
-          </cell>
-          <cell r="M51">
-            <v>0</v>
-          </cell>
-          <cell r="N51">
-            <v>-6.7092460643817606</v>
-          </cell>
-          <cell r="O51">
-            <v>99.018646109371232</v>
-          </cell>
-          <cell r="P51">
-            <v>93.207129449722274</v>
-          </cell>
-          <cell r="Q51">
-            <v>0.50943396226415094</v>
-          </cell>
-          <cell r="R51">
-            <v>72.842580645161291</v>
-          </cell>
-          <cell r="S51">
-            <v>61.548387096774192</v>
-          </cell>
-          <cell r="T51">
-            <v>24.93548387096774</v>
-          </cell>
-          <cell r="U51">
-            <v>11.67741935483871</v>
-          </cell>
-          <cell r="V51">
-            <v>12</v>
-          </cell>
-          <cell r="W51">
-            <v>0</v>
-          </cell>
-          <cell r="X51">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>51</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>South Carolina State</v>
-          </cell>
-          <cell r="C52" t="str">
-            <v>Norfolk State</v>
-          </cell>
-          <cell r="D52">
-            <v>-15.059792168727887</v>
-          </cell>
-          <cell r="E52">
-            <v>94.89192336191384</v>
-          </cell>
-          <cell r="F52">
-            <v>88.02533549738591</v>
-          </cell>
-          <cell r="G52">
-            <v>0.46562123039806996</v>
-          </cell>
-          <cell r="H52">
-            <v>68.835999999999999</v>
-          </cell>
-          <cell r="I52">
-            <v>55.266666666666666</v>
-          </cell>
-          <cell r="J52">
-            <v>22.733333333333334</v>
-          </cell>
-          <cell r="K52">
-            <v>11</v>
-          </cell>
-          <cell r="L52">
-            <v>14.566666666666666</v>
-          </cell>
-          <cell r="M52">
-            <v>0</v>
-          </cell>
-          <cell r="N52">
-            <v>-8.7139195057519103</v>
-          </cell>
-          <cell r="O52">
-            <v>98.578119467907541</v>
-          </cell>
-          <cell r="P52">
-            <v>98.49546939189942</v>
-          </cell>
-          <cell r="Q52">
-            <v>0.51537171604248189</v>
-          </cell>
-          <cell r="R52">
-            <v>69.099354838709672</v>
-          </cell>
-          <cell r="S52">
-            <v>57.70967741935484</v>
-          </cell>
-          <cell r="T52">
-            <v>24.419354838709676</v>
-          </cell>
-          <cell r="U52">
-            <v>11.483870967741936</v>
-          </cell>
-          <cell r="V52">
-            <v>12.129032258064516</v>
-          </cell>
-          <cell r="W52">
-            <v>0</v>
-          </cell>
-          <cell r="X52">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>52</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>Maryland-Eastern Shore</v>
-          </cell>
-          <cell r="C53" t="str">
-            <v>North Carolina Central</v>
-          </cell>
-          <cell r="D53">
-            <v>-15.054111575487484</v>
-          </cell>
-          <cell r="E53">
-            <v>92.100589740736609</v>
-          </cell>
-          <cell r="F53">
-            <v>99.022221353495468</v>
-          </cell>
-          <cell r="G53">
-            <v>0.49519230769230771</v>
-          </cell>
-          <cell r="H53">
-            <v>65.824516129032261</v>
-          </cell>
-          <cell r="I53">
-            <v>53.677419354838712</v>
-          </cell>
-          <cell r="J53">
-            <v>15.290322580645162</v>
-          </cell>
-          <cell r="K53">
-            <v>10.32258064516129</v>
-          </cell>
-          <cell r="L53">
-            <v>15.741935483870968</v>
-          </cell>
-          <cell r="M53">
-            <v>0</v>
-          </cell>
-          <cell r="N53">
-            <v>-12.049706064548028</v>
-          </cell>
-          <cell r="O53">
-            <v>97.391178918169217</v>
-          </cell>
-          <cell r="P53">
-            <v>102.17668911130822</v>
-          </cell>
-          <cell r="Q53">
-            <v>0.49514563106796117</v>
-          </cell>
-          <cell r="R53">
-            <v>68.108965517241387</v>
-          </cell>
-          <cell r="S53">
-            <v>56.827586206896555</v>
-          </cell>
-          <cell r="T53">
-            <v>22.03448275862069</v>
-          </cell>
-          <cell r="U53">
-            <v>10.689655172413794</v>
-          </cell>
-          <cell r="V53">
-            <v>12.275862068965518</v>
-          </cell>
-          <cell r="W53">
-            <v>0</v>
-          </cell>
-          <cell r="X53">
-            <v>1.5</v>
+            <v>15</v>
           </cell>
         </row>
       </sheetData>
@@ -21464,46 +20027,46 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Davidson</v>
+        <v>Missouri State</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Loyola Chicago</v>
+        <v>Louisiana Tech</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>B2</f>
-        <v>Davidson</v>
+        <v>Missouri State</v>
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.669605825431679</v>
+        <v>3.1421879785812341</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>6.5</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.76503986048856765</v>
+        <v>0.37265385549244079</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>8.5987347952965434E-2</v>
+        <v>4.5881118354284427E-2</v>
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>6.5901902246003077E-2</v>
+        <v>4.3114271792206997E-2</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="K2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
-        <v>1.2898102192944816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -21512,87 +20075,55 @@
       </c>
       <c r="B3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>North Carolina Central</v>
+        <v>Tennessee</v>
       </c>
       <c r="C3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Maryland-Eastern Shore</v>
+        <v>Vanderbilt</v>
       </c>
       <c r="D3" s="6" t="str">
         <f t="shared" ref="D3:D4" si="0">B3</f>
-        <v>North Carolina Central</v>
+        <v>Tennessee</v>
       </c>
       <c r="E3" s="5">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>6.1257329326571277</v>
+        <v>3.1650827197892308</v>
       </c>
       <c r="F3" s="5">
         <f>-VLOOKUP(A3,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.46129250554468809</v>
+        <v>0.37465373235659188</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>4.5550631737442553E-2</v>
+        <v>4.6340777072442073E-2</v>
       </c>
       <c r="I3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.2926495305365124E-2</v>
+        <v>4.3375441518432999E-2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="K3" s="9">
         <f t="shared" ref="K3:K4" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
-        <v>0</v>
+        <v>0.69511165608663106</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>36</v>
-      </c>
-      <c r="B4" s="6" t="str">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Louisville</v>
-      </c>
-      <c r="C4" s="6" t="str">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Miami</v>
-      </c>
-      <c r="D4" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Louisville</v>
-      </c>
-      <c r="E4" s="5">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.2253929834058637</v>
-      </c>
-      <c r="F4" s="5">
-        <f>-VLOOKUP(A4,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>2.5</v>
-      </c>
-      <c r="G4" s="7">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.49643981009159899</v>
-      </c>
-      <c r="H4" s="7">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>4.6148053121672909E-2</v>
-      </c>
-      <c r="I4" s="7">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.3265939273677723E-2</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="K4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E5" s="10"/>
@@ -21772,7 +20303,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49754F4-77C8-5D43-B0D7-0D09062FB370}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1"/>
@@ -21815,15 +20346,15 @@
       </c>
       <c r="B2" s="1">
         <f>COUNTIF($C$6:$C$150,"L")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="13">
         <f>SUM(E6:E13)/SUM(D6:D13)</f>
-        <v>-0.1128415788533666</v>
+        <v>-0.37626460284041197</v>
       </c>
       <c r="D2" s="14">
         <f>AVERAGE(G6:G150)</f>
-        <v>2.5431238755099773E-2</v>
+        <v>1.2346518407494022E-2</v>
       </c>
       <c r="E2" s="1">
         <v>2</v>
@@ -22074,6 +20605,56 @@
       </c>
       <c r="N9" s="1">
         <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.2898000000000001</v>
+      </c>
+      <c r="E10" s="15">
+        <f>IF(C10="P",0,IF(C10="L",-D10,IF(I10&lt;0,D10*(100/-I10),D10*(I10/100)))/1)</f>
+        <v>-1.2898000000000001</v>
+      </c>
+      <c r="F10" s="15">
+        <f>E10+F9</f>
+        <v>-1.6344181818181815</v>
+      </c>
+      <c r="G10" s="11">
+        <f>((K10-N10)*3.55%)+(M10-J10)</f>
+        <v>-3.9992362982928985E-2</v>
+      </c>
+      <c r="H10" s="11">
+        <f>AVERAGE($G$6:G10)</f>
+        <v>1.2346518407494022E-2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-112</v>
+      </c>
+      <c r="J10" s="13">
+        <f>IF(I10&lt;0,I10/(I10-100),100/(I10+100))</f>
+        <v>0.52830188679245282</v>
+      </c>
+      <c r="K10" s="1">
+        <v>-6.5</v>
+      </c>
+      <c r="L10" s="1">
+        <v>-110</v>
+      </c>
+      <c r="M10" s="13">
+        <f>IF(L10&lt;0,L10/(L10-100),100/(L10+100))</f>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="N10" s="1">
+        <v>-5.5</v>
       </c>
     </row>
   </sheetData>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3572140-CFF3-B942-9DE1-42EEC952A7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ED0A33-6890-7648-AB8B-B22F2979A763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="26480" windowHeight="20020" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="26480" windowHeight="20020" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -20360,7 +20360,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F61EA5D-A4DD-9846-B64D-AF1C35AA234F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC96171-BDE1-4147-A4AC-21721A12FFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="26480" windowHeight="20020" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="17200" windowHeight="20020" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="440">
   <si>
     <t>Team</t>
   </si>
@@ -1338,6 +1338,33 @@
   </si>
   <si>
     <t>03/12/2026</t>
+  </si>
+  <si>
+    <t>03/13/2026</t>
+  </si>
+  <si>
+    <t>Matchup</t>
+  </si>
+  <si>
+    <t>MST/LT</t>
+  </si>
+  <si>
+    <t>TENN/VAN</t>
+  </si>
+  <si>
+    <t>DAV/LOY</t>
+  </si>
+  <si>
+    <t>XU/MARQ</t>
+  </si>
+  <si>
+    <t>WAKE/VT</t>
+  </si>
+  <si>
+    <t>WEB/EWASH</t>
+  </si>
+  <si>
+    <t>ILL/MD</t>
   </si>
 </sst>
 </file>
@@ -26069,7 +26096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49754F4-77C8-5D43-B0D7-0D09062FB370}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1"/>
@@ -26077,14 +26104,14 @@
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>388</v>
       </c>
@@ -26105,31 +26132,31 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f>COUNTIF($C$6:$C$150,"W")</f>
         <v>2</v>
       </c>
       <c r="B2" s="1">
         <f>COUNTIF($C$6:$C$150,"L")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="13">
-        <f>SUM(E6:E13)/SUM(D6:D13)</f>
-        <v>-0.37626460284041197</v>
+        <f>SUM(F6:F13)/SUM(E6:E13)</f>
+        <v>-0.52691906581309589</v>
       </c>
       <c r="D2" s="14">
-        <f>AVERAGE(G6:G150)</f>
-        <v>1.2346518407494022E-2</v>
+        <f>AVERAGE(H6:H150)</f>
+        <v>4.1788135989584758E-2</v>
       </c>
       <c r="E2" s="1">
         <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -26140,40 +26167,46 @@
         <v>398</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>424</v>
       </c>
@@ -26183,47 +26216,53 @@
       <c r="C6" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6" s="1">
         <v>0.94499999999999995</v>
       </c>
-      <c r="E6" s="15">
-        <f>IF(C6="P",0,IF(C6="L",-D6,IF(I6&lt;0,D6*(100/-I6),D6*(I6/100)))/1)</f>
+      <c r="F6" s="15">
+        <f>IF(C6="P",0,IF(C6="L",-E6,IF(K6&lt;0,E6*(100/-K6),E6*(K6/100)))/1)</f>
         <v>-0.94499999999999995</v>
       </c>
-      <c r="F6" s="15">
-        <f>E6</f>
+      <c r="G6" s="15">
+        <f>F6</f>
         <v>-0.94499999999999995</v>
       </c>
-      <c r="G6" s="11">
-        <f>((K6-N6)*3.55%)+(M6-J6)</f>
+      <c r="H6" s="11">
+        <f>((M6-P6)*3.55%)+(O6-L6)</f>
         <v>-1.9985536081552357E-2</v>
       </c>
-      <c r="H6" s="11">
-        <f>G6</f>
+      <c r="I6" s="11">
+        <f>H6</f>
         <v>-1.9985536081552357E-2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K6" s="1">
         <v>-112</v>
       </c>
-      <c r="J6" s="13">
-        <f>IF(I6&lt;0,I6/(I6-100),100/(I6+100))</f>
+      <c r="L6" s="13">
+        <f>IF(K6&lt;0,K6/(K6-100),100/(K6+100))</f>
         <v>0.52830188679245282</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>-14.5</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>-111</v>
       </c>
-      <c r="M6" s="13">
-        <f>IF(L6&lt;0,L6/(L6-100),100/(L6+100))</f>
+      <c r="O6" s="13">
+        <f>IF(N6&lt;0,N6/(N6-100),100/(N6+100))</f>
         <v>0.52606635071090047</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>-14</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>426</v>
       </c>
@@ -26233,47 +26272,53 @@
       <c r="C7" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E7" s="1">
         <v>0.68979999999999997</v>
       </c>
-      <c r="E7" s="15">
-        <f>IF(C7="P",0,IF(C7="L",-D7,IF(I7&lt;0,D7*(100/-I7),D7*(I7/100)))/1)</f>
+      <c r="F7" s="15">
+        <f>IF(C7="P",0,IF(C7="L",-E7,IF(K7&lt;0,E7*(100/-K7),E7*(K7/100)))/1)</f>
         <v>-0.68979999999999997</v>
       </c>
-      <c r="F7" s="15">
-        <f>E7+F6</f>
+      <c r="G7" s="15">
+        <f>F7+G6</f>
         <v>-1.6347999999999998</v>
       </c>
-      <c r="G7" s="11">
-        <f>((K7-N7)*3.55%)+(M7-J7)</f>
+      <c r="H7" s="11">
+        <f>((M7-P7)*3.55%)+(O7-L7)</f>
         <v>5.3772693633062259E-3</v>
       </c>
-      <c r="H7" s="11">
-        <f>AVERAGE($G$6:G7)</f>
+      <c r="I7" s="11">
+        <f>AVERAGE($H$6:H7)</f>
         <v>-7.3041333591230655E-3</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K7" s="1">
         <v>-103</v>
       </c>
-      <c r="J7" s="13">
-        <f>IF(I7&lt;0,I7/(I7-100),100/(I7+100))</f>
+      <c r="L7" s="13">
+        <f>IF(K7&lt;0,K7/(K7-100),100/(K7+100))</f>
         <v>0.5073891625615764</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>3</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" s="1">
         <v>-113</v>
       </c>
-      <c r="M7" s="13">
-        <f>IF(L7&lt;0,L7/(L7-100),100/(L7+100))</f>
+      <c r="O7" s="13">
+        <f>IF(N7&lt;0,N7/(N7-100),100/(N7+100))</f>
         <v>0.53051643192488263</v>
       </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
         <v>3.5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>427</v>
       </c>
@@ -26283,47 +26328,53 @@
       <c r="C8" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E8" s="1">
         <v>0.74019999999999997</v>
       </c>
-      <c r="E8" s="15">
-        <f>IF(C8="P",0,IF(C8="L",-D8,IF(I8&lt;0,D8*(100/-I8),D8*(I8/100)))/1)</f>
+      <c r="F8" s="15">
+        <f>IF(C8="P",0,IF(C8="L",-E8,IF(K8&lt;0,E8*(100/-K8),E8*(K8/100)))/1)</f>
         <v>0.6729090909090909</v>
       </c>
-      <c r="F8" s="15">
-        <f>E8+F7</f>
+      <c r="G8" s="15">
+        <f>F8+G7</f>
         <v>-0.96189090909090891</v>
       </c>
-      <c r="G8" s="11">
-        <f>((K8-N8)*3.55%)+(M8-J8)</f>
+      <c r="H8" s="11">
+        <f>((M8-P8)*3.55%)+(O8-L8)</f>
         <v>0.10782963875205255</v>
       </c>
-      <c r="H8" s="11">
-        <f>AVERAGE($G$6:G8)</f>
+      <c r="I8" s="11">
+        <f>AVERAGE($H$6:H8)</f>
         <v>3.1073790677935476E-2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K8" s="1">
         <v>-110</v>
       </c>
-      <c r="J8" s="13">
-        <f>IF(I8&lt;0,I8/(I8-100),100/(I8+100))</f>
+      <c r="L8" s="13">
+        <f>IF(K8&lt;0,K8/(K8-100),100/(K8+100))</f>
         <v>0.52380952380952384</v>
       </c>
-      <c r="K8" s="1">
+      <c r="M8" s="1">
         <v>2.5</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>-103</v>
       </c>
-      <c r="M8" s="13">
-        <f>IF(L8&lt;0,L8/(L8-100),100/(L8+100))</f>
+      <c r="O8" s="13">
+        <f>IF(N8&lt;0,N8/(N8-100),100/(N8+100))</f>
         <v>0.5073891625615764</v>
       </c>
-      <c r="N8" s="1">
+      <c r="P8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>429</v>
       </c>
@@ -26333,47 +26384,53 @@
       <c r="C9" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E9" s="1">
         <v>0.67900000000000005</v>
       </c>
-      <c r="E9" s="15">
-        <f>IF(C9="P",0,IF(C9="L",-D9,IF(I9&lt;0,D9*(100/-I9),D9*(I9/100)))/1)</f>
+      <c r="F9" s="15">
+        <f>IF(C9="P",0,IF(C9="L",-E9,IF(K9&lt;0,E9*(100/-K9),E9*(K9/100)))/1)</f>
         <v>0.61727272727272731</v>
       </c>
-      <c r="F9" s="15">
-        <f>E9+F8</f>
+      <c r="G9" s="15">
+        <f>F9+G8</f>
         <v>-0.3446181818181816</v>
       </c>
-      <c r="G9" s="11">
-        <f>((K9-N9)*3.55%)+(M9-J9)</f>
+      <c r="H9" s="11">
+        <f>((M9-P9)*3.55%)+(O9-L9)</f>
         <v>8.5035829865926608E-3</v>
       </c>
-      <c r="H9" s="11">
-        <f>AVERAGE($G$6:G9)</f>
+      <c r="I9" s="11">
+        <f>AVERAGE($H$6:H9)</f>
         <v>2.5431238755099773E-2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K9" s="1">
         <v>-110</v>
       </c>
-      <c r="J9" s="13">
-        <f>IF(I9&lt;0,I9/(I9-100),100/(I9+100))</f>
+      <c r="L9" s="13">
+        <f>IF(K9&lt;0,K9/(K9-100),100/(K9+100))</f>
         <v>0.52380952380952384</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>4.5</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>-106</v>
       </c>
-      <c r="M9" s="13">
-        <f>IF(L9&lt;0,L9/(L9-100),100/(L9+100))</f>
+      <c r="O9" s="13">
+        <f>IF(N9&lt;0,N9/(N9-100),100/(N9+100))</f>
         <v>0.5145631067961165</v>
       </c>
-      <c r="N9" s="1">
+      <c r="P9" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>430</v>
       </c>
@@ -26383,45 +26440,185 @@
       <c r="C10" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E10" s="1">
         <v>1.2898000000000001</v>
       </c>
-      <c r="E10" s="15">
-        <f>IF(C10="P",0,IF(C10="L",-D10,IF(I10&lt;0,D10*(100/-I10),D10*(I10/100)))/1)</f>
+      <c r="F10" s="15">
+        <f>IF(C10="P",0,IF(C10="L",-E10,IF(K10&lt;0,E10*(100/-K10),E10*(K10/100)))/1)</f>
         <v>-1.2898000000000001</v>
       </c>
-      <c r="F10" s="15">
-        <f>E10+F9</f>
+      <c r="G10" s="15">
+        <f>F10+G9</f>
         <v>-1.6344181818181815</v>
       </c>
-      <c r="G10" s="11">
-        <f>((K10-N10)*3.55%)+(M10-J10)</f>
+      <c r="H10" s="11">
+        <f>((M10-P10)*3.55%)+(O10-L10)</f>
         <v>-3.9992362982928985E-2</v>
       </c>
-      <c r="H10" s="11">
-        <f>AVERAGE($G$6:G10)</f>
+      <c r="I10" s="11">
+        <f>AVERAGE($H$6:H10)</f>
         <v>1.2346518407494022E-2</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K10" s="1">
         <v>-112</v>
       </c>
-      <c r="J10" s="13">
-        <f>IF(I10&lt;0,I10/(I10-100),100/(I10+100))</f>
+      <c r="L10" s="13">
+        <f>IF(K10&lt;0,K10/(K10-100),100/(K10+100))</f>
         <v>0.52830188679245282</v>
       </c>
-      <c r="K10" s="1">
+      <c r="M10" s="1">
         <v>-6.5</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" s="1">
         <v>-110</v>
       </c>
-      <c r="M10" s="13">
-        <f>IF(L10&lt;0,L10/(L10-100),100/(L10+100))</f>
+      <c r="O10" s="13">
+        <f>IF(N10&lt;0,N10/(N10-100),100/(N10+100))</f>
         <v>0.52380952380952384</v>
       </c>
-      <c r="N10" s="1">
+      <c r="P10" s="1">
         <v>-5.5</v>
       </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B11" s="1">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.68820000000000003</v>
+      </c>
+      <c r="F11" s="15">
+        <f>IF(C11="P",0,IF(C11="L",-E11,IF(K11&lt;0,E11*(100/-K11),E11*(K11/100)))/1)</f>
+        <v>-0.68820000000000003</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" ref="G11:G12" si="0">F11+G10</f>
+        <v>-2.3226181818181817</v>
+      </c>
+      <c r="H11" s="11">
+        <f>((M11-P11)*3.55%)+(O11-L11)</f>
+        <v>9.1028423331054986E-2</v>
+      </c>
+      <c r="I11" s="11">
+        <f>AVERAGE($H$6:H11)</f>
+        <v>2.5460169228087515E-2</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K11" s="1">
+        <v>-109</v>
+      </c>
+      <c r="L11" s="13">
+        <f>IF(K11&lt;0,K11/(K11-100),100/(K11+100))</f>
+        <v>0.52153110047846885</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="N11" s="1">
+        <v>-110</v>
+      </c>
+      <c r="O11" s="13">
+        <f>IF(N11&lt;0,N11/(N11-100),100/(N11+100))</f>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="P11" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.69510000000000005</v>
+      </c>
+      <c r="F12" s="15">
+        <f>IF(C12="P",0,IF(C12="L",-E12,IF(K12&lt;0,E12*(100/-K12),E12*(K12/100)))/1)</f>
+        <v>-0.69510000000000005</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="0"/>
+        <v>-3.0177181818181817</v>
+      </c>
+      <c r="H12" s="11">
+        <f>((M12-P12)*3.55%)+(O12-L12)</f>
+        <v>0.13975593655856822</v>
+      </c>
+      <c r="I12" s="11">
+        <f>AVERAGE($H$6:H12)</f>
+        <v>4.1788135989584758E-2</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K12" s="1">
+        <v>-109</v>
+      </c>
+      <c r="L12" s="13">
+        <f>IF(K12&lt;0,K12/(K12-100),100/(K12+100))</f>
+        <v>0.52153110047846885</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="N12" s="1">
+        <v>-116</v>
+      </c>
+      <c r="O12" s="13">
+        <f>IF(N12&lt;0,N12/(N12-100),100/(N12+100))</f>
+        <v>0.53703703703703709</v>
+      </c>
+      <c r="P12" s="1">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="I16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9811D0E-79B9-F740-8F17-F00BFC80D834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F08D651-1DA3-0046-82D4-C4750968D8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="1920" windowWidth="17200" windowHeight="20020" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="441">
   <si>
     <t>Team</t>
   </si>
@@ -1540,19 +1540,19 @@
             <v>Cornell</v>
           </cell>
           <cell r="E2">
-            <v>7.9021040788216528</v>
+            <v>8.2271040788216538</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.60671051745526905</v>
+            <v>0.60256507226833311</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>0.1582655333236955</v>
+            <v>0.15035150160318139</v>
           </cell>
           <cell r="J2">
             <v>0.49844464881551681</v>
@@ -1572,19 +1572,19 @@
             <v>Pennsylvania</v>
           </cell>
           <cell r="E3">
-            <v>2.6364785238941821</v>
+            <v>2.961478523894181</v>
           </cell>
           <cell r="F3" t="b">
             <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.50906322566564655</v>
+            <v>0.51342490186336831</v>
           </cell>
           <cell r="H3">
             <v>0</v>
           </cell>
           <cell r="I3">
-            <v>-2.815202372922021E-2</v>
+            <v>-1.9825187351751369E-2</v>
           </cell>
           <cell r="J3">
             <v>6.3007749103253186E-2</v>
@@ -1604,19 +1604,19 @@
             <v>Dayton</v>
           </cell>
           <cell r="E4">
-            <v>9.3411469109932597</v>
+            <v>9.3411469109932579</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.58204384670284748</v>
+            <v>0.58204384670284737</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.1111746164327089</v>
+            <v>0.11117461643270871</v>
           </cell>
           <cell r="J4">
             <v>0.48436634190385669</v>
@@ -1630,31 +1630,31 @@
             <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Michigan</v>
+            <v>VCU</v>
           </cell>
           <cell r="D5" t="str">
-            <v>Wisconsin</v>
+            <v>St. Joseph's</v>
           </cell>
           <cell r="E5">
-            <v>12.51961170652187</v>
+            <v>12.835404558957849</v>
           </cell>
           <cell r="F5" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G5">
-            <v>0.50048899606020381</v>
+            <v>0.64391384734326496</v>
           </cell>
           <cell r="H5">
-            <v>0</v>
+            <v>7.0887631768342563E-2</v>
           </cell>
           <cell r="I5">
-            <v>-4.4521007521429068E-2</v>
+            <v>0.2292900722007786</v>
           </cell>
           <cell r="J5">
-            <v>0.39678660765623858</v>
+            <v>0.70074839245243137</v>
           </cell>
           <cell r="K5">
-            <v>0</v>
+            <v>1.3837265721180469</v>
           </cell>
         </row>
         <row r="6">
@@ -1662,28 +1662,28 @@
             <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Florida</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D6" t="str">
-            <v>Vanderbilt</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="E6">
-            <v>9.706702017032196</v>
+            <v>12.51961170652187</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.57865282190163037</v>
+            <v>0.50048899606020381</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>0.1047008418122035</v>
+            <v>-4.4521007521429068E-2</v>
           </cell>
           <cell r="J6">
-            <v>0.48746067765619733</v>
+            <v>0.39678660765623852</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1694,28 +1694,28 @@
             <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>South Florida</v>
+            <v>UCLA</v>
           </cell>
           <cell r="D7" t="str">
-            <v>Charlotte</v>
+            <v>Purdue</v>
           </cell>
           <cell r="E7">
-            <v>17.504043525620201</v>
+            <v>-3.9259228215636108</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.57649094454931049</v>
+            <v>0.57617974290883289</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>0.1005736214123201</v>
+            <v>9.9979509189590088E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.67424608547320797</v>
+            <v>5.7283370350142193E-2</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1726,28 +1726,28 @@
             <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Wichita State</v>
+            <v>Florida</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Tulsa</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="E8">
-            <v>2.896414169476309</v>
+            <v>11.0067020170322</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.59620098261362253</v>
+            <v>0.56163996807448291</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0.13820187589873401</v>
+            <v>7.2221757233103756E-2</v>
           </cell>
           <cell r="J8">
-            <v>0.32236736296520258</v>
+            <v>0.48746067765619711</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1758,31 +1758,31 @@
             <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Louisiana Tech</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D9" t="str">
-            <v>Kennesaw State</v>
+            <v>Ole Miss</v>
           </cell>
           <cell r="E9">
-            <v>-0.79114588219662485</v>
+            <v>14.94229486295097</v>
           </cell>
           <cell r="F9" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G9">
-            <v>0.51766871220593658</v>
+            <v>0.62509239360555147</v>
           </cell>
           <cell r="H9">
-            <v>0</v>
+            <v>5.5077610628663218E-2</v>
           </cell>
           <cell r="I9">
-            <v>-1.172336760684833E-2</v>
+            <v>0.1933582059742347</v>
           </cell>
           <cell r="J9">
-            <v>1.6879666989596531E-2</v>
+            <v>0.70816933596251053</v>
           </cell>
           <cell r="K9">
-            <v>0</v>
+            <v>1.0751149594715061</v>
           </cell>
         </row>
         <row r="10">
@@ -1790,28 +1790,28 @@
             <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>UMBC</v>
+            <v>South Florida</v>
           </cell>
           <cell r="D10" t="str">
-            <v>Vermont</v>
+            <v>Charlotte</v>
           </cell>
           <cell r="E10">
-            <v>6.2217835352010127</v>
+            <v>17.50404352562019</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.56753876375677981</v>
+            <v>0.57649094454931049</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>8.3483094444761541E-2</v>
+            <v>0.1005736214123201</v>
           </cell>
           <cell r="J10">
-            <v>0.35772478840372851</v>
+            <v>0.67424608547320775</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1822,28 +1822,28 @@
             <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Cornell</v>
+            <v>Wichita State</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Yale</v>
+            <v>Tulsa</v>
           </cell>
           <cell r="E11">
-            <v>-2.391389180240195</v>
+            <v>4.1964141694763084</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.52761988144170813</v>
+            <v>0.57917206917394892</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>7.2743191159883036E-3</v>
+            <v>0.1056921320593571</v>
           </cell>
           <cell r="J11">
-            <v>1.068584300634245E-2</v>
+            <v>0.32236736296520252</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1854,31 +1854,31 @@
             <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Pennsylvania</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Harvard</v>
+            <v>Houston</v>
           </cell>
           <cell r="E12">
-            <v>2.5615469942101572</v>
+            <v>7.0332145568128528</v>
           </cell>
           <cell r="F12" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.6359284526986887</v>
+            <v>0.61080498655456927</v>
           </cell>
           <cell r="H12">
-            <v>6.4179900266898557E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I12">
-            <v>0.21404522787931479</v>
+            <v>0.16608224705872321</v>
           </cell>
           <cell r="J12">
-            <v>0.40688974186433241</v>
+            <v>0.48184382503491208</v>
           </cell>
           <cell r="K12">
-            <v>1.2527916532098597</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="13">
@@ -1886,28 +1886,28 @@
             <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Dayton</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Saint Louis</v>
+            <v>San Diego State</v>
           </cell>
           <cell r="E13">
-            <v>-3.4364666039217679</v>
+            <v>3.1538916921290459</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.56364644216181237</v>
+            <v>0.54116463738385856</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>7.6052298672550922E-2</v>
+            <v>3.3132489551002731E-2</v>
           </cell>
           <cell r="J13">
-            <v>4.255206921151955E-2</v>
+            <v>0.1993819148790523</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1918,28 +1918,28 @@
             <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Wisconsin</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Michigan</v>
+            <v>Uconn</v>
           </cell>
           <cell r="E14">
-            <v>-8.575647555667361</v>
+            <v>-1.515431139992099</v>
           </cell>
           <cell r="F14" t="b">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.59687709552205825</v>
+            <v>0.52453364987669271</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>0.13949263690574759</v>
+            <v>1.38242249186793E-3</v>
           </cell>
           <cell r="J14">
-            <v>4.1369473563244268E-2</v>
+            <v>1.005967045949635E-2</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -1950,28 +1950,28 @@
             <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Vanderbilt</v>
+            <v>Akron</v>
           </cell>
           <cell r="D15" t="str">
-            <v>Florida</v>
+            <v>Toledo</v>
           </cell>
           <cell r="E15">
-            <v>-4.5440442555042679</v>
+            <v>9.5075656347777979</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.54864839019955225</v>
+            <v>0.56226836189641416</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>4.7419654017327062E-2</v>
+            <v>7.3421418165881658E-2</v>
           </cell>
           <cell r="J15">
-            <v>2.929020347228295E-2</v>
+            <v>0.44500813920524279</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -1982,31 +1982,31 @@
             <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Charlotte</v>
+            <v>Duke</v>
           </cell>
           <cell r="D16" t="str">
-            <v>South Florida</v>
+            <v>Virginia</v>
           </cell>
           <cell r="E16">
-            <v>-12.427990110393131</v>
+            <v>15.61990006839136</v>
           </cell>
           <cell r="F16" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G16">
-            <v>0.53913335528575357</v>
+            <v>0.64374327682518317</v>
           </cell>
           <cell r="H16">
-            <v>0</v>
+            <v>7.0744352533153906E-2</v>
           </cell>
           <cell r="I16">
-            <v>2.9254587363711389E-2</v>
+            <v>0.22896443757534979</v>
           </cell>
           <cell r="J16">
-            <v>0.30293008568898622</v>
+            <v>0.75149652484483553</v>
           </cell>
           <cell r="K16">
-            <v>0</v>
+            <v>1.3809297614471643</v>
           </cell>
         </row>
         <row r="17">
@@ -2014,28 +2014,28 @@
             <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Tulsa</v>
+            <v>Louisiana Tech</v>
           </cell>
           <cell r="D17" t="str">
-            <v>Wichita State</v>
+            <v>Kennesaw State</v>
           </cell>
           <cell r="E17">
-            <v>1.3724021653941909</v>
+            <v>-0.79114588219662485</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.50928459726668995</v>
+            <v>0.51766871220593658</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>-2.772940521813733E-2</v>
+            <v>-1.172336760684833E-2</v>
           </cell>
           <cell r="J17">
-            <v>6.630276228573867E-2</v>
+            <v>1.6879666989596531E-2</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2046,31 +2046,31 @@
             <v>17</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Kennesaw State</v>
+            <v>UC Irvine</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Louisiana Tech</v>
+            <v>Hawaii</v>
           </cell>
           <cell r="E18">
-            <v>6.2621855083836966</v>
+            <v>6.0960755683915622</v>
           </cell>
           <cell r="F18" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0.61682897197272468</v>
+            <v>0.60102640481430814</v>
           </cell>
           <cell r="H18">
-            <v>4.8136336457088799E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I18">
-            <v>0.17758258285701989</v>
+            <v>0.14741404555458831</v>
           </cell>
           <cell r="J18">
-            <v>0.47249844996534668</v>
+            <v>0.43128673144021629</v>
           </cell>
           <cell r="K18">
-            <v>0.93962128764237329</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="19">
@@ -2078,28 +2078,28 @@
             <v>18</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Vermont</v>
+            <v>Utah Valley</v>
           </cell>
           <cell r="D19" t="str">
-            <v>UMBC</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="E19">
-            <v>0.41586482678781872</v>
+            <v>5.5346483958487838</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.5966717236818081</v>
+            <v>0.5629353093650703</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>0.1391005633925427</v>
+            <v>7.4694681515134254E-2</v>
           </cell>
           <cell r="J19">
-            <v>0.2457459905417814</v>
+            <v>0.32575964482749847</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2109,23 +2109,29 @@
           <cell r="B20">
             <v>19</v>
           </cell>
+          <cell r="C20" t="str">
+            <v>UMBC</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>Vermont</v>
+          </cell>
           <cell r="E20">
-            <v>0</v>
-          </cell>
-          <cell r="F20">
+            <v>6.2217835352010118</v>
+          </cell>
+          <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0</v>
+            <v>0.56753876375677981</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>0</v>
+            <v>8.3483094444761541E-2</v>
           </cell>
           <cell r="J20">
-            <v>0</v>
+            <v>0.35772478840372829</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2135,23 +2141,29 @@
           <cell r="B21">
             <v>20</v>
           </cell>
+          <cell r="C21" t="str">
+            <v>Howard</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>North Carolina Central</v>
+          </cell>
           <cell r="E21">
-            <v>0</v>
-          </cell>
-          <cell r="F21">
+            <v>13.492808833862689</v>
+          </cell>
+          <cell r="F21" t="b">
             <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0</v>
+            <v>0.51228569994753381</v>
           </cell>
           <cell r="H21">
             <v>0</v>
           </cell>
           <cell r="I21">
-            <v>0</v>
+            <v>-2.2000027372889971E-2</v>
           </cell>
           <cell r="J21">
-            <v>0</v>
+            <v>0.45221204533097692</v>
           </cell>
           <cell r="K21">
             <v>0</v>
@@ -2161,23 +2173,29 @@
           <cell r="B22">
             <v>21</v>
           </cell>
+          <cell r="C22" t="str">
+            <v>Southern</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>Prairie View A&amp;M</v>
+          </cell>
           <cell r="E22">
-            <v>0</v>
-          </cell>
-          <cell r="F22">
+            <v>6.6674465995330454</v>
+          </cell>
+          <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0</v>
+            <v>0.59064925298436843</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>0</v>
+            <v>0.12760311933379431</v>
           </cell>
           <cell r="J22">
-            <v>0</v>
+            <v>0.4245720996618681</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2187,23 +2205,29 @@
           <cell r="B23">
             <v>22</v>
           </cell>
+          <cell r="C23" t="str">
+            <v>Cornell</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>Yale</v>
+          </cell>
           <cell r="E23">
-            <v>0</v>
-          </cell>
-          <cell r="F23">
+            <v>-2.7163891802401952</v>
+          </cell>
+          <cell r="F23" t="b">
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0</v>
+            <v>0.53197111535366171</v>
           </cell>
           <cell r="H23">
             <v>0</v>
           </cell>
           <cell r="I23">
-            <v>0</v>
+            <v>1.5581220220626911E-2</v>
           </cell>
           <cell r="J23">
-            <v>0</v>
+            <v>1.068584300634245E-2</v>
           </cell>
           <cell r="K23">
             <v>0</v>
@@ -2213,49 +2237,61 @@
           <cell r="B24">
             <v>23</v>
           </cell>
+          <cell r="C24" t="str">
+            <v>Pennsylvania</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>Harvard</v>
+          </cell>
           <cell r="E24">
-            <v>0</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
+            <v>2.236546994210157</v>
+          </cell>
+          <cell r="F24" t="b">
+            <v>1</v>
           </cell>
           <cell r="G24">
-            <v>0</v>
+            <v>0.64002820580468123</v>
           </cell>
           <cell r="H24">
-            <v>0</v>
+            <v>6.7623692875932173E-2</v>
           </cell>
           <cell r="I24">
-            <v>0</v>
+            <v>0.2218720292634824</v>
           </cell>
           <cell r="J24">
-            <v>0</v>
+            <v>0.40688974186433241</v>
           </cell>
           <cell r="K24">
-            <v>0</v>
+            <v>1.3200144849381958</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
             <v>24</v>
           </cell>
+          <cell r="C25" t="str">
+            <v>Dayton</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>Saint Louis</v>
+          </cell>
           <cell r="E25">
-            <v>0</v>
-          </cell>
-          <cell r="F25">
+            <v>-3.4364666039217679</v>
+          </cell>
+          <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0</v>
+            <v>0.56364644216181237</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>0</v>
+            <v>7.6052298672550922E-2</v>
           </cell>
           <cell r="J25">
-            <v>0</v>
+            <v>4.255206921151955E-2</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2265,23 +2301,29 @@
           <cell r="B26">
             <v>25</v>
           </cell>
+          <cell r="C26" t="str">
+            <v>St. Joseph's</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>VCU</v>
+          </cell>
           <cell r="E26">
-            <v>0</v>
-          </cell>
-          <cell r="F26">
+            <v>-7.8122263016644933</v>
+          </cell>
+          <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0</v>
+            <v>0.54508942833671536</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>0</v>
+            <v>4.0625272279183937E-2</v>
           </cell>
           <cell r="J26">
-            <v>0</v>
+            <v>0.35468806184106177</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2291,23 +2333,29 @@
           <cell r="B27">
             <v>26</v>
           </cell>
+          <cell r="C27" t="str">
+            <v>Wisconsin</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>Michigan</v>
+          </cell>
           <cell r="E27">
-            <v>0</v>
-          </cell>
-          <cell r="F27">
+            <v>-8.575647555667361</v>
+          </cell>
+          <cell r="F27" t="b">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0</v>
+            <v>0.59687709552205825</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>0</v>
+            <v>0.13949263690574759</v>
           </cell>
           <cell r="J27">
-            <v>0</v>
+            <v>4.1369473563244268E-2</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2317,23 +2365,29 @@
           <cell r="B28">
             <v>27</v>
           </cell>
+          <cell r="C28" t="str">
+            <v>Purdue</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>UCLA</v>
+          </cell>
           <cell r="E28">
-            <v>0</v>
-          </cell>
-          <cell r="F28">
+            <v>8.679598044426573</v>
+          </cell>
+          <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0</v>
+            <v>0.54180212840551689</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>0</v>
+            <v>3.4349517865077728E-2</v>
           </cell>
           <cell r="J28">
-            <v>0</v>
+            <v>0.37373806481233229</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2343,23 +2397,29 @@
           <cell r="B29">
             <v>28</v>
           </cell>
+          <cell r="C29" t="str">
+            <v>Vanderbilt</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>Florida</v>
+          </cell>
           <cell r="E29">
-            <v>0</v>
-          </cell>
-          <cell r="F29">
+            <v>-5.8440442555042678</v>
+          </cell>
+          <cell r="F29" t="b">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0</v>
+            <v>0.56592043655089019</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>0</v>
+            <v>8.0393560688063137E-2</v>
           </cell>
           <cell r="J29">
-            <v>0</v>
+            <v>2.929020347228295E-2</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2369,23 +2429,29 @@
           <cell r="B30">
             <v>29</v>
           </cell>
+          <cell r="C30" t="str">
+            <v>Ole Miss</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>Arkansas</v>
+          </cell>
           <cell r="E30">
-            <v>0</v>
-          </cell>
-          <cell r="F30">
+            <v>-11.16172603118642</v>
+          </cell>
+          <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0</v>
+            <v>0.55359578591625669</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>0</v>
+            <v>5.686468220376284E-2</v>
           </cell>
           <cell r="J30">
-            <v>0</v>
+            <v>0.4744028483255055</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2395,23 +2461,29 @@
           <cell r="B31">
             <v>30</v>
           </cell>
+          <cell r="C31" t="str">
+            <v>Charlotte</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>South Florida</v>
+          </cell>
           <cell r="E31">
-            <v>0</v>
-          </cell>
-          <cell r="F31">
+            <v>-12.427990110393131</v>
+          </cell>
+          <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0</v>
+            <v>0.53913335528575357</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>0</v>
+            <v>2.9254587363711389E-2</v>
           </cell>
           <cell r="J31">
-            <v>0</v>
+            <v>0.30293008568898611</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2421,23 +2493,29 @@
           <cell r="B32">
             <v>31</v>
           </cell>
+          <cell r="C32" t="str">
+            <v>Tulsa</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>Wichita State</v>
+          </cell>
           <cell r="E32">
-            <v>0</v>
-          </cell>
-          <cell r="F32">
+            <v>7.2402165394191087E-2</v>
+          </cell>
+          <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0</v>
+            <v>0.52671915345776943</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>0</v>
+            <v>5.5547475102871169E-3</v>
           </cell>
           <cell r="J32">
-            <v>0</v>
+            <v>6.630276228573867E-2</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2447,23 +2525,29 @@
           <cell r="B33">
             <v>32</v>
           </cell>
+          <cell r="C33" t="str">
+            <v>Houston</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>Arizona</v>
+          </cell>
           <cell r="E33">
-            <v>0</v>
-          </cell>
-          <cell r="F33">
+            <v>-1.7351658207897509</v>
+          </cell>
+          <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0</v>
+            <v>0.51906303296871892</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>0</v>
+            <v>-9.0614825142638633E-3</v>
           </cell>
           <cell r="J33">
-            <v>0</v>
+            <v>1.011447741049815E-2</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -2473,23 +2557,29 @@
           <cell r="B34">
             <v>33</v>
           </cell>
+          <cell r="C34" t="str">
+            <v>San Diego State</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>Utah State</v>
+          </cell>
           <cell r="E34">
-            <v>0</v>
-          </cell>
-          <cell r="F34">
+            <v>-1.3962346637617311</v>
+          </cell>
+          <cell r="F34" t="b">
             <v>0</v>
           </cell>
           <cell r="G34">
-            <v>0</v>
+            <v>0.50258725560511397</v>
           </cell>
           <cell r="H34">
             <v>0</v>
           </cell>
           <cell r="I34">
-            <v>0</v>
+            <v>-4.0515239299327821E-2</v>
           </cell>
           <cell r="J34">
-            <v>0</v>
+            <v>3.8670011336470737E-2</v>
           </cell>
           <cell r="K34">
             <v>0</v>
@@ -2499,23 +2589,29 @@
           <cell r="B35">
             <v>34</v>
           </cell>
+          <cell r="C35" t="str">
+            <v>Uconn</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>St. John's</v>
+          </cell>
           <cell r="E35">
-            <v>0</v>
-          </cell>
-          <cell r="F35">
+            <v>5.7614705934243204</v>
+          </cell>
+          <cell r="F35" t="b">
             <v>0</v>
           </cell>
           <cell r="G35">
-            <v>0</v>
+            <v>0.58076148035619835</v>
           </cell>
           <cell r="H35">
             <v>0</v>
           </cell>
           <cell r="I35">
-            <v>0</v>
+            <v>0.1087264624981968</v>
           </cell>
           <cell r="J35">
-            <v>0</v>
+            <v>0.3743383054479183</v>
           </cell>
           <cell r="K35">
             <v>0</v>
@@ -2525,23 +2621,29 @@
           <cell r="B36">
             <v>35</v>
           </cell>
+          <cell r="C36" t="str">
+            <v>Toledo</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>Akron</v>
+          </cell>
           <cell r="E36">
-            <v>0</v>
-          </cell>
-          <cell r="F36">
+            <v>-4.4333538438309539</v>
+          </cell>
+          <cell r="F36" t="b">
             <v>0</v>
           </cell>
           <cell r="G36">
-            <v>0</v>
+            <v>0.56372306436512742</v>
           </cell>
           <cell r="H36">
             <v>0</v>
           </cell>
           <cell r="I36">
-            <v>0</v>
+            <v>7.6198577424334224E-2</v>
           </cell>
           <cell r="J36">
-            <v>0</v>
+            <v>1.070943588982121E-2</v>
           </cell>
           <cell r="K36">
             <v>0</v>
@@ -2551,23 +2653,29 @@
           <cell r="B37">
             <v>36</v>
           </cell>
+          <cell r="C37" t="str">
+            <v>Virginia</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>Duke</v>
+          </cell>
           <cell r="E37">
-            <v>0</v>
-          </cell>
-          <cell r="F37">
+            <v>-10.501859832677949</v>
+          </cell>
+          <cell r="F37" t="b">
             <v>0</v>
           </cell>
           <cell r="G37">
-            <v>0</v>
+            <v>0.54978423648731911</v>
           </cell>
           <cell r="H37">
             <v>0</v>
           </cell>
           <cell r="I37">
-            <v>0</v>
+            <v>4.9588087839427419E-2</v>
           </cell>
           <cell r="J37">
-            <v>0</v>
+            <v>0.44664110009074121</v>
           </cell>
           <cell r="K37">
             <v>0</v>
@@ -2577,49 +2685,61 @@
           <cell r="B38">
             <v>37</v>
           </cell>
+          <cell r="C38" t="str">
+            <v>Kennesaw State</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>Louisiana Tech</v>
+          </cell>
           <cell r="E38">
-            <v>0</v>
-          </cell>
-          <cell r="F38">
-            <v>0</v>
+            <v>6.2621855083836948</v>
+          </cell>
+          <cell r="F38" t="b">
+            <v>1</v>
           </cell>
           <cell r="G38">
-            <v>0</v>
+            <v>0.61682897197272468</v>
           </cell>
           <cell r="H38">
-            <v>0</v>
+            <v>4.8136336457088799E-2</v>
           </cell>
           <cell r="I38">
-            <v>0</v>
+            <v>0.17758258285701989</v>
           </cell>
           <cell r="J38">
-            <v>0</v>
+            <v>0.47249844996534662</v>
           </cell>
           <cell r="K38">
-            <v>0</v>
+            <v>0.93962128764237329</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39">
             <v>38</v>
           </cell>
+          <cell r="C39" t="str">
+            <v>Hawaii</v>
+          </cell>
+          <cell r="D39" t="str">
+            <v>UC Irvine</v>
+          </cell>
           <cell r="E39">
-            <v>0</v>
-          </cell>
-          <cell r="F39">
+            <v>-2.2082907356595198</v>
+          </cell>
+          <cell r="F39" t="b">
             <v>0</v>
           </cell>
           <cell r="G39">
-            <v>0</v>
+            <v>0.50519335212785865</v>
           </cell>
           <cell r="H39">
             <v>0</v>
           </cell>
           <cell r="I39">
-            <v>0</v>
+            <v>-3.5539964119542522E-2</v>
           </cell>
           <cell r="J39">
-            <v>0</v>
+            <v>8.3347094878473249E-2</v>
           </cell>
           <cell r="K39">
             <v>0</v>
@@ -2629,23 +2749,29 @@
           <cell r="B40">
             <v>39</v>
           </cell>
+          <cell r="C40" t="str">
+            <v>California Baptist</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>Utah Valley</v>
+          </cell>
           <cell r="E40">
-            <v>0</v>
-          </cell>
-          <cell r="F40">
+            <v>-2.3800855006867478</v>
+          </cell>
+          <cell r="F40" t="b">
             <v>0</v>
           </cell>
           <cell r="G40">
-            <v>0</v>
+            <v>0.51545301519246445</v>
           </cell>
           <cell r="H40">
             <v>0</v>
           </cell>
           <cell r="I40">
-            <v>0</v>
+            <v>-1.5953334632567821E-2</v>
           </cell>
           <cell r="J40">
-            <v>0</v>
+            <v>3.9482339377063413E-2</v>
           </cell>
           <cell r="K40">
             <v>0</v>
@@ -2655,23 +2781,29 @@
           <cell r="B41">
             <v>40</v>
           </cell>
+          <cell r="C41" t="str">
+            <v>Vermont</v>
+          </cell>
+          <cell r="D41" t="str">
+            <v>UMBC</v>
+          </cell>
           <cell r="E41">
-            <v>0</v>
-          </cell>
-          <cell r="F41">
+            <v>0.41586482678781778</v>
+          </cell>
+          <cell r="F41" t="b">
             <v>0</v>
           </cell>
           <cell r="G41">
-            <v>0</v>
+            <v>0.5966717236818081</v>
           </cell>
           <cell r="H41">
             <v>0</v>
           </cell>
           <cell r="I41">
-            <v>0</v>
+            <v>0.1391005633925427</v>
           </cell>
           <cell r="J41">
-            <v>0</v>
+            <v>0.2457459905417814</v>
           </cell>
           <cell r="K41">
             <v>0</v>
@@ -2681,23 +2813,29 @@
           <cell r="B42">
             <v>41</v>
           </cell>
+          <cell r="C42" t="str">
+            <v>North Carolina Central</v>
+          </cell>
+          <cell r="D42" t="str">
+            <v>Howard</v>
+          </cell>
           <cell r="E42">
-            <v>0</v>
-          </cell>
-          <cell r="F42">
+            <v>-7.7263125674687121</v>
+          </cell>
+          <cell r="F42" t="b">
             <v>0</v>
           </cell>
           <cell r="G42">
-            <v>0</v>
+            <v>0.62915095347454453</v>
           </cell>
           <cell r="H42">
             <v>0</v>
           </cell>
           <cell r="I42">
-            <v>0</v>
+            <v>0.20110636572413049</v>
           </cell>
           <cell r="J42">
-            <v>0</v>
+            <v>6.6420644224934988E-2</v>
           </cell>
           <cell r="K42">
             <v>0</v>
@@ -2707,23 +2845,29 @@
           <cell r="B43">
             <v>42</v>
           </cell>
+          <cell r="C43" t="str">
+            <v>Prairie View A&amp;M</v>
+          </cell>
+          <cell r="D43" t="str">
+            <v>Southern</v>
+          </cell>
           <cell r="E43">
-            <v>0</v>
-          </cell>
-          <cell r="F43">
+            <v>-2.0777511756776521</v>
+          </cell>
+          <cell r="F43" t="b">
             <v>0</v>
           </cell>
           <cell r="G43">
-            <v>0</v>
+            <v>0.52298252604510409</v>
           </cell>
           <cell r="H43">
             <v>0</v>
           </cell>
           <cell r="I43">
-            <v>0</v>
+            <v>-1.5788139138921411E-3</v>
           </cell>
           <cell r="J43">
-            <v>0</v>
+            <v>1.172898173053832E-2</v>
           </cell>
           <cell r="K43">
             <v>0</v>
@@ -8699,7 +8843,7 @@
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-3.5</v>
+            <v>-4</v>
           </cell>
         </row>
         <row r="3">
@@ -8773,7 +8917,7 @@
             <v>0</v>
           </cell>
           <cell r="X3">
-            <v>-3</v>
+            <v>-3.5</v>
           </cell>
         </row>
         <row r="4">
@@ -8855,73 +8999,73 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>Michigan</v>
+            <v>VCU</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Wisconsin</v>
+            <v>St. Joseph's</v>
           </cell>
           <cell r="D5">
-            <v>23.915638484765847</v>
+            <v>10.046934010674722</v>
           </cell>
           <cell r="E5">
-            <v>98.283491704002756</v>
+            <v>100.11649510419282</v>
           </cell>
           <cell r="F5">
-            <v>95.448163069798071</v>
+            <v>100.40585231866712</v>
           </cell>
           <cell r="G5">
-            <v>0.5870726495726496</v>
+            <v>0.54296008869179602</v>
           </cell>
           <cell r="H5">
-            <v>71.669677419354841</v>
+            <v>69.00645161290322</v>
           </cell>
           <cell r="I5">
-            <v>60.387096774193552</v>
+            <v>58.193548387096776</v>
           </cell>
           <cell r="J5">
-            <v>23.516129032258064</v>
+            <v>25.967741935483872</v>
           </cell>
           <cell r="K5">
-            <v>11.225806451612904</v>
+            <v>11.419354838709678</v>
           </cell>
           <cell r="L5">
-            <v>12.161290322580646</v>
+            <v>10.806451612903226</v>
           </cell>
           <cell r="M5">
             <v>0</v>
           </cell>
           <cell r="N5">
-            <v>15.99115140253407</v>
+            <v>0.35857878605365429</v>
           </cell>
           <cell r="O5">
-            <v>101.25838978230519</v>
+            <v>99.259251438526107</v>
           </cell>
           <cell r="P5">
-            <v>98.106398085976267</v>
+            <v>108.34882848626603</v>
           </cell>
           <cell r="Q5">
-            <v>0.54685863874345553</v>
+            <v>0.5</v>
           </cell>
           <cell r="R5">
-            <v>69.153548387096777</v>
+            <v>68.286451612903235</v>
           </cell>
           <cell r="S5">
-            <v>61.612903225806448</v>
+            <v>59.903225806451616</v>
           </cell>
           <cell r="T5">
-            <v>20.29032258064516</v>
+            <v>18.612903225806452</v>
           </cell>
           <cell r="U5">
-            <v>10.419354838709678</v>
+            <v>11.64516129032258</v>
           </cell>
           <cell r="V5">
-            <v>9.0322580645161299</v>
+            <v>11.838709677419354</v>
           </cell>
           <cell r="W5">
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>-12.5</v>
+            <v>-6</v>
           </cell>
         </row>
         <row r="6">
@@ -8929,73 +9073,73 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>Florida</v>
+            <v>Michigan</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Vanderbilt</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="D6">
-            <v>22.748625673592354</v>
+            <v>23.915638484765847</v>
           </cell>
           <cell r="E6">
-            <v>104.56180875012235</v>
+            <v>98.283491704002756</v>
           </cell>
           <cell r="F6">
-            <v>99.903229832962509</v>
+            <v>95.448163069798071</v>
           </cell>
           <cell r="G6">
-            <v>0.54031856645097065</v>
+            <v>0.5870726495726496</v>
           </cell>
           <cell r="H6">
-            <v>71.534193548387094</v>
+            <v>71.669677419354841</v>
           </cell>
           <cell r="I6">
-            <v>64.806451612903231</v>
+            <v>60.387096774193552</v>
           </cell>
           <cell r="J6">
-            <v>24.967741935483872</v>
+            <v>23.516129032258064</v>
           </cell>
           <cell r="K6">
-            <v>15.903225806451612</v>
+            <v>11.225806451612904</v>
           </cell>
           <cell r="L6">
-            <v>11.64516129032258</v>
+            <v>12.161290322580646</v>
           </cell>
           <cell r="M6">
             <v>0</v>
           </cell>
           <cell r="N6">
-            <v>19.188801343657655</v>
+            <v>15.99115140253407</v>
           </cell>
           <cell r="O6">
-            <v>100.6501092787602</v>
+            <v>101.25838978230519</v>
           </cell>
           <cell r="P6">
-            <v>97.808224636267653</v>
+            <v>98.106398085976267</v>
           </cell>
           <cell r="Q6">
-            <v>0.55637126376507606</v>
+            <v>0.54685863874345553</v>
           </cell>
           <cell r="R6">
-            <v>70.905806451612904</v>
+            <v>69.153548387096777</v>
           </cell>
           <cell r="S6">
-            <v>61.516129032258064</v>
+            <v>61.612903225806448</v>
           </cell>
           <cell r="T6">
-            <v>23.612903225806452</v>
+            <v>20.29032258064516</v>
           </cell>
           <cell r="U6">
-            <v>10.741935483870968</v>
+            <v>10.419354838709678</v>
           </cell>
           <cell r="V6">
-            <v>9.741935483870968</v>
+            <v>9.0322580645161299</v>
           </cell>
           <cell r="W6">
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>-6.5</v>
+            <v>-12.5</v>
           </cell>
         </row>
         <row r="7">
@@ -9003,73 +9147,73 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>South Florida</v>
+            <v>UCLA</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Charlotte</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D7">
-            <v>10.662427729240893</v>
+            <v>16.04165934317437</v>
           </cell>
           <cell r="E7">
-            <v>104.34549376348122</v>
+            <v>100.9511732509619</v>
           </cell>
           <cell r="F7">
-            <v>99.932079382996733</v>
+            <v>92.195689602132376</v>
           </cell>
           <cell r="G7">
-            <v>0.51318359375</v>
+            <v>0.53971318257032541</v>
           </cell>
           <cell r="H7">
-            <v>73.95225806451613</v>
+            <v>65.94580645161291</v>
           </cell>
           <cell r="I7">
-            <v>66.064516129032256</v>
+            <v>58.483870967741936</v>
           </cell>
           <cell r="J7">
-            <v>27.677419354838708</v>
+            <v>19.451612903225808</v>
           </cell>
           <cell r="K7">
-            <v>15.516129032258064</v>
+            <v>10.064516129032258</v>
           </cell>
           <cell r="L7">
-            <v>11.225806451612904</v>
+            <v>8.9677419354838701</v>
           </cell>
           <cell r="M7">
             <v>0</v>
           </cell>
           <cell r="N7">
-            <v>-0.94217041800932655</v>
+            <v>20.822747409737431</v>
           </cell>
           <cell r="O7">
-            <v>97.9635725257845</v>
+            <v>102.36430980153686</v>
           </cell>
           <cell r="P7">
-            <v>108.1900253682186</v>
+            <v>102.10099533949814</v>
           </cell>
           <cell r="Q7">
-            <v>0.5367215041128085</v>
+            <v>0.57913090128755362</v>
           </cell>
           <cell r="R7">
-            <v>64.8</v>
+            <v>65.54451612903226</v>
           </cell>
           <cell r="S7">
-            <v>54.903225806451616</v>
+            <v>60.12903225806452</v>
           </cell>
           <cell r="T7">
-            <v>20</v>
+            <v>17</v>
           </cell>
           <cell r="U7">
-            <v>10.903225806451612</v>
+            <v>11.161290322580646</v>
           </cell>
           <cell r="V7">
-            <v>12</v>
+            <v>9.0967741935483879</v>
           </cell>
           <cell r="W7">
             <v>0</v>
           </cell>
           <cell r="X7">
-            <v>-14</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="8">
@@ -9077,73 +9221,73 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>Wichita State</v>
+            <v>Florida</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Tulsa</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D8">
-            <v>7.770824188202555</v>
+            <v>22.748625673592354</v>
           </cell>
           <cell r="E8">
-            <v>105.2828776380081</v>
+            <v>104.56180875012235</v>
           </cell>
           <cell r="F8">
-            <v>97.27607791375182</v>
+            <v>99.903229832962509</v>
           </cell>
           <cell r="G8">
-            <v>0.50232558139534889</v>
+            <v>0.54031856645097065</v>
           </cell>
           <cell r="H8">
-            <v>67.778064516129021</v>
+            <v>71.534193548387094</v>
           </cell>
           <cell r="I8">
-            <v>62.41935483870968</v>
+            <v>64.806451612903231</v>
           </cell>
           <cell r="J8">
-            <v>22.516129032258064</v>
+            <v>24.967741935483872</v>
           </cell>
           <cell r="K8">
-            <v>14.806451612903226</v>
+            <v>15.903225806451612</v>
           </cell>
           <cell r="L8">
-            <v>10.258064516129032</v>
+            <v>11.64516129032258</v>
           </cell>
           <cell r="M8">
             <v>0</v>
           </cell>
           <cell r="N8">
-            <v>5.3476433114678237</v>
+            <v>19.188801343657655</v>
           </cell>
           <cell r="O8">
-            <v>100.58857934431276</v>
+            <v>100.6501092787602</v>
           </cell>
           <cell r="P8">
-            <v>101.35085266969703</v>
+            <v>97.808224636267653</v>
           </cell>
           <cell r="Q8">
-            <v>0.57346491228070173</v>
+            <v>0.55637126376507606</v>
           </cell>
           <cell r="R8">
-            <v>68.307096774193553</v>
+            <v>70.905806451612904</v>
           </cell>
           <cell r="S8">
-            <v>58.838709677419352</v>
+            <v>61.516129032258064</v>
           </cell>
           <cell r="T8">
-            <v>23.64516129032258</v>
+            <v>23.612903225806452</v>
           </cell>
           <cell r="U8">
-            <v>11.193548387096774</v>
+            <v>10.741935483870968</v>
           </cell>
           <cell r="V8">
-            <v>10.258064516129032</v>
+            <v>9.741935483870968</v>
           </cell>
           <cell r="W8">
             <v>0</v>
           </cell>
           <cell r="X8">
-            <v>1</v>
+            <v>-8.5</v>
           </cell>
         </row>
         <row r="9">
@@ -9151,73 +9295,73 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>Louisiana Tech</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Kennesaw State</v>
+            <v>Ole Miss</v>
           </cell>
           <cell r="D9">
-            <v>2.6443345975686983</v>
+            <v>20.289786813604461</v>
           </cell>
           <cell r="E9">
-            <v>99.919161188678217</v>
+            <v>101.81190917064613</v>
           </cell>
           <cell r="F9">
-            <v>98.415627483867411</v>
+            <v>97.741343816793645</v>
           </cell>
           <cell r="G9">
-            <v>0.49525669642857145</v>
+            <v>0.56654947262682065</v>
           </cell>
           <cell r="H9">
-            <v>65.900645161290328</v>
+            <v>72.56258064516129</v>
           </cell>
           <cell r="I9">
-            <v>57.806451612903224</v>
+            <v>64.225806451612897</v>
           </cell>
           <cell r="J9">
-            <v>19.129032258064516</v>
+            <v>23.419354838709676</v>
           </cell>
           <cell r="K9">
-            <v>12.96774193548387</v>
+            <v>11</v>
           </cell>
           <cell r="L9">
-            <v>12.64516129032258</v>
+            <v>9.0322580645161299</v>
           </cell>
           <cell r="M9">
             <v>0</v>
           </cell>
           <cell r="N9">
-            <v>6.490752715038262</v>
+            <v>8.9278178203979799</v>
           </cell>
           <cell r="O9">
-            <v>101.8432322449375</v>
+            <v>100.09953473783261</v>
           </cell>
           <cell r="P9">
-            <v>97.141081053482708</v>
+            <v>93.948889412718557</v>
           </cell>
           <cell r="Q9">
-            <v>0.52519480519480521</v>
+            <v>0.50161812297734631</v>
           </cell>
           <cell r="R9">
-            <v>71.699354838709667</v>
+            <v>68.278709677419357</v>
           </cell>
           <cell r="S9">
-            <v>62.096774193548384</v>
+            <v>59.806451612903224</v>
           </cell>
           <cell r="T9">
-            <v>26.516129032258064</v>
+            <v>20.35483870967742</v>
           </cell>
           <cell r="U9">
-            <v>13.806451612903226</v>
+            <v>10.225806451612904</v>
           </cell>
           <cell r="V9">
-            <v>11.741935483870968</v>
+            <v>9.741935483870968</v>
           </cell>
           <cell r="W9">
             <v>0</v>
           </cell>
           <cell r="X9">
-            <v>1.5</v>
+            <v>-9</v>
           </cell>
         </row>
         <row r="10">
@@ -9225,73 +9369,73 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>UMBC</v>
+            <v>South Florida</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Vermont</v>
+            <v>Charlotte</v>
           </cell>
           <cell r="D10">
-            <v>-8.1832066239376893</v>
+            <v>10.662427729240893</v>
           </cell>
           <cell r="E10">
-            <v>97.210907835692097</v>
+            <v>104.34549376348122</v>
           </cell>
           <cell r="F10">
-            <v>110.54326482948768</v>
+            <v>99.932079382996733</v>
           </cell>
           <cell r="G10">
-            <v>0.5430982519590114</v>
+            <v>0.51318359375</v>
           </cell>
           <cell r="H10">
-            <v>66.972413793103442</v>
+            <v>73.95225806451613</v>
           </cell>
           <cell r="I10">
-            <v>57.206896551724135</v>
+            <v>66.064516129032256</v>
           </cell>
           <cell r="J10">
-            <v>18.275862068965516</v>
+            <v>27.677419354838708</v>
           </cell>
           <cell r="K10">
-            <v>8.068965517241379</v>
+            <v>15.516129032258064</v>
           </cell>
           <cell r="L10">
-            <v>9.7931034482758612</v>
+            <v>11.225806451612904</v>
           </cell>
           <cell r="M10">
             <v>0</v>
           </cell>
           <cell r="N10">
-            <v>-8.3049596389430835</v>
+            <v>-0.94217041800932655</v>
           </cell>
           <cell r="O10">
-            <v>98.685284640171872</v>
+            <v>97.9635725257845</v>
           </cell>
           <cell r="P10">
-            <v>109.91881615719028</v>
+            <v>108.1900253682186</v>
           </cell>
           <cell r="Q10">
-            <v>0.54303164908384227</v>
+            <v>0.5367215041128085</v>
           </cell>
           <cell r="R10">
-            <v>64.849999999999994</v>
+            <v>64.8</v>
           </cell>
           <cell r="S10">
-            <v>56.28125</v>
+            <v>54.903225806451616</v>
           </cell>
           <cell r="T10">
-            <v>18.125</v>
+            <v>20</v>
           </cell>
           <cell r="U10">
-            <v>8.84375</v>
+            <v>10.903225806451612</v>
           </cell>
           <cell r="V10">
-            <v>9.4375</v>
+            <v>12</v>
           </cell>
           <cell r="W10">
             <v>0</v>
           </cell>
           <cell r="X10">
-            <v>-3.5</v>
+            <v>-14</v>
           </cell>
         </row>
         <row r="11">
@@ -9299,73 +9443,73 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>Cornell</v>
+            <v>Wichita State</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Yale</v>
+            <v>Tulsa</v>
           </cell>
           <cell r="D11">
-            <v>3.782470992490822</v>
+            <v>7.770824188202555</v>
           </cell>
           <cell r="E11">
-            <v>97.272279310137606</v>
+            <v>105.2828776380081</v>
           </cell>
           <cell r="F11">
-            <v>100.79730647263705</v>
+            <v>97.27607791375182</v>
           </cell>
           <cell r="G11">
-            <v>0.59271935283136279</v>
+            <v>0.50232558139534889</v>
           </cell>
           <cell r="H11">
-            <v>71.856923076923081</v>
+            <v>67.778064516129021</v>
           </cell>
           <cell r="I11">
-            <v>61.807692307692307</v>
+            <v>62.41935483870968</v>
           </cell>
           <cell r="J11">
-            <v>18.73076923076923</v>
+            <v>22.516129032258064</v>
           </cell>
           <cell r="K11">
-            <v>10.076923076923077</v>
+            <v>14.806451612903226</v>
           </cell>
           <cell r="L11">
-            <v>11.884615384615385</v>
+            <v>10.258064516129032</v>
           </cell>
           <cell r="M11">
             <v>0</v>
           </cell>
           <cell r="N11">
-            <v>7.4286283767729033</v>
+            <v>5.3476433114678237</v>
           </cell>
           <cell r="O11">
-            <v>100.45512973101643</v>
+            <v>100.58857934431276</v>
           </cell>
           <cell r="P11">
-            <v>103.83477980468992</v>
+            <v>101.35085266969703</v>
           </cell>
           <cell r="Q11">
-            <v>0.56940160394818018</v>
+            <v>0.57346491228070173</v>
           </cell>
           <cell r="R11">
-            <v>66.131428571428572</v>
+            <v>68.307096774193553</v>
           </cell>
           <cell r="S11">
-            <v>57.892857142857146</v>
+            <v>58.838709677419352</v>
           </cell>
           <cell r="T11">
-            <v>20.428571428571427</v>
+            <v>23.64516129032258</v>
           </cell>
           <cell r="U11">
-            <v>10.178571428571429</v>
+            <v>11.193548387096774</v>
           </cell>
           <cell r="V11">
-            <v>9.4285714285714288</v>
+            <v>10.258064516129032</v>
           </cell>
           <cell r="W11">
             <v>0</v>
           </cell>
           <cell r="X11">
-            <v>3.5</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="12">
@@ -9373,73 +9517,73 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>Pennsylvania</v>
+            <v>Arizona</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Harvard</v>
+            <v>Houston</v>
           </cell>
           <cell r="D12">
-            <v>-0.51591821964888473</v>
+            <v>23.726370739322146</v>
           </cell>
           <cell r="E12">
-            <v>100.50742749351569</v>
+            <v>101.71571463594017</v>
           </cell>
           <cell r="F12">
-            <v>109.41069198990621</v>
+            <v>98.8245285938752</v>
           </cell>
           <cell r="G12">
-            <v>0.50901741293532343</v>
+            <v>0.54952581664910427</v>
           </cell>
           <cell r="H12">
-            <v>68.677037037037039</v>
+            <v>70.829677419354852</v>
           </cell>
           <cell r="I12">
-            <v>59.555555555555557</v>
+            <v>61.225806451612904</v>
           </cell>
           <cell r="J12">
-            <v>22.666666666666668</v>
+            <v>26.225806451612904</v>
           </cell>
           <cell r="K12">
-            <v>11.703703703703704</v>
+            <v>12.903225806451612</v>
           </cell>
           <cell r="L12">
-            <v>10.851851851851851</v>
+            <v>10.96774193548387</v>
           </cell>
           <cell r="M12">
             <v>0</v>
           </cell>
           <cell r="N12">
-            <v>-2.8665585524076791</v>
+            <v>20.523299572994468</v>
           </cell>
           <cell r="O12">
-            <v>95.7233341778566</v>
+            <v>105.83703703703704</v>
           </cell>
           <cell r="P12">
-            <v>111.41414803981939</v>
+            <v>98.084829653904706</v>
           </cell>
           <cell r="Q12">
-            <v>0.5349673202614379</v>
+            <v>0.52282491944146081</v>
           </cell>
           <cell r="R12">
-            <v>63.957142857142856</v>
+            <v>64.807999999999993</v>
           </cell>
           <cell r="S12">
-            <v>54.642857142857146</v>
+            <v>62.06666666666667</v>
           </cell>
           <cell r="T12">
-            <v>15</v>
+            <v>16.533333333333335</v>
           </cell>
           <cell r="U12">
-            <v>8.2142857142857135</v>
+            <v>12.833333333333334</v>
           </cell>
           <cell r="V12">
-            <v>10.928571428571429</v>
+            <v>8.3000000000000007</v>
           </cell>
           <cell r="W12">
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>3</v>
+            <v>-2.5</v>
           </cell>
         </row>
         <row r="13">
@@ -9447,73 +9591,73 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>Dayton</v>
+            <v>Utah State</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Saint Louis</v>
+            <v>San Diego State</v>
           </cell>
           <cell r="D13">
-            <v>7.2080821342928445</v>
+            <v>16.347492910416953</v>
           </cell>
           <cell r="E13">
-            <v>95.080309824704429</v>
+            <v>99.814093598708979</v>
           </cell>
           <cell r="F13">
-            <v>92.716319767963711</v>
+            <v>89.773356716311071</v>
           </cell>
           <cell r="G13">
-            <v>0.52316486161251508</v>
+            <v>0.57657142857142862</v>
           </cell>
           <cell r="H13">
-            <v>68.127741935483868</v>
+            <v>67.801333333333332</v>
           </cell>
           <cell r="I13">
-            <v>53.612903225806448</v>
+            <v>58.333333333333336</v>
           </cell>
           <cell r="J13">
-            <v>25.29032258064516</v>
+            <v>22.2</v>
           </cell>
           <cell r="K13">
-            <v>8.7096774193548381</v>
+            <v>10.766666666666667</v>
           </cell>
           <cell r="L13">
-            <v>12.096774193548388</v>
+            <v>10.466666666666667</v>
           </cell>
           <cell r="M13">
             <v>0</v>
           </cell>
           <cell r="N13">
-            <v>12.924462689730786</v>
+            <v>14.550197800997752</v>
           </cell>
           <cell r="O13">
-            <v>96.65371999791742</v>
+            <v>96.841816840552212</v>
           </cell>
           <cell r="P13">
-            <v>94.854733271656428</v>
+            <v>87.434270076584269</v>
           </cell>
           <cell r="Q13">
-            <v>0.60122699386503065</v>
+            <v>0.54383954154727798</v>
           </cell>
           <cell r="R13">
-            <v>71.082666666666668</v>
+            <v>69.707999999999998</v>
           </cell>
           <cell r="S13">
-            <v>59.766666666666666</v>
+            <v>58.166666666666664</v>
           </cell>
           <cell r="T13">
-            <v>20.566666666666666</v>
+            <v>21.533333333333335</v>
           </cell>
           <cell r="U13">
-            <v>10.133333333333333</v>
+            <v>9.6999999999999993</v>
           </cell>
           <cell r="V13">
-            <v>12.4</v>
+            <v>11.766666666666667</v>
           </cell>
           <cell r="W13">
             <v>0</v>
           </cell>
           <cell r="X13">
-            <v>6</v>
+            <v>-1.5</v>
           </cell>
         </row>
         <row r="14">
@@ -9521,73 +9665,73 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>Wisconsin</v>
+            <v>St. John's</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Michigan</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D14">
-            <v>15.99115140253407</v>
+            <v>15.109788733361889</v>
           </cell>
           <cell r="E14">
-            <v>101.25838978230519</v>
+            <v>102.58678864787763</v>
           </cell>
           <cell r="F14">
-            <v>98.106398085976267</v>
+            <v>99.76074998519745</v>
           </cell>
           <cell r="G14">
-            <v>0.54685863874345553</v>
+            <v>0.50967573221757323</v>
           </cell>
           <cell r="H14">
-            <v>69.153548387096777</v>
+            <v>70.571612903225812</v>
           </cell>
           <cell r="I14">
-            <v>61.612903225806448</v>
+            <v>61.677419354838712</v>
           </cell>
           <cell r="J14">
-            <v>20.29032258064516</v>
+            <v>26.225806451612904</v>
           </cell>
           <cell r="K14">
-            <v>10.419354838709678</v>
+            <v>13.193548387096774</v>
           </cell>
           <cell r="L14">
-            <v>9.0322580645161299</v>
+            <v>10.548387096774194</v>
           </cell>
           <cell r="M14">
             <v>0</v>
           </cell>
           <cell r="N14">
-            <v>23.915638484765847</v>
+            <v>18.208291246988694</v>
           </cell>
           <cell r="O14">
-            <v>98.283491704002756</v>
+            <v>99.985237449118031</v>
           </cell>
           <cell r="P14">
-            <v>95.448163069798071</v>
+            <v>95.057403075511033</v>
           </cell>
           <cell r="Q14">
-            <v>0.5870726495726496</v>
+            <v>0.55555555555555558</v>
           </cell>
           <cell r="R14">
-            <v>71.669677419354841</v>
+            <v>66.338064516129037</v>
           </cell>
           <cell r="S14">
-            <v>60.387096774193552</v>
+            <v>58.645161290322584</v>
           </cell>
           <cell r="T14">
-            <v>23.516129032258064</v>
+            <v>18.29032258064516</v>
           </cell>
           <cell r="U14">
-            <v>11.225806451612904</v>
+            <v>11.387096774193548</v>
           </cell>
           <cell r="V14">
-            <v>12.161290322580646</v>
+            <v>11.03225806451613</v>
           </cell>
           <cell r="W14">
             <v>0</v>
           </cell>
           <cell r="X14">
-            <v>12.5</v>
+            <v>2.5</v>
           </cell>
         </row>
         <row r="15">
@@ -9595,73 +9739,73 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>Vanderbilt</v>
+            <v>Akron</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Florida</v>
+            <v>Toledo</v>
           </cell>
           <cell r="D15">
-            <v>19.188801343657655</v>
+            <v>10.49945141256813</v>
           </cell>
           <cell r="E15">
-            <v>100.6501092787602</v>
+            <v>99.8801284338209</v>
           </cell>
           <cell r="F15">
-            <v>97.808224636267653</v>
+            <v>94.797305672709399</v>
           </cell>
           <cell r="G15">
-            <v>0.55637126376507606</v>
+            <v>0.59409687184661952</v>
           </cell>
           <cell r="H15">
-            <v>70.905806451612904</v>
+            <v>71.441290322580642</v>
           </cell>
           <cell r="I15">
-            <v>61.516129032258064</v>
+            <v>63.935483870967744</v>
           </cell>
           <cell r="J15">
-            <v>23.612903225806452</v>
+            <v>17.64516129032258</v>
           </cell>
           <cell r="K15">
-            <v>10.741935483870968</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="L15">
-            <v>9.741935483870968</v>
+            <v>11.096774193548388</v>
           </cell>
           <cell r="M15">
             <v>0</v>
           </cell>
           <cell r="N15">
-            <v>22.748625673592354</v>
+            <v>4.1368006701786264</v>
           </cell>
           <cell r="O15">
-            <v>104.56180875012235</v>
+            <v>100.01830473218929</v>
           </cell>
           <cell r="P15">
-            <v>99.903229832962509</v>
+            <v>101.61078845085268</v>
           </cell>
           <cell r="Q15">
-            <v>0.54031856645097065</v>
+            <v>0.54476439790575915</v>
           </cell>
           <cell r="R15">
-            <v>71.534193548387094</v>
+            <v>69.429677419354846</v>
           </cell>
           <cell r="S15">
-            <v>64.806451612903231</v>
+            <v>61.612903225806448</v>
           </cell>
           <cell r="T15">
-            <v>24.967741935483872</v>
+            <v>18.64516129032258</v>
           </cell>
           <cell r="U15">
-            <v>15.903225806451612</v>
+            <v>10.516129032258064</v>
           </cell>
           <cell r="V15">
-            <v>11.64516129032258</v>
+            <v>10.129032258064516</v>
           </cell>
           <cell r="W15">
             <v>0</v>
           </cell>
           <cell r="X15">
-            <v>6.5</v>
+            <v>-7</v>
           </cell>
         </row>
         <row r="16">
@@ -9669,73 +9813,73 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>Charlotte</v>
+            <v>Duke</v>
           </cell>
           <cell r="C16" t="str">
-            <v>South Florida</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D16">
-            <v>-0.94217041800932655</v>
+            <v>23.818031475685999</v>
           </cell>
           <cell r="E16">
-            <v>97.9635725257845</v>
+            <v>101.49806376319559</v>
           </cell>
           <cell r="F16">
-            <v>108.1900253682186</v>
+            <v>100.14794611787336</v>
           </cell>
           <cell r="G16">
-            <v>0.5367215041128085</v>
+            <v>0.57475083056478404</v>
           </cell>
           <cell r="H16">
-            <v>64.8</v>
+            <v>66.400000000000006</v>
           </cell>
           <cell r="I16">
-            <v>54.903225806451616</v>
+            <v>58.258064516129032</v>
           </cell>
           <cell r="J16">
-            <v>20</v>
+            <v>22.096774193548388</v>
           </cell>
           <cell r="K16">
-            <v>10.903225806451612</v>
+            <v>12</v>
           </cell>
           <cell r="L16">
-            <v>12</v>
+            <v>10.419354838709678</v>
           </cell>
           <cell r="M16">
             <v>0</v>
           </cell>
           <cell r="N16">
-            <v>10.662427729240893</v>
+            <v>13.035509619415494</v>
           </cell>
           <cell r="O16">
-            <v>104.34549376348122</v>
+            <v>102.89121915051371</v>
           </cell>
           <cell r="P16">
-            <v>99.932079382996733</v>
+            <v>105.11224188648033</v>
           </cell>
           <cell r="Q16">
-            <v>0.51318359375</v>
+            <v>0.54407859798194369</v>
           </cell>
           <cell r="R16">
-            <v>73.95225806451613</v>
+            <v>67.184516129032261</v>
           </cell>
           <cell r="S16">
-            <v>66.064516129032256</v>
+            <v>60.741935483870968</v>
           </cell>
           <cell r="T16">
-            <v>27.677419354838708</v>
+            <v>20.580645161290324</v>
           </cell>
           <cell r="U16">
-            <v>15.516129032258064</v>
+            <v>13.451612903225806</v>
           </cell>
           <cell r="V16">
-            <v>11.225806451612904</v>
+            <v>10.838709677419354</v>
           </cell>
           <cell r="W16">
             <v>0</v>
           </cell>
           <cell r="X16">
-            <v>14</v>
+            <v>-8.5</v>
           </cell>
         </row>
         <row r="17">
@@ -9743,73 +9887,73 @@
             <v>16</v>
           </cell>
           <cell r="B17" t="str">
-            <v>Tulsa</v>
+            <v>Louisiana Tech</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Wichita State</v>
+            <v>Kennesaw State</v>
           </cell>
           <cell r="D17">
-            <v>5.3476433114678237</v>
+            <v>2.6443345975686983</v>
           </cell>
           <cell r="E17">
-            <v>100.58857934431276</v>
+            <v>99.919161188678217</v>
           </cell>
           <cell r="F17">
-            <v>101.35085266969703</v>
+            <v>98.415627483867411</v>
           </cell>
           <cell r="G17">
-            <v>0.57346491228070173</v>
+            <v>0.49525669642857145</v>
           </cell>
           <cell r="H17">
-            <v>68.307096774193553</v>
+            <v>65.900645161290328</v>
           </cell>
           <cell r="I17">
-            <v>58.838709677419352</v>
+            <v>57.806451612903224</v>
           </cell>
           <cell r="J17">
-            <v>23.64516129032258</v>
+            <v>19.129032258064516</v>
           </cell>
           <cell r="K17">
-            <v>11.193548387096774</v>
+            <v>12.96774193548387</v>
           </cell>
           <cell r="L17">
-            <v>10.258064516129032</v>
+            <v>12.64516129032258</v>
           </cell>
           <cell r="M17">
             <v>0</v>
           </cell>
           <cell r="N17">
-            <v>7.770824188202555</v>
+            <v>6.490752715038262</v>
           </cell>
           <cell r="O17">
-            <v>105.2828776380081</v>
+            <v>101.8432322449375</v>
           </cell>
           <cell r="P17">
-            <v>97.27607791375182</v>
+            <v>97.141081053482708</v>
           </cell>
           <cell r="Q17">
-            <v>0.50232558139534889</v>
+            <v>0.52519480519480521</v>
           </cell>
           <cell r="R17">
-            <v>67.778064516129021</v>
+            <v>71.699354838709667</v>
           </cell>
           <cell r="S17">
-            <v>62.41935483870968</v>
+            <v>62.096774193548384</v>
           </cell>
           <cell r="T17">
-            <v>22.516129032258064</v>
+            <v>26.516129032258064</v>
           </cell>
           <cell r="U17">
-            <v>14.806451612903226</v>
+            <v>13.806451612903226</v>
           </cell>
           <cell r="V17">
-            <v>10.258064516129032</v>
+            <v>11.741935483870968</v>
           </cell>
           <cell r="W17">
             <v>0</v>
           </cell>
           <cell r="X17">
-            <v>-1</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="18">
@@ -9817,73 +9961,73 @@
             <v>17</v>
           </cell>
           <cell r="B18" t="str">
-            <v>Kennesaw State</v>
+            <v>UC Irvine</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Louisiana Tech</v>
+            <v>Hawaii</v>
           </cell>
           <cell r="D18">
-            <v>6.490752715038262</v>
+            <v>5.2870372643884913</v>
           </cell>
           <cell r="E18">
-            <v>101.8432322449375</v>
+            <v>98.000795228628249</v>
           </cell>
           <cell r="F18">
-            <v>97.141081053482708</v>
+            <v>92.824900535566286</v>
           </cell>
           <cell r="G18">
-            <v>0.52519480519480521</v>
+            <v>0.51370585134422775</v>
           </cell>
           <cell r="H18">
-            <v>71.699354838709667</v>
+            <v>71.811612903225807</v>
           </cell>
           <cell r="I18">
-            <v>62.096774193548384</v>
+            <v>61.193548387096776</v>
           </cell>
           <cell r="J18">
-            <v>26.516129032258064</v>
+            <v>21.419354838709676</v>
           </cell>
           <cell r="K18">
-            <v>13.806451612903226</v>
+            <v>11.548387096774194</v>
           </cell>
           <cell r="L18">
-            <v>11.741935483870968</v>
+            <v>12.741935483870968</v>
           </cell>
           <cell r="M18">
             <v>0</v>
           </cell>
           <cell r="N18">
-            <v>2.6443345975686983</v>
+            <v>2.4205256715728276</v>
           </cell>
           <cell r="O18">
-            <v>99.919161188678217</v>
+            <v>96.251520482533294</v>
           </cell>
           <cell r="P18">
-            <v>98.415627483867411</v>
+            <v>92.252558584997232</v>
           </cell>
           <cell r="Q18">
-            <v>0.49525669642857145</v>
+            <v>0.52753872633390708</v>
           </cell>
           <cell r="R18">
-            <v>65.900645161290328</v>
+            <v>71.861333333333334</v>
           </cell>
           <cell r="S18">
-            <v>57.806451612903224</v>
+            <v>58.1</v>
           </cell>
           <cell r="T18">
-            <v>19.129032258064516</v>
+            <v>25.366666666666667</v>
           </cell>
           <cell r="U18">
-            <v>12.96774193548387</v>
+            <v>10.733333333333333</v>
           </cell>
           <cell r="V18">
-            <v>12.64516129032258</v>
+            <v>13.333333333333334</v>
           </cell>
           <cell r="W18">
             <v>0</v>
           </cell>
           <cell r="X18">
-            <v>-1.5</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="19">
@@ -9891,74 +10035,5392 @@
             <v>18</v>
           </cell>
           <cell r="B19" t="str">
+            <v>Utah Valley</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>California Baptist</v>
+          </cell>
+          <cell r="D19">
+            <v>7.1660953976463073</v>
+          </cell>
+          <cell r="E19">
+            <v>96.788608522667772</v>
+          </cell>
+          <cell r="F19">
+            <v>87.924687269369926</v>
+          </cell>
+          <cell r="G19">
+            <v>0.56105144149236852</v>
+          </cell>
+          <cell r="H19">
+            <v>70.398666666666671</v>
+          </cell>
+          <cell r="I19">
+            <v>58.966666666666669</v>
+          </cell>
+          <cell r="J19">
+            <v>21.133333333333333</v>
+          </cell>
+          <cell r="K19">
+            <v>11.933333333333334</v>
+          </cell>
+          <cell r="L19">
+            <v>14.066666666666666</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>4.601636720836713</v>
+          </cell>
+          <cell r="O19">
+            <v>101.16726287262874</v>
+          </cell>
+          <cell r="P19">
+            <v>89.920292368090941</v>
+          </cell>
+          <cell r="Q19">
+            <v>0.48252536640360766</v>
+          </cell>
+          <cell r="R19">
+            <v>67.391999999999996</v>
+          </cell>
+          <cell r="S19">
+            <v>59.133333333333333</v>
+          </cell>
+          <cell r="T19">
+            <v>21.8</v>
+          </cell>
+          <cell r="U19">
+            <v>13.866666666666667</v>
+          </cell>
+          <cell r="V19">
+            <v>12.533333333333333</v>
+          </cell>
+          <cell r="W19">
+            <v>0</v>
+          </cell>
+          <cell r="X19">
+            <v>-3</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>UMBC</v>
+          </cell>
+          <cell r="C20" t="str">
             <v>Vermont</v>
           </cell>
-          <cell r="C19" t="str">
+          <cell r="D20">
+            <v>-8.1832066239376893</v>
+          </cell>
+          <cell r="E20">
+            <v>97.210907835692097</v>
+          </cell>
+          <cell r="F20">
+            <v>110.54326482948768</v>
+          </cell>
+          <cell r="G20">
+            <v>0.5430982519590114</v>
+          </cell>
+          <cell r="H20">
+            <v>66.972413793103442</v>
+          </cell>
+          <cell r="I20">
+            <v>57.206896551724135</v>
+          </cell>
+          <cell r="J20">
+            <v>18.275862068965516</v>
+          </cell>
+          <cell r="K20">
+            <v>8.068965517241379</v>
+          </cell>
+          <cell r="L20">
+            <v>9.7931034482758612</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>-8.3049596389430835</v>
+          </cell>
+          <cell r="O20">
+            <v>98.685284640171872</v>
+          </cell>
+          <cell r="P20">
+            <v>109.91881615719028</v>
+          </cell>
+          <cell r="Q20">
+            <v>0.54303164908384227</v>
+          </cell>
+          <cell r="R20">
+            <v>64.849999999999994</v>
+          </cell>
+          <cell r="S20">
+            <v>56.28125</v>
+          </cell>
+          <cell r="T20">
+            <v>18.125</v>
+          </cell>
+          <cell r="U20">
+            <v>8.84375</v>
+          </cell>
+          <cell r="V20">
+            <v>9.4375</v>
+          </cell>
+          <cell r="W20">
+            <v>0</v>
+          </cell>
+          <cell r="X20">
+            <v>-3.5</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>Howard</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>North Carolina Central</v>
+          </cell>
+          <cell r="D21">
+            <v>-7.0667288784066029</v>
+          </cell>
+          <cell r="E21">
+            <v>97.771296389419689</v>
+          </cell>
+          <cell r="F21">
+            <v>101.22012384797286</v>
+          </cell>
+          <cell r="G21">
+            <v>0.52172686230248311</v>
+          </cell>
+          <cell r="H21">
+            <v>69.380645161290332</v>
+          </cell>
+          <cell r="I21">
+            <v>57.161290322580648</v>
+          </cell>
+          <cell r="J21">
+            <v>24.838709677419356</v>
+          </cell>
+          <cell r="K21">
+            <v>12.290322580645162</v>
+          </cell>
+          <cell r="L21">
+            <v>13.580645161290322</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>-12.049706064548028</v>
+          </cell>
+          <cell r="O21">
+            <v>97.391178918169217</v>
+          </cell>
+          <cell r="P21">
+            <v>102.17668911130822</v>
+          </cell>
+          <cell r="Q21">
+            <v>0.49514563106796117</v>
+          </cell>
+          <cell r="R21">
+            <v>68.108965517241387</v>
+          </cell>
+          <cell r="S21">
+            <v>56.827586206896555</v>
+          </cell>
+          <cell r="T21">
+            <v>22.03448275862069</v>
+          </cell>
+          <cell r="U21">
+            <v>10.689655172413794</v>
+          </cell>
+          <cell r="V21">
+            <v>12.275862068965518</v>
+          </cell>
+          <cell r="W21">
+            <v>0</v>
+          </cell>
+          <cell r="X21">
+            <v>-13</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>Southern</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>Prairie View A&amp;M</v>
+          </cell>
+          <cell r="D22">
+            <v>-6.7092460643817606</v>
+          </cell>
+          <cell r="E22">
+            <v>99.018646109371232</v>
+          </cell>
+          <cell r="F22">
+            <v>93.207129449722274</v>
+          </cell>
+          <cell r="G22">
+            <v>0.50943396226415094</v>
+          </cell>
+          <cell r="H22">
+            <v>72.842580645161291</v>
+          </cell>
+          <cell r="I22">
+            <v>61.548387096774192</v>
+          </cell>
+          <cell r="J22">
+            <v>24.93548387096774</v>
+          </cell>
+          <cell r="K22">
+            <v>11.67741935483871</v>
+          </cell>
+          <cell r="L22">
+            <v>12</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>-10.748183340293197</v>
+          </cell>
+          <cell r="O22">
+            <v>96.942723004694827</v>
+          </cell>
+          <cell r="P22">
+            <v>93.291737667336207</v>
+          </cell>
+          <cell r="Q22">
+            <v>0.49388297872340425</v>
+          </cell>
+          <cell r="R22">
+            <v>74.380645161290332</v>
+          </cell>
+          <cell r="S22">
+            <v>60.645161290322584</v>
+          </cell>
+          <cell r="T22">
+            <v>26.451612903225808</v>
+          </cell>
+          <cell r="U22">
+            <v>10.161290322580646</v>
+          </cell>
+          <cell r="V22">
+            <v>12.258064516129032</v>
+          </cell>
+          <cell r="W22">
+            <v>0</v>
+          </cell>
+          <cell r="X22">
+            <v>-3</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>Cornell</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>Yale</v>
+          </cell>
+          <cell r="D23">
+            <v>3.782470992490822</v>
+          </cell>
+          <cell r="E23">
+            <v>97.272279310137606</v>
+          </cell>
+          <cell r="F23">
+            <v>100.79730647263705</v>
+          </cell>
+          <cell r="G23">
+            <v>0.59271935283136279</v>
+          </cell>
+          <cell r="H23">
+            <v>71.856923076923081</v>
+          </cell>
+          <cell r="I23">
+            <v>61.807692307692307</v>
+          </cell>
+          <cell r="J23">
+            <v>18.73076923076923</v>
+          </cell>
+          <cell r="K23">
+            <v>10.076923076923077</v>
+          </cell>
+          <cell r="L23">
+            <v>11.884615384615385</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>7.4286283767729033</v>
+          </cell>
+          <cell r="O23">
+            <v>100.45512973101643</v>
+          </cell>
+          <cell r="P23">
+            <v>103.83477980468992</v>
+          </cell>
+          <cell r="Q23">
+            <v>0.56940160394818018</v>
+          </cell>
+          <cell r="R23">
+            <v>66.131428571428572</v>
+          </cell>
+          <cell r="S23">
+            <v>57.892857142857146</v>
+          </cell>
+          <cell r="T23">
+            <v>20.428571428571427</v>
+          </cell>
+          <cell r="U23">
+            <v>10.178571428571429</v>
+          </cell>
+          <cell r="V23">
+            <v>9.4285714285714288</v>
+          </cell>
+          <cell r="W23">
+            <v>0</v>
+          </cell>
+          <cell r="X23">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Pennsylvania</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>Harvard</v>
+          </cell>
+          <cell r="D24">
+            <v>-0.51591821964888473</v>
+          </cell>
+          <cell r="E24">
+            <v>100.50742749351569</v>
+          </cell>
+          <cell r="F24">
+            <v>109.41069198990621</v>
+          </cell>
+          <cell r="G24">
+            <v>0.50901741293532343</v>
+          </cell>
+          <cell r="H24">
+            <v>68.677037037037039</v>
+          </cell>
+          <cell r="I24">
+            <v>59.555555555555557</v>
+          </cell>
+          <cell r="J24">
+            <v>22.666666666666668</v>
+          </cell>
+          <cell r="K24">
+            <v>11.703703703703704</v>
+          </cell>
+          <cell r="L24">
+            <v>10.851851851851851</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>-2.8665585524076791</v>
+          </cell>
+          <cell r="O24">
+            <v>95.7233341778566</v>
+          </cell>
+          <cell r="P24">
+            <v>111.41414803981939</v>
+          </cell>
+          <cell r="Q24">
+            <v>0.5349673202614379</v>
+          </cell>
+          <cell r="R24">
+            <v>63.957142857142856</v>
+          </cell>
+          <cell r="S24">
+            <v>54.642857142857146</v>
+          </cell>
+          <cell r="T24">
+            <v>15</v>
+          </cell>
+          <cell r="U24">
+            <v>8.2142857142857135</v>
+          </cell>
+          <cell r="V24">
+            <v>10.928571428571429</v>
+          </cell>
+          <cell r="W24">
+            <v>0</v>
+          </cell>
+          <cell r="X24">
+            <v>3.5</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Dayton</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Saint Louis</v>
+          </cell>
+          <cell r="D25">
+            <v>7.2080821342928445</v>
+          </cell>
+          <cell r="E25">
+            <v>95.080309824704429</v>
+          </cell>
+          <cell r="F25">
+            <v>92.716319767963711</v>
+          </cell>
+          <cell r="G25">
+            <v>0.52316486161251508</v>
+          </cell>
+          <cell r="H25">
+            <v>68.127741935483868</v>
+          </cell>
+          <cell r="I25">
+            <v>53.612903225806448</v>
+          </cell>
+          <cell r="J25">
+            <v>25.29032258064516</v>
+          </cell>
+          <cell r="K25">
+            <v>8.7096774193548381</v>
+          </cell>
+          <cell r="L25">
+            <v>12.096774193548388</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>12.924462689730786</v>
+          </cell>
+          <cell r="O25">
+            <v>96.65371999791742</v>
+          </cell>
+          <cell r="P25">
+            <v>94.854733271656428</v>
+          </cell>
+          <cell r="Q25">
+            <v>0.60122699386503065</v>
+          </cell>
+          <cell r="R25">
+            <v>71.082666666666668</v>
+          </cell>
+          <cell r="S25">
+            <v>59.766666666666666</v>
+          </cell>
+          <cell r="T25">
+            <v>20.566666666666666</v>
+          </cell>
+          <cell r="U25">
+            <v>10.133333333333333</v>
+          </cell>
+          <cell r="V25">
+            <v>12.4</v>
+          </cell>
+          <cell r="W25">
+            <v>0</v>
+          </cell>
+          <cell r="X25">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>St. Joseph's</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>VCU</v>
+          </cell>
+          <cell r="D26">
+            <v>0.35857878605365429</v>
+          </cell>
+          <cell r="E26">
+            <v>99.259251438526107</v>
+          </cell>
+          <cell r="F26">
+            <v>108.34882848626603</v>
+          </cell>
+          <cell r="G26">
+            <v>0.5</v>
+          </cell>
+          <cell r="H26">
+            <v>68.286451612903235</v>
+          </cell>
+          <cell r="I26">
+            <v>59.903225806451616</v>
+          </cell>
+          <cell r="J26">
+            <v>18.612903225806452</v>
+          </cell>
+          <cell r="K26">
+            <v>11.64516129032258</v>
+          </cell>
+          <cell r="L26">
+            <v>11.838709677419354</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>10.046934010674722</v>
+          </cell>
+          <cell r="O26">
+            <v>100.11649510419282</v>
+          </cell>
+          <cell r="P26">
+            <v>100.40585231866712</v>
+          </cell>
+          <cell r="Q26">
+            <v>0.54296008869179602</v>
+          </cell>
+          <cell r="R26">
+            <v>69.00645161290322</v>
+          </cell>
+          <cell r="S26">
+            <v>58.193548387096776</v>
+          </cell>
+          <cell r="T26">
+            <v>25.967741935483872</v>
+          </cell>
+          <cell r="U26">
+            <v>11.419354838709678</v>
+          </cell>
+          <cell r="V26">
+            <v>10.806451612903226</v>
+          </cell>
+          <cell r="W26">
+            <v>0</v>
+          </cell>
+          <cell r="X26">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Wisconsin</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>Michigan</v>
+          </cell>
+          <cell r="D27">
+            <v>15.99115140253407</v>
+          </cell>
+          <cell r="E27">
+            <v>101.25838978230519</v>
+          </cell>
+          <cell r="F27">
+            <v>98.106398085976267</v>
+          </cell>
+          <cell r="G27">
+            <v>0.54685863874345553</v>
+          </cell>
+          <cell r="H27">
+            <v>69.153548387096777</v>
+          </cell>
+          <cell r="I27">
+            <v>61.612903225806448</v>
+          </cell>
+          <cell r="J27">
+            <v>20.29032258064516</v>
+          </cell>
+          <cell r="K27">
+            <v>10.419354838709678</v>
+          </cell>
+          <cell r="L27">
+            <v>9.0322580645161299</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>23.915638484765847</v>
+          </cell>
+          <cell r="O27">
+            <v>98.283491704002756</v>
+          </cell>
+          <cell r="P27">
+            <v>95.448163069798071</v>
+          </cell>
+          <cell r="Q27">
+            <v>0.5870726495726496</v>
+          </cell>
+          <cell r="R27">
+            <v>71.669677419354841</v>
+          </cell>
+          <cell r="S27">
+            <v>60.387096774193552</v>
+          </cell>
+          <cell r="T27">
+            <v>23.516129032258064</v>
+          </cell>
+          <cell r="U27">
+            <v>11.225806451612904</v>
+          </cell>
+          <cell r="V27">
+            <v>12.161290322580646</v>
+          </cell>
+          <cell r="W27">
+            <v>0</v>
+          </cell>
+          <cell r="X27">
+            <v>12.5</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>Purdue</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>UCLA</v>
+          </cell>
+          <cell r="D28">
+            <v>20.822747409737431</v>
+          </cell>
+          <cell r="E28">
+            <v>102.36430980153686</v>
+          </cell>
+          <cell r="F28">
+            <v>102.10099533949814</v>
+          </cell>
+          <cell r="G28">
+            <v>0.57913090128755362</v>
+          </cell>
+          <cell r="H28">
+            <v>65.54451612903226</v>
+          </cell>
+          <cell r="I28">
+            <v>60.12903225806452</v>
+          </cell>
+          <cell r="J28">
+            <v>17</v>
+          </cell>
+          <cell r="K28">
+            <v>11.161290322580646</v>
+          </cell>
+          <cell r="L28">
+            <v>9.0967741935483879</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>16.04165934317437</v>
+          </cell>
+          <cell r="O28">
+            <v>100.9511732509619</v>
+          </cell>
+          <cell r="P28">
+            <v>92.195689602132376</v>
+          </cell>
+          <cell r="Q28">
+            <v>0.53971318257032541</v>
+          </cell>
+          <cell r="R28">
+            <v>65.94580645161291</v>
+          </cell>
+          <cell r="S28">
+            <v>58.483870967741936</v>
+          </cell>
+          <cell r="T28">
+            <v>19.451612903225808</v>
+          </cell>
+          <cell r="U28">
+            <v>10.064516129032258</v>
+          </cell>
+          <cell r="V28">
+            <v>8.9677419354838701</v>
+          </cell>
+          <cell r="W28">
+            <v>0</v>
+          </cell>
+          <cell r="X28">
+            <v>-7</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Vanderbilt</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>Florida</v>
+          </cell>
+          <cell r="D29">
+            <v>19.188801343657655</v>
+          </cell>
+          <cell r="E29">
+            <v>100.6501092787602</v>
+          </cell>
+          <cell r="F29">
+            <v>97.808224636267653</v>
+          </cell>
+          <cell r="G29">
+            <v>0.55637126376507606</v>
+          </cell>
+          <cell r="H29">
+            <v>70.905806451612904</v>
+          </cell>
+          <cell r="I29">
+            <v>61.516129032258064</v>
+          </cell>
+          <cell r="J29">
+            <v>23.612903225806452</v>
+          </cell>
+          <cell r="K29">
+            <v>10.741935483870968</v>
+          </cell>
+          <cell r="L29">
+            <v>9.741935483870968</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>22.748625673592354</v>
+          </cell>
+          <cell r="O29">
+            <v>104.56180875012235</v>
+          </cell>
+          <cell r="P29">
+            <v>99.903229832962509</v>
+          </cell>
+          <cell r="Q29">
+            <v>0.54031856645097065</v>
+          </cell>
+          <cell r="R29">
+            <v>71.534193548387094</v>
+          </cell>
+          <cell r="S29">
+            <v>64.806451612903231</v>
+          </cell>
+          <cell r="T29">
+            <v>24.967741935483872</v>
+          </cell>
+          <cell r="U29">
+            <v>15.903225806451612</v>
+          </cell>
+          <cell r="V29">
+            <v>11.64516129032258</v>
+          </cell>
+          <cell r="W29">
+            <v>0</v>
+          </cell>
+          <cell r="X29">
+            <v>8.5</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Ole Miss</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>Arkansas</v>
+          </cell>
+          <cell r="D30">
+            <v>8.9278178203979799</v>
+          </cell>
+          <cell r="E30">
+            <v>100.09953473783261</v>
+          </cell>
+          <cell r="F30">
+            <v>93.948889412718557</v>
+          </cell>
+          <cell r="G30">
+            <v>0.50161812297734631</v>
+          </cell>
+          <cell r="H30">
+            <v>68.278709677419357</v>
+          </cell>
+          <cell r="I30">
+            <v>59.806451612903224</v>
+          </cell>
+          <cell r="J30">
+            <v>20.35483870967742</v>
+          </cell>
+          <cell r="K30">
+            <v>10.225806451612904</v>
+          </cell>
+          <cell r="L30">
+            <v>9.741935483870968</v>
+          </cell>
+          <cell r="M30">
+            <v>0</v>
+          </cell>
+          <cell r="N30">
+            <v>20.289786813604461</v>
+          </cell>
+          <cell r="O30">
+            <v>101.81190917064613</v>
+          </cell>
+          <cell r="P30">
+            <v>97.741343816793645</v>
+          </cell>
+          <cell r="Q30">
+            <v>0.56654947262682065</v>
+          </cell>
+          <cell r="R30">
+            <v>72.56258064516129</v>
+          </cell>
+          <cell r="S30">
+            <v>64.225806451612897</v>
+          </cell>
+          <cell r="T30">
+            <v>23.419354838709676</v>
+          </cell>
+          <cell r="U30">
+            <v>11</v>
+          </cell>
+          <cell r="V30">
+            <v>9.0322580645161299</v>
+          </cell>
+          <cell r="W30">
+            <v>0</v>
+          </cell>
+          <cell r="X30">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Charlotte</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>South Florida</v>
+          </cell>
+          <cell r="D31">
+            <v>-0.94217041800932655</v>
+          </cell>
+          <cell r="E31">
+            <v>97.9635725257845</v>
+          </cell>
+          <cell r="F31">
+            <v>108.1900253682186</v>
+          </cell>
+          <cell r="G31">
+            <v>0.5367215041128085</v>
+          </cell>
+          <cell r="H31">
+            <v>64.8</v>
+          </cell>
+          <cell r="I31">
+            <v>54.903225806451616</v>
+          </cell>
+          <cell r="J31">
+            <v>20</v>
+          </cell>
+          <cell r="K31">
+            <v>10.903225806451612</v>
+          </cell>
+          <cell r="L31">
+            <v>12</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+          <cell r="N31">
+            <v>10.662427729240893</v>
+          </cell>
+          <cell r="O31">
+            <v>104.34549376348122</v>
+          </cell>
+          <cell r="P31">
+            <v>99.932079382996733</v>
+          </cell>
+          <cell r="Q31">
+            <v>0.51318359375</v>
+          </cell>
+          <cell r="R31">
+            <v>73.95225806451613</v>
+          </cell>
+          <cell r="S31">
+            <v>66.064516129032256</v>
+          </cell>
+          <cell r="T31">
+            <v>27.677419354838708</v>
+          </cell>
+          <cell r="U31">
+            <v>15.516129032258064</v>
+          </cell>
+          <cell r="V31">
+            <v>11.225806451612904</v>
+          </cell>
+          <cell r="W31">
+            <v>0</v>
+          </cell>
+          <cell r="X31">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>Tulsa</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>Wichita State</v>
+          </cell>
+          <cell r="D32">
+            <v>5.3476433114678237</v>
+          </cell>
+          <cell r="E32">
+            <v>100.58857934431276</v>
+          </cell>
+          <cell r="F32">
+            <v>101.35085266969703</v>
+          </cell>
+          <cell r="G32">
+            <v>0.57346491228070173</v>
+          </cell>
+          <cell r="H32">
+            <v>68.307096774193553</v>
+          </cell>
+          <cell r="I32">
+            <v>58.838709677419352</v>
+          </cell>
+          <cell r="J32">
+            <v>23.64516129032258</v>
+          </cell>
+          <cell r="K32">
+            <v>11.193548387096774</v>
+          </cell>
+          <cell r="L32">
+            <v>10.258064516129032</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+          <cell r="N32">
+            <v>7.770824188202555</v>
+          </cell>
+          <cell r="O32">
+            <v>105.2828776380081</v>
+          </cell>
+          <cell r="P32">
+            <v>97.27607791375182</v>
+          </cell>
+          <cell r="Q32">
+            <v>0.50232558139534889</v>
+          </cell>
+          <cell r="R32">
+            <v>67.778064516129021</v>
+          </cell>
+          <cell r="S32">
+            <v>62.41935483870968</v>
+          </cell>
+          <cell r="T32">
+            <v>22.516129032258064</v>
+          </cell>
+          <cell r="U32">
+            <v>14.806451612903226</v>
+          </cell>
+          <cell r="V32">
+            <v>10.258064516129032</v>
+          </cell>
+          <cell r="W32">
+            <v>0</v>
+          </cell>
+          <cell r="X32">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>Houston</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>Arizona</v>
+          </cell>
+          <cell r="D33">
+            <v>20.523299572994468</v>
+          </cell>
+          <cell r="E33">
+            <v>105.83703703703704</v>
+          </cell>
+          <cell r="F33">
+            <v>98.084829653904706</v>
+          </cell>
+          <cell r="G33">
+            <v>0.52282491944146081</v>
+          </cell>
+          <cell r="H33">
+            <v>64.807999999999993</v>
+          </cell>
+          <cell r="I33">
+            <v>62.06666666666667</v>
+          </cell>
+          <cell r="J33">
+            <v>16.533333333333335</v>
+          </cell>
+          <cell r="K33">
+            <v>12.833333333333334</v>
+          </cell>
+          <cell r="L33">
+            <v>8.3000000000000007</v>
+          </cell>
+          <cell r="M33">
+            <v>0</v>
+          </cell>
+          <cell r="N33">
+            <v>23.726370739322146</v>
+          </cell>
+          <cell r="O33">
+            <v>101.71571463594017</v>
+          </cell>
+          <cell r="P33">
+            <v>98.8245285938752</v>
+          </cell>
+          <cell r="Q33">
+            <v>0.54952581664910427</v>
+          </cell>
+          <cell r="R33">
+            <v>70.829677419354852</v>
+          </cell>
+          <cell r="S33">
+            <v>61.225806451612904</v>
+          </cell>
+          <cell r="T33">
+            <v>26.225806451612904</v>
+          </cell>
+          <cell r="U33">
+            <v>12.903225806451612</v>
+          </cell>
+          <cell r="V33">
+            <v>10.96774193548387</v>
+          </cell>
+          <cell r="W33">
+            <v>0</v>
+          </cell>
+          <cell r="X33">
+            <v>2.5</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>33</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>San Diego State</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>Utah State</v>
+          </cell>
+          <cell r="D34">
+            <v>14.550197800997752</v>
+          </cell>
+          <cell r="E34">
+            <v>96.841816840552212</v>
+          </cell>
+          <cell r="F34">
+            <v>87.434270076584269</v>
+          </cell>
+          <cell r="G34">
+            <v>0.54383954154727798</v>
+          </cell>
+          <cell r="H34">
+            <v>69.707999999999998</v>
+          </cell>
+          <cell r="I34">
+            <v>58.166666666666664</v>
+          </cell>
+          <cell r="J34">
+            <v>21.533333333333335</v>
+          </cell>
+          <cell r="K34">
+            <v>9.6999999999999993</v>
+          </cell>
+          <cell r="L34">
+            <v>11.766666666666667</v>
+          </cell>
+          <cell r="M34">
+            <v>0</v>
+          </cell>
+          <cell r="N34">
+            <v>16.347492910416953</v>
+          </cell>
+          <cell r="O34">
+            <v>99.814093598708979</v>
+          </cell>
+          <cell r="P34">
+            <v>89.773356716311071</v>
+          </cell>
+          <cell r="Q34">
+            <v>0.57657142857142862</v>
+          </cell>
+          <cell r="R34">
+            <v>67.801333333333332</v>
+          </cell>
+          <cell r="S34">
+            <v>58.333333333333336</v>
+          </cell>
+          <cell r="T34">
+            <v>22.2</v>
+          </cell>
+          <cell r="U34">
+            <v>10.766666666666667</v>
+          </cell>
+          <cell r="V34">
+            <v>10.466666666666667</v>
+          </cell>
+          <cell r="W34">
+            <v>0</v>
+          </cell>
+          <cell r="X34">
+            <v>1.5</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>34</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>Uconn</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>St. John's</v>
+          </cell>
+          <cell r="D35">
+            <v>18.208291246988694</v>
+          </cell>
+          <cell r="E35">
+            <v>99.985237449118031</v>
+          </cell>
+          <cell r="F35">
+            <v>95.057403075511033</v>
+          </cell>
+          <cell r="G35">
+            <v>0.55555555555555558</v>
+          </cell>
+          <cell r="H35">
+            <v>66.338064516129037</v>
+          </cell>
+          <cell r="I35">
+            <v>58.645161290322584</v>
+          </cell>
+          <cell r="J35">
+            <v>18.29032258064516</v>
+          </cell>
+          <cell r="K35">
+            <v>11.387096774193548</v>
+          </cell>
+          <cell r="L35">
+            <v>11.03225806451613</v>
+          </cell>
+          <cell r="M35">
+            <v>0</v>
+          </cell>
+          <cell r="N35">
+            <v>15.109788733361889</v>
+          </cell>
+          <cell r="O35">
+            <v>102.58678864787763</v>
+          </cell>
+          <cell r="P35">
+            <v>99.76074998519745</v>
+          </cell>
+          <cell r="Q35">
+            <v>0.50967573221757323</v>
+          </cell>
+          <cell r="R35">
+            <v>70.571612903225812</v>
+          </cell>
+          <cell r="S35">
+            <v>61.677419354838712</v>
+          </cell>
+          <cell r="T35">
+            <v>26.225806451612904</v>
+          </cell>
+          <cell r="U35">
+            <v>13.193548387096774</v>
+          </cell>
+          <cell r="V35">
+            <v>10.548387096774194</v>
+          </cell>
+          <cell r="W35">
+            <v>0</v>
+          </cell>
+          <cell r="X35">
+            <v>-2.5</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>35</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>Toledo</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>Akron</v>
+          </cell>
+          <cell r="D36">
+            <v>4.1368006701786264</v>
+          </cell>
+          <cell r="E36">
+            <v>100.01830473218929</v>
+          </cell>
+          <cell r="F36">
+            <v>101.61078845085268</v>
+          </cell>
+          <cell r="G36">
+            <v>0.54476439790575915</v>
+          </cell>
+          <cell r="H36">
+            <v>69.429677419354846</v>
+          </cell>
+          <cell r="I36">
+            <v>61.612903225806448</v>
+          </cell>
+          <cell r="J36">
+            <v>18.64516129032258</v>
+          </cell>
+          <cell r="K36">
+            <v>10.516129032258064</v>
+          </cell>
+          <cell r="L36">
+            <v>10.129032258064516</v>
+          </cell>
+          <cell r="M36">
+            <v>0</v>
+          </cell>
+          <cell r="N36">
+            <v>10.49945141256813</v>
+          </cell>
+          <cell r="O36">
+            <v>99.8801284338209</v>
+          </cell>
+          <cell r="P36">
+            <v>94.797305672709399</v>
+          </cell>
+          <cell r="Q36">
+            <v>0.59409687184661952</v>
+          </cell>
+          <cell r="R36">
+            <v>71.441290322580642</v>
+          </cell>
+          <cell r="S36">
+            <v>63.935483870967744</v>
+          </cell>
+          <cell r="T36">
+            <v>17.64516129032258</v>
+          </cell>
+          <cell r="U36">
+            <v>11.35483870967742</v>
+          </cell>
+          <cell r="V36">
+            <v>11.096774193548388</v>
+          </cell>
+          <cell r="W36">
+            <v>0</v>
+          </cell>
+          <cell r="X36">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>36</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>Virginia</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>Duke</v>
+          </cell>
+          <cell r="D37">
+            <v>13.035509619415494</v>
+          </cell>
+          <cell r="E37">
+            <v>102.89121915051371</v>
+          </cell>
+          <cell r="F37">
+            <v>105.11224188648033</v>
+          </cell>
+          <cell r="G37">
+            <v>0.54407859798194369</v>
+          </cell>
+          <cell r="H37">
+            <v>67.184516129032261</v>
+          </cell>
+          <cell r="I37">
+            <v>60.741935483870968</v>
+          </cell>
+          <cell r="J37">
+            <v>20.580645161290324</v>
+          </cell>
+          <cell r="K37">
+            <v>13.451612903225806</v>
+          </cell>
+          <cell r="L37">
+            <v>10.838709677419354</v>
+          </cell>
+          <cell r="M37">
+            <v>0</v>
+          </cell>
+          <cell r="N37">
+            <v>23.818031475685999</v>
+          </cell>
+          <cell r="O37">
+            <v>101.49806376319559</v>
+          </cell>
+          <cell r="P37">
+            <v>100.14794611787336</v>
+          </cell>
+          <cell r="Q37">
+            <v>0.57475083056478404</v>
+          </cell>
+          <cell r="R37">
+            <v>66.400000000000006</v>
+          </cell>
+          <cell r="S37">
+            <v>58.258064516129032</v>
+          </cell>
+          <cell r="T37">
+            <v>22.096774193548388</v>
+          </cell>
+          <cell r="U37">
+            <v>12</v>
+          </cell>
+          <cell r="V37">
+            <v>10.419354838709678</v>
+          </cell>
+          <cell r="W37">
+            <v>0</v>
+          </cell>
+          <cell r="X37">
+            <v>8.5</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>37</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>Kennesaw State</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>Louisiana Tech</v>
+          </cell>
+          <cell r="D38">
+            <v>6.490752715038262</v>
+          </cell>
+          <cell r="E38">
+            <v>101.8432322449375</v>
+          </cell>
+          <cell r="F38">
+            <v>97.141081053482708</v>
+          </cell>
+          <cell r="G38">
+            <v>0.52519480519480521</v>
+          </cell>
+          <cell r="H38">
+            <v>71.699354838709667</v>
+          </cell>
+          <cell r="I38">
+            <v>62.096774193548384</v>
+          </cell>
+          <cell r="J38">
+            <v>26.516129032258064</v>
+          </cell>
+          <cell r="K38">
+            <v>13.806451612903226</v>
+          </cell>
+          <cell r="L38">
+            <v>11.741935483870968</v>
+          </cell>
+          <cell r="M38">
+            <v>0</v>
+          </cell>
+          <cell r="N38">
+            <v>2.6443345975686983</v>
+          </cell>
+          <cell r="O38">
+            <v>99.919161188678217</v>
+          </cell>
+          <cell r="P38">
+            <v>98.415627483867411</v>
+          </cell>
+          <cell r="Q38">
+            <v>0.49525669642857145</v>
+          </cell>
+          <cell r="R38">
+            <v>65.900645161290328</v>
+          </cell>
+          <cell r="S38">
+            <v>57.806451612903224</v>
+          </cell>
+          <cell r="T38">
+            <v>19.129032258064516</v>
+          </cell>
+          <cell r="U38">
+            <v>12.96774193548387</v>
+          </cell>
+          <cell r="V38">
+            <v>12.64516129032258</v>
+          </cell>
+          <cell r="W38">
+            <v>0</v>
+          </cell>
+          <cell r="X38">
+            <v>-1.5</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>38</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>Hawaii</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>UC Irvine</v>
+          </cell>
+          <cell r="D39">
+            <v>2.4205256715728276</v>
+          </cell>
+          <cell r="E39">
+            <v>96.251520482533294</v>
+          </cell>
+          <cell r="F39">
+            <v>92.252558584997232</v>
+          </cell>
+          <cell r="G39">
+            <v>0.52753872633390708</v>
+          </cell>
+          <cell r="H39">
+            <v>71.861333333333334</v>
+          </cell>
+          <cell r="I39">
+            <v>58.1</v>
+          </cell>
+          <cell r="J39">
+            <v>25.366666666666667</v>
+          </cell>
+          <cell r="K39">
+            <v>10.733333333333333</v>
+          </cell>
+          <cell r="L39">
+            <v>13.333333333333334</v>
+          </cell>
+          <cell r="M39">
+            <v>0</v>
+          </cell>
+          <cell r="N39">
+            <v>5.2870372643884913</v>
+          </cell>
+          <cell r="O39">
+            <v>98.000795228628249</v>
+          </cell>
+          <cell r="P39">
+            <v>92.824900535566286</v>
+          </cell>
+          <cell r="Q39">
+            <v>0.51370585134422775</v>
+          </cell>
+          <cell r="R39">
+            <v>71.811612903225807</v>
+          </cell>
+          <cell r="S39">
+            <v>61.193548387096776</v>
+          </cell>
+          <cell r="T39">
+            <v>21.419354838709676</v>
+          </cell>
+          <cell r="U39">
+            <v>11.548387096774194</v>
+          </cell>
+          <cell r="V39">
+            <v>12.741935483870968</v>
+          </cell>
+          <cell r="W39">
+            <v>0</v>
+          </cell>
+          <cell r="X39">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>39</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>California Baptist</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>Utah Valley</v>
+          </cell>
+          <cell r="D40">
+            <v>4.601636720836713</v>
+          </cell>
+          <cell r="E40">
+            <v>101.16726287262874</v>
+          </cell>
+          <cell r="F40">
+            <v>89.920292368090941</v>
+          </cell>
+          <cell r="G40">
+            <v>0.48252536640360766</v>
+          </cell>
+          <cell r="H40">
+            <v>67.391999999999996</v>
+          </cell>
+          <cell r="I40">
+            <v>59.133333333333333</v>
+          </cell>
+          <cell r="J40">
+            <v>21.8</v>
+          </cell>
+          <cell r="K40">
+            <v>13.866666666666667</v>
+          </cell>
+          <cell r="L40">
+            <v>12.533333333333333</v>
+          </cell>
+          <cell r="M40">
+            <v>0</v>
+          </cell>
+          <cell r="N40">
+            <v>7.1660953976463073</v>
+          </cell>
+          <cell r="O40">
+            <v>96.788608522667772</v>
+          </cell>
+          <cell r="P40">
+            <v>87.924687269369926</v>
+          </cell>
+          <cell r="Q40">
+            <v>0.56105144149236852</v>
+          </cell>
+          <cell r="R40">
+            <v>70.398666666666671</v>
+          </cell>
+          <cell r="S40">
+            <v>58.966666666666669</v>
+          </cell>
+          <cell r="T40">
+            <v>21.133333333333333</v>
+          </cell>
+          <cell r="U40">
+            <v>11.933333333333334</v>
+          </cell>
+          <cell r="V40">
+            <v>14.066666666666666</v>
+          </cell>
+          <cell r="W40">
+            <v>0</v>
+          </cell>
+          <cell r="X40">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>40</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Vermont</v>
+          </cell>
+          <cell r="C41" t="str">
             <v>UMBC</v>
           </cell>
-          <cell r="D19">
+          <cell r="D41">
             <v>-8.3049596389430835</v>
           </cell>
-          <cell r="E19">
+          <cell r="E41">
             <v>98.685284640171872</v>
           </cell>
-          <cell r="F19">
+          <cell r="F41">
             <v>109.91881615719028</v>
           </cell>
-          <cell r="G19">
+          <cell r="G41">
             <v>0.54303164908384227</v>
           </cell>
-          <cell r="H19">
+          <cell r="H41">
             <v>64.849999999999994</v>
           </cell>
-          <cell r="I19">
+          <cell r="I41">
             <v>56.28125</v>
           </cell>
-          <cell r="J19">
+          <cell r="J41">
             <v>18.125</v>
           </cell>
-          <cell r="K19">
+          <cell r="K41">
             <v>8.84375</v>
           </cell>
-          <cell r="L19">
+          <cell r="L41">
             <v>9.4375</v>
           </cell>
-          <cell r="M19">
-            <v>0</v>
-          </cell>
-          <cell r="N19">
+          <cell r="M41">
+            <v>0</v>
+          </cell>
+          <cell r="N41">
             <v>-8.1832066239376893</v>
           </cell>
-          <cell r="O19">
+          <cell r="O41">
             <v>97.210907835692097</v>
           </cell>
-          <cell r="P19">
+          <cell r="P41">
             <v>110.54326482948768</v>
           </cell>
-          <cell r="Q19">
+          <cell r="Q41">
             <v>0.5430982519590114</v>
           </cell>
-          <cell r="R19">
+          <cell r="R41">
             <v>66.972413793103442</v>
           </cell>
-          <cell r="S19">
+          <cell r="S41">
             <v>57.206896551724135</v>
           </cell>
-          <cell r="T19">
+          <cell r="T41">
             <v>18.275862068965516</v>
           </cell>
-          <cell r="U19">
+          <cell r="U41">
             <v>8.068965517241379</v>
           </cell>
-          <cell r="V19">
+          <cell r="V41">
             <v>9.7931034482758612</v>
           </cell>
-          <cell r="W19">
-            <v>0</v>
-          </cell>
-          <cell r="X19">
+          <cell r="W41">
+            <v>0</v>
+          </cell>
+          <cell r="X41">
             <v>3.5</v>
           </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>41</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>North Carolina Central</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>Howard</v>
+          </cell>
+          <cell r="D42">
+            <v>-12.049706064548028</v>
+          </cell>
+          <cell r="E42">
+            <v>97.391178918169217</v>
+          </cell>
+          <cell r="F42">
+            <v>102.17668911130822</v>
+          </cell>
+          <cell r="G42">
+            <v>0.49514563106796117</v>
+          </cell>
+          <cell r="H42">
+            <v>68.108965517241387</v>
+          </cell>
+          <cell r="I42">
+            <v>56.827586206896555</v>
+          </cell>
+          <cell r="J42">
+            <v>22.03448275862069</v>
+          </cell>
+          <cell r="K42">
+            <v>10.689655172413794</v>
+          </cell>
+          <cell r="L42">
+            <v>12.275862068965518</v>
+          </cell>
+          <cell r="M42">
+            <v>0</v>
+          </cell>
+          <cell r="N42">
+            <v>-7.0667288784066029</v>
+          </cell>
+          <cell r="O42">
+            <v>97.771296389419689</v>
+          </cell>
+          <cell r="P42">
+            <v>101.22012384797286</v>
+          </cell>
+          <cell r="Q42">
+            <v>0.52172686230248311</v>
+          </cell>
+          <cell r="R42">
+            <v>69.380645161290332</v>
+          </cell>
+          <cell r="S42">
+            <v>57.161290322580648</v>
+          </cell>
+          <cell r="T42">
+            <v>24.838709677419356</v>
+          </cell>
+          <cell r="U42">
+            <v>12.290322580645162</v>
+          </cell>
+          <cell r="V42">
+            <v>13.580645161290322</v>
+          </cell>
+          <cell r="W42">
+            <v>0</v>
+          </cell>
+          <cell r="X42">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>42</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Prairie View A&amp;M</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>Southern</v>
+          </cell>
+          <cell r="D43">
+            <v>-10.748183340293197</v>
+          </cell>
+          <cell r="E43">
+            <v>96.942723004694827</v>
+          </cell>
+          <cell r="F43">
+            <v>93.291737667336207</v>
+          </cell>
+          <cell r="G43">
+            <v>0.49388297872340425</v>
+          </cell>
+          <cell r="H43">
+            <v>74.380645161290332</v>
+          </cell>
+          <cell r="I43">
+            <v>60.645161290322584</v>
+          </cell>
+          <cell r="J43">
+            <v>26.451612903225808</v>
+          </cell>
+          <cell r="K43">
+            <v>10.161290322580646</v>
+          </cell>
+          <cell r="L43">
+            <v>12.258064516129032</v>
+          </cell>
+          <cell r="M43">
+            <v>0</v>
+          </cell>
+          <cell r="N43">
+            <v>-6.7092460643817606</v>
+          </cell>
+          <cell r="O43">
+            <v>99.018646109371232</v>
+          </cell>
+          <cell r="P43">
+            <v>93.207129449722274</v>
+          </cell>
+          <cell r="Q43">
+            <v>0.50943396226415094</v>
+          </cell>
+          <cell r="R43">
+            <v>72.842580645161291</v>
+          </cell>
+          <cell r="S43">
+            <v>61.548387096774192</v>
+          </cell>
+          <cell r="T43">
+            <v>24.93548387096774</v>
+          </cell>
+          <cell r="U43">
+            <v>11.67741935483871</v>
+          </cell>
+          <cell r="V43">
+            <v>12</v>
+          </cell>
+          <cell r="W43">
+            <v>0</v>
+          </cell>
+          <cell r="X43">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="D44"/>
+          <cell r="E44"/>
+          <cell r="F44"/>
+          <cell r="G44"/>
+          <cell r="H44"/>
+          <cell r="I44"/>
+          <cell r="J44"/>
+          <cell r="K44"/>
+          <cell r="L44"/>
+          <cell r="M44"/>
+          <cell r="N44"/>
+          <cell r="O44"/>
+          <cell r="P44"/>
+          <cell r="Q44"/>
+          <cell r="R44"/>
+          <cell r="S44"/>
+          <cell r="T44"/>
+          <cell r="U44"/>
+          <cell r="V44"/>
+          <cell r="W44"/>
+          <cell r="X44"/>
+        </row>
+        <row r="45">
+          <cell r="D45"/>
+          <cell r="E45"/>
+          <cell r="F45"/>
+          <cell r="G45"/>
+          <cell r="H45"/>
+          <cell r="I45"/>
+          <cell r="J45"/>
+          <cell r="K45"/>
+          <cell r="L45"/>
+          <cell r="M45"/>
+          <cell r="N45"/>
+          <cell r="O45"/>
+          <cell r="P45"/>
+          <cell r="Q45"/>
+          <cell r="R45"/>
+          <cell r="S45"/>
+          <cell r="T45"/>
+          <cell r="U45"/>
+          <cell r="V45"/>
+          <cell r="W45"/>
+          <cell r="X45"/>
+        </row>
+        <row r="46">
+          <cell r="D46"/>
+          <cell r="E46"/>
+          <cell r="F46"/>
+          <cell r="G46"/>
+          <cell r="H46"/>
+          <cell r="I46"/>
+          <cell r="J46"/>
+          <cell r="K46"/>
+          <cell r="L46"/>
+          <cell r="M46"/>
+          <cell r="N46"/>
+          <cell r="O46"/>
+          <cell r="P46"/>
+          <cell r="Q46"/>
+          <cell r="R46"/>
+          <cell r="S46"/>
+          <cell r="T46"/>
+          <cell r="U46"/>
+          <cell r="V46"/>
+          <cell r="W46"/>
+          <cell r="X46"/>
+        </row>
+        <row r="47">
+          <cell r="D47"/>
+          <cell r="E47"/>
+          <cell r="F47"/>
+          <cell r="G47"/>
+          <cell r="H47"/>
+          <cell r="I47"/>
+          <cell r="J47"/>
+          <cell r="K47"/>
+          <cell r="L47"/>
+          <cell r="M47"/>
+          <cell r="N47"/>
+          <cell r="O47"/>
+          <cell r="P47"/>
+          <cell r="Q47"/>
+          <cell r="R47"/>
+          <cell r="S47"/>
+          <cell r="T47"/>
+          <cell r="U47"/>
+          <cell r="V47"/>
+          <cell r="W47"/>
+          <cell r="X47"/>
+        </row>
+        <row r="48">
+          <cell r="D48"/>
+          <cell r="E48"/>
+          <cell r="F48"/>
+          <cell r="G48"/>
+          <cell r="H48"/>
+          <cell r="I48"/>
+          <cell r="J48"/>
+          <cell r="K48"/>
+          <cell r="L48"/>
+          <cell r="M48"/>
+          <cell r="N48"/>
+          <cell r="O48"/>
+          <cell r="P48"/>
+          <cell r="Q48"/>
+          <cell r="R48"/>
+          <cell r="S48"/>
+          <cell r="T48"/>
+          <cell r="U48"/>
+          <cell r="V48"/>
+          <cell r="W48"/>
+          <cell r="X48"/>
+        </row>
+        <row r="49">
+          <cell r="D49"/>
+          <cell r="E49"/>
+          <cell r="F49"/>
+          <cell r="G49"/>
+          <cell r="H49"/>
+          <cell r="I49"/>
+          <cell r="J49"/>
+          <cell r="K49"/>
+          <cell r="L49"/>
+          <cell r="M49"/>
+          <cell r="N49"/>
+          <cell r="O49"/>
+          <cell r="P49"/>
+          <cell r="Q49"/>
+          <cell r="R49"/>
+          <cell r="S49"/>
+          <cell r="T49"/>
+          <cell r="U49"/>
+          <cell r="V49"/>
+          <cell r="W49"/>
+          <cell r="X49"/>
+        </row>
+        <row r="50">
+          <cell r="D50"/>
+          <cell r="E50"/>
+          <cell r="F50"/>
+          <cell r="G50"/>
+          <cell r="H50"/>
+          <cell r="I50"/>
+          <cell r="J50"/>
+          <cell r="K50"/>
+          <cell r="L50"/>
+          <cell r="M50"/>
+          <cell r="N50"/>
+          <cell r="O50"/>
+          <cell r="P50"/>
+          <cell r="Q50"/>
+          <cell r="R50"/>
+          <cell r="S50"/>
+          <cell r="T50"/>
+          <cell r="U50"/>
+          <cell r="V50"/>
+          <cell r="W50"/>
+          <cell r="X50"/>
+        </row>
+        <row r="51">
+          <cell r="D51"/>
+          <cell r="E51"/>
+          <cell r="F51"/>
+          <cell r="G51"/>
+          <cell r="H51"/>
+          <cell r="I51"/>
+          <cell r="J51"/>
+          <cell r="K51"/>
+          <cell r="L51"/>
+          <cell r="M51"/>
+          <cell r="N51"/>
+          <cell r="O51"/>
+          <cell r="P51"/>
+          <cell r="Q51"/>
+          <cell r="R51"/>
+          <cell r="S51"/>
+          <cell r="T51"/>
+          <cell r="U51"/>
+          <cell r="V51"/>
+          <cell r="W51"/>
+          <cell r="X51"/>
+        </row>
+        <row r="52">
+          <cell r="D52"/>
+          <cell r="E52"/>
+          <cell r="F52"/>
+          <cell r="G52"/>
+          <cell r="H52"/>
+          <cell r="I52"/>
+          <cell r="J52"/>
+          <cell r="K52"/>
+          <cell r="L52"/>
+          <cell r="M52"/>
+          <cell r="N52"/>
+          <cell r="O52"/>
+          <cell r="P52"/>
+          <cell r="Q52"/>
+          <cell r="R52"/>
+          <cell r="S52"/>
+          <cell r="T52"/>
+          <cell r="U52"/>
+          <cell r="V52"/>
+          <cell r="W52"/>
+          <cell r="X52"/>
+        </row>
+        <row r="53">
+          <cell r="D53"/>
+          <cell r="E53"/>
+          <cell r="F53"/>
+          <cell r="G53"/>
+          <cell r="H53"/>
+          <cell r="I53"/>
+          <cell r="J53"/>
+          <cell r="K53"/>
+          <cell r="L53"/>
+          <cell r="M53"/>
+          <cell r="N53"/>
+          <cell r="O53"/>
+          <cell r="P53"/>
+          <cell r="Q53"/>
+          <cell r="R53"/>
+          <cell r="S53"/>
+          <cell r="T53"/>
+          <cell r="U53"/>
+          <cell r="V53"/>
+          <cell r="W53"/>
+          <cell r="X53"/>
+        </row>
+        <row r="54">
+          <cell r="D54"/>
+          <cell r="E54"/>
+          <cell r="F54"/>
+          <cell r="G54"/>
+          <cell r="H54"/>
+          <cell r="I54"/>
+          <cell r="J54"/>
+          <cell r="K54"/>
+          <cell r="L54"/>
+          <cell r="M54"/>
+          <cell r="N54"/>
+          <cell r="O54"/>
+          <cell r="P54"/>
+          <cell r="Q54"/>
+          <cell r="R54"/>
+          <cell r="S54"/>
+          <cell r="T54"/>
+          <cell r="U54"/>
+          <cell r="V54"/>
+          <cell r="W54"/>
+          <cell r="X54"/>
+        </row>
+        <row r="55">
+          <cell r="D55"/>
+          <cell r="E55"/>
+          <cell r="F55"/>
+          <cell r="G55"/>
+          <cell r="H55"/>
+          <cell r="I55"/>
+          <cell r="J55"/>
+          <cell r="K55"/>
+          <cell r="L55"/>
+          <cell r="M55"/>
+          <cell r="N55"/>
+          <cell r="O55"/>
+          <cell r="P55"/>
+          <cell r="Q55"/>
+          <cell r="R55"/>
+          <cell r="S55"/>
+          <cell r="T55"/>
+          <cell r="U55"/>
+          <cell r="V55"/>
+          <cell r="W55"/>
+          <cell r="X55"/>
+        </row>
+        <row r="56">
+          <cell r="D56"/>
+          <cell r="E56"/>
+          <cell r="F56"/>
+          <cell r="G56"/>
+          <cell r="H56"/>
+          <cell r="I56"/>
+          <cell r="J56"/>
+          <cell r="K56"/>
+          <cell r="L56"/>
+          <cell r="M56"/>
+          <cell r="N56"/>
+          <cell r="O56"/>
+          <cell r="P56"/>
+          <cell r="Q56"/>
+          <cell r="R56"/>
+          <cell r="S56"/>
+          <cell r="T56"/>
+          <cell r="U56"/>
+          <cell r="V56"/>
+          <cell r="W56"/>
+          <cell r="X56"/>
+        </row>
+        <row r="57">
+          <cell r="D57"/>
+          <cell r="E57"/>
+          <cell r="F57"/>
+          <cell r="G57"/>
+          <cell r="H57"/>
+          <cell r="I57"/>
+          <cell r="J57"/>
+          <cell r="K57"/>
+          <cell r="L57"/>
+          <cell r="M57"/>
+          <cell r="N57"/>
+          <cell r="O57"/>
+          <cell r="P57"/>
+          <cell r="Q57"/>
+          <cell r="R57"/>
+          <cell r="S57"/>
+          <cell r="T57"/>
+          <cell r="U57"/>
+          <cell r="V57"/>
+          <cell r="W57"/>
+          <cell r="X57"/>
+        </row>
+        <row r="58">
+          <cell r="D58"/>
+          <cell r="E58"/>
+          <cell r="F58"/>
+          <cell r="G58"/>
+          <cell r="H58"/>
+          <cell r="I58"/>
+          <cell r="J58"/>
+          <cell r="K58"/>
+          <cell r="L58"/>
+          <cell r="M58"/>
+          <cell r="N58"/>
+          <cell r="O58"/>
+          <cell r="P58"/>
+          <cell r="Q58"/>
+          <cell r="R58"/>
+          <cell r="S58"/>
+          <cell r="T58"/>
+          <cell r="U58"/>
+          <cell r="V58"/>
+          <cell r="W58"/>
+          <cell r="X58"/>
+        </row>
+        <row r="59">
+          <cell r="D59"/>
+          <cell r="E59"/>
+          <cell r="F59"/>
+          <cell r="G59"/>
+          <cell r="H59"/>
+          <cell r="I59"/>
+          <cell r="J59"/>
+          <cell r="K59"/>
+          <cell r="L59"/>
+          <cell r="M59"/>
+          <cell r="N59"/>
+          <cell r="O59"/>
+          <cell r="P59"/>
+          <cell r="Q59"/>
+          <cell r="R59"/>
+          <cell r="S59"/>
+          <cell r="T59"/>
+          <cell r="U59"/>
+          <cell r="V59"/>
+          <cell r="W59"/>
+          <cell r="X59"/>
+        </row>
+        <row r="60">
+          <cell r="D60"/>
+          <cell r="E60"/>
+          <cell r="F60"/>
+          <cell r="G60"/>
+          <cell r="H60"/>
+          <cell r="I60"/>
+          <cell r="J60"/>
+          <cell r="K60"/>
+          <cell r="L60"/>
+          <cell r="M60"/>
+          <cell r="N60"/>
+          <cell r="O60"/>
+          <cell r="P60"/>
+          <cell r="Q60"/>
+          <cell r="R60"/>
+          <cell r="S60"/>
+          <cell r="T60"/>
+          <cell r="U60"/>
+          <cell r="V60"/>
+          <cell r="W60"/>
+          <cell r="X60"/>
+        </row>
+        <row r="61">
+          <cell r="D61"/>
+          <cell r="E61"/>
+          <cell r="F61"/>
+          <cell r="G61"/>
+          <cell r="H61"/>
+          <cell r="I61"/>
+          <cell r="J61"/>
+          <cell r="K61"/>
+          <cell r="L61"/>
+          <cell r="M61"/>
+          <cell r="N61"/>
+          <cell r="O61"/>
+          <cell r="P61"/>
+          <cell r="Q61"/>
+          <cell r="R61"/>
+          <cell r="S61"/>
+          <cell r="T61"/>
+          <cell r="U61"/>
+          <cell r="V61"/>
+          <cell r="W61"/>
+          <cell r="X61"/>
+        </row>
+        <row r="62">
+          <cell r="D62"/>
+          <cell r="E62"/>
+          <cell r="F62"/>
+          <cell r="G62"/>
+          <cell r="H62"/>
+          <cell r="I62"/>
+          <cell r="J62"/>
+          <cell r="K62"/>
+          <cell r="L62"/>
+          <cell r="M62"/>
+          <cell r="N62"/>
+          <cell r="O62"/>
+          <cell r="P62"/>
+          <cell r="Q62"/>
+          <cell r="R62"/>
+          <cell r="S62"/>
+          <cell r="T62"/>
+          <cell r="U62"/>
+          <cell r="V62"/>
+          <cell r="W62"/>
+          <cell r="X62"/>
+        </row>
+        <row r="63">
+          <cell r="D63"/>
+          <cell r="E63"/>
+          <cell r="F63"/>
+          <cell r="G63"/>
+          <cell r="H63"/>
+          <cell r="I63"/>
+          <cell r="J63"/>
+          <cell r="K63"/>
+          <cell r="L63"/>
+          <cell r="M63"/>
+          <cell r="N63"/>
+          <cell r="O63"/>
+          <cell r="P63"/>
+          <cell r="Q63"/>
+          <cell r="R63"/>
+          <cell r="S63"/>
+          <cell r="T63"/>
+          <cell r="U63"/>
+          <cell r="V63"/>
+          <cell r="W63"/>
+          <cell r="X63"/>
+        </row>
+        <row r="64">
+          <cell r="D64"/>
+          <cell r="E64"/>
+          <cell r="F64"/>
+          <cell r="G64"/>
+          <cell r="H64"/>
+          <cell r="I64"/>
+          <cell r="J64"/>
+          <cell r="K64"/>
+          <cell r="L64"/>
+          <cell r="M64"/>
+          <cell r="N64"/>
+          <cell r="O64"/>
+          <cell r="P64"/>
+          <cell r="Q64"/>
+          <cell r="R64"/>
+          <cell r="S64"/>
+          <cell r="T64"/>
+          <cell r="U64"/>
+          <cell r="V64"/>
+          <cell r="W64"/>
+          <cell r="X64"/>
+        </row>
+        <row r="65">
+          <cell r="D65"/>
+          <cell r="E65"/>
+          <cell r="F65"/>
+          <cell r="G65"/>
+          <cell r="H65"/>
+          <cell r="I65"/>
+          <cell r="J65"/>
+          <cell r="K65"/>
+          <cell r="L65"/>
+          <cell r="M65"/>
+          <cell r="N65"/>
+          <cell r="O65"/>
+          <cell r="P65"/>
+          <cell r="Q65"/>
+          <cell r="R65"/>
+          <cell r="S65"/>
+          <cell r="T65"/>
+          <cell r="U65"/>
+          <cell r="V65"/>
+          <cell r="W65"/>
+          <cell r="X65"/>
+        </row>
+        <row r="66">
+          <cell r="D66"/>
+          <cell r="E66"/>
+          <cell r="F66"/>
+          <cell r="G66"/>
+          <cell r="H66"/>
+          <cell r="I66"/>
+          <cell r="J66"/>
+          <cell r="K66"/>
+          <cell r="L66"/>
+          <cell r="M66"/>
+          <cell r="N66"/>
+          <cell r="O66"/>
+          <cell r="P66"/>
+          <cell r="Q66"/>
+          <cell r="R66"/>
+          <cell r="S66"/>
+          <cell r="T66"/>
+          <cell r="U66"/>
+          <cell r="V66"/>
+          <cell r="W66"/>
+          <cell r="X66"/>
+        </row>
+        <row r="67">
+          <cell r="D67"/>
+          <cell r="E67"/>
+          <cell r="F67"/>
+          <cell r="G67"/>
+          <cell r="H67"/>
+          <cell r="I67"/>
+          <cell r="J67"/>
+          <cell r="K67"/>
+          <cell r="L67"/>
+          <cell r="M67"/>
+          <cell r="N67"/>
+          <cell r="O67"/>
+          <cell r="P67"/>
+          <cell r="Q67"/>
+          <cell r="R67"/>
+          <cell r="S67"/>
+          <cell r="T67"/>
+          <cell r="U67"/>
+          <cell r="V67"/>
+          <cell r="W67"/>
+          <cell r="X67"/>
+        </row>
+        <row r="68">
+          <cell r="D68"/>
+          <cell r="E68"/>
+          <cell r="F68"/>
+          <cell r="G68"/>
+          <cell r="H68"/>
+          <cell r="I68"/>
+          <cell r="J68"/>
+          <cell r="K68"/>
+          <cell r="L68"/>
+          <cell r="M68"/>
+          <cell r="N68"/>
+          <cell r="O68"/>
+          <cell r="P68"/>
+          <cell r="Q68"/>
+          <cell r="R68"/>
+          <cell r="S68"/>
+          <cell r="T68"/>
+          <cell r="U68"/>
+          <cell r="V68"/>
+          <cell r="W68"/>
+          <cell r="X68"/>
+        </row>
+        <row r="69">
+          <cell r="D69"/>
+          <cell r="E69"/>
+          <cell r="F69"/>
+          <cell r="G69"/>
+          <cell r="H69"/>
+          <cell r="I69"/>
+          <cell r="J69"/>
+          <cell r="K69"/>
+          <cell r="L69"/>
+          <cell r="M69"/>
+          <cell r="N69"/>
+          <cell r="O69"/>
+          <cell r="P69"/>
+          <cell r="Q69"/>
+          <cell r="R69"/>
+          <cell r="S69"/>
+          <cell r="T69"/>
+          <cell r="U69"/>
+          <cell r="V69"/>
+          <cell r="W69"/>
+          <cell r="X69"/>
+        </row>
+        <row r="70">
+          <cell r="D70"/>
+          <cell r="E70"/>
+          <cell r="F70"/>
+          <cell r="G70"/>
+          <cell r="H70"/>
+          <cell r="I70"/>
+          <cell r="J70"/>
+          <cell r="K70"/>
+          <cell r="L70"/>
+          <cell r="M70"/>
+          <cell r="N70"/>
+          <cell r="O70"/>
+          <cell r="P70"/>
+          <cell r="Q70"/>
+          <cell r="R70"/>
+          <cell r="S70"/>
+          <cell r="T70"/>
+          <cell r="U70"/>
+          <cell r="V70"/>
+          <cell r="W70"/>
+          <cell r="X70"/>
+        </row>
+        <row r="71">
+          <cell r="D71"/>
+          <cell r="E71"/>
+          <cell r="F71"/>
+          <cell r="G71"/>
+          <cell r="H71"/>
+          <cell r="I71"/>
+          <cell r="J71"/>
+          <cell r="K71"/>
+          <cell r="L71"/>
+          <cell r="M71"/>
+          <cell r="N71"/>
+          <cell r="O71"/>
+          <cell r="P71"/>
+          <cell r="Q71"/>
+          <cell r="R71"/>
+          <cell r="S71"/>
+          <cell r="T71"/>
+          <cell r="U71"/>
+          <cell r="V71"/>
+          <cell r="W71"/>
+          <cell r="X71"/>
+        </row>
+        <row r="72">
+          <cell r="D72"/>
+          <cell r="E72"/>
+          <cell r="F72"/>
+          <cell r="G72"/>
+          <cell r="H72"/>
+          <cell r="I72"/>
+          <cell r="J72"/>
+          <cell r="K72"/>
+          <cell r="L72"/>
+          <cell r="M72"/>
+          <cell r="N72"/>
+          <cell r="O72"/>
+          <cell r="P72"/>
+          <cell r="Q72"/>
+          <cell r="R72"/>
+          <cell r="S72"/>
+          <cell r="T72"/>
+          <cell r="U72"/>
+          <cell r="V72"/>
+          <cell r="W72"/>
+          <cell r="X72"/>
+        </row>
+        <row r="73">
+          <cell r="D73"/>
+          <cell r="E73"/>
+          <cell r="F73"/>
+          <cell r="G73"/>
+          <cell r="H73"/>
+          <cell r="I73"/>
+          <cell r="J73"/>
+          <cell r="K73"/>
+          <cell r="L73"/>
+          <cell r="M73"/>
+          <cell r="N73"/>
+          <cell r="O73"/>
+          <cell r="P73"/>
+          <cell r="Q73"/>
+          <cell r="R73"/>
+          <cell r="S73"/>
+          <cell r="T73"/>
+          <cell r="U73"/>
+          <cell r="V73"/>
+          <cell r="W73"/>
+          <cell r="X73"/>
+        </row>
+        <row r="74">
+          <cell r="D74"/>
+          <cell r="E74"/>
+          <cell r="F74"/>
+          <cell r="G74"/>
+          <cell r="H74"/>
+          <cell r="I74"/>
+          <cell r="J74"/>
+          <cell r="K74"/>
+          <cell r="L74"/>
+          <cell r="M74"/>
+          <cell r="N74"/>
+          <cell r="O74"/>
+          <cell r="P74"/>
+          <cell r="Q74"/>
+          <cell r="R74"/>
+          <cell r="S74"/>
+          <cell r="T74"/>
+          <cell r="U74"/>
+          <cell r="V74"/>
+          <cell r="W74"/>
+          <cell r="X74"/>
+        </row>
+        <row r="75">
+          <cell r="D75"/>
+          <cell r="E75"/>
+          <cell r="F75"/>
+          <cell r="G75"/>
+          <cell r="H75"/>
+          <cell r="I75"/>
+          <cell r="J75"/>
+          <cell r="K75"/>
+          <cell r="L75"/>
+          <cell r="M75"/>
+          <cell r="N75"/>
+          <cell r="O75"/>
+          <cell r="P75"/>
+          <cell r="Q75"/>
+          <cell r="R75"/>
+          <cell r="S75"/>
+          <cell r="T75"/>
+          <cell r="U75"/>
+          <cell r="V75"/>
+          <cell r="W75"/>
+          <cell r="X75"/>
+        </row>
+        <row r="76">
+          <cell r="D76"/>
+          <cell r="E76"/>
+          <cell r="F76"/>
+          <cell r="G76"/>
+          <cell r="H76"/>
+          <cell r="I76"/>
+          <cell r="J76"/>
+          <cell r="K76"/>
+          <cell r="L76"/>
+          <cell r="M76"/>
+          <cell r="N76"/>
+          <cell r="O76"/>
+          <cell r="P76"/>
+          <cell r="Q76"/>
+          <cell r="R76"/>
+          <cell r="S76"/>
+          <cell r="T76"/>
+          <cell r="U76"/>
+          <cell r="V76"/>
+          <cell r="W76"/>
+          <cell r="X76"/>
+        </row>
+        <row r="77">
+          <cell r="D77"/>
+          <cell r="E77"/>
+          <cell r="F77"/>
+          <cell r="G77"/>
+          <cell r="H77"/>
+          <cell r="I77"/>
+          <cell r="J77"/>
+          <cell r="K77"/>
+          <cell r="L77"/>
+          <cell r="M77"/>
+          <cell r="N77"/>
+          <cell r="O77"/>
+          <cell r="P77"/>
+          <cell r="Q77"/>
+          <cell r="R77"/>
+          <cell r="S77"/>
+          <cell r="T77"/>
+          <cell r="U77"/>
+          <cell r="V77"/>
+          <cell r="W77"/>
+          <cell r="X77"/>
+        </row>
+        <row r="78">
+          <cell r="D78"/>
+          <cell r="E78"/>
+          <cell r="F78"/>
+          <cell r="G78"/>
+          <cell r="H78"/>
+          <cell r="I78"/>
+          <cell r="J78"/>
+          <cell r="K78"/>
+          <cell r="L78"/>
+          <cell r="M78"/>
+          <cell r="N78"/>
+          <cell r="O78"/>
+          <cell r="P78"/>
+          <cell r="Q78"/>
+          <cell r="R78"/>
+          <cell r="S78"/>
+          <cell r="T78"/>
+          <cell r="U78"/>
+          <cell r="V78"/>
+          <cell r="W78"/>
+          <cell r="X78"/>
+        </row>
+        <row r="79">
+          <cell r="D79"/>
+          <cell r="E79"/>
+          <cell r="F79"/>
+          <cell r="G79"/>
+          <cell r="H79"/>
+          <cell r="I79"/>
+          <cell r="J79"/>
+          <cell r="K79"/>
+          <cell r="L79"/>
+          <cell r="M79"/>
+          <cell r="N79"/>
+          <cell r="O79"/>
+          <cell r="P79"/>
+          <cell r="Q79"/>
+          <cell r="R79"/>
+          <cell r="S79"/>
+          <cell r="T79"/>
+          <cell r="U79"/>
+          <cell r="V79"/>
+          <cell r="W79"/>
+          <cell r="X79"/>
+        </row>
+        <row r="80">
+          <cell r="D80"/>
+          <cell r="E80"/>
+          <cell r="F80"/>
+          <cell r="G80"/>
+          <cell r="H80"/>
+          <cell r="I80"/>
+          <cell r="J80"/>
+          <cell r="K80"/>
+          <cell r="L80"/>
+          <cell r="M80"/>
+          <cell r="N80"/>
+          <cell r="O80"/>
+          <cell r="P80"/>
+          <cell r="Q80"/>
+          <cell r="R80"/>
+          <cell r="S80"/>
+          <cell r="T80"/>
+          <cell r="U80"/>
+          <cell r="V80"/>
+          <cell r="W80"/>
+          <cell r="X80"/>
+        </row>
+        <row r="81">
+          <cell r="D81"/>
+          <cell r="E81"/>
+          <cell r="F81"/>
+          <cell r="G81"/>
+          <cell r="H81"/>
+          <cell r="I81"/>
+          <cell r="J81"/>
+          <cell r="K81"/>
+          <cell r="L81"/>
+          <cell r="M81"/>
+          <cell r="N81"/>
+          <cell r="O81"/>
+          <cell r="P81"/>
+          <cell r="Q81"/>
+          <cell r="R81"/>
+          <cell r="S81"/>
+          <cell r="T81"/>
+          <cell r="U81"/>
+          <cell r="V81"/>
+          <cell r="W81"/>
+          <cell r="X81"/>
+        </row>
+        <row r="82">
+          <cell r="D82"/>
+          <cell r="E82"/>
+          <cell r="F82"/>
+          <cell r="G82"/>
+          <cell r="H82"/>
+          <cell r="I82"/>
+          <cell r="J82"/>
+          <cell r="K82"/>
+          <cell r="L82"/>
+          <cell r="M82"/>
+          <cell r="N82"/>
+          <cell r="O82"/>
+          <cell r="P82"/>
+          <cell r="Q82"/>
+          <cell r="R82"/>
+          <cell r="S82"/>
+          <cell r="T82"/>
+          <cell r="U82"/>
+          <cell r="V82"/>
+          <cell r="W82"/>
+          <cell r="X82"/>
+        </row>
+        <row r="83">
+          <cell r="D83"/>
+          <cell r="E83"/>
+          <cell r="F83"/>
+          <cell r="G83"/>
+          <cell r="H83"/>
+          <cell r="I83"/>
+          <cell r="J83"/>
+          <cell r="K83"/>
+          <cell r="L83"/>
+          <cell r="M83"/>
+          <cell r="N83"/>
+          <cell r="O83"/>
+          <cell r="P83"/>
+          <cell r="Q83"/>
+          <cell r="R83"/>
+          <cell r="S83"/>
+          <cell r="T83"/>
+          <cell r="U83"/>
+          <cell r="V83"/>
+          <cell r="W83"/>
+          <cell r="X83"/>
+        </row>
+        <row r="84">
+          <cell r="D84"/>
+          <cell r="E84"/>
+          <cell r="F84"/>
+          <cell r="G84"/>
+          <cell r="H84"/>
+          <cell r="I84"/>
+          <cell r="J84"/>
+          <cell r="K84"/>
+          <cell r="L84"/>
+          <cell r="M84"/>
+          <cell r="N84"/>
+          <cell r="O84"/>
+          <cell r="P84"/>
+          <cell r="Q84"/>
+          <cell r="R84"/>
+          <cell r="S84"/>
+          <cell r="T84"/>
+          <cell r="U84"/>
+          <cell r="V84"/>
+          <cell r="W84"/>
+          <cell r="X84"/>
+        </row>
+        <row r="85">
+          <cell r="D85"/>
+          <cell r="E85"/>
+          <cell r="F85"/>
+          <cell r="G85"/>
+          <cell r="H85"/>
+          <cell r="I85"/>
+          <cell r="J85"/>
+          <cell r="K85"/>
+          <cell r="L85"/>
+          <cell r="M85"/>
+          <cell r="N85"/>
+          <cell r="O85"/>
+          <cell r="P85"/>
+          <cell r="Q85"/>
+          <cell r="R85"/>
+          <cell r="S85"/>
+          <cell r="T85"/>
+          <cell r="U85"/>
+          <cell r="V85"/>
+          <cell r="W85"/>
+          <cell r="X85"/>
+        </row>
+        <row r="86">
+          <cell r="D86"/>
+          <cell r="E86"/>
+          <cell r="F86"/>
+          <cell r="G86"/>
+          <cell r="H86"/>
+          <cell r="I86"/>
+          <cell r="J86"/>
+          <cell r="K86"/>
+          <cell r="L86"/>
+          <cell r="M86"/>
+          <cell r="N86"/>
+          <cell r="O86"/>
+          <cell r="P86"/>
+          <cell r="Q86"/>
+          <cell r="R86"/>
+          <cell r="S86"/>
+          <cell r="T86"/>
+          <cell r="U86"/>
+          <cell r="V86"/>
+          <cell r="W86"/>
+          <cell r="X86"/>
+        </row>
+        <row r="87">
+          <cell r="D87"/>
+          <cell r="E87"/>
+          <cell r="F87"/>
+          <cell r="G87"/>
+          <cell r="H87"/>
+          <cell r="I87"/>
+          <cell r="J87"/>
+          <cell r="K87"/>
+          <cell r="L87"/>
+          <cell r="M87"/>
+          <cell r="N87"/>
+          <cell r="O87"/>
+          <cell r="P87"/>
+          <cell r="Q87"/>
+          <cell r="R87"/>
+          <cell r="S87"/>
+          <cell r="T87"/>
+          <cell r="U87"/>
+          <cell r="V87"/>
+          <cell r="W87"/>
+          <cell r="X87"/>
+        </row>
+        <row r="88">
+          <cell r="D88"/>
+          <cell r="E88"/>
+          <cell r="F88"/>
+          <cell r="G88"/>
+          <cell r="H88"/>
+          <cell r="I88"/>
+          <cell r="J88"/>
+          <cell r="K88"/>
+          <cell r="L88"/>
+          <cell r="M88"/>
+          <cell r="N88"/>
+          <cell r="O88"/>
+          <cell r="P88"/>
+          <cell r="Q88"/>
+          <cell r="R88"/>
+          <cell r="S88"/>
+          <cell r="T88"/>
+          <cell r="U88"/>
+          <cell r="V88"/>
+          <cell r="W88"/>
+          <cell r="X88"/>
+        </row>
+        <row r="89">
+          <cell r="D89"/>
+          <cell r="E89"/>
+          <cell r="F89"/>
+          <cell r="G89"/>
+          <cell r="H89"/>
+          <cell r="I89"/>
+          <cell r="J89"/>
+          <cell r="K89"/>
+          <cell r="L89"/>
+          <cell r="M89"/>
+          <cell r="N89"/>
+          <cell r="O89"/>
+          <cell r="P89"/>
+          <cell r="Q89"/>
+          <cell r="R89"/>
+          <cell r="S89"/>
+          <cell r="T89"/>
+          <cell r="U89"/>
+          <cell r="V89"/>
+          <cell r="W89"/>
+          <cell r="X89"/>
+        </row>
+        <row r="90">
+          <cell r="D90"/>
+          <cell r="E90"/>
+          <cell r="F90"/>
+          <cell r="G90"/>
+          <cell r="H90"/>
+          <cell r="I90"/>
+          <cell r="J90"/>
+          <cell r="K90"/>
+          <cell r="L90"/>
+          <cell r="M90"/>
+          <cell r="N90"/>
+          <cell r="O90"/>
+          <cell r="P90"/>
+          <cell r="Q90"/>
+          <cell r="R90"/>
+          <cell r="S90"/>
+          <cell r="T90"/>
+          <cell r="U90"/>
+          <cell r="V90"/>
+          <cell r="W90"/>
+          <cell r="X90"/>
+        </row>
+        <row r="91">
+          <cell r="D91"/>
+          <cell r="E91"/>
+          <cell r="F91"/>
+          <cell r="G91"/>
+          <cell r="H91"/>
+          <cell r="I91"/>
+          <cell r="J91"/>
+          <cell r="K91"/>
+          <cell r="L91"/>
+          <cell r="M91"/>
+          <cell r="N91"/>
+          <cell r="O91"/>
+          <cell r="P91"/>
+          <cell r="Q91"/>
+          <cell r="R91"/>
+          <cell r="S91"/>
+          <cell r="T91"/>
+          <cell r="U91"/>
+          <cell r="V91"/>
+          <cell r="W91"/>
+          <cell r="X91"/>
+        </row>
+        <row r="92">
+          <cell r="D92"/>
+          <cell r="E92"/>
+          <cell r="F92"/>
+          <cell r="G92"/>
+          <cell r="H92"/>
+          <cell r="I92"/>
+          <cell r="J92"/>
+          <cell r="K92"/>
+          <cell r="L92"/>
+          <cell r="M92"/>
+          <cell r="N92"/>
+          <cell r="O92"/>
+          <cell r="P92"/>
+          <cell r="Q92"/>
+          <cell r="R92"/>
+          <cell r="S92"/>
+          <cell r="T92"/>
+          <cell r="U92"/>
+          <cell r="V92"/>
+          <cell r="W92"/>
+          <cell r="X92"/>
+        </row>
+        <row r="93">
+          <cell r="D93"/>
+          <cell r="E93"/>
+          <cell r="F93"/>
+          <cell r="G93"/>
+          <cell r="H93"/>
+          <cell r="I93"/>
+          <cell r="J93"/>
+          <cell r="K93"/>
+          <cell r="L93"/>
+          <cell r="M93"/>
+          <cell r="N93"/>
+          <cell r="O93"/>
+          <cell r="P93"/>
+          <cell r="Q93"/>
+          <cell r="R93"/>
+          <cell r="S93"/>
+          <cell r="T93"/>
+          <cell r="U93"/>
+          <cell r="V93"/>
+          <cell r="W93"/>
+          <cell r="X93"/>
+        </row>
+        <row r="94">
+          <cell r="D94"/>
+          <cell r="E94"/>
+          <cell r="F94"/>
+          <cell r="G94"/>
+          <cell r="H94"/>
+          <cell r="I94"/>
+          <cell r="J94"/>
+          <cell r="K94"/>
+          <cell r="L94"/>
+          <cell r="M94"/>
+          <cell r="N94"/>
+          <cell r="O94"/>
+          <cell r="P94"/>
+          <cell r="Q94"/>
+          <cell r="R94"/>
+          <cell r="S94"/>
+          <cell r="T94"/>
+          <cell r="U94"/>
+          <cell r="V94"/>
+          <cell r="W94"/>
+          <cell r="X94"/>
+        </row>
+        <row r="95">
+          <cell r="D95"/>
+          <cell r="E95"/>
+          <cell r="F95"/>
+          <cell r="G95"/>
+          <cell r="H95"/>
+          <cell r="I95"/>
+          <cell r="J95"/>
+          <cell r="K95"/>
+          <cell r="L95"/>
+          <cell r="M95"/>
+          <cell r="N95"/>
+          <cell r="O95"/>
+          <cell r="P95"/>
+          <cell r="Q95"/>
+          <cell r="R95"/>
+          <cell r="S95"/>
+          <cell r="T95"/>
+          <cell r="U95"/>
+          <cell r="V95"/>
+          <cell r="W95"/>
+          <cell r="X95"/>
+        </row>
+        <row r="96">
+          <cell r="D96"/>
+          <cell r="E96"/>
+          <cell r="F96"/>
+          <cell r="G96"/>
+          <cell r="H96"/>
+          <cell r="I96"/>
+          <cell r="J96"/>
+          <cell r="K96"/>
+          <cell r="L96"/>
+          <cell r="M96"/>
+          <cell r="N96"/>
+          <cell r="O96"/>
+          <cell r="P96"/>
+          <cell r="Q96"/>
+          <cell r="R96"/>
+          <cell r="S96"/>
+          <cell r="T96"/>
+          <cell r="U96"/>
+          <cell r="V96"/>
+          <cell r="W96"/>
+          <cell r="X96"/>
+        </row>
+        <row r="97">
+          <cell r="D97"/>
+          <cell r="E97"/>
+          <cell r="F97"/>
+          <cell r="G97"/>
+          <cell r="H97"/>
+          <cell r="I97"/>
+          <cell r="J97"/>
+          <cell r="K97"/>
+          <cell r="L97"/>
+          <cell r="M97"/>
+          <cell r="N97"/>
+          <cell r="O97"/>
+          <cell r="P97"/>
+          <cell r="Q97"/>
+          <cell r="R97"/>
+          <cell r="S97"/>
+          <cell r="T97"/>
+          <cell r="U97"/>
+          <cell r="V97"/>
+          <cell r="W97"/>
+          <cell r="X97"/>
+        </row>
+        <row r="98">
+          <cell r="D98"/>
+          <cell r="E98"/>
+          <cell r="F98"/>
+          <cell r="G98"/>
+          <cell r="H98"/>
+          <cell r="I98"/>
+          <cell r="J98"/>
+          <cell r="K98"/>
+          <cell r="L98"/>
+          <cell r="M98"/>
+          <cell r="N98"/>
+          <cell r="O98"/>
+          <cell r="P98"/>
+          <cell r="Q98"/>
+          <cell r="R98"/>
+          <cell r="S98"/>
+          <cell r="T98"/>
+          <cell r="U98"/>
+          <cell r="V98"/>
+          <cell r="W98"/>
+          <cell r="X98"/>
+        </row>
+        <row r="99">
+          <cell r="D99"/>
+          <cell r="E99"/>
+          <cell r="F99"/>
+          <cell r="G99"/>
+          <cell r="H99"/>
+          <cell r="I99"/>
+          <cell r="J99"/>
+          <cell r="K99"/>
+          <cell r="L99"/>
+          <cell r="M99"/>
+          <cell r="N99"/>
+          <cell r="O99"/>
+          <cell r="P99"/>
+          <cell r="Q99"/>
+          <cell r="R99"/>
+          <cell r="S99"/>
+          <cell r="T99"/>
+          <cell r="U99"/>
+          <cell r="V99"/>
+          <cell r="W99"/>
+          <cell r="X99"/>
+        </row>
+        <row r="100">
+          <cell r="D100"/>
+          <cell r="E100"/>
+          <cell r="F100"/>
+          <cell r="G100"/>
+          <cell r="H100"/>
+          <cell r="I100"/>
+          <cell r="J100"/>
+          <cell r="K100"/>
+          <cell r="L100"/>
+          <cell r="M100"/>
+          <cell r="N100"/>
+          <cell r="O100"/>
+          <cell r="P100"/>
+          <cell r="Q100"/>
+          <cell r="R100"/>
+          <cell r="S100"/>
+          <cell r="T100"/>
+          <cell r="U100"/>
+          <cell r="V100"/>
+          <cell r="W100"/>
+          <cell r="X100"/>
+        </row>
+        <row r="101">
+          <cell r="D101"/>
+          <cell r="E101"/>
+          <cell r="F101"/>
+          <cell r="G101"/>
+          <cell r="H101"/>
+          <cell r="I101"/>
+          <cell r="J101"/>
+          <cell r="K101"/>
+          <cell r="L101"/>
+          <cell r="M101"/>
+          <cell r="N101"/>
+          <cell r="O101"/>
+          <cell r="P101"/>
+          <cell r="Q101"/>
+          <cell r="R101"/>
+          <cell r="S101"/>
+          <cell r="T101"/>
+          <cell r="U101"/>
+          <cell r="V101"/>
+          <cell r="W101"/>
+          <cell r="X101"/>
+        </row>
+        <row r="102">
+          <cell r="D102"/>
+          <cell r="E102"/>
+          <cell r="F102"/>
+          <cell r="G102"/>
+          <cell r="H102"/>
+          <cell r="I102"/>
+          <cell r="J102"/>
+          <cell r="K102"/>
+          <cell r="L102"/>
+          <cell r="M102"/>
+          <cell r="N102"/>
+          <cell r="O102"/>
+          <cell r="P102"/>
+          <cell r="Q102"/>
+          <cell r="R102"/>
+          <cell r="S102"/>
+          <cell r="T102"/>
+          <cell r="U102"/>
+          <cell r="V102"/>
+          <cell r="W102"/>
+          <cell r="X102"/>
+        </row>
+        <row r="103">
+          <cell r="D103"/>
+          <cell r="E103"/>
+          <cell r="F103"/>
+          <cell r="G103"/>
+          <cell r="H103"/>
+          <cell r="I103"/>
+          <cell r="J103"/>
+          <cell r="K103"/>
+          <cell r="L103"/>
+          <cell r="M103"/>
+          <cell r="N103"/>
+          <cell r="O103"/>
+          <cell r="P103"/>
+          <cell r="Q103"/>
+          <cell r="R103"/>
+          <cell r="S103"/>
+          <cell r="T103"/>
+          <cell r="U103"/>
+          <cell r="V103"/>
+          <cell r="W103"/>
+          <cell r="X103"/>
+        </row>
+        <row r="104">
+          <cell r="D104"/>
+          <cell r="E104"/>
+          <cell r="F104"/>
+          <cell r="G104"/>
+          <cell r="H104"/>
+          <cell r="I104"/>
+          <cell r="J104"/>
+          <cell r="K104"/>
+          <cell r="L104"/>
+          <cell r="M104"/>
+          <cell r="N104"/>
+          <cell r="O104"/>
+          <cell r="P104"/>
+          <cell r="Q104"/>
+          <cell r="R104"/>
+          <cell r="S104"/>
+          <cell r="T104"/>
+          <cell r="U104"/>
+          <cell r="V104"/>
+          <cell r="W104"/>
+          <cell r="X104"/>
+        </row>
+        <row r="105">
+          <cell r="D105"/>
+          <cell r="E105"/>
+          <cell r="F105"/>
+          <cell r="G105"/>
+          <cell r="H105"/>
+          <cell r="I105"/>
+          <cell r="J105"/>
+          <cell r="K105"/>
+          <cell r="L105"/>
+          <cell r="M105"/>
+          <cell r="N105"/>
+          <cell r="O105"/>
+          <cell r="P105"/>
+          <cell r="Q105"/>
+          <cell r="R105"/>
+          <cell r="S105"/>
+          <cell r="T105"/>
+          <cell r="U105"/>
+          <cell r="V105"/>
+          <cell r="W105"/>
+          <cell r="X105"/>
+        </row>
+        <row r="106">
+          <cell r="D106"/>
+          <cell r="E106"/>
+          <cell r="F106"/>
+          <cell r="G106"/>
+          <cell r="H106"/>
+          <cell r="I106"/>
+          <cell r="J106"/>
+          <cell r="K106"/>
+          <cell r="L106"/>
+          <cell r="M106"/>
+          <cell r="N106"/>
+          <cell r="O106"/>
+          <cell r="P106"/>
+          <cell r="Q106"/>
+          <cell r="R106"/>
+          <cell r="S106"/>
+          <cell r="T106"/>
+          <cell r="U106"/>
+          <cell r="V106"/>
+          <cell r="W106"/>
+          <cell r="X106"/>
+        </row>
+        <row r="107">
+          <cell r="D107"/>
+          <cell r="E107"/>
+          <cell r="F107"/>
+          <cell r="G107"/>
+          <cell r="H107"/>
+          <cell r="I107"/>
+          <cell r="J107"/>
+          <cell r="K107"/>
+          <cell r="L107"/>
+          <cell r="M107"/>
+          <cell r="N107"/>
+          <cell r="O107"/>
+          <cell r="P107"/>
+          <cell r="Q107"/>
+          <cell r="R107"/>
+          <cell r="S107"/>
+          <cell r="T107"/>
+          <cell r="U107"/>
+          <cell r="V107"/>
+          <cell r="W107"/>
+          <cell r="X107"/>
+        </row>
+        <row r="108">
+          <cell r="D108"/>
+          <cell r="E108"/>
+          <cell r="F108"/>
+          <cell r="G108"/>
+          <cell r="H108"/>
+          <cell r="I108"/>
+          <cell r="J108"/>
+          <cell r="K108"/>
+          <cell r="L108"/>
+          <cell r="M108"/>
+          <cell r="N108"/>
+          <cell r="O108"/>
+          <cell r="P108"/>
+          <cell r="Q108"/>
+          <cell r="R108"/>
+          <cell r="S108"/>
+          <cell r="T108"/>
+          <cell r="U108"/>
+          <cell r="V108"/>
+          <cell r="W108"/>
+          <cell r="X108"/>
+        </row>
+        <row r="109">
+          <cell r="D109"/>
+          <cell r="E109"/>
+          <cell r="F109"/>
+          <cell r="G109"/>
+          <cell r="H109"/>
+          <cell r="I109"/>
+          <cell r="J109"/>
+          <cell r="K109"/>
+          <cell r="L109"/>
+          <cell r="M109"/>
+          <cell r="N109"/>
+          <cell r="O109"/>
+          <cell r="P109"/>
+          <cell r="Q109"/>
+          <cell r="R109"/>
+          <cell r="S109"/>
+          <cell r="T109"/>
+          <cell r="U109"/>
+          <cell r="V109"/>
+          <cell r="W109"/>
+          <cell r="X109"/>
+        </row>
+        <row r="110">
+          <cell r="D110"/>
+          <cell r="E110"/>
+          <cell r="F110"/>
+          <cell r="G110"/>
+          <cell r="H110"/>
+          <cell r="I110"/>
+          <cell r="J110"/>
+          <cell r="K110"/>
+          <cell r="L110"/>
+          <cell r="M110"/>
+          <cell r="N110"/>
+          <cell r="O110"/>
+          <cell r="P110"/>
+          <cell r="Q110"/>
+          <cell r="R110"/>
+          <cell r="S110"/>
+          <cell r="T110"/>
+          <cell r="U110"/>
+          <cell r="V110"/>
+          <cell r="W110"/>
+          <cell r="X110"/>
+        </row>
+        <row r="111">
+          <cell r="D111"/>
+          <cell r="E111"/>
+          <cell r="F111"/>
+          <cell r="G111"/>
+          <cell r="H111"/>
+          <cell r="I111"/>
+          <cell r="J111"/>
+          <cell r="K111"/>
+          <cell r="L111"/>
+          <cell r="M111"/>
+          <cell r="N111"/>
+          <cell r="O111"/>
+          <cell r="P111"/>
+          <cell r="Q111"/>
+          <cell r="R111"/>
+          <cell r="S111"/>
+          <cell r="T111"/>
+          <cell r="U111"/>
+          <cell r="V111"/>
+          <cell r="W111"/>
+          <cell r="X111"/>
+        </row>
+        <row r="112">
+          <cell r="D112"/>
+          <cell r="E112"/>
+          <cell r="F112"/>
+          <cell r="G112"/>
+          <cell r="H112"/>
+          <cell r="I112"/>
+          <cell r="J112"/>
+          <cell r="K112"/>
+          <cell r="L112"/>
+          <cell r="M112"/>
+          <cell r="N112"/>
+          <cell r="O112"/>
+          <cell r="P112"/>
+          <cell r="Q112"/>
+          <cell r="R112"/>
+          <cell r="S112"/>
+          <cell r="T112"/>
+          <cell r="U112"/>
+          <cell r="V112"/>
+          <cell r="W112"/>
+          <cell r="X112"/>
+        </row>
+        <row r="113">
+          <cell r="D113"/>
+          <cell r="E113"/>
+          <cell r="F113"/>
+          <cell r="G113"/>
+          <cell r="H113"/>
+          <cell r="I113"/>
+          <cell r="J113"/>
+          <cell r="K113"/>
+          <cell r="L113"/>
+          <cell r="M113"/>
+          <cell r="N113"/>
+          <cell r="O113"/>
+          <cell r="P113"/>
+          <cell r="Q113"/>
+          <cell r="R113"/>
+          <cell r="S113"/>
+          <cell r="T113"/>
+          <cell r="U113"/>
+          <cell r="V113"/>
+          <cell r="W113"/>
+          <cell r="X113"/>
+        </row>
+        <row r="114">
+          <cell r="D114"/>
+          <cell r="E114"/>
+          <cell r="F114"/>
+          <cell r="G114"/>
+          <cell r="H114"/>
+          <cell r="I114"/>
+          <cell r="J114"/>
+          <cell r="K114"/>
+          <cell r="L114"/>
+          <cell r="M114"/>
+          <cell r="N114"/>
+          <cell r="O114"/>
+          <cell r="P114"/>
+          <cell r="Q114"/>
+          <cell r="R114"/>
+          <cell r="S114"/>
+          <cell r="T114"/>
+          <cell r="U114"/>
+          <cell r="V114"/>
+          <cell r="W114"/>
+          <cell r="X114"/>
+        </row>
+        <row r="115">
+          <cell r="D115"/>
+          <cell r="E115"/>
+          <cell r="F115"/>
+          <cell r="G115"/>
+          <cell r="H115"/>
+          <cell r="I115"/>
+          <cell r="J115"/>
+          <cell r="K115"/>
+          <cell r="L115"/>
+          <cell r="M115"/>
+          <cell r="N115"/>
+          <cell r="O115"/>
+          <cell r="P115"/>
+          <cell r="Q115"/>
+          <cell r="R115"/>
+          <cell r="S115"/>
+          <cell r="T115"/>
+          <cell r="U115"/>
+          <cell r="V115"/>
+          <cell r="W115"/>
+          <cell r="X115"/>
+        </row>
+        <row r="116">
+          <cell r="D116"/>
+          <cell r="E116"/>
+          <cell r="F116"/>
+          <cell r="G116"/>
+          <cell r="H116"/>
+          <cell r="I116"/>
+          <cell r="J116"/>
+          <cell r="K116"/>
+          <cell r="L116"/>
+          <cell r="M116"/>
+          <cell r="N116"/>
+          <cell r="O116"/>
+          <cell r="P116"/>
+          <cell r="Q116"/>
+          <cell r="R116"/>
+          <cell r="S116"/>
+          <cell r="T116"/>
+          <cell r="U116"/>
+          <cell r="V116"/>
+          <cell r="W116"/>
+          <cell r="X116"/>
+        </row>
+        <row r="117">
+          <cell r="D117"/>
+          <cell r="E117"/>
+          <cell r="F117"/>
+          <cell r="G117"/>
+          <cell r="H117"/>
+          <cell r="I117"/>
+          <cell r="J117"/>
+          <cell r="K117"/>
+          <cell r="L117"/>
+          <cell r="M117"/>
+          <cell r="N117"/>
+          <cell r="O117"/>
+          <cell r="P117"/>
+          <cell r="Q117"/>
+          <cell r="R117"/>
+          <cell r="S117"/>
+          <cell r="T117"/>
+          <cell r="U117"/>
+          <cell r="V117"/>
+          <cell r="W117"/>
+          <cell r="X117"/>
+        </row>
+        <row r="118">
+          <cell r="D118"/>
+          <cell r="E118"/>
+          <cell r="F118"/>
+          <cell r="G118"/>
+          <cell r="H118"/>
+          <cell r="I118"/>
+          <cell r="J118"/>
+          <cell r="K118"/>
+          <cell r="L118"/>
+          <cell r="M118"/>
+          <cell r="N118"/>
+          <cell r="O118"/>
+          <cell r="P118"/>
+          <cell r="Q118"/>
+          <cell r="R118"/>
+          <cell r="S118"/>
+          <cell r="T118"/>
+          <cell r="U118"/>
+          <cell r="V118"/>
+          <cell r="W118"/>
+          <cell r="X118"/>
+        </row>
+        <row r="119">
+          <cell r="D119"/>
+          <cell r="E119"/>
+          <cell r="F119"/>
+          <cell r="G119"/>
+          <cell r="H119"/>
+          <cell r="I119"/>
+          <cell r="J119"/>
+          <cell r="K119"/>
+          <cell r="L119"/>
+          <cell r="M119"/>
+          <cell r="N119"/>
+          <cell r="O119"/>
+          <cell r="P119"/>
+          <cell r="Q119"/>
+          <cell r="R119"/>
+          <cell r="S119"/>
+          <cell r="T119"/>
+          <cell r="U119"/>
+          <cell r="V119"/>
+          <cell r="W119"/>
+          <cell r="X119"/>
+        </row>
+        <row r="120">
+          <cell r="D120"/>
+          <cell r="E120"/>
+          <cell r="F120"/>
+          <cell r="G120"/>
+          <cell r="H120"/>
+          <cell r="I120"/>
+          <cell r="J120"/>
+          <cell r="K120"/>
+          <cell r="L120"/>
+          <cell r="M120"/>
+          <cell r="N120"/>
+          <cell r="O120"/>
+          <cell r="P120"/>
+          <cell r="Q120"/>
+          <cell r="R120"/>
+          <cell r="S120"/>
+          <cell r="T120"/>
+          <cell r="U120"/>
+          <cell r="V120"/>
+          <cell r="W120"/>
+          <cell r="X120"/>
+        </row>
+        <row r="121">
+          <cell r="D121"/>
+          <cell r="E121"/>
+          <cell r="F121"/>
+          <cell r="G121"/>
+          <cell r="H121"/>
+          <cell r="I121"/>
+          <cell r="J121"/>
+          <cell r="K121"/>
+          <cell r="L121"/>
+          <cell r="M121"/>
+          <cell r="N121"/>
+          <cell r="O121"/>
+          <cell r="P121"/>
+          <cell r="Q121"/>
+          <cell r="R121"/>
+          <cell r="S121"/>
+          <cell r="T121"/>
+          <cell r="U121"/>
+          <cell r="V121"/>
+          <cell r="W121"/>
+          <cell r="X121"/>
+        </row>
+        <row r="122">
+          <cell r="D122"/>
+          <cell r="E122"/>
+          <cell r="F122"/>
+          <cell r="G122"/>
+          <cell r="H122"/>
+          <cell r="I122"/>
+          <cell r="J122"/>
+          <cell r="K122"/>
+          <cell r="L122"/>
+          <cell r="M122"/>
+          <cell r="N122"/>
+          <cell r="O122"/>
+          <cell r="P122"/>
+          <cell r="Q122"/>
+          <cell r="R122"/>
+          <cell r="S122"/>
+          <cell r="T122"/>
+          <cell r="U122"/>
+          <cell r="V122"/>
+          <cell r="W122"/>
+          <cell r="X122"/>
+        </row>
+        <row r="123">
+          <cell r="D123"/>
+          <cell r="E123"/>
+          <cell r="F123"/>
+          <cell r="G123"/>
+          <cell r="H123"/>
+          <cell r="I123"/>
+          <cell r="J123"/>
+          <cell r="K123"/>
+          <cell r="L123"/>
+          <cell r="M123"/>
+          <cell r="N123"/>
+          <cell r="O123"/>
+          <cell r="P123"/>
+          <cell r="Q123"/>
+          <cell r="R123"/>
+          <cell r="S123"/>
+          <cell r="T123"/>
+          <cell r="U123"/>
+          <cell r="V123"/>
+          <cell r="W123"/>
+          <cell r="X123"/>
+        </row>
+        <row r="124">
+          <cell r="D124"/>
+          <cell r="E124"/>
+          <cell r="F124"/>
+          <cell r="G124"/>
+          <cell r="H124"/>
+          <cell r="I124"/>
+          <cell r="J124"/>
+          <cell r="K124"/>
+          <cell r="L124"/>
+          <cell r="M124"/>
+          <cell r="N124"/>
+          <cell r="O124"/>
+          <cell r="P124"/>
+          <cell r="Q124"/>
+          <cell r="R124"/>
+          <cell r="S124"/>
+          <cell r="T124"/>
+          <cell r="U124"/>
+          <cell r="V124"/>
+          <cell r="W124"/>
+          <cell r="X124"/>
+        </row>
+        <row r="125">
+          <cell r="D125"/>
+          <cell r="E125"/>
+          <cell r="F125"/>
+          <cell r="G125"/>
+          <cell r="H125"/>
+          <cell r="I125"/>
+          <cell r="J125"/>
+          <cell r="K125"/>
+          <cell r="L125"/>
+          <cell r="M125"/>
+          <cell r="N125"/>
+          <cell r="O125"/>
+          <cell r="P125"/>
+          <cell r="Q125"/>
+          <cell r="R125"/>
+          <cell r="S125"/>
+          <cell r="T125"/>
+          <cell r="U125"/>
+          <cell r="V125"/>
+          <cell r="W125"/>
+          <cell r="X125"/>
+        </row>
+        <row r="126">
+          <cell r="D126"/>
+          <cell r="E126"/>
+          <cell r="F126"/>
+          <cell r="G126"/>
+          <cell r="H126"/>
+          <cell r="I126"/>
+          <cell r="J126"/>
+          <cell r="K126"/>
+          <cell r="L126"/>
+          <cell r="M126"/>
+          <cell r="N126"/>
+          <cell r="O126"/>
+          <cell r="P126"/>
+          <cell r="Q126"/>
+          <cell r="R126"/>
+          <cell r="S126"/>
+          <cell r="T126"/>
+          <cell r="U126"/>
+          <cell r="V126"/>
+          <cell r="W126"/>
+          <cell r="X126"/>
+        </row>
+        <row r="127">
+          <cell r="D127"/>
+          <cell r="E127"/>
+          <cell r="F127"/>
+          <cell r="G127"/>
+          <cell r="H127"/>
+          <cell r="I127"/>
+          <cell r="J127"/>
+          <cell r="K127"/>
+          <cell r="L127"/>
+          <cell r="M127"/>
+          <cell r="N127"/>
+          <cell r="O127"/>
+          <cell r="P127"/>
+          <cell r="Q127"/>
+          <cell r="R127"/>
+          <cell r="S127"/>
+          <cell r="T127"/>
+          <cell r="U127"/>
+          <cell r="V127"/>
+          <cell r="W127"/>
+          <cell r="X127"/>
+        </row>
+        <row r="128">
+          <cell r="D128"/>
+          <cell r="E128"/>
+          <cell r="F128"/>
+          <cell r="G128"/>
+          <cell r="H128"/>
+          <cell r="I128"/>
+          <cell r="J128"/>
+          <cell r="K128"/>
+          <cell r="L128"/>
+          <cell r="M128"/>
+          <cell r="N128"/>
+          <cell r="O128"/>
+          <cell r="P128"/>
+          <cell r="Q128"/>
+          <cell r="R128"/>
+          <cell r="S128"/>
+          <cell r="T128"/>
+          <cell r="U128"/>
+          <cell r="V128"/>
+          <cell r="W128"/>
+          <cell r="X128"/>
+        </row>
+        <row r="129">
+          <cell r="D129"/>
+          <cell r="E129"/>
+          <cell r="F129"/>
+          <cell r="G129"/>
+          <cell r="H129"/>
+          <cell r="I129"/>
+          <cell r="J129"/>
+          <cell r="K129"/>
+          <cell r="L129"/>
+          <cell r="M129"/>
+          <cell r="N129"/>
+          <cell r="O129"/>
+          <cell r="P129"/>
+          <cell r="Q129"/>
+          <cell r="R129"/>
+          <cell r="S129"/>
+          <cell r="T129"/>
+          <cell r="U129"/>
+          <cell r="V129"/>
+          <cell r="W129"/>
+          <cell r="X129"/>
+        </row>
+        <row r="130">
+          <cell r="D130"/>
+          <cell r="E130"/>
+          <cell r="F130"/>
+          <cell r="G130"/>
+          <cell r="H130"/>
+          <cell r="I130"/>
+          <cell r="J130"/>
+          <cell r="K130"/>
+          <cell r="L130"/>
+          <cell r="M130"/>
+          <cell r="N130"/>
+          <cell r="O130"/>
+          <cell r="P130"/>
+          <cell r="Q130"/>
+          <cell r="R130"/>
+          <cell r="S130"/>
+          <cell r="T130"/>
+          <cell r="U130"/>
+          <cell r="V130"/>
+          <cell r="W130"/>
+          <cell r="X130"/>
+        </row>
+        <row r="131">
+          <cell r="D131"/>
+          <cell r="E131"/>
+          <cell r="F131"/>
+          <cell r="G131"/>
+          <cell r="H131"/>
+          <cell r="I131"/>
+          <cell r="J131"/>
+          <cell r="K131"/>
+          <cell r="L131"/>
+          <cell r="M131"/>
+          <cell r="N131"/>
+          <cell r="O131"/>
+          <cell r="P131"/>
+          <cell r="Q131"/>
+          <cell r="R131"/>
+          <cell r="S131"/>
+          <cell r="T131"/>
+          <cell r="U131"/>
+          <cell r="V131"/>
+          <cell r="W131"/>
+          <cell r="X131"/>
+        </row>
+        <row r="132">
+          <cell r="D132"/>
+          <cell r="E132"/>
+          <cell r="F132"/>
+          <cell r="G132"/>
+          <cell r="H132"/>
+          <cell r="I132"/>
+          <cell r="J132"/>
+          <cell r="K132"/>
+          <cell r="L132"/>
+          <cell r="M132"/>
+          <cell r="N132"/>
+          <cell r="O132"/>
+          <cell r="P132"/>
+          <cell r="Q132"/>
+          <cell r="R132"/>
+          <cell r="S132"/>
+          <cell r="T132"/>
+          <cell r="U132"/>
+          <cell r="V132"/>
+          <cell r="W132"/>
+          <cell r="X132"/>
+        </row>
+        <row r="133">
+          <cell r="D133"/>
+          <cell r="E133"/>
+          <cell r="F133"/>
+          <cell r="G133"/>
+          <cell r="H133"/>
+          <cell r="I133"/>
+          <cell r="J133"/>
+          <cell r="K133"/>
+          <cell r="L133"/>
+          <cell r="M133"/>
+          <cell r="N133"/>
+          <cell r="O133"/>
+          <cell r="P133"/>
+          <cell r="Q133"/>
+          <cell r="R133"/>
+          <cell r="S133"/>
+          <cell r="T133"/>
+          <cell r="U133"/>
+          <cell r="V133"/>
+          <cell r="W133"/>
+          <cell r="X133"/>
+        </row>
+        <row r="134">
+          <cell r="D134"/>
+          <cell r="E134"/>
+          <cell r="F134"/>
+          <cell r="G134"/>
+          <cell r="H134"/>
+          <cell r="I134"/>
+          <cell r="J134"/>
+          <cell r="K134"/>
+          <cell r="L134"/>
+          <cell r="M134"/>
+          <cell r="N134"/>
+          <cell r="O134"/>
+          <cell r="P134"/>
+          <cell r="Q134"/>
+          <cell r="R134"/>
+          <cell r="S134"/>
+          <cell r="T134"/>
+          <cell r="U134"/>
+          <cell r="V134"/>
+          <cell r="W134"/>
+          <cell r="X134"/>
+        </row>
+        <row r="135">
+          <cell r="D135"/>
+          <cell r="E135"/>
+          <cell r="F135"/>
+          <cell r="G135"/>
+          <cell r="H135"/>
+          <cell r="I135"/>
+          <cell r="J135"/>
+          <cell r="K135"/>
+          <cell r="L135"/>
+          <cell r="M135"/>
+          <cell r="N135"/>
+          <cell r="O135"/>
+          <cell r="P135"/>
+          <cell r="Q135"/>
+          <cell r="R135"/>
+          <cell r="S135"/>
+          <cell r="T135"/>
+          <cell r="U135"/>
+          <cell r="V135"/>
+          <cell r="W135"/>
+          <cell r="X135"/>
+        </row>
+        <row r="136">
+          <cell r="D136"/>
+          <cell r="E136"/>
+          <cell r="F136"/>
+          <cell r="G136"/>
+          <cell r="H136"/>
+          <cell r="I136"/>
+          <cell r="J136"/>
+          <cell r="K136"/>
+          <cell r="L136"/>
+          <cell r="M136"/>
+          <cell r="N136"/>
+          <cell r="O136"/>
+          <cell r="P136"/>
+          <cell r="Q136"/>
+          <cell r="R136"/>
+          <cell r="S136"/>
+          <cell r="T136"/>
+          <cell r="U136"/>
+          <cell r="V136"/>
+          <cell r="W136"/>
+          <cell r="X136"/>
+        </row>
+        <row r="137">
+          <cell r="D137"/>
+          <cell r="E137"/>
+          <cell r="F137"/>
+          <cell r="G137"/>
+          <cell r="H137"/>
+          <cell r="I137"/>
+          <cell r="J137"/>
+          <cell r="K137"/>
+          <cell r="L137"/>
+          <cell r="M137"/>
+          <cell r="N137"/>
+          <cell r="O137"/>
+          <cell r="P137"/>
+          <cell r="Q137"/>
+          <cell r="R137"/>
+          <cell r="S137"/>
+          <cell r="T137"/>
+          <cell r="U137"/>
+          <cell r="V137"/>
+          <cell r="W137"/>
+          <cell r="X137"/>
+        </row>
+        <row r="138">
+          <cell r="D138"/>
+          <cell r="E138"/>
+          <cell r="F138"/>
+          <cell r="G138"/>
+          <cell r="H138"/>
+          <cell r="I138"/>
+          <cell r="J138"/>
+          <cell r="K138"/>
+          <cell r="L138"/>
+          <cell r="M138"/>
+          <cell r="N138"/>
+          <cell r="O138"/>
+          <cell r="P138"/>
+          <cell r="Q138"/>
+          <cell r="R138"/>
+          <cell r="S138"/>
+          <cell r="T138"/>
+          <cell r="U138"/>
+          <cell r="V138"/>
+          <cell r="W138"/>
+          <cell r="X138"/>
+        </row>
+        <row r="139">
+          <cell r="D139"/>
+          <cell r="E139"/>
+          <cell r="F139"/>
+          <cell r="G139"/>
+          <cell r="H139"/>
+          <cell r="I139"/>
+          <cell r="J139"/>
+          <cell r="K139"/>
+          <cell r="L139"/>
+          <cell r="M139"/>
+          <cell r="N139"/>
+          <cell r="O139"/>
+          <cell r="P139"/>
+          <cell r="Q139"/>
+          <cell r="R139"/>
+          <cell r="S139"/>
+          <cell r="T139"/>
+          <cell r="U139"/>
+          <cell r="V139"/>
+          <cell r="W139"/>
+          <cell r="X139"/>
+        </row>
+        <row r="140">
+          <cell r="D140"/>
+          <cell r="E140"/>
+          <cell r="F140"/>
+          <cell r="G140"/>
+          <cell r="H140"/>
+          <cell r="I140"/>
+          <cell r="J140"/>
+          <cell r="K140"/>
+          <cell r="L140"/>
+          <cell r="M140"/>
+          <cell r="N140"/>
+          <cell r="O140"/>
+          <cell r="P140"/>
+          <cell r="Q140"/>
+          <cell r="R140"/>
+          <cell r="S140"/>
+          <cell r="T140"/>
+          <cell r="U140"/>
+          <cell r="V140"/>
+          <cell r="W140"/>
+          <cell r="X140"/>
+        </row>
+        <row r="141">
+          <cell r="D141"/>
+          <cell r="E141"/>
+          <cell r="F141"/>
+          <cell r="G141"/>
+          <cell r="H141"/>
+          <cell r="I141"/>
+          <cell r="J141"/>
+          <cell r="K141"/>
+          <cell r="L141"/>
+          <cell r="M141"/>
+          <cell r="N141"/>
+          <cell r="O141"/>
+          <cell r="P141"/>
+          <cell r="Q141"/>
+          <cell r="R141"/>
+          <cell r="S141"/>
+          <cell r="T141"/>
+          <cell r="U141"/>
+          <cell r="V141"/>
+          <cell r="W141"/>
+          <cell r="X141"/>
+        </row>
+        <row r="142">
+          <cell r="D142"/>
+          <cell r="E142"/>
+          <cell r="F142"/>
+          <cell r="G142"/>
+          <cell r="H142"/>
+          <cell r="I142"/>
+          <cell r="J142"/>
+          <cell r="K142"/>
+          <cell r="L142"/>
+          <cell r="M142"/>
+          <cell r="N142"/>
+          <cell r="O142"/>
+          <cell r="P142"/>
+          <cell r="Q142"/>
+          <cell r="R142"/>
+          <cell r="S142"/>
+          <cell r="T142"/>
+          <cell r="U142"/>
+          <cell r="V142"/>
+          <cell r="W142"/>
+          <cell r="X142"/>
+        </row>
+        <row r="143">
+          <cell r="D143"/>
+          <cell r="E143"/>
+          <cell r="F143"/>
+          <cell r="G143"/>
+          <cell r="H143"/>
+          <cell r="I143"/>
+          <cell r="J143"/>
+          <cell r="K143"/>
+          <cell r="L143"/>
+          <cell r="M143"/>
+          <cell r="N143"/>
+          <cell r="O143"/>
+          <cell r="P143"/>
+          <cell r="Q143"/>
+          <cell r="R143"/>
+          <cell r="S143"/>
+          <cell r="T143"/>
+          <cell r="U143"/>
+          <cell r="V143"/>
+          <cell r="W143"/>
+          <cell r="X143"/>
+        </row>
+        <row r="144">
+          <cell r="D144"/>
+          <cell r="E144"/>
+          <cell r="F144"/>
+          <cell r="G144"/>
+          <cell r="H144"/>
+          <cell r="I144"/>
+          <cell r="J144"/>
+          <cell r="K144"/>
+          <cell r="L144"/>
+          <cell r="M144"/>
+          <cell r="N144"/>
+          <cell r="O144"/>
+          <cell r="P144"/>
+          <cell r="Q144"/>
+          <cell r="R144"/>
+          <cell r="S144"/>
+          <cell r="T144"/>
+          <cell r="U144"/>
+          <cell r="V144"/>
+          <cell r="W144"/>
+          <cell r="X144"/>
+        </row>
+        <row r="145">
+          <cell r="D145"/>
+          <cell r="E145"/>
+          <cell r="F145"/>
+          <cell r="G145"/>
+          <cell r="H145"/>
+          <cell r="I145"/>
+          <cell r="J145"/>
+          <cell r="K145"/>
+          <cell r="L145"/>
+          <cell r="M145"/>
+          <cell r="N145"/>
+          <cell r="O145"/>
+          <cell r="P145"/>
+          <cell r="Q145"/>
+          <cell r="R145"/>
+          <cell r="S145"/>
+          <cell r="T145"/>
+          <cell r="U145"/>
+          <cell r="V145"/>
+          <cell r="W145"/>
+          <cell r="X145"/>
+        </row>
+        <row r="146">
+          <cell r="D146"/>
+          <cell r="E146"/>
+          <cell r="F146"/>
+          <cell r="G146"/>
+          <cell r="H146"/>
+          <cell r="I146"/>
+          <cell r="J146"/>
+          <cell r="K146"/>
+          <cell r="L146"/>
+          <cell r="M146"/>
+          <cell r="N146"/>
+          <cell r="O146"/>
+          <cell r="P146"/>
+          <cell r="Q146"/>
+          <cell r="R146"/>
+          <cell r="S146"/>
+          <cell r="T146"/>
+          <cell r="U146"/>
+          <cell r="V146"/>
+          <cell r="W146"/>
+          <cell r="X146"/>
+        </row>
+        <row r="147">
+          <cell r="D147"/>
+          <cell r="E147"/>
+          <cell r="F147"/>
+          <cell r="G147"/>
+          <cell r="H147"/>
+          <cell r="I147"/>
+          <cell r="J147"/>
+          <cell r="K147"/>
+          <cell r="L147"/>
+          <cell r="M147"/>
+          <cell r="N147"/>
+          <cell r="O147"/>
+          <cell r="P147"/>
+          <cell r="Q147"/>
+          <cell r="R147"/>
+          <cell r="S147"/>
+          <cell r="T147"/>
+          <cell r="U147"/>
+          <cell r="V147"/>
+          <cell r="W147"/>
+          <cell r="X147"/>
+        </row>
+        <row r="148">
+          <cell r="D148"/>
+          <cell r="E148"/>
+          <cell r="F148"/>
+          <cell r="G148"/>
+          <cell r="H148"/>
+          <cell r="I148"/>
+          <cell r="J148"/>
+          <cell r="K148"/>
+          <cell r="L148"/>
+          <cell r="M148"/>
+          <cell r="N148"/>
+          <cell r="O148"/>
+          <cell r="P148"/>
+          <cell r="Q148"/>
+          <cell r="R148"/>
+          <cell r="S148"/>
+          <cell r="T148"/>
+          <cell r="U148"/>
+          <cell r="V148"/>
+          <cell r="W148"/>
+          <cell r="X148"/>
+        </row>
+        <row r="149">
+          <cell r="D149"/>
+          <cell r="E149"/>
+          <cell r="F149"/>
+          <cell r="G149"/>
+          <cell r="H149"/>
+          <cell r="I149"/>
+          <cell r="J149"/>
+          <cell r="K149"/>
+          <cell r="L149"/>
+          <cell r="M149"/>
+          <cell r="N149"/>
+          <cell r="O149"/>
+          <cell r="P149"/>
+          <cell r="Q149"/>
+          <cell r="R149"/>
+          <cell r="S149"/>
+          <cell r="T149"/>
+          <cell r="U149"/>
+          <cell r="V149"/>
+          <cell r="W149"/>
+          <cell r="X149"/>
+        </row>
+        <row r="150">
+          <cell r="D150"/>
+          <cell r="E150"/>
+          <cell r="F150"/>
+          <cell r="G150"/>
+          <cell r="H150"/>
+          <cell r="I150"/>
+          <cell r="J150"/>
+          <cell r="K150"/>
+          <cell r="L150"/>
+          <cell r="M150"/>
+          <cell r="N150"/>
+          <cell r="O150"/>
+          <cell r="P150"/>
+          <cell r="Q150"/>
+          <cell r="R150"/>
+          <cell r="S150"/>
+          <cell r="T150"/>
+          <cell r="U150"/>
+          <cell r="V150"/>
+          <cell r="W150"/>
+          <cell r="X150"/>
+        </row>
+        <row r="151">
+          <cell r="D151"/>
+          <cell r="E151"/>
+          <cell r="F151"/>
+          <cell r="G151"/>
+          <cell r="H151"/>
+          <cell r="I151"/>
+          <cell r="J151"/>
+          <cell r="K151"/>
+          <cell r="L151"/>
+          <cell r="M151"/>
+          <cell r="N151"/>
+          <cell r="O151"/>
+          <cell r="P151"/>
+          <cell r="Q151"/>
+          <cell r="R151"/>
+          <cell r="S151"/>
+          <cell r="T151"/>
+          <cell r="U151"/>
+          <cell r="V151"/>
+          <cell r="W151"/>
+          <cell r="X151"/>
+        </row>
+        <row r="152">
+          <cell r="D152"/>
+          <cell r="E152"/>
+          <cell r="F152"/>
+          <cell r="G152"/>
+          <cell r="H152"/>
+          <cell r="I152"/>
+          <cell r="J152"/>
+          <cell r="K152"/>
+          <cell r="L152"/>
+          <cell r="M152"/>
+          <cell r="N152"/>
+          <cell r="O152"/>
+          <cell r="P152"/>
+          <cell r="Q152"/>
+          <cell r="R152"/>
+          <cell r="S152"/>
+          <cell r="T152"/>
+          <cell r="U152"/>
+          <cell r="V152"/>
+          <cell r="W152"/>
+          <cell r="X152"/>
+        </row>
+        <row r="153">
+          <cell r="D153"/>
+          <cell r="E153"/>
+          <cell r="F153"/>
+          <cell r="G153"/>
+          <cell r="H153"/>
+          <cell r="I153"/>
+          <cell r="J153"/>
+          <cell r="K153"/>
+          <cell r="L153"/>
+          <cell r="M153"/>
+          <cell r="N153"/>
+          <cell r="O153"/>
+          <cell r="P153"/>
+          <cell r="Q153"/>
+          <cell r="R153"/>
+          <cell r="S153"/>
+          <cell r="T153"/>
+          <cell r="U153"/>
+          <cell r="V153"/>
+          <cell r="W153"/>
+          <cell r="X153"/>
+        </row>
+        <row r="154">
+          <cell r="D154"/>
+          <cell r="E154"/>
+          <cell r="F154"/>
+          <cell r="G154"/>
+          <cell r="H154"/>
+          <cell r="I154"/>
+          <cell r="J154"/>
+          <cell r="K154"/>
+          <cell r="L154"/>
+          <cell r="M154"/>
+          <cell r="N154"/>
+          <cell r="O154"/>
+          <cell r="P154"/>
+          <cell r="Q154"/>
+          <cell r="R154"/>
+          <cell r="S154"/>
+          <cell r="T154"/>
+          <cell r="U154"/>
+          <cell r="V154"/>
+          <cell r="W154"/>
+          <cell r="X154"/>
+        </row>
+        <row r="155">
+          <cell r="D155"/>
+          <cell r="E155"/>
+          <cell r="F155"/>
+          <cell r="G155"/>
+          <cell r="H155"/>
+          <cell r="I155"/>
+          <cell r="J155"/>
+          <cell r="K155"/>
+          <cell r="L155"/>
+          <cell r="M155"/>
+          <cell r="N155"/>
+          <cell r="O155"/>
+          <cell r="P155"/>
+          <cell r="Q155"/>
+          <cell r="R155"/>
+          <cell r="S155"/>
+          <cell r="T155"/>
+          <cell r="U155"/>
+          <cell r="V155"/>
+          <cell r="W155"/>
+          <cell r="X155"/>
+        </row>
+        <row r="156">
+          <cell r="D156"/>
+          <cell r="E156"/>
+          <cell r="F156"/>
+          <cell r="G156"/>
+          <cell r="H156"/>
+          <cell r="I156"/>
+          <cell r="J156"/>
+          <cell r="K156"/>
+          <cell r="L156"/>
+          <cell r="M156"/>
+          <cell r="N156"/>
+          <cell r="O156"/>
+          <cell r="P156"/>
+          <cell r="Q156"/>
+          <cell r="R156"/>
+          <cell r="S156"/>
+          <cell r="T156"/>
+          <cell r="U156"/>
+          <cell r="V156"/>
+          <cell r="W156"/>
+          <cell r="X156"/>
+        </row>
+        <row r="157">
+          <cell r="D157"/>
+          <cell r="E157"/>
+          <cell r="F157"/>
+          <cell r="G157"/>
+          <cell r="H157"/>
+          <cell r="I157"/>
+          <cell r="J157"/>
+          <cell r="K157"/>
+          <cell r="L157"/>
+          <cell r="M157"/>
+          <cell r="N157"/>
+          <cell r="O157"/>
+          <cell r="P157"/>
+          <cell r="Q157"/>
+          <cell r="R157"/>
+          <cell r="S157"/>
+          <cell r="T157"/>
+          <cell r="U157"/>
+          <cell r="V157"/>
+          <cell r="W157"/>
+          <cell r="X157"/>
+        </row>
+        <row r="158">
+          <cell r="D158"/>
+          <cell r="E158"/>
+          <cell r="F158"/>
+          <cell r="G158"/>
+          <cell r="H158"/>
+          <cell r="I158"/>
+          <cell r="J158"/>
+          <cell r="K158"/>
+          <cell r="L158"/>
+          <cell r="M158"/>
+          <cell r="N158"/>
+          <cell r="O158"/>
+          <cell r="P158"/>
+          <cell r="Q158"/>
+          <cell r="R158"/>
+          <cell r="S158"/>
+          <cell r="T158"/>
+          <cell r="U158"/>
+          <cell r="V158"/>
+          <cell r="W158"/>
+          <cell r="X158"/>
+        </row>
+        <row r="159">
+          <cell r="D159"/>
+          <cell r="E159"/>
+          <cell r="F159"/>
+          <cell r="G159"/>
+          <cell r="H159"/>
+          <cell r="I159"/>
+          <cell r="J159"/>
+          <cell r="K159"/>
+          <cell r="L159"/>
+          <cell r="M159"/>
+          <cell r="N159"/>
+          <cell r="O159"/>
+          <cell r="P159"/>
+          <cell r="Q159"/>
+          <cell r="R159"/>
+          <cell r="S159"/>
+          <cell r="T159"/>
+          <cell r="U159"/>
+          <cell r="V159"/>
+          <cell r="W159"/>
+          <cell r="X159"/>
+        </row>
+        <row r="160">
+          <cell r="D160"/>
+          <cell r="E160"/>
+          <cell r="F160"/>
+          <cell r="G160"/>
+          <cell r="H160"/>
+          <cell r="I160"/>
+          <cell r="J160"/>
+          <cell r="K160"/>
+          <cell r="L160"/>
+          <cell r="M160"/>
+          <cell r="N160"/>
+          <cell r="O160"/>
+          <cell r="P160"/>
+          <cell r="Q160"/>
+          <cell r="R160"/>
+          <cell r="S160"/>
+          <cell r="T160"/>
+          <cell r="U160"/>
+          <cell r="V160"/>
+          <cell r="W160"/>
+          <cell r="X160"/>
+        </row>
+        <row r="161">
+          <cell r="D161"/>
+          <cell r="E161"/>
+          <cell r="F161"/>
+          <cell r="G161"/>
+          <cell r="H161"/>
+          <cell r="I161"/>
+          <cell r="J161"/>
+          <cell r="K161"/>
+          <cell r="L161"/>
+          <cell r="M161"/>
+          <cell r="N161"/>
+          <cell r="O161"/>
+          <cell r="P161"/>
+          <cell r="Q161"/>
+          <cell r="R161"/>
+          <cell r="S161"/>
+          <cell r="T161"/>
+          <cell r="U161"/>
+          <cell r="V161"/>
+          <cell r="W161"/>
+          <cell r="X161"/>
+        </row>
+        <row r="162">
+          <cell r="D162"/>
+          <cell r="E162"/>
+          <cell r="F162"/>
+          <cell r="G162"/>
+          <cell r="H162"/>
+          <cell r="I162"/>
+          <cell r="J162"/>
+          <cell r="K162"/>
+          <cell r="L162"/>
+          <cell r="M162"/>
+          <cell r="N162"/>
+          <cell r="O162"/>
+          <cell r="P162"/>
+          <cell r="Q162"/>
+          <cell r="R162"/>
+          <cell r="S162"/>
+          <cell r="T162"/>
+          <cell r="U162"/>
+          <cell r="V162"/>
+          <cell r="W162"/>
+          <cell r="X162"/>
+        </row>
+        <row r="163">
+          <cell r="D163"/>
+          <cell r="E163"/>
+          <cell r="F163"/>
+          <cell r="G163"/>
+          <cell r="H163"/>
+          <cell r="I163"/>
+          <cell r="J163"/>
+          <cell r="K163"/>
+          <cell r="L163"/>
+          <cell r="M163"/>
+          <cell r="N163"/>
+          <cell r="O163"/>
+          <cell r="P163"/>
+          <cell r="Q163"/>
+          <cell r="R163"/>
+          <cell r="S163"/>
+          <cell r="T163"/>
+          <cell r="U163"/>
+          <cell r="V163"/>
+          <cell r="W163"/>
+          <cell r="X163"/>
+        </row>
+        <row r="164">
+          <cell r="D164"/>
+          <cell r="E164"/>
+          <cell r="F164"/>
+          <cell r="G164"/>
+          <cell r="H164"/>
+          <cell r="I164"/>
+          <cell r="J164"/>
+          <cell r="K164"/>
+          <cell r="L164"/>
+          <cell r="M164"/>
+          <cell r="N164"/>
+          <cell r="O164"/>
+          <cell r="P164"/>
+          <cell r="Q164"/>
+          <cell r="R164"/>
+          <cell r="S164"/>
+          <cell r="T164"/>
+          <cell r="U164"/>
+          <cell r="V164"/>
+          <cell r="W164"/>
+          <cell r="X164"/>
+        </row>
+        <row r="165">
+          <cell r="D165"/>
+          <cell r="E165"/>
+          <cell r="F165"/>
+          <cell r="G165"/>
+          <cell r="H165"/>
+          <cell r="I165"/>
+          <cell r="J165"/>
+          <cell r="K165"/>
+          <cell r="L165"/>
+          <cell r="M165"/>
+          <cell r="N165"/>
+          <cell r="O165"/>
+          <cell r="P165"/>
+          <cell r="Q165"/>
+          <cell r="R165"/>
+          <cell r="S165"/>
+          <cell r="T165"/>
+          <cell r="U165"/>
+          <cell r="V165"/>
+          <cell r="W165"/>
+          <cell r="X165"/>
+        </row>
+        <row r="166">
+          <cell r="D166"/>
+          <cell r="E166"/>
+          <cell r="F166"/>
+          <cell r="G166"/>
+          <cell r="H166"/>
+          <cell r="I166"/>
+          <cell r="J166"/>
+          <cell r="K166"/>
+          <cell r="L166"/>
+          <cell r="M166"/>
+          <cell r="N166"/>
+          <cell r="O166"/>
+          <cell r="P166"/>
+          <cell r="Q166"/>
+          <cell r="R166"/>
+          <cell r="S166"/>
+          <cell r="T166"/>
+          <cell r="U166"/>
+          <cell r="V166"/>
+          <cell r="W166"/>
+          <cell r="X166"/>
+        </row>
+        <row r="167">
+          <cell r="D167"/>
+          <cell r="E167"/>
+          <cell r="F167"/>
+          <cell r="G167"/>
+          <cell r="H167"/>
+          <cell r="I167"/>
+          <cell r="J167"/>
+          <cell r="K167"/>
+          <cell r="L167"/>
+          <cell r="M167"/>
+          <cell r="N167"/>
+          <cell r="O167"/>
+          <cell r="P167"/>
+          <cell r="Q167"/>
+          <cell r="R167"/>
+          <cell r="S167"/>
+          <cell r="T167"/>
+          <cell r="U167"/>
+          <cell r="V167"/>
+          <cell r="W167"/>
+          <cell r="X167"/>
+        </row>
+        <row r="168">
+          <cell r="D168"/>
+          <cell r="E168"/>
+          <cell r="F168"/>
+          <cell r="G168"/>
+          <cell r="H168"/>
+          <cell r="I168"/>
+          <cell r="J168"/>
+          <cell r="K168"/>
+          <cell r="L168"/>
+          <cell r="M168"/>
+          <cell r="N168"/>
+          <cell r="O168"/>
+          <cell r="P168"/>
+          <cell r="Q168"/>
+          <cell r="R168"/>
+          <cell r="S168"/>
+          <cell r="T168"/>
+          <cell r="U168"/>
+          <cell r="V168"/>
+          <cell r="W168"/>
+          <cell r="X168"/>
+        </row>
+        <row r="169">
+          <cell r="D169"/>
+          <cell r="E169"/>
+          <cell r="F169"/>
+          <cell r="G169"/>
+          <cell r="H169"/>
+          <cell r="I169"/>
+          <cell r="J169"/>
+          <cell r="K169"/>
+          <cell r="L169"/>
+          <cell r="M169"/>
+          <cell r="N169"/>
+          <cell r="O169"/>
+          <cell r="P169"/>
+          <cell r="Q169"/>
+          <cell r="R169"/>
+          <cell r="S169"/>
+          <cell r="T169"/>
+          <cell r="U169"/>
+          <cell r="V169"/>
+          <cell r="W169"/>
+          <cell r="X169"/>
+        </row>
+        <row r="170">
+          <cell r="D170"/>
+          <cell r="E170"/>
+          <cell r="F170"/>
+          <cell r="G170"/>
+          <cell r="H170"/>
+          <cell r="I170"/>
+          <cell r="J170"/>
+          <cell r="K170"/>
+          <cell r="L170"/>
+          <cell r="M170"/>
+          <cell r="N170"/>
+          <cell r="O170"/>
+          <cell r="P170"/>
+          <cell r="Q170"/>
+          <cell r="R170"/>
+          <cell r="S170"/>
+          <cell r="T170"/>
+          <cell r="U170"/>
+          <cell r="V170"/>
+          <cell r="W170"/>
+          <cell r="X170"/>
+        </row>
+        <row r="171">
+          <cell r="D171"/>
+          <cell r="E171"/>
+          <cell r="F171"/>
+          <cell r="G171"/>
+          <cell r="H171"/>
+          <cell r="I171"/>
+          <cell r="J171"/>
+          <cell r="K171"/>
+          <cell r="L171"/>
+          <cell r="M171"/>
+          <cell r="N171"/>
+          <cell r="O171"/>
+          <cell r="P171"/>
+          <cell r="Q171"/>
+          <cell r="R171"/>
+          <cell r="S171"/>
+          <cell r="T171"/>
+          <cell r="U171"/>
+          <cell r="V171"/>
+          <cell r="W171"/>
+          <cell r="X171"/>
+        </row>
+        <row r="172">
+          <cell r="D172"/>
+          <cell r="E172"/>
+          <cell r="F172"/>
+          <cell r="G172"/>
+          <cell r="H172"/>
+          <cell r="I172"/>
+          <cell r="J172"/>
+          <cell r="K172"/>
+          <cell r="L172"/>
+          <cell r="M172"/>
+          <cell r="N172"/>
+          <cell r="O172"/>
+          <cell r="P172"/>
+          <cell r="Q172"/>
+          <cell r="R172"/>
+          <cell r="S172"/>
+          <cell r="T172"/>
+          <cell r="U172"/>
+          <cell r="V172"/>
+          <cell r="W172"/>
+          <cell r="X172"/>
+        </row>
+        <row r="173">
+          <cell r="D173"/>
+          <cell r="E173"/>
+          <cell r="F173"/>
+          <cell r="G173"/>
+          <cell r="H173"/>
+          <cell r="I173"/>
+          <cell r="J173"/>
+          <cell r="K173"/>
+          <cell r="L173"/>
+          <cell r="M173"/>
+          <cell r="N173"/>
+          <cell r="O173"/>
+          <cell r="P173"/>
+          <cell r="Q173"/>
+          <cell r="R173"/>
+          <cell r="S173"/>
+          <cell r="T173"/>
+          <cell r="U173"/>
+          <cell r="V173"/>
+          <cell r="W173"/>
+          <cell r="X173"/>
+        </row>
+        <row r="174">
+          <cell r="D174"/>
+          <cell r="E174"/>
+          <cell r="F174"/>
+          <cell r="G174"/>
+          <cell r="H174"/>
+          <cell r="I174"/>
+          <cell r="J174"/>
+          <cell r="K174"/>
+          <cell r="L174"/>
+          <cell r="M174"/>
+          <cell r="N174"/>
+          <cell r="O174"/>
+          <cell r="P174"/>
+          <cell r="Q174"/>
+          <cell r="R174"/>
+          <cell r="S174"/>
+          <cell r="T174"/>
+          <cell r="U174"/>
+          <cell r="V174"/>
+          <cell r="W174"/>
+          <cell r="X174"/>
+        </row>
+        <row r="175">
+          <cell r="D175"/>
+          <cell r="E175"/>
+          <cell r="F175"/>
+          <cell r="G175"/>
+          <cell r="H175"/>
+          <cell r="I175"/>
+          <cell r="J175"/>
+          <cell r="K175"/>
+          <cell r="L175"/>
+          <cell r="M175"/>
+          <cell r="N175"/>
+          <cell r="O175"/>
+          <cell r="P175"/>
+          <cell r="Q175"/>
+          <cell r="R175"/>
+          <cell r="S175"/>
+          <cell r="T175"/>
+          <cell r="U175"/>
+          <cell r="V175"/>
+          <cell r="W175"/>
+          <cell r="X175"/>
+        </row>
+        <row r="176">
+          <cell r="D176"/>
+          <cell r="E176"/>
+          <cell r="F176"/>
+          <cell r="G176"/>
+          <cell r="H176"/>
+          <cell r="I176"/>
+          <cell r="J176"/>
+          <cell r="K176"/>
+          <cell r="L176"/>
+          <cell r="M176"/>
+          <cell r="N176"/>
+          <cell r="O176"/>
+          <cell r="P176"/>
+          <cell r="Q176"/>
+          <cell r="R176"/>
+          <cell r="S176"/>
+          <cell r="T176"/>
+          <cell r="U176"/>
+          <cell r="V176"/>
+          <cell r="W176"/>
+          <cell r="X176"/>
+        </row>
+        <row r="177">
+          <cell r="D177"/>
+          <cell r="E177"/>
+          <cell r="F177"/>
+          <cell r="G177"/>
+          <cell r="H177"/>
+          <cell r="I177"/>
+          <cell r="J177"/>
+          <cell r="K177"/>
+          <cell r="L177"/>
+          <cell r="M177"/>
+          <cell r="N177"/>
+          <cell r="O177"/>
+          <cell r="P177"/>
+          <cell r="Q177"/>
+          <cell r="R177"/>
+          <cell r="S177"/>
+          <cell r="T177"/>
+          <cell r="U177"/>
+          <cell r="V177"/>
+          <cell r="W177"/>
+          <cell r="X177"/>
+        </row>
+        <row r="178">
+          <cell r="D178"/>
+          <cell r="E178"/>
+          <cell r="F178"/>
+          <cell r="G178"/>
+          <cell r="H178"/>
+          <cell r="I178"/>
+          <cell r="J178"/>
+          <cell r="K178"/>
+          <cell r="L178"/>
+          <cell r="M178"/>
+          <cell r="N178"/>
+          <cell r="O178"/>
+          <cell r="P178"/>
+          <cell r="Q178"/>
+          <cell r="R178"/>
+          <cell r="S178"/>
+          <cell r="T178"/>
+          <cell r="U178"/>
+          <cell r="V178"/>
+          <cell r="W178"/>
+          <cell r="X178"/>
+        </row>
+        <row r="179">
+          <cell r="D179"/>
+          <cell r="E179"/>
+          <cell r="F179"/>
+          <cell r="G179"/>
+          <cell r="H179"/>
+          <cell r="I179"/>
+          <cell r="J179"/>
+          <cell r="K179"/>
+          <cell r="L179"/>
+          <cell r="M179"/>
+          <cell r="N179"/>
+          <cell r="O179"/>
+          <cell r="P179"/>
+          <cell r="Q179"/>
+          <cell r="R179"/>
+          <cell r="S179"/>
+          <cell r="T179"/>
+          <cell r="U179"/>
+          <cell r="V179"/>
+          <cell r="W179"/>
+          <cell r="X179"/>
+        </row>
+        <row r="180">
+          <cell r="D180"/>
+          <cell r="E180"/>
+          <cell r="F180"/>
+          <cell r="G180"/>
+          <cell r="H180"/>
+          <cell r="I180"/>
+          <cell r="J180"/>
+          <cell r="K180"/>
+          <cell r="L180"/>
+          <cell r="M180"/>
+          <cell r="N180"/>
+          <cell r="O180"/>
+          <cell r="P180"/>
+          <cell r="Q180"/>
+          <cell r="R180"/>
+          <cell r="S180"/>
+          <cell r="T180"/>
+          <cell r="U180"/>
+          <cell r="V180"/>
+          <cell r="W180"/>
+          <cell r="X180"/>
+        </row>
+        <row r="181">
+          <cell r="D181"/>
+          <cell r="E181"/>
+          <cell r="F181"/>
+          <cell r="G181"/>
+          <cell r="H181"/>
+          <cell r="I181"/>
+          <cell r="J181"/>
+          <cell r="K181"/>
+          <cell r="L181"/>
+          <cell r="M181"/>
+          <cell r="N181"/>
+          <cell r="O181"/>
+          <cell r="P181"/>
+          <cell r="Q181"/>
+          <cell r="R181"/>
+          <cell r="S181"/>
+          <cell r="T181"/>
+          <cell r="U181"/>
+          <cell r="V181"/>
+          <cell r="W181"/>
+          <cell r="X181"/>
+        </row>
+        <row r="182">
+          <cell r="D182"/>
+          <cell r="E182"/>
+          <cell r="F182"/>
+          <cell r="G182"/>
+          <cell r="H182"/>
+          <cell r="I182"/>
+          <cell r="J182"/>
+          <cell r="K182"/>
+          <cell r="L182"/>
+          <cell r="M182"/>
+          <cell r="N182"/>
+          <cell r="O182"/>
+          <cell r="P182"/>
+          <cell r="Q182"/>
+          <cell r="R182"/>
+          <cell r="S182"/>
+          <cell r="T182"/>
+          <cell r="U182"/>
+          <cell r="V182"/>
+          <cell r="W182"/>
+          <cell r="X182"/>
+        </row>
+        <row r="183">
+          <cell r="D183"/>
+          <cell r="E183"/>
+          <cell r="F183"/>
+          <cell r="G183"/>
+          <cell r="H183"/>
+          <cell r="I183"/>
+          <cell r="J183"/>
+          <cell r="K183"/>
+          <cell r="L183"/>
+          <cell r="M183"/>
+          <cell r="N183"/>
+          <cell r="O183"/>
+          <cell r="P183"/>
+          <cell r="Q183"/>
+          <cell r="R183"/>
+          <cell r="S183"/>
+          <cell r="T183"/>
+          <cell r="U183"/>
+          <cell r="V183"/>
+          <cell r="W183"/>
+          <cell r="X183"/>
+        </row>
+        <row r="184">
+          <cell r="D184"/>
+          <cell r="E184"/>
+          <cell r="F184"/>
+          <cell r="G184"/>
+          <cell r="H184"/>
+          <cell r="I184"/>
+          <cell r="J184"/>
+          <cell r="K184"/>
+          <cell r="L184"/>
+          <cell r="M184"/>
+          <cell r="N184"/>
+          <cell r="O184"/>
+          <cell r="P184"/>
+          <cell r="Q184"/>
+          <cell r="R184"/>
+          <cell r="S184"/>
+          <cell r="T184"/>
+          <cell r="U184"/>
+          <cell r="V184"/>
+          <cell r="W184"/>
+          <cell r="X184"/>
+        </row>
+        <row r="185">
+          <cell r="D185"/>
+          <cell r="E185"/>
+          <cell r="F185"/>
+          <cell r="G185"/>
+          <cell r="H185"/>
+          <cell r="I185"/>
+          <cell r="J185"/>
+          <cell r="K185"/>
+          <cell r="L185"/>
+          <cell r="M185"/>
+          <cell r="N185"/>
+          <cell r="O185"/>
+          <cell r="P185"/>
+          <cell r="Q185"/>
+          <cell r="R185"/>
+          <cell r="S185"/>
+          <cell r="T185"/>
+          <cell r="U185"/>
+          <cell r="V185"/>
+          <cell r="W185"/>
+          <cell r="X185"/>
+        </row>
+        <row r="186">
+          <cell r="D186"/>
+          <cell r="E186"/>
+          <cell r="F186"/>
+          <cell r="G186"/>
+          <cell r="H186"/>
+          <cell r="I186"/>
+          <cell r="J186"/>
+          <cell r="K186"/>
+          <cell r="L186"/>
+          <cell r="M186"/>
+          <cell r="N186"/>
+          <cell r="O186"/>
+          <cell r="P186"/>
+          <cell r="Q186"/>
+          <cell r="R186"/>
+          <cell r="S186"/>
+          <cell r="T186"/>
+          <cell r="U186"/>
+          <cell r="V186"/>
+          <cell r="W186"/>
+          <cell r="X186"/>
+        </row>
+        <row r="187">
+          <cell r="D187"/>
+          <cell r="E187"/>
+          <cell r="F187"/>
+          <cell r="G187"/>
+          <cell r="H187"/>
+          <cell r="I187"/>
+          <cell r="J187"/>
+          <cell r="K187"/>
+          <cell r="L187"/>
+          <cell r="M187"/>
+          <cell r="N187"/>
+          <cell r="O187"/>
+          <cell r="P187"/>
+          <cell r="Q187"/>
+          <cell r="R187"/>
+          <cell r="S187"/>
+          <cell r="T187"/>
+          <cell r="U187"/>
+          <cell r="V187"/>
+          <cell r="W187"/>
+          <cell r="X187"/>
+        </row>
+        <row r="188">
+          <cell r="D188"/>
+          <cell r="E188"/>
+          <cell r="F188"/>
+          <cell r="G188"/>
+          <cell r="H188"/>
+          <cell r="I188"/>
+          <cell r="J188"/>
+          <cell r="K188"/>
+          <cell r="L188"/>
+          <cell r="M188"/>
+          <cell r="N188"/>
+          <cell r="O188"/>
+          <cell r="P188"/>
+          <cell r="Q188"/>
+          <cell r="R188"/>
+          <cell r="S188"/>
+          <cell r="T188"/>
+          <cell r="U188"/>
+          <cell r="V188"/>
+          <cell r="W188"/>
+          <cell r="X188"/>
+        </row>
+        <row r="189">
+          <cell r="D189"/>
+          <cell r="E189"/>
+          <cell r="F189"/>
+          <cell r="G189"/>
+          <cell r="H189"/>
+          <cell r="I189"/>
+          <cell r="J189"/>
+          <cell r="K189"/>
+          <cell r="L189"/>
+          <cell r="M189"/>
+          <cell r="N189"/>
+          <cell r="O189"/>
+          <cell r="P189"/>
+          <cell r="Q189"/>
+          <cell r="R189"/>
+          <cell r="S189"/>
+          <cell r="T189"/>
+          <cell r="U189"/>
+          <cell r="V189"/>
+          <cell r="W189"/>
+          <cell r="X189"/>
+        </row>
+        <row r="190">
+          <cell r="D190"/>
+          <cell r="E190"/>
+          <cell r="F190"/>
+          <cell r="G190"/>
+          <cell r="H190"/>
+          <cell r="I190"/>
+          <cell r="J190"/>
+          <cell r="K190"/>
+          <cell r="L190"/>
+          <cell r="M190"/>
+          <cell r="N190"/>
+          <cell r="O190"/>
+          <cell r="P190"/>
+          <cell r="Q190"/>
+          <cell r="R190"/>
+          <cell r="S190"/>
+          <cell r="T190"/>
+          <cell r="U190"/>
+          <cell r="V190"/>
+          <cell r="W190"/>
+          <cell r="X190"/>
+        </row>
+        <row r="191">
+          <cell r="D191"/>
+          <cell r="E191"/>
+          <cell r="F191"/>
+          <cell r="G191"/>
+          <cell r="H191"/>
+          <cell r="I191"/>
+          <cell r="J191"/>
+          <cell r="K191"/>
+          <cell r="L191"/>
+          <cell r="M191"/>
+          <cell r="N191"/>
+          <cell r="O191"/>
+          <cell r="P191"/>
+          <cell r="Q191"/>
+          <cell r="R191"/>
+          <cell r="S191"/>
+          <cell r="T191"/>
+          <cell r="U191"/>
+          <cell r="V191"/>
+          <cell r="W191"/>
+          <cell r="X191"/>
+        </row>
+        <row r="192">
+          <cell r="D192"/>
+          <cell r="E192"/>
+          <cell r="F192"/>
+          <cell r="G192"/>
+          <cell r="H192"/>
+          <cell r="I192"/>
+          <cell r="J192"/>
+          <cell r="K192"/>
+          <cell r="L192"/>
+          <cell r="M192"/>
+          <cell r="N192"/>
+          <cell r="O192"/>
+          <cell r="P192"/>
+          <cell r="Q192"/>
+          <cell r="R192"/>
+          <cell r="S192"/>
+          <cell r="T192"/>
+          <cell r="U192"/>
+          <cell r="V192"/>
+          <cell r="W192"/>
+          <cell r="X192"/>
+        </row>
+        <row r="193">
+          <cell r="D193"/>
+          <cell r="E193"/>
+          <cell r="F193"/>
+          <cell r="G193"/>
+          <cell r="H193"/>
+          <cell r="I193"/>
+          <cell r="J193"/>
+          <cell r="K193"/>
+          <cell r="L193"/>
+          <cell r="M193"/>
+          <cell r="N193"/>
+          <cell r="O193"/>
+          <cell r="P193"/>
+          <cell r="Q193"/>
+          <cell r="R193"/>
+          <cell r="S193"/>
+          <cell r="T193"/>
+          <cell r="U193"/>
+          <cell r="V193"/>
+          <cell r="W193"/>
+          <cell r="X193"/>
+        </row>
+        <row r="194">
+          <cell r="D194"/>
+          <cell r="E194"/>
+          <cell r="F194"/>
+          <cell r="G194"/>
+          <cell r="H194"/>
+          <cell r="I194"/>
+          <cell r="J194"/>
+          <cell r="K194"/>
+          <cell r="L194"/>
+          <cell r="M194"/>
+          <cell r="N194"/>
+          <cell r="O194"/>
+          <cell r="P194"/>
+          <cell r="Q194"/>
+          <cell r="R194"/>
+          <cell r="S194"/>
+          <cell r="T194"/>
+          <cell r="U194"/>
+          <cell r="V194"/>
+          <cell r="W194"/>
+          <cell r="X194"/>
+        </row>
+        <row r="195">
+          <cell r="D195"/>
+          <cell r="E195"/>
+          <cell r="F195"/>
+          <cell r="G195"/>
+          <cell r="H195"/>
+          <cell r="I195"/>
+          <cell r="J195"/>
+          <cell r="K195"/>
+          <cell r="L195"/>
+          <cell r="M195"/>
+          <cell r="N195"/>
+          <cell r="O195"/>
+          <cell r="P195"/>
+          <cell r="Q195"/>
+          <cell r="R195"/>
+          <cell r="S195"/>
+          <cell r="T195"/>
+          <cell r="U195"/>
+          <cell r="V195"/>
+          <cell r="W195"/>
+          <cell r="X195"/>
+        </row>
+        <row r="196">
+          <cell r="D196"/>
+          <cell r="E196"/>
+          <cell r="F196"/>
+          <cell r="G196"/>
+          <cell r="H196"/>
+          <cell r="I196"/>
+          <cell r="J196"/>
+          <cell r="K196"/>
+          <cell r="L196"/>
+          <cell r="M196"/>
+          <cell r="N196"/>
+          <cell r="O196"/>
+          <cell r="P196"/>
+          <cell r="Q196"/>
+          <cell r="R196"/>
+          <cell r="S196"/>
+          <cell r="T196"/>
+          <cell r="U196"/>
+          <cell r="V196"/>
+          <cell r="W196"/>
+          <cell r="X196"/>
+        </row>
+        <row r="197">
+          <cell r="D197"/>
+          <cell r="E197"/>
+          <cell r="F197"/>
+          <cell r="G197"/>
+          <cell r="H197"/>
+          <cell r="I197"/>
+          <cell r="J197"/>
+          <cell r="K197"/>
+          <cell r="L197"/>
+          <cell r="M197"/>
+          <cell r="N197"/>
+          <cell r="O197"/>
+          <cell r="P197"/>
+          <cell r="Q197"/>
+          <cell r="R197"/>
+          <cell r="S197"/>
+          <cell r="T197"/>
+          <cell r="U197"/>
+          <cell r="V197"/>
+          <cell r="W197"/>
+          <cell r="X197"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -18777,127 +24239,223 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Pennsylvania</v>
+        <v>VCU</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Harvard</v>
+        <v>St. Joseph's</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>B2</f>
-        <v>Pennsylvania</v>
+        <v>VCU</v>
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>2.5615469942101572</v>
+        <v>12.835404558957849</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.40688974186433241</v>
+        <v>0.70074839245243137</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>6.4179900266898557E-2</v>
+        <v>7.0887631768342563E-2</v>
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.3511306969828698E-2</v>
+        <v>5.732251805019465E-2</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="K2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
-        <v>0</v>
+        <v>1.0633144765251386</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Kennesaw State</v>
+        <v>Arkansas</v>
       </c>
       <c r="C3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Louisiana Tech</v>
+        <v>Ole Miss</v>
       </c>
       <c r="D3" s="6" t="str">
         <f t="shared" ref="D3" si="0">B3</f>
-        <v>Kennesaw State</v>
+        <v>Arkansas</v>
       </c>
       <c r="E3" s="5">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>6.2621855083836966</v>
+        <v>14.94229486295097</v>
       </c>
       <c r="F3" s="5">
         <f>-VLOOKUP(A3,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.47249844996534668</v>
+        <v>0.70816933596251053</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>4.8136336457088799E-2</v>
+        <v>5.5077610628663218E-2</v>
       </c>
       <c r="I3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.4395645714254972E-2</v>
+        <v>4.8339551493558675E-2</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>393</v>
       </c>
       <c r="K3" s="9">
         <f t="shared" ref="K3" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
+        <v>0.82616415942994825</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Duke</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Virginia</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f t="shared" ref="D4:D6" si="2">B4</f>
+        <v>Duke</v>
+      </c>
+      <c r="E4" s="5">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>15.61990006839136</v>
+      </c>
+      <c r="F4" s="5">
+        <f>-VLOOKUP(A4,[2]Games!$A$2:$X$300,24,FALSE)</f>
+        <v>8.5</v>
+      </c>
+      <c r="G4" s="7">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.75149652484483553</v>
+      </c>
+      <c r="H4" s="7">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>7.0744352533153906E-2</v>
+      </c>
+      <c r="I4" s="7">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>5.7241109393837447E-2</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" ref="K4:K6" si="3">IF(J4="Yes",(H4*1500)/100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>23</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Pennsylvania</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Harvard</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Pennsylvania</v>
+      </c>
+      <c r="E5" s="5">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>2.236546994210157</v>
+      </c>
+      <c r="F5" s="5">
+        <f>-VLOOKUP(A5,[2]Games!$A$2:$X$300,24,FALSE)</f>
+        <v>-3.5</v>
+      </c>
+      <c r="G5" s="7">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.40688974186433241</v>
+      </c>
+      <c r="H5" s="7">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>6.7623692875932173E-2</v>
+      </c>
+      <c r="I5" s="7">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>5.54680073158706E-2</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>37</v>
+      </c>
+      <c r="B6" s="6" t="str">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Kennesaw State</v>
+      </c>
+      <c r="C6" s="6" t="str">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Louisiana Tech</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Kennesaw State</v>
+      </c>
+      <c r="E6" s="5">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>6.2621855083836948</v>
+      </c>
+      <c r="F6" s="5">
+        <f>-VLOOKUP(A6,[2]Games!$A$2:$X$300,24,FALSE)</f>
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="7">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.47249844996534662</v>
+      </c>
+      <c r="H6" s="7">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>4.8136336457088799E-2</v>
+      </c>
+      <c r="I6" s="7">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>4.4395645714254972E-2</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="3"/>
         <v>0.72204504685633197</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E7" s="10"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8CC556-3375-F144-BE0D-9972CD86E05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37BB91C-3606-1347-8863-5D322282D70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="27580" windowHeight="20000" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="27580" windowHeight="20000" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="443">
   <si>
     <t>Team</t>
   </si>
@@ -1226,9 +1226,6 @@
     <t>Bet</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -1329,9 +1326,6 @@
   </si>
   <si>
     <t>03/10/2026</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>03/11/2026</t>
@@ -24201,7 +24195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2A118F-D7F3-5348-BECB-A41992F5CAD2}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -24225,13 +24219,13 @@
         <v>368</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>369</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>370</v>
@@ -24250,224 +24244,79 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>4</v>
-      </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="6" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>VCU</v>
-      </c>
-      <c r="C2" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C2" s="6" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>St. Joseph's</v>
-      </c>
-      <c r="D2" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="D2" s="6" t="e">
         <f>B2</f>
-        <v>VCU</v>
-      </c>
-      <c r="E2" s="5">
+        <v>#N/A</v>
+      </c>
+      <c r="E2" s="5" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>12.835404558957849</v>
-      </c>
-      <c r="F2" s="5">
+        <v>#N/A</v>
+      </c>
+      <c r="F2" s="5" t="e">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="G2" s="7">
+        <v>#N/A</v>
+      </c>
+      <c r="G2" s="7" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.70074839245243137</v>
-      </c>
-      <c r="H2" s="7">
+        <v>#N/A</v>
+      </c>
+      <c r="H2" s="7" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>7.0887631768342563E-2</v>
-      </c>
-      <c r="I2" s="7">
+        <v>#N/A</v>
+      </c>
+      <c r="I2" s="7" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.732251805019465E-2</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>393</v>
-      </c>
+        <v>#N/A</v>
+      </c>
+      <c r="J2" s="8"/>
       <c r="K2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
-        <v>1.0633144765251386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Arkansas</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Ole Miss</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <f t="shared" ref="D3" si="0">B3</f>
-        <v>Arkansas</v>
-      </c>
-      <c r="E3" s="5">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.94229486295097</v>
-      </c>
-      <c r="F3" s="5">
-        <f>-VLOOKUP(A3,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="G3" s="7">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.70816933596251053</v>
-      </c>
-      <c r="H3" s="7">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>5.5077610628663218E-2</v>
-      </c>
-      <c r="I3" s="7">
-        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.8339551493558675E-2</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="K3" s="9">
-        <f t="shared" ref="K3" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
-        <v>0.82616415942994825</v>
-      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6" t="str">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Duke</v>
-      </c>
-      <c r="C4" s="6" t="str">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Virginia</v>
-      </c>
-      <c r="D4" s="6" t="str">
-        <f t="shared" ref="D4:D6" si="2">B4</f>
-        <v>Duke</v>
-      </c>
-      <c r="E4" s="5">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>15.61990006839136</v>
-      </c>
-      <c r="F4" s="5">
-        <f>-VLOOKUP(A4,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>8.5</v>
-      </c>
-      <c r="G4" s="7">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.75149652484483553</v>
-      </c>
-      <c r="H4" s="7">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>7.0744352533153906E-2</v>
-      </c>
-      <c r="I4" s="7">
-        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.7241109393837447E-2</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="K4" s="9">
-        <f t="shared" ref="K4:K6" si="3">IF(J4="Yes",(H4*1500)/100,0)</f>
-        <v>0</v>
-      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>23</v>
-      </c>
-      <c r="B5" s="6" t="str">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Pennsylvania</v>
-      </c>
-      <c r="C5" s="6" t="str">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Harvard</v>
-      </c>
-      <c r="D5" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Pennsylvania</v>
-      </c>
-      <c r="E5" s="5">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>2.236546994210157</v>
-      </c>
-      <c r="F5" s="5">
-        <f>-VLOOKUP(A5,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>-3.5</v>
-      </c>
-      <c r="G5" s="7">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.40688974186433241</v>
-      </c>
-      <c r="H5" s="7">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>6.7623692875932173E-2</v>
-      </c>
-      <c r="I5" s="7">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.54680073158706E-2</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="K5" s="9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>37</v>
-      </c>
-      <c r="B6" s="6" t="str">
-        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Kennesaw State</v>
-      </c>
-      <c r="C6" s="6" t="str">
-        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Louisiana Tech</v>
-      </c>
-      <c r="D6" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Kennesaw State</v>
-      </c>
-      <c r="E6" s="5">
-        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>6.2621855083836948</v>
-      </c>
-      <c r="F6" s="5">
-        <f>-VLOOKUP(A6,[2]Games!$A$2:$X$300,24,FALSE)</f>
-        <v>1.5</v>
-      </c>
-      <c r="G6" s="7">
-        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.47249844996534662</v>
-      </c>
-      <c r="H6" s="7">
-        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>4.8136336457088799E-2</v>
-      </c>
-      <c r="I6" s="7">
-        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.4395645714254972E-2</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" si="3"/>
-        <v>0.72204504685633197</v>
-      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E7" s="10"/>
@@ -24585,42 +24434,6 @@
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="10"/>
-    </row>
-    <row r="20" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="10"/>
-    </row>
-    <row r="21" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="10"/>
-    </row>
-    <row r="22" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="10"/>
-    </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24658,10 +24471,10 @@
         <v>391</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="G1" s="1"/>
     </row>
@@ -24693,57 +24506,57 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>391</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L5" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="N5" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -24752,7 +24565,7 @@
         <v>389</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E6" s="1">
         <v>0.94499999999999995</v>
@@ -24774,7 +24587,7 @@
         <v>-1.9985536081552357E-2</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K6" s="1">
         <v>-112</v>
@@ -24799,7 +24612,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B7" s="1">
         <f>B6+1</f>
@@ -24809,7 +24622,7 @@
         <v>389</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E7" s="1">
         <v>0.68979999999999997</v>
@@ -24831,7 +24644,7 @@
         <v>-7.3041333591230655E-3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K7" s="1">
         <v>-103</v>
@@ -24856,7 +24669,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" ref="B8:B16" si="4">B7+1</f>
@@ -24866,7 +24679,7 @@
         <v>388</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E8" s="1">
         <v>0.74019999999999997</v>
@@ -24888,7 +24701,7 @@
         <v>3.1073790677935476E-2</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K8" s="1">
         <v>-110</v>
@@ -24913,7 +24726,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="4"/>
@@ -24923,7 +24736,7 @@
         <v>388</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E9" s="1">
         <v>0.67900000000000005</v>
@@ -24945,7 +24758,7 @@
         <v>2.5431238755099773E-2</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K9" s="1">
         <v>-110</v>
@@ -24970,7 +24783,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="4"/>
@@ -24980,7 +24793,7 @@
         <v>389</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E10" s="1">
         <v>1.2898000000000001</v>
@@ -25002,7 +24815,7 @@
         <v>1.2346518407494022E-2</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K10" s="1">
         <v>-112</v>
@@ -25027,7 +24840,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="4"/>
@@ -25037,7 +24850,7 @@
         <v>389</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E11" s="1">
         <v>0.68820000000000003</v>
@@ -25059,7 +24872,7 @@
         <v>2.5460169228087515E-2</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K11" s="1">
         <v>-109</v>
@@ -25084,7 +24897,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="4"/>
@@ -25094,7 +24907,7 @@
         <v>389</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E12" s="1">
         <v>0.69510000000000005</v>
@@ -25116,7 +24929,7 @@
         <v>4.1788135989584758E-2</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K12" s="1">
         <v>-109</v>
@@ -25141,7 +24954,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="4"/>
@@ -25151,7 +24964,7 @@
         <v>389</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E13" s="1">
         <v>1.0744</v>
@@ -25173,7 +24986,7 @@
         <v>3.4345868990886666E-2</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K13" s="1">
         <v>-107</v>
@@ -25198,7 +25011,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="4"/>
@@ -25208,7 +25021,7 @@
         <v>388</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E14" s="1">
         <v>1.0632999999999999</v>
@@ -25230,7 +25043,7 @@
         <v>3.3490856499044576E-2</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K14" s="1">
         <v>-110</v>
@@ -25255,7 +25068,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="4"/>
@@ -25265,7 +25078,7 @@
         <v>389</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E15" s="1">
         <v>0.82620000000000005</v>
@@ -25287,7 +25100,7 @@
         <v>2.681961318224562E-2</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K15" s="1">
         <v>-109</v>
@@ -25312,7 +25125,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="4"/>
@@ -25322,7 +25135,7 @@
         <v>388</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E16" s="1">
         <v>0.72199999999999998</v>
@@ -25344,7 +25157,7 @@
         <v>2.4502342779500797E-2</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K16" s="1">
         <v>-110</v>
@@ -25631,45 +25444,45 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -25684,10 +25497,10 @@
         <v>475</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K2" s="1">
         <f>IF(J2="W",(D2/100)*E2,IF(J2="",0,-E2))</f>
@@ -25696,10 +25509,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
@@ -25714,10 +25527,10 @@
         <v>6000</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" ref="K3:K5" si="0">IF(J3="W",(D3/100)*E3,IF(J3="",0,-E3))</f>
@@ -25726,10 +25539,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -25744,10 +25557,10 @@
         <v>1800</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="0"/>
@@ -25756,10 +25569,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>48</v>
@@ -25774,10 +25587,10 @@
         <v>50000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="0"/>
@@ -25808,7 +25621,7 @@
         <v>366</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -33583,7 +33396,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B61">
         <v>7.9899999999999999E-2</v>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37BB91C-3606-1347-8863-5D322282D70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFF2058-DF5C-9F4E-8888-BD775227A124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="27580" windowHeight="20000" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="16140" windowHeight="20000" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="445">
   <si>
     <t>Team</t>
   </si>
@@ -1374,6 +1374,12 @@
   </si>
   <si>
     <t>KENN/LT</t>
+  </si>
+  <si>
+    <t>Show</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -24195,7 +24201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2A118F-D7F3-5348-BECB-A41992F5CAD2}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -24208,7 +24214,7 @@
     <col min="8" max="11" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>373</v>
       </c>
@@ -24242,8 +24248,11 @@
       <c r="K1" s="1" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="e">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
         <v>#N/A</v>
@@ -24281,8 +24290,11 @@
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
@@ -24291,7 +24303,7 @@
       <c r="J3" s="11"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="11"/>
@@ -24300,7 +24312,7 @@
       <c r="J4" s="11"/>
       <c r="K4" s="10"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
@@ -24309,7 +24321,7 @@
       <c r="J5" s="11"/>
       <c r="K5" s="10"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
@@ -24318,7 +24330,7 @@
       <c r="J6" s="11"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -24327,7 +24339,7 @@
       <c r="J7" s="11"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
@@ -24336,7 +24348,7 @@
       <c r="J8" s="11"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
@@ -24345,7 +24357,7 @@
       <c r="J9" s="11"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
@@ -24354,7 +24366,7 @@
       <c r="J10" s="11"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
@@ -24363,7 +24375,7 @@
       <c r="J11" s="11"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
@@ -24372,7 +24384,7 @@
       <c r="J12" s="11"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
@@ -24381,7 +24393,7 @@
       <c r="J13" s="11"/>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="11"/>
@@ -24390,7 +24402,7 @@
       <c r="J14" s="11"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="11"/>
@@ -24399,7 +24411,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="11"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27643B03-3EE5-D14A-8A13-C594A85FCB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC30DD1-85B4-6F41-9AA5-2480F82ED5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20000" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="800" yWindow="780" windowWidth="17200" windowHeight="19960" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="449">
   <si>
     <t>Team</t>
   </si>
@@ -1380,6 +1380,18 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>East Region Winner</t>
+  </si>
+  <si>
+    <t>Midwest Region Winner</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>03/15/2025</t>
   </si>
 </sst>
 </file>
@@ -27867,10 +27879,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5527B6-58FD-524E-85CF-A53FB2DF16C9}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="20.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.83203125" style="1"/>
     <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -27966,7 +27981,7 @@
         <v>417</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K5" si="0">IF(J3="W",(D3/100)*E3,IF(J3="",0,-E3))</f>
+        <f t="shared" ref="K3:K7" si="0">IF(J3="W",(D3/100)*E3,IF(J3="",0,-E3))</f>
         <v>0</v>
       </c>
     </row>
@@ -28020,12 +28035,75 @@
         <v>50000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>417</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>389</v>
+      </c>
       <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>816</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="F6" s="1">
+        <v>816</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1725</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1725</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="K7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -33906,6 +33984,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2508B5-8FE0-E24B-BF36-9D8165A8259C}">
   <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC30DD1-85B4-6F41-9AA5-2480F82ED5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADC4D43-A972-FE4C-9910-71FD28BA4E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="780" windowWidth="17200" windowHeight="19960" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="452">
   <si>
     <t>Team</t>
   </si>
@@ -1392,6 +1392,15 @@
   </si>
   <si>
     <t>03/15/2025</t>
+  </si>
+  <si>
+    <t>Reach Sweet 16 - Yes</t>
+  </si>
+  <si>
+    <t>Reach Sweet 16 - No</t>
+  </si>
+  <si>
+    <t>03/16/2025</t>
   </si>
 </sst>
 </file>
@@ -1552,223 +1561,223 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="B2">
+            <v>13</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>Nebraska</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>Troy</v>
+          </cell>
+          <cell r="E2">
+            <v>21.024999999999999</v>
+          </cell>
+          <cell r="F2" t="b">
             <v>1</v>
           </cell>
-          <cell r="C2" t="str">
-            <v>UMBC</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Howard</v>
-          </cell>
-          <cell r="E2">
-            <v>4.5398147803963766</v>
-          </cell>
-          <cell r="F2" t="b">
-            <v>0</v>
-          </cell>
           <cell r="G2">
-            <v>0.56306251790939255</v>
+            <v>0.64124134938575506</v>
           </cell>
           <cell r="H2">
-            <v>0</v>
+            <v>6.8642733484034296E-2</v>
           </cell>
           <cell r="I2">
-            <v>7.4937534190658517E-2</v>
+            <v>0.22418803064553239</v>
           </cell>
           <cell r="J2">
-            <v>0.29505706343244742</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K2">
-            <v>0</v>
+            <v>1.3399061576083495</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>2</v>
+            <v>20</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Texas</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D3" t="str">
-            <v>NC State</v>
+            <v>Hofstra</v>
           </cell>
           <cell r="E3">
-            <v>3.351492666553944</v>
+            <v>21.09470868445722</v>
           </cell>
           <cell r="F3" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G3">
-            <v>0.55842147595203739</v>
+            <v>0.63457190270907826</v>
           </cell>
           <cell r="H3">
-            <v>0</v>
+            <v>6.3040398275625784E-2</v>
           </cell>
           <cell r="I3">
-            <v>6.6077363181162307E-2</v>
+            <v>0.21145545062642221</v>
           </cell>
           <cell r="J3">
-            <v>0.24670500307592891</v>
+            <v>0.81648449863375538</v>
           </cell>
           <cell r="K3">
-            <v>0</v>
+            <v>1.2305485743402154</v>
           </cell>
         </row>
         <row r="4">
           <cell r="B4">
-            <v>3</v>
+            <v>17</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Lehigh Mountain</v>
+            <v>Hawaii</v>
           </cell>
           <cell r="E4">
-            <v>-1.0818703398805221</v>
+            <v>22.324999999999999</v>
           </cell>
           <cell r="F4" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G4">
-            <v>0.53531325069231817</v>
+            <v>0.62859142388829925</v>
           </cell>
           <cell r="H4">
-            <v>0</v>
+            <v>5.801679606617148E-2</v>
           </cell>
           <cell r="I4">
-            <v>2.1961660412607439E-2</v>
+            <v>0.20003817287766221</v>
           </cell>
           <cell r="J4">
-            <v>4.9856358057364769E-2</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K4">
-            <v>0</v>
+            <v>1.1324878592116674</v>
           </cell>
         </row>
         <row r="5">
           <cell r="B5">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Miami (OH)</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D5" t="str">
-            <v>SMU</v>
+            <v>North Dakota State</v>
           </cell>
           <cell r="E5">
-            <v>-6.5280711453208946</v>
+            <v>22.65</v>
           </cell>
           <cell r="F5" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G5">
-            <v>0.54904367295244916</v>
+            <v>0.62540649394971881</v>
           </cell>
           <cell r="H5">
-            <v>0</v>
+            <v>5.5341454917763828E-2</v>
           </cell>
           <cell r="I5">
-            <v>4.8174284727402983E-2</v>
+            <v>0.1939578520858268</v>
           </cell>
           <cell r="J5">
-            <v>9.203326713974791E-2</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K5">
-            <v>0</v>
+            <v>1.0802651999947499</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6">
-            <v>5</v>
+            <v>12</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Louisville</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D6" t="str">
-            <v>South Florida</v>
+            <v>McNeese</v>
           </cell>
           <cell r="E6">
-            <v>8.742776454945794</v>
+            <v>17.448430884808509</v>
           </cell>
           <cell r="F6" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G6">
-            <v>0.58030489249754802</v>
+            <v>0.62141047113878456</v>
           </cell>
           <cell r="H6">
-            <v>0</v>
+            <v>5.1984795756579022E-2</v>
           </cell>
           <cell r="I6">
-            <v>0.1078547947680463</v>
+            <v>0.1863290812649524</v>
           </cell>
           <cell r="J6">
-            <v>0.46272230131594538</v>
+            <v>0.74660937378926895</v>
           </cell>
           <cell r="K6">
-            <v>0</v>
+            <v>1.0147432131684224</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7">
-            <v>6</v>
+            <v>33</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Michigan State</v>
+            <v>Howard</v>
           </cell>
           <cell r="D7" t="str">
-            <v>North Dakota State</v>
+            <v>UMBC</v>
           </cell>
           <cell r="E7">
-            <v>22.65</v>
+            <v>2.711720411891148</v>
           </cell>
           <cell r="F7" t="b">
             <v>1</v>
           </cell>
           <cell r="G7">
-            <v>0.62540649394971881</v>
+            <v>0.61580539290283809</v>
           </cell>
           <cell r="H7">
-            <v>5.5341454917763828E-2</v>
+            <v>4.7276530038383939E-2</v>
           </cell>
           <cell r="I7">
-            <v>0.1939578520858268</v>
+            <v>0.1756284773599637</v>
           </cell>
           <cell r="J7">
-            <v>0.82374745212732714</v>
+            <v>0.3634228852259655</v>
           </cell>
           <cell r="K7">
-            <v>1.0802651999947499</v>
+            <v>0.92283786634925447</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8">
-            <v>7</v>
+            <v>61</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Georgia</v>
+            <v>Northern Iowa</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Saint Louis</v>
+            <v>St. John's</v>
           </cell>
           <cell r="E8">
-            <v>4.2861663978745757</v>
+            <v>-7.0324352932968432</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.55680965526509907</v>
+            <v>0.60996307409599937</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>6.3000250960643767E-2</v>
+            <v>0.164474959637817</v>
           </cell>
           <cell r="J8">
-            <v>0.27233205754770629</v>
+            <v>4.0627657807308433E-2</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1776,31 +1785,31 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>8</v>
+            <v>30</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Duke</v>
+            <v>Kansas</v>
           </cell>
           <cell r="D9" t="str">
-            <v>Siena</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="E9">
-            <v>31.1</v>
+            <v>18.573029871345032</v>
           </cell>
           <cell r="F9" t="b">
             <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.54020950401036416</v>
+            <v>0.59561500793361322</v>
           </cell>
           <cell r="H9">
             <v>0</v>
           </cell>
           <cell r="I9">
-            <v>3.1309053110695262E-2</v>
+            <v>0.13708319696417071</v>
           </cell>
           <cell r="J9">
-            <v>0.82374745212732714</v>
+            <v>0.72543986092307822</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1808,31 +1817,31 @@
         </row>
         <row r="10">
           <cell r="B10">
-            <v>9</v>
+            <v>23</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Ohio State</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D10" t="str">
-            <v>TCU</v>
+            <v>Furman</v>
           </cell>
           <cell r="E10">
-            <v>4.5795233045545594</v>
+            <v>25.492859365224369</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.56404001660924963</v>
+            <v>0.59510350502049691</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>7.6803668072203846E-2</v>
+            <v>0.13610669140276691</v>
           </cell>
           <cell r="J10">
-            <v>0.29860436775963528</v>
+            <v>0.82144469910078188</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1840,31 +1849,31 @@
         </row>
         <row r="11">
           <cell r="B11">
-            <v>10</v>
+            <v>52</v>
           </cell>
           <cell r="C11" t="str">
-            <v>North Carolina</v>
+            <v>Hofstra</v>
           </cell>
           <cell r="D11" t="str">
-            <v>VCU</v>
+            <v>Alabama</v>
           </cell>
           <cell r="E11">
-            <v>5.5088810410605049</v>
+            <v>-18.409254461666698</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.58679379170739043</v>
+            <v>0.59279510849473038</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>0.1202426932595636</v>
+            <v>0.13169975258084901</v>
           </cell>
           <cell r="J11">
-            <v>0.38065457771620442</v>
+            <v>0.71813726064377859</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1872,31 +1881,31 @@
         </row>
         <row r="12">
           <cell r="B12">
-            <v>11</v>
+            <v>57</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Illinois</v>
+            <v>Missouri</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Pennsylvania</v>
+            <v>Miami</v>
           </cell>
           <cell r="E12">
-            <v>27.2</v>
+            <v>1.742263875348123</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.58001156955860289</v>
+            <v>0.59246539086017058</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>0.1072948146118783</v>
+            <v>0.1310702916421439</v>
           </cell>
           <cell r="J12">
-            <v>0.82374745212732714</v>
+            <v>0.2773673651949719</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1904,95 +1913,95 @@
         </row>
         <row r="13">
           <cell r="B13">
-            <v>12</v>
+            <v>18</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Vanderbilt</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="D13" t="str">
-            <v>McNeese</v>
+            <v>Kennesaw State</v>
           </cell>
           <cell r="E13">
-            <v>17.448430884808509</v>
+            <v>23.450459942010621</v>
           </cell>
           <cell r="F13" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.62141047113878456</v>
+            <v>0.58799578958333887</v>
           </cell>
           <cell r="H13">
-            <v>5.1984795756579022E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I13">
-            <v>0.1863290812649524</v>
+            <v>0.12253741647728331</v>
           </cell>
           <cell r="J13">
-            <v>0.74660937378926895</v>
+            <v>0.78843548732025015</v>
           </cell>
           <cell r="K13">
-            <v>1.0147432131684224</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>13</v>
+            <v>49</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Nebraska</v>
+            <v>Hawaii</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Troy</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="E14">
-            <v>21.024999999999999</v>
+            <v>-19.689265506637959</v>
           </cell>
           <cell r="F14" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.64124134938575506</v>
+            <v>0.58728757996436998</v>
           </cell>
           <cell r="H14">
-            <v>6.8642733484034296E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I14">
-            <v>0.22418803064553239</v>
+            <v>0.1211853799319791</v>
           </cell>
           <cell r="J14">
-            <v>0.82374745212732714</v>
+            <v>0.73158718099349851</v>
           </cell>
           <cell r="K14">
-            <v>1.3399061576083495</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15">
-            <v>14</v>
+            <v>10</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Saint Mary's</v>
+            <v>North Carolina</v>
           </cell>
           <cell r="D15" t="str">
-            <v>Texas A&amp;M</v>
+            <v>VCU</v>
           </cell>
           <cell r="E15">
-            <v>4.9704473885420759</v>
+            <v>5.5088810410605049</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.57364154101220122</v>
+            <v>0.58679379170739043</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>9.5133851023293303E-2</v>
+            <v>0.1202426932595636</v>
           </cell>
           <cell r="J15">
-            <v>0.33336045600883751</v>
+            <v>0.38065457771620442</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -2000,31 +2009,31 @@
         </row>
         <row r="16">
           <cell r="B16">
-            <v>15</v>
+            <v>48</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Houston</v>
+            <v>High Point</v>
           </cell>
           <cell r="D16" t="str">
-            <v>Idaho</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="E16">
-            <v>27.2</v>
+            <v>-6.7399272078176624</v>
           </cell>
           <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.58001156955860289</v>
+            <v>0.58072734404629345</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>0.1072948146118783</v>
+            <v>0.10866129317928749</v>
           </cell>
           <cell r="J16">
-            <v>0.82374745212732714</v>
+            <v>2.202740613184884E-2</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -2032,31 +2041,31 @@
         </row>
         <row r="17">
           <cell r="B17">
-            <v>16</v>
+            <v>5</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Wisconsin</v>
+            <v>Louisville</v>
           </cell>
           <cell r="D17" t="str">
-            <v>High Point</v>
+            <v>South Florida</v>
           </cell>
           <cell r="E17">
-            <v>11.446368832524669</v>
+            <v>8.742776454945794</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.53601454769519918</v>
+            <v>0.58030489249754802</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>2.3300500145380321E-2</v>
+            <v>0.1078547947680463</v>
           </cell>
           <cell r="J17">
-            <v>0.44405986090341543</v>
+            <v>0.46272230131594538</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2064,63 +2073,63 @@
         </row>
         <row r="18">
           <cell r="B18">
-            <v>17</v>
+            <v>64</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Arkansas</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Hawaii</v>
+            <v>Villanova</v>
           </cell>
           <cell r="E18">
-            <v>22.324999999999999</v>
+            <v>5.2368487163496038</v>
           </cell>
           <cell r="F18" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0.62859142388829925</v>
+            <v>0.58016009009738734</v>
           </cell>
           <cell r="H18">
-            <v>5.801679606617148E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I18">
-            <v>0.20003817287766221</v>
+            <v>0.10757835382228501</v>
           </cell>
           <cell r="J18">
-            <v>0.82374745212732714</v>
+            <v>0.3568520724234755</v>
           </cell>
           <cell r="K18">
-            <v>1.1324878592116674</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19">
-            <v>18</v>
+            <v>11</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Gonzaga</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D19" t="str">
-            <v>Kennesaw State</v>
+            <v>Pennsylvania</v>
           </cell>
           <cell r="E19">
-            <v>23.450459942010621</v>
+            <v>27.2</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.58799578958333887</v>
+            <v>0.58001156955860289</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>0.12253741647728331</v>
+            <v>0.1072948146118783</v>
           </cell>
           <cell r="J19">
-            <v>0.78843548732025015</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2128,31 +2137,31 @@
         </row>
         <row r="20">
           <cell r="B20">
-            <v>19</v>
+            <v>15</v>
           </cell>
           <cell r="C20" t="str">
-            <v>Texas Tech</v>
+            <v>Houston</v>
           </cell>
           <cell r="D20" t="str">
-            <v>Akron</v>
+            <v>Idaho</v>
           </cell>
           <cell r="E20">
-            <v>10.43081131270095</v>
+            <v>27.2</v>
           </cell>
           <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0.56037723382257887</v>
+            <v>0.58001156955860289</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>6.9811082752196052E-2</v>
+            <v>0.1072948146118783</v>
           </cell>
           <cell r="J20">
-            <v>0.46800018669531451</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2160,63 +2169,63 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>20</v>
+            <v>53</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Alabama</v>
+            <v>Iowa</v>
           </cell>
           <cell r="D21" t="str">
-            <v>Hofstra</v>
+            <v>Clemson</v>
           </cell>
           <cell r="E21">
-            <v>21.09470868445722</v>
+            <v>5.0603260407104784</v>
           </cell>
           <cell r="F21" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0.63457190270907826</v>
+            <v>0.57584311604296001</v>
           </cell>
           <cell r="H21">
-            <v>6.3040398275625784E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I21">
-            <v>0.21145545062642221</v>
+            <v>9.9336857900196418E-2</v>
           </cell>
           <cell r="J21">
-            <v>0.81648449863375538</v>
+            <v>0.3413049040666058</v>
           </cell>
           <cell r="K21">
-            <v>1.2305485743402154</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22">
-            <v>21</v>
+            <v>14</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Clemson</v>
+            <v>Saint Mary's</v>
           </cell>
           <cell r="D22" t="str">
-            <v>Iowa</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="E22">
-            <v>3.3395963530867379E-2</v>
+            <v>4.9704473885420759</v>
           </cell>
           <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0.55056432776779596</v>
+            <v>0.57364154101220122</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>5.1077353011246829E-2</v>
+            <v>9.5133851023293303E-2</v>
           </cell>
           <cell r="J22">
-            <v>0.12227695604597411</v>
+            <v>0.33336045600883751</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2224,31 +2233,31 @@
         </row>
         <row r="23">
           <cell r="B23">
-            <v>22</v>
+            <v>26</v>
           </cell>
           <cell r="C23" t="str">
-            <v>UCLA</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D23" t="str">
-            <v>UCF</v>
+            <v>Queens University</v>
           </cell>
           <cell r="E23">
-            <v>7.3720101204148367</v>
+            <v>28.175000000000001</v>
           </cell>
           <cell r="F23" t="b">
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0.53416767430541012</v>
+            <v>0.57012118173818638</v>
           </cell>
           <cell r="H23">
             <v>0</v>
           </cell>
           <cell r="I23">
-            <v>1.9774650946692118E-2</v>
+            <v>8.841316513653763E-2</v>
           </cell>
           <cell r="J23">
-            <v>0.3157571093517878</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K23">
             <v>0</v>
@@ -2256,31 +2265,31 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>23</v>
+            <v>28</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Uconn</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D24" t="str">
-            <v>Furman</v>
+            <v>Tennessee State</v>
           </cell>
           <cell r="E24">
-            <v>25.492859365224369</v>
+            <v>28.175000000000001</v>
           </cell>
           <cell r="F24" t="b">
             <v>0</v>
           </cell>
           <cell r="G24">
-            <v>0.59510350502049691</v>
+            <v>0.57012118173818638</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>0.13610669140276691</v>
+            <v>8.841316513653763E-2</v>
           </cell>
           <cell r="J24">
-            <v>0.82144469910078188</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2288,31 +2297,31 @@
         </row>
         <row r="25">
           <cell r="B25">
-            <v>24</v>
+            <v>43</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Virginia</v>
+            <v>Pennsylvania</v>
           </cell>
           <cell r="D25" t="str">
-            <v>Wright State</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E25">
-            <v>20.329275195939459</v>
+            <v>-26.584731887521901</v>
           </cell>
           <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0.54026304364429201</v>
+            <v>0.56981806080452269</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>3.1411265139102973E-2</v>
+            <v>8.7834479717725178E-2</v>
           </cell>
           <cell r="J25">
-            <v>0.66902836142407174</v>
+            <v>0.80569684947500253</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2320,31 +2329,31 @@
         </row>
         <row r="26">
           <cell r="B26">
-            <v>25</v>
+            <v>38</v>
           </cell>
           <cell r="C26" t="str">
-            <v>Miami</v>
+            <v>North Dakota State</v>
           </cell>
           <cell r="D26" t="str">
-            <v>Missouri</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="E26">
-            <v>4.4770135283782926</v>
+            <v>-18.957923408995232</v>
           </cell>
           <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0.56151576507289314</v>
+            <v>0.56431388885662104</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>7.1984642411886957E-2</v>
+            <v>7.7326515089912951E-2</v>
           </cell>
           <cell r="J26">
-            <v>0.28944093497921641</v>
+            <v>0.68214224406760438</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2352,31 +2361,31 @@
         </row>
         <row r="27">
           <cell r="B27">
-            <v>26</v>
+            <v>9</v>
           </cell>
           <cell r="C27" t="str">
-            <v>Purdue</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="D27" t="str">
-            <v>Queens University</v>
+            <v>TCU</v>
           </cell>
           <cell r="E27">
-            <v>28.175000000000001</v>
+            <v>4.5795233045545594</v>
           </cell>
           <cell r="F27" t="b">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0.57012118173818638</v>
+            <v>0.56404001660924963</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>8.841316513653763E-2</v>
+            <v>7.6803668072203846E-2</v>
           </cell>
           <cell r="J27">
-            <v>0.82374745212732714</v>
+            <v>0.29860436775963528</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2384,31 +2393,31 @@
         </row>
         <row r="28">
           <cell r="B28">
-            <v>27</v>
+            <v>35</v>
           </cell>
           <cell r="C28" t="str">
-            <v>Kentucky</v>
+            <v>Lehigh Mountain</v>
           </cell>
           <cell r="D28" t="str">
-            <v>Santa Clara</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="E28">
-            <v>5.4103511425263981</v>
+            <v>5.0772786070447582</v>
           </cell>
           <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0.54751955979773603</v>
+            <v>0.56398476960459853</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>4.5264614159314258E-2</v>
+            <v>7.6698196517870021E-2</v>
           </cell>
           <cell r="J28">
-            <v>0.28571132045463621</v>
+            <v>0.3140021880193648</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2416,31 +2425,31 @@
         </row>
         <row r="29">
           <cell r="B29">
-            <v>28</v>
+            <v>1</v>
           </cell>
           <cell r="C29" t="str">
-            <v>Iowa State</v>
+            <v>UMBC</v>
           </cell>
           <cell r="D29" t="str">
-            <v>Tennessee State</v>
+            <v>Howard</v>
           </cell>
           <cell r="E29">
-            <v>28.175000000000001</v>
+            <v>4.5398147803963766</v>
           </cell>
           <cell r="F29" t="b">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0.57012118173818638</v>
+            <v>0.56306251790939255</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>8.841316513653763E-2</v>
+            <v>7.4937534190658517E-2</v>
           </cell>
           <cell r="J29">
-            <v>0.82374745212732714</v>
+            <v>0.29505706343244742</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2448,31 +2457,31 @@
         </row>
         <row r="30">
           <cell r="B30">
-            <v>29</v>
+            <v>25</v>
           </cell>
           <cell r="C30" t="str">
-            <v>St. John's</v>
+            <v>Miami</v>
           </cell>
           <cell r="D30" t="str">
-            <v>Northern Iowa</v>
+            <v>Missouri</v>
           </cell>
           <cell r="E30">
-            <v>12.286890801195611</v>
+            <v>4.4770135283782926</v>
           </cell>
           <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0.51961234415784652</v>
+            <v>0.56151576507289314</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>-8.0127975168384213E-3</v>
+            <v>7.1984642411886957E-2</v>
           </cell>
           <cell r="J30">
-            <v>0.43263467267483402</v>
+            <v>0.28944093497921641</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2480,31 +2489,31 @@
         </row>
         <row r="31">
           <cell r="B31">
-            <v>30</v>
+            <v>19</v>
           </cell>
           <cell r="C31" t="str">
-            <v>Kansas</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="D31" t="str">
-            <v>California Baptist</v>
+            <v>Akron</v>
           </cell>
           <cell r="E31">
-            <v>18.573029871345032</v>
+            <v>10.43081131270095</v>
           </cell>
           <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0.59561500793361322</v>
+            <v>0.56037723382257887</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>0.13708319696417071</v>
+            <v>6.9811082752196052E-2</v>
           </cell>
           <cell r="J31">
-            <v>0.72543986092307822</v>
+            <v>0.46800018669531451</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2512,31 +2521,31 @@
         </row>
         <row r="32">
           <cell r="B32">
-            <v>31</v>
+            <v>2</v>
           </cell>
           <cell r="C32" t="str">
-            <v>Arizona</v>
+            <v>Texas</v>
           </cell>
           <cell r="D32" t="str">
-            <v>Long Island University</v>
+            <v>NC State</v>
           </cell>
           <cell r="E32">
-            <v>32.075000000000003</v>
+            <v>3.351492666553944</v>
           </cell>
           <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0.5301795270136529</v>
+            <v>0.55842147595203739</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>1.216091520788282E-2</v>
+            <v>6.6077363181162307E-2</v>
           </cell>
           <cell r="J32">
-            <v>0.82374745212732714</v>
+            <v>0.24670500307592891</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2544,31 +2553,31 @@
         </row>
         <row r="33">
           <cell r="B33">
-            <v>32</v>
+            <v>7</v>
           </cell>
           <cell r="C33" t="str">
-            <v>Villanova</v>
+            <v>Georgia</v>
           </cell>
           <cell r="D33" t="str">
-            <v>Utah State</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="E33">
-            <v>-0.75126679890107051</v>
+            <v>4.2861663978745757</v>
           </cell>
           <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0.53110419949984844</v>
+            <v>0.55680965526509907</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>1.3926199045165229E-2</v>
+            <v>6.3000250960643767E-2</v>
           </cell>
           <cell r="J33">
-            <v>5.0370532033560012E-2</v>
+            <v>0.27233205754770629</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -2576,63 +2585,63 @@
         </row>
         <row r="34">
           <cell r="B34">
-            <v>33</v>
+            <v>58</v>
           </cell>
           <cell r="C34" t="str">
-            <v>Howard</v>
+            <v>Queens University</v>
           </cell>
           <cell r="D34" t="str">
-            <v>UMBC</v>
+            <v>Purdue</v>
           </cell>
           <cell r="E34">
-            <v>2.711720411891148</v>
+            <v>-27.266982450772101</v>
           </cell>
           <cell r="F34" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G34">
-            <v>0.61580539290283809</v>
+            <v>0.55453717792185397</v>
           </cell>
           <cell r="H34">
-            <v>4.7276530038383939E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I34">
-            <v>0.1756284773599637</v>
+            <v>5.8661885123539433E-2</v>
           </cell>
           <cell r="J34">
-            <v>0.3634228852259655</v>
+            <v>0.79642984416271356</v>
           </cell>
           <cell r="K34">
-            <v>0.92283786634925447</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>34</v>
+            <v>54</v>
           </cell>
           <cell r="C35" t="str">
-            <v>NC State</v>
+            <v>UCF</v>
           </cell>
           <cell r="D35" t="str">
-            <v>Texas</v>
+            <v>UCLA</v>
           </cell>
           <cell r="E35">
-            <v>-0.71724508084755245</v>
+            <v>-3.8266435714985798</v>
           </cell>
           <cell r="F35" t="b">
             <v>0</v>
           </cell>
           <cell r="G35">
-            <v>0.50704981381328074</v>
+            <v>0.55402405102411312</v>
           </cell>
           <cell r="H35">
             <v>0</v>
           </cell>
           <cell r="I35">
-            <v>-3.199580999282764E-2</v>
+            <v>5.7682279227852407E-2</v>
           </cell>
           <cell r="J35">
-            <v>6.1738947754240714E-3</v>
+            <v>6.7349851388678328E-3</v>
           </cell>
           <cell r="K35">
             <v>0</v>
@@ -2640,31 +2649,31 @@
         </row>
         <row r="36">
           <cell r="B36">
-            <v>35</v>
+            <v>45</v>
           </cell>
           <cell r="C36" t="str">
-            <v>Lehigh Mountain</v>
+            <v>Troy</v>
           </cell>
           <cell r="D36" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="E36">
-            <v>5.0772786070447582</v>
+            <v>-15.800660571957931</v>
           </cell>
           <cell r="F36" t="b">
             <v>0</v>
           </cell>
           <cell r="G36">
-            <v>0.56398476960459853</v>
+            <v>0.55314950886908421</v>
           </cell>
           <cell r="H36">
             <v>0</v>
           </cell>
           <cell r="I36">
-            <v>7.6698196517870021E-2</v>
+            <v>5.6012698750069867E-2</v>
           </cell>
           <cell r="J36">
-            <v>0.3140021880193648</v>
+            <v>0.59505082789393093</v>
           </cell>
           <cell r="K36">
             <v>0</v>
@@ -2704,31 +2713,31 @@
         </row>
         <row r="38">
           <cell r="B38">
-            <v>37</v>
+            <v>56</v>
           </cell>
           <cell r="C38" t="str">
-            <v>South Florida</v>
+            <v>Wright State</v>
           </cell>
           <cell r="D38" t="str">
-            <v>Louisville</v>
+            <v>Virginia</v>
           </cell>
           <cell r="E38">
-            <v>-4.0407071170746427</v>
+            <v>-16.44502010603955</v>
           </cell>
           <cell r="F38" t="b">
             <v>0</v>
           </cell>
           <cell r="G38">
-            <v>0.53633546884354921</v>
+            <v>0.5510981247018647</v>
           </cell>
           <cell r="H38">
             <v>0</v>
           </cell>
           <cell r="I38">
-            <v>2.391316779223035E-2</v>
+            <v>5.2096419885378047E-2</v>
           </cell>
           <cell r="J38">
-            <v>4.2751559352500079E-2</v>
+            <v>0.39898549067999339</v>
           </cell>
           <cell r="K38">
             <v>0</v>
@@ -2736,31 +2745,31 @@
         </row>
         <row r="39">
           <cell r="B39">
-            <v>38</v>
+            <v>21</v>
           </cell>
           <cell r="C39" t="str">
-            <v>North Dakota State</v>
+            <v>Clemson</v>
           </cell>
           <cell r="D39" t="str">
-            <v>Michigan State</v>
+            <v>Iowa</v>
           </cell>
           <cell r="E39">
-            <v>-18.957923408995232</v>
+            <v>3.3395963530867379E-2</v>
           </cell>
           <cell r="F39" t="b">
             <v>0</v>
           </cell>
           <cell r="G39">
-            <v>0.56431388885662104</v>
+            <v>0.55056432776779596</v>
           </cell>
           <cell r="H39">
             <v>0</v>
           </cell>
           <cell r="I39">
-            <v>7.7326515089912951E-2</v>
+            <v>5.1077353011246829E-2</v>
           </cell>
           <cell r="J39">
-            <v>0.68214224406760438</v>
+            <v>0.12227695604597411</v>
           </cell>
           <cell r="K39">
             <v>0</v>
@@ -2768,31 +2777,31 @@
         </row>
         <row r="40">
           <cell r="B40">
-            <v>39</v>
+            <v>44</v>
           </cell>
           <cell r="C40" t="str">
-            <v>Saint Louis</v>
+            <v>McNeese</v>
           </cell>
           <cell r="D40" t="str">
-            <v>Georgia</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="E40">
-            <v>-2.323634492416264</v>
+            <v>-13.561700995584451</v>
           </cell>
           <cell r="F40" t="b">
             <v>0</v>
           </cell>
           <cell r="G40">
-            <v>0.50806891743100513</v>
+            <v>0.5494989938305499</v>
           </cell>
           <cell r="H40">
             <v>0</v>
           </cell>
           <cell r="I40">
-            <v>-3.0050248540808341E-2</v>
+            <v>4.9043533676504381E-2</v>
           </cell>
           <cell r="J40">
-            <v>9.3917362818843442E-2</v>
+            <v>0.53201297998911168</v>
           </cell>
           <cell r="K40">
             <v>0</v>
@@ -2800,31 +2809,31 @@
         </row>
         <row r="41">
           <cell r="B41">
-            <v>40</v>
+            <v>4</v>
           </cell>
           <cell r="C41" t="str">
-            <v>Siena</v>
+            <v>Miami (OH)</v>
           </cell>
           <cell r="D41" t="str">
-            <v>Duke</v>
+            <v>SMU</v>
           </cell>
           <cell r="E41">
-            <v>-31.1</v>
+            <v>-6.5280711453208946</v>
           </cell>
           <cell r="F41" t="b">
             <v>0</v>
           </cell>
           <cell r="G41">
-            <v>0.54020950401036405</v>
+            <v>0.54904367295244916</v>
           </cell>
           <cell r="H41">
             <v>0</v>
           </cell>
           <cell r="I41">
-            <v>3.130905311069504E-2</v>
+            <v>4.8174284727402983E-2</v>
           </cell>
           <cell r="J41">
-            <v>0.82374745212732714</v>
+            <v>9.203326713974791E-2</v>
           </cell>
           <cell r="K41">
             <v>0</v>
@@ -2832,31 +2841,31 @@
         </row>
         <row r="42">
           <cell r="B42">
-            <v>41</v>
+            <v>27</v>
           </cell>
           <cell r="C42" t="str">
-            <v>TCU</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D42" t="str">
-            <v>Ohio State</v>
+            <v>Santa Clara</v>
           </cell>
           <cell r="E42">
-            <v>-1.9384527984340609</v>
+            <v>5.4103511425263981</v>
           </cell>
           <cell r="F42" t="b">
             <v>0</v>
           </cell>
           <cell r="G42">
-            <v>0.50153460752444023</v>
+            <v>0.54751955979773603</v>
           </cell>
           <cell r="H42">
             <v>0</v>
           </cell>
           <cell r="I42">
-            <v>-4.2524840180614032E-2</v>
+            <v>4.5264614159314258E-2</v>
           </cell>
           <cell r="J42">
-            <v>5.8602197560207459E-2</v>
+            <v>0.28571132045463621</v>
           </cell>
           <cell r="K42">
             <v>0</v>
@@ -2864,31 +2873,31 @@
         </row>
         <row r="43">
           <cell r="B43">
-            <v>42</v>
+            <v>24</v>
           </cell>
           <cell r="C43" t="str">
-            <v>VCU</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D43" t="str">
-            <v>North Carolina</v>
+            <v>Wright State</v>
           </cell>
           <cell r="E43">
-            <v>-1.733823308460128</v>
+            <v>20.329275195939459</v>
           </cell>
           <cell r="F43" t="b">
             <v>0</v>
           </cell>
           <cell r="G43">
-            <v>0.50663651490010164</v>
+            <v>0.54026304364429201</v>
           </cell>
           <cell r="H43">
             <v>0</v>
           </cell>
           <cell r="I43">
-            <v>-3.2784835190715012E-2</v>
+            <v>3.1411265139102973E-2</v>
           </cell>
           <cell r="J43">
-            <v>3.9825391009848547E-2</v>
+            <v>0.66902836142407174</v>
           </cell>
           <cell r="K43">
             <v>0</v>
@@ -2896,31 +2905,31 @@
         </row>
         <row r="44">
           <cell r="B44">
-            <v>43</v>
+            <v>51</v>
           </cell>
           <cell r="C44" t="str">
-            <v>Pennsylvania</v>
+            <v>Akron</v>
           </cell>
           <cell r="D44" t="str">
-            <v>Illinois</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="E44">
-            <v>-26.584731887521901</v>
+            <v>-6.3844148545709842</v>
           </cell>
           <cell r="F44" t="b">
             <v>0</v>
           </cell>
           <cell r="G44">
-            <v>0.56981806080452269</v>
+            <v>0.5402144785835673</v>
           </cell>
           <cell r="H44">
             <v>0</v>
           </cell>
           <cell r="I44">
-            <v>8.7834479717725178E-2</v>
+            <v>3.1318550023173963E-2</v>
           </cell>
           <cell r="J44">
-            <v>0.80569684947500253</v>
+            <v>0.1086427549134706</v>
           </cell>
           <cell r="K44">
             <v>0</v>
@@ -2928,31 +2937,31 @@
         </row>
         <row r="45">
           <cell r="B45">
-            <v>44</v>
+            <v>8</v>
           </cell>
           <cell r="C45" t="str">
-            <v>McNeese</v>
+            <v>Duke</v>
           </cell>
           <cell r="D45" t="str">
-            <v>Vanderbilt</v>
+            <v>Siena</v>
           </cell>
           <cell r="E45">
-            <v>-13.561700995584451</v>
+            <v>31.1</v>
           </cell>
           <cell r="F45" t="b">
             <v>0</v>
           </cell>
           <cell r="G45">
-            <v>0.5494989938305499</v>
+            <v>0.54020950401036416</v>
           </cell>
           <cell r="H45">
             <v>0</v>
           </cell>
           <cell r="I45">
-            <v>4.9043533676504381E-2</v>
+            <v>3.1309053110695262E-2</v>
           </cell>
           <cell r="J45">
-            <v>0.53201297998911168</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K45">
             <v>0</v>
@@ -2960,31 +2969,31 @@
         </row>
         <row r="46">
           <cell r="B46">
-            <v>45</v>
+            <v>40</v>
           </cell>
           <cell r="C46" t="str">
-            <v>Troy</v>
+            <v>Siena</v>
           </cell>
           <cell r="D46" t="str">
-            <v>Nebraska</v>
+            <v>Duke</v>
           </cell>
           <cell r="E46">
-            <v>-15.800660571957931</v>
+            <v>-31.1</v>
           </cell>
           <cell r="F46" t="b">
             <v>0</v>
           </cell>
           <cell r="G46">
-            <v>0.55314950886908421</v>
+            <v>0.54020950401036405</v>
           </cell>
           <cell r="H46">
             <v>0</v>
           </cell>
           <cell r="I46">
-            <v>5.6012698750069867E-2</v>
+            <v>3.130905311069504E-2</v>
           </cell>
           <cell r="J46">
-            <v>0.59505082789393093</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K46">
             <v>0</v>
@@ -2992,31 +3001,31 @@
         </row>
         <row r="47">
           <cell r="B47">
-            <v>46</v>
+            <v>60</v>
           </cell>
           <cell r="C47" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Tennessee State</v>
           </cell>
           <cell r="D47" t="str">
-            <v>Saint Mary's</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="E47">
-            <v>-0.54471210634917988</v>
+            <v>-26.430767349804981</v>
           </cell>
           <cell r="F47" t="b">
             <v>0</v>
           </cell>
           <cell r="G47">
-            <v>0.53623602221725253</v>
+            <v>0.53922786424151381</v>
           </cell>
           <cell r="H47">
             <v>0</v>
           </cell>
           <cell r="I47">
-            <v>2.3723315142027579E-2</v>
+            <v>2.9435013551980971E-2</v>
           </cell>
           <cell r="J47">
-            <v>6.9318830663357978E-2</v>
+            <v>0.76733006607214982</v>
           </cell>
           <cell r="K47">
             <v>0</v>
@@ -3024,31 +3033,31 @@
         </row>
         <row r="48">
           <cell r="B48">
-            <v>47</v>
+            <v>37</v>
           </cell>
           <cell r="C48" t="str">
-            <v>Idaho</v>
+            <v>South Florida</v>
           </cell>
           <cell r="D48" t="str">
-            <v>Houston</v>
+            <v>Louisville</v>
           </cell>
           <cell r="E48">
-            <v>-24.32380148918374</v>
+            <v>-4.0407071170746427</v>
           </cell>
           <cell r="F48" t="b">
             <v>0</v>
           </cell>
           <cell r="G48">
-            <v>0.52802701210828917</v>
+            <v>0.53633546884354921</v>
           </cell>
           <cell r="H48">
             <v>0</v>
           </cell>
           <cell r="I48">
-            <v>8.05156857037026E-3</v>
+            <v>2.391316779223035E-2</v>
           </cell>
           <cell r="J48">
-            <v>0.72103790251730027</v>
+            <v>4.2751559352500079E-2</v>
           </cell>
           <cell r="K48">
             <v>0</v>
@@ -3056,31 +3065,31 @@
         </row>
         <row r="49">
           <cell r="B49">
-            <v>48</v>
+            <v>46</v>
           </cell>
           <cell r="C49" t="str">
-            <v>High Point</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="D49" t="str">
-            <v>Wisconsin</v>
+            <v>Saint Mary's</v>
           </cell>
           <cell r="E49">
-            <v>-6.7399272078176624</v>
+            <v>-0.54471210634917988</v>
           </cell>
           <cell r="F49" t="b">
             <v>0</v>
           </cell>
           <cell r="G49">
-            <v>0.58072734404629345</v>
+            <v>0.53623602221725253</v>
           </cell>
           <cell r="H49">
             <v>0</v>
           </cell>
           <cell r="I49">
-            <v>0.10866129317928749</v>
+            <v>2.3723315142027579E-2</v>
           </cell>
           <cell r="J49">
-            <v>2.202740613184884E-2</v>
+            <v>6.9318830663357978E-2</v>
           </cell>
           <cell r="K49">
             <v>0</v>
@@ -3088,31 +3097,31 @@
         </row>
         <row r="50">
           <cell r="B50">
-            <v>49</v>
+            <v>16</v>
           </cell>
           <cell r="C50" t="str">
-            <v>Hawaii</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="D50" t="str">
-            <v>Arkansas</v>
+            <v>High Point</v>
           </cell>
           <cell r="E50">
-            <v>-19.689265506637959</v>
+            <v>11.446368832524669</v>
           </cell>
           <cell r="F50" t="b">
             <v>0</v>
           </cell>
           <cell r="G50">
-            <v>0.58728757996436998</v>
+            <v>0.53601454769519918</v>
           </cell>
           <cell r="H50">
             <v>0</v>
           </cell>
           <cell r="I50">
-            <v>0.1211853799319791</v>
+            <v>2.3300500145380321E-2</v>
           </cell>
           <cell r="J50">
-            <v>0.73158718099349851</v>
+            <v>0.44405986090341543</v>
           </cell>
           <cell r="K50">
             <v>0</v>
@@ -3120,31 +3129,31 @@
         </row>
         <row r="51">
           <cell r="B51">
-            <v>50</v>
+            <v>3</v>
           </cell>
           <cell r="C51" t="str">
-            <v>Kennesaw State</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D51" t="str">
-            <v>Gonzaga</v>
+            <v>Lehigh Mountain</v>
           </cell>
           <cell r="E51">
-            <v>-18.939777212918951</v>
+            <v>-1.0818703398805221</v>
           </cell>
           <cell r="F51" t="b">
             <v>0</v>
           </cell>
           <cell r="G51">
-            <v>0.5014200475842292</v>
+            <v>0.53531325069231817</v>
           </cell>
           <cell r="H51">
             <v>0</v>
           </cell>
           <cell r="I51">
-            <v>-4.2743545521016953E-2</v>
+            <v>2.1961660412607439E-2</v>
           </cell>
           <cell r="J51">
-            <v>0.56671791944483352</v>
+            <v>4.9856358057364769E-2</v>
           </cell>
           <cell r="K51">
             <v>0</v>
@@ -3152,31 +3161,31 @@
         </row>
         <row r="52">
           <cell r="B52">
-            <v>51</v>
+            <v>22</v>
           </cell>
           <cell r="C52" t="str">
-            <v>Akron</v>
+            <v>UCLA</v>
           </cell>
           <cell r="D52" t="str">
-            <v>Texas Tech</v>
+            <v>UCF</v>
           </cell>
           <cell r="E52">
-            <v>-6.3844148545709842</v>
+            <v>7.3720101204148367</v>
           </cell>
           <cell r="F52" t="b">
             <v>0</v>
           </cell>
           <cell r="G52">
-            <v>0.5402144785835673</v>
+            <v>0.53416767430541012</v>
           </cell>
           <cell r="H52">
             <v>0</v>
           </cell>
           <cell r="I52">
-            <v>3.1318550023173963E-2</v>
+            <v>1.9774650946692118E-2</v>
           </cell>
           <cell r="J52">
-            <v>0.1086427549134706</v>
+            <v>0.3157571093517878</v>
           </cell>
           <cell r="K52">
             <v>0</v>
@@ -3184,31 +3193,31 @@
         </row>
         <row r="53">
           <cell r="B53">
-            <v>52</v>
+            <v>32</v>
           </cell>
           <cell r="C53" t="str">
-            <v>Hofstra</v>
+            <v>Villanova</v>
           </cell>
           <cell r="D53" t="str">
-            <v>Alabama</v>
+            <v>Utah State</v>
           </cell>
           <cell r="E53">
-            <v>-18.409254461666698</v>
+            <v>-0.75126679890107051</v>
           </cell>
           <cell r="F53" t="b">
             <v>0</v>
           </cell>
           <cell r="G53">
-            <v>0.59279510849473038</v>
+            <v>0.53110419949984844</v>
           </cell>
           <cell r="H53">
             <v>0</v>
           </cell>
           <cell r="I53">
-            <v>0.13169975258084901</v>
+            <v>1.3926199045165229E-2</v>
           </cell>
           <cell r="J53">
-            <v>0.71813726064377859</v>
+            <v>5.0370532033560012E-2</v>
           </cell>
           <cell r="K53">
             <v>0</v>
@@ -3216,31 +3225,31 @@
         </row>
         <row r="54">
           <cell r="B54">
-            <v>53</v>
+            <v>31</v>
           </cell>
           <cell r="C54" t="str">
-            <v>Iowa</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D54" t="str">
-            <v>Clemson</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="E54">
-            <v>5.0603260407104784</v>
+            <v>32.075000000000003</v>
           </cell>
           <cell r="F54" t="b">
             <v>0</v>
           </cell>
           <cell r="G54">
-            <v>0.57584311604296001</v>
+            <v>0.5301795270136529</v>
           </cell>
           <cell r="H54">
             <v>0</v>
           </cell>
           <cell r="I54">
-            <v>9.9336857900196418E-2</v>
+            <v>1.216091520788282E-2</v>
           </cell>
           <cell r="J54">
-            <v>0.3413049040666058</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K54">
             <v>0</v>
@@ -3248,31 +3257,31 @@
         </row>
         <row r="55">
           <cell r="B55">
-            <v>54</v>
+            <v>63</v>
           </cell>
           <cell r="C55" t="str">
-            <v>UCF</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="D55" t="str">
-            <v>UCLA</v>
+            <v>Arizona</v>
           </cell>
           <cell r="E55">
-            <v>-3.8266435714985798</v>
+            <v>-32.075000000000003</v>
           </cell>
           <cell r="F55" t="b">
             <v>0</v>
           </cell>
           <cell r="G55">
-            <v>0.55402405102411312</v>
+            <v>0.5301795270136529</v>
           </cell>
           <cell r="H55">
             <v>0</v>
           </cell>
           <cell r="I55">
-            <v>5.7682279227852407E-2</v>
+            <v>1.216091520788282E-2</v>
           </cell>
           <cell r="J55">
-            <v>6.7349851388678328E-3</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K55">
             <v>0</v>
@@ -3312,31 +3321,31 @@
         </row>
         <row r="57">
           <cell r="B57">
-            <v>56</v>
+            <v>47</v>
           </cell>
           <cell r="C57" t="str">
-            <v>Wright State</v>
+            <v>Idaho</v>
           </cell>
           <cell r="D57" t="str">
-            <v>Virginia</v>
+            <v>Houston</v>
           </cell>
           <cell r="E57">
-            <v>-16.44502010603955</v>
+            <v>-24.32380148918374</v>
           </cell>
           <cell r="F57" t="b">
             <v>0</v>
           </cell>
           <cell r="G57">
-            <v>0.5510981247018647</v>
+            <v>0.52802701210828917</v>
           </cell>
           <cell r="H57">
             <v>0</v>
           </cell>
           <cell r="I57">
-            <v>5.2096419885378047E-2</v>
+            <v>8.05156857037026E-3</v>
           </cell>
           <cell r="J57">
-            <v>0.39898549067999339</v>
+            <v>0.72103790251730027</v>
           </cell>
           <cell r="K57">
             <v>0</v>
@@ -3344,31 +3353,31 @@
         </row>
         <row r="58">
           <cell r="B58">
-            <v>57</v>
+            <v>62</v>
           </cell>
           <cell r="C58" t="str">
-            <v>Missouri</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="D58" t="str">
-            <v>Miami</v>
+            <v>Kansas</v>
           </cell>
           <cell r="E58">
-            <v>1.742263875348123</v>
+            <v>-15.090084378042731</v>
           </cell>
           <cell r="F58" t="b">
             <v>0</v>
           </cell>
           <cell r="G58">
-            <v>0.59246539086017058</v>
+            <v>0.52632532157094747</v>
           </cell>
           <cell r="H58">
             <v>0</v>
           </cell>
           <cell r="I58">
-            <v>0.1310702916421439</v>
+            <v>4.8028866354452027E-3</v>
           </cell>
           <cell r="J58">
-            <v>0.2773673651949719</v>
+            <v>0.52510282618406234</v>
           </cell>
           <cell r="K58">
             <v>0</v>
@@ -3376,31 +3385,31 @@
         </row>
         <row r="59">
           <cell r="B59">
-            <v>58</v>
+            <v>29</v>
           </cell>
           <cell r="C59" t="str">
-            <v>Queens University</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D59" t="str">
-            <v>Purdue</v>
+            <v>Northern Iowa</v>
           </cell>
           <cell r="E59">
-            <v>-27.266982450772101</v>
+            <v>12.286890801195611</v>
           </cell>
           <cell r="F59" t="b">
             <v>0</v>
           </cell>
           <cell r="G59">
-            <v>0.55453717792185397</v>
+            <v>0.51961234415784652</v>
           </cell>
           <cell r="H59">
             <v>0</v>
           </cell>
           <cell r="I59">
-            <v>5.8661885123539433E-2</v>
+            <v>-8.0127975168384213E-3</v>
           </cell>
           <cell r="J59">
-            <v>0.79642984416271356</v>
+            <v>0.43263467267483402</v>
           </cell>
           <cell r="K59">
             <v>0</v>
@@ -3440,31 +3449,31 @@
         </row>
         <row r="61">
           <cell r="B61">
-            <v>60</v>
+            <v>39</v>
           </cell>
           <cell r="C61" t="str">
-            <v>Tennessee State</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D61" t="str">
-            <v>Iowa State</v>
+            <v>Georgia</v>
           </cell>
           <cell r="E61">
-            <v>-26.430767349804981</v>
+            <v>-2.323634492416264</v>
           </cell>
           <cell r="F61" t="b">
             <v>0</v>
           </cell>
           <cell r="G61">
-            <v>0.53922786424151381</v>
+            <v>0.50806891743100513</v>
           </cell>
           <cell r="H61">
             <v>0</v>
           </cell>
           <cell r="I61">
-            <v>2.9435013551980971E-2</v>
+            <v>-3.0050248540808341E-2</v>
           </cell>
           <cell r="J61">
-            <v>0.76733006607214982</v>
+            <v>9.3917362818843442E-2</v>
           </cell>
           <cell r="K61">
             <v>0</v>
@@ -3472,31 +3481,31 @@
         </row>
         <row r="62">
           <cell r="B62">
-            <v>61</v>
+            <v>34</v>
           </cell>
           <cell r="C62" t="str">
-            <v>Northern Iowa</v>
+            <v>NC State</v>
           </cell>
           <cell r="D62" t="str">
-            <v>St. John's</v>
+            <v>Texas</v>
           </cell>
           <cell r="E62">
-            <v>-7.0324352932968432</v>
+            <v>-0.71724508084755245</v>
           </cell>
           <cell r="F62" t="b">
             <v>0</v>
           </cell>
           <cell r="G62">
-            <v>0.60996307409599937</v>
+            <v>0.50704981381328074</v>
           </cell>
           <cell r="H62">
             <v>0</v>
           </cell>
           <cell r="I62">
-            <v>0.164474959637817</v>
+            <v>-3.199580999282764E-2</v>
           </cell>
           <cell r="J62">
-            <v>4.0627657807308433E-2</v>
+            <v>6.1738947754240714E-3</v>
           </cell>
           <cell r="K62">
             <v>0</v>
@@ -3504,31 +3513,31 @@
         </row>
         <row r="63">
           <cell r="B63">
-            <v>62</v>
+            <v>42</v>
           </cell>
           <cell r="C63" t="str">
-            <v>California Baptist</v>
+            <v>VCU</v>
           </cell>
           <cell r="D63" t="str">
-            <v>Kansas</v>
+            <v>North Carolina</v>
           </cell>
           <cell r="E63">
-            <v>-15.090084378042731</v>
+            <v>-1.733823308460128</v>
           </cell>
           <cell r="F63" t="b">
             <v>0</v>
           </cell>
           <cell r="G63">
-            <v>0.52632532157094747</v>
+            <v>0.50663651490010164</v>
           </cell>
           <cell r="H63">
             <v>0</v>
           </cell>
           <cell r="I63">
-            <v>4.8028866354452027E-3</v>
+            <v>-3.2784835190715012E-2</v>
           </cell>
           <cell r="J63">
-            <v>0.52510282618406234</v>
+            <v>3.9825391009848547E-2</v>
           </cell>
           <cell r="K63">
             <v>0</v>
@@ -3536,31 +3545,31 @@
         </row>
         <row r="64">
           <cell r="B64">
-            <v>63</v>
+            <v>41</v>
           </cell>
           <cell r="C64" t="str">
-            <v>Long Island University</v>
+            <v>TCU</v>
           </cell>
           <cell r="D64" t="str">
-            <v>Arizona</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="E64">
-            <v>-32.075000000000003</v>
+            <v>-1.9384527984340609</v>
           </cell>
           <cell r="F64" t="b">
             <v>0</v>
           </cell>
           <cell r="G64">
-            <v>0.5301795270136529</v>
+            <v>0.50153460752444023</v>
           </cell>
           <cell r="H64">
             <v>0</v>
           </cell>
           <cell r="I64">
-            <v>1.216091520788282E-2</v>
+            <v>-4.2524840180614032E-2</v>
           </cell>
           <cell r="J64">
-            <v>0.82374745212732714</v>
+            <v>5.8602197560207459E-2</v>
           </cell>
           <cell r="K64">
             <v>0</v>
@@ -3568,31 +3577,31 @@
         </row>
         <row r="65">
           <cell r="B65">
-            <v>64</v>
+            <v>50</v>
           </cell>
           <cell r="C65" t="str">
-            <v>Utah State</v>
+            <v>Kennesaw State</v>
           </cell>
           <cell r="D65" t="str">
-            <v>Villanova</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="E65">
-            <v>5.2368487163496038</v>
+            <v>-18.939777212918951</v>
           </cell>
           <cell r="F65" t="b">
             <v>0</v>
           </cell>
           <cell r="G65">
-            <v>0.58016009009738734</v>
+            <v>0.5014200475842292</v>
           </cell>
           <cell r="H65">
             <v>0</v>
           </cell>
           <cell r="I65">
-            <v>0.10757835382228501</v>
+            <v>-4.2743545521016953E-2</v>
           </cell>
           <cell r="J65">
-            <v>0.3568520724234755</v>
+            <v>0.56671791944483352</v>
           </cell>
           <cell r="K65">
             <v>0</v>
@@ -13660,2996 +13669,6 @@
           <cell r="X65">
             <v>-2</v>
           </cell>
-        </row>
-        <row r="66">
-          <cell r="D66"/>
-          <cell r="E66"/>
-          <cell r="F66"/>
-          <cell r="G66"/>
-          <cell r="H66"/>
-          <cell r="I66"/>
-          <cell r="J66"/>
-          <cell r="K66"/>
-          <cell r="L66"/>
-          <cell r="M66"/>
-          <cell r="N66"/>
-          <cell r="O66"/>
-          <cell r="P66"/>
-          <cell r="Q66"/>
-          <cell r="R66"/>
-          <cell r="S66"/>
-          <cell r="T66"/>
-          <cell r="U66"/>
-          <cell r="V66"/>
-          <cell r="W66"/>
-          <cell r="X66"/>
-        </row>
-        <row r="67">
-          <cell r="D67"/>
-          <cell r="E67"/>
-          <cell r="F67"/>
-          <cell r="G67"/>
-          <cell r="H67"/>
-          <cell r="I67"/>
-          <cell r="J67"/>
-          <cell r="K67"/>
-          <cell r="L67"/>
-          <cell r="M67"/>
-          <cell r="N67"/>
-          <cell r="O67"/>
-          <cell r="P67"/>
-          <cell r="Q67"/>
-          <cell r="R67"/>
-          <cell r="S67"/>
-          <cell r="T67"/>
-          <cell r="U67"/>
-          <cell r="V67"/>
-          <cell r="W67"/>
-          <cell r="X67"/>
-        </row>
-        <row r="68">
-          <cell r="D68"/>
-          <cell r="E68"/>
-          <cell r="F68"/>
-          <cell r="G68"/>
-          <cell r="H68"/>
-          <cell r="I68"/>
-          <cell r="J68"/>
-          <cell r="K68"/>
-          <cell r="L68"/>
-          <cell r="M68"/>
-          <cell r="N68"/>
-          <cell r="O68"/>
-          <cell r="P68"/>
-          <cell r="Q68"/>
-          <cell r="R68"/>
-          <cell r="S68"/>
-          <cell r="T68"/>
-          <cell r="U68"/>
-          <cell r="V68"/>
-          <cell r="W68"/>
-          <cell r="X68"/>
-        </row>
-        <row r="69">
-          <cell r="D69"/>
-          <cell r="E69"/>
-          <cell r="F69"/>
-          <cell r="G69"/>
-          <cell r="H69"/>
-          <cell r="I69"/>
-          <cell r="J69"/>
-          <cell r="K69"/>
-          <cell r="L69"/>
-          <cell r="M69"/>
-          <cell r="N69"/>
-          <cell r="O69"/>
-          <cell r="P69"/>
-          <cell r="Q69"/>
-          <cell r="R69"/>
-          <cell r="S69"/>
-          <cell r="T69"/>
-          <cell r="U69"/>
-          <cell r="V69"/>
-          <cell r="W69"/>
-          <cell r="X69"/>
-        </row>
-        <row r="70">
-          <cell r="D70"/>
-          <cell r="E70"/>
-          <cell r="F70"/>
-          <cell r="G70"/>
-          <cell r="H70"/>
-          <cell r="I70"/>
-          <cell r="J70"/>
-          <cell r="K70"/>
-          <cell r="L70"/>
-          <cell r="M70"/>
-          <cell r="N70"/>
-          <cell r="O70"/>
-          <cell r="P70"/>
-          <cell r="Q70"/>
-          <cell r="R70"/>
-          <cell r="S70"/>
-          <cell r="T70"/>
-          <cell r="U70"/>
-          <cell r="V70"/>
-          <cell r="W70"/>
-          <cell r="X70"/>
-        </row>
-        <row r="71">
-          <cell r="D71"/>
-          <cell r="E71"/>
-          <cell r="F71"/>
-          <cell r="G71"/>
-          <cell r="H71"/>
-          <cell r="I71"/>
-          <cell r="J71"/>
-          <cell r="K71"/>
-          <cell r="L71"/>
-          <cell r="M71"/>
-          <cell r="N71"/>
-          <cell r="O71"/>
-          <cell r="P71"/>
-          <cell r="Q71"/>
-          <cell r="R71"/>
-          <cell r="S71"/>
-          <cell r="T71"/>
-          <cell r="U71"/>
-          <cell r="V71"/>
-          <cell r="W71"/>
-          <cell r="X71"/>
-        </row>
-        <row r="72">
-          <cell r="D72"/>
-          <cell r="E72"/>
-          <cell r="F72"/>
-          <cell r="G72"/>
-          <cell r="H72"/>
-          <cell r="I72"/>
-          <cell r="J72"/>
-          <cell r="K72"/>
-          <cell r="L72"/>
-          <cell r="M72"/>
-          <cell r="N72"/>
-          <cell r="O72"/>
-          <cell r="P72"/>
-          <cell r="Q72"/>
-          <cell r="R72"/>
-          <cell r="S72"/>
-          <cell r="T72"/>
-          <cell r="U72"/>
-          <cell r="V72"/>
-          <cell r="W72"/>
-          <cell r="X72"/>
-        </row>
-        <row r="73">
-          <cell r="D73"/>
-          <cell r="E73"/>
-          <cell r="F73"/>
-          <cell r="G73"/>
-          <cell r="H73"/>
-          <cell r="I73"/>
-          <cell r="J73"/>
-          <cell r="K73"/>
-          <cell r="L73"/>
-          <cell r="M73"/>
-          <cell r="N73"/>
-          <cell r="O73"/>
-          <cell r="P73"/>
-          <cell r="Q73"/>
-          <cell r="R73"/>
-          <cell r="S73"/>
-          <cell r="T73"/>
-          <cell r="U73"/>
-          <cell r="V73"/>
-          <cell r="W73"/>
-          <cell r="X73"/>
-        </row>
-        <row r="74">
-          <cell r="D74"/>
-          <cell r="E74"/>
-          <cell r="F74"/>
-          <cell r="G74"/>
-          <cell r="H74"/>
-          <cell r="I74"/>
-          <cell r="J74"/>
-          <cell r="K74"/>
-          <cell r="L74"/>
-          <cell r="M74"/>
-          <cell r="N74"/>
-          <cell r="O74"/>
-          <cell r="P74"/>
-          <cell r="Q74"/>
-          <cell r="R74"/>
-          <cell r="S74"/>
-          <cell r="T74"/>
-          <cell r="U74"/>
-          <cell r="V74"/>
-          <cell r="W74"/>
-          <cell r="X74"/>
-        </row>
-        <row r="75">
-          <cell r="D75"/>
-          <cell r="E75"/>
-          <cell r="F75"/>
-          <cell r="G75"/>
-          <cell r="H75"/>
-          <cell r="I75"/>
-          <cell r="J75"/>
-          <cell r="K75"/>
-          <cell r="L75"/>
-          <cell r="M75"/>
-          <cell r="N75"/>
-          <cell r="O75"/>
-          <cell r="P75"/>
-          <cell r="Q75"/>
-          <cell r="R75"/>
-          <cell r="S75"/>
-          <cell r="T75"/>
-          <cell r="U75"/>
-          <cell r="V75"/>
-          <cell r="W75"/>
-          <cell r="X75"/>
-        </row>
-        <row r="76">
-          <cell r="D76"/>
-          <cell r="E76"/>
-          <cell r="F76"/>
-          <cell r="G76"/>
-          <cell r="H76"/>
-          <cell r="I76"/>
-          <cell r="J76"/>
-          <cell r="K76"/>
-          <cell r="L76"/>
-          <cell r="M76"/>
-          <cell r="N76"/>
-          <cell r="O76"/>
-          <cell r="P76"/>
-          <cell r="Q76"/>
-          <cell r="R76"/>
-          <cell r="S76"/>
-          <cell r="T76"/>
-          <cell r="U76"/>
-          <cell r="V76"/>
-          <cell r="W76"/>
-          <cell r="X76"/>
-        </row>
-        <row r="77">
-          <cell r="D77"/>
-          <cell r="E77"/>
-          <cell r="F77"/>
-          <cell r="G77"/>
-          <cell r="H77"/>
-          <cell r="I77"/>
-          <cell r="J77"/>
-          <cell r="K77"/>
-          <cell r="L77"/>
-          <cell r="M77"/>
-          <cell r="N77"/>
-          <cell r="O77"/>
-          <cell r="P77"/>
-          <cell r="Q77"/>
-          <cell r="R77"/>
-          <cell r="S77"/>
-          <cell r="T77"/>
-          <cell r="U77"/>
-          <cell r="V77"/>
-          <cell r="W77"/>
-          <cell r="X77"/>
-        </row>
-        <row r="78">
-          <cell r="D78"/>
-          <cell r="E78"/>
-          <cell r="F78"/>
-          <cell r="G78"/>
-          <cell r="H78"/>
-          <cell r="I78"/>
-          <cell r="J78"/>
-          <cell r="K78"/>
-          <cell r="L78"/>
-          <cell r="M78"/>
-          <cell r="N78"/>
-          <cell r="O78"/>
-          <cell r="P78"/>
-          <cell r="Q78"/>
-          <cell r="R78"/>
-          <cell r="S78"/>
-          <cell r="T78"/>
-          <cell r="U78"/>
-          <cell r="V78"/>
-          <cell r="W78"/>
-          <cell r="X78"/>
-        </row>
-        <row r="79">
-          <cell r="D79"/>
-          <cell r="E79"/>
-          <cell r="F79"/>
-          <cell r="G79"/>
-          <cell r="H79"/>
-          <cell r="I79"/>
-          <cell r="J79"/>
-          <cell r="K79"/>
-          <cell r="L79"/>
-          <cell r="M79"/>
-          <cell r="N79"/>
-          <cell r="O79"/>
-          <cell r="P79"/>
-          <cell r="Q79"/>
-          <cell r="R79"/>
-          <cell r="S79"/>
-          <cell r="T79"/>
-          <cell r="U79"/>
-          <cell r="V79"/>
-          <cell r="W79"/>
-          <cell r="X79"/>
-        </row>
-        <row r="80">
-          <cell r="D80"/>
-          <cell r="E80"/>
-          <cell r="F80"/>
-          <cell r="G80"/>
-          <cell r="H80"/>
-          <cell r="I80"/>
-          <cell r="J80"/>
-          <cell r="K80"/>
-          <cell r="L80"/>
-          <cell r="M80"/>
-          <cell r="N80"/>
-          <cell r="O80"/>
-          <cell r="P80"/>
-          <cell r="Q80"/>
-          <cell r="R80"/>
-          <cell r="S80"/>
-          <cell r="T80"/>
-          <cell r="U80"/>
-          <cell r="V80"/>
-          <cell r="W80"/>
-          <cell r="X80"/>
-        </row>
-        <row r="81">
-          <cell r="D81"/>
-          <cell r="E81"/>
-          <cell r="F81"/>
-          <cell r="G81"/>
-          <cell r="H81"/>
-          <cell r="I81"/>
-          <cell r="J81"/>
-          <cell r="K81"/>
-          <cell r="L81"/>
-          <cell r="M81"/>
-          <cell r="N81"/>
-          <cell r="O81"/>
-          <cell r="P81"/>
-          <cell r="Q81"/>
-          <cell r="R81"/>
-          <cell r="S81"/>
-          <cell r="T81"/>
-          <cell r="U81"/>
-          <cell r="V81"/>
-          <cell r="W81"/>
-          <cell r="X81"/>
-        </row>
-        <row r="82">
-          <cell r="D82"/>
-          <cell r="E82"/>
-          <cell r="F82"/>
-          <cell r="G82"/>
-          <cell r="H82"/>
-          <cell r="I82"/>
-          <cell r="J82"/>
-          <cell r="K82"/>
-          <cell r="L82"/>
-          <cell r="M82"/>
-          <cell r="N82"/>
-          <cell r="O82"/>
-          <cell r="P82"/>
-          <cell r="Q82"/>
-          <cell r="R82"/>
-          <cell r="S82"/>
-          <cell r="T82"/>
-          <cell r="U82"/>
-          <cell r="V82"/>
-          <cell r="W82"/>
-          <cell r="X82"/>
-        </row>
-        <row r="83">
-          <cell r="D83"/>
-          <cell r="E83"/>
-          <cell r="F83"/>
-          <cell r="G83"/>
-          <cell r="H83"/>
-          <cell r="I83"/>
-          <cell r="J83"/>
-          <cell r="K83"/>
-          <cell r="L83"/>
-          <cell r="M83"/>
-          <cell r="N83"/>
-          <cell r="O83"/>
-          <cell r="P83"/>
-          <cell r="Q83"/>
-          <cell r="R83"/>
-          <cell r="S83"/>
-          <cell r="T83"/>
-          <cell r="U83"/>
-          <cell r="V83"/>
-          <cell r="W83"/>
-          <cell r="X83"/>
-        </row>
-        <row r="84">
-          <cell r="D84"/>
-          <cell r="E84"/>
-          <cell r="F84"/>
-          <cell r="G84"/>
-          <cell r="H84"/>
-          <cell r="I84"/>
-          <cell r="J84"/>
-          <cell r="K84"/>
-          <cell r="L84"/>
-          <cell r="M84"/>
-          <cell r="N84"/>
-          <cell r="O84"/>
-          <cell r="P84"/>
-          <cell r="Q84"/>
-          <cell r="R84"/>
-          <cell r="S84"/>
-          <cell r="T84"/>
-          <cell r="U84"/>
-          <cell r="V84"/>
-          <cell r="W84"/>
-          <cell r="X84"/>
-        </row>
-        <row r="85">
-          <cell r="D85"/>
-          <cell r="E85"/>
-          <cell r="F85"/>
-          <cell r="G85"/>
-          <cell r="H85"/>
-          <cell r="I85"/>
-          <cell r="J85"/>
-          <cell r="K85"/>
-          <cell r="L85"/>
-          <cell r="M85"/>
-          <cell r="N85"/>
-          <cell r="O85"/>
-          <cell r="P85"/>
-          <cell r="Q85"/>
-          <cell r="R85"/>
-          <cell r="S85"/>
-          <cell r="T85"/>
-          <cell r="U85"/>
-          <cell r="V85"/>
-          <cell r="W85"/>
-          <cell r="X85"/>
-        </row>
-        <row r="86">
-          <cell r="D86"/>
-          <cell r="E86"/>
-          <cell r="F86"/>
-          <cell r="G86"/>
-          <cell r="H86"/>
-          <cell r="I86"/>
-          <cell r="J86"/>
-          <cell r="K86"/>
-          <cell r="L86"/>
-          <cell r="M86"/>
-          <cell r="N86"/>
-          <cell r="O86"/>
-          <cell r="P86"/>
-          <cell r="Q86"/>
-          <cell r="R86"/>
-          <cell r="S86"/>
-          <cell r="T86"/>
-          <cell r="U86"/>
-          <cell r="V86"/>
-          <cell r="W86"/>
-          <cell r="X86"/>
-        </row>
-        <row r="87">
-          <cell r="D87"/>
-          <cell r="E87"/>
-          <cell r="F87"/>
-          <cell r="G87"/>
-          <cell r="H87"/>
-          <cell r="I87"/>
-          <cell r="J87"/>
-          <cell r="K87"/>
-          <cell r="L87"/>
-          <cell r="M87"/>
-          <cell r="N87"/>
-          <cell r="O87"/>
-          <cell r="P87"/>
-          <cell r="Q87"/>
-          <cell r="R87"/>
-          <cell r="S87"/>
-          <cell r="T87"/>
-          <cell r="U87"/>
-          <cell r="V87"/>
-          <cell r="W87"/>
-          <cell r="X87"/>
-        </row>
-        <row r="88">
-          <cell r="D88"/>
-          <cell r="E88"/>
-          <cell r="F88"/>
-          <cell r="G88"/>
-          <cell r="H88"/>
-          <cell r="I88"/>
-          <cell r="J88"/>
-          <cell r="K88"/>
-          <cell r="L88"/>
-          <cell r="M88"/>
-          <cell r="N88"/>
-          <cell r="O88"/>
-          <cell r="P88"/>
-          <cell r="Q88"/>
-          <cell r="R88"/>
-          <cell r="S88"/>
-          <cell r="T88"/>
-          <cell r="U88"/>
-          <cell r="V88"/>
-          <cell r="W88"/>
-          <cell r="X88"/>
-        </row>
-        <row r="89">
-          <cell r="D89"/>
-          <cell r="E89"/>
-          <cell r="F89"/>
-          <cell r="G89"/>
-          <cell r="H89"/>
-          <cell r="I89"/>
-          <cell r="J89"/>
-          <cell r="K89"/>
-          <cell r="L89"/>
-          <cell r="M89"/>
-          <cell r="N89"/>
-          <cell r="O89"/>
-          <cell r="P89"/>
-          <cell r="Q89"/>
-          <cell r="R89"/>
-          <cell r="S89"/>
-          <cell r="T89"/>
-          <cell r="U89"/>
-          <cell r="V89"/>
-          <cell r="W89"/>
-          <cell r="X89"/>
-        </row>
-        <row r="90">
-          <cell r="D90"/>
-          <cell r="E90"/>
-          <cell r="F90"/>
-          <cell r="G90"/>
-          <cell r="H90"/>
-          <cell r="I90"/>
-          <cell r="J90"/>
-          <cell r="K90"/>
-          <cell r="L90"/>
-          <cell r="M90"/>
-          <cell r="N90"/>
-          <cell r="O90"/>
-          <cell r="P90"/>
-          <cell r="Q90"/>
-          <cell r="R90"/>
-          <cell r="S90"/>
-          <cell r="T90"/>
-          <cell r="U90"/>
-          <cell r="V90"/>
-          <cell r="W90"/>
-          <cell r="X90"/>
-        </row>
-        <row r="91">
-          <cell r="D91"/>
-          <cell r="E91"/>
-          <cell r="F91"/>
-          <cell r="G91"/>
-          <cell r="H91"/>
-          <cell r="I91"/>
-          <cell r="J91"/>
-          <cell r="K91"/>
-          <cell r="L91"/>
-          <cell r="M91"/>
-          <cell r="N91"/>
-          <cell r="O91"/>
-          <cell r="P91"/>
-          <cell r="Q91"/>
-          <cell r="R91"/>
-          <cell r="S91"/>
-          <cell r="T91"/>
-          <cell r="U91"/>
-          <cell r="V91"/>
-          <cell r="W91"/>
-          <cell r="X91"/>
-        </row>
-        <row r="92">
-          <cell r="D92"/>
-          <cell r="E92"/>
-          <cell r="F92"/>
-          <cell r="G92"/>
-          <cell r="H92"/>
-          <cell r="I92"/>
-          <cell r="J92"/>
-          <cell r="K92"/>
-          <cell r="L92"/>
-          <cell r="M92"/>
-          <cell r="N92"/>
-          <cell r="O92"/>
-          <cell r="P92"/>
-          <cell r="Q92"/>
-          <cell r="R92"/>
-          <cell r="S92"/>
-          <cell r="T92"/>
-          <cell r="U92"/>
-          <cell r="V92"/>
-          <cell r="W92"/>
-          <cell r="X92"/>
-        </row>
-        <row r="93">
-          <cell r="D93"/>
-          <cell r="E93"/>
-          <cell r="F93"/>
-          <cell r="G93"/>
-          <cell r="H93"/>
-          <cell r="I93"/>
-          <cell r="J93"/>
-          <cell r="K93"/>
-          <cell r="L93"/>
-          <cell r="M93"/>
-          <cell r="N93"/>
-          <cell r="O93"/>
-          <cell r="P93"/>
-          <cell r="Q93"/>
-          <cell r="R93"/>
-          <cell r="S93"/>
-          <cell r="T93"/>
-          <cell r="U93"/>
-          <cell r="V93"/>
-          <cell r="W93"/>
-          <cell r="X93"/>
-        </row>
-        <row r="94">
-          <cell r="D94"/>
-          <cell r="E94"/>
-          <cell r="F94"/>
-          <cell r="G94"/>
-          <cell r="H94"/>
-          <cell r="I94"/>
-          <cell r="J94"/>
-          <cell r="K94"/>
-          <cell r="L94"/>
-          <cell r="M94"/>
-          <cell r="N94"/>
-          <cell r="O94"/>
-          <cell r="P94"/>
-          <cell r="Q94"/>
-          <cell r="R94"/>
-          <cell r="S94"/>
-          <cell r="T94"/>
-          <cell r="U94"/>
-          <cell r="V94"/>
-          <cell r="W94"/>
-          <cell r="X94"/>
-        </row>
-        <row r="95">
-          <cell r="D95"/>
-          <cell r="E95"/>
-          <cell r="F95"/>
-          <cell r="G95"/>
-          <cell r="H95"/>
-          <cell r="I95"/>
-          <cell r="J95"/>
-          <cell r="K95"/>
-          <cell r="L95"/>
-          <cell r="M95"/>
-          <cell r="N95"/>
-          <cell r="O95"/>
-          <cell r="P95"/>
-          <cell r="Q95"/>
-          <cell r="R95"/>
-          <cell r="S95"/>
-          <cell r="T95"/>
-          <cell r="U95"/>
-          <cell r="V95"/>
-          <cell r="W95"/>
-          <cell r="X95"/>
-        </row>
-        <row r="96">
-          <cell r="D96"/>
-          <cell r="E96"/>
-          <cell r="F96"/>
-          <cell r="G96"/>
-          <cell r="H96"/>
-          <cell r="I96"/>
-          <cell r="J96"/>
-          <cell r="K96"/>
-          <cell r="L96"/>
-          <cell r="M96"/>
-          <cell r="N96"/>
-          <cell r="O96"/>
-          <cell r="P96"/>
-          <cell r="Q96"/>
-          <cell r="R96"/>
-          <cell r="S96"/>
-          <cell r="T96"/>
-          <cell r="U96"/>
-          <cell r="V96"/>
-          <cell r="W96"/>
-          <cell r="X96"/>
-        </row>
-        <row r="97">
-          <cell r="D97"/>
-          <cell r="E97"/>
-          <cell r="F97"/>
-          <cell r="G97"/>
-          <cell r="H97"/>
-          <cell r="I97"/>
-          <cell r="J97"/>
-          <cell r="K97"/>
-          <cell r="L97"/>
-          <cell r="M97"/>
-          <cell r="N97"/>
-          <cell r="O97"/>
-          <cell r="P97"/>
-          <cell r="Q97"/>
-          <cell r="R97"/>
-          <cell r="S97"/>
-          <cell r="T97"/>
-          <cell r="U97"/>
-          <cell r="V97"/>
-          <cell r="W97"/>
-          <cell r="X97"/>
-        </row>
-        <row r="98">
-          <cell r="D98"/>
-          <cell r="E98"/>
-          <cell r="F98"/>
-          <cell r="G98"/>
-          <cell r="H98"/>
-          <cell r="I98"/>
-          <cell r="J98"/>
-          <cell r="K98"/>
-          <cell r="L98"/>
-          <cell r="M98"/>
-          <cell r="N98"/>
-          <cell r="O98"/>
-          <cell r="P98"/>
-          <cell r="Q98"/>
-          <cell r="R98"/>
-          <cell r="S98"/>
-          <cell r="T98"/>
-          <cell r="U98"/>
-          <cell r="V98"/>
-          <cell r="W98"/>
-          <cell r="X98"/>
-        </row>
-        <row r="99">
-          <cell r="D99"/>
-          <cell r="E99"/>
-          <cell r="F99"/>
-          <cell r="G99"/>
-          <cell r="H99"/>
-          <cell r="I99"/>
-          <cell r="J99"/>
-          <cell r="K99"/>
-          <cell r="L99"/>
-          <cell r="M99"/>
-          <cell r="N99"/>
-          <cell r="O99"/>
-          <cell r="P99"/>
-          <cell r="Q99"/>
-          <cell r="R99"/>
-          <cell r="S99"/>
-          <cell r="T99"/>
-          <cell r="U99"/>
-          <cell r="V99"/>
-          <cell r="W99"/>
-          <cell r="X99"/>
-        </row>
-        <row r="100">
-          <cell r="D100"/>
-          <cell r="E100"/>
-          <cell r="F100"/>
-          <cell r="G100"/>
-          <cell r="H100"/>
-          <cell r="I100"/>
-          <cell r="J100"/>
-          <cell r="K100"/>
-          <cell r="L100"/>
-          <cell r="M100"/>
-          <cell r="N100"/>
-          <cell r="O100"/>
-          <cell r="P100"/>
-          <cell r="Q100"/>
-          <cell r="R100"/>
-          <cell r="S100"/>
-          <cell r="T100"/>
-          <cell r="U100"/>
-          <cell r="V100"/>
-          <cell r="W100"/>
-          <cell r="X100"/>
-        </row>
-        <row r="101">
-          <cell r="D101"/>
-          <cell r="E101"/>
-          <cell r="F101"/>
-          <cell r="G101"/>
-          <cell r="H101"/>
-          <cell r="I101"/>
-          <cell r="J101"/>
-          <cell r="K101"/>
-          <cell r="L101"/>
-          <cell r="M101"/>
-          <cell r="N101"/>
-          <cell r="O101"/>
-          <cell r="P101"/>
-          <cell r="Q101"/>
-          <cell r="R101"/>
-          <cell r="S101"/>
-          <cell r="T101"/>
-          <cell r="U101"/>
-          <cell r="V101"/>
-          <cell r="W101"/>
-          <cell r="X101"/>
-        </row>
-        <row r="102">
-          <cell r="D102"/>
-          <cell r="E102"/>
-          <cell r="F102"/>
-          <cell r="G102"/>
-          <cell r="H102"/>
-          <cell r="I102"/>
-          <cell r="J102"/>
-          <cell r="K102"/>
-          <cell r="L102"/>
-          <cell r="M102"/>
-          <cell r="N102"/>
-          <cell r="O102"/>
-          <cell r="P102"/>
-          <cell r="Q102"/>
-          <cell r="R102"/>
-          <cell r="S102"/>
-          <cell r="T102"/>
-          <cell r="U102"/>
-          <cell r="V102"/>
-          <cell r="W102"/>
-          <cell r="X102"/>
-        </row>
-        <row r="103">
-          <cell r="D103"/>
-          <cell r="E103"/>
-          <cell r="F103"/>
-          <cell r="G103"/>
-          <cell r="H103"/>
-          <cell r="I103"/>
-          <cell r="J103"/>
-          <cell r="K103"/>
-          <cell r="L103"/>
-          <cell r="M103"/>
-          <cell r="N103"/>
-          <cell r="O103"/>
-          <cell r="P103"/>
-          <cell r="Q103"/>
-          <cell r="R103"/>
-          <cell r="S103"/>
-          <cell r="T103"/>
-          <cell r="U103"/>
-          <cell r="V103"/>
-          <cell r="W103"/>
-          <cell r="X103"/>
-        </row>
-        <row r="104">
-          <cell r="D104"/>
-          <cell r="E104"/>
-          <cell r="F104"/>
-          <cell r="G104"/>
-          <cell r="H104"/>
-          <cell r="I104"/>
-          <cell r="J104"/>
-          <cell r="K104"/>
-          <cell r="L104"/>
-          <cell r="M104"/>
-          <cell r="N104"/>
-          <cell r="O104"/>
-          <cell r="P104"/>
-          <cell r="Q104"/>
-          <cell r="R104"/>
-          <cell r="S104"/>
-          <cell r="T104"/>
-          <cell r="U104"/>
-          <cell r="V104"/>
-          <cell r="W104"/>
-          <cell r="X104"/>
-        </row>
-        <row r="105">
-          <cell r="D105"/>
-          <cell r="E105"/>
-          <cell r="F105"/>
-          <cell r="G105"/>
-          <cell r="H105"/>
-          <cell r="I105"/>
-          <cell r="J105"/>
-          <cell r="K105"/>
-          <cell r="L105"/>
-          <cell r="M105"/>
-          <cell r="N105"/>
-          <cell r="O105"/>
-          <cell r="P105"/>
-          <cell r="Q105"/>
-          <cell r="R105"/>
-          <cell r="S105"/>
-          <cell r="T105"/>
-          <cell r="U105"/>
-          <cell r="V105"/>
-          <cell r="W105"/>
-          <cell r="X105"/>
-        </row>
-        <row r="106">
-          <cell r="D106"/>
-          <cell r="E106"/>
-          <cell r="F106"/>
-          <cell r="G106"/>
-          <cell r="H106"/>
-          <cell r="I106"/>
-          <cell r="J106"/>
-          <cell r="K106"/>
-          <cell r="L106"/>
-          <cell r="M106"/>
-          <cell r="N106"/>
-          <cell r="O106"/>
-          <cell r="P106"/>
-          <cell r="Q106"/>
-          <cell r="R106"/>
-          <cell r="S106"/>
-          <cell r="T106"/>
-          <cell r="U106"/>
-          <cell r="V106"/>
-          <cell r="W106"/>
-          <cell r="X106"/>
-        </row>
-        <row r="107">
-          <cell r="D107"/>
-          <cell r="E107"/>
-          <cell r="F107"/>
-          <cell r="G107"/>
-          <cell r="H107"/>
-          <cell r="I107"/>
-          <cell r="J107"/>
-          <cell r="K107"/>
-          <cell r="L107"/>
-          <cell r="M107"/>
-          <cell r="N107"/>
-          <cell r="O107"/>
-          <cell r="P107"/>
-          <cell r="Q107"/>
-          <cell r="R107"/>
-          <cell r="S107"/>
-          <cell r="T107"/>
-          <cell r="U107"/>
-          <cell r="V107"/>
-          <cell r="W107"/>
-          <cell r="X107"/>
-        </row>
-        <row r="108">
-          <cell r="D108"/>
-          <cell r="E108"/>
-          <cell r="F108"/>
-          <cell r="G108"/>
-          <cell r="H108"/>
-          <cell r="I108"/>
-          <cell r="J108"/>
-          <cell r="K108"/>
-          <cell r="L108"/>
-          <cell r="M108"/>
-          <cell r="N108"/>
-          <cell r="O108"/>
-          <cell r="P108"/>
-          <cell r="Q108"/>
-          <cell r="R108"/>
-          <cell r="S108"/>
-          <cell r="T108"/>
-          <cell r="U108"/>
-          <cell r="V108"/>
-          <cell r="W108"/>
-          <cell r="X108"/>
-        </row>
-        <row r="109">
-          <cell r="D109"/>
-          <cell r="E109"/>
-          <cell r="F109"/>
-          <cell r="G109"/>
-          <cell r="H109"/>
-          <cell r="I109"/>
-          <cell r="J109"/>
-          <cell r="K109"/>
-          <cell r="L109"/>
-          <cell r="M109"/>
-          <cell r="N109"/>
-          <cell r="O109"/>
-          <cell r="P109"/>
-          <cell r="Q109"/>
-          <cell r="R109"/>
-          <cell r="S109"/>
-          <cell r="T109"/>
-          <cell r="U109"/>
-          <cell r="V109"/>
-          <cell r="W109"/>
-          <cell r="X109"/>
-        </row>
-        <row r="110">
-          <cell r="D110"/>
-          <cell r="E110"/>
-          <cell r="F110"/>
-          <cell r="G110"/>
-          <cell r="H110"/>
-          <cell r="I110"/>
-          <cell r="J110"/>
-          <cell r="K110"/>
-          <cell r="L110"/>
-          <cell r="M110"/>
-          <cell r="N110"/>
-          <cell r="O110"/>
-          <cell r="P110"/>
-          <cell r="Q110"/>
-          <cell r="R110"/>
-          <cell r="S110"/>
-          <cell r="T110"/>
-          <cell r="U110"/>
-          <cell r="V110"/>
-          <cell r="W110"/>
-          <cell r="X110"/>
-        </row>
-        <row r="111">
-          <cell r="D111"/>
-          <cell r="E111"/>
-          <cell r="F111"/>
-          <cell r="G111"/>
-          <cell r="H111"/>
-          <cell r="I111"/>
-          <cell r="J111"/>
-          <cell r="K111"/>
-          <cell r="L111"/>
-          <cell r="M111"/>
-          <cell r="N111"/>
-          <cell r="O111"/>
-          <cell r="P111"/>
-          <cell r="Q111"/>
-          <cell r="R111"/>
-          <cell r="S111"/>
-          <cell r="T111"/>
-          <cell r="U111"/>
-          <cell r="V111"/>
-          <cell r="W111"/>
-          <cell r="X111"/>
-        </row>
-        <row r="112">
-          <cell r="D112"/>
-          <cell r="E112"/>
-          <cell r="F112"/>
-          <cell r="G112"/>
-          <cell r="H112"/>
-          <cell r="I112"/>
-          <cell r="J112"/>
-          <cell r="K112"/>
-          <cell r="L112"/>
-          <cell r="M112"/>
-          <cell r="N112"/>
-          <cell r="O112"/>
-          <cell r="P112"/>
-          <cell r="Q112"/>
-          <cell r="R112"/>
-          <cell r="S112"/>
-          <cell r="T112"/>
-          <cell r="U112"/>
-          <cell r="V112"/>
-          <cell r="W112"/>
-          <cell r="X112"/>
-        </row>
-        <row r="113">
-          <cell r="D113"/>
-          <cell r="E113"/>
-          <cell r="F113"/>
-          <cell r="G113"/>
-          <cell r="H113"/>
-          <cell r="I113"/>
-          <cell r="J113"/>
-          <cell r="K113"/>
-          <cell r="L113"/>
-          <cell r="M113"/>
-          <cell r="N113"/>
-          <cell r="O113"/>
-          <cell r="P113"/>
-          <cell r="Q113"/>
-          <cell r="R113"/>
-          <cell r="S113"/>
-          <cell r="T113"/>
-          <cell r="U113"/>
-          <cell r="V113"/>
-          <cell r="W113"/>
-          <cell r="X113"/>
-        </row>
-        <row r="114">
-          <cell r="D114"/>
-          <cell r="E114"/>
-          <cell r="F114"/>
-          <cell r="G114"/>
-          <cell r="H114"/>
-          <cell r="I114"/>
-          <cell r="J114"/>
-          <cell r="K114"/>
-          <cell r="L114"/>
-          <cell r="M114"/>
-          <cell r="N114"/>
-          <cell r="O114"/>
-          <cell r="P114"/>
-          <cell r="Q114"/>
-          <cell r="R114"/>
-          <cell r="S114"/>
-          <cell r="T114"/>
-          <cell r="U114"/>
-          <cell r="V114"/>
-          <cell r="W114"/>
-          <cell r="X114"/>
-        </row>
-        <row r="115">
-          <cell r="D115"/>
-          <cell r="E115"/>
-          <cell r="F115"/>
-          <cell r="G115"/>
-          <cell r="H115"/>
-          <cell r="I115"/>
-          <cell r="J115"/>
-          <cell r="K115"/>
-          <cell r="L115"/>
-          <cell r="M115"/>
-          <cell r="N115"/>
-          <cell r="O115"/>
-          <cell r="P115"/>
-          <cell r="Q115"/>
-          <cell r="R115"/>
-          <cell r="S115"/>
-          <cell r="T115"/>
-          <cell r="U115"/>
-          <cell r="V115"/>
-          <cell r="W115"/>
-          <cell r="X115"/>
-        </row>
-        <row r="116">
-          <cell r="D116"/>
-          <cell r="E116"/>
-          <cell r="F116"/>
-          <cell r="G116"/>
-          <cell r="H116"/>
-          <cell r="I116"/>
-          <cell r="J116"/>
-          <cell r="K116"/>
-          <cell r="L116"/>
-          <cell r="M116"/>
-          <cell r="N116"/>
-          <cell r="O116"/>
-          <cell r="P116"/>
-          <cell r="Q116"/>
-          <cell r="R116"/>
-          <cell r="S116"/>
-          <cell r="T116"/>
-          <cell r="U116"/>
-          <cell r="V116"/>
-          <cell r="W116"/>
-          <cell r="X116"/>
-        </row>
-        <row r="117">
-          <cell r="D117"/>
-          <cell r="E117"/>
-          <cell r="F117"/>
-          <cell r="G117"/>
-          <cell r="H117"/>
-          <cell r="I117"/>
-          <cell r="J117"/>
-          <cell r="K117"/>
-          <cell r="L117"/>
-          <cell r="M117"/>
-          <cell r="N117"/>
-          <cell r="O117"/>
-          <cell r="P117"/>
-          <cell r="Q117"/>
-          <cell r="R117"/>
-          <cell r="S117"/>
-          <cell r="T117"/>
-          <cell r="U117"/>
-          <cell r="V117"/>
-          <cell r="W117"/>
-          <cell r="X117"/>
-        </row>
-        <row r="118">
-          <cell r="D118"/>
-          <cell r="E118"/>
-          <cell r="F118"/>
-          <cell r="G118"/>
-          <cell r="H118"/>
-          <cell r="I118"/>
-          <cell r="J118"/>
-          <cell r="K118"/>
-          <cell r="L118"/>
-          <cell r="M118"/>
-          <cell r="N118"/>
-          <cell r="O118"/>
-          <cell r="P118"/>
-          <cell r="Q118"/>
-          <cell r="R118"/>
-          <cell r="S118"/>
-          <cell r="T118"/>
-          <cell r="U118"/>
-          <cell r="V118"/>
-          <cell r="W118"/>
-          <cell r="X118"/>
-        </row>
-        <row r="119">
-          <cell r="D119"/>
-          <cell r="E119"/>
-          <cell r="F119"/>
-          <cell r="G119"/>
-          <cell r="H119"/>
-          <cell r="I119"/>
-          <cell r="J119"/>
-          <cell r="K119"/>
-          <cell r="L119"/>
-          <cell r="M119"/>
-          <cell r="N119"/>
-          <cell r="O119"/>
-          <cell r="P119"/>
-          <cell r="Q119"/>
-          <cell r="R119"/>
-          <cell r="S119"/>
-          <cell r="T119"/>
-          <cell r="U119"/>
-          <cell r="V119"/>
-          <cell r="W119"/>
-          <cell r="X119"/>
-        </row>
-        <row r="120">
-          <cell r="D120"/>
-          <cell r="E120"/>
-          <cell r="F120"/>
-          <cell r="G120"/>
-          <cell r="H120"/>
-          <cell r="I120"/>
-          <cell r="J120"/>
-          <cell r="K120"/>
-          <cell r="L120"/>
-          <cell r="M120"/>
-          <cell r="N120"/>
-          <cell r="O120"/>
-          <cell r="P120"/>
-          <cell r="Q120"/>
-          <cell r="R120"/>
-          <cell r="S120"/>
-          <cell r="T120"/>
-          <cell r="U120"/>
-          <cell r="V120"/>
-          <cell r="W120"/>
-          <cell r="X120"/>
-        </row>
-        <row r="121">
-          <cell r="D121"/>
-          <cell r="E121"/>
-          <cell r="F121"/>
-          <cell r="G121"/>
-          <cell r="H121"/>
-          <cell r="I121"/>
-          <cell r="J121"/>
-          <cell r="K121"/>
-          <cell r="L121"/>
-          <cell r="M121"/>
-          <cell r="N121"/>
-          <cell r="O121"/>
-          <cell r="P121"/>
-          <cell r="Q121"/>
-          <cell r="R121"/>
-          <cell r="S121"/>
-          <cell r="T121"/>
-          <cell r="U121"/>
-          <cell r="V121"/>
-          <cell r="W121"/>
-          <cell r="X121"/>
-        </row>
-        <row r="122">
-          <cell r="D122"/>
-          <cell r="E122"/>
-          <cell r="F122"/>
-          <cell r="G122"/>
-          <cell r="H122"/>
-          <cell r="I122"/>
-          <cell r="J122"/>
-          <cell r="K122"/>
-          <cell r="L122"/>
-          <cell r="M122"/>
-          <cell r="N122"/>
-          <cell r="O122"/>
-          <cell r="P122"/>
-          <cell r="Q122"/>
-          <cell r="R122"/>
-          <cell r="S122"/>
-          <cell r="T122"/>
-          <cell r="U122"/>
-          <cell r="V122"/>
-          <cell r="W122"/>
-          <cell r="X122"/>
-        </row>
-        <row r="123">
-          <cell r="D123"/>
-          <cell r="E123"/>
-          <cell r="F123"/>
-          <cell r="G123"/>
-          <cell r="H123"/>
-          <cell r="I123"/>
-          <cell r="J123"/>
-          <cell r="K123"/>
-          <cell r="L123"/>
-          <cell r="M123"/>
-          <cell r="N123"/>
-          <cell r="O123"/>
-          <cell r="P123"/>
-          <cell r="Q123"/>
-          <cell r="R123"/>
-          <cell r="S123"/>
-          <cell r="T123"/>
-          <cell r="U123"/>
-          <cell r="V123"/>
-          <cell r="W123"/>
-          <cell r="X123"/>
-        </row>
-        <row r="124">
-          <cell r="D124"/>
-          <cell r="E124"/>
-          <cell r="F124"/>
-          <cell r="G124"/>
-          <cell r="H124"/>
-          <cell r="I124"/>
-          <cell r="J124"/>
-          <cell r="K124"/>
-          <cell r="L124"/>
-          <cell r="M124"/>
-          <cell r="N124"/>
-          <cell r="O124"/>
-          <cell r="P124"/>
-          <cell r="Q124"/>
-          <cell r="R124"/>
-          <cell r="S124"/>
-          <cell r="T124"/>
-          <cell r="U124"/>
-          <cell r="V124"/>
-          <cell r="W124"/>
-          <cell r="X124"/>
-        </row>
-        <row r="125">
-          <cell r="D125"/>
-          <cell r="E125"/>
-          <cell r="F125"/>
-          <cell r="G125"/>
-          <cell r="H125"/>
-          <cell r="I125"/>
-          <cell r="J125"/>
-          <cell r="K125"/>
-          <cell r="L125"/>
-          <cell r="M125"/>
-          <cell r="N125"/>
-          <cell r="O125"/>
-          <cell r="P125"/>
-          <cell r="Q125"/>
-          <cell r="R125"/>
-          <cell r="S125"/>
-          <cell r="T125"/>
-          <cell r="U125"/>
-          <cell r="V125"/>
-          <cell r="W125"/>
-          <cell r="X125"/>
-        </row>
-        <row r="126">
-          <cell r="D126"/>
-          <cell r="E126"/>
-          <cell r="F126"/>
-          <cell r="G126"/>
-          <cell r="H126"/>
-          <cell r="I126"/>
-          <cell r="J126"/>
-          <cell r="K126"/>
-          <cell r="L126"/>
-          <cell r="M126"/>
-          <cell r="N126"/>
-          <cell r="O126"/>
-          <cell r="P126"/>
-          <cell r="Q126"/>
-          <cell r="R126"/>
-          <cell r="S126"/>
-          <cell r="T126"/>
-          <cell r="U126"/>
-          <cell r="V126"/>
-          <cell r="W126"/>
-          <cell r="X126"/>
-        </row>
-        <row r="127">
-          <cell r="D127"/>
-          <cell r="E127"/>
-          <cell r="F127"/>
-          <cell r="G127"/>
-          <cell r="H127"/>
-          <cell r="I127"/>
-          <cell r="J127"/>
-          <cell r="K127"/>
-          <cell r="L127"/>
-          <cell r="M127"/>
-          <cell r="N127"/>
-          <cell r="O127"/>
-          <cell r="P127"/>
-          <cell r="Q127"/>
-          <cell r="R127"/>
-          <cell r="S127"/>
-          <cell r="T127"/>
-          <cell r="U127"/>
-          <cell r="V127"/>
-          <cell r="W127"/>
-          <cell r="X127"/>
-        </row>
-        <row r="128">
-          <cell r="D128"/>
-          <cell r="E128"/>
-          <cell r="F128"/>
-          <cell r="G128"/>
-          <cell r="H128"/>
-          <cell r="I128"/>
-          <cell r="J128"/>
-          <cell r="K128"/>
-          <cell r="L128"/>
-          <cell r="M128"/>
-          <cell r="N128"/>
-          <cell r="O128"/>
-          <cell r="P128"/>
-          <cell r="Q128"/>
-          <cell r="R128"/>
-          <cell r="S128"/>
-          <cell r="T128"/>
-          <cell r="U128"/>
-          <cell r="V128"/>
-          <cell r="W128"/>
-          <cell r="X128"/>
-        </row>
-        <row r="129">
-          <cell r="D129"/>
-          <cell r="E129"/>
-          <cell r="F129"/>
-          <cell r="G129"/>
-          <cell r="H129"/>
-          <cell r="I129"/>
-          <cell r="J129"/>
-          <cell r="K129"/>
-          <cell r="L129"/>
-          <cell r="M129"/>
-          <cell r="N129"/>
-          <cell r="O129"/>
-          <cell r="P129"/>
-          <cell r="Q129"/>
-          <cell r="R129"/>
-          <cell r="S129"/>
-          <cell r="T129"/>
-          <cell r="U129"/>
-          <cell r="V129"/>
-          <cell r="W129"/>
-          <cell r="X129"/>
-        </row>
-        <row r="130">
-          <cell r="D130"/>
-          <cell r="E130"/>
-          <cell r="F130"/>
-          <cell r="G130"/>
-          <cell r="H130"/>
-          <cell r="I130"/>
-          <cell r="J130"/>
-          <cell r="K130"/>
-          <cell r="L130"/>
-          <cell r="M130"/>
-          <cell r="N130"/>
-          <cell r="O130"/>
-          <cell r="P130"/>
-          <cell r="Q130"/>
-          <cell r="R130"/>
-          <cell r="S130"/>
-          <cell r="T130"/>
-          <cell r="U130"/>
-          <cell r="V130"/>
-          <cell r="W130"/>
-          <cell r="X130"/>
-        </row>
-        <row r="131">
-          <cell r="D131"/>
-          <cell r="E131"/>
-          <cell r="F131"/>
-          <cell r="G131"/>
-          <cell r="H131"/>
-          <cell r="I131"/>
-          <cell r="J131"/>
-          <cell r="K131"/>
-          <cell r="L131"/>
-          <cell r="M131"/>
-          <cell r="N131"/>
-          <cell r="O131"/>
-          <cell r="P131"/>
-          <cell r="Q131"/>
-          <cell r="R131"/>
-          <cell r="S131"/>
-          <cell r="T131"/>
-          <cell r="U131"/>
-          <cell r="V131"/>
-          <cell r="W131"/>
-          <cell r="X131"/>
-        </row>
-        <row r="132">
-          <cell r="D132"/>
-          <cell r="E132"/>
-          <cell r="F132"/>
-          <cell r="G132"/>
-          <cell r="H132"/>
-          <cell r="I132"/>
-          <cell r="J132"/>
-          <cell r="K132"/>
-          <cell r="L132"/>
-          <cell r="M132"/>
-          <cell r="N132"/>
-          <cell r="O132"/>
-          <cell r="P132"/>
-          <cell r="Q132"/>
-          <cell r="R132"/>
-          <cell r="S132"/>
-          <cell r="T132"/>
-          <cell r="U132"/>
-          <cell r="V132"/>
-          <cell r="W132"/>
-          <cell r="X132"/>
-        </row>
-        <row r="133">
-          <cell r="D133"/>
-          <cell r="E133"/>
-          <cell r="F133"/>
-          <cell r="G133"/>
-          <cell r="H133"/>
-          <cell r="I133"/>
-          <cell r="J133"/>
-          <cell r="K133"/>
-          <cell r="L133"/>
-          <cell r="M133"/>
-          <cell r="N133"/>
-          <cell r="O133"/>
-          <cell r="P133"/>
-          <cell r="Q133"/>
-          <cell r="R133"/>
-          <cell r="S133"/>
-          <cell r="T133"/>
-          <cell r="U133"/>
-          <cell r="V133"/>
-          <cell r="W133"/>
-          <cell r="X133"/>
-        </row>
-        <row r="134">
-          <cell r="D134"/>
-          <cell r="E134"/>
-          <cell r="F134"/>
-          <cell r="G134"/>
-          <cell r="H134"/>
-          <cell r="I134"/>
-          <cell r="J134"/>
-          <cell r="K134"/>
-          <cell r="L134"/>
-          <cell r="M134"/>
-          <cell r="N134"/>
-          <cell r="O134"/>
-          <cell r="P134"/>
-          <cell r="Q134"/>
-          <cell r="R134"/>
-          <cell r="S134"/>
-          <cell r="T134"/>
-          <cell r="U134"/>
-          <cell r="V134"/>
-          <cell r="W134"/>
-          <cell r="X134"/>
-        </row>
-        <row r="135">
-          <cell r="D135"/>
-          <cell r="E135"/>
-          <cell r="F135"/>
-          <cell r="G135"/>
-          <cell r="H135"/>
-          <cell r="I135"/>
-          <cell r="J135"/>
-          <cell r="K135"/>
-          <cell r="L135"/>
-          <cell r="M135"/>
-          <cell r="N135"/>
-          <cell r="O135"/>
-          <cell r="P135"/>
-          <cell r="Q135"/>
-          <cell r="R135"/>
-          <cell r="S135"/>
-          <cell r="T135"/>
-          <cell r="U135"/>
-          <cell r="V135"/>
-          <cell r="W135"/>
-          <cell r="X135"/>
-        </row>
-        <row r="136">
-          <cell r="D136"/>
-          <cell r="E136"/>
-          <cell r="F136"/>
-          <cell r="G136"/>
-          <cell r="H136"/>
-          <cell r="I136"/>
-          <cell r="J136"/>
-          <cell r="K136"/>
-          <cell r="L136"/>
-          <cell r="M136"/>
-          <cell r="N136"/>
-          <cell r="O136"/>
-          <cell r="P136"/>
-          <cell r="Q136"/>
-          <cell r="R136"/>
-          <cell r="S136"/>
-          <cell r="T136"/>
-          <cell r="U136"/>
-          <cell r="V136"/>
-          <cell r="W136"/>
-          <cell r="X136"/>
-        </row>
-        <row r="137">
-          <cell r="D137"/>
-          <cell r="E137"/>
-          <cell r="F137"/>
-          <cell r="G137"/>
-          <cell r="H137"/>
-          <cell r="I137"/>
-          <cell r="J137"/>
-          <cell r="K137"/>
-          <cell r="L137"/>
-          <cell r="M137"/>
-          <cell r="N137"/>
-          <cell r="O137"/>
-          <cell r="P137"/>
-          <cell r="Q137"/>
-          <cell r="R137"/>
-          <cell r="S137"/>
-          <cell r="T137"/>
-          <cell r="U137"/>
-          <cell r="V137"/>
-          <cell r="W137"/>
-          <cell r="X137"/>
-        </row>
-        <row r="138">
-          <cell r="D138"/>
-          <cell r="E138"/>
-          <cell r="F138"/>
-          <cell r="G138"/>
-          <cell r="H138"/>
-          <cell r="I138"/>
-          <cell r="J138"/>
-          <cell r="K138"/>
-          <cell r="L138"/>
-          <cell r="M138"/>
-          <cell r="N138"/>
-          <cell r="O138"/>
-          <cell r="P138"/>
-          <cell r="Q138"/>
-          <cell r="R138"/>
-          <cell r="S138"/>
-          <cell r="T138"/>
-          <cell r="U138"/>
-          <cell r="V138"/>
-          <cell r="W138"/>
-          <cell r="X138"/>
-        </row>
-        <row r="139">
-          <cell r="D139"/>
-          <cell r="E139"/>
-          <cell r="F139"/>
-          <cell r="G139"/>
-          <cell r="H139"/>
-          <cell r="I139"/>
-          <cell r="J139"/>
-          <cell r="K139"/>
-          <cell r="L139"/>
-          <cell r="M139"/>
-          <cell r="N139"/>
-          <cell r="O139"/>
-          <cell r="P139"/>
-          <cell r="Q139"/>
-          <cell r="R139"/>
-          <cell r="S139"/>
-          <cell r="T139"/>
-          <cell r="U139"/>
-          <cell r="V139"/>
-          <cell r="W139"/>
-          <cell r="X139"/>
-        </row>
-        <row r="140">
-          <cell r="D140"/>
-          <cell r="E140"/>
-          <cell r="F140"/>
-          <cell r="G140"/>
-          <cell r="H140"/>
-          <cell r="I140"/>
-          <cell r="J140"/>
-          <cell r="K140"/>
-          <cell r="L140"/>
-          <cell r="M140"/>
-          <cell r="N140"/>
-          <cell r="O140"/>
-          <cell r="P140"/>
-          <cell r="Q140"/>
-          <cell r="R140"/>
-          <cell r="S140"/>
-          <cell r="T140"/>
-          <cell r="U140"/>
-          <cell r="V140"/>
-          <cell r="W140"/>
-          <cell r="X140"/>
-        </row>
-        <row r="141">
-          <cell r="D141"/>
-          <cell r="E141"/>
-          <cell r="F141"/>
-          <cell r="G141"/>
-          <cell r="H141"/>
-          <cell r="I141"/>
-          <cell r="J141"/>
-          <cell r="K141"/>
-          <cell r="L141"/>
-          <cell r="M141"/>
-          <cell r="N141"/>
-          <cell r="O141"/>
-          <cell r="P141"/>
-          <cell r="Q141"/>
-          <cell r="R141"/>
-          <cell r="S141"/>
-          <cell r="T141"/>
-          <cell r="U141"/>
-          <cell r="V141"/>
-          <cell r="W141"/>
-          <cell r="X141"/>
-        </row>
-        <row r="142">
-          <cell r="D142"/>
-          <cell r="E142"/>
-          <cell r="F142"/>
-          <cell r="G142"/>
-          <cell r="H142"/>
-          <cell r="I142"/>
-          <cell r="J142"/>
-          <cell r="K142"/>
-          <cell r="L142"/>
-          <cell r="M142"/>
-          <cell r="N142"/>
-          <cell r="O142"/>
-          <cell r="P142"/>
-          <cell r="Q142"/>
-          <cell r="R142"/>
-          <cell r="S142"/>
-          <cell r="T142"/>
-          <cell r="U142"/>
-          <cell r="V142"/>
-          <cell r="W142"/>
-          <cell r="X142"/>
-        </row>
-        <row r="143">
-          <cell r="D143"/>
-          <cell r="E143"/>
-          <cell r="F143"/>
-          <cell r="G143"/>
-          <cell r="H143"/>
-          <cell r="I143"/>
-          <cell r="J143"/>
-          <cell r="K143"/>
-          <cell r="L143"/>
-          <cell r="M143"/>
-          <cell r="N143"/>
-          <cell r="O143"/>
-          <cell r="P143"/>
-          <cell r="Q143"/>
-          <cell r="R143"/>
-          <cell r="S143"/>
-          <cell r="T143"/>
-          <cell r="U143"/>
-          <cell r="V143"/>
-          <cell r="W143"/>
-          <cell r="X143"/>
-        </row>
-        <row r="144">
-          <cell r="D144"/>
-          <cell r="E144"/>
-          <cell r="F144"/>
-          <cell r="G144"/>
-          <cell r="H144"/>
-          <cell r="I144"/>
-          <cell r="J144"/>
-          <cell r="K144"/>
-          <cell r="L144"/>
-          <cell r="M144"/>
-          <cell r="N144"/>
-          <cell r="O144"/>
-          <cell r="P144"/>
-          <cell r="Q144"/>
-          <cell r="R144"/>
-          <cell r="S144"/>
-          <cell r="T144"/>
-          <cell r="U144"/>
-          <cell r="V144"/>
-          <cell r="W144"/>
-          <cell r="X144"/>
-        </row>
-        <row r="145">
-          <cell r="D145"/>
-          <cell r="E145"/>
-          <cell r="F145"/>
-          <cell r="G145"/>
-          <cell r="H145"/>
-          <cell r="I145"/>
-          <cell r="J145"/>
-          <cell r="K145"/>
-          <cell r="L145"/>
-          <cell r="M145"/>
-          <cell r="N145"/>
-          <cell r="O145"/>
-          <cell r="P145"/>
-          <cell r="Q145"/>
-          <cell r="R145"/>
-          <cell r="S145"/>
-          <cell r="T145"/>
-          <cell r="U145"/>
-          <cell r="V145"/>
-          <cell r="W145"/>
-          <cell r="X145"/>
-        </row>
-        <row r="146">
-          <cell r="D146"/>
-          <cell r="E146"/>
-          <cell r="F146"/>
-          <cell r="G146"/>
-          <cell r="H146"/>
-          <cell r="I146"/>
-          <cell r="J146"/>
-          <cell r="K146"/>
-          <cell r="L146"/>
-          <cell r="M146"/>
-          <cell r="N146"/>
-          <cell r="O146"/>
-          <cell r="P146"/>
-          <cell r="Q146"/>
-          <cell r="R146"/>
-          <cell r="S146"/>
-          <cell r="T146"/>
-          <cell r="U146"/>
-          <cell r="V146"/>
-          <cell r="W146"/>
-          <cell r="X146"/>
-        </row>
-        <row r="147">
-          <cell r="D147"/>
-          <cell r="E147"/>
-          <cell r="F147"/>
-          <cell r="G147"/>
-          <cell r="H147"/>
-          <cell r="I147"/>
-          <cell r="J147"/>
-          <cell r="K147"/>
-          <cell r="L147"/>
-          <cell r="M147"/>
-          <cell r="N147"/>
-          <cell r="O147"/>
-          <cell r="P147"/>
-          <cell r="Q147"/>
-          <cell r="R147"/>
-          <cell r="S147"/>
-          <cell r="T147"/>
-          <cell r="U147"/>
-          <cell r="V147"/>
-          <cell r="W147"/>
-          <cell r="X147"/>
-        </row>
-        <row r="148">
-          <cell r="D148"/>
-          <cell r="E148"/>
-          <cell r="F148"/>
-          <cell r="G148"/>
-          <cell r="H148"/>
-          <cell r="I148"/>
-          <cell r="J148"/>
-          <cell r="K148"/>
-          <cell r="L148"/>
-          <cell r="M148"/>
-          <cell r="N148"/>
-          <cell r="O148"/>
-          <cell r="P148"/>
-          <cell r="Q148"/>
-          <cell r="R148"/>
-          <cell r="S148"/>
-          <cell r="T148"/>
-          <cell r="U148"/>
-          <cell r="V148"/>
-          <cell r="W148"/>
-          <cell r="X148"/>
-        </row>
-        <row r="149">
-          <cell r="D149"/>
-          <cell r="E149"/>
-          <cell r="F149"/>
-          <cell r="G149"/>
-          <cell r="H149"/>
-          <cell r="I149"/>
-          <cell r="J149"/>
-          <cell r="K149"/>
-          <cell r="L149"/>
-          <cell r="M149"/>
-          <cell r="N149"/>
-          <cell r="O149"/>
-          <cell r="P149"/>
-          <cell r="Q149"/>
-          <cell r="R149"/>
-          <cell r="S149"/>
-          <cell r="T149"/>
-          <cell r="U149"/>
-          <cell r="V149"/>
-          <cell r="W149"/>
-          <cell r="X149"/>
-        </row>
-        <row r="150">
-          <cell r="D150"/>
-          <cell r="E150"/>
-          <cell r="F150"/>
-          <cell r="G150"/>
-          <cell r="H150"/>
-          <cell r="I150"/>
-          <cell r="J150"/>
-          <cell r="K150"/>
-          <cell r="L150"/>
-          <cell r="M150"/>
-          <cell r="N150"/>
-          <cell r="O150"/>
-          <cell r="P150"/>
-          <cell r="Q150"/>
-          <cell r="R150"/>
-          <cell r="S150"/>
-          <cell r="T150"/>
-          <cell r="U150"/>
-          <cell r="V150"/>
-          <cell r="W150"/>
-          <cell r="X150"/>
-        </row>
-        <row r="151">
-          <cell r="D151"/>
-          <cell r="E151"/>
-          <cell r="F151"/>
-          <cell r="G151"/>
-          <cell r="H151"/>
-          <cell r="I151"/>
-          <cell r="J151"/>
-          <cell r="K151"/>
-          <cell r="L151"/>
-          <cell r="M151"/>
-          <cell r="N151"/>
-          <cell r="O151"/>
-          <cell r="P151"/>
-          <cell r="Q151"/>
-          <cell r="R151"/>
-          <cell r="S151"/>
-          <cell r="T151"/>
-          <cell r="U151"/>
-          <cell r="V151"/>
-          <cell r="W151"/>
-          <cell r="X151"/>
-        </row>
-        <row r="152">
-          <cell r="D152"/>
-          <cell r="E152"/>
-          <cell r="F152"/>
-          <cell r="G152"/>
-          <cell r="H152"/>
-          <cell r="I152"/>
-          <cell r="J152"/>
-          <cell r="K152"/>
-          <cell r="L152"/>
-          <cell r="M152"/>
-          <cell r="N152"/>
-          <cell r="O152"/>
-          <cell r="P152"/>
-          <cell r="Q152"/>
-          <cell r="R152"/>
-          <cell r="S152"/>
-          <cell r="T152"/>
-          <cell r="U152"/>
-          <cell r="V152"/>
-          <cell r="W152"/>
-          <cell r="X152"/>
-        </row>
-        <row r="153">
-          <cell r="D153"/>
-          <cell r="E153"/>
-          <cell r="F153"/>
-          <cell r="G153"/>
-          <cell r="H153"/>
-          <cell r="I153"/>
-          <cell r="J153"/>
-          <cell r="K153"/>
-          <cell r="L153"/>
-          <cell r="M153"/>
-          <cell r="N153"/>
-          <cell r="O153"/>
-          <cell r="P153"/>
-          <cell r="Q153"/>
-          <cell r="R153"/>
-          <cell r="S153"/>
-          <cell r="T153"/>
-          <cell r="U153"/>
-          <cell r="V153"/>
-          <cell r="W153"/>
-          <cell r="X153"/>
-        </row>
-        <row r="154">
-          <cell r="D154"/>
-          <cell r="E154"/>
-          <cell r="F154"/>
-          <cell r="G154"/>
-          <cell r="H154"/>
-          <cell r="I154"/>
-          <cell r="J154"/>
-          <cell r="K154"/>
-          <cell r="L154"/>
-          <cell r="M154"/>
-          <cell r="N154"/>
-          <cell r="O154"/>
-          <cell r="P154"/>
-          <cell r="Q154"/>
-          <cell r="R154"/>
-          <cell r="S154"/>
-          <cell r="T154"/>
-          <cell r="U154"/>
-          <cell r="V154"/>
-          <cell r="W154"/>
-          <cell r="X154"/>
-        </row>
-        <row r="155">
-          <cell r="D155"/>
-          <cell r="E155"/>
-          <cell r="F155"/>
-          <cell r="G155"/>
-          <cell r="H155"/>
-          <cell r="I155"/>
-          <cell r="J155"/>
-          <cell r="K155"/>
-          <cell r="L155"/>
-          <cell r="M155"/>
-          <cell r="N155"/>
-          <cell r="O155"/>
-          <cell r="P155"/>
-          <cell r="Q155"/>
-          <cell r="R155"/>
-          <cell r="S155"/>
-          <cell r="T155"/>
-          <cell r="U155"/>
-          <cell r="V155"/>
-          <cell r="W155"/>
-          <cell r="X155"/>
-        </row>
-        <row r="156">
-          <cell r="D156"/>
-          <cell r="E156"/>
-          <cell r="F156"/>
-          <cell r="G156"/>
-          <cell r="H156"/>
-          <cell r="I156"/>
-          <cell r="J156"/>
-          <cell r="K156"/>
-          <cell r="L156"/>
-          <cell r="M156"/>
-          <cell r="N156"/>
-          <cell r="O156"/>
-          <cell r="P156"/>
-          <cell r="Q156"/>
-          <cell r="R156"/>
-          <cell r="S156"/>
-          <cell r="T156"/>
-          <cell r="U156"/>
-          <cell r="V156"/>
-          <cell r="W156"/>
-          <cell r="X156"/>
-        </row>
-        <row r="157">
-          <cell r="D157"/>
-          <cell r="E157"/>
-          <cell r="F157"/>
-          <cell r="G157"/>
-          <cell r="H157"/>
-          <cell r="I157"/>
-          <cell r="J157"/>
-          <cell r="K157"/>
-          <cell r="L157"/>
-          <cell r="M157"/>
-          <cell r="N157"/>
-          <cell r="O157"/>
-          <cell r="P157"/>
-          <cell r="Q157"/>
-          <cell r="R157"/>
-          <cell r="S157"/>
-          <cell r="T157"/>
-          <cell r="U157"/>
-          <cell r="V157"/>
-          <cell r="W157"/>
-          <cell r="X157"/>
-        </row>
-        <row r="158">
-          <cell r="D158"/>
-          <cell r="E158"/>
-          <cell r="F158"/>
-          <cell r="G158"/>
-          <cell r="H158"/>
-          <cell r="I158"/>
-          <cell r="J158"/>
-          <cell r="K158"/>
-          <cell r="L158"/>
-          <cell r="M158"/>
-          <cell r="N158"/>
-          <cell r="O158"/>
-          <cell r="P158"/>
-          <cell r="Q158"/>
-          <cell r="R158"/>
-          <cell r="S158"/>
-          <cell r="T158"/>
-          <cell r="U158"/>
-          <cell r="V158"/>
-          <cell r="W158"/>
-          <cell r="X158"/>
-        </row>
-        <row r="159">
-          <cell r="D159"/>
-          <cell r="E159"/>
-          <cell r="F159"/>
-          <cell r="G159"/>
-          <cell r="H159"/>
-          <cell r="I159"/>
-          <cell r="J159"/>
-          <cell r="K159"/>
-          <cell r="L159"/>
-          <cell r="M159"/>
-          <cell r="N159"/>
-          <cell r="O159"/>
-          <cell r="P159"/>
-          <cell r="Q159"/>
-          <cell r="R159"/>
-          <cell r="S159"/>
-          <cell r="T159"/>
-          <cell r="U159"/>
-          <cell r="V159"/>
-          <cell r="W159"/>
-          <cell r="X159"/>
-        </row>
-        <row r="160">
-          <cell r="D160"/>
-          <cell r="E160"/>
-          <cell r="F160"/>
-          <cell r="G160"/>
-          <cell r="H160"/>
-          <cell r="I160"/>
-          <cell r="J160"/>
-          <cell r="K160"/>
-          <cell r="L160"/>
-          <cell r="M160"/>
-          <cell r="N160"/>
-          <cell r="O160"/>
-          <cell r="P160"/>
-          <cell r="Q160"/>
-          <cell r="R160"/>
-          <cell r="S160"/>
-          <cell r="T160"/>
-          <cell r="U160"/>
-          <cell r="V160"/>
-          <cell r="W160"/>
-          <cell r="X160"/>
-        </row>
-        <row r="161">
-          <cell r="D161"/>
-          <cell r="E161"/>
-          <cell r="F161"/>
-          <cell r="G161"/>
-          <cell r="H161"/>
-          <cell r="I161"/>
-          <cell r="J161"/>
-          <cell r="K161"/>
-          <cell r="L161"/>
-          <cell r="M161"/>
-          <cell r="N161"/>
-          <cell r="O161"/>
-          <cell r="P161"/>
-          <cell r="Q161"/>
-          <cell r="R161"/>
-          <cell r="S161"/>
-          <cell r="T161"/>
-          <cell r="U161"/>
-          <cell r="V161"/>
-          <cell r="W161"/>
-          <cell r="X161"/>
-        </row>
-        <row r="162">
-          <cell r="D162"/>
-          <cell r="E162"/>
-          <cell r="F162"/>
-          <cell r="G162"/>
-          <cell r="H162"/>
-          <cell r="I162"/>
-          <cell r="J162"/>
-          <cell r="K162"/>
-          <cell r="L162"/>
-          <cell r="M162"/>
-          <cell r="N162"/>
-          <cell r="O162"/>
-          <cell r="P162"/>
-          <cell r="Q162"/>
-          <cell r="R162"/>
-          <cell r="S162"/>
-          <cell r="T162"/>
-          <cell r="U162"/>
-          <cell r="V162"/>
-          <cell r="W162"/>
-          <cell r="X162"/>
-        </row>
-        <row r="163">
-          <cell r="D163"/>
-          <cell r="E163"/>
-          <cell r="F163"/>
-          <cell r="G163"/>
-          <cell r="H163"/>
-          <cell r="I163"/>
-          <cell r="J163"/>
-          <cell r="K163"/>
-          <cell r="L163"/>
-          <cell r="M163"/>
-          <cell r="N163"/>
-          <cell r="O163"/>
-          <cell r="P163"/>
-          <cell r="Q163"/>
-          <cell r="R163"/>
-          <cell r="S163"/>
-          <cell r="T163"/>
-          <cell r="U163"/>
-          <cell r="V163"/>
-          <cell r="W163"/>
-          <cell r="X163"/>
-        </row>
-        <row r="164">
-          <cell r="D164"/>
-          <cell r="E164"/>
-          <cell r="F164"/>
-          <cell r="G164"/>
-          <cell r="H164"/>
-          <cell r="I164"/>
-          <cell r="J164"/>
-          <cell r="K164"/>
-          <cell r="L164"/>
-          <cell r="M164"/>
-          <cell r="N164"/>
-          <cell r="O164"/>
-          <cell r="P164"/>
-          <cell r="Q164"/>
-          <cell r="R164"/>
-          <cell r="S164"/>
-          <cell r="T164"/>
-          <cell r="U164"/>
-          <cell r="V164"/>
-          <cell r="W164"/>
-          <cell r="X164"/>
-        </row>
-        <row r="165">
-          <cell r="D165"/>
-          <cell r="E165"/>
-          <cell r="F165"/>
-          <cell r="G165"/>
-          <cell r="H165"/>
-          <cell r="I165"/>
-          <cell r="J165"/>
-          <cell r="K165"/>
-          <cell r="L165"/>
-          <cell r="M165"/>
-          <cell r="N165"/>
-          <cell r="O165"/>
-          <cell r="P165"/>
-          <cell r="Q165"/>
-          <cell r="R165"/>
-          <cell r="S165"/>
-          <cell r="T165"/>
-          <cell r="U165"/>
-          <cell r="V165"/>
-          <cell r="W165"/>
-          <cell r="X165"/>
-        </row>
-        <row r="166">
-          <cell r="D166"/>
-          <cell r="E166"/>
-          <cell r="F166"/>
-          <cell r="G166"/>
-          <cell r="H166"/>
-          <cell r="I166"/>
-          <cell r="J166"/>
-          <cell r="K166"/>
-          <cell r="L166"/>
-          <cell r="M166"/>
-          <cell r="N166"/>
-          <cell r="O166"/>
-          <cell r="P166"/>
-          <cell r="Q166"/>
-          <cell r="R166"/>
-          <cell r="S166"/>
-          <cell r="T166"/>
-          <cell r="U166"/>
-          <cell r="V166"/>
-          <cell r="W166"/>
-          <cell r="X166"/>
-        </row>
-        <row r="167">
-          <cell r="D167"/>
-          <cell r="E167"/>
-          <cell r="F167"/>
-          <cell r="G167"/>
-          <cell r="H167"/>
-          <cell r="I167"/>
-          <cell r="J167"/>
-          <cell r="K167"/>
-          <cell r="L167"/>
-          <cell r="M167"/>
-          <cell r="N167"/>
-          <cell r="O167"/>
-          <cell r="P167"/>
-          <cell r="Q167"/>
-          <cell r="R167"/>
-          <cell r="S167"/>
-          <cell r="T167"/>
-          <cell r="U167"/>
-          <cell r="V167"/>
-          <cell r="W167"/>
-          <cell r="X167"/>
-        </row>
-        <row r="168">
-          <cell r="D168"/>
-          <cell r="E168"/>
-          <cell r="F168"/>
-          <cell r="G168"/>
-          <cell r="H168"/>
-          <cell r="I168"/>
-          <cell r="J168"/>
-          <cell r="K168"/>
-          <cell r="L168"/>
-          <cell r="M168"/>
-          <cell r="N168"/>
-          <cell r="O168"/>
-          <cell r="P168"/>
-          <cell r="Q168"/>
-          <cell r="R168"/>
-          <cell r="S168"/>
-          <cell r="T168"/>
-          <cell r="U168"/>
-          <cell r="V168"/>
-          <cell r="W168"/>
-          <cell r="X168"/>
-        </row>
-        <row r="169">
-          <cell r="D169"/>
-          <cell r="E169"/>
-          <cell r="F169"/>
-          <cell r="G169"/>
-          <cell r="H169"/>
-          <cell r="I169"/>
-          <cell r="J169"/>
-          <cell r="K169"/>
-          <cell r="L169"/>
-          <cell r="M169"/>
-          <cell r="N169"/>
-          <cell r="O169"/>
-          <cell r="P169"/>
-          <cell r="Q169"/>
-          <cell r="R169"/>
-          <cell r="S169"/>
-          <cell r="T169"/>
-          <cell r="U169"/>
-          <cell r="V169"/>
-          <cell r="W169"/>
-          <cell r="X169"/>
-        </row>
-        <row r="170">
-          <cell r="D170"/>
-          <cell r="E170"/>
-          <cell r="F170"/>
-          <cell r="G170"/>
-          <cell r="H170"/>
-          <cell r="I170"/>
-          <cell r="J170"/>
-          <cell r="K170"/>
-          <cell r="L170"/>
-          <cell r="M170"/>
-          <cell r="N170"/>
-          <cell r="O170"/>
-          <cell r="P170"/>
-          <cell r="Q170"/>
-          <cell r="R170"/>
-          <cell r="S170"/>
-          <cell r="T170"/>
-          <cell r="U170"/>
-          <cell r="V170"/>
-          <cell r="W170"/>
-          <cell r="X170"/>
-        </row>
-        <row r="171">
-          <cell r="D171"/>
-          <cell r="E171"/>
-          <cell r="F171"/>
-          <cell r="G171"/>
-          <cell r="H171"/>
-          <cell r="I171"/>
-          <cell r="J171"/>
-          <cell r="K171"/>
-          <cell r="L171"/>
-          <cell r="M171"/>
-          <cell r="N171"/>
-          <cell r="O171"/>
-          <cell r="P171"/>
-          <cell r="Q171"/>
-          <cell r="R171"/>
-          <cell r="S171"/>
-          <cell r="T171"/>
-          <cell r="U171"/>
-          <cell r="V171"/>
-          <cell r="W171"/>
-          <cell r="X171"/>
-        </row>
-        <row r="172">
-          <cell r="D172"/>
-          <cell r="E172"/>
-          <cell r="F172"/>
-          <cell r="G172"/>
-          <cell r="H172"/>
-          <cell r="I172"/>
-          <cell r="J172"/>
-          <cell r="K172"/>
-          <cell r="L172"/>
-          <cell r="M172"/>
-          <cell r="N172"/>
-          <cell r="O172"/>
-          <cell r="P172"/>
-          <cell r="Q172"/>
-          <cell r="R172"/>
-          <cell r="S172"/>
-          <cell r="T172"/>
-          <cell r="U172"/>
-          <cell r="V172"/>
-          <cell r="W172"/>
-          <cell r="X172"/>
-        </row>
-        <row r="173">
-          <cell r="D173"/>
-          <cell r="E173"/>
-          <cell r="F173"/>
-          <cell r="G173"/>
-          <cell r="H173"/>
-          <cell r="I173"/>
-          <cell r="J173"/>
-          <cell r="K173"/>
-          <cell r="L173"/>
-          <cell r="M173"/>
-          <cell r="N173"/>
-          <cell r="O173"/>
-          <cell r="P173"/>
-          <cell r="Q173"/>
-          <cell r="R173"/>
-          <cell r="S173"/>
-          <cell r="T173"/>
-          <cell r="U173"/>
-          <cell r="V173"/>
-          <cell r="W173"/>
-          <cell r="X173"/>
-        </row>
-        <row r="174">
-          <cell r="D174"/>
-          <cell r="E174"/>
-          <cell r="F174"/>
-          <cell r="G174"/>
-          <cell r="H174"/>
-          <cell r="I174"/>
-          <cell r="J174"/>
-          <cell r="K174"/>
-          <cell r="L174"/>
-          <cell r="M174"/>
-          <cell r="N174"/>
-          <cell r="O174"/>
-          <cell r="P174"/>
-          <cell r="Q174"/>
-          <cell r="R174"/>
-          <cell r="S174"/>
-          <cell r="T174"/>
-          <cell r="U174"/>
-          <cell r="V174"/>
-          <cell r="W174"/>
-          <cell r="X174"/>
-        </row>
-        <row r="175">
-          <cell r="D175"/>
-          <cell r="E175"/>
-          <cell r="F175"/>
-          <cell r="G175"/>
-          <cell r="H175"/>
-          <cell r="I175"/>
-          <cell r="J175"/>
-          <cell r="K175"/>
-          <cell r="L175"/>
-          <cell r="M175"/>
-          <cell r="N175"/>
-          <cell r="O175"/>
-          <cell r="P175"/>
-          <cell r="Q175"/>
-          <cell r="R175"/>
-          <cell r="S175"/>
-          <cell r="T175"/>
-          <cell r="U175"/>
-          <cell r="V175"/>
-          <cell r="W175"/>
-          <cell r="X175"/>
-        </row>
-        <row r="176">
-          <cell r="D176"/>
-          <cell r="E176"/>
-          <cell r="F176"/>
-          <cell r="G176"/>
-          <cell r="H176"/>
-          <cell r="I176"/>
-          <cell r="J176"/>
-          <cell r="K176"/>
-          <cell r="L176"/>
-          <cell r="M176"/>
-          <cell r="N176"/>
-          <cell r="O176"/>
-          <cell r="P176"/>
-          <cell r="Q176"/>
-          <cell r="R176"/>
-          <cell r="S176"/>
-          <cell r="T176"/>
-          <cell r="U176"/>
-          <cell r="V176"/>
-          <cell r="W176"/>
-          <cell r="X176"/>
-        </row>
-        <row r="177">
-          <cell r="D177"/>
-          <cell r="E177"/>
-          <cell r="F177"/>
-          <cell r="G177"/>
-          <cell r="H177"/>
-          <cell r="I177"/>
-          <cell r="J177"/>
-          <cell r="K177"/>
-          <cell r="L177"/>
-          <cell r="M177"/>
-          <cell r="N177"/>
-          <cell r="O177"/>
-          <cell r="P177"/>
-          <cell r="Q177"/>
-          <cell r="R177"/>
-          <cell r="S177"/>
-          <cell r="T177"/>
-          <cell r="U177"/>
-          <cell r="V177"/>
-          <cell r="W177"/>
-          <cell r="X177"/>
-        </row>
-        <row r="178">
-          <cell r="D178"/>
-          <cell r="E178"/>
-          <cell r="F178"/>
-          <cell r="G178"/>
-          <cell r="H178"/>
-          <cell r="I178"/>
-          <cell r="J178"/>
-          <cell r="K178"/>
-          <cell r="L178"/>
-          <cell r="M178"/>
-          <cell r="N178"/>
-          <cell r="O178"/>
-          <cell r="P178"/>
-          <cell r="Q178"/>
-          <cell r="R178"/>
-          <cell r="S178"/>
-          <cell r="T178"/>
-          <cell r="U178"/>
-          <cell r="V178"/>
-          <cell r="W178"/>
-          <cell r="X178"/>
-        </row>
-        <row r="179">
-          <cell r="D179"/>
-          <cell r="E179"/>
-          <cell r="F179"/>
-          <cell r="G179"/>
-          <cell r="H179"/>
-          <cell r="I179"/>
-          <cell r="J179"/>
-          <cell r="K179"/>
-          <cell r="L179"/>
-          <cell r="M179"/>
-          <cell r="N179"/>
-          <cell r="O179"/>
-          <cell r="P179"/>
-          <cell r="Q179"/>
-          <cell r="R179"/>
-          <cell r="S179"/>
-          <cell r="T179"/>
-          <cell r="U179"/>
-          <cell r="V179"/>
-          <cell r="W179"/>
-          <cell r="X179"/>
-        </row>
-        <row r="180">
-          <cell r="D180"/>
-          <cell r="E180"/>
-          <cell r="F180"/>
-          <cell r="G180"/>
-          <cell r="H180"/>
-          <cell r="I180"/>
-          <cell r="J180"/>
-          <cell r="K180"/>
-          <cell r="L180"/>
-          <cell r="M180"/>
-          <cell r="N180"/>
-          <cell r="O180"/>
-          <cell r="P180"/>
-          <cell r="Q180"/>
-          <cell r="R180"/>
-          <cell r="S180"/>
-          <cell r="T180"/>
-          <cell r="U180"/>
-          <cell r="V180"/>
-          <cell r="W180"/>
-          <cell r="X180"/>
-        </row>
-        <row r="181">
-          <cell r="D181"/>
-          <cell r="E181"/>
-          <cell r="F181"/>
-          <cell r="G181"/>
-          <cell r="H181"/>
-          <cell r="I181"/>
-          <cell r="J181"/>
-          <cell r="K181"/>
-          <cell r="L181"/>
-          <cell r="M181"/>
-          <cell r="N181"/>
-          <cell r="O181"/>
-          <cell r="P181"/>
-          <cell r="Q181"/>
-          <cell r="R181"/>
-          <cell r="S181"/>
-          <cell r="T181"/>
-          <cell r="U181"/>
-          <cell r="V181"/>
-          <cell r="W181"/>
-          <cell r="X181"/>
-        </row>
-        <row r="182">
-          <cell r="D182"/>
-          <cell r="E182"/>
-          <cell r="F182"/>
-          <cell r="G182"/>
-          <cell r="H182"/>
-          <cell r="I182"/>
-          <cell r="J182"/>
-          <cell r="K182"/>
-          <cell r="L182"/>
-          <cell r="M182"/>
-          <cell r="N182"/>
-          <cell r="O182"/>
-          <cell r="P182"/>
-          <cell r="Q182"/>
-          <cell r="R182"/>
-          <cell r="S182"/>
-          <cell r="T182"/>
-          <cell r="U182"/>
-          <cell r="V182"/>
-          <cell r="W182"/>
-          <cell r="X182"/>
-        </row>
-        <row r="183">
-          <cell r="D183"/>
-          <cell r="E183"/>
-          <cell r="F183"/>
-          <cell r="G183"/>
-          <cell r="H183"/>
-          <cell r="I183"/>
-          <cell r="J183"/>
-          <cell r="K183"/>
-          <cell r="L183"/>
-          <cell r="M183"/>
-          <cell r="N183"/>
-          <cell r="O183"/>
-          <cell r="P183"/>
-          <cell r="Q183"/>
-          <cell r="R183"/>
-          <cell r="S183"/>
-          <cell r="T183"/>
-          <cell r="U183"/>
-          <cell r="V183"/>
-          <cell r="W183"/>
-          <cell r="X183"/>
-        </row>
-        <row r="184">
-          <cell r="D184"/>
-          <cell r="E184"/>
-          <cell r="F184"/>
-          <cell r="G184"/>
-          <cell r="H184"/>
-          <cell r="I184"/>
-          <cell r="J184"/>
-          <cell r="K184"/>
-          <cell r="L184"/>
-          <cell r="M184"/>
-          <cell r="N184"/>
-          <cell r="O184"/>
-          <cell r="P184"/>
-          <cell r="Q184"/>
-          <cell r="R184"/>
-          <cell r="S184"/>
-          <cell r="T184"/>
-          <cell r="U184"/>
-          <cell r="V184"/>
-          <cell r="W184"/>
-          <cell r="X184"/>
-        </row>
-        <row r="185">
-          <cell r="D185"/>
-          <cell r="E185"/>
-          <cell r="F185"/>
-          <cell r="G185"/>
-          <cell r="H185"/>
-          <cell r="I185"/>
-          <cell r="J185"/>
-          <cell r="K185"/>
-          <cell r="L185"/>
-          <cell r="M185"/>
-          <cell r="N185"/>
-          <cell r="O185"/>
-          <cell r="P185"/>
-          <cell r="Q185"/>
-          <cell r="R185"/>
-          <cell r="S185"/>
-          <cell r="T185"/>
-          <cell r="U185"/>
-          <cell r="V185"/>
-          <cell r="W185"/>
-          <cell r="X185"/>
-        </row>
-        <row r="186">
-          <cell r="D186"/>
-          <cell r="E186"/>
-          <cell r="F186"/>
-          <cell r="G186"/>
-          <cell r="H186"/>
-          <cell r="I186"/>
-          <cell r="J186"/>
-          <cell r="K186"/>
-          <cell r="L186"/>
-          <cell r="M186"/>
-          <cell r="N186"/>
-          <cell r="O186"/>
-          <cell r="P186"/>
-          <cell r="Q186"/>
-          <cell r="R186"/>
-          <cell r="S186"/>
-          <cell r="T186"/>
-          <cell r="U186"/>
-          <cell r="V186"/>
-          <cell r="W186"/>
-          <cell r="X186"/>
-        </row>
-        <row r="187">
-          <cell r="D187"/>
-          <cell r="E187"/>
-          <cell r="F187"/>
-          <cell r="G187"/>
-          <cell r="H187"/>
-          <cell r="I187"/>
-          <cell r="J187"/>
-          <cell r="K187"/>
-          <cell r="L187"/>
-          <cell r="M187"/>
-          <cell r="N187"/>
-          <cell r="O187"/>
-          <cell r="P187"/>
-          <cell r="Q187"/>
-          <cell r="R187"/>
-          <cell r="S187"/>
-          <cell r="T187"/>
-          <cell r="U187"/>
-          <cell r="V187"/>
-          <cell r="W187"/>
-          <cell r="X187"/>
-        </row>
-        <row r="188">
-          <cell r="D188"/>
-          <cell r="E188"/>
-          <cell r="F188"/>
-          <cell r="G188"/>
-          <cell r="H188"/>
-          <cell r="I188"/>
-          <cell r="J188"/>
-          <cell r="K188"/>
-          <cell r="L188"/>
-          <cell r="M188"/>
-          <cell r="N188"/>
-          <cell r="O188"/>
-          <cell r="P188"/>
-          <cell r="Q188"/>
-          <cell r="R188"/>
-          <cell r="S188"/>
-          <cell r="T188"/>
-          <cell r="U188"/>
-          <cell r="V188"/>
-          <cell r="W188"/>
-          <cell r="X188"/>
-        </row>
-        <row r="189">
-          <cell r="D189"/>
-          <cell r="E189"/>
-          <cell r="F189"/>
-          <cell r="G189"/>
-          <cell r="H189"/>
-          <cell r="I189"/>
-          <cell r="J189"/>
-          <cell r="K189"/>
-          <cell r="L189"/>
-          <cell r="M189"/>
-          <cell r="N189"/>
-          <cell r="O189"/>
-          <cell r="P189"/>
-          <cell r="Q189"/>
-          <cell r="R189"/>
-          <cell r="S189"/>
-          <cell r="T189"/>
-          <cell r="U189"/>
-          <cell r="V189"/>
-          <cell r="W189"/>
-          <cell r="X189"/>
-        </row>
-        <row r="190">
-          <cell r="D190"/>
-          <cell r="E190"/>
-          <cell r="F190"/>
-          <cell r="G190"/>
-          <cell r="H190"/>
-          <cell r="I190"/>
-          <cell r="J190"/>
-          <cell r="K190"/>
-          <cell r="L190"/>
-          <cell r="M190"/>
-          <cell r="N190"/>
-          <cell r="O190"/>
-          <cell r="P190"/>
-          <cell r="Q190"/>
-          <cell r="R190"/>
-          <cell r="S190"/>
-          <cell r="T190"/>
-          <cell r="U190"/>
-          <cell r="V190"/>
-          <cell r="W190"/>
-          <cell r="X190"/>
-        </row>
-        <row r="191">
-          <cell r="D191"/>
-          <cell r="E191"/>
-          <cell r="F191"/>
-          <cell r="G191"/>
-          <cell r="H191"/>
-          <cell r="I191"/>
-          <cell r="J191"/>
-          <cell r="K191"/>
-          <cell r="L191"/>
-          <cell r="M191"/>
-          <cell r="N191"/>
-          <cell r="O191"/>
-          <cell r="P191"/>
-          <cell r="Q191"/>
-          <cell r="R191"/>
-          <cell r="S191"/>
-          <cell r="T191"/>
-          <cell r="U191"/>
-          <cell r="V191"/>
-          <cell r="W191"/>
-          <cell r="X191"/>
-        </row>
-        <row r="192">
-          <cell r="D192"/>
-          <cell r="E192"/>
-          <cell r="F192"/>
-          <cell r="G192"/>
-          <cell r="H192"/>
-          <cell r="I192"/>
-          <cell r="J192"/>
-          <cell r="K192"/>
-          <cell r="L192"/>
-          <cell r="M192"/>
-          <cell r="N192"/>
-          <cell r="O192"/>
-          <cell r="P192"/>
-          <cell r="Q192"/>
-          <cell r="R192"/>
-          <cell r="S192"/>
-          <cell r="T192"/>
-          <cell r="U192"/>
-          <cell r="V192"/>
-          <cell r="W192"/>
-          <cell r="X192"/>
-        </row>
-        <row r="193">
-          <cell r="D193"/>
-          <cell r="E193"/>
-          <cell r="F193"/>
-          <cell r="G193"/>
-          <cell r="H193"/>
-          <cell r="I193"/>
-          <cell r="J193"/>
-          <cell r="K193"/>
-          <cell r="L193"/>
-          <cell r="M193"/>
-          <cell r="N193"/>
-          <cell r="O193"/>
-          <cell r="P193"/>
-          <cell r="Q193"/>
-          <cell r="R193"/>
-          <cell r="S193"/>
-          <cell r="T193"/>
-          <cell r="U193"/>
-          <cell r="V193"/>
-          <cell r="W193"/>
-          <cell r="X193"/>
-        </row>
-        <row r="194">
-          <cell r="D194"/>
-          <cell r="E194"/>
-          <cell r="F194"/>
-          <cell r="G194"/>
-          <cell r="H194"/>
-          <cell r="I194"/>
-          <cell r="J194"/>
-          <cell r="K194"/>
-          <cell r="L194"/>
-          <cell r="M194"/>
-          <cell r="N194"/>
-          <cell r="O194"/>
-          <cell r="P194"/>
-          <cell r="Q194"/>
-          <cell r="R194"/>
-          <cell r="S194"/>
-          <cell r="T194"/>
-          <cell r="U194"/>
-          <cell r="V194"/>
-          <cell r="W194"/>
-          <cell r="X194"/>
-        </row>
-        <row r="195">
-          <cell r="D195"/>
-          <cell r="E195"/>
-          <cell r="F195"/>
-          <cell r="G195"/>
-          <cell r="H195"/>
-          <cell r="I195"/>
-          <cell r="J195"/>
-          <cell r="K195"/>
-          <cell r="L195"/>
-          <cell r="M195"/>
-          <cell r="N195"/>
-          <cell r="O195"/>
-          <cell r="P195"/>
-          <cell r="Q195"/>
-          <cell r="R195"/>
-          <cell r="S195"/>
-          <cell r="T195"/>
-          <cell r="U195"/>
-          <cell r="V195"/>
-          <cell r="W195"/>
-          <cell r="X195"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -27016,7 +24035,7 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="F6" s="14">
-        <f t="shared" ref="F6:F12" si="0">IF(C6="P",0,IF(C6="L",-E6,IF(K6&lt;0,E6*(100/-K6),E6*(K6/100)))/1)</f>
+        <f>IF(C6="P",0,IF(C6="L",-E6,IF(K6&lt;0,E6*(100/-K6),E6*(K6/100)))/1)</f>
         <v>-0.94499999999999995</v>
       </c>
       <c r="G6" s="14">
@@ -27024,7 +24043,7 @@
         <v>-0.94499999999999995</v>
       </c>
       <c r="H6" s="10">
-        <f t="shared" ref="H6:H12" si="1">((M6-P6)*3.55%)+(O6-L6)</f>
+        <f t="shared" ref="H6:H12" si="0">((M6-P6)*3.55%)+(O6-L6)</f>
         <v>-1.9985536081552357E-2</v>
       </c>
       <c r="I6" s="10">
@@ -27038,7 +24057,7 @@
         <v>-112</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ref="L6:L16" si="2">IF(K6&lt;0,K6/(K6-100),100/(K6+100))</f>
+        <f t="shared" ref="L6:L16" si="1">IF(K6&lt;0,K6/(K6-100),100/(K6+100))</f>
         <v>0.52830188679245282</v>
       </c>
       <c r="M6" s="1">
@@ -27048,7 +24067,7 @@
         <v>-111</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" ref="O6:O16" si="3">IF(N6&lt;0,N6/(N6-100),100/(N6+100))</f>
+        <f t="shared" ref="O6:O16" si="2">IF(N6&lt;0,N6/(N6-100),100/(N6+100))</f>
         <v>0.52606635071090047</v>
       </c>
       <c r="P6" s="1">
@@ -27073,7 +24092,7 @@
         <v>0.68979999999999997</v>
       </c>
       <c r="F7" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F6:F12" si="3">IF(C7="P",0,IF(C7="L",-E7,IF(K7&lt;0,E7*(100/-K7),E7*(K7/100)))/1)</f>
         <v>-0.68979999999999997</v>
       </c>
       <c r="G7" s="14">
@@ -27081,7 +24100,7 @@
         <v>-1.6347999999999998</v>
       </c>
       <c r="H7" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.3772693633062259E-3</v>
       </c>
       <c r="I7" s="10">
@@ -27095,7 +24114,7 @@
         <v>-103</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.5073891625615764</v>
       </c>
       <c r="M7" s="1">
@@ -27105,7 +24124,7 @@
         <v>-113</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.53051643192488263</v>
       </c>
       <c r="P7" s="1">
@@ -27130,7 +24149,7 @@
         <v>0.74019999999999997</v>
       </c>
       <c r="F8" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.6729090909090909</v>
       </c>
       <c r="G8" s="14">
@@ -27138,7 +24157,7 @@
         <v>-0.96189090909090891</v>
       </c>
       <c r="H8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.10782963875205255</v>
       </c>
       <c r="I8" s="10">
@@ -27152,7 +24171,7 @@
         <v>-110</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="M8" s="1">
@@ -27162,7 +24181,7 @@
         <v>-103</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.5073891625615764</v>
       </c>
       <c r="P8" s="1">
@@ -27187,7 +24206,7 @@
         <v>0.67900000000000005</v>
       </c>
       <c r="F9" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.61727272727272731</v>
       </c>
       <c r="G9" s="14">
@@ -27195,7 +24214,7 @@
         <v>-0.3446181818181816</v>
       </c>
       <c r="H9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8.5035829865926608E-3</v>
       </c>
       <c r="I9" s="10">
@@ -27209,7 +24228,7 @@
         <v>-110</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="M9" s="1">
@@ -27219,7 +24238,7 @@
         <v>-106</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.5145631067961165</v>
       </c>
       <c r="P9" s="1">
@@ -27244,7 +24263,7 @@
         <v>1.2898000000000001</v>
       </c>
       <c r="F10" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-1.2898000000000001</v>
       </c>
       <c r="G10" s="14">
@@ -27252,7 +24271,7 @@
         <v>-1.6344181818181815</v>
       </c>
       <c r="H10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-3.9992362982928985E-2</v>
       </c>
       <c r="I10" s="10">
@@ -27266,7 +24285,7 @@
         <v>-112</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52830188679245282</v>
       </c>
       <c r="M10" s="1">
@@ -27276,7 +24295,7 @@
         <v>-110</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="P10" s="1">
@@ -27301,7 +24320,7 @@
         <v>0.68820000000000003</v>
       </c>
       <c r="F11" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.68820000000000003</v>
       </c>
       <c r="G11" s="14">
@@ -27309,7 +24328,7 @@
         <v>-2.3226181818181817</v>
       </c>
       <c r="H11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9.1028423331054986E-2</v>
       </c>
       <c r="I11" s="10">
@@ -27323,7 +24342,7 @@
         <v>-109</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52153110047846885</v>
       </c>
       <c r="M11" s="1">
@@ -27333,7 +24352,7 @@
         <v>-110</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="P11" s="1">
@@ -27358,7 +24377,7 @@
         <v>0.69510000000000005</v>
       </c>
       <c r="F12" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.69510000000000005</v>
       </c>
       <c r="G12" s="14">
@@ -27366,7 +24385,7 @@
         <v>-3.0177181818181817</v>
       </c>
       <c r="H12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.13975593655856822</v>
       </c>
       <c r="I12" s="10">
@@ -27380,7 +24399,7 @@
         <v>-109</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52153110047846885</v>
       </c>
       <c r="M12" s="1">
@@ -27390,7 +24409,7 @@
         <v>-116</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.53703703703703709</v>
       </c>
       <c r="P12" s="1">
@@ -27437,7 +24456,7 @@
         <v>-107</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.51690821256038644</v>
       </c>
       <c r="M13" s="1">
@@ -27447,7 +24466,7 @@
         <v>-107</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.51690821256038644</v>
       </c>
       <c r="P13" s="1">
@@ -27494,7 +24513,7 @@
         <v>-110</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="M14" s="1">
@@ -27504,7 +24523,7 @@
         <v>-114</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.53271028037383172</v>
       </c>
       <c r="P14" s="1">
@@ -27551,7 +24570,7 @@
         <v>-109</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52153110047846885</v>
       </c>
       <c r="M15" s="1">
@@ -27561,7 +24580,7 @@
         <v>-110</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="P15" s="1">
@@ -27608,7 +24627,7 @@
         <v>-110</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.52380952380952384</v>
       </c>
       <c r="M16" s="1">
@@ -27618,7 +24637,7 @@
         <v>-103</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.5073891625615764</v>
       </c>
       <c r="P16" s="1">
@@ -27879,7 +24898,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5527B6-58FD-524E-85CF-A53FB2DF16C9}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -27951,7 +24970,7 @@
         <v>416</v>
       </c>
       <c r="K2" s="1">
-        <f>IF(J2="W",(D2/100)*E2,IF(J2="",0,-E2))</f>
+        <f>IF(J2=0,0,IF(J2="P",0,IF(J2="L",-E2,IF(D2&lt;0,E2*(100/-D2),E2*(D2/100)))/1))</f>
         <v>0</v>
       </c>
     </row>
@@ -27981,7 +25000,7 @@
         <v>417</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K7" si="0">IF(J3="W",(D3/100)*E3,IF(J3="",0,-E3))</f>
+        <f t="shared" ref="K3:K12" si="0">IF(J3=0,0,IF(J3="P",0,IF(J3="L",-E3,IF(D3&lt;0,E3*(100/-D3),E3*(D3/100)))/1))</f>
         <v>0</v>
       </c>
     </row>
@@ -28104,6 +25123,156 @@
         <v>448</v>
       </c>
       <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1">
+        <v>281</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="F8" s="1">
+        <v>281</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>155</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>155</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="1">
+        <v>111</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>111</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-144</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-144</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-142</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-142</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADC4D43-A972-FE4C-9910-71FD28BA4E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84D6555-85CD-B948-BFC3-0B2E0B0756D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="454">
   <si>
     <t>Team</t>
   </si>
@@ -1401,6 +1401,12 @@
   </si>
   <si>
     <t>03/16/2025</t>
+  </si>
+  <si>
+    <t>03/17/2026</t>
+  </si>
+  <si>
+    <t>HOW/UMBC</t>
   </si>
 </sst>
 </file>
@@ -23945,7 +23951,7 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f>COUNTIF($C$6:$C$150,"W")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <f>COUNTIF($C$6:$C$150,"L")</f>
@@ -23957,15 +23963,15 @@
       </c>
       <c r="D2" s="13">
         <f>AVERAGE(H6:H150)</f>
-        <v>2.4502342779500797E-2</v>
+        <v>3.113621418265972E-2</v>
       </c>
       <c r="E2" s="1">
         <f ca="1">COUNTIF(OFFSET($C$6,COUNTA($C$6:$C$1500)-10,0,10,1),"W")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1">
         <f ca="1">COUNTIF(OFFSET($C$6,COUNTA($C$6:$C$1500)-10,0,10,1),"L")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -24136,7 +24142,7 @@
         <v>425</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" ref="B8:B16" si="4">B7+1</f>
+        <f t="shared" ref="B8:B17" si="4">B7+1</f>
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -24644,20 +24650,64 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="17" spans="6:16" x14ac:dyDescent="0.2">
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.70909999999999995</v>
+      </c>
+      <c r="F17" s="14">
+        <f t="shared" ref="F17" si="9">IF(C17="P",0,IF(C17="L",-E17,IF(K17&lt;0,E17*(100/-K17),E17*(K17/100)))/1)</f>
+        <v>0.67533333333333323</v>
+      </c>
+      <c r="G17" s="14">
+        <f t="shared" ref="G17" si="10">F17+G16</f>
+        <v>-2.6199848484848491</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" ref="H17" si="11">((M17-P17)*3.55%)+(O17-L17)</f>
+        <v>0.10410879961740788</v>
+      </c>
+      <c r="I17" s="10">
+        <f>AVERAGE($H$6:H17)</f>
+        <v>3.113621418265972E-2</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K17" s="1">
+        <v>-105</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" ref="L17" si="12">IF(K17&lt;0,K17/(K17-100),100/(K17+100))</f>
+        <v>0.51219512195121952</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2</v>
+      </c>
+      <c r="N17" s="1">
+        <v>-104</v>
+      </c>
+      <c r="O17" s="12">
+        <f t="shared" ref="O17" si="13">IF(N17&lt;0,N17/(N17-100),100/(N17+100))</f>
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="P17" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="10"/>
@@ -24670,7 +24720,7 @@
       <c r="O18" s="12"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="10"/>
@@ -24683,7 +24733,7 @@
       <c r="O19" s="12"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="10"/>
@@ -24696,7 +24746,7 @@
       <c r="O20" s="12"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="10"/>
@@ -24709,7 +24759,7 @@
       <c r="O21" s="12"/>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="10"/>
@@ -24722,7 +24772,7 @@
       <c r="O22" s="12"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="10"/>
@@ -24735,7 +24785,7 @@
       <c r="O23" s="12"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="10"/>
@@ -24748,7 +24798,7 @@
       <c r="O24" s="12"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="10"/>
@@ -24761,7 +24811,7 @@
       <c r="O25" s="12"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="10"/>
@@ -24774,7 +24824,7 @@
       <c r="O26" s="12"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="10"/>
@@ -24787,7 +24837,7 @@
       <c r="O27" s="12"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
       <c r="H28" s="10"/>
@@ -24800,7 +24850,7 @@
       <c r="O28" s="12"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
       <c r="H29" s="10"/>
@@ -24813,7 +24863,7 @@
       <c r="O29" s="12"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="10"/>
@@ -24826,7 +24876,7 @@
       <c r="O30" s="12"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="10"/>
@@ -24839,7 +24889,7 @@
       <c r="O31" s="12"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="6:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="10"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84D6555-85CD-B948-BFC3-0B2E0B0756D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45A89AF-05BB-7A41-B913-8B561646A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" activeTab="1" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="15760" yWindow="800" windowWidth="30500" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -1567,223 +1567,223 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="B2">
-            <v>13</v>
+            <v>1</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Nebraska</v>
+            <v>Howard</v>
           </cell>
           <cell r="D2" t="str">
-            <v>Troy</v>
+            <v>Michigan</v>
           </cell>
           <cell r="E2">
-            <v>21.024999999999999</v>
+            <v>-32.725000000000001</v>
           </cell>
           <cell r="F2" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.64124134938575506</v>
+            <v>0.52348182337177573</v>
           </cell>
           <cell r="H2">
-            <v>6.8642733484034296E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I2">
-            <v>0.22418803064553239</v>
+            <v>-6.2560992660992687E-4</v>
           </cell>
           <cell r="J2">
             <v>0.82374745212732714</v>
           </cell>
           <cell r="K2">
-            <v>1.3399061576083495</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>20</v>
+            <v>2</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Alabama</v>
+            <v>Texas</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Hofstra</v>
+            <v>BYU</v>
           </cell>
           <cell r="E3">
-            <v>21.09470868445722</v>
+            <v>-1.644803862558186</v>
           </cell>
           <cell r="F3" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.63457190270907826</v>
+            <v>0.52131321988914425</v>
           </cell>
           <cell r="H3">
-            <v>6.3040398275625784E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I3">
-            <v>0.21145545062642221</v>
+            <v>-4.7656711207245683E-3</v>
           </cell>
           <cell r="J3">
-            <v>0.81648449863375538</v>
+            <v>1.81823394406555E-3</v>
           </cell>
           <cell r="K3">
-            <v>1.2305485743402154</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="4">
           <cell r="B4">
-            <v>17</v>
+            <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Arkansas</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Hawaii</v>
+            <v>Florida</v>
           </cell>
           <cell r="E4">
-            <v>22.324999999999999</v>
+            <v>-35</v>
           </cell>
           <cell r="F4" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.62859142388829925</v>
+            <v>0.5</v>
           </cell>
           <cell r="H4">
-            <v>5.801679606617148E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.20003817287766221</v>
+            <v>-4.5454545454545407E-2</v>
           </cell>
           <cell r="J4">
             <v>0.82374745212732714</v>
           </cell>
           <cell r="K4">
-            <v>1.1324878592116674</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="5">
           <cell r="B5">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Michigan State</v>
+            <v>Miami (OH)</v>
           </cell>
           <cell r="D5" t="str">
-            <v>North Dakota State</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="E5">
-            <v>22.65</v>
+            <v>-15.303312069482359</v>
           </cell>
           <cell r="F5" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.62540649394971881</v>
+            <v>0.58474760808922221</v>
           </cell>
           <cell r="H5">
-            <v>5.5341454917763828E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I5">
-            <v>0.1939578520858268</v>
+            <v>0.11633634271578799</v>
           </cell>
           <cell r="J5">
-            <v>0.82374745212732714</v>
+            <v>0.64305103384973317</v>
           </cell>
           <cell r="K5">
-            <v>1.0802651999947499</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6">
-            <v>12</v>
+            <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Vanderbilt</v>
+            <v>Louisville</v>
           </cell>
           <cell r="D6" t="str">
-            <v>McNeese</v>
+            <v>South Florida</v>
           </cell>
           <cell r="E6">
-            <v>17.448430884808509</v>
+            <v>8.0927764549457955</v>
           </cell>
           <cell r="F6" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.62141047113878456</v>
+            <v>0.58883474470434349</v>
           </cell>
           <cell r="H6">
-            <v>5.1984795756579022E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I6">
-            <v>0.1863290812649524</v>
+            <v>0.1241390580719285</v>
           </cell>
           <cell r="J6">
-            <v>0.74660937378926895</v>
+            <v>0.46272230131594561</v>
           </cell>
           <cell r="K6">
-            <v>1.0147432131684224</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7">
-            <v>33</v>
+            <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Howard</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D7" t="str">
-            <v>UMBC</v>
+            <v>North Dakota State</v>
           </cell>
           <cell r="E7">
-            <v>2.711720411891148</v>
+            <v>22.65</v>
           </cell>
           <cell r="F7" t="b">
             <v>1</v>
           </cell>
           <cell r="G7">
-            <v>0.61580539290283809</v>
+            <v>0.62540649394971881</v>
           </cell>
           <cell r="H7">
-            <v>4.7276530038383939E-2</v>
+            <v>5.5341454917763828E-2</v>
           </cell>
           <cell r="I7">
-            <v>0.1756284773599637</v>
+            <v>0.1939578520858268</v>
           </cell>
           <cell r="J7">
-            <v>0.3634228852259655</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K7">
-            <v>0.92283786634925447</v>
+            <v>1.0802651999947499</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8">
-            <v>61</v>
+            <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Northern Iowa</v>
+            <v>Georgia</v>
           </cell>
           <cell r="D8" t="str">
-            <v>St. John's</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="E8">
-            <v>-7.0324352932968432</v>
+            <v>4.2861663978745774</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.60996307409599937</v>
+            <v>0.55680965526509907</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0.164474959637817</v>
+            <v>6.3000250960643767E-2</v>
           </cell>
           <cell r="J8">
-            <v>4.0627657807308433E-2</v>
+            <v>0.27233205754770629</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1791,31 +1791,31 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>30</v>
+            <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Kansas</v>
+            <v>Duke</v>
           </cell>
           <cell r="D9" t="str">
-            <v>California Baptist</v>
+            <v>Siena</v>
           </cell>
           <cell r="E9">
-            <v>18.573029871345032</v>
+            <v>30.774999999999999</v>
           </cell>
           <cell r="F9" t="b">
             <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.59561500793361322</v>
+            <v>0.54354746906015161</v>
           </cell>
           <cell r="H9">
             <v>0</v>
           </cell>
           <cell r="I9">
-            <v>0.13708319696417071</v>
+            <v>3.7681531842107652E-2</v>
           </cell>
           <cell r="J9">
-            <v>0.72543986092307822</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1823,31 +1823,31 @@
         </row>
         <row r="10">
           <cell r="B10">
-            <v>23</v>
+            <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Uconn</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="D10" t="str">
-            <v>Furman</v>
+            <v>TCU</v>
           </cell>
           <cell r="E10">
-            <v>25.492859365224369</v>
+            <v>4.5795233045545602</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.59510350502049691</v>
+            <v>0.56404001660924974</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>0.13610669140276691</v>
+            <v>7.6803668072204068E-2</v>
           </cell>
           <cell r="J10">
-            <v>0.82144469910078188</v>
+            <v>0.29860436775963528</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1855,31 +1855,31 @@
         </row>
         <row r="11">
           <cell r="B11">
-            <v>52</v>
+            <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Hofstra</v>
+            <v>North Carolina</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Alabama</v>
+            <v>VCU</v>
           </cell>
           <cell r="E11">
-            <v>-18.409254461666698</v>
+            <v>5.8338810410605051</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.59279510849473038</v>
+            <v>0.5825290100863949</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>0.13169975258084901</v>
+            <v>0.1121008374376631</v>
           </cell>
           <cell r="J11">
-            <v>0.71813726064377859</v>
+            <v>0.38065457771620442</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1887,31 +1887,31 @@
         </row>
         <row r="12">
           <cell r="B12">
-            <v>57</v>
+            <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Missouri</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Miami</v>
+            <v>Pennsylvania</v>
           </cell>
           <cell r="E12">
-            <v>1.742263875348123</v>
+            <v>27.2</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.59246539086017058</v>
+            <v>0.58001156955860289</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>0.1310702916421439</v>
+            <v>0.1072948146118783</v>
           </cell>
           <cell r="J12">
-            <v>0.2773673651949719</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1919,95 +1919,95 @@
         </row>
         <row r="13">
           <cell r="B13">
-            <v>18</v>
+            <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Gonzaga</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Kennesaw State</v>
+            <v>McNeese</v>
           </cell>
           <cell r="E13">
-            <v>23.450459942010621</v>
+            <v>17.448430884808509</v>
           </cell>
           <cell r="F13" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G13">
-            <v>0.58799578958333887</v>
+            <v>0.62141047113878467</v>
           </cell>
           <cell r="H13">
-            <v>0</v>
+            <v>5.1984795756579258E-2</v>
           </cell>
           <cell r="I13">
-            <v>0.12253741647728331</v>
+            <v>0.1863290812649526</v>
           </cell>
           <cell r="J13">
-            <v>0.78843548732025015</v>
+            <v>0.74660937378926906</v>
           </cell>
           <cell r="K13">
-            <v>0</v>
+            <v>1.0147432131684271</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>49</v>
+            <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Hawaii</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Arkansas</v>
+            <v>Troy</v>
           </cell>
           <cell r="E14">
-            <v>-19.689265506637959</v>
+            <v>21.024999999999999</v>
           </cell>
           <cell r="F14" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G14">
-            <v>0.58728757996436998</v>
+            <v>0.64124134938575506</v>
           </cell>
           <cell r="H14">
-            <v>0</v>
+            <v>6.8642733484034296E-2</v>
           </cell>
           <cell r="I14">
-            <v>0.1211853799319791</v>
+            <v>0.22418803064553239</v>
           </cell>
           <cell r="J14">
-            <v>0.73158718099349851</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K14">
-            <v>0</v>
+            <v>1.3399061576083495</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15">
-            <v>10</v>
+            <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>North Carolina</v>
+            <v>Saint Mary's</v>
           </cell>
           <cell r="D15" t="str">
-            <v>VCU</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="E15">
-            <v>5.5088810410605049</v>
+            <v>5.9454473885420782</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.58679379170739043</v>
+            <v>0.56073795565580786</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>0.1202426932595636</v>
+            <v>7.0499733524724162E-2</v>
           </cell>
           <cell r="J15">
-            <v>0.38065457771620442</v>
+            <v>0.33336045600883768</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -2015,31 +2015,31 @@
         </row>
         <row r="16">
           <cell r="B16">
-            <v>48</v>
+            <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>High Point</v>
+            <v>Houston</v>
           </cell>
           <cell r="D16" t="str">
-            <v>Wisconsin</v>
+            <v>Idaho</v>
           </cell>
           <cell r="E16">
-            <v>-6.7399272078176624</v>
+            <v>27.524999999999999</v>
           </cell>
           <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.58072734404629345</v>
+            <v>0.57672006180649049</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>0.10866129317928749</v>
+            <v>0.10101102708511819</v>
           </cell>
           <cell r="J16">
-            <v>2.202740613184884E-2</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -2047,31 +2047,31 @@
         </row>
         <row r="17">
           <cell r="B17">
-            <v>5</v>
+            <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Louisville</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="D17" t="str">
-            <v>South Florida</v>
+            <v>High Point</v>
           </cell>
           <cell r="E17">
-            <v>8.742776454945794</v>
+            <v>11.446368832524669</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.58030489249754802</v>
+            <v>0.53601454769519918</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>0.1078547947680463</v>
+            <v>2.3300500145380321E-2</v>
           </cell>
           <cell r="J17">
-            <v>0.46272230131594538</v>
+            <v>0.44405986090341548</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2079,63 +2079,63 @@
         </row>
         <row r="18">
           <cell r="B18">
-            <v>64</v>
+            <v>17</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Utah State</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Villanova</v>
+            <v>Hawaii</v>
           </cell>
           <cell r="E18">
-            <v>5.2368487163496038</v>
+            <v>22.324999999999999</v>
           </cell>
           <cell r="F18" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G18">
-            <v>0.58016009009738734</v>
+            <v>0.62859142388829925</v>
           </cell>
           <cell r="H18">
-            <v>0</v>
+            <v>5.801679606617148E-2</v>
           </cell>
           <cell r="I18">
-            <v>0.10757835382228501</v>
+            <v>0.20003817287766221</v>
           </cell>
           <cell r="J18">
-            <v>0.3568520724234755</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K18">
-            <v>0</v>
+            <v>1.1324878592116674</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19">
-            <v>11</v>
+            <v>18</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Illinois</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="D19" t="str">
-            <v>Pennsylvania</v>
+            <v>Kennesaw State</v>
           </cell>
           <cell r="E19">
-            <v>27.2</v>
+            <v>24.750459942010622</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.58001156955860289</v>
+            <v>0.57433156451695166</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>0.1072948146118783</v>
+            <v>9.645116862327141E-2</v>
           </cell>
           <cell r="J19">
-            <v>0.82374745212732714</v>
+            <v>0.78843548732025037</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2143,31 +2143,31 @@
         </row>
         <row r="20">
           <cell r="B20">
-            <v>15</v>
+            <v>19</v>
           </cell>
           <cell r="C20" t="str">
-            <v>Houston</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="D20" t="str">
-            <v>Idaho</v>
+            <v>Akron</v>
           </cell>
           <cell r="E20">
-            <v>27.2</v>
+            <v>10.43081131270095</v>
           </cell>
           <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0.58001156955860289</v>
+            <v>0.56037723382257887</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>0.1072948146118783</v>
+            <v>6.9811082752196052E-2</v>
           </cell>
           <cell r="J20">
-            <v>0.82374745212732714</v>
+            <v>0.46800018669531451</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2175,63 +2175,63 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>53</v>
+            <v>20</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Iowa</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D21" t="str">
-            <v>Clemson</v>
+            <v>Hofstra</v>
           </cell>
           <cell r="E21">
-            <v>5.0603260407104784</v>
+            <v>21.09470868445722</v>
           </cell>
           <cell r="F21" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G21">
-            <v>0.57584311604296001</v>
+            <v>0.63457190270907837</v>
           </cell>
           <cell r="H21">
-            <v>0</v>
+            <v>6.3040398275625784E-2</v>
           </cell>
           <cell r="I21">
-            <v>9.9336857900196418E-2</v>
+            <v>0.21145545062642229</v>
           </cell>
           <cell r="J21">
-            <v>0.3413049040666058</v>
+            <v>0.81648449863375561</v>
           </cell>
           <cell r="K21">
-            <v>0</v>
+            <v>1.2305485743402154</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22">
-            <v>14</v>
+            <v>21</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Saint Mary's</v>
+            <v>Clemson</v>
           </cell>
           <cell r="D22" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Iowa</v>
           </cell>
           <cell r="E22">
-            <v>4.9704473885420759</v>
+            <v>3.3395963530867823E-2</v>
           </cell>
           <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0.57364154101220122</v>
+            <v>0.55056432776779607</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>9.5133851023293303E-2</v>
+            <v>5.1077353011247051E-2</v>
           </cell>
           <cell r="J22">
-            <v>0.33336045600883751</v>
+            <v>0.1222769560459742</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2239,31 +2239,31 @@
         </row>
         <row r="23">
           <cell r="B23">
-            <v>26</v>
+            <v>22</v>
           </cell>
           <cell r="C23" t="str">
-            <v>Purdue</v>
+            <v>UCLA</v>
           </cell>
           <cell r="D23" t="str">
-            <v>Queens University</v>
+            <v>UCF</v>
           </cell>
           <cell r="E23">
-            <v>28.175000000000001</v>
+            <v>7.3720101204148367</v>
           </cell>
           <cell r="F23" t="b">
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0.57012118173818638</v>
+            <v>0.53416767430541012</v>
           </cell>
           <cell r="H23">
             <v>0</v>
           </cell>
           <cell r="I23">
-            <v>8.841316513653763E-2</v>
+            <v>1.9774650946692118E-2</v>
           </cell>
           <cell r="J23">
-            <v>0.82374745212732714</v>
+            <v>0.31575710935178802</v>
           </cell>
           <cell r="K23">
             <v>0</v>
@@ -2271,31 +2271,31 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>28</v>
+            <v>23</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Iowa State</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D24" t="str">
-            <v>Tennessee State</v>
+            <v>Furman</v>
           </cell>
           <cell r="E24">
-            <v>28.175000000000001</v>
+            <v>25.817859365224368</v>
           </cell>
           <cell r="F24" t="b">
             <v>0</v>
           </cell>
           <cell r="G24">
-            <v>0.57012118173818638</v>
+            <v>0.59183071427116474</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>8.841316513653763E-2</v>
+            <v>0.12985863633586001</v>
           </cell>
           <cell r="J24">
-            <v>0.82374745212732714</v>
+            <v>0.82144469910078211</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2303,31 +2303,31 @@
         </row>
         <row r="25">
           <cell r="B25">
-            <v>43</v>
+            <v>24</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Pennsylvania</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D25" t="str">
-            <v>Illinois</v>
+            <v>Wright State</v>
           </cell>
           <cell r="E25">
-            <v>-26.584731887521901</v>
+            <v>20.329275195939459</v>
           </cell>
           <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0.56981806080452269</v>
+            <v>0.54026304364429201</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>8.7834479717725178E-2</v>
+            <v>3.1411265139102973E-2</v>
           </cell>
           <cell r="J25">
-            <v>0.80569684947500253</v>
+            <v>0.66902836142407174</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2335,31 +2335,31 @@
         </row>
         <row r="26">
           <cell r="B26">
-            <v>38</v>
+            <v>25</v>
           </cell>
           <cell r="C26" t="str">
-            <v>North Dakota State</v>
+            <v>Miami</v>
           </cell>
           <cell r="D26" t="str">
-            <v>Michigan State</v>
+            <v>Missouri</v>
           </cell>
           <cell r="E26">
-            <v>-18.957923408995232</v>
+            <v>4.4770135283782926</v>
           </cell>
           <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0.56431388885662104</v>
+            <v>0.56151576507289314</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>7.7326515089912951E-2</v>
+            <v>7.1984642411886957E-2</v>
           </cell>
           <cell r="J26">
-            <v>0.68214224406760438</v>
+            <v>0.28944093497921641</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2367,31 +2367,31 @@
         </row>
         <row r="27">
           <cell r="B27">
-            <v>9</v>
+            <v>26</v>
           </cell>
           <cell r="C27" t="str">
-            <v>Ohio State</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D27" t="str">
-            <v>TCU</v>
+            <v>Queens University</v>
           </cell>
           <cell r="E27">
-            <v>4.5795233045545594</v>
+            <v>28.824999999999999</v>
           </cell>
           <cell r="F27" t="b">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0.56404001660924963</v>
+            <v>0.56350265429938384</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>7.6803668072203846E-2</v>
+            <v>7.5777794571550983E-2</v>
           </cell>
           <cell r="J27">
-            <v>0.29860436775963528</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2399,31 +2399,31 @@
         </row>
         <row r="28">
           <cell r="B28">
-            <v>35</v>
+            <v>27</v>
           </cell>
           <cell r="C28" t="str">
-            <v>Lehigh Mountain</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D28" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>Santa Clara</v>
           </cell>
           <cell r="E28">
-            <v>5.0772786070447582</v>
+            <v>5.4103511425263981</v>
           </cell>
           <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0.56398476960459853</v>
+            <v>0.54751955979773603</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>7.6698196517870021E-2</v>
+            <v>4.5264614159314258E-2</v>
           </cell>
           <cell r="J28">
-            <v>0.3140021880193648</v>
+            <v>0.28571132045463621</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2431,31 +2431,31 @@
         </row>
         <row r="29">
           <cell r="B29">
-            <v>1</v>
+            <v>28</v>
           </cell>
           <cell r="C29" t="str">
-            <v>UMBC</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D29" t="str">
-            <v>Howard</v>
+            <v>Tennessee State</v>
           </cell>
           <cell r="E29">
-            <v>4.5398147803963766</v>
+            <v>28.175000000000001</v>
           </cell>
           <cell r="F29" t="b">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0.56306251790939255</v>
+            <v>0.57012118173818638</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>7.4937534190658517E-2</v>
+            <v>8.841316513653763E-2</v>
           </cell>
           <cell r="J29">
-            <v>0.29505706343244742</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2463,31 +2463,31 @@
         </row>
         <row r="30">
           <cell r="B30">
-            <v>25</v>
+            <v>29</v>
           </cell>
           <cell r="C30" t="str">
-            <v>Miami</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D30" t="str">
-            <v>Missouri</v>
+            <v>Northern Iowa</v>
           </cell>
           <cell r="E30">
-            <v>4.4770135283782926</v>
+            <v>12.286890801195611</v>
           </cell>
           <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0.56151576507289314</v>
+            <v>0.51961234415784652</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>7.1984642411886957E-2</v>
+            <v>-8.0127975168384213E-3</v>
           </cell>
           <cell r="J30">
-            <v>0.28944093497921641</v>
+            <v>0.43263467267483419</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2495,31 +2495,31 @@
         </row>
         <row r="31">
           <cell r="B31">
-            <v>19</v>
+            <v>30</v>
           </cell>
           <cell r="C31" t="str">
-            <v>Texas Tech</v>
+            <v>Kansas</v>
           </cell>
           <cell r="D31" t="str">
-            <v>Akron</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="E31">
-            <v>10.43081131270095</v>
+            <v>18.573029871345032</v>
           </cell>
           <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0.56037723382257887</v>
+            <v>0.59561500793361322</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>6.9811082752196052E-2</v>
+            <v>0.13708319696417071</v>
           </cell>
           <cell r="J31">
-            <v>0.46800018669531451</v>
+            <v>0.72543986092307822</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2527,31 +2527,31 @@
         </row>
         <row r="32">
           <cell r="B32">
-            <v>2</v>
+            <v>31</v>
           </cell>
           <cell r="C32" t="str">
-            <v>Texas</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D32" t="str">
-            <v>NC State</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="E32">
-            <v>3.351492666553944</v>
+            <v>32.075000000000003</v>
           </cell>
           <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0.55842147595203739</v>
+            <v>0.5301795270136529</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>6.6077363181162307E-2</v>
+            <v>1.216091520788282E-2</v>
           </cell>
           <cell r="J32">
-            <v>0.24670500307592891</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2559,31 +2559,31 @@
         </row>
         <row r="33">
           <cell r="B33">
-            <v>7</v>
+            <v>32</v>
           </cell>
           <cell r="C33" t="str">
-            <v>Georgia</v>
+            <v>Villanova</v>
           </cell>
           <cell r="D33" t="str">
-            <v>Saint Louis</v>
+            <v>Utah State</v>
           </cell>
           <cell r="E33">
-            <v>4.2861663978745757</v>
+            <v>-0.7512667989010704</v>
           </cell>
           <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0.55680965526509907</v>
+            <v>0.53110419949984844</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>6.3000250960643767E-2</v>
+            <v>1.3926199045165229E-2</v>
           </cell>
           <cell r="J33">
-            <v>0.27233205754770629</v>
+            <v>5.0370532033560012E-2</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -2591,31 +2591,31 @@
         </row>
         <row r="34">
           <cell r="B34">
-            <v>58</v>
+            <v>33</v>
           </cell>
           <cell r="C34" t="str">
-            <v>Queens University</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D34" t="str">
-            <v>Purdue</v>
+            <v>Howard</v>
           </cell>
           <cell r="E34">
-            <v>-27.266982450772101</v>
+            <v>32.725000000000001</v>
           </cell>
           <cell r="F34" t="b">
             <v>0</v>
           </cell>
           <cell r="G34">
-            <v>0.55453717792185397</v>
+            <v>0.52348182337177573</v>
           </cell>
           <cell r="H34">
             <v>0</v>
           </cell>
           <cell r="I34">
-            <v>5.8661885123539433E-2</v>
+            <v>-6.2560992660992687E-4</v>
           </cell>
           <cell r="J34">
-            <v>0.79642984416271356</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K34">
             <v>0</v>
@@ -2623,31 +2623,31 @@
         </row>
         <row r="35">
           <cell r="B35">
-            <v>54</v>
+            <v>34</v>
           </cell>
           <cell r="C35" t="str">
-            <v>UCF</v>
+            <v>BYU</v>
           </cell>
           <cell r="D35" t="str">
-            <v>UCLA</v>
+            <v>Texas</v>
           </cell>
           <cell r="E35">
-            <v>-3.8266435714985798</v>
+            <v>4.7488665200927818</v>
           </cell>
           <cell r="F35" t="b">
             <v>0</v>
           </cell>
           <cell r="G35">
-            <v>0.55402405102411312</v>
+            <v>0.55588891719011857</v>
           </cell>
           <cell r="H35">
             <v>0</v>
           </cell>
           <cell r="I35">
-            <v>5.7682279227852407E-2</v>
+            <v>6.1242478272044543E-2</v>
           </cell>
           <cell r="J35">
-            <v>6.7349851388678328E-3</v>
+            <v>0.2846826853308746</v>
           </cell>
           <cell r="K35">
             <v>0</v>
@@ -2655,31 +2655,31 @@
         </row>
         <row r="36">
           <cell r="B36">
-            <v>45</v>
+            <v>35</v>
           </cell>
           <cell r="C36" t="str">
-            <v>Troy</v>
+            <v>Florida</v>
           </cell>
           <cell r="D36" t="str">
-            <v>Nebraska</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="E36">
-            <v>-15.800660571957931</v>
+            <v>35</v>
           </cell>
           <cell r="F36" t="b">
             <v>0</v>
           </cell>
           <cell r="G36">
-            <v>0.55314950886908421</v>
+            <v>0.5</v>
           </cell>
           <cell r="H36">
             <v>0</v>
           </cell>
           <cell r="I36">
-            <v>5.6012698750069867E-2</v>
+            <v>-4.5454545454545407E-2</v>
           </cell>
           <cell r="J36">
-            <v>0.59505082789393093</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K36">
             <v>0</v>
@@ -2690,28 +2690,28 @@
             <v>36</v>
           </cell>
           <cell r="C37" t="str">
-            <v>SMU</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D37" t="str">
             <v>Miami (OH)</v>
           </cell>
           <cell r="E37">
-            <v>10.615529021860739</v>
+            <v>16.737612085833891</v>
           </cell>
           <cell r="F37" t="b">
             <v>0</v>
           </cell>
           <cell r="G37">
-            <v>0.55259508184797035</v>
+            <v>0.60999917530085424</v>
           </cell>
           <cell r="H37">
             <v>0</v>
           </cell>
           <cell r="I37">
-            <v>5.495424716430708E-2</v>
+            <v>0.16454388011981269</v>
           </cell>
           <cell r="J37">
-            <v>0.45623272316206448</v>
+            <v>0.71602282287691876</v>
           </cell>
           <cell r="K37">
             <v>0</v>
@@ -2719,31 +2719,31 @@
         </row>
         <row r="38">
           <cell r="B38">
-            <v>56</v>
+            <v>37</v>
           </cell>
           <cell r="C38" t="str">
-            <v>Wright State</v>
+            <v>South Florida</v>
           </cell>
           <cell r="D38" t="str">
-            <v>Virginia</v>
+            <v>Louisville</v>
           </cell>
           <cell r="E38">
-            <v>-16.44502010603955</v>
+            <v>-3.3907071170746428</v>
           </cell>
           <cell r="F38" t="b">
             <v>0</v>
           </cell>
           <cell r="G38">
-            <v>0.5510981247018647</v>
+            <v>0.52763684713245484</v>
           </cell>
           <cell r="H38">
             <v>0</v>
           </cell>
           <cell r="I38">
-            <v>5.2096419885378047E-2</v>
+            <v>7.3067081619592744E-3</v>
           </cell>
           <cell r="J38">
-            <v>0.39898549067999339</v>
+            <v>4.2751559352500079E-2</v>
           </cell>
           <cell r="K38">
             <v>0</v>
@@ -2751,31 +2751,31 @@
         </row>
         <row r="39">
           <cell r="B39">
-            <v>21</v>
+            <v>38</v>
           </cell>
           <cell r="C39" t="str">
-            <v>Clemson</v>
+            <v>North Dakota State</v>
           </cell>
           <cell r="D39" t="str">
-            <v>Iowa</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="E39">
-            <v>3.3395963530867379E-2</v>
+            <v>-18.957923408995232</v>
           </cell>
           <cell r="F39" t="b">
             <v>0</v>
           </cell>
           <cell r="G39">
-            <v>0.55056432776779596</v>
+            <v>0.56431388885662115</v>
           </cell>
           <cell r="H39">
             <v>0</v>
           </cell>
           <cell r="I39">
-            <v>5.1077353011246829E-2</v>
+            <v>7.7326515089913173E-2</v>
           </cell>
           <cell r="J39">
-            <v>0.12227695604597411</v>
+            <v>0.68214224406760449</v>
           </cell>
           <cell r="K39">
             <v>0</v>
@@ -2783,31 +2783,31 @@
         </row>
         <row r="40">
           <cell r="B40">
-            <v>44</v>
+            <v>39</v>
           </cell>
           <cell r="C40" t="str">
-            <v>McNeese</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D40" t="str">
-            <v>Vanderbilt</v>
+            <v>Georgia</v>
           </cell>
           <cell r="E40">
-            <v>-13.561700995584451</v>
+            <v>-2.323634492416264</v>
           </cell>
           <cell r="F40" t="b">
             <v>0</v>
           </cell>
           <cell r="G40">
-            <v>0.5494989938305499</v>
+            <v>0.50806891743100513</v>
           </cell>
           <cell r="H40">
             <v>0</v>
           </cell>
           <cell r="I40">
-            <v>4.9043533676504381E-2</v>
+            <v>-3.0050248540808341E-2</v>
           </cell>
           <cell r="J40">
-            <v>0.53201297998911168</v>
+            <v>9.3917362818843442E-2</v>
           </cell>
           <cell r="K40">
             <v>0</v>
@@ -2815,31 +2815,31 @@
         </row>
         <row r="41">
           <cell r="B41">
-            <v>4</v>
+            <v>40</v>
           </cell>
           <cell r="C41" t="str">
-            <v>Miami (OH)</v>
+            <v>Siena</v>
           </cell>
           <cell r="D41" t="str">
-            <v>SMU</v>
+            <v>Duke</v>
           </cell>
           <cell r="E41">
-            <v>-6.5280711453208946</v>
+            <v>-30.774999999999999</v>
           </cell>
           <cell r="F41" t="b">
             <v>0</v>
           </cell>
           <cell r="G41">
-            <v>0.54904367295244916</v>
+            <v>0.54354746906015161</v>
           </cell>
           <cell r="H41">
             <v>0</v>
           </cell>
           <cell r="I41">
-            <v>4.8174284727402983E-2</v>
+            <v>3.7681531842107652E-2</v>
           </cell>
           <cell r="J41">
-            <v>9.203326713974791E-2</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K41">
             <v>0</v>
@@ -2847,31 +2847,31 @@
         </row>
         <row r="42">
           <cell r="B42">
-            <v>27</v>
+            <v>41</v>
           </cell>
           <cell r="C42" t="str">
-            <v>Kentucky</v>
+            <v>TCU</v>
           </cell>
           <cell r="D42" t="str">
-            <v>Santa Clara</v>
+            <v>Ohio State</v>
           </cell>
           <cell r="E42">
-            <v>5.4103511425263981</v>
+            <v>-1.9384527984340609</v>
           </cell>
           <cell r="F42" t="b">
             <v>0</v>
           </cell>
           <cell r="G42">
-            <v>0.54751955979773603</v>
+            <v>0.50153460752444023</v>
           </cell>
           <cell r="H42">
             <v>0</v>
           </cell>
           <cell r="I42">
-            <v>4.5264614159314258E-2</v>
+            <v>-4.2524840180614032E-2</v>
           </cell>
           <cell r="J42">
-            <v>0.28571132045463621</v>
+            <v>5.8602197560207403E-2</v>
           </cell>
           <cell r="K42">
             <v>0</v>
@@ -2879,31 +2879,31 @@
         </row>
         <row r="43">
           <cell r="B43">
-            <v>24</v>
+            <v>42</v>
           </cell>
           <cell r="C43" t="str">
-            <v>Virginia</v>
+            <v>VCU</v>
           </cell>
           <cell r="D43" t="str">
-            <v>Wright State</v>
+            <v>North Carolina</v>
           </cell>
           <cell r="E43">
-            <v>20.329275195939459</v>
+            <v>-2.058823308460128</v>
           </cell>
           <cell r="F43" t="b">
             <v>0</v>
           </cell>
           <cell r="G43">
-            <v>0.54026304364429201</v>
+            <v>0.51099885845456794</v>
           </cell>
           <cell r="H43">
             <v>0</v>
           </cell>
           <cell r="I43">
-            <v>3.1411265139102973E-2</v>
+            <v>-2.44567247685521E-2</v>
           </cell>
           <cell r="J43">
-            <v>0.66902836142407174</v>
+            <v>3.9825391009848547E-2</v>
           </cell>
           <cell r="K43">
             <v>0</v>
@@ -2911,31 +2911,31 @@
         </row>
         <row r="44">
           <cell r="B44">
-            <v>51</v>
+            <v>43</v>
           </cell>
           <cell r="C44" t="str">
-            <v>Akron</v>
+            <v>Pennsylvania</v>
           </cell>
           <cell r="D44" t="str">
-            <v>Texas Tech</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E44">
-            <v>-6.3844148545709842</v>
+            <v>-26.584731887521901</v>
           </cell>
           <cell r="F44" t="b">
             <v>0</v>
           </cell>
           <cell r="G44">
-            <v>0.5402144785835673</v>
+            <v>0.56981806080452269</v>
           </cell>
           <cell r="H44">
             <v>0</v>
           </cell>
           <cell r="I44">
-            <v>3.1318550023173963E-2</v>
+            <v>8.7834479717725178E-2</v>
           </cell>
           <cell r="J44">
-            <v>0.1086427549134706</v>
+            <v>0.80569684947500253</v>
           </cell>
           <cell r="K44">
             <v>0</v>
@@ -2943,31 +2943,31 @@
         </row>
         <row r="45">
           <cell r="B45">
-            <v>8</v>
+            <v>44</v>
           </cell>
           <cell r="C45" t="str">
-            <v>Duke</v>
+            <v>McNeese</v>
           </cell>
           <cell r="D45" t="str">
-            <v>Siena</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="E45">
-            <v>31.1</v>
+            <v>-13.561700995584451</v>
           </cell>
           <cell r="F45" t="b">
             <v>0</v>
           </cell>
           <cell r="G45">
-            <v>0.54020950401036416</v>
+            <v>0.5494989938305499</v>
           </cell>
           <cell r="H45">
             <v>0</v>
           </cell>
           <cell r="I45">
-            <v>3.1309053110695262E-2</v>
+            <v>4.9043533676504381E-2</v>
           </cell>
           <cell r="J45">
-            <v>0.82374745212732714</v>
+            <v>0.53201297998911179</v>
           </cell>
           <cell r="K45">
             <v>0</v>
@@ -2975,31 +2975,31 @@
         </row>
         <row r="46">
           <cell r="B46">
-            <v>40</v>
+            <v>45</v>
           </cell>
           <cell r="C46" t="str">
-            <v>Siena</v>
+            <v>Troy</v>
           </cell>
           <cell r="D46" t="str">
-            <v>Duke</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="E46">
-            <v>-31.1</v>
+            <v>-15.800660571957931</v>
           </cell>
           <cell r="F46" t="b">
             <v>0</v>
           </cell>
           <cell r="G46">
-            <v>0.54020950401036405</v>
+            <v>0.55314950886908421</v>
           </cell>
           <cell r="H46">
             <v>0</v>
           </cell>
           <cell r="I46">
-            <v>3.130905311069504E-2</v>
+            <v>5.6012698750069867E-2</v>
           </cell>
           <cell r="J46">
-            <v>0.82374745212732714</v>
+            <v>0.59505082789393093</v>
           </cell>
           <cell r="K46">
             <v>0</v>
@@ -3007,31 +3007,31 @@
         </row>
         <row r="47">
           <cell r="B47">
-            <v>60</v>
+            <v>46</v>
           </cell>
           <cell r="C47" t="str">
-            <v>Tennessee State</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="D47" t="str">
-            <v>Iowa State</v>
+            <v>Saint Mary's</v>
           </cell>
           <cell r="E47">
-            <v>-26.430767349804981</v>
+            <v>-1.519712106349179</v>
           </cell>
           <cell r="F47" t="b">
             <v>0</v>
           </cell>
           <cell r="G47">
-            <v>0.53922786424151381</v>
+            <v>0.54925051273903736</v>
           </cell>
           <cell r="H47">
             <v>0</v>
           </cell>
           <cell r="I47">
-            <v>2.9435013551980971E-2</v>
+            <v>4.856916068361683E-2</v>
           </cell>
           <cell r="J47">
-            <v>0.76733006607214982</v>
+            <v>6.9318830663357978E-2</v>
           </cell>
           <cell r="K47">
             <v>0</v>
@@ -3039,31 +3039,31 @@
         </row>
         <row r="48">
           <cell r="B48">
-            <v>37</v>
+            <v>47</v>
           </cell>
           <cell r="C48" t="str">
-            <v>South Florida</v>
+            <v>Idaho</v>
           </cell>
           <cell r="D48" t="str">
-            <v>Louisville</v>
+            <v>Houston</v>
           </cell>
           <cell r="E48">
-            <v>-4.0407071170746427</v>
+            <v>-24.648801489183739</v>
           </cell>
           <cell r="F48" t="b">
             <v>0</v>
           </cell>
           <cell r="G48">
-            <v>0.53633546884354921</v>
+            <v>0.52432692572641548</v>
           </cell>
           <cell r="H48">
             <v>0</v>
           </cell>
           <cell r="I48">
-            <v>2.391316779223035E-2</v>
+            <v>9.8776729588412326E-4</v>
           </cell>
           <cell r="J48">
-            <v>4.2751559352500079E-2</v>
+            <v>0.72103790251730027</v>
           </cell>
           <cell r="K48">
             <v>0</v>
@@ -3071,31 +3071,31 @@
         </row>
         <row r="49">
           <cell r="B49">
-            <v>46</v>
+            <v>48</v>
           </cell>
           <cell r="C49" t="str">
-            <v>Texas A&amp;M</v>
+            <v>High Point</v>
           </cell>
           <cell r="D49" t="str">
-            <v>Saint Mary's</v>
+            <v>Wisconsin</v>
           </cell>
           <cell r="E49">
-            <v>-0.54471210634917988</v>
+            <v>-6.7399272078176624</v>
           </cell>
           <cell r="F49" t="b">
             <v>0</v>
           </cell>
           <cell r="G49">
-            <v>0.53623602221725253</v>
+            <v>0.58072734404629345</v>
           </cell>
           <cell r="H49">
             <v>0</v>
           </cell>
           <cell r="I49">
-            <v>2.3723315142027579E-2</v>
+            <v>0.10866129317928749</v>
           </cell>
           <cell r="J49">
-            <v>6.9318830663357978E-2</v>
+            <v>2.202740613184884E-2</v>
           </cell>
           <cell r="K49">
             <v>0</v>
@@ -3103,31 +3103,31 @@
         </row>
         <row r="50">
           <cell r="B50">
-            <v>16</v>
+            <v>49</v>
           </cell>
           <cell r="C50" t="str">
-            <v>Wisconsin</v>
+            <v>Hawaii</v>
           </cell>
           <cell r="D50" t="str">
-            <v>High Point</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="E50">
-            <v>11.446368832524669</v>
+            <v>-19.689265506637959</v>
           </cell>
           <cell r="F50" t="b">
             <v>0</v>
           </cell>
           <cell r="G50">
-            <v>0.53601454769519918</v>
+            <v>0.58728757996436998</v>
           </cell>
           <cell r="H50">
             <v>0</v>
           </cell>
           <cell r="I50">
-            <v>2.3300500145380321E-2</v>
+            <v>0.1211853799319791</v>
           </cell>
           <cell r="J50">
-            <v>0.44405986090341543</v>
+            <v>0.7315871809934984</v>
           </cell>
           <cell r="K50">
             <v>0</v>
@@ -3135,31 +3135,31 @@
         </row>
         <row r="51">
           <cell r="B51">
-            <v>3</v>
+            <v>50</v>
           </cell>
           <cell r="C51" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>Kennesaw State</v>
           </cell>
           <cell r="D51" t="str">
-            <v>Lehigh Mountain</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="E51">
-            <v>-1.0818703398805221</v>
+            <v>-20.239777212918948</v>
           </cell>
           <cell r="F51" t="b">
             <v>0</v>
           </cell>
           <cell r="G51">
-            <v>0.53531325069231817</v>
+            <v>0.51791998834141129</v>
           </cell>
           <cell r="H51">
             <v>0</v>
           </cell>
           <cell r="I51">
-            <v>2.1961660412607439E-2</v>
+            <v>-1.124365862094207E-2</v>
           </cell>
           <cell r="J51">
-            <v>4.9856358057364769E-2</v>
+            <v>0.56671791944483352</v>
           </cell>
           <cell r="K51">
             <v>0</v>
@@ -3167,31 +3167,31 @@
         </row>
         <row r="52">
           <cell r="B52">
-            <v>22</v>
+            <v>51</v>
           </cell>
           <cell r="C52" t="str">
-            <v>UCLA</v>
+            <v>Akron</v>
           </cell>
           <cell r="D52" t="str">
-            <v>UCF</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="E52">
-            <v>7.3720101204148367</v>
+            <v>-6.3844148545709851</v>
           </cell>
           <cell r="F52" t="b">
             <v>0</v>
           </cell>
           <cell r="G52">
-            <v>0.53416767430541012</v>
+            <v>0.54021447858356719</v>
           </cell>
           <cell r="H52">
             <v>0</v>
           </cell>
           <cell r="I52">
-            <v>1.9774650946692118E-2</v>
+            <v>3.1318550023173797E-2</v>
           </cell>
           <cell r="J52">
-            <v>0.3157571093517878</v>
+            <v>0.1086427549134706</v>
           </cell>
           <cell r="K52">
             <v>0</v>
@@ -3199,31 +3199,31 @@
         </row>
         <row r="53">
           <cell r="B53">
-            <v>32</v>
+            <v>52</v>
           </cell>
           <cell r="C53" t="str">
-            <v>Villanova</v>
+            <v>Hofstra</v>
           </cell>
           <cell r="D53" t="str">
-            <v>Utah State</v>
+            <v>Alabama</v>
           </cell>
           <cell r="E53">
-            <v>-0.75126679890107051</v>
+            <v>-18.409254461666709</v>
           </cell>
           <cell r="F53" t="b">
             <v>0</v>
           </cell>
           <cell r="G53">
-            <v>0.53110419949984844</v>
+            <v>0.59279510849473049</v>
           </cell>
           <cell r="H53">
             <v>0</v>
           </cell>
           <cell r="I53">
-            <v>1.3926199045165229E-2</v>
+            <v>0.13169975258084921</v>
           </cell>
           <cell r="J53">
-            <v>5.0370532033560012E-2</v>
+            <v>0.71813726064377881</v>
           </cell>
           <cell r="K53">
             <v>0</v>
@@ -3231,31 +3231,31 @@
         </row>
         <row r="54">
           <cell r="B54">
-            <v>31</v>
+            <v>53</v>
           </cell>
           <cell r="C54" t="str">
-            <v>Arizona</v>
+            <v>Iowa</v>
           </cell>
           <cell r="D54" t="str">
-            <v>Long Island University</v>
+            <v>Clemson</v>
           </cell>
           <cell r="E54">
-            <v>32.075000000000003</v>
+            <v>5.0603260407104793</v>
           </cell>
           <cell r="F54" t="b">
             <v>0</v>
           </cell>
           <cell r="G54">
-            <v>0.5301795270136529</v>
+            <v>0.57584311604296001</v>
           </cell>
           <cell r="H54">
             <v>0</v>
           </cell>
           <cell r="I54">
-            <v>1.216091520788282E-2</v>
+            <v>9.9336857900196418E-2</v>
           </cell>
           <cell r="J54">
-            <v>0.82374745212732714</v>
+            <v>0.34130490406660591</v>
           </cell>
           <cell r="K54">
             <v>0</v>
@@ -3263,31 +3263,31 @@
         </row>
         <row r="55">
           <cell r="B55">
-            <v>63</v>
+            <v>54</v>
           </cell>
           <cell r="C55" t="str">
-            <v>Long Island University</v>
+            <v>UCF</v>
           </cell>
           <cell r="D55" t="str">
-            <v>Arizona</v>
+            <v>UCLA</v>
           </cell>
           <cell r="E55">
-            <v>-32.075000000000003</v>
+            <v>-3.8266435714985798</v>
           </cell>
           <cell r="F55" t="b">
             <v>0</v>
           </cell>
           <cell r="G55">
-            <v>0.5301795270136529</v>
+            <v>0.55402405102411312</v>
           </cell>
           <cell r="H55">
             <v>0</v>
           </cell>
           <cell r="I55">
-            <v>1.216091520788282E-2</v>
+            <v>5.7682279227852407E-2</v>
           </cell>
           <cell r="J55">
-            <v>0.82374745212732714</v>
+            <v>6.7349851388679438E-3</v>
           </cell>
           <cell r="K55">
             <v>0</v>
@@ -3304,22 +3304,22 @@
             <v>Uconn</v>
           </cell>
           <cell r="E56">
-            <v>-21.85963814259874</v>
+            <v>-22.18463814259874</v>
           </cell>
           <cell r="F56" t="b">
             <v>0</v>
           </cell>
           <cell r="G56">
-            <v>0.52969024321570402</v>
+            <v>0.52587454985377191</v>
           </cell>
           <cell r="H56">
             <v>0</v>
           </cell>
           <cell r="I56">
-            <v>1.122682795725316E-2</v>
+            <v>3.9423224481100472E-3</v>
           </cell>
           <cell r="J56">
-            <v>0.68095911372035789</v>
+            <v>0.680959113720358</v>
           </cell>
           <cell r="K56">
             <v>0</v>
@@ -3327,31 +3327,31 @@
         </row>
         <row r="57">
           <cell r="B57">
-            <v>47</v>
+            <v>56</v>
           </cell>
           <cell r="C57" t="str">
-            <v>Idaho</v>
+            <v>Wright State</v>
           </cell>
           <cell r="D57" t="str">
-            <v>Houston</v>
+            <v>Virginia</v>
           </cell>
           <cell r="E57">
-            <v>-24.32380148918374</v>
+            <v>-16.44502010603955</v>
           </cell>
           <cell r="F57" t="b">
             <v>0</v>
           </cell>
           <cell r="G57">
-            <v>0.52802701210828917</v>
+            <v>0.5510981247018647</v>
           </cell>
           <cell r="H57">
             <v>0</v>
           </cell>
           <cell r="I57">
-            <v>8.05156857037026E-3</v>
+            <v>5.2096419885378047E-2</v>
           </cell>
           <cell r="J57">
-            <v>0.72103790251730027</v>
+            <v>0.39898549067999362</v>
           </cell>
           <cell r="K57">
             <v>0</v>
@@ -3359,31 +3359,31 @@
         </row>
         <row r="58">
           <cell r="B58">
-            <v>62</v>
+            <v>57</v>
           </cell>
           <cell r="C58" t="str">
-            <v>California Baptist</v>
+            <v>Missouri</v>
           </cell>
           <cell r="D58" t="str">
-            <v>Kansas</v>
+            <v>Miami</v>
           </cell>
           <cell r="E58">
-            <v>-15.090084378042731</v>
+            <v>1.7422638753481221</v>
           </cell>
           <cell r="F58" t="b">
             <v>0</v>
           </cell>
           <cell r="G58">
-            <v>0.52632532157094747</v>
+            <v>0.59246539086017058</v>
           </cell>
           <cell r="H58">
             <v>0</v>
           </cell>
           <cell r="I58">
-            <v>4.8028866354452027E-3</v>
+            <v>0.1310702916421439</v>
           </cell>
           <cell r="J58">
-            <v>0.52510282618406234</v>
+            <v>0.27736736519497179</v>
           </cell>
           <cell r="K58">
             <v>0</v>
@@ -3391,31 +3391,31 @@
         </row>
         <row r="59">
           <cell r="B59">
-            <v>29</v>
+            <v>58</v>
           </cell>
           <cell r="C59" t="str">
-            <v>St. John's</v>
+            <v>Queens University</v>
           </cell>
           <cell r="D59" t="str">
-            <v>Northern Iowa</v>
+            <v>Purdue</v>
           </cell>
           <cell r="E59">
-            <v>12.286890801195611</v>
+            <v>-27.9169824507721</v>
           </cell>
           <cell r="F59" t="b">
             <v>0</v>
           </cell>
           <cell r="G59">
-            <v>0.51961234415784652</v>
+            <v>0.54767400294821322</v>
           </cell>
           <cell r="H59">
             <v>0</v>
           </cell>
           <cell r="I59">
-            <v>-8.0127975168384213E-3</v>
+            <v>4.5559460173861643E-2</v>
           </cell>
           <cell r="J59">
-            <v>0.43263467267483402</v>
+            <v>0.79642984416271356</v>
           </cell>
           <cell r="K59">
             <v>0</v>
@@ -3447,7 +3447,7 @@
             <v>-1.7669034601645432E-2</v>
           </cell>
           <cell r="J60">
-            <v>5.8850032027853383E-2</v>
+            <v>5.8850032027853438E-2</v>
           </cell>
           <cell r="K60">
             <v>0</v>
@@ -3455,31 +3455,31 @@
         </row>
         <row r="61">
           <cell r="B61">
-            <v>39</v>
+            <v>60</v>
           </cell>
           <cell r="C61" t="str">
-            <v>Saint Louis</v>
+            <v>Tennessee State</v>
           </cell>
           <cell r="D61" t="str">
-            <v>Georgia</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="E61">
-            <v>-2.323634492416264</v>
+            <v>-26.430767349804981</v>
           </cell>
           <cell r="F61" t="b">
             <v>0</v>
           </cell>
           <cell r="G61">
-            <v>0.50806891743100513</v>
+            <v>0.53922786424151392</v>
           </cell>
           <cell r="H61">
             <v>0</v>
           </cell>
           <cell r="I61">
-            <v>-3.0050248540808341E-2</v>
+            <v>2.9435013551981189E-2</v>
           </cell>
           <cell r="J61">
-            <v>9.3917362818843442E-2</v>
+            <v>0.76733006607215004</v>
           </cell>
           <cell r="K61">
             <v>0</v>
@@ -3487,31 +3487,31 @@
         </row>
         <row r="62">
           <cell r="B62">
-            <v>34</v>
+            <v>61</v>
           </cell>
           <cell r="C62" t="str">
-            <v>NC State</v>
+            <v>Northern Iowa</v>
           </cell>
           <cell r="D62" t="str">
-            <v>Texas</v>
+            <v>St. John's</v>
           </cell>
           <cell r="E62">
-            <v>-0.71724508084755245</v>
+            <v>-7.0324352932968424</v>
           </cell>
           <cell r="F62" t="b">
             <v>0</v>
           </cell>
           <cell r="G62">
-            <v>0.50704981381328074</v>
+            <v>0.60996307409599948</v>
           </cell>
           <cell r="H62">
             <v>0</v>
           </cell>
           <cell r="I62">
-            <v>-3.199580999282764E-2</v>
+            <v>0.16447495963781719</v>
           </cell>
           <cell r="J62">
-            <v>6.1738947754240714E-3</v>
+            <v>4.0627657807308433E-2</v>
           </cell>
           <cell r="K62">
             <v>0</v>
@@ -3519,31 +3519,31 @@
         </row>
         <row r="63">
           <cell r="B63">
-            <v>42</v>
+            <v>62</v>
           </cell>
           <cell r="C63" t="str">
-            <v>VCU</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="D63" t="str">
-            <v>North Carolina</v>
+            <v>Kansas</v>
           </cell>
           <cell r="E63">
-            <v>-1.733823308460128</v>
+            <v>-15.09008437804272</v>
           </cell>
           <cell r="F63" t="b">
             <v>0</v>
           </cell>
           <cell r="G63">
-            <v>0.50663651490010164</v>
+            <v>0.52632532157094736</v>
           </cell>
           <cell r="H63">
             <v>0</v>
           </cell>
           <cell r="I63">
-            <v>-3.2784835190715012E-2</v>
+            <v>4.8028866354449806E-3</v>
           </cell>
           <cell r="J63">
-            <v>3.9825391009848547E-2</v>
+            <v>0.52510282618406223</v>
           </cell>
           <cell r="K63">
             <v>0</v>
@@ -3551,31 +3551,31 @@
         </row>
         <row r="64">
           <cell r="B64">
-            <v>41</v>
+            <v>63</v>
           </cell>
           <cell r="C64" t="str">
-            <v>TCU</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="D64" t="str">
-            <v>Ohio State</v>
+            <v>Arizona</v>
           </cell>
           <cell r="E64">
-            <v>-1.9384527984340609</v>
+            <v>-32.075000000000003</v>
           </cell>
           <cell r="F64" t="b">
             <v>0</v>
           </cell>
           <cell r="G64">
-            <v>0.50153460752444023</v>
+            <v>0.5301795270136529</v>
           </cell>
           <cell r="H64">
             <v>0</v>
           </cell>
           <cell r="I64">
-            <v>-4.2524840180614032E-2</v>
+            <v>1.216091520788282E-2</v>
           </cell>
           <cell r="J64">
-            <v>5.8602197560207459E-2</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K64">
             <v>0</v>
@@ -3583,31 +3583,31 @@
         </row>
         <row r="65">
           <cell r="B65">
-            <v>50</v>
+            <v>64</v>
           </cell>
           <cell r="C65" t="str">
-            <v>Kennesaw State</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D65" t="str">
-            <v>Gonzaga</v>
+            <v>Villanova</v>
           </cell>
           <cell r="E65">
-            <v>-18.939777212918951</v>
+            <v>5.2368487163496047</v>
           </cell>
           <cell r="F65" t="b">
             <v>0</v>
           </cell>
           <cell r="G65">
-            <v>0.5014200475842292</v>
+            <v>0.58016009009738734</v>
           </cell>
           <cell r="H65">
             <v>0</v>
           </cell>
           <cell r="I65">
-            <v>-4.2743545521016953E-2</v>
+            <v>0.10757835382228501</v>
           </cell>
           <cell r="J65">
-            <v>0.56671791944483352</v>
+            <v>0.3568520724234755</v>
           </cell>
           <cell r="K65">
             <v>0</v>
@@ -8945,73 +8945,73 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>UMBC</v>
+            <v>Howard</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Howard</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D2">
-            <v>-7.6816292677242117</v>
+            <v>-7.2160644315092952</v>
           </cell>
           <cell r="E2">
-            <v>97.507117437722428</v>
+            <v>97.663689320388357</v>
           </cell>
           <cell r="F2">
-            <v>110.81504482768236</v>
+            <v>100.3456480810049</v>
           </cell>
           <cell r="G2">
-            <v>0.54563953488372097</v>
+            <v>0.52055921052631582</v>
           </cell>
           <cell r="H2">
-            <v>66.929333333333332</v>
+            <v>69.484999999999999</v>
           </cell>
           <cell r="I2">
-            <v>57.333333333333336</v>
+            <v>57</v>
           </cell>
           <cell r="J2">
-            <v>18.399999999999999</v>
+            <v>25.25</v>
           </cell>
           <cell r="K2">
-            <v>8.1666666666666661</v>
+            <v>12.28125</v>
           </cell>
           <cell r="L2">
-            <v>9.6666666666666661</v>
+            <v>13.65625</v>
           </cell>
           <cell r="M2">
             <v>0</v>
           </cell>
           <cell r="N2">
-            <v>-7.2160644315092952</v>
+            <v>23.158914646956031</v>
           </cell>
           <cell r="O2">
-            <v>97.663689320388357</v>
+            <v>98.200984374253366</v>
           </cell>
           <cell r="P2">
-            <v>100.3456480810049</v>
+            <v>96.383444817292968</v>
           </cell>
           <cell r="Q2">
-            <v>0.52055921052631582</v>
+            <v>0.58467532467532468</v>
           </cell>
           <cell r="R2">
-            <v>69.484999999999999</v>
+            <v>71.510000000000005</v>
           </cell>
           <cell r="S2">
-            <v>57</v>
+            <v>60.15625</v>
           </cell>
           <cell r="T2">
-            <v>25.25</v>
+            <v>23.53125</v>
           </cell>
           <cell r="U2">
-            <v>12.28125</v>
+            <v>11.0625</v>
           </cell>
           <cell r="V2">
-            <v>13.65625</v>
+            <v>12.0625</v>
           </cell>
           <cell r="W2">
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-2</v>
+            <v>31.5</v>
           </cell>
         </row>
         <row r="3">
@@ -9022,7 +9022,7 @@
             <v>Texas</v>
           </cell>
           <cell r="C3" t="str">
-            <v>NC State</v>
+            <v>BYU</v>
           </cell>
           <cell r="D3">
             <v>14.532052109666417</v>
@@ -9055,37 +9055,37 @@
             <v>0</v>
           </cell>
           <cell r="N3">
-            <v>12.200219627889993</v>
+            <v>16.95891571245977</v>
           </cell>
           <cell r="O3">
-            <v>100.22582813250121</v>
+            <v>101.35570594233801</v>
           </cell>
           <cell r="P3">
-            <v>107.83717769619953</v>
+            <v>99.665421267589466</v>
           </cell>
           <cell r="Q3">
-            <v>0.55333998005982055</v>
+            <v>0.54702268431001888</v>
           </cell>
           <cell r="R3">
-            <v>69.595151515151514</v>
+            <v>70.078823529411764</v>
           </cell>
           <cell r="S3">
-            <v>60.787878787878789</v>
+            <v>62.235294117647058</v>
           </cell>
           <cell r="T3">
-            <v>21.393939393939394</v>
+            <v>21.235294117647058</v>
           </cell>
           <cell r="U3">
-            <v>9.8484848484848477</v>
+            <v>12.382352941176471</v>
           </cell>
           <cell r="V3">
-            <v>9.2424242424242422</v>
+            <v>10.882352941176471</v>
           </cell>
           <cell r="W3">
             <v>0</v>
           </cell>
           <cell r="X3">
-            <v>-1</v>
+            <v>2.5</v>
           </cell>
         </row>
         <row r="4">
@@ -9096,7 +9096,7 @@
             <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Lehigh Mountain</v>
+            <v>Florida</v>
           </cell>
           <cell r="D4">
             <v>-11.471425536201773</v>
@@ -9129,37 +9129,37 @@
             <v>0</v>
           </cell>
           <cell r="N4">
-            <v>-9.9103284017639872</v>
+            <v>22.650454216704585</v>
           </cell>
           <cell r="O4">
-            <v>93.603341122656985</v>
+            <v>104.38676700269771</v>
           </cell>
           <cell r="P4">
-            <v>103.96836114726544</v>
+            <v>99.448258680413886</v>
           </cell>
           <cell r="Q4">
-            <v>0.53463203463203468</v>
+            <v>0.53652636671504594</v>
           </cell>
           <cell r="R4">
-            <v>68.395151515151511</v>
+            <v>71.564999999999998</v>
           </cell>
           <cell r="S4">
-            <v>56</v>
+            <v>64.59375</v>
           </cell>
           <cell r="T4">
-            <v>17.90909090909091</v>
+            <v>25.21875</v>
           </cell>
           <cell r="U4">
-            <v>7.5757575757575761</v>
+            <v>15.96875</v>
           </cell>
           <cell r="V4">
-            <v>12.090909090909092</v>
+            <v>11.84375</v>
           </cell>
           <cell r="W4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>2.5</v>
+            <v>35</v>
           </cell>
         </row>
         <row r="5">
@@ -9170,7 +9170,7 @@
             <v>Miami (OH)</v>
           </cell>
           <cell r="C5" t="str">
-            <v>SMU</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D5">
             <v>7.7337055835141966</v>
@@ -9203,37 +9203,37 @@
             <v>0</v>
           </cell>
           <cell r="N5">
-            <v>13.72167513134278</v>
+            <v>20.582457175121956</v>
           </cell>
           <cell r="O5">
-            <v>100.74486746987952</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="P5">
-            <v>98.898212983326317</v>
+            <v>93.637950339797769</v>
           </cell>
           <cell r="Q5">
-            <v>0.55746016417189759</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="R5">
-            <v>70.241212121212129</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="S5">
-            <v>62.757575757575758</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="T5">
-            <v>19.212121212121211</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="U5">
-            <v>12.272727272727273</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="V5">
-            <v>11.303030303030303</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="W5">
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>8.5</v>
+            <v>11.5</v>
           </cell>
         </row>
         <row r="6">
@@ -9307,7 +9307,7 @@
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>-5.5</v>
+            <v>-4.5</v>
           </cell>
         </row>
         <row r="7">
@@ -9529,7 +9529,7 @@
             <v>0</v>
           </cell>
           <cell r="X9">
-            <v>-29</v>
+            <v>-28.5</v>
           </cell>
         </row>
         <row r="10">
@@ -9677,7 +9677,7 @@
             <v>0</v>
           </cell>
           <cell r="X11">
-            <v>-2</v>
+            <v>-2.5</v>
           </cell>
         </row>
         <row r="12">
@@ -9973,7 +9973,7 @@
             <v>0</v>
           </cell>
           <cell r="X15">
-            <v>-2</v>
+            <v>-3.5</v>
           </cell>
         </row>
         <row r="16">
@@ -10047,7 +10047,7 @@
             <v>0</v>
           </cell>
           <cell r="X16">
-            <v>-23</v>
+            <v>-23.5</v>
           </cell>
         </row>
         <row r="17">
@@ -10269,7 +10269,7 @@
             <v>0</v>
           </cell>
           <cell r="X19">
-            <v>-19</v>
+            <v>-21</v>
           </cell>
         </row>
         <row r="20">
@@ -10639,7 +10639,7 @@
             <v>0</v>
           </cell>
           <cell r="X24">
-            <v>-20.5</v>
+            <v>-21</v>
           </cell>
         </row>
         <row r="25">
@@ -10861,7 +10861,7 @@
             <v>0</v>
           </cell>
           <cell r="X27">
-            <v>-24.5</v>
+            <v>-25.5</v>
           </cell>
         </row>
         <row r="28">
@@ -11313,73 +11313,73 @@
             <v>33</v>
           </cell>
           <cell r="B34" t="str">
+            <v>Michigan</v>
+          </cell>
+          <cell r="C34" t="str">
             <v>Howard</v>
           </cell>
-          <cell r="C34" t="str">
-            <v>UMBC</v>
-          </cell>
           <cell r="D34">
+            <v>23.158914646956031</v>
+          </cell>
+          <cell r="E34">
+            <v>98.200984374253366</v>
+          </cell>
+          <cell r="F34">
+            <v>96.383444817292968</v>
+          </cell>
+          <cell r="G34">
+            <v>0.58467532467532468</v>
+          </cell>
+          <cell r="H34">
+            <v>71.510000000000005</v>
+          </cell>
+          <cell r="I34">
+            <v>60.15625</v>
+          </cell>
+          <cell r="J34">
+            <v>23.53125</v>
+          </cell>
+          <cell r="K34">
+            <v>11.0625</v>
+          </cell>
+          <cell r="L34">
+            <v>12.0625</v>
+          </cell>
+          <cell r="M34">
+            <v>0</v>
+          </cell>
+          <cell r="N34">
             <v>-7.2160644315092952</v>
           </cell>
-          <cell r="E34">
+          <cell r="O34">
             <v>97.663689320388357</v>
           </cell>
-          <cell r="F34">
+          <cell r="P34">
             <v>100.3456480810049</v>
           </cell>
-          <cell r="G34">
+          <cell r="Q34">
             <v>0.52055921052631582</v>
           </cell>
-          <cell r="H34">
+          <cell r="R34">
             <v>69.484999999999999</v>
           </cell>
-          <cell r="I34">
+          <cell r="S34">
             <v>57</v>
           </cell>
-          <cell r="J34">
+          <cell r="T34">
             <v>25.25</v>
           </cell>
-          <cell r="K34">
+          <cell r="U34">
             <v>12.28125</v>
           </cell>
-          <cell r="L34">
+          <cell r="V34">
             <v>13.65625</v>
           </cell>
-          <cell r="M34">
-            <v>0</v>
-          </cell>
-          <cell r="N34">
-            <v>-7.6816292677242117</v>
-          </cell>
-          <cell r="O34">
-            <v>97.507117437722428</v>
-          </cell>
-          <cell r="P34">
-            <v>110.81504482768236</v>
-          </cell>
-          <cell r="Q34">
-            <v>0.54563953488372097</v>
-          </cell>
-          <cell r="R34">
-            <v>66.929333333333332</v>
-          </cell>
-          <cell r="S34">
-            <v>57.333333333333336</v>
-          </cell>
-          <cell r="T34">
-            <v>18.399999999999999</v>
-          </cell>
-          <cell r="U34">
-            <v>8.1666666666666661</v>
-          </cell>
-          <cell r="V34">
-            <v>9.6666666666666661</v>
-          </cell>
           <cell r="W34">
             <v>0</v>
           </cell>
           <cell r="X34">
-            <v>2</v>
+            <v>-31.5</v>
           </cell>
         </row>
         <row r="35">
@@ -11387,37 +11387,37 @@
             <v>34</v>
           </cell>
           <cell r="B35" t="str">
-            <v>NC State</v>
+            <v>BYU</v>
           </cell>
           <cell r="C35" t="str">
             <v>Texas</v>
           </cell>
           <cell r="D35">
-            <v>12.200219627889993</v>
+            <v>16.95891571245977</v>
           </cell>
           <cell r="E35">
-            <v>100.22582813250121</v>
+            <v>101.35570594233801</v>
           </cell>
           <cell r="F35">
-            <v>107.83717769619953</v>
+            <v>99.665421267589466</v>
           </cell>
           <cell r="G35">
-            <v>0.55333998005982055</v>
+            <v>0.54702268431001888</v>
           </cell>
           <cell r="H35">
-            <v>69.595151515151514</v>
+            <v>70.078823529411764</v>
           </cell>
           <cell r="I35">
-            <v>60.787878787878789</v>
+            <v>62.235294117647058</v>
           </cell>
           <cell r="J35">
-            <v>21.393939393939394</v>
+            <v>21.235294117647058</v>
           </cell>
           <cell r="K35">
-            <v>9.8484848484848477</v>
+            <v>12.382352941176471</v>
           </cell>
           <cell r="L35">
-            <v>9.2424242424242422</v>
+            <v>10.882352941176471</v>
           </cell>
           <cell r="M35">
             <v>0</v>
@@ -11453,7 +11453,7 @@
             <v>0</v>
           </cell>
           <cell r="X35">
-            <v>1</v>
+            <v>-2.5</v>
           </cell>
         </row>
         <row r="36">
@@ -11461,37 +11461,37 @@
             <v>35</v>
           </cell>
           <cell r="B36" t="str">
-            <v>Lehigh Mountain</v>
+            <v>Florida</v>
           </cell>
           <cell r="C36" t="str">
             <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D36">
-            <v>-9.9103284017639872</v>
+            <v>22.650454216704585</v>
           </cell>
           <cell r="E36">
-            <v>93.603341122656985</v>
+            <v>104.38676700269771</v>
           </cell>
           <cell r="F36">
-            <v>103.96836114726544</v>
+            <v>99.448258680413886</v>
           </cell>
           <cell r="G36">
-            <v>0.53463203463203468</v>
+            <v>0.53652636671504594</v>
           </cell>
           <cell r="H36">
-            <v>68.395151515151511</v>
+            <v>71.564999999999998</v>
           </cell>
           <cell r="I36">
-            <v>56</v>
+            <v>64.59375</v>
           </cell>
           <cell r="J36">
-            <v>17.90909090909091</v>
+            <v>25.21875</v>
           </cell>
           <cell r="K36">
-            <v>7.5757575757575761</v>
+            <v>15.96875</v>
           </cell>
           <cell r="L36">
-            <v>12.090909090909092</v>
+            <v>11.84375</v>
           </cell>
           <cell r="M36">
             <v>0</v>
@@ -11527,7 +11527,7 @@
             <v>0</v>
           </cell>
           <cell r="X36">
-            <v>-2.5</v>
+            <v>-35</v>
           </cell>
         </row>
         <row r="37">
@@ -11535,37 +11535,37 @@
             <v>36</v>
           </cell>
           <cell r="B37" t="str">
-            <v>SMU</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="C37" t="str">
             <v>Miami (OH)</v>
           </cell>
           <cell r="D37">
-            <v>13.72167513134278</v>
+            <v>20.582457175121956</v>
           </cell>
           <cell r="E37">
-            <v>100.74486746987952</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="F37">
-            <v>98.898212983326317</v>
+            <v>93.637950339797769</v>
           </cell>
           <cell r="G37">
-            <v>0.55746016417189759</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="H37">
-            <v>70.241212121212129</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="I37">
-            <v>62.757575757575758</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="J37">
-            <v>19.212121212121211</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="K37">
-            <v>12.272727272727273</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="L37">
-            <v>11.303030303030303</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="M37">
             <v>0</v>
@@ -11601,7 +11601,7 @@
             <v>0</v>
           </cell>
           <cell r="X37">
-            <v>-8.5</v>
+            <v>-11.5</v>
           </cell>
         </row>
         <row r="38">
@@ -11675,7 +11675,7 @@
             <v>0</v>
           </cell>
           <cell r="X38">
-            <v>5.5</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="39">
@@ -11897,7 +11897,7 @@
             <v>0</v>
           </cell>
           <cell r="X41">
-            <v>29</v>
+            <v>28.5</v>
           </cell>
         </row>
         <row r="42">
@@ -12045,7 +12045,7 @@
             <v>0</v>
           </cell>
           <cell r="X43">
-            <v>2</v>
+            <v>2.5</v>
           </cell>
         </row>
         <row r="44">
@@ -12341,7 +12341,7 @@
             <v>0</v>
           </cell>
           <cell r="X47">
-            <v>2</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="48">
@@ -12415,7 +12415,7 @@
             <v>0</v>
           </cell>
           <cell r="X48">
-            <v>23</v>
+            <v>23.5</v>
           </cell>
         </row>
         <row r="49">
@@ -12637,7 +12637,7 @@
             <v>0</v>
           </cell>
           <cell r="X51">
-            <v>19</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="52">
@@ -13007,7 +13007,7 @@
             <v>0</v>
           </cell>
           <cell r="X56">
-            <v>20.5</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="57">
@@ -13229,7 +13229,7 @@
             <v>0</v>
           </cell>
           <cell r="X59">
-            <v>24.5</v>
+            <v>25.5</v>
           </cell>
         </row>
         <row r="60">
@@ -22496,7 +22496,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -22504,7 +22504,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>UMBC</v>
+        <v>Michigan</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>B2</f>
@@ -22512,30 +22512,30 @@
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>2.711720411891148</v>
+        <v>-32.725000000000001</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>-2</v>
+        <v>-31.5</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.3634228852259655</v>
+        <v>0.82374745212732714</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>4.7276530038383939E-2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.3907119339990926E-2</v>
+        <v>-1.5640248165248172E-4</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>444</v>
       </c>
       <c r="K2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
-        <v>0.70914795057575919</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>444</v>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="C3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>NC State</v>
+        <v>BYU</v>
       </c>
       <c r="D3" s="6" t="str">
         <f t="shared" ref="D3:D33" si="0">B3</f>
@@ -22559,15 +22559,15 @@
       </c>
       <c r="E3" s="5">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>3.351492666553944</v>
+        <v>-1.644803862558186</v>
       </c>
       <c r="F3" s="5">
         <f>-VLOOKUP(A3,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.24670500307592891</v>
+        <v>1.81823394406555E-3</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="I3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.6519340795290577E-2</v>
+        <v>-1.1914177801811421E-3</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>443</v>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="C4" s="6" t="str">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Lehigh Mountain</v>
+        <v>Florida</v>
       </c>
       <c r="D4" s="6" t="str">
         <f t="shared" si="0"/>
@@ -22603,15 +22603,15 @@
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-1.0818703398805221</v>
+        <v>-35</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>-2.5</v>
+        <v>-35</v>
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>4.9856358057364769E-2</v>
+        <v>0.82374745212732714</v>
       </c>
       <c r="H4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.4904151031518597E-3</v>
+        <v>-1.1363636363636352E-2</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>443</v>
@@ -22631,46 +22631,45 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B5" s="6" t="str">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Miami (OH)</v>
+        <v>Tennessee</v>
       </c>
       <c r="C5" s="6" t="str">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>SMU</v>
+        <v>Miami (OH)</v>
       </c>
       <c r="D5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Miami (OH)</v>
+        <v>Tennessee</v>
       </c>
       <c r="E5" s="5">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-6.5280711453208946</v>
+        <v>16.737612085833891</v>
       </c>
       <c r="F5" s="5">
         <f>-VLOOKUP(A5,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>-8.5</v>
+        <v>11.5</v>
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>9.203326713974791E-2</v>
+        <v>0.71602282287691876</v>
       </c>
       <c r="H5" s="7">
-        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
+        <v>4.87E-2</v>
       </c>
       <c r="I5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.2043571181850746E-2</v>
+        <v>4.1135970029953173E-2</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.73049999999999993</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -22691,15 +22690,15 @@
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>8.742776454945794</v>
+        <v>8.0927764549457955</v>
       </c>
       <c r="F6" s="5">
         <f>-VLOOKUP(A6,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.46272230131594538</v>
+        <v>0.46272230131594561</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -22707,7 +22706,7 @@
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.6963698692011574E-2</v>
+        <v>3.1034764517982125E-2</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>443</v>
@@ -22779,7 +22778,7 @@
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>4.2861663978745757</v>
+        <v>4.2861663978745774</v>
       </c>
       <c r="F8" s="5">
         <f>-VLOOKUP(A8,[2]Games!$A$2:$X$298,24,FALSE)</f>
@@ -22823,11 +22822,11 @@
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>31.1</v>
+        <v>30.774999999999999</v>
       </c>
       <c r="F9" s="5">
         <f>-VLOOKUP(A9,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="G9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -22839,7 +22838,7 @@
       </c>
       <c r="I9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>7.8272632776738155E-3</v>
+        <v>9.4203829605269129E-3</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>443</v>
@@ -22867,7 +22866,7 @@
       </c>
       <c r="E10" s="5">
         <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>4.5795233045545594</v>
+        <v>4.5795233045545602</v>
       </c>
       <c r="F10" s="5">
         <f>-VLOOKUP(A10,[2]Games!$A$2:$X$298,24,FALSE)</f>
@@ -22883,7 +22882,7 @@
       </c>
       <c r="I10" s="7">
         <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.9200917018050961E-2</v>
+        <v>1.9200917018051017E-2</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>443</v>
@@ -22911,11 +22910,11 @@
       </c>
       <c r="E11" s="5">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>5.5088810410605049</v>
+        <v>5.8338810410605051</v>
       </c>
       <c r="F11" s="5">
         <f>-VLOOKUP(A11,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -22927,7 +22926,7 @@
       </c>
       <c r="I11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.0060673314890901E-2</v>
+        <v>2.8025209359415774E-2</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>443</v>
@@ -23007,22 +23006,22 @@
       </c>
       <c r="G13" s="7">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.74660937378926895</v>
+        <v>0.74660937378926906</v>
       </c>
       <c r="H13" s="7">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>5.1984795756579022E-2</v>
+        <v>5.1984795756579258E-2</v>
       </c>
       <c r="I13" s="7">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.65822703162381E-2</v>
+        <v>4.6582270316238149E-2</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>444</v>
       </c>
       <c r="K13" s="9">
         <f t="shared" si="1"/>
-        <v>0.77977193634868525</v>
+        <v>0.7797719363486888</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -23087,15 +23086,15 @@
       </c>
       <c r="E15" s="5">
         <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>4.9704473885420759</v>
+        <v>5.9454473885420782</v>
       </c>
       <c r="F15" s="5">
         <f>-VLOOKUP(A15,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G15" s="7">
         <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.33336045600883751</v>
+        <v>0.33336045600883768</v>
       </c>
       <c r="H15" s="7">
         <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23103,7 +23102,7 @@
       </c>
       <c r="I15" s="7">
         <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.3783462755823326E-2</v>
+        <v>1.762493338118104E-2</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>443</v>
@@ -23131,11 +23130,11 @@
       </c>
       <c r="E16" s="5">
         <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>27.2</v>
+        <v>27.524999999999999</v>
       </c>
       <c r="F16" s="5">
         <f>-VLOOKUP(A16,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="G16" s="7">
         <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -23147,7 +23146,7 @@
       </c>
       <c r="I16" s="7">
         <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.6823703652969575E-2</v>
+        <v>2.5252756771279548E-2</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>443</v>
@@ -23183,7 +23182,7 @@
       </c>
       <c r="G17" s="7">
         <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.44405986090341543</v>
+        <v>0.44405986090341548</v>
       </c>
       <c r="H17" s="7">
         <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23263,15 +23262,15 @@
       </c>
       <c r="E19" s="5">
         <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>23.450459942010621</v>
+        <v>24.750459942010622</v>
       </c>
       <c r="F19" s="5">
         <f>-VLOOKUP(A19,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G19" s="7">
         <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.78843548732025015</v>
+        <v>0.78843548732025037</v>
       </c>
       <c r="H19" s="7">
         <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23279,7 +23278,7 @@
       </c>
       <c r="I19" s="7">
         <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.0634354119320827E-2</v>
+        <v>2.4112792155817853E-2</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>443</v>
@@ -23359,7 +23358,7 @@
       </c>
       <c r="G21" s="7">
         <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.81648449863375538</v>
+        <v>0.81648449863375561</v>
       </c>
       <c r="H21" s="7">
         <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23367,7 +23366,7 @@
       </c>
       <c r="I21" s="7">
         <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.2863862656605552E-2</v>
+        <v>5.2863862656605573E-2</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>444</v>
@@ -23395,7 +23394,7 @@
       </c>
       <c r="E22" s="5">
         <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>3.3395963530867379E-2</v>
+        <v>3.3395963530867823E-2</v>
       </c>
       <c r="F22" s="5">
         <f>-VLOOKUP(A22,[2]Games!$A$2:$X$298,24,FALSE)</f>
@@ -23403,7 +23402,7 @@
       </c>
       <c r="G22" s="7">
         <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.12227695604597411</v>
+        <v>0.1222769560459742</v>
       </c>
       <c r="H22" s="7">
         <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23411,7 +23410,7 @@
       </c>
       <c r="I22" s="7">
         <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.2769338252811707E-2</v>
+        <v>1.2769338252811763E-2</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>443</v>
@@ -23447,7 +23446,7 @@
       </c>
       <c r="G23" s="7">
         <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.3157571093517878</v>
+        <v>0.31575710935178802</v>
       </c>
       <c r="H23" s="7">
         <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23483,15 +23482,15 @@
       </c>
       <c r="E24" s="5">
         <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>25.492859365224369</v>
+        <v>25.817859365224368</v>
       </c>
       <c r="F24" s="5">
         <f>-VLOOKUP(A24,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="G24" s="7">
         <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82144469910078188</v>
+        <v>0.82144469910078211</v>
       </c>
       <c r="H24" s="7">
         <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23499,7 +23498,7 @@
       </c>
       <c r="I24" s="7">
         <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.4026672850691726E-2</v>
+        <v>3.2464659083965001E-2</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>443</v>
@@ -23615,11 +23614,11 @@
       </c>
       <c r="E27" s="5">
         <f>VLOOKUP(A27,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>28.175000000000001</v>
+        <v>28.824999999999999</v>
       </c>
       <c r="F27" s="5">
         <f>-VLOOKUP(A27,[2]Games!$A$2:$X$298,24,FALSE)</f>
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="G27" s="7">
         <f>VLOOKUP(A27,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -23631,7 +23630,7 @@
       </c>
       <c r="I27" s="7">
         <f>VLOOKUP(A27,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.2103291284134408E-2</v>
+        <v>1.8944448642887746E-2</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>443</v>
@@ -23755,7 +23754,7 @@
       </c>
       <c r="G30" s="7">
         <f>VLOOKUP(A30,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.43263467267483402</v>
+        <v>0.43263467267483419</v>
       </c>
       <c r="H30" s="7">
         <f>VLOOKUP(A30,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23879,7 +23878,7 @@
       </c>
       <c r="E33" s="5">
         <f>VLOOKUP(A33,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-0.75126679890107051</v>
+        <v>-0.7512667989010704</v>
       </c>
       <c r="F33" s="5">
         <f>-VLOOKUP(A33,[2]Games!$A$2:$X$298,24,FALSE)</f>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45A89AF-05BB-7A41-B913-8B561646A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E28109-6AF4-DA47-A4BF-AD27DA80B338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15760" yWindow="800" windowWidth="30500" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
@@ -22531,7 +22531,7 @@
         <v>-1.5640248165248172E-4</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BBD120-09DF-7A4A-AA4F-D4F1B028CC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FE585F-7CFB-B14A-9AE8-F57E485B3861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="780" windowWidth="18820" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="60" yWindow="780" windowWidth="15360" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="462">
   <si>
     <t>Team</t>
   </si>
@@ -1422,6 +1422,15 @@
   </si>
   <si>
     <t>VAN/MCN</t>
+  </si>
+  <si>
+    <t>03/20/2026</t>
+  </si>
+  <si>
+    <t>ALA/HOFS</t>
+  </si>
+  <si>
+    <t>TEN/MIAOH</t>
   </si>
 </sst>
 </file>
@@ -1582,127 +1591,127 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="B2">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Alabama</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="D2" t="str">
-            <v>Hofstra</v>
+            <v>Akron</v>
           </cell>
           <cell r="E2">
-            <v>21.35</v>
+            <v>10.105811312700951</v>
           </cell>
           <cell r="F2" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.63809273344358919</v>
+            <v>0.56468692974454482</v>
           </cell>
           <cell r="H2">
-            <v>6.5997896092614958E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I2">
-            <v>0.21817703657412491</v>
+            <v>7.8038684057767482E-2</v>
           </cell>
           <cell r="J2">
-            <v>0.82374745212732714</v>
+            <v>0.46800018669531451</v>
           </cell>
           <cell r="K2">
-            <v>1.288278931727844</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>7</v>
+            <v>2</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Tennessee</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Miami (OH)</v>
+            <v>Hofstra</v>
           </cell>
           <cell r="E3">
-            <v>17.763320142231279</v>
+            <v>21.35</v>
           </cell>
           <cell r="F3" t="b">
             <v>1</v>
           </cell>
           <cell r="G3">
-            <v>0.63446581889029208</v>
+            <v>0.63809273344358919</v>
           </cell>
           <cell r="H3">
-            <v>6.2951287867845318E-2</v>
+            <v>6.5997896092614958E-2</v>
           </cell>
           <cell r="I3">
-            <v>0.21125292697237591</v>
+            <v>0.21817703657412491</v>
           </cell>
           <cell r="J3">
-            <v>0.77130206914028421</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K3">
-            <v>1.2288091391803406</v>
+            <v>1.288278931727844</v>
           </cell>
         </row>
         <row r="4">
           <cell r="B4">
-            <v>14</v>
+            <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Kansas</v>
+            <v>Florida</v>
           </cell>
           <cell r="D4" t="str">
-            <v>California Baptist</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="E4">
-            <v>20.297186452323341</v>
+            <v>35</v>
           </cell>
           <cell r="F4" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.62310087724532315</v>
+            <v>0.5</v>
           </cell>
           <cell r="H4">
-            <v>5.3404736886071551E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.18955622019561699</v>
+            <v>-4.5454545454545407E-2</v>
           </cell>
           <cell r="J4">
-            <v>0.79167581956681854</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K4">
-            <v>1.0424604640161166</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="5">
           <cell r="B5">
-            <v>19</v>
+            <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Duke</v>
+            <v>Clemson</v>
           </cell>
           <cell r="D5" t="str">
-            <v>TCU</v>
+            <v>Iowa</v>
           </cell>
           <cell r="E5">
-            <v>16.140216310663</v>
+            <v>3.3395963530867379E-2</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.60906422040161368</v>
+            <v>0.55056432776779596</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>0.16275896622126251</v>
+            <v>5.1077353011246829E-2</v>
           </cell>
           <cell r="J5">
-            <v>0.70336153249742339</v>
+            <v>0.12227695604597411</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1710,31 +1719,31 @@
         </row>
         <row r="6">
           <cell r="B6">
-            <v>37</v>
+            <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Northern Iowa</v>
+            <v>UCLA</v>
           </cell>
           <cell r="D6" t="str">
-            <v>St. John's</v>
+            <v>UCF</v>
           </cell>
           <cell r="E6">
-            <v>-5.7155949911145472</v>
+            <v>7.0470101204148357</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.60556386284114683</v>
+            <v>0.53851296772810842</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>0.15607646542400769</v>
+            <v>2.8070211117297909E-2</v>
           </cell>
           <cell r="J6">
-            <v>7.1989015715373472E-2</v>
+            <v>0.3157571093517878</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1742,31 +1751,31 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>33</v>
+            <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Missouri</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D7" t="str">
-            <v>Miami</v>
+            <v>Furman</v>
           </cell>
           <cell r="E7">
-            <v>2.1482075857303151</v>
+            <v>25.574999999999999</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.60228382736083119</v>
+            <v>0.59638086655976275</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>0.1498145795070415</v>
+            <v>0.13854529070500171</v>
           </cell>
           <cell r="J7">
-            <v>0.31364001260244623</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1774,63 +1783,63 @@
         </row>
         <row r="8">
           <cell r="B8">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Uconn</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Furman</v>
+            <v>Miami (OH)</v>
           </cell>
           <cell r="E8">
-            <v>25.574999999999999</v>
+            <v>17.763320142231279</v>
           </cell>
           <cell r="F8" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G8">
-            <v>0.59638086655976275</v>
+            <v>0.63446581889029208</v>
           </cell>
           <cell r="H8">
-            <v>0</v>
+            <v>6.2951287867845318E-2</v>
           </cell>
           <cell r="I8">
-            <v>0.13854529070500171</v>
+            <v>0.21125292697237591</v>
           </cell>
           <cell r="J8">
-            <v>0.82374745212732714</v>
+            <v>0.77130206914028421</v>
           </cell>
           <cell r="K8">
-            <v>0</v>
+            <v>1.2288091391803406</v>
           </cell>
         </row>
         <row r="9">
           <cell r="B9">
-            <v>17</v>
+            <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Michigan State</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D9" t="str">
-            <v>Louisville</v>
+            <v>Wright State</v>
           </cell>
           <cell r="E9">
-            <v>7.7185281356503328</v>
+            <v>20.115791597901271</v>
           </cell>
           <cell r="F9" t="b">
             <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.59188943533172611</v>
+            <v>0.54634765315908873</v>
           </cell>
           <cell r="H9">
             <v>0</v>
           </cell>
           <cell r="I9">
-            <v>0.12997074017874991</v>
+            <v>4.3027337849169463E-2</v>
           </cell>
           <cell r="J9">
-            <v>0.45858766203522988</v>
+            <v>0.67485538426353442</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1838,31 +1847,31 @@
         </row>
         <row r="10">
           <cell r="B10">
-            <v>28</v>
+            <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Iowa</v>
+            <v>Miami</v>
           </cell>
           <cell r="D10" t="str">
-            <v>Clemson</v>
+            <v>Missouri</v>
           </cell>
           <cell r="E10">
-            <v>5.6137133324827877</v>
+            <v>4.4969385785639577</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.58934371104373051</v>
+            <v>0.56200660866546603</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>0.1251107210834855</v>
+            <v>7.2921707452253348E-2</v>
           </cell>
           <cell r="J10">
-            <v>0.38977250670595909</v>
+            <v>0.2912235406823202</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1870,31 +1879,31 @@
         </row>
         <row r="11">
           <cell r="B11">
-            <v>26</v>
+            <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Hofstra</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Alabama</v>
+            <v>Queens University</v>
           </cell>
           <cell r="E11">
-            <v>-18.200910725903629</v>
+            <v>28.5</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.58915163001262683</v>
+            <v>0.56681426051108019</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>0.1247440209331967</v>
+            <v>8.2099951884789468E-2</v>
           </cell>
           <cell r="J11">
-            <v>0.70857165526473465</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1902,31 +1911,31 @@
         </row>
         <row r="12">
           <cell r="B12">
-            <v>20</v>
+            <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Illinois</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D12" t="str">
-            <v>VCU</v>
+            <v>Santa Clara</v>
           </cell>
           <cell r="E12">
-            <v>14.438763270417709</v>
+            <v>5.6593475628966718</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.5884378419425238</v>
+            <v>0.56600384912440083</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>0.1233813346175455</v>
+            <v>8.0552802873856133E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.63074311573987751</v>
+            <v>0.3368011492256191</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1934,31 +1943,31 @@
         </row>
         <row r="13">
           <cell r="B13">
-            <v>31</v>
+            <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Miami (OH)</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Tennessee</v>
+            <v>Tennessee State</v>
           </cell>
           <cell r="E13">
-            <v>-14.923953790708479</v>
+            <v>28.175000000000001</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.58757381148107868</v>
+            <v>0.57012118173818638</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>0.12173182191842299</v>
+            <v>8.841316513653763E-2</v>
           </cell>
           <cell r="J13">
-            <v>0.63996826747857327</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1966,31 +1975,31 @@
         </row>
         <row r="14">
           <cell r="B14">
-            <v>40</v>
+            <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Utah State</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Villanova</v>
+            <v>Northern Iowa</v>
           </cell>
           <cell r="E14">
-            <v>5.4593714883795128</v>
+            <v>11.95141219900553</v>
           </cell>
           <cell r="F14" t="b">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.58558825032111539</v>
+            <v>0.54812259817372755</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>0.117941205158493</v>
+            <v>4.6415869240752639E-2</v>
           </cell>
           <cell r="J14">
-            <v>0.37633750295571428</v>
+            <v>0.48515083858939739</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -1998,63 +2007,63 @@
         </row>
         <row r="15">
           <cell r="B15">
-            <v>44</v>
+            <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>VCU</v>
+            <v>Kansas</v>
           </cell>
           <cell r="D15" t="str">
-            <v>Illinois</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="E15">
-            <v>-7.2568674597012466</v>
+            <v>20.297186452323341</v>
           </cell>
           <cell r="F15" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G15">
-            <v>0.58031359058064103</v>
+            <v>0.62310087724532315</v>
           </cell>
           <cell r="H15">
-            <v>0</v>
+            <v>5.3404736886071551E-2</v>
           </cell>
           <cell r="I15">
-            <v>0.10787140019940571</v>
+            <v>0.18955622019561699</v>
           </cell>
           <cell r="J15">
-            <v>3.9645885764726663E-2</v>
+            <v>0.79167581956681854</v>
           </cell>
           <cell r="K15">
-            <v>0</v>
+            <v>1.0424604640161166</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16">
-            <v>23</v>
+            <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Arkansas</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D16" t="str">
-            <v>High Point</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="E16">
-            <v>14.531806056773171</v>
+            <v>32.400000000000013</v>
           </cell>
           <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.58014282659298355</v>
+            <v>0.5268316233988839</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>0.1075453962229687</v>
+            <v>5.7694628524147529E-3</v>
           </cell>
           <cell r="J16">
-            <v>0.61701013724196296</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -2062,31 +2071,31 @@
         </row>
         <row r="17">
           <cell r="B17">
-            <v>24</v>
+            <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Gonzaga</v>
+            <v>Villanova</v>
           </cell>
           <cell r="D17" t="str">
-            <v>Texas</v>
+            <v>Utah State</v>
           </cell>
           <cell r="E17">
-            <v>8.5492026218240404</v>
+            <v>-0.1780563139182261</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.57557077504574861</v>
+            <v>0.54533016307921067</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>9.881693417824744E-2</v>
+            <v>4.1084856787584063E-2</v>
           </cell>
           <cell r="J17">
-            <v>0.44641629054277171</v>
+            <v>0.102922512580872</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2094,31 +2103,31 @@
         </row>
         <row r="18">
           <cell r="B18">
-            <v>46</v>
+            <v>17</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Houston</v>
+            <v>Louisville</v>
           </cell>
           <cell r="E18">
-            <v>-7.1037832151035936</v>
+            <v>7.7185281356503328</v>
           </cell>
           <cell r="F18" t="b">
             <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0.57182152945754017</v>
+            <v>0.59188943533172611</v>
           </cell>
           <cell r="H18">
             <v>0</v>
           </cell>
           <cell r="I18">
-            <v>9.1659283509849421E-2</v>
+            <v>0.12997074017874991</v>
           </cell>
           <cell r="J18">
-            <v>5.5421511542608992E-2</v>
+            <v>0.45858766203522988</v>
           </cell>
           <cell r="K18">
             <v>0</v>
@@ -2126,31 +2135,31 @@
         </row>
         <row r="19">
           <cell r="B19">
-            <v>12</v>
+            <v>18</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Iowa State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D19" t="str">
-            <v>Tennessee State</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="E19">
-            <v>28.175000000000001</v>
+            <v>15.5119498017062</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.57012118173818638</v>
+            <v>0.56845929673645745</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>8.841316513653763E-2</v>
+            <v>8.5240475587782472E-2</v>
           </cell>
           <cell r="J19">
-            <v>0.82374745212732714</v>
+            <v>0.61731951279916419</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2158,31 +2167,31 @@
         </row>
         <row r="20">
           <cell r="B20">
-            <v>45</v>
+            <v>19</v>
           </cell>
           <cell r="C20" t="str">
-            <v>Vanderbilt</v>
+            <v>Duke</v>
           </cell>
           <cell r="D20" t="str">
-            <v>Nebraska</v>
+            <v>TCU</v>
           </cell>
           <cell r="E20">
-            <v>5.3076158961687021</v>
+            <v>16.140216310663</v>
           </cell>
           <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0.569647183746957</v>
+            <v>0.60906422040161368</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>8.7508259880554329E-2</v>
+            <v>0.16275896622126251</v>
           </cell>
           <cell r="J20">
-            <v>0.33443712076902887</v>
+            <v>0.70336153249742339</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2190,31 +2199,31 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>18</v>
+            <v>20</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Michigan</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D21" t="str">
-            <v>Saint Louis</v>
+            <v>VCU</v>
           </cell>
           <cell r="E21">
-            <v>15.5119498017062</v>
+            <v>14.438763270417709</v>
           </cell>
           <cell r="F21" t="b">
             <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0.56845929673645745</v>
+            <v>0.5884378419425238</v>
           </cell>
           <cell r="H21">
             <v>0</v>
           </cell>
           <cell r="I21">
-            <v>8.5240475587782472E-2</v>
+            <v>0.1233813346175455</v>
           </cell>
           <cell r="J21">
-            <v>0.61731951279916419</v>
+            <v>0.63074311573987751</v>
           </cell>
           <cell r="K21">
             <v>0</v>
@@ -2222,31 +2231,31 @@
         </row>
         <row r="22">
           <cell r="B22">
-            <v>10</v>
+            <v>21</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Purdue</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D22" t="str">
-            <v>Queens University</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="E22">
-            <v>28.5</v>
+            <v>-1.093500554042212</v>
           </cell>
           <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0.56681426051108019</v>
+            <v>0.53502439171067129</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>8.2099951884789468E-2</v>
+            <v>2.141020235673613E-2</v>
           </cell>
           <cell r="J22">
-            <v>0.82374745212732714</v>
+            <v>4.8789164423594489E-2</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2286,31 +2295,31 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>11</v>
+            <v>23</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Kentucky</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D24" t="str">
-            <v>Santa Clara</v>
+            <v>High Point</v>
           </cell>
           <cell r="E24">
-            <v>5.6593475628966718</v>
+            <v>14.531806056773171</v>
           </cell>
           <cell r="F24" t="b">
             <v>0</v>
           </cell>
           <cell r="G24">
-            <v>0.56600384912440083</v>
+            <v>0.58014282659298355</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>8.0552802873856133E-2</v>
+            <v>0.1075453962229687</v>
           </cell>
           <cell r="J24">
-            <v>0.3368011492256191</v>
+            <v>0.61701013724196296</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2318,31 +2327,31 @@
         </row>
         <row r="25">
           <cell r="B25">
-            <v>29</v>
+            <v>24</v>
           </cell>
           <cell r="C25" t="str">
-            <v>UCF</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="D25" t="str">
-            <v>UCLA</v>
+            <v>Texas</v>
           </cell>
           <cell r="E25">
-            <v>-2.8861369669403749</v>
+            <v>8.5492026218240404</v>
           </cell>
           <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0.56488503739422913</v>
+            <v>0.57557077504574861</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>7.8416889570801063E-2</v>
+            <v>9.881693417824744E-2</v>
           </cell>
           <cell r="J25">
-            <v>6.3226472938151368E-2</v>
+            <v>0.44641629054277171</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2350,31 +2359,31 @@
         </row>
         <row r="26">
           <cell r="B26">
-            <v>1</v>
+            <v>25</v>
           </cell>
           <cell r="C26" t="str">
+            <v>Akron</v>
+          </cell>
+          <cell r="D26" t="str">
             <v>Texas Tech</v>
           </cell>
-          <cell r="D26" t="str">
-            <v>Akron</v>
-          </cell>
           <cell r="E26">
-            <v>10.105811312700951</v>
+            <v>-5.7133742605995348</v>
           </cell>
           <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0.56468692974454482</v>
+            <v>0.54445513080134145</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>7.8038684057767482E-2</v>
+            <v>3.9414340620742783E-2</v>
           </cell>
           <cell r="J26">
-            <v>0.46800018669531451</v>
+            <v>7.6937609984081723E-2</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2382,31 +2391,31 @@
         </row>
         <row r="27">
           <cell r="B27">
-            <v>9</v>
+            <v>26</v>
           </cell>
           <cell r="C27" t="str">
-            <v>Miami</v>
+            <v>Hofstra</v>
           </cell>
           <cell r="D27" t="str">
-            <v>Missouri</v>
+            <v>Alabama</v>
           </cell>
           <cell r="E27">
-            <v>4.4969385785639577</v>
+            <v>-18.200910725903629</v>
           </cell>
           <cell r="F27" t="b">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0.56200660866546603</v>
+            <v>0.58915163001262683</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>7.2921707452253348E-2</v>
+            <v>0.1247440209331967</v>
           </cell>
           <cell r="J27">
-            <v>0.2912235406823202</v>
+            <v>0.70857165526473465</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2414,31 +2423,31 @@
         </row>
         <row r="28">
           <cell r="B28">
-            <v>32</v>
+            <v>27</v>
           </cell>
           <cell r="C28" t="str">
-            <v>Wright State</v>
+            <v>Prairie View A&amp;M</v>
           </cell>
           <cell r="D28" t="str">
-            <v>Virginia</v>
+            <v>Florida</v>
           </cell>
           <cell r="E28">
-            <v>-15.96072331533523</v>
+            <v>-35</v>
           </cell>
           <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0.55070977428765122</v>
+            <v>0.5</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>5.1355023640061503E-2</v>
+            <v>-4.5454545454545407E-2</v>
           </cell>
           <cell r="J28">
-            <v>0.38516760636631159</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2446,31 +2455,31 @@
         </row>
         <row r="29">
           <cell r="B29">
-            <v>4</v>
+            <v>28</v>
           </cell>
           <cell r="C29" t="str">
+            <v>Iowa</v>
+          </cell>
+          <cell r="D29" t="str">
             <v>Clemson</v>
           </cell>
-          <cell r="D29" t="str">
-            <v>Iowa</v>
-          </cell>
           <cell r="E29">
-            <v>3.3395963530867379E-2</v>
+            <v>5.6137133324827877</v>
           </cell>
           <cell r="F29" t="b">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0.55056432776779596</v>
+            <v>0.58934371104373051</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>5.1077353011246829E-2</v>
+            <v>0.1251107210834855</v>
           </cell>
           <cell r="J29">
-            <v>0.12227695604597411</v>
+            <v>0.38977250670595909</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2478,31 +2487,31 @@
         </row>
         <row r="30">
           <cell r="B30">
-            <v>34</v>
+            <v>29</v>
           </cell>
           <cell r="C30" t="str">
-            <v>Queens University</v>
+            <v>UCF</v>
           </cell>
           <cell r="D30" t="str">
-            <v>Purdue</v>
+            <v>UCLA</v>
           </cell>
           <cell r="E30">
-            <v>-27.532563309862141</v>
+            <v>-2.8861369669403749</v>
           </cell>
           <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0.55004263682873855</v>
+            <v>0.56488503739422913</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>5.0081397582137248E-2</v>
+            <v>7.8416889570801063E-2</v>
           </cell>
           <cell r="J30">
-            <v>0.79449285353871313</v>
+            <v>6.3226472938151368E-2</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2510,31 +2519,31 @@
         </row>
         <row r="31">
           <cell r="B31">
-            <v>13</v>
+            <v>30</v>
           </cell>
           <cell r="C31" t="str">
-            <v>St. John's</v>
+            <v>Furman</v>
           </cell>
           <cell r="D31" t="str">
-            <v>Northern Iowa</v>
+            <v>Uconn</v>
           </cell>
           <cell r="E31">
-            <v>11.95141219900553</v>
+            <v>-21.482427500798011</v>
           </cell>
           <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0.54812259817372755</v>
+            <v>0.52177084207843238</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>4.6415869240752639E-2</v>
+            <v>-3.8920287593562919E-3</v>
           </cell>
           <cell r="J31">
-            <v>0.48515083858939739</v>
+            <v>0.66120627779014118</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2542,31 +2551,31 @@
         </row>
         <row r="32">
           <cell r="B32">
-            <v>8</v>
+            <v>31</v>
           </cell>
           <cell r="C32" t="str">
-            <v>Virginia</v>
+            <v>Miami (OH)</v>
           </cell>
           <cell r="D32" t="str">
-            <v>Wright State</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="E32">
-            <v>20.115791597901271</v>
+            <v>-14.923953790708479</v>
           </cell>
           <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0.54634765315908873</v>
+            <v>0.58757381148107868</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>4.3027337849169463E-2</v>
+            <v>0.12173182191842299</v>
           </cell>
           <cell r="J32">
-            <v>0.67485538426353442</v>
+            <v>0.63996826747857327</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2574,31 +2583,31 @@
         </row>
         <row r="33">
           <cell r="B33">
-            <v>16</v>
+            <v>32</v>
           </cell>
           <cell r="C33" t="str">
-            <v>Villanova</v>
+            <v>Wright State</v>
           </cell>
           <cell r="D33" t="str">
-            <v>Utah State</v>
+            <v>Virginia</v>
           </cell>
           <cell r="E33">
-            <v>-0.1780563139182261</v>
+            <v>-15.96072331533523</v>
           </cell>
           <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0.54533016307921067</v>
+            <v>0.55070977428765122</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>4.1084856787584063E-2</v>
+            <v>5.1355023640061503E-2</v>
           </cell>
           <cell r="J33">
-            <v>0.102922512580872</v>
+            <v>0.38516760636631159</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -2606,31 +2615,31 @@
         </row>
         <row r="34">
           <cell r="B34">
-            <v>25</v>
+            <v>33</v>
           </cell>
           <cell r="C34" t="str">
-            <v>Akron</v>
+            <v>Missouri</v>
           </cell>
           <cell r="D34" t="str">
-            <v>Texas Tech</v>
+            <v>Miami</v>
           </cell>
           <cell r="E34">
-            <v>-5.7133742605995348</v>
+            <v>2.1482075857303151</v>
           </cell>
           <cell r="F34" t="b">
             <v>0</v>
           </cell>
           <cell r="G34">
-            <v>0.54445513080134145</v>
+            <v>0.60228382736083119</v>
           </cell>
           <cell r="H34">
             <v>0</v>
           </cell>
           <cell r="I34">
-            <v>3.9414340620742783E-2</v>
+            <v>0.1498145795070415</v>
           </cell>
           <cell r="J34">
-            <v>7.6937609984081723E-2</v>
+            <v>0.31364001260244623</v>
           </cell>
           <cell r="K34">
             <v>0</v>
@@ -2638,31 +2647,31 @@
         </row>
         <row r="35">
           <cell r="B35">
-            <v>5</v>
+            <v>34</v>
           </cell>
           <cell r="C35" t="str">
-            <v>UCLA</v>
+            <v>Queens University</v>
           </cell>
           <cell r="D35" t="str">
-            <v>UCF</v>
+            <v>Purdue</v>
           </cell>
           <cell r="E35">
-            <v>7.0470101204148357</v>
+            <v>-27.532563309862141</v>
           </cell>
           <cell r="F35" t="b">
             <v>0</v>
           </cell>
           <cell r="G35">
-            <v>0.53851296772810842</v>
+            <v>0.55004263682873855</v>
           </cell>
           <cell r="H35">
             <v>0</v>
           </cell>
           <cell r="I35">
-            <v>2.8070211117297909E-2</v>
+            <v>5.0081397582137248E-2</v>
           </cell>
           <cell r="J35">
-            <v>0.3157571093517878</v>
+            <v>0.79449285353871313</v>
           </cell>
           <cell r="K35">
             <v>0</v>
@@ -2670,31 +2679,31 @@
         </row>
         <row r="36">
           <cell r="B36">
-            <v>36</v>
+            <v>35</v>
           </cell>
           <cell r="C36" t="str">
-            <v>Tennessee State</v>
+            <v>Santa Clara</v>
           </cell>
           <cell r="D36" t="str">
-            <v>Iowa State</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="E36">
-            <v>-26.323261769434339</v>
+            <v>-2.097560289466216</v>
           </cell>
           <cell r="F36" t="b">
             <v>0</v>
           </cell>
           <cell r="G36">
-            <v>0.53718956657658601</v>
+            <v>0.52248941008610128</v>
           </cell>
           <cell r="H36">
             <v>0</v>
           </cell>
           <cell r="I36">
-            <v>2.5543718009846061E-2</v>
+            <v>-2.5202171083520408E-3</v>
           </cell>
           <cell r="J36">
-            <v>0.76328915590709401</v>
+            <v>1.3547631565368701E-2</v>
           </cell>
           <cell r="K36">
             <v>0</v>
@@ -2702,31 +2711,31 @@
         </row>
         <row r="37">
           <cell r="B37">
-            <v>48</v>
+            <v>36</v>
           </cell>
           <cell r="C37" t="str">
-            <v>Texas</v>
+            <v>Tennessee State</v>
           </cell>
           <cell r="D37" t="str">
-            <v>Gonzaga</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="E37">
-            <v>-4.0735770169153609</v>
+            <v>-26.323261769434339</v>
           </cell>
           <cell r="F37" t="b">
             <v>0</v>
           </cell>
           <cell r="G37">
-            <v>0.53551922013547781</v>
+            <v>0.53718956657658601</v>
           </cell>
           <cell r="H37">
             <v>0</v>
           </cell>
           <cell r="I37">
-            <v>2.2354874804094042E-2</v>
+            <v>2.5543718009846061E-2</v>
           </cell>
           <cell r="J37">
-            <v>4.5768048855342247E-2</v>
+            <v>0.76328915590709401</v>
           </cell>
           <cell r="K37">
             <v>0</v>
@@ -2734,31 +2743,31 @@
         </row>
         <row r="38">
           <cell r="B38">
-            <v>21</v>
+            <v>37</v>
           </cell>
           <cell r="C38" t="str">
-            <v>Nebraska</v>
+            <v>Northern Iowa</v>
           </cell>
           <cell r="D38" t="str">
-            <v>Vanderbilt</v>
+            <v>St. John's</v>
           </cell>
           <cell r="E38">
-            <v>-1.093500554042212</v>
+            <v>-5.7155949911145472</v>
           </cell>
           <cell r="F38" t="b">
             <v>0</v>
           </cell>
           <cell r="G38">
-            <v>0.53502439171067129</v>
+            <v>0.60556386284114683</v>
           </cell>
           <cell r="H38">
             <v>0</v>
           </cell>
           <cell r="I38">
-            <v>2.141020235673613E-2</v>
+            <v>0.15607646542400769</v>
           </cell>
           <cell r="J38">
-            <v>4.8789164423594489E-2</v>
+            <v>7.1989015715373472E-2</v>
           </cell>
           <cell r="K38">
             <v>0</v>
@@ -2766,31 +2775,31 @@
         </row>
         <row r="39">
           <cell r="B39">
-            <v>47</v>
+            <v>38</v>
           </cell>
           <cell r="C39" t="str">
-            <v>High Point</v>
+            <v>California Baptist</v>
           </cell>
           <cell r="D39" t="str">
-            <v>Arkansas</v>
+            <v>Kansas</v>
           </cell>
           <cell r="E39">
-            <v>-12.3836786652074</v>
+            <v>-14.52957082789203</v>
           </cell>
           <cell r="F39" t="b">
             <v>0</v>
           </cell>
           <cell r="G39">
-            <v>0.53445753974774979</v>
+            <v>0.51310106393859689</v>
           </cell>
           <cell r="H39">
             <v>0</v>
           </cell>
           <cell r="I39">
-            <v>2.0328030427522351E-2</v>
+            <v>-2.0443423389951369E-2</v>
           </cell>
           <cell r="J39">
-            <v>0.46823988524848509</v>
+            <v>0.48348064838746119</v>
           </cell>
           <cell r="K39">
             <v>0</v>
@@ -2798,31 +2807,31 @@
         </row>
         <row r="40">
           <cell r="B40">
-            <v>43</v>
+            <v>39</v>
           </cell>
           <cell r="C40" t="str">
-            <v>TCU</v>
+            <v>Long Island University</v>
           </cell>
           <cell r="D40" t="str">
-            <v>Duke</v>
+            <v>Arizona</v>
           </cell>
           <cell r="E40">
-            <v>-12.096831283208401</v>
+            <v>-32.400000000000013</v>
           </cell>
           <cell r="F40" t="b">
             <v>0</v>
           </cell>
           <cell r="G40">
-            <v>0.52732686847916632</v>
+            <v>0.5268316233988839</v>
           </cell>
           <cell r="H40">
             <v>0</v>
           </cell>
           <cell r="I40">
-            <v>6.7149307329539276E-3</v>
+            <v>5.7694628524147529E-3</v>
           </cell>
           <cell r="J40">
-            <v>0.44409903598414241</v>
+            <v>0.82374745212732714</v>
           </cell>
           <cell r="K40">
             <v>0</v>
@@ -2830,31 +2839,31 @@
         </row>
         <row r="41">
           <cell r="B41">
-            <v>15</v>
+            <v>40</v>
           </cell>
           <cell r="C41" t="str">
-            <v>Arizona</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D41" t="str">
-            <v>Long Island University</v>
+            <v>Villanova</v>
           </cell>
           <cell r="E41">
-            <v>32.400000000000013</v>
+            <v>5.4593714883795128</v>
           </cell>
           <cell r="F41" t="b">
             <v>0</v>
           </cell>
           <cell r="G41">
-            <v>0.5268316233988839</v>
+            <v>0.58558825032111539</v>
           </cell>
           <cell r="H41">
             <v>0</v>
           </cell>
           <cell r="I41">
-            <v>5.7694628524147529E-3</v>
+            <v>0.117941205158493</v>
           </cell>
           <cell r="J41">
-            <v>0.82374745212732714</v>
+            <v>0.37633750295571428</v>
           </cell>
           <cell r="K41">
             <v>0</v>
@@ -2862,31 +2871,31 @@
         </row>
         <row r="42">
           <cell r="B42">
-            <v>39</v>
+            <v>41</v>
           </cell>
           <cell r="C42" t="str">
-            <v>Long Island University</v>
+            <v>Louisville</v>
           </cell>
           <cell r="D42" t="str">
-            <v>Arizona</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="E42">
-            <v>-32.400000000000013</v>
+            <v>-3.009819784518605</v>
           </cell>
           <cell r="F42" t="b">
             <v>0</v>
           </cell>
           <cell r="G42">
-            <v>0.5268316233988839</v>
+            <v>0.52467329665300033</v>
           </cell>
           <cell r="H42">
             <v>0</v>
           </cell>
           <cell r="I42">
-            <v>5.7694628524147529E-3</v>
+            <v>1.6490208830006741E-3</v>
           </cell>
           <cell r="J42">
-            <v>0.82374745212732714</v>
+            <v>3.7622338566990272E-2</v>
           </cell>
           <cell r="K42">
             <v>0</v>
@@ -2894,31 +2903,31 @@
         </row>
         <row r="43">
           <cell r="B43">
-            <v>41</v>
+            <v>42</v>
           </cell>
           <cell r="C43" t="str">
-            <v>Louisville</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D43" t="str">
-            <v>Michigan State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="E43">
-            <v>-3.009819784518605</v>
+            <v>-12.429984635021251</v>
           </cell>
           <cell r="F43" t="b">
             <v>0</v>
           </cell>
           <cell r="G43">
-            <v>0.52467329665300033</v>
+            <v>0.50174575001391375</v>
           </cell>
           <cell r="H43">
             <v>0</v>
           </cell>
           <cell r="I43">
-            <v>1.6490208830006741E-3</v>
+            <v>-4.2121749973437372E-2</v>
           </cell>
           <cell r="J43">
-            <v>3.7622338566990272E-2</v>
+            <v>0.38901453824241772</v>
           </cell>
           <cell r="K43">
             <v>0</v>
@@ -2926,31 +2935,31 @@
         </row>
         <row r="44">
           <cell r="B44">
-            <v>35</v>
+            <v>43</v>
           </cell>
           <cell r="C44" t="str">
-            <v>Santa Clara</v>
+            <v>TCU</v>
           </cell>
           <cell r="D44" t="str">
-            <v>Kentucky</v>
+            <v>Duke</v>
           </cell>
           <cell r="E44">
-            <v>-2.097560289466216</v>
+            <v>-12.096831283208401</v>
           </cell>
           <cell r="F44" t="b">
             <v>0</v>
           </cell>
           <cell r="G44">
-            <v>0.52248941008610128</v>
+            <v>0.52732686847916632</v>
           </cell>
           <cell r="H44">
             <v>0</v>
           </cell>
           <cell r="I44">
-            <v>-2.5202171083520408E-3</v>
+            <v>6.7149307329539276E-3</v>
           </cell>
           <cell r="J44">
-            <v>1.3547631565368701E-2</v>
+            <v>0.44409903598414241</v>
           </cell>
           <cell r="K44">
             <v>0</v>
@@ -2958,31 +2967,31 @@
         </row>
         <row r="45">
           <cell r="B45">
-            <v>30</v>
+            <v>44</v>
           </cell>
           <cell r="C45" t="str">
-            <v>Furman</v>
+            <v>VCU</v>
           </cell>
           <cell r="D45" t="str">
-            <v>Uconn</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E45">
-            <v>-21.482427500798011</v>
+            <v>-7.2568674597012466</v>
           </cell>
           <cell r="F45" t="b">
             <v>0</v>
           </cell>
           <cell r="G45">
-            <v>0.52177084207843238</v>
+            <v>0.58031359058064103</v>
           </cell>
           <cell r="H45">
             <v>0</v>
           </cell>
           <cell r="I45">
-            <v>-3.8920287593562919E-3</v>
+            <v>0.10787140019940571</v>
           </cell>
           <cell r="J45">
-            <v>0.66120627779014118</v>
+            <v>3.9645885764726663E-2</v>
           </cell>
           <cell r="K45">
             <v>0</v>
@@ -2990,31 +2999,31 @@
         </row>
         <row r="46">
           <cell r="B46">
-            <v>38</v>
+            <v>45</v>
           </cell>
           <cell r="C46" t="str">
-            <v>California Baptist</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D46" t="str">
-            <v>Kansas</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="E46">
-            <v>-14.52957082789203</v>
+            <v>5.3076158961687021</v>
           </cell>
           <cell r="F46" t="b">
             <v>0</v>
           </cell>
           <cell r="G46">
-            <v>0.51310106393859689</v>
+            <v>0.569647183746957</v>
           </cell>
           <cell r="H46">
             <v>0</v>
           </cell>
           <cell r="I46">
-            <v>-2.0443423389951369E-2</v>
+            <v>8.7508259880554329E-2</v>
           </cell>
           <cell r="J46">
-            <v>0.48348064838746119</v>
+            <v>0.33443712076902887</v>
           </cell>
           <cell r="K46">
             <v>0</v>
@@ -3022,31 +3031,31 @@
         </row>
         <row r="47">
           <cell r="B47">
-            <v>42</v>
+            <v>46</v>
           </cell>
           <cell r="C47" t="str">
-            <v>Saint Louis</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="D47" t="str">
-            <v>Michigan</v>
+            <v>Houston</v>
           </cell>
           <cell r="E47">
-            <v>-12.429984635021251</v>
+            <v>-7.1037832151035936</v>
           </cell>
           <cell r="F47" t="b">
             <v>0</v>
           </cell>
           <cell r="G47">
-            <v>0.50174575001391375</v>
+            <v>0.57182152945754017</v>
           </cell>
           <cell r="H47">
             <v>0</v>
           </cell>
           <cell r="I47">
-            <v>-4.2121749973437372E-2</v>
+            <v>9.1659283509849421E-2</v>
           </cell>
           <cell r="J47">
-            <v>0.38901453824241772</v>
+            <v>5.5421511542608992E-2</v>
           </cell>
           <cell r="K47">
             <v>0</v>
@@ -3054,31 +3063,31 @@
         </row>
         <row r="48">
           <cell r="B48">
-            <v>3</v>
+            <v>47</v>
           </cell>
           <cell r="C48" t="str">
-            <v>Florida</v>
+            <v>High Point</v>
           </cell>
           <cell r="D48" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="E48">
-            <v>35</v>
+            <v>-12.3836786652074</v>
           </cell>
           <cell r="F48" t="b">
             <v>0</v>
           </cell>
           <cell r="G48">
-            <v>0.5</v>
+            <v>0.53445753974774979</v>
           </cell>
           <cell r="H48">
             <v>0</v>
           </cell>
           <cell r="I48">
-            <v>-4.5454545454545407E-2</v>
+            <v>2.0328030427522351E-2</v>
           </cell>
           <cell r="J48">
-            <v>0.82374745212732714</v>
+            <v>0.46823988524848509</v>
           </cell>
           <cell r="K48">
             <v>0</v>
@@ -3086,31 +3095,31 @@
         </row>
         <row r="49">
           <cell r="B49">
-            <v>27</v>
+            <v>48</v>
           </cell>
           <cell r="C49" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>Texas</v>
           </cell>
           <cell r="D49" t="str">
-            <v>Florida</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="E49">
-            <v>-35</v>
+            <v>-4.0735770169153609</v>
           </cell>
           <cell r="F49" t="b">
             <v>0</v>
           </cell>
           <cell r="G49">
-            <v>0.5</v>
+            <v>0.53551922013547781</v>
           </cell>
           <cell r="H49">
             <v>0</v>
           </cell>
           <cell r="I49">
-            <v>-4.5454545454545407E-2</v>
+            <v>2.2354874804094042E-2</v>
           </cell>
           <cell r="J49">
-            <v>0.82374745212732714</v>
+            <v>4.5768048855342247E-2</v>
           </cell>
           <cell r="K49">
             <v>0</v>
@@ -24267,31 +24276,31 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Texas Tech</v>
+        <v>Michigan State</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Akron</v>
+        <v>Louisville</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>B2</f>
-        <v>Texas Tech</v>
+        <v>Michigan State</v>
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>10.105811312700951</v>
+        <v>7.7185281356503328</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.46800018669531451</v>
+        <v>0.45858766203522988</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24299,7 +24308,7 @@
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.9509671014441871E-2</v>
+        <v>3.2492685044687476E-2</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>443</v>
@@ -24314,73 +24323,75 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Alabama</v>
+        <v>Michigan</v>
       </c>
       <c r="C3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Hofstra</v>
+        <v>Saint Louis</v>
       </c>
       <c r="D3" s="6" t="str">
-        <f t="shared" ref="D3:D19" si="0">B3</f>
-        <v>Alabama</v>
+        <f t="shared" ref="D3:D9" si="0">B3</f>
+        <v>Michigan</v>
       </c>
       <c r="E3" s="5">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>21.35</v>
+        <v>15.5119498017062</v>
       </c>
       <c r="F3" s="5">
         <f>-VLOOKUP(A3,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82374745212732714</v>
+        <v>0.61731951279916419</v>
       </c>
       <c r="H3" s="7">
-        <v>6.3E-2</v>
+        <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.4544259143531226E-2</v>
+        <v>2.1310118896945618E-2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K3" s="9">
-        <v>0.94599999999999995</v>
+        <f t="shared" ref="K3:K9" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="str">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Florida</v>
+        <v>Duke</v>
       </c>
       <c r="C4" s="6" t="str">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Prairie View A&amp;M</v>
+        <v>TCU</v>
       </c>
       <c r="D4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Florida</v>
+        <v>Duke</v>
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>35</v>
+        <v>16.140216310663</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82374745212732714</v>
+        <v>0.70336153249742339</v>
       </c>
       <c r="H4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24388,43 +24399,43 @@
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>-1.1363636363636352E-2</v>
+        <v>4.0689741555315628E-2</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>443</v>
       </c>
       <c r="K4" s="9">
-        <f t="shared" ref="K3:K25" si="1">IF(J4="Yes",(H4*1500)/100,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6" t="str">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Clemson</v>
+        <v>Illinois</v>
       </c>
       <c r="C5" s="6" t="str">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Iowa</v>
+        <v>VCU</v>
       </c>
       <c r="D5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Clemson</v>
+        <v>Illinois</v>
       </c>
       <c r="E5" s="5">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>3.3395963530867379E-2</v>
+        <v>14.438763270417709</v>
       </c>
       <c r="F5" s="5">
         <f>-VLOOKUP(A5,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>-2</v>
+        <v>10.5</v>
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.12227695604597411</v>
+        <v>0.63074311573987751</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24432,7 +24443,7 @@
       </c>
       <c r="I5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.2769338252811707E-2</v>
+        <v>3.0845333654386374E-2</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>443</v>
@@ -24444,31 +24455,31 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6" t="str">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>UCLA</v>
+        <v>Nebraska</v>
       </c>
       <c r="C6" s="6" t="str">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>UCF</v>
+        <v>Vanderbilt</v>
       </c>
       <c r="D6" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>UCLA</v>
+        <v>Nebraska</v>
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.0470101204148357</v>
+        <v>-1.093500554042212</v>
       </c>
       <c r="F6" s="5">
         <f>-VLOOKUP(A6,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>5.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.3157571093517878</v>
+        <v>4.8789164423594489E-2</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24476,7 +24487,7 @@
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>7.0175527793244772E-3</v>
+        <v>5.3525505891840325E-3</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>443</v>
@@ -24488,31 +24499,31 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B7" s="6" t="str">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Uconn</v>
+        <v>Houston</v>
       </c>
       <c r="C7" s="6" t="str">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Furman</v>
+        <v>Texas A&amp;M</v>
       </c>
       <c r="D7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Uconn</v>
+        <v>Houston</v>
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>25.574999999999999</v>
+        <v>12.80869246587973</v>
       </c>
       <c r="F7" s="5">
         <f>-VLOOKUP(A7,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>20.5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82374745212732714</v>
+        <v>0.54759166061732523</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24520,7 +24531,7 @@
       </c>
       <c r="I7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.4636322676250428E-2</v>
+        <v>2.0460202169939601E-2</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>443</v>
@@ -24532,23 +24543,23 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6" t="str">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Tennessee</v>
+        <v>Arkansas</v>
       </c>
       <c r="C8" s="6" t="str">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Miami (OH)</v>
+        <v>High Point</v>
       </c>
       <c r="D8" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Tennessee</v>
+        <v>Arkansas</v>
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>17.763320142231279</v>
+        <v>14.531806056773171</v>
       </c>
       <c r="F8" s="5">
         <f>-VLOOKUP(A8,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -24556,49 +24567,51 @@
       </c>
       <c r="G8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.77130206914028421</v>
+        <v>0.61701013724196296</v>
       </c>
       <c r="H8" s="7">
-        <v>4.9000000000000002E-2</v>
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.2813231743093977E-2</v>
+        <v>2.6886349055742175E-2</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K8" s="9">
-        <v>0.73099999999999998</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6" t="str">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Virginia</v>
+        <v>Gonzaga</v>
       </c>
       <c r="C9" s="6" t="str">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Wright State</v>
+        <v>Texas</v>
       </c>
       <c r="D9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Virginia</v>
+        <v>Gonzaga</v>
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>20.115791597901271</v>
+        <v>8.5492026218240404</v>
       </c>
       <c r="F9" s="5">
         <f>-VLOOKUP(A9,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="G9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.67485538426353442</v>
+        <v>0.44641629054277171</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24606,7 +24619,7 @@
       </c>
       <c r="I9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.0756834462292366E-2</v>
+        <v>2.470423354456186E-2</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>443</v>
@@ -24617,709 +24630,198 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="str">
-        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Miami</v>
-      </c>
-      <c r="C10" s="6" t="str">
-        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Missouri</v>
-      </c>
-      <c r="D10" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Miami</v>
-      </c>
-      <c r="E10" s="5">
-        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>4.4969385785639577</v>
-      </c>
-      <c r="F10" s="5">
-        <f>-VLOOKUP(A10,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="G10" s="7">
-        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.2912235406823202</v>
-      </c>
-      <c r="H10" s="7">
-        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="7">
-        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.8230426863063337E-2</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K10" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="str">
-        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Purdue</v>
-      </c>
-      <c r="C11" s="6" t="str">
-        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Queens University</v>
-      </c>
-      <c r="D11" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Purdue</v>
-      </c>
-      <c r="E11" s="5">
-        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>28.5</v>
-      </c>
-      <c r="F11" s="5">
-        <f>-VLOOKUP(A11,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>25</v>
-      </c>
-      <c r="G11" s="7">
-        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82374745212732714</v>
-      </c>
-      <c r="H11" s="7">
-        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="7">
-        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.0524987971197367E-2</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K11" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="str">
-        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Kentucky</v>
-      </c>
-      <c r="C12" s="6" t="str">
-        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Santa Clara</v>
-      </c>
-      <c r="D12" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Kentucky</v>
-      </c>
-      <c r="E12" s="5">
-        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>5.6593475628966718</v>
-      </c>
-      <c r="F12" s="5">
-        <f>-VLOOKUP(A12,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="G12" s="7">
-        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.3368011492256191</v>
-      </c>
-      <c r="H12" s="7">
-        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="7">
-        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.0138200718464033E-2</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K12" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="str">
-        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Iowa State</v>
-      </c>
-      <c r="C13" s="6" t="str">
-        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Tennessee State</v>
-      </c>
-      <c r="D13" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Iowa State</v>
-      </c>
-      <c r="E13" s="5">
-        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>28.175000000000001</v>
-      </c>
-      <c r="F13" s="5">
-        <f>-VLOOKUP(A13,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>24.5</v>
-      </c>
-      <c r="G13" s="7">
-        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82374745212732714</v>
-      </c>
-      <c r="H13" s="7">
-        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="7">
-        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.2103291284134408E-2</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K13" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="str">
-        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>St. John's</v>
-      </c>
-      <c r="C14" s="6" t="str">
-        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Northern Iowa</v>
-      </c>
-      <c r="D14" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>St. John's</v>
-      </c>
-      <c r="E14" s="5">
-        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>11.95141219900553</v>
-      </c>
-      <c r="F14" s="5">
-        <f>-VLOOKUP(A14,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>10</v>
-      </c>
-      <c r="G14" s="7">
-        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.48515083858939739</v>
-      </c>
-      <c r="H14" s="7">
-        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="7">
-        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.160396731018816E-2</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K14" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="str">
-        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Kansas</v>
-      </c>
-      <c r="C15" s="6" t="str">
-        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>California Baptist</v>
-      </c>
-      <c r="D15" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Kansas</v>
-      </c>
-      <c r="E15" s="5">
-        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>20.297186452323341</v>
-      </c>
-      <c r="F15" s="5">
-        <f>-VLOOKUP(A15,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>14</v>
-      </c>
-      <c r="G15" s="7">
-        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.79167581956681854</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7">
-        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.7389055048904248E-2</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K15" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="str">
-        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Arizona</v>
-      </c>
-      <c r="C16" s="6" t="str">
-        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Long Island University</v>
-      </c>
-      <c r="D16" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Arizona</v>
-      </c>
-      <c r="E16" s="5">
-        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>32.400000000000013</v>
-      </c>
-      <c r="F16" s="5">
-        <f>-VLOOKUP(A16,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>31</v>
-      </c>
-      <c r="G16" s="7">
-        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.82374745212732714</v>
-      </c>
-      <c r="H16" s="7">
-        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="7">
-        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.4423657131036882E-3</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="str">
-        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Villanova</v>
-      </c>
-      <c r="C17" s="6" t="str">
-        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Utah State</v>
-      </c>
-      <c r="D17" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Villanova</v>
-      </c>
-      <c r="E17" s="5">
-        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-0.1780563139182261</v>
-      </c>
-      <c r="F17" s="5">
-        <f>-VLOOKUP(A17,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>-2</v>
-      </c>
-      <c r="G17" s="7">
-        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.102922512580872</v>
-      </c>
-      <c r="H17" s="7">
-        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="7">
-        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.0271214196896016E-2</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K17" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="str">
-        <f>VLOOKUP(A18,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Michigan State</v>
-      </c>
-      <c r="C18" s="6" t="str">
-        <f>VLOOKUP(A18,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Louisville</v>
-      </c>
-      <c r="D18" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Michigan State</v>
-      </c>
-      <c r="E18" s="5">
-        <f>VLOOKUP(A18,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.7185281356503328</v>
-      </c>
-      <c r="F18" s="5">
-        <f>-VLOOKUP(A18,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="G18" s="7">
-        <f>VLOOKUP(A18,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.45858766203522988</v>
-      </c>
-      <c r="H18" s="7">
-        <f>VLOOKUP(A18,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <f>VLOOKUP(A18,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.2492685044687476E-2</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K18" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="6" t="str">
-        <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Michigan</v>
-      </c>
-      <c r="C19" s="6" t="str">
-        <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Saint Louis</v>
-      </c>
-      <c r="D19" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Michigan</v>
-      </c>
-      <c r="E19" s="5">
-        <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>15.5119498017062</v>
-      </c>
-      <c r="F19" s="5">
-        <f>-VLOOKUP(A19,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>12.5</v>
-      </c>
-      <c r="G19" s="7">
-        <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.61731951279916419</v>
-      </c>
-      <c r="H19" s="7">
-        <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="7">
-        <f>VLOOKUP(A19,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.1310118896945618E-2</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K19" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="str">
-        <f>VLOOKUP(A20,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Duke</v>
-      </c>
-      <c r="C20" s="6" t="str">
-        <f>VLOOKUP(A20,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>TCU</v>
-      </c>
-      <c r="D20" s="6" t="str">
-        <f t="shared" ref="D20:D25" si="2">B20</f>
-        <v>Duke</v>
-      </c>
-      <c r="E20" s="5">
-        <f>VLOOKUP(A20,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>16.140216310663</v>
-      </c>
-      <c r="F20" s="5">
-        <f>-VLOOKUP(A20,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>11</v>
-      </c>
-      <c r="G20" s="7">
-        <f>VLOOKUP(A20,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.70336153249742339</v>
-      </c>
-      <c r="H20" s="7">
-        <f>VLOOKUP(A20,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="7">
-        <f>VLOOKUP(A20,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.0689741555315628E-2</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K20" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="str">
-        <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Illinois</v>
-      </c>
-      <c r="C21" s="6" t="str">
-        <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>VCU</v>
-      </c>
-      <c r="D21" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Illinois</v>
-      </c>
-      <c r="E21" s="5">
-        <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.438763270417709</v>
-      </c>
-      <c r="F21" s="5">
-        <f>-VLOOKUP(A21,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>10.5</v>
-      </c>
-      <c r="G21" s="7">
-        <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.63074311573987751</v>
-      </c>
-      <c r="H21" s="7">
-        <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="7">
-        <f>VLOOKUP(A21,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.0845333654386374E-2</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="6" t="str">
-        <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Nebraska</v>
-      </c>
-      <c r="C22" s="6" t="str">
-        <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Vanderbilt</v>
-      </c>
-      <c r="D22" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Nebraska</v>
-      </c>
-      <c r="E22" s="5">
-        <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-1.093500554042212</v>
-      </c>
-      <c r="F22" s="5">
-        <f>-VLOOKUP(A22,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>-2.5</v>
-      </c>
-      <c r="G22" s="7">
-        <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>4.8789164423594489E-2</v>
-      </c>
-      <c r="H22" s="7">
-        <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="7">
-        <f>VLOOKUP(A22,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.3525505891840325E-3</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K22" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="str">
-        <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Houston</v>
-      </c>
-      <c r="C23" s="6" t="str">
-        <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Texas A&amp;M</v>
-      </c>
-      <c r="D23" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Houston</v>
-      </c>
-      <c r="E23" s="5">
-        <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>12.80869246587973</v>
-      </c>
-      <c r="F23" s="5">
-        <f>-VLOOKUP(A23,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>10</v>
-      </c>
-      <c r="G23" s="7">
-        <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.54759166061732523</v>
-      </c>
-      <c r="H23" s="7">
-        <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="7">
-        <f>VLOOKUP(A23,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.0460202169939601E-2</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="str">
-        <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Arkansas</v>
-      </c>
-      <c r="C24" s="6" t="str">
-        <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>High Point</v>
-      </c>
-      <c r="D24" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Arkansas</v>
-      </c>
-      <c r="E24" s="5">
-        <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.531806056773171</v>
-      </c>
-      <c r="F24" s="5">
-        <f>-VLOOKUP(A24,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>11</v>
-      </c>
-      <c r="G24" s="7">
-        <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.61701013724196296</v>
-      </c>
-      <c r="H24" s="7">
-        <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="7">
-        <f>VLOOKUP(A24,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.6886349055742175E-2</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K24" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="str">
-        <f>VLOOKUP(A25,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Gonzaga</v>
-      </c>
-      <c r="C25" s="6" t="str">
-        <f>VLOOKUP(A25,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Texas</v>
-      </c>
-      <c r="D25" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Gonzaga</v>
-      </c>
-      <c r="E25" s="5">
-        <f>VLOOKUP(A25,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>8.5492026218240404</v>
-      </c>
-      <c r="F25" s="5">
-        <f>-VLOOKUP(A25,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>5.5</v>
-      </c>
-      <c r="G25" s="7">
-        <f>VLOOKUP(A25,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.44641629054277171</v>
-      </c>
-      <c r="H25" s="7">
-        <f>VLOOKUP(A25,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="7">
-        <f>VLOOKUP(A25,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.470423354456186E-2</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="9"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -25331,7 +24833,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -25343,7 +24845,7 @@
       <c r="J27" s="8"/>
       <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -25355,7 +24857,7 @@
       <c r="J28" s="8"/>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -25367,7 +24869,7 @@
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -25379,7 +24881,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -25391,7 +24893,7 @@
       <c r="J31" s="8"/>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -25509,27 +25011,27 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f>COUNTIF($C$6:$C$150,"W")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1">
         <f>COUNTIF($C$6:$C$150,"L")</f>
         <v>8</v>
       </c>
       <c r="C2" s="12">
-        <f>SUM(F6:F21)/SUM(E6:E21)</f>
-        <v>-5.983462673712589E-2</v>
+        <f>SUM(F6:F24)/SUM(E6:E24)</f>
+        <v>7.871577071601242E-2</v>
       </c>
       <c r="D2" s="13">
         <f>AVERAGE(H6:H150)</f>
-        <v>2.5783431206901603E-2</v>
+        <v>2.1311302327194463E-2</v>
       </c>
       <c r="E2" s="1">
         <f ca="1">COUNTIF(OFFSET($C$6,COUNTA($C$6:$C$1500)-10,0,10,1),"W")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <f ca="1">COUNTIF(OFFSET($C$6,COUNTA($C$6:$C$1500)-10,0,10,1),"L")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -25700,7 +25202,7 @@
         <v>425</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" ref="B8:B21" si="4">B7+1</f>
+        <f t="shared" ref="B8:B24" si="4">B7+1</f>
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -26494,43 +25996,175 @@
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="F22" s="14">
+        <f t="shared" ref="F22:F24" si="24">IF(C22="P",0,IF(C22="L",-E22,IF(K22&lt;0,E22*(100/-K22),E22*(K22/100)))/1)</f>
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="G22" s="14">
+        <f t="shared" ref="G22:G24" si="25">F22+G21</f>
+        <v>0.13034035178217362</v>
+      </c>
+      <c r="H22" s="10">
+        <f t="shared" ref="H22:H24" si="26">((M22-P22)*3.55%)+(O22-L22)</f>
+        <v>-6.9519230769230722E-2</v>
+      </c>
+      <c r="I22" s="10">
+        <f>AVERAGE($H$6:H22)</f>
+        <v>2.0177392267129113E-2</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="L22" s="12">
+        <f t="shared" ref="L22:L24" si="27">IF(K22&lt;0,K22/(K22-100),100/(K22+100))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-14</v>
+      </c>
+      <c r="N22" s="1">
+        <v>-108</v>
+      </c>
+      <c r="O22" s="12">
+        <f t="shared" ref="O22:O24" si="28">IF(N22&lt;0,N22/(N22-100),100/(N22+100))</f>
+        <v>0.51923076923076927</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-11.5</v>
+      </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="F23" s="14">
+        <f t="shared" si="24"/>
+        <v>0.42232142857142857</v>
+      </c>
+      <c r="G23" s="14">
+        <f t="shared" si="25"/>
+        <v>0.55266178035360225</v>
+      </c>
+      <c r="H23" s="10">
+        <f t="shared" si="26"/>
+        <v>1.715265866209259E-2</v>
+      </c>
+      <c r="I23" s="10">
+        <f>AVERAGE($H$6:H23)</f>
+        <v>2.0009351511293752E-2</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K23" s="1">
+        <v>-112</v>
+      </c>
+      <c r="L23" s="12">
+        <f t="shared" si="27"/>
+        <v>0.52830188679245282</v>
+      </c>
+      <c r="M23" s="1">
+        <v>-11.5</v>
+      </c>
+      <c r="N23" s="1">
+        <v>-120</v>
+      </c>
+      <c r="O23" s="12">
+        <f t="shared" si="28"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="P23" s="1">
+        <v>-11.5</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="F24" s="14">
+        <f t="shared" si="24"/>
+        <v>0.68962264150943398</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" si="25"/>
+        <v>1.2422844218630362</v>
+      </c>
+      <c r="H24" s="10">
+        <f t="shared" si="26"/>
+        <v>4.4746417013407334E-2</v>
+      </c>
+      <c r="I24" s="10">
+        <f>AVERAGE($H$6:H24)</f>
+        <v>2.1311302327194463E-2</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K24" s="1">
+        <v>-106</v>
+      </c>
+      <c r="L24" s="12">
+        <f t="shared" si="27"/>
+        <v>0.5145631067961165</v>
+      </c>
+      <c r="M24" s="1">
+        <v>-11</v>
+      </c>
+      <c r="N24" s="1">
+        <v>-110</v>
+      </c>
+      <c r="O24" s="12">
+        <f t="shared" si="28"/>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="P24" s="1">
+        <v>-12</v>
+      </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F25" s="14"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FE585F-7CFB-B14A-9AE8-F57E485B3861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ACE55A-4E6F-FE4C-8ECF-DF978CB7330E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="780" windowWidth="15360" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="462">
   <si>
     <t>Team</t>
   </si>
@@ -1594,28 +1594,28 @@
             <v>1</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Texas Tech</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D2" t="str">
-            <v>Akron</v>
+            <v>Louisville</v>
           </cell>
           <cell r="E2">
-            <v>10.105811312700951</v>
+            <v>7.2987974976589882</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.56468692974454482</v>
+            <v>0.56943065556782912</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>7.8038684057767482E-2</v>
+            <v>8.7094887902219309E-2</v>
           </cell>
           <cell r="J2">
-            <v>0.46800018669531451</v>
+            <v>0.39498384438829071</v>
           </cell>
           <cell r="K2">
             <v>0</v>
@@ -1626,31 +1626,31 @@
             <v>2</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Alabama</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Hofstra</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="E3">
-            <v>21.35</v>
+            <v>14.976006036963041</v>
           </cell>
           <cell r="F3" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.63809273344358919</v>
+            <v>0.55757114715800105</v>
           </cell>
           <cell r="H3">
-            <v>6.5997896092614958E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I3">
-            <v>0.21817703657412491</v>
+            <v>6.445400821072933E-2</v>
           </cell>
           <cell r="J3">
-            <v>0.82374745212732714</v>
+            <v>0.58389146809910786</v>
           </cell>
           <cell r="K3">
-            <v>1.288278931727844</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="4">
@@ -1658,28 +1658,28 @@
             <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Florida</v>
+            <v>Duke</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>TCU</v>
           </cell>
           <cell r="E4">
-            <v>35</v>
+            <v>16.481515841644931</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.5</v>
+            <v>0.59645578309119174</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>-4.5454545454545407E-2</v>
+            <v>0.13868831317409341</v>
           </cell>
           <cell r="J4">
-            <v>0.82374745212732714</v>
+            <v>0.68835260367062623</v>
           </cell>
           <cell r="K4">
             <v>0</v>
@@ -1690,28 +1690,28 @@
             <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Clemson</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D5" t="str">
-            <v>Iowa</v>
+            <v>VCU</v>
           </cell>
           <cell r="E5">
-            <v>3.3395963530867379E-2</v>
+            <v>13.813979689921981</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.55056432776779596</v>
+            <v>0.57642572201149722</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>5.1077353011246829E-2</v>
+            <v>0.1004491056583129</v>
           </cell>
           <cell r="J5">
-            <v>0.12227695604597411</v>
+            <v>0.59272854171055378</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1722,28 +1722,28 @@
             <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>UCLA</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D6" t="str">
-            <v>UCF</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="E6">
-            <v>7.0470101204148357</v>
+            <v>-1.470916172407954</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.53851296772810842</v>
+            <v>0.51318971547862935</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>2.8070211117297909E-2</v>
+            <v>-2.0274179540798461E-2</v>
           </cell>
           <cell r="J6">
-            <v>0.3157571093517878</v>
+            <v>1.5691879196898632E-2</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1754,28 +1754,28 @@
             <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Uconn</v>
+            <v>Houston</v>
           </cell>
           <cell r="D7" t="str">
-            <v>Furman</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="E7">
-            <v>25.574999999999999</v>
+            <v>12.490512577712639</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.59638086655976275</v>
+            <v>0.54864172283435142</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>0.13854529070500171</v>
+            <v>4.7406925411034577E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.82374745212732714</v>
+            <v>0.50131716872622822</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1786,31 +1786,31 @@
             <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Tennessee</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Miami (OH)</v>
+            <v>High Point</v>
           </cell>
           <cell r="E8">
-            <v>17.763320142231279</v>
+            <v>14.409404039669781</v>
           </cell>
           <cell r="F8" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.63446581889029208</v>
+            <v>0.56733563667959253</v>
           </cell>
           <cell r="H8">
-            <v>6.2951287867845318E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0.21125292697237591</v>
+            <v>8.3095306388313084E-2</v>
           </cell>
           <cell r="J8">
-            <v>0.77130206914028421</v>
+            <v>0.58925228425349863</v>
           </cell>
           <cell r="K8">
-            <v>1.2288091391803406</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="9">
@@ -1818,28 +1818,28 @@
             <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Virginia</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="D9" t="str">
-            <v>Wright State</v>
+            <v>Texas</v>
           </cell>
           <cell r="E9">
-            <v>20.115791597901271</v>
+            <v>8.8326972336325653</v>
           </cell>
           <cell r="F9" t="b">
             <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.54634765315908873</v>
+            <v>0.55795782677192751</v>
           </cell>
           <cell r="H9">
             <v>0</v>
           </cell>
           <cell r="I9">
-            <v>4.3027337849169463E-2</v>
+            <v>6.5192214746407129E-2</v>
           </cell>
           <cell r="J9">
-            <v>0.67485538426353442</v>
+            <v>0.41516446029663601</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1850,28 +1850,28 @@
             <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Miami</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D10" t="str">
-            <v>Missouri</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="E10">
-            <v>4.4969385785639577</v>
+            <v>4.1278919748299394</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.56200660866546603</v>
+            <v>0.57749658865455844</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>7.2921707452253348E-2</v>
+            <v>0.1024934874314298</v>
           </cell>
           <cell r="J10">
-            <v>0.2912235406823202</v>
+            <v>0.31628008750747999</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1882,28 +1882,28 @@
             <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Purdue</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Queens University</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="E11">
-            <v>28.5</v>
+            <v>0.62393594721707213</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.56681426051108019</v>
+            <v>0.54042163234016005</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>8.2099951884789468E-2</v>
+            <v>3.171402537666923E-2</v>
           </cell>
           <cell r="J11">
-            <v>0.82374745212732714</v>
+            <v>0.1168367102471547</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1914,28 +1914,28 @@
             <v>11</v>
           </cell>
           <cell r="C12" t="str">
+            <v>Iowa State</v>
+          </cell>
+          <cell r="D12" t="str">
             <v>Kentucky</v>
           </cell>
-          <cell r="D12" t="str">
-            <v>Santa Clara</v>
-          </cell>
           <cell r="E12">
-            <v>5.6593475628966718</v>
+            <v>7.1011751940087526</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.56600384912440083</v>
+            <v>0.55224027884451476</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>8.0552802873856133E-2</v>
+            <v>5.4276895975891908E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.3368011492256191</v>
+            <v>0.34931589557310277</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1946,28 +1946,28 @@
             <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Iowa State</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Tennessee State</v>
+            <v>Utah State</v>
           </cell>
           <cell r="E13">
-            <v>28.175000000000001</v>
+            <v>12.03916810204351</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.57012118173818638</v>
+            <v>0.51344101562434308</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>8.841316513653763E-2</v>
+            <v>-1.9794424717163191E-2</v>
           </cell>
           <cell r="J13">
-            <v>0.82374745212732714</v>
+            <v>0.41142205261584602</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1978,28 +1978,28 @@
             <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>St. John's</v>
+            <v>Louisville</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Northern Iowa</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="E14">
-            <v>11.95141219900553</v>
+            <v>-3.809326919725216</v>
           </cell>
           <cell r="F14" t="b">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.54812259817372755</v>
+            <v>0.51721582153955314</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>4.6415869240752639E-2</v>
+            <v>-1.2587977060853069E-2</v>
           </cell>
           <cell r="J14">
-            <v>0.48515083858939739</v>
+            <v>8.115042882985124E-2</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -2010,31 +2010,31 @@
             <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Kansas</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D15" t="str">
-            <v>California Baptist</v>
+            <v>Michigan</v>
           </cell>
           <cell r="E15">
-            <v>20.297186452323341</v>
+            <v>-12.63418965089744</v>
           </cell>
           <cell r="F15" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.62310087724532315</v>
+            <v>0.50334583110950348</v>
           </cell>
           <cell r="H15">
-            <v>5.3404736886071551E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I15">
-            <v>0.18955622019561699</v>
+            <v>-3.906704970003877E-2</v>
           </cell>
           <cell r="J15">
-            <v>0.79167581956681854</v>
+            <v>0.40668649337587193</v>
           </cell>
           <cell r="K15">
-            <v>1.0424604640161166</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="16">
@@ -2042,28 +2042,28 @@
             <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Arizona</v>
+            <v>TCU</v>
           </cell>
           <cell r="D16" t="str">
-            <v>Long Island University</v>
+            <v>Duke</v>
           </cell>
           <cell r="E16">
-            <v>32.400000000000013</v>
+            <v>-12.900837100669641</v>
           </cell>
           <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.5268316233988839</v>
+            <v>0.52244951418090224</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>5.7694628524147529E-3</v>
+            <v>-2.5963820182774988E-3</v>
           </cell>
           <cell r="J16">
-            <v>0.82374745212732714</v>
+            <v>0.45710006902003109</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -2074,28 +2074,28 @@
             <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Villanova</v>
+            <v>VCU</v>
           </cell>
           <cell r="D17" t="str">
-            <v>Utah State</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E17">
-            <v>-0.1780563139182261</v>
+            <v>-7.6481914140359821</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.54533016307921067</v>
+            <v>0.57073198047378837</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>4.1084856787584063E-2</v>
+            <v>8.9579235449959715E-2</v>
           </cell>
           <cell r="J17">
-            <v>0.102922512580872</v>
+            <v>7.5545540380110965E-2</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2106,28 +2106,28 @@
             <v>17</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Michigan State</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Louisville</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="E18">
-            <v>7.7185281356503328</v>
+            <v>4.7803474147172347</v>
           </cell>
           <cell r="F18" t="b">
             <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0.59188943533172611</v>
+            <v>0.56897756221792961</v>
           </cell>
           <cell r="H18">
             <v>0</v>
           </cell>
           <cell r="I18">
-            <v>0.12997074017874991</v>
+            <v>8.6229891506956591E-2</v>
           </cell>
           <cell r="J18">
-            <v>0.45858766203522988</v>
+            <v>0.31649838901374577</v>
           </cell>
           <cell r="K18">
             <v>0</v>
@@ -2138,28 +2138,28 @@
             <v>18</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Michigan</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="D19" t="str">
-            <v>Saint Louis</v>
+            <v>Houston</v>
           </cell>
           <cell r="E19">
-            <v>15.5119498017062</v>
+            <v>-7.5735379918606291</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.56845929673645745</v>
+            <v>0.57256327900997128</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>8.5240475587782472E-2</v>
+            <v>9.3075350837217963E-2</v>
           </cell>
           <cell r="J19">
-            <v>0.61731951279916419</v>
+            <v>6.8699796942407798E-2</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2170,28 +2170,28 @@
             <v>19</v>
           </cell>
           <cell r="C20" t="str">
-            <v>Duke</v>
+            <v>High Point</v>
           </cell>
           <cell r="D20" t="str">
-            <v>TCU</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="E20">
-            <v>16.140216310663</v>
+            <v>-12.955196747770399</v>
           </cell>
           <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0.60906422040161368</v>
+            <v>0.5358807449944516</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>0.16275896622126251</v>
+            <v>2.3045058625771279E-2</v>
           </cell>
           <cell r="J20">
-            <v>0.70336153249742339</v>
+            <v>0.48734606471556818</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2202,28 +2202,28 @@
             <v>20</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Illinois</v>
+            <v>Texas</v>
           </cell>
           <cell r="D21" t="str">
-            <v>VCU</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="E21">
-            <v>14.438763270417709</v>
+            <v>-4.8282195018383911</v>
           </cell>
           <cell r="F21" t="b">
             <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0.5884378419425238</v>
+            <v>0.5416082726227095</v>
           </cell>
           <cell r="H21">
             <v>0</v>
           </cell>
           <cell r="I21">
-            <v>0.1233813346175455</v>
+            <v>3.3979429552445428E-2</v>
           </cell>
           <cell r="J21">
-            <v>0.63074311573987751</v>
+            <v>5.5369792667541717E-2</v>
           </cell>
           <cell r="K21">
             <v>0</v>
@@ -2234,28 +2234,28 @@
             <v>21</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Nebraska</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="D22" t="str">
-            <v>Vanderbilt</v>
+            <v>Alabama</v>
           </cell>
           <cell r="E22">
-            <v>-1.093500554042212</v>
+            <v>-2.5226261132732191</v>
           </cell>
           <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0.53502439171067129</v>
+            <v>0.53790777044744986</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>2.141020235673613E-2</v>
+            <v>2.6914834490586129E-2</v>
           </cell>
           <cell r="J22">
-            <v>4.8789164423594489E-2</v>
+            <v>0.1715154919189017</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2266,31 +2266,31 @@
             <v>22</v>
           </cell>
           <cell r="C23" t="str">
-            <v>Houston</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D23" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Virginia</v>
           </cell>
           <cell r="E23">
-            <v>12.80869246587973</v>
+            <v>6.3504265210794983</v>
           </cell>
           <cell r="F23" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G23">
-            <v>0.5666785188322544</v>
+            <v>0.62857011124576767</v>
           </cell>
           <cell r="H23">
-            <v>0</v>
+            <v>5.7998893446444849E-2</v>
           </cell>
           <cell r="I23">
-            <v>8.1840808679758403E-2</v>
+            <v>0.19999748510555651</v>
           </cell>
           <cell r="J23">
-            <v>0.54759166061732523</v>
+            <v>0.503917783931362</v>
           </cell>
           <cell r="K23">
-            <v>0</v>
+            <v>1.1321384000746035</v>
           </cell>
         </row>
         <row r="24">
@@ -2298,28 +2298,28 @@
             <v>23</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Arkansas</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D24" t="str">
-            <v>High Point</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="E24">
-            <v>14.531806056773171</v>
+            <v>-4.5359178664915367</v>
           </cell>
           <cell r="F24" t="b">
             <v>0</v>
           </cell>
           <cell r="G24">
-            <v>0.58014282659298355</v>
+            <v>0.51156975174926678</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>0.1075453962229687</v>
+            <v>-2.3366837569581581E-2</v>
           </cell>
           <cell r="J24">
-            <v>0.61701013724196296</v>
+            <v>0.1179331312373687</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2330,28 +2330,28 @@
             <v>24</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Gonzaga</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D25" t="str">
-            <v>Texas</v>
+            <v>Arizona</v>
           </cell>
           <cell r="E25">
-            <v>8.5492026218240404</v>
+            <v>-9.6384453574740654</v>
           </cell>
           <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0.57557077504574861</v>
+            <v>0.54631129649620014</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>9.881693417824744E-2</v>
+            <v>4.2957929674563973E-2</v>
           </cell>
           <cell r="J25">
-            <v>0.44641629054277171</v>
+            <v>0.19797857638448821</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2361,29 +2361,23 @@
           <cell r="B26">
             <v>25</v>
           </cell>
-          <cell r="C26" t="str">
-            <v>Akron</v>
-          </cell>
-          <cell r="D26" t="str">
-            <v>Texas Tech</v>
-          </cell>
           <cell r="E26">
-            <v>-5.7133742605995348</v>
-          </cell>
-          <cell r="F26" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F26">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0.54445513080134145</v>
+            <v>0</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>3.9414340620742783E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J26">
-            <v>7.6937609984081723E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2393,29 +2387,23 @@
           <cell r="B27">
             <v>26</v>
           </cell>
-          <cell r="C27" t="str">
-            <v>Hofstra</v>
-          </cell>
-          <cell r="D27" t="str">
-            <v>Alabama</v>
-          </cell>
           <cell r="E27">
-            <v>-18.200910725903629</v>
-          </cell>
-          <cell r="F27" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F27">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0.58915163001262683</v>
+            <v>0</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>0.1247440209331967</v>
+            <v>0</v>
           </cell>
           <cell r="J27">
-            <v>0.70857165526473465</v>
+            <v>0</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2425,29 +2413,23 @@
           <cell r="B28">
             <v>27</v>
           </cell>
-          <cell r="C28" t="str">
-            <v>Prairie View A&amp;M</v>
-          </cell>
-          <cell r="D28" t="str">
-            <v>Florida</v>
-          </cell>
           <cell r="E28">
-            <v>-35</v>
-          </cell>
-          <cell r="F28" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F28">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0.5</v>
+            <v>0</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>-4.5454545454545407E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J28">
-            <v>0.82374745212732714</v>
+            <v>0</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2457,29 +2439,23 @@
           <cell r="B29">
             <v>28</v>
           </cell>
-          <cell r="C29" t="str">
-            <v>Iowa</v>
-          </cell>
-          <cell r="D29" t="str">
-            <v>Clemson</v>
-          </cell>
           <cell r="E29">
-            <v>5.6137133324827877</v>
-          </cell>
-          <cell r="F29" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F29">
             <v>0</v>
           </cell>
           <cell r="G29">
-            <v>0.58934371104373051</v>
+            <v>0</v>
           </cell>
           <cell r="H29">
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>0.1251107210834855</v>
+            <v>0</v>
           </cell>
           <cell r="J29">
-            <v>0.38977250670595909</v>
+            <v>0</v>
           </cell>
           <cell r="K29">
             <v>0</v>
@@ -2489,29 +2465,23 @@
           <cell r="B30">
             <v>29</v>
           </cell>
-          <cell r="C30" t="str">
-            <v>UCF</v>
-          </cell>
-          <cell r="D30" t="str">
-            <v>UCLA</v>
-          </cell>
           <cell r="E30">
-            <v>-2.8861369669403749</v>
-          </cell>
-          <cell r="F30" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F30">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0.56488503739422913</v>
+            <v>0</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>7.8416889570801063E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J30">
-            <v>6.3226472938151368E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2521,29 +2491,23 @@
           <cell r="B31">
             <v>30</v>
           </cell>
-          <cell r="C31" t="str">
-            <v>Furman</v>
-          </cell>
-          <cell r="D31" t="str">
-            <v>Uconn</v>
-          </cell>
           <cell r="E31">
-            <v>-21.482427500798011</v>
-          </cell>
-          <cell r="F31" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F31">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0.52177084207843238</v>
+            <v>0</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>-3.8920287593562919E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J31">
-            <v>0.66120627779014118</v>
+            <v>0</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2553,29 +2517,23 @@
           <cell r="B32">
             <v>31</v>
           </cell>
-          <cell r="C32" t="str">
-            <v>Miami (OH)</v>
-          </cell>
-          <cell r="D32" t="str">
-            <v>Tennessee</v>
-          </cell>
           <cell r="E32">
-            <v>-14.923953790708479</v>
-          </cell>
-          <cell r="F32" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F32">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0.58757381148107868</v>
+            <v>0</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>0.12173182191842299</v>
+            <v>0</v>
           </cell>
           <cell r="J32">
-            <v>0.63996826747857327</v>
+            <v>0</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2585,29 +2543,23 @@
           <cell r="B33">
             <v>32</v>
           </cell>
-          <cell r="C33" t="str">
-            <v>Wright State</v>
-          </cell>
-          <cell r="D33" t="str">
-            <v>Virginia</v>
-          </cell>
           <cell r="E33">
-            <v>-15.96072331533523</v>
-          </cell>
-          <cell r="F33" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F33">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0.55070977428765122</v>
+            <v>0</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>5.1355023640061503E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J33">
-            <v>0.38516760636631159</v>
+            <v>0</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -2617,29 +2569,23 @@
           <cell r="B34">
             <v>33</v>
           </cell>
-          <cell r="C34" t="str">
-            <v>Missouri</v>
-          </cell>
-          <cell r="D34" t="str">
-            <v>Miami</v>
-          </cell>
           <cell r="E34">
-            <v>2.1482075857303151</v>
-          </cell>
-          <cell r="F34" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F34">
             <v>0</v>
           </cell>
           <cell r="G34">
-            <v>0.60228382736083119</v>
+            <v>0</v>
           </cell>
           <cell r="H34">
             <v>0</v>
           </cell>
           <cell r="I34">
-            <v>0.1498145795070415</v>
+            <v>0</v>
           </cell>
           <cell r="J34">
-            <v>0.31364001260244623</v>
+            <v>0</v>
           </cell>
           <cell r="K34">
             <v>0</v>
@@ -2649,29 +2595,23 @@
           <cell r="B35">
             <v>34</v>
           </cell>
-          <cell r="C35" t="str">
-            <v>Queens University</v>
-          </cell>
-          <cell r="D35" t="str">
-            <v>Purdue</v>
-          </cell>
           <cell r="E35">
-            <v>-27.532563309862141</v>
-          </cell>
-          <cell r="F35" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F35">
             <v>0</v>
           </cell>
           <cell r="G35">
-            <v>0.55004263682873855</v>
+            <v>0</v>
           </cell>
           <cell r="H35">
             <v>0</v>
           </cell>
           <cell r="I35">
-            <v>5.0081397582137248E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J35">
-            <v>0.79449285353871313</v>
+            <v>0</v>
           </cell>
           <cell r="K35">
             <v>0</v>
@@ -2681,29 +2621,23 @@
           <cell r="B36">
             <v>35</v>
           </cell>
-          <cell r="C36" t="str">
-            <v>Santa Clara</v>
-          </cell>
-          <cell r="D36" t="str">
-            <v>Kentucky</v>
-          </cell>
           <cell r="E36">
-            <v>-2.097560289466216</v>
-          </cell>
-          <cell r="F36" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F36">
             <v>0</v>
           </cell>
           <cell r="G36">
-            <v>0.52248941008610128</v>
+            <v>0</v>
           </cell>
           <cell r="H36">
             <v>0</v>
           </cell>
           <cell r="I36">
-            <v>-2.5202171083520408E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J36">
-            <v>1.3547631565368701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K36">
             <v>0</v>
@@ -2713,29 +2647,23 @@
           <cell r="B37">
             <v>36</v>
           </cell>
-          <cell r="C37" t="str">
-            <v>Tennessee State</v>
-          </cell>
-          <cell r="D37" t="str">
-            <v>Iowa State</v>
-          </cell>
           <cell r="E37">
-            <v>-26.323261769434339</v>
-          </cell>
-          <cell r="F37" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F37">
             <v>0</v>
           </cell>
           <cell r="G37">
-            <v>0.53718956657658601</v>
+            <v>0</v>
           </cell>
           <cell r="H37">
             <v>0</v>
           </cell>
           <cell r="I37">
-            <v>2.5543718009846061E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J37">
-            <v>0.76328915590709401</v>
+            <v>0</v>
           </cell>
           <cell r="K37">
             <v>0</v>
@@ -2745,29 +2673,23 @@
           <cell r="B38">
             <v>37</v>
           </cell>
-          <cell r="C38" t="str">
-            <v>Northern Iowa</v>
-          </cell>
-          <cell r="D38" t="str">
-            <v>St. John's</v>
-          </cell>
           <cell r="E38">
-            <v>-5.7155949911145472</v>
-          </cell>
-          <cell r="F38" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F38">
             <v>0</v>
           </cell>
           <cell r="G38">
-            <v>0.60556386284114683</v>
+            <v>0</v>
           </cell>
           <cell r="H38">
             <v>0</v>
           </cell>
           <cell r="I38">
-            <v>0.15607646542400769</v>
+            <v>0</v>
           </cell>
           <cell r="J38">
-            <v>7.1989015715373472E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K38">
             <v>0</v>
@@ -2777,29 +2699,23 @@
           <cell r="B39">
             <v>38</v>
           </cell>
-          <cell r="C39" t="str">
-            <v>California Baptist</v>
-          </cell>
-          <cell r="D39" t="str">
-            <v>Kansas</v>
-          </cell>
           <cell r="E39">
-            <v>-14.52957082789203</v>
-          </cell>
-          <cell r="F39" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F39">
             <v>0</v>
           </cell>
           <cell r="G39">
-            <v>0.51310106393859689</v>
+            <v>0</v>
           </cell>
           <cell r="H39">
             <v>0</v>
           </cell>
           <cell r="I39">
-            <v>-2.0443423389951369E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J39">
-            <v>0.48348064838746119</v>
+            <v>0</v>
           </cell>
           <cell r="K39">
             <v>0</v>
@@ -2809,29 +2725,23 @@
           <cell r="B40">
             <v>39</v>
           </cell>
-          <cell r="C40" t="str">
-            <v>Long Island University</v>
-          </cell>
-          <cell r="D40" t="str">
-            <v>Arizona</v>
-          </cell>
           <cell r="E40">
-            <v>-32.400000000000013</v>
-          </cell>
-          <cell r="F40" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F40">
             <v>0</v>
           </cell>
           <cell r="G40">
-            <v>0.5268316233988839</v>
+            <v>0</v>
           </cell>
           <cell r="H40">
             <v>0</v>
           </cell>
           <cell r="I40">
-            <v>5.7694628524147529E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J40">
-            <v>0.82374745212732714</v>
+            <v>0</v>
           </cell>
           <cell r="K40">
             <v>0</v>
@@ -2841,29 +2751,23 @@
           <cell r="B41">
             <v>40</v>
           </cell>
-          <cell r="C41" t="str">
-            <v>Utah State</v>
-          </cell>
-          <cell r="D41" t="str">
-            <v>Villanova</v>
-          </cell>
           <cell r="E41">
-            <v>5.4593714883795128</v>
-          </cell>
-          <cell r="F41" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F41">
             <v>0</v>
           </cell>
           <cell r="G41">
-            <v>0.58558825032111539</v>
+            <v>0</v>
           </cell>
           <cell r="H41">
             <v>0</v>
           </cell>
           <cell r="I41">
-            <v>0.117941205158493</v>
+            <v>0</v>
           </cell>
           <cell r="J41">
-            <v>0.37633750295571428</v>
+            <v>0</v>
           </cell>
           <cell r="K41">
             <v>0</v>
@@ -2873,29 +2777,23 @@
           <cell r="B42">
             <v>41</v>
           </cell>
-          <cell r="C42" t="str">
-            <v>Louisville</v>
-          </cell>
-          <cell r="D42" t="str">
-            <v>Michigan State</v>
-          </cell>
           <cell r="E42">
-            <v>-3.009819784518605</v>
-          </cell>
-          <cell r="F42" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F42">
             <v>0</v>
           </cell>
           <cell r="G42">
-            <v>0.52467329665300033</v>
+            <v>0</v>
           </cell>
           <cell r="H42">
             <v>0</v>
           </cell>
           <cell r="I42">
-            <v>1.6490208830006741E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J42">
-            <v>3.7622338566990272E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K42">
             <v>0</v>
@@ -2905,29 +2803,23 @@
           <cell r="B43">
             <v>42</v>
           </cell>
-          <cell r="C43" t="str">
-            <v>Saint Louis</v>
-          </cell>
-          <cell r="D43" t="str">
-            <v>Michigan</v>
-          </cell>
           <cell r="E43">
-            <v>-12.429984635021251</v>
-          </cell>
-          <cell r="F43" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F43">
             <v>0</v>
           </cell>
           <cell r="G43">
-            <v>0.50174575001391375</v>
+            <v>0</v>
           </cell>
           <cell r="H43">
             <v>0</v>
           </cell>
           <cell r="I43">
-            <v>-4.2121749973437372E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J43">
-            <v>0.38901453824241772</v>
+            <v>0</v>
           </cell>
           <cell r="K43">
             <v>0</v>
@@ -2937,29 +2829,23 @@
           <cell r="B44">
             <v>43</v>
           </cell>
-          <cell r="C44" t="str">
-            <v>TCU</v>
-          </cell>
-          <cell r="D44" t="str">
-            <v>Duke</v>
-          </cell>
           <cell r="E44">
-            <v>-12.096831283208401</v>
-          </cell>
-          <cell r="F44" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F44">
             <v>0</v>
           </cell>
           <cell r="G44">
-            <v>0.52732686847916632</v>
+            <v>0</v>
           </cell>
           <cell r="H44">
             <v>0</v>
           </cell>
           <cell r="I44">
-            <v>6.7149307329539276E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J44">
-            <v>0.44409903598414241</v>
+            <v>0</v>
           </cell>
           <cell r="K44">
             <v>0</v>
@@ -2969,29 +2855,23 @@
           <cell r="B45">
             <v>44</v>
           </cell>
-          <cell r="C45" t="str">
-            <v>VCU</v>
-          </cell>
-          <cell r="D45" t="str">
-            <v>Illinois</v>
-          </cell>
           <cell r="E45">
-            <v>-7.2568674597012466</v>
-          </cell>
-          <cell r="F45" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F45">
             <v>0</v>
           </cell>
           <cell r="G45">
-            <v>0.58031359058064103</v>
+            <v>0</v>
           </cell>
           <cell r="H45">
             <v>0</v>
           </cell>
           <cell r="I45">
-            <v>0.10787140019940571</v>
+            <v>0</v>
           </cell>
           <cell r="J45">
-            <v>3.9645885764726663E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K45">
             <v>0</v>
@@ -3001,29 +2881,23 @@
           <cell r="B46">
             <v>45</v>
           </cell>
-          <cell r="C46" t="str">
-            <v>Vanderbilt</v>
-          </cell>
-          <cell r="D46" t="str">
-            <v>Nebraska</v>
-          </cell>
           <cell r="E46">
-            <v>5.3076158961687021</v>
-          </cell>
-          <cell r="F46" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F46">
             <v>0</v>
           </cell>
           <cell r="G46">
-            <v>0.569647183746957</v>
+            <v>0</v>
           </cell>
           <cell r="H46">
             <v>0</v>
           </cell>
           <cell r="I46">
-            <v>8.7508259880554329E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J46">
-            <v>0.33443712076902887</v>
+            <v>0</v>
           </cell>
           <cell r="K46">
             <v>0</v>
@@ -3033,29 +2907,23 @@
           <cell r="B47">
             <v>46</v>
           </cell>
-          <cell r="C47" t="str">
-            <v>Texas A&amp;M</v>
-          </cell>
-          <cell r="D47" t="str">
-            <v>Houston</v>
-          </cell>
           <cell r="E47">
-            <v>-7.1037832151035936</v>
-          </cell>
-          <cell r="F47" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F47">
             <v>0</v>
           </cell>
           <cell r="G47">
-            <v>0.57182152945754017</v>
+            <v>0</v>
           </cell>
           <cell r="H47">
             <v>0</v>
           </cell>
           <cell r="I47">
-            <v>9.1659283509849421E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J47">
-            <v>5.5421511542608992E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K47">
             <v>0</v>
@@ -3065,29 +2933,23 @@
           <cell r="B48">
             <v>47</v>
           </cell>
-          <cell r="C48" t="str">
-            <v>High Point</v>
-          </cell>
-          <cell r="D48" t="str">
-            <v>Arkansas</v>
-          </cell>
           <cell r="E48">
-            <v>-12.3836786652074</v>
-          </cell>
-          <cell r="F48" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F48">
             <v>0</v>
           </cell>
           <cell r="G48">
-            <v>0.53445753974774979</v>
+            <v>0</v>
           </cell>
           <cell r="H48">
             <v>0</v>
           </cell>
           <cell r="I48">
-            <v>2.0328030427522351E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J48">
-            <v>0.46823988524848509</v>
+            <v>0</v>
           </cell>
           <cell r="K48">
             <v>0</v>
@@ -3097,29 +2959,23 @@
           <cell r="B49">
             <v>48</v>
           </cell>
-          <cell r="C49" t="str">
-            <v>Texas</v>
-          </cell>
-          <cell r="D49" t="str">
-            <v>Gonzaga</v>
-          </cell>
           <cell r="E49">
-            <v>-4.0735770169153609</v>
-          </cell>
-          <cell r="F49" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F49">
             <v>0</v>
           </cell>
           <cell r="G49">
-            <v>0.53551922013547781</v>
+            <v>0</v>
           </cell>
           <cell r="H49">
             <v>0</v>
           </cell>
           <cell r="I49">
-            <v>2.2354874804094042E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J49">
-            <v>4.5768048855342247E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K49">
             <v>0</v>
@@ -8873,73 +8729,73 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>Texas Tech</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Akron</v>
+            <v>Louisville</v>
           </cell>
           <cell r="D2">
-            <v>17.052374181699321</v>
+            <v>19.982154388171562</v>
           </cell>
           <cell r="E2">
-            <v>100.51882408229335</v>
+            <v>101.32466702184337</v>
           </cell>
           <cell r="F2">
-            <v>104.30065451536628</v>
+            <v>94.579391423053281</v>
           </cell>
           <cell r="G2">
-            <v>0.56166837256908908</v>
+            <v>0.53589041095890411</v>
           </cell>
           <cell r="H2">
-            <v>67.617500000000007</v>
+            <v>66.620645161290327</v>
           </cell>
           <cell r="I2">
-            <v>61.0625</v>
+            <v>58.87096774193548</v>
           </cell>
           <cell r="J2">
-            <v>16.53125</v>
+            <v>20.838709677419356</v>
           </cell>
           <cell r="K2">
-            <v>11.53125</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="L2">
-            <v>10.8125</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="M2">
             <v>0</v>
           </cell>
           <cell r="N2">
-            <v>10.62898797126984</v>
+            <v>16.631119331501349</v>
           </cell>
           <cell r="O2">
-            <v>99.852760736196316</v>
+            <v>99.101896527014759</v>
           </cell>
           <cell r="P2">
-            <v>94.235250093919447</v>
+            <v>98.314439245284362</v>
           </cell>
           <cell r="Q2">
-            <v>0.58984747378455671</v>
+            <v>0.56448412698412698</v>
           </cell>
           <cell r="R2">
-            <v>71.226666666666659</v>
+            <v>70.393939393939391</v>
           </cell>
           <cell r="S2">
-            <v>63.575757575757578</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="T2">
-            <v>17.939393939393938</v>
+            <v>20.454545454545453</v>
           </cell>
           <cell r="U2">
-            <v>11.272727272727273</v>
+            <v>11.333333333333334</v>
           </cell>
           <cell r="V2">
-            <v>11.030303030303031</v>
+            <v>11.636363636363637</v>
           </cell>
           <cell r="W2">
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-7.5</v>
+            <v>-4.5</v>
           </cell>
         </row>
         <row r="3">
@@ -8947,73 +8803,73 @@
             <v>2</v>
           </cell>
           <cell r="B3" t="str">
-            <v>Alabama</v>
+            <v>Michigan</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Hofstra</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D3">
-            <v>19.673613604820769</v>
+            <v>23.158914646956031</v>
           </cell>
           <cell r="E3">
-            <v>102.29455081001471</v>
+            <v>98.200984374253366</v>
           </cell>
           <cell r="F3">
-            <v>103.71887375881523</v>
+            <v>96.383444817292968</v>
           </cell>
           <cell r="G3">
-            <v>0.55384250474383301</v>
+            <v>0.58467532467532468</v>
           </cell>
           <cell r="H3">
-            <v>74.217500000000001</v>
+            <v>71.510000000000005</v>
           </cell>
           <cell r="I3">
-            <v>65.875</v>
+            <v>60.15625</v>
           </cell>
           <cell r="J3">
-            <v>24.5</v>
+            <v>23.53125</v>
           </cell>
           <cell r="K3">
-            <v>12.21875</v>
+            <v>11.0625</v>
           </cell>
           <cell r="L3">
-            <v>9.78125</v>
+            <v>12.0625</v>
           </cell>
           <cell r="M3">
             <v>0</v>
           </cell>
           <cell r="N3">
-            <v>2.1356002741910172</v>
+            <v>12.891007564287897</v>
           </cell>
           <cell r="O3">
-            <v>101.93227153239523</v>
+            <v>96.587342281204442</v>
           </cell>
           <cell r="P3">
-            <v>108.25319811541539</v>
+            <v>96.419529699076293</v>
           </cell>
           <cell r="Q3">
-            <v>0.52252944188428063</v>
+            <v>0.59935205183585316</v>
           </cell>
           <cell r="R3">
-            <v>65.487272727272725</v>
+            <v>71.190967741935481</v>
           </cell>
           <cell r="S3">
-            <v>59.18181818181818</v>
+            <v>59.741935483870968</v>
           </cell>
           <cell r="T3">
-            <v>18.393939393939394</v>
+            <v>20.741935483870968</v>
           </cell>
           <cell r="U3">
-            <v>12.484848484848484</v>
+            <v>10.03225806451613</v>
           </cell>
           <cell r="V3">
-            <v>10.696969696969697</v>
+            <v>12.35483870967742</v>
           </cell>
           <cell r="W3">
             <v>0</v>
           </cell>
           <cell r="X3">
-            <v>-14</v>
+            <v>-12.5</v>
           </cell>
         </row>
         <row r="4">
@@ -9021,73 +8877,73 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>Florida</v>
+            <v>Duke</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Prairie View A&amp;M</v>
+            <v>TCU</v>
           </cell>
           <cell r="D4">
-            <v>22.650454216704585</v>
+            <v>23.054887624413109</v>
           </cell>
           <cell r="E4">
-            <v>104.38676700269771</v>
+            <v>101.57301127857072</v>
           </cell>
           <cell r="F4">
-            <v>99.448258680413886</v>
+            <v>99.414290660558592</v>
           </cell>
           <cell r="G4">
-            <v>0.53652636671504594</v>
+            <v>0.57213541666666667</v>
           </cell>
           <cell r="H4">
-            <v>71.564999999999998</v>
+            <v>66.278787878787867</v>
           </cell>
           <cell r="I4">
-            <v>64.59375</v>
+            <v>58.18181818181818</v>
           </cell>
           <cell r="J4">
-            <v>25.21875</v>
+            <v>22.121212121212121</v>
           </cell>
           <cell r="K4">
-            <v>15.96875</v>
+            <v>12.212121212121213</v>
           </cell>
           <cell r="L4">
-            <v>11.84375</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="M4">
             <v>0</v>
           </cell>
           <cell r="N4">
-            <v>-11.471425536201773</v>
+            <v>12.676356416890858</v>
           </cell>
           <cell r="O4">
-            <v>97.164732374848427</v>
+            <v>101.27537334728432</v>
           </cell>
           <cell r="P4">
-            <v>95.447708530170132</v>
+            <v>97.104848064562987</v>
           </cell>
           <cell r="Q4">
-            <v>0.49387855044074436</v>
+            <v>0.50900000000000001</v>
           </cell>
           <cell r="R4">
-            <v>73.484705882352941</v>
+            <v>69.441212121212118</v>
           </cell>
           <cell r="S4">
-            <v>60.058823529411768</v>
+            <v>60.606060606060609</v>
           </cell>
           <cell r="T4">
-            <v>26.235294117647058</v>
+            <v>23.454545454545453</v>
           </cell>
           <cell r="U4">
-            <v>10.058823529411764</v>
+            <v>12.424242424242424</v>
           </cell>
           <cell r="V4">
-            <v>11.941176470588236</v>
+            <v>10.939393939393939</v>
           </cell>
           <cell r="W4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-35</v>
+            <v>-12</v>
           </cell>
         </row>
         <row r="5">
@@ -9095,73 +8951,73 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>Clemson</v>
+            <v>Illinois</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Iowa</v>
+            <v>VCU</v>
           </cell>
           <cell r="D5">
-            <v>11.025556023298106</v>
+            <v>18.826343007871433</v>
           </cell>
           <cell r="E5">
-            <v>99.36088590073166</v>
+            <v>105.08780903665816</v>
           </cell>
           <cell r="F5">
-            <v>103.15195066761017</v>
+            <v>108.91673393133649</v>
           </cell>
           <cell r="G5">
-            <v>0.52621919244887261</v>
+            <v>0.5511688311688312</v>
           </cell>
           <cell r="H5">
-            <v>65.309411764705885</v>
+            <v>66.809032258064519</v>
           </cell>
           <cell r="I5">
-            <v>56.088235294117645</v>
+            <v>62.096774193548384</v>
           </cell>
           <cell r="J5">
-            <v>20.823529411764707</v>
+            <v>20.387096774193548</v>
           </cell>
           <cell r="K5">
-            <v>9.3235294117647065</v>
+            <v>13.258064516129032</v>
           </cell>
           <cell r="L5">
-            <v>9.382352941176471</v>
+            <v>9</v>
           </cell>
           <cell r="M5">
             <v>0</v>
           </cell>
           <cell r="N5">
-            <v>15.51511812576733</v>
+            <v>10.280535393881047</v>
           </cell>
           <cell r="O5">
-            <v>98.238539943433466</v>
+            <v>99.976592216912124</v>
           </cell>
           <cell r="P5">
-            <v>93.168875634820807</v>
+            <v>99.94980567668172</v>
           </cell>
           <cell r="Q5">
-            <v>0.56555993247045577</v>
+            <v>0.54290339989206693</v>
           </cell>
           <cell r="R5">
-            <v>62.900606060606066</v>
+            <v>68.818749999999994</v>
           </cell>
           <cell r="S5">
-            <v>53.848484848484851</v>
+            <v>57.90625</v>
           </cell>
           <cell r="T5">
-            <v>18.575757575757574</v>
+            <v>25.9375</v>
           </cell>
           <cell r="U5">
-            <v>8.8181818181818183</v>
+            <v>11.3125</v>
           </cell>
           <cell r="V5">
-            <v>9.6969696969696972</v>
+            <v>10.8125</v>
           </cell>
           <cell r="W5">
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>2</v>
+            <v>-10.5</v>
           </cell>
         </row>
         <row r="6">
@@ -9169,73 +9025,73 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>UCLA</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="C6" t="str">
-            <v>UCF</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D6">
-            <v>15.943406980069799</v>
+            <v>15.82631796216417</v>
           </cell>
           <cell r="E6">
-            <v>100.85863980873899</v>
+            <v>98.25476089716463</v>
           </cell>
           <cell r="F6">
-            <v>91.898292422931632</v>
+            <v>102.35159180352665</v>
           </cell>
           <cell r="G6">
-            <v>0.54047742605085625</v>
+            <v>0.55440552016985134</v>
           </cell>
           <cell r="H6">
-            <v>65.963636363636368</v>
+            <v>66.883750000000006</v>
           </cell>
           <cell r="I6">
-            <v>58.393939393939391</v>
+            <v>58.875</v>
           </cell>
           <cell r="J6">
-            <v>19.545454545454547</v>
+            <v>16</v>
           </cell>
           <cell r="K6">
-            <v>10</v>
+            <v>8.78125</v>
           </cell>
           <cell r="L6">
-            <v>8.9696969696969688</v>
+            <v>9.75</v>
           </cell>
           <cell r="M6">
             <v>0</v>
           </cell>
           <cell r="N6">
-            <v>12.780422052740661</v>
+            <v>19.334095266215517</v>
           </cell>
           <cell r="O6">
-            <v>101.06601066010661</v>
+            <v>100.88210871874095</v>
           </cell>
           <cell r="P6">
-            <v>97.015666781333081</v>
+            <v>97.473801766777243</v>
           </cell>
           <cell r="Q6">
-            <v>0.52792008196721307</v>
+            <v>0.55371690427698572</v>
           </cell>
           <cell r="R6">
-            <v>70.258064516129025</v>
+            <v>70.61</v>
           </cell>
           <cell r="S6">
-            <v>62.967741935483872</v>
+            <v>61.375</v>
           </cell>
           <cell r="T6">
-            <v>19.35483870967742</v>
+            <v>23.6875</v>
           </cell>
           <cell r="U6">
-            <v>12.387096774193548</v>
+            <v>10.8125</v>
           </cell>
           <cell r="V6">
-            <v>11.161290322580646</v>
+            <v>9.625</v>
           </cell>
           <cell r="W6">
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>-5.5</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="7">
@@ -9243,73 +9099,73 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>Uconn</v>
+            <v>Houston</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Furman</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="D7">
-            <v>18.120431537245491</v>
+            <v>20.901069562815731</v>
           </cell>
           <cell r="E7">
-            <v>100.0952772073922</v>
+            <v>105.43571389837862</v>
           </cell>
           <cell r="F7">
-            <v>94.261774983054991</v>
+            <v>97.084637989347655</v>
           </cell>
           <cell r="G7">
-            <v>0.55882352941176472</v>
+            <v>0.52154080081094778</v>
           </cell>
           <cell r="H7">
-            <v>66.089696969696973</v>
+            <v>64.762500000000003</v>
           </cell>
           <cell r="I7">
-            <v>58.727272727272727</v>
+            <v>61.65625</v>
           </cell>
           <cell r="J7">
-            <v>17.696969696969695</v>
+            <v>16.71875</v>
           </cell>
           <cell r="K7">
-            <v>11.454545454545455</v>
+            <v>12.78125</v>
           </cell>
           <cell r="L7">
-            <v>11.030303030303031</v>
+            <v>8.53125</v>
           </cell>
           <cell r="M7">
             <v>0</v>
           </cell>
           <cell r="N7">
-            <v>0.19358290778345913</v>
+            <v>13.344745551152522</v>
           </cell>
           <cell r="O7">
-            <v>98.095219377978665</v>
+            <v>101.09664255240216</v>
           </cell>
           <cell r="P7">
-            <v>107.97637861090803</v>
+            <v>98.213295342640578</v>
           </cell>
           <cell r="Q7">
-            <v>0.5527254202750892</v>
+            <v>0.54188861985472159</v>
           </cell>
           <cell r="R7">
-            <v>66.856470588235297</v>
+            <v>73.739999999999995</v>
           </cell>
           <cell r="S7">
-            <v>57.735294117647058</v>
+            <v>64.53125</v>
           </cell>
           <cell r="T7">
-            <v>18.323529411764707</v>
+            <v>24.125</v>
           </cell>
           <cell r="U7">
-            <v>10.882352941176471</v>
+            <v>12.25</v>
           </cell>
           <cell r="V7">
-            <v>11.941176470588236</v>
+            <v>10.84375</v>
           </cell>
           <cell r="W7">
             <v>0</v>
           </cell>
           <cell r="X7">
-            <v>-20.5</v>
+            <v>-10.5</v>
           </cell>
         </row>
         <row r="8">
@@ -9317,73 +9173,73 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>Tennessee</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Miami (OH)</v>
+            <v>High Point</v>
           </cell>
           <cell r="D8">
-            <v>20.582457175121956</v>
+            <v>19.899076876872613</v>
           </cell>
           <cell r="E8">
-            <v>105.02195491662999</v>
+            <v>101.9693472090823</v>
           </cell>
           <cell r="F8">
-            <v>93.637950339797769</v>
+            <v>97.545722643013036</v>
           </cell>
           <cell r="G8">
-            <v>0.51561725334655428</v>
+            <v>0.56447688564476883</v>
           </cell>
           <cell r="H8">
-            <v>67.170909090909092</v>
+            <v>72.41</v>
           </cell>
           <cell r="I8">
-            <v>61.121212121212125</v>
+            <v>64.21875</v>
           </cell>
           <cell r="J8">
-            <v>23.666666666666668</v>
+            <v>23.375</v>
           </cell>
           <cell r="K8">
-            <v>16.030303030303031</v>
+            <v>11.0625</v>
           </cell>
           <cell r="L8">
-            <v>11.666666666666666</v>
+            <v>8.96875</v>
           </cell>
           <cell r="M8">
             <v>0</v>
           </cell>
           <cell r="N8">
-            <v>7.7337055835141966</v>
+            <v>9.7914064574296606</v>
           </cell>
           <cell r="O8">
-            <v>96.443484662576694</v>
+            <v>102.08135263134599</v>
           </cell>
           <cell r="P8">
-            <v>99.09137666807915</v>
+            <v>95.473025683474958</v>
           </cell>
           <cell r="Q8">
-            <v>0.61211129296235678</v>
+            <v>0.56606463878326996</v>
           </cell>
           <cell r="R8">
-            <v>71.92774193548388</v>
+            <v>71.407058823529411</v>
           </cell>
           <cell r="S8">
-            <v>59.12903225806452</v>
+            <v>61.882352941176471</v>
           </cell>
           <cell r="T8">
-            <v>23.516129032258064</v>
+            <v>26.794117647058822</v>
           </cell>
           <cell r="U8">
-            <v>8</v>
+            <v>11.617647058823529</v>
           </cell>
           <cell r="V8">
-            <v>10.451612903225806</v>
+            <v>9.3529411764705888</v>
           </cell>
           <cell r="W8">
             <v>0</v>
           </cell>
           <cell r="X8">
-            <v>-11</v>
+            <v>-11.5</v>
           </cell>
         </row>
         <row r="9">
@@ -9391,73 +9247,73 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>Virginia</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Wright State</v>
+            <v>Texas</v>
           </cell>
           <cell r="D9">
-            <v>12.898930744177012</v>
+            <v>20.959854873623506</v>
           </cell>
           <cell r="E9">
-            <v>102.74660271782574</v>
+            <v>102.65043408841434</v>
           </cell>
           <cell r="F9">
-            <v>105.30602921182151</v>
+            <v>86.043703668873505</v>
           </cell>
           <cell r="G9">
-            <v>0.54717923115327005</v>
+            <v>0.56074766355140182</v>
           </cell>
           <cell r="H9">
-            <v>67.065454545454543</v>
+            <v>69.724999999999994</v>
           </cell>
           <cell r="I9">
-            <v>60.696969696969695</v>
+            <v>63.53125</v>
           </cell>
           <cell r="J9">
-            <v>20.121212121212121</v>
+            <v>19.6875</v>
           </cell>
           <cell r="K9">
-            <v>13.272727272727273</v>
+            <v>12.03125</v>
           </cell>
           <cell r="L9">
-            <v>10.787878787878787</v>
+            <v>9.5625</v>
           </cell>
           <cell r="M9">
             <v>0</v>
           </cell>
           <cell r="N9">
-            <v>3.0807597689023769</v>
+            <v>14.532052109666417</v>
           </cell>
           <cell r="O9">
-            <v>99.432741654503502</v>
+            <v>100.55048907489414</v>
           </cell>
           <cell r="P9">
-            <v>99.184832714478731</v>
+            <v>96.670144874968173</v>
           </cell>
           <cell r="Q9">
-            <v>0.5488476953907816</v>
+            <v>0.5496777658431794</v>
           </cell>
           <cell r="R9">
-            <v>68.45058823529412</v>
+            <v>68.81</v>
           </cell>
           <cell r="S9">
-            <v>58.705882352941174</v>
+            <v>58.1875</v>
           </cell>
           <cell r="T9">
-            <v>22.147058823529413</v>
+            <v>26.34375</v>
           </cell>
           <cell r="U9">
-            <v>11.264705882352942</v>
+            <v>12</v>
           </cell>
           <cell r="V9">
-            <v>11.264705882352942</v>
+            <v>11.03125</v>
           </cell>
           <cell r="W9">
             <v>0</v>
           </cell>
           <cell r="X9">
-            <v>-18</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="10">
@@ -9465,73 +9321,73 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>Miami</v>
+            <v>Alabama</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Missouri</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="D10">
-            <v>12.238890418004498</v>
+            <v>19.673613604820769</v>
           </cell>
           <cell r="E10">
-            <v>100.74202898550723</v>
+            <v>102.29455081001471</v>
           </cell>
           <cell r="F10">
-            <v>98.35968575523485</v>
+            <v>103.71887375881523</v>
           </cell>
           <cell r="G10">
-            <v>0.55597771023302933</v>
+            <v>0.55384250474383301</v>
           </cell>
           <cell r="H10">
-            <v>68.654545454545456</v>
+            <v>74.217500000000001</v>
           </cell>
           <cell r="I10">
-            <v>59.81818181818182</v>
+            <v>65.875</v>
           </cell>
           <cell r="J10">
-            <v>22.424242424242426</v>
+            <v>24.5</v>
           </cell>
           <cell r="K10">
-            <v>12.242424242424242</v>
+            <v>12.21875</v>
           </cell>
           <cell r="L10">
-            <v>11.212121212121213</v>
+            <v>9.78125</v>
           </cell>
           <cell r="M10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N10">
-            <v>11.938625469494365</v>
+            <v>17.052374181699321</v>
           </cell>
           <cell r="O10">
-            <v>98.436590436590436</v>
+            <v>100.51882408229335</v>
           </cell>
           <cell r="P10">
-            <v>95.737468863684654</v>
+            <v>104.30065451536628</v>
           </cell>
           <cell r="Q10">
-            <v>0.55317982456140347</v>
+            <v>0.56166837256908908</v>
           </cell>
           <cell r="R10">
-            <v>68.392499999999998</v>
+            <v>67.617500000000007</v>
           </cell>
           <cell r="S10">
-            <v>57</v>
+            <v>61.0625</v>
           </cell>
           <cell r="T10">
-            <v>24.1875</v>
+            <v>16.53125</v>
           </cell>
           <cell r="U10">
-            <v>11.625</v>
+            <v>11.53125</v>
           </cell>
           <cell r="V10">
-            <v>12.375</v>
+            <v>10.8125</v>
           </cell>
           <cell r="W10">
             <v>0</v>
           </cell>
           <cell r="X10">
-            <v>-2</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="11">
@@ -9539,73 +9395,73 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>Purdue</v>
+            <v>Virginia</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Queens University</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D11">
-            <v>20.933350618351088</v>
+            <v>12.898930744177012</v>
           </cell>
           <cell r="E11">
-            <v>102.749921687376</v>
+            <v>102.74660271782574</v>
           </cell>
           <cell r="F11">
-            <v>101.56518525976452</v>
+            <v>105.30602921182151</v>
           </cell>
           <cell r="G11">
-            <v>0.5771558245083207</v>
+            <v>0.54717923115327005</v>
           </cell>
           <cell r="H11">
-            <v>65.197575757575763</v>
+            <v>67.065454545454543</v>
           </cell>
           <cell r="I11">
-            <v>60.090909090909093</v>
+            <v>60.696969696969695</v>
           </cell>
           <cell r="J11">
-            <v>16.90909090909091</v>
+            <v>20.121212121212121</v>
           </cell>
           <cell r="K11">
-            <v>11.363636363636363</v>
+            <v>13.272727272727273</v>
           </cell>
           <cell r="L11">
-            <v>9.0303030303030312</v>
+            <v>10.787878787878787</v>
           </cell>
           <cell r="M11">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="N11">
-            <v>-2.4386972367557296</v>
+            <v>20.582457175121956</v>
           </cell>
           <cell r="O11">
-            <v>98.853272311212805</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="P11">
-            <v>98.255343754602677</v>
+            <v>93.637950339797769</v>
           </cell>
           <cell r="Q11">
-            <v>0.56723716381418088</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="R11">
-            <v>70.530588235294118</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="S11">
-            <v>60.147058823529413</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="T11">
-            <v>22.529411764705884</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="U11">
-            <v>10.235294117647058</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="V11">
-            <v>10.705882352941176</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="W11">
             <v>0</v>
           </cell>
           <cell r="X11">
-            <v>-25</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="12">
@@ -9613,73 +9469,73 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
+            <v>Iowa State</v>
+          </cell>
+          <cell r="C12" t="str">
             <v>Kentucky</v>
           </cell>
-          <cell r="C12" t="str">
-            <v>Santa Clara</v>
-          </cell>
           <cell r="D12">
+            <v>20.641493911570723</v>
+          </cell>
+          <cell r="E12">
+            <v>101.50134460238188</v>
+          </cell>
+          <cell r="F12">
+            <v>96.951162965358421</v>
+          </cell>
+          <cell r="G12">
+            <v>0.56497313141182215</v>
+          </cell>
+          <cell r="H12">
+            <v>67.654117647058825</v>
+          </cell>
+          <cell r="I12">
+            <v>60.205882352941174</v>
+          </cell>
+          <cell r="J12">
+            <v>20.470588235294116</v>
+          </cell>
+          <cell r="K12">
+            <v>11.823529411764707</v>
+          </cell>
+          <cell r="L12">
+            <v>10.264705882352942</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
             <v>18.034523649586539</v>
           </cell>
-          <cell r="E12">
+          <cell r="O12">
             <v>101.2517590047062</v>
           </cell>
-          <cell r="F12">
+          <cell r="P12">
             <v>98.419793855345077</v>
           </cell>
-          <cell r="G12">
+          <cell r="Q12">
             <v>0.53111327175498302</v>
           </cell>
-          <cell r="H12">
+          <cell r="R12">
             <v>69.036470588235289</v>
           </cell>
-          <cell r="I12">
+          <cell r="S12">
             <v>60.5</v>
           </cell>
-          <cell r="J12">
+          <cell r="T12">
             <v>22.676470588235293</v>
           </cell>
-          <cell r="K12">
+          <cell r="U12">
             <v>11.941176470588236</v>
           </cell>
-          <cell r="L12">
+          <cell r="V12">
             <v>10.5</v>
           </cell>
-          <cell r="M12">
-            <v>3</v>
-          </cell>
-          <cell r="N12">
-            <v>15.7373824689671</v>
-          </cell>
-          <cell r="O12">
-            <v>102.69192816262087</v>
-          </cell>
-          <cell r="P12">
-            <v>86.875904373690886</v>
-          </cell>
-          <cell r="Q12">
-            <v>0.54789719626168221</v>
-          </cell>
-          <cell r="R12">
-            <v>69.654545454545456</v>
-          </cell>
-          <cell r="S12">
-            <v>64.848484848484844</v>
-          </cell>
-          <cell r="T12">
-            <v>16.363636363636363</v>
-          </cell>
-          <cell r="U12">
-            <v>13.090909090909092</v>
-          </cell>
-          <cell r="V12">
-            <v>10.696969696969697</v>
-          </cell>
           <cell r="W12">
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>-3</v>
+            <v>-5</v>
           </cell>
         </row>
         <row r="13">
@@ -9687,73 +9543,73 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>Iowa State</v>
+            <v>Arizona</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Tennessee State</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D13">
-            <v>20.641493911570723</v>
+            <v>23.687310951598352</v>
           </cell>
           <cell r="E13">
-            <v>101.50134460238188</v>
+            <v>101.76807841686704</v>
           </cell>
           <cell r="F13">
-            <v>96.951162965358421</v>
+            <v>98.493332637771204</v>
           </cell>
           <cell r="G13">
-            <v>0.56497313141182215</v>
+            <v>0.55109126984126988</v>
           </cell>
           <cell r="H13">
-            <v>67.654117647058825</v>
+            <v>70.587878787878793</v>
           </cell>
           <cell r="I13">
-            <v>60.205882352941174</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="J13">
-            <v>20.470588235294116</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="K13">
-            <v>11.823529411764707</v>
+            <v>12.878787878787879</v>
           </cell>
           <cell r="L13">
-            <v>10.264705882352942</v>
+            <v>10.909090909090908</v>
           </cell>
           <cell r="M13">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="N13">
-            <v>1.0639361366167945</v>
+            <v>16.287809545840613</v>
           </cell>
           <cell r="O13">
-            <v>100.59318477066054</v>
+            <v>99.539689712306071</v>
           </cell>
           <cell r="P13">
-            <v>92.0991626269942</v>
+            <v>89.1227776403734</v>
           </cell>
           <cell r="Q13">
-            <v>0.50690890481064488</v>
+            <v>0.5741935483870968</v>
           </cell>
           <cell r="R13">
-            <v>71.468387096774194</v>
+            <v>67.972499999999997</v>
           </cell>
           <cell r="S13">
-            <v>63.032258064516128</v>
+            <v>58.125</v>
           </cell>
           <cell r="T13">
-            <v>21.225806451612904</v>
+            <v>22.59375</v>
           </cell>
           <cell r="U13">
-            <v>13.129032258064516</v>
+            <v>10.65625</v>
           </cell>
           <cell r="V13">
-            <v>12.225806451612904</v>
+            <v>10.5625</v>
           </cell>
           <cell r="W13">
             <v>0</v>
           </cell>
           <cell r="X13">
-            <v>-24.5</v>
+            <v>-11.5</v>
           </cell>
         </row>
         <row r="14">
@@ -9761,73 +9617,73 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>St. John's</v>
+            <v>Louisville</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Northern Iowa</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D14">
-            <v>15.123966744544841</v>
+            <v>16.631119331501349</v>
           </cell>
           <cell r="E14">
-            <v>102.62076624097725</v>
+            <v>99.101896527014759</v>
           </cell>
           <cell r="F14">
-            <v>99.067983608660882</v>
+            <v>98.314439245284362</v>
           </cell>
           <cell r="G14">
-            <v>0.50957290132547861</v>
+            <v>0.56448412698412698</v>
           </cell>
           <cell r="H14">
-            <v>70.527272727272731</v>
+            <v>70.393939393939391</v>
           </cell>
           <cell r="I14">
-            <v>61.727272727272727</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="J14">
-            <v>26.060606060606062</v>
+            <v>20.454545454545453</v>
           </cell>
           <cell r="K14">
-            <v>13.242424242424242</v>
+            <v>11.333333333333334</v>
           </cell>
           <cell r="L14">
-            <v>10.575757575757576</v>
+            <v>11.636363636363637</v>
           </cell>
           <cell r="M14">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="N14">
-            <v>9.044790611595948</v>
+            <v>19.982154388171562</v>
           </cell>
           <cell r="O14">
-            <v>96.067511414353874</v>
+            <v>101.32466702184337</v>
           </cell>
           <cell r="P14">
-            <v>96.437852753995415</v>
+            <v>94.579391423053281</v>
           </cell>
           <cell r="Q14">
-            <v>0.54763144195731395</v>
+            <v>0.53589041095890411</v>
           </cell>
           <cell r="R14">
-            <v>63.515428571428572</v>
+            <v>66.620645161290327</v>
           </cell>
           <cell r="S14">
-            <v>54.885714285714286</v>
+            <v>58.87096774193548</v>
           </cell>
           <cell r="T14">
-            <v>14.028571428571428</v>
+            <v>20.838709677419356</v>
           </cell>
           <cell r="U14">
-            <v>6.8571428571428568</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="V14">
-            <v>9.3142857142857149</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="W14">
             <v>0</v>
           </cell>
           <cell r="X14">
-            <v>-10</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="15">
@@ -9835,73 +9691,73 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>Kansas</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="C15" t="str">
-            <v>California Baptist</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D15">
-            <v>16.809475334579385</v>
+            <v>12.891007564287897</v>
           </cell>
           <cell r="E15">
-            <v>98.782531105933685</v>
+            <v>96.587342281204442</v>
           </cell>
           <cell r="F15">
-            <v>105.39233290147665</v>
+            <v>96.419529699076293</v>
           </cell>
           <cell r="G15">
-            <v>0.51565708418891165</v>
+            <v>0.59935205183585316</v>
           </cell>
           <cell r="H15">
-            <v>68.042424242424246</v>
+            <v>71.190967741935481</v>
           </cell>
           <cell r="I15">
-            <v>59.030303030303031</v>
+            <v>59.741935483870968</v>
           </cell>
           <cell r="J15">
-            <v>19.242424242424242</v>
+            <v>20.741935483870968</v>
           </cell>
           <cell r="K15">
-            <v>10.121212121212121</v>
+            <v>10.03225806451613</v>
           </cell>
           <cell r="L15">
-            <v>10.666666666666666</v>
+            <v>12.35483870967742</v>
           </cell>
           <cell r="M15">
-            <v>6</v>
+            <v>0</v>
           </cell>
           <cell r="N15">
-            <v>4.6851123682196496</v>
+            <v>23.158914646956031</v>
           </cell>
           <cell r="O15">
-            <v>101.15808245043532</v>
+            <v>98.200984374253366</v>
           </cell>
           <cell r="P15">
-            <v>89.740557985976295</v>
+            <v>96.383444817292968</v>
           </cell>
           <cell r="Q15">
-            <v>0.48558215451577802</v>
+            <v>0.58467532467532468</v>
           </cell>
           <cell r="R15">
-            <v>67.477419354838716</v>
+            <v>71.510000000000005</v>
           </cell>
           <cell r="S15">
-            <v>59.29032258064516</v>
+            <v>60.15625</v>
           </cell>
           <cell r="T15">
-            <v>21.612903225806452</v>
+            <v>23.53125</v>
           </cell>
           <cell r="U15">
-            <v>13.838709677419354</v>
+            <v>11.0625</v>
           </cell>
           <cell r="V15">
-            <v>12.516129032258064</v>
+            <v>12.0625</v>
           </cell>
           <cell r="W15">
             <v>0</v>
           </cell>
           <cell r="X15">
-            <v>-14</v>
+            <v>12.5</v>
           </cell>
         </row>
         <row r="16">
@@ -9909,73 +9765,73 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>Arizona</v>
+            <v>TCU</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Long Island University</v>
+            <v>Duke</v>
           </cell>
           <cell r="D16">
-            <v>23.687310951598352</v>
+            <v>12.676356416890858</v>
           </cell>
           <cell r="E16">
-            <v>101.76807841686704</v>
+            <v>101.27537334728432</v>
           </cell>
           <cell r="F16">
-            <v>98.493332637771204</v>
+            <v>97.104848064562987</v>
           </cell>
           <cell r="G16">
-            <v>0.55109126984126988</v>
+            <v>0.50900000000000001</v>
           </cell>
           <cell r="H16">
-            <v>70.587878787878793</v>
+            <v>69.441212121212118</v>
           </cell>
           <cell r="I16">
-            <v>61.090909090909093</v>
+            <v>60.606060606060609</v>
           </cell>
           <cell r="J16">
-            <v>26.060606060606062</v>
+            <v>23.454545454545453</v>
           </cell>
           <cell r="K16">
-            <v>12.878787878787879</v>
+            <v>12.424242424242424</v>
           </cell>
           <cell r="L16">
-            <v>10.909090909090908</v>
+            <v>10.939393939393939</v>
           </cell>
           <cell r="M16">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="N16">
-            <v>-5.3079314642110162</v>
+            <v>23.054887624413109</v>
           </cell>
           <cell r="O16">
-            <v>97.176470588235304</v>
+            <v>101.57301127857072</v>
           </cell>
           <cell r="P16">
-            <v>96.766501308175762</v>
+            <v>99.414290660558592</v>
           </cell>
           <cell r="Q16">
-            <v>0.53577106518282991</v>
+            <v>0.57213541666666667</v>
           </cell>
           <cell r="R16">
-            <v>67.672727272727272</v>
+            <v>66.278787878787867</v>
           </cell>
           <cell r="S16">
-            <v>57.18181818181818</v>
+            <v>58.18181818181818</v>
           </cell>
           <cell r="T16">
-            <v>19.848484848484848</v>
+            <v>22.121212121212121</v>
           </cell>
           <cell r="U16">
-            <v>11.303030303030303</v>
+            <v>12.212121212121213</v>
           </cell>
           <cell r="V16">
-            <v>13.060606060606061</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="W16">
             <v>0</v>
           </cell>
           <cell r="X16">
-            <v>-31</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="17">
@@ -9983,73 +9839,73 @@
             <v>16</v>
           </cell>
           <cell r="B17" t="str">
-            <v>Villanova</v>
+            <v>VCU</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Utah State</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D17">
-            <v>11.840993072985095</v>
+            <v>10.280535393881047</v>
           </cell>
           <cell r="E17">
-            <v>101.29752325216845</v>
+            <v>99.976592216912124</v>
           </cell>
           <cell r="F17">
-            <v>98.574654865749267</v>
+            <v>99.94980567668172</v>
           </cell>
           <cell r="G17">
-            <v>0.53713389121338917</v>
+            <v>0.54290339989206693</v>
           </cell>
           <cell r="H17">
-            <v>66.628749999999997</v>
+            <v>68.818749999999994</v>
           </cell>
           <cell r="I17">
-            <v>59.75</v>
+            <v>57.90625</v>
           </cell>
           <cell r="J17">
-            <v>18.6875</v>
+            <v>25.9375</v>
           </cell>
           <cell r="K17">
-            <v>11.5</v>
+            <v>11.3125</v>
           </cell>
           <cell r="L17">
-            <v>10.15625</v>
+            <v>10.8125</v>
           </cell>
           <cell r="M17">
-            <v>8</v>
+            <v>0</v>
           </cell>
           <cell r="N17">
-            <v>16.287809545840613</v>
+            <v>18.826343007871433</v>
           </cell>
           <cell r="O17">
-            <v>99.539689712306071</v>
+            <v>105.08780903665816</v>
           </cell>
           <cell r="P17">
-            <v>89.1227776403734</v>
+            <v>108.91673393133649</v>
           </cell>
           <cell r="Q17">
-            <v>0.5741935483870968</v>
+            <v>0.5511688311688312</v>
           </cell>
           <cell r="R17">
-            <v>67.972499999999997</v>
+            <v>66.809032258064519</v>
           </cell>
           <cell r="S17">
-            <v>58.125</v>
+            <v>62.096774193548384</v>
           </cell>
           <cell r="T17">
-            <v>22.59375</v>
+            <v>20.387096774193548</v>
           </cell>
           <cell r="U17">
-            <v>10.65625</v>
+            <v>13.258064516129032</v>
           </cell>
           <cell r="V17">
-            <v>10.5625</v>
+            <v>9</v>
           </cell>
           <cell r="W17">
             <v>0</v>
           </cell>
           <cell r="X17">
-            <v>2</v>
+            <v>10.5</v>
           </cell>
         </row>
         <row r="18">
@@ -10057,73 +9913,73 @@
             <v>17</v>
           </cell>
           <cell r="B18" t="str">
-            <v>Michigan State</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Louisville</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D18">
-            <v>19.982154388171562</v>
+            <v>19.334095266215517</v>
           </cell>
           <cell r="E18">
-            <v>101.32466702184337</v>
+            <v>100.88210871874095</v>
           </cell>
           <cell r="F18">
-            <v>94.579391423053281</v>
+            <v>97.473801766777243</v>
           </cell>
           <cell r="G18">
-            <v>0.53589041095890411</v>
+            <v>0.55371690427698572</v>
           </cell>
           <cell r="H18">
-            <v>66.620645161290327</v>
+            <v>70.61</v>
           </cell>
           <cell r="I18">
-            <v>58.87096774193548</v>
+            <v>61.375</v>
           </cell>
           <cell r="J18">
-            <v>20.838709677419356</v>
+            <v>23.6875</v>
           </cell>
           <cell r="K18">
-            <v>12.774193548387096</v>
+            <v>10.8125</v>
           </cell>
           <cell r="L18">
-            <v>11.35483870967742</v>
+            <v>9.625</v>
           </cell>
           <cell r="M18">
-            <v>9</v>
+            <v>0</v>
           </cell>
           <cell r="N18">
-            <v>16.631119331501349</v>
+            <v>15.82631796216417</v>
           </cell>
           <cell r="O18">
-            <v>99.101896527014759</v>
+            <v>98.25476089716463</v>
           </cell>
           <cell r="P18">
-            <v>98.314439245284362</v>
+            <v>102.35159180352665</v>
           </cell>
           <cell r="Q18">
-            <v>0.56448412698412698</v>
+            <v>0.55440552016985134</v>
           </cell>
           <cell r="R18">
-            <v>70.393939393939391</v>
+            <v>66.883750000000006</v>
           </cell>
           <cell r="S18">
-            <v>61.090909090909093</v>
+            <v>58.875</v>
           </cell>
           <cell r="T18">
-            <v>20.454545454545453</v>
+            <v>16</v>
           </cell>
           <cell r="U18">
-            <v>11.333333333333334</v>
+            <v>8.78125</v>
           </cell>
           <cell r="V18">
-            <v>11.636363636363637</v>
+            <v>9.75</v>
           </cell>
           <cell r="W18">
             <v>0</v>
           </cell>
           <cell r="X18">
-            <v>-4</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="19">
@@ -10131,73 +9987,73 @@
             <v>18</v>
           </cell>
           <cell r="B19" t="str">
-            <v>Michigan</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Saint Louis</v>
+            <v>Houston</v>
           </cell>
           <cell r="D19">
-            <v>23.158914646956031</v>
+            <v>13.344745551152522</v>
           </cell>
           <cell r="E19">
-            <v>98.200984374253366</v>
+            <v>101.09664255240216</v>
           </cell>
           <cell r="F19">
-            <v>96.383444817292968</v>
+            <v>98.213295342640578</v>
           </cell>
           <cell r="G19">
-            <v>0.58467532467532468</v>
+            <v>0.54188861985472159</v>
           </cell>
           <cell r="H19">
-            <v>71.510000000000005</v>
+            <v>73.739999999999995</v>
           </cell>
           <cell r="I19">
-            <v>60.15625</v>
+            <v>64.53125</v>
           </cell>
           <cell r="J19">
-            <v>23.53125</v>
+            <v>24.125</v>
           </cell>
           <cell r="K19">
-            <v>11.0625</v>
+            <v>12.25</v>
           </cell>
           <cell r="L19">
-            <v>12.0625</v>
+            <v>10.84375</v>
           </cell>
           <cell r="M19">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="N19">
-            <v>12.891007564287897</v>
+            <v>20.901069562815731</v>
           </cell>
           <cell r="O19">
-            <v>96.587342281204442</v>
+            <v>105.43571389837862</v>
           </cell>
           <cell r="P19">
-            <v>96.419529699076293</v>
+            <v>97.084637989347655</v>
           </cell>
           <cell r="Q19">
-            <v>0.59935205183585316</v>
+            <v>0.52154080081094778</v>
           </cell>
           <cell r="R19">
-            <v>71.190967741935481</v>
+            <v>64.762500000000003</v>
           </cell>
           <cell r="S19">
-            <v>59.741935483870968</v>
+            <v>61.65625</v>
           </cell>
           <cell r="T19">
-            <v>20.741935483870968</v>
+            <v>16.71875</v>
           </cell>
           <cell r="U19">
-            <v>10.03225806451613</v>
+            <v>12.78125</v>
           </cell>
           <cell r="V19">
-            <v>12.35483870967742</v>
+            <v>8.53125</v>
           </cell>
           <cell r="W19">
             <v>0</v>
           </cell>
           <cell r="X19">
-            <v>-12.5</v>
+            <v>10.5</v>
           </cell>
         </row>
         <row r="20">
@@ -10205,73 +10061,73 @@
             <v>19</v>
           </cell>
           <cell r="B20" t="str">
-            <v>Duke</v>
+            <v>High Point</v>
           </cell>
           <cell r="C20" t="str">
-            <v>TCU</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D20">
-            <v>23.054887624413109</v>
+            <v>9.7914064574296606</v>
           </cell>
           <cell r="E20">
-            <v>101.57301127857072</v>
+            <v>102.08135263134599</v>
           </cell>
           <cell r="F20">
-            <v>99.414290660558592</v>
+            <v>95.473025683474958</v>
           </cell>
           <cell r="G20">
-            <v>0.57213541666666667</v>
+            <v>0.56606463878326996</v>
           </cell>
           <cell r="H20">
-            <v>66.278787878787867</v>
+            <v>71.407058823529411</v>
           </cell>
           <cell r="I20">
-            <v>58.18181818181818</v>
+            <v>61.882352941176471</v>
           </cell>
           <cell r="J20">
-            <v>22.121212121212121</v>
+            <v>26.794117647058822</v>
           </cell>
           <cell r="K20">
-            <v>12.212121212121213</v>
+            <v>11.617647058823529</v>
           </cell>
           <cell r="L20">
-            <v>10.575757575757576</v>
+            <v>9.3529411764705888</v>
           </cell>
           <cell r="M20">
-            <v>11</v>
+            <v>0</v>
           </cell>
           <cell r="N20">
-            <v>12.676356416890858</v>
+            <v>19.899076876872613</v>
           </cell>
           <cell r="O20">
-            <v>101.27537334728432</v>
+            <v>101.9693472090823</v>
           </cell>
           <cell r="P20">
-            <v>97.104848064562987</v>
+            <v>97.545722643013036</v>
           </cell>
           <cell r="Q20">
-            <v>0.50900000000000001</v>
+            <v>0.56447688564476883</v>
           </cell>
           <cell r="R20">
-            <v>69.441212121212118</v>
+            <v>72.41</v>
           </cell>
           <cell r="S20">
-            <v>60.606060606060609</v>
+            <v>64.21875</v>
           </cell>
           <cell r="T20">
-            <v>23.454545454545453</v>
+            <v>23.375</v>
           </cell>
           <cell r="U20">
-            <v>12.424242424242424</v>
+            <v>11.0625</v>
           </cell>
           <cell r="V20">
-            <v>10.939393939393939</v>
+            <v>8.96875</v>
           </cell>
           <cell r="W20">
             <v>0</v>
           </cell>
           <cell r="X20">
-            <v>-11</v>
+            <v>11.5</v>
           </cell>
         </row>
         <row r="21">
@@ -10279,73 +10135,73 @@
             <v>20</v>
           </cell>
           <cell r="B21" t="str">
-            <v>Illinois</v>
+            <v>Texas</v>
           </cell>
           <cell r="C21" t="str">
-            <v>VCU</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="D21">
-            <v>18.826343007871433</v>
+            <v>14.532052109666417</v>
           </cell>
           <cell r="E21">
-            <v>105.08780903665816</v>
+            <v>100.55048907489414</v>
           </cell>
           <cell r="F21">
-            <v>108.91673393133649</v>
+            <v>96.670144874968173</v>
           </cell>
           <cell r="G21">
-            <v>0.5511688311688312</v>
+            <v>0.5496777658431794</v>
           </cell>
           <cell r="H21">
-            <v>66.809032258064519</v>
+            <v>68.81</v>
           </cell>
           <cell r="I21">
-            <v>62.096774193548384</v>
+            <v>58.1875</v>
           </cell>
           <cell r="J21">
-            <v>20.387096774193548</v>
+            <v>26.34375</v>
           </cell>
           <cell r="K21">
-            <v>13.258064516129032</v>
+            <v>12</v>
           </cell>
           <cell r="L21">
-            <v>9</v>
+            <v>11.03125</v>
           </cell>
           <cell r="M21">
-            <v>12</v>
+            <v>0</v>
           </cell>
           <cell r="N21">
-            <v>10.280535393881047</v>
+            <v>20.959854873623506</v>
           </cell>
           <cell r="O21">
-            <v>99.976592216912124</v>
+            <v>102.65043408841434</v>
           </cell>
           <cell r="P21">
-            <v>99.94980567668172</v>
+            <v>86.043703668873505</v>
           </cell>
           <cell r="Q21">
-            <v>0.54290339989206693</v>
+            <v>0.56074766355140182</v>
           </cell>
           <cell r="R21">
-            <v>68.818749999999994</v>
+            <v>69.724999999999994</v>
           </cell>
           <cell r="S21">
-            <v>57.90625</v>
+            <v>63.53125</v>
           </cell>
           <cell r="T21">
-            <v>25.9375</v>
+            <v>19.6875</v>
           </cell>
           <cell r="U21">
-            <v>11.3125</v>
+            <v>12.03125</v>
           </cell>
           <cell r="V21">
-            <v>10.8125</v>
+            <v>9.5625</v>
           </cell>
           <cell r="W21">
             <v>0</v>
           </cell>
           <cell r="X21">
-            <v>-10.5</v>
+            <v>6.5</v>
           </cell>
         </row>
         <row r="22">
@@ -10353,73 +10209,73 @@
             <v>21</v>
           </cell>
           <cell r="B22" t="str">
-            <v>Nebraska</v>
+            <v>Texas Tech</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Vanderbilt</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D22">
-            <v>15.82631796216417</v>
+            <v>17.052374181699321</v>
           </cell>
           <cell r="E22">
-            <v>98.25476089716463</v>
+            <v>100.51882408229335</v>
           </cell>
           <cell r="F22">
-            <v>102.35159180352665</v>
+            <v>104.30065451536628</v>
           </cell>
           <cell r="G22">
-            <v>0.55440552016985134</v>
+            <v>0.56166837256908908</v>
           </cell>
           <cell r="H22">
-            <v>66.883750000000006</v>
+            <v>67.617500000000007</v>
           </cell>
           <cell r="I22">
-            <v>58.875</v>
+            <v>61.0625</v>
           </cell>
           <cell r="J22">
-            <v>16</v>
+            <v>16.53125</v>
           </cell>
           <cell r="K22">
-            <v>8.78125</v>
+            <v>11.53125</v>
           </cell>
           <cell r="L22">
-            <v>9.75</v>
+            <v>10.8125</v>
           </cell>
           <cell r="M22">
-            <v>13</v>
+            <v>0</v>
           </cell>
           <cell r="N22">
-            <v>19.334095266215517</v>
+            <v>19.673613604820769</v>
           </cell>
           <cell r="O22">
-            <v>100.88210871874095</v>
+            <v>102.29455081001471</v>
           </cell>
           <cell r="P22">
-            <v>97.473801766777243</v>
+            <v>103.71887375881523</v>
           </cell>
           <cell r="Q22">
-            <v>0.55371690427698572</v>
+            <v>0.55384250474383301</v>
           </cell>
           <cell r="R22">
-            <v>70.61</v>
+            <v>74.217500000000001</v>
           </cell>
           <cell r="S22">
-            <v>61.375</v>
+            <v>65.875</v>
           </cell>
           <cell r="T22">
-            <v>23.6875</v>
+            <v>24.5</v>
           </cell>
           <cell r="U22">
-            <v>10.8125</v>
+            <v>12.21875</v>
           </cell>
           <cell r="V22">
-            <v>9.625</v>
+            <v>9.78125</v>
           </cell>
           <cell r="W22">
             <v>0</v>
           </cell>
           <cell r="X22">
-            <v>2.5</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="23">
@@ -10427,73 +10283,73 @@
             <v>22</v>
           </cell>
           <cell r="B23" t="str">
-            <v>Houston</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="C23" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D23">
-            <v>20.901069562815731</v>
+            <v>20.582457175121956</v>
           </cell>
           <cell r="E23">
-            <v>105.43571389837862</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="F23">
-            <v>97.084637989347655</v>
+            <v>93.637950339797769</v>
           </cell>
           <cell r="G23">
-            <v>0.52154080081094778</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="H23">
-            <v>64.762500000000003</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="I23">
-            <v>61.65625</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="J23">
-            <v>16.71875</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="K23">
-            <v>12.78125</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="L23">
-            <v>8.53125</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="M23">
-            <v>14</v>
+            <v>0</v>
           </cell>
           <cell r="N23">
-            <v>13.344745551152522</v>
+            <v>12.898930744177012</v>
           </cell>
           <cell r="O23">
-            <v>101.09664255240216</v>
+            <v>102.74660271782574</v>
           </cell>
           <cell r="P23">
-            <v>98.213295342640578</v>
+            <v>105.30602921182151</v>
           </cell>
           <cell r="Q23">
-            <v>0.54188861985472159</v>
+            <v>0.54717923115327005</v>
           </cell>
           <cell r="R23">
-            <v>73.739999999999995</v>
+            <v>67.065454545454543</v>
           </cell>
           <cell r="S23">
-            <v>64.53125</v>
+            <v>60.696969696969695</v>
           </cell>
           <cell r="T23">
-            <v>24.125</v>
+            <v>20.121212121212121</v>
           </cell>
           <cell r="U23">
-            <v>12.25</v>
+            <v>13.272727272727273</v>
           </cell>
           <cell r="V23">
-            <v>10.84375</v>
+            <v>10.787878787878787</v>
           </cell>
           <cell r="W23">
             <v>0</v>
           </cell>
           <cell r="X23">
-            <v>-10</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="24">
@@ -10501,73 +10357,73 @@
             <v>23</v>
           </cell>
           <cell r="B24" t="str">
-            <v>Arkansas</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="C24" t="str">
-            <v>High Point</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D24">
-            <v>19.899076876872613</v>
+            <v>18.034523649586539</v>
           </cell>
           <cell r="E24">
-            <v>101.9693472090823</v>
+            <v>101.2517590047062</v>
           </cell>
           <cell r="F24">
-            <v>97.545722643013036</v>
+            <v>98.419793855345077</v>
           </cell>
           <cell r="G24">
-            <v>0.56447688564476883</v>
+            <v>0.53111327175498302</v>
           </cell>
           <cell r="H24">
-            <v>72.41</v>
+            <v>69.036470588235289</v>
           </cell>
           <cell r="I24">
-            <v>64.21875</v>
+            <v>60.5</v>
           </cell>
           <cell r="J24">
-            <v>23.375</v>
+            <v>22.676470588235293</v>
           </cell>
           <cell r="K24">
-            <v>11.0625</v>
+            <v>11.941176470588236</v>
           </cell>
           <cell r="L24">
-            <v>8.96875</v>
+            <v>10.5</v>
           </cell>
           <cell r="M24">
-            <v>15</v>
+            <v>0</v>
           </cell>
           <cell r="N24">
-            <v>9.7914064574296606</v>
+            <v>20.641493911570723</v>
           </cell>
           <cell r="O24">
-            <v>102.08135263134599</v>
+            <v>101.50134460238188</v>
           </cell>
           <cell r="P24">
-            <v>95.473025683474958</v>
+            <v>96.951162965358421</v>
           </cell>
           <cell r="Q24">
-            <v>0.56606463878326996</v>
+            <v>0.56497313141182215</v>
           </cell>
           <cell r="R24">
-            <v>71.407058823529411</v>
+            <v>67.654117647058825</v>
           </cell>
           <cell r="S24">
-            <v>61.882352941176471</v>
+            <v>60.205882352941174</v>
           </cell>
           <cell r="T24">
-            <v>26.794117647058822</v>
+            <v>20.470588235294116</v>
           </cell>
           <cell r="U24">
-            <v>11.617647058823529</v>
+            <v>11.823529411764707</v>
           </cell>
           <cell r="V24">
-            <v>9.3529411764705888</v>
+            <v>10.264705882352942</v>
           </cell>
           <cell r="W24">
             <v>0</v>
           </cell>
           <cell r="X24">
-            <v>-11</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="25">
@@ -10575,1850 +10431,626 @@
             <v>24</v>
           </cell>
           <cell r="B25" t="str">
-            <v>Gonzaga</v>
+            <v>Utah State</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Texas</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D25">
-            <v>20.959854873623506</v>
+            <v>16.287809545840613</v>
           </cell>
           <cell r="E25">
-            <v>102.65043408841434</v>
+            <v>99.539689712306071</v>
           </cell>
           <cell r="F25">
-            <v>86.043703668873505</v>
+            <v>89.1227776403734</v>
           </cell>
           <cell r="G25">
-            <v>0.56074766355140182</v>
+            <v>0.5741935483870968</v>
           </cell>
           <cell r="H25">
-            <v>69.724999999999994</v>
+            <v>67.972499999999997</v>
           </cell>
           <cell r="I25">
-            <v>63.53125</v>
+            <v>58.125</v>
           </cell>
           <cell r="J25">
-            <v>19.6875</v>
+            <v>22.59375</v>
           </cell>
           <cell r="K25">
-            <v>12.03125</v>
+            <v>10.65625</v>
           </cell>
           <cell r="L25">
-            <v>9.5625</v>
+            <v>10.5625</v>
           </cell>
           <cell r="M25">
-            <v>16</v>
+            <v>0</v>
           </cell>
           <cell r="N25">
-            <v>14.532052109666417</v>
+            <v>23.687310951598352</v>
           </cell>
           <cell r="O25">
-            <v>100.55048907489414</v>
+            <v>101.76807841686704</v>
           </cell>
           <cell r="P25">
-            <v>96.670144874968173</v>
+            <v>98.493332637771204</v>
           </cell>
           <cell r="Q25">
-            <v>0.5496777658431794</v>
+            <v>0.55109126984126988</v>
           </cell>
           <cell r="R25">
-            <v>68.81</v>
+            <v>70.587878787878793</v>
           </cell>
           <cell r="S25">
-            <v>58.1875</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="T25">
-            <v>26.34375</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="U25">
-            <v>12</v>
+            <v>12.878787878787879</v>
           </cell>
           <cell r="V25">
-            <v>11.03125</v>
+            <v>10.909090909090908</v>
           </cell>
           <cell r="W25">
             <v>0</v>
           </cell>
           <cell r="X25">
-            <v>-5.5</v>
+            <v>11.5</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="A26">
-            <v>25</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>Akron</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>Texas Tech</v>
-          </cell>
-          <cell r="D26">
-            <v>10.62898797126984</v>
-          </cell>
-          <cell r="E26">
-            <v>99.852760736196316</v>
-          </cell>
-          <cell r="F26">
-            <v>94.235250093919447</v>
-          </cell>
-          <cell r="G26">
-            <v>0.58984747378455671</v>
-          </cell>
-          <cell r="H26">
-            <v>71.226666666666659</v>
-          </cell>
-          <cell r="I26">
-            <v>63.575757575757578</v>
-          </cell>
-          <cell r="J26">
-            <v>17.939393939393938</v>
-          </cell>
-          <cell r="K26">
-            <v>11.272727272727273</v>
-          </cell>
-          <cell r="L26">
-            <v>11.030303030303031</v>
-          </cell>
-          <cell r="M26">
-            <v>17</v>
-          </cell>
-          <cell r="N26">
-            <v>17.052374181699321</v>
-          </cell>
-          <cell r="O26">
-            <v>100.51882408229335</v>
-          </cell>
-          <cell r="P26">
-            <v>104.30065451536628</v>
-          </cell>
-          <cell r="Q26">
-            <v>0.56166837256908908</v>
-          </cell>
-          <cell r="R26">
-            <v>67.617500000000007</v>
-          </cell>
-          <cell r="S26">
-            <v>61.0625</v>
-          </cell>
-          <cell r="T26">
-            <v>16.53125</v>
-          </cell>
-          <cell r="U26">
-            <v>11.53125</v>
-          </cell>
-          <cell r="V26">
-            <v>10.8125</v>
-          </cell>
-          <cell r="W26">
-            <v>0</v>
-          </cell>
-          <cell r="X26">
-            <v>7.5</v>
-          </cell>
+          <cell r="D26"/>
+          <cell r="E26"/>
+          <cell r="F26"/>
+          <cell r="G26"/>
+          <cell r="H26"/>
+          <cell r="I26"/>
+          <cell r="J26"/>
+          <cell r="K26"/>
+          <cell r="L26"/>
+          <cell r="M26"/>
+          <cell r="N26"/>
+          <cell r="O26"/>
+          <cell r="P26"/>
+          <cell r="Q26"/>
+          <cell r="R26"/>
+          <cell r="S26"/>
+          <cell r="T26"/>
+          <cell r="U26"/>
+          <cell r="V26"/>
+          <cell r="W26"/>
+          <cell r="X26"/>
         </row>
         <row r="27">
-          <cell r="A27">
-            <v>26</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>Hofstra</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>Alabama</v>
-          </cell>
-          <cell r="D27">
-            <v>2.1356002741910172</v>
-          </cell>
-          <cell r="E27">
-            <v>101.93227153239523</v>
-          </cell>
-          <cell r="F27">
-            <v>108.25319811541539</v>
-          </cell>
-          <cell r="G27">
-            <v>0.52252944188428063</v>
-          </cell>
-          <cell r="H27">
-            <v>65.487272727272725</v>
-          </cell>
-          <cell r="I27">
-            <v>59.18181818181818</v>
-          </cell>
-          <cell r="J27">
-            <v>18.393939393939394</v>
-          </cell>
-          <cell r="K27">
-            <v>12.484848484848484</v>
-          </cell>
-          <cell r="L27">
-            <v>10.696969696969697</v>
-          </cell>
-          <cell r="M27">
-            <v>18</v>
-          </cell>
-          <cell r="N27">
-            <v>19.673613604820769</v>
-          </cell>
-          <cell r="O27">
-            <v>102.29455081001471</v>
-          </cell>
-          <cell r="P27">
-            <v>103.71887375881523</v>
-          </cell>
-          <cell r="Q27">
-            <v>0.55384250474383301</v>
-          </cell>
-          <cell r="R27">
-            <v>74.217500000000001</v>
-          </cell>
-          <cell r="S27">
-            <v>65.875</v>
-          </cell>
-          <cell r="T27">
-            <v>24.5</v>
-          </cell>
-          <cell r="U27">
-            <v>12.21875</v>
-          </cell>
-          <cell r="V27">
-            <v>9.78125</v>
-          </cell>
-          <cell r="W27">
-            <v>0</v>
-          </cell>
-          <cell r="X27">
-            <v>14</v>
-          </cell>
+          <cell r="D27"/>
+          <cell r="E27"/>
+          <cell r="F27"/>
+          <cell r="G27"/>
+          <cell r="H27"/>
+          <cell r="I27"/>
+          <cell r="J27"/>
+          <cell r="K27"/>
+          <cell r="L27"/>
+          <cell r="M27"/>
+          <cell r="N27"/>
+          <cell r="O27"/>
+          <cell r="P27"/>
+          <cell r="Q27"/>
+          <cell r="R27"/>
+          <cell r="S27"/>
+          <cell r="T27"/>
+          <cell r="U27"/>
+          <cell r="V27"/>
+          <cell r="W27"/>
+          <cell r="X27"/>
         </row>
         <row r="28">
-          <cell r="A28">
-            <v>27</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Prairie View A&amp;M</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>Florida</v>
-          </cell>
-          <cell r="D28">
-            <v>-11.471425536201773</v>
-          </cell>
-          <cell r="E28">
-            <v>97.164732374848427</v>
-          </cell>
-          <cell r="F28">
-            <v>95.447708530170132</v>
-          </cell>
-          <cell r="G28">
-            <v>0.49387855044074436</v>
-          </cell>
-          <cell r="H28">
-            <v>73.484705882352941</v>
-          </cell>
-          <cell r="I28">
-            <v>60.058823529411768</v>
-          </cell>
-          <cell r="J28">
-            <v>26.235294117647058</v>
-          </cell>
-          <cell r="K28">
-            <v>10.058823529411764</v>
-          </cell>
-          <cell r="L28">
-            <v>11.941176470588236</v>
-          </cell>
-          <cell r="M28">
-            <v>19</v>
-          </cell>
-          <cell r="N28">
-            <v>22.650454216704585</v>
-          </cell>
-          <cell r="O28">
-            <v>104.38676700269771</v>
-          </cell>
-          <cell r="P28">
-            <v>99.448258680413886</v>
-          </cell>
-          <cell r="Q28">
-            <v>0.53652636671504594</v>
-          </cell>
-          <cell r="R28">
-            <v>71.564999999999998</v>
-          </cell>
-          <cell r="S28">
-            <v>64.59375</v>
-          </cell>
-          <cell r="T28">
-            <v>25.21875</v>
-          </cell>
-          <cell r="U28">
-            <v>15.96875</v>
-          </cell>
-          <cell r="V28">
-            <v>11.84375</v>
-          </cell>
-          <cell r="W28">
-            <v>0</v>
-          </cell>
-          <cell r="X28">
-            <v>35</v>
-          </cell>
+          <cell r="D28"/>
+          <cell r="E28"/>
+          <cell r="F28"/>
+          <cell r="G28"/>
+          <cell r="H28"/>
+          <cell r="I28"/>
+          <cell r="J28"/>
+          <cell r="K28"/>
+          <cell r="L28"/>
+          <cell r="M28"/>
+          <cell r="N28"/>
+          <cell r="O28"/>
+          <cell r="P28"/>
+          <cell r="Q28"/>
+          <cell r="R28"/>
+          <cell r="S28"/>
+          <cell r="T28"/>
+          <cell r="U28"/>
+          <cell r="V28"/>
+          <cell r="W28"/>
+          <cell r="X28"/>
         </row>
         <row r="29">
-          <cell r="A29">
-            <v>28</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Iowa</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>Clemson</v>
-          </cell>
-          <cell r="D29">
-            <v>15.51511812576733</v>
-          </cell>
-          <cell r="E29">
-            <v>98.238539943433466</v>
-          </cell>
-          <cell r="F29">
-            <v>93.168875634820807</v>
-          </cell>
-          <cell r="G29">
-            <v>0.56555993247045577</v>
-          </cell>
-          <cell r="H29">
-            <v>62.900606060606066</v>
-          </cell>
-          <cell r="I29">
-            <v>53.848484848484851</v>
-          </cell>
-          <cell r="J29">
-            <v>18.575757575757574</v>
-          </cell>
-          <cell r="K29">
-            <v>8.8181818181818183</v>
-          </cell>
-          <cell r="L29">
-            <v>9.6969696969696972</v>
-          </cell>
-          <cell r="M29">
-            <v>20</v>
-          </cell>
-          <cell r="N29">
-            <v>11.025556023298106</v>
-          </cell>
-          <cell r="O29">
-            <v>99.36088590073166</v>
-          </cell>
-          <cell r="P29">
-            <v>103.15195066761017</v>
-          </cell>
-          <cell r="Q29">
-            <v>0.52621919244887261</v>
-          </cell>
-          <cell r="R29">
-            <v>65.309411764705885</v>
-          </cell>
-          <cell r="S29">
-            <v>56.088235294117645</v>
-          </cell>
-          <cell r="T29">
-            <v>20.823529411764707</v>
-          </cell>
-          <cell r="U29">
-            <v>9.3235294117647065</v>
-          </cell>
-          <cell r="V29">
-            <v>9.382352941176471</v>
-          </cell>
-          <cell r="W29">
-            <v>0</v>
-          </cell>
-          <cell r="X29">
-            <v>-2</v>
-          </cell>
+          <cell r="D29"/>
+          <cell r="E29"/>
+          <cell r="F29"/>
+          <cell r="G29"/>
+          <cell r="H29"/>
+          <cell r="I29"/>
+          <cell r="J29"/>
+          <cell r="K29"/>
+          <cell r="L29"/>
+          <cell r="M29"/>
+          <cell r="N29"/>
+          <cell r="O29"/>
+          <cell r="P29"/>
+          <cell r="Q29"/>
+          <cell r="R29"/>
+          <cell r="S29"/>
+          <cell r="T29"/>
+          <cell r="U29"/>
+          <cell r="V29"/>
+          <cell r="W29"/>
+          <cell r="X29"/>
         </row>
         <row r="30">
-          <cell r="A30">
-            <v>29</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>UCF</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>UCLA</v>
-          </cell>
-          <cell r="D30">
-            <v>12.780422052740661</v>
-          </cell>
-          <cell r="E30">
-            <v>101.06601066010661</v>
-          </cell>
-          <cell r="F30">
-            <v>97.015666781333081</v>
-          </cell>
-          <cell r="G30">
-            <v>0.52792008196721307</v>
-          </cell>
-          <cell r="H30">
-            <v>70.258064516129025</v>
-          </cell>
-          <cell r="I30">
-            <v>62.967741935483872</v>
-          </cell>
-          <cell r="J30">
-            <v>19.35483870967742</v>
-          </cell>
-          <cell r="K30">
-            <v>12.387096774193548</v>
-          </cell>
-          <cell r="L30">
-            <v>11.161290322580646</v>
-          </cell>
-          <cell r="M30">
-            <v>21</v>
-          </cell>
-          <cell r="N30">
-            <v>15.943406980069799</v>
-          </cell>
-          <cell r="O30">
-            <v>100.85863980873899</v>
-          </cell>
-          <cell r="P30">
-            <v>91.898292422931632</v>
-          </cell>
-          <cell r="Q30">
-            <v>0.54047742605085625</v>
-          </cell>
-          <cell r="R30">
-            <v>65.963636363636368</v>
-          </cell>
-          <cell r="S30">
-            <v>58.393939393939391</v>
-          </cell>
-          <cell r="T30">
-            <v>19.545454545454547</v>
-          </cell>
-          <cell r="U30">
-            <v>10</v>
-          </cell>
-          <cell r="V30">
-            <v>8.9696969696969688</v>
-          </cell>
-          <cell r="W30">
-            <v>0</v>
-          </cell>
-          <cell r="X30">
-            <v>5.5</v>
-          </cell>
+          <cell r="D30"/>
+          <cell r="E30"/>
+          <cell r="F30"/>
+          <cell r="G30"/>
+          <cell r="H30"/>
+          <cell r="I30"/>
+          <cell r="J30"/>
+          <cell r="K30"/>
+          <cell r="L30"/>
+          <cell r="M30"/>
+          <cell r="N30"/>
+          <cell r="O30"/>
+          <cell r="P30"/>
+          <cell r="Q30"/>
+          <cell r="R30"/>
+          <cell r="S30"/>
+          <cell r="T30"/>
+          <cell r="U30"/>
+          <cell r="V30"/>
+          <cell r="W30"/>
+          <cell r="X30"/>
         </row>
         <row r="31">
-          <cell r="A31">
-            <v>30</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>Furman</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>Uconn</v>
-          </cell>
-          <cell r="D31">
-            <v>0.19358290778345913</v>
-          </cell>
-          <cell r="E31">
-            <v>98.095219377978665</v>
-          </cell>
-          <cell r="F31">
-            <v>107.97637861090803</v>
-          </cell>
-          <cell r="G31">
-            <v>0.5527254202750892</v>
-          </cell>
-          <cell r="H31">
-            <v>66.856470588235297</v>
-          </cell>
-          <cell r="I31">
-            <v>57.735294117647058</v>
-          </cell>
-          <cell r="J31">
-            <v>18.323529411764707</v>
-          </cell>
-          <cell r="K31">
-            <v>10.882352941176471</v>
-          </cell>
-          <cell r="L31">
-            <v>11.941176470588236</v>
-          </cell>
-          <cell r="M31">
-            <v>22</v>
-          </cell>
-          <cell r="N31">
-            <v>18.120431537245491</v>
-          </cell>
-          <cell r="O31">
-            <v>100.0952772073922</v>
-          </cell>
-          <cell r="P31">
-            <v>94.261774983054991</v>
-          </cell>
-          <cell r="Q31">
-            <v>0.55882352941176472</v>
-          </cell>
-          <cell r="R31">
-            <v>66.089696969696973</v>
-          </cell>
-          <cell r="S31">
-            <v>58.727272727272727</v>
-          </cell>
-          <cell r="T31">
-            <v>17.696969696969695</v>
-          </cell>
-          <cell r="U31">
-            <v>11.454545454545455</v>
-          </cell>
-          <cell r="V31">
-            <v>11.030303030303031</v>
-          </cell>
-          <cell r="W31">
-            <v>0</v>
-          </cell>
-          <cell r="X31">
-            <v>20.5</v>
-          </cell>
+          <cell r="D31"/>
+          <cell r="E31"/>
+          <cell r="F31"/>
+          <cell r="G31"/>
+          <cell r="H31"/>
+          <cell r="I31"/>
+          <cell r="J31"/>
+          <cell r="K31"/>
+          <cell r="L31"/>
+          <cell r="M31"/>
+          <cell r="N31"/>
+          <cell r="O31"/>
+          <cell r="P31"/>
+          <cell r="Q31"/>
+          <cell r="R31"/>
+          <cell r="S31"/>
+          <cell r="T31"/>
+          <cell r="U31"/>
+          <cell r="V31"/>
+          <cell r="W31"/>
+          <cell r="X31"/>
         </row>
         <row r="32">
-          <cell r="A32">
-            <v>31</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>Miami (OH)</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>Tennessee</v>
-          </cell>
-          <cell r="D32">
-            <v>7.7337055835141966</v>
-          </cell>
-          <cell r="E32">
-            <v>96.443484662576694</v>
-          </cell>
-          <cell r="F32">
-            <v>99.09137666807915</v>
-          </cell>
-          <cell r="G32">
-            <v>0.61211129296235678</v>
-          </cell>
-          <cell r="H32">
-            <v>71.92774193548388</v>
-          </cell>
-          <cell r="I32">
-            <v>59.12903225806452</v>
-          </cell>
-          <cell r="J32">
-            <v>23.516129032258064</v>
-          </cell>
-          <cell r="K32">
-            <v>8</v>
-          </cell>
-          <cell r="L32">
-            <v>10.451612903225806</v>
-          </cell>
-          <cell r="M32">
-            <v>23</v>
-          </cell>
-          <cell r="N32">
-            <v>20.582457175121956</v>
-          </cell>
-          <cell r="O32">
-            <v>105.02195491662999</v>
-          </cell>
-          <cell r="P32">
-            <v>93.637950339797769</v>
-          </cell>
-          <cell r="Q32">
-            <v>0.51561725334655428</v>
-          </cell>
-          <cell r="R32">
-            <v>67.170909090909092</v>
-          </cell>
-          <cell r="S32">
-            <v>61.121212121212125</v>
-          </cell>
-          <cell r="T32">
-            <v>23.666666666666668</v>
-          </cell>
-          <cell r="U32">
-            <v>16.030303030303031</v>
-          </cell>
-          <cell r="V32">
-            <v>11.666666666666666</v>
-          </cell>
-          <cell r="W32">
-            <v>0</v>
-          </cell>
-          <cell r="X32">
-            <v>11</v>
-          </cell>
+          <cell r="D32"/>
+          <cell r="E32"/>
+          <cell r="F32"/>
+          <cell r="G32"/>
+          <cell r="H32"/>
+          <cell r="I32"/>
+          <cell r="J32"/>
+          <cell r="K32"/>
+          <cell r="L32"/>
+          <cell r="M32"/>
+          <cell r="N32"/>
+          <cell r="O32"/>
+          <cell r="P32"/>
+          <cell r="Q32"/>
+          <cell r="R32"/>
+          <cell r="S32"/>
+          <cell r="T32"/>
+          <cell r="U32"/>
+          <cell r="V32"/>
+          <cell r="W32"/>
+          <cell r="X32"/>
         </row>
         <row r="33">
-          <cell r="A33">
-            <v>32</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>Wright State</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>Virginia</v>
-          </cell>
-          <cell r="D33">
-            <v>3.0807597689023769</v>
-          </cell>
-          <cell r="E33">
-            <v>99.432741654503502</v>
-          </cell>
-          <cell r="F33">
-            <v>99.184832714478731</v>
-          </cell>
-          <cell r="G33">
-            <v>0.5488476953907816</v>
-          </cell>
-          <cell r="H33">
-            <v>68.45058823529412</v>
-          </cell>
-          <cell r="I33">
-            <v>58.705882352941174</v>
-          </cell>
-          <cell r="J33">
-            <v>22.147058823529413</v>
-          </cell>
-          <cell r="K33">
-            <v>11.264705882352942</v>
-          </cell>
-          <cell r="L33">
-            <v>11.264705882352942</v>
-          </cell>
-          <cell r="M33">
-            <v>24</v>
-          </cell>
-          <cell r="N33">
-            <v>12.898930744177012</v>
-          </cell>
-          <cell r="O33">
-            <v>102.74660271782574</v>
-          </cell>
-          <cell r="P33">
-            <v>105.30602921182151</v>
-          </cell>
-          <cell r="Q33">
-            <v>0.54717923115327005</v>
-          </cell>
-          <cell r="R33">
-            <v>67.065454545454543</v>
-          </cell>
-          <cell r="S33">
-            <v>60.696969696969695</v>
-          </cell>
-          <cell r="T33">
-            <v>20.121212121212121</v>
-          </cell>
-          <cell r="U33">
-            <v>13.272727272727273</v>
-          </cell>
-          <cell r="V33">
-            <v>10.787878787878787</v>
-          </cell>
-          <cell r="W33">
-            <v>0</v>
-          </cell>
-          <cell r="X33">
-            <v>18</v>
-          </cell>
+          <cell r="D33"/>
+          <cell r="E33"/>
+          <cell r="F33"/>
+          <cell r="G33"/>
+          <cell r="H33"/>
+          <cell r="I33"/>
+          <cell r="J33"/>
+          <cell r="K33"/>
+          <cell r="L33"/>
+          <cell r="M33"/>
+          <cell r="N33"/>
+          <cell r="O33"/>
+          <cell r="P33"/>
+          <cell r="Q33"/>
+          <cell r="R33"/>
+          <cell r="S33"/>
+          <cell r="T33"/>
+          <cell r="U33"/>
+          <cell r="V33"/>
+          <cell r="W33"/>
+          <cell r="X33"/>
         </row>
         <row r="34">
-          <cell r="A34">
-            <v>33</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>Missouri</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>Miami</v>
-          </cell>
-          <cell r="D34">
-            <v>11.938625469494365</v>
-          </cell>
-          <cell r="E34">
-            <v>98.436590436590436</v>
-          </cell>
-          <cell r="F34">
-            <v>95.737468863684654</v>
-          </cell>
-          <cell r="G34">
-            <v>0.55317982456140347</v>
-          </cell>
-          <cell r="H34">
-            <v>68.392499999999998</v>
-          </cell>
-          <cell r="I34">
-            <v>57</v>
-          </cell>
-          <cell r="J34">
-            <v>24.1875</v>
-          </cell>
-          <cell r="K34">
-            <v>11.625</v>
-          </cell>
-          <cell r="L34">
-            <v>12.375</v>
-          </cell>
-          <cell r="M34">
-            <v>25</v>
-          </cell>
-          <cell r="N34">
-            <v>12.238890418004498</v>
-          </cell>
-          <cell r="O34">
-            <v>100.74202898550723</v>
-          </cell>
-          <cell r="P34">
-            <v>98.35968575523485</v>
-          </cell>
-          <cell r="Q34">
-            <v>0.55597771023302933</v>
-          </cell>
-          <cell r="R34">
-            <v>68.654545454545456</v>
-          </cell>
-          <cell r="S34">
-            <v>59.81818181818182</v>
-          </cell>
-          <cell r="T34">
-            <v>22.424242424242426</v>
-          </cell>
-          <cell r="U34">
-            <v>12.242424242424242</v>
-          </cell>
-          <cell r="V34">
-            <v>11.212121212121213</v>
-          </cell>
-          <cell r="W34">
-            <v>0</v>
-          </cell>
-          <cell r="X34">
-            <v>2</v>
-          </cell>
+          <cell r="D34"/>
+          <cell r="E34"/>
+          <cell r="F34"/>
+          <cell r="G34"/>
+          <cell r="H34"/>
+          <cell r="I34"/>
+          <cell r="J34"/>
+          <cell r="K34"/>
+          <cell r="L34"/>
+          <cell r="M34"/>
+          <cell r="N34"/>
+          <cell r="O34"/>
+          <cell r="P34"/>
+          <cell r="Q34"/>
+          <cell r="R34"/>
+          <cell r="S34"/>
+          <cell r="T34"/>
+          <cell r="U34"/>
+          <cell r="V34"/>
+          <cell r="W34"/>
+          <cell r="X34"/>
         </row>
         <row r="35">
-          <cell r="A35">
-            <v>34</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Queens University</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>Purdue</v>
-          </cell>
-          <cell r="D35">
-            <v>-2.4386972367557296</v>
-          </cell>
-          <cell r="E35">
-            <v>98.853272311212805</v>
-          </cell>
-          <cell r="F35">
-            <v>98.255343754602677</v>
-          </cell>
-          <cell r="G35">
-            <v>0.56723716381418088</v>
-          </cell>
-          <cell r="H35">
-            <v>70.530588235294118</v>
-          </cell>
-          <cell r="I35">
-            <v>60.147058823529413</v>
-          </cell>
-          <cell r="J35">
-            <v>22.529411764705884</v>
-          </cell>
-          <cell r="K35">
-            <v>10.235294117647058</v>
-          </cell>
-          <cell r="L35">
-            <v>10.705882352941176</v>
-          </cell>
-          <cell r="M35">
-            <v>26</v>
-          </cell>
-          <cell r="N35">
-            <v>20.933350618351088</v>
-          </cell>
-          <cell r="O35">
-            <v>102.749921687376</v>
-          </cell>
-          <cell r="P35">
-            <v>101.56518525976452</v>
-          </cell>
-          <cell r="Q35">
-            <v>0.5771558245083207</v>
-          </cell>
-          <cell r="R35">
-            <v>65.197575757575763</v>
-          </cell>
-          <cell r="S35">
-            <v>60.090909090909093</v>
-          </cell>
-          <cell r="T35">
-            <v>16.90909090909091</v>
-          </cell>
-          <cell r="U35">
-            <v>11.363636363636363</v>
-          </cell>
-          <cell r="V35">
-            <v>9.0303030303030312</v>
-          </cell>
-          <cell r="W35">
-            <v>0</v>
-          </cell>
-          <cell r="X35">
-            <v>25</v>
-          </cell>
+          <cell r="D35"/>
+          <cell r="E35"/>
+          <cell r="F35"/>
+          <cell r="G35"/>
+          <cell r="H35"/>
+          <cell r="I35"/>
+          <cell r="J35"/>
+          <cell r="K35"/>
+          <cell r="L35"/>
+          <cell r="M35"/>
+          <cell r="N35"/>
+          <cell r="O35"/>
+          <cell r="P35"/>
+          <cell r="Q35"/>
+          <cell r="R35"/>
+          <cell r="S35"/>
+          <cell r="T35"/>
+          <cell r="U35"/>
+          <cell r="V35"/>
+          <cell r="W35"/>
+          <cell r="X35"/>
         </row>
         <row r="36">
-          <cell r="A36">
-            <v>35</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>Santa Clara</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>Kentucky</v>
-          </cell>
-          <cell r="D36">
-            <v>15.7373824689671</v>
-          </cell>
-          <cell r="E36">
-            <v>102.69192816262087</v>
-          </cell>
-          <cell r="F36">
-            <v>86.875904373690886</v>
-          </cell>
-          <cell r="G36">
-            <v>0.54789719626168221</v>
-          </cell>
-          <cell r="H36">
-            <v>69.654545454545456</v>
-          </cell>
-          <cell r="I36">
-            <v>64.848484848484844</v>
-          </cell>
-          <cell r="J36">
-            <v>16.363636363636363</v>
-          </cell>
-          <cell r="K36">
-            <v>13.090909090909092</v>
-          </cell>
-          <cell r="L36">
-            <v>10.696969696969697</v>
-          </cell>
-          <cell r="M36">
-            <v>27</v>
-          </cell>
-          <cell r="N36">
-            <v>18.034523649586539</v>
-          </cell>
-          <cell r="O36">
-            <v>101.2517590047062</v>
-          </cell>
-          <cell r="P36">
-            <v>98.419793855345077</v>
-          </cell>
-          <cell r="Q36">
-            <v>0.53111327175498302</v>
-          </cell>
-          <cell r="R36">
-            <v>69.036470588235289</v>
-          </cell>
-          <cell r="S36">
-            <v>60.5</v>
-          </cell>
-          <cell r="T36">
-            <v>22.676470588235293</v>
-          </cell>
-          <cell r="U36">
-            <v>11.941176470588236</v>
-          </cell>
-          <cell r="V36">
-            <v>10.5</v>
-          </cell>
-          <cell r="W36">
-            <v>0</v>
-          </cell>
-          <cell r="X36">
-            <v>3</v>
-          </cell>
+          <cell r="D36"/>
+          <cell r="E36"/>
+          <cell r="F36"/>
+          <cell r="G36"/>
+          <cell r="H36"/>
+          <cell r="I36"/>
+          <cell r="J36"/>
+          <cell r="K36"/>
+          <cell r="L36"/>
+          <cell r="M36"/>
+          <cell r="N36"/>
+          <cell r="O36"/>
+          <cell r="P36"/>
+          <cell r="Q36"/>
+          <cell r="R36"/>
+          <cell r="S36"/>
+          <cell r="T36"/>
+          <cell r="U36"/>
+          <cell r="V36"/>
+          <cell r="W36"/>
+          <cell r="X36"/>
         </row>
         <row r="37">
-          <cell r="A37">
-            <v>36</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Tennessee State</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>Iowa State</v>
-          </cell>
-          <cell r="D37">
-            <v>1.0639361366167945</v>
-          </cell>
-          <cell r="E37">
-            <v>100.59318477066054</v>
-          </cell>
-          <cell r="F37">
-            <v>92.0991626269942</v>
-          </cell>
-          <cell r="G37">
-            <v>0.50690890481064488</v>
-          </cell>
-          <cell r="H37">
-            <v>71.468387096774194</v>
-          </cell>
-          <cell r="I37">
-            <v>63.032258064516128</v>
-          </cell>
-          <cell r="J37">
-            <v>21.225806451612904</v>
-          </cell>
-          <cell r="K37">
-            <v>13.129032258064516</v>
-          </cell>
-          <cell r="L37">
-            <v>12.225806451612904</v>
-          </cell>
-          <cell r="M37">
-            <v>28</v>
-          </cell>
-          <cell r="N37">
-            <v>20.641493911570723</v>
-          </cell>
-          <cell r="O37">
-            <v>101.50134460238188</v>
-          </cell>
-          <cell r="P37">
-            <v>96.951162965358421</v>
-          </cell>
-          <cell r="Q37">
-            <v>0.56497313141182215</v>
-          </cell>
-          <cell r="R37">
-            <v>67.654117647058825</v>
-          </cell>
-          <cell r="S37">
-            <v>60.205882352941174</v>
-          </cell>
-          <cell r="T37">
-            <v>20.470588235294116</v>
-          </cell>
-          <cell r="U37">
-            <v>11.823529411764707</v>
-          </cell>
-          <cell r="V37">
-            <v>10.264705882352942</v>
-          </cell>
-          <cell r="W37">
-            <v>0</v>
-          </cell>
-          <cell r="X37">
-            <v>24.5</v>
-          </cell>
+          <cell r="D37"/>
+          <cell r="E37"/>
+          <cell r="F37"/>
+          <cell r="G37"/>
+          <cell r="H37"/>
+          <cell r="I37"/>
+          <cell r="J37"/>
+          <cell r="K37"/>
+          <cell r="L37"/>
+          <cell r="M37"/>
+          <cell r="N37"/>
+          <cell r="O37"/>
+          <cell r="P37"/>
+          <cell r="Q37"/>
+          <cell r="R37"/>
+          <cell r="S37"/>
+          <cell r="T37"/>
+          <cell r="U37"/>
+          <cell r="V37"/>
+          <cell r="W37"/>
+          <cell r="X37"/>
         </row>
         <row r="38">
-          <cell r="A38">
-            <v>37</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Northern Iowa</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>St. John's</v>
-          </cell>
-          <cell r="D38">
-            <v>9.044790611595948</v>
-          </cell>
-          <cell r="E38">
-            <v>96.067511414353874</v>
-          </cell>
-          <cell r="F38">
-            <v>96.437852753995415</v>
-          </cell>
-          <cell r="G38">
-            <v>0.54763144195731395</v>
-          </cell>
-          <cell r="H38">
-            <v>63.515428571428572</v>
-          </cell>
-          <cell r="I38">
-            <v>54.885714285714286</v>
-          </cell>
-          <cell r="J38">
-            <v>14.028571428571428</v>
-          </cell>
-          <cell r="K38">
-            <v>6.8571428571428568</v>
-          </cell>
-          <cell r="L38">
-            <v>9.3142857142857149</v>
-          </cell>
-          <cell r="M38">
-            <v>29</v>
-          </cell>
-          <cell r="N38">
-            <v>15.123966744544841</v>
-          </cell>
-          <cell r="O38">
-            <v>102.62076624097725</v>
-          </cell>
-          <cell r="P38">
-            <v>99.067983608660882</v>
-          </cell>
-          <cell r="Q38">
-            <v>0.50957290132547861</v>
-          </cell>
-          <cell r="R38">
-            <v>70.527272727272731</v>
-          </cell>
-          <cell r="S38">
-            <v>61.727272727272727</v>
-          </cell>
-          <cell r="T38">
-            <v>26.060606060606062</v>
-          </cell>
-          <cell r="U38">
-            <v>13.242424242424242</v>
-          </cell>
-          <cell r="V38">
-            <v>10.575757575757576</v>
-          </cell>
-          <cell r="W38">
-            <v>0</v>
-          </cell>
-          <cell r="X38">
-            <v>10</v>
-          </cell>
+          <cell r="D38"/>
+          <cell r="E38"/>
+          <cell r="F38"/>
+          <cell r="G38"/>
+          <cell r="H38"/>
+          <cell r="I38"/>
+          <cell r="J38"/>
+          <cell r="K38"/>
+          <cell r="L38"/>
+          <cell r="M38"/>
+          <cell r="N38"/>
+          <cell r="O38"/>
+          <cell r="P38"/>
+          <cell r="Q38"/>
+          <cell r="R38"/>
+          <cell r="S38"/>
+          <cell r="T38"/>
+          <cell r="U38"/>
+          <cell r="V38"/>
+          <cell r="W38"/>
+          <cell r="X38"/>
         </row>
         <row r="39">
-          <cell r="A39">
-            <v>38</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>California Baptist</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>Kansas</v>
-          </cell>
-          <cell r="D39">
-            <v>4.6851123682196496</v>
-          </cell>
-          <cell r="E39">
-            <v>101.15808245043532</v>
-          </cell>
-          <cell r="F39">
-            <v>89.740557985976295</v>
-          </cell>
-          <cell r="G39">
-            <v>0.48558215451577802</v>
-          </cell>
-          <cell r="H39">
-            <v>67.477419354838716</v>
-          </cell>
-          <cell r="I39">
-            <v>59.29032258064516</v>
-          </cell>
-          <cell r="J39">
-            <v>21.612903225806452</v>
-          </cell>
-          <cell r="K39">
-            <v>13.838709677419354</v>
-          </cell>
-          <cell r="L39">
-            <v>12.516129032258064</v>
-          </cell>
-          <cell r="M39">
-            <v>30</v>
-          </cell>
-          <cell r="N39">
-            <v>16.809475334579385</v>
-          </cell>
-          <cell r="O39">
-            <v>98.782531105933685</v>
-          </cell>
-          <cell r="P39">
-            <v>105.39233290147665</v>
-          </cell>
-          <cell r="Q39">
-            <v>0.51565708418891165</v>
-          </cell>
-          <cell r="R39">
-            <v>68.042424242424246</v>
-          </cell>
-          <cell r="S39">
-            <v>59.030303030303031</v>
-          </cell>
-          <cell r="T39">
-            <v>19.242424242424242</v>
-          </cell>
-          <cell r="U39">
-            <v>10.121212121212121</v>
-          </cell>
-          <cell r="V39">
-            <v>10.666666666666666</v>
-          </cell>
-          <cell r="W39">
-            <v>0</v>
-          </cell>
-          <cell r="X39">
-            <v>14</v>
-          </cell>
+          <cell r="D39"/>
+          <cell r="E39"/>
+          <cell r="F39"/>
+          <cell r="G39"/>
+          <cell r="H39"/>
+          <cell r="I39"/>
+          <cell r="J39"/>
+          <cell r="K39"/>
+          <cell r="L39"/>
+          <cell r="M39"/>
+          <cell r="N39"/>
+          <cell r="O39"/>
+          <cell r="P39"/>
+          <cell r="Q39"/>
+          <cell r="R39"/>
+          <cell r="S39"/>
+          <cell r="T39"/>
+          <cell r="U39"/>
+          <cell r="V39"/>
+          <cell r="W39"/>
+          <cell r="X39"/>
         </row>
         <row r="40">
-          <cell r="A40">
-            <v>39</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Long Island University</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>Arizona</v>
-          </cell>
-          <cell r="D40">
-            <v>-5.3079314642110162</v>
-          </cell>
-          <cell r="E40">
-            <v>97.176470588235304</v>
-          </cell>
-          <cell r="F40">
-            <v>96.766501308175762</v>
-          </cell>
-          <cell r="G40">
-            <v>0.53577106518282991</v>
-          </cell>
-          <cell r="H40">
-            <v>67.672727272727272</v>
-          </cell>
-          <cell r="I40">
-            <v>57.18181818181818</v>
-          </cell>
-          <cell r="J40">
-            <v>19.848484848484848</v>
-          </cell>
-          <cell r="K40">
-            <v>11.303030303030303</v>
-          </cell>
-          <cell r="L40">
-            <v>13.060606060606061</v>
-          </cell>
-          <cell r="M40">
-            <v>31</v>
-          </cell>
-          <cell r="N40">
-            <v>23.687310951598352</v>
-          </cell>
-          <cell r="O40">
-            <v>101.76807841686704</v>
-          </cell>
-          <cell r="P40">
-            <v>98.493332637771204</v>
-          </cell>
-          <cell r="Q40">
-            <v>0.55109126984126988</v>
-          </cell>
-          <cell r="R40">
-            <v>70.587878787878793</v>
-          </cell>
-          <cell r="S40">
-            <v>61.090909090909093</v>
-          </cell>
-          <cell r="T40">
-            <v>26.060606060606062</v>
-          </cell>
-          <cell r="U40">
-            <v>12.878787878787879</v>
-          </cell>
-          <cell r="V40">
-            <v>10.909090909090908</v>
-          </cell>
-          <cell r="W40">
-            <v>0</v>
-          </cell>
-          <cell r="X40">
-            <v>31</v>
-          </cell>
+          <cell r="D40"/>
+          <cell r="E40"/>
+          <cell r="F40"/>
+          <cell r="G40"/>
+          <cell r="H40"/>
+          <cell r="I40"/>
+          <cell r="J40"/>
+          <cell r="K40"/>
+          <cell r="L40"/>
+          <cell r="M40"/>
+          <cell r="N40"/>
+          <cell r="O40"/>
+          <cell r="P40"/>
+          <cell r="Q40"/>
+          <cell r="R40"/>
+          <cell r="S40"/>
+          <cell r="T40"/>
+          <cell r="U40"/>
+          <cell r="V40"/>
+          <cell r="W40"/>
+          <cell r="X40"/>
         </row>
         <row r="41">
-          <cell r="A41">
-            <v>40</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Utah State</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>Villanova</v>
-          </cell>
-          <cell r="D41">
-            <v>16.287809545840613</v>
-          </cell>
-          <cell r="E41">
-            <v>99.539689712306071</v>
-          </cell>
-          <cell r="F41">
-            <v>89.1227776403734</v>
-          </cell>
-          <cell r="G41">
-            <v>0.5741935483870968</v>
-          </cell>
-          <cell r="H41">
-            <v>67.972499999999997</v>
-          </cell>
-          <cell r="I41">
-            <v>58.125</v>
-          </cell>
-          <cell r="J41">
-            <v>22.59375</v>
-          </cell>
-          <cell r="K41">
-            <v>10.65625</v>
-          </cell>
-          <cell r="L41">
-            <v>10.5625</v>
-          </cell>
-          <cell r="M41">
-            <v>32</v>
-          </cell>
-          <cell r="N41">
-            <v>11.840993072985095</v>
-          </cell>
-          <cell r="O41">
-            <v>101.29752325216845</v>
-          </cell>
-          <cell r="P41">
-            <v>98.574654865749267</v>
-          </cell>
-          <cell r="Q41">
-            <v>0.53713389121338917</v>
-          </cell>
-          <cell r="R41">
-            <v>66.628749999999997</v>
-          </cell>
-          <cell r="S41">
-            <v>59.75</v>
-          </cell>
-          <cell r="T41">
-            <v>18.6875</v>
-          </cell>
-          <cell r="U41">
-            <v>11.5</v>
-          </cell>
-          <cell r="V41">
-            <v>10.15625</v>
-          </cell>
-          <cell r="W41">
-            <v>0</v>
-          </cell>
-          <cell r="X41">
-            <v>-2</v>
-          </cell>
+          <cell r="D41"/>
+          <cell r="E41"/>
+          <cell r="F41"/>
+          <cell r="G41"/>
+          <cell r="H41"/>
+          <cell r="I41"/>
+          <cell r="J41"/>
+          <cell r="K41"/>
+          <cell r="L41"/>
+          <cell r="M41"/>
+          <cell r="N41"/>
+          <cell r="O41"/>
+          <cell r="P41"/>
+          <cell r="Q41"/>
+          <cell r="R41"/>
+          <cell r="S41"/>
+          <cell r="T41"/>
+          <cell r="U41"/>
+          <cell r="V41"/>
+          <cell r="W41"/>
+          <cell r="X41"/>
         </row>
         <row r="42">
-          <cell r="A42">
-            <v>41</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Louisville</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>Michigan State</v>
-          </cell>
-          <cell r="D42">
-            <v>16.631119331501349</v>
-          </cell>
-          <cell r="E42">
-            <v>99.101896527014759</v>
-          </cell>
-          <cell r="F42">
-            <v>98.314439245284362</v>
-          </cell>
-          <cell r="G42">
-            <v>0.56448412698412698</v>
-          </cell>
-          <cell r="H42">
-            <v>70.393939393939391</v>
-          </cell>
-          <cell r="I42">
-            <v>61.090909090909093</v>
-          </cell>
-          <cell r="J42">
-            <v>20.454545454545453</v>
-          </cell>
-          <cell r="K42">
-            <v>11.333333333333334</v>
-          </cell>
-          <cell r="L42">
-            <v>11.636363636363637</v>
-          </cell>
-          <cell r="M42">
-            <v>33</v>
-          </cell>
-          <cell r="N42">
-            <v>19.982154388171562</v>
-          </cell>
-          <cell r="O42">
-            <v>101.32466702184337</v>
-          </cell>
-          <cell r="P42">
-            <v>94.579391423053281</v>
-          </cell>
-          <cell r="Q42">
-            <v>0.53589041095890411</v>
-          </cell>
-          <cell r="R42">
-            <v>66.620645161290327</v>
-          </cell>
-          <cell r="S42">
-            <v>58.87096774193548</v>
-          </cell>
-          <cell r="T42">
-            <v>20.838709677419356</v>
-          </cell>
-          <cell r="U42">
-            <v>12.774193548387096</v>
-          </cell>
-          <cell r="V42">
-            <v>11.35483870967742</v>
-          </cell>
-          <cell r="W42">
-            <v>0</v>
-          </cell>
-          <cell r="X42">
-            <v>4</v>
-          </cell>
+          <cell r="D42"/>
+          <cell r="E42"/>
+          <cell r="F42"/>
+          <cell r="G42"/>
+          <cell r="H42"/>
+          <cell r="I42"/>
+          <cell r="J42"/>
+          <cell r="K42"/>
+          <cell r="L42"/>
+          <cell r="M42"/>
+          <cell r="N42"/>
+          <cell r="O42"/>
+          <cell r="P42"/>
+          <cell r="Q42"/>
+          <cell r="R42"/>
+          <cell r="S42"/>
+          <cell r="T42"/>
+          <cell r="U42"/>
+          <cell r="V42"/>
+          <cell r="W42"/>
+          <cell r="X42"/>
         </row>
         <row r="43">
-          <cell r="A43">
-            <v>42</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Saint Louis</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>Michigan</v>
-          </cell>
-          <cell r="D43">
-            <v>12.891007564287897</v>
-          </cell>
-          <cell r="E43">
-            <v>96.587342281204442</v>
-          </cell>
-          <cell r="F43">
-            <v>96.419529699076293</v>
-          </cell>
-          <cell r="G43">
-            <v>0.59935205183585316</v>
-          </cell>
-          <cell r="H43">
-            <v>71.190967741935481</v>
-          </cell>
-          <cell r="I43">
-            <v>59.741935483870968</v>
-          </cell>
-          <cell r="J43">
-            <v>20.741935483870968</v>
-          </cell>
-          <cell r="K43">
-            <v>10.03225806451613</v>
-          </cell>
-          <cell r="L43">
-            <v>12.35483870967742</v>
-          </cell>
-          <cell r="M43">
-            <v>34</v>
-          </cell>
-          <cell r="N43">
-            <v>23.158914646956031</v>
-          </cell>
-          <cell r="O43">
-            <v>98.200984374253366</v>
-          </cell>
-          <cell r="P43">
-            <v>96.383444817292968</v>
-          </cell>
-          <cell r="Q43">
-            <v>0.58467532467532468</v>
-          </cell>
-          <cell r="R43">
-            <v>71.510000000000005</v>
-          </cell>
-          <cell r="S43">
-            <v>60.15625</v>
-          </cell>
-          <cell r="T43">
-            <v>23.53125</v>
-          </cell>
-          <cell r="U43">
-            <v>11.0625</v>
-          </cell>
-          <cell r="V43">
-            <v>12.0625</v>
-          </cell>
-          <cell r="W43">
-            <v>0</v>
-          </cell>
-          <cell r="X43">
-            <v>12.5</v>
-          </cell>
+          <cell r="D43"/>
+          <cell r="E43"/>
+          <cell r="F43"/>
+          <cell r="G43"/>
+          <cell r="H43"/>
+          <cell r="I43"/>
+          <cell r="J43"/>
+          <cell r="K43"/>
+          <cell r="L43"/>
+          <cell r="M43"/>
+          <cell r="N43"/>
+          <cell r="O43"/>
+          <cell r="P43"/>
+          <cell r="Q43"/>
+          <cell r="R43"/>
+          <cell r="S43"/>
+          <cell r="T43"/>
+          <cell r="U43"/>
+          <cell r="V43"/>
+          <cell r="W43"/>
+          <cell r="X43"/>
         </row>
         <row r="44">
-          <cell r="A44">
-            <v>43</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>TCU</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>Duke</v>
-          </cell>
-          <cell r="D44">
-            <v>12.676356416890858</v>
-          </cell>
-          <cell r="E44">
-            <v>101.27537334728432</v>
-          </cell>
-          <cell r="F44">
-            <v>97.104848064562987</v>
-          </cell>
-          <cell r="G44">
-            <v>0.50900000000000001</v>
-          </cell>
-          <cell r="H44">
-            <v>69.441212121212118</v>
-          </cell>
-          <cell r="I44">
-            <v>60.606060606060609</v>
-          </cell>
-          <cell r="J44">
-            <v>23.454545454545453</v>
-          </cell>
-          <cell r="K44">
-            <v>12.424242424242424</v>
-          </cell>
-          <cell r="L44">
-            <v>10.939393939393939</v>
-          </cell>
-          <cell r="M44">
-            <v>35</v>
-          </cell>
-          <cell r="N44">
-            <v>23.054887624413109</v>
-          </cell>
-          <cell r="O44">
-            <v>101.57301127857072</v>
-          </cell>
-          <cell r="P44">
-            <v>99.414290660558592</v>
-          </cell>
-          <cell r="Q44">
-            <v>0.57213541666666667</v>
-          </cell>
-          <cell r="R44">
-            <v>66.278787878787867</v>
-          </cell>
-          <cell r="S44">
-            <v>58.18181818181818</v>
-          </cell>
-          <cell r="T44">
-            <v>22.121212121212121</v>
-          </cell>
-          <cell r="U44">
-            <v>12.212121212121213</v>
-          </cell>
-          <cell r="V44">
-            <v>10.575757575757576</v>
-          </cell>
-          <cell r="W44">
-            <v>0</v>
-          </cell>
-          <cell r="X44">
-            <v>11</v>
-          </cell>
+          <cell r="D44"/>
+          <cell r="E44"/>
+          <cell r="F44"/>
+          <cell r="G44"/>
+          <cell r="H44"/>
+          <cell r="I44"/>
+          <cell r="J44"/>
+          <cell r="K44"/>
+          <cell r="L44"/>
+          <cell r="M44"/>
+          <cell r="N44"/>
+          <cell r="O44"/>
+          <cell r="P44"/>
+          <cell r="Q44"/>
+          <cell r="R44"/>
+          <cell r="S44"/>
+          <cell r="T44"/>
+          <cell r="U44"/>
+          <cell r="V44"/>
+          <cell r="W44"/>
+          <cell r="X44"/>
         </row>
         <row r="45">
-          <cell r="A45">
-            <v>44</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>VCU</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>Illinois</v>
-          </cell>
-          <cell r="D45">
-            <v>10.280535393881047</v>
-          </cell>
-          <cell r="E45">
-            <v>99.976592216912124</v>
-          </cell>
-          <cell r="F45">
-            <v>99.94980567668172</v>
-          </cell>
-          <cell r="G45">
-            <v>0.54290339989206693</v>
-          </cell>
-          <cell r="H45">
-            <v>68.818749999999994</v>
-          </cell>
-          <cell r="I45">
-            <v>57.90625</v>
-          </cell>
-          <cell r="J45">
-            <v>25.9375</v>
-          </cell>
-          <cell r="K45">
-            <v>11.3125</v>
-          </cell>
-          <cell r="L45">
-            <v>10.8125</v>
-          </cell>
-          <cell r="M45">
-            <v>36</v>
-          </cell>
-          <cell r="N45">
-            <v>18.826343007871433</v>
-          </cell>
-          <cell r="O45">
-            <v>105.08780903665816</v>
-          </cell>
-          <cell r="P45">
-            <v>108.91673393133649</v>
-          </cell>
-          <cell r="Q45">
-            <v>0.5511688311688312</v>
-          </cell>
-          <cell r="R45">
-            <v>66.809032258064519</v>
-          </cell>
-          <cell r="S45">
-            <v>62.096774193548384</v>
-          </cell>
-          <cell r="T45">
-            <v>20.387096774193548</v>
-          </cell>
-          <cell r="U45">
-            <v>13.258064516129032</v>
-          </cell>
-          <cell r="V45">
-            <v>9</v>
-          </cell>
-          <cell r="W45">
-            <v>0</v>
-          </cell>
-          <cell r="X45">
-            <v>10.5</v>
-          </cell>
+          <cell r="D45"/>
+          <cell r="E45"/>
+          <cell r="F45"/>
+          <cell r="G45"/>
+          <cell r="H45"/>
+          <cell r="I45"/>
+          <cell r="J45"/>
+          <cell r="K45"/>
+          <cell r="L45"/>
+          <cell r="M45"/>
+          <cell r="N45"/>
+          <cell r="O45"/>
+          <cell r="P45"/>
+          <cell r="Q45"/>
+          <cell r="R45"/>
+          <cell r="S45"/>
+          <cell r="T45"/>
+          <cell r="U45"/>
+          <cell r="V45"/>
+          <cell r="W45"/>
+          <cell r="X45"/>
         </row>
         <row r="46">
-          <cell r="A46">
-            <v>45</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Vanderbilt</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>Nebraska</v>
-          </cell>
-          <cell r="D46">
-            <v>19.334095266215517</v>
-          </cell>
-          <cell r="E46">
-            <v>100.88210871874095</v>
-          </cell>
-          <cell r="F46">
-            <v>97.473801766777243</v>
-          </cell>
-          <cell r="G46">
-            <v>0.55371690427698572</v>
-          </cell>
-          <cell r="H46">
-            <v>70.61</v>
-          </cell>
-          <cell r="I46">
-            <v>61.375</v>
-          </cell>
-          <cell r="J46">
-            <v>23.6875</v>
-          </cell>
-          <cell r="K46">
-            <v>10.8125</v>
-          </cell>
-          <cell r="L46">
-            <v>9.625</v>
-          </cell>
-          <cell r="M46">
-            <v>37</v>
-          </cell>
-          <cell r="N46">
-            <v>15.82631796216417</v>
-          </cell>
-          <cell r="O46">
-            <v>98.25476089716463</v>
-          </cell>
-          <cell r="P46">
-            <v>102.35159180352665</v>
-          </cell>
-          <cell r="Q46">
-            <v>0.55440552016985134</v>
-          </cell>
-          <cell r="R46">
-            <v>66.883750000000006</v>
-          </cell>
-          <cell r="S46">
-            <v>58.875</v>
-          </cell>
-          <cell r="T46">
-            <v>16</v>
-          </cell>
-          <cell r="U46">
-            <v>8.78125</v>
-          </cell>
-          <cell r="V46">
-            <v>9.75</v>
-          </cell>
-          <cell r="W46">
-            <v>0</v>
-          </cell>
-          <cell r="X46">
-            <v>-2.5</v>
-          </cell>
+          <cell r="D46"/>
+          <cell r="E46"/>
+          <cell r="F46"/>
+          <cell r="G46"/>
+          <cell r="H46"/>
+          <cell r="I46"/>
+          <cell r="J46"/>
+          <cell r="K46"/>
+          <cell r="L46"/>
+          <cell r="M46"/>
+          <cell r="N46"/>
+          <cell r="O46"/>
+          <cell r="P46"/>
+          <cell r="Q46"/>
+          <cell r="R46"/>
+          <cell r="S46"/>
+          <cell r="T46"/>
+          <cell r="U46"/>
+          <cell r="V46"/>
+          <cell r="W46"/>
+          <cell r="X46"/>
         </row>
         <row r="47">
-          <cell r="A47">
-            <v>46</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Texas A&amp;M</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>Houston</v>
-          </cell>
-          <cell r="D47">
-            <v>13.344745551152522</v>
-          </cell>
-          <cell r="E47">
-            <v>101.09664255240216</v>
-          </cell>
-          <cell r="F47">
-            <v>98.213295342640578</v>
-          </cell>
-          <cell r="G47">
-            <v>0.54188861985472159</v>
-          </cell>
-          <cell r="H47">
-            <v>73.739999999999995</v>
-          </cell>
-          <cell r="I47">
-            <v>64.53125</v>
-          </cell>
-          <cell r="J47">
-            <v>24.125</v>
-          </cell>
-          <cell r="K47">
-            <v>12.25</v>
-          </cell>
-          <cell r="L47">
-            <v>10.84375</v>
-          </cell>
-          <cell r="M47">
-            <v>38</v>
-          </cell>
-          <cell r="N47">
-            <v>20.901069562815731</v>
-          </cell>
-          <cell r="O47">
-            <v>105.43571389837862</v>
-          </cell>
-          <cell r="P47">
-            <v>97.084637989347655</v>
-          </cell>
-          <cell r="Q47">
-            <v>0.52154080081094778</v>
-          </cell>
-          <cell r="R47">
-            <v>64.762500000000003</v>
-          </cell>
-          <cell r="S47">
-            <v>61.65625</v>
-          </cell>
-          <cell r="T47">
-            <v>16.71875</v>
-          </cell>
-          <cell r="U47">
-            <v>12.78125</v>
-          </cell>
-          <cell r="V47">
-            <v>8.53125</v>
-          </cell>
-          <cell r="W47">
-            <v>0</v>
-          </cell>
-          <cell r="X47">
-            <v>10</v>
-          </cell>
+          <cell r="D47"/>
+          <cell r="E47"/>
+          <cell r="F47"/>
+          <cell r="G47"/>
+          <cell r="H47"/>
+          <cell r="I47"/>
+          <cell r="J47"/>
+          <cell r="K47"/>
+          <cell r="L47"/>
+          <cell r="M47"/>
+          <cell r="N47"/>
+          <cell r="O47"/>
+          <cell r="P47"/>
+          <cell r="Q47"/>
+          <cell r="R47"/>
+          <cell r="S47"/>
+          <cell r="T47"/>
+          <cell r="U47"/>
+          <cell r="V47"/>
+          <cell r="W47"/>
+          <cell r="X47"/>
         </row>
         <row r="48">
-          <cell r="A48">
-            <v>47</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>High Point</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>Arkansas</v>
-          </cell>
-          <cell r="D48">
-            <v>9.7914064574296606</v>
-          </cell>
-          <cell r="E48">
-            <v>102.08135263134599</v>
-          </cell>
-          <cell r="F48">
-            <v>95.473025683474958</v>
-          </cell>
-          <cell r="G48">
-            <v>0.56606463878326996</v>
-          </cell>
-          <cell r="H48">
-            <v>71.407058823529411</v>
-          </cell>
-          <cell r="I48">
-            <v>61.882352941176471</v>
-          </cell>
-          <cell r="J48">
-            <v>26.794117647058822</v>
-          </cell>
-          <cell r="K48">
-            <v>11.617647058823529</v>
-          </cell>
-          <cell r="L48">
-            <v>9.3529411764705888</v>
-          </cell>
-          <cell r="M48">
-            <v>39</v>
-          </cell>
-          <cell r="N48">
-            <v>19.899076876872613</v>
-          </cell>
-          <cell r="O48">
-            <v>101.9693472090823</v>
-          </cell>
-          <cell r="P48">
-            <v>97.545722643013036</v>
-          </cell>
-          <cell r="Q48">
-            <v>0.56447688564476883</v>
-          </cell>
-          <cell r="R48">
-            <v>72.41</v>
-          </cell>
-          <cell r="S48">
-            <v>64.21875</v>
-          </cell>
-          <cell r="T48">
-            <v>23.375</v>
-          </cell>
-          <cell r="U48">
-            <v>11.0625</v>
-          </cell>
-          <cell r="V48">
-            <v>8.96875</v>
-          </cell>
-          <cell r="W48">
-            <v>0</v>
-          </cell>
-          <cell r="X48">
-            <v>11</v>
-          </cell>
+          <cell r="D48"/>
+          <cell r="E48"/>
+          <cell r="F48"/>
+          <cell r="G48"/>
+          <cell r="H48"/>
+          <cell r="I48"/>
+          <cell r="J48"/>
+          <cell r="K48"/>
+          <cell r="L48"/>
+          <cell r="M48"/>
+          <cell r="N48"/>
+          <cell r="O48"/>
+          <cell r="P48"/>
+          <cell r="Q48"/>
+          <cell r="R48"/>
+          <cell r="S48"/>
+          <cell r="T48"/>
+          <cell r="U48"/>
+          <cell r="V48"/>
+          <cell r="W48"/>
+          <cell r="X48"/>
         </row>
         <row r="49">
-          <cell r="A49">
-            <v>48</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>Texas</v>
-          </cell>
-          <cell r="C49" t="str">
-            <v>Gonzaga</v>
-          </cell>
-          <cell r="D49">
-            <v>14.532052109666417</v>
-          </cell>
-          <cell r="E49">
-            <v>100.55048907489414</v>
-          </cell>
-          <cell r="F49">
-            <v>96.670144874968173</v>
-          </cell>
-          <cell r="G49">
-            <v>0.5496777658431794</v>
-          </cell>
-          <cell r="H49">
-            <v>68.81</v>
-          </cell>
-          <cell r="I49">
-            <v>58.1875</v>
-          </cell>
-          <cell r="J49">
-            <v>26.34375</v>
-          </cell>
-          <cell r="K49">
-            <v>12</v>
-          </cell>
-          <cell r="L49">
-            <v>11.03125</v>
-          </cell>
-          <cell r="M49">
-            <v>40</v>
-          </cell>
-          <cell r="N49">
-            <v>20.959854873623506</v>
-          </cell>
-          <cell r="O49">
-            <v>102.65043408841434</v>
-          </cell>
-          <cell r="P49">
-            <v>86.043703668873505</v>
-          </cell>
-          <cell r="Q49">
-            <v>0.56074766355140182</v>
-          </cell>
-          <cell r="R49">
-            <v>69.724999999999994</v>
-          </cell>
-          <cell r="S49">
-            <v>63.53125</v>
-          </cell>
-          <cell r="T49">
-            <v>19.6875</v>
-          </cell>
-          <cell r="U49">
-            <v>12.03125</v>
-          </cell>
-          <cell r="V49">
-            <v>9.5625</v>
-          </cell>
-          <cell r="W49">
-            <v>0</v>
-          </cell>
-          <cell r="X49">
-            <v>5.5</v>
-          </cell>
+          <cell r="D49"/>
+          <cell r="E49"/>
+          <cell r="F49"/>
+          <cell r="G49"/>
+          <cell r="H49"/>
+          <cell r="I49"/>
+          <cell r="J49"/>
+          <cell r="K49"/>
+          <cell r="L49"/>
+          <cell r="M49"/>
+          <cell r="N49"/>
+          <cell r="O49"/>
+          <cell r="P49"/>
+          <cell r="Q49"/>
+          <cell r="R49"/>
+          <cell r="S49"/>
+          <cell r="T49"/>
+          <cell r="U49"/>
+          <cell r="V49"/>
+          <cell r="W49"/>
+          <cell r="X49"/>
         </row>
         <row r="50">
           <cell r="D50"/>
@@ -24276,7 +22908,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24292,15 +22924,15 @@
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.7185281356503328</v>
+        <v>7.2987974976589882</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.45858766203522988</v>
+        <v>0.39498384438829071</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24308,7 +22940,7 @@
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.2492685044687476E-2</v>
+        <v>2.1773721975554827E-2</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>443</v>
@@ -24323,7 +22955,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24339,7 +22971,7 @@
       </c>
       <c r="E3" s="5">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>15.5119498017062</v>
+        <v>14.976006036963041</v>
       </c>
       <c r="F3" s="5">
         <f>-VLOOKUP(A3,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -24347,7 +22979,7 @@
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.61731951279916419</v>
+        <v>0.58389146809910786</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24355,7 +22987,7 @@
       </c>
       <c r="I3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.1310118896945618E-2</v>
+        <v>1.6113502052682332E-2</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>443</v>
@@ -24367,7 +22999,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B4" s="6" t="str">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24383,15 +23015,15 @@
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>16.140216310663</v>
+        <v>16.481515841644931</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.70336153249742339</v>
+        <v>0.68835260367062623</v>
       </c>
       <c r="H4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24399,7 +23031,7 @@
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.0689741555315628E-2</v>
+        <v>3.4672078293523353E-2</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>443</v>
@@ -24411,7 +23043,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B5" s="6" t="str">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24427,7 +23059,7 @@
       </c>
       <c r="E5" s="5">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.438763270417709</v>
+        <v>13.813979689921981</v>
       </c>
       <c r="F5" s="5">
         <f>-VLOOKUP(A5,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -24435,7 +23067,7 @@
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.63074311573987751</v>
+        <v>0.59272854171055378</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24443,7 +23075,7 @@
       </c>
       <c r="I5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.0845333654386374E-2</v>
+        <v>2.5112276414578225E-2</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>443</v>
@@ -24455,7 +23087,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6" t="str">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24471,15 +23103,15 @@
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-1.093500554042212</v>
+        <v>-1.470916172407954</v>
       </c>
       <c r="F6" s="5">
         <f>-VLOOKUP(A6,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="G6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>4.8789164423594489E-2</v>
+        <v>1.5691879196898632E-2</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24487,7 +23119,7 @@
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>5.3525505891840325E-3</v>
+        <v>-5.0685448851996153E-3</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>443</v>
@@ -24499,7 +23131,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6" t="str">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24515,15 +23147,15 @@
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>12.80869246587973</v>
+        <v>12.490512577712639</v>
       </c>
       <c r="F7" s="5">
         <f>-VLOOKUP(A7,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.54759166061732523</v>
+        <v>0.50131716872622822</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24531,7 +23163,7 @@
       </c>
       <c r="I7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.0460202169939601E-2</v>
+        <v>1.1851731352758644E-2</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>443</v>
@@ -24543,7 +23175,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B8" s="6" t="str">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24559,15 +23191,15 @@
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.531806056773171</v>
+        <v>14.409404039669781</v>
       </c>
       <c r="F8" s="5">
         <f>-VLOOKUP(A8,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.61701013724196296</v>
+        <v>0.58925228425349863</v>
       </c>
       <c r="H8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24575,7 +23207,7 @@
       </c>
       <c r="I8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.6886349055742175E-2</v>
+        <v>2.0773826597078271E-2</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>443</v>
@@ -24587,7 +23219,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="str">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,2,FALSE)</f>
@@ -24603,15 +23235,15 @@
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>8.5492026218240404</v>
+        <v>8.8326972336325653</v>
       </c>
       <c r="F9" s="5">
         <f>-VLOOKUP(A9,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="G9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.44641629054277171</v>
+        <v>0.41516446029663601</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -24619,7 +23251,7 @@
       </c>
       <c r="I9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.470423354456186E-2</v>
+        <v>1.6298053686601782E-2</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>443</v>
@@ -24630,52 +23262,180 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="9"/>
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="str">
+        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Alabama</v>
+      </c>
+      <c r="C10" s="6" t="str">
+        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Texas Tech</v>
+      </c>
+      <c r="D10" s="6" t="str">
+        <f t="shared" ref="D10:D13" si="2">B10</f>
+        <v>Alabama</v>
+      </c>
+      <c r="E10" s="5">
+        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>4.1278919748299394</v>
+      </c>
+      <c r="F10" s="5">
+        <f>-VLOOKUP(A10,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="7">
+        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.31628008750747999</v>
+      </c>
+      <c r="H10" s="7">
+        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>2.5623371857857451E-2</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K10" s="9">
+        <f t="shared" ref="K10:K13" si="3">IF(J10="Yes",(H10*1500)/100,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
+      <c r="A11" s="1">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6" t="str">
+        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Tennessee</v>
+      </c>
+      <c r="C11" s="6" t="str">
+        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Virginia</v>
+      </c>
+      <c r="D11" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Tennessee</v>
+      </c>
+      <c r="E11" s="5">
+        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>6.3504265210794983</v>
+      </c>
+      <c r="F11" s="5">
+        <f>-VLOOKUP(A11,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="7">
+        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.503917783931362</v>
+      </c>
+      <c r="H11" s="7">
+        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>5.7998893446444849E-2</v>
+      </c>
+      <c r="I11" s="7">
+        <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>4.9999371276389128E-2</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="shared" si="3"/>
+        <v>0.86998340169667276</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="str">
+        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Iowa State</v>
+      </c>
+      <c r="C12" s="6" t="str">
+        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Kentucky</v>
+      </c>
+      <c r="D12" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Iowa State</v>
+      </c>
+      <c r="E12" s="5">
+        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>7.1011751940087526</v>
+      </c>
+      <c r="F12" s="5">
+        <f>-VLOOKUP(A12,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G12" s="7">
+        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.34931589557310277</v>
+      </c>
+      <c r="H12" s="7">
+        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>1.3569223993972977E-2</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="str">
+        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Arizona</v>
+      </c>
+      <c r="C13" s="6" t="str">
+        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Utah State</v>
+      </c>
+      <c r="D13" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Arizona</v>
+      </c>
+      <c r="E13" s="5">
+        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>12.03916810204351</v>
+      </c>
+      <c r="F13" s="5">
+        <f>-VLOOKUP(A13,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>11.5</v>
+      </c>
+      <c r="G13" s="7">
+        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.41142205261584602</v>
+      </c>
+      <c r="H13" s="7">
+        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="7">
+        <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>-4.9486061792907978E-3</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="6"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ACE55A-4E6F-FE4C-8ECF-DF978CB7330E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E8C1C4-55A0-3248-A565-06B30C854093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="15440" yWindow="780" windowWidth="18760" windowHeight="19960" activeTab="4" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="462">
   <si>
     <t>Team</t>
   </si>
@@ -1600,19 +1600,19 @@
             <v>Louisville</v>
           </cell>
           <cell r="E2">
-            <v>7.2987974976589882</v>
+            <v>7.6237974976589857</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.56943065556782912</v>
+            <v>0.5651294463644575</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>8.7094887902219309E-2</v>
+            <v>7.8883488513964317E-2</v>
           </cell>
           <cell r="J2">
             <v>0.39498384438829071</v>
@@ -1664,19 +1664,19 @@
             <v>TCU</v>
           </cell>
           <cell r="E4">
-            <v>16.481515841644931</v>
+            <v>16.156515841644939</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.59645578309119174</v>
+            <v>0.60014369447283544</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.13868831317409341</v>
+            <v>0.14572887126632231</v>
           </cell>
           <cell r="J4">
             <v>0.68835260367062623</v>
@@ -1696,22 +1696,22 @@
             <v>VCU</v>
           </cell>
           <cell r="E5">
-            <v>13.813979689921981</v>
+            <v>14.138979689921969</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.57642572201149722</v>
+            <v>0.57243583222898409</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>0.1004491056583129</v>
+            <v>9.2832043346242399E-2</v>
           </cell>
           <cell r="J5">
-            <v>0.59272854171055378</v>
+            <v>0.59272854171055356</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1760,7 +1760,7 @@
             <v>Texas A&amp;M</v>
           </cell>
           <cell r="E7">
-            <v>12.490512577712639</v>
+            <v>12.49051257771263</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
@@ -1775,7 +1775,7 @@
             <v>4.7406925411034577E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.50131716872622822</v>
+            <v>0.50131716872622811</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1798,13 +1798,13 @@
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.56733563667959253</v>
+            <v>0.56733563667959241</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>8.3095306388313084E-2</v>
+            <v>8.3095306388312862E-2</v>
           </cell>
           <cell r="J8">
             <v>0.58925228425349863</v>
@@ -1839,7 +1839,7 @@
             <v>6.5192214746407129E-2</v>
           </cell>
           <cell r="J9">
-            <v>0.41516446029663601</v>
+            <v>0.41516446029663578</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1882,28 +1882,28 @@
             <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Virginia</v>
+            <v>Florida</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Tennessee</v>
+            <v>Iowa</v>
           </cell>
           <cell r="E11">
-            <v>0.62393594721707213</v>
+            <v>11.194715824766851</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0.54042163234016005</v>
+            <v>0.51731652847327136</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>3.171402537666923E-2</v>
+            <v>-1.239571836920916E-2</v>
           </cell>
           <cell r="J11">
-            <v>0.1168367102471547</v>
+            <v>0.39463016781725752</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1914,28 +1914,28 @@
             <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Iowa State</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Kentucky</v>
+            <v>UCLA</v>
           </cell>
           <cell r="E12">
-            <v>7.1011751940087526</v>
+            <v>5.391134817228437</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.55224027884451476</v>
+            <v>0.53464275300729347</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>5.4276895975891908E-2</v>
+            <v>2.0681619377560301E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.34931589557310277</v>
+            <v>0.25478768357222192</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1946,28 +1946,28 @@
             <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Arizona</v>
+            <v>Virginia</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Utah State</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="E13">
-            <v>12.03916810204351</v>
+            <v>0.62393594721707168</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.51344101562434308</v>
+            <v>0.54042163234016005</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>-1.9794424717163191E-2</v>
+            <v>3.171402537666923E-2</v>
           </cell>
           <cell r="J13">
-            <v>0.41142205261584602</v>
+            <v>0.1168367102471546</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1978,31 +1978,31 @@
             <v>13</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Louisville</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D14" t="str">
-            <v>Michigan State</v>
+            <v>Miami</v>
           </cell>
           <cell r="E14">
-            <v>-3.809326919725216</v>
+            <v>12.5746195342281</v>
           </cell>
           <cell r="F14" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G14">
-            <v>0.51721582153955314</v>
+            <v>0.61295541220788918</v>
           </cell>
           <cell r="H14">
-            <v>0</v>
+            <v>4.4882546254626871E-2</v>
           </cell>
           <cell r="I14">
-            <v>-1.2587977060853069E-2</v>
+            <v>0.1701876051241521</v>
           </cell>
           <cell r="J14">
-            <v>8.115042882985124E-2</v>
+            <v>0.63571360517770981</v>
           </cell>
           <cell r="K14">
-            <v>0</v>
+            <v>0.87610730289031646</v>
           </cell>
         </row>
         <row r="15">
@@ -2010,28 +2010,28 @@
             <v>14</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Saint Louis</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D15" t="str">
-            <v>Michigan</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="E15">
-            <v>-12.63418965089744</v>
+            <v>7.1011751940087526</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.50334583110950348</v>
+            <v>0.55224027884451476</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>-3.906704970003877E-2</v>
+            <v>5.4276895975891908E-2</v>
           </cell>
           <cell r="J15">
-            <v>0.40668649337587193</v>
+            <v>0.34931589557310277</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -2042,31 +2042,31 @@
             <v>15</v>
           </cell>
           <cell r="C16" t="str">
-            <v>TCU</v>
+            <v>Kansas</v>
           </cell>
           <cell r="D16" t="str">
-            <v>Duke</v>
+            <v>St. John's</v>
           </cell>
           <cell r="E16">
-            <v>-12.900837100669641</v>
+            <v>1.26500591653001</v>
           </cell>
           <cell r="F16" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G16">
-            <v>0.52244951418090224</v>
+            <v>0.61707700432140333</v>
           </cell>
           <cell r="H16">
-            <v>0</v>
+            <v>4.8344683629978888E-2</v>
           </cell>
           <cell r="I16">
-            <v>-2.5963820182774988E-3</v>
+            <v>0.17805609915904269</v>
           </cell>
           <cell r="J16">
-            <v>0.45710006902003109</v>
+            <v>0.32179849370920788</v>
           </cell>
           <cell r="K16">
-            <v>0</v>
+            <v>0.94368822445718792</v>
           </cell>
         </row>
         <row r="17">
@@ -2074,28 +2074,28 @@
             <v>16</v>
           </cell>
           <cell r="C17" t="str">
-            <v>VCU</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D17" t="str">
-            <v>Illinois</v>
+            <v>Utah State</v>
           </cell>
           <cell r="E17">
-            <v>-7.6481914140359821</v>
+            <v>12.03916810204351</v>
           </cell>
           <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.57073198047378837</v>
+            <v>0.51344101562434308</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>8.9579235449959715E-2</v>
+            <v>-1.9794424717163191E-2</v>
           </cell>
           <cell r="J17">
-            <v>7.5545540380110965E-2</v>
+            <v>0.41142205261584602</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -2106,28 +2106,28 @@
             <v>17</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Vanderbilt</v>
+            <v>Louisville</v>
           </cell>
           <cell r="D18" t="str">
-            <v>Nebraska</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="E18">
-            <v>4.7803474147172347</v>
+            <v>-4.1343269197252157</v>
           </cell>
           <cell r="F18" t="b">
             <v>0</v>
           </cell>
           <cell r="G18">
-            <v>0.56897756221792961</v>
+            <v>0.52157407338626549</v>
           </cell>
           <cell r="H18">
             <v>0</v>
           </cell>
           <cell r="I18">
-            <v>8.6229891506956591E-2</v>
+            <v>-4.2676780807658346E-3</v>
           </cell>
           <cell r="J18">
-            <v>0.31649838901374577</v>
+            <v>8.115042882985124E-2</v>
           </cell>
           <cell r="K18">
             <v>0</v>
@@ -2138,28 +2138,28 @@
             <v>18</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="D19" t="str">
-            <v>Houston</v>
+            <v>Michigan</v>
           </cell>
           <cell r="E19">
-            <v>-7.5735379918606291</v>
+            <v>-12.63418965089744</v>
           </cell>
           <cell r="F19" t="b">
             <v>0</v>
           </cell>
           <cell r="G19">
-            <v>0.57256327900997128</v>
+            <v>0.50334583110950348</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>9.3075350837217963E-2</v>
+            <v>-3.906704970003877E-2</v>
           </cell>
           <cell r="J19">
-            <v>6.8699796942407798E-2</v>
+            <v>0.40668649337587193</v>
           </cell>
           <cell r="K19">
             <v>0</v>
@@ -2170,28 +2170,28 @@
             <v>19</v>
           </cell>
           <cell r="C20" t="str">
-            <v>High Point</v>
+            <v>TCU</v>
           </cell>
           <cell r="D20" t="str">
-            <v>Arkansas</v>
+            <v>Duke</v>
           </cell>
           <cell r="E20">
-            <v>-12.955196747770399</v>
+            <v>-12.57583710066964</v>
           </cell>
           <cell r="F20" t="b">
             <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0.5358807449944516</v>
+            <v>0.52680460698779541</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>2.3045058625771279E-2</v>
+            <v>5.7178860676094789E-3</v>
           </cell>
           <cell r="J20">
-            <v>0.48734606471556818</v>
+            <v>0.45710006902003097</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -2202,28 +2202,28 @@
             <v>20</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Texas</v>
+            <v>VCU</v>
           </cell>
           <cell r="D21" t="str">
-            <v>Gonzaga</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E21">
-            <v>-4.8282195018383911</v>
+            <v>-7.9731914140359823</v>
           </cell>
           <cell r="F21" t="b">
             <v>0</v>
           </cell>
           <cell r="G21">
-            <v>0.5416082726227095</v>
+            <v>0.57502237979486459</v>
           </cell>
           <cell r="H21">
             <v>0</v>
           </cell>
           <cell r="I21">
-            <v>3.3979429552445428E-2</v>
+            <v>9.7769997790196128E-2</v>
           </cell>
           <cell r="J21">
-            <v>5.5369792667541717E-2</v>
+            <v>7.5545540380110965E-2</v>
           </cell>
           <cell r="K21">
             <v>0</v>
@@ -2234,28 +2234,28 @@
             <v>21</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Texas Tech</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="D22" t="str">
-            <v>Alabama</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="E22">
-            <v>-2.5226261132732191</v>
+            <v>4.7803474147172347</v>
           </cell>
           <cell r="F22" t="b">
             <v>0</v>
           </cell>
           <cell r="G22">
-            <v>0.53790777044744986</v>
+            <v>0.56897756221792961</v>
           </cell>
           <cell r="H22">
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>2.6914834490586129E-2</v>
+            <v>8.6229891506956591E-2</v>
           </cell>
           <cell r="J22">
-            <v>0.1715154919189017</v>
+            <v>0.31649838901374572</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2266,31 +2266,31 @@
             <v>22</v>
           </cell>
           <cell r="C23" t="str">
-            <v>Tennessee</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="D23" t="str">
-            <v>Virginia</v>
+            <v>Houston</v>
           </cell>
           <cell r="E23">
-            <v>6.3504265210794983</v>
+            <v>-7.5735379918606291</v>
           </cell>
           <cell r="F23" t="b">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0.62857011124576767</v>
+            <v>0.57256327900997128</v>
           </cell>
           <cell r="H23">
-            <v>5.7998893446444849E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I23">
-            <v>0.19999748510555651</v>
+            <v>9.3075350837217963E-2</v>
           </cell>
           <cell r="J23">
-            <v>0.503917783931362</v>
+            <v>6.8699796942407798E-2</v>
           </cell>
           <cell r="K23">
-            <v>1.1321384000746035</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="24">
@@ -2298,28 +2298,28 @@
             <v>23</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Kentucky</v>
+            <v>High Point</v>
           </cell>
           <cell r="D24" t="str">
-            <v>Iowa State</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="E24">
-            <v>-4.5359178664915367</v>
+            <v>-12.955196747770399</v>
           </cell>
           <cell r="F24" t="b">
             <v>0</v>
           </cell>
           <cell r="G24">
-            <v>0.51156975174926678</v>
+            <v>0.5358807449944516</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>-2.3366837569581581E-2</v>
+            <v>2.3045058625771279E-2</v>
           </cell>
           <cell r="J24">
-            <v>0.1179331312373687</v>
+            <v>0.48734606471556807</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2330,28 +2330,28 @@
             <v>24</v>
           </cell>
           <cell r="C25" t="str">
-            <v>Utah State</v>
+            <v>Texas</v>
           </cell>
           <cell r="D25" t="str">
-            <v>Arizona</v>
+            <v>Gonzaga</v>
           </cell>
           <cell r="E25">
-            <v>-9.6384453574740654</v>
+            <v>-4.8282195018383911</v>
           </cell>
           <cell r="F25" t="b">
             <v>0</v>
           </cell>
           <cell r="G25">
-            <v>0.54631129649620014</v>
+            <v>0.5416082726227095</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>4.2957929674563973E-2</v>
+            <v>3.3979429552445428E-2</v>
           </cell>
           <cell r="J25">
-            <v>0.19797857638448821</v>
+            <v>5.5369792667541717E-2</v>
           </cell>
           <cell r="K25">
             <v>0</v>
@@ -2361,23 +2361,29 @@
           <cell r="B26">
             <v>25</v>
           </cell>
+          <cell r="C26" t="str">
+            <v>Texas Tech</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>Alabama</v>
+          </cell>
           <cell r="E26">
-            <v>0</v>
-          </cell>
-          <cell r="F26">
+            <v>-2.5226261132732191</v>
+          </cell>
+          <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0</v>
+            <v>0.53790777044744986</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>0</v>
+            <v>2.6914834490586129E-2</v>
           </cell>
           <cell r="J26">
-            <v>0</v>
+            <v>0.1715154919189017</v>
           </cell>
           <cell r="K26">
             <v>0</v>
@@ -2387,23 +2393,29 @@
           <cell r="B27">
             <v>26</v>
           </cell>
+          <cell r="C27" t="str">
+            <v>Iowa</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>Florida</v>
+          </cell>
           <cell r="E27">
-            <v>0</v>
-          </cell>
-          <cell r="F27">
+            <v>-7.106672621036318</v>
+          </cell>
+          <cell r="F27" t="b">
             <v>0</v>
           </cell>
           <cell r="G27">
-            <v>0</v>
+            <v>0.58397884382351473</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>0</v>
+            <v>0.1148687018448918</v>
           </cell>
           <cell r="J27">
-            <v>0</v>
+            <v>2.5859635062304261E-2</v>
           </cell>
           <cell r="K27">
             <v>0</v>
@@ -2413,23 +2425,29 @@
           <cell r="B28">
             <v>27</v>
           </cell>
+          <cell r="C28" t="str">
+            <v>UCLA</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>Uconn</v>
+          </cell>
           <cell r="E28">
-            <v>0</v>
-          </cell>
-          <cell r="F28">
+            <v>-2.5258509357806149</v>
+          </cell>
+          <cell r="F28" t="b">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>0</v>
+            <v>0.5367043381194001</v>
           </cell>
           <cell r="H28">
             <v>0</v>
           </cell>
           <cell r="I28">
-            <v>0</v>
+            <v>2.4617372773400259E-2</v>
           </cell>
           <cell r="J28">
-            <v>0</v>
+            <v>6.8077579319985038E-3</v>
           </cell>
           <cell r="K28">
             <v>0</v>
@@ -2439,49 +2457,61 @@
           <cell r="B29">
             <v>28</v>
           </cell>
+          <cell r="C29" t="str">
+            <v>Tennessee</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>Virginia</v>
+          </cell>
           <cell r="E29">
-            <v>0</v>
-          </cell>
-          <cell r="F29">
-            <v>0</v>
+            <v>6.3504265210794983</v>
+          </cell>
+          <cell r="F29" t="b">
+            <v>1</v>
           </cell>
           <cell r="G29">
-            <v>0</v>
+            <v>0.62857011124576767</v>
           </cell>
           <cell r="H29">
-            <v>0</v>
+            <v>5.7998893446444849E-2</v>
           </cell>
           <cell r="I29">
-            <v>0</v>
+            <v>0.19999748510555651</v>
           </cell>
           <cell r="J29">
-            <v>0</v>
+            <v>0.503917783931362</v>
           </cell>
           <cell r="K29">
-            <v>0</v>
+            <v>1.1321384000746035</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
             <v>29</v>
           </cell>
+          <cell r="C30" t="str">
+            <v>Miami</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>Purdue</v>
+          </cell>
           <cell r="E30">
-            <v>0</v>
-          </cell>
-          <cell r="F30">
+            <v>-6.4513442417313867</v>
+          </cell>
+          <cell r="F30" t="b">
             <v>0</v>
           </cell>
           <cell r="G30">
-            <v>0</v>
+            <v>0.52612836237902483</v>
           </cell>
           <cell r="H30">
             <v>0</v>
           </cell>
           <cell r="I30">
-            <v>0</v>
+            <v>4.4268736326837921E-3</v>
           </cell>
           <cell r="J30">
-            <v>0</v>
+            <v>0.14448487310626509</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -2491,23 +2521,29 @@
           <cell r="B31">
             <v>30</v>
           </cell>
+          <cell r="C31" t="str">
+            <v>Kentucky</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>Iowa State</v>
+          </cell>
           <cell r="E31">
-            <v>0</v>
-          </cell>
-          <cell r="F31">
+            <v>-4.5359178664915367</v>
+          </cell>
+          <cell r="F31" t="b">
             <v>0</v>
           </cell>
           <cell r="G31">
-            <v>0</v>
+            <v>0.51156975174926678</v>
           </cell>
           <cell r="H31">
             <v>0</v>
           </cell>
           <cell r="I31">
-            <v>0</v>
+            <v>-2.3366837569581581E-2</v>
           </cell>
           <cell r="J31">
-            <v>0</v>
+            <v>0.1179331312373687</v>
           </cell>
           <cell r="K31">
             <v>0</v>
@@ -2517,23 +2553,29 @@
           <cell r="B32">
             <v>31</v>
           </cell>
+          <cell r="C32" t="str">
+            <v>St. John's</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>Kansas</v>
+          </cell>
           <cell r="E32">
-            <v>0</v>
-          </cell>
-          <cell r="F32">
+            <v>3.1590318805399149</v>
+          </cell>
+          <cell r="F32" t="b">
             <v>0</v>
           </cell>
           <cell r="G32">
-            <v>0</v>
+            <v>0.50850101900132016</v>
           </cell>
           <cell r="H32">
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>0</v>
+            <v>-2.922532736111599E-2</v>
           </cell>
           <cell r="J32">
-            <v>0</v>
+            <v>8.1123382590810478E-2</v>
           </cell>
           <cell r="K32">
             <v>0</v>
@@ -2543,23 +2585,29 @@
           <cell r="B33">
             <v>32</v>
           </cell>
+          <cell r="C33" t="str">
+            <v>Utah State</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>Arizona</v>
+          </cell>
           <cell r="E33">
-            <v>0</v>
-          </cell>
-          <cell r="F33">
+            <v>-9.6384453574740654</v>
+          </cell>
+          <cell r="F33" t="b">
             <v>0</v>
           </cell>
           <cell r="G33">
-            <v>0</v>
+            <v>0.54631129649620014</v>
           </cell>
           <cell r="H33">
             <v>0</v>
           </cell>
           <cell r="I33">
-            <v>0</v>
+            <v>4.2957929674563973E-2</v>
           </cell>
           <cell r="J33">
-            <v>0</v>
+            <v>0.19797857638448799</v>
           </cell>
           <cell r="K33">
             <v>0</v>
@@ -8795,7 +8843,7 @@
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-4.5</v>
+            <v>-5</v>
           </cell>
         </row>
         <row r="3">
@@ -8943,7 +8991,7 @@
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-12</v>
+            <v>-11.5</v>
           </cell>
         </row>
         <row r="5">
@@ -9017,7 +9065,7 @@
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>-10.5</v>
+            <v>-11</v>
           </cell>
         </row>
         <row r="6">
@@ -9395,73 +9443,73 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>Virginia</v>
+            <v>Florida</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Tennessee</v>
+            <v>Iowa</v>
           </cell>
           <cell r="D11">
-            <v>12.898930744177012</v>
+            <v>22.650454216704585</v>
           </cell>
           <cell r="E11">
-            <v>102.74660271782574</v>
+            <v>104.38676700269771</v>
           </cell>
           <cell r="F11">
-            <v>105.30602921182151</v>
+            <v>99.448258680413886</v>
           </cell>
           <cell r="G11">
-            <v>0.54717923115327005</v>
+            <v>0.53652636671504594</v>
           </cell>
           <cell r="H11">
-            <v>67.065454545454543</v>
+            <v>71.564999999999998</v>
           </cell>
           <cell r="I11">
-            <v>60.696969696969695</v>
+            <v>64.59375</v>
           </cell>
           <cell r="J11">
-            <v>20.121212121212121</v>
+            <v>25.21875</v>
           </cell>
           <cell r="K11">
-            <v>13.272727272727273</v>
+            <v>15.96875</v>
           </cell>
           <cell r="L11">
-            <v>10.787878787878787</v>
+            <v>11.84375</v>
           </cell>
           <cell r="M11">
             <v>0</v>
           </cell>
           <cell r="N11">
-            <v>20.582457175121956</v>
+            <v>15.51511812576733</v>
           </cell>
           <cell r="O11">
-            <v>105.02195491662999</v>
+            <v>98.238539943433466</v>
           </cell>
           <cell r="P11">
-            <v>93.637950339797769</v>
+            <v>93.168875634820807</v>
           </cell>
           <cell r="Q11">
-            <v>0.51561725334655428</v>
+            <v>0.56555993247045577</v>
           </cell>
           <cell r="R11">
-            <v>67.170909090909092</v>
+            <v>62.900606060606066</v>
           </cell>
           <cell r="S11">
-            <v>61.121212121212125</v>
+            <v>53.848484848484851</v>
           </cell>
           <cell r="T11">
-            <v>23.666666666666668</v>
+            <v>18.575757575757574</v>
           </cell>
           <cell r="U11">
-            <v>16.030303030303031</v>
+            <v>8.8181818181818183</v>
           </cell>
           <cell r="V11">
-            <v>11.666666666666666</v>
+            <v>9.6969696969696972</v>
           </cell>
           <cell r="W11">
             <v>0</v>
           </cell>
           <cell r="X11">
-            <v>1</v>
+            <v>-10.5</v>
           </cell>
         </row>
         <row r="12">
@@ -9469,73 +9517,73 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>Iowa State</v>
+            <v>Uconn</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Kentucky</v>
+            <v>UCLA</v>
           </cell>
           <cell r="D12">
-            <v>20.641493911570723</v>
+            <v>18.120431537245491</v>
           </cell>
           <cell r="E12">
-            <v>101.50134460238188</v>
+            <v>100.0952772073922</v>
           </cell>
           <cell r="F12">
-            <v>96.951162965358421</v>
+            <v>94.261774983054991</v>
           </cell>
           <cell r="G12">
-            <v>0.56497313141182215</v>
+            <v>0.55882352941176472</v>
           </cell>
           <cell r="H12">
-            <v>67.654117647058825</v>
+            <v>66.089696969696973</v>
           </cell>
           <cell r="I12">
-            <v>60.205882352941174</v>
+            <v>58.727272727272727</v>
           </cell>
           <cell r="J12">
-            <v>20.470588235294116</v>
+            <v>17.696969696969695</v>
           </cell>
           <cell r="K12">
-            <v>11.823529411764707</v>
+            <v>11.454545454545455</v>
           </cell>
           <cell r="L12">
-            <v>10.264705882352942</v>
+            <v>11.030303030303031</v>
           </cell>
           <cell r="M12">
             <v>0</v>
           </cell>
           <cell r="N12">
-            <v>18.034523649586539</v>
+            <v>15.943406980069799</v>
           </cell>
           <cell r="O12">
-            <v>101.2517590047062</v>
+            <v>100.85863980873899</v>
           </cell>
           <cell r="P12">
-            <v>98.419793855345077</v>
+            <v>91.898292422931632</v>
           </cell>
           <cell r="Q12">
-            <v>0.53111327175498302</v>
+            <v>0.54047742605085625</v>
           </cell>
           <cell r="R12">
-            <v>69.036470588235289</v>
+            <v>65.963636363636368</v>
           </cell>
           <cell r="S12">
-            <v>60.5</v>
+            <v>58.393939393939391</v>
           </cell>
           <cell r="T12">
-            <v>22.676470588235293</v>
+            <v>19.545454545454547</v>
           </cell>
           <cell r="U12">
-            <v>11.941176470588236</v>
+            <v>10</v>
           </cell>
           <cell r="V12">
-            <v>10.5</v>
+            <v>8.9696969696969688</v>
           </cell>
           <cell r="W12">
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>-5</v>
+            <v>-4</v>
           </cell>
         </row>
         <row r="13">
@@ -9543,73 +9591,73 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>Arizona</v>
+            <v>Virginia</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Utah State</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D13">
-            <v>23.687310951598352</v>
+            <v>12.898930744177012</v>
           </cell>
           <cell r="E13">
-            <v>101.76807841686704</v>
+            <v>102.74660271782574</v>
           </cell>
           <cell r="F13">
-            <v>98.493332637771204</v>
+            <v>105.30602921182151</v>
           </cell>
           <cell r="G13">
-            <v>0.55109126984126988</v>
+            <v>0.54717923115327005</v>
           </cell>
           <cell r="H13">
-            <v>70.587878787878793</v>
+            <v>67.065454545454543</v>
           </cell>
           <cell r="I13">
-            <v>61.090909090909093</v>
+            <v>60.696969696969695</v>
           </cell>
           <cell r="J13">
-            <v>26.060606060606062</v>
+            <v>20.121212121212121</v>
           </cell>
           <cell r="K13">
-            <v>12.878787878787879</v>
+            <v>13.272727272727273</v>
           </cell>
           <cell r="L13">
-            <v>10.909090909090908</v>
+            <v>10.787878787878787</v>
           </cell>
           <cell r="M13">
             <v>0</v>
           </cell>
           <cell r="N13">
-            <v>16.287809545840613</v>
+            <v>20.582457175121956</v>
           </cell>
           <cell r="O13">
-            <v>99.539689712306071</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="P13">
-            <v>89.1227776403734</v>
+            <v>93.637950339797769</v>
           </cell>
           <cell r="Q13">
-            <v>0.5741935483870968</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="R13">
-            <v>67.972499999999997</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="S13">
-            <v>58.125</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="T13">
-            <v>22.59375</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="U13">
-            <v>10.65625</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="V13">
-            <v>10.5625</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="W13">
             <v>0</v>
           </cell>
           <cell r="X13">
-            <v>-11.5</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="14">
@@ -9617,73 +9665,73 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>Louisville</v>
+            <v>Purdue</v>
           </cell>
           <cell r="C14" t="str">
-            <v>Michigan State</v>
+            <v>Miami</v>
           </cell>
           <cell r="D14">
-            <v>16.631119331501349</v>
+            <v>20.933350618351088</v>
           </cell>
           <cell r="E14">
-            <v>99.101896527014759</v>
+            <v>102.749921687376</v>
           </cell>
           <cell r="F14">
-            <v>98.314439245284362</v>
+            <v>101.56518525976452</v>
           </cell>
           <cell r="G14">
-            <v>0.56448412698412698</v>
+            <v>0.5771558245083207</v>
           </cell>
           <cell r="H14">
-            <v>70.393939393939391</v>
+            <v>65.197575757575763</v>
           </cell>
           <cell r="I14">
-            <v>61.090909090909093</v>
+            <v>60.090909090909093</v>
           </cell>
           <cell r="J14">
-            <v>20.454545454545453</v>
+            <v>16.90909090909091</v>
           </cell>
           <cell r="K14">
-            <v>11.333333333333334</v>
+            <v>11.363636363636363</v>
           </cell>
           <cell r="L14">
-            <v>11.636363636363637</v>
+            <v>9.0303030303030312</v>
           </cell>
           <cell r="M14">
             <v>0</v>
           </cell>
           <cell r="N14">
-            <v>19.982154388171562</v>
+            <v>12.238890418004498</v>
           </cell>
           <cell r="O14">
-            <v>101.32466702184337</v>
+            <v>100.74202898550723</v>
           </cell>
           <cell r="P14">
-            <v>94.579391423053281</v>
+            <v>98.35968575523485</v>
           </cell>
           <cell r="Q14">
-            <v>0.53589041095890411</v>
+            <v>0.55597771023302933</v>
           </cell>
           <cell r="R14">
-            <v>66.620645161290327</v>
+            <v>68.654545454545456</v>
           </cell>
           <cell r="S14">
-            <v>58.87096774193548</v>
+            <v>59.81818181818182</v>
           </cell>
           <cell r="T14">
-            <v>20.838709677419356</v>
+            <v>22.424242424242426</v>
           </cell>
           <cell r="U14">
-            <v>12.774193548387096</v>
+            <v>12.242424242424242</v>
           </cell>
           <cell r="V14">
-            <v>11.35483870967742</v>
+            <v>11.212121212121213</v>
           </cell>
           <cell r="W14">
             <v>0</v>
           </cell>
           <cell r="X14">
-            <v>4.5</v>
+            <v>-7.5</v>
           </cell>
         </row>
         <row r="15">
@@ -9691,73 +9739,73 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>Saint Louis</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="C15" t="str">
-            <v>Michigan</v>
+            <v>Kentucky</v>
           </cell>
           <cell r="D15">
-            <v>12.891007564287897</v>
+            <v>20.641493911570723</v>
           </cell>
           <cell r="E15">
-            <v>96.587342281204442</v>
+            <v>101.50134460238188</v>
           </cell>
           <cell r="F15">
-            <v>96.419529699076293</v>
+            <v>96.951162965358421</v>
           </cell>
           <cell r="G15">
-            <v>0.59935205183585316</v>
+            <v>0.56497313141182215</v>
           </cell>
           <cell r="H15">
-            <v>71.190967741935481</v>
+            <v>67.654117647058825</v>
           </cell>
           <cell r="I15">
-            <v>59.741935483870968</v>
+            <v>60.205882352941174</v>
           </cell>
           <cell r="J15">
-            <v>20.741935483870968</v>
+            <v>20.470588235294116</v>
           </cell>
           <cell r="K15">
-            <v>10.03225806451613</v>
+            <v>11.823529411764707</v>
           </cell>
           <cell r="L15">
-            <v>12.35483870967742</v>
+            <v>10.264705882352942</v>
           </cell>
           <cell r="M15">
             <v>0</v>
           </cell>
           <cell r="N15">
-            <v>23.158914646956031</v>
+            <v>18.034523649586539</v>
           </cell>
           <cell r="O15">
-            <v>98.200984374253366</v>
+            <v>101.2517590047062</v>
           </cell>
           <cell r="P15">
-            <v>96.383444817292968</v>
+            <v>98.419793855345077</v>
           </cell>
           <cell r="Q15">
-            <v>0.58467532467532468</v>
+            <v>0.53111327175498302</v>
           </cell>
           <cell r="R15">
-            <v>71.510000000000005</v>
+            <v>69.036470588235289</v>
           </cell>
           <cell r="S15">
-            <v>60.15625</v>
+            <v>60.5</v>
           </cell>
           <cell r="T15">
-            <v>23.53125</v>
+            <v>22.676470588235293</v>
           </cell>
           <cell r="U15">
-            <v>11.0625</v>
+            <v>11.941176470588236</v>
           </cell>
           <cell r="V15">
-            <v>12.0625</v>
+            <v>10.5</v>
           </cell>
           <cell r="W15">
             <v>0</v>
           </cell>
           <cell r="X15">
-            <v>12.5</v>
+            <v>-5</v>
           </cell>
         </row>
         <row r="16">
@@ -9765,64 +9813,64 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>TCU</v>
+            <v>Kansas</v>
           </cell>
           <cell r="C16" t="str">
-            <v>Duke</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D16">
-            <v>12.676356416890858</v>
+            <v>16.809475334579385</v>
           </cell>
           <cell r="E16">
-            <v>101.27537334728432</v>
+            <v>98.782531105933685</v>
           </cell>
           <cell r="F16">
-            <v>97.104848064562987</v>
+            <v>105.39233290147665</v>
           </cell>
           <cell r="G16">
-            <v>0.50900000000000001</v>
+            <v>0.51565708418891165</v>
           </cell>
           <cell r="H16">
-            <v>69.441212121212118</v>
+            <v>68.042424242424246</v>
           </cell>
           <cell r="I16">
-            <v>60.606060606060609</v>
+            <v>59.030303030303031</v>
           </cell>
           <cell r="J16">
-            <v>23.454545454545453</v>
+            <v>19.242424242424242</v>
           </cell>
           <cell r="K16">
-            <v>12.424242424242424</v>
+            <v>10.121212121212121</v>
           </cell>
           <cell r="L16">
-            <v>10.939393939393939</v>
+            <v>10.666666666666666</v>
           </cell>
           <cell r="M16">
             <v>0</v>
           </cell>
           <cell r="N16">
-            <v>23.054887624413109</v>
+            <v>15.123966744544841</v>
           </cell>
           <cell r="O16">
-            <v>101.57301127857072</v>
+            <v>102.62076624097725</v>
           </cell>
           <cell r="P16">
-            <v>99.414290660558592</v>
+            <v>99.067983608660882</v>
           </cell>
           <cell r="Q16">
-            <v>0.57213541666666667</v>
+            <v>0.50957290132547861</v>
           </cell>
           <cell r="R16">
-            <v>66.278787878787867</v>
+            <v>70.527272727272731</v>
           </cell>
           <cell r="S16">
-            <v>58.18181818181818</v>
+            <v>61.727272727272727</v>
           </cell>
           <cell r="T16">
-            <v>22.121212121212121</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="U16">
-            <v>12.212121212121213</v>
+            <v>13.242424242424242</v>
           </cell>
           <cell r="V16">
             <v>10.575757575757576</v>
@@ -9831,7 +9879,7 @@
             <v>0</v>
           </cell>
           <cell r="X16">
-            <v>12</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="17">
@@ -9839,73 +9887,73 @@
             <v>16</v>
           </cell>
           <cell r="B17" t="str">
-            <v>VCU</v>
+            <v>Arizona</v>
           </cell>
           <cell r="C17" t="str">
-            <v>Illinois</v>
+            <v>Utah State</v>
           </cell>
           <cell r="D17">
-            <v>10.280535393881047</v>
+            <v>23.687310951598352</v>
           </cell>
           <cell r="E17">
-            <v>99.976592216912124</v>
+            <v>101.76807841686704</v>
           </cell>
           <cell r="F17">
-            <v>99.94980567668172</v>
+            <v>98.493332637771204</v>
           </cell>
           <cell r="G17">
-            <v>0.54290339989206693</v>
+            <v>0.55109126984126988</v>
           </cell>
           <cell r="H17">
-            <v>68.818749999999994</v>
+            <v>70.587878787878793</v>
           </cell>
           <cell r="I17">
-            <v>57.90625</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="J17">
-            <v>25.9375</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="K17">
-            <v>11.3125</v>
+            <v>12.878787878787879</v>
           </cell>
           <cell r="L17">
-            <v>10.8125</v>
+            <v>10.909090909090908</v>
           </cell>
           <cell r="M17">
             <v>0</v>
           </cell>
           <cell r="N17">
-            <v>18.826343007871433</v>
+            <v>16.287809545840613</v>
           </cell>
           <cell r="O17">
-            <v>105.08780903665816</v>
+            <v>99.539689712306071</v>
           </cell>
           <cell r="P17">
-            <v>108.91673393133649</v>
+            <v>89.1227776403734</v>
           </cell>
           <cell r="Q17">
-            <v>0.5511688311688312</v>
+            <v>0.5741935483870968</v>
           </cell>
           <cell r="R17">
-            <v>66.809032258064519</v>
+            <v>67.972499999999997</v>
           </cell>
           <cell r="S17">
-            <v>62.096774193548384</v>
+            <v>58.125</v>
           </cell>
           <cell r="T17">
-            <v>20.387096774193548</v>
+            <v>22.59375</v>
           </cell>
           <cell r="U17">
-            <v>13.258064516129032</v>
+            <v>10.65625</v>
           </cell>
           <cell r="V17">
-            <v>9</v>
+            <v>10.5625</v>
           </cell>
           <cell r="W17">
             <v>0</v>
           </cell>
           <cell r="X17">
-            <v>10.5</v>
+            <v>-11.5</v>
           </cell>
         </row>
         <row r="18">
@@ -9913,73 +9961,73 @@
             <v>17</v>
           </cell>
           <cell r="B18" t="str">
-            <v>Vanderbilt</v>
+            <v>Louisville</v>
           </cell>
           <cell r="C18" t="str">
-            <v>Nebraska</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D18">
-            <v>19.334095266215517</v>
+            <v>16.631119331501349</v>
           </cell>
           <cell r="E18">
-            <v>100.88210871874095</v>
+            <v>99.101896527014759</v>
           </cell>
           <cell r="F18">
-            <v>97.473801766777243</v>
+            <v>98.314439245284362</v>
           </cell>
           <cell r="G18">
-            <v>0.55371690427698572</v>
+            <v>0.56448412698412698</v>
           </cell>
           <cell r="H18">
-            <v>70.61</v>
+            <v>70.393939393939391</v>
           </cell>
           <cell r="I18">
-            <v>61.375</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="J18">
-            <v>23.6875</v>
+            <v>20.454545454545453</v>
           </cell>
           <cell r="K18">
-            <v>10.8125</v>
+            <v>11.333333333333334</v>
           </cell>
           <cell r="L18">
-            <v>9.625</v>
+            <v>11.636363636363637</v>
           </cell>
           <cell r="M18">
             <v>0</v>
           </cell>
           <cell r="N18">
-            <v>15.82631796216417</v>
+            <v>19.982154388171562</v>
           </cell>
           <cell r="O18">
-            <v>98.25476089716463</v>
+            <v>101.32466702184337</v>
           </cell>
           <cell r="P18">
-            <v>102.35159180352665</v>
+            <v>94.579391423053281</v>
           </cell>
           <cell r="Q18">
-            <v>0.55440552016985134</v>
+            <v>0.53589041095890411</v>
           </cell>
           <cell r="R18">
-            <v>66.883750000000006</v>
+            <v>66.620645161290327</v>
           </cell>
           <cell r="S18">
-            <v>58.875</v>
+            <v>58.87096774193548</v>
           </cell>
           <cell r="T18">
-            <v>16</v>
+            <v>20.838709677419356</v>
           </cell>
           <cell r="U18">
-            <v>8.78125</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="V18">
-            <v>9.75</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="W18">
             <v>0</v>
           </cell>
           <cell r="X18">
-            <v>-2</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="19">
@@ -9987,73 +10035,73 @@
             <v>18</v>
           </cell>
           <cell r="B19" t="str">
-            <v>Texas A&amp;M</v>
+            <v>Saint Louis</v>
           </cell>
           <cell r="C19" t="str">
-            <v>Houston</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D19">
-            <v>13.344745551152522</v>
+            <v>12.891007564287897</v>
           </cell>
           <cell r="E19">
-            <v>101.09664255240216</v>
+            <v>96.587342281204442</v>
           </cell>
           <cell r="F19">
-            <v>98.213295342640578</v>
+            <v>96.419529699076293</v>
           </cell>
           <cell r="G19">
-            <v>0.54188861985472159</v>
+            <v>0.59935205183585316</v>
           </cell>
           <cell r="H19">
-            <v>73.739999999999995</v>
+            <v>71.190967741935481</v>
           </cell>
           <cell r="I19">
-            <v>64.53125</v>
+            <v>59.741935483870968</v>
           </cell>
           <cell r="J19">
-            <v>24.125</v>
+            <v>20.741935483870968</v>
           </cell>
           <cell r="K19">
-            <v>12.25</v>
+            <v>10.03225806451613</v>
           </cell>
           <cell r="L19">
-            <v>10.84375</v>
+            <v>12.35483870967742</v>
           </cell>
           <cell r="M19">
             <v>0</v>
           </cell>
           <cell r="N19">
-            <v>20.901069562815731</v>
+            <v>23.158914646956031</v>
           </cell>
           <cell r="O19">
-            <v>105.43571389837862</v>
+            <v>98.200984374253366</v>
           </cell>
           <cell r="P19">
-            <v>97.084637989347655</v>
+            <v>96.383444817292968</v>
           </cell>
           <cell r="Q19">
-            <v>0.52154080081094778</v>
+            <v>0.58467532467532468</v>
           </cell>
           <cell r="R19">
-            <v>64.762500000000003</v>
+            <v>71.510000000000005</v>
           </cell>
           <cell r="S19">
-            <v>61.65625</v>
+            <v>60.15625</v>
           </cell>
           <cell r="T19">
-            <v>16.71875</v>
+            <v>23.53125</v>
           </cell>
           <cell r="U19">
-            <v>12.78125</v>
+            <v>11.0625</v>
           </cell>
           <cell r="V19">
-            <v>8.53125</v>
+            <v>12.0625</v>
           </cell>
           <cell r="W19">
             <v>0</v>
           </cell>
           <cell r="X19">
-            <v>10.5</v>
+            <v>12.5</v>
           </cell>
         </row>
         <row r="20">
@@ -10061,67 +10109,67 @@
             <v>19</v>
           </cell>
           <cell r="B20" t="str">
-            <v>High Point</v>
+            <v>TCU</v>
           </cell>
           <cell r="C20" t="str">
-            <v>Arkansas</v>
+            <v>Duke</v>
           </cell>
           <cell r="D20">
-            <v>9.7914064574296606</v>
+            <v>12.676356416890858</v>
           </cell>
           <cell r="E20">
-            <v>102.08135263134599</v>
+            <v>101.27537334728432</v>
           </cell>
           <cell r="F20">
-            <v>95.473025683474958</v>
+            <v>97.104848064562987</v>
           </cell>
           <cell r="G20">
-            <v>0.56606463878326996</v>
+            <v>0.50900000000000001</v>
           </cell>
           <cell r="H20">
-            <v>71.407058823529411</v>
+            <v>69.441212121212118</v>
           </cell>
           <cell r="I20">
-            <v>61.882352941176471</v>
+            <v>60.606060606060609</v>
           </cell>
           <cell r="J20">
-            <v>26.794117647058822</v>
+            <v>23.454545454545453</v>
           </cell>
           <cell r="K20">
-            <v>11.617647058823529</v>
+            <v>12.424242424242424</v>
           </cell>
           <cell r="L20">
-            <v>9.3529411764705888</v>
+            <v>10.939393939393939</v>
           </cell>
           <cell r="M20">
             <v>0</v>
           </cell>
           <cell r="N20">
-            <v>19.899076876872613</v>
+            <v>23.054887624413109</v>
           </cell>
           <cell r="O20">
-            <v>101.9693472090823</v>
+            <v>101.57301127857072</v>
           </cell>
           <cell r="P20">
-            <v>97.545722643013036</v>
+            <v>99.414290660558592</v>
           </cell>
           <cell r="Q20">
-            <v>0.56447688564476883</v>
+            <v>0.57213541666666667</v>
           </cell>
           <cell r="R20">
-            <v>72.41</v>
+            <v>66.278787878787867</v>
           </cell>
           <cell r="S20">
-            <v>64.21875</v>
+            <v>58.18181818181818</v>
           </cell>
           <cell r="T20">
-            <v>23.375</v>
+            <v>22.121212121212121</v>
           </cell>
           <cell r="U20">
-            <v>11.0625</v>
+            <v>12.212121212121213</v>
           </cell>
           <cell r="V20">
-            <v>8.96875</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="W20">
             <v>0</v>
@@ -10135,73 +10183,73 @@
             <v>20</v>
           </cell>
           <cell r="B21" t="str">
-            <v>Texas</v>
+            <v>VCU</v>
           </cell>
           <cell r="C21" t="str">
-            <v>Gonzaga</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D21">
-            <v>14.532052109666417</v>
+            <v>10.280535393881047</v>
           </cell>
           <cell r="E21">
-            <v>100.55048907489414</v>
+            <v>99.976592216912124</v>
           </cell>
           <cell r="F21">
-            <v>96.670144874968173</v>
+            <v>99.94980567668172</v>
           </cell>
           <cell r="G21">
-            <v>0.5496777658431794</v>
+            <v>0.54290339989206693</v>
           </cell>
           <cell r="H21">
-            <v>68.81</v>
+            <v>68.818749999999994</v>
           </cell>
           <cell r="I21">
-            <v>58.1875</v>
+            <v>57.90625</v>
           </cell>
           <cell r="J21">
-            <v>26.34375</v>
+            <v>25.9375</v>
           </cell>
           <cell r="K21">
-            <v>12</v>
+            <v>11.3125</v>
           </cell>
           <cell r="L21">
-            <v>11.03125</v>
+            <v>10.8125</v>
           </cell>
           <cell r="M21">
             <v>0</v>
           </cell>
           <cell r="N21">
-            <v>20.959854873623506</v>
+            <v>18.826343007871433</v>
           </cell>
           <cell r="O21">
-            <v>102.65043408841434</v>
+            <v>105.08780903665816</v>
           </cell>
           <cell r="P21">
-            <v>86.043703668873505</v>
+            <v>108.91673393133649</v>
           </cell>
           <cell r="Q21">
-            <v>0.56074766355140182</v>
+            <v>0.5511688311688312</v>
           </cell>
           <cell r="R21">
-            <v>69.724999999999994</v>
+            <v>66.809032258064519</v>
           </cell>
           <cell r="S21">
-            <v>63.53125</v>
+            <v>62.096774193548384</v>
           </cell>
           <cell r="T21">
-            <v>19.6875</v>
+            <v>20.387096774193548</v>
           </cell>
           <cell r="U21">
-            <v>12.03125</v>
+            <v>13.258064516129032</v>
           </cell>
           <cell r="V21">
-            <v>9.5625</v>
+            <v>9</v>
           </cell>
           <cell r="W21">
             <v>0</v>
           </cell>
           <cell r="X21">
-            <v>6.5</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="22">
@@ -10209,73 +10257,73 @@
             <v>21</v>
           </cell>
           <cell r="B22" t="str">
-            <v>Texas Tech</v>
+            <v>Vanderbilt</v>
           </cell>
           <cell r="C22" t="str">
-            <v>Alabama</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D22">
-            <v>17.052374181699321</v>
+            <v>19.334095266215517</v>
           </cell>
           <cell r="E22">
-            <v>100.51882408229335</v>
+            <v>100.88210871874095</v>
           </cell>
           <cell r="F22">
-            <v>104.30065451536628</v>
+            <v>97.473801766777243</v>
           </cell>
           <cell r="G22">
-            <v>0.56166837256908908</v>
+            <v>0.55371690427698572</v>
           </cell>
           <cell r="H22">
-            <v>67.617500000000007</v>
+            <v>70.61</v>
           </cell>
           <cell r="I22">
-            <v>61.0625</v>
+            <v>61.375</v>
           </cell>
           <cell r="J22">
-            <v>16.53125</v>
+            <v>23.6875</v>
           </cell>
           <cell r="K22">
-            <v>11.53125</v>
+            <v>10.8125</v>
           </cell>
           <cell r="L22">
-            <v>10.8125</v>
+            <v>9.625</v>
           </cell>
           <cell r="M22">
             <v>0</v>
           </cell>
           <cell r="N22">
-            <v>19.673613604820769</v>
+            <v>15.82631796216417</v>
           </cell>
           <cell r="O22">
-            <v>102.29455081001471</v>
+            <v>98.25476089716463</v>
           </cell>
           <cell r="P22">
-            <v>103.71887375881523</v>
+            <v>102.35159180352665</v>
           </cell>
           <cell r="Q22">
-            <v>0.55384250474383301</v>
+            <v>0.55440552016985134</v>
           </cell>
           <cell r="R22">
-            <v>74.217500000000001</v>
+            <v>66.883750000000006</v>
           </cell>
           <cell r="S22">
-            <v>65.875</v>
+            <v>58.875</v>
           </cell>
           <cell r="T22">
-            <v>24.5</v>
+            <v>16</v>
           </cell>
           <cell r="U22">
-            <v>12.21875</v>
+            <v>8.78125</v>
           </cell>
           <cell r="V22">
-            <v>9.78125</v>
+            <v>9.75</v>
           </cell>
           <cell r="W22">
             <v>0</v>
           </cell>
           <cell r="X22">
-            <v>1</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="23">
@@ -10283,73 +10331,73 @@
             <v>22</v>
           </cell>
           <cell r="B23" t="str">
-            <v>Tennessee</v>
+            <v>Texas A&amp;M</v>
           </cell>
           <cell r="C23" t="str">
-            <v>Virginia</v>
+            <v>Houston</v>
           </cell>
           <cell r="D23">
-            <v>20.582457175121956</v>
+            <v>13.344745551152522</v>
           </cell>
           <cell r="E23">
-            <v>105.02195491662999</v>
+            <v>101.09664255240216</v>
           </cell>
           <cell r="F23">
-            <v>93.637950339797769</v>
+            <v>98.213295342640578</v>
           </cell>
           <cell r="G23">
-            <v>0.51561725334655428</v>
+            <v>0.54188861985472159</v>
           </cell>
           <cell r="H23">
-            <v>67.170909090909092</v>
+            <v>73.739999999999995</v>
           </cell>
           <cell r="I23">
-            <v>61.121212121212125</v>
+            <v>64.53125</v>
           </cell>
           <cell r="J23">
-            <v>23.666666666666668</v>
+            <v>24.125</v>
           </cell>
           <cell r="K23">
-            <v>16.030303030303031</v>
+            <v>12.25</v>
           </cell>
           <cell r="L23">
-            <v>11.666666666666666</v>
+            <v>10.84375</v>
           </cell>
           <cell r="M23">
             <v>0</v>
           </cell>
           <cell r="N23">
-            <v>12.898930744177012</v>
+            <v>20.901069562815731</v>
           </cell>
           <cell r="O23">
-            <v>102.74660271782574</v>
+            <v>105.43571389837862</v>
           </cell>
           <cell r="P23">
-            <v>105.30602921182151</v>
+            <v>97.084637989347655</v>
           </cell>
           <cell r="Q23">
-            <v>0.54717923115327005</v>
+            <v>0.52154080081094778</v>
           </cell>
           <cell r="R23">
-            <v>67.065454545454543</v>
+            <v>64.762500000000003</v>
           </cell>
           <cell r="S23">
-            <v>60.696969696969695</v>
+            <v>61.65625</v>
           </cell>
           <cell r="T23">
-            <v>20.121212121212121</v>
+            <v>16.71875</v>
           </cell>
           <cell r="U23">
-            <v>13.272727272727273</v>
+            <v>12.78125</v>
           </cell>
           <cell r="V23">
-            <v>10.787878787878787</v>
+            <v>8.53125</v>
           </cell>
           <cell r="W23">
             <v>0</v>
           </cell>
           <cell r="X23">
-            <v>-1</v>
+            <v>10.5</v>
           </cell>
         </row>
         <row r="24">
@@ -10357,73 +10405,73 @@
             <v>23</v>
           </cell>
           <cell r="B24" t="str">
-            <v>Kentucky</v>
+            <v>High Point</v>
           </cell>
           <cell r="C24" t="str">
-            <v>Iowa State</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D24">
-            <v>18.034523649586539</v>
+            <v>9.7914064574296606</v>
           </cell>
           <cell r="E24">
-            <v>101.2517590047062</v>
+            <v>102.08135263134599</v>
           </cell>
           <cell r="F24">
-            <v>98.419793855345077</v>
+            <v>95.473025683474958</v>
           </cell>
           <cell r="G24">
-            <v>0.53111327175498302</v>
+            <v>0.56606463878326996</v>
           </cell>
           <cell r="H24">
-            <v>69.036470588235289</v>
+            <v>71.407058823529411</v>
           </cell>
           <cell r="I24">
-            <v>60.5</v>
+            <v>61.882352941176471</v>
           </cell>
           <cell r="J24">
-            <v>22.676470588235293</v>
+            <v>26.794117647058822</v>
           </cell>
           <cell r="K24">
-            <v>11.941176470588236</v>
+            <v>11.617647058823529</v>
           </cell>
           <cell r="L24">
-            <v>10.5</v>
+            <v>9.3529411764705888</v>
           </cell>
           <cell r="M24">
             <v>0</v>
           </cell>
           <cell r="N24">
-            <v>20.641493911570723</v>
+            <v>19.899076876872613</v>
           </cell>
           <cell r="O24">
-            <v>101.50134460238188</v>
+            <v>101.9693472090823</v>
           </cell>
           <cell r="P24">
-            <v>96.951162965358421</v>
+            <v>97.545722643013036</v>
           </cell>
           <cell r="Q24">
-            <v>0.56497313141182215</v>
+            <v>0.56447688564476883</v>
           </cell>
           <cell r="R24">
-            <v>67.654117647058825</v>
+            <v>72.41</v>
           </cell>
           <cell r="S24">
-            <v>60.205882352941174</v>
+            <v>64.21875</v>
           </cell>
           <cell r="T24">
-            <v>20.470588235294116</v>
+            <v>23.375</v>
           </cell>
           <cell r="U24">
-            <v>11.823529411764707</v>
+            <v>11.0625</v>
           </cell>
           <cell r="V24">
-            <v>10.264705882352942</v>
+            <v>8.96875</v>
           </cell>
           <cell r="W24">
             <v>0</v>
           </cell>
           <cell r="X24">
-            <v>5</v>
+            <v>11.5</v>
           </cell>
         </row>
         <row r="25">
@@ -10431,258 +10479,666 @@
             <v>24</v>
           </cell>
           <cell r="B25" t="str">
+            <v>Texas</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Gonzaga</v>
+          </cell>
+          <cell r="D25">
+            <v>14.532052109666417</v>
+          </cell>
+          <cell r="E25">
+            <v>100.55048907489414</v>
+          </cell>
+          <cell r="F25">
+            <v>96.670144874968173</v>
+          </cell>
+          <cell r="G25">
+            <v>0.5496777658431794</v>
+          </cell>
+          <cell r="H25">
+            <v>68.81</v>
+          </cell>
+          <cell r="I25">
+            <v>58.1875</v>
+          </cell>
+          <cell r="J25">
+            <v>26.34375</v>
+          </cell>
+          <cell r="K25">
+            <v>12</v>
+          </cell>
+          <cell r="L25">
+            <v>11.03125</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>20.959854873623506</v>
+          </cell>
+          <cell r="O25">
+            <v>102.65043408841434</v>
+          </cell>
+          <cell r="P25">
+            <v>86.043703668873505</v>
+          </cell>
+          <cell r="Q25">
+            <v>0.56074766355140182</v>
+          </cell>
+          <cell r="R25">
+            <v>69.724999999999994</v>
+          </cell>
+          <cell r="S25">
+            <v>63.53125</v>
+          </cell>
+          <cell r="T25">
+            <v>19.6875</v>
+          </cell>
+          <cell r="U25">
+            <v>12.03125</v>
+          </cell>
+          <cell r="V25">
+            <v>9.5625</v>
+          </cell>
+          <cell r="W25">
+            <v>0</v>
+          </cell>
+          <cell r="X25">
+            <v>6.5</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>Texas Tech</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>Alabama</v>
+          </cell>
+          <cell r="D26">
+            <v>17.052374181699321</v>
+          </cell>
+          <cell r="E26">
+            <v>100.51882408229335</v>
+          </cell>
+          <cell r="F26">
+            <v>104.30065451536628</v>
+          </cell>
+          <cell r="G26">
+            <v>0.56166837256908908</v>
+          </cell>
+          <cell r="H26">
+            <v>67.617500000000007</v>
+          </cell>
+          <cell r="I26">
+            <v>61.0625</v>
+          </cell>
+          <cell r="J26">
+            <v>16.53125</v>
+          </cell>
+          <cell r="K26">
+            <v>11.53125</v>
+          </cell>
+          <cell r="L26">
+            <v>10.8125</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>19.673613604820769</v>
+          </cell>
+          <cell r="O26">
+            <v>102.29455081001471</v>
+          </cell>
+          <cell r="P26">
+            <v>103.71887375881523</v>
+          </cell>
+          <cell r="Q26">
+            <v>0.55384250474383301</v>
+          </cell>
+          <cell r="R26">
+            <v>74.217500000000001</v>
+          </cell>
+          <cell r="S26">
+            <v>65.875</v>
+          </cell>
+          <cell r="T26">
+            <v>24.5</v>
+          </cell>
+          <cell r="U26">
+            <v>12.21875</v>
+          </cell>
+          <cell r="V26">
+            <v>9.78125</v>
+          </cell>
+          <cell r="W26">
+            <v>0</v>
+          </cell>
+          <cell r="X26">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Iowa</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>Florida</v>
+          </cell>
+          <cell r="D27">
+            <v>15.51511812576733</v>
+          </cell>
+          <cell r="E27">
+            <v>98.238539943433466</v>
+          </cell>
+          <cell r="F27">
+            <v>93.168875634820807</v>
+          </cell>
+          <cell r="G27">
+            <v>0.56555993247045577</v>
+          </cell>
+          <cell r="H27">
+            <v>62.900606060606066</v>
+          </cell>
+          <cell r="I27">
+            <v>53.848484848484851</v>
+          </cell>
+          <cell r="J27">
+            <v>18.575757575757574</v>
+          </cell>
+          <cell r="K27">
+            <v>8.8181818181818183</v>
+          </cell>
+          <cell r="L27">
+            <v>9.6969696969696972</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>22.650454216704585</v>
+          </cell>
+          <cell r="O27">
+            <v>104.38676700269771</v>
+          </cell>
+          <cell r="P27">
+            <v>99.448258680413886</v>
+          </cell>
+          <cell r="Q27">
+            <v>0.53652636671504594</v>
+          </cell>
+          <cell r="R27">
+            <v>71.564999999999998</v>
+          </cell>
+          <cell r="S27">
+            <v>64.59375</v>
+          </cell>
+          <cell r="T27">
+            <v>25.21875</v>
+          </cell>
+          <cell r="U27">
+            <v>15.96875</v>
+          </cell>
+          <cell r="V27">
+            <v>11.84375</v>
+          </cell>
+          <cell r="W27">
+            <v>0</v>
+          </cell>
+          <cell r="X27">
+            <v>10.5</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>UCLA</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>Uconn</v>
+          </cell>
+          <cell r="D28">
+            <v>15.943406980069799</v>
+          </cell>
+          <cell r="E28">
+            <v>100.85863980873899</v>
+          </cell>
+          <cell r="F28">
+            <v>91.898292422931632</v>
+          </cell>
+          <cell r="G28">
+            <v>0.54047742605085625</v>
+          </cell>
+          <cell r="H28">
+            <v>65.963636363636368</v>
+          </cell>
+          <cell r="I28">
+            <v>58.393939393939391</v>
+          </cell>
+          <cell r="J28">
+            <v>19.545454545454547</v>
+          </cell>
+          <cell r="K28">
+            <v>10</v>
+          </cell>
+          <cell r="L28">
+            <v>8.9696969696969688</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>18.120431537245491</v>
+          </cell>
+          <cell r="O28">
+            <v>100.0952772073922</v>
+          </cell>
+          <cell r="P28">
+            <v>94.261774983054991</v>
+          </cell>
+          <cell r="Q28">
+            <v>0.55882352941176472</v>
+          </cell>
+          <cell r="R28">
+            <v>66.089696969696973</v>
+          </cell>
+          <cell r="S28">
+            <v>58.727272727272727</v>
+          </cell>
+          <cell r="T28">
+            <v>17.696969696969695</v>
+          </cell>
+          <cell r="U28">
+            <v>11.454545454545455</v>
+          </cell>
+          <cell r="V28">
+            <v>11.030303030303031</v>
+          </cell>
+          <cell r="W28">
+            <v>0</v>
+          </cell>
+          <cell r="X28">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Tennessee</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>Virginia</v>
+          </cell>
+          <cell r="D29">
+            <v>20.582457175121956</v>
+          </cell>
+          <cell r="E29">
+            <v>105.02195491662999</v>
+          </cell>
+          <cell r="F29">
+            <v>93.637950339797769</v>
+          </cell>
+          <cell r="G29">
+            <v>0.51561725334655428</v>
+          </cell>
+          <cell r="H29">
+            <v>67.170909090909092</v>
+          </cell>
+          <cell r="I29">
+            <v>61.121212121212125</v>
+          </cell>
+          <cell r="J29">
+            <v>23.666666666666668</v>
+          </cell>
+          <cell r="K29">
+            <v>16.030303030303031</v>
+          </cell>
+          <cell r="L29">
+            <v>11.666666666666666</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>12.898930744177012</v>
+          </cell>
+          <cell r="O29">
+            <v>102.74660271782574</v>
+          </cell>
+          <cell r="P29">
+            <v>105.30602921182151</v>
+          </cell>
+          <cell r="Q29">
+            <v>0.54717923115327005</v>
+          </cell>
+          <cell r="R29">
+            <v>67.065454545454543</v>
+          </cell>
+          <cell r="S29">
+            <v>60.696969696969695</v>
+          </cell>
+          <cell r="T29">
+            <v>20.121212121212121</v>
+          </cell>
+          <cell r="U29">
+            <v>13.272727272727273</v>
+          </cell>
+          <cell r="V29">
+            <v>10.787878787878787</v>
+          </cell>
+          <cell r="W29">
+            <v>0</v>
+          </cell>
+          <cell r="X29">
+            <v>-1</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Miami</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>Purdue</v>
+          </cell>
+          <cell r="D30">
+            <v>12.238890418004498</v>
+          </cell>
+          <cell r="E30">
+            <v>100.74202898550723</v>
+          </cell>
+          <cell r="F30">
+            <v>98.35968575523485</v>
+          </cell>
+          <cell r="G30">
+            <v>0.55597771023302933</v>
+          </cell>
+          <cell r="H30">
+            <v>68.654545454545456</v>
+          </cell>
+          <cell r="I30">
+            <v>59.81818181818182</v>
+          </cell>
+          <cell r="J30">
+            <v>22.424242424242426</v>
+          </cell>
+          <cell r="K30">
+            <v>12.242424242424242</v>
+          </cell>
+          <cell r="L30">
+            <v>11.212121212121213</v>
+          </cell>
+          <cell r="M30">
+            <v>0</v>
+          </cell>
+          <cell r="N30">
+            <v>20.933350618351088</v>
+          </cell>
+          <cell r="O30">
+            <v>102.749921687376</v>
+          </cell>
+          <cell r="P30">
+            <v>101.56518525976452</v>
+          </cell>
+          <cell r="Q30">
+            <v>0.5771558245083207</v>
+          </cell>
+          <cell r="R30">
+            <v>65.197575757575763</v>
+          </cell>
+          <cell r="S30">
+            <v>60.090909090909093</v>
+          </cell>
+          <cell r="T30">
+            <v>16.90909090909091</v>
+          </cell>
+          <cell r="U30">
+            <v>11.363636363636363</v>
+          </cell>
+          <cell r="V30">
+            <v>9.0303030303030312</v>
+          </cell>
+          <cell r="W30">
+            <v>0</v>
+          </cell>
+          <cell r="X30">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Kentucky</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>Iowa State</v>
+          </cell>
+          <cell r="D31">
+            <v>18.034523649586539</v>
+          </cell>
+          <cell r="E31">
+            <v>101.2517590047062</v>
+          </cell>
+          <cell r="F31">
+            <v>98.419793855345077</v>
+          </cell>
+          <cell r="G31">
+            <v>0.53111327175498302</v>
+          </cell>
+          <cell r="H31">
+            <v>69.036470588235289</v>
+          </cell>
+          <cell r="I31">
+            <v>60.5</v>
+          </cell>
+          <cell r="J31">
+            <v>22.676470588235293</v>
+          </cell>
+          <cell r="K31">
+            <v>11.941176470588236</v>
+          </cell>
+          <cell r="L31">
+            <v>10.5</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+          <cell r="N31">
+            <v>20.641493911570723</v>
+          </cell>
+          <cell r="O31">
+            <v>101.50134460238188</v>
+          </cell>
+          <cell r="P31">
+            <v>96.951162965358421</v>
+          </cell>
+          <cell r="Q31">
+            <v>0.56497313141182215</v>
+          </cell>
+          <cell r="R31">
+            <v>67.654117647058825</v>
+          </cell>
+          <cell r="S31">
+            <v>60.205882352941174</v>
+          </cell>
+          <cell r="T31">
+            <v>20.470588235294116</v>
+          </cell>
+          <cell r="U31">
+            <v>11.823529411764707</v>
+          </cell>
+          <cell r="V31">
+            <v>10.264705882352942</v>
+          </cell>
+          <cell r="W31">
+            <v>0</v>
+          </cell>
+          <cell r="X31">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>St. John's</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>Kansas</v>
+          </cell>
+          <cell r="D32">
+            <v>15.123966744544841</v>
+          </cell>
+          <cell r="E32">
+            <v>102.62076624097725</v>
+          </cell>
+          <cell r="F32">
+            <v>99.067983608660882</v>
+          </cell>
+          <cell r="G32">
+            <v>0.50957290132547861</v>
+          </cell>
+          <cell r="H32">
+            <v>70.527272727272731</v>
+          </cell>
+          <cell r="I32">
+            <v>61.727272727272727</v>
+          </cell>
+          <cell r="J32">
+            <v>26.060606060606062</v>
+          </cell>
+          <cell r="K32">
+            <v>13.242424242424242</v>
+          </cell>
+          <cell r="L32">
+            <v>10.575757575757576</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+          <cell r="N32">
+            <v>16.809475334579385</v>
+          </cell>
+          <cell r="O32">
+            <v>98.782531105933685</v>
+          </cell>
+          <cell r="P32">
+            <v>105.39233290147665</v>
+          </cell>
+          <cell r="Q32">
+            <v>0.51565708418891165</v>
+          </cell>
+          <cell r="R32">
+            <v>68.042424242424246</v>
+          </cell>
+          <cell r="S32">
+            <v>59.030303030303031</v>
+          </cell>
+          <cell r="T32">
+            <v>19.242424242424242</v>
+          </cell>
+          <cell r="U32">
+            <v>10.121212121212121</v>
+          </cell>
+          <cell r="V32">
+            <v>10.666666666666666</v>
+          </cell>
+          <cell r="W32">
+            <v>0</v>
+          </cell>
+          <cell r="X32">
+            <v>-3.5</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+          <cell r="B33" t="str">
             <v>Utah State</v>
           </cell>
-          <cell r="C25" t="str">
+          <cell r="C33" t="str">
             <v>Arizona</v>
           </cell>
-          <cell r="D25">
+          <cell r="D33">
             <v>16.287809545840613</v>
           </cell>
-          <cell r="E25">
+          <cell r="E33">
             <v>99.539689712306071</v>
           </cell>
-          <cell r="F25">
+          <cell r="F33">
             <v>89.1227776403734</v>
           </cell>
-          <cell r="G25">
+          <cell r="G33">
             <v>0.5741935483870968</v>
           </cell>
-          <cell r="H25">
+          <cell r="H33">
             <v>67.972499999999997</v>
           </cell>
-          <cell r="I25">
+          <cell r="I33">
             <v>58.125</v>
           </cell>
-          <cell r="J25">
+          <cell r="J33">
             <v>22.59375</v>
           </cell>
-          <cell r="K25">
+          <cell r="K33">
             <v>10.65625</v>
           </cell>
-          <cell r="L25">
+          <cell r="L33">
             <v>10.5625</v>
           </cell>
-          <cell r="M25">
-            <v>0</v>
-          </cell>
-          <cell r="N25">
+          <cell r="M33">
+            <v>0</v>
+          </cell>
+          <cell r="N33">
             <v>23.687310951598352</v>
           </cell>
-          <cell r="O25">
+          <cell r="O33">
             <v>101.76807841686704</v>
           </cell>
-          <cell r="P25">
+          <cell r="P33">
             <v>98.493332637771204</v>
           </cell>
-          <cell r="Q25">
+          <cell r="Q33">
             <v>0.55109126984126988</v>
           </cell>
-          <cell r="R25">
+          <cell r="R33">
             <v>70.587878787878793</v>
           </cell>
-          <cell r="S25">
+          <cell r="S33">
             <v>61.090909090909093</v>
           </cell>
-          <cell r="T25">
+          <cell r="T33">
             <v>26.060606060606062</v>
           </cell>
-          <cell r="U25">
+          <cell r="U33">
             <v>12.878787878787879</v>
           </cell>
-          <cell r="V25">
+          <cell r="V33">
             <v>10.909090909090908</v>
           </cell>
-          <cell r="W25">
-            <v>0</v>
-          </cell>
-          <cell r="X25">
+          <cell r="W33">
+            <v>0</v>
+          </cell>
+          <cell r="X33">
             <v>11.5</v>
           </cell>
-        </row>
-        <row r="26">
-          <cell r="D26"/>
-          <cell r="E26"/>
-          <cell r="F26"/>
-          <cell r="G26"/>
-          <cell r="H26"/>
-          <cell r="I26"/>
-          <cell r="J26"/>
-          <cell r="K26"/>
-          <cell r="L26"/>
-          <cell r="M26"/>
-          <cell r="N26"/>
-          <cell r="O26"/>
-          <cell r="P26"/>
-          <cell r="Q26"/>
-          <cell r="R26"/>
-          <cell r="S26"/>
-          <cell r="T26"/>
-          <cell r="U26"/>
-          <cell r="V26"/>
-          <cell r="W26"/>
-          <cell r="X26"/>
-        </row>
-        <row r="27">
-          <cell r="D27"/>
-          <cell r="E27"/>
-          <cell r="F27"/>
-          <cell r="G27"/>
-          <cell r="H27"/>
-          <cell r="I27"/>
-          <cell r="J27"/>
-          <cell r="K27"/>
-          <cell r="L27"/>
-          <cell r="M27"/>
-          <cell r="N27"/>
-          <cell r="O27"/>
-          <cell r="P27"/>
-          <cell r="Q27"/>
-          <cell r="R27"/>
-          <cell r="S27"/>
-          <cell r="T27"/>
-          <cell r="U27"/>
-          <cell r="V27"/>
-          <cell r="W27"/>
-          <cell r="X27"/>
-        </row>
-        <row r="28">
-          <cell r="D28"/>
-          <cell r="E28"/>
-          <cell r="F28"/>
-          <cell r="G28"/>
-          <cell r="H28"/>
-          <cell r="I28"/>
-          <cell r="J28"/>
-          <cell r="K28"/>
-          <cell r="L28"/>
-          <cell r="M28"/>
-          <cell r="N28"/>
-          <cell r="O28"/>
-          <cell r="P28"/>
-          <cell r="Q28"/>
-          <cell r="R28"/>
-          <cell r="S28"/>
-          <cell r="T28"/>
-          <cell r="U28"/>
-          <cell r="V28"/>
-          <cell r="W28"/>
-          <cell r="X28"/>
-        </row>
-        <row r="29">
-          <cell r="D29"/>
-          <cell r="E29"/>
-          <cell r="F29"/>
-          <cell r="G29"/>
-          <cell r="H29"/>
-          <cell r="I29"/>
-          <cell r="J29"/>
-          <cell r="K29"/>
-          <cell r="L29"/>
-          <cell r="M29"/>
-          <cell r="N29"/>
-          <cell r="O29"/>
-          <cell r="P29"/>
-          <cell r="Q29"/>
-          <cell r="R29"/>
-          <cell r="S29"/>
-          <cell r="T29"/>
-          <cell r="U29"/>
-          <cell r="V29"/>
-          <cell r="W29"/>
-          <cell r="X29"/>
-        </row>
-        <row r="30">
-          <cell r="D30"/>
-          <cell r="E30"/>
-          <cell r="F30"/>
-          <cell r="G30"/>
-          <cell r="H30"/>
-          <cell r="I30"/>
-          <cell r="J30"/>
-          <cell r="K30"/>
-          <cell r="L30"/>
-          <cell r="M30"/>
-          <cell r="N30"/>
-          <cell r="O30"/>
-          <cell r="P30"/>
-          <cell r="Q30"/>
-          <cell r="R30"/>
-          <cell r="S30"/>
-          <cell r="T30"/>
-          <cell r="U30"/>
-          <cell r="V30"/>
-          <cell r="W30"/>
-          <cell r="X30"/>
-        </row>
-        <row r="31">
-          <cell r="D31"/>
-          <cell r="E31"/>
-          <cell r="F31"/>
-          <cell r="G31"/>
-          <cell r="H31"/>
-          <cell r="I31"/>
-          <cell r="J31"/>
-          <cell r="K31"/>
-          <cell r="L31"/>
-          <cell r="M31"/>
-          <cell r="N31"/>
-          <cell r="O31"/>
-          <cell r="P31"/>
-          <cell r="Q31"/>
-          <cell r="R31"/>
-          <cell r="S31"/>
-          <cell r="T31"/>
-          <cell r="U31"/>
-          <cell r="V31"/>
-          <cell r="W31"/>
-          <cell r="X31"/>
-        </row>
-        <row r="32">
-          <cell r="D32"/>
-          <cell r="E32"/>
-          <cell r="F32"/>
-          <cell r="G32"/>
-          <cell r="H32"/>
-          <cell r="I32"/>
-          <cell r="J32"/>
-          <cell r="K32"/>
-          <cell r="L32"/>
-          <cell r="M32"/>
-          <cell r="N32"/>
-          <cell r="O32"/>
-          <cell r="P32"/>
-          <cell r="Q32"/>
-          <cell r="R32"/>
-          <cell r="S32"/>
-          <cell r="T32"/>
-          <cell r="U32"/>
-          <cell r="V32"/>
-          <cell r="W32"/>
-          <cell r="X32"/>
-        </row>
-        <row r="33">
-          <cell r="D33"/>
-          <cell r="E33"/>
-          <cell r="F33"/>
-          <cell r="G33"/>
-          <cell r="H33"/>
-          <cell r="I33"/>
-          <cell r="J33"/>
-          <cell r="K33"/>
-          <cell r="L33"/>
-          <cell r="M33"/>
-          <cell r="N33"/>
-          <cell r="O33"/>
-          <cell r="P33"/>
-          <cell r="Q33"/>
-          <cell r="R33"/>
-          <cell r="S33"/>
-          <cell r="T33"/>
-          <cell r="U33"/>
-          <cell r="V33"/>
-          <cell r="W33"/>
-          <cell r="X33"/>
         </row>
         <row r="34">
           <cell r="D34"/>
@@ -22924,11 +23380,11 @@
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.2987974976589882</v>
+        <v>7.6237974976589857</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -22940,7 +23396,7 @@
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.1773721975554827E-2</v>
+        <v>1.9720872128491079E-2</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>443</v>
@@ -23015,11 +23471,11 @@
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>16.481515841644931</v>
+        <v>16.156515841644939</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -23031,7 +23487,7 @@
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.4672078293523353E-2</v>
+        <v>3.6432217816580577E-2</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>443</v>
@@ -23059,15 +23515,15 @@
       </c>
       <c r="E5" s="5">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>13.813979689921981</v>
+        <v>14.138979689921969</v>
       </c>
       <c r="F5" s="5">
         <f>-VLOOKUP(A5,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.59272854171055378</v>
+        <v>0.59272854171055356</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23075,7 +23531,7 @@
       </c>
       <c r="I5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.5112276414578225E-2</v>
+        <v>2.32080108365606E-2</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>443</v>
@@ -23147,7 +23603,7 @@
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>12.490512577712639</v>
+        <v>12.49051257771263</v>
       </c>
       <c r="F7" s="5">
         <f>-VLOOKUP(A7,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -23155,7 +23611,7 @@
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.50131716872622822</v>
+        <v>0.50131716872622811</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23207,7 +23663,7 @@
       </c>
       <c r="I8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.0773826597078271E-2</v>
+        <v>2.0773826597078215E-2</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>443</v>
@@ -23243,7 +23699,7 @@
       </c>
       <c r="G9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.41516446029663601</v>
+        <v>0.41516446029663578</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23307,46 +23763,46 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6" t="str">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Tennessee</v>
+        <v>Florida</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Virginia</v>
+        <v>Iowa</v>
       </c>
       <c r="D11" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>Tennessee</v>
+        <v>Florida</v>
       </c>
       <c r="E11" s="5">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>6.3504265210794983</v>
+        <v>11.194715824766851</v>
       </c>
       <c r="F11" s="5">
         <f>-VLOOKUP(A11,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="G11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.503917783931362</v>
+        <v>0.39463016781725752</v>
       </c>
       <c r="H11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>5.7998893446444849E-2</v>
+        <v>0</v>
       </c>
       <c r="I11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.9999371276389128E-2</v>
+        <v>-3.0989295923022899E-3</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>444</v>
       </c>
       <c r="K11" s="9">
         <f t="shared" si="3"/>
-        <v>0.86998340169667276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -23355,27 +23811,27 @@
       </c>
       <c r="B12" s="6" t="str">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Iowa State</v>
+        <v>Uconn</v>
       </c>
       <c r="C12" s="6" t="str">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Kentucky</v>
+        <v>UCLA</v>
       </c>
       <c r="D12" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>Iowa State</v>
+        <v>Uconn</v>
       </c>
       <c r="E12" s="5">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.1011751940087526</v>
+        <v>5.391134817228437</v>
       </c>
       <c r="F12" s="5">
         <f>-VLOOKUP(A12,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="7">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.34931589557310277</v>
+        <v>0.25478768357222192</v>
       </c>
       <c r="H12" s="7">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23383,7 +23839,7 @@
       </c>
       <c r="I12" s="7">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.3569223993972977E-2</v>
+        <v>5.1704048443900752E-3</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>443</v>
@@ -23395,97 +23851,225 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6" t="str">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Arizona</v>
+        <v>Tennessee</v>
       </c>
       <c r="C13" s="6" t="str">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Utah State</v>
+        <v>Virginia</v>
       </c>
       <c r="D13" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>Arizona</v>
+        <v>Tennessee</v>
       </c>
       <c r="E13" s="5">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>12.03916810204351</v>
+        <v>6.3504265210794983</v>
       </c>
       <c r="F13" s="5">
         <f>-VLOOKUP(A13,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.41142205261584602</v>
+        <v>0.503917783931362</v>
       </c>
       <c r="H13" s="7">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
+        <v>5.7998893446444849E-2</v>
       </c>
       <c r="I13" s="7">
         <f>VLOOKUP(A13,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>-4.9486061792907978E-3</v>
+        <v>4.9999371276389128E-2</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K13" s="9">
         <f t="shared" si="3"/>
+        <v>0.86998340169667276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="str">
+        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Purdue</v>
+      </c>
+      <c r="C14" s="6" t="str">
+        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Miami</v>
+      </c>
+      <c r="D14" s="6" t="str">
+        <f t="shared" ref="D14:D17" si="4">B14</f>
+        <v>Purdue</v>
+      </c>
+      <c r="E14" s="5">
+        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>12.5746195342281</v>
+      </c>
+      <c r="F14" s="5">
+        <f>-VLOOKUP(A14,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>7.5</v>
+      </c>
+      <c r="G14" s="7">
+        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.63571360517770981</v>
+      </c>
+      <c r="H14" s="7">
+        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>4.4882546254626871E-2</v>
+      </c>
+      <c r="I14" s="7">
+        <f>VLOOKUP(A14,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>4.2546901281038024E-2</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="K14" s="9">
+        <f t="shared" ref="K14:K17" si="5">IF(J14="Yes",(H14*1500)/100,0)</f>
+        <v>0.67323819381940309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="str">
+        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Iowa State</v>
+      </c>
+      <c r="C15" s="6" t="str">
+        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Kentucky</v>
+      </c>
+      <c r="D15" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>Iowa State</v>
+      </c>
+      <c r="E15" s="5">
+        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>7.1011751940087526</v>
+      </c>
+      <c r="F15" s="5">
+        <f>-VLOOKUP(A15,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G15" s="7">
+        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.34931589557310277</v>
+      </c>
+      <c r="H15" s="7">
+        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,7,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
+      <c r="I15" s="7">
+        <f>VLOOKUP(A15,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>1.3569223993972977E-2</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>31</v>
+      </c>
+      <c r="B16" s="6" t="str">
+        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>St. John's</v>
+      </c>
+      <c r="C16" s="6" t="str">
+        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Kansas</v>
+      </c>
+      <c r="D16" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>St. John's</v>
+      </c>
+      <c r="E16" s="5">
+        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>3.1590318805399149</v>
+      </c>
+      <c r="F16" s="5">
+        <f>-VLOOKUP(A16,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>3.5</v>
+      </c>
+      <c r="G16" s="7">
+        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>8.1123382590810478E-2</v>
+      </c>
+      <c r="H16" s="7">
+        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="7">
+        <f>VLOOKUP(A16,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>-7.3063318402789975E-3</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="str">
+        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Arizona</v>
+      </c>
+      <c r="C17" s="6" t="str">
+        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Utah State</v>
+      </c>
+      <c r="D17" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>Arizona</v>
+      </c>
+      <c r="E17" s="5">
+        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>12.03916810204351</v>
+      </c>
+      <c r="F17" s="5">
+        <f>-VLOOKUP(A17,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>11.5</v>
+      </c>
+      <c r="G17" s="7">
+        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.41142205261584602</v>
+      </c>
+      <c r="H17" s="7">
+        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <f>VLOOKUP(A17,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>-4.9486061792907978E-3</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -23497,7 +24081,7 @@
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -23509,7 +24093,7 @@
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -23521,7 +24105,7 @@
       <c r="J20" s="8"/>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -23533,7 +24117,7 @@
       <c r="J21" s="8"/>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -23545,7 +24129,7 @@
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -23557,7 +24141,7 @@
       <c r="J23" s="8"/>
       <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -23569,7 +24153,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -23581,7 +24165,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -23593,7 +24177,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -23605,7 +24189,7 @@
       <c r="J27" s="8"/>
       <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -23617,7 +24201,7 @@
       <c r="J28" s="8"/>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -23629,7 +24213,7 @@
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -23641,7 +24225,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -23653,7 +24237,7 @@
       <c r="J31" s="8"/>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -31372,19 +31956,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.7752</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="D2">
-        <v>0.56345000000000001</v>
+        <v>0.54344999999999999</v>
       </c>
       <c r="E2">
-        <v>0.36745</v>
+        <v>0.35235</v>
       </c>
       <c r="F2">
-        <v>0.21435000000000001</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1188</v>
+        <v>0.11915000000000001</v>
       </c>
       <c r="H2" t="s">
         <v>384</v>
@@ -31401,22 +31985,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.96835000000000004</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.73114999999999997</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="D3">
-        <v>0.48599999999999999</v>
+        <v>0.46884999999999999</v>
       </c>
       <c r="E3">
-        <v>0.30630000000000002</v>
+        <v>0.2888</v>
       </c>
       <c r="F3">
-        <v>0.18210000000000001</v>
+        <v>0.1704</v>
       </c>
       <c r="G3">
-        <v>0.1114</v>
+        <v>0.10445</v>
       </c>
       <c r="H3" t="s">
         <v>383</v>
@@ -31436,19 +32020,19 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.77395000000000003</v>
+        <v>0.77080000000000004</v>
       </c>
       <c r="D4">
-        <v>0.50795000000000001</v>
+        <v>0.48220000000000002</v>
       </c>
       <c r="E4">
-        <v>0.31414999999999998</v>
+        <v>0.29485</v>
       </c>
       <c r="F4">
-        <v>0.18015</v>
+        <v>0.16830000000000001</v>
       </c>
       <c r="G4">
-        <v>0.11</v>
+        <v>9.9250000000000005E-2</v>
       </c>
       <c r="H4" t="s">
         <v>382</v>
@@ -31465,22 +32049,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.98219999999999996</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0.72609999999999997</v>
+        <v>0.7016</v>
       </c>
       <c r="D5">
-        <v>0.45924999999999999</v>
+        <v>0.44555</v>
       </c>
       <c r="E5">
-        <v>0.28594999999999998</v>
+        <v>0.27579999999999999</v>
       </c>
       <c r="F5">
-        <v>0.16994999999999999</v>
+        <v>0.16025</v>
       </c>
       <c r="G5">
-        <v>9.3850000000000003E-2</v>
+        <v>8.5599999999999996E-2</v>
       </c>
       <c r="H5" t="s">
         <v>385</v>
@@ -31500,19 +32084,19 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>0.71684999999999999</v>
+        <v>0.70814999999999995</v>
       </c>
       <c r="D6">
-        <v>0.44435000000000002</v>
+        <v>0.44405</v>
       </c>
       <c r="E6">
-        <v>0.23180000000000001</v>
+        <v>0.23455000000000001</v>
       </c>
       <c r="F6">
-        <v>0.125</v>
+        <v>0.12825</v>
       </c>
       <c r="G6">
-        <v>6.3250000000000001E-2</v>
+        <v>6.515E-2</v>
       </c>
       <c r="H6" t="s">
         <v>385</v>
@@ -31526,194 +32110,194 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>0.68510000000000004</v>
+        <v>0.73945000000000005</v>
       </c>
       <c r="D7">
-        <v>0.39145000000000002</v>
+        <v>0.40915000000000001</v>
       </c>
       <c r="E7">
-        <v>0.19384999999999999</v>
+        <v>0.20449999999999999</v>
       </c>
       <c r="F7">
-        <v>0.1008</v>
+        <v>0.1053</v>
       </c>
       <c r="G7">
-        <v>5.355E-2</v>
+        <v>5.5050000000000002E-2</v>
       </c>
       <c r="H7" t="s">
         <v>383</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>20.95985487362351</v>
+        <v>20.933350618351088</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>0.94215000000000004</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0.69989999999999997</v>
+        <v>0.68059999999999998</v>
       </c>
       <c r="D8">
-        <v>0.38795000000000002</v>
+        <v>0.38345000000000001</v>
       </c>
       <c r="E8">
-        <v>0.19655</v>
+        <v>0.19395000000000001</v>
       </c>
       <c r="F8">
-        <v>0.10085</v>
+        <v>0.10015</v>
       </c>
       <c r="G8">
-        <v>0.05</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="H8" t="s">
         <v>383</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>20.933350618351088</v>
+        <v>20.95985487362351</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>0.77595000000000003</v>
+        <v>0.71745000000000003</v>
       </c>
       <c r="D9">
-        <v>0.35199999999999998</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="E9">
-        <v>0.18149999999999999</v>
+        <v>0.18584999999999999</v>
       </c>
       <c r="F9">
-        <v>9.0749999999999997E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="G9">
-        <v>4.5150000000000003E-2</v>
+        <v>4.8300000000000003E-2</v>
       </c>
       <c r="H9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>19.899076876872609</v>
+        <v>20.582457175121959</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>0.91315000000000002</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.5484</v>
+        <v>0.76895000000000002</v>
       </c>
       <c r="D10">
-        <v>0.33679999999999999</v>
+        <v>0.34825</v>
       </c>
       <c r="E10">
-        <v>0.17115</v>
+        <v>0.17760000000000001</v>
       </c>
       <c r="F10">
-        <v>8.4250000000000005E-2</v>
+        <v>8.7099999999999997E-2</v>
       </c>
       <c r="G10">
-        <v>4.3799999999999999E-2</v>
+        <v>4.2950000000000002E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>20.64149391157072</v>
+        <v>19.899076876872609</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.6018</v>
+        <v>0.57520000000000004</v>
       </c>
       <c r="D11">
-        <v>0.36314999999999997</v>
+        <v>0.32435000000000003</v>
       </c>
       <c r="E11">
-        <v>0.18440000000000001</v>
+        <v>0.16170000000000001</v>
       </c>
       <c r="F11">
-        <v>9.4049999999999995E-2</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="G11">
-        <v>4.2549999999999998E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="H11" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>19.982154388171558</v>
+        <v>20.64149391157072</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12">
-        <v>0.77900000000000003</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.57984999999999998</v>
+        <v>0.59484999999999999</v>
       </c>
       <c r="D12">
-        <v>0.31735000000000002</v>
+        <v>0.34484999999999999</v>
       </c>
       <c r="E12">
-        <v>0.1603</v>
+        <v>0.17674999999999999</v>
       </c>
       <c r="F12">
-        <v>7.7600000000000002E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="G12">
-        <v>3.8899999999999997E-2</v>
+        <v>4.095E-2</v>
       </c>
       <c r="H12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>20.582457175121959</v>
+        <v>19.982154388171558</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -31724,19 +32308,19 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>0.73540000000000005</v>
+        <v>0.73275000000000001</v>
       </c>
       <c r="D13">
-        <v>0.36675000000000002</v>
+        <v>0.36275000000000002</v>
       </c>
       <c r="E13">
-        <v>0.17235</v>
+        <v>0.16664999999999999</v>
       </c>
       <c r="F13">
-        <v>8.3099999999999993E-2</v>
+        <v>7.8600000000000003E-2</v>
       </c>
       <c r="G13">
-        <v>3.6249999999999998E-2</v>
+        <v>3.4799999999999998E-2</v>
       </c>
       <c r="H13" t="s">
         <v>385</v>
@@ -31750,66 +32334,66 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>0.87385000000000002</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>0.55259999999999998</v>
+        <v>0.59504999999999997</v>
       </c>
       <c r="D14">
-        <v>0.25640000000000002</v>
+        <v>0.27705000000000002</v>
       </c>
       <c r="E14">
-        <v>0.13675000000000001</v>
+        <v>0.14660000000000001</v>
       </c>
       <c r="F14">
-        <v>6.2449999999999999E-2</v>
+        <v>7.4300000000000005E-2</v>
       </c>
       <c r="G14">
-        <v>3.1800000000000002E-2</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="H14" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>19.673613604820769</v>
+        <v>19.33409526621552</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>0.60494999999999999</v>
+        <v>0.57769999999999999</v>
       </c>
       <c r="D15">
-        <v>0.28505000000000003</v>
+        <v>0.26769999999999999</v>
       </c>
       <c r="E15">
-        <v>0.1489</v>
+        <v>0.1384</v>
       </c>
       <c r="F15">
-        <v>7.2099999999999997E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
       <c r="G15">
-        <v>3.1600000000000003E-2</v>
+        <v>3.175E-2</v>
       </c>
       <c r="H15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>19.33409526621552</v>
+        <v>19.673613604820769</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -31817,22 +32401,22 @@
         <v>386</v>
       </c>
       <c r="B16">
-        <v>0.89975000000000005</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0.54085000000000005</v>
+        <v>0.56415000000000004</v>
       </c>
       <c r="D16">
-        <v>0.25785000000000002</v>
+        <v>0.27405000000000002</v>
       </c>
       <c r="E16">
-        <v>0.1166</v>
+        <v>0.12705</v>
       </c>
       <c r="F16">
-        <v>5.3400000000000003E-2</v>
+        <v>5.6349999999999997E-2</v>
       </c>
       <c r="G16">
-        <v>2.12E-2</v>
+        <v>2.3349999999999999E-2</v>
       </c>
       <c r="H16" t="s">
         <v>384</v>
@@ -31846,130 +32430,130 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17">
-        <v>0.80815000000000003</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0.49080000000000001</v>
+        <v>0.42480000000000001</v>
       </c>
       <c r="D17">
-        <v>0.19114999999999999</v>
+        <v>0.20985000000000001</v>
       </c>
       <c r="E17">
-        <v>8.8400000000000006E-2</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="F17">
-        <v>3.705E-2</v>
+        <v>4.0250000000000001E-2</v>
       </c>
       <c r="G17">
-        <v>1.37E-2</v>
+        <v>1.7850000000000001E-2</v>
       </c>
       <c r="H17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>16.809475334579389</v>
+        <v>18.034523649586539</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>0.3982</v>
+        <v>0.54944999999999999</v>
       </c>
       <c r="D18">
-        <v>0.20280000000000001</v>
+        <v>0.2104</v>
       </c>
       <c r="E18">
-        <v>8.3199999999999996E-2</v>
+        <v>9.4950000000000007E-2</v>
       </c>
       <c r="F18">
-        <v>3.4099999999999998E-2</v>
+        <v>3.8850000000000003E-2</v>
       </c>
       <c r="G18">
-        <v>1.315E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="H18" t="s">
         <v>384</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>16.631119331501349</v>
+        <v>16.809475334579389</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>0.60145000000000004</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0.27960000000000002</v>
+        <v>0.40515000000000001</v>
       </c>
       <c r="D19">
-        <v>0.14715</v>
+        <v>0.19364999999999999</v>
       </c>
       <c r="E19">
-        <v>6.3649999999999998E-2</v>
+        <v>8.1500000000000003E-2</v>
       </c>
       <c r="F19">
-        <v>2.665E-2</v>
+        <v>3.3849999999999998E-2</v>
       </c>
       <c r="G19">
-        <v>1.11E-2</v>
+        <v>1.26E-2</v>
       </c>
       <c r="H19" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>18.034523649586539</v>
+        <v>16.631119331501349</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>0.39505000000000001</v>
+        <v>0.43585000000000002</v>
       </c>
       <c r="D20">
-        <v>0.14799999999999999</v>
+        <v>0.18745000000000001</v>
       </c>
       <c r="E20">
-        <v>6.4799999999999996E-2</v>
+        <v>7.3050000000000004E-2</v>
       </c>
       <c r="F20">
-        <v>2.6849999999999999E-2</v>
+        <v>2.9950000000000001E-2</v>
       </c>
       <c r="G20">
-        <v>9.1999999999999998E-3</v>
+        <v>1.1350000000000001E-2</v>
       </c>
       <c r="H20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>15.82631796216417</v>
+        <v>15.943406980069801</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -31977,22 +32561,22 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>0.66815000000000002</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0.31840000000000002</v>
+        <v>0.42230000000000001</v>
       </c>
       <c r="D21">
-        <v>0.1239</v>
+        <v>0.16925000000000001</v>
       </c>
       <c r="E21">
-        <v>5.3900000000000003E-2</v>
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="F21">
-        <v>2.2349999999999998E-2</v>
+        <v>2.845E-2</v>
       </c>
       <c r="G21">
-        <v>8.6999999999999994E-3</v>
+        <v>1.115E-2</v>
       </c>
       <c r="H21" t="s">
         <v>382</v>
@@ -32006,162 +32590,162 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
-        <v>0.61529999999999996</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0.2949</v>
+        <v>0.40494999999999998</v>
       </c>
       <c r="D22">
-        <v>0.125</v>
+        <v>0.14765</v>
       </c>
       <c r="E22">
-        <v>4.965E-2</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="F22">
-        <v>1.9599999999999999E-2</v>
+        <v>2.5899999999999999E-2</v>
       </c>
       <c r="G22">
-        <v>7.3000000000000001E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="H22" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>15.943406980069801</v>
+        <v>15.82631796216417</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>0.65805000000000002</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0.33760000000000001</v>
+        <v>0.29320000000000002</v>
       </c>
       <c r="D23">
-        <v>0.1181</v>
+        <v>0.13439999999999999</v>
       </c>
       <c r="E23">
-        <v>5.0650000000000001E-2</v>
+        <v>5.7450000000000001E-2</v>
       </c>
       <c r="F23">
-        <v>1.8599999999999998E-2</v>
+        <v>2.3050000000000001E-2</v>
       </c>
       <c r="G23">
-        <v>5.8500000000000002E-3</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="H23" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>15.123966744544839</v>
+        <v>16.287809545840609</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B24">
-        <v>0.58784999999999998</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0.17824999999999999</v>
+        <v>0.45055000000000001</v>
       </c>
       <c r="D24">
-        <v>8.3000000000000004E-2</v>
+        <v>0.15359999999999999</v>
       </c>
       <c r="E24">
-        <v>3.27E-2</v>
+        <v>6.2549999999999994E-2</v>
       </c>
       <c r="F24">
-        <v>1.375E-2</v>
+        <v>2.4649999999999998E-2</v>
       </c>
       <c r="G24">
-        <v>5.1000000000000004E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="H24" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>16.287809545840609</v>
+        <v>15.123966744544839</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>0.31490000000000001</v>
+        <v>0.2984</v>
       </c>
       <c r="D25">
-        <v>0.1273</v>
+        <v>0.12975</v>
       </c>
       <c r="E25">
-        <v>4.1950000000000001E-2</v>
+        <v>5.5750000000000001E-2</v>
       </c>
       <c r="F25">
-        <v>1.495E-2</v>
+        <v>2.1149999999999999E-2</v>
       </c>
       <c r="G25">
-        <v>4.8999999999999998E-3</v>
+        <v>7.9500000000000005E-3</v>
       </c>
       <c r="H25" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>14.53205210966642</v>
+        <v>15.51511812576733</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>0.58265</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>0.18260000000000001</v>
+        <v>0.31940000000000002</v>
       </c>
       <c r="D26">
-        <v>7.9350000000000004E-2</v>
+        <v>0.12470000000000001</v>
       </c>
       <c r="E26">
-        <v>3.3300000000000003E-2</v>
+        <v>4.1149999999999999E-2</v>
       </c>
       <c r="F26">
-        <v>1.35E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="G26">
-        <v>4.7499999999999999E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="H26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I26">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J26">
-        <v>15.51511812576733</v>
+        <v>14.53205210966642</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -32172,19 +32756,19 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>0.2248</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="D27">
-        <v>9.6199999999999994E-2</v>
+        <v>9.2549999999999993E-2</v>
       </c>
       <c r="E27">
-        <v>3.5950000000000003E-2</v>
+        <v>3.1800000000000002E-2</v>
       </c>
       <c r="F27">
-        <v>1.125E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="G27">
-        <v>3.8500000000000001E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H27" t="s">
         <v>384</v>
@@ -32204,19 +32788,19 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>0.28315000000000001</v>
+        <v>0.29185</v>
       </c>
       <c r="D28">
-        <v>0.11855</v>
+        <v>0.11945</v>
       </c>
       <c r="E28">
-        <v>3.8449999999999998E-2</v>
+        <v>3.875E-2</v>
       </c>
       <c r="F28">
-        <v>1.2999999999999999E-2</v>
+        <v>1.115E-2</v>
       </c>
       <c r="G28">
-        <v>3.5999999999999999E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="H28" t="s">
         <v>385</v>
@@ -32230,34 +32814,34 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B29">
-        <v>0.39855000000000002</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>0.16075</v>
+        <v>0.22919999999999999</v>
       </c>
       <c r="D29">
-        <v>7.5499999999999998E-2</v>
+        <v>8.0850000000000005E-2</v>
       </c>
       <c r="E29">
-        <v>2.8750000000000001E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="F29">
-        <v>1.025E-2</v>
+        <v>9.4500000000000001E-3</v>
       </c>
       <c r="G29">
-        <v>3.4499999999999999E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="H29" t="s">
         <v>382</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>15.7373824689671</v>
+        <v>12.8910075642879</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -32265,22 +32849,22 @@
         <v>40</v>
       </c>
       <c r="B30">
-        <v>0.78995000000000004</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>0.29594999999999999</v>
+        <v>0.28255000000000002</v>
       </c>
       <c r="D30">
-        <v>9.7350000000000006E-2</v>
+        <v>8.6199999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>2.9649999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F30">
-        <v>8.7500000000000008E-3</v>
+        <v>7.5500000000000003E-3</v>
       </c>
       <c r="G30">
-        <v>3.0500000000000002E-3</v>
+        <v>2.3500000000000001E-3</v>
       </c>
       <c r="H30" t="s">
         <v>382</v>
@@ -32294,467 +32878,467 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>0.22605</v>
+        <v>0.26055</v>
       </c>
       <c r="D31">
-        <v>8.4699999999999998E-2</v>
+        <v>8.2699999999999996E-2</v>
       </c>
       <c r="E31">
-        <v>2.955E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="F31">
-        <v>8.1499999999999993E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="G31">
-        <v>2.5000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="H31" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>12.8910075642879</v>
+        <v>12.2388904180045</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B32">
-        <v>0.38469999999999999</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>0.14824999999999999</v>
+        <v>0.26724999999999999</v>
       </c>
       <c r="D32">
-        <v>4.9500000000000002E-2</v>
+        <v>7.3749999999999996E-2</v>
       </c>
       <c r="E32">
-        <v>1.55E-2</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="F32">
-        <v>5.3499999999999997E-3</v>
+        <v>4.7499999999999999E-3</v>
       </c>
       <c r="G32">
-        <v>1.4499999999999999E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="H32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J32">
-        <v>12.78042205274066</v>
+        <v>10.280535393881051</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>0.2646</v>
+        <v>0.23105000000000001</v>
       </c>
       <c r="D33">
-        <v>7.0349999999999996E-2</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="E33">
-        <v>1.695E-2</v>
+        <v>1.255E-2</v>
       </c>
       <c r="F33">
-        <v>4.7000000000000002E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G33">
-        <v>1.25E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="H33" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33">
-        <v>10.280535393881051</v>
+        <v>9.7914064574296606</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B34">
-        <v>0.57250000000000001</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.16875000000000001</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>5.425E-2</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>1.465E-2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>4.45E-3</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1.25E-3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J34">
-        <v>12.2388904180045</v>
+        <v>10.62898797126984</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="B35">
-        <v>0.42749999999999999</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.12335</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>3.8300000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>1.1599999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>3.7499999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>1.1000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="s">
         <v>383</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>11.938625469494371</v>
+        <v>16.95891571245977</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="B36">
-        <v>0.41215000000000002</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>8.7599999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>3.1099999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>9.1999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>3.15E-3</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>9.5E-4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J36">
-        <v>11.840993072985089</v>
+        <v>4.6851123682196496</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.22405</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>4.7699999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>1.1599999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>2.5500000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I37">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>9.7914064574296606</v>
+        <v>11.02555602329811</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="B38">
-        <v>0.34194999999999998</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.11650000000000001</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>2.375E-2</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>6.7499999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>1.5499999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="H38" t="s">
         <v>384</v>
       </c>
       <c r="I38">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J38">
-        <v>9.044790611595948</v>
+        <v>0.1935829077834591</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B39">
-        <v>0.41735</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>9.035E-2</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>2.835E-2</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>7.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>2.3500000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>4.0000000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I39">
         <v>8</v>
       </c>
       <c r="J39">
-        <v>11.02555602329811</v>
+        <v>14.114224917334671</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="B40">
-        <v>0.33184999999999998</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.1057</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>2.4850000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>7.5500000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>1.3500000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1.4999999999999999E-4</v>
+        <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I40">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J40">
-        <v>10.62898797126984</v>
+        <v>2.5953665153972891</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="B41">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>8.8200000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1.8800000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>3.65E-3</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>7.5000000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="s">
         <v>382</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J41">
-        <v>7.7337055835141966</v>
+        <v>2.1356002741910172</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="B42">
-        <v>0.10025000000000001</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>1.6E-2</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1.6999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>1.4999999999999999E-4</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>5.0000000000000002E-5</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>5.0000000000000002E-5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J42">
-        <v>0.1935829077834591</v>
+        <v>-7.2160644315092952</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B43">
-        <v>0.19184999999999999</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>5.5100000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>7.3499999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>1.2999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I43">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J43">
-        <v>4.6851123682196496</v>
+        <v>3.928312715113337</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="B44">
-        <v>0.21004999999999999</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>3.5999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>5.1999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>4.0000000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I44">
         <v>14</v>
       </c>
       <c r="J44">
-        <v>3.0807597689023769</v>
+        <v>6.9567142213273874</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>275</v>
       </c>
       <c r="B45">
-        <v>0.12615000000000001</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>2.3300000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2.2000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>2.9999999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -32763,62 +33347,62 @@
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I45">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J45">
-        <v>2.1356002741910172</v>
+        <v>-5.3079314642110162</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="B46">
-        <v>8.6849999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1.125E-2</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1.8500000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>2.5000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I46">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J46">
-        <v>1.063936136616795</v>
+        <v>7.3382243907443794</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="B47">
-        <v>5.7849999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>8.0000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>7.5000000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -32827,18 +33411,18 @@
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I47">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J47">
-        <v>-2.43869723675573</v>
+        <v>7.7337055835141966</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -32862,15 +33446,15 @@
         <v>383</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J48">
-        <v>16.95891571245977</v>
+        <v>11.938625469494371</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -32891,18 +33475,18 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I49">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J49">
-        <v>14.114224917334671</v>
+        <v>13.976487221924669</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -32923,18 +33507,18 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I50">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50">
-        <v>2.5953665153972891</v>
+        <v>3.8559349343715992</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -32955,18 +33539,18 @@
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I51">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J51">
-        <v>-7.2160644315092952</v>
+        <v>9.044790611595948</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -32987,18 +33571,18 @@
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I52">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J52">
-        <v>3.928312715113337</v>
+        <v>14.72942352472889</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -33019,27 +33603,27 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I53">
         <v>14</v>
       </c>
       <c r="J53">
-        <v>6.9567142213273874</v>
+        <v>-0.34703170207646011</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="B54">
-        <v>3.1649999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>2.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -33051,18 +33635,18 @@
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I54">
         <v>16</v>
       </c>
       <c r="J54">
-        <v>-5.3079314642110162</v>
+        <v>-11.471425536201769</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -33083,18 +33667,18 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I55">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J55">
-        <v>7.3382243907443794</v>
+        <v>-2.43869723675573</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -33118,15 +33702,15 @@
         <v>385</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>13.976487221924669</v>
+        <v>15.01820898903012</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -33147,18 +33731,18 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I57">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J57">
-        <v>3.8559349343715992</v>
+        <v>15.7373824689671</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>316</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -33182,15 +33766,15 @@
         <v>384</v>
       </c>
       <c r="I58">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J58">
-        <v>14.72942352472889</v>
+        <v>-9.4717636747576321</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>221</v>
+        <v>55</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -33211,24 +33795,24 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I59">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J59">
-        <v>-0.34703170207646011</v>
+        <v>10.62507679613563</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>319</v>
+        <v>186</v>
       </c>
       <c r="B60">
-        <v>1.78E-2</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>9.5E-4</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -33243,18 +33827,18 @@
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I60">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J60">
-        <v>-11.471425536201769</v>
+        <v>1.063936136616795</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -33278,15 +33862,15 @@
         <v>385</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J61">
-        <v>15.01820898903012</v>
+        <v>1.3139417704256631</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>316</v>
+        <v>43</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -33310,15 +33894,15 @@
         <v>384</v>
       </c>
       <c r="I62">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J62">
-        <v>-9.4717636747576321</v>
+        <v>12.78042205274066</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -33339,18 +33923,18 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I63">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J63">
-        <v>10.62507679613563</v>
+        <v>11.840993072985089</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>26</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -33371,18 +33955,18 @@
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I64">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J64">
-        <v>1.3139417704256631</v>
+        <v>16.148066436541431</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -33403,13 +33987,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J65">
-        <v>16.148066436541431</v>
+        <v>3.0807597689023769</v>
       </c>
     </row>
   </sheetData>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E8C1C4-55A0-3248-A565-06B30C854093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001366F8-90AD-534A-9F99-1A83881D4DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15440" yWindow="780" windowWidth="18760" windowHeight="19960" activeTab="4" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="18760" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -23798,7 +23798,7 @@
         <v>-3.0989295923022899E-3</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K11" s="9">
         <f t="shared" si="3"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001366F8-90AD-534A-9F99-1A83881D4DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4108FE-80BB-2B4C-A765-9FDFACF913CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="18760" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="462">
   <si>
     <t>Team</t>
   </si>
@@ -1600,7 +1600,7 @@
             <v>Louisville</v>
           </cell>
           <cell r="E2">
-            <v>7.6237974976589857</v>
+            <v>7.6237974976589866</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
@@ -1696,7 +1696,7 @@
             <v>VCU</v>
           </cell>
           <cell r="E5">
-            <v>14.138979689921969</v>
+            <v>14.13897968992198</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
@@ -1775,7 +1775,7 @@
             <v>4.7406925411034577E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.50131716872622811</v>
+            <v>0.50131716872622822</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1856,19 +1856,19 @@
             <v>Texas Tech</v>
           </cell>
           <cell r="E10">
-            <v>4.1278919748299394</v>
+            <v>2.502891974829939</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.57749658865455844</v>
+            <v>0.59877621375734469</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>0.1024934874314298</v>
+            <v>0.14311822626402171</v>
           </cell>
           <cell r="J10">
             <v>0.31628008750747999</v>
@@ -1903,7 +1903,7 @@
             <v>-1.239571836920916E-2</v>
           </cell>
           <cell r="J11">
-            <v>0.39463016781725752</v>
+            <v>0.39463016781725763</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1920,7 +1920,7 @@
             <v>UCLA</v>
           </cell>
           <cell r="E12">
-            <v>5.391134817228437</v>
+            <v>5.3911348172284379</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
@@ -1935,7 +1935,7 @@
             <v>2.0681619377560301E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.25478768357222192</v>
+            <v>0.25478768357222198</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1952,7 +1952,7 @@
             <v>Tennessee</v>
           </cell>
           <cell r="E13">
-            <v>0.62393594721707168</v>
+            <v>0.62393594721707213</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
@@ -1967,7 +1967,7 @@
             <v>3.171402537666923E-2</v>
           </cell>
           <cell r="J13">
-            <v>0.1168367102471546</v>
+            <v>0.1168367102471547</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -2255,7 +2255,7 @@
             <v>8.6229891506956591E-2</v>
           </cell>
           <cell r="J22">
-            <v>0.31649838901374572</v>
+            <v>0.31649838901374577</v>
           </cell>
           <cell r="K22">
             <v>0</v>
@@ -2272,7 +2272,7 @@
             <v>Houston</v>
           </cell>
           <cell r="E23">
-            <v>-7.5735379918606291</v>
+            <v>-7.5735379918606283</v>
           </cell>
           <cell r="F23" t="b">
             <v>0</v>
@@ -2319,7 +2319,7 @@
             <v>2.3045058625771279E-2</v>
           </cell>
           <cell r="J24">
-            <v>0.48734606471556807</v>
+            <v>0.48734606471556818</v>
           </cell>
           <cell r="K24">
             <v>0</v>
@@ -2368,19 +2368,19 @@
             <v>Alabama</v>
           </cell>
           <cell r="E26">
-            <v>-2.5226261132732191</v>
+            <v>-0.89762611327321906</v>
           </cell>
           <cell r="F26" t="b">
             <v>0</v>
           </cell>
           <cell r="G26">
-            <v>0.53790777044744986</v>
+            <v>0.55955916364119873</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>2.6914834490586129E-2</v>
+            <v>6.8249312405924911E-2</v>
           </cell>
           <cell r="J26">
             <v>0.1715154919189017</v>
@@ -2496,7 +2496,7 @@
             <v>Purdue</v>
           </cell>
           <cell r="E30">
-            <v>-6.4513442417313867</v>
+            <v>-6.4513442417313884</v>
           </cell>
           <cell r="F30" t="b">
             <v>0</v>
@@ -2511,7 +2511,7 @@
             <v>4.4268736326837921E-3</v>
           </cell>
           <cell r="J30">
-            <v>0.14448487310626509</v>
+            <v>0.1444848731062652</v>
           </cell>
           <cell r="K30">
             <v>0</v>
@@ -9435,7 +9435,7 @@
             <v>0</v>
           </cell>
           <cell r="X10">
-            <v>-1</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="11">
@@ -10619,7 +10619,7 @@
             <v>0</v>
           </cell>
           <cell r="X26">
-            <v>1</v>
+            <v>-1.5</v>
           </cell>
         </row>
         <row r="27">
@@ -11139,3410 +11139,6 @@
           <cell r="X33">
             <v>11.5</v>
           </cell>
-        </row>
-        <row r="34">
-          <cell r="D34"/>
-          <cell r="E34"/>
-          <cell r="F34"/>
-          <cell r="G34"/>
-          <cell r="H34"/>
-          <cell r="I34"/>
-          <cell r="J34"/>
-          <cell r="K34"/>
-          <cell r="L34"/>
-          <cell r="M34"/>
-          <cell r="N34"/>
-          <cell r="O34"/>
-          <cell r="P34"/>
-          <cell r="Q34"/>
-          <cell r="R34"/>
-          <cell r="S34"/>
-          <cell r="T34"/>
-          <cell r="U34"/>
-          <cell r="V34"/>
-          <cell r="W34"/>
-          <cell r="X34"/>
-        </row>
-        <row r="35">
-          <cell r="D35"/>
-          <cell r="E35"/>
-          <cell r="F35"/>
-          <cell r="G35"/>
-          <cell r="H35"/>
-          <cell r="I35"/>
-          <cell r="J35"/>
-          <cell r="K35"/>
-          <cell r="L35"/>
-          <cell r="M35"/>
-          <cell r="N35"/>
-          <cell r="O35"/>
-          <cell r="P35"/>
-          <cell r="Q35"/>
-          <cell r="R35"/>
-          <cell r="S35"/>
-          <cell r="T35"/>
-          <cell r="U35"/>
-          <cell r="V35"/>
-          <cell r="W35"/>
-          <cell r="X35"/>
-        </row>
-        <row r="36">
-          <cell r="D36"/>
-          <cell r="E36"/>
-          <cell r="F36"/>
-          <cell r="G36"/>
-          <cell r="H36"/>
-          <cell r="I36"/>
-          <cell r="J36"/>
-          <cell r="K36"/>
-          <cell r="L36"/>
-          <cell r="M36"/>
-          <cell r="N36"/>
-          <cell r="O36"/>
-          <cell r="P36"/>
-          <cell r="Q36"/>
-          <cell r="R36"/>
-          <cell r="S36"/>
-          <cell r="T36"/>
-          <cell r="U36"/>
-          <cell r="V36"/>
-          <cell r="W36"/>
-          <cell r="X36"/>
-        </row>
-        <row r="37">
-          <cell r="D37"/>
-          <cell r="E37"/>
-          <cell r="F37"/>
-          <cell r="G37"/>
-          <cell r="H37"/>
-          <cell r="I37"/>
-          <cell r="J37"/>
-          <cell r="K37"/>
-          <cell r="L37"/>
-          <cell r="M37"/>
-          <cell r="N37"/>
-          <cell r="O37"/>
-          <cell r="P37"/>
-          <cell r="Q37"/>
-          <cell r="R37"/>
-          <cell r="S37"/>
-          <cell r="T37"/>
-          <cell r="U37"/>
-          <cell r="V37"/>
-          <cell r="W37"/>
-          <cell r="X37"/>
-        </row>
-        <row r="38">
-          <cell r="D38"/>
-          <cell r="E38"/>
-          <cell r="F38"/>
-          <cell r="G38"/>
-          <cell r="H38"/>
-          <cell r="I38"/>
-          <cell r="J38"/>
-          <cell r="K38"/>
-          <cell r="L38"/>
-          <cell r="M38"/>
-          <cell r="N38"/>
-          <cell r="O38"/>
-          <cell r="P38"/>
-          <cell r="Q38"/>
-          <cell r="R38"/>
-          <cell r="S38"/>
-          <cell r="T38"/>
-          <cell r="U38"/>
-          <cell r="V38"/>
-          <cell r="W38"/>
-          <cell r="X38"/>
-        </row>
-        <row r="39">
-          <cell r="D39"/>
-          <cell r="E39"/>
-          <cell r="F39"/>
-          <cell r="G39"/>
-          <cell r="H39"/>
-          <cell r="I39"/>
-          <cell r="J39"/>
-          <cell r="K39"/>
-          <cell r="L39"/>
-          <cell r="M39"/>
-          <cell r="N39"/>
-          <cell r="O39"/>
-          <cell r="P39"/>
-          <cell r="Q39"/>
-          <cell r="R39"/>
-          <cell r="S39"/>
-          <cell r="T39"/>
-          <cell r="U39"/>
-          <cell r="V39"/>
-          <cell r="W39"/>
-          <cell r="X39"/>
-        </row>
-        <row r="40">
-          <cell r="D40"/>
-          <cell r="E40"/>
-          <cell r="F40"/>
-          <cell r="G40"/>
-          <cell r="H40"/>
-          <cell r="I40"/>
-          <cell r="J40"/>
-          <cell r="K40"/>
-          <cell r="L40"/>
-          <cell r="M40"/>
-          <cell r="N40"/>
-          <cell r="O40"/>
-          <cell r="P40"/>
-          <cell r="Q40"/>
-          <cell r="R40"/>
-          <cell r="S40"/>
-          <cell r="T40"/>
-          <cell r="U40"/>
-          <cell r="V40"/>
-          <cell r="W40"/>
-          <cell r="X40"/>
-        </row>
-        <row r="41">
-          <cell r="D41"/>
-          <cell r="E41"/>
-          <cell r="F41"/>
-          <cell r="G41"/>
-          <cell r="H41"/>
-          <cell r="I41"/>
-          <cell r="J41"/>
-          <cell r="K41"/>
-          <cell r="L41"/>
-          <cell r="M41"/>
-          <cell r="N41"/>
-          <cell r="O41"/>
-          <cell r="P41"/>
-          <cell r="Q41"/>
-          <cell r="R41"/>
-          <cell r="S41"/>
-          <cell r="T41"/>
-          <cell r="U41"/>
-          <cell r="V41"/>
-          <cell r="W41"/>
-          <cell r="X41"/>
-        </row>
-        <row r="42">
-          <cell r="D42"/>
-          <cell r="E42"/>
-          <cell r="F42"/>
-          <cell r="G42"/>
-          <cell r="H42"/>
-          <cell r="I42"/>
-          <cell r="J42"/>
-          <cell r="K42"/>
-          <cell r="L42"/>
-          <cell r="M42"/>
-          <cell r="N42"/>
-          <cell r="O42"/>
-          <cell r="P42"/>
-          <cell r="Q42"/>
-          <cell r="R42"/>
-          <cell r="S42"/>
-          <cell r="T42"/>
-          <cell r="U42"/>
-          <cell r="V42"/>
-          <cell r="W42"/>
-          <cell r="X42"/>
-        </row>
-        <row r="43">
-          <cell r="D43"/>
-          <cell r="E43"/>
-          <cell r="F43"/>
-          <cell r="G43"/>
-          <cell r="H43"/>
-          <cell r="I43"/>
-          <cell r="J43"/>
-          <cell r="K43"/>
-          <cell r="L43"/>
-          <cell r="M43"/>
-          <cell r="N43"/>
-          <cell r="O43"/>
-          <cell r="P43"/>
-          <cell r="Q43"/>
-          <cell r="R43"/>
-          <cell r="S43"/>
-          <cell r="T43"/>
-          <cell r="U43"/>
-          <cell r="V43"/>
-          <cell r="W43"/>
-          <cell r="X43"/>
-        </row>
-        <row r="44">
-          <cell r="D44"/>
-          <cell r="E44"/>
-          <cell r="F44"/>
-          <cell r="G44"/>
-          <cell r="H44"/>
-          <cell r="I44"/>
-          <cell r="J44"/>
-          <cell r="K44"/>
-          <cell r="L44"/>
-          <cell r="M44"/>
-          <cell r="N44"/>
-          <cell r="O44"/>
-          <cell r="P44"/>
-          <cell r="Q44"/>
-          <cell r="R44"/>
-          <cell r="S44"/>
-          <cell r="T44"/>
-          <cell r="U44"/>
-          <cell r="V44"/>
-          <cell r="W44"/>
-          <cell r="X44"/>
-        </row>
-        <row r="45">
-          <cell r="D45"/>
-          <cell r="E45"/>
-          <cell r="F45"/>
-          <cell r="G45"/>
-          <cell r="H45"/>
-          <cell r="I45"/>
-          <cell r="J45"/>
-          <cell r="K45"/>
-          <cell r="L45"/>
-          <cell r="M45"/>
-          <cell r="N45"/>
-          <cell r="O45"/>
-          <cell r="P45"/>
-          <cell r="Q45"/>
-          <cell r="R45"/>
-          <cell r="S45"/>
-          <cell r="T45"/>
-          <cell r="U45"/>
-          <cell r="V45"/>
-          <cell r="W45"/>
-          <cell r="X45"/>
-        </row>
-        <row r="46">
-          <cell r="D46"/>
-          <cell r="E46"/>
-          <cell r="F46"/>
-          <cell r="G46"/>
-          <cell r="H46"/>
-          <cell r="I46"/>
-          <cell r="J46"/>
-          <cell r="K46"/>
-          <cell r="L46"/>
-          <cell r="M46"/>
-          <cell r="N46"/>
-          <cell r="O46"/>
-          <cell r="P46"/>
-          <cell r="Q46"/>
-          <cell r="R46"/>
-          <cell r="S46"/>
-          <cell r="T46"/>
-          <cell r="U46"/>
-          <cell r="V46"/>
-          <cell r="W46"/>
-          <cell r="X46"/>
-        </row>
-        <row r="47">
-          <cell r="D47"/>
-          <cell r="E47"/>
-          <cell r="F47"/>
-          <cell r="G47"/>
-          <cell r="H47"/>
-          <cell r="I47"/>
-          <cell r="J47"/>
-          <cell r="K47"/>
-          <cell r="L47"/>
-          <cell r="M47"/>
-          <cell r="N47"/>
-          <cell r="O47"/>
-          <cell r="P47"/>
-          <cell r="Q47"/>
-          <cell r="R47"/>
-          <cell r="S47"/>
-          <cell r="T47"/>
-          <cell r="U47"/>
-          <cell r="V47"/>
-          <cell r="W47"/>
-          <cell r="X47"/>
-        </row>
-        <row r="48">
-          <cell r="D48"/>
-          <cell r="E48"/>
-          <cell r="F48"/>
-          <cell r="G48"/>
-          <cell r="H48"/>
-          <cell r="I48"/>
-          <cell r="J48"/>
-          <cell r="K48"/>
-          <cell r="L48"/>
-          <cell r="M48"/>
-          <cell r="N48"/>
-          <cell r="O48"/>
-          <cell r="P48"/>
-          <cell r="Q48"/>
-          <cell r="R48"/>
-          <cell r="S48"/>
-          <cell r="T48"/>
-          <cell r="U48"/>
-          <cell r="V48"/>
-          <cell r="W48"/>
-          <cell r="X48"/>
-        </row>
-        <row r="49">
-          <cell r="D49"/>
-          <cell r="E49"/>
-          <cell r="F49"/>
-          <cell r="G49"/>
-          <cell r="H49"/>
-          <cell r="I49"/>
-          <cell r="J49"/>
-          <cell r="K49"/>
-          <cell r="L49"/>
-          <cell r="M49"/>
-          <cell r="N49"/>
-          <cell r="O49"/>
-          <cell r="P49"/>
-          <cell r="Q49"/>
-          <cell r="R49"/>
-          <cell r="S49"/>
-          <cell r="T49"/>
-          <cell r="U49"/>
-          <cell r="V49"/>
-          <cell r="W49"/>
-          <cell r="X49"/>
-        </row>
-        <row r="50">
-          <cell r="D50"/>
-          <cell r="E50"/>
-          <cell r="F50"/>
-          <cell r="G50"/>
-          <cell r="H50"/>
-          <cell r="I50"/>
-          <cell r="J50"/>
-          <cell r="K50"/>
-          <cell r="L50"/>
-          <cell r="M50"/>
-          <cell r="N50"/>
-          <cell r="O50"/>
-          <cell r="P50"/>
-          <cell r="Q50"/>
-          <cell r="R50"/>
-          <cell r="S50"/>
-          <cell r="T50"/>
-          <cell r="U50"/>
-          <cell r="V50"/>
-          <cell r="W50"/>
-          <cell r="X50"/>
-        </row>
-        <row r="51">
-          <cell r="D51"/>
-          <cell r="E51"/>
-          <cell r="F51"/>
-          <cell r="G51"/>
-          <cell r="H51"/>
-          <cell r="I51"/>
-          <cell r="J51"/>
-          <cell r="K51"/>
-          <cell r="L51"/>
-          <cell r="M51"/>
-          <cell r="N51"/>
-          <cell r="O51"/>
-          <cell r="P51"/>
-          <cell r="Q51"/>
-          <cell r="R51"/>
-          <cell r="S51"/>
-          <cell r="T51"/>
-          <cell r="U51"/>
-          <cell r="V51"/>
-          <cell r="W51"/>
-          <cell r="X51"/>
-        </row>
-        <row r="52">
-          <cell r="D52"/>
-          <cell r="E52"/>
-          <cell r="F52"/>
-          <cell r="G52"/>
-          <cell r="H52"/>
-          <cell r="I52"/>
-          <cell r="J52"/>
-          <cell r="K52"/>
-          <cell r="L52"/>
-          <cell r="M52"/>
-          <cell r="N52"/>
-          <cell r="O52"/>
-          <cell r="P52"/>
-          <cell r="Q52"/>
-          <cell r="R52"/>
-          <cell r="S52"/>
-          <cell r="T52"/>
-          <cell r="U52"/>
-          <cell r="V52"/>
-          <cell r="W52"/>
-          <cell r="X52"/>
-        </row>
-        <row r="53">
-          <cell r="D53"/>
-          <cell r="E53"/>
-          <cell r="F53"/>
-          <cell r="G53"/>
-          <cell r="H53"/>
-          <cell r="I53"/>
-          <cell r="J53"/>
-          <cell r="K53"/>
-          <cell r="L53"/>
-          <cell r="M53"/>
-          <cell r="N53"/>
-          <cell r="O53"/>
-          <cell r="P53"/>
-          <cell r="Q53"/>
-          <cell r="R53"/>
-          <cell r="S53"/>
-          <cell r="T53"/>
-          <cell r="U53"/>
-          <cell r="V53"/>
-          <cell r="W53"/>
-          <cell r="X53"/>
-        </row>
-        <row r="54">
-          <cell r="D54"/>
-          <cell r="E54"/>
-          <cell r="F54"/>
-          <cell r="G54"/>
-          <cell r="H54"/>
-          <cell r="I54"/>
-          <cell r="J54"/>
-          <cell r="K54"/>
-          <cell r="L54"/>
-          <cell r="M54"/>
-          <cell r="N54"/>
-          <cell r="O54"/>
-          <cell r="P54"/>
-          <cell r="Q54"/>
-          <cell r="R54"/>
-          <cell r="S54"/>
-          <cell r="T54"/>
-          <cell r="U54"/>
-          <cell r="V54"/>
-          <cell r="W54"/>
-          <cell r="X54"/>
-        </row>
-        <row r="55">
-          <cell r="D55"/>
-          <cell r="E55"/>
-          <cell r="F55"/>
-          <cell r="G55"/>
-          <cell r="H55"/>
-          <cell r="I55"/>
-          <cell r="J55"/>
-          <cell r="K55"/>
-          <cell r="L55"/>
-          <cell r="M55"/>
-          <cell r="N55"/>
-          <cell r="O55"/>
-          <cell r="P55"/>
-          <cell r="Q55"/>
-          <cell r="R55"/>
-          <cell r="S55"/>
-          <cell r="T55"/>
-          <cell r="U55"/>
-          <cell r="V55"/>
-          <cell r="W55"/>
-          <cell r="X55"/>
-        </row>
-        <row r="56">
-          <cell r="D56"/>
-          <cell r="E56"/>
-          <cell r="F56"/>
-          <cell r="G56"/>
-          <cell r="H56"/>
-          <cell r="I56"/>
-          <cell r="J56"/>
-          <cell r="K56"/>
-          <cell r="L56"/>
-          <cell r="M56"/>
-          <cell r="N56"/>
-          <cell r="O56"/>
-          <cell r="P56"/>
-          <cell r="Q56"/>
-          <cell r="R56"/>
-          <cell r="S56"/>
-          <cell r="T56"/>
-          <cell r="U56"/>
-          <cell r="V56"/>
-          <cell r="W56"/>
-          <cell r="X56"/>
-        </row>
-        <row r="57">
-          <cell r="D57"/>
-          <cell r="E57"/>
-          <cell r="F57"/>
-          <cell r="G57"/>
-          <cell r="H57"/>
-          <cell r="I57"/>
-          <cell r="J57"/>
-          <cell r="K57"/>
-          <cell r="L57"/>
-          <cell r="M57"/>
-          <cell r="N57"/>
-          <cell r="O57"/>
-          <cell r="P57"/>
-          <cell r="Q57"/>
-          <cell r="R57"/>
-          <cell r="S57"/>
-          <cell r="T57"/>
-          <cell r="U57"/>
-          <cell r="V57"/>
-          <cell r="W57"/>
-          <cell r="X57"/>
-        </row>
-        <row r="58">
-          <cell r="D58"/>
-          <cell r="E58"/>
-          <cell r="F58"/>
-          <cell r="G58"/>
-          <cell r="H58"/>
-          <cell r="I58"/>
-          <cell r="J58"/>
-          <cell r="K58"/>
-          <cell r="L58"/>
-          <cell r="M58"/>
-          <cell r="N58"/>
-          <cell r="O58"/>
-          <cell r="P58"/>
-          <cell r="Q58"/>
-          <cell r="R58"/>
-          <cell r="S58"/>
-          <cell r="T58"/>
-          <cell r="U58"/>
-          <cell r="V58"/>
-          <cell r="W58"/>
-          <cell r="X58"/>
-        </row>
-        <row r="59">
-          <cell r="D59"/>
-          <cell r="E59"/>
-          <cell r="F59"/>
-          <cell r="G59"/>
-          <cell r="H59"/>
-          <cell r="I59"/>
-          <cell r="J59"/>
-          <cell r="K59"/>
-          <cell r="L59"/>
-          <cell r="M59"/>
-          <cell r="N59"/>
-          <cell r="O59"/>
-          <cell r="P59"/>
-          <cell r="Q59"/>
-          <cell r="R59"/>
-          <cell r="S59"/>
-          <cell r="T59"/>
-          <cell r="U59"/>
-          <cell r="V59"/>
-          <cell r="W59"/>
-          <cell r="X59"/>
-        </row>
-        <row r="60">
-          <cell r="D60"/>
-          <cell r="E60"/>
-          <cell r="F60"/>
-          <cell r="G60"/>
-          <cell r="H60"/>
-          <cell r="I60"/>
-          <cell r="J60"/>
-          <cell r="K60"/>
-          <cell r="L60"/>
-          <cell r="M60"/>
-          <cell r="N60"/>
-          <cell r="O60"/>
-          <cell r="P60"/>
-          <cell r="Q60"/>
-          <cell r="R60"/>
-          <cell r="S60"/>
-          <cell r="T60"/>
-          <cell r="U60"/>
-          <cell r="V60"/>
-          <cell r="W60"/>
-          <cell r="X60"/>
-        </row>
-        <row r="61">
-          <cell r="D61"/>
-          <cell r="E61"/>
-          <cell r="F61"/>
-          <cell r="G61"/>
-          <cell r="H61"/>
-          <cell r="I61"/>
-          <cell r="J61"/>
-          <cell r="K61"/>
-          <cell r="L61"/>
-          <cell r="M61"/>
-          <cell r="N61"/>
-          <cell r="O61"/>
-          <cell r="P61"/>
-          <cell r="Q61"/>
-          <cell r="R61"/>
-          <cell r="S61"/>
-          <cell r="T61"/>
-          <cell r="U61"/>
-          <cell r="V61"/>
-          <cell r="W61"/>
-          <cell r="X61"/>
-        </row>
-        <row r="62">
-          <cell r="D62"/>
-          <cell r="E62"/>
-          <cell r="F62"/>
-          <cell r="G62"/>
-          <cell r="H62"/>
-          <cell r="I62"/>
-          <cell r="J62"/>
-          <cell r="K62"/>
-          <cell r="L62"/>
-          <cell r="M62"/>
-          <cell r="N62"/>
-          <cell r="O62"/>
-          <cell r="P62"/>
-          <cell r="Q62"/>
-          <cell r="R62"/>
-          <cell r="S62"/>
-          <cell r="T62"/>
-          <cell r="U62"/>
-          <cell r="V62"/>
-          <cell r="W62"/>
-          <cell r="X62"/>
-        </row>
-        <row r="63">
-          <cell r="D63"/>
-          <cell r="E63"/>
-          <cell r="F63"/>
-          <cell r="G63"/>
-          <cell r="H63"/>
-          <cell r="I63"/>
-          <cell r="J63"/>
-          <cell r="K63"/>
-          <cell r="L63"/>
-          <cell r="M63"/>
-          <cell r="N63"/>
-          <cell r="O63"/>
-          <cell r="P63"/>
-          <cell r="Q63"/>
-          <cell r="R63"/>
-          <cell r="S63"/>
-          <cell r="T63"/>
-          <cell r="U63"/>
-          <cell r="V63"/>
-          <cell r="W63"/>
-          <cell r="X63"/>
-        </row>
-        <row r="64">
-          <cell r="D64"/>
-          <cell r="E64"/>
-          <cell r="F64"/>
-          <cell r="G64"/>
-          <cell r="H64"/>
-          <cell r="I64"/>
-          <cell r="J64"/>
-          <cell r="K64"/>
-          <cell r="L64"/>
-          <cell r="M64"/>
-          <cell r="N64"/>
-          <cell r="O64"/>
-          <cell r="P64"/>
-          <cell r="Q64"/>
-          <cell r="R64"/>
-          <cell r="S64"/>
-          <cell r="T64"/>
-          <cell r="U64"/>
-          <cell r="V64"/>
-          <cell r="W64"/>
-          <cell r="X64"/>
-        </row>
-        <row r="65">
-          <cell r="D65"/>
-          <cell r="E65"/>
-          <cell r="F65"/>
-          <cell r="G65"/>
-          <cell r="H65"/>
-          <cell r="I65"/>
-          <cell r="J65"/>
-          <cell r="K65"/>
-          <cell r="L65"/>
-          <cell r="M65"/>
-          <cell r="N65"/>
-          <cell r="O65"/>
-          <cell r="P65"/>
-          <cell r="Q65"/>
-          <cell r="R65"/>
-          <cell r="S65"/>
-          <cell r="T65"/>
-          <cell r="U65"/>
-          <cell r="V65"/>
-          <cell r="W65"/>
-          <cell r="X65"/>
-        </row>
-        <row r="66">
-          <cell r="D66"/>
-          <cell r="E66"/>
-          <cell r="F66"/>
-          <cell r="G66"/>
-          <cell r="H66"/>
-          <cell r="I66"/>
-          <cell r="J66"/>
-          <cell r="K66"/>
-          <cell r="L66"/>
-          <cell r="M66"/>
-          <cell r="N66"/>
-          <cell r="O66"/>
-          <cell r="P66"/>
-          <cell r="Q66"/>
-          <cell r="R66"/>
-          <cell r="S66"/>
-          <cell r="T66"/>
-          <cell r="U66"/>
-          <cell r="V66"/>
-          <cell r="W66"/>
-          <cell r="X66"/>
-        </row>
-        <row r="67">
-          <cell r="D67"/>
-          <cell r="E67"/>
-          <cell r="F67"/>
-          <cell r="G67"/>
-          <cell r="H67"/>
-          <cell r="I67"/>
-          <cell r="J67"/>
-          <cell r="K67"/>
-          <cell r="L67"/>
-          <cell r="M67"/>
-          <cell r="N67"/>
-          <cell r="O67"/>
-          <cell r="P67"/>
-          <cell r="Q67"/>
-          <cell r="R67"/>
-          <cell r="S67"/>
-          <cell r="T67"/>
-          <cell r="U67"/>
-          <cell r="V67"/>
-          <cell r="W67"/>
-          <cell r="X67"/>
-        </row>
-        <row r="68">
-          <cell r="D68"/>
-          <cell r="E68"/>
-          <cell r="F68"/>
-          <cell r="G68"/>
-          <cell r="H68"/>
-          <cell r="I68"/>
-          <cell r="J68"/>
-          <cell r="K68"/>
-          <cell r="L68"/>
-          <cell r="M68"/>
-          <cell r="N68"/>
-          <cell r="O68"/>
-          <cell r="P68"/>
-          <cell r="Q68"/>
-          <cell r="R68"/>
-          <cell r="S68"/>
-          <cell r="T68"/>
-          <cell r="U68"/>
-          <cell r="V68"/>
-          <cell r="W68"/>
-          <cell r="X68"/>
-        </row>
-        <row r="69">
-          <cell r="D69"/>
-          <cell r="E69"/>
-          <cell r="F69"/>
-          <cell r="G69"/>
-          <cell r="H69"/>
-          <cell r="I69"/>
-          <cell r="J69"/>
-          <cell r="K69"/>
-          <cell r="L69"/>
-          <cell r="M69"/>
-          <cell r="N69"/>
-          <cell r="O69"/>
-          <cell r="P69"/>
-          <cell r="Q69"/>
-          <cell r="R69"/>
-          <cell r="S69"/>
-          <cell r="T69"/>
-          <cell r="U69"/>
-          <cell r="V69"/>
-          <cell r="W69"/>
-          <cell r="X69"/>
-        </row>
-        <row r="70">
-          <cell r="D70"/>
-          <cell r="E70"/>
-          <cell r="F70"/>
-          <cell r="G70"/>
-          <cell r="H70"/>
-          <cell r="I70"/>
-          <cell r="J70"/>
-          <cell r="K70"/>
-          <cell r="L70"/>
-          <cell r="M70"/>
-          <cell r="N70"/>
-          <cell r="O70"/>
-          <cell r="P70"/>
-          <cell r="Q70"/>
-          <cell r="R70"/>
-          <cell r="S70"/>
-          <cell r="T70"/>
-          <cell r="U70"/>
-          <cell r="V70"/>
-          <cell r="W70"/>
-          <cell r="X70"/>
-        </row>
-        <row r="71">
-          <cell r="D71"/>
-          <cell r="E71"/>
-          <cell r="F71"/>
-          <cell r="G71"/>
-          <cell r="H71"/>
-          <cell r="I71"/>
-          <cell r="J71"/>
-          <cell r="K71"/>
-          <cell r="L71"/>
-          <cell r="M71"/>
-          <cell r="N71"/>
-          <cell r="O71"/>
-          <cell r="P71"/>
-          <cell r="Q71"/>
-          <cell r="R71"/>
-          <cell r="S71"/>
-          <cell r="T71"/>
-          <cell r="U71"/>
-          <cell r="V71"/>
-          <cell r="W71"/>
-          <cell r="X71"/>
-        </row>
-        <row r="72">
-          <cell r="D72"/>
-          <cell r="E72"/>
-          <cell r="F72"/>
-          <cell r="G72"/>
-          <cell r="H72"/>
-          <cell r="I72"/>
-          <cell r="J72"/>
-          <cell r="K72"/>
-          <cell r="L72"/>
-          <cell r="M72"/>
-          <cell r="N72"/>
-          <cell r="O72"/>
-          <cell r="P72"/>
-          <cell r="Q72"/>
-          <cell r="R72"/>
-          <cell r="S72"/>
-          <cell r="T72"/>
-          <cell r="U72"/>
-          <cell r="V72"/>
-          <cell r="W72"/>
-          <cell r="X72"/>
-        </row>
-        <row r="73">
-          <cell r="D73"/>
-          <cell r="E73"/>
-          <cell r="F73"/>
-          <cell r="G73"/>
-          <cell r="H73"/>
-          <cell r="I73"/>
-          <cell r="J73"/>
-          <cell r="K73"/>
-          <cell r="L73"/>
-          <cell r="M73"/>
-          <cell r="N73"/>
-          <cell r="O73"/>
-          <cell r="P73"/>
-          <cell r="Q73"/>
-          <cell r="R73"/>
-          <cell r="S73"/>
-          <cell r="T73"/>
-          <cell r="U73"/>
-          <cell r="V73"/>
-          <cell r="W73"/>
-          <cell r="X73"/>
-        </row>
-        <row r="74">
-          <cell r="D74"/>
-          <cell r="E74"/>
-          <cell r="F74"/>
-          <cell r="G74"/>
-          <cell r="H74"/>
-          <cell r="I74"/>
-          <cell r="J74"/>
-          <cell r="K74"/>
-          <cell r="L74"/>
-          <cell r="M74"/>
-          <cell r="N74"/>
-          <cell r="O74"/>
-          <cell r="P74"/>
-          <cell r="Q74"/>
-          <cell r="R74"/>
-          <cell r="S74"/>
-          <cell r="T74"/>
-          <cell r="U74"/>
-          <cell r="V74"/>
-          <cell r="W74"/>
-          <cell r="X74"/>
-        </row>
-        <row r="75">
-          <cell r="D75"/>
-          <cell r="E75"/>
-          <cell r="F75"/>
-          <cell r="G75"/>
-          <cell r="H75"/>
-          <cell r="I75"/>
-          <cell r="J75"/>
-          <cell r="K75"/>
-          <cell r="L75"/>
-          <cell r="M75"/>
-          <cell r="N75"/>
-          <cell r="O75"/>
-          <cell r="P75"/>
-          <cell r="Q75"/>
-          <cell r="R75"/>
-          <cell r="S75"/>
-          <cell r="T75"/>
-          <cell r="U75"/>
-          <cell r="V75"/>
-          <cell r="W75"/>
-          <cell r="X75"/>
-        </row>
-        <row r="76">
-          <cell r="D76"/>
-          <cell r="E76"/>
-          <cell r="F76"/>
-          <cell r="G76"/>
-          <cell r="H76"/>
-          <cell r="I76"/>
-          <cell r="J76"/>
-          <cell r="K76"/>
-          <cell r="L76"/>
-          <cell r="M76"/>
-          <cell r="N76"/>
-          <cell r="O76"/>
-          <cell r="P76"/>
-          <cell r="Q76"/>
-          <cell r="R76"/>
-          <cell r="S76"/>
-          <cell r="T76"/>
-          <cell r="U76"/>
-          <cell r="V76"/>
-          <cell r="W76"/>
-          <cell r="X76"/>
-        </row>
-        <row r="77">
-          <cell r="D77"/>
-          <cell r="E77"/>
-          <cell r="F77"/>
-          <cell r="G77"/>
-          <cell r="H77"/>
-          <cell r="I77"/>
-          <cell r="J77"/>
-          <cell r="K77"/>
-          <cell r="L77"/>
-          <cell r="M77"/>
-          <cell r="N77"/>
-          <cell r="O77"/>
-          <cell r="P77"/>
-          <cell r="Q77"/>
-          <cell r="R77"/>
-          <cell r="S77"/>
-          <cell r="T77"/>
-          <cell r="U77"/>
-          <cell r="V77"/>
-          <cell r="W77"/>
-          <cell r="X77"/>
-        </row>
-        <row r="78">
-          <cell r="D78"/>
-          <cell r="E78"/>
-          <cell r="F78"/>
-          <cell r="G78"/>
-          <cell r="H78"/>
-          <cell r="I78"/>
-          <cell r="J78"/>
-          <cell r="K78"/>
-          <cell r="L78"/>
-          <cell r="M78"/>
-          <cell r="N78"/>
-          <cell r="O78"/>
-          <cell r="P78"/>
-          <cell r="Q78"/>
-          <cell r="R78"/>
-          <cell r="S78"/>
-          <cell r="T78"/>
-          <cell r="U78"/>
-          <cell r="V78"/>
-          <cell r="W78"/>
-          <cell r="X78"/>
-        </row>
-        <row r="79">
-          <cell r="D79"/>
-          <cell r="E79"/>
-          <cell r="F79"/>
-          <cell r="G79"/>
-          <cell r="H79"/>
-          <cell r="I79"/>
-          <cell r="J79"/>
-          <cell r="K79"/>
-          <cell r="L79"/>
-          <cell r="M79"/>
-          <cell r="N79"/>
-          <cell r="O79"/>
-          <cell r="P79"/>
-          <cell r="Q79"/>
-          <cell r="R79"/>
-          <cell r="S79"/>
-          <cell r="T79"/>
-          <cell r="U79"/>
-          <cell r="V79"/>
-          <cell r="W79"/>
-          <cell r="X79"/>
-        </row>
-        <row r="80">
-          <cell r="D80"/>
-          <cell r="E80"/>
-          <cell r="F80"/>
-          <cell r="G80"/>
-          <cell r="H80"/>
-          <cell r="I80"/>
-          <cell r="J80"/>
-          <cell r="K80"/>
-          <cell r="L80"/>
-          <cell r="M80"/>
-          <cell r="N80"/>
-          <cell r="O80"/>
-          <cell r="P80"/>
-          <cell r="Q80"/>
-          <cell r="R80"/>
-          <cell r="S80"/>
-          <cell r="T80"/>
-          <cell r="U80"/>
-          <cell r="V80"/>
-          <cell r="W80"/>
-          <cell r="X80"/>
-        </row>
-        <row r="81">
-          <cell r="D81"/>
-          <cell r="E81"/>
-          <cell r="F81"/>
-          <cell r="G81"/>
-          <cell r="H81"/>
-          <cell r="I81"/>
-          <cell r="J81"/>
-          <cell r="K81"/>
-          <cell r="L81"/>
-          <cell r="M81"/>
-          <cell r="N81"/>
-          <cell r="O81"/>
-          <cell r="P81"/>
-          <cell r="Q81"/>
-          <cell r="R81"/>
-          <cell r="S81"/>
-          <cell r="T81"/>
-          <cell r="U81"/>
-          <cell r="V81"/>
-          <cell r="W81"/>
-          <cell r="X81"/>
-        </row>
-        <row r="82">
-          <cell r="D82"/>
-          <cell r="E82"/>
-          <cell r="F82"/>
-          <cell r="G82"/>
-          <cell r="H82"/>
-          <cell r="I82"/>
-          <cell r="J82"/>
-          <cell r="K82"/>
-          <cell r="L82"/>
-          <cell r="M82"/>
-          <cell r="N82"/>
-          <cell r="O82"/>
-          <cell r="P82"/>
-          <cell r="Q82"/>
-          <cell r="R82"/>
-          <cell r="S82"/>
-          <cell r="T82"/>
-          <cell r="U82"/>
-          <cell r="V82"/>
-          <cell r="W82"/>
-          <cell r="X82"/>
-        </row>
-        <row r="83">
-          <cell r="D83"/>
-          <cell r="E83"/>
-          <cell r="F83"/>
-          <cell r="G83"/>
-          <cell r="H83"/>
-          <cell r="I83"/>
-          <cell r="J83"/>
-          <cell r="K83"/>
-          <cell r="L83"/>
-          <cell r="M83"/>
-          <cell r="N83"/>
-          <cell r="O83"/>
-          <cell r="P83"/>
-          <cell r="Q83"/>
-          <cell r="R83"/>
-          <cell r="S83"/>
-          <cell r="T83"/>
-          <cell r="U83"/>
-          <cell r="V83"/>
-          <cell r="W83"/>
-          <cell r="X83"/>
-        </row>
-        <row r="84">
-          <cell r="D84"/>
-          <cell r="E84"/>
-          <cell r="F84"/>
-          <cell r="G84"/>
-          <cell r="H84"/>
-          <cell r="I84"/>
-          <cell r="J84"/>
-          <cell r="K84"/>
-          <cell r="L84"/>
-          <cell r="M84"/>
-          <cell r="N84"/>
-          <cell r="O84"/>
-          <cell r="P84"/>
-          <cell r="Q84"/>
-          <cell r="R84"/>
-          <cell r="S84"/>
-          <cell r="T84"/>
-          <cell r="U84"/>
-          <cell r="V84"/>
-          <cell r="W84"/>
-          <cell r="X84"/>
-        </row>
-        <row r="85">
-          <cell r="D85"/>
-          <cell r="E85"/>
-          <cell r="F85"/>
-          <cell r="G85"/>
-          <cell r="H85"/>
-          <cell r="I85"/>
-          <cell r="J85"/>
-          <cell r="K85"/>
-          <cell r="L85"/>
-          <cell r="M85"/>
-          <cell r="N85"/>
-          <cell r="O85"/>
-          <cell r="P85"/>
-          <cell r="Q85"/>
-          <cell r="R85"/>
-          <cell r="S85"/>
-          <cell r="T85"/>
-          <cell r="U85"/>
-          <cell r="V85"/>
-          <cell r="W85"/>
-          <cell r="X85"/>
-        </row>
-        <row r="86">
-          <cell r="D86"/>
-          <cell r="E86"/>
-          <cell r="F86"/>
-          <cell r="G86"/>
-          <cell r="H86"/>
-          <cell r="I86"/>
-          <cell r="J86"/>
-          <cell r="K86"/>
-          <cell r="L86"/>
-          <cell r="M86"/>
-          <cell r="N86"/>
-          <cell r="O86"/>
-          <cell r="P86"/>
-          <cell r="Q86"/>
-          <cell r="R86"/>
-          <cell r="S86"/>
-          <cell r="T86"/>
-          <cell r="U86"/>
-          <cell r="V86"/>
-          <cell r="W86"/>
-          <cell r="X86"/>
-        </row>
-        <row r="87">
-          <cell r="D87"/>
-          <cell r="E87"/>
-          <cell r="F87"/>
-          <cell r="G87"/>
-          <cell r="H87"/>
-          <cell r="I87"/>
-          <cell r="J87"/>
-          <cell r="K87"/>
-          <cell r="L87"/>
-          <cell r="M87"/>
-          <cell r="N87"/>
-          <cell r="O87"/>
-          <cell r="P87"/>
-          <cell r="Q87"/>
-          <cell r="R87"/>
-          <cell r="S87"/>
-          <cell r="T87"/>
-          <cell r="U87"/>
-          <cell r="V87"/>
-          <cell r="W87"/>
-          <cell r="X87"/>
-        </row>
-        <row r="88">
-          <cell r="D88"/>
-          <cell r="E88"/>
-          <cell r="F88"/>
-          <cell r="G88"/>
-          <cell r="H88"/>
-          <cell r="I88"/>
-          <cell r="J88"/>
-          <cell r="K88"/>
-          <cell r="L88"/>
-          <cell r="M88"/>
-          <cell r="N88"/>
-          <cell r="O88"/>
-          <cell r="P88"/>
-          <cell r="Q88"/>
-          <cell r="R88"/>
-          <cell r="S88"/>
-          <cell r="T88"/>
-          <cell r="U88"/>
-          <cell r="V88"/>
-          <cell r="W88"/>
-          <cell r="X88"/>
-        </row>
-        <row r="89">
-          <cell r="D89"/>
-          <cell r="E89"/>
-          <cell r="F89"/>
-          <cell r="G89"/>
-          <cell r="H89"/>
-          <cell r="I89"/>
-          <cell r="J89"/>
-          <cell r="K89"/>
-          <cell r="L89"/>
-          <cell r="M89"/>
-          <cell r="N89"/>
-          <cell r="O89"/>
-          <cell r="P89"/>
-          <cell r="Q89"/>
-          <cell r="R89"/>
-          <cell r="S89"/>
-          <cell r="T89"/>
-          <cell r="U89"/>
-          <cell r="V89"/>
-          <cell r="W89"/>
-          <cell r="X89"/>
-        </row>
-        <row r="90">
-          <cell r="D90"/>
-          <cell r="E90"/>
-          <cell r="F90"/>
-          <cell r="G90"/>
-          <cell r="H90"/>
-          <cell r="I90"/>
-          <cell r="J90"/>
-          <cell r="K90"/>
-          <cell r="L90"/>
-          <cell r="M90"/>
-          <cell r="N90"/>
-          <cell r="O90"/>
-          <cell r="P90"/>
-          <cell r="Q90"/>
-          <cell r="R90"/>
-          <cell r="S90"/>
-          <cell r="T90"/>
-          <cell r="U90"/>
-          <cell r="V90"/>
-          <cell r="W90"/>
-          <cell r="X90"/>
-        </row>
-        <row r="91">
-          <cell r="D91"/>
-          <cell r="E91"/>
-          <cell r="F91"/>
-          <cell r="G91"/>
-          <cell r="H91"/>
-          <cell r="I91"/>
-          <cell r="J91"/>
-          <cell r="K91"/>
-          <cell r="L91"/>
-          <cell r="M91"/>
-          <cell r="N91"/>
-          <cell r="O91"/>
-          <cell r="P91"/>
-          <cell r="Q91"/>
-          <cell r="R91"/>
-          <cell r="S91"/>
-          <cell r="T91"/>
-          <cell r="U91"/>
-          <cell r="V91"/>
-          <cell r="W91"/>
-          <cell r="X91"/>
-        </row>
-        <row r="92">
-          <cell r="D92"/>
-          <cell r="E92"/>
-          <cell r="F92"/>
-          <cell r="G92"/>
-          <cell r="H92"/>
-          <cell r="I92"/>
-          <cell r="J92"/>
-          <cell r="K92"/>
-          <cell r="L92"/>
-          <cell r="M92"/>
-          <cell r="N92"/>
-          <cell r="O92"/>
-          <cell r="P92"/>
-          <cell r="Q92"/>
-          <cell r="R92"/>
-          <cell r="S92"/>
-          <cell r="T92"/>
-          <cell r="U92"/>
-          <cell r="V92"/>
-          <cell r="W92"/>
-          <cell r="X92"/>
-        </row>
-        <row r="93">
-          <cell r="D93"/>
-          <cell r="E93"/>
-          <cell r="F93"/>
-          <cell r="G93"/>
-          <cell r="H93"/>
-          <cell r="I93"/>
-          <cell r="J93"/>
-          <cell r="K93"/>
-          <cell r="L93"/>
-          <cell r="M93"/>
-          <cell r="N93"/>
-          <cell r="O93"/>
-          <cell r="P93"/>
-          <cell r="Q93"/>
-          <cell r="R93"/>
-          <cell r="S93"/>
-          <cell r="T93"/>
-          <cell r="U93"/>
-          <cell r="V93"/>
-          <cell r="W93"/>
-          <cell r="X93"/>
-        </row>
-        <row r="94">
-          <cell r="D94"/>
-          <cell r="E94"/>
-          <cell r="F94"/>
-          <cell r="G94"/>
-          <cell r="H94"/>
-          <cell r="I94"/>
-          <cell r="J94"/>
-          <cell r="K94"/>
-          <cell r="L94"/>
-          <cell r="M94"/>
-          <cell r="N94"/>
-          <cell r="O94"/>
-          <cell r="P94"/>
-          <cell r="Q94"/>
-          <cell r="R94"/>
-          <cell r="S94"/>
-          <cell r="T94"/>
-          <cell r="U94"/>
-          <cell r="V94"/>
-          <cell r="W94"/>
-          <cell r="X94"/>
-        </row>
-        <row r="95">
-          <cell r="D95"/>
-          <cell r="E95"/>
-          <cell r="F95"/>
-          <cell r="G95"/>
-          <cell r="H95"/>
-          <cell r="I95"/>
-          <cell r="J95"/>
-          <cell r="K95"/>
-          <cell r="L95"/>
-          <cell r="M95"/>
-          <cell r="N95"/>
-          <cell r="O95"/>
-          <cell r="P95"/>
-          <cell r="Q95"/>
-          <cell r="R95"/>
-          <cell r="S95"/>
-          <cell r="T95"/>
-          <cell r="U95"/>
-          <cell r="V95"/>
-          <cell r="W95"/>
-          <cell r="X95"/>
-        </row>
-        <row r="96">
-          <cell r="D96"/>
-          <cell r="E96"/>
-          <cell r="F96"/>
-          <cell r="G96"/>
-          <cell r="H96"/>
-          <cell r="I96"/>
-          <cell r="J96"/>
-          <cell r="K96"/>
-          <cell r="L96"/>
-          <cell r="M96"/>
-          <cell r="N96"/>
-          <cell r="O96"/>
-          <cell r="P96"/>
-          <cell r="Q96"/>
-          <cell r="R96"/>
-          <cell r="S96"/>
-          <cell r="T96"/>
-          <cell r="U96"/>
-          <cell r="V96"/>
-          <cell r="W96"/>
-          <cell r="X96"/>
-        </row>
-        <row r="97">
-          <cell r="D97"/>
-          <cell r="E97"/>
-          <cell r="F97"/>
-          <cell r="G97"/>
-          <cell r="H97"/>
-          <cell r="I97"/>
-          <cell r="J97"/>
-          <cell r="K97"/>
-          <cell r="L97"/>
-          <cell r="M97"/>
-          <cell r="N97"/>
-          <cell r="O97"/>
-          <cell r="P97"/>
-          <cell r="Q97"/>
-          <cell r="R97"/>
-          <cell r="S97"/>
-          <cell r="T97"/>
-          <cell r="U97"/>
-          <cell r="V97"/>
-          <cell r="W97"/>
-          <cell r="X97"/>
-        </row>
-        <row r="98">
-          <cell r="D98"/>
-          <cell r="E98"/>
-          <cell r="F98"/>
-          <cell r="G98"/>
-          <cell r="H98"/>
-          <cell r="I98"/>
-          <cell r="J98"/>
-          <cell r="K98"/>
-          <cell r="L98"/>
-          <cell r="M98"/>
-          <cell r="N98"/>
-          <cell r="O98"/>
-          <cell r="P98"/>
-          <cell r="Q98"/>
-          <cell r="R98"/>
-          <cell r="S98"/>
-          <cell r="T98"/>
-          <cell r="U98"/>
-          <cell r="V98"/>
-          <cell r="W98"/>
-          <cell r="X98"/>
-        </row>
-        <row r="99">
-          <cell r="D99"/>
-          <cell r="E99"/>
-          <cell r="F99"/>
-          <cell r="G99"/>
-          <cell r="H99"/>
-          <cell r="I99"/>
-          <cell r="J99"/>
-          <cell r="K99"/>
-          <cell r="L99"/>
-          <cell r="M99"/>
-          <cell r="N99"/>
-          <cell r="O99"/>
-          <cell r="P99"/>
-          <cell r="Q99"/>
-          <cell r="R99"/>
-          <cell r="S99"/>
-          <cell r="T99"/>
-          <cell r="U99"/>
-          <cell r="V99"/>
-          <cell r="W99"/>
-          <cell r="X99"/>
-        </row>
-        <row r="100">
-          <cell r="D100"/>
-          <cell r="E100"/>
-          <cell r="F100"/>
-          <cell r="G100"/>
-          <cell r="H100"/>
-          <cell r="I100"/>
-          <cell r="J100"/>
-          <cell r="K100"/>
-          <cell r="L100"/>
-          <cell r="M100"/>
-          <cell r="N100"/>
-          <cell r="O100"/>
-          <cell r="P100"/>
-          <cell r="Q100"/>
-          <cell r="R100"/>
-          <cell r="S100"/>
-          <cell r="T100"/>
-          <cell r="U100"/>
-          <cell r="V100"/>
-          <cell r="W100"/>
-          <cell r="X100"/>
-        </row>
-        <row r="101">
-          <cell r="D101"/>
-          <cell r="E101"/>
-          <cell r="F101"/>
-          <cell r="G101"/>
-          <cell r="H101"/>
-          <cell r="I101"/>
-          <cell r="J101"/>
-          <cell r="K101"/>
-          <cell r="L101"/>
-          <cell r="M101"/>
-          <cell r="N101"/>
-          <cell r="O101"/>
-          <cell r="P101"/>
-          <cell r="Q101"/>
-          <cell r="R101"/>
-          <cell r="S101"/>
-          <cell r="T101"/>
-          <cell r="U101"/>
-          <cell r="V101"/>
-          <cell r="W101"/>
-          <cell r="X101"/>
-        </row>
-        <row r="102">
-          <cell r="D102"/>
-          <cell r="E102"/>
-          <cell r="F102"/>
-          <cell r="G102"/>
-          <cell r="H102"/>
-          <cell r="I102"/>
-          <cell r="J102"/>
-          <cell r="K102"/>
-          <cell r="L102"/>
-          <cell r="M102"/>
-          <cell r="N102"/>
-          <cell r="O102"/>
-          <cell r="P102"/>
-          <cell r="Q102"/>
-          <cell r="R102"/>
-          <cell r="S102"/>
-          <cell r="T102"/>
-          <cell r="U102"/>
-          <cell r="V102"/>
-          <cell r="W102"/>
-          <cell r="X102"/>
-        </row>
-        <row r="103">
-          <cell r="D103"/>
-          <cell r="E103"/>
-          <cell r="F103"/>
-          <cell r="G103"/>
-          <cell r="H103"/>
-          <cell r="I103"/>
-          <cell r="J103"/>
-          <cell r="K103"/>
-          <cell r="L103"/>
-          <cell r="M103"/>
-          <cell r="N103"/>
-          <cell r="O103"/>
-          <cell r="P103"/>
-          <cell r="Q103"/>
-          <cell r="R103"/>
-          <cell r="S103"/>
-          <cell r="T103"/>
-          <cell r="U103"/>
-          <cell r="V103"/>
-          <cell r="W103"/>
-          <cell r="X103"/>
-        </row>
-        <row r="104">
-          <cell r="D104"/>
-          <cell r="E104"/>
-          <cell r="F104"/>
-          <cell r="G104"/>
-          <cell r="H104"/>
-          <cell r="I104"/>
-          <cell r="J104"/>
-          <cell r="K104"/>
-          <cell r="L104"/>
-          <cell r="M104"/>
-          <cell r="N104"/>
-          <cell r="O104"/>
-          <cell r="P104"/>
-          <cell r="Q104"/>
-          <cell r="R104"/>
-          <cell r="S104"/>
-          <cell r="T104"/>
-          <cell r="U104"/>
-          <cell r="V104"/>
-          <cell r="W104"/>
-          <cell r="X104"/>
-        </row>
-        <row r="105">
-          <cell r="D105"/>
-          <cell r="E105"/>
-          <cell r="F105"/>
-          <cell r="G105"/>
-          <cell r="H105"/>
-          <cell r="I105"/>
-          <cell r="J105"/>
-          <cell r="K105"/>
-          <cell r="L105"/>
-          <cell r="M105"/>
-          <cell r="N105"/>
-          <cell r="O105"/>
-          <cell r="P105"/>
-          <cell r="Q105"/>
-          <cell r="R105"/>
-          <cell r="S105"/>
-          <cell r="T105"/>
-          <cell r="U105"/>
-          <cell r="V105"/>
-          <cell r="W105"/>
-          <cell r="X105"/>
-        </row>
-        <row r="106">
-          <cell r="D106"/>
-          <cell r="E106"/>
-          <cell r="F106"/>
-          <cell r="G106"/>
-          <cell r="H106"/>
-          <cell r="I106"/>
-          <cell r="J106"/>
-          <cell r="K106"/>
-          <cell r="L106"/>
-          <cell r="M106"/>
-          <cell r="N106"/>
-          <cell r="O106"/>
-          <cell r="P106"/>
-          <cell r="Q106"/>
-          <cell r="R106"/>
-          <cell r="S106"/>
-          <cell r="T106"/>
-          <cell r="U106"/>
-          <cell r="V106"/>
-          <cell r="W106"/>
-          <cell r="X106"/>
-        </row>
-        <row r="107">
-          <cell r="D107"/>
-          <cell r="E107"/>
-          <cell r="F107"/>
-          <cell r="G107"/>
-          <cell r="H107"/>
-          <cell r="I107"/>
-          <cell r="J107"/>
-          <cell r="K107"/>
-          <cell r="L107"/>
-          <cell r="M107"/>
-          <cell r="N107"/>
-          <cell r="O107"/>
-          <cell r="P107"/>
-          <cell r="Q107"/>
-          <cell r="R107"/>
-          <cell r="S107"/>
-          <cell r="T107"/>
-          <cell r="U107"/>
-          <cell r="V107"/>
-          <cell r="W107"/>
-          <cell r="X107"/>
-        </row>
-        <row r="108">
-          <cell r="D108"/>
-          <cell r="E108"/>
-          <cell r="F108"/>
-          <cell r="G108"/>
-          <cell r="H108"/>
-          <cell r="I108"/>
-          <cell r="J108"/>
-          <cell r="K108"/>
-          <cell r="L108"/>
-          <cell r="M108"/>
-          <cell r="N108"/>
-          <cell r="O108"/>
-          <cell r="P108"/>
-          <cell r="Q108"/>
-          <cell r="R108"/>
-          <cell r="S108"/>
-          <cell r="T108"/>
-          <cell r="U108"/>
-          <cell r="V108"/>
-          <cell r="W108"/>
-          <cell r="X108"/>
-        </row>
-        <row r="109">
-          <cell r="D109"/>
-          <cell r="E109"/>
-          <cell r="F109"/>
-          <cell r="G109"/>
-          <cell r="H109"/>
-          <cell r="I109"/>
-          <cell r="J109"/>
-          <cell r="K109"/>
-          <cell r="L109"/>
-          <cell r="M109"/>
-          <cell r="N109"/>
-          <cell r="O109"/>
-          <cell r="P109"/>
-          <cell r="Q109"/>
-          <cell r="R109"/>
-          <cell r="S109"/>
-          <cell r="T109"/>
-          <cell r="U109"/>
-          <cell r="V109"/>
-          <cell r="W109"/>
-          <cell r="X109"/>
-        </row>
-        <row r="110">
-          <cell r="D110"/>
-          <cell r="E110"/>
-          <cell r="F110"/>
-          <cell r="G110"/>
-          <cell r="H110"/>
-          <cell r="I110"/>
-          <cell r="J110"/>
-          <cell r="K110"/>
-          <cell r="L110"/>
-          <cell r="M110"/>
-          <cell r="N110"/>
-          <cell r="O110"/>
-          <cell r="P110"/>
-          <cell r="Q110"/>
-          <cell r="R110"/>
-          <cell r="S110"/>
-          <cell r="T110"/>
-          <cell r="U110"/>
-          <cell r="V110"/>
-          <cell r="W110"/>
-          <cell r="X110"/>
-        </row>
-        <row r="111">
-          <cell r="D111"/>
-          <cell r="E111"/>
-          <cell r="F111"/>
-          <cell r="G111"/>
-          <cell r="H111"/>
-          <cell r="I111"/>
-          <cell r="J111"/>
-          <cell r="K111"/>
-          <cell r="L111"/>
-          <cell r="M111"/>
-          <cell r="N111"/>
-          <cell r="O111"/>
-          <cell r="P111"/>
-          <cell r="Q111"/>
-          <cell r="R111"/>
-          <cell r="S111"/>
-          <cell r="T111"/>
-          <cell r="U111"/>
-          <cell r="V111"/>
-          <cell r="W111"/>
-          <cell r="X111"/>
-        </row>
-        <row r="112">
-          <cell r="D112"/>
-          <cell r="E112"/>
-          <cell r="F112"/>
-          <cell r="G112"/>
-          <cell r="H112"/>
-          <cell r="I112"/>
-          <cell r="J112"/>
-          <cell r="K112"/>
-          <cell r="L112"/>
-          <cell r="M112"/>
-          <cell r="N112"/>
-          <cell r="O112"/>
-          <cell r="P112"/>
-          <cell r="Q112"/>
-          <cell r="R112"/>
-          <cell r="S112"/>
-          <cell r="T112"/>
-          <cell r="U112"/>
-          <cell r="V112"/>
-          <cell r="W112"/>
-          <cell r="X112"/>
-        </row>
-        <row r="113">
-          <cell r="D113"/>
-          <cell r="E113"/>
-          <cell r="F113"/>
-          <cell r="G113"/>
-          <cell r="H113"/>
-          <cell r="I113"/>
-          <cell r="J113"/>
-          <cell r="K113"/>
-          <cell r="L113"/>
-          <cell r="M113"/>
-          <cell r="N113"/>
-          <cell r="O113"/>
-          <cell r="P113"/>
-          <cell r="Q113"/>
-          <cell r="R113"/>
-          <cell r="S113"/>
-          <cell r="T113"/>
-          <cell r="U113"/>
-          <cell r="V113"/>
-          <cell r="W113"/>
-          <cell r="X113"/>
-        </row>
-        <row r="114">
-          <cell r="D114"/>
-          <cell r="E114"/>
-          <cell r="F114"/>
-          <cell r="G114"/>
-          <cell r="H114"/>
-          <cell r="I114"/>
-          <cell r="J114"/>
-          <cell r="K114"/>
-          <cell r="L114"/>
-          <cell r="M114"/>
-          <cell r="N114"/>
-          <cell r="O114"/>
-          <cell r="P114"/>
-          <cell r="Q114"/>
-          <cell r="R114"/>
-          <cell r="S114"/>
-          <cell r="T114"/>
-          <cell r="U114"/>
-          <cell r="V114"/>
-          <cell r="W114"/>
-          <cell r="X114"/>
-        </row>
-        <row r="115">
-          <cell r="D115"/>
-          <cell r="E115"/>
-          <cell r="F115"/>
-          <cell r="G115"/>
-          <cell r="H115"/>
-          <cell r="I115"/>
-          <cell r="J115"/>
-          <cell r="K115"/>
-          <cell r="L115"/>
-          <cell r="M115"/>
-          <cell r="N115"/>
-          <cell r="O115"/>
-          <cell r="P115"/>
-          <cell r="Q115"/>
-          <cell r="R115"/>
-          <cell r="S115"/>
-          <cell r="T115"/>
-          <cell r="U115"/>
-          <cell r="V115"/>
-          <cell r="W115"/>
-          <cell r="X115"/>
-        </row>
-        <row r="116">
-          <cell r="D116"/>
-          <cell r="E116"/>
-          <cell r="F116"/>
-          <cell r="G116"/>
-          <cell r="H116"/>
-          <cell r="I116"/>
-          <cell r="J116"/>
-          <cell r="K116"/>
-          <cell r="L116"/>
-          <cell r="M116"/>
-          <cell r="N116"/>
-          <cell r="O116"/>
-          <cell r="P116"/>
-          <cell r="Q116"/>
-          <cell r="R116"/>
-          <cell r="S116"/>
-          <cell r="T116"/>
-          <cell r="U116"/>
-          <cell r="V116"/>
-          <cell r="W116"/>
-          <cell r="X116"/>
-        </row>
-        <row r="117">
-          <cell r="D117"/>
-          <cell r="E117"/>
-          <cell r="F117"/>
-          <cell r="G117"/>
-          <cell r="H117"/>
-          <cell r="I117"/>
-          <cell r="J117"/>
-          <cell r="K117"/>
-          <cell r="L117"/>
-          <cell r="M117"/>
-          <cell r="N117"/>
-          <cell r="O117"/>
-          <cell r="P117"/>
-          <cell r="Q117"/>
-          <cell r="R117"/>
-          <cell r="S117"/>
-          <cell r="T117"/>
-          <cell r="U117"/>
-          <cell r="V117"/>
-          <cell r="W117"/>
-          <cell r="X117"/>
-        </row>
-        <row r="118">
-          <cell r="D118"/>
-          <cell r="E118"/>
-          <cell r="F118"/>
-          <cell r="G118"/>
-          <cell r="H118"/>
-          <cell r="I118"/>
-          <cell r="J118"/>
-          <cell r="K118"/>
-          <cell r="L118"/>
-          <cell r="M118"/>
-          <cell r="N118"/>
-          <cell r="O118"/>
-          <cell r="P118"/>
-          <cell r="Q118"/>
-          <cell r="R118"/>
-          <cell r="S118"/>
-          <cell r="T118"/>
-          <cell r="U118"/>
-          <cell r="V118"/>
-          <cell r="W118"/>
-          <cell r="X118"/>
-        </row>
-        <row r="119">
-          <cell r="D119"/>
-          <cell r="E119"/>
-          <cell r="F119"/>
-          <cell r="G119"/>
-          <cell r="H119"/>
-          <cell r="I119"/>
-          <cell r="J119"/>
-          <cell r="K119"/>
-          <cell r="L119"/>
-          <cell r="M119"/>
-          <cell r="N119"/>
-          <cell r="O119"/>
-          <cell r="P119"/>
-          <cell r="Q119"/>
-          <cell r="R119"/>
-          <cell r="S119"/>
-          <cell r="T119"/>
-          <cell r="U119"/>
-          <cell r="V119"/>
-          <cell r="W119"/>
-          <cell r="X119"/>
-        </row>
-        <row r="120">
-          <cell r="D120"/>
-          <cell r="E120"/>
-          <cell r="F120"/>
-          <cell r="G120"/>
-          <cell r="H120"/>
-          <cell r="I120"/>
-          <cell r="J120"/>
-          <cell r="K120"/>
-          <cell r="L120"/>
-          <cell r="M120"/>
-          <cell r="N120"/>
-          <cell r="O120"/>
-          <cell r="P120"/>
-          <cell r="Q120"/>
-          <cell r="R120"/>
-          <cell r="S120"/>
-          <cell r="T120"/>
-          <cell r="U120"/>
-          <cell r="V120"/>
-          <cell r="W120"/>
-          <cell r="X120"/>
-        </row>
-        <row r="121">
-          <cell r="D121"/>
-          <cell r="E121"/>
-          <cell r="F121"/>
-          <cell r="G121"/>
-          <cell r="H121"/>
-          <cell r="I121"/>
-          <cell r="J121"/>
-          <cell r="K121"/>
-          <cell r="L121"/>
-          <cell r="M121"/>
-          <cell r="N121"/>
-          <cell r="O121"/>
-          <cell r="P121"/>
-          <cell r="Q121"/>
-          <cell r="R121"/>
-          <cell r="S121"/>
-          <cell r="T121"/>
-          <cell r="U121"/>
-          <cell r="V121"/>
-          <cell r="W121"/>
-          <cell r="X121"/>
-        </row>
-        <row r="122">
-          <cell r="D122"/>
-          <cell r="E122"/>
-          <cell r="F122"/>
-          <cell r="G122"/>
-          <cell r="H122"/>
-          <cell r="I122"/>
-          <cell r="J122"/>
-          <cell r="K122"/>
-          <cell r="L122"/>
-          <cell r="M122"/>
-          <cell r="N122"/>
-          <cell r="O122"/>
-          <cell r="P122"/>
-          <cell r="Q122"/>
-          <cell r="R122"/>
-          <cell r="S122"/>
-          <cell r="T122"/>
-          <cell r="U122"/>
-          <cell r="V122"/>
-          <cell r="W122"/>
-          <cell r="X122"/>
-        </row>
-        <row r="123">
-          <cell r="D123"/>
-          <cell r="E123"/>
-          <cell r="F123"/>
-          <cell r="G123"/>
-          <cell r="H123"/>
-          <cell r="I123"/>
-          <cell r="J123"/>
-          <cell r="K123"/>
-          <cell r="L123"/>
-          <cell r="M123"/>
-          <cell r="N123"/>
-          <cell r="O123"/>
-          <cell r="P123"/>
-          <cell r="Q123"/>
-          <cell r="R123"/>
-          <cell r="S123"/>
-          <cell r="T123"/>
-          <cell r="U123"/>
-          <cell r="V123"/>
-          <cell r="W123"/>
-          <cell r="X123"/>
-        </row>
-        <row r="124">
-          <cell r="D124"/>
-          <cell r="E124"/>
-          <cell r="F124"/>
-          <cell r="G124"/>
-          <cell r="H124"/>
-          <cell r="I124"/>
-          <cell r="J124"/>
-          <cell r="K124"/>
-          <cell r="L124"/>
-          <cell r="M124"/>
-          <cell r="N124"/>
-          <cell r="O124"/>
-          <cell r="P124"/>
-          <cell r="Q124"/>
-          <cell r="R124"/>
-          <cell r="S124"/>
-          <cell r="T124"/>
-          <cell r="U124"/>
-          <cell r="V124"/>
-          <cell r="W124"/>
-          <cell r="X124"/>
-        </row>
-        <row r="125">
-          <cell r="D125"/>
-          <cell r="E125"/>
-          <cell r="F125"/>
-          <cell r="G125"/>
-          <cell r="H125"/>
-          <cell r="I125"/>
-          <cell r="J125"/>
-          <cell r="K125"/>
-          <cell r="L125"/>
-          <cell r="M125"/>
-          <cell r="N125"/>
-          <cell r="O125"/>
-          <cell r="P125"/>
-          <cell r="Q125"/>
-          <cell r="R125"/>
-          <cell r="S125"/>
-          <cell r="T125"/>
-          <cell r="U125"/>
-          <cell r="V125"/>
-          <cell r="W125"/>
-          <cell r="X125"/>
-        </row>
-        <row r="126">
-          <cell r="D126"/>
-          <cell r="E126"/>
-          <cell r="F126"/>
-          <cell r="G126"/>
-          <cell r="H126"/>
-          <cell r="I126"/>
-          <cell r="J126"/>
-          <cell r="K126"/>
-          <cell r="L126"/>
-          <cell r="M126"/>
-          <cell r="N126"/>
-          <cell r="O126"/>
-          <cell r="P126"/>
-          <cell r="Q126"/>
-          <cell r="R126"/>
-          <cell r="S126"/>
-          <cell r="T126"/>
-          <cell r="U126"/>
-          <cell r="V126"/>
-          <cell r="W126"/>
-          <cell r="X126"/>
-        </row>
-        <row r="127">
-          <cell r="D127"/>
-          <cell r="E127"/>
-          <cell r="F127"/>
-          <cell r="G127"/>
-          <cell r="H127"/>
-          <cell r="I127"/>
-          <cell r="J127"/>
-          <cell r="K127"/>
-          <cell r="L127"/>
-          <cell r="M127"/>
-          <cell r="N127"/>
-          <cell r="O127"/>
-          <cell r="P127"/>
-          <cell r="Q127"/>
-          <cell r="R127"/>
-          <cell r="S127"/>
-          <cell r="T127"/>
-          <cell r="U127"/>
-          <cell r="V127"/>
-          <cell r="W127"/>
-          <cell r="X127"/>
-        </row>
-        <row r="128">
-          <cell r="D128"/>
-          <cell r="E128"/>
-          <cell r="F128"/>
-          <cell r="G128"/>
-          <cell r="H128"/>
-          <cell r="I128"/>
-          <cell r="J128"/>
-          <cell r="K128"/>
-          <cell r="L128"/>
-          <cell r="M128"/>
-          <cell r="N128"/>
-          <cell r="O128"/>
-          <cell r="P128"/>
-          <cell r="Q128"/>
-          <cell r="R128"/>
-          <cell r="S128"/>
-          <cell r="T128"/>
-          <cell r="U128"/>
-          <cell r="V128"/>
-          <cell r="W128"/>
-          <cell r="X128"/>
-        </row>
-        <row r="129">
-          <cell r="D129"/>
-          <cell r="E129"/>
-          <cell r="F129"/>
-          <cell r="G129"/>
-          <cell r="H129"/>
-          <cell r="I129"/>
-          <cell r="J129"/>
-          <cell r="K129"/>
-          <cell r="L129"/>
-          <cell r="M129"/>
-          <cell r="N129"/>
-          <cell r="O129"/>
-          <cell r="P129"/>
-          <cell r="Q129"/>
-          <cell r="R129"/>
-          <cell r="S129"/>
-          <cell r="T129"/>
-          <cell r="U129"/>
-          <cell r="V129"/>
-          <cell r="W129"/>
-          <cell r="X129"/>
-        </row>
-        <row r="130">
-          <cell r="D130"/>
-          <cell r="E130"/>
-          <cell r="F130"/>
-          <cell r="G130"/>
-          <cell r="H130"/>
-          <cell r="I130"/>
-          <cell r="J130"/>
-          <cell r="K130"/>
-          <cell r="L130"/>
-          <cell r="M130"/>
-          <cell r="N130"/>
-          <cell r="O130"/>
-          <cell r="P130"/>
-          <cell r="Q130"/>
-          <cell r="R130"/>
-          <cell r="S130"/>
-          <cell r="T130"/>
-          <cell r="U130"/>
-          <cell r="V130"/>
-          <cell r="W130"/>
-          <cell r="X130"/>
-        </row>
-        <row r="131">
-          <cell r="D131"/>
-          <cell r="E131"/>
-          <cell r="F131"/>
-          <cell r="G131"/>
-          <cell r="H131"/>
-          <cell r="I131"/>
-          <cell r="J131"/>
-          <cell r="K131"/>
-          <cell r="L131"/>
-          <cell r="M131"/>
-          <cell r="N131"/>
-          <cell r="O131"/>
-          <cell r="P131"/>
-          <cell r="Q131"/>
-          <cell r="R131"/>
-          <cell r="S131"/>
-          <cell r="T131"/>
-          <cell r="U131"/>
-          <cell r="V131"/>
-          <cell r="W131"/>
-          <cell r="X131"/>
-        </row>
-        <row r="132">
-          <cell r="D132"/>
-          <cell r="E132"/>
-          <cell r="F132"/>
-          <cell r="G132"/>
-          <cell r="H132"/>
-          <cell r="I132"/>
-          <cell r="J132"/>
-          <cell r="K132"/>
-          <cell r="L132"/>
-          <cell r="M132"/>
-          <cell r="N132"/>
-          <cell r="O132"/>
-          <cell r="P132"/>
-          <cell r="Q132"/>
-          <cell r="R132"/>
-          <cell r="S132"/>
-          <cell r="T132"/>
-          <cell r="U132"/>
-          <cell r="V132"/>
-          <cell r="W132"/>
-          <cell r="X132"/>
-        </row>
-        <row r="133">
-          <cell r="D133"/>
-          <cell r="E133"/>
-          <cell r="F133"/>
-          <cell r="G133"/>
-          <cell r="H133"/>
-          <cell r="I133"/>
-          <cell r="J133"/>
-          <cell r="K133"/>
-          <cell r="L133"/>
-          <cell r="M133"/>
-          <cell r="N133"/>
-          <cell r="O133"/>
-          <cell r="P133"/>
-          <cell r="Q133"/>
-          <cell r="R133"/>
-          <cell r="S133"/>
-          <cell r="T133"/>
-          <cell r="U133"/>
-          <cell r="V133"/>
-          <cell r="W133"/>
-          <cell r="X133"/>
-        </row>
-        <row r="134">
-          <cell r="D134"/>
-          <cell r="E134"/>
-          <cell r="F134"/>
-          <cell r="G134"/>
-          <cell r="H134"/>
-          <cell r="I134"/>
-          <cell r="J134"/>
-          <cell r="K134"/>
-          <cell r="L134"/>
-          <cell r="M134"/>
-          <cell r="N134"/>
-          <cell r="O134"/>
-          <cell r="P134"/>
-          <cell r="Q134"/>
-          <cell r="R134"/>
-          <cell r="S134"/>
-          <cell r="T134"/>
-          <cell r="U134"/>
-          <cell r="V134"/>
-          <cell r="W134"/>
-          <cell r="X134"/>
-        </row>
-        <row r="135">
-          <cell r="D135"/>
-          <cell r="E135"/>
-          <cell r="F135"/>
-          <cell r="G135"/>
-          <cell r="H135"/>
-          <cell r="I135"/>
-          <cell r="J135"/>
-          <cell r="K135"/>
-          <cell r="L135"/>
-          <cell r="M135"/>
-          <cell r="N135"/>
-          <cell r="O135"/>
-          <cell r="P135"/>
-          <cell r="Q135"/>
-          <cell r="R135"/>
-          <cell r="S135"/>
-          <cell r="T135"/>
-          <cell r="U135"/>
-          <cell r="V135"/>
-          <cell r="W135"/>
-          <cell r="X135"/>
-        </row>
-        <row r="136">
-          <cell r="D136"/>
-          <cell r="E136"/>
-          <cell r="F136"/>
-          <cell r="G136"/>
-          <cell r="H136"/>
-          <cell r="I136"/>
-          <cell r="J136"/>
-          <cell r="K136"/>
-          <cell r="L136"/>
-          <cell r="M136"/>
-          <cell r="N136"/>
-          <cell r="O136"/>
-          <cell r="P136"/>
-          <cell r="Q136"/>
-          <cell r="R136"/>
-          <cell r="S136"/>
-          <cell r="T136"/>
-          <cell r="U136"/>
-          <cell r="V136"/>
-          <cell r="W136"/>
-          <cell r="X136"/>
-        </row>
-        <row r="137">
-          <cell r="D137"/>
-          <cell r="E137"/>
-          <cell r="F137"/>
-          <cell r="G137"/>
-          <cell r="H137"/>
-          <cell r="I137"/>
-          <cell r="J137"/>
-          <cell r="K137"/>
-          <cell r="L137"/>
-          <cell r="M137"/>
-          <cell r="N137"/>
-          <cell r="O137"/>
-          <cell r="P137"/>
-          <cell r="Q137"/>
-          <cell r="R137"/>
-          <cell r="S137"/>
-          <cell r="T137"/>
-          <cell r="U137"/>
-          <cell r="V137"/>
-          <cell r="W137"/>
-          <cell r="X137"/>
-        </row>
-        <row r="138">
-          <cell r="D138"/>
-          <cell r="E138"/>
-          <cell r="F138"/>
-          <cell r="G138"/>
-          <cell r="H138"/>
-          <cell r="I138"/>
-          <cell r="J138"/>
-          <cell r="K138"/>
-          <cell r="L138"/>
-          <cell r="M138"/>
-          <cell r="N138"/>
-          <cell r="O138"/>
-          <cell r="P138"/>
-          <cell r="Q138"/>
-          <cell r="R138"/>
-          <cell r="S138"/>
-          <cell r="T138"/>
-          <cell r="U138"/>
-          <cell r="V138"/>
-          <cell r="W138"/>
-          <cell r="X138"/>
-        </row>
-        <row r="139">
-          <cell r="D139"/>
-          <cell r="E139"/>
-          <cell r="F139"/>
-          <cell r="G139"/>
-          <cell r="H139"/>
-          <cell r="I139"/>
-          <cell r="J139"/>
-          <cell r="K139"/>
-          <cell r="L139"/>
-          <cell r="M139"/>
-          <cell r="N139"/>
-          <cell r="O139"/>
-          <cell r="P139"/>
-          <cell r="Q139"/>
-          <cell r="R139"/>
-          <cell r="S139"/>
-          <cell r="T139"/>
-          <cell r="U139"/>
-          <cell r="V139"/>
-          <cell r="W139"/>
-          <cell r="X139"/>
-        </row>
-        <row r="140">
-          <cell r="D140"/>
-          <cell r="E140"/>
-          <cell r="F140"/>
-          <cell r="G140"/>
-          <cell r="H140"/>
-          <cell r="I140"/>
-          <cell r="J140"/>
-          <cell r="K140"/>
-          <cell r="L140"/>
-          <cell r="M140"/>
-          <cell r="N140"/>
-          <cell r="O140"/>
-          <cell r="P140"/>
-          <cell r="Q140"/>
-          <cell r="R140"/>
-          <cell r="S140"/>
-          <cell r="T140"/>
-          <cell r="U140"/>
-          <cell r="V140"/>
-          <cell r="W140"/>
-          <cell r="X140"/>
-        </row>
-        <row r="141">
-          <cell r="D141"/>
-          <cell r="E141"/>
-          <cell r="F141"/>
-          <cell r="G141"/>
-          <cell r="H141"/>
-          <cell r="I141"/>
-          <cell r="J141"/>
-          <cell r="K141"/>
-          <cell r="L141"/>
-          <cell r="M141"/>
-          <cell r="N141"/>
-          <cell r="O141"/>
-          <cell r="P141"/>
-          <cell r="Q141"/>
-          <cell r="R141"/>
-          <cell r="S141"/>
-          <cell r="T141"/>
-          <cell r="U141"/>
-          <cell r="V141"/>
-          <cell r="W141"/>
-          <cell r="X141"/>
-        </row>
-        <row r="142">
-          <cell r="D142"/>
-          <cell r="E142"/>
-          <cell r="F142"/>
-          <cell r="G142"/>
-          <cell r="H142"/>
-          <cell r="I142"/>
-          <cell r="J142"/>
-          <cell r="K142"/>
-          <cell r="L142"/>
-          <cell r="M142"/>
-          <cell r="N142"/>
-          <cell r="O142"/>
-          <cell r="P142"/>
-          <cell r="Q142"/>
-          <cell r="R142"/>
-          <cell r="S142"/>
-          <cell r="T142"/>
-          <cell r="U142"/>
-          <cell r="V142"/>
-          <cell r="W142"/>
-          <cell r="X142"/>
-        </row>
-        <row r="143">
-          <cell r="D143"/>
-          <cell r="E143"/>
-          <cell r="F143"/>
-          <cell r="G143"/>
-          <cell r="H143"/>
-          <cell r="I143"/>
-          <cell r="J143"/>
-          <cell r="K143"/>
-          <cell r="L143"/>
-          <cell r="M143"/>
-          <cell r="N143"/>
-          <cell r="O143"/>
-          <cell r="P143"/>
-          <cell r="Q143"/>
-          <cell r="R143"/>
-          <cell r="S143"/>
-          <cell r="T143"/>
-          <cell r="U143"/>
-          <cell r="V143"/>
-          <cell r="W143"/>
-          <cell r="X143"/>
-        </row>
-        <row r="144">
-          <cell r="D144"/>
-          <cell r="E144"/>
-          <cell r="F144"/>
-          <cell r="G144"/>
-          <cell r="H144"/>
-          <cell r="I144"/>
-          <cell r="J144"/>
-          <cell r="K144"/>
-          <cell r="L144"/>
-          <cell r="M144"/>
-          <cell r="N144"/>
-          <cell r="O144"/>
-          <cell r="P144"/>
-          <cell r="Q144"/>
-          <cell r="R144"/>
-          <cell r="S144"/>
-          <cell r="T144"/>
-          <cell r="U144"/>
-          <cell r="V144"/>
-          <cell r="W144"/>
-          <cell r="X144"/>
-        </row>
-        <row r="145">
-          <cell r="D145"/>
-          <cell r="E145"/>
-          <cell r="F145"/>
-          <cell r="G145"/>
-          <cell r="H145"/>
-          <cell r="I145"/>
-          <cell r="J145"/>
-          <cell r="K145"/>
-          <cell r="L145"/>
-          <cell r="M145"/>
-          <cell r="N145"/>
-          <cell r="O145"/>
-          <cell r="P145"/>
-          <cell r="Q145"/>
-          <cell r="R145"/>
-          <cell r="S145"/>
-          <cell r="T145"/>
-          <cell r="U145"/>
-          <cell r="V145"/>
-          <cell r="W145"/>
-          <cell r="X145"/>
-        </row>
-        <row r="146">
-          <cell r="D146"/>
-          <cell r="E146"/>
-          <cell r="F146"/>
-          <cell r="G146"/>
-          <cell r="H146"/>
-          <cell r="I146"/>
-          <cell r="J146"/>
-          <cell r="K146"/>
-          <cell r="L146"/>
-          <cell r="M146"/>
-          <cell r="N146"/>
-          <cell r="O146"/>
-          <cell r="P146"/>
-          <cell r="Q146"/>
-          <cell r="R146"/>
-          <cell r="S146"/>
-          <cell r="T146"/>
-          <cell r="U146"/>
-          <cell r="V146"/>
-          <cell r="W146"/>
-          <cell r="X146"/>
-        </row>
-        <row r="147">
-          <cell r="D147"/>
-          <cell r="E147"/>
-          <cell r="F147"/>
-          <cell r="G147"/>
-          <cell r="H147"/>
-          <cell r="I147"/>
-          <cell r="J147"/>
-          <cell r="K147"/>
-          <cell r="L147"/>
-          <cell r="M147"/>
-          <cell r="N147"/>
-          <cell r="O147"/>
-          <cell r="P147"/>
-          <cell r="Q147"/>
-          <cell r="R147"/>
-          <cell r="S147"/>
-          <cell r="T147"/>
-          <cell r="U147"/>
-          <cell r="V147"/>
-          <cell r="W147"/>
-          <cell r="X147"/>
-        </row>
-        <row r="148">
-          <cell r="D148"/>
-          <cell r="E148"/>
-          <cell r="F148"/>
-          <cell r="G148"/>
-          <cell r="H148"/>
-          <cell r="I148"/>
-          <cell r="J148"/>
-          <cell r="K148"/>
-          <cell r="L148"/>
-          <cell r="M148"/>
-          <cell r="N148"/>
-          <cell r="O148"/>
-          <cell r="P148"/>
-          <cell r="Q148"/>
-          <cell r="R148"/>
-          <cell r="S148"/>
-          <cell r="T148"/>
-          <cell r="U148"/>
-          <cell r="V148"/>
-          <cell r="W148"/>
-          <cell r="X148"/>
-        </row>
-        <row r="149">
-          <cell r="D149"/>
-          <cell r="E149"/>
-          <cell r="F149"/>
-          <cell r="G149"/>
-          <cell r="H149"/>
-          <cell r="I149"/>
-          <cell r="J149"/>
-          <cell r="K149"/>
-          <cell r="L149"/>
-          <cell r="M149"/>
-          <cell r="N149"/>
-          <cell r="O149"/>
-          <cell r="P149"/>
-          <cell r="Q149"/>
-          <cell r="R149"/>
-          <cell r="S149"/>
-          <cell r="T149"/>
-          <cell r="U149"/>
-          <cell r="V149"/>
-          <cell r="W149"/>
-          <cell r="X149"/>
-        </row>
-        <row r="150">
-          <cell r="D150"/>
-          <cell r="E150"/>
-          <cell r="F150"/>
-          <cell r="G150"/>
-          <cell r="H150"/>
-          <cell r="I150"/>
-          <cell r="J150"/>
-          <cell r="K150"/>
-          <cell r="L150"/>
-          <cell r="M150"/>
-          <cell r="N150"/>
-          <cell r="O150"/>
-          <cell r="P150"/>
-          <cell r="Q150"/>
-          <cell r="R150"/>
-          <cell r="S150"/>
-          <cell r="T150"/>
-          <cell r="U150"/>
-          <cell r="V150"/>
-          <cell r="W150"/>
-          <cell r="X150"/>
-        </row>
-        <row r="151">
-          <cell r="D151"/>
-          <cell r="E151"/>
-          <cell r="F151"/>
-          <cell r="G151"/>
-          <cell r="H151"/>
-          <cell r="I151"/>
-          <cell r="J151"/>
-          <cell r="K151"/>
-          <cell r="L151"/>
-          <cell r="M151"/>
-          <cell r="N151"/>
-          <cell r="O151"/>
-          <cell r="P151"/>
-          <cell r="Q151"/>
-          <cell r="R151"/>
-          <cell r="S151"/>
-          <cell r="T151"/>
-          <cell r="U151"/>
-          <cell r="V151"/>
-          <cell r="W151"/>
-          <cell r="X151"/>
-        </row>
-        <row r="152">
-          <cell r="D152"/>
-          <cell r="E152"/>
-          <cell r="F152"/>
-          <cell r="G152"/>
-          <cell r="H152"/>
-          <cell r="I152"/>
-          <cell r="J152"/>
-          <cell r="K152"/>
-          <cell r="L152"/>
-          <cell r="M152"/>
-          <cell r="N152"/>
-          <cell r="O152"/>
-          <cell r="P152"/>
-          <cell r="Q152"/>
-          <cell r="R152"/>
-          <cell r="S152"/>
-          <cell r="T152"/>
-          <cell r="U152"/>
-          <cell r="V152"/>
-          <cell r="W152"/>
-          <cell r="X152"/>
-        </row>
-        <row r="153">
-          <cell r="D153"/>
-          <cell r="E153"/>
-          <cell r="F153"/>
-          <cell r="G153"/>
-          <cell r="H153"/>
-          <cell r="I153"/>
-          <cell r="J153"/>
-          <cell r="K153"/>
-          <cell r="L153"/>
-          <cell r="M153"/>
-          <cell r="N153"/>
-          <cell r="O153"/>
-          <cell r="P153"/>
-          <cell r="Q153"/>
-          <cell r="R153"/>
-          <cell r="S153"/>
-          <cell r="T153"/>
-          <cell r="U153"/>
-          <cell r="V153"/>
-          <cell r="W153"/>
-          <cell r="X153"/>
-        </row>
-        <row r="154">
-          <cell r="D154"/>
-          <cell r="E154"/>
-          <cell r="F154"/>
-          <cell r="G154"/>
-          <cell r="H154"/>
-          <cell r="I154"/>
-          <cell r="J154"/>
-          <cell r="K154"/>
-          <cell r="L154"/>
-          <cell r="M154"/>
-          <cell r="N154"/>
-          <cell r="O154"/>
-          <cell r="P154"/>
-          <cell r="Q154"/>
-          <cell r="R154"/>
-          <cell r="S154"/>
-          <cell r="T154"/>
-          <cell r="U154"/>
-          <cell r="V154"/>
-          <cell r="W154"/>
-          <cell r="X154"/>
-        </row>
-        <row r="155">
-          <cell r="D155"/>
-          <cell r="E155"/>
-          <cell r="F155"/>
-          <cell r="G155"/>
-          <cell r="H155"/>
-          <cell r="I155"/>
-          <cell r="J155"/>
-          <cell r="K155"/>
-          <cell r="L155"/>
-          <cell r="M155"/>
-          <cell r="N155"/>
-          <cell r="O155"/>
-          <cell r="P155"/>
-          <cell r="Q155"/>
-          <cell r="R155"/>
-          <cell r="S155"/>
-          <cell r="T155"/>
-          <cell r="U155"/>
-          <cell r="V155"/>
-          <cell r="W155"/>
-          <cell r="X155"/>
-        </row>
-        <row r="156">
-          <cell r="D156"/>
-          <cell r="E156"/>
-          <cell r="F156"/>
-          <cell r="G156"/>
-          <cell r="H156"/>
-          <cell r="I156"/>
-          <cell r="J156"/>
-          <cell r="K156"/>
-          <cell r="L156"/>
-          <cell r="M156"/>
-          <cell r="N156"/>
-          <cell r="O156"/>
-          <cell r="P156"/>
-          <cell r="Q156"/>
-          <cell r="R156"/>
-          <cell r="S156"/>
-          <cell r="T156"/>
-          <cell r="U156"/>
-          <cell r="V156"/>
-          <cell r="W156"/>
-          <cell r="X156"/>
-        </row>
-        <row r="157">
-          <cell r="D157"/>
-          <cell r="E157"/>
-          <cell r="F157"/>
-          <cell r="G157"/>
-          <cell r="H157"/>
-          <cell r="I157"/>
-          <cell r="J157"/>
-          <cell r="K157"/>
-          <cell r="L157"/>
-          <cell r="M157"/>
-          <cell r="N157"/>
-          <cell r="O157"/>
-          <cell r="P157"/>
-          <cell r="Q157"/>
-          <cell r="R157"/>
-          <cell r="S157"/>
-          <cell r="T157"/>
-          <cell r="U157"/>
-          <cell r="V157"/>
-          <cell r="W157"/>
-          <cell r="X157"/>
-        </row>
-        <row r="158">
-          <cell r="D158"/>
-          <cell r="E158"/>
-          <cell r="F158"/>
-          <cell r="G158"/>
-          <cell r="H158"/>
-          <cell r="I158"/>
-          <cell r="J158"/>
-          <cell r="K158"/>
-          <cell r="L158"/>
-          <cell r="M158"/>
-          <cell r="N158"/>
-          <cell r="O158"/>
-          <cell r="P158"/>
-          <cell r="Q158"/>
-          <cell r="R158"/>
-          <cell r="S158"/>
-          <cell r="T158"/>
-          <cell r="U158"/>
-          <cell r="V158"/>
-          <cell r="W158"/>
-          <cell r="X158"/>
-        </row>
-        <row r="159">
-          <cell r="D159"/>
-          <cell r="E159"/>
-          <cell r="F159"/>
-          <cell r="G159"/>
-          <cell r="H159"/>
-          <cell r="I159"/>
-          <cell r="J159"/>
-          <cell r="K159"/>
-          <cell r="L159"/>
-          <cell r="M159"/>
-          <cell r="N159"/>
-          <cell r="O159"/>
-          <cell r="P159"/>
-          <cell r="Q159"/>
-          <cell r="R159"/>
-          <cell r="S159"/>
-          <cell r="T159"/>
-          <cell r="U159"/>
-          <cell r="V159"/>
-          <cell r="W159"/>
-          <cell r="X159"/>
-        </row>
-        <row r="160">
-          <cell r="D160"/>
-          <cell r="E160"/>
-          <cell r="F160"/>
-          <cell r="G160"/>
-          <cell r="H160"/>
-          <cell r="I160"/>
-          <cell r="J160"/>
-          <cell r="K160"/>
-          <cell r="L160"/>
-          <cell r="M160"/>
-          <cell r="N160"/>
-          <cell r="O160"/>
-          <cell r="P160"/>
-          <cell r="Q160"/>
-          <cell r="R160"/>
-          <cell r="S160"/>
-          <cell r="T160"/>
-          <cell r="U160"/>
-          <cell r="V160"/>
-          <cell r="W160"/>
-          <cell r="X160"/>
-        </row>
-        <row r="161">
-          <cell r="D161"/>
-          <cell r="E161"/>
-          <cell r="F161"/>
-          <cell r="G161"/>
-          <cell r="H161"/>
-          <cell r="I161"/>
-          <cell r="J161"/>
-          <cell r="K161"/>
-          <cell r="L161"/>
-          <cell r="M161"/>
-          <cell r="N161"/>
-          <cell r="O161"/>
-          <cell r="P161"/>
-          <cell r="Q161"/>
-          <cell r="R161"/>
-          <cell r="S161"/>
-          <cell r="T161"/>
-          <cell r="U161"/>
-          <cell r="V161"/>
-          <cell r="W161"/>
-          <cell r="X161"/>
-        </row>
-        <row r="162">
-          <cell r="D162"/>
-          <cell r="E162"/>
-          <cell r="F162"/>
-          <cell r="G162"/>
-          <cell r="H162"/>
-          <cell r="I162"/>
-          <cell r="J162"/>
-          <cell r="K162"/>
-          <cell r="L162"/>
-          <cell r="M162"/>
-          <cell r="N162"/>
-          <cell r="O162"/>
-          <cell r="P162"/>
-          <cell r="Q162"/>
-          <cell r="R162"/>
-          <cell r="S162"/>
-          <cell r="T162"/>
-          <cell r="U162"/>
-          <cell r="V162"/>
-          <cell r="W162"/>
-          <cell r="X162"/>
-        </row>
-        <row r="163">
-          <cell r="D163"/>
-          <cell r="E163"/>
-          <cell r="F163"/>
-          <cell r="G163"/>
-          <cell r="H163"/>
-          <cell r="I163"/>
-          <cell r="J163"/>
-          <cell r="K163"/>
-          <cell r="L163"/>
-          <cell r="M163"/>
-          <cell r="N163"/>
-          <cell r="O163"/>
-          <cell r="P163"/>
-          <cell r="Q163"/>
-          <cell r="R163"/>
-          <cell r="S163"/>
-          <cell r="T163"/>
-          <cell r="U163"/>
-          <cell r="V163"/>
-          <cell r="W163"/>
-          <cell r="X163"/>
-        </row>
-        <row r="164">
-          <cell r="D164"/>
-          <cell r="E164"/>
-          <cell r="F164"/>
-          <cell r="G164"/>
-          <cell r="H164"/>
-          <cell r="I164"/>
-          <cell r="J164"/>
-          <cell r="K164"/>
-          <cell r="L164"/>
-          <cell r="M164"/>
-          <cell r="N164"/>
-          <cell r="O164"/>
-          <cell r="P164"/>
-          <cell r="Q164"/>
-          <cell r="R164"/>
-          <cell r="S164"/>
-          <cell r="T164"/>
-          <cell r="U164"/>
-          <cell r="V164"/>
-          <cell r="W164"/>
-          <cell r="X164"/>
-        </row>
-        <row r="165">
-          <cell r="D165"/>
-          <cell r="E165"/>
-          <cell r="F165"/>
-          <cell r="G165"/>
-          <cell r="H165"/>
-          <cell r="I165"/>
-          <cell r="J165"/>
-          <cell r="K165"/>
-          <cell r="L165"/>
-          <cell r="M165"/>
-          <cell r="N165"/>
-          <cell r="O165"/>
-          <cell r="P165"/>
-          <cell r="Q165"/>
-          <cell r="R165"/>
-          <cell r="S165"/>
-          <cell r="T165"/>
-          <cell r="U165"/>
-          <cell r="V165"/>
-          <cell r="W165"/>
-          <cell r="X165"/>
-        </row>
-        <row r="166">
-          <cell r="D166"/>
-          <cell r="E166"/>
-          <cell r="F166"/>
-          <cell r="G166"/>
-          <cell r="H166"/>
-          <cell r="I166"/>
-          <cell r="J166"/>
-          <cell r="K166"/>
-          <cell r="L166"/>
-          <cell r="M166"/>
-          <cell r="N166"/>
-          <cell r="O166"/>
-          <cell r="P166"/>
-          <cell r="Q166"/>
-          <cell r="R166"/>
-          <cell r="S166"/>
-          <cell r="T166"/>
-          <cell r="U166"/>
-          <cell r="V166"/>
-          <cell r="W166"/>
-          <cell r="X166"/>
-        </row>
-        <row r="167">
-          <cell r="D167"/>
-          <cell r="E167"/>
-          <cell r="F167"/>
-          <cell r="G167"/>
-          <cell r="H167"/>
-          <cell r="I167"/>
-          <cell r="J167"/>
-          <cell r="K167"/>
-          <cell r="L167"/>
-          <cell r="M167"/>
-          <cell r="N167"/>
-          <cell r="O167"/>
-          <cell r="P167"/>
-          <cell r="Q167"/>
-          <cell r="R167"/>
-          <cell r="S167"/>
-          <cell r="T167"/>
-          <cell r="U167"/>
-          <cell r="V167"/>
-          <cell r="W167"/>
-          <cell r="X167"/>
-        </row>
-        <row r="168">
-          <cell r="D168"/>
-          <cell r="E168"/>
-          <cell r="F168"/>
-          <cell r="G168"/>
-          <cell r="H168"/>
-          <cell r="I168"/>
-          <cell r="J168"/>
-          <cell r="K168"/>
-          <cell r="L168"/>
-          <cell r="M168"/>
-          <cell r="N168"/>
-          <cell r="O168"/>
-          <cell r="P168"/>
-          <cell r="Q168"/>
-          <cell r="R168"/>
-          <cell r="S168"/>
-          <cell r="T168"/>
-          <cell r="U168"/>
-          <cell r="V168"/>
-          <cell r="W168"/>
-          <cell r="X168"/>
-        </row>
-        <row r="169">
-          <cell r="D169"/>
-          <cell r="E169"/>
-          <cell r="F169"/>
-          <cell r="G169"/>
-          <cell r="H169"/>
-          <cell r="I169"/>
-          <cell r="J169"/>
-          <cell r="K169"/>
-          <cell r="L169"/>
-          <cell r="M169"/>
-          <cell r="N169"/>
-          <cell r="O169"/>
-          <cell r="P169"/>
-          <cell r="Q169"/>
-          <cell r="R169"/>
-          <cell r="S169"/>
-          <cell r="T169"/>
-          <cell r="U169"/>
-          <cell r="V169"/>
-          <cell r="W169"/>
-          <cell r="X169"/>
-        </row>
-        <row r="170">
-          <cell r="D170"/>
-          <cell r="E170"/>
-          <cell r="F170"/>
-          <cell r="G170"/>
-          <cell r="H170"/>
-          <cell r="I170"/>
-          <cell r="J170"/>
-          <cell r="K170"/>
-          <cell r="L170"/>
-          <cell r="M170"/>
-          <cell r="N170"/>
-          <cell r="O170"/>
-          <cell r="P170"/>
-          <cell r="Q170"/>
-          <cell r="R170"/>
-          <cell r="S170"/>
-          <cell r="T170"/>
-          <cell r="U170"/>
-          <cell r="V170"/>
-          <cell r="W170"/>
-          <cell r="X170"/>
-        </row>
-        <row r="171">
-          <cell r="D171"/>
-          <cell r="E171"/>
-          <cell r="F171"/>
-          <cell r="G171"/>
-          <cell r="H171"/>
-          <cell r="I171"/>
-          <cell r="J171"/>
-          <cell r="K171"/>
-          <cell r="L171"/>
-          <cell r="M171"/>
-          <cell r="N171"/>
-          <cell r="O171"/>
-          <cell r="P171"/>
-          <cell r="Q171"/>
-          <cell r="R171"/>
-          <cell r="S171"/>
-          <cell r="T171"/>
-          <cell r="U171"/>
-          <cell r="V171"/>
-          <cell r="W171"/>
-          <cell r="X171"/>
-        </row>
-        <row r="172">
-          <cell r="D172"/>
-          <cell r="E172"/>
-          <cell r="F172"/>
-          <cell r="G172"/>
-          <cell r="H172"/>
-          <cell r="I172"/>
-          <cell r="J172"/>
-          <cell r="K172"/>
-          <cell r="L172"/>
-          <cell r="M172"/>
-          <cell r="N172"/>
-          <cell r="O172"/>
-          <cell r="P172"/>
-          <cell r="Q172"/>
-          <cell r="R172"/>
-          <cell r="S172"/>
-          <cell r="T172"/>
-          <cell r="U172"/>
-          <cell r="V172"/>
-          <cell r="W172"/>
-          <cell r="X172"/>
-        </row>
-        <row r="173">
-          <cell r="D173"/>
-          <cell r="E173"/>
-          <cell r="F173"/>
-          <cell r="G173"/>
-          <cell r="H173"/>
-          <cell r="I173"/>
-          <cell r="J173"/>
-          <cell r="K173"/>
-          <cell r="L173"/>
-          <cell r="M173"/>
-          <cell r="N173"/>
-          <cell r="O173"/>
-          <cell r="P173"/>
-          <cell r="Q173"/>
-          <cell r="R173"/>
-          <cell r="S173"/>
-          <cell r="T173"/>
-          <cell r="U173"/>
-          <cell r="V173"/>
-          <cell r="W173"/>
-          <cell r="X173"/>
-        </row>
-        <row r="174">
-          <cell r="D174"/>
-          <cell r="E174"/>
-          <cell r="F174"/>
-          <cell r="G174"/>
-          <cell r="H174"/>
-          <cell r="I174"/>
-          <cell r="J174"/>
-          <cell r="K174"/>
-          <cell r="L174"/>
-          <cell r="M174"/>
-          <cell r="N174"/>
-          <cell r="O174"/>
-          <cell r="P174"/>
-          <cell r="Q174"/>
-          <cell r="R174"/>
-          <cell r="S174"/>
-          <cell r="T174"/>
-          <cell r="U174"/>
-          <cell r="V174"/>
-          <cell r="W174"/>
-          <cell r="X174"/>
-        </row>
-        <row r="175">
-          <cell r="D175"/>
-          <cell r="E175"/>
-          <cell r="F175"/>
-          <cell r="G175"/>
-          <cell r="H175"/>
-          <cell r="I175"/>
-          <cell r="J175"/>
-          <cell r="K175"/>
-          <cell r="L175"/>
-          <cell r="M175"/>
-          <cell r="N175"/>
-          <cell r="O175"/>
-          <cell r="P175"/>
-          <cell r="Q175"/>
-          <cell r="R175"/>
-          <cell r="S175"/>
-          <cell r="T175"/>
-          <cell r="U175"/>
-          <cell r="V175"/>
-          <cell r="W175"/>
-          <cell r="X175"/>
-        </row>
-        <row r="176">
-          <cell r="D176"/>
-          <cell r="E176"/>
-          <cell r="F176"/>
-          <cell r="G176"/>
-          <cell r="H176"/>
-          <cell r="I176"/>
-          <cell r="J176"/>
-          <cell r="K176"/>
-          <cell r="L176"/>
-          <cell r="M176"/>
-          <cell r="N176"/>
-          <cell r="O176"/>
-          <cell r="P176"/>
-          <cell r="Q176"/>
-          <cell r="R176"/>
-          <cell r="S176"/>
-          <cell r="T176"/>
-          <cell r="U176"/>
-          <cell r="V176"/>
-          <cell r="W176"/>
-          <cell r="X176"/>
-        </row>
-        <row r="177">
-          <cell r="D177"/>
-          <cell r="E177"/>
-          <cell r="F177"/>
-          <cell r="G177"/>
-          <cell r="H177"/>
-          <cell r="I177"/>
-          <cell r="J177"/>
-          <cell r="K177"/>
-          <cell r="L177"/>
-          <cell r="M177"/>
-          <cell r="N177"/>
-          <cell r="O177"/>
-          <cell r="P177"/>
-          <cell r="Q177"/>
-          <cell r="R177"/>
-          <cell r="S177"/>
-          <cell r="T177"/>
-          <cell r="U177"/>
-          <cell r="V177"/>
-          <cell r="W177"/>
-          <cell r="X177"/>
-        </row>
-        <row r="178">
-          <cell r="D178"/>
-          <cell r="E178"/>
-          <cell r="F178"/>
-          <cell r="G178"/>
-          <cell r="H178"/>
-          <cell r="I178"/>
-          <cell r="J178"/>
-          <cell r="K178"/>
-          <cell r="L178"/>
-          <cell r="M178"/>
-          <cell r="N178"/>
-          <cell r="O178"/>
-          <cell r="P178"/>
-          <cell r="Q178"/>
-          <cell r="R178"/>
-          <cell r="S178"/>
-          <cell r="T178"/>
-          <cell r="U178"/>
-          <cell r="V178"/>
-          <cell r="W178"/>
-          <cell r="X178"/>
-        </row>
-        <row r="179">
-          <cell r="D179"/>
-          <cell r="E179"/>
-          <cell r="F179"/>
-          <cell r="G179"/>
-          <cell r="H179"/>
-          <cell r="I179"/>
-          <cell r="J179"/>
-          <cell r="K179"/>
-          <cell r="L179"/>
-          <cell r="M179"/>
-          <cell r="N179"/>
-          <cell r="O179"/>
-          <cell r="P179"/>
-          <cell r="Q179"/>
-          <cell r="R179"/>
-          <cell r="S179"/>
-          <cell r="T179"/>
-          <cell r="U179"/>
-          <cell r="V179"/>
-          <cell r="W179"/>
-          <cell r="X179"/>
-        </row>
-        <row r="180">
-          <cell r="D180"/>
-          <cell r="E180"/>
-          <cell r="F180"/>
-          <cell r="G180"/>
-          <cell r="H180"/>
-          <cell r="I180"/>
-          <cell r="J180"/>
-          <cell r="K180"/>
-          <cell r="L180"/>
-          <cell r="M180"/>
-          <cell r="N180"/>
-          <cell r="O180"/>
-          <cell r="P180"/>
-          <cell r="Q180"/>
-          <cell r="R180"/>
-          <cell r="S180"/>
-          <cell r="T180"/>
-          <cell r="U180"/>
-          <cell r="V180"/>
-          <cell r="W180"/>
-          <cell r="X180"/>
-        </row>
-        <row r="181">
-          <cell r="D181"/>
-          <cell r="E181"/>
-          <cell r="F181"/>
-          <cell r="G181"/>
-          <cell r="H181"/>
-          <cell r="I181"/>
-          <cell r="J181"/>
-          <cell r="K181"/>
-          <cell r="L181"/>
-          <cell r="M181"/>
-          <cell r="N181"/>
-          <cell r="O181"/>
-          <cell r="P181"/>
-          <cell r="Q181"/>
-          <cell r="R181"/>
-          <cell r="S181"/>
-          <cell r="T181"/>
-          <cell r="U181"/>
-          <cell r="V181"/>
-          <cell r="W181"/>
-          <cell r="X181"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -23380,7 +19976,7 @@
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>7.6237974976589857</v>
+        <v>7.6237974976589866</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -23515,7 +20111,7 @@
       </c>
       <c r="E5" s="5">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>14.138979689921969</v>
+        <v>14.13897968992198</v>
       </c>
       <c r="F5" s="5">
         <f>-VLOOKUP(A5,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -23611,7 +20207,7 @@
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.50131716872622811</v>
+        <v>0.50131716872622822</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23735,11 +20331,11 @@
       </c>
       <c r="E10" s="5">
         <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>4.1278919748299394</v>
+        <v>2.502891974829939</v>
       </c>
       <c r="F10" s="5">
         <f>-VLOOKUP(A10,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="G10" s="7">
         <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -23751,7 +20347,7 @@
       </c>
       <c r="I10" s="7">
         <f>VLOOKUP(A10,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.5623371857857451E-2</v>
+        <v>3.5779556566005427E-2</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>443</v>
@@ -23787,7 +20383,7 @@
       </c>
       <c r="G11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.39463016781725752</v>
+        <v>0.39463016781725763</v>
       </c>
       <c r="H11" s="7">
         <f>VLOOKUP(A11,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -23823,7 +20419,7 @@
       </c>
       <c r="E12" s="5">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>5.391134817228437</v>
+        <v>5.3911348172284379</v>
       </c>
       <c r="F12" s="5">
         <f>-VLOOKUP(A12,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -23831,7 +20427,7 @@
       </c>
       <c r="G12" s="7">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.25478768357222192</v>
+        <v>0.25478768357222198</v>
       </c>
       <c r="H12" s="7">
         <f>VLOOKUP(A12,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -26004,9 +22600,12 @@
       <c r="H11" s="1" t="s">
         <v>451</v>
       </c>
+      <c r="J11" s="1" t="s">
+        <v>388</v>
+      </c>
       <c r="K11" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4108FE-80BB-2B4C-A765-9FDFACF913CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6CCB3D-F4EA-2A4D-9B48-98C4E2595AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="18760" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="18760" windowHeight="19960" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -22595,7 +22595,7 @@
         <v>-144</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>451</v>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6CCB3D-F4EA-2A4D-9B48-98C4E2595AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A363B56D-BD1B-7942-8E56-559FA91DABD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="18760" windowHeight="19960" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="462">
   <si>
     <t>Team</t>
   </si>
@@ -22628,14 +22628,17 @@
         <v>-142</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>451</v>
       </c>
+      <c r="J12" s="1" t="s">
+        <v>389</v>
+      </c>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1.0649999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DB9FF3-87F2-9642-A5D4-10B69171EB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDED37A-4651-AB48-8E2F-E514F1935E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="18760" windowHeight="19960" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="1700" yWindow="780" windowWidth="14900" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="465">
   <si>
     <t>Team</t>
   </si>
@@ -1609,22 +1609,22 @@
             <v>Illinois</v>
           </cell>
           <cell r="E2">
-            <v>5.449294502348879</v>
+            <v>5.7742945023488801</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.5731230652375563</v>
+            <v>0.56882889622899346</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>9.4144033635334745E-2</v>
+            <v>8.5946074618987622E-2</v>
           </cell>
           <cell r="J2">
-            <v>0.34694764321218979</v>
+            <v>0.34694764321219002</v>
           </cell>
           <cell r="K2">
             <v>0</v>
@@ -1635,28 +1635,28 @@
             <v>2</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Purdue</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Texas</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="E3">
-            <v>10.092842152691439</v>
+            <v>10.17544759009586</v>
           </cell>
           <cell r="F3" t="b">
             <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.55203428057968584</v>
+            <v>0.55407571254869992</v>
           </cell>
           <cell r="H3">
             <v>0</v>
           </cell>
           <cell r="I3">
-            <v>5.3883626561218478E-2</v>
+            <v>5.7780905774790781E-2</v>
           </cell>
           <cell r="J3">
-            <v>0.43952016208204348</v>
+            <v>0.44652162262184503</v>
           </cell>
           <cell r="K3">
             <v>0</v>
@@ -1667,28 +1667,28 @@
             <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Illinois</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Houston</v>
+            <v>Iowa</v>
           </cell>
           <cell r="E4">
-            <v>-2.2722659968097489</v>
+            <v>6.2329743724806317</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.50567810343901931</v>
+            <v>0.58006544201941912</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>-3.4614529798235823E-2</v>
+            <v>0.10739766203707291</v>
           </cell>
           <cell r="J4">
-            <v>5.9410701506423469E-2</v>
+            <v>0.38710225177014629</v>
           </cell>
           <cell r="K4">
             <v>0</v>
@@ -1699,28 +1699,28 @@
             <v>4</v>
           </cell>
           <cell r="C5" t="str">
+            <v>Purdue</v>
+          </cell>
+          <cell r="D5" t="str">
             <v>Texas</v>
           </cell>
-          <cell r="D5" t="str">
-            <v>Purdue</v>
-          </cell>
           <cell r="E5">
-            <v>-4.9701845204405686</v>
+            <v>9.7678421526914398</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.57509602242469182</v>
+            <v>0.55635736390936186</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>9.7910588265320841E-2</v>
+            <v>6.2136785645145347E-2</v>
           </cell>
           <cell r="J5">
-            <v>2.1099126100401319E-2</v>
+            <v>0.43952016208204359</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1730,23 +1730,29 @@
           <cell r="B6">
             <v>5</v>
           </cell>
+          <cell r="C6" t="str">
+            <v>Duke</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>St. John's</v>
+          </cell>
           <cell r="E6">
-            <v>0</v>
-          </cell>
-          <cell r="F6">
+            <v>11.225624027579791</v>
+          </cell>
+          <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0</v>
+            <v>0.59827880603963801</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>0</v>
+            <v>0.14216862971203631</v>
           </cell>
           <cell r="J6">
-            <v>0</v>
+            <v>0.57242552718101858</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1756,23 +1762,29 @@
           <cell r="B7">
             <v>6</v>
           </cell>
+          <cell r="C7" t="str">
+            <v>Iowa State</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Tennessee</v>
+          </cell>
           <cell r="E7">
-            <v>0</v>
-          </cell>
-          <cell r="F7">
+            <v>6.169396104264961</v>
+          </cell>
+          <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0</v>
+            <v>0.55392620988041141</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>0</v>
+            <v>5.7495491589876317E-2</v>
           </cell>
           <cell r="J7">
-            <v>0</v>
+            <v>0.32440678103529191</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1782,23 +1794,29 @@
           <cell r="B8">
             <v>7</v>
           </cell>
+          <cell r="C8" t="str">
+            <v>Uconn</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Michigan State</v>
+          </cell>
           <cell r="E8">
-            <v>0</v>
-          </cell>
-          <cell r="F8">
+            <v>0.50337688569523242</v>
+          </cell>
+          <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0</v>
+            <v>0.51238075935518723</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0</v>
+            <v>-2.1818550321915261E-2</v>
           </cell>
           <cell r="J8">
-            <v>0</v>
+            <v>1.3461591133435419E-2</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1808,23 +1826,29 @@
           <cell r="B9">
             <v>8</v>
           </cell>
+          <cell r="C9" t="str">
+            <v>Michigan</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Alabama</v>
+          </cell>
           <cell r="E9">
-            <v>0</v>
-          </cell>
-          <cell r="F9">
+            <v>10.995761388698931</v>
+          </cell>
+          <cell r="F9" t="b">
             <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0</v>
+            <v>0.52481218929335105</v>
           </cell>
           <cell r="H9">
             <v>0</v>
           </cell>
           <cell r="I9">
-            <v>0</v>
+            <v>1.914179560033868E-3</v>
           </cell>
           <cell r="J9">
-            <v>0</v>
+            <v>0.40552838063197372</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1834,23 +1858,29 @@
           <cell r="B10">
             <v>9</v>
           </cell>
+          <cell r="C10" t="str">
+            <v>Illinois</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Houston</v>
+          </cell>
           <cell r="E10">
-            <v>0</v>
-          </cell>
-          <cell r="F10">
+            <v>-2.5972659968097491</v>
+          </cell>
+          <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0</v>
+            <v>0.51004066609146437</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>0</v>
+            <v>-2.6286001098113469E-2</v>
           </cell>
           <cell r="J10">
-            <v>0</v>
+            <v>5.9410701506423469E-2</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1860,23 +1890,29 @@
           <cell r="B11">
             <v>10</v>
           </cell>
+          <cell r="C11" t="str">
+            <v>Texas</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Arizona</v>
+          </cell>
           <cell r="E11">
-            <v>0</v>
-          </cell>
-          <cell r="F11">
+            <v>-7.8495794140245847</v>
+          </cell>
+          <cell r="F11" t="b">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>0</v>
+            <v>0.50375051547647842</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>0</v>
+            <v>-3.8294470453995699E-2</v>
           </cell>
           <cell r="J11">
-            <v>0</v>
+            <v>0.2420191120804065</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1886,23 +1922,29 @@
           <cell r="B12">
             <v>11</v>
           </cell>
+          <cell r="C12" t="str">
+            <v>Iowa</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Nebraska</v>
+          </cell>
           <cell r="E12">
-            <v>0</v>
-          </cell>
-          <cell r="F12">
+            <v>0.15615277998045449</v>
+          </cell>
+          <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0</v>
+            <v>0.57818778361142664</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>0</v>
+            <v>0.1038130414399964</v>
           </cell>
           <cell r="J12">
-            <v>0</v>
+            <v>0.19277136123939681</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1912,23 +1954,29 @@
           <cell r="B13">
             <v>12</v>
           </cell>
+          <cell r="C13" t="str">
+            <v>Arkansas</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Purdue</v>
+          </cell>
           <cell r="E13">
-            <v>0</v>
-          </cell>
-          <cell r="F13">
+            <v>-4.8613947236177699</v>
+          </cell>
+          <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0</v>
+            <v>0.56549370301584623</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>0</v>
+            <v>7.9578887575706525E-2</v>
           </cell>
           <cell r="J13">
-            <v>0</v>
+            <v>1.249128979806335E-3</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1938,23 +1986,29 @@
           <cell r="B14">
             <v>13</v>
           </cell>
+          <cell r="C14" t="str">
+            <v>St. John's</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>Duke</v>
+          </cell>
           <cell r="E14">
-            <v>0</v>
-          </cell>
-          <cell r="F14">
+            <v>-6.0324469950208446</v>
+          </cell>
+          <cell r="F14" t="b">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0</v>
+            <v>0.52411016711772884</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>0</v>
+            <v>5.7395540657328992E-4</v>
           </cell>
           <cell r="J14">
-            <v>0</v>
+            <v>0.1359058509226507</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -1964,23 +2018,29 @@
           <cell r="B15">
             <v>14</v>
           </cell>
+          <cell r="C15" t="str">
+            <v>Tennessee</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>Iowa State</v>
+          </cell>
           <cell r="E15">
-            <v>0</v>
-          </cell>
-          <cell r="F15">
+            <v>0.5490944982080217</v>
+          </cell>
+          <cell r="F15" t="b">
             <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0</v>
+            <v>0.61191680905930845</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>0</v>
+            <v>0.16820481729504341</v>
           </cell>
           <cell r="J15">
-            <v>0</v>
+            <v>0.28694196100801311</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -1990,23 +2050,29 @@
           <cell r="B16">
             <v>15</v>
           </cell>
+          <cell r="C16" t="str">
+            <v>Michigan State</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>Uconn</v>
+          </cell>
           <cell r="E16">
-            <v>0</v>
-          </cell>
-          <cell r="F16">
+            <v>3.3825498930097022</v>
+          </cell>
+          <cell r="F16" t="b">
             <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0</v>
+            <v>0.60792286402285589</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>0</v>
+            <v>0.16058001313454309</v>
           </cell>
           <cell r="J16">
-            <v>0</v>
+            <v>0.36524831529047619</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -2016,23 +2082,29 @@
           <cell r="B17">
             <v>16</v>
           </cell>
+          <cell r="C17" t="str">
+            <v>Alabama</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>Michigan</v>
+          </cell>
           <cell r="E17">
-            <v>0</v>
-          </cell>
-          <cell r="F17">
+            <v>-6.390332324615847</v>
+          </cell>
+          <cell r="F17" t="b">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0</v>
+            <v>0.58924537458598858</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>0</v>
+            <v>0.1249229878459782</v>
           </cell>
           <cell r="J17">
-            <v>0</v>
+            <v>1.00687426971065E-2</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -8684,7 +8756,7 @@
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-2.5</v>
+            <v>-3</v>
           </cell>
         </row>
         <row r="3">
@@ -8692,67 +8764,67 @@
             <v>2</v>
           </cell>
           <cell r="B3" t="str">
-            <v>Purdue</v>
+            <v>Arizona</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Texas</v>
+            <v>Arkansas</v>
           </cell>
           <cell r="D3">
-            <v>20.952342842063047</v>
+            <v>23.698276332727119</v>
           </cell>
           <cell r="E3">
-            <v>102.749921687376</v>
+            <v>101.76807841686704</v>
           </cell>
           <cell r="F3">
-            <v>101.58084764470013</v>
+            <v>98.508521311778111</v>
           </cell>
           <cell r="G3">
-            <v>0.5771558245083207</v>
+            <v>0.55109126984126988</v>
           </cell>
           <cell r="H3">
-            <v>65.197575757575763</v>
+            <v>70.587878787878793</v>
           </cell>
           <cell r="I3">
-            <v>60.090909090909093</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="J3">
-            <v>16.90909090909091</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="K3">
-            <v>11.363636363636363</v>
+            <v>12.878787878787879</v>
           </cell>
           <cell r="L3">
-            <v>9.0303030303030312</v>
+            <v>10.909090909090908</v>
           </cell>
           <cell r="M3">
             <v>0</v>
           </cell>
           <cell r="N3">
-            <v>14.540908746576733</v>
+            <v>19.912380875616748</v>
           </cell>
           <cell r="O3">
-            <v>100.55048907489414</v>
+            <v>101.9693472090823</v>
           </cell>
           <cell r="P3">
-            <v>96.685052394872145</v>
+            <v>97.560765185917347</v>
           </cell>
           <cell r="Q3">
-            <v>0.5496777658431794</v>
+            <v>0.56447688564476883</v>
           </cell>
           <cell r="R3">
-            <v>68.81</v>
+            <v>72.41</v>
           </cell>
           <cell r="S3">
-            <v>58.1875</v>
+            <v>64.21875</v>
           </cell>
           <cell r="T3">
-            <v>26.34375</v>
+            <v>23.375</v>
           </cell>
           <cell r="U3">
-            <v>12</v>
+            <v>11.0625</v>
           </cell>
           <cell r="V3">
-            <v>11.03125</v>
+            <v>8.96875</v>
           </cell>
           <cell r="W3">
             <v>0</v>
@@ -8766,73 +8838,73 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>Illinois</v>
+            <v>Nebraska</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Houston</v>
+            <v>Iowa</v>
           </cell>
           <cell r="D4">
-            <v>18.836157720404749</v>
+            <v>15.832130159542826</v>
           </cell>
           <cell r="E4">
-            <v>105.08780903665816</v>
+            <v>98.25476089716463</v>
           </cell>
           <cell r="F4">
-            <v>108.93352999987511</v>
+            <v>102.36737546035253</v>
           </cell>
           <cell r="G4">
-            <v>0.5511688311688312</v>
+            <v>0.55440552016985134</v>
           </cell>
           <cell r="H4">
-            <v>66.809032258064519</v>
+            <v>66.883750000000006</v>
           </cell>
           <cell r="I4">
-            <v>62.096774193548384</v>
+            <v>58.875</v>
           </cell>
           <cell r="J4">
-            <v>20.387096774193548</v>
+            <v>16</v>
           </cell>
           <cell r="K4">
-            <v>13.258064516129032</v>
+            <v>8.78125</v>
           </cell>
           <cell r="L4">
-            <v>9</v>
+            <v>9.75</v>
           </cell>
           <cell r="M4">
             <v>0</v>
           </cell>
           <cell r="N4">
-            <v>20.908506008479332</v>
+            <v>15.533956620207105</v>
           </cell>
           <cell r="O4">
-            <v>105.43571389837862</v>
+            <v>98.238539943433466</v>
           </cell>
           <cell r="P4">
-            <v>97.099609428307105</v>
+            <v>93.183243223384508</v>
           </cell>
           <cell r="Q4">
-            <v>0.52154080081094778</v>
+            <v>0.56555993247045577</v>
           </cell>
           <cell r="R4">
-            <v>64.762500000000003</v>
+            <v>62.900606060606066</v>
           </cell>
           <cell r="S4">
-            <v>61.65625</v>
+            <v>53.848484848484851</v>
           </cell>
           <cell r="T4">
-            <v>16.71875</v>
+            <v>18.575757575757574</v>
           </cell>
           <cell r="U4">
-            <v>12.78125</v>
+            <v>8.8181818181818183</v>
           </cell>
           <cell r="V4">
-            <v>8.53125</v>
+            <v>9.6969696969696972</v>
           </cell>
           <cell r="W4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>2.5</v>
+            <v>-3</v>
           </cell>
         </row>
         <row r="5">
@@ -8840,73 +8912,961 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
+            <v>Purdue</v>
+          </cell>
+          <cell r="C5" t="str">
             <v>Texas</v>
           </cell>
-          <cell r="C5" t="str">
+          <cell r="D5">
+            <v>20.952342842063047</v>
+          </cell>
+          <cell r="E5">
+            <v>102.749921687376</v>
+          </cell>
+          <cell r="F5">
+            <v>101.58084764470013</v>
+          </cell>
+          <cell r="G5">
+            <v>0.5771558245083207</v>
+          </cell>
+          <cell r="H5">
+            <v>65.197575757575763</v>
+          </cell>
+          <cell r="I5">
+            <v>60.090909090909093</v>
+          </cell>
+          <cell r="J5">
+            <v>16.90909090909091</v>
+          </cell>
+          <cell r="K5">
+            <v>11.363636363636363</v>
+          </cell>
+          <cell r="L5">
+            <v>9.0303030303030312</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>14.540908746576733</v>
+          </cell>
+          <cell r="O5">
+            <v>100.55048907489414</v>
+          </cell>
+          <cell r="P5">
+            <v>96.685052394872145</v>
+          </cell>
+          <cell r="Q5">
+            <v>0.5496777658431794</v>
+          </cell>
+          <cell r="R5">
+            <v>68.81</v>
+          </cell>
+          <cell r="S5">
+            <v>58.1875</v>
+          </cell>
+          <cell r="T5">
+            <v>26.34375</v>
+          </cell>
+          <cell r="U5">
+            <v>12</v>
+          </cell>
+          <cell r="V5">
+            <v>11.03125</v>
+          </cell>
+          <cell r="W5">
+            <v>0</v>
+          </cell>
+          <cell r="X5">
+            <v>-7.5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Duke</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>St. John's</v>
+          </cell>
+          <cell r="D6">
+            <v>23.057528028184478</v>
+          </cell>
+          <cell r="E6">
+            <v>101.57301127857072</v>
+          </cell>
+          <cell r="F6">
+            <v>99.429621355662846</v>
+          </cell>
+          <cell r="G6">
+            <v>0.57213541666666667</v>
+          </cell>
+          <cell r="H6">
+            <v>66.278787878787867</v>
+          </cell>
+          <cell r="I6">
+            <v>58.18181818181818</v>
+          </cell>
+          <cell r="J6">
+            <v>22.121212121212121</v>
+          </cell>
+          <cell r="K6">
+            <v>12.212121212121213</v>
+          </cell>
+          <cell r="L6">
+            <v>10.575757575757576</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>15.127354829706851</v>
+          </cell>
+          <cell r="O6">
+            <v>102.62076624097725</v>
+          </cell>
+          <cell r="P6">
+            <v>99.083260899694253</v>
+          </cell>
+          <cell r="Q6">
+            <v>0.50957290132547861</v>
+          </cell>
+          <cell r="R6">
+            <v>70.527272727272731</v>
+          </cell>
+          <cell r="S6">
+            <v>61.727272727272727</v>
+          </cell>
+          <cell r="T6">
+            <v>26.060606060606062</v>
+          </cell>
+          <cell r="U6">
+            <v>13.242424242424242</v>
+          </cell>
+          <cell r="V6">
+            <v>10.575757575757576</v>
+          </cell>
+          <cell r="W6">
+            <v>0</v>
+          </cell>
+          <cell r="X6">
+            <v>-7</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Iowa State</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>Tennessee</v>
+          </cell>
+          <cell r="D7">
+            <v>20.65655264831895</v>
+          </cell>
+          <cell r="E7">
+            <v>101.50134460238188</v>
+          </cell>
+          <cell r="F7">
+            <v>96.966113821111122</v>
+          </cell>
+          <cell r="G7">
+            <v>0.56497313141182215</v>
+          </cell>
+          <cell r="H7">
+            <v>67.654117647058825</v>
+          </cell>
+          <cell r="I7">
+            <v>60.205882352941174</v>
+          </cell>
+          <cell r="J7">
+            <v>20.470588235294116</v>
+          </cell>
+          <cell r="K7">
+            <v>11.823529411764707</v>
+          </cell>
+          <cell r="L7">
+            <v>10.264705882352942</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>20.60232878669483</v>
+          </cell>
+          <cell r="O7">
+            <v>105.02195491662999</v>
+          </cell>
+          <cell r="P7">
+            <v>93.652390264453544</v>
+          </cell>
+          <cell r="Q7">
+            <v>0.51561725334655428</v>
+          </cell>
+          <cell r="R7">
+            <v>67.170909090909092</v>
+          </cell>
+          <cell r="S7">
+            <v>61.121212121212125</v>
+          </cell>
+          <cell r="T7">
+            <v>23.666666666666668</v>
+          </cell>
+          <cell r="U7">
+            <v>16.030303030303031</v>
+          </cell>
+          <cell r="V7">
+            <v>11.666666666666666</v>
+          </cell>
+          <cell r="W7">
+            <v>0</v>
+          </cell>
+          <cell r="X7">
+            <v>-4</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Uconn</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>Michigan State</v>
+          </cell>
+          <cell r="D8">
+            <v>18.116591097400342</v>
+          </cell>
+          <cell r="E8">
+            <v>100.0952772073922</v>
+          </cell>
+          <cell r="F8">
+            <v>94.276311107817818</v>
+          </cell>
+          <cell r="G8">
+            <v>0.55882352941176472</v>
+          </cell>
+          <cell r="H8">
+            <v>66.089696969696973</v>
+          </cell>
+          <cell r="I8">
+            <v>58.727272727272727</v>
+          </cell>
+          <cell r="J8">
+            <v>17.696969696969695</v>
+          </cell>
+          <cell r="K8">
+            <v>11.454545454545455</v>
+          </cell>
+          <cell r="L8">
+            <v>11.030303030303031</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>19.991205466978023</v>
+          </cell>
+          <cell r="O8">
+            <v>101.32466702184337</v>
+          </cell>
+          <cell r="P8">
+            <v>94.593976527502747</v>
+          </cell>
+          <cell r="Q8">
+            <v>0.53589041095890411</v>
+          </cell>
+          <cell r="R8">
+            <v>66.620645161290327</v>
+          </cell>
+          <cell r="S8">
+            <v>58.87096774193548</v>
+          </cell>
+          <cell r="T8">
+            <v>20.838709677419356</v>
+          </cell>
+          <cell r="U8">
+            <v>12.774193548387096</v>
+          </cell>
+          <cell r="V8">
+            <v>11.35483870967742</v>
+          </cell>
+          <cell r="W8">
+            <v>0</v>
+          </cell>
+          <cell r="X8">
+            <v>-1</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Michigan</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>Alabama</v>
+          </cell>
+          <cell r="D9">
+            <v>23.168628302235671</v>
+          </cell>
+          <cell r="E9">
+            <v>98.200984374253366</v>
+          </cell>
+          <cell r="F9">
+            <v>96.398308125131024</v>
+          </cell>
+          <cell r="G9">
+            <v>0.58467532467532468</v>
+          </cell>
+          <cell r="H9">
+            <v>71.510000000000005</v>
+          </cell>
+          <cell r="I9">
+            <v>60.15625</v>
+          </cell>
+          <cell r="J9">
+            <v>23.53125</v>
+          </cell>
+          <cell r="K9">
+            <v>11.0625</v>
+          </cell>
+          <cell r="L9">
+            <v>12.0625</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>19.656169100501042</v>
+          </cell>
+          <cell r="O9">
+            <v>102.29455081001471</v>
+          </cell>
+          <cell r="P9">
+            <v>103.73486826442995</v>
+          </cell>
+          <cell r="Q9">
+            <v>0.55384250474383301</v>
+          </cell>
+          <cell r="R9">
+            <v>74.217500000000001</v>
+          </cell>
+          <cell r="S9">
+            <v>65.875</v>
+          </cell>
+          <cell r="T9">
+            <v>24.5</v>
+          </cell>
+          <cell r="U9">
+            <v>12.21875</v>
+          </cell>
+          <cell r="V9">
+            <v>9.78125</v>
+          </cell>
+          <cell r="W9">
+            <v>0</v>
+          </cell>
+          <cell r="X9">
+            <v>-10</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Illinois</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>Houston</v>
+          </cell>
+          <cell r="D10">
+            <v>18.836157720404749</v>
+          </cell>
+          <cell r="E10">
+            <v>105.08780903665816</v>
+          </cell>
+          <cell r="F10">
+            <v>108.93352999987511</v>
+          </cell>
+          <cell r="G10">
+            <v>0.5511688311688312</v>
+          </cell>
+          <cell r="H10">
+            <v>66.809032258064519</v>
+          </cell>
+          <cell r="I10">
+            <v>62.096774193548384</v>
+          </cell>
+          <cell r="J10">
+            <v>20.387096774193548</v>
+          </cell>
+          <cell r="K10">
+            <v>13.258064516129032</v>
+          </cell>
+          <cell r="L10">
+            <v>9</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>20.908506008479332</v>
+          </cell>
+          <cell r="O10">
+            <v>105.43571389837862</v>
+          </cell>
+          <cell r="P10">
+            <v>97.099609428307105</v>
+          </cell>
+          <cell r="Q10">
+            <v>0.52154080081094778</v>
+          </cell>
+          <cell r="R10">
+            <v>64.762500000000003</v>
+          </cell>
+          <cell r="S10">
+            <v>61.65625</v>
+          </cell>
+          <cell r="T10">
+            <v>16.71875</v>
+          </cell>
+          <cell r="U10">
+            <v>12.78125</v>
+          </cell>
+          <cell r="V10">
+            <v>8.53125</v>
+          </cell>
+          <cell r="W10">
+            <v>0</v>
+          </cell>
+          <cell r="X10">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Texas</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>Arizona</v>
+          </cell>
+          <cell r="D11">
+            <v>14.540908746576733</v>
+          </cell>
+          <cell r="E11">
+            <v>100.55048907489414</v>
+          </cell>
+          <cell r="F11">
+            <v>96.685052394872145</v>
+          </cell>
+          <cell r="G11">
+            <v>0.5496777658431794</v>
+          </cell>
+          <cell r="H11">
+            <v>68.81</v>
+          </cell>
+          <cell r="I11">
+            <v>58.1875</v>
+          </cell>
+          <cell r="J11">
+            <v>26.34375</v>
+          </cell>
+          <cell r="K11">
+            <v>12</v>
+          </cell>
+          <cell r="L11">
+            <v>11.03125</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>23.698276332727119</v>
+          </cell>
+          <cell r="O11">
+            <v>101.76807841686704</v>
+          </cell>
+          <cell r="P11">
+            <v>98.508521311778111</v>
+          </cell>
+          <cell r="Q11">
+            <v>0.55109126984126988</v>
+          </cell>
+          <cell r="R11">
+            <v>70.587878787878793</v>
+          </cell>
+          <cell r="S11">
+            <v>61.090909090909093</v>
+          </cell>
+          <cell r="T11">
+            <v>26.060606060606062</v>
+          </cell>
+          <cell r="U11">
+            <v>12.878787878787879</v>
+          </cell>
+          <cell r="V11">
+            <v>10.909090909090908</v>
+          </cell>
+          <cell r="W11">
+            <v>0</v>
+          </cell>
+          <cell r="X11">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Iowa</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>Nebraska</v>
+          </cell>
+          <cell r="D12">
+            <v>15.533956620207105</v>
+          </cell>
+          <cell r="E12">
+            <v>98.238539943433466</v>
+          </cell>
+          <cell r="F12">
+            <v>93.183243223384508</v>
+          </cell>
+          <cell r="G12">
+            <v>0.56555993247045577</v>
+          </cell>
+          <cell r="H12">
+            <v>62.900606060606066</v>
+          </cell>
+          <cell r="I12">
+            <v>53.848484848484851</v>
+          </cell>
+          <cell r="J12">
+            <v>18.575757575757574</v>
+          </cell>
+          <cell r="K12">
+            <v>8.8181818181818183</v>
+          </cell>
+          <cell r="L12">
+            <v>9.6969696969696972</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>15.832130159542826</v>
+          </cell>
+          <cell r="O12">
+            <v>98.25476089716463</v>
+          </cell>
+          <cell r="P12">
+            <v>102.36737546035253</v>
+          </cell>
+          <cell r="Q12">
+            <v>0.55440552016985134</v>
+          </cell>
+          <cell r="R12">
+            <v>66.883750000000006</v>
+          </cell>
+          <cell r="S12">
+            <v>58.875</v>
+          </cell>
+          <cell r="T12">
+            <v>16</v>
+          </cell>
+          <cell r="U12">
+            <v>8.78125</v>
+          </cell>
+          <cell r="V12">
+            <v>9.75</v>
+          </cell>
+          <cell r="W12">
+            <v>0</v>
+          </cell>
+          <cell r="X12">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Arkansas</v>
+          </cell>
+          <cell r="C13" t="str">
             <v>Purdue</v>
           </cell>
-          <cell r="D5">
-            <v>14.540908746576733</v>
-          </cell>
-          <cell r="E5">
-            <v>100.55048907489414</v>
-          </cell>
-          <cell r="F5">
-            <v>96.685052394872145</v>
-          </cell>
-          <cell r="G5">
-            <v>0.5496777658431794</v>
-          </cell>
-          <cell r="H5">
-            <v>68.81</v>
-          </cell>
-          <cell r="I5">
-            <v>58.1875</v>
-          </cell>
-          <cell r="J5">
-            <v>26.34375</v>
-          </cell>
-          <cell r="K5">
-            <v>12</v>
-          </cell>
-          <cell r="L5">
-            <v>11.03125</v>
-          </cell>
-          <cell r="M5">
-            <v>0</v>
-          </cell>
-          <cell r="N5">
+          <cell r="D13">
+            <v>19.912380875616748</v>
+          </cell>
+          <cell r="E13">
+            <v>101.9693472090823</v>
+          </cell>
+          <cell r="F13">
+            <v>97.560765185917347</v>
+          </cell>
+          <cell r="G13">
+            <v>0.56447688564476883</v>
+          </cell>
+          <cell r="H13">
+            <v>72.41</v>
+          </cell>
+          <cell r="I13">
+            <v>64.21875</v>
+          </cell>
+          <cell r="J13">
+            <v>23.375</v>
+          </cell>
+          <cell r="K13">
+            <v>11.0625</v>
+          </cell>
+          <cell r="L13">
+            <v>8.96875</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
             <v>20.952342842063047</v>
           </cell>
-          <cell r="O5">
+          <cell r="O13">
             <v>102.749921687376</v>
           </cell>
-          <cell r="P5">
+          <cell r="P13">
             <v>101.58084764470013</v>
           </cell>
-          <cell r="Q5">
+          <cell r="Q13">
             <v>0.5771558245083207</v>
           </cell>
-          <cell r="R5">
+          <cell r="R13">
             <v>65.197575757575763</v>
           </cell>
-          <cell r="S5">
+          <cell r="S13">
             <v>60.090909090909093</v>
           </cell>
-          <cell r="T5">
+          <cell r="T13">
             <v>16.90909090909091</v>
           </cell>
-          <cell r="U5">
+          <cell r="U13">
             <v>11.363636363636363</v>
           </cell>
-          <cell r="V5">
+          <cell r="V13">
             <v>9.0303030303030312</v>
           </cell>
-          <cell r="W5">
-            <v>0</v>
-          </cell>
-          <cell r="X5">
-            <v>8</v>
+          <cell r="W13">
+            <v>0</v>
+          </cell>
+          <cell r="X13">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>St. John's</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>Duke</v>
+          </cell>
+          <cell r="D14">
+            <v>15.127354829706851</v>
+          </cell>
+          <cell r="E14">
+            <v>102.62076624097725</v>
+          </cell>
+          <cell r="F14">
+            <v>99.083260899694253</v>
+          </cell>
+          <cell r="G14">
+            <v>0.50957290132547861</v>
+          </cell>
+          <cell r="H14">
+            <v>70.527272727272731</v>
+          </cell>
+          <cell r="I14">
+            <v>61.727272727272727</v>
+          </cell>
+          <cell r="J14">
+            <v>26.060606060606062</v>
+          </cell>
+          <cell r="K14">
+            <v>13.242424242424242</v>
+          </cell>
+          <cell r="L14">
+            <v>10.575757575757576</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>23.057528028184478</v>
+          </cell>
+          <cell r="O14">
+            <v>101.57301127857072</v>
+          </cell>
+          <cell r="P14">
+            <v>99.429621355662846</v>
+          </cell>
+          <cell r="Q14">
+            <v>0.57213541666666667</v>
+          </cell>
+          <cell r="R14">
+            <v>66.278787878787867</v>
+          </cell>
+          <cell r="S14">
+            <v>58.18181818181818</v>
+          </cell>
+          <cell r="T14">
+            <v>22.121212121212121</v>
+          </cell>
+          <cell r="U14">
+            <v>12.212121212121213</v>
+          </cell>
+          <cell r="V14">
+            <v>10.575757575757576</v>
+          </cell>
+          <cell r="W14">
+            <v>0</v>
+          </cell>
+          <cell r="X14">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Tennessee</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>Iowa State</v>
+          </cell>
+          <cell r="D15">
+            <v>20.60232878669483</v>
+          </cell>
+          <cell r="E15">
+            <v>105.02195491662999</v>
+          </cell>
+          <cell r="F15">
+            <v>93.652390264453544</v>
+          </cell>
+          <cell r="G15">
+            <v>0.51561725334655428</v>
+          </cell>
+          <cell r="H15">
+            <v>67.170909090909092</v>
+          </cell>
+          <cell r="I15">
+            <v>61.121212121212125</v>
+          </cell>
+          <cell r="J15">
+            <v>23.666666666666668</v>
+          </cell>
+          <cell r="K15">
+            <v>16.030303030303031</v>
+          </cell>
+          <cell r="L15">
+            <v>11.666666666666666</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>20.65655264831895</v>
+          </cell>
+          <cell r="O15">
+            <v>101.50134460238188</v>
+          </cell>
+          <cell r="P15">
+            <v>96.966113821111122</v>
+          </cell>
+          <cell r="Q15">
+            <v>0.56497313141182215</v>
+          </cell>
+          <cell r="R15">
+            <v>67.654117647058825</v>
+          </cell>
+          <cell r="S15">
+            <v>60.205882352941174</v>
+          </cell>
+          <cell r="T15">
+            <v>20.470588235294116</v>
+          </cell>
+          <cell r="U15">
+            <v>11.823529411764707</v>
+          </cell>
+          <cell r="V15">
+            <v>10.264705882352942</v>
+          </cell>
+          <cell r="W15">
+            <v>0</v>
+          </cell>
+          <cell r="X15">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Michigan State</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>Uconn</v>
+          </cell>
+          <cell r="D16">
+            <v>19.991205466978023</v>
+          </cell>
+          <cell r="E16">
+            <v>101.32466702184337</v>
+          </cell>
+          <cell r="F16">
+            <v>94.593976527502747</v>
+          </cell>
+          <cell r="G16">
+            <v>0.53589041095890411</v>
+          </cell>
+          <cell r="H16">
+            <v>66.620645161290327</v>
+          </cell>
+          <cell r="I16">
+            <v>58.87096774193548</v>
+          </cell>
+          <cell r="J16">
+            <v>20.838709677419356</v>
+          </cell>
+          <cell r="K16">
+            <v>12.774193548387096</v>
+          </cell>
+          <cell r="L16">
+            <v>11.35483870967742</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>18.116591097400342</v>
+          </cell>
+          <cell r="O16">
+            <v>100.0952772073922</v>
+          </cell>
+          <cell r="P16">
+            <v>94.276311107817818</v>
+          </cell>
+          <cell r="Q16">
+            <v>0.55882352941176472</v>
+          </cell>
+          <cell r="R16">
+            <v>66.089696969696973</v>
+          </cell>
+          <cell r="S16">
+            <v>58.727272727272727</v>
+          </cell>
+          <cell r="T16">
+            <v>17.696969696969695</v>
+          </cell>
+          <cell r="U16">
+            <v>11.454545454545455</v>
+          </cell>
+          <cell r="V16">
+            <v>11.030303030303031</v>
+          </cell>
+          <cell r="W16">
+            <v>0</v>
+          </cell>
+          <cell r="X16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>Alabama</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>Michigan</v>
+          </cell>
+          <cell r="D17">
+            <v>19.656169100501042</v>
+          </cell>
+          <cell r="E17">
+            <v>102.29455081001471</v>
+          </cell>
+          <cell r="F17">
+            <v>103.73486826442995</v>
+          </cell>
+          <cell r="G17">
+            <v>0.55384250474383301</v>
+          </cell>
+          <cell r="H17">
+            <v>74.217500000000001</v>
+          </cell>
+          <cell r="I17">
+            <v>65.875</v>
+          </cell>
+          <cell r="J17">
+            <v>24.5</v>
+          </cell>
+          <cell r="K17">
+            <v>12.21875</v>
+          </cell>
+          <cell r="L17">
+            <v>9.78125</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>23.168628302235671</v>
+          </cell>
+          <cell r="O17">
+            <v>98.200984374253366</v>
+          </cell>
+          <cell r="P17">
+            <v>96.398308125131024</v>
+          </cell>
+          <cell r="Q17">
+            <v>0.58467532467532468</v>
+          </cell>
+          <cell r="R17">
+            <v>71.510000000000005</v>
+          </cell>
+          <cell r="S17">
+            <v>60.15625</v>
+          </cell>
+          <cell r="T17">
+            <v>23.53125</v>
+          </cell>
+          <cell r="U17">
+            <v>11.0625</v>
+          </cell>
+          <cell r="V17">
+            <v>12.0625</v>
+          </cell>
+          <cell r="W17">
+            <v>0</v>
+          </cell>
+          <cell r="X17">
+            <v>10</v>
           </cell>
         </row>
       </sheetData>
@@ -17729,31 +18689,31 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Houston</v>
+        <v>Illinois</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Illinois</v>
+        <v>Houston</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>B2</f>
-        <v>Houston</v>
+        <v>Illinois</v>
       </c>
       <c r="E2" s="5">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>5.449294502348879</v>
+        <v>-2.5972659968097491</v>
       </c>
       <c r="F2" s="5">
         <f>-VLOOKUP(A2,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>2.5</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.34694764321218979</v>
+        <v>5.9410701506423469E-2</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -17761,7 +18721,7 @@
       </c>
       <c r="I2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.3536008408833686E-2</v>
+        <v>-6.5715002745283671E-3</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>443</v>
@@ -17776,31 +18736,31 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,2,FALSE)</f>
-        <v>Texas</v>
+        <v>Arizona</v>
       </c>
       <c r="C3" s="6" t="str">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,3,FALSE)</f>
-        <v>Purdue</v>
+        <v>Arkansas</v>
       </c>
       <c r="D3" s="6" t="str">
         <f t="shared" ref="D3:D9" si="0">B3</f>
-        <v>Texas</v>
+        <v>Arizona</v>
       </c>
       <c r="E3" s="5">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>-4.9701845204405686</v>
+        <v>10.17544759009586</v>
       </c>
       <c r="F3" s="5">
         <f>-VLOOKUP(A3,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>2.1099126100401319E-2</v>
+        <v>0.44652162262184503</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -17808,7 +18768,7 @@
       </c>
       <c r="I3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.447764706633021E-2</v>
+        <v>1.4445226443697695E-2</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>443</v>
@@ -17819,76 +18779,267 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Nebraska</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Iowa</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f t="shared" ref="D4:D9" si="2">B4</f>
+        <v>Nebraska</v>
+      </c>
+      <c r="E4" s="5">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>6.2329743724806317</v>
+      </c>
+      <c r="F4" s="5">
+        <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="G4" s="7">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.38710225177014629</v>
+      </c>
+      <c r="H4" s="7">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="7">
+        <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>2.6849415509268226E-2</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" ref="K4:K9" si="3">IF(J4="Yes",(H4*1500)/100,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Purdue</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Texas</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Purdue</v>
+      </c>
+      <c r="E5" s="5">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>9.7678421526914398</v>
+      </c>
+      <c r="F5" s="5">
+        <f>-VLOOKUP(A5,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>7.5</v>
+      </c>
+      <c r="G5" s="7">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.43952016208204359</v>
+      </c>
+      <c r="H5" s="7">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>1.5534196411286337E-2</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="str">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Duke</v>
+      </c>
+      <c r="C6" s="6" t="str">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>St. John's</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Duke</v>
+      </c>
+      <c r="E6" s="5">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>11.225624027579791</v>
+      </c>
+      <c r="F6" s="5">
+        <f>-VLOOKUP(A6,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G6" s="7">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.57242552718101858</v>
+      </c>
+      <c r="H6" s="7">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>3.5542157428009077E-2</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
+      <c r="A7" s="1">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="str">
+        <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Tennessee</v>
+      </c>
+      <c r="C7" s="6" t="str">
+        <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Iowa State</v>
+      </c>
+      <c r="D7" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Tennessee</v>
+      </c>
+      <c r="E7" s="5">
+        <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>0.5490944982080217</v>
+      </c>
+      <c r="F7" s="5">
+        <f>-VLOOKUP(A7,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>-4</v>
+      </c>
+      <c r="G7" s="7">
+        <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.28694196100801311</v>
+      </c>
+      <c r="H7" s="7">
+        <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>4.2051204323760853E-2</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
+      <c r="A8" s="1">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Michigan State</v>
+      </c>
+      <c r="C8" s="6" t="str">
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Uconn</v>
+      </c>
+      <c r="D8" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Michigan State</v>
+      </c>
+      <c r="E8" s="5">
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>3.3825498930097022</v>
+      </c>
+      <c r="F8" s="5">
+        <f>-VLOOKUP(A8,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="G8" s="7">
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.36524831529047619</v>
+      </c>
+      <c r="H8" s="7">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="I8" s="7">
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>4.0145003283635773E-2</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="K8" s="9">
+        <f t="shared" si="3"/>
+        <v>0.68100000000000005</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="str">
+        <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,2,FALSE)</f>
+        <v>Michigan</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,3,FALSE)</f>
+        <v>Alabama</v>
+      </c>
+      <c r="D9" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Michigan</v>
+      </c>
+      <c r="E9" s="5">
+        <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,4,FALSE)</f>
+        <v>10.995761388698931</v>
+      </c>
+      <c r="F9" s="5">
+        <f>-VLOOKUP(A9,[2]Games!$A$2:$X$284,24,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="G9" s="7">
+        <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,9,FALSE)</f>
+        <v>0.40552838063197372</v>
+      </c>
+      <c r="H9" s="7">
+        <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
+        <v>4.7854489000846701E-4</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
@@ -19914,14 +21065,17 @@
         <v>281</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>451</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>389</v>
+      </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDED37A-4651-AB48-8E2F-E514F1935E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47787EA-0E91-5441-8D93-15FECB3664D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="780" windowWidth="14900" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -1609,7 +1609,7 @@
             <v>Illinois</v>
           </cell>
           <cell r="E2">
-            <v>5.7742945023488801</v>
+            <v>5.7742945023488783</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
@@ -1624,7 +1624,7 @@
             <v>8.5946074618987622E-2</v>
           </cell>
           <cell r="J2">
-            <v>0.34694764321219002</v>
+            <v>0.34694764321218979</v>
           </cell>
           <cell r="K2">
             <v>0</v>
@@ -1656,7 +1656,7 @@
             <v>5.7780905774790781E-2</v>
           </cell>
           <cell r="J3">
-            <v>0.44652162262184503</v>
+            <v>0.44652162262184469</v>
           </cell>
           <cell r="K3">
             <v>0</v>
@@ -1673,19 +1673,19 @@
             <v>Iowa</v>
           </cell>
           <cell r="E4">
-            <v>6.2329743724806317</v>
+            <v>5.5829743724806304</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.58006544201941912</v>
+            <v>0.58859640890923282</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.10739766203707291</v>
+            <v>0.1236840533721718</v>
           </cell>
           <cell r="J4">
             <v>0.38710225177014629</v>
@@ -1705,22 +1705,22 @@
             <v>Texas</v>
           </cell>
           <cell r="E5">
-            <v>9.7678421526914398</v>
+            <v>9.442842152691437</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.55635736390936186</v>
+            <v>0.56067375049667179</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>6.2136785645145347E-2</v>
+            <v>7.0377160039100772E-2</v>
           </cell>
           <cell r="J5">
-            <v>0.43952016208204359</v>
+            <v>0.43952016208204348</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1737,22 +1737,22 @@
             <v>St. John's</v>
           </cell>
           <cell r="E6">
-            <v>11.225624027579791</v>
+            <v>10.90062402757979</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.59827880603963801</v>
+            <v>0.60226039075025728</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>0.14216862971203631</v>
+            <v>0.14976983688685491</v>
           </cell>
           <cell r="J6">
-            <v>0.57242552718101858</v>
+            <v>0.57242552718101847</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1769,7 +1769,7 @@
             <v>Tennessee</v>
           </cell>
           <cell r="E7">
-            <v>6.169396104264961</v>
+            <v>6.1693961042649601</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
@@ -1784,7 +1784,7 @@
             <v>5.7495491589876317E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.32440678103529191</v>
+            <v>0.32440678103529169</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1801,19 +1801,19 @@
             <v>Michigan State</v>
           </cell>
           <cell r="E8">
-            <v>0.50337688569523242</v>
+            <v>1.153376885695232</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.51238075935518723</v>
+            <v>0.52109976312859441</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>-2.1818550321915261E-2</v>
+            <v>-5.1731794817742593E-3</v>
           </cell>
           <cell r="J8">
             <v>1.3461591133435419E-2</v>
@@ -1848,7 +1848,7 @@
             <v>1.914179560033868E-3</v>
           </cell>
           <cell r="J9">
-            <v>0.40552838063197372</v>
+            <v>0.4055283806319735</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1929,22 +1929,22 @@
             <v>Nebraska</v>
           </cell>
           <cell r="E12">
-            <v>0.15615277998045449</v>
+            <v>0.8061527799804542</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.57818778361142664</v>
+            <v>0.56961125963652415</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>0.1038130414399964</v>
+            <v>8.7439677487909817E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.19277136123939681</v>
+            <v>0.19277136123939659</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1961,19 +1961,19 @@
             <v>Purdue</v>
           </cell>
           <cell r="E13">
-            <v>-4.8613947236177699</v>
+            <v>-4.5363947236177697</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.56549370301584623</v>
+            <v>0.56118540620989066</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>7.9578887575706525E-2</v>
+            <v>7.1353957309791327E-2</v>
           </cell>
           <cell r="J13">
             <v>1.249128979806335E-3</v>
@@ -1993,19 +1993,19 @@
             <v>Duke</v>
           </cell>
           <cell r="E14">
-            <v>-6.0324469950208446</v>
+            <v>-5.7074469950208453</v>
           </cell>
           <cell r="F14" t="b">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.52411016711772884</v>
+            <v>0.51975335307188941</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>5.7395540657328992E-4</v>
+            <v>-7.7435986809383786E-3</v>
           </cell>
           <cell r="J14">
             <v>0.1359058509226507</v>
@@ -2057,25 +2057,25 @@
             <v>Uconn</v>
           </cell>
           <cell r="E16">
-            <v>3.3825498930097022</v>
+            <v>2.732549893009701</v>
           </cell>
           <cell r="F16" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G16">
-            <v>0.60792286402285589</v>
+            <v>0.61630261928910979</v>
           </cell>
           <cell r="H16">
-            <v>0</v>
+            <v>4.7694200202852269E-2</v>
           </cell>
           <cell r="I16">
-            <v>0.16058001313454309</v>
+            <v>0.1765777277337551</v>
           </cell>
           <cell r="J16">
-            <v>0.36524831529047619</v>
+            <v>0.36524831529047608</v>
           </cell>
           <cell r="K16">
-            <v>0</v>
+            <v>0.93099078795967627</v>
           </cell>
         </row>
         <row r="17">
@@ -8904,7 +8904,7 @@
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-3</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="5">
@@ -8978,7 +8978,7 @@
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>-7.5</v>
+            <v>-7</v>
           </cell>
         </row>
         <row r="6">
@@ -9052,7 +9052,7 @@
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>-7</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="7">
@@ -9200,7 +9200,7 @@
             <v>0</v>
           </cell>
           <cell r="X8">
-            <v>-1</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="9">
@@ -9496,7 +9496,7 @@
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>3</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
@@ -9570,7 +9570,7 @@
             <v>0</v>
           </cell>
           <cell r="X13">
-            <v>7.5</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="14">
@@ -9644,7 +9644,7 @@
             <v>0</v>
           </cell>
           <cell r="X14">
-            <v>7</v>
+            <v>6.5</v>
           </cell>
         </row>
         <row r="15">
@@ -9792,7 +9792,7 @@
             <v>0</v>
           </cell>
           <cell r="X16">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="17">
@@ -9868,6 +9868,3778 @@
           <cell r="X17">
             <v>10</v>
           </cell>
+        </row>
+        <row r="18">
+          <cell r="D18"/>
+          <cell r="E18"/>
+          <cell r="F18"/>
+          <cell r="G18"/>
+          <cell r="H18"/>
+          <cell r="I18"/>
+          <cell r="J18"/>
+          <cell r="K18"/>
+          <cell r="L18"/>
+          <cell r="M18"/>
+          <cell r="N18"/>
+          <cell r="O18"/>
+          <cell r="P18"/>
+          <cell r="Q18"/>
+          <cell r="R18"/>
+          <cell r="S18"/>
+          <cell r="T18"/>
+          <cell r="U18"/>
+          <cell r="V18"/>
+          <cell r="W18"/>
+          <cell r="X18"/>
+        </row>
+        <row r="19">
+          <cell r="D19"/>
+          <cell r="E19"/>
+          <cell r="F19"/>
+          <cell r="G19"/>
+          <cell r="H19"/>
+          <cell r="I19"/>
+          <cell r="J19"/>
+          <cell r="K19"/>
+          <cell r="L19"/>
+          <cell r="M19"/>
+          <cell r="N19"/>
+          <cell r="O19"/>
+          <cell r="P19"/>
+          <cell r="Q19"/>
+          <cell r="R19"/>
+          <cell r="S19"/>
+          <cell r="T19"/>
+          <cell r="U19"/>
+          <cell r="V19"/>
+          <cell r="W19"/>
+          <cell r="X19"/>
+        </row>
+        <row r="20">
+          <cell r="D20"/>
+          <cell r="E20"/>
+          <cell r="F20"/>
+          <cell r="G20"/>
+          <cell r="H20"/>
+          <cell r="I20"/>
+          <cell r="J20"/>
+          <cell r="K20"/>
+          <cell r="L20"/>
+          <cell r="M20"/>
+          <cell r="N20"/>
+          <cell r="O20"/>
+          <cell r="P20"/>
+          <cell r="Q20"/>
+          <cell r="R20"/>
+          <cell r="S20"/>
+          <cell r="T20"/>
+          <cell r="U20"/>
+          <cell r="V20"/>
+          <cell r="W20"/>
+          <cell r="X20"/>
+        </row>
+        <row r="21">
+          <cell r="D21"/>
+          <cell r="E21"/>
+          <cell r="F21"/>
+          <cell r="G21"/>
+          <cell r="H21"/>
+          <cell r="I21"/>
+          <cell r="J21"/>
+          <cell r="K21"/>
+          <cell r="L21"/>
+          <cell r="M21"/>
+          <cell r="N21"/>
+          <cell r="O21"/>
+          <cell r="P21"/>
+          <cell r="Q21"/>
+          <cell r="R21"/>
+          <cell r="S21"/>
+          <cell r="T21"/>
+          <cell r="U21"/>
+          <cell r="V21"/>
+          <cell r="W21"/>
+          <cell r="X21"/>
+        </row>
+        <row r="22">
+          <cell r="D22"/>
+          <cell r="E22"/>
+          <cell r="F22"/>
+          <cell r="G22"/>
+          <cell r="H22"/>
+          <cell r="I22"/>
+          <cell r="J22"/>
+          <cell r="K22"/>
+          <cell r="L22"/>
+          <cell r="M22"/>
+          <cell r="N22"/>
+          <cell r="O22"/>
+          <cell r="P22"/>
+          <cell r="Q22"/>
+          <cell r="R22"/>
+          <cell r="S22"/>
+          <cell r="T22"/>
+          <cell r="U22"/>
+          <cell r="V22"/>
+          <cell r="W22"/>
+          <cell r="X22"/>
+        </row>
+        <row r="23">
+          <cell r="D23"/>
+          <cell r="E23"/>
+          <cell r="F23"/>
+          <cell r="G23"/>
+          <cell r="H23"/>
+          <cell r="I23"/>
+          <cell r="J23"/>
+          <cell r="K23"/>
+          <cell r="L23"/>
+          <cell r="M23"/>
+          <cell r="N23"/>
+          <cell r="O23"/>
+          <cell r="P23"/>
+          <cell r="Q23"/>
+          <cell r="R23"/>
+          <cell r="S23"/>
+          <cell r="T23"/>
+          <cell r="U23"/>
+          <cell r="V23"/>
+          <cell r="W23"/>
+          <cell r="X23"/>
+        </row>
+        <row r="24">
+          <cell r="D24"/>
+          <cell r="E24"/>
+          <cell r="F24"/>
+          <cell r="G24"/>
+          <cell r="H24"/>
+          <cell r="I24"/>
+          <cell r="J24"/>
+          <cell r="K24"/>
+          <cell r="L24"/>
+          <cell r="M24"/>
+          <cell r="N24"/>
+          <cell r="O24"/>
+          <cell r="P24"/>
+          <cell r="Q24"/>
+          <cell r="R24"/>
+          <cell r="S24"/>
+          <cell r="T24"/>
+          <cell r="U24"/>
+          <cell r="V24"/>
+          <cell r="W24"/>
+          <cell r="X24"/>
+        </row>
+        <row r="25">
+          <cell r="D25"/>
+          <cell r="E25"/>
+          <cell r="F25"/>
+          <cell r="G25"/>
+          <cell r="H25"/>
+          <cell r="I25"/>
+          <cell r="J25"/>
+          <cell r="K25"/>
+          <cell r="L25"/>
+          <cell r="M25"/>
+          <cell r="N25"/>
+          <cell r="O25"/>
+          <cell r="P25"/>
+          <cell r="Q25"/>
+          <cell r="R25"/>
+          <cell r="S25"/>
+          <cell r="T25"/>
+          <cell r="U25"/>
+          <cell r="V25"/>
+          <cell r="W25"/>
+          <cell r="X25"/>
+        </row>
+        <row r="26">
+          <cell r="D26"/>
+          <cell r="E26"/>
+          <cell r="F26"/>
+          <cell r="G26"/>
+          <cell r="H26"/>
+          <cell r="I26"/>
+          <cell r="J26"/>
+          <cell r="K26"/>
+          <cell r="L26"/>
+          <cell r="M26"/>
+          <cell r="N26"/>
+          <cell r="O26"/>
+          <cell r="P26"/>
+          <cell r="Q26"/>
+          <cell r="R26"/>
+          <cell r="S26"/>
+          <cell r="T26"/>
+          <cell r="U26"/>
+          <cell r="V26"/>
+          <cell r="W26"/>
+          <cell r="X26"/>
+        </row>
+        <row r="27">
+          <cell r="D27"/>
+          <cell r="E27"/>
+          <cell r="F27"/>
+          <cell r="G27"/>
+          <cell r="H27"/>
+          <cell r="I27"/>
+          <cell r="J27"/>
+          <cell r="K27"/>
+          <cell r="L27"/>
+          <cell r="M27"/>
+          <cell r="N27"/>
+          <cell r="O27"/>
+          <cell r="P27"/>
+          <cell r="Q27"/>
+          <cell r="R27"/>
+          <cell r="S27"/>
+          <cell r="T27"/>
+          <cell r="U27"/>
+          <cell r="V27"/>
+          <cell r="W27"/>
+          <cell r="X27"/>
+        </row>
+        <row r="28">
+          <cell r="D28"/>
+          <cell r="E28"/>
+          <cell r="F28"/>
+          <cell r="G28"/>
+          <cell r="H28"/>
+          <cell r="I28"/>
+          <cell r="J28"/>
+          <cell r="K28"/>
+          <cell r="L28"/>
+          <cell r="M28"/>
+          <cell r="N28"/>
+          <cell r="O28"/>
+          <cell r="P28"/>
+          <cell r="Q28"/>
+          <cell r="R28"/>
+          <cell r="S28"/>
+          <cell r="T28"/>
+          <cell r="U28"/>
+          <cell r="V28"/>
+          <cell r="W28"/>
+          <cell r="X28"/>
+        </row>
+        <row r="29">
+          <cell r="D29"/>
+          <cell r="E29"/>
+          <cell r="F29"/>
+          <cell r="G29"/>
+          <cell r="H29"/>
+          <cell r="I29"/>
+          <cell r="J29"/>
+          <cell r="K29"/>
+          <cell r="L29"/>
+          <cell r="M29"/>
+          <cell r="N29"/>
+          <cell r="O29"/>
+          <cell r="P29"/>
+          <cell r="Q29"/>
+          <cell r="R29"/>
+          <cell r="S29"/>
+          <cell r="T29"/>
+          <cell r="U29"/>
+          <cell r="V29"/>
+          <cell r="W29"/>
+          <cell r="X29"/>
+        </row>
+        <row r="30">
+          <cell r="D30"/>
+          <cell r="E30"/>
+          <cell r="F30"/>
+          <cell r="G30"/>
+          <cell r="H30"/>
+          <cell r="I30"/>
+          <cell r="J30"/>
+          <cell r="K30"/>
+          <cell r="L30"/>
+          <cell r="M30"/>
+          <cell r="N30"/>
+          <cell r="O30"/>
+          <cell r="P30"/>
+          <cell r="Q30"/>
+          <cell r="R30"/>
+          <cell r="S30"/>
+          <cell r="T30"/>
+          <cell r="U30"/>
+          <cell r="V30"/>
+          <cell r="W30"/>
+          <cell r="X30"/>
+        </row>
+        <row r="31">
+          <cell r="D31"/>
+          <cell r="E31"/>
+          <cell r="F31"/>
+          <cell r="G31"/>
+          <cell r="H31"/>
+          <cell r="I31"/>
+          <cell r="J31"/>
+          <cell r="K31"/>
+          <cell r="L31"/>
+          <cell r="M31"/>
+          <cell r="N31"/>
+          <cell r="O31"/>
+          <cell r="P31"/>
+          <cell r="Q31"/>
+          <cell r="R31"/>
+          <cell r="S31"/>
+          <cell r="T31"/>
+          <cell r="U31"/>
+          <cell r="V31"/>
+          <cell r="W31"/>
+          <cell r="X31"/>
+        </row>
+        <row r="32">
+          <cell r="D32"/>
+          <cell r="E32"/>
+          <cell r="F32"/>
+          <cell r="G32"/>
+          <cell r="H32"/>
+          <cell r="I32"/>
+          <cell r="J32"/>
+          <cell r="K32"/>
+          <cell r="L32"/>
+          <cell r="M32"/>
+          <cell r="N32"/>
+          <cell r="O32"/>
+          <cell r="P32"/>
+          <cell r="Q32"/>
+          <cell r="R32"/>
+          <cell r="S32"/>
+          <cell r="T32"/>
+          <cell r="U32"/>
+          <cell r="V32"/>
+          <cell r="W32"/>
+          <cell r="X32"/>
+        </row>
+        <row r="33">
+          <cell r="D33"/>
+          <cell r="E33"/>
+          <cell r="F33"/>
+          <cell r="G33"/>
+          <cell r="H33"/>
+          <cell r="I33"/>
+          <cell r="J33"/>
+          <cell r="K33"/>
+          <cell r="L33"/>
+          <cell r="M33"/>
+          <cell r="N33"/>
+          <cell r="O33"/>
+          <cell r="P33"/>
+          <cell r="Q33"/>
+          <cell r="R33"/>
+          <cell r="S33"/>
+          <cell r="T33"/>
+          <cell r="U33"/>
+          <cell r="V33"/>
+          <cell r="W33"/>
+          <cell r="X33"/>
+        </row>
+        <row r="34">
+          <cell r="D34"/>
+          <cell r="E34"/>
+          <cell r="F34"/>
+          <cell r="G34"/>
+          <cell r="H34"/>
+          <cell r="I34"/>
+          <cell r="J34"/>
+          <cell r="K34"/>
+          <cell r="L34"/>
+          <cell r="M34"/>
+          <cell r="N34"/>
+          <cell r="O34"/>
+          <cell r="P34"/>
+          <cell r="Q34"/>
+          <cell r="R34"/>
+          <cell r="S34"/>
+          <cell r="T34"/>
+          <cell r="U34"/>
+          <cell r="V34"/>
+          <cell r="W34"/>
+          <cell r="X34"/>
+        </row>
+        <row r="35">
+          <cell r="D35"/>
+          <cell r="E35"/>
+          <cell r="F35"/>
+          <cell r="G35"/>
+          <cell r="H35"/>
+          <cell r="I35"/>
+          <cell r="J35"/>
+          <cell r="K35"/>
+          <cell r="L35"/>
+          <cell r="M35"/>
+          <cell r="N35"/>
+          <cell r="O35"/>
+          <cell r="P35"/>
+          <cell r="Q35"/>
+          <cell r="R35"/>
+          <cell r="S35"/>
+          <cell r="T35"/>
+          <cell r="U35"/>
+          <cell r="V35"/>
+          <cell r="W35"/>
+          <cell r="X35"/>
+        </row>
+        <row r="36">
+          <cell r="D36"/>
+          <cell r="E36"/>
+          <cell r="F36"/>
+          <cell r="G36"/>
+          <cell r="H36"/>
+          <cell r="I36"/>
+          <cell r="J36"/>
+          <cell r="K36"/>
+          <cell r="L36"/>
+          <cell r="M36"/>
+          <cell r="N36"/>
+          <cell r="O36"/>
+          <cell r="P36"/>
+          <cell r="Q36"/>
+          <cell r="R36"/>
+          <cell r="S36"/>
+          <cell r="T36"/>
+          <cell r="U36"/>
+          <cell r="V36"/>
+          <cell r="W36"/>
+          <cell r="X36"/>
+        </row>
+        <row r="37">
+          <cell r="D37"/>
+          <cell r="E37"/>
+          <cell r="F37"/>
+          <cell r="G37"/>
+          <cell r="H37"/>
+          <cell r="I37"/>
+          <cell r="J37"/>
+          <cell r="K37"/>
+          <cell r="L37"/>
+          <cell r="M37"/>
+          <cell r="N37"/>
+          <cell r="O37"/>
+          <cell r="P37"/>
+          <cell r="Q37"/>
+          <cell r="R37"/>
+          <cell r="S37"/>
+          <cell r="T37"/>
+          <cell r="U37"/>
+          <cell r="V37"/>
+          <cell r="W37"/>
+          <cell r="X37"/>
+        </row>
+        <row r="38">
+          <cell r="D38"/>
+          <cell r="E38"/>
+          <cell r="F38"/>
+          <cell r="G38"/>
+          <cell r="H38"/>
+          <cell r="I38"/>
+          <cell r="J38"/>
+          <cell r="K38"/>
+          <cell r="L38"/>
+          <cell r="M38"/>
+          <cell r="N38"/>
+          <cell r="O38"/>
+          <cell r="P38"/>
+          <cell r="Q38"/>
+          <cell r="R38"/>
+          <cell r="S38"/>
+          <cell r="T38"/>
+          <cell r="U38"/>
+          <cell r="V38"/>
+          <cell r="W38"/>
+          <cell r="X38"/>
+        </row>
+        <row r="39">
+          <cell r="D39"/>
+          <cell r="E39"/>
+          <cell r="F39"/>
+          <cell r="G39"/>
+          <cell r="H39"/>
+          <cell r="I39"/>
+          <cell r="J39"/>
+          <cell r="K39"/>
+          <cell r="L39"/>
+          <cell r="M39"/>
+          <cell r="N39"/>
+          <cell r="O39"/>
+          <cell r="P39"/>
+          <cell r="Q39"/>
+          <cell r="R39"/>
+          <cell r="S39"/>
+          <cell r="T39"/>
+          <cell r="U39"/>
+          <cell r="V39"/>
+          <cell r="W39"/>
+          <cell r="X39"/>
+        </row>
+        <row r="40">
+          <cell r="D40"/>
+          <cell r="E40"/>
+          <cell r="F40"/>
+          <cell r="G40"/>
+          <cell r="H40"/>
+          <cell r="I40"/>
+          <cell r="J40"/>
+          <cell r="K40"/>
+          <cell r="L40"/>
+          <cell r="M40"/>
+          <cell r="N40"/>
+          <cell r="O40"/>
+          <cell r="P40"/>
+          <cell r="Q40"/>
+          <cell r="R40"/>
+          <cell r="S40"/>
+          <cell r="T40"/>
+          <cell r="U40"/>
+          <cell r="V40"/>
+          <cell r="W40"/>
+          <cell r="X40"/>
+        </row>
+        <row r="41">
+          <cell r="D41"/>
+          <cell r="E41"/>
+          <cell r="F41"/>
+          <cell r="G41"/>
+          <cell r="H41"/>
+          <cell r="I41"/>
+          <cell r="J41"/>
+          <cell r="K41"/>
+          <cell r="L41"/>
+          <cell r="M41"/>
+          <cell r="N41"/>
+          <cell r="O41"/>
+          <cell r="P41"/>
+          <cell r="Q41"/>
+          <cell r="R41"/>
+          <cell r="S41"/>
+          <cell r="T41"/>
+          <cell r="U41"/>
+          <cell r="V41"/>
+          <cell r="W41"/>
+          <cell r="X41"/>
+        </row>
+        <row r="42">
+          <cell r="D42"/>
+          <cell r="E42"/>
+          <cell r="F42"/>
+          <cell r="G42"/>
+          <cell r="H42"/>
+          <cell r="I42"/>
+          <cell r="J42"/>
+          <cell r="K42"/>
+          <cell r="L42"/>
+          <cell r="M42"/>
+          <cell r="N42"/>
+          <cell r="O42"/>
+          <cell r="P42"/>
+          <cell r="Q42"/>
+          <cell r="R42"/>
+          <cell r="S42"/>
+          <cell r="T42"/>
+          <cell r="U42"/>
+          <cell r="V42"/>
+          <cell r="W42"/>
+          <cell r="X42"/>
+        </row>
+        <row r="43">
+          <cell r="D43"/>
+          <cell r="E43"/>
+          <cell r="F43"/>
+          <cell r="G43"/>
+          <cell r="H43"/>
+          <cell r="I43"/>
+          <cell r="J43"/>
+          <cell r="K43"/>
+          <cell r="L43"/>
+          <cell r="M43"/>
+          <cell r="N43"/>
+          <cell r="O43"/>
+          <cell r="P43"/>
+          <cell r="Q43"/>
+          <cell r="R43"/>
+          <cell r="S43"/>
+          <cell r="T43"/>
+          <cell r="U43"/>
+          <cell r="V43"/>
+          <cell r="W43"/>
+          <cell r="X43"/>
+        </row>
+        <row r="44">
+          <cell r="D44"/>
+          <cell r="E44"/>
+          <cell r="F44"/>
+          <cell r="G44"/>
+          <cell r="H44"/>
+          <cell r="I44"/>
+          <cell r="J44"/>
+          <cell r="K44"/>
+          <cell r="L44"/>
+          <cell r="M44"/>
+          <cell r="N44"/>
+          <cell r="O44"/>
+          <cell r="P44"/>
+          <cell r="Q44"/>
+          <cell r="R44"/>
+          <cell r="S44"/>
+          <cell r="T44"/>
+          <cell r="U44"/>
+          <cell r="V44"/>
+          <cell r="W44"/>
+          <cell r="X44"/>
+        </row>
+        <row r="45">
+          <cell r="D45"/>
+          <cell r="E45"/>
+          <cell r="F45"/>
+          <cell r="G45"/>
+          <cell r="H45"/>
+          <cell r="I45"/>
+          <cell r="J45"/>
+          <cell r="K45"/>
+          <cell r="L45"/>
+          <cell r="M45"/>
+          <cell r="N45"/>
+          <cell r="O45"/>
+          <cell r="P45"/>
+          <cell r="Q45"/>
+          <cell r="R45"/>
+          <cell r="S45"/>
+          <cell r="T45"/>
+          <cell r="U45"/>
+          <cell r="V45"/>
+          <cell r="W45"/>
+          <cell r="X45"/>
+        </row>
+        <row r="46">
+          <cell r="D46"/>
+          <cell r="E46"/>
+          <cell r="F46"/>
+          <cell r="G46"/>
+          <cell r="H46"/>
+          <cell r="I46"/>
+          <cell r="J46"/>
+          <cell r="K46"/>
+          <cell r="L46"/>
+          <cell r="M46"/>
+          <cell r="N46"/>
+          <cell r="O46"/>
+          <cell r="P46"/>
+          <cell r="Q46"/>
+          <cell r="R46"/>
+          <cell r="S46"/>
+          <cell r="T46"/>
+          <cell r="U46"/>
+          <cell r="V46"/>
+          <cell r="W46"/>
+          <cell r="X46"/>
+        </row>
+        <row r="47">
+          <cell r="D47"/>
+          <cell r="E47"/>
+          <cell r="F47"/>
+          <cell r="G47"/>
+          <cell r="H47"/>
+          <cell r="I47"/>
+          <cell r="J47"/>
+          <cell r="K47"/>
+          <cell r="L47"/>
+          <cell r="M47"/>
+          <cell r="N47"/>
+          <cell r="O47"/>
+          <cell r="P47"/>
+          <cell r="Q47"/>
+          <cell r="R47"/>
+          <cell r="S47"/>
+          <cell r="T47"/>
+          <cell r="U47"/>
+          <cell r="V47"/>
+          <cell r="W47"/>
+          <cell r="X47"/>
+        </row>
+        <row r="48">
+          <cell r="D48"/>
+          <cell r="E48"/>
+          <cell r="F48"/>
+          <cell r="G48"/>
+          <cell r="H48"/>
+          <cell r="I48"/>
+          <cell r="J48"/>
+          <cell r="K48"/>
+          <cell r="L48"/>
+          <cell r="M48"/>
+          <cell r="N48"/>
+          <cell r="O48"/>
+          <cell r="P48"/>
+          <cell r="Q48"/>
+          <cell r="R48"/>
+          <cell r="S48"/>
+          <cell r="T48"/>
+          <cell r="U48"/>
+          <cell r="V48"/>
+          <cell r="W48"/>
+          <cell r="X48"/>
+        </row>
+        <row r="49">
+          <cell r="D49"/>
+          <cell r="E49"/>
+          <cell r="F49"/>
+          <cell r="G49"/>
+          <cell r="H49"/>
+          <cell r="I49"/>
+          <cell r="J49"/>
+          <cell r="K49"/>
+          <cell r="L49"/>
+          <cell r="M49"/>
+          <cell r="N49"/>
+          <cell r="O49"/>
+          <cell r="P49"/>
+          <cell r="Q49"/>
+          <cell r="R49"/>
+          <cell r="S49"/>
+          <cell r="T49"/>
+          <cell r="U49"/>
+          <cell r="V49"/>
+          <cell r="W49"/>
+          <cell r="X49"/>
+        </row>
+        <row r="50">
+          <cell r="D50"/>
+          <cell r="E50"/>
+          <cell r="F50"/>
+          <cell r="G50"/>
+          <cell r="H50"/>
+          <cell r="I50"/>
+          <cell r="J50"/>
+          <cell r="K50"/>
+          <cell r="L50"/>
+          <cell r="M50"/>
+          <cell r="N50"/>
+          <cell r="O50"/>
+          <cell r="P50"/>
+          <cell r="Q50"/>
+          <cell r="R50"/>
+          <cell r="S50"/>
+          <cell r="T50"/>
+          <cell r="U50"/>
+          <cell r="V50"/>
+          <cell r="W50"/>
+          <cell r="X50"/>
+        </row>
+        <row r="51">
+          <cell r="D51"/>
+          <cell r="E51"/>
+          <cell r="F51"/>
+          <cell r="G51"/>
+          <cell r="H51"/>
+          <cell r="I51"/>
+          <cell r="J51"/>
+          <cell r="K51"/>
+          <cell r="L51"/>
+          <cell r="M51"/>
+          <cell r="N51"/>
+          <cell r="O51"/>
+          <cell r="P51"/>
+          <cell r="Q51"/>
+          <cell r="R51"/>
+          <cell r="S51"/>
+          <cell r="T51"/>
+          <cell r="U51"/>
+          <cell r="V51"/>
+          <cell r="W51"/>
+          <cell r="X51"/>
+        </row>
+        <row r="52">
+          <cell r="D52"/>
+          <cell r="E52"/>
+          <cell r="F52"/>
+          <cell r="G52"/>
+          <cell r="H52"/>
+          <cell r="I52"/>
+          <cell r="J52"/>
+          <cell r="K52"/>
+          <cell r="L52"/>
+          <cell r="M52"/>
+          <cell r="N52"/>
+          <cell r="O52"/>
+          <cell r="P52"/>
+          <cell r="Q52"/>
+          <cell r="R52"/>
+          <cell r="S52"/>
+          <cell r="T52"/>
+          <cell r="U52"/>
+          <cell r="V52"/>
+          <cell r="W52"/>
+          <cell r="X52"/>
+        </row>
+        <row r="53">
+          <cell r="D53"/>
+          <cell r="E53"/>
+          <cell r="F53"/>
+          <cell r="G53"/>
+          <cell r="H53"/>
+          <cell r="I53"/>
+          <cell r="J53"/>
+          <cell r="K53"/>
+          <cell r="L53"/>
+          <cell r="M53"/>
+          <cell r="N53"/>
+          <cell r="O53"/>
+          <cell r="P53"/>
+          <cell r="Q53"/>
+          <cell r="R53"/>
+          <cell r="S53"/>
+          <cell r="T53"/>
+          <cell r="U53"/>
+          <cell r="V53"/>
+          <cell r="W53"/>
+          <cell r="X53"/>
+        </row>
+        <row r="54">
+          <cell r="D54"/>
+          <cell r="E54"/>
+          <cell r="F54"/>
+          <cell r="G54"/>
+          <cell r="H54"/>
+          <cell r="I54"/>
+          <cell r="J54"/>
+          <cell r="K54"/>
+          <cell r="L54"/>
+          <cell r="M54"/>
+          <cell r="N54"/>
+          <cell r="O54"/>
+          <cell r="P54"/>
+          <cell r="Q54"/>
+          <cell r="R54"/>
+          <cell r="S54"/>
+          <cell r="T54"/>
+          <cell r="U54"/>
+          <cell r="V54"/>
+          <cell r="W54"/>
+          <cell r="X54"/>
+        </row>
+        <row r="55">
+          <cell r="D55"/>
+          <cell r="E55"/>
+          <cell r="F55"/>
+          <cell r="G55"/>
+          <cell r="H55"/>
+          <cell r="I55"/>
+          <cell r="J55"/>
+          <cell r="K55"/>
+          <cell r="L55"/>
+          <cell r="M55"/>
+          <cell r="N55"/>
+          <cell r="O55"/>
+          <cell r="P55"/>
+          <cell r="Q55"/>
+          <cell r="R55"/>
+          <cell r="S55"/>
+          <cell r="T55"/>
+          <cell r="U55"/>
+          <cell r="V55"/>
+          <cell r="W55"/>
+          <cell r="X55"/>
+        </row>
+        <row r="56">
+          <cell r="D56"/>
+          <cell r="E56"/>
+          <cell r="F56"/>
+          <cell r="G56"/>
+          <cell r="H56"/>
+          <cell r="I56"/>
+          <cell r="J56"/>
+          <cell r="K56"/>
+          <cell r="L56"/>
+          <cell r="M56"/>
+          <cell r="N56"/>
+          <cell r="O56"/>
+          <cell r="P56"/>
+          <cell r="Q56"/>
+          <cell r="R56"/>
+          <cell r="S56"/>
+          <cell r="T56"/>
+          <cell r="U56"/>
+          <cell r="V56"/>
+          <cell r="W56"/>
+          <cell r="X56"/>
+        </row>
+        <row r="57">
+          <cell r="D57"/>
+          <cell r="E57"/>
+          <cell r="F57"/>
+          <cell r="G57"/>
+          <cell r="H57"/>
+          <cell r="I57"/>
+          <cell r="J57"/>
+          <cell r="K57"/>
+          <cell r="L57"/>
+          <cell r="M57"/>
+          <cell r="N57"/>
+          <cell r="O57"/>
+          <cell r="P57"/>
+          <cell r="Q57"/>
+          <cell r="R57"/>
+          <cell r="S57"/>
+          <cell r="T57"/>
+          <cell r="U57"/>
+          <cell r="V57"/>
+          <cell r="W57"/>
+          <cell r="X57"/>
+        </row>
+        <row r="58">
+          <cell r="D58"/>
+          <cell r="E58"/>
+          <cell r="F58"/>
+          <cell r="G58"/>
+          <cell r="H58"/>
+          <cell r="I58"/>
+          <cell r="J58"/>
+          <cell r="K58"/>
+          <cell r="L58"/>
+          <cell r="M58"/>
+          <cell r="N58"/>
+          <cell r="O58"/>
+          <cell r="P58"/>
+          <cell r="Q58"/>
+          <cell r="R58"/>
+          <cell r="S58"/>
+          <cell r="T58"/>
+          <cell r="U58"/>
+          <cell r="V58"/>
+          <cell r="W58"/>
+          <cell r="X58"/>
+        </row>
+        <row r="59">
+          <cell r="D59"/>
+          <cell r="E59"/>
+          <cell r="F59"/>
+          <cell r="G59"/>
+          <cell r="H59"/>
+          <cell r="I59"/>
+          <cell r="J59"/>
+          <cell r="K59"/>
+          <cell r="L59"/>
+          <cell r="M59"/>
+          <cell r="N59"/>
+          <cell r="O59"/>
+          <cell r="P59"/>
+          <cell r="Q59"/>
+          <cell r="R59"/>
+          <cell r="S59"/>
+          <cell r="T59"/>
+          <cell r="U59"/>
+          <cell r="V59"/>
+          <cell r="W59"/>
+          <cell r="X59"/>
+        </row>
+        <row r="60">
+          <cell r="D60"/>
+          <cell r="E60"/>
+          <cell r="F60"/>
+          <cell r="G60"/>
+          <cell r="H60"/>
+          <cell r="I60"/>
+          <cell r="J60"/>
+          <cell r="K60"/>
+          <cell r="L60"/>
+          <cell r="M60"/>
+          <cell r="N60"/>
+          <cell r="O60"/>
+          <cell r="P60"/>
+          <cell r="Q60"/>
+          <cell r="R60"/>
+          <cell r="S60"/>
+          <cell r="T60"/>
+          <cell r="U60"/>
+          <cell r="V60"/>
+          <cell r="W60"/>
+          <cell r="X60"/>
+        </row>
+        <row r="61">
+          <cell r="D61"/>
+          <cell r="E61"/>
+          <cell r="F61"/>
+          <cell r="G61"/>
+          <cell r="H61"/>
+          <cell r="I61"/>
+          <cell r="J61"/>
+          <cell r="K61"/>
+          <cell r="L61"/>
+          <cell r="M61"/>
+          <cell r="N61"/>
+          <cell r="O61"/>
+          <cell r="P61"/>
+          <cell r="Q61"/>
+          <cell r="R61"/>
+          <cell r="S61"/>
+          <cell r="T61"/>
+          <cell r="U61"/>
+          <cell r="V61"/>
+          <cell r="W61"/>
+          <cell r="X61"/>
+        </row>
+        <row r="62">
+          <cell r="D62"/>
+          <cell r="E62"/>
+          <cell r="F62"/>
+          <cell r="G62"/>
+          <cell r="H62"/>
+          <cell r="I62"/>
+          <cell r="J62"/>
+          <cell r="K62"/>
+          <cell r="L62"/>
+          <cell r="M62"/>
+          <cell r="N62"/>
+          <cell r="O62"/>
+          <cell r="P62"/>
+          <cell r="Q62"/>
+          <cell r="R62"/>
+          <cell r="S62"/>
+          <cell r="T62"/>
+          <cell r="U62"/>
+          <cell r="V62"/>
+          <cell r="W62"/>
+          <cell r="X62"/>
+        </row>
+        <row r="63">
+          <cell r="D63"/>
+          <cell r="E63"/>
+          <cell r="F63"/>
+          <cell r="G63"/>
+          <cell r="H63"/>
+          <cell r="I63"/>
+          <cell r="J63"/>
+          <cell r="K63"/>
+          <cell r="L63"/>
+          <cell r="M63"/>
+          <cell r="N63"/>
+          <cell r="O63"/>
+          <cell r="P63"/>
+          <cell r="Q63"/>
+          <cell r="R63"/>
+          <cell r="S63"/>
+          <cell r="T63"/>
+          <cell r="U63"/>
+          <cell r="V63"/>
+          <cell r="W63"/>
+          <cell r="X63"/>
+        </row>
+        <row r="64">
+          <cell r="D64"/>
+          <cell r="E64"/>
+          <cell r="F64"/>
+          <cell r="G64"/>
+          <cell r="H64"/>
+          <cell r="I64"/>
+          <cell r="J64"/>
+          <cell r="K64"/>
+          <cell r="L64"/>
+          <cell r="M64"/>
+          <cell r="N64"/>
+          <cell r="O64"/>
+          <cell r="P64"/>
+          <cell r="Q64"/>
+          <cell r="R64"/>
+          <cell r="S64"/>
+          <cell r="T64"/>
+          <cell r="U64"/>
+          <cell r="V64"/>
+          <cell r="W64"/>
+          <cell r="X64"/>
+        </row>
+        <row r="65">
+          <cell r="D65"/>
+          <cell r="E65"/>
+          <cell r="F65"/>
+          <cell r="G65"/>
+          <cell r="H65"/>
+          <cell r="I65"/>
+          <cell r="J65"/>
+          <cell r="K65"/>
+          <cell r="L65"/>
+          <cell r="M65"/>
+          <cell r="N65"/>
+          <cell r="O65"/>
+          <cell r="P65"/>
+          <cell r="Q65"/>
+          <cell r="R65"/>
+          <cell r="S65"/>
+          <cell r="T65"/>
+          <cell r="U65"/>
+          <cell r="V65"/>
+          <cell r="W65"/>
+          <cell r="X65"/>
+        </row>
+        <row r="66">
+          <cell r="D66"/>
+          <cell r="E66"/>
+          <cell r="F66"/>
+          <cell r="G66"/>
+          <cell r="H66"/>
+          <cell r="I66"/>
+          <cell r="J66"/>
+          <cell r="K66"/>
+          <cell r="L66"/>
+          <cell r="M66"/>
+          <cell r="N66"/>
+          <cell r="O66"/>
+          <cell r="P66"/>
+          <cell r="Q66"/>
+          <cell r="R66"/>
+          <cell r="S66"/>
+          <cell r="T66"/>
+          <cell r="U66"/>
+          <cell r="V66"/>
+          <cell r="W66"/>
+          <cell r="X66"/>
+        </row>
+        <row r="67">
+          <cell r="D67"/>
+          <cell r="E67"/>
+          <cell r="F67"/>
+          <cell r="G67"/>
+          <cell r="H67"/>
+          <cell r="I67"/>
+          <cell r="J67"/>
+          <cell r="K67"/>
+          <cell r="L67"/>
+          <cell r="M67"/>
+          <cell r="N67"/>
+          <cell r="O67"/>
+          <cell r="P67"/>
+          <cell r="Q67"/>
+          <cell r="R67"/>
+          <cell r="S67"/>
+          <cell r="T67"/>
+          <cell r="U67"/>
+          <cell r="V67"/>
+          <cell r="W67"/>
+          <cell r="X67"/>
+        </row>
+        <row r="68">
+          <cell r="D68"/>
+          <cell r="E68"/>
+          <cell r="F68"/>
+          <cell r="G68"/>
+          <cell r="H68"/>
+          <cell r="I68"/>
+          <cell r="J68"/>
+          <cell r="K68"/>
+          <cell r="L68"/>
+          <cell r="M68"/>
+          <cell r="N68"/>
+          <cell r="O68"/>
+          <cell r="P68"/>
+          <cell r="Q68"/>
+          <cell r="R68"/>
+          <cell r="S68"/>
+          <cell r="T68"/>
+          <cell r="U68"/>
+          <cell r="V68"/>
+          <cell r="W68"/>
+          <cell r="X68"/>
+        </row>
+        <row r="69">
+          <cell r="D69"/>
+          <cell r="E69"/>
+          <cell r="F69"/>
+          <cell r="G69"/>
+          <cell r="H69"/>
+          <cell r="I69"/>
+          <cell r="J69"/>
+          <cell r="K69"/>
+          <cell r="L69"/>
+          <cell r="M69"/>
+          <cell r="N69"/>
+          <cell r="O69"/>
+          <cell r="P69"/>
+          <cell r="Q69"/>
+          <cell r="R69"/>
+          <cell r="S69"/>
+          <cell r="T69"/>
+          <cell r="U69"/>
+          <cell r="V69"/>
+          <cell r="W69"/>
+          <cell r="X69"/>
+        </row>
+        <row r="70">
+          <cell r="D70"/>
+          <cell r="E70"/>
+          <cell r="F70"/>
+          <cell r="G70"/>
+          <cell r="H70"/>
+          <cell r="I70"/>
+          <cell r="J70"/>
+          <cell r="K70"/>
+          <cell r="L70"/>
+          <cell r="M70"/>
+          <cell r="N70"/>
+          <cell r="O70"/>
+          <cell r="P70"/>
+          <cell r="Q70"/>
+          <cell r="R70"/>
+          <cell r="S70"/>
+          <cell r="T70"/>
+          <cell r="U70"/>
+          <cell r="V70"/>
+          <cell r="W70"/>
+          <cell r="X70"/>
+        </row>
+        <row r="71">
+          <cell r="D71"/>
+          <cell r="E71"/>
+          <cell r="F71"/>
+          <cell r="G71"/>
+          <cell r="H71"/>
+          <cell r="I71"/>
+          <cell r="J71"/>
+          <cell r="K71"/>
+          <cell r="L71"/>
+          <cell r="M71"/>
+          <cell r="N71"/>
+          <cell r="O71"/>
+          <cell r="P71"/>
+          <cell r="Q71"/>
+          <cell r="R71"/>
+          <cell r="S71"/>
+          <cell r="T71"/>
+          <cell r="U71"/>
+          <cell r="V71"/>
+          <cell r="W71"/>
+          <cell r="X71"/>
+        </row>
+        <row r="72">
+          <cell r="D72"/>
+          <cell r="E72"/>
+          <cell r="F72"/>
+          <cell r="G72"/>
+          <cell r="H72"/>
+          <cell r="I72"/>
+          <cell r="J72"/>
+          <cell r="K72"/>
+          <cell r="L72"/>
+          <cell r="M72"/>
+          <cell r="N72"/>
+          <cell r="O72"/>
+          <cell r="P72"/>
+          <cell r="Q72"/>
+          <cell r="R72"/>
+          <cell r="S72"/>
+          <cell r="T72"/>
+          <cell r="U72"/>
+          <cell r="V72"/>
+          <cell r="W72"/>
+          <cell r="X72"/>
+        </row>
+        <row r="73">
+          <cell r="D73"/>
+          <cell r="E73"/>
+          <cell r="F73"/>
+          <cell r="G73"/>
+          <cell r="H73"/>
+          <cell r="I73"/>
+          <cell r="J73"/>
+          <cell r="K73"/>
+          <cell r="L73"/>
+          <cell r="M73"/>
+          <cell r="N73"/>
+          <cell r="O73"/>
+          <cell r="P73"/>
+          <cell r="Q73"/>
+          <cell r="R73"/>
+          <cell r="S73"/>
+          <cell r="T73"/>
+          <cell r="U73"/>
+          <cell r="V73"/>
+          <cell r="W73"/>
+          <cell r="X73"/>
+        </row>
+        <row r="74">
+          <cell r="D74"/>
+          <cell r="E74"/>
+          <cell r="F74"/>
+          <cell r="G74"/>
+          <cell r="H74"/>
+          <cell r="I74"/>
+          <cell r="J74"/>
+          <cell r="K74"/>
+          <cell r="L74"/>
+          <cell r="M74"/>
+          <cell r="N74"/>
+          <cell r="O74"/>
+          <cell r="P74"/>
+          <cell r="Q74"/>
+          <cell r="R74"/>
+          <cell r="S74"/>
+          <cell r="T74"/>
+          <cell r="U74"/>
+          <cell r="V74"/>
+          <cell r="W74"/>
+          <cell r="X74"/>
+        </row>
+        <row r="75">
+          <cell r="D75"/>
+          <cell r="E75"/>
+          <cell r="F75"/>
+          <cell r="G75"/>
+          <cell r="H75"/>
+          <cell r="I75"/>
+          <cell r="J75"/>
+          <cell r="K75"/>
+          <cell r="L75"/>
+          <cell r="M75"/>
+          <cell r="N75"/>
+          <cell r="O75"/>
+          <cell r="P75"/>
+          <cell r="Q75"/>
+          <cell r="R75"/>
+          <cell r="S75"/>
+          <cell r="T75"/>
+          <cell r="U75"/>
+          <cell r="V75"/>
+          <cell r="W75"/>
+          <cell r="X75"/>
+        </row>
+        <row r="76">
+          <cell r="D76"/>
+          <cell r="E76"/>
+          <cell r="F76"/>
+          <cell r="G76"/>
+          <cell r="H76"/>
+          <cell r="I76"/>
+          <cell r="J76"/>
+          <cell r="K76"/>
+          <cell r="L76"/>
+          <cell r="M76"/>
+          <cell r="N76"/>
+          <cell r="O76"/>
+          <cell r="P76"/>
+          <cell r="Q76"/>
+          <cell r="R76"/>
+          <cell r="S76"/>
+          <cell r="T76"/>
+          <cell r="U76"/>
+          <cell r="V76"/>
+          <cell r="W76"/>
+          <cell r="X76"/>
+        </row>
+        <row r="77">
+          <cell r="D77"/>
+          <cell r="E77"/>
+          <cell r="F77"/>
+          <cell r="G77"/>
+          <cell r="H77"/>
+          <cell r="I77"/>
+          <cell r="J77"/>
+          <cell r="K77"/>
+          <cell r="L77"/>
+          <cell r="M77"/>
+          <cell r="N77"/>
+          <cell r="O77"/>
+          <cell r="P77"/>
+          <cell r="Q77"/>
+          <cell r="R77"/>
+          <cell r="S77"/>
+          <cell r="T77"/>
+          <cell r="U77"/>
+          <cell r="V77"/>
+          <cell r="W77"/>
+          <cell r="X77"/>
+        </row>
+        <row r="78">
+          <cell r="D78"/>
+          <cell r="E78"/>
+          <cell r="F78"/>
+          <cell r="G78"/>
+          <cell r="H78"/>
+          <cell r="I78"/>
+          <cell r="J78"/>
+          <cell r="K78"/>
+          <cell r="L78"/>
+          <cell r="M78"/>
+          <cell r="N78"/>
+          <cell r="O78"/>
+          <cell r="P78"/>
+          <cell r="Q78"/>
+          <cell r="R78"/>
+          <cell r="S78"/>
+          <cell r="T78"/>
+          <cell r="U78"/>
+          <cell r="V78"/>
+          <cell r="W78"/>
+          <cell r="X78"/>
+        </row>
+        <row r="79">
+          <cell r="D79"/>
+          <cell r="E79"/>
+          <cell r="F79"/>
+          <cell r="G79"/>
+          <cell r="H79"/>
+          <cell r="I79"/>
+          <cell r="J79"/>
+          <cell r="K79"/>
+          <cell r="L79"/>
+          <cell r="M79"/>
+          <cell r="N79"/>
+          <cell r="O79"/>
+          <cell r="P79"/>
+          <cell r="Q79"/>
+          <cell r="R79"/>
+          <cell r="S79"/>
+          <cell r="T79"/>
+          <cell r="U79"/>
+          <cell r="V79"/>
+          <cell r="W79"/>
+          <cell r="X79"/>
+        </row>
+        <row r="80">
+          <cell r="D80"/>
+          <cell r="E80"/>
+          <cell r="F80"/>
+          <cell r="G80"/>
+          <cell r="H80"/>
+          <cell r="I80"/>
+          <cell r="J80"/>
+          <cell r="K80"/>
+          <cell r="L80"/>
+          <cell r="M80"/>
+          <cell r="N80"/>
+          <cell r="O80"/>
+          <cell r="P80"/>
+          <cell r="Q80"/>
+          <cell r="R80"/>
+          <cell r="S80"/>
+          <cell r="T80"/>
+          <cell r="U80"/>
+          <cell r="V80"/>
+          <cell r="W80"/>
+          <cell r="X80"/>
+        </row>
+        <row r="81">
+          <cell r="D81"/>
+          <cell r="E81"/>
+          <cell r="F81"/>
+          <cell r="G81"/>
+          <cell r="H81"/>
+          <cell r="I81"/>
+          <cell r="J81"/>
+          <cell r="K81"/>
+          <cell r="L81"/>
+          <cell r="M81"/>
+          <cell r="N81"/>
+          <cell r="O81"/>
+          <cell r="P81"/>
+          <cell r="Q81"/>
+          <cell r="R81"/>
+          <cell r="S81"/>
+          <cell r="T81"/>
+          <cell r="U81"/>
+          <cell r="V81"/>
+          <cell r="W81"/>
+          <cell r="X81"/>
+        </row>
+        <row r="82">
+          <cell r="D82"/>
+          <cell r="E82"/>
+          <cell r="F82"/>
+          <cell r="G82"/>
+          <cell r="H82"/>
+          <cell r="I82"/>
+          <cell r="J82"/>
+          <cell r="K82"/>
+          <cell r="L82"/>
+          <cell r="M82"/>
+          <cell r="N82"/>
+          <cell r="O82"/>
+          <cell r="P82"/>
+          <cell r="Q82"/>
+          <cell r="R82"/>
+          <cell r="S82"/>
+          <cell r="T82"/>
+          <cell r="U82"/>
+          <cell r="V82"/>
+          <cell r="W82"/>
+          <cell r="X82"/>
+        </row>
+        <row r="83">
+          <cell r="D83"/>
+          <cell r="E83"/>
+          <cell r="F83"/>
+          <cell r="G83"/>
+          <cell r="H83"/>
+          <cell r="I83"/>
+          <cell r="J83"/>
+          <cell r="K83"/>
+          <cell r="L83"/>
+          <cell r="M83"/>
+          <cell r="N83"/>
+          <cell r="O83"/>
+          <cell r="P83"/>
+          <cell r="Q83"/>
+          <cell r="R83"/>
+          <cell r="S83"/>
+          <cell r="T83"/>
+          <cell r="U83"/>
+          <cell r="V83"/>
+          <cell r="W83"/>
+          <cell r="X83"/>
+        </row>
+        <row r="84">
+          <cell r="D84"/>
+          <cell r="E84"/>
+          <cell r="F84"/>
+          <cell r="G84"/>
+          <cell r="H84"/>
+          <cell r="I84"/>
+          <cell r="J84"/>
+          <cell r="K84"/>
+          <cell r="L84"/>
+          <cell r="M84"/>
+          <cell r="N84"/>
+          <cell r="O84"/>
+          <cell r="P84"/>
+          <cell r="Q84"/>
+          <cell r="R84"/>
+          <cell r="S84"/>
+          <cell r="T84"/>
+          <cell r="U84"/>
+          <cell r="V84"/>
+          <cell r="W84"/>
+          <cell r="X84"/>
+        </row>
+        <row r="85">
+          <cell r="D85"/>
+          <cell r="E85"/>
+          <cell r="F85"/>
+          <cell r="G85"/>
+          <cell r="H85"/>
+          <cell r="I85"/>
+          <cell r="J85"/>
+          <cell r="K85"/>
+          <cell r="L85"/>
+          <cell r="M85"/>
+          <cell r="N85"/>
+          <cell r="O85"/>
+          <cell r="P85"/>
+          <cell r="Q85"/>
+          <cell r="R85"/>
+          <cell r="S85"/>
+          <cell r="T85"/>
+          <cell r="U85"/>
+          <cell r="V85"/>
+          <cell r="W85"/>
+          <cell r="X85"/>
+        </row>
+        <row r="86">
+          <cell r="D86"/>
+          <cell r="E86"/>
+          <cell r="F86"/>
+          <cell r="G86"/>
+          <cell r="H86"/>
+          <cell r="I86"/>
+          <cell r="J86"/>
+          <cell r="K86"/>
+          <cell r="L86"/>
+          <cell r="M86"/>
+          <cell r="N86"/>
+          <cell r="O86"/>
+          <cell r="P86"/>
+          <cell r="Q86"/>
+          <cell r="R86"/>
+          <cell r="S86"/>
+          <cell r="T86"/>
+          <cell r="U86"/>
+          <cell r="V86"/>
+          <cell r="W86"/>
+          <cell r="X86"/>
+        </row>
+        <row r="87">
+          <cell r="D87"/>
+          <cell r="E87"/>
+          <cell r="F87"/>
+          <cell r="G87"/>
+          <cell r="H87"/>
+          <cell r="I87"/>
+          <cell r="J87"/>
+          <cell r="K87"/>
+          <cell r="L87"/>
+          <cell r="M87"/>
+          <cell r="N87"/>
+          <cell r="O87"/>
+          <cell r="P87"/>
+          <cell r="Q87"/>
+          <cell r="R87"/>
+          <cell r="S87"/>
+          <cell r="T87"/>
+          <cell r="U87"/>
+          <cell r="V87"/>
+          <cell r="W87"/>
+          <cell r="X87"/>
+        </row>
+        <row r="88">
+          <cell r="D88"/>
+          <cell r="E88"/>
+          <cell r="F88"/>
+          <cell r="G88"/>
+          <cell r="H88"/>
+          <cell r="I88"/>
+          <cell r="J88"/>
+          <cell r="K88"/>
+          <cell r="L88"/>
+          <cell r="M88"/>
+          <cell r="N88"/>
+          <cell r="O88"/>
+          <cell r="P88"/>
+          <cell r="Q88"/>
+          <cell r="R88"/>
+          <cell r="S88"/>
+          <cell r="T88"/>
+          <cell r="U88"/>
+          <cell r="V88"/>
+          <cell r="W88"/>
+          <cell r="X88"/>
+        </row>
+        <row r="89">
+          <cell r="D89"/>
+          <cell r="E89"/>
+          <cell r="F89"/>
+          <cell r="G89"/>
+          <cell r="H89"/>
+          <cell r="I89"/>
+          <cell r="J89"/>
+          <cell r="K89"/>
+          <cell r="L89"/>
+          <cell r="M89"/>
+          <cell r="N89"/>
+          <cell r="O89"/>
+          <cell r="P89"/>
+          <cell r="Q89"/>
+          <cell r="R89"/>
+          <cell r="S89"/>
+          <cell r="T89"/>
+          <cell r="U89"/>
+          <cell r="V89"/>
+          <cell r="W89"/>
+          <cell r="X89"/>
+        </row>
+        <row r="90">
+          <cell r="D90"/>
+          <cell r="E90"/>
+          <cell r="F90"/>
+          <cell r="G90"/>
+          <cell r="H90"/>
+          <cell r="I90"/>
+          <cell r="J90"/>
+          <cell r="K90"/>
+          <cell r="L90"/>
+          <cell r="M90"/>
+          <cell r="N90"/>
+          <cell r="O90"/>
+          <cell r="P90"/>
+          <cell r="Q90"/>
+          <cell r="R90"/>
+          <cell r="S90"/>
+          <cell r="T90"/>
+          <cell r="U90"/>
+          <cell r="V90"/>
+          <cell r="W90"/>
+          <cell r="X90"/>
+        </row>
+        <row r="91">
+          <cell r="D91"/>
+          <cell r="E91"/>
+          <cell r="F91"/>
+          <cell r="G91"/>
+          <cell r="H91"/>
+          <cell r="I91"/>
+          <cell r="J91"/>
+          <cell r="K91"/>
+          <cell r="L91"/>
+          <cell r="M91"/>
+          <cell r="N91"/>
+          <cell r="O91"/>
+          <cell r="P91"/>
+          <cell r="Q91"/>
+          <cell r="R91"/>
+          <cell r="S91"/>
+          <cell r="T91"/>
+          <cell r="U91"/>
+          <cell r="V91"/>
+          <cell r="W91"/>
+          <cell r="X91"/>
+        </row>
+        <row r="92">
+          <cell r="D92"/>
+          <cell r="E92"/>
+          <cell r="F92"/>
+          <cell r="G92"/>
+          <cell r="H92"/>
+          <cell r="I92"/>
+          <cell r="J92"/>
+          <cell r="K92"/>
+          <cell r="L92"/>
+          <cell r="M92"/>
+          <cell r="N92"/>
+          <cell r="O92"/>
+          <cell r="P92"/>
+          <cell r="Q92"/>
+          <cell r="R92"/>
+          <cell r="S92"/>
+          <cell r="T92"/>
+          <cell r="U92"/>
+          <cell r="V92"/>
+          <cell r="W92"/>
+          <cell r="X92"/>
+        </row>
+        <row r="93">
+          <cell r="D93"/>
+          <cell r="E93"/>
+          <cell r="F93"/>
+          <cell r="G93"/>
+          <cell r="H93"/>
+          <cell r="I93"/>
+          <cell r="J93"/>
+          <cell r="K93"/>
+          <cell r="L93"/>
+          <cell r="M93"/>
+          <cell r="N93"/>
+          <cell r="O93"/>
+          <cell r="P93"/>
+          <cell r="Q93"/>
+          <cell r="R93"/>
+          <cell r="S93"/>
+          <cell r="T93"/>
+          <cell r="U93"/>
+          <cell r="V93"/>
+          <cell r="W93"/>
+          <cell r="X93"/>
+        </row>
+        <row r="94">
+          <cell r="D94"/>
+          <cell r="E94"/>
+          <cell r="F94"/>
+          <cell r="G94"/>
+          <cell r="H94"/>
+          <cell r="I94"/>
+          <cell r="J94"/>
+          <cell r="K94"/>
+          <cell r="L94"/>
+          <cell r="M94"/>
+          <cell r="N94"/>
+          <cell r="O94"/>
+          <cell r="P94"/>
+          <cell r="Q94"/>
+          <cell r="R94"/>
+          <cell r="S94"/>
+          <cell r="T94"/>
+          <cell r="U94"/>
+          <cell r="V94"/>
+          <cell r="W94"/>
+          <cell r="X94"/>
+        </row>
+        <row r="95">
+          <cell r="D95"/>
+          <cell r="E95"/>
+          <cell r="F95"/>
+          <cell r="G95"/>
+          <cell r="H95"/>
+          <cell r="I95"/>
+          <cell r="J95"/>
+          <cell r="K95"/>
+          <cell r="L95"/>
+          <cell r="M95"/>
+          <cell r="N95"/>
+          <cell r="O95"/>
+          <cell r="P95"/>
+          <cell r="Q95"/>
+          <cell r="R95"/>
+          <cell r="S95"/>
+          <cell r="T95"/>
+          <cell r="U95"/>
+          <cell r="V95"/>
+          <cell r="W95"/>
+          <cell r="X95"/>
+        </row>
+        <row r="96">
+          <cell r="D96"/>
+          <cell r="E96"/>
+          <cell r="F96"/>
+          <cell r="G96"/>
+          <cell r="H96"/>
+          <cell r="I96"/>
+          <cell r="J96"/>
+          <cell r="K96"/>
+          <cell r="L96"/>
+          <cell r="M96"/>
+          <cell r="N96"/>
+          <cell r="O96"/>
+          <cell r="P96"/>
+          <cell r="Q96"/>
+          <cell r="R96"/>
+          <cell r="S96"/>
+          <cell r="T96"/>
+          <cell r="U96"/>
+          <cell r="V96"/>
+          <cell r="W96"/>
+          <cell r="X96"/>
+        </row>
+        <row r="97">
+          <cell r="D97"/>
+          <cell r="E97"/>
+          <cell r="F97"/>
+          <cell r="G97"/>
+          <cell r="H97"/>
+          <cell r="I97"/>
+          <cell r="J97"/>
+          <cell r="K97"/>
+          <cell r="L97"/>
+          <cell r="M97"/>
+          <cell r="N97"/>
+          <cell r="O97"/>
+          <cell r="P97"/>
+          <cell r="Q97"/>
+          <cell r="R97"/>
+          <cell r="S97"/>
+          <cell r="T97"/>
+          <cell r="U97"/>
+          <cell r="V97"/>
+          <cell r="W97"/>
+          <cell r="X97"/>
+        </row>
+        <row r="98">
+          <cell r="D98"/>
+          <cell r="E98"/>
+          <cell r="F98"/>
+          <cell r="G98"/>
+          <cell r="H98"/>
+          <cell r="I98"/>
+          <cell r="J98"/>
+          <cell r="K98"/>
+          <cell r="L98"/>
+          <cell r="M98"/>
+          <cell r="N98"/>
+          <cell r="O98"/>
+          <cell r="P98"/>
+          <cell r="Q98"/>
+          <cell r="R98"/>
+          <cell r="S98"/>
+          <cell r="T98"/>
+          <cell r="U98"/>
+          <cell r="V98"/>
+          <cell r="W98"/>
+          <cell r="X98"/>
+        </row>
+        <row r="99">
+          <cell r="D99"/>
+          <cell r="E99"/>
+          <cell r="F99"/>
+          <cell r="G99"/>
+          <cell r="H99"/>
+          <cell r="I99"/>
+          <cell r="J99"/>
+          <cell r="K99"/>
+          <cell r="L99"/>
+          <cell r="M99"/>
+          <cell r="N99"/>
+          <cell r="O99"/>
+          <cell r="P99"/>
+          <cell r="Q99"/>
+          <cell r="R99"/>
+          <cell r="S99"/>
+          <cell r="T99"/>
+          <cell r="U99"/>
+          <cell r="V99"/>
+          <cell r="W99"/>
+          <cell r="X99"/>
+        </row>
+        <row r="100">
+          <cell r="D100"/>
+          <cell r="E100"/>
+          <cell r="F100"/>
+          <cell r="G100"/>
+          <cell r="H100"/>
+          <cell r="I100"/>
+          <cell r="J100"/>
+          <cell r="K100"/>
+          <cell r="L100"/>
+          <cell r="M100"/>
+          <cell r="N100"/>
+          <cell r="O100"/>
+          <cell r="P100"/>
+          <cell r="Q100"/>
+          <cell r="R100"/>
+          <cell r="S100"/>
+          <cell r="T100"/>
+          <cell r="U100"/>
+          <cell r="V100"/>
+          <cell r="W100"/>
+          <cell r="X100"/>
+        </row>
+        <row r="101">
+          <cell r="D101"/>
+          <cell r="E101"/>
+          <cell r="F101"/>
+          <cell r="G101"/>
+          <cell r="H101"/>
+          <cell r="I101"/>
+          <cell r="J101"/>
+          <cell r="K101"/>
+          <cell r="L101"/>
+          <cell r="M101"/>
+          <cell r="N101"/>
+          <cell r="O101"/>
+          <cell r="P101"/>
+          <cell r="Q101"/>
+          <cell r="R101"/>
+          <cell r="S101"/>
+          <cell r="T101"/>
+          <cell r="U101"/>
+          <cell r="V101"/>
+          <cell r="W101"/>
+          <cell r="X101"/>
+        </row>
+        <row r="102">
+          <cell r="D102"/>
+          <cell r="E102"/>
+          <cell r="F102"/>
+          <cell r="G102"/>
+          <cell r="H102"/>
+          <cell r="I102"/>
+          <cell r="J102"/>
+          <cell r="K102"/>
+          <cell r="L102"/>
+          <cell r="M102"/>
+          <cell r="N102"/>
+          <cell r="O102"/>
+          <cell r="P102"/>
+          <cell r="Q102"/>
+          <cell r="R102"/>
+          <cell r="S102"/>
+          <cell r="T102"/>
+          <cell r="U102"/>
+          <cell r="V102"/>
+          <cell r="W102"/>
+          <cell r="X102"/>
+        </row>
+        <row r="103">
+          <cell r="D103"/>
+          <cell r="E103"/>
+          <cell r="F103"/>
+          <cell r="G103"/>
+          <cell r="H103"/>
+          <cell r="I103"/>
+          <cell r="J103"/>
+          <cell r="K103"/>
+          <cell r="L103"/>
+          <cell r="M103"/>
+          <cell r="N103"/>
+          <cell r="O103"/>
+          <cell r="P103"/>
+          <cell r="Q103"/>
+          <cell r="R103"/>
+          <cell r="S103"/>
+          <cell r="T103"/>
+          <cell r="U103"/>
+          <cell r="V103"/>
+          <cell r="W103"/>
+          <cell r="X103"/>
+        </row>
+        <row r="104">
+          <cell r="D104"/>
+          <cell r="E104"/>
+          <cell r="F104"/>
+          <cell r="G104"/>
+          <cell r="H104"/>
+          <cell r="I104"/>
+          <cell r="J104"/>
+          <cell r="K104"/>
+          <cell r="L104"/>
+          <cell r="M104"/>
+          <cell r="N104"/>
+          <cell r="O104"/>
+          <cell r="P104"/>
+          <cell r="Q104"/>
+          <cell r="R104"/>
+          <cell r="S104"/>
+          <cell r="T104"/>
+          <cell r="U104"/>
+          <cell r="V104"/>
+          <cell r="W104"/>
+          <cell r="X104"/>
+        </row>
+        <row r="105">
+          <cell r="D105"/>
+          <cell r="E105"/>
+          <cell r="F105"/>
+          <cell r="G105"/>
+          <cell r="H105"/>
+          <cell r="I105"/>
+          <cell r="J105"/>
+          <cell r="K105"/>
+          <cell r="L105"/>
+          <cell r="M105"/>
+          <cell r="N105"/>
+          <cell r="O105"/>
+          <cell r="P105"/>
+          <cell r="Q105"/>
+          <cell r="R105"/>
+          <cell r="S105"/>
+          <cell r="T105"/>
+          <cell r="U105"/>
+          <cell r="V105"/>
+          <cell r="W105"/>
+          <cell r="X105"/>
+        </row>
+        <row r="106">
+          <cell r="D106"/>
+          <cell r="E106"/>
+          <cell r="F106"/>
+          <cell r="G106"/>
+          <cell r="H106"/>
+          <cell r="I106"/>
+          <cell r="J106"/>
+          <cell r="K106"/>
+          <cell r="L106"/>
+          <cell r="M106"/>
+          <cell r="N106"/>
+          <cell r="O106"/>
+          <cell r="P106"/>
+          <cell r="Q106"/>
+          <cell r="R106"/>
+          <cell r="S106"/>
+          <cell r="T106"/>
+          <cell r="U106"/>
+          <cell r="V106"/>
+          <cell r="W106"/>
+          <cell r="X106"/>
+        </row>
+        <row r="107">
+          <cell r="D107"/>
+          <cell r="E107"/>
+          <cell r="F107"/>
+          <cell r="G107"/>
+          <cell r="H107"/>
+          <cell r="I107"/>
+          <cell r="J107"/>
+          <cell r="K107"/>
+          <cell r="L107"/>
+          <cell r="M107"/>
+          <cell r="N107"/>
+          <cell r="O107"/>
+          <cell r="P107"/>
+          <cell r="Q107"/>
+          <cell r="R107"/>
+          <cell r="S107"/>
+          <cell r="T107"/>
+          <cell r="U107"/>
+          <cell r="V107"/>
+          <cell r="W107"/>
+          <cell r="X107"/>
+        </row>
+        <row r="108">
+          <cell r="D108"/>
+          <cell r="E108"/>
+          <cell r="F108"/>
+          <cell r="G108"/>
+          <cell r="H108"/>
+          <cell r="I108"/>
+          <cell r="J108"/>
+          <cell r="K108"/>
+          <cell r="L108"/>
+          <cell r="M108"/>
+          <cell r="N108"/>
+          <cell r="O108"/>
+          <cell r="P108"/>
+          <cell r="Q108"/>
+          <cell r="R108"/>
+          <cell r="S108"/>
+          <cell r="T108"/>
+          <cell r="U108"/>
+          <cell r="V108"/>
+          <cell r="W108"/>
+          <cell r="X108"/>
+        </row>
+        <row r="109">
+          <cell r="D109"/>
+          <cell r="E109"/>
+          <cell r="F109"/>
+          <cell r="G109"/>
+          <cell r="H109"/>
+          <cell r="I109"/>
+          <cell r="J109"/>
+          <cell r="K109"/>
+          <cell r="L109"/>
+          <cell r="M109"/>
+          <cell r="N109"/>
+          <cell r="O109"/>
+          <cell r="P109"/>
+          <cell r="Q109"/>
+          <cell r="R109"/>
+          <cell r="S109"/>
+          <cell r="T109"/>
+          <cell r="U109"/>
+          <cell r="V109"/>
+          <cell r="W109"/>
+          <cell r="X109"/>
+        </row>
+        <row r="110">
+          <cell r="D110"/>
+          <cell r="E110"/>
+          <cell r="F110"/>
+          <cell r="G110"/>
+          <cell r="H110"/>
+          <cell r="I110"/>
+          <cell r="J110"/>
+          <cell r="K110"/>
+          <cell r="L110"/>
+          <cell r="M110"/>
+          <cell r="N110"/>
+          <cell r="O110"/>
+          <cell r="P110"/>
+          <cell r="Q110"/>
+          <cell r="R110"/>
+          <cell r="S110"/>
+          <cell r="T110"/>
+          <cell r="U110"/>
+          <cell r="V110"/>
+          <cell r="W110"/>
+          <cell r="X110"/>
+        </row>
+        <row r="111">
+          <cell r="D111"/>
+          <cell r="E111"/>
+          <cell r="F111"/>
+          <cell r="G111"/>
+          <cell r="H111"/>
+          <cell r="I111"/>
+          <cell r="J111"/>
+          <cell r="K111"/>
+          <cell r="L111"/>
+          <cell r="M111"/>
+          <cell r="N111"/>
+          <cell r="O111"/>
+          <cell r="P111"/>
+          <cell r="Q111"/>
+          <cell r="R111"/>
+          <cell r="S111"/>
+          <cell r="T111"/>
+          <cell r="U111"/>
+          <cell r="V111"/>
+          <cell r="W111"/>
+          <cell r="X111"/>
+        </row>
+        <row r="112">
+          <cell r="D112"/>
+          <cell r="E112"/>
+          <cell r="F112"/>
+          <cell r="G112"/>
+          <cell r="H112"/>
+          <cell r="I112"/>
+          <cell r="J112"/>
+          <cell r="K112"/>
+          <cell r="L112"/>
+          <cell r="M112"/>
+          <cell r="N112"/>
+          <cell r="O112"/>
+          <cell r="P112"/>
+          <cell r="Q112"/>
+          <cell r="R112"/>
+          <cell r="S112"/>
+          <cell r="T112"/>
+          <cell r="U112"/>
+          <cell r="V112"/>
+          <cell r="W112"/>
+          <cell r="X112"/>
+        </row>
+        <row r="113">
+          <cell r="D113"/>
+          <cell r="E113"/>
+          <cell r="F113"/>
+          <cell r="G113"/>
+          <cell r="H113"/>
+          <cell r="I113"/>
+          <cell r="J113"/>
+          <cell r="K113"/>
+          <cell r="L113"/>
+          <cell r="M113"/>
+          <cell r="N113"/>
+          <cell r="O113"/>
+          <cell r="P113"/>
+          <cell r="Q113"/>
+          <cell r="R113"/>
+          <cell r="S113"/>
+          <cell r="T113"/>
+          <cell r="U113"/>
+          <cell r="V113"/>
+          <cell r="W113"/>
+          <cell r="X113"/>
+        </row>
+        <row r="114">
+          <cell r="D114"/>
+          <cell r="E114"/>
+          <cell r="F114"/>
+          <cell r="G114"/>
+          <cell r="H114"/>
+          <cell r="I114"/>
+          <cell r="J114"/>
+          <cell r="K114"/>
+          <cell r="L114"/>
+          <cell r="M114"/>
+          <cell r="N114"/>
+          <cell r="O114"/>
+          <cell r="P114"/>
+          <cell r="Q114"/>
+          <cell r="R114"/>
+          <cell r="S114"/>
+          <cell r="T114"/>
+          <cell r="U114"/>
+          <cell r="V114"/>
+          <cell r="W114"/>
+          <cell r="X114"/>
+        </row>
+        <row r="115">
+          <cell r="D115"/>
+          <cell r="E115"/>
+          <cell r="F115"/>
+          <cell r="G115"/>
+          <cell r="H115"/>
+          <cell r="I115"/>
+          <cell r="J115"/>
+          <cell r="K115"/>
+          <cell r="L115"/>
+          <cell r="M115"/>
+          <cell r="N115"/>
+          <cell r="O115"/>
+          <cell r="P115"/>
+          <cell r="Q115"/>
+          <cell r="R115"/>
+          <cell r="S115"/>
+          <cell r="T115"/>
+          <cell r="U115"/>
+          <cell r="V115"/>
+          <cell r="W115"/>
+          <cell r="X115"/>
+        </row>
+        <row r="116">
+          <cell r="D116"/>
+          <cell r="E116"/>
+          <cell r="F116"/>
+          <cell r="G116"/>
+          <cell r="H116"/>
+          <cell r="I116"/>
+          <cell r="J116"/>
+          <cell r="K116"/>
+          <cell r="L116"/>
+          <cell r="M116"/>
+          <cell r="N116"/>
+          <cell r="O116"/>
+          <cell r="P116"/>
+          <cell r="Q116"/>
+          <cell r="R116"/>
+          <cell r="S116"/>
+          <cell r="T116"/>
+          <cell r="U116"/>
+          <cell r="V116"/>
+          <cell r="W116"/>
+          <cell r="X116"/>
+        </row>
+        <row r="117">
+          <cell r="D117"/>
+          <cell r="E117"/>
+          <cell r="F117"/>
+          <cell r="G117"/>
+          <cell r="H117"/>
+          <cell r="I117"/>
+          <cell r="J117"/>
+          <cell r="K117"/>
+          <cell r="L117"/>
+          <cell r="M117"/>
+          <cell r="N117"/>
+          <cell r="O117"/>
+          <cell r="P117"/>
+          <cell r="Q117"/>
+          <cell r="R117"/>
+          <cell r="S117"/>
+          <cell r="T117"/>
+          <cell r="U117"/>
+          <cell r="V117"/>
+          <cell r="W117"/>
+          <cell r="X117"/>
+        </row>
+        <row r="118">
+          <cell r="D118"/>
+          <cell r="E118"/>
+          <cell r="F118"/>
+          <cell r="G118"/>
+          <cell r="H118"/>
+          <cell r="I118"/>
+          <cell r="J118"/>
+          <cell r="K118"/>
+          <cell r="L118"/>
+          <cell r="M118"/>
+          <cell r="N118"/>
+          <cell r="O118"/>
+          <cell r="P118"/>
+          <cell r="Q118"/>
+          <cell r="R118"/>
+          <cell r="S118"/>
+          <cell r="T118"/>
+          <cell r="U118"/>
+          <cell r="V118"/>
+          <cell r="W118"/>
+          <cell r="X118"/>
+        </row>
+        <row r="119">
+          <cell r="D119"/>
+          <cell r="E119"/>
+          <cell r="F119"/>
+          <cell r="G119"/>
+          <cell r="H119"/>
+          <cell r="I119"/>
+          <cell r="J119"/>
+          <cell r="K119"/>
+          <cell r="L119"/>
+          <cell r="M119"/>
+          <cell r="N119"/>
+          <cell r="O119"/>
+          <cell r="P119"/>
+          <cell r="Q119"/>
+          <cell r="R119"/>
+          <cell r="S119"/>
+          <cell r="T119"/>
+          <cell r="U119"/>
+          <cell r="V119"/>
+          <cell r="W119"/>
+          <cell r="X119"/>
+        </row>
+        <row r="120">
+          <cell r="D120"/>
+          <cell r="E120"/>
+          <cell r="F120"/>
+          <cell r="G120"/>
+          <cell r="H120"/>
+          <cell r="I120"/>
+          <cell r="J120"/>
+          <cell r="K120"/>
+          <cell r="L120"/>
+          <cell r="M120"/>
+          <cell r="N120"/>
+          <cell r="O120"/>
+          <cell r="P120"/>
+          <cell r="Q120"/>
+          <cell r="R120"/>
+          <cell r="S120"/>
+          <cell r="T120"/>
+          <cell r="U120"/>
+          <cell r="V120"/>
+          <cell r="W120"/>
+          <cell r="X120"/>
+        </row>
+        <row r="121">
+          <cell r="D121"/>
+          <cell r="E121"/>
+          <cell r="F121"/>
+          <cell r="G121"/>
+          <cell r="H121"/>
+          <cell r="I121"/>
+          <cell r="J121"/>
+          <cell r="K121"/>
+          <cell r="L121"/>
+          <cell r="M121"/>
+          <cell r="N121"/>
+          <cell r="O121"/>
+          <cell r="P121"/>
+          <cell r="Q121"/>
+          <cell r="R121"/>
+          <cell r="S121"/>
+          <cell r="T121"/>
+          <cell r="U121"/>
+          <cell r="V121"/>
+          <cell r="W121"/>
+          <cell r="X121"/>
+        </row>
+        <row r="122">
+          <cell r="D122"/>
+          <cell r="E122"/>
+          <cell r="F122"/>
+          <cell r="G122"/>
+          <cell r="H122"/>
+          <cell r="I122"/>
+          <cell r="J122"/>
+          <cell r="K122"/>
+          <cell r="L122"/>
+          <cell r="M122"/>
+          <cell r="N122"/>
+          <cell r="O122"/>
+          <cell r="P122"/>
+          <cell r="Q122"/>
+          <cell r="R122"/>
+          <cell r="S122"/>
+          <cell r="T122"/>
+          <cell r="U122"/>
+          <cell r="V122"/>
+          <cell r="W122"/>
+          <cell r="X122"/>
+        </row>
+        <row r="123">
+          <cell r="D123"/>
+          <cell r="E123"/>
+          <cell r="F123"/>
+          <cell r="G123"/>
+          <cell r="H123"/>
+          <cell r="I123"/>
+          <cell r="J123"/>
+          <cell r="K123"/>
+          <cell r="L123"/>
+          <cell r="M123"/>
+          <cell r="N123"/>
+          <cell r="O123"/>
+          <cell r="P123"/>
+          <cell r="Q123"/>
+          <cell r="R123"/>
+          <cell r="S123"/>
+          <cell r="T123"/>
+          <cell r="U123"/>
+          <cell r="V123"/>
+          <cell r="W123"/>
+          <cell r="X123"/>
+        </row>
+        <row r="124">
+          <cell r="D124"/>
+          <cell r="E124"/>
+          <cell r="F124"/>
+          <cell r="G124"/>
+          <cell r="H124"/>
+          <cell r="I124"/>
+          <cell r="J124"/>
+          <cell r="K124"/>
+          <cell r="L124"/>
+          <cell r="M124"/>
+          <cell r="N124"/>
+          <cell r="O124"/>
+          <cell r="P124"/>
+          <cell r="Q124"/>
+          <cell r="R124"/>
+          <cell r="S124"/>
+          <cell r="T124"/>
+          <cell r="U124"/>
+          <cell r="V124"/>
+          <cell r="W124"/>
+          <cell r="X124"/>
+        </row>
+        <row r="125">
+          <cell r="D125"/>
+          <cell r="E125"/>
+          <cell r="F125"/>
+          <cell r="G125"/>
+          <cell r="H125"/>
+          <cell r="I125"/>
+          <cell r="J125"/>
+          <cell r="K125"/>
+          <cell r="L125"/>
+          <cell r="M125"/>
+          <cell r="N125"/>
+          <cell r="O125"/>
+          <cell r="P125"/>
+          <cell r="Q125"/>
+          <cell r="R125"/>
+          <cell r="S125"/>
+          <cell r="T125"/>
+          <cell r="U125"/>
+          <cell r="V125"/>
+          <cell r="W125"/>
+          <cell r="X125"/>
+        </row>
+        <row r="126">
+          <cell r="D126"/>
+          <cell r="E126"/>
+          <cell r="F126"/>
+          <cell r="G126"/>
+          <cell r="H126"/>
+          <cell r="I126"/>
+          <cell r="J126"/>
+          <cell r="K126"/>
+          <cell r="L126"/>
+          <cell r="M126"/>
+          <cell r="N126"/>
+          <cell r="O126"/>
+          <cell r="P126"/>
+          <cell r="Q126"/>
+          <cell r="R126"/>
+          <cell r="S126"/>
+          <cell r="T126"/>
+          <cell r="U126"/>
+          <cell r="V126"/>
+          <cell r="W126"/>
+          <cell r="X126"/>
+        </row>
+        <row r="127">
+          <cell r="D127"/>
+          <cell r="E127"/>
+          <cell r="F127"/>
+          <cell r="G127"/>
+          <cell r="H127"/>
+          <cell r="I127"/>
+          <cell r="J127"/>
+          <cell r="K127"/>
+          <cell r="L127"/>
+          <cell r="M127"/>
+          <cell r="N127"/>
+          <cell r="O127"/>
+          <cell r="P127"/>
+          <cell r="Q127"/>
+          <cell r="R127"/>
+          <cell r="S127"/>
+          <cell r="T127"/>
+          <cell r="U127"/>
+          <cell r="V127"/>
+          <cell r="W127"/>
+          <cell r="X127"/>
+        </row>
+        <row r="128">
+          <cell r="D128"/>
+          <cell r="E128"/>
+          <cell r="F128"/>
+          <cell r="G128"/>
+          <cell r="H128"/>
+          <cell r="I128"/>
+          <cell r="J128"/>
+          <cell r="K128"/>
+          <cell r="L128"/>
+          <cell r="M128"/>
+          <cell r="N128"/>
+          <cell r="O128"/>
+          <cell r="P128"/>
+          <cell r="Q128"/>
+          <cell r="R128"/>
+          <cell r="S128"/>
+          <cell r="T128"/>
+          <cell r="U128"/>
+          <cell r="V128"/>
+          <cell r="W128"/>
+          <cell r="X128"/>
+        </row>
+        <row r="129">
+          <cell r="D129"/>
+          <cell r="E129"/>
+          <cell r="F129"/>
+          <cell r="G129"/>
+          <cell r="H129"/>
+          <cell r="I129"/>
+          <cell r="J129"/>
+          <cell r="K129"/>
+          <cell r="L129"/>
+          <cell r="M129"/>
+          <cell r="N129"/>
+          <cell r="O129"/>
+          <cell r="P129"/>
+          <cell r="Q129"/>
+          <cell r="R129"/>
+          <cell r="S129"/>
+          <cell r="T129"/>
+          <cell r="U129"/>
+          <cell r="V129"/>
+          <cell r="W129"/>
+          <cell r="X129"/>
+        </row>
+        <row r="130">
+          <cell r="D130"/>
+          <cell r="E130"/>
+          <cell r="F130"/>
+          <cell r="G130"/>
+          <cell r="H130"/>
+          <cell r="I130"/>
+          <cell r="J130"/>
+          <cell r="K130"/>
+          <cell r="L130"/>
+          <cell r="M130"/>
+          <cell r="N130"/>
+          <cell r="O130"/>
+          <cell r="P130"/>
+          <cell r="Q130"/>
+          <cell r="R130"/>
+          <cell r="S130"/>
+          <cell r="T130"/>
+          <cell r="U130"/>
+          <cell r="V130"/>
+          <cell r="W130"/>
+          <cell r="X130"/>
+        </row>
+        <row r="131">
+          <cell r="D131"/>
+          <cell r="E131"/>
+          <cell r="F131"/>
+          <cell r="G131"/>
+          <cell r="H131"/>
+          <cell r="I131"/>
+          <cell r="J131"/>
+          <cell r="K131"/>
+          <cell r="L131"/>
+          <cell r="M131"/>
+          <cell r="N131"/>
+          <cell r="O131"/>
+          <cell r="P131"/>
+          <cell r="Q131"/>
+          <cell r="R131"/>
+          <cell r="S131"/>
+          <cell r="T131"/>
+          <cell r="U131"/>
+          <cell r="V131"/>
+          <cell r="W131"/>
+          <cell r="X131"/>
+        </row>
+        <row r="132">
+          <cell r="D132"/>
+          <cell r="E132"/>
+          <cell r="F132"/>
+          <cell r="G132"/>
+          <cell r="H132"/>
+          <cell r="I132"/>
+          <cell r="J132"/>
+          <cell r="K132"/>
+          <cell r="L132"/>
+          <cell r="M132"/>
+          <cell r="N132"/>
+          <cell r="O132"/>
+          <cell r="P132"/>
+          <cell r="Q132"/>
+          <cell r="R132"/>
+          <cell r="S132"/>
+          <cell r="T132"/>
+          <cell r="U132"/>
+          <cell r="V132"/>
+          <cell r="W132"/>
+          <cell r="X132"/>
+        </row>
+        <row r="133">
+          <cell r="D133"/>
+          <cell r="E133"/>
+          <cell r="F133"/>
+          <cell r="G133"/>
+          <cell r="H133"/>
+          <cell r="I133"/>
+          <cell r="J133"/>
+          <cell r="K133"/>
+          <cell r="L133"/>
+          <cell r="M133"/>
+          <cell r="N133"/>
+          <cell r="O133"/>
+          <cell r="P133"/>
+          <cell r="Q133"/>
+          <cell r="R133"/>
+          <cell r="S133"/>
+          <cell r="T133"/>
+          <cell r="U133"/>
+          <cell r="V133"/>
+          <cell r="W133"/>
+          <cell r="X133"/>
+        </row>
+        <row r="134">
+          <cell r="D134"/>
+          <cell r="E134"/>
+          <cell r="F134"/>
+          <cell r="G134"/>
+          <cell r="H134"/>
+          <cell r="I134"/>
+          <cell r="J134"/>
+          <cell r="K134"/>
+          <cell r="L134"/>
+          <cell r="M134"/>
+          <cell r="N134"/>
+          <cell r="O134"/>
+          <cell r="P134"/>
+          <cell r="Q134"/>
+          <cell r="R134"/>
+          <cell r="S134"/>
+          <cell r="T134"/>
+          <cell r="U134"/>
+          <cell r="V134"/>
+          <cell r="W134"/>
+          <cell r="X134"/>
+        </row>
+        <row r="135">
+          <cell r="D135"/>
+          <cell r="E135"/>
+          <cell r="F135"/>
+          <cell r="G135"/>
+          <cell r="H135"/>
+          <cell r="I135"/>
+          <cell r="J135"/>
+          <cell r="K135"/>
+          <cell r="L135"/>
+          <cell r="M135"/>
+          <cell r="N135"/>
+          <cell r="O135"/>
+          <cell r="P135"/>
+          <cell r="Q135"/>
+          <cell r="R135"/>
+          <cell r="S135"/>
+          <cell r="T135"/>
+          <cell r="U135"/>
+          <cell r="V135"/>
+          <cell r="W135"/>
+          <cell r="X135"/>
+        </row>
+        <row r="136">
+          <cell r="D136"/>
+          <cell r="E136"/>
+          <cell r="F136"/>
+          <cell r="G136"/>
+          <cell r="H136"/>
+          <cell r="I136"/>
+          <cell r="J136"/>
+          <cell r="K136"/>
+          <cell r="L136"/>
+          <cell r="M136"/>
+          <cell r="N136"/>
+          <cell r="O136"/>
+          <cell r="P136"/>
+          <cell r="Q136"/>
+          <cell r="R136"/>
+          <cell r="S136"/>
+          <cell r="T136"/>
+          <cell r="U136"/>
+          <cell r="V136"/>
+          <cell r="W136"/>
+          <cell r="X136"/>
+        </row>
+        <row r="137">
+          <cell r="D137"/>
+          <cell r="E137"/>
+          <cell r="F137"/>
+          <cell r="G137"/>
+          <cell r="H137"/>
+          <cell r="I137"/>
+          <cell r="J137"/>
+          <cell r="K137"/>
+          <cell r="L137"/>
+          <cell r="M137"/>
+          <cell r="N137"/>
+          <cell r="O137"/>
+          <cell r="P137"/>
+          <cell r="Q137"/>
+          <cell r="R137"/>
+          <cell r="S137"/>
+          <cell r="T137"/>
+          <cell r="U137"/>
+          <cell r="V137"/>
+          <cell r="W137"/>
+          <cell r="X137"/>
+        </row>
+        <row r="138">
+          <cell r="D138"/>
+          <cell r="E138"/>
+          <cell r="F138"/>
+          <cell r="G138"/>
+          <cell r="H138"/>
+          <cell r="I138"/>
+          <cell r="J138"/>
+          <cell r="K138"/>
+          <cell r="L138"/>
+          <cell r="M138"/>
+          <cell r="N138"/>
+          <cell r="O138"/>
+          <cell r="P138"/>
+          <cell r="Q138"/>
+          <cell r="R138"/>
+          <cell r="S138"/>
+          <cell r="T138"/>
+          <cell r="U138"/>
+          <cell r="V138"/>
+          <cell r="W138"/>
+          <cell r="X138"/>
+        </row>
+        <row r="139">
+          <cell r="D139"/>
+          <cell r="E139"/>
+          <cell r="F139"/>
+          <cell r="G139"/>
+          <cell r="H139"/>
+          <cell r="I139"/>
+          <cell r="J139"/>
+          <cell r="K139"/>
+          <cell r="L139"/>
+          <cell r="M139"/>
+          <cell r="N139"/>
+          <cell r="O139"/>
+          <cell r="P139"/>
+          <cell r="Q139"/>
+          <cell r="R139"/>
+          <cell r="S139"/>
+          <cell r="T139"/>
+          <cell r="U139"/>
+          <cell r="V139"/>
+          <cell r="W139"/>
+          <cell r="X139"/>
+        </row>
+        <row r="140">
+          <cell r="D140"/>
+          <cell r="E140"/>
+          <cell r="F140"/>
+          <cell r="G140"/>
+          <cell r="H140"/>
+          <cell r="I140"/>
+          <cell r="J140"/>
+          <cell r="K140"/>
+          <cell r="L140"/>
+          <cell r="M140"/>
+          <cell r="N140"/>
+          <cell r="O140"/>
+          <cell r="P140"/>
+          <cell r="Q140"/>
+          <cell r="R140"/>
+          <cell r="S140"/>
+          <cell r="T140"/>
+          <cell r="U140"/>
+          <cell r="V140"/>
+          <cell r="W140"/>
+          <cell r="X140"/>
+        </row>
+        <row r="141">
+          <cell r="D141"/>
+          <cell r="E141"/>
+          <cell r="F141"/>
+          <cell r="G141"/>
+          <cell r="H141"/>
+          <cell r="I141"/>
+          <cell r="J141"/>
+          <cell r="K141"/>
+          <cell r="L141"/>
+          <cell r="M141"/>
+          <cell r="N141"/>
+          <cell r="O141"/>
+          <cell r="P141"/>
+          <cell r="Q141"/>
+          <cell r="R141"/>
+          <cell r="S141"/>
+          <cell r="T141"/>
+          <cell r="U141"/>
+          <cell r="V141"/>
+          <cell r="W141"/>
+          <cell r="X141"/>
+        </row>
+        <row r="142">
+          <cell r="D142"/>
+          <cell r="E142"/>
+          <cell r="F142"/>
+          <cell r="G142"/>
+          <cell r="H142"/>
+          <cell r="I142"/>
+          <cell r="J142"/>
+          <cell r="K142"/>
+          <cell r="L142"/>
+          <cell r="M142"/>
+          <cell r="N142"/>
+          <cell r="O142"/>
+          <cell r="P142"/>
+          <cell r="Q142"/>
+          <cell r="R142"/>
+          <cell r="S142"/>
+          <cell r="T142"/>
+          <cell r="U142"/>
+          <cell r="V142"/>
+          <cell r="W142"/>
+          <cell r="X142"/>
+        </row>
+        <row r="143">
+          <cell r="D143"/>
+          <cell r="E143"/>
+          <cell r="F143"/>
+          <cell r="G143"/>
+          <cell r="H143"/>
+          <cell r="I143"/>
+          <cell r="J143"/>
+          <cell r="K143"/>
+          <cell r="L143"/>
+          <cell r="M143"/>
+          <cell r="N143"/>
+          <cell r="O143"/>
+          <cell r="P143"/>
+          <cell r="Q143"/>
+          <cell r="R143"/>
+          <cell r="S143"/>
+          <cell r="T143"/>
+          <cell r="U143"/>
+          <cell r="V143"/>
+          <cell r="W143"/>
+          <cell r="X143"/>
+        </row>
+        <row r="144">
+          <cell r="D144"/>
+          <cell r="E144"/>
+          <cell r="F144"/>
+          <cell r="G144"/>
+          <cell r="H144"/>
+          <cell r="I144"/>
+          <cell r="J144"/>
+          <cell r="K144"/>
+          <cell r="L144"/>
+          <cell r="M144"/>
+          <cell r="N144"/>
+          <cell r="O144"/>
+          <cell r="P144"/>
+          <cell r="Q144"/>
+          <cell r="R144"/>
+          <cell r="S144"/>
+          <cell r="T144"/>
+          <cell r="U144"/>
+          <cell r="V144"/>
+          <cell r="W144"/>
+          <cell r="X144"/>
+        </row>
+        <row r="145">
+          <cell r="D145"/>
+          <cell r="E145"/>
+          <cell r="F145"/>
+          <cell r="G145"/>
+          <cell r="H145"/>
+          <cell r="I145"/>
+          <cell r="J145"/>
+          <cell r="K145"/>
+          <cell r="L145"/>
+          <cell r="M145"/>
+          <cell r="N145"/>
+          <cell r="O145"/>
+          <cell r="P145"/>
+          <cell r="Q145"/>
+          <cell r="R145"/>
+          <cell r="S145"/>
+          <cell r="T145"/>
+          <cell r="U145"/>
+          <cell r="V145"/>
+          <cell r="W145"/>
+          <cell r="X145"/>
+        </row>
+        <row r="146">
+          <cell r="D146"/>
+          <cell r="E146"/>
+          <cell r="F146"/>
+          <cell r="G146"/>
+          <cell r="H146"/>
+          <cell r="I146"/>
+          <cell r="J146"/>
+          <cell r="K146"/>
+          <cell r="L146"/>
+          <cell r="M146"/>
+          <cell r="N146"/>
+          <cell r="O146"/>
+          <cell r="P146"/>
+          <cell r="Q146"/>
+          <cell r="R146"/>
+          <cell r="S146"/>
+          <cell r="T146"/>
+          <cell r="U146"/>
+          <cell r="V146"/>
+          <cell r="W146"/>
+          <cell r="X146"/>
+        </row>
+        <row r="147">
+          <cell r="D147"/>
+          <cell r="E147"/>
+          <cell r="F147"/>
+          <cell r="G147"/>
+          <cell r="H147"/>
+          <cell r="I147"/>
+          <cell r="J147"/>
+          <cell r="K147"/>
+          <cell r="L147"/>
+          <cell r="M147"/>
+          <cell r="N147"/>
+          <cell r="O147"/>
+          <cell r="P147"/>
+          <cell r="Q147"/>
+          <cell r="R147"/>
+          <cell r="S147"/>
+          <cell r="T147"/>
+          <cell r="U147"/>
+          <cell r="V147"/>
+          <cell r="W147"/>
+          <cell r="X147"/>
+        </row>
+        <row r="148">
+          <cell r="D148"/>
+          <cell r="E148"/>
+          <cell r="F148"/>
+          <cell r="G148"/>
+          <cell r="H148"/>
+          <cell r="I148"/>
+          <cell r="J148"/>
+          <cell r="K148"/>
+          <cell r="L148"/>
+          <cell r="M148"/>
+          <cell r="N148"/>
+          <cell r="O148"/>
+          <cell r="P148"/>
+          <cell r="Q148"/>
+          <cell r="R148"/>
+          <cell r="S148"/>
+          <cell r="T148"/>
+          <cell r="U148"/>
+          <cell r="V148"/>
+          <cell r="W148"/>
+          <cell r="X148"/>
+        </row>
+        <row r="149">
+          <cell r="D149"/>
+          <cell r="E149"/>
+          <cell r="F149"/>
+          <cell r="G149"/>
+          <cell r="H149"/>
+          <cell r="I149"/>
+          <cell r="J149"/>
+          <cell r="K149"/>
+          <cell r="L149"/>
+          <cell r="M149"/>
+          <cell r="N149"/>
+          <cell r="O149"/>
+          <cell r="P149"/>
+          <cell r="Q149"/>
+          <cell r="R149"/>
+          <cell r="S149"/>
+          <cell r="T149"/>
+          <cell r="U149"/>
+          <cell r="V149"/>
+          <cell r="W149"/>
+          <cell r="X149"/>
+        </row>
+        <row r="150">
+          <cell r="D150"/>
+          <cell r="E150"/>
+          <cell r="F150"/>
+          <cell r="G150"/>
+          <cell r="H150"/>
+          <cell r="I150"/>
+          <cell r="J150"/>
+          <cell r="K150"/>
+          <cell r="L150"/>
+          <cell r="M150"/>
+          <cell r="N150"/>
+          <cell r="O150"/>
+          <cell r="P150"/>
+          <cell r="Q150"/>
+          <cell r="R150"/>
+          <cell r="S150"/>
+          <cell r="T150"/>
+          <cell r="U150"/>
+          <cell r="V150"/>
+          <cell r="W150"/>
+          <cell r="X150"/>
+        </row>
+        <row r="151">
+          <cell r="D151"/>
+          <cell r="E151"/>
+          <cell r="F151"/>
+          <cell r="G151"/>
+          <cell r="H151"/>
+          <cell r="I151"/>
+          <cell r="J151"/>
+          <cell r="K151"/>
+          <cell r="L151"/>
+          <cell r="M151"/>
+          <cell r="N151"/>
+          <cell r="O151"/>
+          <cell r="P151"/>
+          <cell r="Q151"/>
+          <cell r="R151"/>
+          <cell r="S151"/>
+          <cell r="T151"/>
+          <cell r="U151"/>
+          <cell r="V151"/>
+          <cell r="W151"/>
+          <cell r="X151"/>
+        </row>
+        <row r="152">
+          <cell r="D152"/>
+          <cell r="E152"/>
+          <cell r="F152"/>
+          <cell r="G152"/>
+          <cell r="H152"/>
+          <cell r="I152"/>
+          <cell r="J152"/>
+          <cell r="K152"/>
+          <cell r="L152"/>
+          <cell r="M152"/>
+          <cell r="N152"/>
+          <cell r="O152"/>
+          <cell r="P152"/>
+          <cell r="Q152"/>
+          <cell r="R152"/>
+          <cell r="S152"/>
+          <cell r="T152"/>
+          <cell r="U152"/>
+          <cell r="V152"/>
+          <cell r="W152"/>
+          <cell r="X152"/>
+        </row>
+        <row r="153">
+          <cell r="D153"/>
+          <cell r="E153"/>
+          <cell r="F153"/>
+          <cell r="G153"/>
+          <cell r="H153"/>
+          <cell r="I153"/>
+          <cell r="J153"/>
+          <cell r="K153"/>
+          <cell r="L153"/>
+          <cell r="M153"/>
+          <cell r="N153"/>
+          <cell r="O153"/>
+          <cell r="P153"/>
+          <cell r="Q153"/>
+          <cell r="R153"/>
+          <cell r="S153"/>
+          <cell r="T153"/>
+          <cell r="U153"/>
+          <cell r="V153"/>
+          <cell r="W153"/>
+          <cell r="X153"/>
+        </row>
+        <row r="154">
+          <cell r="D154"/>
+          <cell r="E154"/>
+          <cell r="F154"/>
+          <cell r="G154"/>
+          <cell r="H154"/>
+          <cell r="I154"/>
+          <cell r="J154"/>
+          <cell r="K154"/>
+          <cell r="L154"/>
+          <cell r="M154"/>
+          <cell r="N154"/>
+          <cell r="O154"/>
+          <cell r="P154"/>
+          <cell r="Q154"/>
+          <cell r="R154"/>
+          <cell r="S154"/>
+          <cell r="T154"/>
+          <cell r="U154"/>
+          <cell r="V154"/>
+          <cell r="W154"/>
+          <cell r="X154"/>
+        </row>
+        <row r="155">
+          <cell r="D155"/>
+          <cell r="E155"/>
+          <cell r="F155"/>
+          <cell r="G155"/>
+          <cell r="H155"/>
+          <cell r="I155"/>
+          <cell r="J155"/>
+          <cell r="K155"/>
+          <cell r="L155"/>
+          <cell r="M155"/>
+          <cell r="N155"/>
+          <cell r="O155"/>
+          <cell r="P155"/>
+          <cell r="Q155"/>
+          <cell r="R155"/>
+          <cell r="S155"/>
+          <cell r="T155"/>
+          <cell r="U155"/>
+          <cell r="V155"/>
+          <cell r="W155"/>
+          <cell r="X155"/>
+        </row>
+        <row r="156">
+          <cell r="D156"/>
+          <cell r="E156"/>
+          <cell r="F156"/>
+          <cell r="G156"/>
+          <cell r="H156"/>
+          <cell r="I156"/>
+          <cell r="J156"/>
+          <cell r="K156"/>
+          <cell r="L156"/>
+          <cell r="M156"/>
+          <cell r="N156"/>
+          <cell r="O156"/>
+          <cell r="P156"/>
+          <cell r="Q156"/>
+          <cell r="R156"/>
+          <cell r="S156"/>
+          <cell r="T156"/>
+          <cell r="U156"/>
+          <cell r="V156"/>
+          <cell r="W156"/>
+          <cell r="X156"/>
+        </row>
+        <row r="157">
+          <cell r="D157"/>
+          <cell r="E157"/>
+          <cell r="F157"/>
+          <cell r="G157"/>
+          <cell r="H157"/>
+          <cell r="I157"/>
+          <cell r="J157"/>
+          <cell r="K157"/>
+          <cell r="L157"/>
+          <cell r="M157"/>
+          <cell r="N157"/>
+          <cell r="O157"/>
+          <cell r="P157"/>
+          <cell r="Q157"/>
+          <cell r="R157"/>
+          <cell r="S157"/>
+          <cell r="T157"/>
+          <cell r="U157"/>
+          <cell r="V157"/>
+          <cell r="W157"/>
+          <cell r="X157"/>
+        </row>
+        <row r="158">
+          <cell r="D158"/>
+          <cell r="E158"/>
+          <cell r="F158"/>
+          <cell r="G158"/>
+          <cell r="H158"/>
+          <cell r="I158"/>
+          <cell r="J158"/>
+          <cell r="K158"/>
+          <cell r="L158"/>
+          <cell r="M158"/>
+          <cell r="N158"/>
+          <cell r="O158"/>
+          <cell r="P158"/>
+          <cell r="Q158"/>
+          <cell r="R158"/>
+          <cell r="S158"/>
+          <cell r="T158"/>
+          <cell r="U158"/>
+          <cell r="V158"/>
+          <cell r="W158"/>
+          <cell r="X158"/>
+        </row>
+        <row r="159">
+          <cell r="D159"/>
+          <cell r="E159"/>
+          <cell r="F159"/>
+          <cell r="G159"/>
+          <cell r="H159"/>
+          <cell r="I159"/>
+          <cell r="J159"/>
+          <cell r="K159"/>
+          <cell r="L159"/>
+          <cell r="M159"/>
+          <cell r="N159"/>
+          <cell r="O159"/>
+          <cell r="P159"/>
+          <cell r="Q159"/>
+          <cell r="R159"/>
+          <cell r="S159"/>
+          <cell r="T159"/>
+          <cell r="U159"/>
+          <cell r="V159"/>
+          <cell r="W159"/>
+          <cell r="X159"/>
+        </row>
+        <row r="160">
+          <cell r="D160"/>
+          <cell r="E160"/>
+          <cell r="F160"/>
+          <cell r="G160"/>
+          <cell r="H160"/>
+          <cell r="I160"/>
+          <cell r="J160"/>
+          <cell r="K160"/>
+          <cell r="L160"/>
+          <cell r="M160"/>
+          <cell r="N160"/>
+          <cell r="O160"/>
+          <cell r="P160"/>
+          <cell r="Q160"/>
+          <cell r="R160"/>
+          <cell r="S160"/>
+          <cell r="T160"/>
+          <cell r="U160"/>
+          <cell r="V160"/>
+          <cell r="W160"/>
+          <cell r="X160"/>
+        </row>
+        <row r="161">
+          <cell r="D161"/>
+          <cell r="E161"/>
+          <cell r="F161"/>
+          <cell r="G161"/>
+          <cell r="H161"/>
+          <cell r="I161"/>
+          <cell r="J161"/>
+          <cell r="K161"/>
+          <cell r="L161"/>
+          <cell r="M161"/>
+          <cell r="N161"/>
+          <cell r="O161"/>
+          <cell r="P161"/>
+          <cell r="Q161"/>
+          <cell r="R161"/>
+          <cell r="S161"/>
+          <cell r="T161"/>
+          <cell r="U161"/>
+          <cell r="V161"/>
+          <cell r="W161"/>
+          <cell r="X161"/>
+        </row>
+        <row r="162">
+          <cell r="D162"/>
+          <cell r="E162"/>
+          <cell r="F162"/>
+          <cell r="G162"/>
+          <cell r="H162"/>
+          <cell r="I162"/>
+          <cell r="J162"/>
+          <cell r="K162"/>
+          <cell r="L162"/>
+          <cell r="M162"/>
+          <cell r="N162"/>
+          <cell r="O162"/>
+          <cell r="P162"/>
+          <cell r="Q162"/>
+          <cell r="R162"/>
+          <cell r="S162"/>
+          <cell r="T162"/>
+          <cell r="U162"/>
+          <cell r="V162"/>
+          <cell r="W162"/>
+          <cell r="X162"/>
+        </row>
+        <row r="163">
+          <cell r="D163"/>
+          <cell r="E163"/>
+          <cell r="F163"/>
+          <cell r="G163"/>
+          <cell r="H163"/>
+          <cell r="I163"/>
+          <cell r="J163"/>
+          <cell r="K163"/>
+          <cell r="L163"/>
+          <cell r="M163"/>
+          <cell r="N163"/>
+          <cell r="O163"/>
+          <cell r="P163"/>
+          <cell r="Q163"/>
+          <cell r="R163"/>
+          <cell r="S163"/>
+          <cell r="T163"/>
+          <cell r="U163"/>
+          <cell r="V163"/>
+          <cell r="W163"/>
+          <cell r="X163"/>
+        </row>
+        <row r="164">
+          <cell r="D164"/>
+          <cell r="E164"/>
+          <cell r="F164"/>
+          <cell r="G164"/>
+          <cell r="H164"/>
+          <cell r="I164"/>
+          <cell r="J164"/>
+          <cell r="K164"/>
+          <cell r="L164"/>
+          <cell r="M164"/>
+          <cell r="N164"/>
+          <cell r="O164"/>
+          <cell r="P164"/>
+          <cell r="Q164"/>
+          <cell r="R164"/>
+          <cell r="S164"/>
+          <cell r="T164"/>
+          <cell r="U164"/>
+          <cell r="V164"/>
+          <cell r="W164"/>
+          <cell r="X164"/>
+        </row>
+        <row r="165">
+          <cell r="D165"/>
+          <cell r="E165"/>
+          <cell r="F165"/>
+          <cell r="G165"/>
+          <cell r="H165"/>
+          <cell r="I165"/>
+          <cell r="J165"/>
+          <cell r="K165"/>
+          <cell r="L165"/>
+          <cell r="M165"/>
+          <cell r="N165"/>
+          <cell r="O165"/>
+          <cell r="P165"/>
+          <cell r="Q165"/>
+          <cell r="R165"/>
+          <cell r="S165"/>
+          <cell r="T165"/>
+          <cell r="U165"/>
+          <cell r="V165"/>
+          <cell r="W165"/>
+          <cell r="X165"/>
+        </row>
+        <row r="166">
+          <cell r="D166"/>
+          <cell r="E166"/>
+          <cell r="F166"/>
+          <cell r="G166"/>
+          <cell r="H166"/>
+          <cell r="I166"/>
+          <cell r="J166"/>
+          <cell r="K166"/>
+          <cell r="L166"/>
+          <cell r="M166"/>
+          <cell r="N166"/>
+          <cell r="O166"/>
+          <cell r="P166"/>
+          <cell r="Q166"/>
+          <cell r="R166"/>
+          <cell r="S166"/>
+          <cell r="T166"/>
+          <cell r="U166"/>
+          <cell r="V166"/>
+          <cell r="W166"/>
+          <cell r="X166"/>
+        </row>
+        <row r="167">
+          <cell r="D167"/>
+          <cell r="E167"/>
+          <cell r="F167"/>
+          <cell r="G167"/>
+          <cell r="H167"/>
+          <cell r="I167"/>
+          <cell r="J167"/>
+          <cell r="K167"/>
+          <cell r="L167"/>
+          <cell r="M167"/>
+          <cell r="N167"/>
+          <cell r="O167"/>
+          <cell r="P167"/>
+          <cell r="Q167"/>
+          <cell r="R167"/>
+          <cell r="S167"/>
+          <cell r="T167"/>
+          <cell r="U167"/>
+          <cell r="V167"/>
+          <cell r="W167"/>
+          <cell r="X167"/>
+        </row>
+        <row r="168">
+          <cell r="D168"/>
+          <cell r="E168"/>
+          <cell r="F168"/>
+          <cell r="G168"/>
+          <cell r="H168"/>
+          <cell r="I168"/>
+          <cell r="J168"/>
+          <cell r="K168"/>
+          <cell r="L168"/>
+          <cell r="M168"/>
+          <cell r="N168"/>
+          <cell r="O168"/>
+          <cell r="P168"/>
+          <cell r="Q168"/>
+          <cell r="R168"/>
+          <cell r="S168"/>
+          <cell r="T168"/>
+          <cell r="U168"/>
+          <cell r="V168"/>
+          <cell r="W168"/>
+          <cell r="X168"/>
+        </row>
+        <row r="169">
+          <cell r="D169"/>
+          <cell r="E169"/>
+          <cell r="F169"/>
+          <cell r="G169"/>
+          <cell r="H169"/>
+          <cell r="I169"/>
+          <cell r="J169"/>
+          <cell r="K169"/>
+          <cell r="L169"/>
+          <cell r="M169"/>
+          <cell r="N169"/>
+          <cell r="O169"/>
+          <cell r="P169"/>
+          <cell r="Q169"/>
+          <cell r="R169"/>
+          <cell r="S169"/>
+          <cell r="T169"/>
+          <cell r="U169"/>
+          <cell r="V169"/>
+          <cell r="W169"/>
+          <cell r="X169"/>
+        </row>
+        <row r="170">
+          <cell r="D170"/>
+          <cell r="E170"/>
+          <cell r="F170"/>
+          <cell r="G170"/>
+          <cell r="H170"/>
+          <cell r="I170"/>
+          <cell r="J170"/>
+          <cell r="K170"/>
+          <cell r="L170"/>
+          <cell r="M170"/>
+          <cell r="N170"/>
+          <cell r="O170"/>
+          <cell r="P170"/>
+          <cell r="Q170"/>
+          <cell r="R170"/>
+          <cell r="S170"/>
+          <cell r="T170"/>
+          <cell r="U170"/>
+          <cell r="V170"/>
+          <cell r="W170"/>
+          <cell r="X170"/>
+        </row>
+        <row r="171">
+          <cell r="D171"/>
+          <cell r="E171"/>
+          <cell r="F171"/>
+          <cell r="G171"/>
+          <cell r="H171"/>
+          <cell r="I171"/>
+          <cell r="J171"/>
+          <cell r="K171"/>
+          <cell r="L171"/>
+          <cell r="M171"/>
+          <cell r="N171"/>
+          <cell r="O171"/>
+          <cell r="P171"/>
+          <cell r="Q171"/>
+          <cell r="R171"/>
+          <cell r="S171"/>
+          <cell r="T171"/>
+          <cell r="U171"/>
+          <cell r="V171"/>
+          <cell r="W171"/>
+          <cell r="X171"/>
+        </row>
+        <row r="172">
+          <cell r="D172"/>
+          <cell r="E172"/>
+          <cell r="F172"/>
+          <cell r="G172"/>
+          <cell r="H172"/>
+          <cell r="I172"/>
+          <cell r="J172"/>
+          <cell r="K172"/>
+          <cell r="L172"/>
+          <cell r="M172"/>
+          <cell r="N172"/>
+          <cell r="O172"/>
+          <cell r="P172"/>
+          <cell r="Q172"/>
+          <cell r="R172"/>
+          <cell r="S172"/>
+          <cell r="T172"/>
+          <cell r="U172"/>
+          <cell r="V172"/>
+          <cell r="W172"/>
+          <cell r="X172"/>
+        </row>
+        <row r="173">
+          <cell r="D173"/>
+          <cell r="E173"/>
+          <cell r="F173"/>
+          <cell r="G173"/>
+          <cell r="H173"/>
+          <cell r="I173"/>
+          <cell r="J173"/>
+          <cell r="K173"/>
+          <cell r="L173"/>
+          <cell r="M173"/>
+          <cell r="N173"/>
+          <cell r="O173"/>
+          <cell r="P173"/>
+          <cell r="Q173"/>
+          <cell r="R173"/>
+          <cell r="S173"/>
+          <cell r="T173"/>
+          <cell r="U173"/>
+          <cell r="V173"/>
+          <cell r="W173"/>
+          <cell r="X173"/>
+        </row>
+        <row r="174">
+          <cell r="D174"/>
+          <cell r="E174"/>
+          <cell r="F174"/>
+          <cell r="G174"/>
+          <cell r="H174"/>
+          <cell r="I174"/>
+          <cell r="J174"/>
+          <cell r="K174"/>
+          <cell r="L174"/>
+          <cell r="M174"/>
+          <cell r="N174"/>
+          <cell r="O174"/>
+          <cell r="P174"/>
+          <cell r="Q174"/>
+          <cell r="R174"/>
+          <cell r="S174"/>
+          <cell r="T174"/>
+          <cell r="U174"/>
+          <cell r="V174"/>
+          <cell r="W174"/>
+          <cell r="X174"/>
+        </row>
+        <row r="175">
+          <cell r="D175"/>
+          <cell r="E175"/>
+          <cell r="F175"/>
+          <cell r="G175"/>
+          <cell r="H175"/>
+          <cell r="I175"/>
+          <cell r="J175"/>
+          <cell r="K175"/>
+          <cell r="L175"/>
+          <cell r="M175"/>
+          <cell r="N175"/>
+          <cell r="O175"/>
+          <cell r="P175"/>
+          <cell r="Q175"/>
+          <cell r="R175"/>
+          <cell r="S175"/>
+          <cell r="T175"/>
+          <cell r="U175"/>
+          <cell r="V175"/>
+          <cell r="W175"/>
+          <cell r="X175"/>
+        </row>
+        <row r="176">
+          <cell r="D176"/>
+          <cell r="E176"/>
+          <cell r="F176"/>
+          <cell r="G176"/>
+          <cell r="H176"/>
+          <cell r="I176"/>
+          <cell r="J176"/>
+          <cell r="K176"/>
+          <cell r="L176"/>
+          <cell r="M176"/>
+          <cell r="N176"/>
+          <cell r="O176"/>
+          <cell r="P176"/>
+          <cell r="Q176"/>
+          <cell r="R176"/>
+          <cell r="S176"/>
+          <cell r="T176"/>
+          <cell r="U176"/>
+          <cell r="V176"/>
+          <cell r="W176"/>
+          <cell r="X176"/>
+        </row>
+        <row r="177">
+          <cell r="D177"/>
+          <cell r="E177"/>
+          <cell r="F177"/>
+          <cell r="G177"/>
+          <cell r="H177"/>
+          <cell r="I177"/>
+          <cell r="J177"/>
+          <cell r="K177"/>
+          <cell r="L177"/>
+          <cell r="M177"/>
+          <cell r="N177"/>
+          <cell r="O177"/>
+          <cell r="P177"/>
+          <cell r="Q177"/>
+          <cell r="R177"/>
+          <cell r="S177"/>
+          <cell r="T177"/>
+          <cell r="U177"/>
+          <cell r="V177"/>
+          <cell r="W177"/>
+          <cell r="X177"/>
+        </row>
+        <row r="178">
+          <cell r="D178"/>
+          <cell r="E178"/>
+          <cell r="F178"/>
+          <cell r="G178"/>
+          <cell r="H178"/>
+          <cell r="I178"/>
+          <cell r="J178"/>
+          <cell r="K178"/>
+          <cell r="L178"/>
+          <cell r="M178"/>
+          <cell r="N178"/>
+          <cell r="O178"/>
+          <cell r="P178"/>
+          <cell r="Q178"/>
+          <cell r="R178"/>
+          <cell r="S178"/>
+          <cell r="T178"/>
+          <cell r="U178"/>
+          <cell r="V178"/>
+          <cell r="W178"/>
+          <cell r="X178"/>
+        </row>
+        <row r="179">
+          <cell r="D179"/>
+          <cell r="E179"/>
+          <cell r="F179"/>
+          <cell r="G179"/>
+          <cell r="H179"/>
+          <cell r="I179"/>
+          <cell r="J179"/>
+          <cell r="K179"/>
+          <cell r="L179"/>
+          <cell r="M179"/>
+          <cell r="N179"/>
+          <cell r="O179"/>
+          <cell r="P179"/>
+          <cell r="Q179"/>
+          <cell r="R179"/>
+          <cell r="S179"/>
+          <cell r="T179"/>
+          <cell r="U179"/>
+          <cell r="V179"/>
+          <cell r="W179"/>
+          <cell r="X179"/>
+        </row>
+        <row r="180">
+          <cell r="D180"/>
+          <cell r="E180"/>
+          <cell r="F180"/>
+          <cell r="G180"/>
+          <cell r="H180"/>
+          <cell r="I180"/>
+          <cell r="J180"/>
+          <cell r="K180"/>
+          <cell r="L180"/>
+          <cell r="M180"/>
+          <cell r="N180"/>
+          <cell r="O180"/>
+          <cell r="P180"/>
+          <cell r="Q180"/>
+          <cell r="R180"/>
+          <cell r="S180"/>
+          <cell r="T180"/>
+          <cell r="U180"/>
+          <cell r="V180"/>
+          <cell r="W180"/>
+          <cell r="X180"/>
+        </row>
+        <row r="181">
+          <cell r="D181"/>
+          <cell r="E181"/>
+          <cell r="F181"/>
+          <cell r="G181"/>
+          <cell r="H181"/>
+          <cell r="I181"/>
+          <cell r="J181"/>
+          <cell r="K181"/>
+          <cell r="L181"/>
+          <cell r="M181"/>
+          <cell r="N181"/>
+          <cell r="O181"/>
+          <cell r="P181"/>
+          <cell r="Q181"/>
+          <cell r="R181"/>
+          <cell r="S181"/>
+          <cell r="T181"/>
+          <cell r="U181"/>
+          <cell r="V181"/>
+          <cell r="W181"/>
+          <cell r="X181"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -18747,7 +22519,7 @@
         <v>Arkansas</v>
       </c>
       <c r="D3" s="6" t="str">
-        <f t="shared" ref="D3:D9" si="0">B3</f>
+        <f t="shared" ref="D3" si="0">B3</f>
         <v>Arizona</v>
       </c>
       <c r="E3" s="5">
@@ -18760,7 +22532,7 @@
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.44652162262184503</v>
+        <v>0.44652162262184469</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -18774,7 +22546,7 @@
         <v>443</v>
       </c>
       <c r="K3" s="9">
-        <f t="shared" ref="K3:K9" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
+        <f t="shared" ref="K3" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18796,11 +22568,11 @@
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>6.2329743724806317</v>
+        <v>5.5829743724806304</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -18812,7 +22584,7 @@
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>2.6849415509268226E-2</v>
+        <v>3.0921013343042949E-2</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>443</v>
@@ -18840,15 +22612,15 @@
       </c>
       <c r="E5" s="5">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>9.7678421526914398</v>
+        <v>9.442842152691437</v>
       </c>
       <c r="F5" s="5">
         <f>-VLOOKUP(A5,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.43952016208204359</v>
+        <v>0.43952016208204348</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -18856,7 +22628,7 @@
       </c>
       <c r="I5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>1.5534196411286337E-2</v>
+        <v>1.7594290009775193E-2</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>443</v>
@@ -18884,15 +22656,15 @@
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>11.225624027579791</v>
+        <v>10.90062402757979</v>
       </c>
       <c r="F6" s="5">
         <f>-VLOOKUP(A6,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.57242552718101858</v>
+        <v>0.57242552718101847</v>
       </c>
       <c r="H6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -18900,7 +22672,7 @@
       </c>
       <c r="I6" s="7">
         <f>VLOOKUP(A6,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.5542157428009077E-2</v>
+        <v>3.7442459221713728E-2</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>443</v>
@@ -18972,29 +22744,30 @@
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>3.3825498930097022</v>
+        <v>2.732549893009701</v>
       </c>
       <c r="F8" s="5">
         <f>-VLOOKUP(A8,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.36524831529047619</v>
+        <v>0.36524831529047608</v>
       </c>
       <c r="H8" s="7">
-        <v>4.5400000000000003E-2</v>
+        <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,7,FALSE)</f>
+        <v>4.7694200202852269E-2</v>
       </c>
       <c r="I8" s="7">
         <f>VLOOKUP(A8,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.0145003283635773E-2</v>
+        <v>4.4144431933438776E-2</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>444</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="3"/>
-        <v>0.68100000000000005</v>
+        <v>0.7154130030427841</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -19023,7 +22796,7 @@
       </c>
       <c r="G9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.40552838063197372</v>
+        <v>0.4055283806319735</v>
       </c>
       <c r="H9" s="7">
         <f>VLOOKUP(A9,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -27127,19 +30900,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.77400000000000002</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.54344999999999999</v>
+        <v>0.78559999999999997</v>
       </c>
       <c r="E2">
-        <v>0.35235</v>
+        <v>0.51839999999999997</v>
       </c>
       <c r="F2">
-        <v>0.21299999999999999</v>
+        <v>0.34449999999999997</v>
       </c>
       <c r="G2">
-        <v>0.11915000000000001</v>
+        <v>0.19015000000000001</v>
       </c>
       <c r="H2" t="s">
         <v>384</v>
@@ -27148,7 +30921,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>23.054887624413109</v>
+        <v>23.057528028184478</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -27159,19 +30932,19 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.70679999999999998</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0.46884999999999999</v>
+        <v>0.6411</v>
       </c>
       <c r="E3">
-        <v>0.2888</v>
+        <v>0.42809999999999998</v>
       </c>
       <c r="F3">
-        <v>0.1704</v>
+        <v>0.25369999999999998</v>
       </c>
       <c r="G3">
-        <v>0.10445</v>
+        <v>0.16009999999999999</v>
       </c>
       <c r="H3" t="s">
         <v>383</v>
@@ -27180,7 +30953,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>23.687310951598349</v>
+        <v>23.698276332727119</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -27191,19 +30964,19 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.77080000000000004</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0.48220000000000002</v>
+        <v>0.63749999999999996</v>
       </c>
       <c r="E4">
-        <v>0.29485</v>
+        <v>0.38324999999999998</v>
       </c>
       <c r="F4">
-        <v>0.16830000000000001</v>
+        <v>0.21410000000000001</v>
       </c>
       <c r="G4">
-        <v>9.9250000000000005E-2</v>
+        <v>0.13034999999999999</v>
       </c>
       <c r="H4" t="s">
         <v>382</v>
@@ -27212,940 +30985,940 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>23.158914646956031</v>
+        <v>23.168628302235671</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0.7016</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.44555</v>
+        <v>0.58425000000000005</v>
       </c>
       <c r="E5">
-        <v>0.27579999999999999</v>
+        <v>0.41144999999999998</v>
       </c>
       <c r="F5">
-        <v>0.16025</v>
+        <v>0.20455000000000001</v>
       </c>
       <c r="G5">
-        <v>8.5599999999999996E-2</v>
+        <v>9.1450000000000004E-2</v>
       </c>
       <c r="H5" t="s">
         <v>385</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>22.650454216704581</v>
+        <v>20.908506008479328</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>0.70814999999999995</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0.44405</v>
+        <v>0.74629999999999996</v>
       </c>
       <c r="E6">
-        <v>0.23455000000000001</v>
+        <v>0.32645000000000002</v>
       </c>
       <c r="F6">
-        <v>0.12825</v>
+        <v>0.1535</v>
       </c>
       <c r="G6">
-        <v>6.515E-2</v>
+        <v>7.8149999999999997E-2</v>
       </c>
       <c r="H6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6">
-        <v>20.901069562815731</v>
+        <v>20.95234284206305</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>0.73945000000000005</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0.40915000000000001</v>
+        <v>0.61180000000000001</v>
       </c>
       <c r="E7">
-        <v>0.20449999999999999</v>
+        <v>0.27289999999999998</v>
       </c>
       <c r="F7">
-        <v>0.1053</v>
+        <v>0.15145</v>
       </c>
       <c r="G7">
-        <v>5.5050000000000002E-2</v>
+        <v>6.4949999999999994E-2</v>
       </c>
       <c r="H7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>20.933350618351088</v>
+        <v>19.99120546697802</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.68059999999999998</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0.38345000000000001</v>
+        <v>0.50075000000000003</v>
       </c>
       <c r="E8">
-        <v>0.19395000000000001</v>
+        <v>0.22869999999999999</v>
       </c>
       <c r="F8">
-        <v>0.10015</v>
+        <v>0.10539999999999999</v>
       </c>
       <c r="G8">
-        <v>5.3100000000000001E-2</v>
+        <v>5.355E-2</v>
       </c>
       <c r="H8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>20.95985487362351</v>
+        <v>20.60232878669483</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>0.71745000000000003</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0.37959999999999999</v>
+        <v>0.49925000000000003</v>
       </c>
       <c r="E9">
-        <v>0.18584999999999999</v>
+        <v>0.2228</v>
       </c>
       <c r="F9">
-        <v>9.0999999999999998E-2</v>
+        <v>0.1052</v>
       </c>
       <c r="G9">
-        <v>4.8300000000000003E-2</v>
+        <v>5.2749999999999998E-2</v>
       </c>
       <c r="H9" t="s">
         <v>382</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>20.582457175121959</v>
+        <v>20.65655264831895</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0.76895000000000002</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0.34825</v>
+        <v>0.41575000000000001</v>
       </c>
       <c r="E10">
-        <v>0.17760000000000001</v>
+        <v>0.25890000000000002</v>
       </c>
       <c r="F10">
-        <v>8.7099999999999997E-2</v>
+        <v>0.11070000000000001</v>
       </c>
       <c r="G10">
-        <v>4.2950000000000002E-2</v>
+        <v>4.4499999999999998E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>19.899076876872609</v>
+        <v>18.836157720404749</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.57520000000000004</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0.32435000000000003</v>
+        <v>0.3589</v>
       </c>
       <c r="E11">
-        <v>0.16170000000000001</v>
+        <v>0.1885</v>
       </c>
       <c r="F11">
-        <v>8.0100000000000005E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="G11">
-        <v>4.1000000000000002E-2</v>
+        <v>4.1500000000000002E-2</v>
       </c>
       <c r="H11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>20.64149391157072</v>
+        <v>19.912380875616751</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.59484999999999999</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0.34484999999999999</v>
+        <v>0.36249999999999999</v>
       </c>
       <c r="E12">
-        <v>0.17674999999999999</v>
+        <v>0.16525000000000001</v>
       </c>
       <c r="F12">
-        <v>8.7999999999999995E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="G12">
-        <v>4.095E-2</v>
+        <v>3.295E-2</v>
       </c>
       <c r="H12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>19.982154388171558</v>
+        <v>19.656169100501039</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>386</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13">
-        <v>0.73275000000000001</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0.36275000000000002</v>
+        <v>0.38179999999999997</v>
       </c>
       <c r="E13">
-        <v>0.16664999999999999</v>
+        <v>0.27429999999999999</v>
       </c>
       <c r="F13">
-        <v>7.8600000000000003E-2</v>
+        <v>0.14344999999999999</v>
       </c>
       <c r="G13">
-        <v>3.4799999999999998E-2</v>
+        <v>6.1949999999999998E-2</v>
       </c>
       <c r="H13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>18.826343007871429</v>
+        <v>18.116591097400342</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14">
-        <v>0.59504999999999997</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>0.27705000000000002</v>
+        <v>0.51070000000000004</v>
       </c>
       <c r="E14">
-        <v>0.14660000000000001</v>
+        <v>0.1719</v>
       </c>
       <c r="F14">
-        <v>7.4300000000000005E-2</v>
+        <v>5.2449999999999997E-2</v>
       </c>
       <c r="G14">
-        <v>3.2500000000000001E-2</v>
+        <v>1.465E-2</v>
       </c>
       <c r="H14" t="s">
         <v>385</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>19.33409526621552</v>
+        <v>15.83213015954283</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>0.57769999999999999</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0.26769999999999999</v>
+        <v>0.48930000000000001</v>
       </c>
       <c r="E15">
-        <v>0.1384</v>
+        <v>0.15775</v>
       </c>
       <c r="F15">
-        <v>6.5299999999999997E-2</v>
+        <v>4.7800000000000002E-2</v>
       </c>
       <c r="G15">
-        <v>3.175E-2</v>
+        <v>1.325E-2</v>
       </c>
       <c r="H15" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>19.673613604820769</v>
+        <v>15.53395662020711</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>0.56415000000000004</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0.27405000000000002</v>
+        <v>0.21440000000000001</v>
       </c>
       <c r="E16">
-        <v>0.12705</v>
+        <v>7.6450000000000004E-2</v>
       </c>
       <c r="F16">
-        <v>5.6349999999999997E-2</v>
+        <v>2.8049999999999999E-2</v>
       </c>
       <c r="G16">
-        <v>2.3349999999999999E-2</v>
+        <v>7.0499999999999998E-3</v>
       </c>
       <c r="H16" t="s">
         <v>384</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>18.120431537245491</v>
+        <v>15.127354829706849</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>0.42480000000000001</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0.20985000000000001</v>
+        <v>0.25369999999999998</v>
       </c>
       <c r="E17">
-        <v>9.3200000000000005E-2</v>
+        <v>5.6950000000000001E-2</v>
       </c>
       <c r="F17">
-        <v>4.0250000000000001E-2</v>
+        <v>1.43E-2</v>
       </c>
       <c r="G17">
-        <v>1.7850000000000001E-2</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="H17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J17">
-        <v>18.034523649586539</v>
+        <v>14.540908746576729</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.54944999999999999</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0.2104</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>9.4950000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>3.8850000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>1.52E-2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J18">
-        <v>16.809475334579389</v>
+        <v>10.607575381157361</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.40515000000000001</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.19364999999999999</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>8.1500000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>3.3849999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1.26E-2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I19">
         <v>6</v>
       </c>
       <c r="J19">
-        <v>16.631119331501349</v>
+        <v>16.968495718532171</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.43585000000000002</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0.18745000000000001</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>7.3050000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>2.9950000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>1.1350000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="s">
         <v>384</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J20">
-        <v>15.943406980069801</v>
+        <v>4.7044196436570411</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0.42230000000000001</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0.16925000000000001</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>7.3599999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>2.845E-2</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>1.115E-2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>17.052374181699321</v>
+        <v>11.029310509440901</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.40494999999999998</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0.14765</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>6.3700000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>2.5899999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>9.5999999999999992E-3</v>
+        <v>0</v>
       </c>
       <c r="H22" t="s">
         <v>385</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>15.82631796216417</v>
+        <v>22.660012020194909</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.29320000000000002</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0.13439999999999999</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>5.7450000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>2.3050000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>9.1999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J23">
-        <v>16.287809545840609</v>
+        <v>0.21312405184055919</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.45055000000000001</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0.15359999999999999</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>6.2549999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>2.4649999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>8.3999999999999995E-3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>15.123966744544839</v>
+        <v>14.1383998729836</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.2984</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0.12975</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>5.5750000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2.1149999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>7.9500000000000005E-3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J25">
-        <v>15.51511812576733</v>
+        <v>20.97083468579552</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.31940000000000002</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0.12470000000000001</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>4.1149999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>1.34E-2</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>4.5999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="s">
         <v>383</v>
       </c>
       <c r="I26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J26">
-        <v>14.53205210966642</v>
+        <v>2.6083148574060759</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.22600000000000001</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>9.2549999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>3.1800000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1.0999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>3.3E-3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J27">
-        <v>12.67635641689086</v>
+        <v>9.7941357758882948</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.29185</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0.11945</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>3.875E-2</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>1.115E-2</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>2.8999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28">
-        <v>13.344745551152521</v>
+        <v>2.1310612455384579</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>293</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.22919999999999999</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>8.0850000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>2.7400000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>9.4500000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>2.3999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="H29" t="s">
         <v>382</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J29">
-        <v>12.8910075642879</v>
+        <v>-7.2185591209035449</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.28255000000000002</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>8.6199999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>7.5500000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>2.3500000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J30">
-        <v>12.89893074417701</v>
+        <v>3.942693201935243</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.26055</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>8.2699999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>2.4E-2</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>7.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>1.6000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>12.2388904180045</v>
+        <v>16.816980413993029</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.26724999999999999</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>7.3749999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1.8200000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>4.7499999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>1.2999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I32">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J32">
-        <v>10.280535393881051</v>
+        <v>6.970747918389864</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.23105000000000001</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>4.8500000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>1.255E-2</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>3.2000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I33">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>9.7914064574296606</v>
+        <v>18.061704750271812</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>275</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -28166,18 +31939,18 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I34">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J34">
-        <v>10.62898797126984</v>
+        <v>-5.3135212359347586</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -28198,18 +31971,18 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I35">
         <v>6</v>
       </c>
       <c r="J35">
-        <v>16.95891571245977</v>
+        <v>16.63084451378386</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -28230,18 +32003,18 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J36">
-        <v>4.6851123682196496</v>
+        <v>7.3588143041314016</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -28262,18 +32035,18 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>11.02555602329811</v>
+        <v>12.241609973382021</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -28294,18 +32067,18 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I38">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J38">
-        <v>0.1935829077834591</v>
+        <v>7.7373456911862846</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -28326,18 +32099,18 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>14.114224917334671</v>
+        <v>11.96195079214662</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -28358,18 +32131,18 @@
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I40">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>2.5953665153972891</v>
+        <v>13.97752668447534</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -28390,18 +32163,18 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41">
-        <v>2.1356002741910172</v>
+        <v>3.8798755560939222</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -28422,18 +32195,18 @@
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I42">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J42">
-        <v>-7.2160644315092952</v>
+        <v>9.0872035902891817</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -28454,18 +32227,18 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I43">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J43">
-        <v>3.928312715113337</v>
+        <v>14.73771853734006</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -28486,18 +32259,18 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I44">
         <v>14</v>
       </c>
       <c r="J44">
-        <v>6.9567142213273874</v>
+        <v>-0.36300712066444207</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -28518,18 +32291,18 @@
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I45">
         <v>16</v>
       </c>
       <c r="J45">
-        <v>-5.3079314642110162</v>
+        <v>-11.44814822660846</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -28550,18 +32323,18 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I46">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J46">
-        <v>7.3382243907443794</v>
+        <v>-2.423138952361608</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -28585,15 +32358,15 @@
         <v>382</v>
       </c>
       <c r="I47">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J47">
-        <v>7.7337055835141966</v>
+        <v>12.90381283391684</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -28614,18 +32387,18 @@
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J48">
-        <v>11.938625469494371</v>
+        <v>15.029836879013709</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -28646,18 +32419,18 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J49">
-        <v>13.976487221924669</v>
+        <v>15.748134392962729</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>138</v>
+        <v>316</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -28681,15 +32454,15 @@
         <v>384</v>
       </c>
       <c r="I50">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J50">
-        <v>3.8559349343715992</v>
+        <v>-9.5097540407855199</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -28713,15 +32486,15 @@
         <v>384</v>
       </c>
       <c r="I51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J51">
-        <v>9.044790611595948</v>
+        <v>10.63039633378199</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -28745,15 +32518,15 @@
         <v>384</v>
       </c>
       <c r="I52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J52">
-        <v>14.72942352472889</v>
+        <v>12.689579175374289</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -28774,18 +32547,18 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I53">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J53">
-        <v>-0.34703170207646011</v>
+        <v>1.2683199118622079</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>319</v>
+        <v>37</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -28809,15 +32582,15 @@
         <v>385</v>
       </c>
       <c r="I54">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J54">
-        <v>-11.471425536201769</v>
+        <v>13.356192913880911</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>235</v>
+        <v>11</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -28838,18 +32611,18 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I55">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J55">
-        <v>-2.43869723675573</v>
+        <v>17.0702498636938</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -28873,15 +32646,15 @@
         <v>385</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J56">
-        <v>15.01820898903012</v>
+        <v>1.3275629744540129</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -28902,18 +32675,18 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I57">
         <v>10</v>
       </c>
       <c r="J57">
-        <v>15.7373824689671</v>
+        <v>12.789403074251901</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>316</v>
+        <v>23</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -28937,15 +32710,15 @@
         <v>384</v>
       </c>
       <c r="I58">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J58">
-        <v>-9.4717636747576321</v>
+        <v>15.9543796000304</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -28966,18 +32739,18 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I59">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J59">
-        <v>10.62507679613563</v>
+        <v>16.302758515786241</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -28998,18 +32771,18 @@
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I60">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J60">
-        <v>1.063936136616795</v>
+        <v>10.27897449131121</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>179</v>
+        <v>15</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -29033,15 +32806,15 @@
         <v>385</v>
       </c>
       <c r="I61">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>1.3139417704256631</v>
+        <v>19.34915077848537</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -29062,18 +32835,18 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J62">
-        <v>12.78042205274066</v>
+        <v>11.84309439202905</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -29094,13 +32867,13 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I63">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>11.840993072985089</v>
+        <v>12.899059162147511</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -29132,7 +32905,7 @@
         <v>5</v>
       </c>
       <c r="J64">
-        <v>16.148066436541431</v>
+        <v>16.165764580511631</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
@@ -29164,7 +32937,7 @@
         <v>14</v>
       </c>
       <c r="J65">
-        <v>3.0807597689023769</v>
+        <v>3.093516573216617</v>
       </c>
     </row>
   </sheetData>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47787EA-0E91-5441-8D93-15FECB3664D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0352D0-A2A8-2343-9AD1-C3E281D15A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="20680" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="465">
   <si>
     <t>Team</t>
   </si>
@@ -1656,7 +1656,7 @@
             <v>5.7780905774790781E-2</v>
           </cell>
           <cell r="J3">
-            <v>0.44652162262184469</v>
+            <v>0.44652162262184492</v>
           </cell>
           <cell r="K3">
             <v>0</v>
@@ -1673,19 +1673,19 @@
             <v>Iowa</v>
           </cell>
           <cell r="E4">
-            <v>5.5829743724806304</v>
+            <v>5.257974372480632</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.58859640890923282</v>
+            <v>0.59284650142001671</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.1236840533721718</v>
+            <v>0.1317978663473047</v>
           </cell>
           <cell r="J4">
             <v>0.38710225177014629</v>
@@ -1769,7 +1769,7 @@
             <v>Tennessee</v>
           </cell>
           <cell r="E7">
-            <v>6.1693961042649601</v>
+            <v>6.1693961042649592</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
@@ -1784,7 +1784,7 @@
             <v>5.7495491589876317E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.32440678103529169</v>
+            <v>0.32440678103529158</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1929,22 +1929,22 @@
             <v>Nebraska</v>
           </cell>
           <cell r="E12">
-            <v>0.8061527799804542</v>
+            <v>1.131152779980455</v>
           </cell>
           <cell r="F12" t="b">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0.56961125963652415</v>
+            <v>0.5653103859347075</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>8.7439677487909817E-2</v>
+            <v>7.9228918602623488E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.19277136123939659</v>
+            <v>0.19277136123939681</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -1993,7 +1993,7 @@
             <v>Duke</v>
           </cell>
           <cell r="E14">
-            <v>-5.7074469950208453</v>
+            <v>-5.7074469950208462</v>
           </cell>
           <cell r="F14" t="b">
             <v>0</v>
@@ -2008,7 +2008,7 @@
             <v>-7.7435986809383786E-3</v>
           </cell>
           <cell r="J14">
-            <v>0.1359058509226507</v>
+            <v>0.13590585092265101</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -2025,7 +2025,7 @@
             <v>Iowa State</v>
           </cell>
           <cell r="E15">
-            <v>0.5490944982080217</v>
+            <v>0.54909449820802081</v>
           </cell>
           <cell r="F15" t="b">
             <v>0</v>
@@ -2040,7 +2040,7 @@
             <v>0.16820481729504341</v>
           </cell>
           <cell r="J15">
-            <v>0.28694196100801311</v>
+            <v>0.28694196100801289</v>
           </cell>
           <cell r="K15">
             <v>0</v>
@@ -8904,7 +8904,7 @@
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-2</v>
+            <v>-1.5</v>
           </cell>
         </row>
         <row r="5">
@@ -9496,7 +9496,7 @@
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>2</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="13">
@@ -9868,3778 +9868,6 @@
           <cell r="X17">
             <v>10</v>
           </cell>
-        </row>
-        <row r="18">
-          <cell r="D18"/>
-          <cell r="E18"/>
-          <cell r="F18"/>
-          <cell r="G18"/>
-          <cell r="H18"/>
-          <cell r="I18"/>
-          <cell r="J18"/>
-          <cell r="K18"/>
-          <cell r="L18"/>
-          <cell r="M18"/>
-          <cell r="N18"/>
-          <cell r="O18"/>
-          <cell r="P18"/>
-          <cell r="Q18"/>
-          <cell r="R18"/>
-          <cell r="S18"/>
-          <cell r="T18"/>
-          <cell r="U18"/>
-          <cell r="V18"/>
-          <cell r="W18"/>
-          <cell r="X18"/>
-        </row>
-        <row r="19">
-          <cell r="D19"/>
-          <cell r="E19"/>
-          <cell r="F19"/>
-          <cell r="G19"/>
-          <cell r="H19"/>
-          <cell r="I19"/>
-          <cell r="J19"/>
-          <cell r="K19"/>
-          <cell r="L19"/>
-          <cell r="M19"/>
-          <cell r="N19"/>
-          <cell r="O19"/>
-          <cell r="P19"/>
-          <cell r="Q19"/>
-          <cell r="R19"/>
-          <cell r="S19"/>
-          <cell r="T19"/>
-          <cell r="U19"/>
-          <cell r="V19"/>
-          <cell r="W19"/>
-          <cell r="X19"/>
-        </row>
-        <row r="20">
-          <cell r="D20"/>
-          <cell r="E20"/>
-          <cell r="F20"/>
-          <cell r="G20"/>
-          <cell r="H20"/>
-          <cell r="I20"/>
-          <cell r="J20"/>
-          <cell r="K20"/>
-          <cell r="L20"/>
-          <cell r="M20"/>
-          <cell r="N20"/>
-          <cell r="O20"/>
-          <cell r="P20"/>
-          <cell r="Q20"/>
-          <cell r="R20"/>
-          <cell r="S20"/>
-          <cell r="T20"/>
-          <cell r="U20"/>
-          <cell r="V20"/>
-          <cell r="W20"/>
-          <cell r="X20"/>
-        </row>
-        <row r="21">
-          <cell r="D21"/>
-          <cell r="E21"/>
-          <cell r="F21"/>
-          <cell r="G21"/>
-          <cell r="H21"/>
-          <cell r="I21"/>
-          <cell r="J21"/>
-          <cell r="K21"/>
-          <cell r="L21"/>
-          <cell r="M21"/>
-          <cell r="N21"/>
-          <cell r="O21"/>
-          <cell r="P21"/>
-          <cell r="Q21"/>
-          <cell r="R21"/>
-          <cell r="S21"/>
-          <cell r="T21"/>
-          <cell r="U21"/>
-          <cell r="V21"/>
-          <cell r="W21"/>
-          <cell r="X21"/>
-        </row>
-        <row r="22">
-          <cell r="D22"/>
-          <cell r="E22"/>
-          <cell r="F22"/>
-          <cell r="G22"/>
-          <cell r="H22"/>
-          <cell r="I22"/>
-          <cell r="J22"/>
-          <cell r="K22"/>
-          <cell r="L22"/>
-          <cell r="M22"/>
-          <cell r="N22"/>
-          <cell r="O22"/>
-          <cell r="P22"/>
-          <cell r="Q22"/>
-          <cell r="R22"/>
-          <cell r="S22"/>
-          <cell r="T22"/>
-          <cell r="U22"/>
-          <cell r="V22"/>
-          <cell r="W22"/>
-          <cell r="X22"/>
-        </row>
-        <row r="23">
-          <cell r="D23"/>
-          <cell r="E23"/>
-          <cell r="F23"/>
-          <cell r="G23"/>
-          <cell r="H23"/>
-          <cell r="I23"/>
-          <cell r="J23"/>
-          <cell r="K23"/>
-          <cell r="L23"/>
-          <cell r="M23"/>
-          <cell r="N23"/>
-          <cell r="O23"/>
-          <cell r="P23"/>
-          <cell r="Q23"/>
-          <cell r="R23"/>
-          <cell r="S23"/>
-          <cell r="T23"/>
-          <cell r="U23"/>
-          <cell r="V23"/>
-          <cell r="W23"/>
-          <cell r="X23"/>
-        </row>
-        <row r="24">
-          <cell r="D24"/>
-          <cell r="E24"/>
-          <cell r="F24"/>
-          <cell r="G24"/>
-          <cell r="H24"/>
-          <cell r="I24"/>
-          <cell r="J24"/>
-          <cell r="K24"/>
-          <cell r="L24"/>
-          <cell r="M24"/>
-          <cell r="N24"/>
-          <cell r="O24"/>
-          <cell r="P24"/>
-          <cell r="Q24"/>
-          <cell r="R24"/>
-          <cell r="S24"/>
-          <cell r="T24"/>
-          <cell r="U24"/>
-          <cell r="V24"/>
-          <cell r="W24"/>
-          <cell r="X24"/>
-        </row>
-        <row r="25">
-          <cell r="D25"/>
-          <cell r="E25"/>
-          <cell r="F25"/>
-          <cell r="G25"/>
-          <cell r="H25"/>
-          <cell r="I25"/>
-          <cell r="J25"/>
-          <cell r="K25"/>
-          <cell r="L25"/>
-          <cell r="M25"/>
-          <cell r="N25"/>
-          <cell r="O25"/>
-          <cell r="P25"/>
-          <cell r="Q25"/>
-          <cell r="R25"/>
-          <cell r="S25"/>
-          <cell r="T25"/>
-          <cell r="U25"/>
-          <cell r="V25"/>
-          <cell r="W25"/>
-          <cell r="X25"/>
-        </row>
-        <row r="26">
-          <cell r="D26"/>
-          <cell r="E26"/>
-          <cell r="F26"/>
-          <cell r="G26"/>
-          <cell r="H26"/>
-          <cell r="I26"/>
-          <cell r="J26"/>
-          <cell r="K26"/>
-          <cell r="L26"/>
-          <cell r="M26"/>
-          <cell r="N26"/>
-          <cell r="O26"/>
-          <cell r="P26"/>
-          <cell r="Q26"/>
-          <cell r="R26"/>
-          <cell r="S26"/>
-          <cell r="T26"/>
-          <cell r="U26"/>
-          <cell r="V26"/>
-          <cell r="W26"/>
-          <cell r="X26"/>
-        </row>
-        <row r="27">
-          <cell r="D27"/>
-          <cell r="E27"/>
-          <cell r="F27"/>
-          <cell r="G27"/>
-          <cell r="H27"/>
-          <cell r="I27"/>
-          <cell r="J27"/>
-          <cell r="K27"/>
-          <cell r="L27"/>
-          <cell r="M27"/>
-          <cell r="N27"/>
-          <cell r="O27"/>
-          <cell r="P27"/>
-          <cell r="Q27"/>
-          <cell r="R27"/>
-          <cell r="S27"/>
-          <cell r="T27"/>
-          <cell r="U27"/>
-          <cell r="V27"/>
-          <cell r="W27"/>
-          <cell r="X27"/>
-        </row>
-        <row r="28">
-          <cell r="D28"/>
-          <cell r="E28"/>
-          <cell r="F28"/>
-          <cell r="G28"/>
-          <cell r="H28"/>
-          <cell r="I28"/>
-          <cell r="J28"/>
-          <cell r="K28"/>
-          <cell r="L28"/>
-          <cell r="M28"/>
-          <cell r="N28"/>
-          <cell r="O28"/>
-          <cell r="P28"/>
-          <cell r="Q28"/>
-          <cell r="R28"/>
-          <cell r="S28"/>
-          <cell r="T28"/>
-          <cell r="U28"/>
-          <cell r="V28"/>
-          <cell r="W28"/>
-          <cell r="X28"/>
-        </row>
-        <row r="29">
-          <cell r="D29"/>
-          <cell r="E29"/>
-          <cell r="F29"/>
-          <cell r="G29"/>
-          <cell r="H29"/>
-          <cell r="I29"/>
-          <cell r="J29"/>
-          <cell r="K29"/>
-          <cell r="L29"/>
-          <cell r="M29"/>
-          <cell r="N29"/>
-          <cell r="O29"/>
-          <cell r="P29"/>
-          <cell r="Q29"/>
-          <cell r="R29"/>
-          <cell r="S29"/>
-          <cell r="T29"/>
-          <cell r="U29"/>
-          <cell r="V29"/>
-          <cell r="W29"/>
-          <cell r="X29"/>
-        </row>
-        <row r="30">
-          <cell r="D30"/>
-          <cell r="E30"/>
-          <cell r="F30"/>
-          <cell r="G30"/>
-          <cell r="H30"/>
-          <cell r="I30"/>
-          <cell r="J30"/>
-          <cell r="K30"/>
-          <cell r="L30"/>
-          <cell r="M30"/>
-          <cell r="N30"/>
-          <cell r="O30"/>
-          <cell r="P30"/>
-          <cell r="Q30"/>
-          <cell r="R30"/>
-          <cell r="S30"/>
-          <cell r="T30"/>
-          <cell r="U30"/>
-          <cell r="V30"/>
-          <cell r="W30"/>
-          <cell r="X30"/>
-        </row>
-        <row r="31">
-          <cell r="D31"/>
-          <cell r="E31"/>
-          <cell r="F31"/>
-          <cell r="G31"/>
-          <cell r="H31"/>
-          <cell r="I31"/>
-          <cell r="J31"/>
-          <cell r="K31"/>
-          <cell r="L31"/>
-          <cell r="M31"/>
-          <cell r="N31"/>
-          <cell r="O31"/>
-          <cell r="P31"/>
-          <cell r="Q31"/>
-          <cell r="R31"/>
-          <cell r="S31"/>
-          <cell r="T31"/>
-          <cell r="U31"/>
-          <cell r="V31"/>
-          <cell r="W31"/>
-          <cell r="X31"/>
-        </row>
-        <row r="32">
-          <cell r="D32"/>
-          <cell r="E32"/>
-          <cell r="F32"/>
-          <cell r="G32"/>
-          <cell r="H32"/>
-          <cell r="I32"/>
-          <cell r="J32"/>
-          <cell r="K32"/>
-          <cell r="L32"/>
-          <cell r="M32"/>
-          <cell r="N32"/>
-          <cell r="O32"/>
-          <cell r="P32"/>
-          <cell r="Q32"/>
-          <cell r="R32"/>
-          <cell r="S32"/>
-          <cell r="T32"/>
-          <cell r="U32"/>
-          <cell r="V32"/>
-          <cell r="W32"/>
-          <cell r="X32"/>
-        </row>
-        <row r="33">
-          <cell r="D33"/>
-          <cell r="E33"/>
-          <cell r="F33"/>
-          <cell r="G33"/>
-          <cell r="H33"/>
-          <cell r="I33"/>
-          <cell r="J33"/>
-          <cell r="K33"/>
-          <cell r="L33"/>
-          <cell r="M33"/>
-          <cell r="N33"/>
-          <cell r="O33"/>
-          <cell r="P33"/>
-          <cell r="Q33"/>
-          <cell r="R33"/>
-          <cell r="S33"/>
-          <cell r="T33"/>
-          <cell r="U33"/>
-          <cell r="V33"/>
-          <cell r="W33"/>
-          <cell r="X33"/>
-        </row>
-        <row r="34">
-          <cell r="D34"/>
-          <cell r="E34"/>
-          <cell r="F34"/>
-          <cell r="G34"/>
-          <cell r="H34"/>
-          <cell r="I34"/>
-          <cell r="J34"/>
-          <cell r="K34"/>
-          <cell r="L34"/>
-          <cell r="M34"/>
-          <cell r="N34"/>
-          <cell r="O34"/>
-          <cell r="P34"/>
-          <cell r="Q34"/>
-          <cell r="R34"/>
-          <cell r="S34"/>
-          <cell r="T34"/>
-          <cell r="U34"/>
-          <cell r="V34"/>
-          <cell r="W34"/>
-          <cell r="X34"/>
-        </row>
-        <row r="35">
-          <cell r="D35"/>
-          <cell r="E35"/>
-          <cell r="F35"/>
-          <cell r="G35"/>
-          <cell r="H35"/>
-          <cell r="I35"/>
-          <cell r="J35"/>
-          <cell r="K35"/>
-          <cell r="L35"/>
-          <cell r="M35"/>
-          <cell r="N35"/>
-          <cell r="O35"/>
-          <cell r="P35"/>
-          <cell r="Q35"/>
-          <cell r="R35"/>
-          <cell r="S35"/>
-          <cell r="T35"/>
-          <cell r="U35"/>
-          <cell r="V35"/>
-          <cell r="W35"/>
-          <cell r="X35"/>
-        </row>
-        <row r="36">
-          <cell r="D36"/>
-          <cell r="E36"/>
-          <cell r="F36"/>
-          <cell r="G36"/>
-          <cell r="H36"/>
-          <cell r="I36"/>
-          <cell r="J36"/>
-          <cell r="K36"/>
-          <cell r="L36"/>
-          <cell r="M36"/>
-          <cell r="N36"/>
-          <cell r="O36"/>
-          <cell r="P36"/>
-          <cell r="Q36"/>
-          <cell r="R36"/>
-          <cell r="S36"/>
-          <cell r="T36"/>
-          <cell r="U36"/>
-          <cell r="V36"/>
-          <cell r="W36"/>
-          <cell r="X36"/>
-        </row>
-        <row r="37">
-          <cell r="D37"/>
-          <cell r="E37"/>
-          <cell r="F37"/>
-          <cell r="G37"/>
-          <cell r="H37"/>
-          <cell r="I37"/>
-          <cell r="J37"/>
-          <cell r="K37"/>
-          <cell r="L37"/>
-          <cell r="M37"/>
-          <cell r="N37"/>
-          <cell r="O37"/>
-          <cell r="P37"/>
-          <cell r="Q37"/>
-          <cell r="R37"/>
-          <cell r="S37"/>
-          <cell r="T37"/>
-          <cell r="U37"/>
-          <cell r="V37"/>
-          <cell r="W37"/>
-          <cell r="X37"/>
-        </row>
-        <row r="38">
-          <cell r="D38"/>
-          <cell r="E38"/>
-          <cell r="F38"/>
-          <cell r="G38"/>
-          <cell r="H38"/>
-          <cell r="I38"/>
-          <cell r="J38"/>
-          <cell r="K38"/>
-          <cell r="L38"/>
-          <cell r="M38"/>
-          <cell r="N38"/>
-          <cell r="O38"/>
-          <cell r="P38"/>
-          <cell r="Q38"/>
-          <cell r="R38"/>
-          <cell r="S38"/>
-          <cell r="T38"/>
-          <cell r="U38"/>
-          <cell r="V38"/>
-          <cell r="W38"/>
-          <cell r="X38"/>
-        </row>
-        <row r="39">
-          <cell r="D39"/>
-          <cell r="E39"/>
-          <cell r="F39"/>
-          <cell r="G39"/>
-          <cell r="H39"/>
-          <cell r="I39"/>
-          <cell r="J39"/>
-          <cell r="K39"/>
-          <cell r="L39"/>
-          <cell r="M39"/>
-          <cell r="N39"/>
-          <cell r="O39"/>
-          <cell r="P39"/>
-          <cell r="Q39"/>
-          <cell r="R39"/>
-          <cell r="S39"/>
-          <cell r="T39"/>
-          <cell r="U39"/>
-          <cell r="V39"/>
-          <cell r="W39"/>
-          <cell r="X39"/>
-        </row>
-        <row r="40">
-          <cell r="D40"/>
-          <cell r="E40"/>
-          <cell r="F40"/>
-          <cell r="G40"/>
-          <cell r="H40"/>
-          <cell r="I40"/>
-          <cell r="J40"/>
-          <cell r="K40"/>
-          <cell r="L40"/>
-          <cell r="M40"/>
-          <cell r="N40"/>
-          <cell r="O40"/>
-          <cell r="P40"/>
-          <cell r="Q40"/>
-          <cell r="R40"/>
-          <cell r="S40"/>
-          <cell r="T40"/>
-          <cell r="U40"/>
-          <cell r="V40"/>
-          <cell r="W40"/>
-          <cell r="X40"/>
-        </row>
-        <row r="41">
-          <cell r="D41"/>
-          <cell r="E41"/>
-          <cell r="F41"/>
-          <cell r="G41"/>
-          <cell r="H41"/>
-          <cell r="I41"/>
-          <cell r="J41"/>
-          <cell r="K41"/>
-          <cell r="L41"/>
-          <cell r="M41"/>
-          <cell r="N41"/>
-          <cell r="O41"/>
-          <cell r="P41"/>
-          <cell r="Q41"/>
-          <cell r="R41"/>
-          <cell r="S41"/>
-          <cell r="T41"/>
-          <cell r="U41"/>
-          <cell r="V41"/>
-          <cell r="W41"/>
-          <cell r="X41"/>
-        </row>
-        <row r="42">
-          <cell r="D42"/>
-          <cell r="E42"/>
-          <cell r="F42"/>
-          <cell r="G42"/>
-          <cell r="H42"/>
-          <cell r="I42"/>
-          <cell r="J42"/>
-          <cell r="K42"/>
-          <cell r="L42"/>
-          <cell r="M42"/>
-          <cell r="N42"/>
-          <cell r="O42"/>
-          <cell r="P42"/>
-          <cell r="Q42"/>
-          <cell r="R42"/>
-          <cell r="S42"/>
-          <cell r="T42"/>
-          <cell r="U42"/>
-          <cell r="V42"/>
-          <cell r="W42"/>
-          <cell r="X42"/>
-        </row>
-        <row r="43">
-          <cell r="D43"/>
-          <cell r="E43"/>
-          <cell r="F43"/>
-          <cell r="G43"/>
-          <cell r="H43"/>
-          <cell r="I43"/>
-          <cell r="J43"/>
-          <cell r="K43"/>
-          <cell r="L43"/>
-          <cell r="M43"/>
-          <cell r="N43"/>
-          <cell r="O43"/>
-          <cell r="P43"/>
-          <cell r="Q43"/>
-          <cell r="R43"/>
-          <cell r="S43"/>
-          <cell r="T43"/>
-          <cell r="U43"/>
-          <cell r="V43"/>
-          <cell r="W43"/>
-          <cell r="X43"/>
-        </row>
-        <row r="44">
-          <cell r="D44"/>
-          <cell r="E44"/>
-          <cell r="F44"/>
-          <cell r="G44"/>
-          <cell r="H44"/>
-          <cell r="I44"/>
-          <cell r="J44"/>
-          <cell r="K44"/>
-          <cell r="L44"/>
-          <cell r="M44"/>
-          <cell r="N44"/>
-          <cell r="O44"/>
-          <cell r="P44"/>
-          <cell r="Q44"/>
-          <cell r="R44"/>
-          <cell r="S44"/>
-          <cell r="T44"/>
-          <cell r="U44"/>
-          <cell r="V44"/>
-          <cell r="W44"/>
-          <cell r="X44"/>
-        </row>
-        <row r="45">
-          <cell r="D45"/>
-          <cell r="E45"/>
-          <cell r="F45"/>
-          <cell r="G45"/>
-          <cell r="H45"/>
-          <cell r="I45"/>
-          <cell r="J45"/>
-          <cell r="K45"/>
-          <cell r="L45"/>
-          <cell r="M45"/>
-          <cell r="N45"/>
-          <cell r="O45"/>
-          <cell r="P45"/>
-          <cell r="Q45"/>
-          <cell r="R45"/>
-          <cell r="S45"/>
-          <cell r="T45"/>
-          <cell r="U45"/>
-          <cell r="V45"/>
-          <cell r="W45"/>
-          <cell r="X45"/>
-        </row>
-        <row r="46">
-          <cell r="D46"/>
-          <cell r="E46"/>
-          <cell r="F46"/>
-          <cell r="G46"/>
-          <cell r="H46"/>
-          <cell r="I46"/>
-          <cell r="J46"/>
-          <cell r="K46"/>
-          <cell r="L46"/>
-          <cell r="M46"/>
-          <cell r="N46"/>
-          <cell r="O46"/>
-          <cell r="P46"/>
-          <cell r="Q46"/>
-          <cell r="R46"/>
-          <cell r="S46"/>
-          <cell r="T46"/>
-          <cell r="U46"/>
-          <cell r="V46"/>
-          <cell r="W46"/>
-          <cell r="X46"/>
-        </row>
-        <row r="47">
-          <cell r="D47"/>
-          <cell r="E47"/>
-          <cell r="F47"/>
-          <cell r="G47"/>
-          <cell r="H47"/>
-          <cell r="I47"/>
-          <cell r="J47"/>
-          <cell r="K47"/>
-          <cell r="L47"/>
-          <cell r="M47"/>
-          <cell r="N47"/>
-          <cell r="O47"/>
-          <cell r="P47"/>
-          <cell r="Q47"/>
-          <cell r="R47"/>
-          <cell r="S47"/>
-          <cell r="T47"/>
-          <cell r="U47"/>
-          <cell r="V47"/>
-          <cell r="W47"/>
-          <cell r="X47"/>
-        </row>
-        <row r="48">
-          <cell r="D48"/>
-          <cell r="E48"/>
-          <cell r="F48"/>
-          <cell r="G48"/>
-          <cell r="H48"/>
-          <cell r="I48"/>
-          <cell r="J48"/>
-          <cell r="K48"/>
-          <cell r="L48"/>
-          <cell r="M48"/>
-          <cell r="N48"/>
-          <cell r="O48"/>
-          <cell r="P48"/>
-          <cell r="Q48"/>
-          <cell r="R48"/>
-          <cell r="S48"/>
-          <cell r="T48"/>
-          <cell r="U48"/>
-          <cell r="V48"/>
-          <cell r="W48"/>
-          <cell r="X48"/>
-        </row>
-        <row r="49">
-          <cell r="D49"/>
-          <cell r="E49"/>
-          <cell r="F49"/>
-          <cell r="G49"/>
-          <cell r="H49"/>
-          <cell r="I49"/>
-          <cell r="J49"/>
-          <cell r="K49"/>
-          <cell r="L49"/>
-          <cell r="M49"/>
-          <cell r="N49"/>
-          <cell r="O49"/>
-          <cell r="P49"/>
-          <cell r="Q49"/>
-          <cell r="R49"/>
-          <cell r="S49"/>
-          <cell r="T49"/>
-          <cell r="U49"/>
-          <cell r="V49"/>
-          <cell r="W49"/>
-          <cell r="X49"/>
-        </row>
-        <row r="50">
-          <cell r="D50"/>
-          <cell r="E50"/>
-          <cell r="F50"/>
-          <cell r="G50"/>
-          <cell r="H50"/>
-          <cell r="I50"/>
-          <cell r="J50"/>
-          <cell r="K50"/>
-          <cell r="L50"/>
-          <cell r="M50"/>
-          <cell r="N50"/>
-          <cell r="O50"/>
-          <cell r="P50"/>
-          <cell r="Q50"/>
-          <cell r="R50"/>
-          <cell r="S50"/>
-          <cell r="T50"/>
-          <cell r="U50"/>
-          <cell r="V50"/>
-          <cell r="W50"/>
-          <cell r="X50"/>
-        </row>
-        <row r="51">
-          <cell r="D51"/>
-          <cell r="E51"/>
-          <cell r="F51"/>
-          <cell r="G51"/>
-          <cell r="H51"/>
-          <cell r="I51"/>
-          <cell r="J51"/>
-          <cell r="K51"/>
-          <cell r="L51"/>
-          <cell r="M51"/>
-          <cell r="N51"/>
-          <cell r="O51"/>
-          <cell r="P51"/>
-          <cell r="Q51"/>
-          <cell r="R51"/>
-          <cell r="S51"/>
-          <cell r="T51"/>
-          <cell r="U51"/>
-          <cell r="V51"/>
-          <cell r="W51"/>
-          <cell r="X51"/>
-        </row>
-        <row r="52">
-          <cell r="D52"/>
-          <cell r="E52"/>
-          <cell r="F52"/>
-          <cell r="G52"/>
-          <cell r="H52"/>
-          <cell r="I52"/>
-          <cell r="J52"/>
-          <cell r="K52"/>
-          <cell r="L52"/>
-          <cell r="M52"/>
-          <cell r="N52"/>
-          <cell r="O52"/>
-          <cell r="P52"/>
-          <cell r="Q52"/>
-          <cell r="R52"/>
-          <cell r="S52"/>
-          <cell r="T52"/>
-          <cell r="U52"/>
-          <cell r="V52"/>
-          <cell r="W52"/>
-          <cell r="X52"/>
-        </row>
-        <row r="53">
-          <cell r="D53"/>
-          <cell r="E53"/>
-          <cell r="F53"/>
-          <cell r="G53"/>
-          <cell r="H53"/>
-          <cell r="I53"/>
-          <cell r="J53"/>
-          <cell r="K53"/>
-          <cell r="L53"/>
-          <cell r="M53"/>
-          <cell r="N53"/>
-          <cell r="O53"/>
-          <cell r="P53"/>
-          <cell r="Q53"/>
-          <cell r="R53"/>
-          <cell r="S53"/>
-          <cell r="T53"/>
-          <cell r="U53"/>
-          <cell r="V53"/>
-          <cell r="W53"/>
-          <cell r="X53"/>
-        </row>
-        <row r="54">
-          <cell r="D54"/>
-          <cell r="E54"/>
-          <cell r="F54"/>
-          <cell r="G54"/>
-          <cell r="H54"/>
-          <cell r="I54"/>
-          <cell r="J54"/>
-          <cell r="K54"/>
-          <cell r="L54"/>
-          <cell r="M54"/>
-          <cell r="N54"/>
-          <cell r="O54"/>
-          <cell r="P54"/>
-          <cell r="Q54"/>
-          <cell r="R54"/>
-          <cell r="S54"/>
-          <cell r="T54"/>
-          <cell r="U54"/>
-          <cell r="V54"/>
-          <cell r="W54"/>
-          <cell r="X54"/>
-        </row>
-        <row r="55">
-          <cell r="D55"/>
-          <cell r="E55"/>
-          <cell r="F55"/>
-          <cell r="G55"/>
-          <cell r="H55"/>
-          <cell r="I55"/>
-          <cell r="J55"/>
-          <cell r="K55"/>
-          <cell r="L55"/>
-          <cell r="M55"/>
-          <cell r="N55"/>
-          <cell r="O55"/>
-          <cell r="P55"/>
-          <cell r="Q55"/>
-          <cell r="R55"/>
-          <cell r="S55"/>
-          <cell r="T55"/>
-          <cell r="U55"/>
-          <cell r="V55"/>
-          <cell r="W55"/>
-          <cell r="X55"/>
-        </row>
-        <row r="56">
-          <cell r="D56"/>
-          <cell r="E56"/>
-          <cell r="F56"/>
-          <cell r="G56"/>
-          <cell r="H56"/>
-          <cell r="I56"/>
-          <cell r="J56"/>
-          <cell r="K56"/>
-          <cell r="L56"/>
-          <cell r="M56"/>
-          <cell r="N56"/>
-          <cell r="O56"/>
-          <cell r="P56"/>
-          <cell r="Q56"/>
-          <cell r="R56"/>
-          <cell r="S56"/>
-          <cell r="T56"/>
-          <cell r="U56"/>
-          <cell r="V56"/>
-          <cell r="W56"/>
-          <cell r="X56"/>
-        </row>
-        <row r="57">
-          <cell r="D57"/>
-          <cell r="E57"/>
-          <cell r="F57"/>
-          <cell r="G57"/>
-          <cell r="H57"/>
-          <cell r="I57"/>
-          <cell r="J57"/>
-          <cell r="K57"/>
-          <cell r="L57"/>
-          <cell r="M57"/>
-          <cell r="N57"/>
-          <cell r="O57"/>
-          <cell r="P57"/>
-          <cell r="Q57"/>
-          <cell r="R57"/>
-          <cell r="S57"/>
-          <cell r="T57"/>
-          <cell r="U57"/>
-          <cell r="V57"/>
-          <cell r="W57"/>
-          <cell r="X57"/>
-        </row>
-        <row r="58">
-          <cell r="D58"/>
-          <cell r="E58"/>
-          <cell r="F58"/>
-          <cell r="G58"/>
-          <cell r="H58"/>
-          <cell r="I58"/>
-          <cell r="J58"/>
-          <cell r="K58"/>
-          <cell r="L58"/>
-          <cell r="M58"/>
-          <cell r="N58"/>
-          <cell r="O58"/>
-          <cell r="P58"/>
-          <cell r="Q58"/>
-          <cell r="R58"/>
-          <cell r="S58"/>
-          <cell r="T58"/>
-          <cell r="U58"/>
-          <cell r="V58"/>
-          <cell r="W58"/>
-          <cell r="X58"/>
-        </row>
-        <row r="59">
-          <cell r="D59"/>
-          <cell r="E59"/>
-          <cell r="F59"/>
-          <cell r="G59"/>
-          <cell r="H59"/>
-          <cell r="I59"/>
-          <cell r="J59"/>
-          <cell r="K59"/>
-          <cell r="L59"/>
-          <cell r="M59"/>
-          <cell r="N59"/>
-          <cell r="O59"/>
-          <cell r="P59"/>
-          <cell r="Q59"/>
-          <cell r="R59"/>
-          <cell r="S59"/>
-          <cell r="T59"/>
-          <cell r="U59"/>
-          <cell r="V59"/>
-          <cell r="W59"/>
-          <cell r="X59"/>
-        </row>
-        <row r="60">
-          <cell r="D60"/>
-          <cell r="E60"/>
-          <cell r="F60"/>
-          <cell r="G60"/>
-          <cell r="H60"/>
-          <cell r="I60"/>
-          <cell r="J60"/>
-          <cell r="K60"/>
-          <cell r="L60"/>
-          <cell r="M60"/>
-          <cell r="N60"/>
-          <cell r="O60"/>
-          <cell r="P60"/>
-          <cell r="Q60"/>
-          <cell r="R60"/>
-          <cell r="S60"/>
-          <cell r="T60"/>
-          <cell r="U60"/>
-          <cell r="V60"/>
-          <cell r="W60"/>
-          <cell r="X60"/>
-        </row>
-        <row r="61">
-          <cell r="D61"/>
-          <cell r="E61"/>
-          <cell r="F61"/>
-          <cell r="G61"/>
-          <cell r="H61"/>
-          <cell r="I61"/>
-          <cell r="J61"/>
-          <cell r="K61"/>
-          <cell r="L61"/>
-          <cell r="M61"/>
-          <cell r="N61"/>
-          <cell r="O61"/>
-          <cell r="P61"/>
-          <cell r="Q61"/>
-          <cell r="R61"/>
-          <cell r="S61"/>
-          <cell r="T61"/>
-          <cell r="U61"/>
-          <cell r="V61"/>
-          <cell r="W61"/>
-          <cell r="X61"/>
-        </row>
-        <row r="62">
-          <cell r="D62"/>
-          <cell r="E62"/>
-          <cell r="F62"/>
-          <cell r="G62"/>
-          <cell r="H62"/>
-          <cell r="I62"/>
-          <cell r="J62"/>
-          <cell r="K62"/>
-          <cell r="L62"/>
-          <cell r="M62"/>
-          <cell r="N62"/>
-          <cell r="O62"/>
-          <cell r="P62"/>
-          <cell r="Q62"/>
-          <cell r="R62"/>
-          <cell r="S62"/>
-          <cell r="T62"/>
-          <cell r="U62"/>
-          <cell r="V62"/>
-          <cell r="W62"/>
-          <cell r="X62"/>
-        </row>
-        <row r="63">
-          <cell r="D63"/>
-          <cell r="E63"/>
-          <cell r="F63"/>
-          <cell r="G63"/>
-          <cell r="H63"/>
-          <cell r="I63"/>
-          <cell r="J63"/>
-          <cell r="K63"/>
-          <cell r="L63"/>
-          <cell r="M63"/>
-          <cell r="N63"/>
-          <cell r="O63"/>
-          <cell r="P63"/>
-          <cell r="Q63"/>
-          <cell r="R63"/>
-          <cell r="S63"/>
-          <cell r="T63"/>
-          <cell r="U63"/>
-          <cell r="V63"/>
-          <cell r="W63"/>
-          <cell r="X63"/>
-        </row>
-        <row r="64">
-          <cell r="D64"/>
-          <cell r="E64"/>
-          <cell r="F64"/>
-          <cell r="G64"/>
-          <cell r="H64"/>
-          <cell r="I64"/>
-          <cell r="J64"/>
-          <cell r="K64"/>
-          <cell r="L64"/>
-          <cell r="M64"/>
-          <cell r="N64"/>
-          <cell r="O64"/>
-          <cell r="P64"/>
-          <cell r="Q64"/>
-          <cell r="R64"/>
-          <cell r="S64"/>
-          <cell r="T64"/>
-          <cell r="U64"/>
-          <cell r="V64"/>
-          <cell r="W64"/>
-          <cell r="X64"/>
-        </row>
-        <row r="65">
-          <cell r="D65"/>
-          <cell r="E65"/>
-          <cell r="F65"/>
-          <cell r="G65"/>
-          <cell r="H65"/>
-          <cell r="I65"/>
-          <cell r="J65"/>
-          <cell r="K65"/>
-          <cell r="L65"/>
-          <cell r="M65"/>
-          <cell r="N65"/>
-          <cell r="O65"/>
-          <cell r="P65"/>
-          <cell r="Q65"/>
-          <cell r="R65"/>
-          <cell r="S65"/>
-          <cell r="T65"/>
-          <cell r="U65"/>
-          <cell r="V65"/>
-          <cell r="W65"/>
-          <cell r="X65"/>
-        </row>
-        <row r="66">
-          <cell r="D66"/>
-          <cell r="E66"/>
-          <cell r="F66"/>
-          <cell r="G66"/>
-          <cell r="H66"/>
-          <cell r="I66"/>
-          <cell r="J66"/>
-          <cell r="K66"/>
-          <cell r="L66"/>
-          <cell r="M66"/>
-          <cell r="N66"/>
-          <cell r="O66"/>
-          <cell r="P66"/>
-          <cell r="Q66"/>
-          <cell r="R66"/>
-          <cell r="S66"/>
-          <cell r="T66"/>
-          <cell r="U66"/>
-          <cell r="V66"/>
-          <cell r="W66"/>
-          <cell r="X66"/>
-        </row>
-        <row r="67">
-          <cell r="D67"/>
-          <cell r="E67"/>
-          <cell r="F67"/>
-          <cell r="G67"/>
-          <cell r="H67"/>
-          <cell r="I67"/>
-          <cell r="J67"/>
-          <cell r="K67"/>
-          <cell r="L67"/>
-          <cell r="M67"/>
-          <cell r="N67"/>
-          <cell r="O67"/>
-          <cell r="P67"/>
-          <cell r="Q67"/>
-          <cell r="R67"/>
-          <cell r="S67"/>
-          <cell r="T67"/>
-          <cell r="U67"/>
-          <cell r="V67"/>
-          <cell r="W67"/>
-          <cell r="X67"/>
-        </row>
-        <row r="68">
-          <cell r="D68"/>
-          <cell r="E68"/>
-          <cell r="F68"/>
-          <cell r="G68"/>
-          <cell r="H68"/>
-          <cell r="I68"/>
-          <cell r="J68"/>
-          <cell r="K68"/>
-          <cell r="L68"/>
-          <cell r="M68"/>
-          <cell r="N68"/>
-          <cell r="O68"/>
-          <cell r="P68"/>
-          <cell r="Q68"/>
-          <cell r="R68"/>
-          <cell r="S68"/>
-          <cell r="T68"/>
-          <cell r="U68"/>
-          <cell r="V68"/>
-          <cell r="W68"/>
-          <cell r="X68"/>
-        </row>
-        <row r="69">
-          <cell r="D69"/>
-          <cell r="E69"/>
-          <cell r="F69"/>
-          <cell r="G69"/>
-          <cell r="H69"/>
-          <cell r="I69"/>
-          <cell r="J69"/>
-          <cell r="K69"/>
-          <cell r="L69"/>
-          <cell r="M69"/>
-          <cell r="N69"/>
-          <cell r="O69"/>
-          <cell r="P69"/>
-          <cell r="Q69"/>
-          <cell r="R69"/>
-          <cell r="S69"/>
-          <cell r="T69"/>
-          <cell r="U69"/>
-          <cell r="V69"/>
-          <cell r="W69"/>
-          <cell r="X69"/>
-        </row>
-        <row r="70">
-          <cell r="D70"/>
-          <cell r="E70"/>
-          <cell r="F70"/>
-          <cell r="G70"/>
-          <cell r="H70"/>
-          <cell r="I70"/>
-          <cell r="J70"/>
-          <cell r="K70"/>
-          <cell r="L70"/>
-          <cell r="M70"/>
-          <cell r="N70"/>
-          <cell r="O70"/>
-          <cell r="P70"/>
-          <cell r="Q70"/>
-          <cell r="R70"/>
-          <cell r="S70"/>
-          <cell r="T70"/>
-          <cell r="U70"/>
-          <cell r="V70"/>
-          <cell r="W70"/>
-          <cell r="X70"/>
-        </row>
-        <row r="71">
-          <cell r="D71"/>
-          <cell r="E71"/>
-          <cell r="F71"/>
-          <cell r="G71"/>
-          <cell r="H71"/>
-          <cell r="I71"/>
-          <cell r="J71"/>
-          <cell r="K71"/>
-          <cell r="L71"/>
-          <cell r="M71"/>
-          <cell r="N71"/>
-          <cell r="O71"/>
-          <cell r="P71"/>
-          <cell r="Q71"/>
-          <cell r="R71"/>
-          <cell r="S71"/>
-          <cell r="T71"/>
-          <cell r="U71"/>
-          <cell r="V71"/>
-          <cell r="W71"/>
-          <cell r="X71"/>
-        </row>
-        <row r="72">
-          <cell r="D72"/>
-          <cell r="E72"/>
-          <cell r="F72"/>
-          <cell r="G72"/>
-          <cell r="H72"/>
-          <cell r="I72"/>
-          <cell r="J72"/>
-          <cell r="K72"/>
-          <cell r="L72"/>
-          <cell r="M72"/>
-          <cell r="N72"/>
-          <cell r="O72"/>
-          <cell r="P72"/>
-          <cell r="Q72"/>
-          <cell r="R72"/>
-          <cell r="S72"/>
-          <cell r="T72"/>
-          <cell r="U72"/>
-          <cell r="V72"/>
-          <cell r="W72"/>
-          <cell r="X72"/>
-        </row>
-        <row r="73">
-          <cell r="D73"/>
-          <cell r="E73"/>
-          <cell r="F73"/>
-          <cell r="G73"/>
-          <cell r="H73"/>
-          <cell r="I73"/>
-          <cell r="J73"/>
-          <cell r="K73"/>
-          <cell r="L73"/>
-          <cell r="M73"/>
-          <cell r="N73"/>
-          <cell r="O73"/>
-          <cell r="P73"/>
-          <cell r="Q73"/>
-          <cell r="R73"/>
-          <cell r="S73"/>
-          <cell r="T73"/>
-          <cell r="U73"/>
-          <cell r="V73"/>
-          <cell r="W73"/>
-          <cell r="X73"/>
-        </row>
-        <row r="74">
-          <cell r="D74"/>
-          <cell r="E74"/>
-          <cell r="F74"/>
-          <cell r="G74"/>
-          <cell r="H74"/>
-          <cell r="I74"/>
-          <cell r="J74"/>
-          <cell r="K74"/>
-          <cell r="L74"/>
-          <cell r="M74"/>
-          <cell r="N74"/>
-          <cell r="O74"/>
-          <cell r="P74"/>
-          <cell r="Q74"/>
-          <cell r="R74"/>
-          <cell r="S74"/>
-          <cell r="T74"/>
-          <cell r="U74"/>
-          <cell r="V74"/>
-          <cell r="W74"/>
-          <cell r="X74"/>
-        </row>
-        <row r="75">
-          <cell r="D75"/>
-          <cell r="E75"/>
-          <cell r="F75"/>
-          <cell r="G75"/>
-          <cell r="H75"/>
-          <cell r="I75"/>
-          <cell r="J75"/>
-          <cell r="K75"/>
-          <cell r="L75"/>
-          <cell r="M75"/>
-          <cell r="N75"/>
-          <cell r="O75"/>
-          <cell r="P75"/>
-          <cell r="Q75"/>
-          <cell r="R75"/>
-          <cell r="S75"/>
-          <cell r="T75"/>
-          <cell r="U75"/>
-          <cell r="V75"/>
-          <cell r="W75"/>
-          <cell r="X75"/>
-        </row>
-        <row r="76">
-          <cell r="D76"/>
-          <cell r="E76"/>
-          <cell r="F76"/>
-          <cell r="G76"/>
-          <cell r="H76"/>
-          <cell r="I76"/>
-          <cell r="J76"/>
-          <cell r="K76"/>
-          <cell r="L76"/>
-          <cell r="M76"/>
-          <cell r="N76"/>
-          <cell r="O76"/>
-          <cell r="P76"/>
-          <cell r="Q76"/>
-          <cell r="R76"/>
-          <cell r="S76"/>
-          <cell r="T76"/>
-          <cell r="U76"/>
-          <cell r="V76"/>
-          <cell r="W76"/>
-          <cell r="X76"/>
-        </row>
-        <row r="77">
-          <cell r="D77"/>
-          <cell r="E77"/>
-          <cell r="F77"/>
-          <cell r="G77"/>
-          <cell r="H77"/>
-          <cell r="I77"/>
-          <cell r="J77"/>
-          <cell r="K77"/>
-          <cell r="L77"/>
-          <cell r="M77"/>
-          <cell r="N77"/>
-          <cell r="O77"/>
-          <cell r="P77"/>
-          <cell r="Q77"/>
-          <cell r="R77"/>
-          <cell r="S77"/>
-          <cell r="T77"/>
-          <cell r="U77"/>
-          <cell r="V77"/>
-          <cell r="W77"/>
-          <cell r="X77"/>
-        </row>
-        <row r="78">
-          <cell r="D78"/>
-          <cell r="E78"/>
-          <cell r="F78"/>
-          <cell r="G78"/>
-          <cell r="H78"/>
-          <cell r="I78"/>
-          <cell r="J78"/>
-          <cell r="K78"/>
-          <cell r="L78"/>
-          <cell r="M78"/>
-          <cell r="N78"/>
-          <cell r="O78"/>
-          <cell r="P78"/>
-          <cell r="Q78"/>
-          <cell r="R78"/>
-          <cell r="S78"/>
-          <cell r="T78"/>
-          <cell r="U78"/>
-          <cell r="V78"/>
-          <cell r="W78"/>
-          <cell r="X78"/>
-        </row>
-        <row r="79">
-          <cell r="D79"/>
-          <cell r="E79"/>
-          <cell r="F79"/>
-          <cell r="G79"/>
-          <cell r="H79"/>
-          <cell r="I79"/>
-          <cell r="J79"/>
-          <cell r="K79"/>
-          <cell r="L79"/>
-          <cell r="M79"/>
-          <cell r="N79"/>
-          <cell r="O79"/>
-          <cell r="P79"/>
-          <cell r="Q79"/>
-          <cell r="R79"/>
-          <cell r="S79"/>
-          <cell r="T79"/>
-          <cell r="U79"/>
-          <cell r="V79"/>
-          <cell r="W79"/>
-          <cell r="X79"/>
-        </row>
-        <row r="80">
-          <cell r="D80"/>
-          <cell r="E80"/>
-          <cell r="F80"/>
-          <cell r="G80"/>
-          <cell r="H80"/>
-          <cell r="I80"/>
-          <cell r="J80"/>
-          <cell r="K80"/>
-          <cell r="L80"/>
-          <cell r="M80"/>
-          <cell r="N80"/>
-          <cell r="O80"/>
-          <cell r="P80"/>
-          <cell r="Q80"/>
-          <cell r="R80"/>
-          <cell r="S80"/>
-          <cell r="T80"/>
-          <cell r="U80"/>
-          <cell r="V80"/>
-          <cell r="W80"/>
-          <cell r="X80"/>
-        </row>
-        <row r="81">
-          <cell r="D81"/>
-          <cell r="E81"/>
-          <cell r="F81"/>
-          <cell r="G81"/>
-          <cell r="H81"/>
-          <cell r="I81"/>
-          <cell r="J81"/>
-          <cell r="K81"/>
-          <cell r="L81"/>
-          <cell r="M81"/>
-          <cell r="N81"/>
-          <cell r="O81"/>
-          <cell r="P81"/>
-          <cell r="Q81"/>
-          <cell r="R81"/>
-          <cell r="S81"/>
-          <cell r="T81"/>
-          <cell r="U81"/>
-          <cell r="V81"/>
-          <cell r="W81"/>
-          <cell r="X81"/>
-        </row>
-        <row r="82">
-          <cell r="D82"/>
-          <cell r="E82"/>
-          <cell r="F82"/>
-          <cell r="G82"/>
-          <cell r="H82"/>
-          <cell r="I82"/>
-          <cell r="J82"/>
-          <cell r="K82"/>
-          <cell r="L82"/>
-          <cell r="M82"/>
-          <cell r="N82"/>
-          <cell r="O82"/>
-          <cell r="P82"/>
-          <cell r="Q82"/>
-          <cell r="R82"/>
-          <cell r="S82"/>
-          <cell r="T82"/>
-          <cell r="U82"/>
-          <cell r="V82"/>
-          <cell r="W82"/>
-          <cell r="X82"/>
-        </row>
-        <row r="83">
-          <cell r="D83"/>
-          <cell r="E83"/>
-          <cell r="F83"/>
-          <cell r="G83"/>
-          <cell r="H83"/>
-          <cell r="I83"/>
-          <cell r="J83"/>
-          <cell r="K83"/>
-          <cell r="L83"/>
-          <cell r="M83"/>
-          <cell r="N83"/>
-          <cell r="O83"/>
-          <cell r="P83"/>
-          <cell r="Q83"/>
-          <cell r="R83"/>
-          <cell r="S83"/>
-          <cell r="T83"/>
-          <cell r="U83"/>
-          <cell r="V83"/>
-          <cell r="W83"/>
-          <cell r="X83"/>
-        </row>
-        <row r="84">
-          <cell r="D84"/>
-          <cell r="E84"/>
-          <cell r="F84"/>
-          <cell r="G84"/>
-          <cell r="H84"/>
-          <cell r="I84"/>
-          <cell r="J84"/>
-          <cell r="K84"/>
-          <cell r="L84"/>
-          <cell r="M84"/>
-          <cell r="N84"/>
-          <cell r="O84"/>
-          <cell r="P84"/>
-          <cell r="Q84"/>
-          <cell r="R84"/>
-          <cell r="S84"/>
-          <cell r="T84"/>
-          <cell r="U84"/>
-          <cell r="V84"/>
-          <cell r="W84"/>
-          <cell r="X84"/>
-        </row>
-        <row r="85">
-          <cell r="D85"/>
-          <cell r="E85"/>
-          <cell r="F85"/>
-          <cell r="G85"/>
-          <cell r="H85"/>
-          <cell r="I85"/>
-          <cell r="J85"/>
-          <cell r="K85"/>
-          <cell r="L85"/>
-          <cell r="M85"/>
-          <cell r="N85"/>
-          <cell r="O85"/>
-          <cell r="P85"/>
-          <cell r="Q85"/>
-          <cell r="R85"/>
-          <cell r="S85"/>
-          <cell r="T85"/>
-          <cell r="U85"/>
-          <cell r="V85"/>
-          <cell r="W85"/>
-          <cell r="X85"/>
-        </row>
-        <row r="86">
-          <cell r="D86"/>
-          <cell r="E86"/>
-          <cell r="F86"/>
-          <cell r="G86"/>
-          <cell r="H86"/>
-          <cell r="I86"/>
-          <cell r="J86"/>
-          <cell r="K86"/>
-          <cell r="L86"/>
-          <cell r="M86"/>
-          <cell r="N86"/>
-          <cell r="O86"/>
-          <cell r="P86"/>
-          <cell r="Q86"/>
-          <cell r="R86"/>
-          <cell r="S86"/>
-          <cell r="T86"/>
-          <cell r="U86"/>
-          <cell r="V86"/>
-          <cell r="W86"/>
-          <cell r="X86"/>
-        </row>
-        <row r="87">
-          <cell r="D87"/>
-          <cell r="E87"/>
-          <cell r="F87"/>
-          <cell r="G87"/>
-          <cell r="H87"/>
-          <cell r="I87"/>
-          <cell r="J87"/>
-          <cell r="K87"/>
-          <cell r="L87"/>
-          <cell r="M87"/>
-          <cell r="N87"/>
-          <cell r="O87"/>
-          <cell r="P87"/>
-          <cell r="Q87"/>
-          <cell r="R87"/>
-          <cell r="S87"/>
-          <cell r="T87"/>
-          <cell r="U87"/>
-          <cell r="V87"/>
-          <cell r="W87"/>
-          <cell r="X87"/>
-        </row>
-        <row r="88">
-          <cell r="D88"/>
-          <cell r="E88"/>
-          <cell r="F88"/>
-          <cell r="G88"/>
-          <cell r="H88"/>
-          <cell r="I88"/>
-          <cell r="J88"/>
-          <cell r="K88"/>
-          <cell r="L88"/>
-          <cell r="M88"/>
-          <cell r="N88"/>
-          <cell r="O88"/>
-          <cell r="P88"/>
-          <cell r="Q88"/>
-          <cell r="R88"/>
-          <cell r="S88"/>
-          <cell r="T88"/>
-          <cell r="U88"/>
-          <cell r="V88"/>
-          <cell r="W88"/>
-          <cell r="X88"/>
-        </row>
-        <row r="89">
-          <cell r="D89"/>
-          <cell r="E89"/>
-          <cell r="F89"/>
-          <cell r="G89"/>
-          <cell r="H89"/>
-          <cell r="I89"/>
-          <cell r="J89"/>
-          <cell r="K89"/>
-          <cell r="L89"/>
-          <cell r="M89"/>
-          <cell r="N89"/>
-          <cell r="O89"/>
-          <cell r="P89"/>
-          <cell r="Q89"/>
-          <cell r="R89"/>
-          <cell r="S89"/>
-          <cell r="T89"/>
-          <cell r="U89"/>
-          <cell r="V89"/>
-          <cell r="W89"/>
-          <cell r="X89"/>
-        </row>
-        <row r="90">
-          <cell r="D90"/>
-          <cell r="E90"/>
-          <cell r="F90"/>
-          <cell r="G90"/>
-          <cell r="H90"/>
-          <cell r="I90"/>
-          <cell r="J90"/>
-          <cell r="K90"/>
-          <cell r="L90"/>
-          <cell r="M90"/>
-          <cell r="N90"/>
-          <cell r="O90"/>
-          <cell r="P90"/>
-          <cell r="Q90"/>
-          <cell r="R90"/>
-          <cell r="S90"/>
-          <cell r="T90"/>
-          <cell r="U90"/>
-          <cell r="V90"/>
-          <cell r="W90"/>
-          <cell r="X90"/>
-        </row>
-        <row r="91">
-          <cell r="D91"/>
-          <cell r="E91"/>
-          <cell r="F91"/>
-          <cell r="G91"/>
-          <cell r="H91"/>
-          <cell r="I91"/>
-          <cell r="J91"/>
-          <cell r="K91"/>
-          <cell r="L91"/>
-          <cell r="M91"/>
-          <cell r="N91"/>
-          <cell r="O91"/>
-          <cell r="P91"/>
-          <cell r="Q91"/>
-          <cell r="R91"/>
-          <cell r="S91"/>
-          <cell r="T91"/>
-          <cell r="U91"/>
-          <cell r="V91"/>
-          <cell r="W91"/>
-          <cell r="X91"/>
-        </row>
-        <row r="92">
-          <cell r="D92"/>
-          <cell r="E92"/>
-          <cell r="F92"/>
-          <cell r="G92"/>
-          <cell r="H92"/>
-          <cell r="I92"/>
-          <cell r="J92"/>
-          <cell r="K92"/>
-          <cell r="L92"/>
-          <cell r="M92"/>
-          <cell r="N92"/>
-          <cell r="O92"/>
-          <cell r="P92"/>
-          <cell r="Q92"/>
-          <cell r="R92"/>
-          <cell r="S92"/>
-          <cell r="T92"/>
-          <cell r="U92"/>
-          <cell r="V92"/>
-          <cell r="W92"/>
-          <cell r="X92"/>
-        </row>
-        <row r="93">
-          <cell r="D93"/>
-          <cell r="E93"/>
-          <cell r="F93"/>
-          <cell r="G93"/>
-          <cell r="H93"/>
-          <cell r="I93"/>
-          <cell r="J93"/>
-          <cell r="K93"/>
-          <cell r="L93"/>
-          <cell r="M93"/>
-          <cell r="N93"/>
-          <cell r="O93"/>
-          <cell r="P93"/>
-          <cell r="Q93"/>
-          <cell r="R93"/>
-          <cell r="S93"/>
-          <cell r="T93"/>
-          <cell r="U93"/>
-          <cell r="V93"/>
-          <cell r="W93"/>
-          <cell r="X93"/>
-        </row>
-        <row r="94">
-          <cell r="D94"/>
-          <cell r="E94"/>
-          <cell r="F94"/>
-          <cell r="G94"/>
-          <cell r="H94"/>
-          <cell r="I94"/>
-          <cell r="J94"/>
-          <cell r="K94"/>
-          <cell r="L94"/>
-          <cell r="M94"/>
-          <cell r="N94"/>
-          <cell r="O94"/>
-          <cell r="P94"/>
-          <cell r="Q94"/>
-          <cell r="R94"/>
-          <cell r="S94"/>
-          <cell r="T94"/>
-          <cell r="U94"/>
-          <cell r="V94"/>
-          <cell r="W94"/>
-          <cell r="X94"/>
-        </row>
-        <row r="95">
-          <cell r="D95"/>
-          <cell r="E95"/>
-          <cell r="F95"/>
-          <cell r="G95"/>
-          <cell r="H95"/>
-          <cell r="I95"/>
-          <cell r="J95"/>
-          <cell r="K95"/>
-          <cell r="L95"/>
-          <cell r="M95"/>
-          <cell r="N95"/>
-          <cell r="O95"/>
-          <cell r="P95"/>
-          <cell r="Q95"/>
-          <cell r="R95"/>
-          <cell r="S95"/>
-          <cell r="T95"/>
-          <cell r="U95"/>
-          <cell r="V95"/>
-          <cell r="W95"/>
-          <cell r="X95"/>
-        </row>
-        <row r="96">
-          <cell r="D96"/>
-          <cell r="E96"/>
-          <cell r="F96"/>
-          <cell r="G96"/>
-          <cell r="H96"/>
-          <cell r="I96"/>
-          <cell r="J96"/>
-          <cell r="K96"/>
-          <cell r="L96"/>
-          <cell r="M96"/>
-          <cell r="N96"/>
-          <cell r="O96"/>
-          <cell r="P96"/>
-          <cell r="Q96"/>
-          <cell r="R96"/>
-          <cell r="S96"/>
-          <cell r="T96"/>
-          <cell r="U96"/>
-          <cell r="V96"/>
-          <cell r="W96"/>
-          <cell r="X96"/>
-        </row>
-        <row r="97">
-          <cell r="D97"/>
-          <cell r="E97"/>
-          <cell r="F97"/>
-          <cell r="G97"/>
-          <cell r="H97"/>
-          <cell r="I97"/>
-          <cell r="J97"/>
-          <cell r="K97"/>
-          <cell r="L97"/>
-          <cell r="M97"/>
-          <cell r="N97"/>
-          <cell r="O97"/>
-          <cell r="P97"/>
-          <cell r="Q97"/>
-          <cell r="R97"/>
-          <cell r="S97"/>
-          <cell r="T97"/>
-          <cell r="U97"/>
-          <cell r="V97"/>
-          <cell r="W97"/>
-          <cell r="X97"/>
-        </row>
-        <row r="98">
-          <cell r="D98"/>
-          <cell r="E98"/>
-          <cell r="F98"/>
-          <cell r="G98"/>
-          <cell r="H98"/>
-          <cell r="I98"/>
-          <cell r="J98"/>
-          <cell r="K98"/>
-          <cell r="L98"/>
-          <cell r="M98"/>
-          <cell r="N98"/>
-          <cell r="O98"/>
-          <cell r="P98"/>
-          <cell r="Q98"/>
-          <cell r="R98"/>
-          <cell r="S98"/>
-          <cell r="T98"/>
-          <cell r="U98"/>
-          <cell r="V98"/>
-          <cell r="W98"/>
-          <cell r="X98"/>
-        </row>
-        <row r="99">
-          <cell r="D99"/>
-          <cell r="E99"/>
-          <cell r="F99"/>
-          <cell r="G99"/>
-          <cell r="H99"/>
-          <cell r="I99"/>
-          <cell r="J99"/>
-          <cell r="K99"/>
-          <cell r="L99"/>
-          <cell r="M99"/>
-          <cell r="N99"/>
-          <cell r="O99"/>
-          <cell r="P99"/>
-          <cell r="Q99"/>
-          <cell r="R99"/>
-          <cell r="S99"/>
-          <cell r="T99"/>
-          <cell r="U99"/>
-          <cell r="V99"/>
-          <cell r="W99"/>
-          <cell r="X99"/>
-        </row>
-        <row r="100">
-          <cell r="D100"/>
-          <cell r="E100"/>
-          <cell r="F100"/>
-          <cell r="G100"/>
-          <cell r="H100"/>
-          <cell r="I100"/>
-          <cell r="J100"/>
-          <cell r="K100"/>
-          <cell r="L100"/>
-          <cell r="M100"/>
-          <cell r="N100"/>
-          <cell r="O100"/>
-          <cell r="P100"/>
-          <cell r="Q100"/>
-          <cell r="R100"/>
-          <cell r="S100"/>
-          <cell r="T100"/>
-          <cell r="U100"/>
-          <cell r="V100"/>
-          <cell r="W100"/>
-          <cell r="X100"/>
-        </row>
-        <row r="101">
-          <cell r="D101"/>
-          <cell r="E101"/>
-          <cell r="F101"/>
-          <cell r="G101"/>
-          <cell r="H101"/>
-          <cell r="I101"/>
-          <cell r="J101"/>
-          <cell r="K101"/>
-          <cell r="L101"/>
-          <cell r="M101"/>
-          <cell r="N101"/>
-          <cell r="O101"/>
-          <cell r="P101"/>
-          <cell r="Q101"/>
-          <cell r="R101"/>
-          <cell r="S101"/>
-          <cell r="T101"/>
-          <cell r="U101"/>
-          <cell r="V101"/>
-          <cell r="W101"/>
-          <cell r="X101"/>
-        </row>
-        <row r="102">
-          <cell r="D102"/>
-          <cell r="E102"/>
-          <cell r="F102"/>
-          <cell r="G102"/>
-          <cell r="H102"/>
-          <cell r="I102"/>
-          <cell r="J102"/>
-          <cell r="K102"/>
-          <cell r="L102"/>
-          <cell r="M102"/>
-          <cell r="N102"/>
-          <cell r="O102"/>
-          <cell r="P102"/>
-          <cell r="Q102"/>
-          <cell r="R102"/>
-          <cell r="S102"/>
-          <cell r="T102"/>
-          <cell r="U102"/>
-          <cell r="V102"/>
-          <cell r="W102"/>
-          <cell r="X102"/>
-        </row>
-        <row r="103">
-          <cell r="D103"/>
-          <cell r="E103"/>
-          <cell r="F103"/>
-          <cell r="G103"/>
-          <cell r="H103"/>
-          <cell r="I103"/>
-          <cell r="J103"/>
-          <cell r="K103"/>
-          <cell r="L103"/>
-          <cell r="M103"/>
-          <cell r="N103"/>
-          <cell r="O103"/>
-          <cell r="P103"/>
-          <cell r="Q103"/>
-          <cell r="R103"/>
-          <cell r="S103"/>
-          <cell r="T103"/>
-          <cell r="U103"/>
-          <cell r="V103"/>
-          <cell r="W103"/>
-          <cell r="X103"/>
-        </row>
-        <row r="104">
-          <cell r="D104"/>
-          <cell r="E104"/>
-          <cell r="F104"/>
-          <cell r="G104"/>
-          <cell r="H104"/>
-          <cell r="I104"/>
-          <cell r="J104"/>
-          <cell r="K104"/>
-          <cell r="L104"/>
-          <cell r="M104"/>
-          <cell r="N104"/>
-          <cell r="O104"/>
-          <cell r="P104"/>
-          <cell r="Q104"/>
-          <cell r="R104"/>
-          <cell r="S104"/>
-          <cell r="T104"/>
-          <cell r="U104"/>
-          <cell r="V104"/>
-          <cell r="W104"/>
-          <cell r="X104"/>
-        </row>
-        <row r="105">
-          <cell r="D105"/>
-          <cell r="E105"/>
-          <cell r="F105"/>
-          <cell r="G105"/>
-          <cell r="H105"/>
-          <cell r="I105"/>
-          <cell r="J105"/>
-          <cell r="K105"/>
-          <cell r="L105"/>
-          <cell r="M105"/>
-          <cell r="N105"/>
-          <cell r="O105"/>
-          <cell r="P105"/>
-          <cell r="Q105"/>
-          <cell r="R105"/>
-          <cell r="S105"/>
-          <cell r="T105"/>
-          <cell r="U105"/>
-          <cell r="V105"/>
-          <cell r="W105"/>
-          <cell r="X105"/>
-        </row>
-        <row r="106">
-          <cell r="D106"/>
-          <cell r="E106"/>
-          <cell r="F106"/>
-          <cell r="G106"/>
-          <cell r="H106"/>
-          <cell r="I106"/>
-          <cell r="J106"/>
-          <cell r="K106"/>
-          <cell r="L106"/>
-          <cell r="M106"/>
-          <cell r="N106"/>
-          <cell r="O106"/>
-          <cell r="P106"/>
-          <cell r="Q106"/>
-          <cell r="R106"/>
-          <cell r="S106"/>
-          <cell r="T106"/>
-          <cell r="U106"/>
-          <cell r="V106"/>
-          <cell r="W106"/>
-          <cell r="X106"/>
-        </row>
-        <row r="107">
-          <cell r="D107"/>
-          <cell r="E107"/>
-          <cell r="F107"/>
-          <cell r="G107"/>
-          <cell r="H107"/>
-          <cell r="I107"/>
-          <cell r="J107"/>
-          <cell r="K107"/>
-          <cell r="L107"/>
-          <cell r="M107"/>
-          <cell r="N107"/>
-          <cell r="O107"/>
-          <cell r="P107"/>
-          <cell r="Q107"/>
-          <cell r="R107"/>
-          <cell r="S107"/>
-          <cell r="T107"/>
-          <cell r="U107"/>
-          <cell r="V107"/>
-          <cell r="W107"/>
-          <cell r="X107"/>
-        </row>
-        <row r="108">
-          <cell r="D108"/>
-          <cell r="E108"/>
-          <cell r="F108"/>
-          <cell r="G108"/>
-          <cell r="H108"/>
-          <cell r="I108"/>
-          <cell r="J108"/>
-          <cell r="K108"/>
-          <cell r="L108"/>
-          <cell r="M108"/>
-          <cell r="N108"/>
-          <cell r="O108"/>
-          <cell r="P108"/>
-          <cell r="Q108"/>
-          <cell r="R108"/>
-          <cell r="S108"/>
-          <cell r="T108"/>
-          <cell r="U108"/>
-          <cell r="V108"/>
-          <cell r="W108"/>
-          <cell r="X108"/>
-        </row>
-        <row r="109">
-          <cell r="D109"/>
-          <cell r="E109"/>
-          <cell r="F109"/>
-          <cell r="G109"/>
-          <cell r="H109"/>
-          <cell r="I109"/>
-          <cell r="J109"/>
-          <cell r="K109"/>
-          <cell r="L109"/>
-          <cell r="M109"/>
-          <cell r="N109"/>
-          <cell r="O109"/>
-          <cell r="P109"/>
-          <cell r="Q109"/>
-          <cell r="R109"/>
-          <cell r="S109"/>
-          <cell r="T109"/>
-          <cell r="U109"/>
-          <cell r="V109"/>
-          <cell r="W109"/>
-          <cell r="X109"/>
-        </row>
-        <row r="110">
-          <cell r="D110"/>
-          <cell r="E110"/>
-          <cell r="F110"/>
-          <cell r="G110"/>
-          <cell r="H110"/>
-          <cell r="I110"/>
-          <cell r="J110"/>
-          <cell r="K110"/>
-          <cell r="L110"/>
-          <cell r="M110"/>
-          <cell r="N110"/>
-          <cell r="O110"/>
-          <cell r="P110"/>
-          <cell r="Q110"/>
-          <cell r="R110"/>
-          <cell r="S110"/>
-          <cell r="T110"/>
-          <cell r="U110"/>
-          <cell r="V110"/>
-          <cell r="W110"/>
-          <cell r="X110"/>
-        </row>
-        <row r="111">
-          <cell r="D111"/>
-          <cell r="E111"/>
-          <cell r="F111"/>
-          <cell r="G111"/>
-          <cell r="H111"/>
-          <cell r="I111"/>
-          <cell r="J111"/>
-          <cell r="K111"/>
-          <cell r="L111"/>
-          <cell r="M111"/>
-          <cell r="N111"/>
-          <cell r="O111"/>
-          <cell r="P111"/>
-          <cell r="Q111"/>
-          <cell r="R111"/>
-          <cell r="S111"/>
-          <cell r="T111"/>
-          <cell r="U111"/>
-          <cell r="V111"/>
-          <cell r="W111"/>
-          <cell r="X111"/>
-        </row>
-        <row r="112">
-          <cell r="D112"/>
-          <cell r="E112"/>
-          <cell r="F112"/>
-          <cell r="G112"/>
-          <cell r="H112"/>
-          <cell r="I112"/>
-          <cell r="J112"/>
-          <cell r="K112"/>
-          <cell r="L112"/>
-          <cell r="M112"/>
-          <cell r="N112"/>
-          <cell r="O112"/>
-          <cell r="P112"/>
-          <cell r="Q112"/>
-          <cell r="R112"/>
-          <cell r="S112"/>
-          <cell r="T112"/>
-          <cell r="U112"/>
-          <cell r="V112"/>
-          <cell r="W112"/>
-          <cell r="X112"/>
-        </row>
-        <row r="113">
-          <cell r="D113"/>
-          <cell r="E113"/>
-          <cell r="F113"/>
-          <cell r="G113"/>
-          <cell r="H113"/>
-          <cell r="I113"/>
-          <cell r="J113"/>
-          <cell r="K113"/>
-          <cell r="L113"/>
-          <cell r="M113"/>
-          <cell r="N113"/>
-          <cell r="O113"/>
-          <cell r="P113"/>
-          <cell r="Q113"/>
-          <cell r="R113"/>
-          <cell r="S113"/>
-          <cell r="T113"/>
-          <cell r="U113"/>
-          <cell r="V113"/>
-          <cell r="W113"/>
-          <cell r="X113"/>
-        </row>
-        <row r="114">
-          <cell r="D114"/>
-          <cell r="E114"/>
-          <cell r="F114"/>
-          <cell r="G114"/>
-          <cell r="H114"/>
-          <cell r="I114"/>
-          <cell r="J114"/>
-          <cell r="K114"/>
-          <cell r="L114"/>
-          <cell r="M114"/>
-          <cell r="N114"/>
-          <cell r="O114"/>
-          <cell r="P114"/>
-          <cell r="Q114"/>
-          <cell r="R114"/>
-          <cell r="S114"/>
-          <cell r="T114"/>
-          <cell r="U114"/>
-          <cell r="V114"/>
-          <cell r="W114"/>
-          <cell r="X114"/>
-        </row>
-        <row r="115">
-          <cell r="D115"/>
-          <cell r="E115"/>
-          <cell r="F115"/>
-          <cell r="G115"/>
-          <cell r="H115"/>
-          <cell r="I115"/>
-          <cell r="J115"/>
-          <cell r="K115"/>
-          <cell r="L115"/>
-          <cell r="M115"/>
-          <cell r="N115"/>
-          <cell r="O115"/>
-          <cell r="P115"/>
-          <cell r="Q115"/>
-          <cell r="R115"/>
-          <cell r="S115"/>
-          <cell r="T115"/>
-          <cell r="U115"/>
-          <cell r="V115"/>
-          <cell r="W115"/>
-          <cell r="X115"/>
-        </row>
-        <row r="116">
-          <cell r="D116"/>
-          <cell r="E116"/>
-          <cell r="F116"/>
-          <cell r="G116"/>
-          <cell r="H116"/>
-          <cell r="I116"/>
-          <cell r="J116"/>
-          <cell r="K116"/>
-          <cell r="L116"/>
-          <cell r="M116"/>
-          <cell r="N116"/>
-          <cell r="O116"/>
-          <cell r="P116"/>
-          <cell r="Q116"/>
-          <cell r="R116"/>
-          <cell r="S116"/>
-          <cell r="T116"/>
-          <cell r="U116"/>
-          <cell r="V116"/>
-          <cell r="W116"/>
-          <cell r="X116"/>
-        </row>
-        <row r="117">
-          <cell r="D117"/>
-          <cell r="E117"/>
-          <cell r="F117"/>
-          <cell r="G117"/>
-          <cell r="H117"/>
-          <cell r="I117"/>
-          <cell r="J117"/>
-          <cell r="K117"/>
-          <cell r="L117"/>
-          <cell r="M117"/>
-          <cell r="N117"/>
-          <cell r="O117"/>
-          <cell r="P117"/>
-          <cell r="Q117"/>
-          <cell r="R117"/>
-          <cell r="S117"/>
-          <cell r="T117"/>
-          <cell r="U117"/>
-          <cell r="V117"/>
-          <cell r="W117"/>
-          <cell r="X117"/>
-        </row>
-        <row r="118">
-          <cell r="D118"/>
-          <cell r="E118"/>
-          <cell r="F118"/>
-          <cell r="G118"/>
-          <cell r="H118"/>
-          <cell r="I118"/>
-          <cell r="J118"/>
-          <cell r="K118"/>
-          <cell r="L118"/>
-          <cell r="M118"/>
-          <cell r="N118"/>
-          <cell r="O118"/>
-          <cell r="P118"/>
-          <cell r="Q118"/>
-          <cell r="R118"/>
-          <cell r="S118"/>
-          <cell r="T118"/>
-          <cell r="U118"/>
-          <cell r="V118"/>
-          <cell r="W118"/>
-          <cell r="X118"/>
-        </row>
-        <row r="119">
-          <cell r="D119"/>
-          <cell r="E119"/>
-          <cell r="F119"/>
-          <cell r="G119"/>
-          <cell r="H119"/>
-          <cell r="I119"/>
-          <cell r="J119"/>
-          <cell r="K119"/>
-          <cell r="L119"/>
-          <cell r="M119"/>
-          <cell r="N119"/>
-          <cell r="O119"/>
-          <cell r="P119"/>
-          <cell r="Q119"/>
-          <cell r="R119"/>
-          <cell r="S119"/>
-          <cell r="T119"/>
-          <cell r="U119"/>
-          <cell r="V119"/>
-          <cell r="W119"/>
-          <cell r="X119"/>
-        </row>
-        <row r="120">
-          <cell r="D120"/>
-          <cell r="E120"/>
-          <cell r="F120"/>
-          <cell r="G120"/>
-          <cell r="H120"/>
-          <cell r="I120"/>
-          <cell r="J120"/>
-          <cell r="K120"/>
-          <cell r="L120"/>
-          <cell r="M120"/>
-          <cell r="N120"/>
-          <cell r="O120"/>
-          <cell r="P120"/>
-          <cell r="Q120"/>
-          <cell r="R120"/>
-          <cell r="S120"/>
-          <cell r="T120"/>
-          <cell r="U120"/>
-          <cell r="V120"/>
-          <cell r="W120"/>
-          <cell r="X120"/>
-        </row>
-        <row r="121">
-          <cell r="D121"/>
-          <cell r="E121"/>
-          <cell r="F121"/>
-          <cell r="G121"/>
-          <cell r="H121"/>
-          <cell r="I121"/>
-          <cell r="J121"/>
-          <cell r="K121"/>
-          <cell r="L121"/>
-          <cell r="M121"/>
-          <cell r="N121"/>
-          <cell r="O121"/>
-          <cell r="P121"/>
-          <cell r="Q121"/>
-          <cell r="R121"/>
-          <cell r="S121"/>
-          <cell r="T121"/>
-          <cell r="U121"/>
-          <cell r="V121"/>
-          <cell r="W121"/>
-          <cell r="X121"/>
-        </row>
-        <row r="122">
-          <cell r="D122"/>
-          <cell r="E122"/>
-          <cell r="F122"/>
-          <cell r="G122"/>
-          <cell r="H122"/>
-          <cell r="I122"/>
-          <cell r="J122"/>
-          <cell r="K122"/>
-          <cell r="L122"/>
-          <cell r="M122"/>
-          <cell r="N122"/>
-          <cell r="O122"/>
-          <cell r="P122"/>
-          <cell r="Q122"/>
-          <cell r="R122"/>
-          <cell r="S122"/>
-          <cell r="T122"/>
-          <cell r="U122"/>
-          <cell r="V122"/>
-          <cell r="W122"/>
-          <cell r="X122"/>
-        </row>
-        <row r="123">
-          <cell r="D123"/>
-          <cell r="E123"/>
-          <cell r="F123"/>
-          <cell r="G123"/>
-          <cell r="H123"/>
-          <cell r="I123"/>
-          <cell r="J123"/>
-          <cell r="K123"/>
-          <cell r="L123"/>
-          <cell r="M123"/>
-          <cell r="N123"/>
-          <cell r="O123"/>
-          <cell r="P123"/>
-          <cell r="Q123"/>
-          <cell r="R123"/>
-          <cell r="S123"/>
-          <cell r="T123"/>
-          <cell r="U123"/>
-          <cell r="V123"/>
-          <cell r="W123"/>
-          <cell r="X123"/>
-        </row>
-        <row r="124">
-          <cell r="D124"/>
-          <cell r="E124"/>
-          <cell r="F124"/>
-          <cell r="G124"/>
-          <cell r="H124"/>
-          <cell r="I124"/>
-          <cell r="J124"/>
-          <cell r="K124"/>
-          <cell r="L124"/>
-          <cell r="M124"/>
-          <cell r="N124"/>
-          <cell r="O124"/>
-          <cell r="P124"/>
-          <cell r="Q124"/>
-          <cell r="R124"/>
-          <cell r="S124"/>
-          <cell r="T124"/>
-          <cell r="U124"/>
-          <cell r="V124"/>
-          <cell r="W124"/>
-          <cell r="X124"/>
-        </row>
-        <row r="125">
-          <cell r="D125"/>
-          <cell r="E125"/>
-          <cell r="F125"/>
-          <cell r="G125"/>
-          <cell r="H125"/>
-          <cell r="I125"/>
-          <cell r="J125"/>
-          <cell r="K125"/>
-          <cell r="L125"/>
-          <cell r="M125"/>
-          <cell r="N125"/>
-          <cell r="O125"/>
-          <cell r="P125"/>
-          <cell r="Q125"/>
-          <cell r="R125"/>
-          <cell r="S125"/>
-          <cell r="T125"/>
-          <cell r="U125"/>
-          <cell r="V125"/>
-          <cell r="W125"/>
-          <cell r="X125"/>
-        </row>
-        <row r="126">
-          <cell r="D126"/>
-          <cell r="E126"/>
-          <cell r="F126"/>
-          <cell r="G126"/>
-          <cell r="H126"/>
-          <cell r="I126"/>
-          <cell r="J126"/>
-          <cell r="K126"/>
-          <cell r="L126"/>
-          <cell r="M126"/>
-          <cell r="N126"/>
-          <cell r="O126"/>
-          <cell r="P126"/>
-          <cell r="Q126"/>
-          <cell r="R126"/>
-          <cell r="S126"/>
-          <cell r="T126"/>
-          <cell r="U126"/>
-          <cell r="V126"/>
-          <cell r="W126"/>
-          <cell r="X126"/>
-        </row>
-        <row r="127">
-          <cell r="D127"/>
-          <cell r="E127"/>
-          <cell r="F127"/>
-          <cell r="G127"/>
-          <cell r="H127"/>
-          <cell r="I127"/>
-          <cell r="J127"/>
-          <cell r="K127"/>
-          <cell r="L127"/>
-          <cell r="M127"/>
-          <cell r="N127"/>
-          <cell r="O127"/>
-          <cell r="P127"/>
-          <cell r="Q127"/>
-          <cell r="R127"/>
-          <cell r="S127"/>
-          <cell r="T127"/>
-          <cell r="U127"/>
-          <cell r="V127"/>
-          <cell r="W127"/>
-          <cell r="X127"/>
-        </row>
-        <row r="128">
-          <cell r="D128"/>
-          <cell r="E128"/>
-          <cell r="F128"/>
-          <cell r="G128"/>
-          <cell r="H128"/>
-          <cell r="I128"/>
-          <cell r="J128"/>
-          <cell r="K128"/>
-          <cell r="L128"/>
-          <cell r="M128"/>
-          <cell r="N128"/>
-          <cell r="O128"/>
-          <cell r="P128"/>
-          <cell r="Q128"/>
-          <cell r="R128"/>
-          <cell r="S128"/>
-          <cell r="T128"/>
-          <cell r="U128"/>
-          <cell r="V128"/>
-          <cell r="W128"/>
-          <cell r="X128"/>
-        </row>
-        <row r="129">
-          <cell r="D129"/>
-          <cell r="E129"/>
-          <cell r="F129"/>
-          <cell r="G129"/>
-          <cell r="H129"/>
-          <cell r="I129"/>
-          <cell r="J129"/>
-          <cell r="K129"/>
-          <cell r="L129"/>
-          <cell r="M129"/>
-          <cell r="N129"/>
-          <cell r="O129"/>
-          <cell r="P129"/>
-          <cell r="Q129"/>
-          <cell r="R129"/>
-          <cell r="S129"/>
-          <cell r="T129"/>
-          <cell r="U129"/>
-          <cell r="V129"/>
-          <cell r="W129"/>
-          <cell r="X129"/>
-        </row>
-        <row r="130">
-          <cell r="D130"/>
-          <cell r="E130"/>
-          <cell r="F130"/>
-          <cell r="G130"/>
-          <cell r="H130"/>
-          <cell r="I130"/>
-          <cell r="J130"/>
-          <cell r="K130"/>
-          <cell r="L130"/>
-          <cell r="M130"/>
-          <cell r="N130"/>
-          <cell r="O130"/>
-          <cell r="P130"/>
-          <cell r="Q130"/>
-          <cell r="R130"/>
-          <cell r="S130"/>
-          <cell r="T130"/>
-          <cell r="U130"/>
-          <cell r="V130"/>
-          <cell r="W130"/>
-          <cell r="X130"/>
-        </row>
-        <row r="131">
-          <cell r="D131"/>
-          <cell r="E131"/>
-          <cell r="F131"/>
-          <cell r="G131"/>
-          <cell r="H131"/>
-          <cell r="I131"/>
-          <cell r="J131"/>
-          <cell r="K131"/>
-          <cell r="L131"/>
-          <cell r="M131"/>
-          <cell r="N131"/>
-          <cell r="O131"/>
-          <cell r="P131"/>
-          <cell r="Q131"/>
-          <cell r="R131"/>
-          <cell r="S131"/>
-          <cell r="T131"/>
-          <cell r="U131"/>
-          <cell r="V131"/>
-          <cell r="W131"/>
-          <cell r="X131"/>
-        </row>
-        <row r="132">
-          <cell r="D132"/>
-          <cell r="E132"/>
-          <cell r="F132"/>
-          <cell r="G132"/>
-          <cell r="H132"/>
-          <cell r="I132"/>
-          <cell r="J132"/>
-          <cell r="K132"/>
-          <cell r="L132"/>
-          <cell r="M132"/>
-          <cell r="N132"/>
-          <cell r="O132"/>
-          <cell r="P132"/>
-          <cell r="Q132"/>
-          <cell r="R132"/>
-          <cell r="S132"/>
-          <cell r="T132"/>
-          <cell r="U132"/>
-          <cell r="V132"/>
-          <cell r="W132"/>
-          <cell r="X132"/>
-        </row>
-        <row r="133">
-          <cell r="D133"/>
-          <cell r="E133"/>
-          <cell r="F133"/>
-          <cell r="G133"/>
-          <cell r="H133"/>
-          <cell r="I133"/>
-          <cell r="J133"/>
-          <cell r="K133"/>
-          <cell r="L133"/>
-          <cell r="M133"/>
-          <cell r="N133"/>
-          <cell r="O133"/>
-          <cell r="P133"/>
-          <cell r="Q133"/>
-          <cell r="R133"/>
-          <cell r="S133"/>
-          <cell r="T133"/>
-          <cell r="U133"/>
-          <cell r="V133"/>
-          <cell r="W133"/>
-          <cell r="X133"/>
-        </row>
-        <row r="134">
-          <cell r="D134"/>
-          <cell r="E134"/>
-          <cell r="F134"/>
-          <cell r="G134"/>
-          <cell r="H134"/>
-          <cell r="I134"/>
-          <cell r="J134"/>
-          <cell r="K134"/>
-          <cell r="L134"/>
-          <cell r="M134"/>
-          <cell r="N134"/>
-          <cell r="O134"/>
-          <cell r="P134"/>
-          <cell r="Q134"/>
-          <cell r="R134"/>
-          <cell r="S134"/>
-          <cell r="T134"/>
-          <cell r="U134"/>
-          <cell r="V134"/>
-          <cell r="W134"/>
-          <cell r="X134"/>
-        </row>
-        <row r="135">
-          <cell r="D135"/>
-          <cell r="E135"/>
-          <cell r="F135"/>
-          <cell r="G135"/>
-          <cell r="H135"/>
-          <cell r="I135"/>
-          <cell r="J135"/>
-          <cell r="K135"/>
-          <cell r="L135"/>
-          <cell r="M135"/>
-          <cell r="N135"/>
-          <cell r="O135"/>
-          <cell r="P135"/>
-          <cell r="Q135"/>
-          <cell r="R135"/>
-          <cell r="S135"/>
-          <cell r="T135"/>
-          <cell r="U135"/>
-          <cell r="V135"/>
-          <cell r="W135"/>
-          <cell r="X135"/>
-        </row>
-        <row r="136">
-          <cell r="D136"/>
-          <cell r="E136"/>
-          <cell r="F136"/>
-          <cell r="G136"/>
-          <cell r="H136"/>
-          <cell r="I136"/>
-          <cell r="J136"/>
-          <cell r="K136"/>
-          <cell r="L136"/>
-          <cell r="M136"/>
-          <cell r="N136"/>
-          <cell r="O136"/>
-          <cell r="P136"/>
-          <cell r="Q136"/>
-          <cell r="R136"/>
-          <cell r="S136"/>
-          <cell r="T136"/>
-          <cell r="U136"/>
-          <cell r="V136"/>
-          <cell r="W136"/>
-          <cell r="X136"/>
-        </row>
-        <row r="137">
-          <cell r="D137"/>
-          <cell r="E137"/>
-          <cell r="F137"/>
-          <cell r="G137"/>
-          <cell r="H137"/>
-          <cell r="I137"/>
-          <cell r="J137"/>
-          <cell r="K137"/>
-          <cell r="L137"/>
-          <cell r="M137"/>
-          <cell r="N137"/>
-          <cell r="O137"/>
-          <cell r="P137"/>
-          <cell r="Q137"/>
-          <cell r="R137"/>
-          <cell r="S137"/>
-          <cell r="T137"/>
-          <cell r="U137"/>
-          <cell r="V137"/>
-          <cell r="W137"/>
-          <cell r="X137"/>
-        </row>
-        <row r="138">
-          <cell r="D138"/>
-          <cell r="E138"/>
-          <cell r="F138"/>
-          <cell r="G138"/>
-          <cell r="H138"/>
-          <cell r="I138"/>
-          <cell r="J138"/>
-          <cell r="K138"/>
-          <cell r="L138"/>
-          <cell r="M138"/>
-          <cell r="N138"/>
-          <cell r="O138"/>
-          <cell r="P138"/>
-          <cell r="Q138"/>
-          <cell r="R138"/>
-          <cell r="S138"/>
-          <cell r="T138"/>
-          <cell r="U138"/>
-          <cell r="V138"/>
-          <cell r="W138"/>
-          <cell r="X138"/>
-        </row>
-        <row r="139">
-          <cell r="D139"/>
-          <cell r="E139"/>
-          <cell r="F139"/>
-          <cell r="G139"/>
-          <cell r="H139"/>
-          <cell r="I139"/>
-          <cell r="J139"/>
-          <cell r="K139"/>
-          <cell r="L139"/>
-          <cell r="M139"/>
-          <cell r="N139"/>
-          <cell r="O139"/>
-          <cell r="P139"/>
-          <cell r="Q139"/>
-          <cell r="R139"/>
-          <cell r="S139"/>
-          <cell r="T139"/>
-          <cell r="U139"/>
-          <cell r="V139"/>
-          <cell r="W139"/>
-          <cell r="X139"/>
-        </row>
-        <row r="140">
-          <cell r="D140"/>
-          <cell r="E140"/>
-          <cell r="F140"/>
-          <cell r="G140"/>
-          <cell r="H140"/>
-          <cell r="I140"/>
-          <cell r="J140"/>
-          <cell r="K140"/>
-          <cell r="L140"/>
-          <cell r="M140"/>
-          <cell r="N140"/>
-          <cell r="O140"/>
-          <cell r="P140"/>
-          <cell r="Q140"/>
-          <cell r="R140"/>
-          <cell r="S140"/>
-          <cell r="T140"/>
-          <cell r="U140"/>
-          <cell r="V140"/>
-          <cell r="W140"/>
-          <cell r="X140"/>
-        </row>
-        <row r="141">
-          <cell r="D141"/>
-          <cell r="E141"/>
-          <cell r="F141"/>
-          <cell r="G141"/>
-          <cell r="H141"/>
-          <cell r="I141"/>
-          <cell r="J141"/>
-          <cell r="K141"/>
-          <cell r="L141"/>
-          <cell r="M141"/>
-          <cell r="N141"/>
-          <cell r="O141"/>
-          <cell r="P141"/>
-          <cell r="Q141"/>
-          <cell r="R141"/>
-          <cell r="S141"/>
-          <cell r="T141"/>
-          <cell r="U141"/>
-          <cell r="V141"/>
-          <cell r="W141"/>
-          <cell r="X141"/>
-        </row>
-        <row r="142">
-          <cell r="D142"/>
-          <cell r="E142"/>
-          <cell r="F142"/>
-          <cell r="G142"/>
-          <cell r="H142"/>
-          <cell r="I142"/>
-          <cell r="J142"/>
-          <cell r="K142"/>
-          <cell r="L142"/>
-          <cell r="M142"/>
-          <cell r="N142"/>
-          <cell r="O142"/>
-          <cell r="P142"/>
-          <cell r="Q142"/>
-          <cell r="R142"/>
-          <cell r="S142"/>
-          <cell r="T142"/>
-          <cell r="U142"/>
-          <cell r="V142"/>
-          <cell r="W142"/>
-          <cell r="X142"/>
-        </row>
-        <row r="143">
-          <cell r="D143"/>
-          <cell r="E143"/>
-          <cell r="F143"/>
-          <cell r="G143"/>
-          <cell r="H143"/>
-          <cell r="I143"/>
-          <cell r="J143"/>
-          <cell r="K143"/>
-          <cell r="L143"/>
-          <cell r="M143"/>
-          <cell r="N143"/>
-          <cell r="O143"/>
-          <cell r="P143"/>
-          <cell r="Q143"/>
-          <cell r="R143"/>
-          <cell r="S143"/>
-          <cell r="T143"/>
-          <cell r="U143"/>
-          <cell r="V143"/>
-          <cell r="W143"/>
-          <cell r="X143"/>
-        </row>
-        <row r="144">
-          <cell r="D144"/>
-          <cell r="E144"/>
-          <cell r="F144"/>
-          <cell r="G144"/>
-          <cell r="H144"/>
-          <cell r="I144"/>
-          <cell r="J144"/>
-          <cell r="K144"/>
-          <cell r="L144"/>
-          <cell r="M144"/>
-          <cell r="N144"/>
-          <cell r="O144"/>
-          <cell r="P144"/>
-          <cell r="Q144"/>
-          <cell r="R144"/>
-          <cell r="S144"/>
-          <cell r="T144"/>
-          <cell r="U144"/>
-          <cell r="V144"/>
-          <cell r="W144"/>
-          <cell r="X144"/>
-        </row>
-        <row r="145">
-          <cell r="D145"/>
-          <cell r="E145"/>
-          <cell r="F145"/>
-          <cell r="G145"/>
-          <cell r="H145"/>
-          <cell r="I145"/>
-          <cell r="J145"/>
-          <cell r="K145"/>
-          <cell r="L145"/>
-          <cell r="M145"/>
-          <cell r="N145"/>
-          <cell r="O145"/>
-          <cell r="P145"/>
-          <cell r="Q145"/>
-          <cell r="R145"/>
-          <cell r="S145"/>
-          <cell r="T145"/>
-          <cell r="U145"/>
-          <cell r="V145"/>
-          <cell r="W145"/>
-          <cell r="X145"/>
-        </row>
-        <row r="146">
-          <cell r="D146"/>
-          <cell r="E146"/>
-          <cell r="F146"/>
-          <cell r="G146"/>
-          <cell r="H146"/>
-          <cell r="I146"/>
-          <cell r="J146"/>
-          <cell r="K146"/>
-          <cell r="L146"/>
-          <cell r="M146"/>
-          <cell r="N146"/>
-          <cell r="O146"/>
-          <cell r="P146"/>
-          <cell r="Q146"/>
-          <cell r="R146"/>
-          <cell r="S146"/>
-          <cell r="T146"/>
-          <cell r="U146"/>
-          <cell r="V146"/>
-          <cell r="W146"/>
-          <cell r="X146"/>
-        </row>
-        <row r="147">
-          <cell r="D147"/>
-          <cell r="E147"/>
-          <cell r="F147"/>
-          <cell r="G147"/>
-          <cell r="H147"/>
-          <cell r="I147"/>
-          <cell r="J147"/>
-          <cell r="K147"/>
-          <cell r="L147"/>
-          <cell r="M147"/>
-          <cell r="N147"/>
-          <cell r="O147"/>
-          <cell r="P147"/>
-          <cell r="Q147"/>
-          <cell r="R147"/>
-          <cell r="S147"/>
-          <cell r="T147"/>
-          <cell r="U147"/>
-          <cell r="V147"/>
-          <cell r="W147"/>
-          <cell r="X147"/>
-        </row>
-        <row r="148">
-          <cell r="D148"/>
-          <cell r="E148"/>
-          <cell r="F148"/>
-          <cell r="G148"/>
-          <cell r="H148"/>
-          <cell r="I148"/>
-          <cell r="J148"/>
-          <cell r="K148"/>
-          <cell r="L148"/>
-          <cell r="M148"/>
-          <cell r="N148"/>
-          <cell r="O148"/>
-          <cell r="P148"/>
-          <cell r="Q148"/>
-          <cell r="R148"/>
-          <cell r="S148"/>
-          <cell r="T148"/>
-          <cell r="U148"/>
-          <cell r="V148"/>
-          <cell r="W148"/>
-          <cell r="X148"/>
-        </row>
-        <row r="149">
-          <cell r="D149"/>
-          <cell r="E149"/>
-          <cell r="F149"/>
-          <cell r="G149"/>
-          <cell r="H149"/>
-          <cell r="I149"/>
-          <cell r="J149"/>
-          <cell r="K149"/>
-          <cell r="L149"/>
-          <cell r="M149"/>
-          <cell r="N149"/>
-          <cell r="O149"/>
-          <cell r="P149"/>
-          <cell r="Q149"/>
-          <cell r="R149"/>
-          <cell r="S149"/>
-          <cell r="T149"/>
-          <cell r="U149"/>
-          <cell r="V149"/>
-          <cell r="W149"/>
-          <cell r="X149"/>
-        </row>
-        <row r="150">
-          <cell r="D150"/>
-          <cell r="E150"/>
-          <cell r="F150"/>
-          <cell r="G150"/>
-          <cell r="H150"/>
-          <cell r="I150"/>
-          <cell r="J150"/>
-          <cell r="K150"/>
-          <cell r="L150"/>
-          <cell r="M150"/>
-          <cell r="N150"/>
-          <cell r="O150"/>
-          <cell r="P150"/>
-          <cell r="Q150"/>
-          <cell r="R150"/>
-          <cell r="S150"/>
-          <cell r="T150"/>
-          <cell r="U150"/>
-          <cell r="V150"/>
-          <cell r="W150"/>
-          <cell r="X150"/>
-        </row>
-        <row r="151">
-          <cell r="D151"/>
-          <cell r="E151"/>
-          <cell r="F151"/>
-          <cell r="G151"/>
-          <cell r="H151"/>
-          <cell r="I151"/>
-          <cell r="J151"/>
-          <cell r="K151"/>
-          <cell r="L151"/>
-          <cell r="M151"/>
-          <cell r="N151"/>
-          <cell r="O151"/>
-          <cell r="P151"/>
-          <cell r="Q151"/>
-          <cell r="R151"/>
-          <cell r="S151"/>
-          <cell r="T151"/>
-          <cell r="U151"/>
-          <cell r="V151"/>
-          <cell r="W151"/>
-          <cell r="X151"/>
-        </row>
-        <row r="152">
-          <cell r="D152"/>
-          <cell r="E152"/>
-          <cell r="F152"/>
-          <cell r="G152"/>
-          <cell r="H152"/>
-          <cell r="I152"/>
-          <cell r="J152"/>
-          <cell r="K152"/>
-          <cell r="L152"/>
-          <cell r="M152"/>
-          <cell r="N152"/>
-          <cell r="O152"/>
-          <cell r="P152"/>
-          <cell r="Q152"/>
-          <cell r="R152"/>
-          <cell r="S152"/>
-          <cell r="T152"/>
-          <cell r="U152"/>
-          <cell r="V152"/>
-          <cell r="W152"/>
-          <cell r="X152"/>
-        </row>
-        <row r="153">
-          <cell r="D153"/>
-          <cell r="E153"/>
-          <cell r="F153"/>
-          <cell r="G153"/>
-          <cell r="H153"/>
-          <cell r="I153"/>
-          <cell r="J153"/>
-          <cell r="K153"/>
-          <cell r="L153"/>
-          <cell r="M153"/>
-          <cell r="N153"/>
-          <cell r="O153"/>
-          <cell r="P153"/>
-          <cell r="Q153"/>
-          <cell r="R153"/>
-          <cell r="S153"/>
-          <cell r="T153"/>
-          <cell r="U153"/>
-          <cell r="V153"/>
-          <cell r="W153"/>
-          <cell r="X153"/>
-        </row>
-        <row r="154">
-          <cell r="D154"/>
-          <cell r="E154"/>
-          <cell r="F154"/>
-          <cell r="G154"/>
-          <cell r="H154"/>
-          <cell r="I154"/>
-          <cell r="J154"/>
-          <cell r="K154"/>
-          <cell r="L154"/>
-          <cell r="M154"/>
-          <cell r="N154"/>
-          <cell r="O154"/>
-          <cell r="P154"/>
-          <cell r="Q154"/>
-          <cell r="R154"/>
-          <cell r="S154"/>
-          <cell r="T154"/>
-          <cell r="U154"/>
-          <cell r="V154"/>
-          <cell r="W154"/>
-          <cell r="X154"/>
-        </row>
-        <row r="155">
-          <cell r="D155"/>
-          <cell r="E155"/>
-          <cell r="F155"/>
-          <cell r="G155"/>
-          <cell r="H155"/>
-          <cell r="I155"/>
-          <cell r="J155"/>
-          <cell r="K155"/>
-          <cell r="L155"/>
-          <cell r="M155"/>
-          <cell r="N155"/>
-          <cell r="O155"/>
-          <cell r="P155"/>
-          <cell r="Q155"/>
-          <cell r="R155"/>
-          <cell r="S155"/>
-          <cell r="T155"/>
-          <cell r="U155"/>
-          <cell r="V155"/>
-          <cell r="W155"/>
-          <cell r="X155"/>
-        </row>
-        <row r="156">
-          <cell r="D156"/>
-          <cell r="E156"/>
-          <cell r="F156"/>
-          <cell r="G156"/>
-          <cell r="H156"/>
-          <cell r="I156"/>
-          <cell r="J156"/>
-          <cell r="K156"/>
-          <cell r="L156"/>
-          <cell r="M156"/>
-          <cell r="N156"/>
-          <cell r="O156"/>
-          <cell r="P156"/>
-          <cell r="Q156"/>
-          <cell r="R156"/>
-          <cell r="S156"/>
-          <cell r="T156"/>
-          <cell r="U156"/>
-          <cell r="V156"/>
-          <cell r="W156"/>
-          <cell r="X156"/>
-        </row>
-        <row r="157">
-          <cell r="D157"/>
-          <cell r="E157"/>
-          <cell r="F157"/>
-          <cell r="G157"/>
-          <cell r="H157"/>
-          <cell r="I157"/>
-          <cell r="J157"/>
-          <cell r="K157"/>
-          <cell r="L157"/>
-          <cell r="M157"/>
-          <cell r="N157"/>
-          <cell r="O157"/>
-          <cell r="P157"/>
-          <cell r="Q157"/>
-          <cell r="R157"/>
-          <cell r="S157"/>
-          <cell r="T157"/>
-          <cell r="U157"/>
-          <cell r="V157"/>
-          <cell r="W157"/>
-          <cell r="X157"/>
-        </row>
-        <row r="158">
-          <cell r="D158"/>
-          <cell r="E158"/>
-          <cell r="F158"/>
-          <cell r="G158"/>
-          <cell r="H158"/>
-          <cell r="I158"/>
-          <cell r="J158"/>
-          <cell r="K158"/>
-          <cell r="L158"/>
-          <cell r="M158"/>
-          <cell r="N158"/>
-          <cell r="O158"/>
-          <cell r="P158"/>
-          <cell r="Q158"/>
-          <cell r="R158"/>
-          <cell r="S158"/>
-          <cell r="T158"/>
-          <cell r="U158"/>
-          <cell r="V158"/>
-          <cell r="W158"/>
-          <cell r="X158"/>
-        </row>
-        <row r="159">
-          <cell r="D159"/>
-          <cell r="E159"/>
-          <cell r="F159"/>
-          <cell r="G159"/>
-          <cell r="H159"/>
-          <cell r="I159"/>
-          <cell r="J159"/>
-          <cell r="K159"/>
-          <cell r="L159"/>
-          <cell r="M159"/>
-          <cell r="N159"/>
-          <cell r="O159"/>
-          <cell r="P159"/>
-          <cell r="Q159"/>
-          <cell r="R159"/>
-          <cell r="S159"/>
-          <cell r="T159"/>
-          <cell r="U159"/>
-          <cell r="V159"/>
-          <cell r="W159"/>
-          <cell r="X159"/>
-        </row>
-        <row r="160">
-          <cell r="D160"/>
-          <cell r="E160"/>
-          <cell r="F160"/>
-          <cell r="G160"/>
-          <cell r="H160"/>
-          <cell r="I160"/>
-          <cell r="J160"/>
-          <cell r="K160"/>
-          <cell r="L160"/>
-          <cell r="M160"/>
-          <cell r="N160"/>
-          <cell r="O160"/>
-          <cell r="P160"/>
-          <cell r="Q160"/>
-          <cell r="R160"/>
-          <cell r="S160"/>
-          <cell r="T160"/>
-          <cell r="U160"/>
-          <cell r="V160"/>
-          <cell r="W160"/>
-          <cell r="X160"/>
-        </row>
-        <row r="161">
-          <cell r="D161"/>
-          <cell r="E161"/>
-          <cell r="F161"/>
-          <cell r="G161"/>
-          <cell r="H161"/>
-          <cell r="I161"/>
-          <cell r="J161"/>
-          <cell r="K161"/>
-          <cell r="L161"/>
-          <cell r="M161"/>
-          <cell r="N161"/>
-          <cell r="O161"/>
-          <cell r="P161"/>
-          <cell r="Q161"/>
-          <cell r="R161"/>
-          <cell r="S161"/>
-          <cell r="T161"/>
-          <cell r="U161"/>
-          <cell r="V161"/>
-          <cell r="W161"/>
-          <cell r="X161"/>
-        </row>
-        <row r="162">
-          <cell r="D162"/>
-          <cell r="E162"/>
-          <cell r="F162"/>
-          <cell r="G162"/>
-          <cell r="H162"/>
-          <cell r="I162"/>
-          <cell r="J162"/>
-          <cell r="K162"/>
-          <cell r="L162"/>
-          <cell r="M162"/>
-          <cell r="N162"/>
-          <cell r="O162"/>
-          <cell r="P162"/>
-          <cell r="Q162"/>
-          <cell r="R162"/>
-          <cell r="S162"/>
-          <cell r="T162"/>
-          <cell r="U162"/>
-          <cell r="V162"/>
-          <cell r="W162"/>
-          <cell r="X162"/>
-        </row>
-        <row r="163">
-          <cell r="D163"/>
-          <cell r="E163"/>
-          <cell r="F163"/>
-          <cell r="G163"/>
-          <cell r="H163"/>
-          <cell r="I163"/>
-          <cell r="J163"/>
-          <cell r="K163"/>
-          <cell r="L163"/>
-          <cell r="M163"/>
-          <cell r="N163"/>
-          <cell r="O163"/>
-          <cell r="P163"/>
-          <cell r="Q163"/>
-          <cell r="R163"/>
-          <cell r="S163"/>
-          <cell r="T163"/>
-          <cell r="U163"/>
-          <cell r="V163"/>
-          <cell r="W163"/>
-          <cell r="X163"/>
-        </row>
-        <row r="164">
-          <cell r="D164"/>
-          <cell r="E164"/>
-          <cell r="F164"/>
-          <cell r="G164"/>
-          <cell r="H164"/>
-          <cell r="I164"/>
-          <cell r="J164"/>
-          <cell r="K164"/>
-          <cell r="L164"/>
-          <cell r="M164"/>
-          <cell r="N164"/>
-          <cell r="O164"/>
-          <cell r="P164"/>
-          <cell r="Q164"/>
-          <cell r="R164"/>
-          <cell r="S164"/>
-          <cell r="T164"/>
-          <cell r="U164"/>
-          <cell r="V164"/>
-          <cell r="W164"/>
-          <cell r="X164"/>
-        </row>
-        <row r="165">
-          <cell r="D165"/>
-          <cell r="E165"/>
-          <cell r="F165"/>
-          <cell r="G165"/>
-          <cell r="H165"/>
-          <cell r="I165"/>
-          <cell r="J165"/>
-          <cell r="K165"/>
-          <cell r="L165"/>
-          <cell r="M165"/>
-          <cell r="N165"/>
-          <cell r="O165"/>
-          <cell r="P165"/>
-          <cell r="Q165"/>
-          <cell r="R165"/>
-          <cell r="S165"/>
-          <cell r="T165"/>
-          <cell r="U165"/>
-          <cell r="V165"/>
-          <cell r="W165"/>
-          <cell r="X165"/>
-        </row>
-        <row r="166">
-          <cell r="D166"/>
-          <cell r="E166"/>
-          <cell r="F166"/>
-          <cell r="G166"/>
-          <cell r="H166"/>
-          <cell r="I166"/>
-          <cell r="J166"/>
-          <cell r="K166"/>
-          <cell r="L166"/>
-          <cell r="M166"/>
-          <cell r="N166"/>
-          <cell r="O166"/>
-          <cell r="P166"/>
-          <cell r="Q166"/>
-          <cell r="R166"/>
-          <cell r="S166"/>
-          <cell r="T166"/>
-          <cell r="U166"/>
-          <cell r="V166"/>
-          <cell r="W166"/>
-          <cell r="X166"/>
-        </row>
-        <row r="167">
-          <cell r="D167"/>
-          <cell r="E167"/>
-          <cell r="F167"/>
-          <cell r="G167"/>
-          <cell r="H167"/>
-          <cell r="I167"/>
-          <cell r="J167"/>
-          <cell r="K167"/>
-          <cell r="L167"/>
-          <cell r="M167"/>
-          <cell r="N167"/>
-          <cell r="O167"/>
-          <cell r="P167"/>
-          <cell r="Q167"/>
-          <cell r="R167"/>
-          <cell r="S167"/>
-          <cell r="T167"/>
-          <cell r="U167"/>
-          <cell r="V167"/>
-          <cell r="W167"/>
-          <cell r="X167"/>
-        </row>
-        <row r="168">
-          <cell r="D168"/>
-          <cell r="E168"/>
-          <cell r="F168"/>
-          <cell r="G168"/>
-          <cell r="H168"/>
-          <cell r="I168"/>
-          <cell r="J168"/>
-          <cell r="K168"/>
-          <cell r="L168"/>
-          <cell r="M168"/>
-          <cell r="N168"/>
-          <cell r="O168"/>
-          <cell r="P168"/>
-          <cell r="Q168"/>
-          <cell r="R168"/>
-          <cell r="S168"/>
-          <cell r="T168"/>
-          <cell r="U168"/>
-          <cell r="V168"/>
-          <cell r="W168"/>
-          <cell r="X168"/>
-        </row>
-        <row r="169">
-          <cell r="D169"/>
-          <cell r="E169"/>
-          <cell r="F169"/>
-          <cell r="G169"/>
-          <cell r="H169"/>
-          <cell r="I169"/>
-          <cell r="J169"/>
-          <cell r="K169"/>
-          <cell r="L169"/>
-          <cell r="M169"/>
-          <cell r="N169"/>
-          <cell r="O169"/>
-          <cell r="P169"/>
-          <cell r="Q169"/>
-          <cell r="R169"/>
-          <cell r="S169"/>
-          <cell r="T169"/>
-          <cell r="U169"/>
-          <cell r="V169"/>
-          <cell r="W169"/>
-          <cell r="X169"/>
-        </row>
-        <row r="170">
-          <cell r="D170"/>
-          <cell r="E170"/>
-          <cell r="F170"/>
-          <cell r="G170"/>
-          <cell r="H170"/>
-          <cell r="I170"/>
-          <cell r="J170"/>
-          <cell r="K170"/>
-          <cell r="L170"/>
-          <cell r="M170"/>
-          <cell r="N170"/>
-          <cell r="O170"/>
-          <cell r="P170"/>
-          <cell r="Q170"/>
-          <cell r="R170"/>
-          <cell r="S170"/>
-          <cell r="T170"/>
-          <cell r="U170"/>
-          <cell r="V170"/>
-          <cell r="W170"/>
-          <cell r="X170"/>
-        </row>
-        <row r="171">
-          <cell r="D171"/>
-          <cell r="E171"/>
-          <cell r="F171"/>
-          <cell r="G171"/>
-          <cell r="H171"/>
-          <cell r="I171"/>
-          <cell r="J171"/>
-          <cell r="K171"/>
-          <cell r="L171"/>
-          <cell r="M171"/>
-          <cell r="N171"/>
-          <cell r="O171"/>
-          <cell r="P171"/>
-          <cell r="Q171"/>
-          <cell r="R171"/>
-          <cell r="S171"/>
-          <cell r="T171"/>
-          <cell r="U171"/>
-          <cell r="V171"/>
-          <cell r="W171"/>
-          <cell r="X171"/>
-        </row>
-        <row r="172">
-          <cell r="D172"/>
-          <cell r="E172"/>
-          <cell r="F172"/>
-          <cell r="G172"/>
-          <cell r="H172"/>
-          <cell r="I172"/>
-          <cell r="J172"/>
-          <cell r="K172"/>
-          <cell r="L172"/>
-          <cell r="M172"/>
-          <cell r="N172"/>
-          <cell r="O172"/>
-          <cell r="P172"/>
-          <cell r="Q172"/>
-          <cell r="R172"/>
-          <cell r="S172"/>
-          <cell r="T172"/>
-          <cell r="U172"/>
-          <cell r="V172"/>
-          <cell r="W172"/>
-          <cell r="X172"/>
-        </row>
-        <row r="173">
-          <cell r="D173"/>
-          <cell r="E173"/>
-          <cell r="F173"/>
-          <cell r="G173"/>
-          <cell r="H173"/>
-          <cell r="I173"/>
-          <cell r="J173"/>
-          <cell r="K173"/>
-          <cell r="L173"/>
-          <cell r="M173"/>
-          <cell r="N173"/>
-          <cell r="O173"/>
-          <cell r="P173"/>
-          <cell r="Q173"/>
-          <cell r="R173"/>
-          <cell r="S173"/>
-          <cell r="T173"/>
-          <cell r="U173"/>
-          <cell r="V173"/>
-          <cell r="W173"/>
-          <cell r="X173"/>
-        </row>
-        <row r="174">
-          <cell r="D174"/>
-          <cell r="E174"/>
-          <cell r="F174"/>
-          <cell r="G174"/>
-          <cell r="H174"/>
-          <cell r="I174"/>
-          <cell r="J174"/>
-          <cell r="K174"/>
-          <cell r="L174"/>
-          <cell r="M174"/>
-          <cell r="N174"/>
-          <cell r="O174"/>
-          <cell r="P174"/>
-          <cell r="Q174"/>
-          <cell r="R174"/>
-          <cell r="S174"/>
-          <cell r="T174"/>
-          <cell r="U174"/>
-          <cell r="V174"/>
-          <cell r="W174"/>
-          <cell r="X174"/>
-        </row>
-        <row r="175">
-          <cell r="D175"/>
-          <cell r="E175"/>
-          <cell r="F175"/>
-          <cell r="G175"/>
-          <cell r="H175"/>
-          <cell r="I175"/>
-          <cell r="J175"/>
-          <cell r="K175"/>
-          <cell r="L175"/>
-          <cell r="M175"/>
-          <cell r="N175"/>
-          <cell r="O175"/>
-          <cell r="P175"/>
-          <cell r="Q175"/>
-          <cell r="R175"/>
-          <cell r="S175"/>
-          <cell r="T175"/>
-          <cell r="U175"/>
-          <cell r="V175"/>
-          <cell r="W175"/>
-          <cell r="X175"/>
-        </row>
-        <row r="176">
-          <cell r="D176"/>
-          <cell r="E176"/>
-          <cell r="F176"/>
-          <cell r="G176"/>
-          <cell r="H176"/>
-          <cell r="I176"/>
-          <cell r="J176"/>
-          <cell r="K176"/>
-          <cell r="L176"/>
-          <cell r="M176"/>
-          <cell r="N176"/>
-          <cell r="O176"/>
-          <cell r="P176"/>
-          <cell r="Q176"/>
-          <cell r="R176"/>
-          <cell r="S176"/>
-          <cell r="T176"/>
-          <cell r="U176"/>
-          <cell r="V176"/>
-          <cell r="W176"/>
-          <cell r="X176"/>
-        </row>
-        <row r="177">
-          <cell r="D177"/>
-          <cell r="E177"/>
-          <cell r="F177"/>
-          <cell r="G177"/>
-          <cell r="H177"/>
-          <cell r="I177"/>
-          <cell r="J177"/>
-          <cell r="K177"/>
-          <cell r="L177"/>
-          <cell r="M177"/>
-          <cell r="N177"/>
-          <cell r="O177"/>
-          <cell r="P177"/>
-          <cell r="Q177"/>
-          <cell r="R177"/>
-          <cell r="S177"/>
-          <cell r="T177"/>
-          <cell r="U177"/>
-          <cell r="V177"/>
-          <cell r="W177"/>
-          <cell r="X177"/>
-        </row>
-        <row r="178">
-          <cell r="D178"/>
-          <cell r="E178"/>
-          <cell r="F178"/>
-          <cell r="G178"/>
-          <cell r="H178"/>
-          <cell r="I178"/>
-          <cell r="J178"/>
-          <cell r="K178"/>
-          <cell r="L178"/>
-          <cell r="M178"/>
-          <cell r="N178"/>
-          <cell r="O178"/>
-          <cell r="P178"/>
-          <cell r="Q178"/>
-          <cell r="R178"/>
-          <cell r="S178"/>
-          <cell r="T178"/>
-          <cell r="U178"/>
-          <cell r="V178"/>
-          <cell r="W178"/>
-          <cell r="X178"/>
-        </row>
-        <row r="179">
-          <cell r="D179"/>
-          <cell r="E179"/>
-          <cell r="F179"/>
-          <cell r="G179"/>
-          <cell r="H179"/>
-          <cell r="I179"/>
-          <cell r="J179"/>
-          <cell r="K179"/>
-          <cell r="L179"/>
-          <cell r="M179"/>
-          <cell r="N179"/>
-          <cell r="O179"/>
-          <cell r="P179"/>
-          <cell r="Q179"/>
-          <cell r="R179"/>
-          <cell r="S179"/>
-          <cell r="T179"/>
-          <cell r="U179"/>
-          <cell r="V179"/>
-          <cell r="W179"/>
-          <cell r="X179"/>
-        </row>
-        <row r="180">
-          <cell r="D180"/>
-          <cell r="E180"/>
-          <cell r="F180"/>
-          <cell r="G180"/>
-          <cell r="H180"/>
-          <cell r="I180"/>
-          <cell r="J180"/>
-          <cell r="K180"/>
-          <cell r="L180"/>
-          <cell r="M180"/>
-          <cell r="N180"/>
-          <cell r="O180"/>
-          <cell r="P180"/>
-          <cell r="Q180"/>
-          <cell r="R180"/>
-          <cell r="S180"/>
-          <cell r="T180"/>
-          <cell r="U180"/>
-          <cell r="V180"/>
-          <cell r="W180"/>
-          <cell r="X180"/>
-        </row>
-        <row r="181">
-          <cell r="D181"/>
-          <cell r="E181"/>
-          <cell r="F181"/>
-          <cell r="G181"/>
-          <cell r="H181"/>
-          <cell r="I181"/>
-          <cell r="J181"/>
-          <cell r="K181"/>
-          <cell r="L181"/>
-          <cell r="M181"/>
-          <cell r="N181"/>
-          <cell r="O181"/>
-          <cell r="P181"/>
-          <cell r="Q181"/>
-          <cell r="R181"/>
-          <cell r="S181"/>
-          <cell r="T181"/>
-          <cell r="U181"/>
-          <cell r="V181"/>
-          <cell r="W181"/>
-          <cell r="X181"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -22408,7 +18636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2A118F-D7F3-5348-BECB-A41992F5CAD2}">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -22418,10 +18646,10 @@
     <col min="5" max="5" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="8" max="12" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>373</v>
       </c>
@@ -22453,13 +18681,16 @@
         <v>392</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>9</v>
       </c>
@@ -22498,15 +18729,16 @@
       <c r="J2" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5"/>
+      <c r="L2" s="9">
         <f>IF(J2="Yes",(H2*1500)/100,0)</f>
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -22532,7 +18764,7 @@
       </c>
       <c r="G3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.44652162262184469</v>
+        <v>0.44652162262184492</v>
       </c>
       <c r="H3" s="7">
         <f>VLOOKUP(A3,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -22545,12 +18777,13 @@
       <c r="J3" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K3" s="9">
-        <f t="shared" ref="K3" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K3" s="5"/>
+      <c r="L3" s="9">
+        <f t="shared" ref="L3" si="1">IF(J3="Yes",(H3*1500)/100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -22568,11 +18801,11 @@
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>5.5829743724806304</v>
+        <v>5.257974372480632</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,9,FALSE)</f>
@@ -22584,17 +18817,18 @@
       </c>
       <c r="I4" s="7">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>3.0921013343042949E-2</v>
+        <v>3.2949466586826175E-2</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K4" s="9">
-        <f t="shared" ref="K4:K9" si="3">IF(J4="Yes",(H4*1500)/100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K4" s="5"/>
+      <c r="L4" s="9">
+        <f t="shared" ref="L4:L9" si="3">IF(J4="Yes",(H4*1500)/100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -22633,12 +18867,13 @@
       <c r="J5" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="5"/>
+      <c r="L5" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -22677,12 +18912,13 @@
       <c r="J6" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="5"/>
+      <c r="L6" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>14</v>
       </c>
@@ -22700,7 +18936,7 @@
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>0.5490944982080217</v>
+        <v>0.54909449820802081</v>
       </c>
       <c r="F7" s="5">
         <f>-VLOOKUP(A7,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -22708,7 +18944,7 @@
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.28694196100801311</v>
+        <v>0.28694196100801289</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -22721,12 +18957,13 @@
       <c r="J7" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="5"/>
+      <c r="L7" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>15</v>
       </c>
@@ -22765,12 +19002,15 @@
       <c r="J8" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="5">
+        <v>-111</v>
+      </c>
+      <c r="L8" s="9">
         <f t="shared" si="3"/>
         <v>0.7154130030427841</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -22809,12 +19049,13 @@
       <c r="J9" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="5"/>
+      <c r="L9" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -22824,9 +19065,10 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K10" s="5"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -22836,9 +19078,10 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K11" s="5"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -22848,9 +19091,10 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K12" s="5"/>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -22860,9 +19104,10 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K13" s="5"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -22872,9 +19117,10 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K14" s="5"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -22884,9 +19130,10 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K15" s="5"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -22896,9 +19143,10 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K16" s="5"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -22908,9 +19156,10 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="5"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -22920,9 +19169,10 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="8"/>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="5"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -22932,9 +19182,10 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K19" s="5"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -22944,9 +19195,10 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="5"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -22956,9 +19208,10 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="5"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -22968,9 +19221,10 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="5"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -22980,9 +19234,10 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="8"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="5"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -22992,9 +19247,10 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="5"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -23004,9 +19260,10 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="9"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="5"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -23016,9 +19273,10 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="9"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="5"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -23028,9 +19286,10 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
-      <c r="K27" s="9"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="5"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -23040,9 +19299,10 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="5"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -23052,9 +19312,10 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
-      <c r="K29" s="9"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="5"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -23064,9 +19325,10 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="5"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -23076,9 +19338,10 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="8"/>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="5"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -23088,9 +19351,10 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="5"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -23100,9 +19364,10 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
-      <c r="K33" s="9"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="5"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -23112,9 +19377,10 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="5"/>
+      <c r="L34" s="9"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -23124,9 +19390,10 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="8"/>
-      <c r="K35" s="9"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="5"/>
+      <c r="L35" s="9"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -23136,9 +19403,10 @@
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="9"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K36" s="5"/>
+      <c r="L36" s="9"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -23148,7 +19416,8 @@
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="8"/>
-      <c r="K37" s="9"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0352D0-A2A8-2343-9AD1-C3E281D15A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D336FB-0D04-A242-871A-AFB49472DAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="20680" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="40" yWindow="780" windowWidth="20680" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -1609,7 +1609,7 @@
             <v>Illinois</v>
           </cell>
           <cell r="E2">
-            <v>5.7742945023488783</v>
+            <v>5.7742945023488801</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
@@ -1673,7 +1673,7 @@
             <v>Iowa</v>
           </cell>
           <cell r="E4">
-            <v>5.257974372480632</v>
+            <v>5.2579743724806303</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
@@ -1720,7 +1720,7 @@
             <v>7.0377160039100772E-2</v>
           </cell>
           <cell r="J5">
-            <v>0.43952016208204348</v>
+            <v>0.43952016208204359</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1769,19 +1769,19 @@
             <v>Tennessee</v>
           </cell>
           <cell r="E7">
-            <v>6.1693961042649592</v>
+            <v>6.4943961042649594</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.55392620988041141</v>
+            <v>0.54959958222770045</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>5.7495491589876317E-2</v>
+            <v>4.9235566071064552E-2</v>
           </cell>
           <cell r="J7">
             <v>0.32440678103529158</v>
@@ -1880,7 +1880,7 @@
             <v>-2.6286001098113469E-2</v>
           </cell>
           <cell r="J10">
-            <v>5.9410701506423469E-2</v>
+            <v>5.941070150642358E-2</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1897,7 +1897,7 @@
             <v>Arizona</v>
           </cell>
           <cell r="E11">
-            <v>-7.8495794140245847</v>
+            <v>-7.8495794140245838</v>
           </cell>
           <cell r="F11" t="b">
             <v>0</v>
@@ -1912,7 +1912,7 @@
             <v>-3.8294470453995699E-2</v>
           </cell>
           <cell r="J11">
-            <v>0.2420191120804065</v>
+            <v>0.24201911208040641</v>
           </cell>
           <cell r="K11">
             <v>0</v>
@@ -1944,7 +1944,7 @@
             <v>7.9228918602623488E-2</v>
           </cell>
           <cell r="J12">
-            <v>0.19277136123939681</v>
+            <v>0.1927713612393967</v>
           </cell>
           <cell r="K12">
             <v>0</v>
@@ -2025,25 +2025,25 @@
             <v>Iowa State</v>
           </cell>
           <cell r="E15">
-            <v>0.54909449820802081</v>
+            <v>0.22409449820802149</v>
           </cell>
           <cell r="F15" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G15">
-            <v>0.61191680905930845</v>
+            <v>0.61610080122619892</v>
           </cell>
           <cell r="H15">
-            <v>0</v>
+            <v>4.7524673030007021E-2</v>
           </cell>
           <cell r="I15">
-            <v>0.16820481729504341</v>
+            <v>0.17619243870456161</v>
           </cell>
           <cell r="J15">
-            <v>0.28694196100801289</v>
+            <v>0.28694196100801311</v>
           </cell>
           <cell r="K15">
-            <v>0</v>
+            <v>0.92768161754573708</v>
           </cell>
         </row>
         <row r="16">
@@ -9126,7 +9126,7 @@
             <v>0</v>
           </cell>
           <cell r="X7">
-            <v>-4</v>
+            <v>-4.5</v>
           </cell>
         </row>
         <row r="8">
@@ -9718,7 +9718,7 @@
             <v>0</v>
           </cell>
           <cell r="X15">
-            <v>4</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="16">
@@ -18309,7 +18309,13 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="12">
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>McNeese</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
@@ -18716,7 +18722,7 @@
       </c>
       <c r="G2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>5.9410701506423469E-2</v>
+        <v>5.941070150642358E-2</v>
       </c>
       <c r="H2" s="7">
         <f>VLOOKUP(A2,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -18801,7 +18807,7 @@
       </c>
       <c r="E4" s="5">
         <f>VLOOKUP(A4,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>5.257974372480632</v>
+        <v>5.2579743724806303</v>
       </c>
       <c r="F4" s="5">
         <f>-VLOOKUP(A4,[2]Games!$A$2:$X$284,24,FALSE)</f>
@@ -18854,7 +18860,7 @@
       </c>
       <c r="G5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.43952016208204348</v>
+        <v>0.43952016208204359</v>
       </c>
       <c r="H5" s="7">
         <f>VLOOKUP(A5,[1]Games!$B$2:$K$398,7,FALSE)</f>
@@ -18936,31 +18942,32 @@
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,4,FALSE)</f>
-        <v>0.54909449820802081</v>
+        <v>0.22409449820802149</v>
       </c>
       <c r="F7" s="5">
-        <f>-VLOOKUP(A7,[2]Games!$A$2:$X$284,24,FALSE)</f>
         <v>-4</v>
       </c>
       <c r="G7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,9,FALSE)</f>
-        <v>0.28694196100801289</v>
+        <v>0.28694196100801311</v>
       </c>
       <c r="H7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,7,FALSE)</f>
-        <v>0</v>
+        <v>4.7524673030007021E-2</v>
       </c>
       <c r="I7" s="7">
         <f>VLOOKUP(A7,[1]Games!$B$2:$K$398,8,FALSE)/4</f>
-        <v>4.2051204323760853E-2</v>
+        <v>4.4048109676140403E-2</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="K7" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="K7" s="5">
+        <v>-111</v>
+      </c>
       <c r="L7" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.71287009545010538</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -19472,8 +19479,8 @@
         <v>8</v>
       </c>
       <c r="C2" s="12">
-        <f>SUM(F6:F25)/SUM(E6:E25)</f>
-        <v>0.11202337575793919</v>
+        <f>SUM(F6:F26)/SUM(E6:E26)</f>
+        <v>0.15083707192796833</v>
       </c>
       <c r="D2" s="13">
         <f>AVERAGE(H6:H150)</f>
@@ -20921,7 +20928,7 @@
         <v>1.111</v>
       </c>
       <c r="F2" s="1">
-        <v>475</v>
+        <v>345</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>413</v>
@@ -20951,7 +20958,7 @@
         <v>1.58</v>
       </c>
       <c r="F3" s="1">
-        <v>6000</v>
+        <v>3619</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>413</v>
@@ -20981,7 +20988,7 @@
         <v>0.45</v>
       </c>
       <c r="F4" s="1">
-        <v>1800</v>
+        <v>1455</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>413</v>
@@ -21044,7 +21051,7 @@
         <v>0.85</v>
       </c>
       <c r="F6" s="1">
-        <v>816</v>
+        <v>468</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>413</v>
@@ -21074,7 +21081,7 @@
         <v>0.45</v>
       </c>
       <c r="F7" s="1">
-        <v>1725</v>
+        <v>698</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>413</v>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D336FB-0D04-A242-871A-AFB49472DAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D410358C-821F-3E46-ABDC-663B959C1F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="780" windowWidth="20680" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="220" yWindow="780" windowWidth="17860" windowHeight="19940" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="465">
   <si>
     <t>Team</t>
   </si>
@@ -1603,28 +1603,28 @@
             <v>1</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Houston</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D2" t="str">
-            <v>Illinois</v>
+            <v>Iowa</v>
           </cell>
           <cell r="E2">
-            <v>5.7742945023488801</v>
+            <v>8.4421231024287486</v>
           </cell>
           <cell r="F2" t="b">
             <v>0</v>
           </cell>
           <cell r="G2">
-            <v>0.56882889622899346</v>
+            <v>0.53590911551584863</v>
           </cell>
           <cell r="H2">
             <v>0</v>
           </cell>
           <cell r="I2">
-            <v>8.5946074618987622E-2</v>
+            <v>2.309922053025654E-2</v>
           </cell>
           <cell r="J2">
-            <v>0.34694764321218979</v>
+            <v>0.35292010839599519</v>
           </cell>
           <cell r="K2">
             <v>0</v>
@@ -1638,25 +1638,25 @@
             <v>Arizona</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Arkansas</v>
+            <v>Purdue</v>
           </cell>
           <cell r="E3">
-            <v>10.17544759009586</v>
+            <v>7.8873391448450363</v>
           </cell>
           <cell r="F3" t="b">
             <v>0</v>
           </cell>
           <cell r="G3">
-            <v>0.55407571254869992</v>
+            <v>0.54694980764634271</v>
           </cell>
           <cell r="H3">
             <v>0</v>
           </cell>
           <cell r="I3">
-            <v>5.7780905774790781E-2</v>
+            <v>4.4176905506654318E-2</v>
           </cell>
           <cell r="J3">
-            <v>0.44652162262184492</v>
+            <v>0.36128474795445259</v>
           </cell>
           <cell r="K3">
             <v>0</v>
@@ -1667,28 +1667,28 @@
             <v>3</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Nebraska</v>
+            <v>Duke</v>
           </cell>
           <cell r="D4" t="str">
-            <v>Iowa</v>
+            <v>St. John's</v>
           </cell>
           <cell r="E4">
-            <v>5.2579743724806303</v>
+            <v>10.90062402757979</v>
           </cell>
           <cell r="F4" t="b">
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0.59284650142001671</v>
+            <v>0.60226039075025728</v>
           </cell>
           <cell r="H4">
             <v>0</v>
           </cell>
           <cell r="I4">
-            <v>0.1317978663473047</v>
+            <v>0.14976983688685491</v>
           </cell>
           <cell r="J4">
-            <v>0.38710225177014629</v>
+            <v>0.57242552718101847</v>
           </cell>
           <cell r="K4">
             <v>0</v>
@@ -1699,28 +1699,28 @@
             <v>4</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Purdue</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D5" t="str">
-            <v>Texas</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="E5">
-            <v>9.442842152691437</v>
+            <v>6.4943961042649594</v>
           </cell>
           <cell r="F5" t="b">
             <v>0</v>
           </cell>
           <cell r="G5">
-            <v>0.56067375049667179</v>
+            <v>0.54959958222770045</v>
           </cell>
           <cell r="H5">
             <v>0</v>
           </cell>
           <cell r="I5">
-            <v>7.0377160039100772E-2</v>
+            <v>4.9235566071064552E-2</v>
           </cell>
           <cell r="J5">
-            <v>0.43952016208204359</v>
+            <v>0.32440678103529158</v>
           </cell>
           <cell r="K5">
             <v>0</v>
@@ -1731,28 +1731,28 @@
             <v>5</v>
           </cell>
           <cell r="C6" t="str">
-            <v>Duke</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D6" t="str">
-            <v>St. John's</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="E6">
-            <v>10.90062402757979</v>
+            <v>1.153376885695232</v>
           </cell>
           <cell r="F6" t="b">
             <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0.60226039075025728</v>
+            <v>0.52109976312859441</v>
           </cell>
           <cell r="H6">
             <v>0</v>
           </cell>
           <cell r="I6">
-            <v>0.14976983688685491</v>
+            <v>-5.1731794817742593E-3</v>
           </cell>
           <cell r="J6">
-            <v>0.57242552718101847</v>
+            <v>1.3461591133435419E-2</v>
           </cell>
           <cell r="K6">
             <v>0</v>
@@ -1763,28 +1763,28 @@
             <v>6</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Iowa State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D7" t="str">
-            <v>Tennessee</v>
+            <v>Alabama</v>
           </cell>
           <cell r="E7">
-            <v>6.4943961042649594</v>
+            <v>10.34576138869893</v>
           </cell>
           <cell r="F7" t="b">
             <v>0</v>
           </cell>
           <cell r="G7">
-            <v>0.54959958222770045</v>
+            <v>0.53351554751848562</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>4.9235566071064552E-2</v>
+            <v>1.852968162619989E-2</v>
           </cell>
           <cell r="J7">
-            <v>0.32440678103529158</v>
+            <v>0.4055283806319735</v>
           </cell>
           <cell r="K7">
             <v>0</v>
@@ -1795,28 +1795,28 @@
             <v>7</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Uconn</v>
+            <v>Iowa</v>
           </cell>
           <cell r="D8" t="str">
-            <v>Michigan State</v>
+            <v>Illinois</v>
           </cell>
           <cell r="E8">
-            <v>1.153376885695232</v>
+            <v>-5.2914917827182704</v>
           </cell>
           <cell r="F8" t="b">
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0.52109976312859441</v>
+            <v>0.54251894234960674</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>-5.1731794817742593E-3</v>
+            <v>3.5717980849249258E-2</v>
           </cell>
           <cell r="J8">
-            <v>1.3461591133435419E-2</v>
+            <v>6.8053575495246432E-2</v>
           </cell>
           <cell r="K8">
             <v>0</v>
@@ -1827,28 +1827,28 @@
             <v>8</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Michigan</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D9" t="str">
-            <v>Alabama</v>
+            <v>Arizona</v>
           </cell>
           <cell r="E9">
-            <v>10.995761388698931</v>
+            <v>-4.2845034550100038</v>
           </cell>
           <cell r="F9" t="b">
             <v>0</v>
           </cell>
           <cell r="G9">
-            <v>0.52481218929335105</v>
+            <v>0.54269219393462931</v>
           </cell>
           <cell r="H9">
             <v>0</v>
           </cell>
           <cell r="I9">
-            <v>1.914179560033868E-3</v>
+            <v>3.6048733875201473E-2</v>
           </cell>
           <cell r="J9">
-            <v>0.4055283806319735</v>
+            <v>3.529870472828367E-2</v>
           </cell>
           <cell r="K9">
             <v>0</v>
@@ -1859,28 +1859,28 @@
             <v>9</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Illinois</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D10" t="str">
-            <v>Houston</v>
+            <v>Duke</v>
           </cell>
           <cell r="E10">
-            <v>-2.5972659968097491</v>
+            <v>-5.7074469950208462</v>
           </cell>
           <cell r="F10" t="b">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0.51004066609146437</v>
+            <v>0.51975335307188941</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>-2.6286001098113469E-2</v>
+            <v>-7.7435986809383786E-3</v>
           </cell>
           <cell r="J10">
-            <v>5.941070150642358E-2</v>
+            <v>0.1359058509226507</v>
           </cell>
           <cell r="K10">
             <v>0</v>
@@ -1891,31 +1891,31 @@
             <v>10</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Texas</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D11" t="str">
-            <v>Arizona</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="E11">
-            <v>-7.8495794140245838</v>
+            <v>0.22409449820802241</v>
           </cell>
           <cell r="F11" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G11">
-            <v>0.50375051547647842</v>
+            <v>0.61610080122619892</v>
           </cell>
           <cell r="H11">
-            <v>0</v>
+            <v>4.7524673030007021E-2</v>
           </cell>
           <cell r="I11">
-            <v>-3.8294470453995699E-2</v>
+            <v>0.17619243870456161</v>
           </cell>
           <cell r="J11">
-            <v>0.24201911208040641</v>
+            <v>0.28694196100801322</v>
           </cell>
           <cell r="K11">
-            <v>0</v>
+            <v>0.92768161754573708</v>
           </cell>
         </row>
         <row r="12">
@@ -1923,31 +1923,31 @@
             <v>11</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Iowa</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D12" t="str">
-            <v>Nebraska</v>
+            <v>Uconn</v>
           </cell>
           <cell r="E12">
-            <v>1.131152779980455</v>
+            <v>2.732549893009701</v>
           </cell>
           <cell r="F12" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G12">
-            <v>0.5653103859347075</v>
+            <v>0.61630261928910979</v>
           </cell>
           <cell r="H12">
-            <v>0</v>
+            <v>4.7694200202852269E-2</v>
           </cell>
           <cell r="I12">
-            <v>7.9228918602623488E-2</v>
+            <v>0.1765777277337551</v>
           </cell>
           <cell r="J12">
-            <v>0.1927713612393967</v>
+            <v>0.36524831529047608</v>
           </cell>
           <cell r="K12">
-            <v>0</v>
+            <v>0.93099078795967627</v>
           </cell>
         </row>
         <row r="13">
@@ -1955,28 +1955,28 @@
             <v>12</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Arkansas</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Purdue</v>
+            <v>Michigan</v>
           </cell>
           <cell r="E13">
-            <v>-4.5363947236177697</v>
+            <v>-2.8153323246158468</v>
           </cell>
           <cell r="F13" t="b">
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0.56118540620989066</v>
+            <v>0.54192783738377759</v>
           </cell>
           <cell r="H13">
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>7.1353957309791327E-2</v>
+            <v>3.4589507732666343E-2</v>
           </cell>
           <cell r="J13">
-            <v>1.249128979806335E-3</v>
+            <v>1.00687426971065E-2</v>
           </cell>
           <cell r="K13">
             <v>0</v>
@@ -1986,29 +1986,23 @@
           <cell r="B14">
             <v>13</v>
           </cell>
-          <cell r="C14" t="str">
-            <v>St. John's</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>Duke</v>
-          </cell>
           <cell r="E14">
-            <v>-5.7074469950208462</v>
-          </cell>
-          <cell r="F14" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F14">
             <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0.51975335307188941</v>
+            <v>0</v>
           </cell>
           <cell r="H14">
             <v>0</v>
           </cell>
           <cell r="I14">
-            <v>-7.7435986809383786E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J14">
-            <v>0.13590585092265101</v>
+            <v>0</v>
           </cell>
           <cell r="K14">
             <v>0</v>
@@ -2018,93 +2012,75 @@
           <cell r="B15">
             <v>14</v>
           </cell>
-          <cell r="C15" t="str">
-            <v>Tennessee</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>Iowa State</v>
-          </cell>
           <cell r="E15">
-            <v>0.22409449820802149</v>
-          </cell>
-          <cell r="F15" t="b">
-            <v>1</v>
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>0</v>
           </cell>
           <cell r="G15">
-            <v>0.61610080122619892</v>
+            <v>0</v>
           </cell>
           <cell r="H15">
-            <v>4.7524673030007021E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I15">
-            <v>0.17619243870456161</v>
+            <v>0</v>
           </cell>
           <cell r="J15">
-            <v>0.28694196100801311</v>
+            <v>0</v>
           </cell>
           <cell r="K15">
-            <v>0.92768161754573708</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16">
             <v>15</v>
           </cell>
-          <cell r="C16" t="str">
-            <v>Michigan State</v>
-          </cell>
-          <cell r="D16" t="str">
-            <v>Uconn</v>
-          </cell>
           <cell r="E16">
-            <v>2.732549893009701</v>
-          </cell>
-          <cell r="F16" t="b">
-            <v>1</v>
+            <v>0</v>
+          </cell>
+          <cell r="F16">
+            <v>0</v>
           </cell>
           <cell r="G16">
-            <v>0.61630261928910979</v>
+            <v>0</v>
           </cell>
           <cell r="H16">
-            <v>4.7694200202852269E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I16">
-            <v>0.1765777277337551</v>
+            <v>0</v>
           </cell>
           <cell r="J16">
-            <v>0.36524831529047608</v>
+            <v>0</v>
           </cell>
           <cell r="K16">
-            <v>0.93099078795967627</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17">
             <v>16</v>
           </cell>
-          <cell r="C17" t="str">
-            <v>Alabama</v>
-          </cell>
-          <cell r="D17" t="str">
-            <v>Michigan</v>
-          </cell>
           <cell r="E17">
-            <v>-6.390332324615847</v>
-          </cell>
-          <cell r="F17" t="b">
+            <v>0</v>
+          </cell>
+          <cell r="F17">
             <v>0</v>
           </cell>
           <cell r="G17">
-            <v>0.58924537458598858</v>
+            <v>0</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>0.1249229878459782</v>
+            <v>0</v>
           </cell>
           <cell r="J17">
-            <v>1.00687426971065E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K17">
             <v>0</v>
@@ -8690,73 +8666,73 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>Houston</v>
+            <v>Illinois</v>
           </cell>
           <cell r="C2" t="str">
-            <v>Illinois</v>
+            <v>Iowa</v>
           </cell>
           <cell r="D2">
-            <v>20.908506008479332</v>
+            <v>18.836157720404749</v>
           </cell>
           <cell r="E2">
-            <v>105.43571389837862</v>
+            <v>105.08780903665816</v>
           </cell>
           <cell r="F2">
-            <v>97.099609428307105</v>
+            <v>108.93352999987511</v>
           </cell>
           <cell r="G2">
-            <v>0.52154080081094778</v>
+            <v>0.5511688311688312</v>
           </cell>
           <cell r="H2">
-            <v>64.762500000000003</v>
+            <v>66.809032258064519</v>
           </cell>
           <cell r="I2">
-            <v>61.65625</v>
+            <v>62.096774193548384</v>
           </cell>
           <cell r="J2">
-            <v>16.71875</v>
+            <v>20.387096774193548</v>
           </cell>
           <cell r="K2">
-            <v>12.78125</v>
+            <v>13.258064516129032</v>
           </cell>
           <cell r="L2">
-            <v>8.53125</v>
+            <v>9</v>
           </cell>
           <cell r="M2">
             <v>0</v>
           </cell>
           <cell r="N2">
-            <v>18.836157720404749</v>
+            <v>15.533956620207105</v>
           </cell>
           <cell r="O2">
-            <v>105.08780903665816</v>
+            <v>98.238539943433466</v>
           </cell>
           <cell r="P2">
-            <v>108.93352999987511</v>
+            <v>93.183243223384508</v>
           </cell>
           <cell r="Q2">
-            <v>0.5511688311688312</v>
+            <v>0.56555993247045577</v>
           </cell>
           <cell r="R2">
-            <v>66.809032258064519</v>
+            <v>62.900606060606066</v>
           </cell>
           <cell r="S2">
-            <v>62.096774193548384</v>
+            <v>53.848484848484851</v>
           </cell>
           <cell r="T2">
-            <v>20.387096774193548</v>
+            <v>18.575757575757574</v>
           </cell>
           <cell r="U2">
-            <v>13.258064516129032</v>
+            <v>8.8181818181818183</v>
           </cell>
           <cell r="V2">
-            <v>9</v>
+            <v>9.6969696969696972</v>
           </cell>
           <cell r="W2">
             <v>0</v>
           </cell>
           <cell r="X2">
-            <v>-3</v>
+            <v>-7</v>
           </cell>
         </row>
         <row r="3">
@@ -8767,7 +8743,7 @@
             <v>Arizona</v>
           </cell>
           <cell r="C3" t="str">
-            <v>Arkansas</v>
+            <v>Purdue</v>
           </cell>
           <cell r="D3">
             <v>23.698276332727119</v>
@@ -8800,37 +8776,37 @@
             <v>0</v>
           </cell>
           <cell r="N3">
-            <v>19.912380875616748</v>
+            <v>20.952342842063047</v>
           </cell>
           <cell r="O3">
-            <v>101.9693472090823</v>
+            <v>102.749921687376</v>
           </cell>
           <cell r="P3">
-            <v>97.560765185917347</v>
+            <v>101.58084764470013</v>
           </cell>
           <cell r="Q3">
-            <v>0.56447688564476883</v>
+            <v>0.5771558245083207</v>
           </cell>
           <cell r="R3">
-            <v>72.41</v>
+            <v>65.197575757575763</v>
           </cell>
           <cell r="S3">
-            <v>64.21875</v>
+            <v>60.090909090909093</v>
           </cell>
           <cell r="T3">
-            <v>23.375</v>
+            <v>16.90909090909091</v>
           </cell>
           <cell r="U3">
-            <v>11.0625</v>
+            <v>11.363636363636363</v>
           </cell>
           <cell r="V3">
-            <v>8.96875</v>
+            <v>9.0303030303030312</v>
           </cell>
           <cell r="W3">
             <v>0</v>
           </cell>
           <cell r="X3">
-            <v>-8</v>
+            <v>-6</v>
           </cell>
         </row>
         <row r="4">
@@ -8838,73 +8814,73 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>Nebraska</v>
+            <v>Duke</v>
           </cell>
           <cell r="C4" t="str">
-            <v>Iowa</v>
+            <v>St. John's</v>
           </cell>
           <cell r="D4">
-            <v>15.832130159542826</v>
+            <v>23.057528028184478</v>
           </cell>
           <cell r="E4">
-            <v>98.25476089716463</v>
+            <v>101.57301127857072</v>
           </cell>
           <cell r="F4">
-            <v>102.36737546035253</v>
+            <v>99.429621355662846</v>
           </cell>
           <cell r="G4">
-            <v>0.55440552016985134</v>
+            <v>0.57213541666666667</v>
           </cell>
           <cell r="H4">
-            <v>66.883750000000006</v>
+            <v>66.278787878787867</v>
           </cell>
           <cell r="I4">
-            <v>58.875</v>
+            <v>58.18181818181818</v>
           </cell>
           <cell r="J4">
-            <v>16</v>
+            <v>22.121212121212121</v>
           </cell>
           <cell r="K4">
-            <v>8.78125</v>
+            <v>12.212121212121213</v>
           </cell>
           <cell r="L4">
-            <v>9.75</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="M4">
             <v>0</v>
           </cell>
           <cell r="N4">
-            <v>15.533956620207105</v>
+            <v>15.127354829706851</v>
           </cell>
           <cell r="O4">
-            <v>98.238539943433466</v>
+            <v>102.62076624097725</v>
           </cell>
           <cell r="P4">
-            <v>93.183243223384508</v>
+            <v>99.083260899694253</v>
           </cell>
           <cell r="Q4">
-            <v>0.56555993247045577</v>
+            <v>0.50957290132547861</v>
           </cell>
           <cell r="R4">
-            <v>62.900606060606066</v>
+            <v>70.527272727272731</v>
           </cell>
           <cell r="S4">
-            <v>53.848484848484851</v>
+            <v>61.727272727272727</v>
           </cell>
           <cell r="T4">
-            <v>18.575757575757574</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="U4">
-            <v>8.8181818181818183</v>
+            <v>13.242424242424242</v>
           </cell>
           <cell r="V4">
-            <v>9.6969696969696972</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="W4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>-1.5</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="5">
@@ -8912,73 +8888,73 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>Purdue</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="C5" t="str">
-            <v>Texas</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="D5">
-            <v>20.952342842063047</v>
+            <v>20.65655264831895</v>
           </cell>
           <cell r="E5">
-            <v>102.749921687376</v>
+            <v>101.50134460238188</v>
           </cell>
           <cell r="F5">
-            <v>101.58084764470013</v>
+            <v>96.966113821111122</v>
           </cell>
           <cell r="G5">
-            <v>0.5771558245083207</v>
+            <v>0.56497313141182215</v>
           </cell>
           <cell r="H5">
-            <v>65.197575757575763</v>
+            <v>67.654117647058825</v>
           </cell>
           <cell r="I5">
-            <v>60.090909090909093</v>
+            <v>60.205882352941174</v>
           </cell>
           <cell r="J5">
-            <v>16.90909090909091</v>
+            <v>20.470588235294116</v>
           </cell>
           <cell r="K5">
-            <v>11.363636363636363</v>
+            <v>11.823529411764707</v>
           </cell>
           <cell r="L5">
-            <v>9.0303030303030312</v>
+            <v>10.264705882352942</v>
           </cell>
           <cell r="M5">
             <v>0</v>
           </cell>
           <cell r="N5">
-            <v>14.540908746576733</v>
+            <v>20.60232878669483</v>
           </cell>
           <cell r="O5">
-            <v>100.55048907489414</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="P5">
-            <v>96.685052394872145</v>
+            <v>93.652390264453544</v>
           </cell>
           <cell r="Q5">
-            <v>0.5496777658431794</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="R5">
-            <v>68.81</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="S5">
-            <v>58.1875</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="T5">
-            <v>26.34375</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="U5">
-            <v>12</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="V5">
-            <v>11.03125</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="W5">
             <v>0</v>
           </cell>
           <cell r="X5">
-            <v>-7</v>
+            <v>-4.5</v>
           </cell>
         </row>
         <row r="6">
@@ -8986,73 +8962,73 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>Duke</v>
+            <v>Uconn</v>
           </cell>
           <cell r="C6" t="str">
-            <v>St. John's</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="D6">
-            <v>23.057528028184478</v>
+            <v>18.116591097400342</v>
           </cell>
           <cell r="E6">
-            <v>101.57301127857072</v>
+            <v>100.0952772073922</v>
           </cell>
           <cell r="F6">
-            <v>99.429621355662846</v>
+            <v>94.276311107817818</v>
           </cell>
           <cell r="G6">
-            <v>0.57213541666666667</v>
+            <v>0.55882352941176472</v>
           </cell>
           <cell r="H6">
-            <v>66.278787878787867</v>
+            <v>66.089696969696973</v>
           </cell>
           <cell r="I6">
-            <v>58.18181818181818</v>
+            <v>58.727272727272727</v>
           </cell>
           <cell r="J6">
-            <v>22.121212121212121</v>
+            <v>17.696969696969695</v>
           </cell>
           <cell r="K6">
-            <v>12.212121212121213</v>
+            <v>11.454545454545455</v>
           </cell>
           <cell r="L6">
-            <v>10.575757575757576</v>
+            <v>11.030303030303031</v>
           </cell>
           <cell r="M6">
             <v>0</v>
           </cell>
           <cell r="N6">
-            <v>15.127354829706851</v>
+            <v>19.991205466978023</v>
           </cell>
           <cell r="O6">
-            <v>102.62076624097725</v>
+            <v>101.32466702184337</v>
           </cell>
           <cell r="P6">
-            <v>99.083260899694253</v>
+            <v>94.593976527502747</v>
           </cell>
           <cell r="Q6">
-            <v>0.50957290132547861</v>
+            <v>0.53589041095890411</v>
           </cell>
           <cell r="R6">
-            <v>70.527272727272731</v>
+            <v>66.620645161290327</v>
           </cell>
           <cell r="S6">
-            <v>61.727272727272727</v>
+            <v>58.87096774193548</v>
           </cell>
           <cell r="T6">
-            <v>26.060606060606062</v>
+            <v>20.838709677419356</v>
           </cell>
           <cell r="U6">
-            <v>13.242424242424242</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="V6">
-            <v>10.575757575757576</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="W6">
             <v>0</v>
           </cell>
           <cell r="X6">
-            <v>-6.5</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="7">
@@ -9060,73 +9036,73 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>Iowa State</v>
+            <v>Michigan</v>
           </cell>
           <cell r="C7" t="str">
-            <v>Tennessee</v>
+            <v>Alabama</v>
           </cell>
           <cell r="D7">
-            <v>20.65655264831895</v>
+            <v>23.168628302235671</v>
           </cell>
           <cell r="E7">
-            <v>101.50134460238188</v>
+            <v>98.200984374253366</v>
           </cell>
           <cell r="F7">
-            <v>96.966113821111122</v>
+            <v>96.398308125131024</v>
           </cell>
           <cell r="G7">
-            <v>0.56497313141182215</v>
+            <v>0.58467532467532468</v>
           </cell>
           <cell r="H7">
-            <v>67.654117647058825</v>
+            <v>71.510000000000005</v>
           </cell>
           <cell r="I7">
-            <v>60.205882352941174</v>
+            <v>60.15625</v>
           </cell>
           <cell r="J7">
-            <v>20.470588235294116</v>
+            <v>23.53125</v>
           </cell>
           <cell r="K7">
-            <v>11.823529411764707</v>
+            <v>11.0625</v>
           </cell>
           <cell r="L7">
-            <v>10.264705882352942</v>
+            <v>12.0625</v>
           </cell>
           <cell r="M7">
             <v>0</v>
           </cell>
           <cell r="N7">
-            <v>20.60232878669483</v>
+            <v>19.656169100501042</v>
           </cell>
           <cell r="O7">
-            <v>105.02195491662999</v>
+            <v>102.29455081001471</v>
           </cell>
           <cell r="P7">
-            <v>93.652390264453544</v>
+            <v>103.73486826442995</v>
           </cell>
           <cell r="Q7">
-            <v>0.51561725334655428</v>
+            <v>0.55384250474383301</v>
           </cell>
           <cell r="R7">
-            <v>67.170909090909092</v>
+            <v>74.217500000000001</v>
           </cell>
           <cell r="S7">
-            <v>61.121212121212125</v>
+            <v>65.875</v>
           </cell>
           <cell r="T7">
-            <v>23.666666666666668</v>
+            <v>24.5</v>
           </cell>
           <cell r="U7">
-            <v>16.030303030303031</v>
+            <v>12.21875</v>
           </cell>
           <cell r="V7">
-            <v>11.666666666666666</v>
+            <v>9.78125</v>
           </cell>
           <cell r="W7">
             <v>0</v>
           </cell>
           <cell r="X7">
-            <v>-4.5</v>
+            <v>-9</v>
           </cell>
         </row>
         <row r="8">
@@ -9134,73 +9110,73 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>Uconn</v>
+            <v>Iowa</v>
           </cell>
           <cell r="C8" t="str">
-            <v>Michigan State</v>
+            <v>Illinois</v>
           </cell>
           <cell r="D8">
-            <v>18.116591097400342</v>
+            <v>15.533956620207105</v>
           </cell>
           <cell r="E8">
-            <v>100.0952772073922</v>
+            <v>98.238539943433466</v>
           </cell>
           <cell r="F8">
-            <v>94.276311107817818</v>
+            <v>93.183243223384508</v>
           </cell>
           <cell r="G8">
-            <v>0.55882352941176472</v>
+            <v>0.56555993247045577</v>
           </cell>
           <cell r="H8">
-            <v>66.089696969696973</v>
+            <v>62.900606060606066</v>
           </cell>
           <cell r="I8">
-            <v>58.727272727272727</v>
+            <v>53.848484848484851</v>
           </cell>
           <cell r="J8">
-            <v>17.696969696969695</v>
+            <v>18.575757575757574</v>
           </cell>
           <cell r="K8">
-            <v>11.454545454545455</v>
+            <v>8.8181818181818183</v>
           </cell>
           <cell r="L8">
-            <v>11.030303030303031</v>
+            <v>9.6969696969696972</v>
           </cell>
           <cell r="M8">
             <v>0</v>
           </cell>
           <cell r="N8">
-            <v>19.991205466978023</v>
+            <v>18.836157720404749</v>
           </cell>
           <cell r="O8">
-            <v>101.32466702184337</v>
+            <v>105.08780903665816</v>
           </cell>
           <cell r="P8">
-            <v>94.593976527502747</v>
+            <v>108.93352999987511</v>
           </cell>
           <cell r="Q8">
-            <v>0.53589041095890411</v>
+            <v>0.5511688311688312</v>
           </cell>
           <cell r="R8">
-            <v>66.620645161290327</v>
+            <v>66.809032258064519</v>
           </cell>
           <cell r="S8">
-            <v>58.87096774193548</v>
+            <v>62.096774193548384</v>
           </cell>
           <cell r="T8">
-            <v>20.838709677419356</v>
+            <v>20.387096774193548</v>
           </cell>
           <cell r="U8">
-            <v>12.774193548387096</v>
+            <v>13.258064516129032</v>
           </cell>
           <cell r="V8">
-            <v>11.35483870967742</v>
+            <v>9</v>
           </cell>
           <cell r="W8">
             <v>0</v>
           </cell>
           <cell r="X8">
-            <v>-2</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="9">
@@ -9208,73 +9184,73 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>Michigan</v>
+            <v>Purdue</v>
           </cell>
           <cell r="C9" t="str">
-            <v>Alabama</v>
+            <v>Arizona</v>
           </cell>
           <cell r="D9">
-            <v>23.168628302235671</v>
+            <v>20.952342842063047</v>
           </cell>
           <cell r="E9">
-            <v>98.200984374253366</v>
+            <v>102.749921687376</v>
           </cell>
           <cell r="F9">
-            <v>96.398308125131024</v>
+            <v>101.58084764470013</v>
           </cell>
           <cell r="G9">
-            <v>0.58467532467532468</v>
+            <v>0.5771558245083207</v>
           </cell>
           <cell r="H9">
-            <v>71.510000000000005</v>
+            <v>65.197575757575763</v>
           </cell>
           <cell r="I9">
-            <v>60.15625</v>
+            <v>60.090909090909093</v>
           </cell>
           <cell r="J9">
-            <v>23.53125</v>
+            <v>16.90909090909091</v>
           </cell>
           <cell r="K9">
-            <v>11.0625</v>
+            <v>11.363636363636363</v>
           </cell>
           <cell r="L9">
-            <v>12.0625</v>
+            <v>9.0303030303030312</v>
           </cell>
           <cell r="M9">
             <v>0</v>
           </cell>
           <cell r="N9">
-            <v>19.656169100501042</v>
+            <v>23.698276332727119</v>
           </cell>
           <cell r="O9">
-            <v>102.29455081001471</v>
+            <v>101.76807841686704</v>
           </cell>
           <cell r="P9">
-            <v>103.73486826442995</v>
+            <v>98.508521311778111</v>
           </cell>
           <cell r="Q9">
-            <v>0.55384250474383301</v>
+            <v>0.55109126984126988</v>
           </cell>
           <cell r="R9">
-            <v>74.217500000000001</v>
+            <v>70.587878787878793</v>
           </cell>
           <cell r="S9">
-            <v>65.875</v>
+            <v>61.090909090909093</v>
           </cell>
           <cell r="T9">
-            <v>24.5</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="U9">
-            <v>12.21875</v>
+            <v>12.878787878787879</v>
           </cell>
           <cell r="V9">
-            <v>9.78125</v>
+            <v>10.909090909090908</v>
           </cell>
           <cell r="W9">
             <v>0</v>
           </cell>
           <cell r="X9">
-            <v>-10</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="10">
@@ -9282,73 +9258,73 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>Illinois</v>
+            <v>St. John's</v>
           </cell>
           <cell r="C10" t="str">
-            <v>Houston</v>
+            <v>Duke</v>
           </cell>
           <cell r="D10">
-            <v>18.836157720404749</v>
+            <v>15.127354829706851</v>
           </cell>
           <cell r="E10">
-            <v>105.08780903665816</v>
+            <v>102.62076624097725</v>
           </cell>
           <cell r="F10">
-            <v>108.93352999987511</v>
+            <v>99.083260899694253</v>
           </cell>
           <cell r="G10">
-            <v>0.5511688311688312</v>
+            <v>0.50957290132547861</v>
           </cell>
           <cell r="H10">
-            <v>66.809032258064519</v>
+            <v>70.527272727272731</v>
           </cell>
           <cell r="I10">
-            <v>62.096774193548384</v>
+            <v>61.727272727272727</v>
           </cell>
           <cell r="J10">
-            <v>20.387096774193548</v>
+            <v>26.060606060606062</v>
           </cell>
           <cell r="K10">
-            <v>13.258064516129032</v>
+            <v>13.242424242424242</v>
           </cell>
           <cell r="L10">
-            <v>9</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="M10">
             <v>0</v>
           </cell>
           <cell r="N10">
-            <v>20.908506008479332</v>
+            <v>23.057528028184478</v>
           </cell>
           <cell r="O10">
-            <v>105.43571389837862</v>
+            <v>101.57301127857072</v>
           </cell>
           <cell r="P10">
-            <v>97.099609428307105</v>
+            <v>99.429621355662846</v>
           </cell>
           <cell r="Q10">
-            <v>0.52154080081094778</v>
+            <v>0.57213541666666667</v>
           </cell>
           <cell r="R10">
-            <v>64.762500000000003</v>
+            <v>66.278787878787867</v>
           </cell>
           <cell r="S10">
-            <v>61.65625</v>
+            <v>58.18181818181818</v>
           </cell>
           <cell r="T10">
-            <v>16.71875</v>
+            <v>22.121212121212121</v>
           </cell>
           <cell r="U10">
-            <v>12.78125</v>
+            <v>12.212121212121213</v>
           </cell>
           <cell r="V10">
-            <v>8.53125</v>
+            <v>10.575757575757576</v>
           </cell>
           <cell r="W10">
             <v>0</v>
           </cell>
           <cell r="X10">
-            <v>3</v>
+            <v>6.5</v>
           </cell>
         </row>
         <row r="11">
@@ -9356,73 +9332,73 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>Texas</v>
+            <v>Tennessee</v>
           </cell>
           <cell r="C11" t="str">
-            <v>Arizona</v>
+            <v>Iowa State</v>
           </cell>
           <cell r="D11">
-            <v>14.540908746576733</v>
+            <v>20.60232878669483</v>
           </cell>
           <cell r="E11">
-            <v>100.55048907489414</v>
+            <v>105.02195491662999</v>
           </cell>
           <cell r="F11">
-            <v>96.685052394872145</v>
+            <v>93.652390264453544</v>
           </cell>
           <cell r="G11">
-            <v>0.5496777658431794</v>
+            <v>0.51561725334655428</v>
           </cell>
           <cell r="H11">
-            <v>68.81</v>
+            <v>67.170909090909092</v>
           </cell>
           <cell r="I11">
-            <v>58.1875</v>
+            <v>61.121212121212125</v>
           </cell>
           <cell r="J11">
-            <v>26.34375</v>
+            <v>23.666666666666668</v>
           </cell>
           <cell r="K11">
-            <v>12</v>
+            <v>16.030303030303031</v>
           </cell>
           <cell r="L11">
-            <v>11.03125</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="M11">
             <v>0</v>
           </cell>
           <cell r="N11">
-            <v>23.698276332727119</v>
+            <v>20.65655264831895</v>
           </cell>
           <cell r="O11">
-            <v>101.76807841686704</v>
+            <v>101.50134460238188</v>
           </cell>
           <cell r="P11">
-            <v>98.508521311778111</v>
+            <v>96.966113821111122</v>
           </cell>
           <cell r="Q11">
-            <v>0.55109126984126988</v>
+            <v>0.56497313141182215</v>
           </cell>
           <cell r="R11">
-            <v>70.587878787878793</v>
+            <v>67.654117647058825</v>
           </cell>
           <cell r="S11">
-            <v>61.090909090909093</v>
+            <v>60.205882352941174</v>
           </cell>
           <cell r="T11">
-            <v>26.060606060606062</v>
+            <v>20.470588235294116</v>
           </cell>
           <cell r="U11">
-            <v>12.878787878787879</v>
+            <v>11.823529411764707</v>
           </cell>
           <cell r="V11">
-            <v>10.909090909090908</v>
+            <v>10.264705882352942</v>
           </cell>
           <cell r="W11">
             <v>0</v>
           </cell>
           <cell r="X11">
-            <v>8</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="12">
@@ -9430,73 +9406,73 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>Iowa</v>
+            <v>Michigan State</v>
           </cell>
           <cell r="C12" t="str">
-            <v>Nebraska</v>
+            <v>Uconn</v>
           </cell>
           <cell r="D12">
-            <v>15.533956620207105</v>
+            <v>19.991205466978023</v>
           </cell>
           <cell r="E12">
-            <v>98.238539943433466</v>
+            <v>101.32466702184337</v>
           </cell>
           <cell r="F12">
-            <v>93.183243223384508</v>
+            <v>94.593976527502747</v>
           </cell>
           <cell r="G12">
-            <v>0.56555993247045577</v>
+            <v>0.53589041095890411</v>
           </cell>
           <cell r="H12">
-            <v>62.900606060606066</v>
+            <v>66.620645161290327</v>
           </cell>
           <cell r="I12">
-            <v>53.848484848484851</v>
+            <v>58.87096774193548</v>
           </cell>
           <cell r="J12">
-            <v>18.575757575757574</v>
+            <v>20.838709677419356</v>
           </cell>
           <cell r="K12">
-            <v>8.8181818181818183</v>
+            <v>12.774193548387096</v>
           </cell>
           <cell r="L12">
-            <v>9.6969696969696972</v>
+            <v>11.35483870967742</v>
           </cell>
           <cell r="M12">
             <v>0</v>
           </cell>
           <cell r="N12">
-            <v>15.832130159542826</v>
+            <v>18.116591097400342</v>
           </cell>
           <cell r="O12">
-            <v>98.25476089716463</v>
+            <v>100.0952772073922</v>
           </cell>
           <cell r="P12">
-            <v>102.36737546035253</v>
+            <v>94.276311107817818</v>
           </cell>
           <cell r="Q12">
-            <v>0.55440552016985134</v>
+            <v>0.55882352941176472</v>
           </cell>
           <cell r="R12">
-            <v>66.883750000000006</v>
+            <v>66.089696969696973</v>
           </cell>
           <cell r="S12">
-            <v>58.875</v>
+            <v>58.727272727272727</v>
           </cell>
           <cell r="T12">
-            <v>16</v>
+            <v>17.696969696969695</v>
           </cell>
           <cell r="U12">
-            <v>8.78125</v>
+            <v>11.454545454545455</v>
           </cell>
           <cell r="V12">
-            <v>9.75</v>
+            <v>11.030303030303031</v>
           </cell>
           <cell r="W12">
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>1.5</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
@@ -9504,370 +9480,3938 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>Arkansas</v>
+            <v>Alabama</v>
           </cell>
           <cell r="C13" t="str">
-            <v>Purdue</v>
+            <v>Michigan</v>
           </cell>
           <cell r="D13">
-            <v>19.912380875616748</v>
+            <v>19.656169100501042</v>
           </cell>
           <cell r="E13">
-            <v>101.9693472090823</v>
+            <v>102.29455081001471</v>
           </cell>
           <cell r="F13">
-            <v>97.560765185917347</v>
+            <v>103.73486826442995</v>
           </cell>
           <cell r="G13">
-            <v>0.56447688564476883</v>
+            <v>0.55384250474383301</v>
           </cell>
           <cell r="H13">
-            <v>72.41</v>
+            <v>74.217500000000001</v>
           </cell>
           <cell r="I13">
-            <v>64.21875</v>
+            <v>65.875</v>
           </cell>
           <cell r="J13">
-            <v>23.375</v>
+            <v>24.5</v>
           </cell>
           <cell r="K13">
+            <v>12.21875</v>
+          </cell>
+          <cell r="L13">
+            <v>9.78125</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>23.168628302235671</v>
+          </cell>
+          <cell r="O13">
+            <v>98.200984374253366</v>
+          </cell>
+          <cell r="P13">
+            <v>96.398308125131024</v>
+          </cell>
+          <cell r="Q13">
+            <v>0.58467532467532468</v>
+          </cell>
+          <cell r="R13">
+            <v>71.510000000000005</v>
+          </cell>
+          <cell r="S13">
+            <v>60.15625</v>
+          </cell>
+          <cell r="T13">
+            <v>23.53125</v>
+          </cell>
+          <cell r="U13">
             <v>11.0625</v>
           </cell>
-          <cell r="L13">
-            <v>8.96875</v>
-          </cell>
-          <cell r="M13">
-            <v>0</v>
-          </cell>
-          <cell r="N13">
-            <v>20.952342842063047</v>
-          </cell>
-          <cell r="O13">
-            <v>102.749921687376</v>
-          </cell>
-          <cell r="P13">
-            <v>101.58084764470013</v>
-          </cell>
-          <cell r="Q13">
-            <v>0.5771558245083207</v>
-          </cell>
-          <cell r="R13">
-            <v>65.197575757575763</v>
-          </cell>
-          <cell r="S13">
-            <v>60.090909090909093</v>
-          </cell>
-          <cell r="T13">
-            <v>16.90909090909091</v>
-          </cell>
-          <cell r="U13">
-            <v>11.363636363636363</v>
-          </cell>
           <cell r="V13">
-            <v>9.0303030303030312</v>
+            <v>12.0625</v>
           </cell>
           <cell r="W13">
             <v>0</v>
           </cell>
           <cell r="X13">
-            <v>7</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="14">
-          <cell r="A14">
-            <v>13</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>St. John's</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>Duke</v>
-          </cell>
-          <cell r="D14">
-            <v>15.127354829706851</v>
-          </cell>
-          <cell r="E14">
-            <v>102.62076624097725</v>
-          </cell>
-          <cell r="F14">
-            <v>99.083260899694253</v>
-          </cell>
-          <cell r="G14">
-            <v>0.50957290132547861</v>
-          </cell>
-          <cell r="H14">
-            <v>70.527272727272731</v>
-          </cell>
-          <cell r="I14">
-            <v>61.727272727272727</v>
-          </cell>
-          <cell r="J14">
-            <v>26.060606060606062</v>
-          </cell>
-          <cell r="K14">
-            <v>13.242424242424242</v>
-          </cell>
-          <cell r="L14">
-            <v>10.575757575757576</v>
-          </cell>
-          <cell r="M14">
-            <v>0</v>
-          </cell>
-          <cell r="N14">
-            <v>23.057528028184478</v>
-          </cell>
-          <cell r="O14">
-            <v>101.57301127857072</v>
-          </cell>
-          <cell r="P14">
-            <v>99.429621355662846</v>
-          </cell>
-          <cell r="Q14">
-            <v>0.57213541666666667</v>
-          </cell>
-          <cell r="R14">
-            <v>66.278787878787867</v>
-          </cell>
-          <cell r="S14">
-            <v>58.18181818181818</v>
-          </cell>
-          <cell r="T14">
-            <v>22.121212121212121</v>
-          </cell>
-          <cell r="U14">
-            <v>12.212121212121213</v>
-          </cell>
-          <cell r="V14">
-            <v>10.575757575757576</v>
-          </cell>
-          <cell r="W14">
-            <v>0</v>
-          </cell>
-          <cell r="X14">
-            <v>6.5</v>
-          </cell>
+          <cell r="D14"/>
+          <cell r="E14"/>
+          <cell r="F14"/>
+          <cell r="G14"/>
+          <cell r="H14"/>
+          <cell r="I14"/>
+          <cell r="J14"/>
+          <cell r="K14"/>
+          <cell r="L14"/>
+          <cell r="M14"/>
+          <cell r="N14"/>
+          <cell r="O14"/>
+          <cell r="P14"/>
+          <cell r="Q14"/>
+          <cell r="R14"/>
+          <cell r="S14"/>
+          <cell r="T14"/>
+          <cell r="U14"/>
+          <cell r="V14"/>
+          <cell r="W14"/>
+          <cell r="X14"/>
         </row>
         <row r="15">
-          <cell r="A15">
-            <v>14</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Tennessee</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>Iowa State</v>
-          </cell>
-          <cell r="D15">
-            <v>20.60232878669483</v>
-          </cell>
-          <cell r="E15">
-            <v>105.02195491662999</v>
-          </cell>
-          <cell r="F15">
-            <v>93.652390264453544</v>
-          </cell>
-          <cell r="G15">
-            <v>0.51561725334655428</v>
-          </cell>
-          <cell r="H15">
-            <v>67.170909090909092</v>
-          </cell>
-          <cell r="I15">
-            <v>61.121212121212125</v>
-          </cell>
-          <cell r="J15">
-            <v>23.666666666666668</v>
-          </cell>
-          <cell r="K15">
-            <v>16.030303030303031</v>
-          </cell>
-          <cell r="L15">
-            <v>11.666666666666666</v>
-          </cell>
-          <cell r="M15">
-            <v>0</v>
-          </cell>
-          <cell r="N15">
-            <v>20.65655264831895</v>
-          </cell>
-          <cell r="O15">
-            <v>101.50134460238188</v>
-          </cell>
-          <cell r="P15">
-            <v>96.966113821111122</v>
-          </cell>
-          <cell r="Q15">
-            <v>0.56497313141182215</v>
-          </cell>
-          <cell r="R15">
-            <v>67.654117647058825</v>
-          </cell>
-          <cell r="S15">
-            <v>60.205882352941174</v>
-          </cell>
-          <cell r="T15">
-            <v>20.470588235294116</v>
-          </cell>
-          <cell r="U15">
-            <v>11.823529411764707</v>
-          </cell>
-          <cell r="V15">
-            <v>10.264705882352942</v>
-          </cell>
-          <cell r="W15">
-            <v>0</v>
-          </cell>
-          <cell r="X15">
-            <v>4.5</v>
-          </cell>
+          <cell r="D15"/>
+          <cell r="E15"/>
+          <cell r="F15"/>
+          <cell r="G15"/>
+          <cell r="H15"/>
+          <cell r="I15"/>
+          <cell r="J15"/>
+          <cell r="K15"/>
+          <cell r="L15"/>
+          <cell r="M15"/>
+          <cell r="N15"/>
+          <cell r="O15"/>
+          <cell r="P15"/>
+          <cell r="Q15"/>
+          <cell r="R15"/>
+          <cell r="S15"/>
+          <cell r="T15"/>
+          <cell r="U15"/>
+          <cell r="V15"/>
+          <cell r="W15"/>
+          <cell r="X15"/>
         </row>
         <row r="16">
-          <cell r="A16">
-            <v>15</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Michigan State</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>Uconn</v>
-          </cell>
-          <cell r="D16">
-            <v>19.991205466978023</v>
-          </cell>
-          <cell r="E16">
-            <v>101.32466702184337</v>
-          </cell>
-          <cell r="F16">
-            <v>94.593976527502747</v>
-          </cell>
-          <cell r="G16">
-            <v>0.53589041095890411</v>
-          </cell>
-          <cell r="H16">
-            <v>66.620645161290327</v>
-          </cell>
-          <cell r="I16">
-            <v>58.87096774193548</v>
-          </cell>
-          <cell r="J16">
-            <v>20.838709677419356</v>
-          </cell>
-          <cell r="K16">
-            <v>12.774193548387096</v>
-          </cell>
-          <cell r="L16">
-            <v>11.35483870967742</v>
-          </cell>
-          <cell r="M16">
-            <v>0</v>
-          </cell>
-          <cell r="N16">
-            <v>18.116591097400342</v>
-          </cell>
-          <cell r="O16">
-            <v>100.0952772073922</v>
-          </cell>
-          <cell r="P16">
-            <v>94.276311107817818</v>
-          </cell>
-          <cell r="Q16">
-            <v>0.55882352941176472</v>
-          </cell>
-          <cell r="R16">
-            <v>66.089696969696973</v>
-          </cell>
-          <cell r="S16">
-            <v>58.727272727272727</v>
-          </cell>
-          <cell r="T16">
-            <v>17.696969696969695</v>
-          </cell>
-          <cell r="U16">
-            <v>11.454545454545455</v>
-          </cell>
-          <cell r="V16">
-            <v>11.030303030303031</v>
-          </cell>
-          <cell r="W16">
-            <v>0</v>
-          </cell>
-          <cell r="X16">
-            <v>2</v>
-          </cell>
+          <cell r="D16"/>
+          <cell r="E16"/>
+          <cell r="F16"/>
+          <cell r="G16"/>
+          <cell r="H16"/>
+          <cell r="I16"/>
+          <cell r="J16"/>
+          <cell r="K16"/>
+          <cell r="L16"/>
+          <cell r="M16"/>
+          <cell r="N16"/>
+          <cell r="O16"/>
+          <cell r="P16"/>
+          <cell r="Q16"/>
+          <cell r="R16"/>
+          <cell r="S16"/>
+          <cell r="T16"/>
+          <cell r="U16"/>
+          <cell r="V16"/>
+          <cell r="W16"/>
+          <cell r="X16"/>
         </row>
         <row r="17">
-          <cell r="A17">
-            <v>16</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>Alabama</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>Michigan</v>
-          </cell>
-          <cell r="D17">
-            <v>19.656169100501042</v>
-          </cell>
-          <cell r="E17">
-            <v>102.29455081001471</v>
-          </cell>
-          <cell r="F17">
-            <v>103.73486826442995</v>
-          </cell>
-          <cell r="G17">
-            <v>0.55384250474383301</v>
-          </cell>
-          <cell r="H17">
-            <v>74.217500000000001</v>
-          </cell>
-          <cell r="I17">
-            <v>65.875</v>
-          </cell>
-          <cell r="J17">
-            <v>24.5</v>
-          </cell>
-          <cell r="K17">
-            <v>12.21875</v>
-          </cell>
-          <cell r="L17">
-            <v>9.78125</v>
-          </cell>
-          <cell r="M17">
-            <v>0</v>
-          </cell>
-          <cell r="N17">
-            <v>23.168628302235671</v>
-          </cell>
-          <cell r="O17">
-            <v>98.200984374253366</v>
-          </cell>
-          <cell r="P17">
-            <v>96.398308125131024</v>
-          </cell>
-          <cell r="Q17">
-            <v>0.58467532467532468</v>
-          </cell>
-          <cell r="R17">
-            <v>71.510000000000005</v>
-          </cell>
-          <cell r="S17">
-            <v>60.15625</v>
-          </cell>
-          <cell r="T17">
-            <v>23.53125</v>
-          </cell>
-          <cell r="U17">
-            <v>11.0625</v>
-          </cell>
-          <cell r="V17">
-            <v>12.0625</v>
-          </cell>
-          <cell r="W17">
-            <v>0</v>
-          </cell>
-          <cell r="X17">
-            <v>10</v>
-          </cell>
+          <cell r="D17"/>
+          <cell r="E17"/>
+          <cell r="F17"/>
+          <cell r="G17"/>
+          <cell r="H17"/>
+          <cell r="I17"/>
+          <cell r="J17"/>
+          <cell r="K17"/>
+          <cell r="L17"/>
+          <cell r="M17"/>
+          <cell r="N17"/>
+          <cell r="O17"/>
+          <cell r="P17"/>
+          <cell r="Q17"/>
+          <cell r="R17"/>
+          <cell r="S17"/>
+          <cell r="T17"/>
+          <cell r="U17"/>
+          <cell r="V17"/>
+          <cell r="W17"/>
+          <cell r="X17"/>
+        </row>
+        <row r="18">
+          <cell r="D18"/>
+          <cell r="E18"/>
+          <cell r="F18"/>
+          <cell r="G18"/>
+          <cell r="H18"/>
+          <cell r="I18"/>
+          <cell r="J18"/>
+          <cell r="K18"/>
+          <cell r="L18"/>
+          <cell r="M18"/>
+          <cell r="N18"/>
+          <cell r="O18"/>
+          <cell r="P18"/>
+          <cell r="Q18"/>
+          <cell r="R18"/>
+          <cell r="S18"/>
+          <cell r="T18"/>
+          <cell r="U18"/>
+          <cell r="V18"/>
+          <cell r="W18"/>
+          <cell r="X18"/>
+        </row>
+        <row r="19">
+          <cell r="D19"/>
+          <cell r="E19"/>
+          <cell r="F19"/>
+          <cell r="G19"/>
+          <cell r="H19"/>
+          <cell r="I19"/>
+          <cell r="J19"/>
+          <cell r="K19"/>
+          <cell r="L19"/>
+          <cell r="M19"/>
+          <cell r="N19"/>
+          <cell r="O19"/>
+          <cell r="P19"/>
+          <cell r="Q19"/>
+          <cell r="R19"/>
+          <cell r="S19"/>
+          <cell r="T19"/>
+          <cell r="U19"/>
+          <cell r="V19"/>
+          <cell r="W19"/>
+          <cell r="X19"/>
+        </row>
+        <row r="20">
+          <cell r="D20"/>
+          <cell r="E20"/>
+          <cell r="F20"/>
+          <cell r="G20"/>
+          <cell r="H20"/>
+          <cell r="I20"/>
+          <cell r="J20"/>
+          <cell r="K20"/>
+          <cell r="L20"/>
+          <cell r="M20"/>
+          <cell r="N20"/>
+          <cell r="O20"/>
+          <cell r="P20"/>
+          <cell r="Q20"/>
+          <cell r="R20"/>
+          <cell r="S20"/>
+          <cell r="T20"/>
+          <cell r="U20"/>
+          <cell r="V20"/>
+          <cell r="W20"/>
+          <cell r="X20"/>
+        </row>
+        <row r="21">
+          <cell r="D21"/>
+          <cell r="E21"/>
+          <cell r="F21"/>
+          <cell r="G21"/>
+          <cell r="H21"/>
+          <cell r="I21"/>
+          <cell r="J21"/>
+          <cell r="K21"/>
+          <cell r="L21"/>
+          <cell r="M21"/>
+          <cell r="N21"/>
+          <cell r="O21"/>
+          <cell r="P21"/>
+          <cell r="Q21"/>
+          <cell r="R21"/>
+          <cell r="S21"/>
+          <cell r="T21"/>
+          <cell r="U21"/>
+          <cell r="V21"/>
+          <cell r="W21"/>
+          <cell r="X21"/>
+        </row>
+        <row r="22">
+          <cell r="D22"/>
+          <cell r="E22"/>
+          <cell r="F22"/>
+          <cell r="G22"/>
+          <cell r="H22"/>
+          <cell r="I22"/>
+          <cell r="J22"/>
+          <cell r="K22"/>
+          <cell r="L22"/>
+          <cell r="M22"/>
+          <cell r="N22"/>
+          <cell r="O22"/>
+          <cell r="P22"/>
+          <cell r="Q22"/>
+          <cell r="R22"/>
+          <cell r="S22"/>
+          <cell r="T22"/>
+          <cell r="U22"/>
+          <cell r="V22"/>
+          <cell r="W22"/>
+          <cell r="X22"/>
+        </row>
+        <row r="23">
+          <cell r="D23"/>
+          <cell r="E23"/>
+          <cell r="F23"/>
+          <cell r="G23"/>
+          <cell r="H23"/>
+          <cell r="I23"/>
+          <cell r="J23"/>
+          <cell r="K23"/>
+          <cell r="L23"/>
+          <cell r="M23"/>
+          <cell r="N23"/>
+          <cell r="O23"/>
+          <cell r="P23"/>
+          <cell r="Q23"/>
+          <cell r="R23"/>
+          <cell r="S23"/>
+          <cell r="T23"/>
+          <cell r="U23"/>
+          <cell r="V23"/>
+          <cell r="W23"/>
+          <cell r="X23"/>
+        </row>
+        <row r="24">
+          <cell r="D24"/>
+          <cell r="E24"/>
+          <cell r="F24"/>
+          <cell r="G24"/>
+          <cell r="H24"/>
+          <cell r="I24"/>
+          <cell r="J24"/>
+          <cell r="K24"/>
+          <cell r="L24"/>
+          <cell r="M24"/>
+          <cell r="N24"/>
+          <cell r="O24"/>
+          <cell r="P24"/>
+          <cell r="Q24"/>
+          <cell r="R24"/>
+          <cell r="S24"/>
+          <cell r="T24"/>
+          <cell r="U24"/>
+          <cell r="V24"/>
+          <cell r="W24"/>
+          <cell r="X24"/>
+        </row>
+        <row r="25">
+          <cell r="D25"/>
+          <cell r="E25"/>
+          <cell r="F25"/>
+          <cell r="G25"/>
+          <cell r="H25"/>
+          <cell r="I25"/>
+          <cell r="J25"/>
+          <cell r="K25"/>
+          <cell r="L25"/>
+          <cell r="M25"/>
+          <cell r="N25"/>
+          <cell r="O25"/>
+          <cell r="P25"/>
+          <cell r="Q25"/>
+          <cell r="R25"/>
+          <cell r="S25"/>
+          <cell r="T25"/>
+          <cell r="U25"/>
+          <cell r="V25"/>
+          <cell r="W25"/>
+          <cell r="X25"/>
+        </row>
+        <row r="26">
+          <cell r="D26"/>
+          <cell r="E26"/>
+          <cell r="F26"/>
+          <cell r="G26"/>
+          <cell r="H26"/>
+          <cell r="I26"/>
+          <cell r="J26"/>
+          <cell r="K26"/>
+          <cell r="L26"/>
+          <cell r="M26"/>
+          <cell r="N26"/>
+          <cell r="O26"/>
+          <cell r="P26"/>
+          <cell r="Q26"/>
+          <cell r="R26"/>
+          <cell r="S26"/>
+          <cell r="T26"/>
+          <cell r="U26"/>
+          <cell r="V26"/>
+          <cell r="W26"/>
+          <cell r="X26"/>
+        </row>
+        <row r="27">
+          <cell r="D27"/>
+          <cell r="E27"/>
+          <cell r="F27"/>
+          <cell r="G27"/>
+          <cell r="H27"/>
+          <cell r="I27"/>
+          <cell r="J27"/>
+          <cell r="K27"/>
+          <cell r="L27"/>
+          <cell r="M27"/>
+          <cell r="N27"/>
+          <cell r="O27"/>
+          <cell r="P27"/>
+          <cell r="Q27"/>
+          <cell r="R27"/>
+          <cell r="S27"/>
+          <cell r="T27"/>
+          <cell r="U27"/>
+          <cell r="V27"/>
+          <cell r="W27"/>
+          <cell r="X27"/>
+        </row>
+        <row r="28">
+          <cell r="D28"/>
+          <cell r="E28"/>
+          <cell r="F28"/>
+          <cell r="G28"/>
+          <cell r="H28"/>
+          <cell r="I28"/>
+          <cell r="J28"/>
+          <cell r="K28"/>
+          <cell r="L28"/>
+          <cell r="M28"/>
+          <cell r="N28"/>
+          <cell r="O28"/>
+          <cell r="P28"/>
+          <cell r="Q28"/>
+          <cell r="R28"/>
+          <cell r="S28"/>
+          <cell r="T28"/>
+          <cell r="U28"/>
+          <cell r="V28"/>
+          <cell r="W28"/>
+          <cell r="X28"/>
+        </row>
+        <row r="29">
+          <cell r="D29"/>
+          <cell r="E29"/>
+          <cell r="F29"/>
+          <cell r="G29"/>
+          <cell r="H29"/>
+          <cell r="I29"/>
+          <cell r="J29"/>
+          <cell r="K29"/>
+          <cell r="L29"/>
+          <cell r="M29"/>
+          <cell r="N29"/>
+          <cell r="O29"/>
+          <cell r="P29"/>
+          <cell r="Q29"/>
+          <cell r="R29"/>
+          <cell r="S29"/>
+          <cell r="T29"/>
+          <cell r="U29"/>
+          <cell r="V29"/>
+          <cell r="W29"/>
+          <cell r="X29"/>
+        </row>
+        <row r="30">
+          <cell r="D30"/>
+          <cell r="E30"/>
+          <cell r="F30"/>
+          <cell r="G30"/>
+          <cell r="H30"/>
+          <cell r="I30"/>
+          <cell r="J30"/>
+          <cell r="K30"/>
+          <cell r="L30"/>
+          <cell r="M30"/>
+          <cell r="N30"/>
+          <cell r="O30"/>
+          <cell r="P30"/>
+          <cell r="Q30"/>
+          <cell r="R30"/>
+          <cell r="S30"/>
+          <cell r="T30"/>
+          <cell r="U30"/>
+          <cell r="V30"/>
+          <cell r="W30"/>
+          <cell r="X30"/>
+        </row>
+        <row r="31">
+          <cell r="D31"/>
+          <cell r="E31"/>
+          <cell r="F31"/>
+          <cell r="G31"/>
+          <cell r="H31"/>
+          <cell r="I31"/>
+          <cell r="J31"/>
+          <cell r="K31"/>
+          <cell r="L31"/>
+          <cell r="M31"/>
+          <cell r="N31"/>
+          <cell r="O31"/>
+          <cell r="P31"/>
+          <cell r="Q31"/>
+          <cell r="R31"/>
+          <cell r="S31"/>
+          <cell r="T31"/>
+          <cell r="U31"/>
+          <cell r="V31"/>
+          <cell r="W31"/>
+          <cell r="X31"/>
+        </row>
+        <row r="32">
+          <cell r="D32"/>
+          <cell r="E32"/>
+          <cell r="F32"/>
+          <cell r="G32"/>
+          <cell r="H32"/>
+          <cell r="I32"/>
+          <cell r="J32"/>
+          <cell r="K32"/>
+          <cell r="L32"/>
+          <cell r="M32"/>
+          <cell r="N32"/>
+          <cell r="O32"/>
+          <cell r="P32"/>
+          <cell r="Q32"/>
+          <cell r="R32"/>
+          <cell r="S32"/>
+          <cell r="T32"/>
+          <cell r="U32"/>
+          <cell r="V32"/>
+          <cell r="W32"/>
+          <cell r="X32"/>
+        </row>
+        <row r="33">
+          <cell r="D33"/>
+          <cell r="E33"/>
+          <cell r="F33"/>
+          <cell r="G33"/>
+          <cell r="H33"/>
+          <cell r="I33"/>
+          <cell r="J33"/>
+          <cell r="K33"/>
+          <cell r="L33"/>
+          <cell r="M33"/>
+          <cell r="N33"/>
+          <cell r="O33"/>
+          <cell r="P33"/>
+          <cell r="Q33"/>
+          <cell r="R33"/>
+          <cell r="S33"/>
+          <cell r="T33"/>
+          <cell r="U33"/>
+          <cell r="V33"/>
+          <cell r="W33"/>
+          <cell r="X33"/>
+        </row>
+        <row r="34">
+          <cell r="D34"/>
+          <cell r="E34"/>
+          <cell r="F34"/>
+          <cell r="G34"/>
+          <cell r="H34"/>
+          <cell r="I34"/>
+          <cell r="J34"/>
+          <cell r="K34"/>
+          <cell r="L34"/>
+          <cell r="M34"/>
+          <cell r="N34"/>
+          <cell r="O34"/>
+          <cell r="P34"/>
+          <cell r="Q34"/>
+          <cell r="R34"/>
+          <cell r="S34"/>
+          <cell r="T34"/>
+          <cell r="U34"/>
+          <cell r="V34"/>
+          <cell r="W34"/>
+          <cell r="X34"/>
+        </row>
+        <row r="35">
+          <cell r="D35"/>
+          <cell r="E35"/>
+          <cell r="F35"/>
+          <cell r="G35"/>
+          <cell r="H35"/>
+          <cell r="I35"/>
+          <cell r="J35"/>
+          <cell r="K35"/>
+          <cell r="L35"/>
+          <cell r="M35"/>
+          <cell r="N35"/>
+          <cell r="O35"/>
+          <cell r="P35"/>
+          <cell r="Q35"/>
+          <cell r="R35"/>
+          <cell r="S35"/>
+          <cell r="T35"/>
+          <cell r="U35"/>
+          <cell r="V35"/>
+          <cell r="W35"/>
+          <cell r="X35"/>
+        </row>
+        <row r="36">
+          <cell r="D36"/>
+          <cell r="E36"/>
+          <cell r="F36"/>
+          <cell r="G36"/>
+          <cell r="H36"/>
+          <cell r="I36"/>
+          <cell r="J36"/>
+          <cell r="K36"/>
+          <cell r="L36"/>
+          <cell r="M36"/>
+          <cell r="N36"/>
+          <cell r="O36"/>
+          <cell r="P36"/>
+          <cell r="Q36"/>
+          <cell r="R36"/>
+          <cell r="S36"/>
+          <cell r="T36"/>
+          <cell r="U36"/>
+          <cell r="V36"/>
+          <cell r="W36"/>
+          <cell r="X36"/>
+        </row>
+        <row r="37">
+          <cell r="D37"/>
+          <cell r="E37"/>
+          <cell r="F37"/>
+          <cell r="G37"/>
+          <cell r="H37"/>
+          <cell r="I37"/>
+          <cell r="J37"/>
+          <cell r="K37"/>
+          <cell r="L37"/>
+          <cell r="M37"/>
+          <cell r="N37"/>
+          <cell r="O37"/>
+          <cell r="P37"/>
+          <cell r="Q37"/>
+          <cell r="R37"/>
+          <cell r="S37"/>
+          <cell r="T37"/>
+          <cell r="U37"/>
+          <cell r="V37"/>
+          <cell r="W37"/>
+          <cell r="X37"/>
+        </row>
+        <row r="38">
+          <cell r="D38"/>
+          <cell r="E38"/>
+          <cell r="F38"/>
+          <cell r="G38"/>
+          <cell r="H38"/>
+          <cell r="I38"/>
+          <cell r="J38"/>
+          <cell r="K38"/>
+          <cell r="L38"/>
+          <cell r="M38"/>
+          <cell r="N38"/>
+          <cell r="O38"/>
+          <cell r="P38"/>
+          <cell r="Q38"/>
+          <cell r="R38"/>
+          <cell r="S38"/>
+          <cell r="T38"/>
+          <cell r="U38"/>
+          <cell r="V38"/>
+          <cell r="W38"/>
+          <cell r="X38"/>
+        </row>
+        <row r="39">
+          <cell r="D39"/>
+          <cell r="E39"/>
+          <cell r="F39"/>
+          <cell r="G39"/>
+          <cell r="H39"/>
+          <cell r="I39"/>
+          <cell r="J39"/>
+          <cell r="K39"/>
+          <cell r="L39"/>
+          <cell r="M39"/>
+          <cell r="N39"/>
+          <cell r="O39"/>
+          <cell r="P39"/>
+          <cell r="Q39"/>
+          <cell r="R39"/>
+          <cell r="S39"/>
+          <cell r="T39"/>
+          <cell r="U39"/>
+          <cell r="V39"/>
+          <cell r="W39"/>
+          <cell r="X39"/>
+        </row>
+        <row r="40">
+          <cell r="D40"/>
+          <cell r="E40"/>
+          <cell r="F40"/>
+          <cell r="G40"/>
+          <cell r="H40"/>
+          <cell r="I40"/>
+          <cell r="J40"/>
+          <cell r="K40"/>
+          <cell r="L40"/>
+          <cell r="M40"/>
+          <cell r="N40"/>
+          <cell r="O40"/>
+          <cell r="P40"/>
+          <cell r="Q40"/>
+          <cell r="R40"/>
+          <cell r="S40"/>
+          <cell r="T40"/>
+          <cell r="U40"/>
+          <cell r="V40"/>
+          <cell r="W40"/>
+   